--- a/Gorev-Listesi.xlsx
+++ b/Gorev-Listesi.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23676" windowHeight="10992" tabRatio="515"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23670" windowHeight="10995" tabRatio="515"/>
   </bookViews>
   <sheets>
     <sheet name="SES SERVİSİ ÇALIŞMA PLANI" sheetId="2" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="101">
   <si>
     <t>CUMA</t>
   </si>
@@ -306,6 +306,27 @@
   </si>
   <si>
     <t>E.SAVAŞ.</t>
+  </si>
+  <si>
+    <t>19.00</t>
+  </si>
+  <si>
+    <t>Çekmeköy</t>
+  </si>
+  <si>
+    <t>M.DİNER.</t>
+  </si>
+  <si>
+    <t>D.YÖNDEM.</t>
+  </si>
+  <si>
+    <t>T.ERDEN.</t>
+  </si>
+  <si>
+    <t>NY TEST / DÜZENLEME</t>
+  </si>
+  <si>
+    <t>Çekmeköy Depo</t>
   </si>
 </sst>
 </file>
@@ -1347,7 +1368,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1500,25 +1521,238 @@
     <xf numFmtId="49" fontId="11" fillId="6" borderId="10" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="10" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="9" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="11" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="12" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="17" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="18" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="9" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="12" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="13" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="14" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="11" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="12" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="13" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="17" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="18" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="19" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="18" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="8" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="9" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="10" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="9" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="12" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="13" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1527,230 +1761,35 @@
     <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="11" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="12" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="40" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="40" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="18" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="14" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="8" borderId="8" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="15" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="8" borderId="9" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="8" borderId="10" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="12" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="13" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="14" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="12" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="13" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="18" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="17" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="18" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="19" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="10" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="11" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="12" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="13" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="9" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="17" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="18" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="58">
@@ -2124,7 +2163,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="1" width="182" row="5" locked="1">
+  <wetp:taskpane dockstate="right" visibility="1" width="350" row="1" locked="1">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -2150,197 +2189,197 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AR133"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.6640625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="2.6640625" style="26" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="26" customWidth="1"/>
-    <col min="4" max="4" width="6.6640625" style="26" customWidth="1"/>
-    <col min="5" max="5" width="1.6640625" style="26" customWidth="1"/>
-    <col min="6" max="6" width="2.6640625" style="26" customWidth="1"/>
-    <col min="7" max="7" width="20.6640625" style="26" customWidth="1"/>
-    <col min="8" max="8" width="6.6640625" style="26" customWidth="1"/>
-    <col min="9" max="9" width="1.6640625" style="26" customWidth="1"/>
-    <col min="10" max="10" width="2.6640625" style="26" customWidth="1"/>
-    <col min="11" max="11" width="20.6640625" style="26" customWidth="1"/>
-    <col min="12" max="12" width="6.6640625" style="26" customWidth="1"/>
-    <col min="13" max="13" width="1.6640625" style="26" customWidth="1"/>
-    <col min="14" max="14" width="2.6640625" customWidth="1"/>
-    <col min="15" max="15" width="20.6640625" customWidth="1"/>
-    <col min="16" max="16" width="6.6640625" customWidth="1"/>
-    <col min="17" max="17" width="1.6640625" customWidth="1"/>
-    <col min="18" max="18" width="2.6640625" customWidth="1"/>
-    <col min="19" max="19" width="20.6640625" customWidth="1"/>
-    <col min="20" max="20" width="6.6640625" customWidth="1"/>
-    <col min="21" max="21" width="1.6640625" customWidth="1"/>
-    <col min="22" max="22" width="2.6640625" customWidth="1"/>
-    <col min="23" max="23" width="20.6640625" customWidth="1"/>
-    <col min="24" max="24" width="6.6640625" customWidth="1"/>
-    <col min="25" max="25" width="1.6640625" customWidth="1"/>
-    <col min="26" max="26" width="2.6640625" customWidth="1"/>
-    <col min="27" max="27" width="20.6640625" customWidth="1"/>
-    <col min="28" max="28" width="6.6640625" customWidth="1"/>
-    <col min="29" max="29" width="1.6640625" customWidth="1"/>
-    <col min="30" max="30" width="2.6640625" customWidth="1"/>
-    <col min="31" max="31" width="20.6640625" customWidth="1"/>
-    <col min="32" max="32" width="6.6640625" customWidth="1"/>
-    <col min="33" max="33" width="1.6640625" customWidth="1"/>
-    <col min="34" max="34" width="2.6640625" customWidth="1"/>
-    <col min="35" max="35" width="20.6640625" customWidth="1"/>
-    <col min="36" max="36" width="6.6640625" customWidth="1"/>
-    <col min="37" max="37" width="1.6640625" customWidth="1"/>
-    <col min="38" max="38" width="2.6640625" customWidth="1"/>
-    <col min="39" max="39" width="20.6640625" customWidth="1"/>
-    <col min="40" max="40" width="6.6640625" customWidth="1"/>
-    <col min="41" max="41" width="2.6640625" customWidth="1"/>
-    <col min="42" max="42" width="16.6640625" customWidth="1"/>
-    <col min="43" max="43" width="3.6640625" customWidth="1"/>
-    <col min="44" max="44" width="8.33203125" customWidth="1"/>
+    <col min="1" max="1" width="1.7109375" style="26" customWidth="1"/>
+    <col min="2" max="2" width="2.7109375" style="26" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" style="26" customWidth="1"/>
+    <col min="4" max="4" width="6.7109375" style="26" customWidth="1"/>
+    <col min="5" max="5" width="1.7109375" style="26" customWidth="1"/>
+    <col min="6" max="6" width="2.7109375" style="26" customWidth="1"/>
+    <col min="7" max="7" width="20.7109375" style="26" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="26" customWidth="1"/>
+    <col min="9" max="9" width="1.7109375" style="26" customWidth="1"/>
+    <col min="10" max="10" width="2.7109375" style="26" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" style="26" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" style="26" customWidth="1"/>
+    <col min="13" max="13" width="1.7109375" style="26" customWidth="1"/>
+    <col min="14" max="14" width="2.7109375" customWidth="1"/>
+    <col min="15" max="15" width="20.7109375" customWidth="1"/>
+    <col min="16" max="16" width="6.7109375" customWidth="1"/>
+    <col min="17" max="17" width="1.7109375" customWidth="1"/>
+    <col min="18" max="18" width="2.7109375" customWidth="1"/>
+    <col min="19" max="19" width="20.7109375" customWidth="1"/>
+    <col min="20" max="20" width="6.7109375" customWidth="1"/>
+    <col min="21" max="21" width="1.7109375" customWidth="1"/>
+    <col min="22" max="22" width="2.7109375" customWidth="1"/>
+    <col min="23" max="23" width="20.7109375" customWidth="1"/>
+    <col min="24" max="24" width="6.7109375" customWidth="1"/>
+    <col min="25" max="25" width="1.7109375" customWidth="1"/>
+    <col min="26" max="26" width="2.7109375" customWidth="1"/>
+    <col min="27" max="27" width="20.7109375" customWidth="1"/>
+    <col min="28" max="28" width="6.7109375" customWidth="1"/>
+    <col min="29" max="29" width="1.7109375" customWidth="1"/>
+    <col min="30" max="30" width="2.7109375" customWidth="1"/>
+    <col min="31" max="31" width="20.7109375" customWidth="1"/>
+    <col min="32" max="32" width="6.7109375" customWidth="1"/>
+    <col min="33" max="33" width="1.7109375" customWidth="1"/>
+    <col min="34" max="34" width="2.7109375" customWidth="1"/>
+    <col min="35" max="35" width="20.7109375" customWidth="1"/>
+    <col min="36" max="36" width="6.7109375" customWidth="1"/>
+    <col min="37" max="37" width="1.7109375" customWidth="1"/>
+    <col min="38" max="38" width="2.7109375" customWidth="1"/>
+    <col min="39" max="39" width="20.7109375" customWidth="1"/>
+    <col min="40" max="40" width="6.7109375" customWidth="1"/>
+    <col min="41" max="41" width="2.7109375" customWidth="1"/>
+    <col min="42" max="42" width="16.7109375" customWidth="1"/>
+    <col min="43" max="43" width="3.7109375" customWidth="1"/>
+    <col min="44" max="44" width="8.28515625" customWidth="1"/>
     <col min="45" max="48" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12"/>
-      <c r="B1" s="97" t="s">
+      <c r="B1" s="127" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
       <c r="E1" s="10"/>
-      <c r="F1" s="98" t="s">
+      <c r="F1" s="128" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="98"/>
-      <c r="H1" s="98"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
       <c r="I1" s="10"/>
-      <c r="J1" s="98" t="s">
+      <c r="J1" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="98"/>
-      <c r="L1" s="99"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="129"/>
       <c r="M1" s="12"/>
-      <c r="N1" s="102" t="s">
+      <c r="N1" s="132" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="96"/>
-      <c r="P1" s="96"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="96" t="s">
+      <c r="R1" s="122" t="s">
         <v>4</v>
       </c>
-      <c r="S1" s="96"/>
-      <c r="T1" s="96"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="96" t="s">
+      <c r="V1" s="122" t="s">
         <v>5</v>
       </c>
-      <c r="W1" s="96"/>
-      <c r="X1" s="96"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="96" t="s">
+      <c r="Z1" s="122" t="s">
         <v>6</v>
       </c>
-      <c r="AA1" s="96"/>
-      <c r="AB1" s="96"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="1"/>
-      <c r="AD1" s="96" t="s">
+      <c r="AD1" s="122" t="s">
         <v>0</v>
       </c>
-      <c r="AE1" s="96"/>
-      <c r="AF1" s="96"/>
+      <c r="AE1" s="122"/>
+      <c r="AF1" s="122"/>
       <c r="AG1" s="1"/>
-      <c r="AH1" s="96" t="s">
+      <c r="AH1" s="122" t="s">
         <v>1</v>
       </c>
-      <c r="AI1" s="96"/>
-      <c r="AJ1" s="96"/>
+      <c r="AI1" s="122"/>
+      <c r="AJ1" s="122"/>
       <c r="AK1" s="1"/>
-      <c r="AL1" s="96" t="s">
+      <c r="AL1" s="122" t="s">
         <v>2</v>
       </c>
-      <c r="AM1" s="96"/>
-      <c r="AN1" s="106"/>
+      <c r="AM1" s="122"/>
+      <c r="AN1" s="123"/>
       <c r="AO1" s="12"/>
       <c r="AP1" s="12"/>
       <c r="AQ1" s="12"/>
       <c r="AR1" s="13"/>
     </row>
-    <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
-      <c r="B2" s="100">
+      <c r="B2" s="130">
         <f>N2-3</f>
         <v>46276</v>
       </c>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="131"/>
       <c r="E2" s="11"/>
-      <c r="F2" s="101">
+      <c r="F2" s="131">
         <f>N2-2</f>
         <v>46277</v>
       </c>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
+      <c r="G2" s="131"/>
+      <c r="H2" s="131"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="101">
+      <c r="J2" s="131">
         <f>N2-1</f>
         <v>46278</v>
       </c>
-      <c r="K2" s="101"/>
-      <c r="L2" s="104"/>
+      <c r="K2" s="131"/>
+      <c r="L2" s="134"/>
       <c r="M2" s="12"/>
-      <c r="N2" s="103">
+      <c r="N2" s="133">
         <v>46279</v>
       </c>
-      <c r="O2" s="95"/>
-      <c r="P2" s="95"/>
+      <c r="O2" s="124"/>
+      <c r="P2" s="124"/>
       <c r="Q2" s="53"/>
-      <c r="R2" s="95">
+      <c r="R2" s="124">
         <f>N2+1</f>
         <v>46280</v>
       </c>
-      <c r="S2" s="95"/>
-      <c r="T2" s="95"/>
+      <c r="S2" s="124"/>
+      <c r="T2" s="124"/>
       <c r="U2" s="53"/>
-      <c r="V2" s="95">
+      <c r="V2" s="124">
         <f>N2+2</f>
         <v>46281</v>
       </c>
-      <c r="W2" s="95"/>
-      <c r="X2" s="95"/>
+      <c r="W2" s="124"/>
+      <c r="X2" s="124"/>
       <c r="Y2" s="53"/>
-      <c r="Z2" s="95">
+      <c r="Z2" s="124">
         <f>N2+3</f>
         <v>46282</v>
       </c>
-      <c r="AA2" s="95"/>
-      <c r="AB2" s="95"/>
+      <c r="AA2" s="124"/>
+      <c r="AB2" s="124"/>
       <c r="AC2" s="53"/>
-      <c r="AD2" s="95">
+      <c r="AD2" s="124">
         <f>N2+4</f>
         <v>46283</v>
       </c>
-      <c r="AE2" s="95"/>
-      <c r="AF2" s="95"/>
+      <c r="AE2" s="124"/>
+      <c r="AF2" s="124"/>
       <c r="AG2" s="53"/>
-      <c r="AH2" s="95">
+      <c r="AH2" s="124">
         <f>N2+5</f>
         <v>46284</v>
       </c>
-      <c r="AI2" s="95"/>
-      <c r="AJ2" s="95"/>
+      <c r="AI2" s="124"/>
+      <c r="AJ2" s="124"/>
       <c r="AK2" s="53"/>
-      <c r="AL2" s="95">
+      <c r="AL2" s="124">
         <f>N2+6</f>
         <v>46285</v>
       </c>
-      <c r="AM2" s="95"/>
-      <c r="AN2" s="107"/>
+      <c r="AM2" s="124"/>
+      <c r="AN2" s="125"/>
       <c r="AO2" s="12"/>
       <c r="AP2" s="12"/>
       <c r="AQ2" s="12"/>
       <c r="AR2" s="13"/>
     </row>
-    <row r="3" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="12"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -2386,145 +2425,145 @@
       <c r="AQ3" s="12"/>
       <c r="AR3" s="13"/>
     </row>
-    <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="12"/>
-      <c r="B4" s="105"/>
-      <c r="C4" s="105"/>
-      <c r="D4" s="105"/>
-      <c r="E4" s="105"/>
-      <c r="F4" s="105"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="105"/>
-      <c r="I4" s="105"/>
-      <c r="J4" s="105"/>
-      <c r="K4" s="105"/>
-      <c r="L4" s="105"/>
+      <c r="B4" s="126"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="126"/>
+      <c r="E4" s="126"/>
+      <c r="F4" s="126"/>
+      <c r="G4" s="126"/>
+      <c r="H4" s="126"/>
+      <c r="I4" s="126"/>
+      <c r="J4" s="126"/>
+      <c r="K4" s="126"/>
+      <c r="L4" s="126"/>
       <c r="M4" s="14"/>
-      <c r="N4" s="88" t="s">
+      <c r="N4" s="110" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="88"/>
-      <c r="W4" s="88"/>
-      <c r="X4" s="88"/>
-      <c r="Y4" s="88"/>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
-      <c r="AB4" s="88"/>
+      <c r="O4" s="110"/>
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110"/>
+      <c r="S4" s="110"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="110"/>
+      <c r="V4" s="110"/>
+      <c r="W4" s="110"/>
+      <c r="X4" s="110"/>
+      <c r="Y4" s="110"/>
+      <c r="Z4" s="110"/>
+      <c r="AA4" s="110"/>
+      <c r="AB4" s="110"/>
       <c r="AC4" s="33"/>
-      <c r="AD4" s="105"/>
-      <c r="AE4" s="105"/>
-      <c r="AF4" s="105"/>
-      <c r="AG4" s="105"/>
-      <c r="AH4" s="105"/>
-      <c r="AI4" s="105"/>
-      <c r="AJ4" s="105"/>
-      <c r="AK4" s="105"/>
-      <c r="AL4" s="105"/>
-      <c r="AM4" s="105"/>
-      <c r="AN4" s="105"/>
+      <c r="AD4" s="126"/>
+      <c r="AE4" s="126"/>
+      <c r="AF4" s="126"/>
+      <c r="AG4" s="126"/>
+      <c r="AH4" s="126"/>
+      <c r="AI4" s="126"/>
+      <c r="AJ4" s="126"/>
+      <c r="AK4" s="126"/>
+      <c r="AL4" s="126"/>
+      <c r="AM4" s="126"/>
+      <c r="AN4" s="126"/>
       <c r="AO4" s="12"/>
       <c r="AP4" s="12"/>
       <c r="AQ4" s="12"/>
       <c r="AR4" s="13"/>
     </row>
-    <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12"/>
-      <c r="B5" s="105"/>
-      <c r="C5" s="105"/>
-      <c r="D5" s="105"/>
-      <c r="E5" s="105"/>
-      <c r="F5" s="105"/>
-      <c r="G5" s="105"/>
-      <c r="H5" s="105"/>
-      <c r="I5" s="105"/>
-      <c r="J5" s="105"/>
-      <c r="K5" s="105"/>
-      <c r="L5" s="105"/>
+      <c r="B5" s="126"/>
+      <c r="C5" s="126"/>
+      <c r="D5" s="126"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="126"/>
+      <c r="K5" s="126"/>
+      <c r="L5" s="126"/>
       <c r="M5" s="14"/>
-      <c r="N5" s="88"/>
-      <c r="O5" s="88"/>
-      <c r="P5" s="88"/>
-      <c r="Q5" s="88"/>
-      <c r="R5" s="88"/>
-      <c r="S5" s="88"/>
-      <c r="T5" s="88"/>
-      <c r="U5" s="88"/>
-      <c r="V5" s="88"/>
-      <c r="W5" s="88"/>
-      <c r="X5" s="88"/>
-      <c r="Y5" s="88"/>
-      <c r="Z5" s="88"/>
-      <c r="AA5" s="88"/>
-      <c r="AB5" s="88"/>
+      <c r="N5" s="110"/>
+      <c r="O5" s="110"/>
+      <c r="P5" s="110"/>
+      <c r="Q5" s="110"/>
+      <c r="R5" s="110"/>
+      <c r="S5" s="110"/>
+      <c r="T5" s="110"/>
+      <c r="U5" s="110"/>
+      <c r="V5" s="110"/>
+      <c r="W5" s="110"/>
+      <c r="X5" s="110"/>
+      <c r="Y5" s="110"/>
+      <c r="Z5" s="110"/>
+      <c r="AA5" s="110"/>
+      <c r="AB5" s="110"/>
       <c r="AC5" s="33"/>
-      <c r="AD5" s="105"/>
-      <c r="AE5" s="105"/>
-      <c r="AF5" s="105"/>
-      <c r="AG5" s="105"/>
-      <c r="AH5" s="105"/>
-      <c r="AI5" s="105"/>
-      <c r="AJ5" s="105"/>
-      <c r="AK5" s="105"/>
-      <c r="AL5" s="105"/>
-      <c r="AM5" s="105"/>
-      <c r="AN5" s="105"/>
+      <c r="AD5" s="126"/>
+      <c r="AE5" s="126"/>
+      <c r="AF5" s="126"/>
+      <c r="AG5" s="126"/>
+      <c r="AH5" s="126"/>
+      <c r="AI5" s="126"/>
+      <c r="AJ5" s="126"/>
+      <c r="AK5" s="126"/>
+      <c r="AL5" s="126"/>
+      <c r="AM5" s="126"/>
+      <c r="AN5" s="126"/>
       <c r="AO5" s="12"/>
       <c r="AP5" s="12"/>
       <c r="AQ5" s="12"/>
       <c r="AR5" s="13"/>
     </row>
-    <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="114"/>
-      <c r="C6" s="115"/>
+    <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="65"/>
+      <c r="C6" s="66"/>
       <c r="D6" s="57"/>
       <c r="E6" s="39"/>
-      <c r="F6" s="114"/>
-      <c r="G6" s="115"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
       <c r="H6" s="57"/>
       <c r="I6" s="36"/>
-      <c r="J6" s="114"/>
-      <c r="K6" s="115"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
       <c r="L6" s="57"/>
       <c r="M6" s="3"/>
-      <c r="N6" s="65"/>
-      <c r="O6" s="66"/>
+      <c r="N6" s="67"/>
+      <c r="O6" s="68"/>
       <c r="P6" s="34"/>
       <c r="Q6" s="39"/>
-      <c r="R6" s="65"/>
-      <c r="S6" s="66"/>
+      <c r="R6" s="67"/>
+      <c r="S6" s="68"/>
       <c r="T6" s="34"/>
       <c r="U6" s="36"/>
-      <c r="V6" s="65"/>
-      <c r="W6" s="66"/>
+      <c r="V6" s="67"/>
+      <c r="W6" s="68"/>
       <c r="X6" s="34"/>
       <c r="Y6" s="23"/>
-      <c r="Z6" s="65"/>
-      <c r="AA6" s="66"/>
+      <c r="Z6" s="67"/>
+      <c r="AA6" s="68"/>
       <c r="AB6" s="34"/>
       <c r="AC6" s="36"/>
-      <c r="AD6" s="65"/>
-      <c r="AE6" s="66"/>
+      <c r="AD6" s="67"/>
+      <c r="AE6" s="68"/>
       <c r="AF6" s="34"/>
       <c r="AG6" s="39"/>
-      <c r="AH6" s="65" t="s">
+      <c r="AH6" s="67" t="s">
         <v>77</v>
       </c>
-      <c r="AI6" s="66"/>
+      <c r="AI6" s="68"/>
       <c r="AJ6" s="34" t="s">
         <v>68</v>
       </c>
       <c r="AK6" s="36"/>
-      <c r="AL6" s="65" t="s">
+      <c r="AL6" s="67" t="s">
         <v>77</v>
       </c>
-      <c r="AM6" s="66"/>
+      <c r="AM6" s="68"/>
       <c r="AN6" s="34" t="s">
         <v>68</v>
       </c>
@@ -2537,45 +2576,45 @@
       </c>
       <c r="AR6" s="30"/>
     </row>
-    <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="116"/>
-      <c r="C7" s="117"/>
-      <c r="D7" s="143"/>
+    <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="90"/>
+      <c r="C7" s="91"/>
+      <c r="D7" s="61"/>
       <c r="E7" s="38"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="117"/>
-      <c r="H7" s="143"/>
+      <c r="F7" s="90"/>
+      <c r="G7" s="91"/>
+      <c r="H7" s="61"/>
       <c r="I7" s="36"/>
-      <c r="J7" s="116"/>
-      <c r="K7" s="117"/>
-      <c r="L7" s="143"/>
+      <c r="J7" s="90"/>
+      <c r="K7" s="91"/>
+      <c r="L7" s="61"/>
       <c r="M7" s="3"/>
-      <c r="N7" s="75"/>
-      <c r="O7" s="76"/>
+      <c r="N7" s="81"/>
+      <c r="O7" s="82"/>
       <c r="P7" s="18"/>
       <c r="Q7" s="36"/>
-      <c r="R7" s="75"/>
-      <c r="S7" s="76"/>
+      <c r="R7" s="81"/>
+      <c r="S7" s="82"/>
       <c r="T7" s="18"/>
       <c r="U7" s="36"/>
-      <c r="V7" s="75"/>
-      <c r="W7" s="76"/>
+      <c r="V7" s="81"/>
+      <c r="W7" s="82"/>
       <c r="X7" s="18"/>
       <c r="Y7" s="36"/>
-      <c r="Z7" s="75"/>
-      <c r="AA7" s="76"/>
+      <c r="Z7" s="81"/>
+      <c r="AA7" s="82"/>
       <c r="AB7" s="18"/>
       <c r="AC7" s="36"/>
-      <c r="AD7" s="75"/>
-      <c r="AE7" s="76"/>
+      <c r="AD7" s="81"/>
+      <c r="AE7" s="82"/>
       <c r="AF7" s="18"/>
       <c r="AG7" s="38"/>
-      <c r="AH7" s="75"/>
-      <c r="AI7" s="76"/>
+      <c r="AH7" s="81"/>
+      <c r="AI7" s="82"/>
       <c r="AJ7" s="18"/>
       <c r="AK7" s="36"/>
-      <c r="AL7" s="75"/>
-      <c r="AM7" s="76"/>
+      <c r="AL7" s="81"/>
+      <c r="AM7" s="82"/>
       <c r="AN7" s="18"/>
       <c r="AP7" s="46" t="s">
         <v>9</v>
@@ -2586,50 +2625,50 @@
       </c>
       <c r="AR7" s="30"/>
     </row>
-    <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="78"/>
-      <c r="C8" s="79"/>
-      <c r="D8" s="80"/>
+    <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="87"/>
+      <c r="C8" s="88"/>
+      <c r="D8" s="89"/>
       <c r="E8" s="35"/>
-      <c r="F8" s="78"/>
-      <c r="G8" s="79"/>
-      <c r="H8" s="80"/>
+      <c r="F8" s="87"/>
+      <c r="G8" s="88"/>
+      <c r="H8" s="89"/>
       <c r="I8" s="37"/>
-      <c r="J8" s="78"/>
-      <c r="K8" s="79"/>
-      <c r="L8" s="80"/>
+      <c r="J8" s="87"/>
+      <c r="K8" s="88"/>
+      <c r="L8" s="89"/>
       <c r="M8" s="3"/>
-      <c r="N8" s="78"/>
-      <c r="O8" s="79"/>
-      <c r="P8" s="80"/>
+      <c r="N8" s="87"/>
+      <c r="O8" s="88"/>
+      <c r="P8" s="89"/>
       <c r="Q8" s="35"/>
-      <c r="R8" s="78"/>
-      <c r="S8" s="79"/>
-      <c r="T8" s="80"/>
+      <c r="R8" s="87"/>
+      <c r="S8" s="88"/>
+      <c r="T8" s="89"/>
       <c r="U8" s="37"/>
-      <c r="V8" s="78"/>
-      <c r="W8" s="79"/>
-      <c r="X8" s="80"/>
+      <c r="V8" s="87"/>
+      <c r="W8" s="88"/>
+      <c r="X8" s="89"/>
       <c r="Y8" s="35"/>
-      <c r="Z8" s="78"/>
-      <c r="AA8" s="79"/>
-      <c r="AB8" s="80"/>
+      <c r="Z8" s="87"/>
+      <c r="AA8" s="88"/>
+      <c r="AB8" s="89"/>
       <c r="AC8" s="35"/>
-      <c r="AD8" s="78"/>
-      <c r="AE8" s="79"/>
-      <c r="AF8" s="80"/>
+      <c r="AD8" s="87"/>
+      <c r="AE8" s="88"/>
+      <c r="AF8" s="89"/>
       <c r="AG8" s="35"/>
-      <c r="AH8" s="108" t="s">
+      <c r="AH8" s="115" t="s">
         <v>85</v>
       </c>
-      <c r="AI8" s="109"/>
-      <c r="AJ8" s="110"/>
+      <c r="AI8" s="116"/>
+      <c r="AJ8" s="117"/>
       <c r="AK8" s="37"/>
-      <c r="AL8" s="78" t="s">
+      <c r="AL8" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="AM8" s="79"/>
-      <c r="AN8" s="80"/>
+      <c r="AM8" s="88"/>
+      <c r="AN8" s="89"/>
       <c r="AP8" s="46" t="s">
         <v>16</v>
       </c>
@@ -2639,48 +2678,48 @@
       </c>
       <c r="AR8" s="30"/>
     </row>
-    <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="72"/>
-      <c r="C9" s="73"/>
-      <c r="D9" s="74"/>
+    <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="78"/>
+      <c r="C9" s="79"/>
+      <c r="D9" s="80"/>
       <c r="E9" s="43"/>
-      <c r="F9" s="72"/>
-      <c r="G9" s="73"/>
-      <c r="H9" s="74"/>
+      <c r="F9" s="78"/>
+      <c r="G9" s="79"/>
+      <c r="H9" s="80"/>
       <c r="I9" s="43"/>
-      <c r="J9" s="72"/>
-      <c r="K9" s="73"/>
-      <c r="L9" s="74"/>
+      <c r="J9" s="78"/>
+      <c r="K9" s="79"/>
+      <c r="L9" s="80"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="72"/>
-      <c r="O9" s="73"/>
-      <c r="P9" s="74"/>
+      <c r="N9" s="78"/>
+      <c r="O9" s="79"/>
+      <c r="P9" s="80"/>
       <c r="Q9" s="43"/>
-      <c r="R9" s="72"/>
-      <c r="S9" s="73"/>
-      <c r="T9" s="74"/>
+      <c r="R9" s="78"/>
+      <c r="S9" s="79"/>
+      <c r="T9" s="80"/>
       <c r="U9" s="44"/>
-      <c r="V9" s="72"/>
-      <c r="W9" s="73"/>
-      <c r="X9" s="74"/>
+      <c r="V9" s="78"/>
+      <c r="W9" s="79"/>
+      <c r="X9" s="80"/>
       <c r="Y9" s="43"/>
-      <c r="Z9" s="72"/>
-      <c r="AA9" s="73"/>
-      <c r="AB9" s="74"/>
+      <c r="Z9" s="78"/>
+      <c r="AA9" s="79"/>
+      <c r="AB9" s="80"/>
       <c r="AC9" s="43"/>
-      <c r="AD9" s="72"/>
-      <c r="AE9" s="73"/>
-      <c r="AF9" s="74"/>
+      <c r="AD9" s="78"/>
+      <c r="AE9" s="79"/>
+      <c r="AF9" s="80"/>
       <c r="AG9" s="43"/>
-      <c r="AH9" s="72"/>
-      <c r="AI9" s="73"/>
-      <c r="AJ9" s="74"/>
+      <c r="AH9" s="78"/>
+      <c r="AI9" s="79"/>
+      <c r="AJ9" s="80"/>
       <c r="AK9" s="43"/>
-      <c r="AL9" s="72" t="s">
+      <c r="AL9" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="AM9" s="73"/>
-      <c r="AN9" s="74"/>
+      <c r="AM9" s="79"/>
+      <c r="AN9" s="80"/>
       <c r="AP9" s="46" t="s">
         <v>11</v>
       </c>
@@ -2690,46 +2729,46 @@
       </c>
       <c r="AR9" s="30"/>
     </row>
-    <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="81"/>
-      <c r="C10" s="82"/>
-      <c r="D10" s="83"/>
+    <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="107"/>
+      <c r="C10" s="108"/>
+      <c r="D10" s="109"/>
       <c r="E10" s="44"/>
-      <c r="F10" s="81"/>
-      <c r="G10" s="82"/>
-      <c r="H10" s="83"/>
+      <c r="F10" s="107"/>
+      <c r="G10" s="108"/>
+      <c r="H10" s="109"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="81"/>
-      <c r="K10" s="82"/>
-      <c r="L10" s="83"/>
+      <c r="J10" s="107"/>
+      <c r="K10" s="108"/>
+      <c r="L10" s="109"/>
       <c r="M10" s="5"/>
-      <c r="N10" s="81"/>
-      <c r="O10" s="82"/>
-      <c r="P10" s="83"/>
+      <c r="N10" s="107"/>
+      <c r="O10" s="108"/>
+      <c r="P10" s="109"/>
       <c r="Q10" s="44"/>
-      <c r="R10" s="81"/>
-      <c r="S10" s="82"/>
-      <c r="T10" s="83"/>
+      <c r="R10" s="107"/>
+      <c r="S10" s="108"/>
+      <c r="T10" s="109"/>
       <c r="U10" s="44"/>
-      <c r="V10" s="81"/>
-      <c r="W10" s="82"/>
-      <c r="X10" s="83"/>
+      <c r="V10" s="107"/>
+      <c r="W10" s="108"/>
+      <c r="X10" s="109"/>
       <c r="Y10" s="44"/>
-      <c r="Z10" s="81"/>
-      <c r="AA10" s="82"/>
-      <c r="AB10" s="83"/>
+      <c r="Z10" s="107"/>
+      <c r="AA10" s="108"/>
+      <c r="AB10" s="109"/>
       <c r="AC10" s="44"/>
-      <c r="AD10" s="81"/>
-      <c r="AE10" s="82"/>
-      <c r="AF10" s="83"/>
+      <c r="AD10" s="107"/>
+      <c r="AE10" s="108"/>
+      <c r="AF10" s="109"/>
       <c r="AG10" s="44"/>
-      <c r="AH10" s="81"/>
-      <c r="AI10" s="82"/>
-      <c r="AJ10" s="83"/>
+      <c r="AH10" s="107"/>
+      <c r="AI10" s="108"/>
+      <c r="AJ10" s="109"/>
       <c r="AK10" s="44"/>
-      <c r="AL10" s="81"/>
-      <c r="AM10" s="82"/>
-      <c r="AN10" s="83"/>
+      <c r="AL10" s="107"/>
+      <c r="AM10" s="108"/>
+      <c r="AN10" s="109"/>
       <c r="AP10" s="46" t="s">
         <v>8</v>
       </c>
@@ -2739,7 +2778,7 @@
       </c>
       <c r="AR10" s="30"/>
     </row>
-    <row r="11" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="33"/>
       <c r="C11" s="33"/>
       <c r="D11" s="33"/>
@@ -2790,53 +2829,53 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="114"/>
-      <c r="C12" s="115"/>
+    <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="65"/>
+      <c r="C12" s="66"/>
       <c r="D12" s="57"/>
       <c r="E12" s="39"/>
-      <c r="F12" s="93" t="s">
+      <c r="F12" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="94"/>
+      <c r="G12" s="112"/>
       <c r="H12" s="59" t="s">
         <v>69</v>
       </c>
       <c r="I12" s="36"/>
-      <c r="J12" s="114"/>
-      <c r="K12" s="115"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="66"/>
       <c r="L12" s="57"/>
       <c r="M12" s="5"/>
-      <c r="N12" s="65"/>
-      <c r="O12" s="66"/>
+      <c r="N12" s="67"/>
+      <c r="O12" s="68"/>
       <c r="P12" s="34"/>
       <c r="Q12" s="23"/>
-      <c r="R12" s="65"/>
-      <c r="S12" s="66"/>
+      <c r="R12" s="67"/>
+      <c r="S12" s="68"/>
       <c r="T12" s="34"/>
       <c r="U12" s="36"/>
-      <c r="V12" s="65"/>
-      <c r="W12" s="66"/>
+      <c r="V12" s="67"/>
+      <c r="W12" s="68"/>
       <c r="X12" s="34"/>
       <c r="Y12" s="23"/>
-      <c r="Z12" s="65"/>
-      <c r="AA12" s="66"/>
+      <c r="Z12" s="67"/>
+      <c r="AA12" s="68"/>
       <c r="AB12" s="34"/>
       <c r="AC12" s="36"/>
-      <c r="AD12" s="65"/>
-      <c r="AE12" s="66"/>
+      <c r="AD12" s="67"/>
+      <c r="AE12" s="68"/>
       <c r="AF12" s="34"/>
       <c r="AG12" s="39"/>
-      <c r="AH12" s="65" t="s">
+      <c r="AH12" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="AI12" s="66"/>
+      <c r="AI12" s="68"/>
       <c r="AJ12" s="34" t="s">
         <v>57</v>
       </c>
       <c r="AK12" s="36"/>
-      <c r="AL12" s="65"/>
-      <c r="AM12" s="66"/>
+      <c r="AL12" s="67"/>
+      <c r="AM12" s="68"/>
       <c r="AN12" s="34"/>
       <c r="AP12" s="46" t="s">
         <v>19</v>
@@ -2847,103 +2886,103 @@
       </c>
       <c r="AR12" s="30"/>
     </row>
-    <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="116"/>
-      <c r="C13" s="117"/>
-      <c r="D13" s="143"/>
+    <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="90"/>
+      <c r="C13" s="91"/>
+      <c r="D13" s="61"/>
       <c r="E13" s="38"/>
-      <c r="F13" s="116" t="s">
+      <c r="F13" s="90" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="117"/>
-      <c r="H13" s="143" t="s">
+      <c r="G13" s="91"/>
+      <c r="H13" s="61" t="s">
         <v>57</v>
       </c>
       <c r="I13" s="36"/>
-      <c r="J13" s="116"/>
-      <c r="K13" s="117"/>
-      <c r="L13" s="143"/>
+      <c r="J13" s="90"/>
+      <c r="K13" s="91"/>
+      <c r="L13" s="61"/>
       <c r="M13" s="5"/>
-      <c r="N13" s="75"/>
-      <c r="O13" s="76"/>
+      <c r="N13" s="81"/>
+      <c r="O13" s="82"/>
       <c r="P13" s="18"/>
       <c r="Q13" s="36"/>
-      <c r="R13" s="75"/>
-      <c r="S13" s="76"/>
+      <c r="R13" s="81"/>
+      <c r="S13" s="82"/>
       <c r="T13" s="18"/>
       <c r="U13" s="36"/>
-      <c r="V13" s="75"/>
-      <c r="W13" s="76"/>
+      <c r="V13" s="81"/>
+      <c r="W13" s="82"/>
       <c r="X13" s="18"/>
       <c r="Y13" s="36"/>
-      <c r="Z13" s="75"/>
-      <c r="AA13" s="76"/>
+      <c r="Z13" s="81"/>
+      <c r="AA13" s="82"/>
       <c r="AB13" s="18"/>
       <c r="AC13" s="36"/>
-      <c r="AD13" s="75"/>
-      <c r="AE13" s="76"/>
+      <c r="AD13" s="81"/>
+      <c r="AE13" s="82"/>
       <c r="AF13" s="18"/>
       <c r="AG13" s="38"/>
-      <c r="AH13" s="75"/>
-      <c r="AI13" s="76"/>
+      <c r="AH13" s="81"/>
+      <c r="AI13" s="82"/>
       <c r="AJ13" s="18"/>
       <c r="AK13" s="36"/>
-      <c r="AL13" s="75"/>
-      <c r="AM13" s="76"/>
+      <c r="AL13" s="81"/>
+      <c r="AM13" s="82"/>
       <c r="AN13" s="18"/>
       <c r="AP13" s="46" t="s">
         <v>22</v>
       </c>
       <c r="AQ13" s="25">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AR13" s="30"/>
     </row>
-    <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="78"/>
-      <c r="C14" s="79"/>
-      <c r="D14" s="80"/>
+    <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="87"/>
+      <c r="C14" s="88"/>
+      <c r="D14" s="89"/>
       <c r="E14" s="37"/>
-      <c r="F14" s="78" t="s">
+      <c r="F14" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="G14" s="79"/>
-      <c r="H14" s="80"/>
+      <c r="G14" s="88"/>
+      <c r="H14" s="89"/>
       <c r="I14" s="35"/>
-      <c r="J14" s="78"/>
-      <c r="K14" s="79"/>
-      <c r="L14" s="80"/>
+      <c r="J14" s="87"/>
+      <c r="K14" s="88"/>
+      <c r="L14" s="89"/>
       <c r="M14" s="3"/>
-      <c r="N14" s="78"/>
-      <c r="O14" s="79"/>
-      <c r="P14" s="80"/>
+      <c r="N14" s="87"/>
+      <c r="O14" s="88"/>
+      <c r="P14" s="89"/>
       <c r="Q14" s="35"/>
-      <c r="R14" s="78"/>
-      <c r="S14" s="79"/>
-      <c r="T14" s="80"/>
+      <c r="R14" s="87"/>
+      <c r="S14" s="88"/>
+      <c r="T14" s="89"/>
       <c r="U14" s="37"/>
-      <c r="V14" s="78"/>
-      <c r="W14" s="79"/>
-      <c r="X14" s="80"/>
+      <c r="V14" s="87"/>
+      <c r="W14" s="88"/>
+      <c r="X14" s="89"/>
       <c r="Y14" s="35"/>
-      <c r="Z14" s="78"/>
-      <c r="AA14" s="79"/>
-      <c r="AB14" s="80"/>
+      <c r="Z14" s="87"/>
+      <c r="AA14" s="88"/>
+      <c r="AB14" s="89"/>
       <c r="AC14" s="37"/>
-      <c r="AD14" s="78"/>
-      <c r="AE14" s="79"/>
-      <c r="AF14" s="80"/>
+      <c r="AD14" s="87"/>
+      <c r="AE14" s="88"/>
+      <c r="AF14" s="89"/>
       <c r="AG14" s="37"/>
-      <c r="AH14" s="78" t="s">
+      <c r="AH14" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="AI14" s="79"/>
-      <c r="AJ14" s="80"/>
+      <c r="AI14" s="88"/>
+      <c r="AJ14" s="89"/>
       <c r="AK14" s="35"/>
-      <c r="AL14" s="78"/>
-      <c r="AM14" s="79"/>
-      <c r="AN14" s="80"/>
+      <c r="AL14" s="87"/>
+      <c r="AM14" s="88"/>
+      <c r="AN14" s="89"/>
       <c r="AP14" s="58" t="s">
         <v>23</v>
       </c>
@@ -2955,50 +2994,50 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="72"/>
-      <c r="C15" s="73"/>
-      <c r="D15" s="74"/>
+    <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="78"/>
+      <c r="C15" s="79"/>
+      <c r="D15" s="80"/>
       <c r="E15" s="44"/>
-      <c r="F15" s="119" t="s">
+      <c r="F15" s="135" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="120"/>
-      <c r="H15" s="121"/>
+      <c r="G15" s="136"/>
+      <c r="H15" s="137"/>
       <c r="I15" s="43"/>
-      <c r="J15" s="72"/>
-      <c r="K15" s="73"/>
-      <c r="L15" s="74"/>
+      <c r="J15" s="78"/>
+      <c r="K15" s="79"/>
+      <c r="L15" s="80"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="72"/>
-      <c r="O15" s="73"/>
-      <c r="P15" s="74"/>
+      <c r="N15" s="78"/>
+      <c r="O15" s="79"/>
+      <c r="P15" s="80"/>
       <c r="Q15" s="43"/>
-      <c r="R15" s="72"/>
-      <c r="S15" s="73"/>
-      <c r="T15" s="74"/>
+      <c r="R15" s="78"/>
+      <c r="S15" s="79"/>
+      <c r="T15" s="80"/>
       <c r="U15" s="44"/>
-      <c r="V15" s="72"/>
-      <c r="W15" s="73"/>
-      <c r="X15" s="74"/>
+      <c r="V15" s="78"/>
+      <c r="W15" s="79"/>
+      <c r="X15" s="80"/>
       <c r="Y15" s="43"/>
-      <c r="Z15" s="72"/>
-      <c r="AA15" s="73"/>
-      <c r="AB15" s="74"/>
+      <c r="Z15" s="78"/>
+      <c r="AA15" s="79"/>
+      <c r="AB15" s="80"/>
       <c r="AC15" s="43"/>
-      <c r="AD15" s="72"/>
-      <c r="AE15" s="73"/>
-      <c r="AF15" s="74"/>
+      <c r="AD15" s="78"/>
+      <c r="AE15" s="79"/>
+      <c r="AF15" s="80"/>
       <c r="AG15" s="44"/>
-      <c r="AH15" s="72" t="s">
+      <c r="AH15" s="78" t="s">
         <v>29</v>
       </c>
-      <c r="AI15" s="73"/>
-      <c r="AJ15" s="74"/>
+      <c r="AI15" s="79"/>
+      <c r="AJ15" s="80"/>
       <c r="AK15" s="43"/>
-      <c r="AL15" s="72"/>
-      <c r="AM15" s="73"/>
-      <c r="AN15" s="74"/>
+      <c r="AL15" s="78"/>
+      <c r="AM15" s="79"/>
+      <c r="AN15" s="80"/>
       <c r="AP15" s="46" t="s">
         <v>18</v>
       </c>
@@ -3008,58 +3047,58 @@
       </c>
       <c r="AR15" s="30"/>
     </row>
-    <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="81"/>
-      <c r="C16" s="82"/>
-      <c r="D16" s="83"/>
+    <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="107"/>
+      <c r="C16" s="108"/>
+      <c r="D16" s="109"/>
       <c r="E16" s="44"/>
-      <c r="F16" s="122" t="s">
+      <c r="F16" s="104" t="s">
         <v>88</v>
       </c>
-      <c r="G16" s="123"/>
-      <c r="H16" s="124"/>
+      <c r="G16" s="105"/>
+      <c r="H16" s="106"/>
       <c r="I16" s="44"/>
-      <c r="J16" s="81"/>
-      <c r="K16" s="82"/>
-      <c r="L16" s="83"/>
+      <c r="J16" s="107"/>
+      <c r="K16" s="108"/>
+      <c r="L16" s="109"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="81"/>
-      <c r="O16" s="82"/>
-      <c r="P16" s="83"/>
+      <c r="N16" s="107"/>
+      <c r="O16" s="108"/>
+      <c r="P16" s="109"/>
       <c r="Q16" s="44"/>
-      <c r="R16" s="81"/>
-      <c r="S16" s="82"/>
-      <c r="T16" s="83"/>
+      <c r="R16" s="107"/>
+      <c r="S16" s="108"/>
+      <c r="T16" s="109"/>
       <c r="U16" s="44"/>
-      <c r="V16" s="81"/>
-      <c r="W16" s="82"/>
-      <c r="X16" s="83"/>
+      <c r="V16" s="107"/>
+      <c r="W16" s="108"/>
+      <c r="X16" s="109"/>
       <c r="Y16" s="44"/>
-      <c r="Z16" s="81"/>
-      <c r="AA16" s="82"/>
-      <c r="AB16" s="83"/>
+      <c r="Z16" s="107"/>
+      <c r="AA16" s="108"/>
+      <c r="AB16" s="109"/>
       <c r="AC16" s="44"/>
-      <c r="AD16" s="81"/>
-      <c r="AE16" s="82"/>
-      <c r="AF16" s="83"/>
+      <c r="AD16" s="107"/>
+      <c r="AE16" s="108"/>
+      <c r="AF16" s="109"/>
       <c r="AG16" s="44"/>
-      <c r="AH16" s="81"/>
-      <c r="AI16" s="82"/>
-      <c r="AJ16" s="83"/>
+      <c r="AH16" s="107"/>
+      <c r="AI16" s="108"/>
+      <c r="AJ16" s="109"/>
       <c r="AK16" s="44"/>
-      <c r="AL16" s="81"/>
-      <c r="AM16" s="82"/>
-      <c r="AN16" s="83"/>
+      <c r="AL16" s="107"/>
+      <c r="AM16" s="108"/>
+      <c r="AN16" s="109"/>
       <c r="AP16" s="46" t="s">
         <v>24</v>
       </c>
       <c r="AQ16" s="25">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR16" s="30"/>
     </row>
-    <row r="17" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="33"/>
       <c r="C17" s="33"/>
       <c r="D17" s="33"/>
@@ -3104,11 +3143,11 @@
       </c>
       <c r="AQ17" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR17" s="30"/>
     </row>
-    <row r="18" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="33"/>
       <c r="C18" s="33"/>
       <c r="D18" s="33"/>
@@ -3121,23 +3160,23 @@
       <c r="K18" s="33"/>
       <c r="L18" s="33"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="88" t="s">
+      <c r="N18" s="110" t="s">
         <v>59</v>
       </c>
-      <c r="O18" s="88"/>
-      <c r="P18" s="88"/>
-      <c r="Q18" s="88"/>
-      <c r="R18" s="88"/>
-      <c r="S18" s="88"/>
-      <c r="T18" s="88"/>
-      <c r="U18" s="88"/>
-      <c r="V18" s="88"/>
-      <c r="W18" s="88"/>
-      <c r="X18" s="88"/>
-      <c r="Y18" s="88"/>
-      <c r="Z18" s="88"/>
-      <c r="AA18" s="88"/>
-      <c r="AB18" s="88"/>
+      <c r="O18" s="110"/>
+      <c r="P18" s="110"/>
+      <c r="Q18" s="110"/>
+      <c r="R18" s="110"/>
+      <c r="S18" s="110"/>
+      <c r="T18" s="110"/>
+      <c r="U18" s="110"/>
+      <c r="V18" s="110"/>
+      <c r="W18" s="110"/>
+      <c r="X18" s="110"/>
+      <c r="Y18" s="110"/>
+      <c r="Z18" s="110"/>
+      <c r="AA18" s="110"/>
+      <c r="AB18" s="110"/>
       <c r="AC18" s="33"/>
       <c r="AD18" s="33"/>
       <c r="AE18" s="33"/>
@@ -3159,7 +3198,7 @@
       </c>
       <c r="AR18" s="30"/>
     </row>
-    <row r="19" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="33"/>
       <c r="C19" s="33"/>
       <c r="D19" s="33"/>
@@ -3172,21 +3211,21 @@
       <c r="K19" s="33"/>
       <c r="L19" s="33"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="88"/>
-      <c r="O19" s="88"/>
-      <c r="P19" s="88"/>
-      <c r="Q19" s="88"/>
-      <c r="R19" s="88"/>
-      <c r="S19" s="88"/>
-      <c r="T19" s="88"/>
-      <c r="U19" s="88"/>
-      <c r="V19" s="88"/>
-      <c r="W19" s="88"/>
-      <c r="X19" s="88"/>
-      <c r="Y19" s="88"/>
-      <c r="Z19" s="88"/>
-      <c r="AA19" s="88"/>
-      <c r="AB19" s="88"/>
+      <c r="N19" s="110"/>
+      <c r="O19" s="110"/>
+      <c r="P19" s="110"/>
+      <c r="Q19" s="110"/>
+      <c r="R19" s="110"/>
+      <c r="S19" s="110"/>
+      <c r="T19" s="110"/>
+      <c r="U19" s="110"/>
+      <c r="V19" s="110"/>
+      <c r="W19" s="110"/>
+      <c r="X19" s="110"/>
+      <c r="Y19" s="110"/>
+      <c r="Z19" s="110"/>
+      <c r="AA19" s="110"/>
+      <c r="AB19" s="110"/>
       <c r="AC19" s="33"/>
       <c r="AD19" s="33"/>
       <c r="AE19" s="33"/>
@@ -3204,176 +3243,180 @@
       </c>
       <c r="AQ19" s="25">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR19" s="30"/>
     </row>
-    <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="114"/>
-      <c r="C20" s="115"/>
+    <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="65"/>
+      <c r="C20" s="66"/>
       <c r="D20" s="57"/>
       <c r="E20" s="39"/>
-      <c r="F20" s="114"/>
-      <c r="G20" s="115"/>
+      <c r="F20" s="65"/>
+      <c r="G20" s="66"/>
       <c r="H20" s="57"/>
       <c r="I20" s="36"/>
-      <c r="J20" s="114"/>
-      <c r="K20" s="115"/>
+      <c r="J20" s="65"/>
+      <c r="K20" s="66"/>
       <c r="L20" s="57"/>
       <c r="M20" s="4"/>
-      <c r="N20" s="65" t="s">
+      <c r="N20" s="99" t="s">
         <v>87</v>
       </c>
-      <c r="O20" s="66"/>
-      <c r="P20" s="34" t="s">
+      <c r="O20" s="100"/>
+      <c r="P20" s="60" t="s">
         <v>49</v>
       </c>
       <c r="Q20" s="39"/>
-      <c r="R20" s="65" t="s">
+      <c r="R20" s="99" t="s">
         <v>87</v>
       </c>
-      <c r="S20" s="66"/>
-      <c r="T20" s="34" t="s">
+      <c r="S20" s="100"/>
+      <c r="T20" s="60" t="s">
         <v>49</v>
       </c>
       <c r="U20" s="36"/>
-      <c r="V20" s="65" t="s">
+      <c r="V20" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="W20" s="66"/>
+      <c r="W20" s="68"/>
       <c r="X20" s="34" t="s">
         <v>55</v>
       </c>
       <c r="Y20" s="23"/>
-      <c r="Z20" s="65"/>
-      <c r="AA20" s="66"/>
+      <c r="Z20" s="67"/>
+      <c r="AA20" s="68"/>
       <c r="AB20" s="34"/>
       <c r="AC20" s="36"/>
-      <c r="AD20" s="65"/>
-      <c r="AE20" s="66"/>
+      <c r="AD20" s="67"/>
+      <c r="AE20" s="68"/>
       <c r="AF20" s="34"/>
       <c r="AG20" s="39"/>
-      <c r="AH20" s="65" t="s">
+      <c r="AH20" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="AI20" s="66"/>
+      <c r="AI20" s="68"/>
       <c r="AJ20" s="34" t="s">
         <v>86</v>
       </c>
       <c r="AK20" s="36"/>
-      <c r="AL20" s="65"/>
-      <c r="AM20" s="66"/>
+      <c r="AL20" s="67"/>
+      <c r="AM20" s="68"/>
       <c r="AN20" s="34"/>
       <c r="AP20" s="46" t="s">
         <v>26</v>
       </c>
       <c r="AQ20" s="25">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR20" s="30"/>
     </row>
-    <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="116"/>
-      <c r="C21" s="117"/>
-      <c r="D21" s="143"/>
+    <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="90"/>
+      <c r="C21" s="91"/>
+      <c r="D21" s="61"/>
       <c r="E21" s="38"/>
-      <c r="F21" s="116"/>
-      <c r="G21" s="117"/>
-      <c r="H21" s="143"/>
+      <c r="F21" s="90"/>
+      <c r="G21" s="91"/>
+      <c r="H21" s="61"/>
       <c r="I21" s="36"/>
-      <c r="J21" s="116"/>
-      <c r="K21" s="117"/>
-      <c r="L21" s="143"/>
+      <c r="J21" s="90"/>
+      <c r="K21" s="91"/>
+      <c r="L21" s="61"/>
       <c r="M21" s="15"/>
-      <c r="N21" s="75"/>
-      <c r="O21" s="76"/>
-      <c r="P21" s="18"/>
+      <c r="N21" s="148" t="s">
+        <v>92</v>
+      </c>
+      <c r="O21" s="149"/>
+      <c r="P21" s="147"/>
       <c r="Q21" s="36"/>
-      <c r="R21" s="75"/>
-      <c r="S21" s="76"/>
-      <c r="T21" s="18"/>
+      <c r="R21" s="148" t="s">
+        <v>92</v>
+      </c>
+      <c r="S21" s="149"/>
+      <c r="T21" s="147"/>
       <c r="U21" s="36"/>
-      <c r="V21" s="75" t="s">
+      <c r="V21" s="81" t="s">
         <v>54</v>
       </c>
-      <c r="W21" s="76"/>
+      <c r="W21" s="82"/>
       <c r="X21" s="18" t="s">
         <v>50</v>
       </c>
       <c r="Y21" s="36"/>
-      <c r="Z21" s="75"/>
-      <c r="AA21" s="76"/>
+      <c r="Z21" s="81"/>
+      <c r="AA21" s="82"/>
       <c r="AB21" s="18"/>
       <c r="AC21" s="36"/>
-      <c r="AD21" s="75"/>
-      <c r="AE21" s="76"/>
+      <c r="AD21" s="81"/>
+      <c r="AE21" s="82"/>
       <c r="AF21" s="18"/>
       <c r="AG21" s="38"/>
-      <c r="AH21" s="75"/>
-      <c r="AI21" s="76"/>
+      <c r="AH21" s="81"/>
+      <c r="AI21" s="82"/>
       <c r="AJ21" s="18"/>
       <c r="AK21" s="36"/>
-      <c r="AL21" s="75"/>
-      <c r="AM21" s="76"/>
+      <c r="AL21" s="81"/>
+      <c r="AM21" s="82"/>
       <c r="AN21" s="18"/>
       <c r="AP21" s="46" t="s">
         <v>12</v>
       </c>
       <c r="AQ21" s="25">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR21" s="30"/>
     </row>
-    <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="78"/>
-      <c r="C22" s="79"/>
-      <c r="D22" s="80"/>
+    <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="87"/>
+      <c r="C22" s="88"/>
+      <c r="D22" s="89"/>
       <c r="E22" s="35"/>
-      <c r="F22" s="78"/>
-      <c r="G22" s="79"/>
-      <c r="H22" s="80"/>
+      <c r="F22" s="87"/>
+      <c r="G22" s="88"/>
+      <c r="H22" s="89"/>
       <c r="I22" s="37"/>
-      <c r="J22" s="78"/>
-      <c r="K22" s="79"/>
-      <c r="L22" s="80"/>
+      <c r="J22" s="87"/>
+      <c r="K22" s="88"/>
+      <c r="L22" s="89"/>
       <c r="M22" s="4"/>
-      <c r="N22" s="78" t="s">
-        <v>37</v>
-      </c>
-      <c r="O22" s="79"/>
-      <c r="P22" s="80"/>
+      <c r="N22" s="75" t="s">
+        <v>97</v>
+      </c>
+      <c r="O22" s="76"/>
+      <c r="P22" s="77"/>
       <c r="Q22" s="35"/>
-      <c r="R22" s="78" t="s">
+      <c r="R22" s="75" t="s">
+        <v>98</v>
+      </c>
+      <c r="S22" s="76"/>
+      <c r="T22" s="77"/>
+      <c r="U22" s="37"/>
+      <c r="V22" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="S22" s="79"/>
-      <c r="T22" s="80"/>
-      <c r="U22" s="37"/>
-      <c r="V22" s="78" t="s">
-        <v>12</v>
-      </c>
-      <c r="W22" s="79"/>
-      <c r="X22" s="80"/>
+      <c r="W22" s="88"/>
+      <c r="X22" s="89"/>
       <c r="Y22" s="35"/>
-      <c r="Z22" s="78"/>
-      <c r="AA22" s="79"/>
-      <c r="AB22" s="80"/>
+      <c r="Z22" s="87"/>
+      <c r="AA22" s="88"/>
+      <c r="AB22" s="89"/>
       <c r="AC22" s="35"/>
-      <c r="AD22" s="78"/>
-      <c r="AE22" s="79"/>
-      <c r="AF22" s="80"/>
+      <c r="AD22" s="87"/>
+      <c r="AE22" s="88"/>
+      <c r="AF22" s="89"/>
       <c r="AG22" s="35"/>
-      <c r="AH22" s="108" t="s">
+      <c r="AH22" s="115" t="s">
         <v>9</v>
       </c>
-      <c r="AI22" s="109"/>
-      <c r="AJ22" s="110"/>
+      <c r="AI22" s="116"/>
+      <c r="AJ22" s="117"/>
       <c r="AK22" s="37"/>
-      <c r="AL22" s="78"/>
-      <c r="AM22" s="79"/>
-      <c r="AN22" s="80"/>
+      <c r="AL22" s="87"/>
+      <c r="AM22" s="88"/>
+      <c r="AN22" s="89"/>
       <c r="AP22" s="46" t="s">
         <v>15</v>
       </c>
@@ -3383,46 +3426,46 @@
       </c>
       <c r="AR22" s="30"/>
     </row>
-    <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="81"/>
-      <c r="C23" s="82"/>
-      <c r="D23" s="83"/>
+    <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="107"/>
+      <c r="C23" s="108"/>
+      <c r="D23" s="109"/>
       <c r="E23" s="44"/>
-      <c r="F23" s="81"/>
-      <c r="G23" s="82"/>
-      <c r="H23" s="83"/>
+      <c r="F23" s="107"/>
+      <c r="G23" s="108"/>
+      <c r="H23" s="109"/>
       <c r="I23" s="44"/>
-      <c r="J23" s="81"/>
-      <c r="K23" s="82"/>
-      <c r="L23" s="83"/>
+      <c r="J23" s="107"/>
+      <c r="K23" s="108"/>
+      <c r="L23" s="109"/>
       <c r="M23" s="4"/>
-      <c r="N23" s="81"/>
-      <c r="O23" s="82"/>
-      <c r="P23" s="83"/>
+      <c r="N23" s="72"/>
+      <c r="O23" s="73"/>
+      <c r="P23" s="74"/>
       <c r="Q23" s="44"/>
-      <c r="R23" s="81"/>
-      <c r="S23" s="82"/>
-      <c r="T23" s="83"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="73"/>
+      <c r="T23" s="74"/>
       <c r="U23" s="44"/>
-      <c r="V23" s="81"/>
-      <c r="W23" s="82"/>
-      <c r="X23" s="83"/>
+      <c r="V23" s="107"/>
+      <c r="W23" s="108"/>
+      <c r="X23" s="109"/>
       <c r="Y23" s="44"/>
-      <c r="Z23" s="81"/>
-      <c r="AA23" s="82"/>
-      <c r="AB23" s="83"/>
+      <c r="Z23" s="107"/>
+      <c r="AA23" s="108"/>
+      <c r="AB23" s="109"/>
       <c r="AC23" s="44"/>
-      <c r="AD23" s="81"/>
-      <c r="AE23" s="82"/>
-      <c r="AF23" s="83"/>
+      <c r="AD23" s="107"/>
+      <c r="AE23" s="108"/>
+      <c r="AF23" s="109"/>
       <c r="AG23" s="44"/>
-      <c r="AH23" s="81"/>
-      <c r="AI23" s="82"/>
-      <c r="AJ23" s="83"/>
+      <c r="AH23" s="107"/>
+      <c r="AI23" s="108"/>
+      <c r="AJ23" s="109"/>
       <c r="AK23" s="44"/>
-      <c r="AL23" s="81"/>
-      <c r="AM23" s="82"/>
-      <c r="AN23" s="83"/>
+      <c r="AL23" s="107"/>
+      <c r="AM23" s="108"/>
+      <c r="AN23" s="109"/>
       <c r="AP23" s="58" t="s">
         <v>20</v>
       </c>
@@ -3434,7 +3477,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="33"/>
       <c r="C24" s="33"/>
       <c r="D24" s="33"/>
@@ -3483,7 +3526,7 @@
       </c>
       <c r="AR24" s="30"/>
     </row>
-    <row r="25" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="33"/>
       <c r="C25" s="33"/>
       <c r="D25" s="33"/>
@@ -3496,23 +3539,23 @@
       <c r="K25" s="33"/>
       <c r="L25" s="33"/>
       <c r="M25" s="4"/>
-      <c r="N25" s="88" t="s">
+      <c r="N25" s="110" t="s">
         <v>39</v>
       </c>
-      <c r="O25" s="88"/>
-      <c r="P25" s="88"/>
-      <c r="Q25" s="88"/>
-      <c r="R25" s="88"/>
-      <c r="S25" s="88"/>
-      <c r="T25" s="88"/>
-      <c r="U25" s="88"/>
-      <c r="V25" s="88"/>
-      <c r="W25" s="88"/>
-      <c r="X25" s="88"/>
-      <c r="Y25" s="88"/>
-      <c r="Z25" s="88"/>
-      <c r="AA25" s="88"/>
-      <c r="AB25" s="88"/>
+      <c r="O25" s="110"/>
+      <c r="P25" s="110"/>
+      <c r="Q25" s="110"/>
+      <c r="R25" s="110"/>
+      <c r="S25" s="110"/>
+      <c r="T25" s="110"/>
+      <c r="U25" s="110"/>
+      <c r="V25" s="110"/>
+      <c r="W25" s="110"/>
+      <c r="X25" s="110"/>
+      <c r="Y25" s="110"/>
+      <c r="Z25" s="110"/>
+      <c r="AA25" s="110"/>
+      <c r="AB25" s="110"/>
       <c r="AC25" s="33"/>
       <c r="AD25" s="33"/>
       <c r="AE25" s="33"/>
@@ -3534,7 +3577,7 @@
       </c>
       <c r="AR25" s="30"/>
     </row>
-    <row r="26" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="33"/>
       <c r="C26" s="33"/>
       <c r="D26" s="33"/>
@@ -3547,21 +3590,21 @@
       <c r="K26" s="33"/>
       <c r="L26" s="33"/>
       <c r="M26" s="4"/>
-      <c r="N26" s="88"/>
-      <c r="O26" s="88"/>
-      <c r="P26" s="88"/>
-      <c r="Q26" s="88"/>
-      <c r="R26" s="88"/>
-      <c r="S26" s="88"/>
-      <c r="T26" s="88"/>
-      <c r="U26" s="88"/>
-      <c r="V26" s="88"/>
-      <c r="W26" s="88"/>
-      <c r="X26" s="88"/>
-      <c r="Y26" s="88"/>
-      <c r="Z26" s="88"/>
-      <c r="AA26" s="88"/>
-      <c r="AB26" s="88"/>
+      <c r="N26" s="110"/>
+      <c r="O26" s="110"/>
+      <c r="P26" s="110"/>
+      <c r="Q26" s="110"/>
+      <c r="R26" s="110"/>
+      <c r="S26" s="110"/>
+      <c r="T26" s="110"/>
+      <c r="U26" s="110"/>
+      <c r="V26" s="110"/>
+      <c r="W26" s="110"/>
+      <c r="X26" s="110"/>
+      <c r="Y26" s="110"/>
+      <c r="Z26" s="110"/>
+      <c r="AA26" s="110"/>
+      <c r="AB26" s="110"/>
       <c r="AC26" s="33"/>
       <c r="AD26" s="33"/>
       <c r="AE26" s="33"/>
@@ -3585,55 +3628,55 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="114"/>
-      <c r="C27" s="115"/>
+    <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="65"/>
+      <c r="C27" s="66"/>
       <c r="D27" s="57"/>
       <c r="E27" s="36"/>
-      <c r="F27" s="114"/>
-      <c r="G27" s="115"/>
+      <c r="F27" s="65"/>
+      <c r="G27" s="66"/>
       <c r="H27" s="57"/>
       <c r="I27" s="36"/>
-      <c r="J27" s="114"/>
-      <c r="K27" s="115"/>
+      <c r="J27" s="65"/>
+      <c r="K27" s="66"/>
       <c r="L27" s="57"/>
       <c r="M27" s="5"/>
-      <c r="N27" s="65"/>
-      <c r="O27" s="66"/>
+      <c r="N27" s="67"/>
+      <c r="O27" s="68"/>
       <c r="P27" s="34"/>
       <c r="Q27" s="36"/>
-      <c r="R27" s="91"/>
-      <c r="S27" s="92"/>
+      <c r="R27" s="120"/>
+      <c r="S27" s="121"/>
       <c r="T27" s="55"/>
       <c r="U27" s="36"/>
-      <c r="V27" s="91"/>
-      <c r="W27" s="92"/>
+      <c r="V27" s="120"/>
+      <c r="W27" s="121"/>
       <c r="X27" s="55"/>
       <c r="Y27" s="36"/>
-      <c r="Z27" s="91"/>
-      <c r="AA27" s="92"/>
+      <c r="Z27" s="120"/>
+      <c r="AA27" s="121"/>
       <c r="AB27" s="55"/>
       <c r="AC27" s="36"/>
-      <c r="AD27" s="65" t="s">
+      <c r="AD27" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="AE27" s="66"/>
+      <c r="AE27" s="68"/>
       <c r="AF27" s="34" t="s">
         <v>66</v>
       </c>
       <c r="AG27" s="36"/>
-      <c r="AH27" s="65" t="s">
+      <c r="AH27" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="AI27" s="66"/>
+      <c r="AI27" s="68"/>
       <c r="AJ27" s="34" t="s">
         <v>66</v>
       </c>
       <c r="AK27" s="36"/>
-      <c r="AL27" s="65" t="s">
+      <c r="AL27" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="AM27" s="66"/>
+      <c r="AM27" s="68"/>
       <c r="AN27" s="34" t="s">
         <v>66</v>
       </c>
@@ -3646,45 +3689,45 @@
       </c>
       <c r="AR27" s="30"/>
     </row>
-    <row r="28" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="116"/>
-      <c r="C28" s="117"/>
-      <c r="D28" s="143"/>
+    <row r="28" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="90"/>
+      <c r="C28" s="91"/>
+      <c r="D28" s="61"/>
       <c r="E28" s="38"/>
-      <c r="F28" s="116"/>
-      <c r="G28" s="117"/>
-      <c r="H28" s="143"/>
+      <c r="F28" s="90"/>
+      <c r="G28" s="91"/>
+      <c r="H28" s="61"/>
       <c r="I28" s="36"/>
-      <c r="J28" s="116"/>
-      <c r="K28" s="117"/>
-      <c r="L28" s="143"/>
+      <c r="J28" s="90"/>
+      <c r="K28" s="91"/>
+      <c r="L28" s="61"/>
       <c r="M28" s="5"/>
-      <c r="N28" s="75"/>
-      <c r="O28" s="76"/>
+      <c r="N28" s="81"/>
+      <c r="O28" s="82"/>
       <c r="P28" s="18"/>
       <c r="Q28" s="38"/>
-      <c r="R28" s="75"/>
-      <c r="S28" s="76"/>
+      <c r="R28" s="81"/>
+      <c r="S28" s="82"/>
       <c r="T28" s="18"/>
       <c r="U28" s="38"/>
-      <c r="V28" s="89"/>
-      <c r="W28" s="90"/>
+      <c r="V28" s="142"/>
+      <c r="W28" s="143"/>
       <c r="X28" s="56"/>
       <c r="Y28" s="36"/>
-      <c r="Z28" s="89"/>
-      <c r="AA28" s="90"/>
+      <c r="Z28" s="142"/>
+      <c r="AA28" s="143"/>
       <c r="AB28" s="56"/>
       <c r="AC28" s="36"/>
-      <c r="AD28" s="75"/>
-      <c r="AE28" s="76"/>
+      <c r="AD28" s="81"/>
+      <c r="AE28" s="82"/>
       <c r="AF28" s="18"/>
       <c r="AG28" s="38"/>
-      <c r="AH28" s="75"/>
-      <c r="AI28" s="76"/>
+      <c r="AH28" s="81"/>
+      <c r="AI28" s="82"/>
       <c r="AJ28" s="18"/>
       <c r="AK28" s="36"/>
-      <c r="AL28" s="75"/>
-      <c r="AM28" s="76"/>
+      <c r="AL28" s="81"/>
+      <c r="AM28" s="82"/>
       <c r="AN28" s="18"/>
       <c r="AP28" s="46" t="s">
         <v>28</v>
@@ -3695,55 +3738,55 @@
       </c>
       <c r="AR28" s="30"/>
     </row>
-    <row r="29" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="84"/>
-      <c r="C29" s="85"/>
+    <row r="29" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="118"/>
+      <c r="C29" s="119"/>
       <c r="D29" s="41"/>
       <c r="E29" s="37"/>
-      <c r="F29" s="84"/>
-      <c r="G29" s="85"/>
+      <c r="F29" s="118"/>
+      <c r="G29" s="119"/>
       <c r="H29" s="41"/>
       <c r="I29" s="35"/>
-      <c r="J29" s="84"/>
-      <c r="K29" s="85"/>
+      <c r="J29" s="118"/>
+      <c r="K29" s="119"/>
       <c r="L29" s="41"/>
       <c r="M29" s="5"/>
-      <c r="N29" s="84"/>
-      <c r="O29" s="85"/>
+      <c r="N29" s="118"/>
+      <c r="O29" s="119"/>
       <c r="P29" s="41"/>
       <c r="Q29" s="35"/>
-      <c r="R29" s="84"/>
-      <c r="S29" s="85"/>
+      <c r="R29" s="118"/>
+      <c r="S29" s="119"/>
       <c r="T29" s="41"/>
       <c r="U29" s="37"/>
-      <c r="V29" s="84"/>
-      <c r="W29" s="85"/>
+      <c r="V29" s="118"/>
+      <c r="W29" s="119"/>
       <c r="X29" s="41"/>
       <c r="Y29" s="35"/>
-      <c r="Z29" s="84"/>
-      <c r="AA29" s="85"/>
+      <c r="Z29" s="118"/>
+      <c r="AA29" s="119"/>
       <c r="AB29" s="41"/>
       <c r="AC29" s="35"/>
-      <c r="AD29" s="84" t="s">
+      <c r="AD29" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="AE29" s="85"/>
+      <c r="AE29" s="119"/>
       <c r="AF29" s="41" t="s">
         <v>32</v>
       </c>
       <c r="AG29" s="37"/>
-      <c r="AH29" s="84" t="s">
+      <c r="AH29" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="AI29" s="85"/>
+      <c r="AI29" s="119"/>
       <c r="AJ29" s="41" t="s">
         <v>32</v>
       </c>
       <c r="AK29" s="35"/>
-      <c r="AL29" s="84" t="s">
+      <c r="AL29" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="AM29" s="85"/>
+      <c r="AM29" s="119"/>
       <c r="AN29" s="41" t="s">
         <v>32</v>
       </c>
@@ -3756,55 +3799,55 @@
       </c>
       <c r="AR29" s="30"/>
     </row>
-    <row r="30" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="86"/>
-      <c r="C30" s="87"/>
+    <row r="30" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="140"/>
+      <c r="C30" s="141"/>
       <c r="D30" s="45"/>
       <c r="E30" s="43"/>
-      <c r="F30" s="86"/>
-      <c r="G30" s="87"/>
+      <c r="F30" s="140"/>
+      <c r="G30" s="141"/>
       <c r="H30" s="45"/>
       <c r="I30" s="43"/>
-      <c r="J30" s="86"/>
-      <c r="K30" s="87"/>
+      <c r="J30" s="140"/>
+      <c r="K30" s="141"/>
       <c r="L30" s="45"/>
       <c r="M30" s="5"/>
-      <c r="N30" s="86"/>
-      <c r="O30" s="87"/>
+      <c r="N30" s="140"/>
+      <c r="O30" s="141"/>
       <c r="P30" s="45"/>
       <c r="Q30" s="43"/>
-      <c r="R30" s="86"/>
-      <c r="S30" s="87"/>
+      <c r="R30" s="140"/>
+      <c r="S30" s="141"/>
       <c r="T30" s="45"/>
       <c r="U30" s="43"/>
-      <c r="V30" s="86"/>
-      <c r="W30" s="87"/>
+      <c r="V30" s="140"/>
+      <c r="W30" s="141"/>
       <c r="X30" s="45"/>
       <c r="Y30" s="43"/>
-      <c r="Z30" s="86"/>
-      <c r="AA30" s="87"/>
+      <c r="Z30" s="140"/>
+      <c r="AA30" s="141"/>
       <c r="AB30" s="45"/>
       <c r="AC30" s="43"/>
-      <c r="AD30" s="86" t="s">
+      <c r="AD30" s="140" t="s">
         <v>19</v>
       </c>
-      <c r="AE30" s="87"/>
+      <c r="AE30" s="141"/>
       <c r="AF30" s="45" t="s">
         <v>33</v>
       </c>
       <c r="AG30" s="43"/>
-      <c r="AH30" s="86" t="s">
+      <c r="AH30" s="140" t="s">
         <v>19</v>
       </c>
-      <c r="AI30" s="87"/>
+      <c r="AI30" s="141"/>
       <c r="AJ30" s="45" t="s">
         <v>33</v>
       </c>
       <c r="AK30" s="43"/>
-      <c r="AL30" s="86" t="s">
+      <c r="AL30" s="140" t="s">
         <v>19</v>
       </c>
-      <c r="AM30" s="87"/>
+      <c r="AM30" s="141"/>
       <c r="AN30" s="45" t="s">
         <v>33</v>
       </c>
@@ -3817,55 +3860,55 @@
       </c>
       <c r="AR30" s="30"/>
     </row>
-    <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="60"/>
-      <c r="C31" s="61"/>
+    <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="113"/>
+      <c r="C31" s="114"/>
       <c r="D31" s="45"/>
       <c r="E31" s="43"/>
-      <c r="F31" s="60"/>
-      <c r="G31" s="61"/>
+      <c r="F31" s="113"/>
+      <c r="G31" s="114"/>
       <c r="H31" s="45"/>
       <c r="I31" s="44"/>
-      <c r="J31" s="60"/>
-      <c r="K31" s="61"/>
+      <c r="J31" s="113"/>
+      <c r="K31" s="114"/>
       <c r="L31" s="45"/>
       <c r="M31" s="6"/>
-      <c r="N31" s="60"/>
-      <c r="O31" s="61"/>
+      <c r="N31" s="113"/>
+      <c r="O31" s="114"/>
       <c r="P31" s="45"/>
       <c r="Q31" s="43"/>
-      <c r="R31" s="60"/>
-      <c r="S31" s="61"/>
+      <c r="R31" s="113"/>
+      <c r="S31" s="114"/>
       <c r="T31" s="45"/>
       <c r="U31" s="44"/>
-      <c r="V31" s="60"/>
-      <c r="W31" s="61"/>
+      <c r="V31" s="113"/>
+      <c r="W31" s="114"/>
       <c r="X31" s="45"/>
       <c r="Y31" s="43"/>
-      <c r="Z31" s="60"/>
-      <c r="AA31" s="61"/>
+      <c r="Z31" s="113"/>
+      <c r="AA31" s="114"/>
       <c r="AB31" s="45"/>
       <c r="AC31" s="43"/>
-      <c r="AD31" s="60" t="s">
+      <c r="AD31" s="113" t="s">
         <v>37</v>
       </c>
-      <c r="AE31" s="61"/>
+      <c r="AE31" s="114"/>
       <c r="AF31" s="45" t="s">
         <v>34</v>
       </c>
       <c r="AG31" s="43"/>
-      <c r="AH31" s="60" t="s">
+      <c r="AH31" s="113" t="s">
         <v>8</v>
       </c>
-      <c r="AI31" s="61"/>
+      <c r="AI31" s="114"/>
       <c r="AJ31" s="45" t="s">
         <v>34</v>
       </c>
       <c r="AK31" s="44"/>
-      <c r="AL31" s="60" t="s">
+      <c r="AL31" s="113" t="s">
         <v>8</v>
       </c>
-      <c r="AM31" s="61"/>
+      <c r="AM31" s="114"/>
       <c r="AN31" s="45" t="s">
         <v>34</v>
       </c>
@@ -3873,55 +3916,55 @@
       <c r="AQ31" s="49"/>
       <c r="AR31" s="30"/>
     </row>
-    <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="60"/>
-      <c r="C32" s="61"/>
+    <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B32" s="113"/>
+      <c r="C32" s="114"/>
       <c r="D32" s="45"/>
       <c r="E32" s="44"/>
-      <c r="F32" s="60"/>
-      <c r="G32" s="61"/>
+      <c r="F32" s="113"/>
+      <c r="G32" s="114"/>
       <c r="H32" s="45"/>
       <c r="I32" s="44"/>
-      <c r="J32" s="60"/>
-      <c r="K32" s="61"/>
+      <c r="J32" s="113"/>
+      <c r="K32" s="114"/>
       <c r="L32" s="45"/>
       <c r="M32" s="5"/>
-      <c r="N32" s="60"/>
-      <c r="O32" s="61"/>
+      <c r="N32" s="113"/>
+      <c r="O32" s="114"/>
       <c r="P32" s="45"/>
       <c r="Q32" s="44"/>
-      <c r="R32" s="60"/>
-      <c r="S32" s="61"/>
+      <c r="R32" s="113"/>
+      <c r="S32" s="114"/>
       <c r="T32" s="45"/>
       <c r="U32" s="44"/>
-      <c r="V32" s="60"/>
-      <c r="W32" s="61"/>
+      <c r="V32" s="113"/>
+      <c r="W32" s="114"/>
       <c r="X32" s="45"/>
       <c r="Y32" s="44"/>
-      <c r="Z32" s="60"/>
-      <c r="AA32" s="61"/>
+      <c r="Z32" s="113"/>
+      <c r="AA32" s="114"/>
       <c r="AB32" s="45"/>
       <c r="AC32" s="44"/>
-      <c r="AD32" s="60" t="s">
+      <c r="AD32" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="AE32" s="61"/>
+      <c r="AE32" s="114"/>
       <c r="AF32" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AG32" s="44"/>
-      <c r="AH32" s="60" t="s">
+      <c r="AH32" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="AI32" s="61"/>
+      <c r="AI32" s="114"/>
       <c r="AJ32" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AK32" s="44"/>
-      <c r="AL32" s="60" t="s">
+      <c r="AL32" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="AM32" s="61"/>
+      <c r="AM32" s="114"/>
       <c r="AN32" s="45" t="s">
         <v>35</v>
       </c>
@@ -3929,99 +3972,99 @@
       <c r="AQ32" s="52"/>
       <c r="AR32" s="30"/>
     </row>
-    <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="60"/>
-      <c r="C33" s="61"/>
+    <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="113"/>
+      <c r="C33" s="114"/>
       <c r="D33" s="45"/>
       <c r="E33" s="44"/>
-      <c r="F33" s="60"/>
-      <c r="G33" s="61"/>
+      <c r="F33" s="113"/>
+      <c r="G33" s="114"/>
       <c r="H33" s="45"/>
       <c r="I33" s="44"/>
-      <c r="J33" s="60"/>
-      <c r="K33" s="61"/>
+      <c r="J33" s="113"/>
+      <c r="K33" s="114"/>
       <c r="L33" s="45"/>
       <c r="M33" s="5"/>
-      <c r="N33" s="60"/>
-      <c r="O33" s="61"/>
+      <c r="N33" s="113"/>
+      <c r="O33" s="114"/>
       <c r="P33" s="45"/>
       <c r="Q33" s="44"/>
-      <c r="R33" s="60"/>
-      <c r="S33" s="61"/>
+      <c r="R33" s="113"/>
+      <c r="S33" s="114"/>
       <c r="T33" s="45"/>
       <c r="U33" s="44"/>
-      <c r="V33" s="60"/>
-      <c r="W33" s="61"/>
+      <c r="V33" s="113"/>
+      <c r="W33" s="114"/>
       <c r="X33" s="45"/>
       <c r="Y33" s="44"/>
-      <c r="Z33" s="60"/>
-      <c r="AA33" s="61"/>
+      <c r="Z33" s="113"/>
+      <c r="AA33" s="114"/>
       <c r="AB33" s="45"/>
       <c r="AC33" s="44"/>
-      <c r="AD33" s="60" t="s">
+      <c r="AD33" s="113" t="s">
         <v>14</v>
       </c>
-      <c r="AE33" s="61"/>
+      <c r="AE33" s="114"/>
       <c r="AF33" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AG33" s="44"/>
-      <c r="AH33" s="60"/>
-      <c r="AI33" s="61"/>
+      <c r="AH33" s="113"/>
+      <c r="AI33" s="114"/>
       <c r="AJ33" s="45"/>
       <c r="AK33" s="44"/>
-      <c r="AL33" s="60"/>
-      <c r="AM33" s="61"/>
+      <c r="AL33" s="113"/>
+      <c r="AM33" s="114"/>
       <c r="AN33" s="45"/>
       <c r="AR33" s="13"/>
     </row>
-    <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="12"/>
-      <c r="B34" s="67"/>
-      <c r="C34" s="68"/>
+      <c r="B34" s="138"/>
+      <c r="C34" s="139"/>
       <c r="D34" s="42"/>
       <c r="E34" s="44"/>
-      <c r="F34" s="67"/>
-      <c r="G34" s="68"/>
+      <c r="F34" s="138"/>
+      <c r="G34" s="139"/>
       <c r="H34" s="42"/>
       <c r="I34" s="44"/>
-      <c r="J34" s="67"/>
-      <c r="K34" s="68"/>
+      <c r="J34" s="138"/>
+      <c r="K34" s="139"/>
       <c r="L34" s="42"/>
       <c r="M34" s="2"/>
-      <c r="N34" s="67"/>
-      <c r="O34" s="68"/>
+      <c r="N34" s="138"/>
+      <c r="O34" s="139"/>
       <c r="P34" s="42"/>
       <c r="Q34" s="44"/>
-      <c r="R34" s="67"/>
-      <c r="S34" s="68"/>
+      <c r="R34" s="138"/>
+      <c r="S34" s="139"/>
       <c r="T34" s="42"/>
       <c r="U34" s="44"/>
-      <c r="V34" s="67"/>
-      <c r="W34" s="68"/>
+      <c r="V34" s="138"/>
+      <c r="W34" s="139"/>
       <c r="X34" s="42"/>
       <c r="Y34" s="44"/>
-      <c r="Z34" s="67"/>
-      <c r="AA34" s="68"/>
+      <c r="Z34" s="138"/>
+      <c r="AA34" s="139"/>
       <c r="AB34" s="42"/>
       <c r="AC34" s="44"/>
-      <c r="AD34" s="67"/>
-      <c r="AE34" s="68"/>
+      <c r="AD34" s="138"/>
+      <c r="AE34" s="139"/>
       <c r="AF34" s="42"/>
       <c r="AG34" s="44"/>
-      <c r="AH34" s="67"/>
-      <c r="AI34" s="68"/>
+      <c r="AH34" s="138"/>
+      <c r="AI34" s="139"/>
       <c r="AJ34" s="42"/>
       <c r="AK34" s="44"/>
-      <c r="AL34" s="67"/>
-      <c r="AM34" s="68"/>
+      <c r="AL34" s="138"/>
+      <c r="AM34" s="139"/>
       <c r="AN34" s="42"/>
       <c r="AO34" s="12"/>
       <c r="AP34" s="12"/>
       <c r="AQ34" s="12"/>
       <c r="AR34" s="13"/>
     </row>
-    <row r="35" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="12"/>
       <c r="B35" s="33"/>
       <c r="C35" s="33"/>
@@ -4066,7 +4109,7 @@
       <c r="AQ35" s="12"/>
       <c r="AR35" s="13"/>
     </row>
-    <row r="36" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="12"/>
       <c r="B36" s="33"/>
       <c r="C36" s="33"/>
@@ -4080,23 +4123,23 @@
       <c r="K36" s="33"/>
       <c r="L36" s="33"/>
       <c r="M36" s="4"/>
-      <c r="N36" s="88" t="s">
+      <c r="N36" s="110" t="s">
         <v>36</v>
       </c>
-      <c r="O36" s="88"/>
-      <c r="P36" s="88"/>
-      <c r="Q36" s="88"/>
-      <c r="R36" s="88"/>
-      <c r="S36" s="88"/>
-      <c r="T36" s="88"/>
-      <c r="U36" s="88"/>
-      <c r="V36" s="88"/>
-      <c r="W36" s="88"/>
-      <c r="X36" s="88"/>
-      <c r="Y36" s="88"/>
-      <c r="Z36" s="88"/>
-      <c r="AA36" s="88"/>
-      <c r="AB36" s="88"/>
+      <c r="O36" s="110"/>
+      <c r="P36" s="110"/>
+      <c r="Q36" s="110"/>
+      <c r="R36" s="110"/>
+      <c r="S36" s="110"/>
+      <c r="T36" s="110"/>
+      <c r="U36" s="110"/>
+      <c r="V36" s="110"/>
+      <c r="W36" s="110"/>
+      <c r="X36" s="110"/>
+      <c r="Y36" s="110"/>
+      <c r="Z36" s="110"/>
+      <c r="AA36" s="110"/>
+      <c r="AB36" s="110"/>
       <c r="AC36" s="33"/>
       <c r="AD36" s="33"/>
       <c r="AE36" s="33"/>
@@ -4114,7 +4157,7 @@
       <c r="AQ36" s="31"/>
       <c r="AR36" s="13"/>
     </row>
-    <row r="37" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="12"/>
       <c r="B37" s="33"/>
       <c r="C37" s="33"/>
@@ -4128,21 +4171,21 @@
       <c r="K37" s="33"/>
       <c r="L37" s="33"/>
       <c r="M37" s="5"/>
-      <c r="N37" s="88"/>
-      <c r="O37" s="88"/>
-      <c r="P37" s="88"/>
-      <c r="Q37" s="88"/>
-      <c r="R37" s="88"/>
-      <c r="S37" s="88"/>
-      <c r="T37" s="88"/>
-      <c r="U37" s="88"/>
-      <c r="V37" s="88"/>
-      <c r="W37" s="88"/>
-      <c r="X37" s="88"/>
-      <c r="Y37" s="88"/>
-      <c r="Z37" s="88"/>
-      <c r="AA37" s="88"/>
-      <c r="AB37" s="88"/>
+      <c r="N37" s="110"/>
+      <c r="O37" s="110"/>
+      <c r="P37" s="110"/>
+      <c r="Q37" s="110"/>
+      <c r="R37" s="110"/>
+      <c r="S37" s="110"/>
+      <c r="T37" s="110"/>
+      <c r="U37" s="110"/>
+      <c r="V37" s="110"/>
+      <c r="W37" s="110"/>
+      <c r="X37" s="110"/>
+      <c r="Y37" s="110"/>
+      <c r="Z37" s="110"/>
+      <c r="AA37" s="110"/>
+      <c r="AB37" s="110"/>
       <c r="AC37" s="33"/>
       <c r="AD37" s="33"/>
       <c r="AE37" s="33"/>
@@ -4160,76 +4203,76 @@
       <c r="AQ37" s="31"/>
       <c r="AR37" s="13"/>
     </row>
-    <row r="38" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12"/>
-      <c r="B38" s="114" t="s">
+      <c r="B38" s="65" t="s">
         <v>51</v>
       </c>
-      <c r="C38" s="115"/>
+      <c r="C38" s="66"/>
       <c r="D38" s="57"/>
       <c r="E38" s="36"/>
-      <c r="F38" s="114" t="s">
+      <c r="F38" s="65" t="s">
         <v>51</v>
       </c>
-      <c r="G38" s="115"/>
+      <c r="G38" s="66"/>
       <c r="H38" s="57"/>
       <c r="I38" s="36"/>
-      <c r="J38" s="114" t="s">
+      <c r="J38" s="65" t="s">
         <v>61</v>
       </c>
-      <c r="K38" s="115"/>
+      <c r="K38" s="66"/>
       <c r="L38" s="57" t="s">
         <v>64</v>
       </c>
       <c r="M38" s="5"/>
-      <c r="N38" s="65"/>
-      <c r="O38" s="66"/>
+      <c r="N38" s="67"/>
+      <c r="O38" s="68"/>
       <c r="P38" s="34"/>
       <c r="Q38" s="36"/>
-      <c r="R38" s="65" t="s">
+      <c r="R38" s="67" t="s">
         <v>76</v>
       </c>
-      <c r="S38" s="66"/>
+      <c r="S38" s="68"/>
       <c r="T38" s="34" t="s">
         <v>67</v>
       </c>
       <c r="U38" s="36"/>
-      <c r="V38" s="65" t="s">
+      <c r="V38" s="67" t="s">
         <v>76</v>
       </c>
-      <c r="W38" s="66"/>
+      <c r="W38" s="68"/>
       <c r="X38" s="34" t="s">
         <v>67</v>
       </c>
       <c r="Y38" s="36"/>
-      <c r="Z38" s="65" t="s">
+      <c r="Z38" s="67" t="s">
         <v>76</v>
       </c>
-      <c r="AA38" s="66"/>
+      <c r="AA38" s="68"/>
       <c r="AB38" s="34" t="s">
         <v>67</v>
       </c>
       <c r="AC38" s="36"/>
-      <c r="AD38" s="65" t="s">
+      <c r="AD38" s="67" t="s">
         <v>76</v>
       </c>
-      <c r="AE38" s="66"/>
+      <c r="AE38" s="68"/>
       <c r="AF38" s="34" t="s">
         <v>67</v>
       </c>
       <c r="AG38" s="36"/>
-      <c r="AH38" s="65" t="s">
+      <c r="AH38" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="AI38" s="66"/>
+      <c r="AI38" s="68"/>
       <c r="AJ38" s="34" t="s">
         <v>49</v>
       </c>
       <c r="AK38" s="36"/>
-      <c r="AL38" s="65" t="s">
+      <c r="AL38" s="67" t="s">
         <v>73</v>
       </c>
-      <c r="AM38" s="66"/>
+      <c r="AM38" s="68"/>
       <c r="AN38" s="34" t="s">
         <v>74</v>
       </c>
@@ -4238,25 +4281,25 @@
       <c r="AQ38" s="31"/>
       <c r="AR38" s="13"/>
     </row>
-    <row r="39" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12"/>
-      <c r="B39" s="111" t="s">
+      <c r="B39" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="C39" s="112"/>
-      <c r="D39" s="113"/>
+      <c r="C39" s="85"/>
+      <c r="D39" s="86"/>
       <c r="E39" s="36"/>
-      <c r="F39" s="111" t="s">
+      <c r="F39" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="G39" s="112"/>
-      <c r="H39" s="113"/>
+      <c r="G39" s="85"/>
+      <c r="H39" s="86"/>
       <c r="I39" s="36"/>
-      <c r="J39" s="111" t="s">
+      <c r="J39" s="84" t="s">
         <v>62</v>
       </c>
-      <c r="K39" s="112"/>
-      <c r="L39" s="113"/>
+      <c r="K39" s="85"/>
+      <c r="L39" s="86"/>
       <c r="M39" s="5"/>
       <c r="N39" s="69"/>
       <c r="O39" s="70"/>
@@ -4302,181 +4345,181 @@
       <c r="AQ39" s="31"/>
       <c r="AR39" s="13"/>
     </row>
-    <row r="40" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12"/>
-      <c r="B40" s="116"/>
-      <c r="C40" s="117"/>
-      <c r="D40" s="118"/>
+      <c r="B40" s="90"/>
+      <c r="C40" s="91"/>
+      <c r="D40" s="92"/>
       <c r="E40" s="43"/>
-      <c r="F40" s="116"/>
-      <c r="G40" s="117"/>
-      <c r="H40" s="118"/>
+      <c r="F40" s="90"/>
+      <c r="G40" s="91"/>
+      <c r="H40" s="92"/>
       <c r="I40" s="43"/>
-      <c r="J40" s="116"/>
-      <c r="K40" s="117"/>
-      <c r="L40" s="118"/>
+      <c r="J40" s="90"/>
+      <c r="K40" s="91"/>
+      <c r="L40" s="92"/>
       <c r="M40" s="4"/>
-      <c r="N40" s="75"/>
-      <c r="O40" s="76"/>
-      <c r="P40" s="77"/>
+      <c r="N40" s="81"/>
+      <c r="O40" s="82"/>
+      <c r="P40" s="83"/>
       <c r="Q40" s="43"/>
-      <c r="R40" s="75"/>
-      <c r="S40" s="76"/>
-      <c r="T40" s="77"/>
+      <c r="R40" s="81"/>
+      <c r="S40" s="82"/>
+      <c r="T40" s="83"/>
       <c r="U40" s="35"/>
-      <c r="V40" s="75"/>
-      <c r="W40" s="76"/>
-      <c r="X40" s="77"/>
+      <c r="V40" s="81"/>
+      <c r="W40" s="82"/>
+      <c r="X40" s="83"/>
       <c r="Y40" s="36"/>
-      <c r="Z40" s="75"/>
-      <c r="AA40" s="76"/>
-      <c r="AB40" s="77"/>
+      <c r="Z40" s="81"/>
+      <c r="AA40" s="82"/>
+      <c r="AB40" s="83"/>
       <c r="AC40" s="36"/>
-      <c r="AD40" s="75"/>
-      <c r="AE40" s="76"/>
-      <c r="AF40" s="77"/>
+      <c r="AD40" s="81"/>
+      <c r="AE40" s="82"/>
+      <c r="AF40" s="83"/>
       <c r="AG40" s="43"/>
-      <c r="AH40" s="75"/>
-      <c r="AI40" s="76"/>
-      <c r="AJ40" s="77"/>
+      <c r="AH40" s="81"/>
+      <c r="AI40" s="82"/>
+      <c r="AJ40" s="83"/>
       <c r="AK40" s="43"/>
-      <c r="AL40" s="75"/>
-      <c r="AM40" s="76"/>
-      <c r="AN40" s="77"/>
+      <c r="AL40" s="81"/>
+      <c r="AM40" s="82"/>
+      <c r="AN40" s="83"/>
       <c r="AO40" s="31"/>
       <c r="AP40" s="31"/>
       <c r="AQ40" s="31"/>
       <c r="AR40" s="13"/>
     </row>
-    <row r="41" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12"/>
-      <c r="B41" s="72" t="s">
+      <c r="B41" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="C41" s="73"/>
-      <c r="D41" s="74"/>
+      <c r="C41" s="79"/>
+      <c r="D41" s="80"/>
       <c r="E41" s="37"/>
-      <c r="F41" s="72" t="s">
+      <c r="F41" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="G41" s="73"/>
-      <c r="H41" s="74"/>
+      <c r="G41" s="79"/>
+      <c r="H41" s="80"/>
       <c r="I41" s="31"/>
-      <c r="J41" s="72" t="s">
+      <c r="J41" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="K41" s="73"/>
-      <c r="L41" s="74"/>
+      <c r="K41" s="79"/>
+      <c r="L41" s="80"/>
       <c r="M41" s="5"/>
-      <c r="N41" s="72"/>
-      <c r="O41" s="73"/>
-      <c r="P41" s="74"/>
+      <c r="N41" s="78"/>
+      <c r="O41" s="79"/>
+      <c r="P41" s="80"/>
       <c r="Q41" s="32"/>
-      <c r="R41" s="72" t="s">
+      <c r="R41" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="S41" s="73"/>
-      <c r="T41" s="74"/>
+      <c r="S41" s="79"/>
+      <c r="T41" s="80"/>
       <c r="U41" s="31"/>
-      <c r="V41" s="72" t="s">
+      <c r="V41" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="W41" s="73"/>
-      <c r="X41" s="74"/>
+      <c r="W41" s="79"/>
+      <c r="X41" s="80"/>
       <c r="Y41" s="32"/>
-      <c r="Z41" s="72" t="s">
+      <c r="Z41" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="AA41" s="73"/>
-      <c r="AB41" s="74"/>
+      <c r="AA41" s="79"/>
+      <c r="AB41" s="80"/>
       <c r="AC41" s="32"/>
-      <c r="AD41" s="72" t="s">
+      <c r="AD41" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="AE41" s="73"/>
-      <c r="AF41" s="74"/>
+      <c r="AE41" s="79"/>
+      <c r="AF41" s="80"/>
       <c r="AG41" s="37"/>
-      <c r="AH41" s="72" t="s">
+      <c r="AH41" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="AI41" s="73"/>
-      <c r="AJ41" s="74"/>
+      <c r="AI41" s="79"/>
+      <c r="AJ41" s="80"/>
       <c r="AK41" s="31"/>
-      <c r="AL41" s="72" t="s">
+      <c r="AL41" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="AM41" s="73"/>
-      <c r="AN41" s="74"/>
+      <c r="AM41" s="79"/>
+      <c r="AN41" s="80"/>
       <c r="AO41" s="31"/>
       <c r="AP41" s="31"/>
       <c r="AQ41" s="31"/>
       <c r="AR41" s="13"/>
     </row>
-    <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12"/>
-      <c r="B42" s="72" t="s">
+      <c r="B42" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="C42" s="73"/>
-      <c r="D42" s="74"/>
+      <c r="C42" s="79"/>
+      <c r="D42" s="80"/>
       <c r="E42" s="44"/>
-      <c r="F42" s="72" t="s">
+      <c r="F42" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="G42" s="73"/>
-      <c r="H42" s="74"/>
+      <c r="G42" s="79"/>
+      <c r="H42" s="80"/>
       <c r="I42" s="31"/>
-      <c r="J42" s="72" t="s">
+      <c r="J42" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="K42" s="73"/>
-      <c r="L42" s="74"/>
+      <c r="K42" s="79"/>
+      <c r="L42" s="80"/>
       <c r="M42" s="5"/>
-      <c r="N42" s="72"/>
-      <c r="O42" s="73"/>
-      <c r="P42" s="74"/>
+      <c r="N42" s="78"/>
+      <c r="O42" s="79"/>
+      <c r="P42" s="80"/>
       <c r="Q42" s="31"/>
-      <c r="R42" s="72" t="s">
+      <c r="R42" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="S42" s="73"/>
-      <c r="T42" s="74"/>
+      <c r="S42" s="79"/>
+      <c r="T42" s="80"/>
       <c r="U42" s="32"/>
-      <c r="V42" s="72" t="s">
+      <c r="V42" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="W42" s="73"/>
-      <c r="X42" s="74"/>
+      <c r="W42" s="79"/>
+      <c r="X42" s="80"/>
       <c r="Y42" s="32"/>
-      <c r="Z42" s="72" t="s">
+      <c r="Z42" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="AA42" s="73"/>
-      <c r="AB42" s="74"/>
+      <c r="AA42" s="79"/>
+      <c r="AB42" s="80"/>
       <c r="AC42" s="32"/>
-      <c r="AD42" s="72" t="s">
+      <c r="AD42" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="AE42" s="73"/>
-      <c r="AF42" s="74"/>
+      <c r="AE42" s="79"/>
+      <c r="AF42" s="80"/>
       <c r="AG42" s="44"/>
-      <c r="AH42" s="72" t="s">
+      <c r="AH42" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="AI42" s="73"/>
-      <c r="AJ42" s="74"/>
+      <c r="AI42" s="79"/>
+      <c r="AJ42" s="80"/>
       <c r="AK42" s="31"/>
-      <c r="AL42" s="72" t="s">
+      <c r="AL42" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="AM42" s="73"/>
-      <c r="AN42" s="74"/>
+      <c r="AM42" s="79"/>
+      <c r="AN42" s="80"/>
       <c r="AO42" s="31"/>
       <c r="AP42" s="31"/>
       <c r="AQ42" s="31"/>
       <c r="AR42" s="13"/>
     </row>
-    <row r="43" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12"/>
       <c r="B43" s="62" t="s">
         <v>27</v>
@@ -4528,7 +4571,7 @@
       <c r="AQ43" s="31"/>
       <c r="AR43" s="13"/>
     </row>
-    <row r="44" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12"/>
       <c r="B44" s="35"/>
       <c r="C44" s="35"/>
@@ -4574,76 +4617,76 @@
       <c r="AQ44" s="31"/>
       <c r="AR44" s="13"/>
     </row>
-    <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12"/>
-      <c r="B45" s="114" t="s">
+      <c r="B45" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="C45" s="115"/>
+      <c r="C45" s="66"/>
       <c r="D45" s="57" t="s">
         <v>50</v>
       </c>
       <c r="E45" s="36"/>
-      <c r="F45" s="114" t="s">
+      <c r="F45" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="G45" s="115"/>
+      <c r="G45" s="66"/>
       <c r="H45" s="57" t="s">
         <v>49</v>
       </c>
       <c r="I45" s="32"/>
-      <c r="J45" s="114" t="s">
+      <c r="J45" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="K45" s="115"/>
+      <c r="K45" s="66"/>
       <c r="L45" s="57" t="s">
         <v>50</v>
       </c>
       <c r="M45" s="14"/>
-      <c r="N45" s="65"/>
-      <c r="O45" s="66"/>
+      <c r="N45" s="67"/>
+      <c r="O45" s="68"/>
       <c r="P45" s="34"/>
       <c r="Q45" s="36"/>
-      <c r="R45" s="65" t="s">
+      <c r="R45" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="S45" s="66"/>
+      <c r="S45" s="68"/>
       <c r="T45" s="34" t="s">
         <v>66</v>
       </c>
       <c r="U45" s="36"/>
-      <c r="V45" s="65" t="s">
+      <c r="V45" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="W45" s="66"/>
+      <c r="W45" s="68"/>
       <c r="X45" s="34"/>
       <c r="Y45" s="54"/>
-      <c r="Z45" s="65" t="s">
+      <c r="Z45" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="AA45" s="66"/>
+      <c r="AA45" s="68"/>
       <c r="AB45" s="34"/>
       <c r="AC45" s="36"/>
-      <c r="AD45" s="65" t="s">
+      <c r="AD45" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="AE45" s="66"/>
+      <c r="AE45" s="68"/>
       <c r="AF45" s="34" t="s">
         <v>66</v>
       </c>
       <c r="AG45" s="36"/>
-      <c r="AH45" s="65" t="s">
+      <c r="AH45" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="AI45" s="66"/>
+      <c r="AI45" s="68"/>
       <c r="AJ45" s="34" t="s">
         <v>50</v>
       </c>
       <c r="AK45" s="32"/>
-      <c r="AL45" s="65" t="s">
+      <c r="AL45" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="AM45" s="66"/>
+      <c r="AM45" s="68"/>
       <c r="AN45" s="34" t="s">
         <v>49</v>
       </c>
@@ -4652,25 +4695,25 @@
       <c r="AQ45" s="31"/>
       <c r="AR45" s="13"/>
     </row>
-    <row r="46" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12"/>
-      <c r="B46" s="111" t="s">
+      <c r="B46" s="84" t="s">
         <v>47</v>
       </c>
-      <c r="C46" s="112"/>
-      <c r="D46" s="113"/>
+      <c r="C46" s="85"/>
+      <c r="D46" s="86"/>
       <c r="E46" s="36"/>
-      <c r="F46" s="111" t="s">
+      <c r="F46" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="G46" s="112"/>
-      <c r="H46" s="113"/>
+      <c r="G46" s="85"/>
+      <c r="H46" s="86"/>
       <c r="I46" s="54"/>
-      <c r="J46" s="111" t="s">
+      <c r="J46" s="84" t="s">
         <v>47</v>
       </c>
-      <c r="K46" s="112"/>
-      <c r="L46" s="113"/>
+      <c r="K46" s="85"/>
+      <c r="L46" s="86"/>
       <c r="M46" s="4"/>
       <c r="N46" s="69"/>
       <c r="O46" s="70"/>
@@ -4716,182 +4759,182 @@
       <c r="AQ46" s="31"/>
       <c r="AR46" s="13"/>
     </row>
-    <row r="47" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12"/>
-      <c r="B47" s="116"/>
-      <c r="C47" s="117"/>
-      <c r="D47" s="118"/>
+      <c r="B47" s="90"/>
+      <c r="C47" s="91"/>
+      <c r="D47" s="92"/>
       <c r="E47" s="43"/>
-      <c r="F47" s="116"/>
-      <c r="G47" s="117"/>
-      <c r="H47" s="118"/>
+      <c r="F47" s="90"/>
+      <c r="G47" s="91"/>
+      <c r="H47" s="92"/>
       <c r="I47" s="37"/>
-      <c r="J47" s="116"/>
-      <c r="K47" s="117"/>
-      <c r="L47" s="118"/>
+      <c r="J47" s="90"/>
+      <c r="K47" s="91"/>
+      <c r="L47" s="92"/>
       <c r="M47" s="4"/>
-      <c r="N47" s="75"/>
-      <c r="O47" s="76"/>
-      <c r="P47" s="77"/>
+      <c r="N47" s="81"/>
+      <c r="O47" s="82"/>
+      <c r="P47" s="83"/>
       <c r="Q47" s="37"/>
-      <c r="R47" s="75"/>
-      <c r="S47" s="76"/>
-      <c r="T47" s="77"/>
+      <c r="R47" s="81"/>
+      <c r="S47" s="82"/>
+      <c r="T47" s="83"/>
       <c r="U47" s="43"/>
-      <c r="V47" s="75" t="s">
+      <c r="V47" s="81" t="s">
         <v>46</v>
       </c>
-      <c r="W47" s="76"/>
-      <c r="X47" s="77"/>
+      <c r="W47" s="82"/>
+      <c r="X47" s="83"/>
       <c r="Y47" s="35"/>
-      <c r="Z47" s="75"/>
-      <c r="AA47" s="76"/>
-      <c r="AB47" s="77"/>
+      <c r="Z47" s="81"/>
+      <c r="AA47" s="82"/>
+      <c r="AB47" s="83"/>
       <c r="AC47" s="35"/>
-      <c r="AD47" s="75"/>
-      <c r="AE47" s="76"/>
-      <c r="AF47" s="77"/>
+      <c r="AD47" s="81"/>
+      <c r="AE47" s="82"/>
+      <c r="AF47" s="83"/>
       <c r="AG47" s="43"/>
-      <c r="AH47" s="75"/>
-      <c r="AI47" s="76"/>
-      <c r="AJ47" s="77"/>
+      <c r="AH47" s="81"/>
+      <c r="AI47" s="82"/>
+      <c r="AJ47" s="83"/>
       <c r="AK47" s="37"/>
-      <c r="AL47" s="75"/>
-      <c r="AM47" s="76"/>
-      <c r="AN47" s="77"/>
+      <c r="AL47" s="81"/>
+      <c r="AM47" s="82"/>
+      <c r="AN47" s="83"/>
       <c r="AO47" s="31"/>
       <c r="AP47" s="31"/>
       <c r="AQ47" s="31"/>
       <c r="AR47" s="13"/>
     </row>
-    <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12"/>
-      <c r="B48" s="72" t="s">
+      <c r="B48" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="73"/>
-      <c r="D48" s="74"/>
+      <c r="C48" s="79"/>
+      <c r="D48" s="80"/>
       <c r="E48" s="37"/>
-      <c r="F48" s="72" t="s">
+      <c r="F48" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="G48" s="73"/>
-      <c r="H48" s="74"/>
+      <c r="G48" s="79"/>
+      <c r="H48" s="80"/>
       <c r="I48" s="44"/>
-      <c r="J48" s="72" t="s">
+      <c r="J48" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="K48" s="73"/>
-      <c r="L48" s="74"/>
+      <c r="K48" s="79"/>
+      <c r="L48" s="80"/>
       <c r="M48" s="5"/>
-      <c r="N48" s="72"/>
-      <c r="O48" s="73"/>
-      <c r="P48" s="74"/>
+      <c r="N48" s="78"/>
+      <c r="O48" s="79"/>
+      <c r="P48" s="80"/>
       <c r="Q48" s="44"/>
-      <c r="R48" s="72" t="s">
+      <c r="R48" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="S48" s="73"/>
-      <c r="T48" s="74"/>
+      <c r="S48" s="79"/>
+      <c r="T48" s="80"/>
       <c r="U48" s="37"/>
-      <c r="V48" s="72" t="s">
+      <c r="V48" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="W48" s="73"/>
-      <c r="X48" s="74"/>
+      <c r="W48" s="79"/>
+      <c r="X48" s="80"/>
       <c r="Y48" s="40"/>
-      <c r="Z48" s="72" t="s">
+      <c r="Z48" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="AA48" s="73"/>
-      <c r="AB48" s="74"/>
+      <c r="AA48" s="79"/>
+      <c r="AB48" s="80"/>
       <c r="AC48" s="43"/>
-      <c r="AD48" s="72" t="s">
+      <c r="AD48" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="AE48" s="73"/>
-      <c r="AF48" s="74"/>
+      <c r="AE48" s="79"/>
+      <c r="AF48" s="80"/>
       <c r="AG48" s="37"/>
-      <c r="AH48" s="72" t="s">
+      <c r="AH48" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="AI48" s="73"/>
-      <c r="AJ48" s="74"/>
+      <c r="AI48" s="79"/>
+      <c r="AJ48" s="80"/>
       <c r="AK48" s="44"/>
-      <c r="AL48" s="72" t="s">
+      <c r="AL48" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="AM48" s="73"/>
-      <c r="AN48" s="74"/>
+      <c r="AM48" s="79"/>
+      <c r="AN48" s="80"/>
       <c r="AO48" s="31"/>
       <c r="AP48" s="31"/>
       <c r="AQ48" s="31"/>
       <c r="AR48" s="13"/>
     </row>
-    <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="72" t="s">
+    <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="C49" s="73"/>
-      <c r="D49" s="74"/>
+      <c r="C49" s="79"/>
+      <c r="D49" s="80"/>
       <c r="E49" s="35"/>
-      <c r="F49" s="72" t="s">
+      <c r="F49" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="G49" s="73"/>
-      <c r="H49" s="74"/>
+      <c r="G49" s="79"/>
+      <c r="H49" s="80"/>
       <c r="I49" s="44"/>
-      <c r="J49" s="72" t="s">
+      <c r="J49" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="K49" s="73"/>
-      <c r="L49" s="74"/>
+      <c r="K49" s="79"/>
+      <c r="L49" s="80"/>
       <c r="M49" s="5"/>
-      <c r="N49" s="72"/>
-      <c r="O49" s="73"/>
-      <c r="P49" s="74"/>
+      <c r="N49" s="78"/>
+      <c r="O49" s="79"/>
+      <c r="P49" s="80"/>
       <c r="Q49" s="44"/>
-      <c r="R49" s="72" t="s">
-        <v>10</v>
-      </c>
-      <c r="S49" s="73"/>
-      <c r="T49" s="74"/>
+      <c r="R49" s="135" t="s">
+        <v>37</v>
+      </c>
+      <c r="S49" s="136"/>
+      <c r="T49" s="137"/>
       <c r="U49" s="44"/>
-      <c r="V49" s="72" t="s">
+      <c r="V49" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="W49" s="73"/>
-      <c r="X49" s="74"/>
+      <c r="W49" s="79"/>
+      <c r="X49" s="80"/>
       <c r="Y49" s="44"/>
-      <c r="Z49" s="72" t="s">
+      <c r="Z49" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="AA49" s="73"/>
-      <c r="AB49" s="74"/>
+      <c r="AA49" s="79"/>
+      <c r="AB49" s="80"/>
       <c r="AC49" s="35"/>
-      <c r="AD49" s="72" t="s">
+      <c r="AD49" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="AE49" s="73"/>
-      <c r="AF49" s="74"/>
+      <c r="AE49" s="79"/>
+      <c r="AF49" s="80"/>
       <c r="AG49" s="35"/>
-      <c r="AH49" s="72" t="s">
+      <c r="AH49" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="AI49" s="73"/>
-      <c r="AJ49" s="74"/>
+      <c r="AI49" s="79"/>
+      <c r="AJ49" s="80"/>
       <c r="AK49" s="44"/>
-      <c r="AL49" s="72" t="s">
+      <c r="AL49" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="AM49" s="73"/>
-      <c r="AN49" s="74"/>
+      <c r="AM49" s="79"/>
+      <c r="AN49" s="80"/>
       <c r="AO49" s="31"/>
       <c r="AP49" s="31"/>
       <c r="AQ49" s="31"/>
       <c r="AR49" s="13"/>
     </row>
-    <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B50" s="62" t="s">
         <v>15</v>
       </c>
@@ -4914,21 +4957,23 @@
       <c r="O50" s="63"/>
       <c r="P50" s="64"/>
       <c r="Q50" s="50"/>
-      <c r="R50" s="62"/>
-      <c r="S50" s="63"/>
-      <c r="T50" s="64"/>
+      <c r="R50" s="144" t="s">
+        <v>96</v>
+      </c>
+      <c r="S50" s="145"/>
+      <c r="T50" s="146"/>
       <c r="U50" s="50"/>
-      <c r="V50" s="72" t="s">
+      <c r="V50" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="W50" s="73"/>
-      <c r="X50" s="74"/>
+      <c r="W50" s="79"/>
+      <c r="X50" s="80"/>
       <c r="Y50" s="36"/>
-      <c r="Z50" s="72" t="s">
+      <c r="Z50" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="AA50" s="73"/>
-      <c r="AB50" s="74"/>
+      <c r="AA50" s="79"/>
+      <c r="AB50" s="80"/>
       <c r="AC50" s="50"/>
       <c r="AD50" s="62" t="s">
         <v>26</v>
@@ -4952,7 +4997,7 @@
       <c r="AQ50" s="31"/>
       <c r="AR50" s="13"/>
     </row>
-    <row r="51" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B51" s="35"/>
       <c r="C51" s="35"/>
       <c r="D51" s="35"/>
@@ -5001,34 +5046,38 @@
       <c r="AQ51" s="31"/>
       <c r="AR51" s="13"/>
     </row>
-    <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="114"/>
-      <c r="C52" s="115"/>
+    <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B52" s="65"/>
+      <c r="C52" s="66"/>
       <c r="D52" s="57"/>
       <c r="E52" s="36"/>
-      <c r="F52" s="93" t="s">
+      <c r="F52" s="111" t="s">
         <v>89</v>
       </c>
-      <c r="G52" s="94"/>
+      <c r="G52" s="112"/>
       <c r="H52" s="59" t="s">
         <v>90</v>
       </c>
       <c r="I52" s="54"/>
-      <c r="J52" s="114" t="s">
+      <c r="J52" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="K52" s="115"/>
+      <c r="K52" s="66"/>
       <c r="L52" s="57" t="s">
         <v>50</v>
       </c>
       <c r="M52" s="14"/>
-      <c r="N52" s="65"/>
-      <c r="O52" s="66"/>
+      <c r="N52" s="67"/>
+      <c r="O52" s="68"/>
       <c r="P52" s="34"/>
       <c r="Q52" s="31"/>
-      <c r="R52" s="65"/>
-      <c r="S52" s="66"/>
-      <c r="T52" s="34"/>
+      <c r="R52" s="111" t="s">
+        <v>89</v>
+      </c>
+      <c r="S52" s="112"/>
+      <c r="T52" s="59" t="s">
+        <v>94</v>
+      </c>
       <c r="U52" s="35"/>
       <c r="V52" s="35"/>
       <c r="W52" s="35"/>
@@ -5038,54 +5087,56 @@
       <c r="AA52" s="35"/>
       <c r="AB52" s="35"/>
       <c r="AC52" s="36"/>
-      <c r="AD52" s="65"/>
-      <c r="AE52" s="66"/>
+      <c r="AD52" s="67"/>
+      <c r="AE52" s="68"/>
       <c r="AF52" s="34"/>
       <c r="AG52" s="36"/>
-      <c r="AH52" s="65"/>
-      <c r="AI52" s="66"/>
+      <c r="AH52" s="67"/>
+      <c r="AI52" s="68"/>
       <c r="AJ52" s="34"/>
       <c r="AK52" s="54"/>
-      <c r="AL52" s="65"/>
-      <c r="AM52" s="66"/>
+      <c r="AL52" s="67"/>
+      <c r="AM52" s="68"/>
       <c r="AN52" s="34"/>
       <c r="AR52" s="13"/>
     </row>
-    <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="111"/>
-      <c r="C53" s="112"/>
-      <c r="D53" s="113"/>
+    <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B53" s="84"/>
+      <c r="C53" s="85"/>
+      <c r="D53" s="86"/>
       <c r="E53" s="36"/>
-      <c r="F53" s="111" t="s">
+      <c r="F53" s="84" t="s">
         <v>91</v>
       </c>
-      <c r="G53" s="112"/>
-      <c r="H53" s="113"/>
+      <c r="G53" s="85"/>
+      <c r="H53" s="86"/>
       <c r="I53" s="35"/>
-      <c r="J53" s="111" t="s">
+      <c r="J53" s="84" t="s">
         <v>63</v>
       </c>
-      <c r="K53" s="112"/>
-      <c r="L53" s="113"/>
+      <c r="K53" s="85"/>
+      <c r="L53" s="86"/>
       <c r="M53" s="4"/>
       <c r="N53" s="69"/>
       <c r="O53" s="70"/>
       <c r="P53" s="71"/>
       <c r="Q53" s="32"/>
-      <c r="R53" s="69"/>
+      <c r="R53" s="69" t="s">
+        <v>95</v>
+      </c>
       <c r="S53" s="70"/>
       <c r="T53" s="71"/>
       <c r="U53" s="43"/>
-      <c r="V53" s="65" t="s">
+      <c r="V53" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="W53" s="66"/>
+      <c r="W53" s="68"/>
       <c r="X53" s="34" t="s">
         <v>66</v>
       </c>
       <c r="Y53" s="35"/>
-      <c r="Z53" s="65"/>
-      <c r="AA53" s="66"/>
+      <c r="Z53" s="67"/>
+      <c r="AA53" s="68"/>
       <c r="AB53" s="34"/>
       <c r="AC53" s="35"/>
       <c r="AD53" s="69"/>
@@ -5101,26 +5152,26 @@
       <c r="AN53" s="71"/>
       <c r="AR53" s="13"/>
     </row>
-    <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="116"/>
-      <c r="C54" s="117"/>
-      <c r="D54" s="118"/>
+    <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B54" s="90"/>
+      <c r="C54" s="91"/>
+      <c r="D54" s="92"/>
       <c r="E54" s="43"/>
-      <c r="F54" s="116"/>
-      <c r="G54" s="117"/>
-      <c r="H54" s="118"/>
+      <c r="F54" s="90"/>
+      <c r="G54" s="91"/>
+      <c r="H54" s="92"/>
       <c r="I54" s="35"/>
-      <c r="J54" s="116"/>
-      <c r="K54" s="117"/>
-      <c r="L54" s="118"/>
+      <c r="J54" s="90"/>
+      <c r="K54" s="91"/>
+      <c r="L54" s="92"/>
       <c r="M54" s="4"/>
-      <c r="N54" s="75"/>
-      <c r="O54" s="76"/>
-      <c r="P54" s="77"/>
+      <c r="N54" s="81"/>
+      <c r="O54" s="82"/>
+      <c r="P54" s="83"/>
       <c r="Q54" s="43"/>
-      <c r="R54" s="75"/>
-      <c r="S54" s="76"/>
-      <c r="T54" s="77"/>
+      <c r="R54" s="81"/>
+      <c r="S54" s="82"/>
+      <c r="T54" s="83"/>
       <c r="U54" s="37"/>
       <c r="V54" s="69" t="s">
         <v>83</v>
@@ -5132,114 +5183,118 @@
       <c r="AA54" s="70"/>
       <c r="AB54" s="71"/>
       <c r="AC54" s="31"/>
-      <c r="AD54" s="75"/>
-      <c r="AE54" s="76"/>
-      <c r="AF54" s="77"/>
+      <c r="AD54" s="81"/>
+      <c r="AE54" s="82"/>
+      <c r="AF54" s="83"/>
       <c r="AG54" s="43"/>
-      <c r="AH54" s="75"/>
-      <c r="AI54" s="76"/>
-      <c r="AJ54" s="77"/>
+      <c r="AH54" s="81"/>
+      <c r="AI54" s="82"/>
+      <c r="AJ54" s="83"/>
       <c r="AK54" s="35"/>
-      <c r="AL54" s="75"/>
-      <c r="AM54" s="76"/>
-      <c r="AN54" s="77"/>
+      <c r="AL54" s="81"/>
+      <c r="AM54" s="82"/>
+      <c r="AN54" s="83"/>
       <c r="AR54" s="13"/>
     </row>
-    <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="72"/>
-      <c r="C55" s="73"/>
-      <c r="D55" s="74"/>
+    <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="78"/>
+      <c r="C55" s="79"/>
+      <c r="D55" s="80"/>
       <c r="E55" s="37"/>
-      <c r="F55" s="72" t="s">
+      <c r="F55" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="G55" s="73"/>
-      <c r="H55" s="74"/>
+      <c r="G55" s="79"/>
+      <c r="H55" s="80"/>
       <c r="I55" s="40"/>
-      <c r="J55" s="72" t="s">
+      <c r="J55" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="K55" s="73"/>
-      <c r="L55" s="74"/>
+      <c r="K55" s="79"/>
+      <c r="L55" s="80"/>
       <c r="M55" s="5"/>
-      <c r="N55" s="72"/>
-      <c r="O55" s="73"/>
-      <c r="P55" s="74"/>
+      <c r="N55" s="78"/>
+      <c r="O55" s="79"/>
+      <c r="P55" s="80"/>
       <c r="Q55" s="43"/>
-      <c r="R55" s="72"/>
-      <c r="S55" s="73"/>
-      <c r="T55" s="74"/>
+      <c r="R55" s="78" t="s">
+        <v>22</v>
+      </c>
+      <c r="S55" s="79"/>
+      <c r="T55" s="80"/>
       <c r="U55" s="44"/>
-      <c r="V55" s="75"/>
-      <c r="W55" s="76"/>
-      <c r="X55" s="77"/>
+      <c r="V55" s="81"/>
+      <c r="W55" s="82"/>
+      <c r="X55" s="83"/>
       <c r="Y55" s="44"/>
-      <c r="Z55" s="75"/>
-      <c r="AA55" s="76"/>
-      <c r="AB55" s="77"/>
+      <c r="Z55" s="81"/>
+      <c r="AA55" s="82"/>
+      <c r="AB55" s="83"/>
       <c r="AC55" s="35"/>
-      <c r="AD55" s="72"/>
-      <c r="AE55" s="73"/>
-      <c r="AF55" s="74"/>
+      <c r="AD55" s="78"/>
+      <c r="AE55" s="79"/>
+      <c r="AF55" s="80"/>
       <c r="AG55" s="37"/>
-      <c r="AH55" s="72"/>
-      <c r="AI55" s="73"/>
-      <c r="AJ55" s="74"/>
+      <c r="AH55" s="78"/>
+      <c r="AI55" s="79"/>
+      <c r="AJ55" s="80"/>
       <c r="AK55" s="40"/>
-      <c r="AL55" s="72"/>
-      <c r="AM55" s="73"/>
-      <c r="AN55" s="74"/>
+      <c r="AL55" s="78"/>
+      <c r="AM55" s="79"/>
+      <c r="AN55" s="80"/>
       <c r="AR55" s="13"/>
     </row>
-    <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="72"/>
-      <c r="C56" s="73"/>
-      <c r="D56" s="74"/>
+    <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B56" s="78"/>
+      <c r="C56" s="79"/>
+      <c r="D56" s="80"/>
       <c r="E56" s="44"/>
-      <c r="F56" s="72" t="s">
+      <c r="F56" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="G56" s="73"/>
-      <c r="H56" s="74"/>
+      <c r="G56" s="79"/>
+      <c r="H56" s="80"/>
       <c r="I56" s="44"/>
-      <c r="J56" s="72" t="s">
+      <c r="J56" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="K56" s="73"/>
-      <c r="L56" s="74"/>
+      <c r="K56" s="79"/>
+      <c r="L56" s="80"/>
       <c r="M56" s="5"/>
-      <c r="N56" s="72"/>
-      <c r="O56" s="73"/>
-      <c r="P56" s="74"/>
+      <c r="N56" s="78"/>
+      <c r="O56" s="79"/>
+      <c r="P56" s="80"/>
       <c r="Q56" s="43"/>
-      <c r="R56" s="72"/>
-      <c r="S56" s="73"/>
-      <c r="T56" s="74"/>
+      <c r="R56" s="78" t="s">
+        <v>10</v>
+      </c>
+      <c r="S56" s="79"/>
+      <c r="T56" s="80"/>
       <c r="U56" s="44"/>
-      <c r="V56" s="72" t="s">
+      <c r="V56" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="W56" s="73"/>
-      <c r="X56" s="74"/>
+      <c r="W56" s="79"/>
+      <c r="X56" s="80"/>
       <c r="Y56" s="50"/>
-      <c r="Z56" s="72"/>
-      <c r="AA56" s="73"/>
-      <c r="AB56" s="74"/>
+      <c r="Z56" s="78"/>
+      <c r="AA56" s="79"/>
+      <c r="AB56" s="80"/>
       <c r="AC56" s="43"/>
-      <c r="AD56" s="72"/>
-      <c r="AE56" s="73"/>
-      <c r="AF56" s="74"/>
+      <c r="AD56" s="78"/>
+      <c r="AE56" s="79"/>
+      <c r="AF56" s="80"/>
       <c r="AG56" s="44"/>
-      <c r="AH56" s="72"/>
-      <c r="AI56" s="73"/>
-      <c r="AJ56" s="74"/>
+      <c r="AH56" s="78"/>
+      <c r="AI56" s="79"/>
+      <c r="AJ56" s="80"/>
       <c r="AK56" s="44"/>
-      <c r="AL56" s="72"/>
-      <c r="AM56" s="73"/>
-      <c r="AN56" s="74"/>
+      <c r="AL56" s="78"/>
+      <c r="AM56" s="79"/>
+      <c r="AN56" s="80"/>
       <c r="AR56" s="13"/>
     </row>
-    <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B57" s="62"/>
       <c r="C57" s="63"/>
       <c r="D57" s="64"/>
@@ -5248,11 +5303,11 @@
       <c r="G57" s="63"/>
       <c r="H57" s="64"/>
       <c r="I57" s="50"/>
-      <c r="J57" s="125" t="s">
+      <c r="J57" s="101" t="s">
         <v>8</v>
       </c>
-      <c r="K57" s="126"/>
-      <c r="L57" s="127"/>
+      <c r="K57" s="102"/>
+      <c r="L57" s="103"/>
       <c r="M57" s="5"/>
       <c r="N57" s="62"/>
       <c r="O57" s="63"/>
@@ -5285,7 +5340,7 @@
       <c r="AN57" s="64"/>
       <c r="AR57" s="13"/>
     </row>
-    <row r="58" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B58" s="35"/>
       <c r="C58" s="35"/>
       <c r="D58" s="35"/>
@@ -5327,60 +5382,60 @@
       <c r="AN58" s="35"/>
       <c r="AR58" s="13"/>
     </row>
-    <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="114"/>
-      <c r="C59" s="115"/>
+    <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B59" s="65"/>
+      <c r="C59" s="66"/>
       <c r="D59" s="57"/>
       <c r="E59" s="50"/>
-      <c r="F59" s="114"/>
-      <c r="G59" s="115"/>
+      <c r="F59" s="65"/>
+      <c r="G59" s="66"/>
       <c r="H59" s="57"/>
       <c r="I59" s="32"/>
-      <c r="J59" s="114"/>
-      <c r="K59" s="115"/>
+      <c r="J59" s="65"/>
+      <c r="K59" s="66"/>
       <c r="L59" s="57"/>
       <c r="M59" s="6"/>
-      <c r="N59" s="65"/>
-      <c r="O59" s="66"/>
+      <c r="N59" s="67"/>
+      <c r="O59" s="68"/>
       <c r="P59" s="34"/>
       <c r="Q59" s="36"/>
-      <c r="R59" s="65"/>
-      <c r="S59" s="66"/>
+      <c r="R59" s="67"/>
+      <c r="S59" s="68"/>
       <c r="T59" s="34"/>
       <c r="U59" s="50"/>
-      <c r="V59" s="65"/>
-      <c r="W59" s="66"/>
+      <c r="V59" s="67"/>
+      <c r="W59" s="68"/>
       <c r="X59" s="34"/>
       <c r="Y59" s="32"/>
-      <c r="Z59" s="65"/>
-      <c r="AA59" s="66"/>
+      <c r="Z59" s="67"/>
+      <c r="AA59" s="68"/>
       <c r="AB59" s="34"/>
       <c r="AC59" s="32"/>
-      <c r="AD59" s="65"/>
-      <c r="AE59" s="66"/>
+      <c r="AD59" s="67"/>
+      <c r="AE59" s="68"/>
       <c r="AF59" s="34"/>
       <c r="AG59" s="50"/>
-      <c r="AH59" s="65"/>
-      <c r="AI59" s="66"/>
+      <c r="AH59" s="67"/>
+      <c r="AI59" s="68"/>
       <c r="AJ59" s="34"/>
       <c r="AK59" s="32"/>
-      <c r="AL59" s="65"/>
-      <c r="AM59" s="66"/>
+      <c r="AL59" s="67"/>
+      <c r="AM59" s="68"/>
       <c r="AN59" s="34"/>
       <c r="AR59" s="13"/>
     </row>
-    <row r="60" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="111"/>
-      <c r="C60" s="112"/>
-      <c r="D60" s="113"/>
+    <row r="60" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B60" s="84"/>
+      <c r="C60" s="85"/>
+      <c r="D60" s="86"/>
       <c r="E60" s="32"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="113"/>
+      <c r="F60" s="84"/>
+      <c r="G60" s="85"/>
+      <c r="H60" s="86"/>
       <c r="I60" s="32"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
-      <c r="L60" s="113"/>
+      <c r="J60" s="84"/>
+      <c r="K60" s="85"/>
+      <c r="L60" s="86"/>
       <c r="M60" s="4"/>
       <c r="N60" s="69"/>
       <c r="O60" s="70"/>
@@ -5411,133 +5466,133 @@
       <c r="AN60" s="71"/>
       <c r="AR60" s="13"/>
     </row>
-    <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="116"/>
-      <c r="C61" s="117"/>
-      <c r="D61" s="118"/>
+    <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B61" s="90"/>
+      <c r="C61" s="91"/>
+      <c r="D61" s="92"/>
       <c r="E61" s="32"/>
-      <c r="F61" s="116"/>
-      <c r="G61" s="117"/>
-      <c r="H61" s="118"/>
+      <c r="F61" s="90"/>
+      <c r="G61" s="91"/>
+      <c r="H61" s="92"/>
       <c r="I61" s="32"/>
-      <c r="J61" s="116"/>
-      <c r="K61" s="117"/>
-      <c r="L61" s="118"/>
+      <c r="J61" s="90"/>
+      <c r="K61" s="91"/>
+      <c r="L61" s="92"/>
       <c r="M61" s="4"/>
-      <c r="N61" s="75"/>
-      <c r="O61" s="76"/>
-      <c r="P61" s="77"/>
+      <c r="N61" s="81"/>
+      <c r="O61" s="82"/>
+      <c r="P61" s="83"/>
       <c r="Q61" s="37"/>
-      <c r="R61" s="75"/>
-      <c r="S61" s="76"/>
-      <c r="T61" s="77"/>
+      <c r="R61" s="81"/>
+      <c r="S61" s="82"/>
+      <c r="T61" s="83"/>
       <c r="U61" s="32"/>
-      <c r="V61" s="75"/>
-      <c r="W61" s="76"/>
-      <c r="X61" s="77"/>
+      <c r="V61" s="81"/>
+      <c r="W61" s="82"/>
+      <c r="X61" s="83"/>
       <c r="Y61" s="32"/>
-      <c r="Z61" s="75"/>
-      <c r="AA61" s="76"/>
-      <c r="AB61" s="77"/>
+      <c r="Z61" s="81"/>
+      <c r="AA61" s="82"/>
+      <c r="AB61" s="83"/>
       <c r="AC61" s="35"/>
-      <c r="AD61" s="75"/>
-      <c r="AE61" s="76"/>
-      <c r="AF61" s="77"/>
+      <c r="AD61" s="81"/>
+      <c r="AE61" s="82"/>
+      <c r="AF61" s="83"/>
       <c r="AG61" s="32"/>
-      <c r="AH61" s="75"/>
-      <c r="AI61" s="76"/>
-      <c r="AJ61" s="77"/>
+      <c r="AH61" s="81"/>
+      <c r="AI61" s="82"/>
+      <c r="AJ61" s="83"/>
       <c r="AK61" s="32"/>
-      <c r="AL61" s="75"/>
-      <c r="AM61" s="76"/>
-      <c r="AN61" s="77"/>
+      <c r="AL61" s="81"/>
+      <c r="AM61" s="82"/>
+      <c r="AN61" s="83"/>
       <c r="AR61" s="13"/>
     </row>
-    <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="78"/>
-      <c r="C62" s="79"/>
-      <c r="D62" s="80"/>
+    <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="87"/>
+      <c r="C62" s="88"/>
+      <c r="D62" s="89"/>
       <c r="E62" s="37"/>
-      <c r="F62" s="78"/>
-      <c r="G62" s="79"/>
-      <c r="H62" s="80"/>
+      <c r="F62" s="87"/>
+      <c r="G62" s="88"/>
+      <c r="H62" s="89"/>
       <c r="I62" s="35"/>
-      <c r="J62" s="78"/>
-      <c r="K62" s="79"/>
-      <c r="L62" s="80"/>
+      <c r="J62" s="87"/>
+      <c r="K62" s="88"/>
+      <c r="L62" s="89"/>
       <c r="M62" s="4"/>
-      <c r="N62" s="72"/>
-      <c r="O62" s="73"/>
-      <c r="P62" s="74"/>
+      <c r="N62" s="78"/>
+      <c r="O62" s="79"/>
+      <c r="P62" s="80"/>
       <c r="Q62" s="44"/>
-      <c r="R62" s="78"/>
-      <c r="S62" s="79"/>
-      <c r="T62" s="80"/>
+      <c r="R62" s="87"/>
+      <c r="S62" s="88"/>
+      <c r="T62" s="89"/>
       <c r="U62" s="37"/>
-      <c r="V62" s="78"/>
-      <c r="W62" s="79"/>
-      <c r="X62" s="80"/>
+      <c r="V62" s="87"/>
+      <c r="W62" s="88"/>
+      <c r="X62" s="89"/>
       <c r="Y62" s="35"/>
-      <c r="Z62" s="72"/>
-      <c r="AA62" s="73"/>
-      <c r="AB62" s="74"/>
+      <c r="Z62" s="78"/>
+      <c r="AA62" s="79"/>
+      <c r="AB62" s="80"/>
       <c r="AC62" s="35"/>
-      <c r="AD62" s="78"/>
-      <c r="AE62" s="79"/>
-      <c r="AF62" s="80"/>
+      <c r="AD62" s="87"/>
+      <c r="AE62" s="88"/>
+      <c r="AF62" s="89"/>
       <c r="AG62" s="37"/>
-      <c r="AH62" s="72"/>
-      <c r="AI62" s="73"/>
-      <c r="AJ62" s="74"/>
+      <c r="AH62" s="78"/>
+      <c r="AI62" s="79"/>
+      <c r="AJ62" s="80"/>
       <c r="AK62" s="35"/>
-      <c r="AL62" s="78"/>
-      <c r="AM62" s="79"/>
-      <c r="AN62" s="80"/>
+      <c r="AL62" s="87"/>
+      <c r="AM62" s="88"/>
+      <c r="AN62" s="89"/>
       <c r="AR62" s="13"/>
     </row>
-    <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="72"/>
-      <c r="C63" s="73"/>
-      <c r="D63" s="74"/>
+    <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B63" s="78"/>
+      <c r="C63" s="79"/>
+      <c r="D63" s="80"/>
       <c r="E63" s="44"/>
-      <c r="F63" s="72"/>
-      <c r="G63" s="73"/>
-      <c r="H63" s="74"/>
+      <c r="F63" s="78"/>
+      <c r="G63" s="79"/>
+      <c r="H63" s="80"/>
       <c r="I63" s="40"/>
-      <c r="J63" s="72"/>
-      <c r="K63" s="73"/>
-      <c r="L63" s="74"/>
+      <c r="J63" s="78"/>
+      <c r="K63" s="79"/>
+      <c r="L63" s="80"/>
       <c r="M63" s="5"/>
-      <c r="N63" s="72"/>
-      <c r="O63" s="73"/>
-      <c r="P63" s="74"/>
+      <c r="N63" s="78"/>
+      <c r="O63" s="79"/>
+      <c r="P63" s="80"/>
       <c r="Q63" s="44"/>
-      <c r="R63" s="72"/>
-      <c r="S63" s="73"/>
-      <c r="T63" s="74"/>
+      <c r="R63" s="78"/>
+      <c r="S63" s="79"/>
+      <c r="T63" s="80"/>
       <c r="U63" s="44"/>
-      <c r="V63" s="72"/>
-      <c r="W63" s="73"/>
-      <c r="X63" s="74"/>
+      <c r="V63" s="78"/>
+      <c r="W63" s="79"/>
+      <c r="X63" s="80"/>
       <c r="Y63" s="40"/>
-      <c r="Z63" s="72"/>
-      <c r="AA63" s="73"/>
-      <c r="AB63" s="74"/>
+      <c r="Z63" s="78"/>
+      <c r="AA63" s="79"/>
+      <c r="AB63" s="80"/>
       <c r="AC63" s="40"/>
-      <c r="AD63" s="72"/>
-      <c r="AE63" s="73"/>
-      <c r="AF63" s="74"/>
+      <c r="AD63" s="78"/>
+      <c r="AE63" s="79"/>
+      <c r="AF63" s="80"/>
       <c r="AG63" s="44"/>
-      <c r="AH63" s="72"/>
-      <c r="AI63" s="73"/>
-      <c r="AJ63" s="74"/>
+      <c r="AH63" s="78"/>
+      <c r="AI63" s="79"/>
+      <c r="AJ63" s="80"/>
       <c r="AK63" s="40"/>
-      <c r="AL63" s="72"/>
-      <c r="AM63" s="73"/>
-      <c r="AN63" s="74"/>
+      <c r="AL63" s="78"/>
+      <c r="AM63" s="79"/>
+      <c r="AN63" s="80"/>
       <c r="AR63" s="13"/>
     </row>
-    <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B64" s="62"/>
       <c r="C64" s="63"/>
       <c r="D64" s="64"/>
@@ -5579,7 +5634,7 @@
       <c r="AN64" s="64"/>
       <c r="AR64" s="13"/>
     </row>
-    <row r="65" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="12"/>
       <c r="B65" s="35"/>
       <c r="C65" s="35"/>
@@ -5625,65 +5680,69 @@
       <c r="AQ65" s="12"/>
       <c r="AR65" s="13"/>
     </row>
-    <row r="66" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="12"/>
-      <c r="B66" s="114"/>
-      <c r="C66" s="115"/>
+      <c r="B66" s="65"/>
+      <c r="C66" s="66"/>
       <c r="D66" s="57"/>
       <c r="E66" s="36"/>
-      <c r="F66" s="114"/>
-      <c r="G66" s="115"/>
+      <c r="F66" s="65"/>
+      <c r="G66" s="66"/>
       <c r="H66" s="57"/>
       <c r="I66" s="32"/>
-      <c r="J66" s="114"/>
-      <c r="K66" s="115"/>
+      <c r="J66" s="65"/>
+      <c r="K66" s="66"/>
       <c r="L66" s="57"/>
       <c r="M66" s="6"/>
-      <c r="N66" s="65"/>
-      <c r="O66" s="66"/>
+      <c r="N66" s="67"/>
+      <c r="O66" s="68"/>
       <c r="P66" s="34"/>
       <c r="Q66" s="36"/>
-      <c r="R66" s="65"/>
-      <c r="S66" s="66"/>
+      <c r="R66" s="67"/>
+      <c r="S66" s="68"/>
       <c r="T66" s="34"/>
       <c r="U66" s="36"/>
-      <c r="V66" s="65"/>
-      <c r="W66" s="66"/>
-      <c r="X66" s="34"/>
+      <c r="V66" s="111" t="s">
+        <v>99</v>
+      </c>
+      <c r="W66" s="112"/>
+      <c r="X66" s="59"/>
       <c r="Y66" s="36"/>
-      <c r="Z66" s="65"/>
-      <c r="AA66" s="66"/>
-      <c r="AB66" s="34"/>
+      <c r="Z66" s="111" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA66" s="112"/>
+      <c r="AB66" s="59"/>
       <c r="AC66" s="36"/>
-      <c r="AD66" s="65"/>
-      <c r="AE66" s="66"/>
+      <c r="AD66" s="67"/>
+      <c r="AE66" s="68"/>
       <c r="AF66" s="34"/>
       <c r="AG66" s="36"/>
-      <c r="AH66" s="65"/>
-      <c r="AI66" s="66"/>
+      <c r="AH66" s="67"/>
+      <c r="AI66" s="68"/>
       <c r="AJ66" s="34"/>
       <c r="AK66" s="32"/>
-      <c r="AL66" s="65"/>
-      <c r="AM66" s="66"/>
+      <c r="AL66" s="67"/>
+      <c r="AM66" s="68"/>
       <c r="AN66" s="34"/>
       <c r="AO66" s="17"/>
       <c r="AP66" s="12"/>
       <c r="AQ66" s="12"/>
       <c r="AR66" s="13"/>
     </row>
-    <row r="67" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="12"/>
-      <c r="B67" s="111"/>
-      <c r="C67" s="112"/>
-      <c r="D67" s="113"/>
+      <c r="B67" s="84"/>
+      <c r="C67" s="85"/>
+      <c r="D67" s="86"/>
       <c r="E67" s="36"/>
-      <c r="F67" s="111"/>
-      <c r="G67" s="112"/>
-      <c r="H67" s="113"/>
+      <c r="F67" s="84"/>
+      <c r="G67" s="85"/>
+      <c r="H67" s="86"/>
       <c r="I67" s="54"/>
-      <c r="J67" s="111"/>
-      <c r="K67" s="112"/>
-      <c r="L67" s="113"/>
+      <c r="J67" s="84"/>
+      <c r="K67" s="85"/>
+      <c r="L67" s="86"/>
       <c r="M67" s="4"/>
       <c r="N67" s="69"/>
       <c r="O67" s="70"/>
@@ -5693,11 +5752,15 @@
       <c r="S67" s="70"/>
       <c r="T67" s="71"/>
       <c r="U67" s="36"/>
-      <c r="V67" s="69"/>
+      <c r="V67" s="69" t="s">
+        <v>100</v>
+      </c>
       <c r="W67" s="70"/>
       <c r="X67" s="71"/>
       <c r="Y67" s="36"/>
-      <c r="Z67" s="69"/>
+      <c r="Z67" s="69" t="s">
+        <v>100</v>
+      </c>
       <c r="AA67" s="70"/>
       <c r="AB67" s="71"/>
       <c r="AC67" s="36"/>
@@ -5717,47 +5780,47 @@
       <c r="AQ67" s="12"/>
       <c r="AR67" s="13"/>
     </row>
-    <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="12"/>
-      <c r="B68" s="116"/>
-      <c r="C68" s="117"/>
-      <c r="D68" s="118"/>
+      <c r="B68" s="90"/>
+      <c r="C68" s="91"/>
+      <c r="D68" s="92"/>
       <c r="E68" s="43"/>
-      <c r="F68" s="116"/>
-      <c r="G68" s="117"/>
-      <c r="H68" s="118"/>
+      <c r="F68" s="90"/>
+      <c r="G68" s="91"/>
+      <c r="H68" s="92"/>
       <c r="I68" s="35"/>
-      <c r="J68" s="116"/>
-      <c r="K68" s="117"/>
-      <c r="L68" s="118"/>
+      <c r="J68" s="90"/>
+      <c r="K68" s="91"/>
+      <c r="L68" s="92"/>
       <c r="M68" s="4"/>
-      <c r="N68" s="75"/>
-      <c r="O68" s="76"/>
-      <c r="P68" s="77"/>
+      <c r="N68" s="81"/>
+      <c r="O68" s="82"/>
+      <c r="P68" s="83"/>
       <c r="Q68" s="36"/>
-      <c r="R68" s="75"/>
-      <c r="S68" s="76"/>
-      <c r="T68" s="77"/>
+      <c r="R68" s="81"/>
+      <c r="S68" s="82"/>
+      <c r="T68" s="83"/>
       <c r="U68" s="43"/>
-      <c r="V68" s="75"/>
-      <c r="W68" s="76"/>
-      <c r="X68" s="77"/>
+      <c r="V68" s="81"/>
+      <c r="W68" s="82"/>
+      <c r="X68" s="83"/>
       <c r="Y68" s="43"/>
-      <c r="Z68" s="75"/>
-      <c r="AA68" s="76"/>
-      <c r="AB68" s="77"/>
+      <c r="Z68" s="81"/>
+      <c r="AA68" s="82"/>
+      <c r="AB68" s="83"/>
       <c r="AC68" s="35"/>
-      <c r="AD68" s="75"/>
-      <c r="AE68" s="76"/>
-      <c r="AF68" s="77"/>
+      <c r="AD68" s="81"/>
+      <c r="AE68" s="82"/>
+      <c r="AF68" s="83"/>
       <c r="AG68" s="43"/>
-      <c r="AH68" s="75"/>
-      <c r="AI68" s="76"/>
-      <c r="AJ68" s="77"/>
+      <c r="AH68" s="81"/>
+      <c r="AI68" s="82"/>
+      <c r="AJ68" s="83"/>
       <c r="AK68" s="35"/>
-      <c r="AL68" s="75"/>
-      <c r="AM68" s="76"/>
-      <c r="AN68" s="77"/>
+      <c r="AL68" s="81"/>
+      <c r="AM68" s="82"/>
+      <c r="AN68" s="83"/>
       <c r="AO68" s="17"/>
       <c r="AP68" s="27" t="s">
         <v>32</v>
@@ -5765,47 +5828,51 @@
       <c r="AQ68" s="12"/>
       <c r="AR68" s="13"/>
     </row>
-    <row r="69" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="12"/>
-      <c r="B69" s="72"/>
-      <c r="C69" s="73"/>
-      <c r="D69" s="74"/>
+      <c r="B69" s="78"/>
+      <c r="C69" s="79"/>
+      <c r="D69" s="80"/>
       <c r="E69" s="37"/>
-      <c r="F69" s="72"/>
-      <c r="G69" s="73"/>
-      <c r="H69" s="74"/>
+      <c r="F69" s="78"/>
+      <c r="G69" s="79"/>
+      <c r="H69" s="80"/>
       <c r="I69" s="37"/>
-      <c r="J69" s="72"/>
-      <c r="K69" s="73"/>
-      <c r="L69" s="74"/>
+      <c r="J69" s="78"/>
+      <c r="K69" s="79"/>
+      <c r="L69" s="80"/>
       <c r="M69" s="4"/>
-      <c r="N69" s="72"/>
-      <c r="O69" s="73"/>
-      <c r="P69" s="74"/>
+      <c r="N69" s="78"/>
+      <c r="O69" s="79"/>
+      <c r="P69" s="80"/>
       <c r="Q69" s="43"/>
-      <c r="R69" s="72"/>
-      <c r="S69" s="73"/>
-      <c r="T69" s="74"/>
+      <c r="R69" s="78"/>
+      <c r="S69" s="79"/>
+      <c r="T69" s="80"/>
       <c r="U69" s="37"/>
-      <c r="V69" s="78"/>
+      <c r="V69" s="78" t="s">
+        <v>25</v>
+      </c>
       <c r="W69" s="79"/>
       <c r="X69" s="80"/>
       <c r="Y69" s="35"/>
-      <c r="Z69" s="78"/>
+      <c r="Z69" s="78" t="s">
+        <v>22</v>
+      </c>
       <c r="AA69" s="79"/>
       <c r="AB69" s="80"/>
       <c r="AC69" s="43"/>
-      <c r="AD69" s="72"/>
-      <c r="AE69" s="73"/>
-      <c r="AF69" s="74"/>
+      <c r="AD69" s="78"/>
+      <c r="AE69" s="79"/>
+      <c r="AF69" s="80"/>
       <c r="AG69" s="37"/>
-      <c r="AH69" s="78"/>
-      <c r="AI69" s="79"/>
-      <c r="AJ69" s="80"/>
+      <c r="AH69" s="87"/>
+      <c r="AI69" s="88"/>
+      <c r="AJ69" s="89"/>
       <c r="AK69" s="37"/>
-      <c r="AL69" s="72"/>
-      <c r="AM69" s="73"/>
-      <c r="AN69" s="74"/>
+      <c r="AL69" s="78"/>
+      <c r="AM69" s="79"/>
+      <c r="AN69" s="80"/>
       <c r="AO69" s="12"/>
       <c r="AP69" s="27" t="s">
         <v>33</v>
@@ -5813,47 +5880,51 @@
       <c r="AQ69" s="12"/>
       <c r="AR69" s="13"/>
     </row>
-    <row r="70" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="12"/>
-      <c r="B70" s="72"/>
-      <c r="C70" s="73"/>
-      <c r="D70" s="74"/>
+      <c r="B70" s="78"/>
+      <c r="C70" s="79"/>
+      <c r="D70" s="80"/>
       <c r="E70" s="44"/>
-      <c r="F70" s="72"/>
-      <c r="G70" s="73"/>
-      <c r="H70" s="74"/>
+      <c r="F70" s="78"/>
+      <c r="G70" s="79"/>
+      <c r="H70" s="80"/>
       <c r="I70" s="44"/>
-      <c r="J70" s="72"/>
-      <c r="K70" s="73"/>
-      <c r="L70" s="74"/>
+      <c r="J70" s="78"/>
+      <c r="K70" s="79"/>
+      <c r="L70" s="80"/>
       <c r="M70" s="9"/>
-      <c r="N70" s="72"/>
-      <c r="O70" s="73"/>
-      <c r="P70" s="74"/>
+      <c r="N70" s="78"/>
+      <c r="O70" s="79"/>
+      <c r="P70" s="80"/>
       <c r="Q70" s="50"/>
-      <c r="R70" s="72"/>
-      <c r="S70" s="73"/>
-      <c r="T70" s="74"/>
+      <c r="R70" s="78"/>
+      <c r="S70" s="79"/>
+      <c r="T70" s="80"/>
       <c r="U70" s="44"/>
-      <c r="V70" s="72"/>
-      <c r="W70" s="73"/>
-      <c r="X70" s="74"/>
+      <c r="V70" s="78" t="s">
+        <v>24</v>
+      </c>
+      <c r="W70" s="79"/>
+      <c r="X70" s="80"/>
       <c r="Y70" s="40"/>
-      <c r="Z70" s="72"/>
-      <c r="AA70" s="73"/>
-      <c r="AB70" s="74"/>
+      <c r="Z70" s="78" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA70" s="79"/>
+      <c r="AB70" s="80"/>
       <c r="AC70" s="44"/>
-      <c r="AD70" s="72"/>
-      <c r="AE70" s="73"/>
-      <c r="AF70" s="74"/>
+      <c r="AD70" s="78"/>
+      <c r="AE70" s="79"/>
+      <c r="AF70" s="80"/>
       <c r="AG70" s="44"/>
-      <c r="AH70" s="72"/>
-      <c r="AI70" s="73"/>
-      <c r="AJ70" s="74"/>
+      <c r="AH70" s="78"/>
+      <c r="AI70" s="79"/>
+      <c r="AJ70" s="80"/>
       <c r="AK70" s="44"/>
-      <c r="AL70" s="72"/>
-      <c r="AM70" s="73"/>
-      <c r="AN70" s="74"/>
+      <c r="AL70" s="78"/>
+      <c r="AM70" s="79"/>
+      <c r="AN70" s="80"/>
       <c r="AO70" s="12"/>
       <c r="AP70" s="27" t="s">
         <v>34</v>
@@ -5861,7 +5932,7 @@
       <c r="AQ70" s="12"/>
       <c r="AR70" s="13"/>
     </row>
-    <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A71" s="12"/>
       <c r="B71" s="62"/>
       <c r="C71" s="63"/>
@@ -5883,7 +5954,9 @@
       <c r="S71" s="63"/>
       <c r="T71" s="64"/>
       <c r="U71" s="44"/>
-      <c r="V71" s="62"/>
+      <c r="V71" s="62" t="s">
+        <v>26</v>
+      </c>
       <c r="W71" s="63"/>
       <c r="X71" s="64"/>
       <c r="Y71" s="44"/>
@@ -5909,7 +5982,7 @@
       <c r="AQ71" s="12"/>
       <c r="AR71" s="13"/>
     </row>
-    <row r="72" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="12"/>
       <c r="B72" s="33"/>
       <c r="C72" s="33"/>
@@ -5955,7 +6028,7 @@
       <c r="AQ72" s="12"/>
       <c r="AR72" s="13"/>
     </row>
-    <row r="73" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="12"/>
       <c r="B73" s="40"/>
       <c r="C73" s="33"/>
@@ -5969,23 +6042,23 @@
       <c r="K73" s="33"/>
       <c r="L73" s="33"/>
       <c r="M73" s="14"/>
-      <c r="N73" s="88" t="s">
+      <c r="N73" s="110" t="s">
         <v>31</v>
       </c>
-      <c r="O73" s="88"/>
-      <c r="P73" s="88"/>
-      <c r="Q73" s="88"/>
-      <c r="R73" s="88"/>
-      <c r="S73" s="88"/>
-      <c r="T73" s="88"/>
-      <c r="U73" s="88"/>
-      <c r="V73" s="88"/>
-      <c r="W73" s="88"/>
-      <c r="X73" s="88"/>
-      <c r="Y73" s="88"/>
-      <c r="Z73" s="88"/>
-      <c r="AA73" s="88"/>
-      <c r="AB73" s="88"/>
+      <c r="O73" s="110"/>
+      <c r="P73" s="110"/>
+      <c r="Q73" s="110"/>
+      <c r="R73" s="110"/>
+      <c r="S73" s="110"/>
+      <c r="T73" s="110"/>
+      <c r="U73" s="110"/>
+      <c r="V73" s="110"/>
+      <c r="W73" s="110"/>
+      <c r="X73" s="110"/>
+      <c r="Y73" s="110"/>
+      <c r="Z73" s="110"/>
+      <c r="AA73" s="110"/>
+      <c r="AB73" s="110"/>
       <c r="AD73" s="40"/>
       <c r="AE73" s="33"/>
       <c r="AF73" s="33"/>
@@ -6002,7 +6075,7 @@
       <c r="AQ73" s="12"/>
       <c r="AR73" s="13"/>
     </row>
-    <row r="74" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="12"/>
       <c r="B74" s="33"/>
       <c r="C74" s="33"/>
@@ -6016,21 +6089,21 @@
       <c r="K74" s="33"/>
       <c r="L74" s="33"/>
       <c r="M74" s="14"/>
-      <c r="N74" s="88"/>
-      <c r="O74" s="88"/>
-      <c r="P74" s="88"/>
-      <c r="Q74" s="88"/>
-      <c r="R74" s="88"/>
-      <c r="S74" s="88"/>
-      <c r="T74" s="88"/>
-      <c r="U74" s="88"/>
-      <c r="V74" s="88"/>
-      <c r="W74" s="88"/>
-      <c r="X74" s="88"/>
-      <c r="Y74" s="88"/>
-      <c r="Z74" s="88"/>
-      <c r="AA74" s="88"/>
-      <c r="AB74" s="88"/>
+      <c r="N74" s="110"/>
+      <c r="O74" s="110"/>
+      <c r="P74" s="110"/>
+      <c r="Q74" s="110"/>
+      <c r="R74" s="110"/>
+      <c r="S74" s="110"/>
+      <c r="T74" s="110"/>
+      <c r="U74" s="110"/>
+      <c r="V74" s="110"/>
+      <c r="W74" s="110"/>
+      <c r="X74" s="110"/>
+      <c r="Y74" s="110"/>
+      <c r="Z74" s="110"/>
+      <c r="AA74" s="110"/>
+      <c r="AB74" s="110"/>
       <c r="AC74" s="21"/>
       <c r="AD74" s="33"/>
       <c r="AE74" s="33"/>
@@ -6048,93 +6121,93 @@
       <c r="AQ74" s="12"/>
       <c r="AR74" s="13"/>
     </row>
-    <row r="75" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="12"/>
-      <c r="B75" s="128" t="s">
+      <c r="B75" s="99" t="s">
         <v>58</v>
       </c>
-      <c r="C75" s="129"/>
-      <c r="D75" s="130"/>
+      <c r="C75" s="100"/>
+      <c r="D75" s="60"/>
       <c r="E75" s="32"/>
-      <c r="F75" s="128" t="s">
+      <c r="F75" s="99" t="s">
         <v>52</v>
       </c>
-      <c r="G75" s="129"/>
-      <c r="H75" s="130"/>
+      <c r="G75" s="100"/>
+      <c r="H75" s="60"/>
       <c r="I75" s="32"/>
-      <c r="J75" s="114"/>
-      <c r="K75" s="115"/>
+      <c r="J75" s="65"/>
+      <c r="K75" s="66"/>
       <c r="L75" s="57"/>
       <c r="M75" s="14"/>
-      <c r="N75" s="65"/>
-      <c r="O75" s="66"/>
+      <c r="N75" s="67"/>
+      <c r="O75" s="68"/>
       <c r="P75" s="34"/>
       <c r="Q75" s="44"/>
-      <c r="R75" s="65" t="s">
+      <c r="R75" s="67" t="s">
         <v>78</v>
       </c>
-      <c r="S75" s="66"/>
+      <c r="S75" s="68"/>
       <c r="T75" s="34" t="s">
         <v>64</v>
       </c>
       <c r="U75" s="36"/>
-      <c r="V75" s="65" t="s">
+      <c r="V75" s="67" t="s">
         <v>78</v>
       </c>
-      <c r="W75" s="66"/>
+      <c r="W75" s="68"/>
       <c r="X75" s="34" t="s">
         <v>64</v>
       </c>
       <c r="Y75" s="32"/>
-      <c r="Z75" s="65" t="s">
+      <c r="Z75" s="67" t="s">
         <v>78</v>
       </c>
-      <c r="AA75" s="66"/>
+      <c r="AA75" s="68"/>
       <c r="AB75" s="34" t="s">
         <v>64</v>
       </c>
       <c r="AC75" s="32"/>
-      <c r="AD75" s="65" t="s">
+      <c r="AD75" s="67" t="s">
         <v>78</v>
       </c>
-      <c r="AE75" s="66"/>
+      <c r="AE75" s="68"/>
       <c r="AF75" s="34" t="s">
         <v>64</v>
       </c>
       <c r="AG75" s="32"/>
-      <c r="AH75" s="65" t="s">
+      <c r="AH75" s="67" t="s">
         <v>78</v>
       </c>
-      <c r="AI75" s="66"/>
+      <c r="AI75" s="68"/>
       <c r="AJ75" s="34" t="s">
         <v>64</v>
       </c>
       <c r="AK75" s="32"/>
-      <c r="AL75" s="65"/>
-      <c r="AM75" s="66"/>
+      <c r="AL75" s="67"/>
+      <c r="AM75" s="68"/>
       <c r="AN75" s="34"/>
       <c r="AO75" s="16"/>
       <c r="AP75" s="29"/>
       <c r="AQ75" s="26"/>
       <c r="AR75" s="24"/>
     </row>
-    <row r="76" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="12"/>
-      <c r="B76" s="131" t="s">
+      <c r="B76" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="C76" s="132"/>
-      <c r="D76" s="133"/>
+      <c r="C76" s="94"/>
+      <c r="D76" s="95"/>
       <c r="E76" s="32"/>
-      <c r="F76" s="131" t="s">
+      <c r="F76" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="G76" s="132"/>
-      <c r="H76" s="133"/>
+      <c r="G76" s="94"/>
+      <c r="H76" s="95"/>
       <c r="I76" s="32"/>
-      <c r="J76" s="111"/>
-      <c r="K76" s="112"/>
-      <c r="L76" s="113"/>
+      <c r="J76" s="84"/>
+      <c r="K76" s="85"/>
+      <c r="L76" s="86"/>
       <c r="M76" s="4"/>
       <c r="N76" s="69"/>
       <c r="O76" s="70"/>
@@ -6178,125 +6251,125 @@
       <c r="AQ76" s="26"/>
       <c r="AR76" s="24"/>
     </row>
-    <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="16"/>
-      <c r="B77" s="134" t="s">
+      <c r="B77" s="96" t="s">
         <v>60</v>
       </c>
-      <c r="C77" s="135"/>
-      <c r="D77" s="136"/>
+      <c r="C77" s="97"/>
+      <c r="D77" s="98"/>
       <c r="E77" s="32"/>
-      <c r="F77" s="134" t="s">
+      <c r="F77" s="96" t="s">
         <v>60</v>
       </c>
-      <c r="G77" s="135"/>
-      <c r="H77" s="136"/>
+      <c r="G77" s="97"/>
+      <c r="H77" s="98"/>
       <c r="I77" s="32"/>
-      <c r="J77" s="116"/>
-      <c r="K77" s="117"/>
-      <c r="L77" s="118"/>
+      <c r="J77" s="90"/>
+      <c r="K77" s="91"/>
+      <c r="L77" s="92"/>
       <c r="M77" s="4"/>
-      <c r="N77" s="75"/>
-      <c r="O77" s="76"/>
-      <c r="P77" s="77"/>
+      <c r="N77" s="81"/>
+      <c r="O77" s="82"/>
+      <c r="P77" s="83"/>
       <c r="Q77" s="44"/>
-      <c r="R77" s="75"/>
-      <c r="S77" s="76"/>
-      <c r="T77" s="77"/>
+      <c r="R77" s="81"/>
+      <c r="S77" s="82"/>
+      <c r="T77" s="83"/>
       <c r="U77" s="31"/>
-      <c r="V77" s="75"/>
-      <c r="W77" s="76"/>
-      <c r="X77" s="77"/>
+      <c r="V77" s="81"/>
+      <c r="W77" s="82"/>
+      <c r="X77" s="83"/>
       <c r="Y77" s="32"/>
-      <c r="Z77" s="75"/>
-      <c r="AA77" s="76"/>
-      <c r="AB77" s="77"/>
+      <c r="Z77" s="81"/>
+      <c r="AA77" s="82"/>
+      <c r="AB77" s="83"/>
       <c r="AC77" s="31"/>
-      <c r="AD77" s="75"/>
-      <c r="AE77" s="76"/>
-      <c r="AF77" s="77"/>
+      <c r="AD77" s="81"/>
+      <c r="AE77" s="82"/>
+      <c r="AF77" s="83"/>
       <c r="AG77" s="32"/>
-      <c r="AH77" s="75"/>
-      <c r="AI77" s="76"/>
-      <c r="AJ77" s="77"/>
+      <c r="AH77" s="81"/>
+      <c r="AI77" s="82"/>
+      <c r="AJ77" s="83"/>
       <c r="AK77" s="32"/>
-      <c r="AL77" s="75"/>
-      <c r="AM77" s="76"/>
-      <c r="AN77" s="77"/>
+      <c r="AL77" s="81"/>
+      <c r="AM77" s="82"/>
+      <c r="AN77" s="83"/>
       <c r="AO77" s="12"/>
       <c r="AP77" s="29"/>
       <c r="AQ77" s="26"/>
       <c r="AR77" s="24"/>
     </row>
-    <row r="78" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="16"/>
-      <c r="B78" s="137" t="s">
+      <c r="B78" s="75" t="s">
         <v>93</v>
       </c>
-      <c r="C78" s="138"/>
-      <c r="D78" s="139"/>
+      <c r="C78" s="76"/>
+      <c r="D78" s="77"/>
       <c r="E78" s="32"/>
-      <c r="F78" s="137" t="s">
+      <c r="F78" s="75" t="s">
         <v>93</v>
       </c>
-      <c r="G78" s="138"/>
-      <c r="H78" s="139"/>
+      <c r="G78" s="76"/>
+      <c r="H78" s="77"/>
       <c r="I78" s="43"/>
-      <c r="J78" s="78"/>
-      <c r="K78" s="79"/>
-      <c r="L78" s="80"/>
+      <c r="J78" s="87"/>
+      <c r="K78" s="88"/>
+      <c r="L78" s="89"/>
       <c r="M78" s="5"/>
-      <c r="N78" s="78"/>
-      <c r="O78" s="79"/>
-      <c r="P78" s="80"/>
+      <c r="N78" s="87"/>
+      <c r="O78" s="88"/>
+      <c r="P78" s="89"/>
       <c r="Q78" s="44"/>
-      <c r="R78" s="78" t="s">
+      <c r="R78" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="S78" s="79"/>
-      <c r="T78" s="80"/>
+      <c r="S78" s="88"/>
+      <c r="T78" s="89"/>
       <c r="U78" s="32"/>
-      <c r="V78" s="78" t="s">
+      <c r="V78" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="W78" s="79"/>
-      <c r="X78" s="80"/>
+      <c r="W78" s="88"/>
+      <c r="X78" s="89"/>
       <c r="Y78" s="32"/>
-      <c r="Z78" s="78" t="s">
+      <c r="Z78" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="AA78" s="79"/>
-      <c r="AB78" s="80"/>
+      <c r="AA78" s="88"/>
+      <c r="AB78" s="89"/>
       <c r="AC78" s="32"/>
-      <c r="AD78" s="78" t="s">
+      <c r="AD78" s="87" t="s">
         <v>29</v>
       </c>
-      <c r="AE78" s="79"/>
-      <c r="AF78" s="80"/>
+      <c r="AE78" s="88"/>
+      <c r="AF78" s="89"/>
       <c r="AG78" s="32"/>
-      <c r="AH78" s="78" t="s">
+      <c r="AH78" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="AI78" s="79"/>
-      <c r="AJ78" s="80"/>
+      <c r="AI78" s="88"/>
+      <c r="AJ78" s="89"/>
       <c r="AK78" s="43"/>
-      <c r="AL78" s="78"/>
-      <c r="AM78" s="79"/>
-      <c r="AN78" s="80"/>
+      <c r="AL78" s="87"/>
+      <c r="AM78" s="88"/>
+      <c r="AN78" s="89"/>
       <c r="AO78" s="12"/>
       <c r="AP78" s="29"/>
       <c r="AQ78" s="26"/>
       <c r="AR78" s="24"/>
     </row>
-    <row r="79" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A79" s="16"/>
-      <c r="B79" s="140"/>
-      <c r="C79" s="141"/>
-      <c r="D79" s="142"/>
+      <c r="B79" s="72"/>
+      <c r="C79" s="73"/>
+      <c r="D79" s="74"/>
       <c r="E79" s="31"/>
-      <c r="F79" s="140"/>
-      <c r="G79" s="141"/>
-      <c r="H79" s="142"/>
+      <c r="F79" s="72"/>
+      <c r="G79" s="73"/>
+      <c r="H79" s="74"/>
       <c r="I79" s="32"/>
       <c r="J79" s="62"/>
       <c r="K79" s="63"/>
@@ -6338,7 +6411,7 @@
       <c r="AQ79" s="26"/>
       <c r="AR79" s="24"/>
     </row>
-    <row r="80" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="12"/>
       <c r="B80" s="35"/>
       <c r="C80" s="35"/>
@@ -6384,91 +6457,91 @@
       <c r="AQ80" s="26"/>
       <c r="AR80" s="24"/>
     </row>
-    <row r="81" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="12"/>
-      <c r="B81" s="114" t="s">
+      <c r="B81" s="65" t="s">
         <v>70</v>
       </c>
-      <c r="C81" s="115"/>
+      <c r="C81" s="66"/>
       <c r="D81" s="57"/>
       <c r="E81" s="32"/>
-      <c r="F81" s="114" t="s">
+      <c r="F81" s="65" t="s">
         <v>70</v>
       </c>
-      <c r="G81" s="115"/>
+      <c r="G81" s="66"/>
       <c r="H81" s="57"/>
       <c r="I81" s="50"/>
-      <c r="J81" s="114" t="s">
+      <c r="J81" s="65" t="s">
         <v>70</v>
       </c>
-      <c r="K81" s="115"/>
+      <c r="K81" s="66"/>
       <c r="L81" s="57"/>
       <c r="M81" s="5"/>
-      <c r="N81" s="65" t="s">
+      <c r="N81" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="O81" s="66"/>
+      <c r="O81" s="68"/>
       <c r="P81" s="34"/>
       <c r="Q81" s="32"/>
-      <c r="R81" s="65" t="s">
+      <c r="R81" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="S81" s="66"/>
+      <c r="S81" s="68"/>
       <c r="T81" s="34"/>
       <c r="U81" s="36"/>
-      <c r="V81" s="65" t="s">
+      <c r="V81" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="W81" s="66"/>
+      <c r="W81" s="68"/>
       <c r="X81" s="34"/>
       <c r="Y81" s="32"/>
-      <c r="Z81" s="65" t="s">
+      <c r="Z81" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="AA81" s="66"/>
+      <c r="AA81" s="68"/>
       <c r="AB81" s="34"/>
       <c r="AC81" s="32"/>
-      <c r="AD81" s="65" t="s">
+      <c r="AD81" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="AE81" s="66"/>
+      <c r="AE81" s="68"/>
       <c r="AF81" s="34"/>
       <c r="AG81" s="32"/>
-      <c r="AH81" s="65" t="s">
+      <c r="AH81" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="AI81" s="66"/>
+      <c r="AI81" s="68"/>
       <c r="AJ81" s="34"/>
       <c r="AK81" s="50"/>
-      <c r="AL81" s="65" t="s">
+      <c r="AL81" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="AM81" s="66"/>
+      <c r="AM81" s="68"/>
       <c r="AN81" s="34"/>
       <c r="AO81" s="12"/>
       <c r="AP81" s="29"/>
       <c r="AQ81" s="26"/>
       <c r="AR81" s="24"/>
     </row>
-    <row r="82" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="12"/>
-      <c r="B82" s="111" t="s">
+      <c r="B82" s="84" t="s">
         <v>65</v>
       </c>
-      <c r="C82" s="112"/>
-      <c r="D82" s="113"/>
+      <c r="C82" s="85"/>
+      <c r="D82" s="86"/>
       <c r="E82" s="32"/>
-      <c r="F82" s="111" t="s">
+      <c r="F82" s="84" t="s">
         <v>65</v>
       </c>
-      <c r="G82" s="112"/>
-      <c r="H82" s="113"/>
+      <c r="G82" s="85"/>
+      <c r="H82" s="86"/>
       <c r="I82" s="36"/>
-      <c r="J82" s="111" t="s">
+      <c r="J82" s="84" t="s">
         <v>65</v>
       </c>
-      <c r="K82" s="112"/>
-      <c r="L82" s="113"/>
+      <c r="K82" s="85"/>
+      <c r="L82" s="86"/>
       <c r="M82" s="5"/>
       <c r="N82" s="69" t="s">
         <v>65</v>
@@ -6516,139 +6589,139 @@
       <c r="AQ82" s="26"/>
       <c r="AR82" s="24"/>
     </row>
-    <row r="83" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="12"/>
-      <c r="B83" s="116" t="s">
+      <c r="B83" s="90" t="s">
         <v>60</v>
       </c>
-      <c r="C83" s="117"/>
-      <c r="D83" s="118"/>
+      <c r="C83" s="91"/>
+      <c r="D83" s="92"/>
       <c r="E83" s="32"/>
-      <c r="F83" s="116" t="s">
+      <c r="F83" s="90" t="s">
         <v>60</v>
       </c>
-      <c r="G83" s="117"/>
-      <c r="H83" s="118"/>
+      <c r="G83" s="91"/>
+      <c r="H83" s="92"/>
       <c r="I83" s="32"/>
-      <c r="J83" s="116" t="s">
+      <c r="J83" s="90" t="s">
         <v>60</v>
       </c>
-      <c r="K83" s="117"/>
-      <c r="L83" s="118"/>
+      <c r="K83" s="91"/>
+      <c r="L83" s="92"/>
       <c r="M83" s="5"/>
-      <c r="N83" s="75" t="s">
+      <c r="N83" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="O83" s="76"/>
-      <c r="P83" s="77"/>
+      <c r="O83" s="82"/>
+      <c r="P83" s="83"/>
       <c r="Q83" s="31"/>
-      <c r="R83" s="75" t="s">
+      <c r="R83" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="S83" s="76"/>
-      <c r="T83" s="77"/>
+      <c r="S83" s="82"/>
+      <c r="T83" s="83"/>
       <c r="U83" s="31"/>
-      <c r="V83" s="75" t="s">
+      <c r="V83" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="W83" s="76"/>
-      <c r="X83" s="77"/>
+      <c r="W83" s="82"/>
+      <c r="X83" s="83"/>
       <c r="Y83" s="32"/>
-      <c r="Z83" s="75" t="s">
+      <c r="Z83" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="AA83" s="76"/>
-      <c r="AB83" s="77"/>
+      <c r="AA83" s="82"/>
+      <c r="AB83" s="83"/>
       <c r="AC83" s="32"/>
-      <c r="AD83" s="75" t="s">
+      <c r="AD83" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="AE83" s="76"/>
-      <c r="AF83" s="77"/>
+      <c r="AE83" s="82"/>
+      <c r="AF83" s="83"/>
       <c r="AG83" s="32"/>
-      <c r="AH83" s="75" t="s">
+      <c r="AH83" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="AI83" s="76"/>
-      <c r="AJ83" s="77"/>
+      <c r="AI83" s="82"/>
+      <c r="AJ83" s="83"/>
       <c r="AK83" s="32"/>
-      <c r="AL83" s="75" t="s">
+      <c r="AL83" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="AM83" s="76"/>
-      <c r="AN83" s="77"/>
+      <c r="AM83" s="82"/>
+      <c r="AN83" s="83"/>
       <c r="AO83" s="12"/>
       <c r="AP83" s="29"/>
       <c r="AQ83" s="26"/>
       <c r="AR83" s="24"/>
     </row>
-    <row r="84" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="12"/>
-      <c r="B84" s="78" t="s">
+      <c r="B84" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="C84" s="79"/>
-      <c r="D84" s="80"/>
+      <c r="C84" s="88"/>
+      <c r="D84" s="89"/>
       <c r="E84" s="32"/>
-      <c r="F84" s="78" t="s">
+      <c r="F84" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="G84" s="79"/>
-      <c r="H84" s="80"/>
+      <c r="G84" s="88"/>
+      <c r="H84" s="89"/>
       <c r="I84" s="32"/>
-      <c r="J84" s="78" t="s">
+      <c r="J84" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="K84" s="79"/>
-      <c r="L84" s="80"/>
+      <c r="K84" s="88"/>
+      <c r="L84" s="89"/>
       <c r="M84" s="5"/>
-      <c r="N84" s="78" t="s">
+      <c r="N84" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="O84" s="79"/>
-      <c r="P84" s="80"/>
+      <c r="O84" s="88"/>
+      <c r="P84" s="89"/>
       <c r="Q84" s="32"/>
-      <c r="R84" s="78" t="s">
+      <c r="R84" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="S84" s="79"/>
-      <c r="T84" s="80"/>
+      <c r="S84" s="88"/>
+      <c r="T84" s="89"/>
       <c r="U84" s="32"/>
-      <c r="V84" s="78" t="s">
+      <c r="V84" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="W84" s="79"/>
-      <c r="X84" s="80"/>
+      <c r="W84" s="88"/>
+      <c r="X84" s="89"/>
       <c r="Y84" s="32"/>
-      <c r="Z84" s="78" t="s">
+      <c r="Z84" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="AA84" s="79"/>
-      <c r="AB84" s="80"/>
+      <c r="AA84" s="88"/>
+      <c r="AB84" s="89"/>
       <c r="AC84" s="43"/>
-      <c r="AD84" s="78" t="s">
+      <c r="AD84" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="AE84" s="79"/>
-      <c r="AF84" s="80"/>
+      <c r="AE84" s="88"/>
+      <c r="AF84" s="89"/>
       <c r="AG84" s="32"/>
-      <c r="AH84" s="78" t="s">
+      <c r="AH84" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="AI84" s="79"/>
-      <c r="AJ84" s="80"/>
+      <c r="AI84" s="88"/>
+      <c r="AJ84" s="89"/>
       <c r="AK84" s="32"/>
-      <c r="AL84" s="78" t="s">
+      <c r="AL84" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="AM84" s="79"/>
-      <c r="AN84" s="80"/>
+      <c r="AM84" s="88"/>
+      <c r="AN84" s="89"/>
       <c r="AO84" s="12"/>
       <c r="AP84" s="29"/>
       <c r="AQ84" s="26"/>
       <c r="AR84" s="24"/>
     </row>
-    <row r="85" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A85" s="12"/>
       <c r="B85" s="62"/>
       <c r="C85" s="63"/>
@@ -6694,7 +6767,7 @@
       <c r="AQ85" s="26"/>
       <c r="AR85" s="24"/>
     </row>
-    <row r="86" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="12"/>
       <c r="B86" s="35"/>
       <c r="C86" s="35"/>
@@ -6740,73 +6813,73 @@
       <c r="AQ86" s="26"/>
       <c r="AR86" s="24"/>
     </row>
-    <row r="87" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="12"/>
-      <c r="B87" s="114"/>
-      <c r="C87" s="115"/>
+      <c r="B87" s="65"/>
+      <c r="C87" s="66"/>
       <c r="D87" s="57"/>
       <c r="E87" s="36"/>
-      <c r="F87" s="114"/>
-      <c r="G87" s="115"/>
+      <c r="F87" s="65"/>
+      <c r="G87" s="66"/>
       <c r="H87" s="57"/>
       <c r="I87" s="32"/>
-      <c r="J87" s="114"/>
-      <c r="K87" s="115"/>
+      <c r="J87" s="65"/>
+      <c r="K87" s="66"/>
       <c r="L87" s="57"/>
       <c r="M87" s="6"/>
-      <c r="N87" s="65"/>
-      <c r="O87" s="66"/>
+      <c r="N87" s="67"/>
+      <c r="O87" s="68"/>
       <c r="P87" s="34"/>
       <c r="Q87" s="32"/>
-      <c r="R87" s="65"/>
-      <c r="S87" s="66"/>
+      <c r="R87" s="67"/>
+      <c r="S87" s="68"/>
       <c r="T87" s="34"/>
       <c r="U87" s="36"/>
-      <c r="V87" s="65" t="s">
+      <c r="V87" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="W87" s="66"/>
+      <c r="W87" s="68"/>
       <c r="X87" s="34"/>
       <c r="Y87" s="32"/>
-      <c r="Z87" s="65"/>
-      <c r="AA87" s="66"/>
+      <c r="Z87" s="67"/>
+      <c r="AA87" s="68"/>
       <c r="AB87" s="34"/>
       <c r="AC87" s="32"/>
-      <c r="AD87" s="65" t="s">
+      <c r="AD87" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="AE87" s="66"/>
+      <c r="AE87" s="68"/>
       <c r="AF87" s="34"/>
       <c r="AG87" s="32"/>
-      <c r="AH87" s="65" t="s">
+      <c r="AH87" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="AI87" s="66"/>
+      <c r="AI87" s="68"/>
       <c r="AJ87" s="34"/>
       <c r="AK87" s="32"/>
-      <c r="AL87" s="65" t="s">
+      <c r="AL87" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="AM87" s="66"/>
+      <c r="AM87" s="68"/>
       <c r="AN87" s="34"/>
       <c r="AO87" s="12"/>
       <c r="AP87" s="29"/>
       <c r="AQ87" s="26"/>
       <c r="AR87" s="24"/>
     </row>
-    <row r="88" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="12"/>
-      <c r="B88" s="111"/>
-      <c r="C88" s="112"/>
-      <c r="D88" s="113"/>
+      <c r="B88" s="84"/>
+      <c r="C88" s="85"/>
+      <c r="D88" s="86"/>
       <c r="E88" s="32"/>
-      <c r="F88" s="111"/>
-      <c r="G88" s="112"/>
-      <c r="H88" s="113"/>
+      <c r="F88" s="84"/>
+      <c r="G88" s="85"/>
+      <c r="H88" s="86"/>
       <c r="I88" s="32"/>
-      <c r="J88" s="111"/>
-      <c r="K88" s="112"/>
-      <c r="L88" s="113"/>
+      <c r="J88" s="84"/>
+      <c r="K88" s="85"/>
+      <c r="L88" s="86"/>
       <c r="M88" s="6"/>
       <c r="N88" s="69"/>
       <c r="O88" s="70"/>
@@ -6842,113 +6915,113 @@
       <c r="AQ88" s="26"/>
       <c r="AR88" s="24"/>
     </row>
-    <row r="89" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="12"/>
-      <c r="B89" s="116"/>
-      <c r="C89" s="117"/>
-      <c r="D89" s="118"/>
+      <c r="B89" s="90"/>
+      <c r="C89" s="91"/>
+      <c r="D89" s="92"/>
       <c r="E89" s="31"/>
-      <c r="F89" s="116"/>
-      <c r="G89" s="117"/>
-      <c r="H89" s="118"/>
+      <c r="F89" s="90"/>
+      <c r="G89" s="91"/>
+      <c r="H89" s="92"/>
       <c r="I89" s="32"/>
-      <c r="J89" s="116"/>
-      <c r="K89" s="117"/>
-      <c r="L89" s="118"/>
+      <c r="J89" s="90"/>
+      <c r="K89" s="91"/>
+      <c r="L89" s="92"/>
       <c r="M89" s="6"/>
-      <c r="N89" s="75"/>
-      <c r="O89" s="76"/>
-      <c r="P89" s="77"/>
+      <c r="N89" s="81"/>
+      <c r="O89" s="82"/>
+      <c r="P89" s="83"/>
       <c r="Q89" s="32"/>
-      <c r="R89" s="75"/>
-      <c r="S89" s="76"/>
-      <c r="T89" s="77"/>
+      <c r="R89" s="81"/>
+      <c r="S89" s="82"/>
+      <c r="T89" s="83"/>
       <c r="U89" s="31"/>
-      <c r="V89" s="75" t="s">
+      <c r="V89" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="W89" s="76"/>
-      <c r="X89" s="77"/>
+      <c r="W89" s="82"/>
+      <c r="X89" s="83"/>
       <c r="Y89" s="32"/>
-      <c r="Z89" s="75"/>
-      <c r="AA89" s="76"/>
-      <c r="AB89" s="77"/>
+      <c r="Z89" s="81"/>
+      <c r="AA89" s="82"/>
+      <c r="AB89" s="83"/>
       <c r="AC89" s="31"/>
-      <c r="AD89" s="75" t="s">
+      <c r="AD89" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="AE89" s="76"/>
-      <c r="AF89" s="77"/>
+      <c r="AE89" s="82"/>
+      <c r="AF89" s="83"/>
       <c r="AG89" s="32"/>
-      <c r="AH89" s="75" t="s">
+      <c r="AH89" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="AI89" s="76"/>
-      <c r="AJ89" s="77"/>
+      <c r="AI89" s="82"/>
+      <c r="AJ89" s="83"/>
       <c r="AK89" s="32"/>
-      <c r="AL89" s="75"/>
-      <c r="AM89" s="76"/>
-      <c r="AN89" s="77"/>
+      <c r="AL89" s="81"/>
+      <c r="AM89" s="82"/>
+      <c r="AN89" s="83"/>
       <c r="AO89" s="12"/>
       <c r="AP89" s="29"/>
       <c r="AQ89" s="26"/>
       <c r="AR89" s="24"/>
     </row>
-    <row r="90" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="12"/>
-      <c r="B90" s="78"/>
-      <c r="C90" s="79"/>
-      <c r="D90" s="80"/>
+      <c r="B90" s="87"/>
+      <c r="C90" s="88"/>
+      <c r="D90" s="89"/>
       <c r="E90" s="32"/>
-      <c r="F90" s="78"/>
-      <c r="G90" s="79"/>
-      <c r="H90" s="80"/>
+      <c r="F90" s="87"/>
+      <c r="G90" s="88"/>
+      <c r="H90" s="89"/>
       <c r="I90" s="32"/>
-      <c r="J90" s="78"/>
-      <c r="K90" s="79"/>
-      <c r="L90" s="80"/>
+      <c r="J90" s="87"/>
+      <c r="K90" s="88"/>
+      <c r="L90" s="89"/>
       <c r="M90" s="6"/>
-      <c r="N90" s="78"/>
-      <c r="O90" s="79"/>
-      <c r="P90" s="80"/>
+      <c r="N90" s="87"/>
+      <c r="O90" s="88"/>
+      <c r="P90" s="89"/>
       <c r="Q90" s="32"/>
-      <c r="R90" s="78"/>
-      <c r="S90" s="79"/>
-      <c r="T90" s="80"/>
+      <c r="R90" s="87"/>
+      <c r="S90" s="88"/>
+      <c r="T90" s="89"/>
       <c r="U90" s="32"/>
-      <c r="V90" s="78" t="s">
+      <c r="V90" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="W90" s="79"/>
-      <c r="X90" s="80"/>
+      <c r="W90" s="88"/>
+      <c r="X90" s="89"/>
       <c r="Y90" s="32"/>
-      <c r="Z90" s="78"/>
-      <c r="AA90" s="79"/>
-      <c r="AB90" s="80"/>
+      <c r="Z90" s="87"/>
+      <c r="AA90" s="88"/>
+      <c r="AB90" s="89"/>
       <c r="AC90" s="32"/>
-      <c r="AD90" s="78" t="s">
+      <c r="AD90" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="AE90" s="79"/>
-      <c r="AF90" s="80"/>
+      <c r="AE90" s="88"/>
+      <c r="AF90" s="89"/>
       <c r="AG90" s="32"/>
-      <c r="AH90" s="78" t="s">
+      <c r="AH90" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="AI90" s="79"/>
-      <c r="AJ90" s="80"/>
+      <c r="AI90" s="88"/>
+      <c r="AJ90" s="89"/>
       <c r="AK90" s="32"/>
-      <c r="AL90" s="78" t="s">
+      <c r="AL90" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="AM90" s="79"/>
-      <c r="AN90" s="80"/>
+      <c r="AM90" s="88"/>
+      <c r="AN90" s="89"/>
       <c r="AO90" s="12"/>
       <c r="AP90" s="29"/>
       <c r="AQ90" s="26"/>
       <c r="AR90" s="24"/>
     </row>
-    <row r="91" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A91" s="12"/>
       <c r="B91" s="62"/>
       <c r="C91" s="63"/>
@@ -6994,7 +7067,7 @@
       <c r="AQ91" s="26"/>
       <c r="AR91" s="24"/>
     </row>
-    <row r="92" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="12"/>
       <c r="B92" s="35"/>
       <c r="C92" s="35"/>
@@ -7040,65 +7113,65 @@
       <c r="AQ92" s="26"/>
       <c r="AR92" s="24"/>
     </row>
-    <row r="93" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="12"/>
-      <c r="B93" s="114"/>
-      <c r="C93" s="115"/>
+      <c r="B93" s="65"/>
+      <c r="C93" s="66"/>
       <c r="D93" s="57"/>
       <c r="E93" s="36"/>
-      <c r="F93" s="114"/>
-      <c r="G93" s="115"/>
+      <c r="F93" s="65"/>
+      <c r="G93" s="66"/>
       <c r="H93" s="57"/>
       <c r="I93" s="32"/>
-      <c r="J93" s="114"/>
-      <c r="K93" s="115"/>
+      <c r="J93" s="65"/>
+      <c r="K93" s="66"/>
       <c r="L93" s="57"/>
       <c r="M93" s="6"/>
-      <c r="N93" s="65"/>
-      <c r="O93" s="66"/>
+      <c r="N93" s="67"/>
+      <c r="O93" s="68"/>
       <c r="P93" s="34"/>
       <c r="Q93" s="44"/>
-      <c r="R93" s="65"/>
-      <c r="S93" s="66"/>
+      <c r="R93" s="67"/>
+      <c r="S93" s="68"/>
       <c r="T93" s="34"/>
       <c r="U93" s="36"/>
-      <c r="V93" s="65"/>
-      <c r="W93" s="66"/>
+      <c r="V93" s="67"/>
+      <c r="W93" s="68"/>
       <c r="X93" s="34"/>
       <c r="Y93" s="32"/>
-      <c r="Z93" s="65"/>
-      <c r="AA93" s="66"/>
+      <c r="Z93" s="67"/>
+      <c r="AA93" s="68"/>
       <c r="AB93" s="34"/>
       <c r="AC93" s="36"/>
-      <c r="AD93" s="65"/>
-      <c r="AE93" s="66"/>
+      <c r="AD93" s="67"/>
+      <c r="AE93" s="68"/>
       <c r="AF93" s="34"/>
       <c r="AG93" s="36"/>
-      <c r="AH93" s="65"/>
-      <c r="AI93" s="66"/>
+      <c r="AH93" s="67"/>
+      <c r="AI93" s="68"/>
       <c r="AJ93" s="34"/>
       <c r="AK93" s="32"/>
-      <c r="AL93" s="65"/>
-      <c r="AM93" s="66"/>
+      <c r="AL93" s="67"/>
+      <c r="AM93" s="68"/>
       <c r="AN93" s="34"/>
       <c r="AO93" s="12"/>
       <c r="AP93" s="29"/>
       <c r="AQ93" s="26"/>
       <c r="AR93" s="24"/>
     </row>
-    <row r="94" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="12"/>
-      <c r="B94" s="111"/>
-      <c r="C94" s="112"/>
-      <c r="D94" s="113"/>
+      <c r="B94" s="84"/>
+      <c r="C94" s="85"/>
+      <c r="D94" s="86"/>
       <c r="E94" s="32"/>
-      <c r="F94" s="111"/>
-      <c r="G94" s="112"/>
-      <c r="H94" s="113"/>
+      <c r="F94" s="84"/>
+      <c r="G94" s="85"/>
+      <c r="H94" s="86"/>
       <c r="I94" s="32"/>
-      <c r="J94" s="111"/>
-      <c r="K94" s="112"/>
-      <c r="L94" s="113"/>
+      <c r="J94" s="84"/>
+      <c r="K94" s="85"/>
+      <c r="L94" s="86"/>
       <c r="M94" s="26"/>
       <c r="N94" s="69"/>
       <c r="O94" s="70"/>
@@ -7132,99 +7205,99 @@
       <c r="AQ94" s="26"/>
       <c r="AR94" s="24"/>
     </row>
-    <row r="95" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="12"/>
-      <c r="B95" s="116"/>
-      <c r="C95" s="117"/>
-      <c r="D95" s="118"/>
+      <c r="B95" s="90"/>
+      <c r="C95" s="91"/>
+      <c r="D95" s="92"/>
       <c r="E95" s="31"/>
-      <c r="F95" s="116"/>
-      <c r="G95" s="117"/>
-      <c r="H95" s="118"/>
+      <c r="F95" s="90"/>
+      <c r="G95" s="91"/>
+      <c r="H95" s="92"/>
       <c r="I95" s="32"/>
-      <c r="J95" s="116"/>
-      <c r="K95" s="117"/>
-      <c r="L95" s="118"/>
+      <c r="J95" s="90"/>
+      <c r="K95" s="91"/>
+      <c r="L95" s="92"/>
       <c r="M95" s="26"/>
-      <c r="N95" s="75"/>
-      <c r="O95" s="76"/>
-      <c r="P95" s="77"/>
+      <c r="N95" s="81"/>
+      <c r="O95" s="82"/>
+      <c r="P95" s="83"/>
       <c r="Q95" s="44"/>
-      <c r="R95" s="75"/>
-      <c r="S95" s="76"/>
-      <c r="T95" s="77"/>
+      <c r="R95" s="81"/>
+      <c r="S95" s="82"/>
+      <c r="T95" s="83"/>
       <c r="U95" s="31"/>
-      <c r="V95" s="75"/>
-      <c r="W95" s="76"/>
-      <c r="X95" s="77"/>
+      <c r="V95" s="81"/>
+      <c r="W95" s="82"/>
+      <c r="X95" s="83"/>
       <c r="Y95" s="32"/>
-      <c r="Z95" s="75"/>
-      <c r="AA95" s="76"/>
-      <c r="AB95" s="77"/>
+      <c r="Z95" s="81"/>
+      <c r="AA95" s="82"/>
+      <c r="AB95" s="83"/>
       <c r="AC95" s="35"/>
-      <c r="AD95" s="75"/>
-      <c r="AE95" s="76"/>
-      <c r="AF95" s="77"/>
+      <c r="AD95" s="81"/>
+      <c r="AE95" s="82"/>
+      <c r="AF95" s="83"/>
       <c r="AG95" s="31"/>
-      <c r="AH95" s="75"/>
-      <c r="AI95" s="76"/>
-      <c r="AJ95" s="77"/>
+      <c r="AH95" s="81"/>
+      <c r="AI95" s="82"/>
+      <c r="AJ95" s="83"/>
       <c r="AK95" s="32"/>
-      <c r="AL95" s="75"/>
-      <c r="AM95" s="76"/>
-      <c r="AN95" s="77"/>
+      <c r="AL95" s="81"/>
+      <c r="AM95" s="82"/>
+      <c r="AN95" s="83"/>
       <c r="AO95" s="12"/>
       <c r="AP95" s="29"/>
       <c r="AQ95" s="26"/>
       <c r="AR95" s="24"/>
     </row>
-    <row r="96" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="12"/>
-      <c r="B96" s="78"/>
-      <c r="C96" s="79"/>
-      <c r="D96" s="80"/>
+      <c r="B96" s="87"/>
+      <c r="C96" s="88"/>
+      <c r="D96" s="89"/>
       <c r="E96" s="32"/>
-      <c r="F96" s="78"/>
-      <c r="G96" s="79"/>
-      <c r="H96" s="80"/>
+      <c r="F96" s="87"/>
+      <c r="G96" s="88"/>
+      <c r="H96" s="89"/>
       <c r="I96" s="32"/>
-      <c r="J96" s="78"/>
-      <c r="K96" s="79"/>
-      <c r="L96" s="80"/>
+      <c r="J96" s="87"/>
+      <c r="K96" s="88"/>
+      <c r="L96" s="89"/>
       <c r="M96" s="26"/>
-      <c r="N96" s="78"/>
-      <c r="O96" s="79"/>
-      <c r="P96" s="80"/>
+      <c r="N96" s="87"/>
+      <c r="O96" s="88"/>
+      <c r="P96" s="89"/>
       <c r="Q96" s="44"/>
-      <c r="R96" s="78"/>
-      <c r="S96" s="79"/>
-      <c r="T96" s="80"/>
+      <c r="R96" s="87"/>
+      <c r="S96" s="88"/>
+      <c r="T96" s="89"/>
       <c r="U96" s="32"/>
-      <c r="V96" s="78"/>
-      <c r="W96" s="79"/>
-      <c r="X96" s="80"/>
+      <c r="V96" s="87"/>
+      <c r="W96" s="88"/>
+      <c r="X96" s="89"/>
       <c r="Y96" s="32"/>
-      <c r="Z96" s="78"/>
-      <c r="AA96" s="79"/>
-      <c r="AB96" s="80"/>
+      <c r="Z96" s="87"/>
+      <c r="AA96" s="88"/>
+      <c r="AB96" s="89"/>
       <c r="AC96" s="31"/>
-      <c r="AD96" s="78"/>
-      <c r="AE96" s="79"/>
-      <c r="AF96" s="80"/>
+      <c r="AD96" s="87"/>
+      <c r="AE96" s="88"/>
+      <c r="AF96" s="89"/>
       <c r="AG96" s="32"/>
-      <c r="AH96" s="78"/>
-      <c r="AI96" s="79"/>
-      <c r="AJ96" s="80"/>
+      <c r="AH96" s="87"/>
+      <c r="AI96" s="88"/>
+      <c r="AJ96" s="89"/>
       <c r="AK96" s="32"/>
-      <c r="AL96" s="78"/>
-      <c r="AM96" s="79"/>
-      <c r="AN96" s="80"/>
+      <c r="AL96" s="87"/>
+      <c r="AM96" s="88"/>
+      <c r="AN96" s="89"/>
       <c r="AO96" s="12"/>
       <c r="AP96" s="29"/>
       <c r="AQ96" s="26"/>
       <c r="AR96" s="24"/>
     </row>
-    <row r="97" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A97" s="12"/>
       <c r="B97" s="62"/>
       <c r="C97" s="63"/>
@@ -7270,7 +7343,7 @@
       <c r="AQ97" s="26"/>
       <c r="AR97" s="24"/>
     </row>
-    <row r="98" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="12"/>
       <c r="B98" s="35"/>
       <c r="C98" s="35"/>
@@ -7316,145 +7389,145 @@
       <c r="AQ98" s="26"/>
       <c r="AR98" s="24"/>
     </row>
-    <row r="99" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="12"/>
-      <c r="B99" s="114"/>
-      <c r="C99" s="115"/>
+      <c r="B99" s="65"/>
+      <c r="C99" s="66"/>
       <c r="D99" s="57"/>
       <c r="E99" s="32"/>
-      <c r="F99" s="114"/>
-      <c r="G99" s="115"/>
+      <c r="F99" s="65"/>
+      <c r="G99" s="66"/>
       <c r="H99" s="57"/>
       <c r="I99" s="36"/>
-      <c r="J99" s="114"/>
-      <c r="K99" s="115"/>
+      <c r="J99" s="65"/>
+      <c r="K99" s="66"/>
       <c r="L99" s="57"/>
       <c r="M99" s="26"/>
-      <c r="N99" s="65"/>
-      <c r="O99" s="66"/>
+      <c r="N99" s="67"/>
+      <c r="O99" s="68"/>
       <c r="P99" s="34"/>
       <c r="Q99" s="44"/>
-      <c r="R99" s="65"/>
-      <c r="S99" s="66"/>
+      <c r="R99" s="67"/>
+      <c r="S99" s="68"/>
       <c r="T99" s="34"/>
       <c r="U99" s="36"/>
-      <c r="V99" s="65"/>
-      <c r="W99" s="66"/>
+      <c r="V99" s="67"/>
+      <c r="W99" s="68"/>
       <c r="X99" s="34"/>
       <c r="Y99" s="32"/>
-      <c r="Z99" s="65"/>
-      <c r="AA99" s="66"/>
+      <c r="Z99" s="67"/>
+      <c r="AA99" s="68"/>
       <c r="AB99" s="34"/>
       <c r="AC99" s="36"/>
-      <c r="AD99" s="65"/>
-      <c r="AE99" s="66"/>
+      <c r="AD99" s="67"/>
+      <c r="AE99" s="68"/>
       <c r="AF99" s="34"/>
       <c r="AG99" s="32"/>
-      <c r="AH99" s="65"/>
-      <c r="AI99" s="66"/>
+      <c r="AH99" s="67"/>
+      <c r="AI99" s="68"/>
       <c r="AJ99" s="34"/>
       <c r="AK99" s="36"/>
-      <c r="AL99" s="65"/>
-      <c r="AM99" s="66"/>
+      <c r="AL99" s="67"/>
+      <c r="AM99" s="68"/>
       <c r="AN99" s="34"/>
       <c r="AO99" s="12"/>
       <c r="AP99" s="29"/>
       <c r="AQ99" s="26"/>
       <c r="AR99" s="24"/>
     </row>
-    <row r="100" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="12"/>
-      <c r="B100" s="116"/>
-      <c r="C100" s="117"/>
-      <c r="D100" s="118"/>
+      <c r="B100" s="90"/>
+      <c r="C100" s="91"/>
+      <c r="D100" s="92"/>
       <c r="E100" s="32"/>
-      <c r="F100" s="116"/>
-      <c r="G100" s="117"/>
-      <c r="H100" s="118"/>
+      <c r="F100" s="90"/>
+      <c r="G100" s="91"/>
+      <c r="H100" s="92"/>
       <c r="I100" s="31"/>
-      <c r="J100" s="116"/>
-      <c r="K100" s="117"/>
-      <c r="L100" s="118"/>
+      <c r="J100" s="90"/>
+      <c r="K100" s="91"/>
+      <c r="L100" s="92"/>
       <c r="M100" s="26"/>
-      <c r="N100" s="75"/>
-      <c r="O100" s="76"/>
-      <c r="P100" s="77"/>
+      <c r="N100" s="81"/>
+      <c r="O100" s="82"/>
+      <c r="P100" s="83"/>
       <c r="Q100" s="31"/>
-      <c r="R100" s="75"/>
-      <c r="S100" s="76"/>
-      <c r="T100" s="77"/>
+      <c r="R100" s="81"/>
+      <c r="S100" s="82"/>
+      <c r="T100" s="83"/>
       <c r="U100" s="31"/>
-      <c r="V100" s="75"/>
-      <c r="W100" s="76"/>
-      <c r="X100" s="77"/>
+      <c r="V100" s="81"/>
+      <c r="W100" s="82"/>
+      <c r="X100" s="83"/>
       <c r="Y100" s="32"/>
-      <c r="Z100" s="75"/>
-      <c r="AA100" s="76"/>
-      <c r="AB100" s="77"/>
+      <c r="Z100" s="81"/>
+      <c r="AA100" s="82"/>
+      <c r="AB100" s="83"/>
       <c r="AC100" s="36"/>
-      <c r="AD100" s="75"/>
-      <c r="AE100" s="76"/>
-      <c r="AF100" s="77"/>
+      <c r="AD100" s="81"/>
+      <c r="AE100" s="82"/>
+      <c r="AF100" s="83"/>
       <c r="AG100" s="32"/>
-      <c r="AH100" s="75"/>
-      <c r="AI100" s="76"/>
-      <c r="AJ100" s="77"/>
+      <c r="AH100" s="81"/>
+      <c r="AI100" s="82"/>
+      <c r="AJ100" s="83"/>
       <c r="AK100" s="31"/>
-      <c r="AL100" s="75"/>
-      <c r="AM100" s="76"/>
-      <c r="AN100" s="77"/>
+      <c r="AL100" s="81"/>
+      <c r="AM100" s="82"/>
+      <c r="AN100" s="83"/>
       <c r="AO100" s="12"/>
       <c r="AP100" s="29"/>
       <c r="AQ100" s="26"/>
       <c r="AR100" s="24"/>
     </row>
-    <row r="101" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="12"/>
-      <c r="B101" s="78"/>
-      <c r="C101" s="79"/>
-      <c r="D101" s="80"/>
+      <c r="B101" s="87"/>
+      <c r="C101" s="88"/>
+      <c r="D101" s="89"/>
       <c r="E101" s="32"/>
-      <c r="F101" s="78"/>
-      <c r="G101" s="79"/>
-      <c r="H101" s="80"/>
+      <c r="F101" s="87"/>
+      <c r="G101" s="88"/>
+      <c r="H101" s="89"/>
       <c r="I101" s="31"/>
-      <c r="J101" s="78"/>
-      <c r="K101" s="79"/>
-      <c r="L101" s="80"/>
+      <c r="J101" s="87"/>
+      <c r="K101" s="88"/>
+      <c r="L101" s="89"/>
       <c r="M101" s="26"/>
-      <c r="N101" s="78"/>
-      <c r="O101" s="79"/>
-      <c r="P101" s="80"/>
+      <c r="N101" s="87"/>
+      <c r="O101" s="88"/>
+      <c r="P101" s="89"/>
       <c r="Q101" s="31"/>
-      <c r="R101" s="78"/>
-      <c r="S101" s="79"/>
-      <c r="T101" s="80"/>
+      <c r="R101" s="87"/>
+      <c r="S101" s="88"/>
+      <c r="T101" s="89"/>
       <c r="U101" s="32"/>
-      <c r="V101" s="78"/>
-      <c r="W101" s="79"/>
-      <c r="X101" s="80"/>
+      <c r="V101" s="87"/>
+      <c r="W101" s="88"/>
+      <c r="X101" s="89"/>
       <c r="Y101" s="32"/>
-      <c r="Z101" s="78"/>
-      <c r="AA101" s="79"/>
-      <c r="AB101" s="80"/>
+      <c r="Z101" s="87"/>
+      <c r="AA101" s="88"/>
+      <c r="AB101" s="89"/>
       <c r="AC101" s="31"/>
-      <c r="AD101" s="78"/>
-      <c r="AE101" s="79"/>
-      <c r="AF101" s="80"/>
+      <c r="AD101" s="87"/>
+      <c r="AE101" s="88"/>
+      <c r="AF101" s="89"/>
       <c r="AG101" s="32"/>
-      <c r="AH101" s="78"/>
-      <c r="AI101" s="79"/>
-      <c r="AJ101" s="80"/>
+      <c r="AH101" s="87"/>
+      <c r="AI101" s="88"/>
+      <c r="AJ101" s="89"/>
       <c r="AK101" s="31"/>
-      <c r="AL101" s="78"/>
-      <c r="AM101" s="79"/>
-      <c r="AN101" s="80"/>
+      <c r="AL101" s="87"/>
+      <c r="AM101" s="88"/>
+      <c r="AN101" s="89"/>
       <c r="AO101" s="12"/>
       <c r="AP101" s="29"/>
       <c r="AQ101" s="26"/>
       <c r="AR101" s="24"/>
     </row>
-    <row r="102" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A102" s="12"/>
       <c r="B102" s="62"/>
       <c r="C102" s="63"/>
@@ -7500,7 +7573,7 @@
       <c r="AQ102" s="26"/>
       <c r="AR102" s="24"/>
     </row>
-    <row r="103" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="12"/>
       <c r="B103" s="40"/>
       <c r="C103" s="33"/>
@@ -7546,7 +7619,7 @@
       <c r="AQ103" s="26"/>
       <c r="AR103" s="26"/>
     </row>
-    <row r="104" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B104" s="33"/>
       <c r="C104" s="33"/>
       <c r="D104" s="33"/>
@@ -7563,21 +7636,21 @@
       <c r="AQ104" s="26"/>
       <c r="AR104" s="26"/>
     </row>
-    <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B105" s="65"/>
-      <c r="C105" s="66"/>
+    <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B105" s="67"/>
+      <c r="C105" s="68"/>
       <c r="D105" s="34"/>
       <c r="E105" s="32"/>
-      <c r="F105" s="65"/>
-      <c r="G105" s="66"/>
+      <c r="F105" s="67"/>
+      <c r="G105" s="68"/>
       <c r="H105" s="34"/>
       <c r="I105" s="32"/>
-      <c r="J105" s="65"/>
-      <c r="K105" s="66"/>
+      <c r="J105" s="67"/>
+      <c r="K105" s="68"/>
       <c r="L105" s="34"/>
       <c r="AO105" s="26"/>
     </row>
-    <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B106" s="69"/>
       <c r="C106" s="70"/>
       <c r="D106" s="71"/>
@@ -7590,33 +7663,33 @@
       <c r="K106" s="70"/>
       <c r="L106" s="71"/>
     </row>
-    <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B107" s="75"/>
-      <c r="C107" s="76"/>
-      <c r="D107" s="77"/>
+    <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B107" s="81"/>
+      <c r="C107" s="82"/>
+      <c r="D107" s="83"/>
       <c r="E107" s="32"/>
-      <c r="F107" s="75"/>
-      <c r="G107" s="76"/>
-      <c r="H107" s="77"/>
+      <c r="F107" s="81"/>
+      <c r="G107" s="82"/>
+      <c r="H107" s="83"/>
       <c r="I107" s="32"/>
-      <c r="J107" s="75"/>
-      <c r="K107" s="76"/>
-      <c r="L107" s="77"/>
-    </row>
-    <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B108" s="78"/>
-      <c r="C108" s="79"/>
-      <c r="D108" s="80"/>
+      <c r="J107" s="81"/>
+      <c r="K107" s="82"/>
+      <c r="L107" s="83"/>
+    </row>
+    <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B108" s="87"/>
+      <c r="C108" s="88"/>
+      <c r="D108" s="89"/>
       <c r="E108" s="32"/>
-      <c r="F108" s="78"/>
-      <c r="G108" s="79"/>
-      <c r="H108" s="80"/>
+      <c r="F108" s="87"/>
+      <c r="G108" s="88"/>
+      <c r="H108" s="89"/>
       <c r="I108" s="31"/>
-      <c r="J108" s="78"/>
-      <c r="K108" s="79"/>
-      <c r="L108" s="80"/>
-    </row>
-    <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J108" s="87"/>
+      <c r="K108" s="88"/>
+      <c r="L108" s="89"/>
+    </row>
+    <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B109" s="62"/>
       <c r="C109" s="63"/>
       <c r="D109" s="64"/>
@@ -7629,7 +7702,7 @@
       <c r="K109" s="63"/>
       <c r="L109" s="64"/>
     </row>
-    <row r="110" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B110" s="35"/>
       <c r="C110" s="35"/>
       <c r="D110" s="35"/>
@@ -7642,20 +7715,20 @@
       <c r="K110" s="35"/>
       <c r="L110" s="35"/>
     </row>
-    <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B111" s="65"/>
-      <c r="C111" s="66"/>
+    <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B111" s="67"/>
+      <c r="C111" s="68"/>
       <c r="D111" s="34"/>
       <c r="E111" s="31"/>
-      <c r="F111" s="65"/>
-      <c r="G111" s="66"/>
+      <c r="F111" s="67"/>
+      <c r="G111" s="68"/>
       <c r="H111" s="34"/>
       <c r="I111" s="31"/>
-      <c r="J111" s="65"/>
-      <c r="K111" s="66"/>
+      <c r="J111" s="67"/>
+      <c r="K111" s="68"/>
       <c r="L111" s="34"/>
     </row>
-    <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B112" s="69"/>
       <c r="C112" s="70"/>
       <c r="D112" s="71"/>
@@ -7668,33 +7741,33 @@
       <c r="K112" s="70"/>
       <c r="L112" s="71"/>
     </row>
-    <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B113" s="75"/>
-      <c r="C113" s="76"/>
-      <c r="D113" s="77"/>
+    <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B113" s="81"/>
+      <c r="C113" s="82"/>
+      <c r="D113" s="83"/>
       <c r="E113" s="35"/>
-      <c r="F113" s="75"/>
-      <c r="G113" s="76"/>
-      <c r="H113" s="77"/>
+      <c r="F113" s="81"/>
+      <c r="G113" s="82"/>
+      <c r="H113" s="83"/>
       <c r="I113" s="35"/>
-      <c r="J113" s="75"/>
-      <c r="K113" s="76"/>
-      <c r="L113" s="77"/>
-    </row>
-    <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B114" s="78"/>
-      <c r="C114" s="79"/>
-      <c r="D114" s="80"/>
+      <c r="J113" s="81"/>
+      <c r="K113" s="82"/>
+      <c r="L113" s="83"/>
+    </row>
+    <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B114" s="87"/>
+      <c r="C114" s="88"/>
+      <c r="D114" s="89"/>
       <c r="E114" s="32"/>
-      <c r="F114" s="78"/>
-      <c r="G114" s="79"/>
-      <c r="H114" s="80"/>
+      <c r="F114" s="87"/>
+      <c r="G114" s="88"/>
+      <c r="H114" s="89"/>
       <c r="I114" s="32"/>
-      <c r="J114" s="78"/>
-      <c r="K114" s="79"/>
-      <c r="L114" s="80"/>
-    </row>
-    <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J114" s="87"/>
+      <c r="K114" s="88"/>
+      <c r="L114" s="89"/>
+    </row>
+    <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B115" s="62"/>
       <c r="C115" s="63"/>
       <c r="D115" s="64"/>
@@ -7707,7 +7780,7 @@
       <c r="K115" s="63"/>
       <c r="L115" s="64"/>
     </row>
-    <row r="116" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B116" s="35"/>
       <c r="C116" s="35"/>
       <c r="D116" s="35"/>
@@ -7720,20 +7793,20 @@
       <c r="K116" s="35"/>
       <c r="L116" s="35"/>
     </row>
-    <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="65"/>
-      <c r="C117" s="66"/>
+    <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B117" s="67"/>
+      <c r="C117" s="68"/>
       <c r="D117" s="34"/>
       <c r="E117" s="32"/>
-      <c r="F117" s="65"/>
-      <c r="G117" s="66"/>
+      <c r="F117" s="67"/>
+      <c r="G117" s="68"/>
       <c r="H117" s="34"/>
       <c r="I117" s="32"/>
-      <c r="J117" s="65"/>
-      <c r="K117" s="66"/>
+      <c r="J117" s="67"/>
+      <c r="K117" s="68"/>
       <c r="L117" s="34"/>
     </row>
-    <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B118" s="69"/>
       <c r="C118" s="70"/>
       <c r="D118" s="71"/>
@@ -7746,33 +7819,33 @@
       <c r="K118" s="70"/>
       <c r="L118" s="71"/>
     </row>
-    <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B119" s="75"/>
-      <c r="C119" s="76"/>
-      <c r="D119" s="77"/>
+    <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B119" s="81"/>
+      <c r="C119" s="82"/>
+      <c r="D119" s="83"/>
       <c r="E119" s="32"/>
-      <c r="F119" s="75"/>
-      <c r="G119" s="76"/>
-      <c r="H119" s="77"/>
+      <c r="F119" s="81"/>
+      <c r="G119" s="82"/>
+      <c r="H119" s="83"/>
       <c r="I119" s="32"/>
-      <c r="J119" s="75"/>
-      <c r="K119" s="76"/>
-      <c r="L119" s="77"/>
-    </row>
-    <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B120" s="78"/>
-      <c r="C120" s="79"/>
-      <c r="D120" s="80"/>
+      <c r="J119" s="81"/>
+      <c r="K119" s="82"/>
+      <c r="L119" s="83"/>
+    </row>
+    <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B120" s="87"/>
+      <c r="C120" s="88"/>
+      <c r="D120" s="89"/>
       <c r="E120" s="32"/>
-      <c r="F120" s="78"/>
-      <c r="G120" s="79"/>
-      <c r="H120" s="80"/>
+      <c r="F120" s="87"/>
+      <c r="G120" s="88"/>
+      <c r="H120" s="89"/>
       <c r="I120" s="32"/>
-      <c r="J120" s="78"/>
-      <c r="K120" s="79"/>
-      <c r="L120" s="80"/>
-    </row>
-    <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J120" s="87"/>
+      <c r="K120" s="88"/>
+      <c r="L120" s="89"/>
+    </row>
+    <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B121" s="62"/>
       <c r="C121" s="63"/>
       <c r="D121" s="64"/>
@@ -7785,7 +7858,7 @@
       <c r="K121" s="63"/>
       <c r="L121" s="64"/>
     </row>
-    <row r="122" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B122" s="35"/>
       <c r="C122" s="35"/>
       <c r="D122" s="35"/>
@@ -7798,20 +7871,20 @@
       <c r="K122" s="35"/>
       <c r="L122" s="35"/>
     </row>
-    <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="65"/>
-      <c r="C123" s="66"/>
+    <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B123" s="67"/>
+      <c r="C123" s="68"/>
       <c r="D123" s="34"/>
       <c r="E123" s="32"/>
-      <c r="F123" s="65"/>
-      <c r="G123" s="66"/>
+      <c r="F123" s="67"/>
+      <c r="G123" s="68"/>
       <c r="H123" s="34"/>
       <c r="I123" s="32"/>
-      <c r="J123" s="65"/>
-      <c r="K123" s="66"/>
+      <c r="J123" s="67"/>
+      <c r="K123" s="68"/>
       <c r="L123" s="34"/>
     </row>
-    <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B124" s="69"/>
       <c r="C124" s="70"/>
       <c r="D124" s="71"/>
@@ -7824,33 +7897,33 @@
       <c r="K124" s="70"/>
       <c r="L124" s="71"/>
     </row>
-    <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="75"/>
-      <c r="C125" s="76"/>
-      <c r="D125" s="77"/>
+    <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B125" s="81"/>
+      <c r="C125" s="82"/>
+      <c r="D125" s="83"/>
       <c r="E125" s="32"/>
-      <c r="F125" s="75"/>
-      <c r="G125" s="76"/>
-      <c r="H125" s="77"/>
+      <c r="F125" s="81"/>
+      <c r="G125" s="82"/>
+      <c r="H125" s="83"/>
       <c r="I125" s="32"/>
-      <c r="J125" s="75"/>
-      <c r="K125" s="76"/>
-      <c r="L125" s="77"/>
-    </row>
-    <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B126" s="78"/>
-      <c r="C126" s="79"/>
-      <c r="D126" s="80"/>
+      <c r="J125" s="81"/>
+      <c r="K125" s="82"/>
+      <c r="L125" s="83"/>
+    </row>
+    <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B126" s="87"/>
+      <c r="C126" s="88"/>
+      <c r="D126" s="89"/>
       <c r="E126" s="32"/>
-      <c r="F126" s="78"/>
-      <c r="G126" s="79"/>
-      <c r="H126" s="80"/>
+      <c r="F126" s="87"/>
+      <c r="G126" s="88"/>
+      <c r="H126" s="89"/>
       <c r="I126" s="31"/>
-      <c r="J126" s="78"/>
-      <c r="K126" s="79"/>
-      <c r="L126" s="80"/>
-    </row>
-    <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J126" s="87"/>
+      <c r="K126" s="88"/>
+      <c r="L126" s="89"/>
+    </row>
+    <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B127" s="62"/>
       <c r="C127" s="63"/>
       <c r="D127" s="64"/>
@@ -7863,7 +7936,7 @@
       <c r="K127" s="63"/>
       <c r="L127" s="64"/>
     </row>
-    <row r="128" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B128" s="35"/>
       <c r="C128" s="35"/>
       <c r="D128" s="35"/>
@@ -7876,20 +7949,20 @@
       <c r="K128" s="35"/>
       <c r="L128" s="35"/>
     </row>
-    <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B129" s="65"/>
-      <c r="C129" s="66"/>
+    <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B129" s="67"/>
+      <c r="C129" s="68"/>
       <c r="D129" s="34"/>
       <c r="E129" s="31"/>
-      <c r="F129" s="65"/>
-      <c r="G129" s="66"/>
+      <c r="F129" s="67"/>
+      <c r="G129" s="68"/>
       <c r="H129" s="34"/>
       <c r="I129" s="32"/>
-      <c r="J129" s="65"/>
-      <c r="K129" s="66"/>
+      <c r="J129" s="67"/>
+      <c r="K129" s="68"/>
       <c r="L129" s="34"/>
     </row>
-    <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B130" s="69"/>
       <c r="C130" s="70"/>
       <c r="D130" s="71"/>
@@ -7902,33 +7975,33 @@
       <c r="K130" s="70"/>
       <c r="L130" s="71"/>
     </row>
-    <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B131" s="75"/>
-      <c r="C131" s="76"/>
-      <c r="D131" s="77"/>
+    <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B131" s="81"/>
+      <c r="C131" s="82"/>
+      <c r="D131" s="83"/>
       <c r="E131" s="35"/>
-      <c r="F131" s="75"/>
-      <c r="G131" s="76"/>
-      <c r="H131" s="77"/>
+      <c r="F131" s="81"/>
+      <c r="G131" s="82"/>
+      <c r="H131" s="83"/>
       <c r="I131" s="32"/>
-      <c r="J131" s="75"/>
-      <c r="K131" s="76"/>
-      <c r="L131" s="77"/>
-    </row>
-    <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B132" s="78"/>
-      <c r="C132" s="79"/>
-      <c r="D132" s="80"/>
+      <c r="J131" s="81"/>
+      <c r="K131" s="82"/>
+      <c r="L131" s="83"/>
+    </row>
+    <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B132" s="87"/>
+      <c r="C132" s="88"/>
+      <c r="D132" s="89"/>
       <c r="E132" s="35"/>
-      <c r="F132" s="78"/>
-      <c r="G132" s="79"/>
-      <c r="H132" s="80"/>
+      <c r="F132" s="87"/>
+      <c r="G132" s="88"/>
+      <c r="H132" s="89"/>
       <c r="I132" s="31"/>
-      <c r="J132" s="78"/>
-      <c r="K132" s="79"/>
-      <c r="L132" s="80"/>
-    </row>
-    <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J132" s="87"/>
+      <c r="K132" s="88"/>
+      <c r="L132" s="89"/>
+    </row>
+    <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B133" s="62"/>
       <c r="C133" s="63"/>
       <c r="D133" s="64"/>
@@ -7945,21 +8018,829 @@
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0" selectUnlockedCells="1"/>
   <dataConsolidate/>
   <mergeCells count="862">
-    <mergeCell ref="B97:D97"/>
-    <mergeCell ref="F97:H97"/>
-    <mergeCell ref="J97:L97"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="F99:G99"/>
-    <mergeCell ref="J99:K99"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="J87:K87"/>
-    <mergeCell ref="B91:D91"/>
-    <mergeCell ref="F91:H91"/>
-    <mergeCell ref="J91:L91"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="F93:G93"/>
-    <mergeCell ref="J93:K93"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="J39:L39"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="AL75:AM75"/>
+    <mergeCell ref="AH71:AJ71"/>
+    <mergeCell ref="AD71:AF71"/>
+    <mergeCell ref="Z71:AB71"/>
+    <mergeCell ref="AL66:AM66"/>
+    <mergeCell ref="AD69:AF69"/>
+    <mergeCell ref="AH69:AJ69"/>
+    <mergeCell ref="AD64:AF64"/>
+    <mergeCell ref="AD61:AF61"/>
+    <mergeCell ref="AH61:AJ61"/>
+    <mergeCell ref="Z57:AB57"/>
+    <mergeCell ref="AD54:AF54"/>
+    <mergeCell ref="AD55:AF55"/>
+    <mergeCell ref="AD32:AE32"/>
+    <mergeCell ref="AH32:AI32"/>
+    <mergeCell ref="AL32:AM32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="AH13:AI13"/>
+    <mergeCell ref="AL13:AM13"/>
+    <mergeCell ref="AH67:AJ67"/>
+    <mergeCell ref="AL67:AN67"/>
+    <mergeCell ref="AH48:AJ48"/>
+    <mergeCell ref="AH50:AJ50"/>
+    <mergeCell ref="AL29:AM29"/>
+    <mergeCell ref="Z30:AA30"/>
+    <mergeCell ref="AD30:AE30"/>
+    <mergeCell ref="AH30:AI30"/>
+    <mergeCell ref="AL30:AM30"/>
+    <mergeCell ref="N25:AB26"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="V28:W28"/>
+    <mergeCell ref="Z28:AA28"/>
+    <mergeCell ref="AL40:AN40"/>
+    <mergeCell ref="AL41:AN41"/>
+    <mergeCell ref="AL47:AN47"/>
+    <mergeCell ref="AL48:AN48"/>
+    <mergeCell ref="AH42:AJ42"/>
+    <mergeCell ref="AH43:AJ43"/>
+    <mergeCell ref="AH49:AJ49"/>
+    <mergeCell ref="Z47:AB47"/>
+    <mergeCell ref="AD99:AE99"/>
+    <mergeCell ref="AH99:AI99"/>
+    <mergeCell ref="AL99:AM99"/>
+    <mergeCell ref="R91:T91"/>
+    <mergeCell ref="V91:X91"/>
+    <mergeCell ref="Z91:AB91"/>
+    <mergeCell ref="AD91:AF91"/>
+    <mergeCell ref="AH91:AJ91"/>
+    <mergeCell ref="AL91:AN91"/>
+    <mergeCell ref="R97:T97"/>
+    <mergeCell ref="V97:X97"/>
+    <mergeCell ref="Z97:AB97"/>
+    <mergeCell ref="AD93:AE93"/>
+    <mergeCell ref="AH93:AI93"/>
+    <mergeCell ref="AL93:AM93"/>
+    <mergeCell ref="R93:S93"/>
+    <mergeCell ref="V93:W93"/>
+    <mergeCell ref="Z93:AA93"/>
+    <mergeCell ref="N76:P76"/>
+    <mergeCell ref="N77:P77"/>
+    <mergeCell ref="R46:T46"/>
+    <mergeCell ref="Z85:AB85"/>
+    <mergeCell ref="Z89:AB89"/>
+    <mergeCell ref="Z90:AB90"/>
+    <mergeCell ref="Z83:AB83"/>
+    <mergeCell ref="Z84:AB84"/>
+    <mergeCell ref="Z82:AB82"/>
+    <mergeCell ref="V51:X51"/>
+    <mergeCell ref="Z51:AB51"/>
+    <mergeCell ref="Z62:AB62"/>
+    <mergeCell ref="N69:P69"/>
+    <mergeCell ref="N68:P68"/>
+    <mergeCell ref="R68:T68"/>
+    <mergeCell ref="V68:X68"/>
+    <mergeCell ref="N67:P67"/>
+    <mergeCell ref="N71:P71"/>
+    <mergeCell ref="AL31:AM31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="R87:S87"/>
+    <mergeCell ref="V87:W87"/>
+    <mergeCell ref="Z87:AA87"/>
+    <mergeCell ref="AD87:AE87"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="V34:W34"/>
+    <mergeCell ref="Z34:AA34"/>
+    <mergeCell ref="AD34:AE34"/>
+    <mergeCell ref="R66:S66"/>
+    <mergeCell ref="V66:W66"/>
+    <mergeCell ref="Z66:AA66"/>
+    <mergeCell ref="R67:T67"/>
+    <mergeCell ref="V67:X67"/>
+    <mergeCell ref="Z67:AB67"/>
+    <mergeCell ref="V69:X69"/>
+    <mergeCell ref="R69:T69"/>
+    <mergeCell ref="V70:X70"/>
+    <mergeCell ref="R70:T70"/>
+    <mergeCell ref="R77:T77"/>
+    <mergeCell ref="AD33:AE33"/>
+    <mergeCell ref="AH33:AI33"/>
+    <mergeCell ref="AL33:AM33"/>
+    <mergeCell ref="AL38:AM38"/>
+    <mergeCell ref="AL39:AN39"/>
+    <mergeCell ref="AH41:AJ41"/>
+    <mergeCell ref="AD41:AF41"/>
+    <mergeCell ref="AL43:AN43"/>
+    <mergeCell ref="AL45:AM45"/>
+    <mergeCell ref="AL42:AN42"/>
+    <mergeCell ref="Z41:AB41"/>
+    <mergeCell ref="Z40:AB40"/>
+    <mergeCell ref="Z38:AA38"/>
+    <mergeCell ref="Z39:AB39"/>
+    <mergeCell ref="AL34:AM34"/>
+    <mergeCell ref="N55:P55"/>
+    <mergeCell ref="R56:T56"/>
+    <mergeCell ref="N59:O59"/>
+    <mergeCell ref="N56:P56"/>
+    <mergeCell ref="R54:T54"/>
+    <mergeCell ref="V54:X54"/>
+    <mergeCell ref="V53:W53"/>
+    <mergeCell ref="N54:P54"/>
+    <mergeCell ref="N53:P53"/>
+    <mergeCell ref="R55:T55"/>
+    <mergeCell ref="R59:S59"/>
+    <mergeCell ref="V59:W59"/>
+    <mergeCell ref="R53:T53"/>
+    <mergeCell ref="V56:X56"/>
+    <mergeCell ref="N57:P57"/>
+    <mergeCell ref="V55:X55"/>
+    <mergeCell ref="V57:X57"/>
+    <mergeCell ref="R57:T57"/>
+    <mergeCell ref="V42:X42"/>
+    <mergeCell ref="AH52:AI52"/>
+    <mergeCell ref="AH54:AJ54"/>
+    <mergeCell ref="AH55:AJ55"/>
+    <mergeCell ref="R42:T42"/>
+    <mergeCell ref="Z54:AB54"/>
+    <mergeCell ref="Z50:AB50"/>
+    <mergeCell ref="V45:W45"/>
+    <mergeCell ref="V46:X46"/>
+    <mergeCell ref="V47:X47"/>
+    <mergeCell ref="Z49:AB49"/>
+    <mergeCell ref="V49:X49"/>
+    <mergeCell ref="V48:X48"/>
+    <mergeCell ref="AH34:AI34"/>
+    <mergeCell ref="AD46:AF46"/>
+    <mergeCell ref="AD47:AF47"/>
+    <mergeCell ref="AH40:AJ40"/>
+    <mergeCell ref="AH46:AJ46"/>
+    <mergeCell ref="AH45:AI45"/>
+    <mergeCell ref="AH38:AI38"/>
+    <mergeCell ref="AH39:AJ39"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="J46:L46"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="N45:O45"/>
+    <mergeCell ref="J49:L49"/>
+    <mergeCell ref="J47:L47"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="N60:P60"/>
+    <mergeCell ref="V33:W33"/>
+    <mergeCell ref="Z33:AA33"/>
+    <mergeCell ref="N32:O32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="V32:W32"/>
+    <mergeCell ref="Z32:AA32"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="N29:O29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="V29:W29"/>
+    <mergeCell ref="Z29:AA29"/>
+    <mergeCell ref="Z27:AA27"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="V30:W30"/>
+    <mergeCell ref="Z31:AA31"/>
+    <mergeCell ref="V50:X50"/>
+    <mergeCell ref="Z53:AA53"/>
+    <mergeCell ref="R49:T49"/>
+    <mergeCell ref="R47:T47"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="AL28:AM28"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="N61:P61"/>
+    <mergeCell ref="AD66:AE66"/>
+    <mergeCell ref="AH66:AI66"/>
+    <mergeCell ref="R61:T61"/>
+    <mergeCell ref="V61:X61"/>
+    <mergeCell ref="Z61:AB61"/>
+    <mergeCell ref="Z59:AA59"/>
+    <mergeCell ref="AH63:AJ63"/>
+    <mergeCell ref="AH62:AJ62"/>
+    <mergeCell ref="AD62:AF62"/>
+    <mergeCell ref="AD60:AF60"/>
+    <mergeCell ref="AH60:AJ60"/>
+    <mergeCell ref="V62:X62"/>
+    <mergeCell ref="V63:X63"/>
+    <mergeCell ref="Z64:AB64"/>
+    <mergeCell ref="R60:T60"/>
+    <mergeCell ref="V60:X60"/>
+    <mergeCell ref="Z60:AB60"/>
+    <mergeCell ref="V64:X64"/>
+    <mergeCell ref="R64:T64"/>
+    <mergeCell ref="N63:P63"/>
+    <mergeCell ref="N66:O66"/>
+    <mergeCell ref="AH64:AJ64"/>
+    <mergeCell ref="AD67:AF67"/>
+    <mergeCell ref="AL20:AM20"/>
+    <mergeCell ref="AL27:AM27"/>
+    <mergeCell ref="AL21:AM21"/>
+    <mergeCell ref="AH27:AI27"/>
+    <mergeCell ref="AD20:AE20"/>
+    <mergeCell ref="AH20:AI20"/>
+    <mergeCell ref="Z68:AB68"/>
+    <mergeCell ref="AD68:AF68"/>
+    <mergeCell ref="AH68:AJ68"/>
+    <mergeCell ref="AL68:AN68"/>
+    <mergeCell ref="Z63:AB63"/>
+    <mergeCell ref="AL60:AN60"/>
+    <mergeCell ref="AL64:AN64"/>
+    <mergeCell ref="AL61:AN61"/>
+    <mergeCell ref="Z56:AB56"/>
+    <mergeCell ref="AL22:AN22"/>
+    <mergeCell ref="Z23:AB23"/>
+    <mergeCell ref="AD23:AF23"/>
+    <mergeCell ref="AH23:AJ23"/>
+    <mergeCell ref="AL23:AN23"/>
+    <mergeCell ref="AD28:AE28"/>
+    <mergeCell ref="AH28:AI28"/>
+    <mergeCell ref="N82:P82"/>
+    <mergeCell ref="AH76:AJ76"/>
+    <mergeCell ref="AL76:AN76"/>
+    <mergeCell ref="AD76:AF76"/>
+    <mergeCell ref="Z81:AA81"/>
+    <mergeCell ref="AL62:AN62"/>
+    <mergeCell ref="AL63:AN63"/>
+    <mergeCell ref="AL71:AN71"/>
+    <mergeCell ref="AL70:AN70"/>
+    <mergeCell ref="AL69:AN69"/>
+    <mergeCell ref="N73:AB74"/>
+    <mergeCell ref="N75:O75"/>
+    <mergeCell ref="R75:S75"/>
+    <mergeCell ref="V75:W75"/>
+    <mergeCell ref="Z75:AA75"/>
+    <mergeCell ref="AD75:AE75"/>
+    <mergeCell ref="N64:P64"/>
+    <mergeCell ref="N70:P70"/>
+    <mergeCell ref="AH70:AJ70"/>
+    <mergeCell ref="AD70:AF70"/>
+    <mergeCell ref="Z69:AB69"/>
+    <mergeCell ref="Z70:AB70"/>
+    <mergeCell ref="V71:X71"/>
+    <mergeCell ref="AD63:AF63"/>
+    <mergeCell ref="N78:P78"/>
+    <mergeCell ref="Z78:AB78"/>
+    <mergeCell ref="N79:P79"/>
+    <mergeCell ref="R79:T79"/>
+    <mergeCell ref="V79:X79"/>
+    <mergeCell ref="Z79:AB79"/>
+    <mergeCell ref="N81:O81"/>
+    <mergeCell ref="R81:S81"/>
+    <mergeCell ref="V81:W81"/>
+    <mergeCell ref="AH88:AJ88"/>
+    <mergeCell ref="AH89:AJ89"/>
+    <mergeCell ref="AD85:AF85"/>
+    <mergeCell ref="AH85:AJ85"/>
+    <mergeCell ref="AL85:AN85"/>
+    <mergeCell ref="AH75:AI75"/>
+    <mergeCell ref="V89:X89"/>
+    <mergeCell ref="R89:T89"/>
+    <mergeCell ref="R84:T84"/>
+    <mergeCell ref="R85:T85"/>
+    <mergeCell ref="V85:X85"/>
+    <mergeCell ref="Z76:AB76"/>
+    <mergeCell ref="Z77:AB77"/>
+    <mergeCell ref="V76:X76"/>
+    <mergeCell ref="AH77:AJ77"/>
+    <mergeCell ref="AD78:AF78"/>
+    <mergeCell ref="V82:X82"/>
+    <mergeCell ref="R88:T88"/>
+    <mergeCell ref="V77:X77"/>
+    <mergeCell ref="V78:X78"/>
+    <mergeCell ref="R78:T78"/>
+    <mergeCell ref="V84:X84"/>
+    <mergeCell ref="R82:T82"/>
+    <mergeCell ref="V83:X83"/>
+    <mergeCell ref="R83:T83"/>
+    <mergeCell ref="AD82:AF82"/>
+    <mergeCell ref="AH83:AJ83"/>
+    <mergeCell ref="AD84:AF84"/>
+    <mergeCell ref="AH84:AJ84"/>
+    <mergeCell ref="AD83:AF83"/>
+    <mergeCell ref="AH94:AJ94"/>
+    <mergeCell ref="AL100:AN100"/>
+    <mergeCell ref="AD97:AF97"/>
+    <mergeCell ref="AH97:AJ97"/>
+    <mergeCell ref="AL97:AN97"/>
+    <mergeCell ref="AL77:AN77"/>
+    <mergeCell ref="AL78:AN78"/>
+    <mergeCell ref="AD77:AF77"/>
+    <mergeCell ref="AD79:AF79"/>
+    <mergeCell ref="AH79:AJ79"/>
+    <mergeCell ref="AL79:AN79"/>
+    <mergeCell ref="AD81:AE81"/>
+    <mergeCell ref="AH81:AI81"/>
+    <mergeCell ref="AL81:AM81"/>
+    <mergeCell ref="AH82:AJ82"/>
+    <mergeCell ref="AH78:AJ78"/>
+    <mergeCell ref="AL88:AN88"/>
+    <mergeCell ref="AL89:AN89"/>
+    <mergeCell ref="AL83:AN83"/>
+    <mergeCell ref="AL84:AN84"/>
+    <mergeCell ref="AD88:AF88"/>
+    <mergeCell ref="AD89:AF89"/>
+    <mergeCell ref="AH87:AI87"/>
+    <mergeCell ref="AL87:AM87"/>
+    <mergeCell ref="AD39:AF39"/>
+    <mergeCell ref="AD40:AF40"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="AL82:AN82"/>
+    <mergeCell ref="AL102:AN102"/>
+    <mergeCell ref="AL101:AN101"/>
+    <mergeCell ref="AL96:AN96"/>
+    <mergeCell ref="AD102:AF102"/>
+    <mergeCell ref="AH102:AJ102"/>
+    <mergeCell ref="AL90:AN90"/>
+    <mergeCell ref="AL95:AN95"/>
+    <mergeCell ref="AD101:AF101"/>
+    <mergeCell ref="AH101:AJ101"/>
+    <mergeCell ref="AH100:AJ100"/>
+    <mergeCell ref="AL94:AN94"/>
+    <mergeCell ref="AD100:AF100"/>
+    <mergeCell ref="AD96:AF96"/>
+    <mergeCell ref="AD94:AF94"/>
+    <mergeCell ref="AD95:AF95"/>
+    <mergeCell ref="AH96:AJ96"/>
+    <mergeCell ref="AD90:AF90"/>
+    <mergeCell ref="AH95:AJ95"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="AH90:AJ90"/>
+    <mergeCell ref="AD42:AF42"/>
+    <mergeCell ref="AD48:AF48"/>
+    <mergeCell ref="Z9:AB9"/>
+    <mergeCell ref="R10:T10"/>
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="AD21:AE21"/>
+    <mergeCell ref="AD49:AF49"/>
+    <mergeCell ref="AD43:AF43"/>
+    <mergeCell ref="AD45:AE45"/>
+    <mergeCell ref="R48:T48"/>
+    <mergeCell ref="Z42:AB42"/>
+    <mergeCell ref="Z43:AB43"/>
+    <mergeCell ref="N36:AB37"/>
+    <mergeCell ref="Z48:AB48"/>
+    <mergeCell ref="Z45:AA45"/>
+    <mergeCell ref="Z46:AB46"/>
+    <mergeCell ref="AD38:AE38"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="R9:T9"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="V1:X1"/>
+    <mergeCell ref="V14:X14"/>
+    <mergeCell ref="R15:T15"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="B4:L5"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="V2:X2"/>
+    <mergeCell ref="N4:AB5"/>
+    <mergeCell ref="V90:X90"/>
+    <mergeCell ref="V88:X88"/>
+    <mergeCell ref="R90:T90"/>
+    <mergeCell ref="AL1:AN1"/>
+    <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="AD2:AF2"/>
+    <mergeCell ref="AH2:AJ2"/>
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="AH8:AJ8"/>
+    <mergeCell ref="AL6:AM6"/>
+    <mergeCell ref="AD1:AF1"/>
+    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="AL7:AM7"/>
+    <mergeCell ref="AD8:AF8"/>
+    <mergeCell ref="Z8:AB8"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AH7:AI7"/>
+    <mergeCell ref="AD7:AE7"/>
+    <mergeCell ref="Z7:AA7"/>
+    <mergeCell ref="AL8:AN8"/>
+    <mergeCell ref="AD4:AN5"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="AD6:AE6"/>
+    <mergeCell ref="AH31:AI31"/>
+    <mergeCell ref="AD31:AE31"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="Z21:AA21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="R22:T22"/>
+    <mergeCell ref="V22:X22"/>
+    <mergeCell ref="Z22:AB22"/>
+    <mergeCell ref="AD22:AF22"/>
+    <mergeCell ref="AH22:AJ22"/>
+    <mergeCell ref="AD29:AE29"/>
+    <mergeCell ref="AH29:AI29"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:T23"/>
+    <mergeCell ref="V23:X23"/>
+    <mergeCell ref="V27:W27"/>
+    <mergeCell ref="AD27:AE27"/>
+    <mergeCell ref="V31:W31"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="AL9:AN9"/>
+    <mergeCell ref="AD9:AF9"/>
+    <mergeCell ref="AH16:AJ16"/>
+    <mergeCell ref="AL10:AN10"/>
+    <mergeCell ref="AL14:AN14"/>
+    <mergeCell ref="AL16:AN16"/>
+    <mergeCell ref="Z15:AB15"/>
+    <mergeCell ref="AD15:AF15"/>
+    <mergeCell ref="Z13:AA13"/>
+    <mergeCell ref="AL15:AN15"/>
+    <mergeCell ref="AL12:AM12"/>
+    <mergeCell ref="AD16:AF16"/>
+    <mergeCell ref="Z10:AB10"/>
+    <mergeCell ref="AH14:AJ14"/>
+    <mergeCell ref="Z14:AB14"/>
+    <mergeCell ref="AD14:AF14"/>
+    <mergeCell ref="AD13:AE13"/>
+    <mergeCell ref="AH10:AJ10"/>
+    <mergeCell ref="AH15:AJ15"/>
+    <mergeCell ref="AD10:AF10"/>
+    <mergeCell ref="AD12:AE12"/>
+    <mergeCell ref="AH12:AI12"/>
+    <mergeCell ref="Z12:AA12"/>
+    <mergeCell ref="Z16:AB16"/>
+    <mergeCell ref="AH9:AJ9"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="AH21:AI21"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="Z20:AA20"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="V15:X15"/>
+    <mergeCell ref="V16:X16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="V13:W13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="J105:K105"/>
+    <mergeCell ref="V41:X41"/>
+    <mergeCell ref="V40:X40"/>
+    <mergeCell ref="J106:L106"/>
+    <mergeCell ref="Z102:AB102"/>
+    <mergeCell ref="V102:X102"/>
+    <mergeCell ref="Z55:AB55"/>
+    <mergeCell ref="J75:K75"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="J69:L69"/>
+    <mergeCell ref="N62:P62"/>
+    <mergeCell ref="R62:T62"/>
+    <mergeCell ref="R71:T71"/>
+    <mergeCell ref="R76:T76"/>
+    <mergeCell ref="R63:T63"/>
+    <mergeCell ref="F101:H101"/>
+    <mergeCell ref="R94:T94"/>
+    <mergeCell ref="Z88:AB88"/>
+    <mergeCell ref="J94:L94"/>
+    <mergeCell ref="J95:L95"/>
+    <mergeCell ref="V94:X94"/>
+    <mergeCell ref="V96:X96"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="N18:AB19"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="R14:T14"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="J101:L101"/>
+    <mergeCell ref="J118:L118"/>
+    <mergeCell ref="B124:D124"/>
+    <mergeCell ref="F108:H108"/>
+    <mergeCell ref="B133:D133"/>
+    <mergeCell ref="F133:H133"/>
+    <mergeCell ref="J133:L133"/>
+    <mergeCell ref="B127:D127"/>
+    <mergeCell ref="F127:H127"/>
+    <mergeCell ref="J127:L127"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="F129:G129"/>
+    <mergeCell ref="J129:K129"/>
+    <mergeCell ref="B130:D130"/>
+    <mergeCell ref="F130:H130"/>
+    <mergeCell ref="J130:L130"/>
+    <mergeCell ref="B132:D132"/>
+    <mergeCell ref="F132:H132"/>
+    <mergeCell ref="J132:L132"/>
+    <mergeCell ref="B131:D131"/>
+    <mergeCell ref="F131:H131"/>
+    <mergeCell ref="J131:L131"/>
+    <mergeCell ref="J120:L120"/>
+    <mergeCell ref="B101:D101"/>
+    <mergeCell ref="B126:D126"/>
+    <mergeCell ref="F126:H126"/>
+    <mergeCell ref="J126:L126"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="J117:K117"/>
+    <mergeCell ref="J108:L108"/>
+    <mergeCell ref="F121:H121"/>
+    <mergeCell ref="J123:K123"/>
+    <mergeCell ref="F112:H112"/>
+    <mergeCell ref="B125:D125"/>
+    <mergeCell ref="F125:H125"/>
+    <mergeCell ref="J121:L121"/>
+    <mergeCell ref="J125:L125"/>
+    <mergeCell ref="B118:D118"/>
+    <mergeCell ref="F118:H118"/>
+    <mergeCell ref="B109:D109"/>
+    <mergeCell ref="F109:H109"/>
+    <mergeCell ref="F124:H124"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="F111:G111"/>
+    <mergeCell ref="J124:L124"/>
+    <mergeCell ref="F119:H119"/>
+    <mergeCell ref="J119:L119"/>
+    <mergeCell ref="J109:L109"/>
+    <mergeCell ref="B120:D120"/>
+    <mergeCell ref="B121:D121"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="F123:G123"/>
+    <mergeCell ref="B119:D119"/>
+    <mergeCell ref="B113:D113"/>
+    <mergeCell ref="F113:H113"/>
+    <mergeCell ref="J113:L113"/>
+    <mergeCell ref="B114:D114"/>
+    <mergeCell ref="F114:H114"/>
+    <mergeCell ref="J114:L114"/>
+    <mergeCell ref="B115:D115"/>
+    <mergeCell ref="F115:H115"/>
+    <mergeCell ref="J115:L115"/>
+    <mergeCell ref="B112:D112"/>
+    <mergeCell ref="F120:H120"/>
+    <mergeCell ref="B108:D108"/>
+    <mergeCell ref="J102:L102"/>
+    <mergeCell ref="J112:L112"/>
+    <mergeCell ref="J111:K111"/>
+    <mergeCell ref="B106:D106"/>
+    <mergeCell ref="B107:D107"/>
+    <mergeCell ref="F106:H106"/>
+    <mergeCell ref="F105:G105"/>
+    <mergeCell ref="N102:P102"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="F102:H102"/>
+    <mergeCell ref="F107:H107"/>
+    <mergeCell ref="J107:L107"/>
+    <mergeCell ref="R102:T102"/>
+    <mergeCell ref="R100:T100"/>
+    <mergeCell ref="V100:X100"/>
+    <mergeCell ref="R101:T101"/>
+    <mergeCell ref="N100:P100"/>
+    <mergeCell ref="Z100:AB100"/>
+    <mergeCell ref="N94:P94"/>
+    <mergeCell ref="R95:T95"/>
+    <mergeCell ref="N96:P96"/>
+    <mergeCell ref="R99:S99"/>
+    <mergeCell ref="V99:W99"/>
+    <mergeCell ref="Z99:AA99"/>
+    <mergeCell ref="V95:X95"/>
+    <mergeCell ref="Z96:AB96"/>
+    <mergeCell ref="R96:T96"/>
+    <mergeCell ref="N101:P101"/>
+    <mergeCell ref="N95:P95"/>
+    <mergeCell ref="V101:X101"/>
+    <mergeCell ref="Z101:AB101"/>
+    <mergeCell ref="Z94:AB94"/>
+    <mergeCell ref="Z95:AB95"/>
+    <mergeCell ref="N91:P91"/>
+    <mergeCell ref="N97:P97"/>
+    <mergeCell ref="J96:L96"/>
+    <mergeCell ref="J90:L90"/>
+    <mergeCell ref="N99:O99"/>
+    <mergeCell ref="N88:P88"/>
+    <mergeCell ref="N83:P83"/>
+    <mergeCell ref="N84:P84"/>
+    <mergeCell ref="N90:P90"/>
+    <mergeCell ref="J89:L89"/>
+    <mergeCell ref="J83:L83"/>
+    <mergeCell ref="J84:L84"/>
+    <mergeCell ref="N89:P89"/>
+    <mergeCell ref="N87:O87"/>
+    <mergeCell ref="N93:O93"/>
+    <mergeCell ref="N85:P85"/>
+    <mergeCell ref="J85:L85"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="F54:H54"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="J100:L100"/>
+    <mergeCell ref="J88:L88"/>
+    <mergeCell ref="J77:L77"/>
+    <mergeCell ref="J76:L76"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="B96:D96"/>
+    <mergeCell ref="F96:H96"/>
+    <mergeCell ref="B100:D100"/>
+    <mergeCell ref="F100:H100"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="F88:H88"/>
+    <mergeCell ref="B89:D89"/>
+    <mergeCell ref="F83:H83"/>
+    <mergeCell ref="F84:H84"/>
+    <mergeCell ref="F77:H77"/>
+    <mergeCell ref="J53:L53"/>
+    <mergeCell ref="J54:L54"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="J78:L78"/>
+    <mergeCell ref="J81:K81"/>
+    <mergeCell ref="J82:L82"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B95:D95"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="J70:L70"/>
+    <mergeCell ref="B71:D71"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="F70:H70"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="F76:H76"/>
+    <mergeCell ref="F90:H90"/>
+    <mergeCell ref="F95:H95"/>
+    <mergeCell ref="F89:H89"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="F94:H94"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="B85:D85"/>
+    <mergeCell ref="F85:H85"/>
+    <mergeCell ref="F75:G75"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="F82:H82"/>
+    <mergeCell ref="AL50:AN50"/>
+    <mergeCell ref="AL52:AM52"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="F62:H62"/>
+    <mergeCell ref="F61:H61"/>
+    <mergeCell ref="J64:L64"/>
+    <mergeCell ref="F69:H69"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="J66:K66"/>
+    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="F67:H67"/>
+    <mergeCell ref="J67:L67"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="F68:H68"/>
+    <mergeCell ref="J68:L68"/>
+    <mergeCell ref="F63:H63"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="AD56:AF56"/>
+    <mergeCell ref="AH57:AJ57"/>
+    <mergeCell ref="AH59:AI59"/>
+    <mergeCell ref="AH56:AJ56"/>
+    <mergeCell ref="AH53:AJ53"/>
+    <mergeCell ref="AH47:AJ47"/>
+    <mergeCell ref="AD59:AE59"/>
+    <mergeCell ref="AD53:AF53"/>
+    <mergeCell ref="AD50:AF50"/>
+    <mergeCell ref="AD52:AE52"/>
+    <mergeCell ref="AD57:AF57"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R41:T41"/>
+    <mergeCell ref="R40:T40"/>
+    <mergeCell ref="R43:T43"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="R39:T39"/>
+    <mergeCell ref="V38:W38"/>
+    <mergeCell ref="V39:X39"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="V43:X43"/>
     <mergeCell ref="AL57:AN57"/>
     <mergeCell ref="AL59:AM59"/>
     <mergeCell ref="AL46:AN46"/>
@@ -7984,835 +8865,27 @@
     <mergeCell ref="F60:H60"/>
     <mergeCell ref="F57:H57"/>
     <mergeCell ref="J60:L60"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="N38:O38"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R41:T41"/>
-    <mergeCell ref="R40:T40"/>
-    <mergeCell ref="R43:T43"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="R39:T39"/>
-    <mergeCell ref="V38:W38"/>
-    <mergeCell ref="V39:X39"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="V43:X43"/>
-    <mergeCell ref="AD56:AF56"/>
-    <mergeCell ref="AH57:AJ57"/>
-    <mergeCell ref="AH59:AI59"/>
-    <mergeCell ref="AH56:AJ56"/>
-    <mergeCell ref="AH53:AJ53"/>
-    <mergeCell ref="AH47:AJ47"/>
-    <mergeCell ref="AD59:AE59"/>
-    <mergeCell ref="AD53:AF53"/>
-    <mergeCell ref="AD50:AF50"/>
-    <mergeCell ref="AD52:AE52"/>
-    <mergeCell ref="AD57:AF57"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="F82:H82"/>
-    <mergeCell ref="AL50:AN50"/>
-    <mergeCell ref="AL52:AM52"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="F62:H62"/>
-    <mergeCell ref="F61:H61"/>
-    <mergeCell ref="J64:L64"/>
-    <mergeCell ref="F69:H69"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="J63:L63"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="J66:K66"/>
-    <mergeCell ref="B67:D67"/>
-    <mergeCell ref="F67:H67"/>
-    <mergeCell ref="J67:L67"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="F68:H68"/>
-    <mergeCell ref="J68:L68"/>
-    <mergeCell ref="F63:H63"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="J78:L78"/>
-    <mergeCell ref="J81:K81"/>
-    <mergeCell ref="J82:L82"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B95:D95"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="J70:L70"/>
-    <mergeCell ref="B71:D71"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="F70:H70"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="F76:H76"/>
-    <mergeCell ref="F90:H90"/>
-    <mergeCell ref="F95:H95"/>
-    <mergeCell ref="F89:H89"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="F94:H94"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B79:D79"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="F53:H53"/>
-    <mergeCell ref="F54:H54"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="J100:L100"/>
-    <mergeCell ref="J88:L88"/>
-    <mergeCell ref="J77:L77"/>
-    <mergeCell ref="J76:L76"/>
-    <mergeCell ref="J55:L55"/>
-    <mergeCell ref="B96:D96"/>
-    <mergeCell ref="F96:H96"/>
-    <mergeCell ref="B100:D100"/>
-    <mergeCell ref="F100:H100"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="F88:H88"/>
-    <mergeCell ref="B89:D89"/>
-    <mergeCell ref="N91:P91"/>
-    <mergeCell ref="N97:P97"/>
-    <mergeCell ref="J96:L96"/>
-    <mergeCell ref="J90:L90"/>
-    <mergeCell ref="N99:O99"/>
-    <mergeCell ref="N88:P88"/>
-    <mergeCell ref="N83:P83"/>
-    <mergeCell ref="N84:P84"/>
-    <mergeCell ref="N90:P90"/>
-    <mergeCell ref="J89:L89"/>
-    <mergeCell ref="J83:L83"/>
-    <mergeCell ref="J84:L84"/>
-    <mergeCell ref="N89:P89"/>
-    <mergeCell ref="N87:O87"/>
-    <mergeCell ref="N93:O93"/>
-    <mergeCell ref="R102:T102"/>
-    <mergeCell ref="R100:T100"/>
-    <mergeCell ref="V100:X100"/>
-    <mergeCell ref="R101:T101"/>
-    <mergeCell ref="N100:P100"/>
-    <mergeCell ref="Z100:AB100"/>
-    <mergeCell ref="N94:P94"/>
-    <mergeCell ref="R95:T95"/>
-    <mergeCell ref="N96:P96"/>
-    <mergeCell ref="R99:S99"/>
-    <mergeCell ref="V99:W99"/>
-    <mergeCell ref="Z99:AA99"/>
-    <mergeCell ref="B108:D108"/>
-    <mergeCell ref="J102:L102"/>
-    <mergeCell ref="J112:L112"/>
-    <mergeCell ref="J111:K111"/>
-    <mergeCell ref="B106:D106"/>
-    <mergeCell ref="B107:D107"/>
-    <mergeCell ref="F106:H106"/>
-    <mergeCell ref="F105:G105"/>
-    <mergeCell ref="N102:P102"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="F102:H102"/>
-    <mergeCell ref="F124:H124"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="F111:G111"/>
-    <mergeCell ref="J124:L124"/>
-    <mergeCell ref="F119:H119"/>
-    <mergeCell ref="J119:L119"/>
-    <mergeCell ref="J109:L109"/>
-    <mergeCell ref="B120:D120"/>
-    <mergeCell ref="B121:D121"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="F123:G123"/>
-    <mergeCell ref="B119:D119"/>
-    <mergeCell ref="B113:D113"/>
-    <mergeCell ref="F113:H113"/>
-    <mergeCell ref="J113:L113"/>
-    <mergeCell ref="B114:D114"/>
-    <mergeCell ref="F114:H114"/>
-    <mergeCell ref="J114:L114"/>
-    <mergeCell ref="B115:D115"/>
-    <mergeCell ref="F115:H115"/>
-    <mergeCell ref="J115:L115"/>
-    <mergeCell ref="B112:D112"/>
-    <mergeCell ref="F120:H120"/>
-    <mergeCell ref="B126:D126"/>
-    <mergeCell ref="F126:H126"/>
-    <mergeCell ref="J126:L126"/>
-    <mergeCell ref="F117:G117"/>
-    <mergeCell ref="J117:K117"/>
-    <mergeCell ref="J108:L108"/>
-    <mergeCell ref="F121:H121"/>
-    <mergeCell ref="J123:K123"/>
-    <mergeCell ref="F112:H112"/>
-    <mergeCell ref="B125:D125"/>
-    <mergeCell ref="F125:H125"/>
-    <mergeCell ref="J121:L121"/>
-    <mergeCell ref="J125:L125"/>
-    <mergeCell ref="F107:H107"/>
-    <mergeCell ref="B118:D118"/>
-    <mergeCell ref="F118:H118"/>
-    <mergeCell ref="B109:D109"/>
-    <mergeCell ref="F109:H109"/>
-    <mergeCell ref="J107:L107"/>
-    <mergeCell ref="J101:L101"/>
-    <mergeCell ref="J118:L118"/>
-    <mergeCell ref="B124:D124"/>
-    <mergeCell ref="F108:H108"/>
-    <mergeCell ref="B133:D133"/>
-    <mergeCell ref="F133:H133"/>
-    <mergeCell ref="J133:L133"/>
-    <mergeCell ref="B127:D127"/>
-    <mergeCell ref="F127:H127"/>
-    <mergeCell ref="J127:L127"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="F129:G129"/>
-    <mergeCell ref="J129:K129"/>
-    <mergeCell ref="B130:D130"/>
-    <mergeCell ref="F130:H130"/>
-    <mergeCell ref="J130:L130"/>
-    <mergeCell ref="B132:D132"/>
-    <mergeCell ref="F132:H132"/>
-    <mergeCell ref="J132:L132"/>
-    <mergeCell ref="B131:D131"/>
-    <mergeCell ref="F131:H131"/>
-    <mergeCell ref="J131:L131"/>
-    <mergeCell ref="J120:L120"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="N18:AB19"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="R14:T14"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="F83:H83"/>
-    <mergeCell ref="F84:H84"/>
-    <mergeCell ref="F77:H77"/>
-    <mergeCell ref="J50:L50"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="J105:K105"/>
-    <mergeCell ref="V41:X41"/>
-    <mergeCell ref="V40:X40"/>
-    <mergeCell ref="J106:L106"/>
-    <mergeCell ref="Z102:AB102"/>
-    <mergeCell ref="V102:X102"/>
-    <mergeCell ref="Z55:AB55"/>
-    <mergeCell ref="AH9:AJ9"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J75:K75"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="AL9:AN9"/>
-    <mergeCell ref="AD9:AF9"/>
-    <mergeCell ref="AH16:AJ16"/>
-    <mergeCell ref="AL10:AN10"/>
-    <mergeCell ref="AL14:AN14"/>
-    <mergeCell ref="AL16:AN16"/>
-    <mergeCell ref="Z15:AB15"/>
-    <mergeCell ref="AD15:AF15"/>
-    <mergeCell ref="Z13:AA13"/>
-    <mergeCell ref="AL15:AN15"/>
-    <mergeCell ref="AL12:AM12"/>
-    <mergeCell ref="AD16:AF16"/>
-    <mergeCell ref="Z10:AB10"/>
-    <mergeCell ref="AH14:AJ14"/>
-    <mergeCell ref="Z14:AB14"/>
-    <mergeCell ref="AD14:AF14"/>
-    <mergeCell ref="AD13:AE13"/>
-    <mergeCell ref="AH10:AJ10"/>
-    <mergeCell ref="AH15:AJ15"/>
-    <mergeCell ref="AD10:AF10"/>
-    <mergeCell ref="AD12:AE12"/>
-    <mergeCell ref="AH12:AI12"/>
-    <mergeCell ref="J69:L69"/>
-    <mergeCell ref="N62:P62"/>
-    <mergeCell ref="R62:T62"/>
-    <mergeCell ref="R71:T71"/>
-    <mergeCell ref="R76:T76"/>
-    <mergeCell ref="R63:T63"/>
-    <mergeCell ref="AH21:AI21"/>
-    <mergeCell ref="AH31:AI31"/>
-    <mergeCell ref="AD31:AE31"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="Z21:AA21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="R22:T22"/>
-    <mergeCell ref="V22:X22"/>
-    <mergeCell ref="Z22:AB22"/>
-    <mergeCell ref="AD22:AF22"/>
-    <mergeCell ref="AH22:AJ22"/>
-    <mergeCell ref="AD29:AE29"/>
-    <mergeCell ref="AH29:AI29"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:T23"/>
-    <mergeCell ref="V23:X23"/>
-    <mergeCell ref="V27:W27"/>
-    <mergeCell ref="AD27:AE27"/>
-    <mergeCell ref="F101:H101"/>
-    <mergeCell ref="R94:T94"/>
-    <mergeCell ref="Z88:AB88"/>
-    <mergeCell ref="J94:L94"/>
-    <mergeCell ref="J95:L95"/>
-    <mergeCell ref="V94:X94"/>
-    <mergeCell ref="V96:X96"/>
-    <mergeCell ref="V95:X95"/>
-    <mergeCell ref="Z96:AB96"/>
-    <mergeCell ref="R96:T96"/>
-    <mergeCell ref="B101:D101"/>
-    <mergeCell ref="N101:P101"/>
-    <mergeCell ref="N95:P95"/>
-    <mergeCell ref="V101:X101"/>
-    <mergeCell ref="Z101:AB101"/>
-    <mergeCell ref="Z94:AB94"/>
-    <mergeCell ref="Z95:AB95"/>
-    <mergeCell ref="V90:X90"/>
-    <mergeCell ref="V88:X88"/>
-    <mergeCell ref="R90:T90"/>
-    <mergeCell ref="AL1:AN1"/>
-    <mergeCell ref="Z2:AB2"/>
-    <mergeCell ref="AD2:AF2"/>
-    <mergeCell ref="AH2:AJ2"/>
-    <mergeCell ref="AL2:AN2"/>
-    <mergeCell ref="AH8:AJ8"/>
-    <mergeCell ref="AL6:AM6"/>
-    <mergeCell ref="AD1:AF1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="AL7:AM7"/>
-    <mergeCell ref="AD8:AF8"/>
-    <mergeCell ref="Z8:AB8"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AH7:AI7"/>
-    <mergeCell ref="AD7:AE7"/>
-    <mergeCell ref="Z7:AA7"/>
-    <mergeCell ref="AL8:AN8"/>
-    <mergeCell ref="AD4:AN5"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="AD6:AE6"/>
-    <mergeCell ref="R1:T1"/>
-    <mergeCell ref="V1:X1"/>
-    <mergeCell ref="V14:X14"/>
-    <mergeCell ref="R15:T15"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="B4:L5"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="V2:X2"/>
-    <mergeCell ref="N4:AB5"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="R9:T9"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="V8:X8"/>
-    <mergeCell ref="V9:X9"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="Z12:AA12"/>
-    <mergeCell ref="V31:W31"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="Z20:AA20"/>
-    <mergeCell ref="J15:L15"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="V15:X15"/>
-    <mergeCell ref="V16:X16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="Z16:AB16"/>
-    <mergeCell ref="V13:W13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="AH90:AJ90"/>
-    <mergeCell ref="AD42:AF42"/>
-    <mergeCell ref="AD48:AF48"/>
-    <mergeCell ref="Z9:AB9"/>
-    <mergeCell ref="R10:T10"/>
-    <mergeCell ref="V10:X10"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="AD21:AE21"/>
-    <mergeCell ref="AD49:AF49"/>
-    <mergeCell ref="AD43:AF43"/>
-    <mergeCell ref="AD45:AE45"/>
-    <mergeCell ref="R48:T48"/>
-    <mergeCell ref="Z42:AB42"/>
-    <mergeCell ref="Z43:AB43"/>
-    <mergeCell ref="N36:AB37"/>
-    <mergeCell ref="Z48:AB48"/>
-    <mergeCell ref="Z45:AA45"/>
-    <mergeCell ref="Z46:AB46"/>
-    <mergeCell ref="AD38:AE38"/>
-    <mergeCell ref="AD39:AF39"/>
-    <mergeCell ref="AD40:AF40"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="AL82:AN82"/>
-    <mergeCell ref="AL102:AN102"/>
-    <mergeCell ref="AL101:AN101"/>
-    <mergeCell ref="AL96:AN96"/>
-    <mergeCell ref="AD102:AF102"/>
-    <mergeCell ref="AH102:AJ102"/>
-    <mergeCell ref="AL90:AN90"/>
-    <mergeCell ref="AL95:AN95"/>
-    <mergeCell ref="AD101:AF101"/>
-    <mergeCell ref="AH101:AJ101"/>
-    <mergeCell ref="AH100:AJ100"/>
-    <mergeCell ref="AL94:AN94"/>
-    <mergeCell ref="AD100:AF100"/>
-    <mergeCell ref="AD96:AF96"/>
-    <mergeCell ref="AD94:AF94"/>
-    <mergeCell ref="AD95:AF95"/>
-    <mergeCell ref="AH96:AJ96"/>
-    <mergeCell ref="AD90:AF90"/>
-    <mergeCell ref="AH95:AJ95"/>
-    <mergeCell ref="AH94:AJ94"/>
-    <mergeCell ref="AL100:AN100"/>
-    <mergeCell ref="AD97:AF97"/>
-    <mergeCell ref="AH97:AJ97"/>
-    <mergeCell ref="AL97:AN97"/>
-    <mergeCell ref="AL77:AN77"/>
-    <mergeCell ref="AL78:AN78"/>
-    <mergeCell ref="AD77:AF77"/>
-    <mergeCell ref="AD79:AF79"/>
-    <mergeCell ref="AH79:AJ79"/>
-    <mergeCell ref="AL79:AN79"/>
-    <mergeCell ref="AD81:AE81"/>
-    <mergeCell ref="AH81:AI81"/>
-    <mergeCell ref="AL81:AM81"/>
-    <mergeCell ref="AH82:AJ82"/>
-    <mergeCell ref="AH78:AJ78"/>
-    <mergeCell ref="V78:X78"/>
-    <mergeCell ref="R78:T78"/>
-    <mergeCell ref="V84:X84"/>
-    <mergeCell ref="R82:T82"/>
-    <mergeCell ref="V83:X83"/>
-    <mergeCell ref="R83:T83"/>
-    <mergeCell ref="AD82:AF82"/>
-    <mergeCell ref="AH83:AJ83"/>
-    <mergeCell ref="AD84:AF84"/>
-    <mergeCell ref="AH84:AJ84"/>
-    <mergeCell ref="AD83:AF83"/>
-    <mergeCell ref="AL88:AN88"/>
-    <mergeCell ref="AL89:AN89"/>
-    <mergeCell ref="AL83:AN83"/>
-    <mergeCell ref="AL84:AN84"/>
-    <mergeCell ref="AD88:AF88"/>
-    <mergeCell ref="AD89:AF89"/>
-    <mergeCell ref="AH87:AI87"/>
-    <mergeCell ref="AL87:AM87"/>
-    <mergeCell ref="AH88:AJ88"/>
-    <mergeCell ref="AH89:AJ89"/>
-    <mergeCell ref="AD85:AF85"/>
-    <mergeCell ref="AH85:AJ85"/>
-    <mergeCell ref="AL85:AN85"/>
-    <mergeCell ref="AH75:AI75"/>
-    <mergeCell ref="V89:X89"/>
-    <mergeCell ref="R89:T89"/>
-    <mergeCell ref="R84:T84"/>
-    <mergeCell ref="N85:P85"/>
-    <mergeCell ref="R85:T85"/>
-    <mergeCell ref="V85:X85"/>
-    <mergeCell ref="Z76:AB76"/>
-    <mergeCell ref="Z77:AB77"/>
-    <mergeCell ref="V76:X76"/>
-    <mergeCell ref="N78:P78"/>
-    <mergeCell ref="Z78:AB78"/>
-    <mergeCell ref="N79:P79"/>
-    <mergeCell ref="R79:T79"/>
-    <mergeCell ref="V79:X79"/>
-    <mergeCell ref="Z79:AB79"/>
-    <mergeCell ref="N81:O81"/>
-    <mergeCell ref="R81:S81"/>
-    <mergeCell ref="V81:W81"/>
-    <mergeCell ref="AH77:AJ77"/>
-    <mergeCell ref="AD78:AF78"/>
-    <mergeCell ref="V82:X82"/>
-    <mergeCell ref="R88:T88"/>
-    <mergeCell ref="N82:P82"/>
-    <mergeCell ref="AH76:AJ76"/>
-    <mergeCell ref="AL76:AN76"/>
-    <mergeCell ref="AD76:AF76"/>
-    <mergeCell ref="Z81:AA81"/>
-    <mergeCell ref="AL62:AN62"/>
-    <mergeCell ref="AL63:AN63"/>
-    <mergeCell ref="AL71:AN71"/>
-    <mergeCell ref="AL70:AN70"/>
-    <mergeCell ref="AL69:AN69"/>
-    <mergeCell ref="N73:AB74"/>
-    <mergeCell ref="N75:O75"/>
-    <mergeCell ref="R75:S75"/>
-    <mergeCell ref="V75:W75"/>
-    <mergeCell ref="Z75:AA75"/>
-    <mergeCell ref="AD75:AE75"/>
-    <mergeCell ref="N64:P64"/>
-    <mergeCell ref="N70:P70"/>
-    <mergeCell ref="AH70:AJ70"/>
-    <mergeCell ref="AD70:AF70"/>
-    <mergeCell ref="Z69:AB69"/>
-    <mergeCell ref="Z70:AB70"/>
-    <mergeCell ref="V71:X71"/>
-    <mergeCell ref="AD63:AF63"/>
-    <mergeCell ref="AH64:AJ64"/>
-    <mergeCell ref="AD67:AF67"/>
-    <mergeCell ref="AL20:AM20"/>
-    <mergeCell ref="AL27:AM27"/>
-    <mergeCell ref="AL21:AM21"/>
-    <mergeCell ref="AH27:AI27"/>
-    <mergeCell ref="AD20:AE20"/>
-    <mergeCell ref="AH20:AI20"/>
-    <mergeCell ref="Z68:AB68"/>
-    <mergeCell ref="AD68:AF68"/>
-    <mergeCell ref="AH68:AJ68"/>
-    <mergeCell ref="AL68:AN68"/>
-    <mergeCell ref="Z63:AB63"/>
-    <mergeCell ref="AL60:AN60"/>
-    <mergeCell ref="AL64:AN64"/>
-    <mergeCell ref="AL61:AN61"/>
-    <mergeCell ref="Z56:AB56"/>
-    <mergeCell ref="AL22:AN22"/>
-    <mergeCell ref="Z23:AB23"/>
-    <mergeCell ref="AD23:AF23"/>
-    <mergeCell ref="AH23:AJ23"/>
-    <mergeCell ref="AL23:AN23"/>
-    <mergeCell ref="AD28:AE28"/>
-    <mergeCell ref="AH28:AI28"/>
-    <mergeCell ref="AL28:AM28"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="N61:P61"/>
-    <mergeCell ref="AD66:AE66"/>
-    <mergeCell ref="AH66:AI66"/>
-    <mergeCell ref="R61:T61"/>
-    <mergeCell ref="V61:X61"/>
-    <mergeCell ref="Z61:AB61"/>
-    <mergeCell ref="Z59:AA59"/>
-    <mergeCell ref="AH63:AJ63"/>
-    <mergeCell ref="AH62:AJ62"/>
-    <mergeCell ref="AD62:AF62"/>
-    <mergeCell ref="AD60:AF60"/>
-    <mergeCell ref="AH60:AJ60"/>
-    <mergeCell ref="V62:X62"/>
-    <mergeCell ref="V63:X63"/>
-    <mergeCell ref="Z64:AB64"/>
-    <mergeCell ref="R60:T60"/>
-    <mergeCell ref="V60:X60"/>
-    <mergeCell ref="Z60:AB60"/>
-    <mergeCell ref="V64:X64"/>
-    <mergeCell ref="R64:T64"/>
-    <mergeCell ref="N63:P63"/>
-    <mergeCell ref="N66:O66"/>
-    <mergeCell ref="N60:P60"/>
-    <mergeCell ref="V33:W33"/>
-    <mergeCell ref="Z33:AA33"/>
-    <mergeCell ref="N32:O32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="V32:W32"/>
-    <mergeCell ref="Z32:AA32"/>
-    <mergeCell ref="N34:O34"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="N29:O29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="V29:W29"/>
-    <mergeCell ref="Z29:AA29"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="Z27:AA27"/>
-    <mergeCell ref="N30:O30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="V30:W30"/>
-    <mergeCell ref="Z31:AA31"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="J46:L46"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="J53:L53"/>
-    <mergeCell ref="V50:X50"/>
-    <mergeCell ref="Z53:AA53"/>
-    <mergeCell ref="R49:T49"/>
-    <mergeCell ref="R47:T47"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="J54:L54"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="N45:O45"/>
-    <mergeCell ref="J49:L49"/>
-    <mergeCell ref="J47:L47"/>
-    <mergeCell ref="Z54:AB54"/>
-    <mergeCell ref="Z50:AB50"/>
-    <mergeCell ref="V45:W45"/>
-    <mergeCell ref="V46:X46"/>
-    <mergeCell ref="V47:X47"/>
-    <mergeCell ref="Z49:AB49"/>
-    <mergeCell ref="V49:X49"/>
-    <mergeCell ref="V48:X48"/>
-    <mergeCell ref="AH34:AI34"/>
-    <mergeCell ref="AL34:AM34"/>
-    <mergeCell ref="N55:P55"/>
-    <mergeCell ref="R56:T56"/>
-    <mergeCell ref="N59:O59"/>
-    <mergeCell ref="N56:P56"/>
-    <mergeCell ref="R54:T54"/>
-    <mergeCell ref="V54:X54"/>
-    <mergeCell ref="V53:W53"/>
-    <mergeCell ref="N54:P54"/>
-    <mergeCell ref="N53:P53"/>
-    <mergeCell ref="R55:T55"/>
-    <mergeCell ref="R59:S59"/>
-    <mergeCell ref="V59:W59"/>
-    <mergeCell ref="R53:T53"/>
-    <mergeCell ref="V56:X56"/>
-    <mergeCell ref="N57:P57"/>
-    <mergeCell ref="V55:X55"/>
-    <mergeCell ref="V57:X57"/>
-    <mergeCell ref="R57:T57"/>
-    <mergeCell ref="V42:X42"/>
-    <mergeCell ref="AH52:AI52"/>
-    <mergeCell ref="AH54:AJ54"/>
-    <mergeCell ref="AH55:AJ55"/>
-    <mergeCell ref="R42:T42"/>
-    <mergeCell ref="AD46:AF46"/>
-    <mergeCell ref="AD47:AF47"/>
-    <mergeCell ref="AH40:AJ40"/>
-    <mergeCell ref="AH46:AJ46"/>
-    <mergeCell ref="AH45:AI45"/>
-    <mergeCell ref="AH38:AI38"/>
-    <mergeCell ref="AH39:AJ39"/>
-    <mergeCell ref="AL38:AM38"/>
-    <mergeCell ref="AL39:AN39"/>
-    <mergeCell ref="AH41:AJ41"/>
-    <mergeCell ref="AD41:AF41"/>
-    <mergeCell ref="AL43:AN43"/>
-    <mergeCell ref="AL45:AM45"/>
-    <mergeCell ref="AL42:AN42"/>
-    <mergeCell ref="Z41:AB41"/>
-    <mergeCell ref="Z40:AB40"/>
-    <mergeCell ref="Z38:AA38"/>
-    <mergeCell ref="Z39:AB39"/>
-    <mergeCell ref="AL31:AM31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="R87:S87"/>
-    <mergeCell ref="V87:W87"/>
-    <mergeCell ref="Z87:AA87"/>
-    <mergeCell ref="AD87:AE87"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="V34:W34"/>
-    <mergeCell ref="Z34:AA34"/>
-    <mergeCell ref="AD34:AE34"/>
-    <mergeCell ref="R66:S66"/>
-    <mergeCell ref="V66:W66"/>
-    <mergeCell ref="Z66:AA66"/>
-    <mergeCell ref="R67:T67"/>
-    <mergeCell ref="V67:X67"/>
-    <mergeCell ref="Z67:AB67"/>
-    <mergeCell ref="V69:X69"/>
-    <mergeCell ref="R69:T69"/>
-    <mergeCell ref="V70:X70"/>
-    <mergeCell ref="R70:T70"/>
-    <mergeCell ref="R77:T77"/>
-    <mergeCell ref="AD33:AE33"/>
-    <mergeCell ref="AH33:AI33"/>
-    <mergeCell ref="AL33:AM33"/>
-    <mergeCell ref="V77:X77"/>
-    <mergeCell ref="N76:P76"/>
-    <mergeCell ref="N77:P77"/>
-    <mergeCell ref="R46:T46"/>
-    <mergeCell ref="Z85:AB85"/>
-    <mergeCell ref="Z89:AB89"/>
-    <mergeCell ref="Z90:AB90"/>
-    <mergeCell ref="Z83:AB83"/>
-    <mergeCell ref="Z84:AB84"/>
-    <mergeCell ref="Z82:AB82"/>
-    <mergeCell ref="V51:X51"/>
-    <mergeCell ref="Z51:AB51"/>
-    <mergeCell ref="Z62:AB62"/>
-    <mergeCell ref="N69:P69"/>
-    <mergeCell ref="N68:P68"/>
-    <mergeCell ref="R68:T68"/>
-    <mergeCell ref="V68:X68"/>
-    <mergeCell ref="N67:P67"/>
-    <mergeCell ref="N71:P71"/>
-    <mergeCell ref="AD99:AE99"/>
-    <mergeCell ref="AH99:AI99"/>
-    <mergeCell ref="AL99:AM99"/>
-    <mergeCell ref="R91:T91"/>
-    <mergeCell ref="V91:X91"/>
-    <mergeCell ref="Z91:AB91"/>
-    <mergeCell ref="AD91:AF91"/>
-    <mergeCell ref="AH91:AJ91"/>
-    <mergeCell ref="AL91:AN91"/>
-    <mergeCell ref="R97:T97"/>
-    <mergeCell ref="V97:X97"/>
-    <mergeCell ref="Z97:AB97"/>
-    <mergeCell ref="AD93:AE93"/>
-    <mergeCell ref="AH93:AI93"/>
-    <mergeCell ref="AL93:AM93"/>
-    <mergeCell ref="R93:S93"/>
-    <mergeCell ref="V93:W93"/>
-    <mergeCell ref="Z93:AA93"/>
-    <mergeCell ref="AH13:AI13"/>
-    <mergeCell ref="AL13:AM13"/>
-    <mergeCell ref="AH67:AJ67"/>
-    <mergeCell ref="AL67:AN67"/>
-    <mergeCell ref="AH48:AJ48"/>
-    <mergeCell ref="AH50:AJ50"/>
-    <mergeCell ref="AL29:AM29"/>
-    <mergeCell ref="Z30:AA30"/>
-    <mergeCell ref="AD30:AE30"/>
-    <mergeCell ref="AH30:AI30"/>
-    <mergeCell ref="AL30:AM30"/>
-    <mergeCell ref="N25:AB26"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="V28:W28"/>
-    <mergeCell ref="Z28:AA28"/>
-    <mergeCell ref="AL40:AN40"/>
-    <mergeCell ref="AL41:AN41"/>
-    <mergeCell ref="AL47:AN47"/>
-    <mergeCell ref="AL48:AN48"/>
-    <mergeCell ref="AH42:AJ42"/>
-    <mergeCell ref="AH43:AJ43"/>
-    <mergeCell ref="AH49:AJ49"/>
-    <mergeCell ref="Z47:AB47"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="J41:L41"/>
-    <mergeCell ref="J40:L40"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="AL75:AM75"/>
-    <mergeCell ref="AH71:AJ71"/>
-    <mergeCell ref="AD71:AF71"/>
-    <mergeCell ref="Z71:AB71"/>
-    <mergeCell ref="AL66:AM66"/>
-    <mergeCell ref="AD69:AF69"/>
-    <mergeCell ref="AH69:AJ69"/>
-    <mergeCell ref="AD64:AF64"/>
-    <mergeCell ref="AD61:AF61"/>
-    <mergeCell ref="AH61:AJ61"/>
-    <mergeCell ref="Z57:AB57"/>
-    <mergeCell ref="AD54:AF54"/>
-    <mergeCell ref="AD55:AF55"/>
-    <mergeCell ref="AD32:AE32"/>
-    <mergeCell ref="AH32:AI32"/>
-    <mergeCell ref="AL32:AM32"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="B85:D85"/>
-    <mergeCell ref="F85:H85"/>
-    <mergeCell ref="J85:L85"/>
-    <mergeCell ref="F75:G75"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="J39:L39"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="B97:D97"/>
+    <mergeCell ref="F97:H97"/>
+    <mergeCell ref="J97:L97"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="F99:G99"/>
+    <mergeCell ref="J99:K99"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="J87:K87"/>
+    <mergeCell ref="B91:D91"/>
+    <mergeCell ref="F91:H91"/>
+    <mergeCell ref="J91:L91"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="F93:G93"/>
+    <mergeCell ref="J93:K93"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="D29:D34 AJ29:AJ34 X29:X34 T29:T34 AB29:AB34 AF29:AF34 P29:P34 H29:H34 L29:L34 AN29:AN34">
       <formula1>$AP$68:$AP$71</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="AL41:AN43 AH69:AJ71 AL90:AN91 J48:L50 N29:O34 Z29:AA34 F55:H57 J132:L133 V78:X79 R78:T79 AD96:AF97 Z56:AB57 R69:T71 Z78:AB79 Z48:AB51 Z96:AB97 B55:D57 AH48:AJ50 V8:X10 R101:T102 AD69:AF71 J114:L115 AL78:AN79 AL69:AN71 AH41:AJ43 R8:T10 B41:D43 B108:D109 B62:D64 Z14:AB16 AD41:AF43 R14:T16 F48:H50 AL14:AN16 F62:H64 J55:L57 N78:P79 R62:T64 B8:D10 J120:L121 F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 B126:D127 AD14:AF16 B114:D115 J126:L127 N48:P50 Z101:AB102 AD22:AF23 N84:P85 AD84:AF85 R22:T23 V14:X16 V22:X23 F108:H109 Z22:AB23 AL101:AN102 AL22:AN23 V69:X71 AD90:AF91 AD55:AF57 N22:P23 N90:P91 J22:L23 J62:L64 V48:X51 N96:P97 R84:T85 V96:X97 R41:T43 AD101:AF102 N14:P16 AD62:AF64 AH90:AJ91 V84:X85 Z41:AB43 AH62:AJ64 N101:P102 Z84:AB85 V41:X43 AH78:AJ79 AL84:AN85 AH55:AJ57 V56:X57 B29:C34 J29:K34 AH96:AJ97 AH101:AJ102 AL48:AN50 V90:X91 AL96:AN97 Z8:AB10 AH84:AJ85 AL8:AN10 N62:P64 N8:P10 AD78:AF79 Z69:AB71 AD8:AF10 V101:X102 V62:X64 AH8:AJ10 N55:P57 R29:S34 Z62:AB64 N41:P43 V29:W34 AL55:AN57 R55:T57 AL62:AN64 F29:G34 AD48:AF50 N69:P71 AL29:AM34 AH22:AJ23 AD29:AE34 AH29:AI34 R96:T97 AH14:AJ16 F22:H23 R90:T91 F8:H10 R48:T50 J8:L10 F14:H16 Z90:AB91 J14:L16 B14:D16 B22:D23 J41:L43 F69:H71 B69:D71 B48:D50 J69:L71 F41:H43 F78:H79 B96:D97 J78:L79 F84:H85 J101:L102 B84:D85 B101:D102 B90:D91 F96:H97 F101:H102 J90:L91 J96:L97 F90:H91 J84:L85 B78:D79">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="AL41:AN43 AH69:AJ71 AL90:AN91 J48:L50 N29:O34 Z29:AA34 F55:H57 J132:L133 V78:X79 R78:T79 AD96:AF97 Z56:AB57 R69:T71 Z78:AB79 Z48:AB51 Z96:AB97 B55:D57 AH48:AJ50 V8:X10 R101:T102 AD69:AF71 J114:L115 AL78:AN79 AL69:AN71 AH41:AJ43 R8:T10 B41:D43 B108:D109 B62:D64 Z14:AB16 AD41:AF43 R14:T16 F48:H50 AL14:AN16 F62:H64 J55:L57 N78:P79 R62:T64 B8:D10 J120:L121 F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 B126:D127 AD14:AF16 B114:D115 J126:L127 N48:P50 Z101:AB102 AD22:AF23 N84:P85 AD84:AF85 R22:T23 V14:X16 V22:X23 F108:H109 Z22:AB23 AL101:AN102 AL22:AN23 R55:T57 AD90:AF91 AD55:AF57 N22:P23 N90:P91 J22:L23 J62:L64 V48:X51 N96:P97 R84:T85 V96:X97 R41:T43 AD101:AF102 N14:P16 AD62:AF64 AH90:AJ91 V84:X85 Z41:AB43 AH62:AJ64 N101:P102 Z84:AB85 V41:X43 AH78:AJ79 AL84:AN85 AH55:AJ57 V56:X57 B29:C34 J29:K34 AH96:AJ97 AH101:AJ102 AL48:AN50 V90:X91 AL96:AN97 Z8:AB10 AH84:AJ85 AL8:AN10 N62:P64 N8:P10 AD78:AF79 V69:X71 AD8:AF10 V101:X102 V62:X64 AH8:AJ10 N55:P57 R29:S34 Z62:AB64 N41:P43 V29:W34 AL55:AN57 B78:D79 AL62:AN64 F29:G34 AD48:AF50 N69:P71 AL29:AM34 AH22:AJ23 AD29:AE34 AH29:AI34 R96:T97 AH14:AJ16 F22:H23 R90:T91 F8:H10 R48:T50 J8:L10 F14:H16 Z90:AB91 J14:L16 B14:D16 B22:D23 J41:L43 F69:H71 B69:D71 B48:D50 J69:L71 F41:H43 F78:H79 B96:D97 J78:L79 F84:H85 J101:L102 B84:D85 B101:D102 B90:D91 F96:H97 F101:H102 J90:L91 J96:L97 F90:H91 J84:L85 Z69:AB71">
       <formula1>$AP$6:$AP$30</formula1>
     </dataValidation>
   </dataValidations>

--- a/Gorev-Listesi.xlsx
+++ b/Gorev-Listesi.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="107">
   <si>
     <t>CUMA</t>
   </si>
@@ -327,6 +327,24 @@
   </si>
   <si>
     <t>Çekmeköy Depo</t>
+  </si>
+  <si>
+    <t>Sultanahmet</t>
+  </si>
+  <si>
+    <t>10.00</t>
+  </si>
+  <si>
+    <t>İstanbul Havalimanı</t>
+  </si>
+  <si>
+    <t>???</t>
+  </si>
+  <si>
+    <t>S.CÜREBAL.</t>
+  </si>
+  <si>
+    <t>F.BOZKURT.</t>
   </si>
 </sst>
 </file>
@@ -1368,7 +1386,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1527,6 +1545,33 @@
     <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="14" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1536,10 +1581,43 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="12" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="13" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="7" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1548,6 +1626,15 @@
     <xf numFmtId="49" fontId="11" fillId="7" borderId="9" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="7" borderId="11" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1557,6 +1644,105 @@
     <xf numFmtId="49" fontId="11" fillId="7" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="12" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="13" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="8" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="9" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="10" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="9" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="9" borderId="17" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1566,58 +1752,43 @@
     <xf numFmtId="49" fontId="7" fillId="9" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="14" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="9" xfId="57" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="15" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="18" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="12" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="17" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="13" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="18" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="14" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="19" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="11" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1629,150 +1800,6 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="13" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="17" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="18" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="19" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="18" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="8" borderId="8" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="8" borderId="9" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="8" borderId="10" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="12" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="13" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1782,13 +1809,13 @@
     <xf numFmtId="0" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="14" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="11" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="15" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="12" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="13" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2240,65 +2267,65 @@
   <sheetData>
     <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12"/>
-      <c r="B1" s="127" t="s">
+      <c r="B1" s="111" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
       <c r="E1" s="10"/>
-      <c r="F1" s="128" t="s">
+      <c r="F1" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="128"/>
-      <c r="H1" s="128"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="112"/>
       <c r="I1" s="10"/>
-      <c r="J1" s="128" t="s">
+      <c r="J1" s="112" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="128"/>
-      <c r="L1" s="129"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="113"/>
       <c r="M1" s="12"/>
-      <c r="N1" s="132" t="s">
+      <c r="N1" s="116" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="122" t="s">
+      <c r="R1" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="122" t="s">
+      <c r="V1" s="110" t="s">
         <v>5</v>
       </c>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
+      <c r="W1" s="110"/>
+      <c r="X1" s="110"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="122" t="s">
+      <c r="Z1" s="110" t="s">
         <v>6</v>
       </c>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="AA1" s="110"/>
+      <c r="AB1" s="110"/>
       <c r="AC1" s="1"/>
-      <c r="AD1" s="122" t="s">
+      <c r="AD1" s="110" t="s">
         <v>0</v>
       </c>
-      <c r="AE1" s="122"/>
-      <c r="AF1" s="122"/>
+      <c r="AE1" s="110"/>
+      <c r="AF1" s="110"/>
       <c r="AG1" s="1"/>
-      <c r="AH1" s="122" t="s">
+      <c r="AH1" s="110" t="s">
         <v>1</v>
       </c>
-      <c r="AI1" s="122"/>
-      <c r="AJ1" s="122"/>
+      <c r="AI1" s="110"/>
+      <c r="AJ1" s="110"/>
       <c r="AK1" s="1"/>
-      <c r="AL1" s="122" t="s">
+      <c r="AL1" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="AM1" s="122"/>
-      <c r="AN1" s="123"/>
+      <c r="AM1" s="110"/>
+      <c r="AN1" s="120"/>
       <c r="AO1" s="12"/>
       <c r="AP1" s="12"/>
       <c r="AQ1" s="12"/>
@@ -2306,74 +2333,74 @@
     </row>
     <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
-      <c r="B2" s="130">
+      <c r="B2" s="114">
         <f>N2-3</f>
         <v>46276</v>
       </c>
-      <c r="C2" s="131"/>
-      <c r="D2" s="131"/>
+      <c r="C2" s="115"/>
+      <c r="D2" s="115"/>
       <c r="E2" s="11"/>
-      <c r="F2" s="131">
+      <c r="F2" s="115">
         <f>N2-2</f>
         <v>46277</v>
       </c>
-      <c r="G2" s="131"/>
-      <c r="H2" s="131"/>
+      <c r="G2" s="115"/>
+      <c r="H2" s="115"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="131">
+      <c r="J2" s="115">
         <f>N2-1</f>
         <v>46278</v>
       </c>
-      <c r="K2" s="131"/>
-      <c r="L2" s="134"/>
+      <c r="K2" s="115"/>
+      <c r="L2" s="118"/>
       <c r="M2" s="12"/>
-      <c r="N2" s="133">
+      <c r="N2" s="117">
         <v>46279</v>
       </c>
-      <c r="O2" s="124"/>
-      <c r="P2" s="124"/>
+      <c r="O2" s="109"/>
+      <c r="P2" s="109"/>
       <c r="Q2" s="53"/>
-      <c r="R2" s="124">
+      <c r="R2" s="109">
         <f>N2+1</f>
         <v>46280</v>
       </c>
-      <c r="S2" s="124"/>
-      <c r="T2" s="124"/>
+      <c r="S2" s="109"/>
+      <c r="T2" s="109"/>
       <c r="U2" s="53"/>
-      <c r="V2" s="124">
+      <c r="V2" s="109">
         <f>N2+2</f>
         <v>46281</v>
       </c>
-      <c r="W2" s="124"/>
-      <c r="X2" s="124"/>
+      <c r="W2" s="109"/>
+      <c r="X2" s="109"/>
       <c r="Y2" s="53"/>
-      <c r="Z2" s="124">
+      <c r="Z2" s="109">
         <f>N2+3</f>
         <v>46282</v>
       </c>
-      <c r="AA2" s="124"/>
-      <c r="AB2" s="124"/>
+      <c r="AA2" s="109"/>
+      <c r="AB2" s="109"/>
       <c r="AC2" s="53"/>
-      <c r="AD2" s="124">
+      <c r="AD2" s="109">
         <f>N2+4</f>
         <v>46283</v>
       </c>
-      <c r="AE2" s="124"/>
-      <c r="AF2" s="124"/>
+      <c r="AE2" s="109"/>
+      <c r="AF2" s="109"/>
       <c r="AG2" s="53"/>
-      <c r="AH2" s="124">
+      <c r="AH2" s="109">
         <f>N2+5</f>
         <v>46284</v>
       </c>
-      <c r="AI2" s="124"/>
-      <c r="AJ2" s="124"/>
+      <c r="AI2" s="109"/>
+      <c r="AJ2" s="109"/>
       <c r="AK2" s="53"/>
-      <c r="AL2" s="124">
+      <c r="AL2" s="109">
         <f>N2+6</f>
         <v>46285</v>
       </c>
-      <c r="AM2" s="124"/>
-      <c r="AN2" s="125"/>
+      <c r="AM2" s="109"/>
+      <c r="AN2" s="121"/>
       <c r="AO2" s="12"/>
       <c r="AP2" s="12"/>
       <c r="AQ2" s="12"/>
@@ -2427,47 +2454,47 @@
     </row>
     <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="12"/>
-      <c r="B4" s="126"/>
-      <c r="C4" s="126"/>
-      <c r="D4" s="126"/>
-      <c r="E4" s="126"/>
-      <c r="F4" s="126"/>
-      <c r="G4" s="126"/>
-      <c r="H4" s="126"/>
-      <c r="I4" s="126"/>
-      <c r="J4" s="126"/>
-      <c r="K4" s="126"/>
-      <c r="L4" s="126"/>
+      <c r="B4" s="119"/>
+      <c r="C4" s="119"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="119"/>
+      <c r="L4" s="119"/>
       <c r="M4" s="14"/>
-      <c r="N4" s="110" t="s">
+      <c r="N4" s="99" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="110"/>
-      <c r="P4" s="110"/>
-      <c r="Q4" s="110"/>
-      <c r="R4" s="110"/>
-      <c r="S4" s="110"/>
-      <c r="T4" s="110"/>
-      <c r="U4" s="110"/>
-      <c r="V4" s="110"/>
-      <c r="W4" s="110"/>
-      <c r="X4" s="110"/>
-      <c r="Y4" s="110"/>
-      <c r="Z4" s="110"/>
-      <c r="AA4" s="110"/>
-      <c r="AB4" s="110"/>
+      <c r="O4" s="99"/>
+      <c r="P4" s="99"/>
+      <c r="Q4" s="99"/>
+      <c r="R4" s="99"/>
+      <c r="S4" s="99"/>
+      <c r="T4" s="99"/>
+      <c r="U4" s="99"/>
+      <c r="V4" s="99"/>
+      <c r="W4" s="99"/>
+      <c r="X4" s="99"/>
+      <c r="Y4" s="99"/>
+      <c r="Z4" s="99"/>
+      <c r="AA4" s="99"/>
+      <c r="AB4" s="99"/>
       <c r="AC4" s="33"/>
-      <c r="AD4" s="126"/>
-      <c r="AE4" s="126"/>
-      <c r="AF4" s="126"/>
-      <c r="AG4" s="126"/>
-      <c r="AH4" s="126"/>
-      <c r="AI4" s="126"/>
-      <c r="AJ4" s="126"/>
-      <c r="AK4" s="126"/>
-      <c r="AL4" s="126"/>
-      <c r="AM4" s="126"/>
-      <c r="AN4" s="126"/>
+      <c r="AD4" s="119"/>
+      <c r="AE4" s="119"/>
+      <c r="AF4" s="119"/>
+      <c r="AG4" s="119"/>
+      <c r="AH4" s="119"/>
+      <c r="AI4" s="119"/>
+      <c r="AJ4" s="119"/>
+      <c r="AK4" s="119"/>
+      <c r="AL4" s="119"/>
+      <c r="AM4" s="119"/>
+      <c r="AN4" s="119"/>
       <c r="AO4" s="12"/>
       <c r="AP4" s="12"/>
       <c r="AQ4" s="12"/>
@@ -2475,95 +2502,95 @@
     </row>
     <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12"/>
-      <c r="B5" s="126"/>
-      <c r="C5" s="126"/>
-      <c r="D5" s="126"/>
-      <c r="E5" s="126"/>
-      <c r="F5" s="126"/>
-      <c r="G5" s="126"/>
-      <c r="H5" s="126"/>
-      <c r="I5" s="126"/>
-      <c r="J5" s="126"/>
-      <c r="K5" s="126"/>
-      <c r="L5" s="126"/>
+      <c r="B5" s="119"/>
+      <c r="C5" s="119"/>
+      <c r="D5" s="119"/>
+      <c r="E5" s="119"/>
+      <c r="F5" s="119"/>
+      <c r="G5" s="119"/>
+      <c r="H5" s="119"/>
+      <c r="I5" s="119"/>
+      <c r="J5" s="119"/>
+      <c r="K5" s="119"/>
+      <c r="L5" s="119"/>
       <c r="M5" s="14"/>
-      <c r="N5" s="110"/>
-      <c r="O5" s="110"/>
-      <c r="P5" s="110"/>
-      <c r="Q5" s="110"/>
-      <c r="R5" s="110"/>
-      <c r="S5" s="110"/>
-      <c r="T5" s="110"/>
-      <c r="U5" s="110"/>
-      <c r="V5" s="110"/>
-      <c r="W5" s="110"/>
-      <c r="X5" s="110"/>
-      <c r="Y5" s="110"/>
-      <c r="Z5" s="110"/>
-      <c r="AA5" s="110"/>
-      <c r="AB5" s="110"/>
+      <c r="N5" s="99"/>
+      <c r="O5" s="99"/>
+      <c r="P5" s="99"/>
+      <c r="Q5" s="99"/>
+      <c r="R5" s="99"/>
+      <c r="S5" s="99"/>
+      <c r="T5" s="99"/>
+      <c r="U5" s="99"/>
+      <c r="V5" s="99"/>
+      <c r="W5" s="99"/>
+      <c r="X5" s="99"/>
+      <c r="Y5" s="99"/>
+      <c r="Z5" s="99"/>
+      <c r="AA5" s="99"/>
+      <c r="AB5" s="99"/>
       <c r="AC5" s="33"/>
-      <c r="AD5" s="126"/>
-      <c r="AE5" s="126"/>
-      <c r="AF5" s="126"/>
-      <c r="AG5" s="126"/>
-      <c r="AH5" s="126"/>
-      <c r="AI5" s="126"/>
-      <c r="AJ5" s="126"/>
-      <c r="AK5" s="126"/>
-      <c r="AL5" s="126"/>
-      <c r="AM5" s="126"/>
-      <c r="AN5" s="126"/>
+      <c r="AD5" s="119"/>
+      <c r="AE5" s="119"/>
+      <c r="AF5" s="119"/>
+      <c r="AG5" s="119"/>
+      <c r="AH5" s="119"/>
+      <c r="AI5" s="119"/>
+      <c r="AJ5" s="119"/>
+      <c r="AK5" s="119"/>
+      <c r="AL5" s="119"/>
+      <c r="AM5" s="119"/>
+      <c r="AN5" s="119"/>
       <c r="AO5" s="12"/>
       <c r="AP5" s="12"/>
       <c r="AQ5" s="12"/>
       <c r="AR5" s="13"/>
     </row>
     <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="65"/>
-      <c r="C6" s="66"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="64"/>
       <c r="D6" s="57"/>
       <c r="E6" s="39"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="66"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
       <c r="H6" s="57"/>
       <c r="I6" s="36"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="66"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
       <c r="L6" s="57"/>
       <c r="M6" s="3"/>
-      <c r="N6" s="67"/>
-      <c r="O6" s="68"/>
+      <c r="N6" s="87"/>
+      <c r="O6" s="88"/>
       <c r="P6" s="34"/>
       <c r="Q6" s="39"/>
-      <c r="R6" s="67"/>
-      <c r="S6" s="68"/>
+      <c r="R6" s="87"/>
+      <c r="S6" s="88"/>
       <c r="T6" s="34"/>
       <c r="U6" s="36"/>
-      <c r="V6" s="67"/>
-      <c r="W6" s="68"/>
+      <c r="V6" s="87"/>
+      <c r="W6" s="88"/>
       <c r="X6" s="34"/>
       <c r="Y6" s="23"/>
-      <c r="Z6" s="67"/>
-      <c r="AA6" s="68"/>
+      <c r="Z6" s="87"/>
+      <c r="AA6" s="88"/>
       <c r="AB6" s="34"/>
       <c r="AC6" s="36"/>
-      <c r="AD6" s="67"/>
-      <c r="AE6" s="68"/>
+      <c r="AD6" s="87"/>
+      <c r="AE6" s="88"/>
       <c r="AF6" s="34"/>
       <c r="AG6" s="39"/>
-      <c r="AH6" s="67" t="s">
+      <c r="AH6" s="87" t="s">
         <v>77</v>
       </c>
-      <c r="AI6" s="68"/>
+      <c r="AI6" s="88"/>
       <c r="AJ6" s="34" t="s">
         <v>68</v>
       </c>
       <c r="AK6" s="36"/>
-      <c r="AL6" s="67" t="s">
+      <c r="AL6" s="87" t="s">
         <v>77</v>
       </c>
-      <c r="AM6" s="68"/>
+      <c r="AM6" s="88"/>
       <c r="AN6" s="34" t="s">
         <v>68</v>
       </c>
@@ -2577,44 +2604,44 @@
       <c r="AR6" s="30"/>
     </row>
     <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="90"/>
-      <c r="C7" s="91"/>
+      <c r="B7" s="68"/>
+      <c r="C7" s="69"/>
       <c r="D7" s="61"/>
       <c r="E7" s="38"/>
-      <c r="F7" s="90"/>
-      <c r="G7" s="91"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="69"/>
       <c r="H7" s="61"/>
       <c r="I7" s="36"/>
-      <c r="J7" s="90"/>
-      <c r="K7" s="91"/>
+      <c r="J7" s="68"/>
+      <c r="K7" s="69"/>
       <c r="L7" s="61"/>
       <c r="M7" s="3"/>
-      <c r="N7" s="81"/>
-      <c r="O7" s="82"/>
+      <c r="N7" s="89"/>
+      <c r="O7" s="90"/>
       <c r="P7" s="18"/>
       <c r="Q7" s="36"/>
-      <c r="R7" s="81"/>
-      <c r="S7" s="82"/>
+      <c r="R7" s="89"/>
+      <c r="S7" s="90"/>
       <c r="T7" s="18"/>
       <c r="U7" s="36"/>
-      <c r="V7" s="81"/>
-      <c r="W7" s="82"/>
+      <c r="V7" s="89"/>
+      <c r="W7" s="90"/>
       <c r="X7" s="18"/>
       <c r="Y7" s="36"/>
-      <c r="Z7" s="81"/>
-      <c r="AA7" s="82"/>
+      <c r="Z7" s="89"/>
+      <c r="AA7" s="90"/>
       <c r="AB7" s="18"/>
       <c r="AC7" s="36"/>
-      <c r="AD7" s="81"/>
-      <c r="AE7" s="82"/>
+      <c r="AD7" s="89"/>
+      <c r="AE7" s="90"/>
       <c r="AF7" s="18"/>
       <c r="AG7" s="38"/>
-      <c r="AH7" s="81"/>
-      <c r="AI7" s="82"/>
+      <c r="AH7" s="89"/>
+      <c r="AI7" s="90"/>
       <c r="AJ7" s="18"/>
       <c r="AK7" s="36"/>
-      <c r="AL7" s="81"/>
-      <c r="AM7" s="82"/>
+      <c r="AL7" s="89"/>
+      <c r="AM7" s="90"/>
       <c r="AN7" s="18"/>
       <c r="AP7" s="46" t="s">
         <v>9</v>
@@ -2626,49 +2653,49 @@
       <c r="AR7" s="30"/>
     </row>
     <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="87"/>
-      <c r="C8" s="88"/>
-      <c r="D8" s="89"/>
+      <c r="B8" s="81"/>
+      <c r="C8" s="82"/>
+      <c r="D8" s="83"/>
       <c r="E8" s="35"/>
-      <c r="F8" s="87"/>
-      <c r="G8" s="88"/>
-      <c r="H8" s="89"/>
+      <c r="F8" s="81"/>
+      <c r="G8" s="82"/>
+      <c r="H8" s="83"/>
       <c r="I8" s="37"/>
-      <c r="J8" s="87"/>
-      <c r="K8" s="88"/>
-      <c r="L8" s="89"/>
+      <c r="J8" s="81"/>
+      <c r="K8" s="82"/>
+      <c r="L8" s="83"/>
       <c r="M8" s="3"/>
-      <c r="N8" s="87"/>
-      <c r="O8" s="88"/>
-      <c r="P8" s="89"/>
+      <c r="N8" s="81"/>
+      <c r="O8" s="82"/>
+      <c r="P8" s="83"/>
       <c r="Q8" s="35"/>
-      <c r="R8" s="87"/>
-      <c r="S8" s="88"/>
-      <c r="T8" s="89"/>
+      <c r="R8" s="81"/>
+      <c r="S8" s="82"/>
+      <c r="T8" s="83"/>
       <c r="U8" s="37"/>
-      <c r="V8" s="87"/>
-      <c r="W8" s="88"/>
-      <c r="X8" s="89"/>
+      <c r="V8" s="81"/>
+      <c r="W8" s="82"/>
+      <c r="X8" s="83"/>
       <c r="Y8" s="35"/>
-      <c r="Z8" s="87"/>
-      <c r="AA8" s="88"/>
-      <c r="AB8" s="89"/>
+      <c r="Z8" s="81"/>
+      <c r="AA8" s="82"/>
+      <c r="AB8" s="83"/>
       <c r="AC8" s="35"/>
-      <c r="AD8" s="87"/>
-      <c r="AE8" s="88"/>
-      <c r="AF8" s="89"/>
+      <c r="AD8" s="81"/>
+      <c r="AE8" s="82"/>
+      <c r="AF8" s="83"/>
       <c r="AG8" s="35"/>
-      <c r="AH8" s="115" t="s">
+      <c r="AH8" s="122" t="s">
         <v>85</v>
       </c>
-      <c r="AI8" s="116"/>
-      <c r="AJ8" s="117"/>
+      <c r="AI8" s="123"/>
+      <c r="AJ8" s="124"/>
       <c r="AK8" s="37"/>
-      <c r="AL8" s="87" t="s">
+      <c r="AL8" s="81" t="s">
         <v>12</v>
       </c>
-      <c r="AM8" s="88"/>
-      <c r="AN8" s="89"/>
+      <c r="AM8" s="82"/>
+      <c r="AN8" s="83"/>
       <c r="AP8" s="46" t="s">
         <v>16</v>
       </c>
@@ -2679,47 +2706,47 @@
       <c r="AR8" s="30"/>
     </row>
     <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="78"/>
-      <c r="C9" s="79"/>
-      <c r="D9" s="80"/>
+      <c r="B9" s="65"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="67"/>
       <c r="E9" s="43"/>
-      <c r="F9" s="78"/>
-      <c r="G9" s="79"/>
-      <c r="H9" s="80"/>
+      <c r="F9" s="65"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="67"/>
       <c r="I9" s="43"/>
-      <c r="J9" s="78"/>
-      <c r="K9" s="79"/>
-      <c r="L9" s="80"/>
+      <c r="J9" s="65"/>
+      <c r="K9" s="66"/>
+      <c r="L9" s="67"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="78"/>
-      <c r="O9" s="79"/>
-      <c r="P9" s="80"/>
+      <c r="N9" s="65"/>
+      <c r="O9" s="66"/>
+      <c r="P9" s="67"/>
       <c r="Q9" s="43"/>
-      <c r="R9" s="78"/>
-      <c r="S9" s="79"/>
-      <c r="T9" s="80"/>
+      <c r="R9" s="65"/>
+      <c r="S9" s="66"/>
+      <c r="T9" s="67"/>
       <c r="U9" s="44"/>
-      <c r="V9" s="78"/>
-      <c r="W9" s="79"/>
-      <c r="X9" s="80"/>
+      <c r="V9" s="65"/>
+      <c r="W9" s="66"/>
+      <c r="X9" s="67"/>
       <c r="Y9" s="43"/>
-      <c r="Z9" s="78"/>
-      <c r="AA9" s="79"/>
-      <c r="AB9" s="80"/>
+      <c r="Z9" s="65"/>
+      <c r="AA9" s="66"/>
+      <c r="AB9" s="67"/>
       <c r="AC9" s="43"/>
-      <c r="AD9" s="78"/>
-      <c r="AE9" s="79"/>
-      <c r="AF9" s="80"/>
+      <c r="AD9" s="65"/>
+      <c r="AE9" s="66"/>
+      <c r="AF9" s="67"/>
       <c r="AG9" s="43"/>
-      <c r="AH9" s="78"/>
-      <c r="AI9" s="79"/>
-      <c r="AJ9" s="80"/>
+      <c r="AH9" s="65"/>
+      <c r="AI9" s="66"/>
+      <c r="AJ9" s="67"/>
       <c r="AK9" s="43"/>
-      <c r="AL9" s="78" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM9" s="79"/>
-      <c r="AN9" s="80"/>
+      <c r="AL9" s="106" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM9" s="107"/>
+      <c r="AN9" s="108"/>
       <c r="AP9" s="46" t="s">
         <v>11</v>
       </c>
@@ -2730,51 +2757,53 @@
       <c r="AR9" s="30"/>
     </row>
     <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="107"/>
-      <c r="C10" s="108"/>
-      <c r="D10" s="109"/>
+      <c r="B10" s="84"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="86"/>
       <c r="E10" s="44"/>
-      <c r="F10" s="107"/>
-      <c r="G10" s="108"/>
-      <c r="H10" s="109"/>
+      <c r="F10" s="84"/>
+      <c r="G10" s="85"/>
+      <c r="H10" s="86"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="107"/>
-      <c r="K10" s="108"/>
-      <c r="L10" s="109"/>
+      <c r="J10" s="84"/>
+      <c r="K10" s="85"/>
+      <c r="L10" s="86"/>
       <c r="M10" s="5"/>
-      <c r="N10" s="107"/>
-      <c r="O10" s="108"/>
-      <c r="P10" s="109"/>
+      <c r="N10" s="84"/>
+      <c r="O10" s="85"/>
+      <c r="P10" s="86"/>
       <c r="Q10" s="44"/>
-      <c r="R10" s="107"/>
-      <c r="S10" s="108"/>
-      <c r="T10" s="109"/>
+      <c r="R10" s="84"/>
+      <c r="S10" s="85"/>
+      <c r="T10" s="86"/>
       <c r="U10" s="44"/>
-      <c r="V10" s="107"/>
-      <c r="W10" s="108"/>
-      <c r="X10" s="109"/>
+      <c r="V10" s="84"/>
+      <c r="W10" s="85"/>
+      <c r="X10" s="86"/>
       <c r="Y10" s="44"/>
-      <c r="Z10" s="107"/>
-      <c r="AA10" s="108"/>
-      <c r="AB10" s="109"/>
+      <c r="Z10" s="84"/>
+      <c r="AA10" s="85"/>
+      <c r="AB10" s="86"/>
       <c r="AC10" s="44"/>
-      <c r="AD10" s="107"/>
-      <c r="AE10" s="108"/>
-      <c r="AF10" s="109"/>
+      <c r="AD10" s="84"/>
+      <c r="AE10" s="85"/>
+      <c r="AF10" s="86"/>
       <c r="AG10" s="44"/>
-      <c r="AH10" s="107"/>
-      <c r="AI10" s="108"/>
-      <c r="AJ10" s="109"/>
+      <c r="AH10" s="84"/>
+      <c r="AI10" s="85"/>
+      <c r="AJ10" s="86"/>
       <c r="AK10" s="44"/>
-      <c r="AL10" s="107"/>
-      <c r="AM10" s="108"/>
-      <c r="AN10" s="109"/>
+      <c r="AL10" s="133" t="s">
+        <v>96</v>
+      </c>
+      <c r="AM10" s="134"/>
+      <c r="AN10" s="135"/>
       <c r="AP10" s="46" t="s">
         <v>8</v>
       </c>
       <c r="AQ10" s="25">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR10" s="30"/>
     </row>
@@ -2830,52 +2859,52 @@
       </c>
     </row>
     <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="65"/>
-      <c r="C12" s="66"/>
+      <c r="B12" s="63"/>
+      <c r="C12" s="64"/>
       <c r="D12" s="57"/>
       <c r="E12" s="39"/>
-      <c r="F12" s="111" t="s">
+      <c r="F12" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="112"/>
+      <c r="G12" s="103"/>
       <c r="H12" s="59" t="s">
         <v>69</v>
       </c>
       <c r="I12" s="36"/>
-      <c r="J12" s="65"/>
-      <c r="K12" s="66"/>
+      <c r="J12" s="63"/>
+      <c r="K12" s="64"/>
       <c r="L12" s="57"/>
       <c r="M12" s="5"/>
-      <c r="N12" s="67"/>
-      <c r="O12" s="68"/>
+      <c r="N12" s="87"/>
+      <c r="O12" s="88"/>
       <c r="P12" s="34"/>
       <c r="Q12" s="23"/>
-      <c r="R12" s="67"/>
-      <c r="S12" s="68"/>
+      <c r="R12" s="87"/>
+      <c r="S12" s="88"/>
       <c r="T12" s="34"/>
       <c r="U12" s="36"/>
-      <c r="V12" s="67"/>
-      <c r="W12" s="68"/>
+      <c r="V12" s="87"/>
+      <c r="W12" s="88"/>
       <c r="X12" s="34"/>
       <c r="Y12" s="23"/>
-      <c r="Z12" s="67"/>
-      <c r="AA12" s="68"/>
+      <c r="Z12" s="87"/>
+      <c r="AA12" s="88"/>
       <c r="AB12" s="34"/>
       <c r="AC12" s="36"/>
-      <c r="AD12" s="67"/>
-      <c r="AE12" s="68"/>
+      <c r="AD12" s="87"/>
+      <c r="AE12" s="88"/>
       <c r="AF12" s="34"/>
       <c r="AG12" s="39"/>
-      <c r="AH12" s="67" t="s">
+      <c r="AH12" s="87" t="s">
         <v>41</v>
       </c>
-      <c r="AI12" s="68"/>
+      <c r="AI12" s="88"/>
       <c r="AJ12" s="34" t="s">
         <v>57</v>
       </c>
       <c r="AK12" s="36"/>
-      <c r="AL12" s="67"/>
-      <c r="AM12" s="68"/>
+      <c r="AL12" s="87"/>
+      <c r="AM12" s="88"/>
       <c r="AN12" s="34"/>
       <c r="AP12" s="46" t="s">
         <v>19</v>
@@ -2887,48 +2916,48 @@
       <c r="AR12" s="30"/>
     </row>
     <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="90"/>
-      <c r="C13" s="91"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="69"/>
       <c r="D13" s="61"/>
       <c r="E13" s="38"/>
-      <c r="F13" s="90" t="s">
+      <c r="F13" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="91"/>
+      <c r="G13" s="69"/>
       <c r="H13" s="61" t="s">
         <v>57</v>
       </c>
       <c r="I13" s="36"/>
-      <c r="J13" s="90"/>
-      <c r="K13" s="91"/>
+      <c r="J13" s="68"/>
+      <c r="K13" s="69"/>
       <c r="L13" s="61"/>
       <c r="M13" s="5"/>
-      <c r="N13" s="81"/>
-      <c r="O13" s="82"/>
+      <c r="N13" s="89"/>
+      <c r="O13" s="90"/>
       <c r="P13" s="18"/>
       <c r="Q13" s="36"/>
-      <c r="R13" s="81"/>
-      <c r="S13" s="82"/>
+      <c r="R13" s="89"/>
+      <c r="S13" s="90"/>
       <c r="T13" s="18"/>
       <c r="U13" s="36"/>
-      <c r="V13" s="81"/>
-      <c r="W13" s="82"/>
+      <c r="V13" s="89"/>
+      <c r="W13" s="90"/>
       <c r="X13" s="18"/>
       <c r="Y13" s="36"/>
-      <c r="Z13" s="81"/>
-      <c r="AA13" s="82"/>
+      <c r="Z13" s="89"/>
+      <c r="AA13" s="90"/>
       <c r="AB13" s="18"/>
       <c r="AC13" s="36"/>
-      <c r="AD13" s="81"/>
-      <c r="AE13" s="82"/>
+      <c r="AD13" s="89"/>
+      <c r="AE13" s="90"/>
       <c r="AF13" s="18"/>
       <c r="AG13" s="38"/>
-      <c r="AH13" s="81"/>
-      <c r="AI13" s="82"/>
+      <c r="AH13" s="89"/>
+      <c r="AI13" s="90"/>
       <c r="AJ13" s="18"/>
       <c r="AK13" s="36"/>
-      <c r="AL13" s="81"/>
-      <c r="AM13" s="82"/>
+      <c r="AL13" s="89"/>
+      <c r="AM13" s="90"/>
       <c r="AN13" s="18"/>
       <c r="AP13" s="46" t="s">
         <v>22</v>
@@ -2940,49 +2969,49 @@
       <c r="AR13" s="30"/>
     </row>
     <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="87"/>
-      <c r="C14" s="88"/>
-      <c r="D14" s="89"/>
+      <c r="B14" s="81"/>
+      <c r="C14" s="82"/>
+      <c r="D14" s="83"/>
       <c r="E14" s="37"/>
-      <c r="F14" s="87" t="s">
+      <c r="F14" s="81" t="s">
         <v>37</v>
       </c>
-      <c r="G14" s="88"/>
-      <c r="H14" s="89"/>
+      <c r="G14" s="82"/>
+      <c r="H14" s="83"/>
       <c r="I14" s="35"/>
-      <c r="J14" s="87"/>
-      <c r="K14" s="88"/>
-      <c r="L14" s="89"/>
+      <c r="J14" s="81"/>
+      <c r="K14" s="82"/>
+      <c r="L14" s="83"/>
       <c r="M14" s="3"/>
-      <c r="N14" s="87"/>
-      <c r="O14" s="88"/>
-      <c r="P14" s="89"/>
+      <c r="N14" s="81"/>
+      <c r="O14" s="82"/>
+      <c r="P14" s="83"/>
       <c r="Q14" s="35"/>
-      <c r="R14" s="87"/>
-      <c r="S14" s="88"/>
-      <c r="T14" s="89"/>
+      <c r="R14" s="81"/>
+      <c r="S14" s="82"/>
+      <c r="T14" s="83"/>
       <c r="U14" s="37"/>
-      <c r="V14" s="87"/>
-      <c r="W14" s="88"/>
-      <c r="X14" s="89"/>
+      <c r="V14" s="81"/>
+      <c r="W14" s="82"/>
+      <c r="X14" s="83"/>
       <c r="Y14" s="35"/>
-      <c r="Z14" s="87"/>
-      <c r="AA14" s="88"/>
-      <c r="AB14" s="89"/>
+      <c r="Z14" s="81"/>
+      <c r="AA14" s="82"/>
+      <c r="AB14" s="83"/>
       <c r="AC14" s="37"/>
-      <c r="AD14" s="87"/>
-      <c r="AE14" s="88"/>
-      <c r="AF14" s="89"/>
+      <c r="AD14" s="81"/>
+      <c r="AE14" s="82"/>
+      <c r="AF14" s="83"/>
       <c r="AG14" s="37"/>
-      <c r="AH14" s="87" t="s">
+      <c r="AH14" s="81" t="s">
         <v>37</v>
       </c>
-      <c r="AI14" s="88"/>
-      <c r="AJ14" s="89"/>
+      <c r="AI14" s="82"/>
+      <c r="AJ14" s="83"/>
       <c r="AK14" s="35"/>
-      <c r="AL14" s="87"/>
-      <c r="AM14" s="88"/>
-      <c r="AN14" s="89"/>
+      <c r="AL14" s="81"/>
+      <c r="AM14" s="82"/>
+      <c r="AN14" s="83"/>
       <c r="AP14" s="58" t="s">
         <v>23</v>
       </c>
@@ -2995,100 +3024,100 @@
       </c>
     </row>
     <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="78"/>
-      <c r="C15" s="79"/>
-      <c r="D15" s="80"/>
+      <c r="B15" s="65"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="67"/>
       <c r="E15" s="44"/>
-      <c r="F15" s="135" t="s">
+      <c r="F15" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="136"/>
-      <c r="H15" s="137"/>
+      <c r="G15" s="107"/>
+      <c r="H15" s="108"/>
       <c r="I15" s="43"/>
-      <c r="J15" s="78"/>
-      <c r="K15" s="79"/>
-      <c r="L15" s="80"/>
+      <c r="J15" s="65"/>
+      <c r="K15" s="66"/>
+      <c r="L15" s="67"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="78"/>
-      <c r="O15" s="79"/>
-      <c r="P15" s="80"/>
+      <c r="N15" s="65"/>
+      <c r="O15" s="66"/>
+      <c r="P15" s="67"/>
       <c r="Q15" s="43"/>
-      <c r="R15" s="78"/>
-      <c r="S15" s="79"/>
-      <c r="T15" s="80"/>
+      <c r="R15" s="65"/>
+      <c r="S15" s="66"/>
+      <c r="T15" s="67"/>
       <c r="U15" s="44"/>
-      <c r="V15" s="78"/>
-      <c r="W15" s="79"/>
-      <c r="X15" s="80"/>
+      <c r="V15" s="65"/>
+      <c r="W15" s="66"/>
+      <c r="X15" s="67"/>
       <c r="Y15" s="43"/>
-      <c r="Z15" s="78"/>
-      <c r="AA15" s="79"/>
-      <c r="AB15" s="80"/>
+      <c r="Z15" s="65"/>
+      <c r="AA15" s="66"/>
+      <c r="AB15" s="67"/>
       <c r="AC15" s="43"/>
-      <c r="AD15" s="78"/>
-      <c r="AE15" s="79"/>
-      <c r="AF15" s="80"/>
+      <c r="AD15" s="65"/>
+      <c r="AE15" s="66"/>
+      <c r="AF15" s="67"/>
       <c r="AG15" s="44"/>
-      <c r="AH15" s="78" t="s">
+      <c r="AH15" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="AI15" s="79"/>
-      <c r="AJ15" s="80"/>
+      <c r="AI15" s="66"/>
+      <c r="AJ15" s="67"/>
       <c r="AK15" s="43"/>
-      <c r="AL15" s="78"/>
-      <c r="AM15" s="79"/>
-      <c r="AN15" s="80"/>
+      <c r="AL15" s="65"/>
+      <c r="AM15" s="66"/>
+      <c r="AN15" s="67"/>
       <c r="AP15" s="46" t="s">
         <v>18</v>
       </c>
       <c r="AQ15" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR15" s="30"/>
     </row>
     <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="107"/>
-      <c r="C16" s="108"/>
-      <c r="D16" s="109"/>
+      <c r="B16" s="84"/>
+      <c r="C16" s="85"/>
+      <c r="D16" s="86"/>
       <c r="E16" s="44"/>
-      <c r="F16" s="104" t="s">
+      <c r="F16" s="133" t="s">
         <v>88</v>
       </c>
-      <c r="G16" s="105"/>
-      <c r="H16" s="106"/>
+      <c r="G16" s="134"/>
+      <c r="H16" s="135"/>
       <c r="I16" s="44"/>
-      <c r="J16" s="107"/>
-      <c r="K16" s="108"/>
-      <c r="L16" s="109"/>
+      <c r="J16" s="84"/>
+      <c r="K16" s="85"/>
+      <c r="L16" s="86"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="107"/>
-      <c r="O16" s="108"/>
-      <c r="P16" s="109"/>
+      <c r="N16" s="84"/>
+      <c r="O16" s="85"/>
+      <c r="P16" s="86"/>
       <c r="Q16" s="44"/>
-      <c r="R16" s="107"/>
-      <c r="S16" s="108"/>
-      <c r="T16" s="109"/>
+      <c r="R16" s="84"/>
+      <c r="S16" s="85"/>
+      <c r="T16" s="86"/>
       <c r="U16" s="44"/>
-      <c r="V16" s="107"/>
-      <c r="W16" s="108"/>
-      <c r="X16" s="109"/>
+      <c r="V16" s="84"/>
+      <c r="W16" s="85"/>
+      <c r="X16" s="86"/>
       <c r="Y16" s="44"/>
-      <c r="Z16" s="107"/>
-      <c r="AA16" s="108"/>
-      <c r="AB16" s="109"/>
+      <c r="Z16" s="84"/>
+      <c r="AA16" s="85"/>
+      <c r="AB16" s="86"/>
       <c r="AC16" s="44"/>
-      <c r="AD16" s="107"/>
-      <c r="AE16" s="108"/>
-      <c r="AF16" s="109"/>
+      <c r="AD16" s="84"/>
+      <c r="AE16" s="85"/>
+      <c r="AF16" s="86"/>
       <c r="AG16" s="44"/>
-      <c r="AH16" s="107"/>
-      <c r="AI16" s="108"/>
-      <c r="AJ16" s="109"/>
+      <c r="AH16" s="84"/>
+      <c r="AI16" s="85"/>
+      <c r="AJ16" s="86"/>
       <c r="AK16" s="44"/>
-      <c r="AL16" s="107"/>
-      <c r="AM16" s="108"/>
-      <c r="AN16" s="109"/>
+      <c r="AL16" s="84"/>
+      <c r="AM16" s="85"/>
+      <c r="AN16" s="86"/>
       <c r="AP16" s="46" t="s">
         <v>24</v>
       </c>
@@ -3160,23 +3189,23 @@
       <c r="K18" s="33"/>
       <c r="L18" s="33"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="110" t="s">
+      <c r="N18" s="99" t="s">
         <v>59</v>
       </c>
-      <c r="O18" s="110"/>
-      <c r="P18" s="110"/>
-      <c r="Q18" s="110"/>
-      <c r="R18" s="110"/>
-      <c r="S18" s="110"/>
-      <c r="T18" s="110"/>
-      <c r="U18" s="110"/>
-      <c r="V18" s="110"/>
-      <c r="W18" s="110"/>
-      <c r="X18" s="110"/>
-      <c r="Y18" s="110"/>
-      <c r="Z18" s="110"/>
-      <c r="AA18" s="110"/>
-      <c r="AB18" s="110"/>
+      <c r="O18" s="99"/>
+      <c r="P18" s="99"/>
+      <c r="Q18" s="99"/>
+      <c r="R18" s="99"/>
+      <c r="S18" s="99"/>
+      <c r="T18" s="99"/>
+      <c r="U18" s="99"/>
+      <c r="V18" s="99"/>
+      <c r="W18" s="99"/>
+      <c r="X18" s="99"/>
+      <c r="Y18" s="99"/>
+      <c r="Z18" s="99"/>
+      <c r="AA18" s="99"/>
+      <c r="AB18" s="99"/>
       <c r="AC18" s="33"/>
       <c r="AD18" s="33"/>
       <c r="AE18" s="33"/>
@@ -3211,21 +3240,21 @@
       <c r="K19" s="33"/>
       <c r="L19" s="33"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="110"/>
-      <c r="O19" s="110"/>
-      <c r="P19" s="110"/>
-      <c r="Q19" s="110"/>
-      <c r="R19" s="110"/>
-      <c r="S19" s="110"/>
-      <c r="T19" s="110"/>
-      <c r="U19" s="110"/>
-      <c r="V19" s="110"/>
-      <c r="W19" s="110"/>
-      <c r="X19" s="110"/>
-      <c r="Y19" s="110"/>
-      <c r="Z19" s="110"/>
-      <c r="AA19" s="110"/>
-      <c r="AB19" s="110"/>
+      <c r="N19" s="99"/>
+      <c r="O19" s="99"/>
+      <c r="P19" s="99"/>
+      <c r="Q19" s="99"/>
+      <c r="R19" s="99"/>
+      <c r="S19" s="99"/>
+      <c r="T19" s="99"/>
+      <c r="U19" s="99"/>
+      <c r="V19" s="99"/>
+      <c r="W19" s="99"/>
+      <c r="X19" s="99"/>
+      <c r="Y19" s="99"/>
+      <c r="Z19" s="99"/>
+      <c r="AA19" s="99"/>
+      <c r="AB19" s="99"/>
       <c r="AC19" s="33"/>
       <c r="AD19" s="33"/>
       <c r="AE19" s="33"/>
@@ -3248,60 +3277,60 @@
       <c r="AR19" s="30"/>
     </row>
     <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="65"/>
-      <c r="C20" s="66"/>
+      <c r="B20" s="63"/>
+      <c r="C20" s="64"/>
       <c r="D20" s="57"/>
       <c r="E20" s="39"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="66"/>
+      <c r="F20" s="63"/>
+      <c r="G20" s="64"/>
       <c r="H20" s="57"/>
       <c r="I20" s="36"/>
-      <c r="J20" s="65"/>
-      <c r="K20" s="66"/>
+      <c r="J20" s="63"/>
+      <c r="K20" s="64"/>
       <c r="L20" s="57"/>
       <c r="M20" s="4"/>
-      <c r="N20" s="99" t="s">
+      <c r="N20" s="136" t="s">
         <v>87</v>
       </c>
-      <c r="O20" s="100"/>
+      <c r="O20" s="137"/>
       <c r="P20" s="60" t="s">
         <v>49</v>
       </c>
       <c r="Q20" s="39"/>
-      <c r="R20" s="99" t="s">
+      <c r="R20" s="136" t="s">
         <v>87</v>
       </c>
-      <c r="S20" s="100"/>
+      <c r="S20" s="137"/>
       <c r="T20" s="60" t="s">
         <v>49</v>
       </c>
       <c r="U20" s="36"/>
-      <c r="V20" s="67" t="s">
+      <c r="V20" s="87" t="s">
         <v>56</v>
       </c>
-      <c r="W20" s="68"/>
+      <c r="W20" s="88"/>
       <c r="X20" s="34" t="s">
         <v>55</v>
       </c>
       <c r="Y20" s="23"/>
-      <c r="Z20" s="67"/>
-      <c r="AA20" s="68"/>
+      <c r="Z20" s="87"/>
+      <c r="AA20" s="88"/>
       <c r="AB20" s="34"/>
       <c r="AC20" s="36"/>
-      <c r="AD20" s="67"/>
-      <c r="AE20" s="68"/>
+      <c r="AD20" s="87"/>
+      <c r="AE20" s="88"/>
       <c r="AF20" s="34"/>
       <c r="AG20" s="39"/>
-      <c r="AH20" s="67" t="s">
+      <c r="AH20" s="87" t="s">
         <v>56</v>
       </c>
-      <c r="AI20" s="68"/>
+      <c r="AI20" s="88"/>
       <c r="AJ20" s="34" t="s">
         <v>86</v>
       </c>
       <c r="AK20" s="36"/>
-      <c r="AL20" s="67"/>
-      <c r="AM20" s="68"/>
+      <c r="AL20" s="87"/>
+      <c r="AM20" s="88"/>
       <c r="AN20" s="34"/>
       <c r="AP20" s="46" t="s">
         <v>26</v>
@@ -3313,159 +3342,159 @@
       <c r="AR20" s="30"/>
     </row>
     <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="90"/>
-      <c r="C21" s="91"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="69"/>
       <c r="D21" s="61"/>
       <c r="E21" s="38"/>
-      <c r="F21" s="90"/>
-      <c r="G21" s="91"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="69"/>
       <c r="H21" s="61"/>
       <c r="I21" s="36"/>
-      <c r="J21" s="90"/>
-      <c r="K21" s="91"/>
+      <c r="J21" s="68"/>
+      <c r="K21" s="69"/>
       <c r="L21" s="61"/>
       <c r="M21" s="15"/>
-      <c r="N21" s="148" t="s">
+      <c r="N21" s="131" t="s">
         <v>92</v>
       </c>
-      <c r="O21" s="149"/>
-      <c r="P21" s="147"/>
+      <c r="O21" s="132"/>
+      <c r="P21" s="62"/>
       <c r="Q21" s="36"/>
-      <c r="R21" s="148" t="s">
+      <c r="R21" s="131" t="s">
         <v>92</v>
       </c>
-      <c r="S21" s="149"/>
-      <c r="T21" s="147"/>
+      <c r="S21" s="132"/>
+      <c r="T21" s="62"/>
       <c r="U21" s="36"/>
-      <c r="V21" s="81" t="s">
+      <c r="V21" s="89" t="s">
         <v>54</v>
       </c>
-      <c r="W21" s="82"/>
+      <c r="W21" s="90"/>
       <c r="X21" s="18" t="s">
         <v>50</v>
       </c>
       <c r="Y21" s="36"/>
-      <c r="Z21" s="81"/>
-      <c r="AA21" s="82"/>
+      <c r="Z21" s="89"/>
+      <c r="AA21" s="90"/>
       <c r="AB21" s="18"/>
       <c r="AC21" s="36"/>
-      <c r="AD21" s="81"/>
-      <c r="AE21" s="82"/>
+      <c r="AD21" s="89"/>
+      <c r="AE21" s="90"/>
       <c r="AF21" s="18"/>
       <c r="AG21" s="38"/>
-      <c r="AH21" s="81"/>
-      <c r="AI21" s="82"/>
+      <c r="AH21" s="89"/>
+      <c r="AI21" s="90"/>
       <c r="AJ21" s="18"/>
       <c r="AK21" s="36"/>
-      <c r="AL21" s="81"/>
-      <c r="AM21" s="82"/>
+      <c r="AL21" s="89"/>
+      <c r="AM21" s="90"/>
       <c r="AN21" s="18"/>
       <c r="AP21" s="46" t="s">
         <v>12</v>
       </c>
       <c r="AQ21" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR21" s="30"/>
     </row>
     <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="87"/>
-      <c r="C22" s="88"/>
-      <c r="D22" s="89"/>
+      <c r="B22" s="81"/>
+      <c r="C22" s="82"/>
+      <c r="D22" s="83"/>
       <c r="E22" s="35"/>
-      <c r="F22" s="87"/>
-      <c r="G22" s="88"/>
-      <c r="H22" s="89"/>
+      <c r="F22" s="81"/>
+      <c r="G22" s="82"/>
+      <c r="H22" s="83"/>
       <c r="I22" s="37"/>
-      <c r="J22" s="87"/>
-      <c r="K22" s="88"/>
-      <c r="L22" s="89"/>
+      <c r="J22" s="81"/>
+      <c r="K22" s="82"/>
+      <c r="L22" s="83"/>
       <c r="M22" s="4"/>
-      <c r="N22" s="75" t="s">
+      <c r="N22" s="125" t="s">
         <v>97</v>
       </c>
-      <c r="O22" s="76"/>
-      <c r="P22" s="77"/>
+      <c r="O22" s="126"/>
+      <c r="P22" s="127"/>
       <c r="Q22" s="35"/>
-      <c r="R22" s="75" t="s">
+      <c r="R22" s="125" t="s">
         <v>98</v>
       </c>
-      <c r="S22" s="76"/>
-      <c r="T22" s="77"/>
+      <c r="S22" s="126"/>
+      <c r="T22" s="127"/>
       <c r="U22" s="37"/>
-      <c r="V22" s="87" t="s">
+      <c r="V22" s="81" t="s">
         <v>12</v>
       </c>
-      <c r="W22" s="88"/>
-      <c r="X22" s="89"/>
+      <c r="W22" s="82"/>
+      <c r="X22" s="83"/>
       <c r="Y22" s="35"/>
-      <c r="Z22" s="87"/>
-      <c r="AA22" s="88"/>
-      <c r="AB22" s="89"/>
+      <c r="Z22" s="81"/>
+      <c r="AA22" s="82"/>
+      <c r="AB22" s="83"/>
       <c r="AC22" s="35"/>
-      <c r="AD22" s="87"/>
-      <c r="AE22" s="88"/>
-      <c r="AF22" s="89"/>
+      <c r="AD22" s="81"/>
+      <c r="AE22" s="82"/>
+      <c r="AF22" s="83"/>
       <c r="AG22" s="35"/>
-      <c r="AH22" s="115" t="s">
+      <c r="AH22" s="122" t="s">
         <v>9</v>
       </c>
-      <c r="AI22" s="116"/>
-      <c r="AJ22" s="117"/>
+      <c r="AI22" s="123"/>
+      <c r="AJ22" s="124"/>
       <c r="AK22" s="37"/>
-      <c r="AL22" s="87"/>
-      <c r="AM22" s="88"/>
-      <c r="AN22" s="89"/>
+      <c r="AL22" s="81"/>
+      <c r="AM22" s="82"/>
+      <c r="AN22" s="83"/>
       <c r="AP22" s="46" t="s">
         <v>15</v>
       </c>
       <c r="AQ22" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR22" s="30"/>
     </row>
     <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="107"/>
-      <c r="C23" s="108"/>
-      <c r="D23" s="109"/>
+      <c r="B23" s="84"/>
+      <c r="C23" s="85"/>
+      <c r="D23" s="86"/>
       <c r="E23" s="44"/>
-      <c r="F23" s="107"/>
-      <c r="G23" s="108"/>
-      <c r="H23" s="109"/>
+      <c r="F23" s="84"/>
+      <c r="G23" s="85"/>
+      <c r="H23" s="86"/>
       <c r="I23" s="44"/>
-      <c r="J23" s="107"/>
-      <c r="K23" s="108"/>
-      <c r="L23" s="109"/>
+      <c r="J23" s="84"/>
+      <c r="K23" s="85"/>
+      <c r="L23" s="86"/>
       <c r="M23" s="4"/>
-      <c r="N23" s="72"/>
-      <c r="O23" s="73"/>
-      <c r="P23" s="74"/>
+      <c r="N23" s="128"/>
+      <c r="O23" s="129"/>
+      <c r="P23" s="130"/>
       <c r="Q23" s="44"/>
-      <c r="R23" s="72"/>
-      <c r="S23" s="73"/>
-      <c r="T23" s="74"/>
+      <c r="R23" s="128"/>
+      <c r="S23" s="129"/>
+      <c r="T23" s="130"/>
       <c r="U23" s="44"/>
-      <c r="V23" s="107"/>
-      <c r="W23" s="108"/>
-      <c r="X23" s="109"/>
+      <c r="V23" s="84"/>
+      <c r="W23" s="85"/>
+      <c r="X23" s="86"/>
       <c r="Y23" s="44"/>
-      <c r="Z23" s="107"/>
-      <c r="AA23" s="108"/>
-      <c r="AB23" s="109"/>
+      <c r="Z23" s="84"/>
+      <c r="AA23" s="85"/>
+      <c r="AB23" s="86"/>
       <c r="AC23" s="44"/>
-      <c r="AD23" s="107"/>
-      <c r="AE23" s="108"/>
-      <c r="AF23" s="109"/>
+      <c r="AD23" s="84"/>
+      <c r="AE23" s="85"/>
+      <c r="AF23" s="86"/>
       <c r="AG23" s="44"/>
-      <c r="AH23" s="107"/>
-      <c r="AI23" s="108"/>
-      <c r="AJ23" s="109"/>
+      <c r="AH23" s="84"/>
+      <c r="AI23" s="85"/>
+      <c r="AJ23" s="86"/>
       <c r="AK23" s="44"/>
-      <c r="AL23" s="107"/>
-      <c r="AM23" s="108"/>
-      <c r="AN23" s="109"/>
+      <c r="AL23" s="84"/>
+      <c r="AM23" s="85"/>
+      <c r="AN23" s="86"/>
       <c r="AP23" s="58" t="s">
         <v>20</v>
       </c>
@@ -3539,23 +3568,23 @@
       <c r="K25" s="33"/>
       <c r="L25" s="33"/>
       <c r="M25" s="4"/>
-      <c r="N25" s="110" t="s">
+      <c r="N25" s="99" t="s">
         <v>39</v>
       </c>
-      <c r="O25" s="110"/>
-      <c r="P25" s="110"/>
-      <c r="Q25" s="110"/>
-      <c r="R25" s="110"/>
-      <c r="S25" s="110"/>
-      <c r="T25" s="110"/>
-      <c r="U25" s="110"/>
-      <c r="V25" s="110"/>
-      <c r="W25" s="110"/>
-      <c r="X25" s="110"/>
-      <c r="Y25" s="110"/>
-      <c r="Z25" s="110"/>
-      <c r="AA25" s="110"/>
-      <c r="AB25" s="110"/>
+      <c r="O25" s="99"/>
+      <c r="P25" s="99"/>
+      <c r="Q25" s="99"/>
+      <c r="R25" s="99"/>
+      <c r="S25" s="99"/>
+      <c r="T25" s="99"/>
+      <c r="U25" s="99"/>
+      <c r="V25" s="99"/>
+      <c r="W25" s="99"/>
+      <c r="X25" s="99"/>
+      <c r="Y25" s="99"/>
+      <c r="Z25" s="99"/>
+      <c r="AA25" s="99"/>
+      <c r="AB25" s="99"/>
       <c r="AC25" s="33"/>
       <c r="AD25" s="33"/>
       <c r="AE25" s="33"/>
@@ -3590,21 +3619,21 @@
       <c r="K26" s="33"/>
       <c r="L26" s="33"/>
       <c r="M26" s="4"/>
-      <c r="N26" s="110"/>
-      <c r="O26" s="110"/>
-      <c r="P26" s="110"/>
-      <c r="Q26" s="110"/>
-      <c r="R26" s="110"/>
-      <c r="S26" s="110"/>
-      <c r="T26" s="110"/>
-      <c r="U26" s="110"/>
-      <c r="V26" s="110"/>
-      <c r="W26" s="110"/>
-      <c r="X26" s="110"/>
-      <c r="Y26" s="110"/>
-      <c r="Z26" s="110"/>
-      <c r="AA26" s="110"/>
-      <c r="AB26" s="110"/>
+      <c r="N26" s="99"/>
+      <c r="O26" s="99"/>
+      <c r="P26" s="99"/>
+      <c r="Q26" s="99"/>
+      <c r="R26" s="99"/>
+      <c r="S26" s="99"/>
+      <c r="T26" s="99"/>
+      <c r="U26" s="99"/>
+      <c r="V26" s="99"/>
+      <c r="W26" s="99"/>
+      <c r="X26" s="99"/>
+      <c r="Y26" s="99"/>
+      <c r="Z26" s="99"/>
+      <c r="AA26" s="99"/>
+      <c r="AB26" s="99"/>
       <c r="AC26" s="33"/>
       <c r="AD26" s="33"/>
       <c r="AE26" s="33"/>
@@ -3629,54 +3658,54 @@
       </c>
     </row>
     <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="65"/>
-      <c r="C27" s="66"/>
+      <c r="B27" s="63"/>
+      <c r="C27" s="64"/>
       <c r="D27" s="57"/>
       <c r="E27" s="36"/>
-      <c r="F27" s="65"/>
-      <c r="G27" s="66"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="64"/>
       <c r="H27" s="57"/>
       <c r="I27" s="36"/>
-      <c r="J27" s="65"/>
-      <c r="K27" s="66"/>
+      <c r="J27" s="63"/>
+      <c r="K27" s="64"/>
       <c r="L27" s="57"/>
       <c r="M27" s="5"/>
-      <c r="N27" s="67"/>
-      <c r="O27" s="68"/>
+      <c r="N27" s="87"/>
+      <c r="O27" s="88"/>
       <c r="P27" s="34"/>
       <c r="Q27" s="36"/>
-      <c r="R27" s="120"/>
-      <c r="S27" s="121"/>
+      <c r="R27" s="104"/>
+      <c r="S27" s="105"/>
       <c r="T27" s="55"/>
       <c r="U27" s="36"/>
-      <c r="V27" s="120"/>
-      <c r="W27" s="121"/>
+      <c r="V27" s="104"/>
+      <c r="W27" s="105"/>
       <c r="X27" s="55"/>
       <c r="Y27" s="36"/>
-      <c r="Z27" s="120"/>
-      <c r="AA27" s="121"/>
+      <c r="Z27" s="104"/>
+      <c r="AA27" s="105"/>
       <c r="AB27" s="55"/>
       <c r="AC27" s="36"/>
-      <c r="AD27" s="67" t="s">
+      <c r="AD27" s="87" t="s">
         <v>84</v>
       </c>
-      <c r="AE27" s="68"/>
+      <c r="AE27" s="88"/>
       <c r="AF27" s="34" t="s">
         <v>66</v>
       </c>
       <c r="AG27" s="36"/>
-      <c r="AH27" s="67" t="s">
+      <c r="AH27" s="87" t="s">
         <v>84</v>
       </c>
-      <c r="AI27" s="68"/>
+      <c r="AI27" s="88"/>
       <c r="AJ27" s="34" t="s">
         <v>66</v>
       </c>
       <c r="AK27" s="36"/>
-      <c r="AL27" s="67" t="s">
+      <c r="AL27" s="87" t="s">
         <v>84</v>
       </c>
-      <c r="AM27" s="68"/>
+      <c r="AM27" s="88"/>
       <c r="AN27" s="34" t="s">
         <v>66</v>
       </c>
@@ -3690,44 +3719,44 @@
       <c r="AR27" s="30"/>
     </row>
     <row r="28" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="90"/>
-      <c r="C28" s="91"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="69"/>
       <c r="D28" s="61"/>
       <c r="E28" s="38"/>
-      <c r="F28" s="90"/>
-      <c r="G28" s="91"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="69"/>
       <c r="H28" s="61"/>
       <c r="I28" s="36"/>
-      <c r="J28" s="90"/>
-      <c r="K28" s="91"/>
+      <c r="J28" s="68"/>
+      <c r="K28" s="69"/>
       <c r="L28" s="61"/>
       <c r="M28" s="5"/>
-      <c r="N28" s="81"/>
-      <c r="O28" s="82"/>
+      <c r="N28" s="89"/>
+      <c r="O28" s="90"/>
       <c r="P28" s="18"/>
       <c r="Q28" s="38"/>
-      <c r="R28" s="81"/>
-      <c r="S28" s="82"/>
+      <c r="R28" s="89"/>
+      <c r="S28" s="90"/>
       <c r="T28" s="18"/>
       <c r="U28" s="38"/>
-      <c r="V28" s="142"/>
-      <c r="W28" s="143"/>
+      <c r="V28" s="100"/>
+      <c r="W28" s="101"/>
       <c r="X28" s="56"/>
       <c r="Y28" s="36"/>
-      <c r="Z28" s="142"/>
-      <c r="AA28" s="143"/>
+      <c r="Z28" s="100"/>
+      <c r="AA28" s="101"/>
       <c r="AB28" s="56"/>
       <c r="AC28" s="36"/>
-      <c r="AD28" s="81"/>
-      <c r="AE28" s="82"/>
+      <c r="AD28" s="89"/>
+      <c r="AE28" s="90"/>
       <c r="AF28" s="18"/>
       <c r="AG28" s="38"/>
-      <c r="AH28" s="81"/>
-      <c r="AI28" s="82"/>
+      <c r="AH28" s="89"/>
+      <c r="AI28" s="90"/>
       <c r="AJ28" s="18"/>
       <c r="AK28" s="36"/>
-      <c r="AL28" s="81"/>
-      <c r="AM28" s="82"/>
+      <c r="AL28" s="89"/>
+      <c r="AM28" s="90"/>
       <c r="AN28" s="18"/>
       <c r="AP28" s="46" t="s">
         <v>28</v>
@@ -3739,54 +3768,54 @@
       <c r="AR28" s="30"/>
     </row>
     <row r="29" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="118"/>
-      <c r="C29" s="119"/>
+      <c r="B29" s="95"/>
+      <c r="C29" s="96"/>
       <c r="D29" s="41"/>
       <c r="E29" s="37"/>
-      <c r="F29" s="118"/>
-      <c r="G29" s="119"/>
+      <c r="F29" s="95"/>
+      <c r="G29" s="96"/>
       <c r="H29" s="41"/>
       <c r="I29" s="35"/>
-      <c r="J29" s="118"/>
-      <c r="K29" s="119"/>
+      <c r="J29" s="95"/>
+      <c r="K29" s="96"/>
       <c r="L29" s="41"/>
       <c r="M29" s="5"/>
-      <c r="N29" s="118"/>
-      <c r="O29" s="119"/>
+      <c r="N29" s="95"/>
+      <c r="O29" s="96"/>
       <c r="P29" s="41"/>
       <c r="Q29" s="35"/>
-      <c r="R29" s="118"/>
-      <c r="S29" s="119"/>
+      <c r="R29" s="95"/>
+      <c r="S29" s="96"/>
       <c r="T29" s="41"/>
       <c r="U29" s="37"/>
-      <c r="V29" s="118"/>
-      <c r="W29" s="119"/>
+      <c r="V29" s="95"/>
+      <c r="W29" s="96"/>
       <c r="X29" s="41"/>
       <c r="Y29" s="35"/>
-      <c r="Z29" s="118"/>
-      <c r="AA29" s="119"/>
+      <c r="Z29" s="95"/>
+      <c r="AA29" s="96"/>
       <c r="AB29" s="41"/>
       <c r="AC29" s="35"/>
-      <c r="AD29" s="118" t="s">
+      <c r="AD29" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="AE29" s="119"/>
+      <c r="AE29" s="96"/>
       <c r="AF29" s="41" t="s">
         <v>32</v>
       </c>
       <c r="AG29" s="37"/>
-      <c r="AH29" s="118" t="s">
+      <c r="AH29" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="AI29" s="119"/>
+      <c r="AI29" s="96"/>
       <c r="AJ29" s="41" t="s">
         <v>32</v>
       </c>
       <c r="AK29" s="35"/>
-      <c r="AL29" s="118" t="s">
+      <c r="AL29" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="AM29" s="119"/>
+      <c r="AM29" s="96"/>
       <c r="AN29" s="41" t="s">
         <v>32</v>
       </c>
@@ -3800,54 +3829,54 @@
       <c r="AR29" s="30"/>
     </row>
     <row r="30" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="140"/>
-      <c r="C30" s="141"/>
+      <c r="B30" s="97"/>
+      <c r="C30" s="98"/>
       <c r="D30" s="45"/>
       <c r="E30" s="43"/>
-      <c r="F30" s="140"/>
-      <c r="G30" s="141"/>
+      <c r="F30" s="97"/>
+      <c r="G30" s="98"/>
       <c r="H30" s="45"/>
       <c r="I30" s="43"/>
-      <c r="J30" s="140"/>
-      <c r="K30" s="141"/>
+      <c r="J30" s="97"/>
+      <c r="K30" s="98"/>
       <c r="L30" s="45"/>
       <c r="M30" s="5"/>
-      <c r="N30" s="140"/>
-      <c r="O30" s="141"/>
+      <c r="N30" s="97"/>
+      <c r="O30" s="98"/>
       <c r="P30" s="45"/>
       <c r="Q30" s="43"/>
-      <c r="R30" s="140"/>
-      <c r="S30" s="141"/>
+      <c r="R30" s="97"/>
+      <c r="S30" s="98"/>
       <c r="T30" s="45"/>
       <c r="U30" s="43"/>
-      <c r="V30" s="140"/>
-      <c r="W30" s="141"/>
+      <c r="V30" s="97"/>
+      <c r="W30" s="98"/>
       <c r="X30" s="45"/>
       <c r="Y30" s="43"/>
-      <c r="Z30" s="140"/>
-      <c r="AA30" s="141"/>
+      <c r="Z30" s="97"/>
+      <c r="AA30" s="98"/>
       <c r="AB30" s="45"/>
       <c r="AC30" s="43"/>
-      <c r="AD30" s="140" t="s">
+      <c r="AD30" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="AE30" s="141"/>
+      <c r="AE30" s="98"/>
       <c r="AF30" s="45" t="s">
         <v>33</v>
       </c>
       <c r="AG30" s="43"/>
-      <c r="AH30" s="140" t="s">
+      <c r="AH30" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="AI30" s="141"/>
+      <c r="AI30" s="98"/>
       <c r="AJ30" s="45" t="s">
         <v>33</v>
       </c>
       <c r="AK30" s="43"/>
-      <c r="AL30" s="140" t="s">
+      <c r="AL30" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="AM30" s="141"/>
+      <c r="AM30" s="98"/>
       <c r="AN30" s="45" t="s">
         <v>33</v>
       </c>
@@ -3861,54 +3890,54 @@
       <c r="AR30" s="30"/>
     </row>
     <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="113"/>
-      <c r="C31" s="114"/>
+      <c r="B31" s="74"/>
+      <c r="C31" s="75"/>
       <c r="D31" s="45"/>
       <c r="E31" s="43"/>
-      <c r="F31" s="113"/>
-      <c r="G31" s="114"/>
+      <c r="F31" s="74"/>
+      <c r="G31" s="75"/>
       <c r="H31" s="45"/>
       <c r="I31" s="44"/>
-      <c r="J31" s="113"/>
-      <c r="K31" s="114"/>
+      <c r="J31" s="74"/>
+      <c r="K31" s="75"/>
       <c r="L31" s="45"/>
       <c r="M31" s="6"/>
-      <c r="N31" s="113"/>
-      <c r="O31" s="114"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="75"/>
       <c r="P31" s="45"/>
       <c r="Q31" s="43"/>
-      <c r="R31" s="113"/>
-      <c r="S31" s="114"/>
+      <c r="R31" s="74"/>
+      <c r="S31" s="75"/>
       <c r="T31" s="45"/>
       <c r="U31" s="44"/>
-      <c r="V31" s="113"/>
-      <c r="W31" s="114"/>
+      <c r="V31" s="74"/>
+      <c r="W31" s="75"/>
       <c r="X31" s="45"/>
       <c r="Y31" s="43"/>
-      <c r="Z31" s="113"/>
-      <c r="AA31" s="114"/>
+      <c r="Z31" s="74"/>
+      <c r="AA31" s="75"/>
       <c r="AB31" s="45"/>
       <c r="AC31" s="43"/>
-      <c r="AD31" s="113" t="s">
+      <c r="AD31" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="AE31" s="114"/>
+      <c r="AE31" s="75"/>
       <c r="AF31" s="45" t="s">
         <v>34</v>
       </c>
       <c r="AG31" s="43"/>
-      <c r="AH31" s="113" t="s">
+      <c r="AH31" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="AI31" s="114"/>
+      <c r="AI31" s="75"/>
       <c r="AJ31" s="45" t="s">
         <v>34</v>
       </c>
       <c r="AK31" s="44"/>
-      <c r="AL31" s="113" t="s">
+      <c r="AL31" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="AM31" s="114"/>
+      <c r="AM31" s="75"/>
       <c r="AN31" s="45" t="s">
         <v>34</v>
       </c>
@@ -3917,54 +3946,54 @@
       <c r="AR31" s="30"/>
     </row>
     <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="113"/>
-      <c r="C32" s="114"/>
+      <c r="B32" s="74"/>
+      <c r="C32" s="75"/>
       <c r="D32" s="45"/>
       <c r="E32" s="44"/>
-      <c r="F32" s="113"/>
-      <c r="G32" s="114"/>
+      <c r="F32" s="74"/>
+      <c r="G32" s="75"/>
       <c r="H32" s="45"/>
       <c r="I32" s="44"/>
-      <c r="J32" s="113"/>
-      <c r="K32" s="114"/>
+      <c r="J32" s="74"/>
+      <c r="K32" s="75"/>
       <c r="L32" s="45"/>
       <c r="M32" s="5"/>
-      <c r="N32" s="113"/>
-      <c r="O32" s="114"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="75"/>
       <c r="P32" s="45"/>
       <c r="Q32" s="44"/>
-      <c r="R32" s="113"/>
-      <c r="S32" s="114"/>
+      <c r="R32" s="74"/>
+      <c r="S32" s="75"/>
       <c r="T32" s="45"/>
       <c r="U32" s="44"/>
-      <c r="V32" s="113"/>
-      <c r="W32" s="114"/>
+      <c r="V32" s="74"/>
+      <c r="W32" s="75"/>
       <c r="X32" s="45"/>
       <c r="Y32" s="44"/>
-      <c r="Z32" s="113"/>
-      <c r="AA32" s="114"/>
+      <c r="Z32" s="74"/>
+      <c r="AA32" s="75"/>
       <c r="AB32" s="45"/>
       <c r="AC32" s="44"/>
-      <c r="AD32" s="113" t="s">
+      <c r="AD32" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="AE32" s="114"/>
+      <c r="AE32" s="75"/>
       <c r="AF32" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AG32" s="44"/>
-      <c r="AH32" s="113" t="s">
+      <c r="AH32" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="AI32" s="114"/>
+      <c r="AI32" s="75"/>
       <c r="AJ32" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AK32" s="44"/>
-      <c r="AL32" s="113" t="s">
+      <c r="AL32" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="AM32" s="114"/>
+      <c r="AM32" s="75"/>
       <c r="AN32" s="45" t="s">
         <v>35</v>
       </c>
@@ -3973,91 +4002,91 @@
       <c r="AR32" s="30"/>
     </row>
     <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="113"/>
-      <c r="C33" s="114"/>
+      <c r="B33" s="74"/>
+      <c r="C33" s="75"/>
       <c r="D33" s="45"/>
       <c r="E33" s="44"/>
-      <c r="F33" s="113"/>
-      <c r="G33" s="114"/>
+      <c r="F33" s="74"/>
+      <c r="G33" s="75"/>
       <c r="H33" s="45"/>
       <c r="I33" s="44"/>
-      <c r="J33" s="113"/>
-      <c r="K33" s="114"/>
+      <c r="J33" s="74"/>
+      <c r="K33" s="75"/>
       <c r="L33" s="45"/>
       <c r="M33" s="5"/>
-      <c r="N33" s="113"/>
-      <c r="O33" s="114"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="75"/>
       <c r="P33" s="45"/>
       <c r="Q33" s="44"/>
-      <c r="R33" s="113"/>
-      <c r="S33" s="114"/>
+      <c r="R33" s="74"/>
+      <c r="S33" s="75"/>
       <c r="T33" s="45"/>
       <c r="U33" s="44"/>
-      <c r="V33" s="113"/>
-      <c r="W33" s="114"/>
+      <c r="V33" s="74"/>
+      <c r="W33" s="75"/>
       <c r="X33" s="45"/>
       <c r="Y33" s="44"/>
-      <c r="Z33" s="113"/>
-      <c r="AA33" s="114"/>
+      <c r="Z33" s="74"/>
+      <c r="AA33" s="75"/>
       <c r="AB33" s="45"/>
       <c r="AC33" s="44"/>
-      <c r="AD33" s="113" t="s">
+      <c r="AD33" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="AE33" s="114"/>
+      <c r="AE33" s="75"/>
       <c r="AF33" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AG33" s="44"/>
-      <c r="AH33" s="113"/>
-      <c r="AI33" s="114"/>
+      <c r="AH33" s="74"/>
+      <c r="AI33" s="75"/>
       <c r="AJ33" s="45"/>
       <c r="AK33" s="44"/>
-      <c r="AL33" s="113"/>
-      <c r="AM33" s="114"/>
+      <c r="AL33" s="74"/>
+      <c r="AM33" s="75"/>
       <c r="AN33" s="45"/>
       <c r="AR33" s="13"/>
     </row>
     <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="12"/>
-      <c r="B34" s="138"/>
-      <c r="C34" s="139"/>
+      <c r="B34" s="76"/>
+      <c r="C34" s="77"/>
       <c r="D34" s="42"/>
       <c r="E34" s="44"/>
-      <c r="F34" s="138"/>
-      <c r="G34" s="139"/>
+      <c r="F34" s="76"/>
+      <c r="G34" s="77"/>
       <c r="H34" s="42"/>
       <c r="I34" s="44"/>
-      <c r="J34" s="138"/>
-      <c r="K34" s="139"/>
+      <c r="J34" s="76"/>
+      <c r="K34" s="77"/>
       <c r="L34" s="42"/>
       <c r="M34" s="2"/>
-      <c r="N34" s="138"/>
-      <c r="O34" s="139"/>
+      <c r="N34" s="76"/>
+      <c r="O34" s="77"/>
       <c r="P34" s="42"/>
       <c r="Q34" s="44"/>
-      <c r="R34" s="138"/>
-      <c r="S34" s="139"/>
+      <c r="R34" s="76"/>
+      <c r="S34" s="77"/>
       <c r="T34" s="42"/>
       <c r="U34" s="44"/>
-      <c r="V34" s="138"/>
-      <c r="W34" s="139"/>
+      <c r="V34" s="76"/>
+      <c r="W34" s="77"/>
       <c r="X34" s="42"/>
       <c r="Y34" s="44"/>
-      <c r="Z34" s="138"/>
-      <c r="AA34" s="139"/>
+      <c r="Z34" s="76"/>
+      <c r="AA34" s="77"/>
       <c r="AB34" s="42"/>
       <c r="AC34" s="44"/>
-      <c r="AD34" s="138"/>
-      <c r="AE34" s="139"/>
+      <c r="AD34" s="76"/>
+      <c r="AE34" s="77"/>
       <c r="AF34" s="42"/>
       <c r="AG34" s="44"/>
-      <c r="AH34" s="138"/>
-      <c r="AI34" s="139"/>
+      <c r="AH34" s="76"/>
+      <c r="AI34" s="77"/>
       <c r="AJ34" s="42"/>
       <c r="AK34" s="44"/>
-      <c r="AL34" s="138"/>
-      <c r="AM34" s="139"/>
+      <c r="AL34" s="76"/>
+      <c r="AM34" s="77"/>
       <c r="AN34" s="42"/>
       <c r="AO34" s="12"/>
       <c r="AP34" s="12"/>
@@ -4123,23 +4152,23 @@
       <c r="K36" s="33"/>
       <c r="L36" s="33"/>
       <c r="M36" s="4"/>
-      <c r="N36" s="110" t="s">
+      <c r="N36" s="99" t="s">
         <v>36</v>
       </c>
-      <c r="O36" s="110"/>
-      <c r="P36" s="110"/>
-      <c r="Q36" s="110"/>
-      <c r="R36" s="110"/>
-      <c r="S36" s="110"/>
-      <c r="T36" s="110"/>
-      <c r="U36" s="110"/>
-      <c r="V36" s="110"/>
-      <c r="W36" s="110"/>
-      <c r="X36" s="110"/>
-      <c r="Y36" s="110"/>
-      <c r="Z36" s="110"/>
-      <c r="AA36" s="110"/>
-      <c r="AB36" s="110"/>
+      <c r="O36" s="99"/>
+      <c r="P36" s="99"/>
+      <c r="Q36" s="99"/>
+      <c r="R36" s="99"/>
+      <c r="S36" s="99"/>
+      <c r="T36" s="99"/>
+      <c r="U36" s="99"/>
+      <c r="V36" s="99"/>
+      <c r="W36" s="99"/>
+      <c r="X36" s="99"/>
+      <c r="Y36" s="99"/>
+      <c r="Z36" s="99"/>
+      <c r="AA36" s="99"/>
+      <c r="AB36" s="99"/>
       <c r="AC36" s="33"/>
       <c r="AD36" s="33"/>
       <c r="AE36" s="33"/>
@@ -4171,21 +4200,21 @@
       <c r="K37" s="33"/>
       <c r="L37" s="33"/>
       <c r="M37" s="5"/>
-      <c r="N37" s="110"/>
-      <c r="O37" s="110"/>
-      <c r="P37" s="110"/>
-      <c r="Q37" s="110"/>
-      <c r="R37" s="110"/>
-      <c r="S37" s="110"/>
-      <c r="T37" s="110"/>
-      <c r="U37" s="110"/>
-      <c r="V37" s="110"/>
-      <c r="W37" s="110"/>
-      <c r="X37" s="110"/>
-      <c r="Y37" s="110"/>
-      <c r="Z37" s="110"/>
-      <c r="AA37" s="110"/>
-      <c r="AB37" s="110"/>
+      <c r="N37" s="99"/>
+      <c r="O37" s="99"/>
+      <c r="P37" s="99"/>
+      <c r="Q37" s="99"/>
+      <c r="R37" s="99"/>
+      <c r="S37" s="99"/>
+      <c r="T37" s="99"/>
+      <c r="U37" s="99"/>
+      <c r="V37" s="99"/>
+      <c r="W37" s="99"/>
+      <c r="X37" s="99"/>
+      <c r="Y37" s="99"/>
+      <c r="Z37" s="99"/>
+      <c r="AA37" s="99"/>
+      <c r="AB37" s="99"/>
       <c r="AC37" s="33"/>
       <c r="AD37" s="33"/>
       <c r="AE37" s="33"/>
@@ -4205,74 +4234,74 @@
     </row>
     <row r="38" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12"/>
-      <c r="B38" s="65" t="s">
+      <c r="B38" s="63" t="s">
         <v>51</v>
       </c>
-      <c r="C38" s="66"/>
+      <c r="C38" s="64"/>
       <c r="D38" s="57"/>
       <c r="E38" s="36"/>
-      <c r="F38" s="65" t="s">
+      <c r="F38" s="63" t="s">
         <v>51</v>
       </c>
-      <c r="G38" s="66"/>
+      <c r="G38" s="64"/>
       <c r="H38" s="57"/>
       <c r="I38" s="36"/>
-      <c r="J38" s="65" t="s">
+      <c r="J38" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="K38" s="66"/>
+      <c r="K38" s="64"/>
       <c r="L38" s="57" t="s">
         <v>64</v>
       </c>
       <c r="M38" s="5"/>
-      <c r="N38" s="67"/>
-      <c r="O38" s="68"/>
+      <c r="N38" s="87"/>
+      <c r="O38" s="88"/>
       <c r="P38" s="34"/>
       <c r="Q38" s="36"/>
-      <c r="R38" s="67" t="s">
+      <c r="R38" s="87" t="s">
         <v>76</v>
       </c>
-      <c r="S38" s="68"/>
+      <c r="S38" s="88"/>
       <c r="T38" s="34" t="s">
         <v>67</v>
       </c>
       <c r="U38" s="36"/>
-      <c r="V38" s="67" t="s">
+      <c r="V38" s="87" t="s">
         <v>76</v>
       </c>
-      <c r="W38" s="68"/>
+      <c r="W38" s="88"/>
       <c r="X38" s="34" t="s">
         <v>67</v>
       </c>
       <c r="Y38" s="36"/>
-      <c r="Z38" s="67" t="s">
+      <c r="Z38" s="87" t="s">
         <v>76</v>
       </c>
-      <c r="AA38" s="68"/>
+      <c r="AA38" s="88"/>
       <c r="AB38" s="34" t="s">
         <v>67</v>
       </c>
       <c r="AC38" s="36"/>
-      <c r="AD38" s="67" t="s">
+      <c r="AD38" s="87" t="s">
         <v>76</v>
       </c>
-      <c r="AE38" s="68"/>
+      <c r="AE38" s="88"/>
       <c r="AF38" s="34" t="s">
         <v>67</v>
       </c>
       <c r="AG38" s="36"/>
-      <c r="AH38" s="67" t="s">
+      <c r="AH38" s="87" t="s">
         <v>42</v>
       </c>
-      <c r="AI38" s="68"/>
+      <c r="AI38" s="88"/>
       <c r="AJ38" s="34" t="s">
         <v>49</v>
       </c>
       <c r="AK38" s="36"/>
-      <c r="AL38" s="67" t="s">
+      <c r="AL38" s="87" t="s">
         <v>73</v>
       </c>
-      <c r="AM38" s="68"/>
+      <c r="AM38" s="88"/>
       <c r="AN38" s="34" t="s">
         <v>74</v>
       </c>
@@ -4283,63 +4312,63 @@
     </row>
     <row r="39" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12"/>
-      <c r="B39" s="84" t="s">
+      <c r="B39" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="C39" s="85"/>
-      <c r="D39" s="86"/>
+      <c r="C39" s="79"/>
+      <c r="D39" s="80"/>
       <c r="E39" s="36"/>
-      <c r="F39" s="84" t="s">
+      <c r="F39" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="G39" s="85"/>
-      <c r="H39" s="86"/>
+      <c r="G39" s="79"/>
+      <c r="H39" s="80"/>
       <c r="I39" s="36"/>
-      <c r="J39" s="84" t="s">
+      <c r="J39" s="78" t="s">
         <v>62</v>
       </c>
-      <c r="K39" s="85"/>
-      <c r="L39" s="86"/>
+      <c r="K39" s="79"/>
+      <c r="L39" s="80"/>
       <c r="M39" s="5"/>
-      <c r="N39" s="69"/>
-      <c r="O39" s="70"/>
-      <c r="P39" s="71"/>
+      <c r="N39" s="92"/>
+      <c r="O39" s="93"/>
+      <c r="P39" s="94"/>
       <c r="Q39" s="36"/>
-      <c r="R39" s="69" t="s">
+      <c r="R39" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="S39" s="70"/>
-      <c r="T39" s="71"/>
+      <c r="S39" s="93"/>
+      <c r="T39" s="94"/>
       <c r="U39" s="36"/>
-      <c r="V39" s="69" t="s">
+      <c r="V39" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="W39" s="70"/>
-      <c r="X39" s="71"/>
+      <c r="W39" s="93"/>
+      <c r="X39" s="94"/>
       <c r="Y39" s="37"/>
-      <c r="Z39" s="69" t="s">
+      <c r="Z39" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="AA39" s="70"/>
-      <c r="AB39" s="71"/>
+      <c r="AA39" s="93"/>
+      <c r="AB39" s="94"/>
       <c r="AC39" s="36"/>
-      <c r="AD39" s="69" t="s">
+      <c r="AD39" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="AE39" s="70"/>
-      <c r="AF39" s="71"/>
+      <c r="AE39" s="93"/>
+      <c r="AF39" s="94"/>
       <c r="AG39" s="36"/>
-      <c r="AH39" s="69" t="s">
+      <c r="AH39" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="AI39" s="70"/>
-      <c r="AJ39" s="71"/>
+      <c r="AI39" s="93"/>
+      <c r="AJ39" s="94"/>
       <c r="AK39" s="36"/>
-      <c r="AL39" s="69" t="s">
+      <c r="AL39" s="92" t="s">
         <v>75</v>
       </c>
-      <c r="AM39" s="70"/>
-      <c r="AN39" s="71"/>
+      <c r="AM39" s="93"/>
+      <c r="AN39" s="94"/>
       <c r="AO39" s="31"/>
       <c r="AP39" s="31"/>
       <c r="AQ39" s="31"/>
@@ -4347,45 +4376,45 @@
     </row>
     <row r="40" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12"/>
-      <c r="B40" s="90"/>
-      <c r="C40" s="91"/>
-      <c r="D40" s="92"/>
+      <c r="B40" s="68"/>
+      <c r="C40" s="69"/>
+      <c r="D40" s="70"/>
       <c r="E40" s="43"/>
-      <c r="F40" s="90"/>
-      <c r="G40" s="91"/>
-      <c r="H40" s="92"/>
+      <c r="F40" s="68"/>
+      <c r="G40" s="69"/>
+      <c r="H40" s="70"/>
       <c r="I40" s="43"/>
-      <c r="J40" s="90"/>
-      <c r="K40" s="91"/>
-      <c r="L40" s="92"/>
+      <c r="J40" s="68"/>
+      <c r="K40" s="69"/>
+      <c r="L40" s="70"/>
       <c r="M40" s="4"/>
-      <c r="N40" s="81"/>
-      <c r="O40" s="82"/>
-      <c r="P40" s="83"/>
+      <c r="N40" s="89"/>
+      <c r="O40" s="90"/>
+      <c r="P40" s="91"/>
       <c r="Q40" s="43"/>
-      <c r="R40" s="81"/>
-      <c r="S40" s="82"/>
-      <c r="T40" s="83"/>
+      <c r="R40" s="89"/>
+      <c r="S40" s="90"/>
+      <c r="T40" s="91"/>
       <c r="U40" s="35"/>
-      <c r="V40" s="81"/>
-      <c r="W40" s="82"/>
-      <c r="X40" s="83"/>
+      <c r="V40" s="89"/>
+      <c r="W40" s="90"/>
+      <c r="X40" s="91"/>
       <c r="Y40" s="36"/>
-      <c r="Z40" s="81"/>
-      <c r="AA40" s="82"/>
-      <c r="AB40" s="83"/>
+      <c r="Z40" s="89"/>
+      <c r="AA40" s="90"/>
+      <c r="AB40" s="91"/>
       <c r="AC40" s="36"/>
-      <c r="AD40" s="81"/>
-      <c r="AE40" s="82"/>
-      <c r="AF40" s="83"/>
+      <c r="AD40" s="89"/>
+      <c r="AE40" s="90"/>
+      <c r="AF40" s="91"/>
       <c r="AG40" s="43"/>
-      <c r="AH40" s="81"/>
-      <c r="AI40" s="82"/>
-      <c r="AJ40" s="83"/>
+      <c r="AH40" s="89"/>
+      <c r="AI40" s="90"/>
+      <c r="AJ40" s="91"/>
       <c r="AK40" s="43"/>
-      <c r="AL40" s="81"/>
-      <c r="AM40" s="82"/>
-      <c r="AN40" s="83"/>
+      <c r="AL40" s="89"/>
+      <c r="AM40" s="90"/>
+      <c r="AN40" s="91"/>
       <c r="AO40" s="31"/>
       <c r="AP40" s="31"/>
       <c r="AQ40" s="31"/>
@@ -4393,63 +4422,63 @@
     </row>
     <row r="41" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12"/>
-      <c r="B41" s="78" t="s">
+      <c r="B41" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="C41" s="79"/>
-      <c r="D41" s="80"/>
+      <c r="C41" s="66"/>
+      <c r="D41" s="67"/>
       <c r="E41" s="37"/>
-      <c r="F41" s="78" t="s">
+      <c r="F41" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="G41" s="79"/>
-      <c r="H41" s="80"/>
+      <c r="G41" s="66"/>
+      <c r="H41" s="67"/>
       <c r="I41" s="31"/>
-      <c r="J41" s="78" t="s">
+      <c r="J41" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="K41" s="79"/>
-      <c r="L41" s="80"/>
+      <c r="K41" s="66"/>
+      <c r="L41" s="67"/>
       <c r="M41" s="5"/>
-      <c r="N41" s="78"/>
-      <c r="O41" s="79"/>
-      <c r="P41" s="80"/>
+      <c r="N41" s="65"/>
+      <c r="O41" s="66"/>
+      <c r="P41" s="67"/>
       <c r="Q41" s="32"/>
-      <c r="R41" s="78" t="s">
+      <c r="R41" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="S41" s="79"/>
-      <c r="T41" s="80"/>
+      <c r="S41" s="66"/>
+      <c r="T41" s="67"/>
       <c r="U41" s="31"/>
-      <c r="V41" s="78" t="s">
+      <c r="V41" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="W41" s="79"/>
-      <c r="X41" s="80"/>
+      <c r="W41" s="66"/>
+      <c r="X41" s="67"/>
       <c r="Y41" s="32"/>
-      <c r="Z41" s="78" t="s">
+      <c r="Z41" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="AA41" s="79"/>
-      <c r="AB41" s="80"/>
+      <c r="AA41" s="66"/>
+      <c r="AB41" s="67"/>
       <c r="AC41" s="32"/>
-      <c r="AD41" s="78" t="s">
+      <c r="AD41" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="AE41" s="79"/>
-      <c r="AF41" s="80"/>
+      <c r="AE41" s="66"/>
+      <c r="AF41" s="67"/>
       <c r="AG41" s="37"/>
-      <c r="AH41" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="AI41" s="79"/>
-      <c r="AJ41" s="80"/>
+      <c r="AH41" s="150" t="s">
+        <v>106</v>
+      </c>
+      <c r="AI41" s="151"/>
+      <c r="AJ41" s="152"/>
       <c r="AK41" s="31"/>
-      <c r="AL41" s="78" t="s">
+      <c r="AL41" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="AM41" s="79"/>
-      <c r="AN41" s="80"/>
+      <c r="AM41" s="66"/>
+      <c r="AN41" s="67"/>
       <c r="AO41" s="31"/>
       <c r="AP41" s="31"/>
       <c r="AQ41" s="31"/>
@@ -4457,63 +4486,63 @@
     </row>
     <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12"/>
-      <c r="B42" s="78" t="s">
+      <c r="B42" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="C42" s="79"/>
-      <c r="D42" s="80"/>
+      <c r="C42" s="66"/>
+      <c r="D42" s="67"/>
       <c r="E42" s="44"/>
-      <c r="F42" s="78" t="s">
+      <c r="F42" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="G42" s="79"/>
-      <c r="H42" s="80"/>
+      <c r="G42" s="66"/>
+      <c r="H42" s="67"/>
       <c r="I42" s="31"/>
-      <c r="J42" s="78" t="s">
+      <c r="J42" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="K42" s="79"/>
-      <c r="L42" s="80"/>
+      <c r="K42" s="66"/>
+      <c r="L42" s="67"/>
       <c r="M42" s="5"/>
-      <c r="N42" s="78"/>
-      <c r="O42" s="79"/>
-      <c r="P42" s="80"/>
+      <c r="N42" s="65"/>
+      <c r="O42" s="66"/>
+      <c r="P42" s="67"/>
       <c r="Q42" s="31"/>
-      <c r="R42" s="78" t="s">
+      <c r="R42" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="S42" s="79"/>
-      <c r="T42" s="80"/>
+      <c r="S42" s="66"/>
+      <c r="T42" s="67"/>
       <c r="U42" s="32"/>
-      <c r="V42" s="78" t="s">
+      <c r="V42" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="W42" s="79"/>
-      <c r="X42" s="80"/>
+      <c r="W42" s="66"/>
+      <c r="X42" s="67"/>
       <c r="Y42" s="32"/>
-      <c r="Z42" s="78" t="s">
+      <c r="Z42" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="AA42" s="79"/>
-      <c r="AB42" s="80"/>
+      <c r="AA42" s="66"/>
+      <c r="AB42" s="67"/>
       <c r="AC42" s="32"/>
-      <c r="AD42" s="78" t="s">
+      <c r="AD42" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="AE42" s="79"/>
-      <c r="AF42" s="80"/>
+      <c r="AE42" s="66"/>
+      <c r="AF42" s="67"/>
       <c r="AG42" s="44"/>
-      <c r="AH42" s="78" t="s">
+      <c r="AH42" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="AI42" s="79"/>
-      <c r="AJ42" s="80"/>
+      <c r="AI42" s="66"/>
+      <c r="AJ42" s="67"/>
       <c r="AK42" s="31"/>
-      <c r="AL42" s="78" t="s">
+      <c r="AL42" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="AM42" s="79"/>
-      <c r="AN42" s="80"/>
+      <c r="AM42" s="66"/>
+      <c r="AN42" s="67"/>
       <c r="AO42" s="31"/>
       <c r="AP42" s="31"/>
       <c r="AQ42" s="31"/>
@@ -4521,51 +4550,51 @@
     </row>
     <row r="43" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12"/>
-      <c r="B43" s="62" t="s">
+      <c r="B43" s="71" t="s">
         <v>27</v>
       </c>
-      <c r="C43" s="63"/>
-      <c r="D43" s="64"/>
+      <c r="C43" s="72"/>
+      <c r="D43" s="73"/>
       <c r="E43" s="35"/>
-      <c r="F43" s="62" t="s">
+      <c r="F43" s="71" t="s">
         <v>27</v>
       </c>
-      <c r="G43" s="63"/>
-      <c r="H43" s="64"/>
+      <c r="G43" s="72"/>
+      <c r="H43" s="73"/>
       <c r="I43" s="40"/>
-      <c r="J43" s="62"/>
-      <c r="K43" s="63"/>
-      <c r="L43" s="64"/>
+      <c r="J43" s="71"/>
+      <c r="K43" s="72"/>
+      <c r="L43" s="73"/>
       <c r="M43" s="14"/>
-      <c r="N43" s="62"/>
-      <c r="O43" s="63"/>
-      <c r="P43" s="64"/>
+      <c r="N43" s="71"/>
+      <c r="O43" s="72"/>
+      <c r="P43" s="73"/>
       <c r="Q43" s="40"/>
-      <c r="R43" s="62"/>
-      <c r="S43" s="63"/>
-      <c r="T43" s="64"/>
+      <c r="R43" s="71"/>
+      <c r="S43" s="72"/>
+      <c r="T43" s="73"/>
       <c r="U43" s="40"/>
-      <c r="V43" s="62"/>
-      <c r="W43" s="63"/>
-      <c r="X43" s="64"/>
+      <c r="V43" s="71"/>
+      <c r="W43" s="72"/>
+      <c r="X43" s="73"/>
       <c r="Y43" s="40"/>
-      <c r="Z43" s="62"/>
-      <c r="AA43" s="63"/>
-      <c r="AB43" s="64"/>
+      <c r="Z43" s="71"/>
+      <c r="AA43" s="72"/>
+      <c r="AB43" s="73"/>
       <c r="AC43" s="40"/>
-      <c r="AD43" s="62"/>
-      <c r="AE43" s="63"/>
-      <c r="AF43" s="64"/>
+      <c r="AD43" s="71"/>
+      <c r="AE43" s="72"/>
+      <c r="AF43" s="73"/>
       <c r="AG43" s="35"/>
-      <c r="AH43" s="62" t="s">
+      <c r="AH43" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="AI43" s="63"/>
-      <c r="AJ43" s="64"/>
+      <c r="AI43" s="72"/>
+      <c r="AJ43" s="73"/>
       <c r="AK43" s="40"/>
-      <c r="AL43" s="62"/>
-      <c r="AM43" s="63"/>
-      <c r="AN43" s="64"/>
+      <c r="AL43" s="71"/>
+      <c r="AM43" s="72"/>
+      <c r="AN43" s="73"/>
       <c r="AO43" s="31"/>
       <c r="AP43" s="31"/>
       <c r="AQ43" s="31"/>
@@ -4619,74 +4648,74 @@
     </row>
     <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12"/>
-      <c r="B45" s="65" t="s">
+      <c r="B45" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="C45" s="66"/>
+      <c r="C45" s="64"/>
       <c r="D45" s="57" t="s">
         <v>50</v>
       </c>
       <c r="E45" s="36"/>
-      <c r="F45" s="65" t="s">
+      <c r="F45" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="G45" s="66"/>
+      <c r="G45" s="64"/>
       <c r="H45" s="57" t="s">
         <v>49</v>
       </c>
       <c r="I45" s="32"/>
-      <c r="J45" s="65" t="s">
+      <c r="J45" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="K45" s="66"/>
+      <c r="K45" s="64"/>
       <c r="L45" s="57" t="s">
         <v>50</v>
       </c>
       <c r="M45" s="14"/>
-      <c r="N45" s="67"/>
-      <c r="O45" s="68"/>
+      <c r="N45" s="87"/>
+      <c r="O45" s="88"/>
       <c r="P45" s="34"/>
       <c r="Q45" s="36"/>
-      <c r="R45" s="67" t="s">
+      <c r="R45" s="87" t="s">
         <v>82</v>
       </c>
-      <c r="S45" s="68"/>
+      <c r="S45" s="88"/>
       <c r="T45" s="34" t="s">
         <v>66</v>
       </c>
       <c r="U45" s="36"/>
-      <c r="V45" s="67" t="s">
+      <c r="V45" s="87" t="s">
         <v>53</v>
       </c>
-      <c r="W45" s="68"/>
+      <c r="W45" s="88"/>
       <c r="X45" s="34"/>
       <c r="Y45" s="54"/>
-      <c r="Z45" s="67" t="s">
+      <c r="Z45" s="87" t="s">
         <v>53</v>
       </c>
-      <c r="AA45" s="68"/>
+      <c r="AA45" s="88"/>
       <c r="AB45" s="34"/>
       <c r="AC45" s="36"/>
-      <c r="AD45" s="67" t="s">
+      <c r="AD45" s="87" t="s">
         <v>42</v>
       </c>
-      <c r="AE45" s="68"/>
+      <c r="AE45" s="88"/>
       <c r="AF45" s="34" t="s">
         <v>66</v>
       </c>
       <c r="AG45" s="36"/>
-      <c r="AH45" s="67" t="s">
+      <c r="AH45" s="87" t="s">
         <v>42</v>
       </c>
-      <c r="AI45" s="68"/>
+      <c r="AI45" s="88"/>
       <c r="AJ45" s="34" t="s">
         <v>50</v>
       </c>
       <c r="AK45" s="32"/>
-      <c r="AL45" s="67" t="s">
+      <c r="AL45" s="87" t="s">
         <v>42</v>
       </c>
-      <c r="AM45" s="68"/>
+      <c r="AM45" s="88"/>
       <c r="AN45" s="34" t="s">
         <v>49</v>
       </c>
@@ -4697,63 +4726,63 @@
     </row>
     <row r="46" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12"/>
-      <c r="B46" s="84" t="s">
+      <c r="B46" s="78" t="s">
         <v>47</v>
       </c>
-      <c r="C46" s="85"/>
-      <c r="D46" s="86"/>
+      <c r="C46" s="79"/>
+      <c r="D46" s="80"/>
       <c r="E46" s="36"/>
-      <c r="F46" s="84" t="s">
+      <c r="F46" s="78" t="s">
         <v>48</v>
       </c>
-      <c r="G46" s="85"/>
-      <c r="H46" s="86"/>
+      <c r="G46" s="79"/>
+      <c r="H46" s="80"/>
       <c r="I46" s="54"/>
-      <c r="J46" s="84" t="s">
+      <c r="J46" s="78" t="s">
         <v>47</v>
       </c>
-      <c r="K46" s="85"/>
-      <c r="L46" s="86"/>
+      <c r="K46" s="79"/>
+      <c r="L46" s="80"/>
       <c r="M46" s="4"/>
-      <c r="N46" s="69"/>
-      <c r="O46" s="70"/>
-      <c r="P46" s="71"/>
+      <c r="N46" s="92"/>
+      <c r="O46" s="93"/>
+      <c r="P46" s="94"/>
       <c r="Q46" s="43"/>
-      <c r="R46" s="69" t="s">
+      <c r="R46" s="92" t="s">
         <v>83</v>
       </c>
-      <c r="S46" s="70"/>
-      <c r="T46" s="71"/>
+      <c r="S46" s="93"/>
+      <c r="T46" s="94"/>
       <c r="U46" s="36"/>
-      <c r="V46" s="69" t="s">
+      <c r="V46" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="W46" s="70"/>
-      <c r="X46" s="71"/>
+      <c r="W46" s="93"/>
+      <c r="X46" s="94"/>
       <c r="Y46" s="35"/>
-      <c r="Z46" s="69" t="s">
+      <c r="Z46" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="AA46" s="70"/>
-      <c r="AB46" s="71"/>
+      <c r="AA46" s="93"/>
+      <c r="AB46" s="94"/>
       <c r="AC46" s="36"/>
-      <c r="AD46" s="69" t="s">
+      <c r="AD46" s="92" t="s">
         <v>72</v>
       </c>
-      <c r="AE46" s="70"/>
-      <c r="AF46" s="71"/>
+      <c r="AE46" s="93"/>
+      <c r="AF46" s="94"/>
       <c r="AG46" s="36"/>
-      <c r="AH46" s="69" t="s">
+      <c r="AH46" s="92" t="s">
         <v>43</v>
       </c>
-      <c r="AI46" s="70"/>
-      <c r="AJ46" s="71"/>
+      <c r="AI46" s="93"/>
+      <c r="AJ46" s="94"/>
       <c r="AK46" s="54"/>
-      <c r="AL46" s="69" t="s">
+      <c r="AL46" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="AM46" s="70"/>
-      <c r="AN46" s="71"/>
+      <c r="AM46" s="93"/>
+      <c r="AN46" s="94"/>
       <c r="AO46" s="31"/>
       <c r="AP46" s="31"/>
       <c r="AQ46" s="31"/>
@@ -4761,47 +4790,47 @@
     </row>
     <row r="47" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12"/>
-      <c r="B47" s="90"/>
-      <c r="C47" s="91"/>
-      <c r="D47" s="92"/>
+      <c r="B47" s="68"/>
+      <c r="C47" s="69"/>
+      <c r="D47" s="70"/>
       <c r="E47" s="43"/>
-      <c r="F47" s="90"/>
-      <c r="G47" s="91"/>
-      <c r="H47" s="92"/>
+      <c r="F47" s="68"/>
+      <c r="G47" s="69"/>
+      <c r="H47" s="70"/>
       <c r="I47" s="37"/>
-      <c r="J47" s="90"/>
-      <c r="K47" s="91"/>
-      <c r="L47" s="92"/>
+      <c r="J47" s="68"/>
+      <c r="K47" s="69"/>
+      <c r="L47" s="70"/>
       <c r="M47" s="4"/>
-      <c r="N47" s="81"/>
-      <c r="O47" s="82"/>
-      <c r="P47" s="83"/>
+      <c r="N47" s="89"/>
+      <c r="O47" s="90"/>
+      <c r="P47" s="91"/>
       <c r="Q47" s="37"/>
-      <c r="R47" s="81"/>
-      <c r="S47" s="82"/>
-      <c r="T47" s="83"/>
+      <c r="R47" s="89"/>
+      <c r="S47" s="90"/>
+      <c r="T47" s="91"/>
       <c r="U47" s="43"/>
-      <c r="V47" s="81" t="s">
+      <c r="V47" s="89" t="s">
         <v>46</v>
       </c>
-      <c r="W47" s="82"/>
-      <c r="X47" s="83"/>
+      <c r="W47" s="90"/>
+      <c r="X47" s="91"/>
       <c r="Y47" s="35"/>
-      <c r="Z47" s="81"/>
-      <c r="AA47" s="82"/>
-      <c r="AB47" s="83"/>
+      <c r="Z47" s="89"/>
+      <c r="AA47" s="90"/>
+      <c r="AB47" s="91"/>
       <c r="AC47" s="35"/>
-      <c r="AD47" s="81"/>
-      <c r="AE47" s="82"/>
-      <c r="AF47" s="83"/>
+      <c r="AD47" s="89"/>
+      <c r="AE47" s="90"/>
+      <c r="AF47" s="91"/>
       <c r="AG47" s="43"/>
-      <c r="AH47" s="81"/>
-      <c r="AI47" s="82"/>
-      <c r="AJ47" s="83"/>
+      <c r="AH47" s="89"/>
+      <c r="AI47" s="90"/>
+      <c r="AJ47" s="91"/>
       <c r="AK47" s="37"/>
-      <c r="AL47" s="81"/>
-      <c r="AM47" s="82"/>
-      <c r="AN47" s="83"/>
+      <c r="AL47" s="89"/>
+      <c r="AM47" s="90"/>
+      <c r="AN47" s="91"/>
       <c r="AO47" s="31"/>
       <c r="AP47" s="31"/>
       <c r="AQ47" s="31"/>
@@ -4809,189 +4838,189 @@
     </row>
     <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12"/>
-      <c r="B48" s="78" t="s">
+      <c r="B48" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="79"/>
-      <c r="D48" s="80"/>
+      <c r="C48" s="66"/>
+      <c r="D48" s="67"/>
       <c r="E48" s="37"/>
-      <c r="F48" s="78" t="s">
+      <c r="F48" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="G48" s="79"/>
-      <c r="H48" s="80"/>
+      <c r="G48" s="66"/>
+      <c r="H48" s="67"/>
       <c r="I48" s="44"/>
-      <c r="J48" s="78" t="s">
+      <c r="J48" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="K48" s="79"/>
-      <c r="L48" s="80"/>
+      <c r="K48" s="66"/>
+      <c r="L48" s="67"/>
       <c r="M48" s="5"/>
-      <c r="N48" s="78"/>
-      <c r="O48" s="79"/>
-      <c r="P48" s="80"/>
+      <c r="N48" s="65"/>
+      <c r="O48" s="66"/>
+      <c r="P48" s="67"/>
       <c r="Q48" s="44"/>
-      <c r="R48" s="78" t="s">
+      <c r="R48" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="S48" s="79"/>
-      <c r="T48" s="80"/>
+      <c r="S48" s="66"/>
+      <c r="T48" s="67"/>
       <c r="U48" s="37"/>
-      <c r="V48" s="78" t="s">
+      <c r="V48" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="W48" s="79"/>
-      <c r="X48" s="80"/>
+      <c r="W48" s="66"/>
+      <c r="X48" s="67"/>
       <c r="Y48" s="40"/>
-      <c r="Z48" s="78" t="s">
+      <c r="Z48" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="AA48" s="79"/>
-      <c r="AB48" s="80"/>
+      <c r="AA48" s="66"/>
+      <c r="AB48" s="67"/>
       <c r="AC48" s="43"/>
-      <c r="AD48" s="78" t="s">
+      <c r="AD48" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="AE48" s="79"/>
-      <c r="AF48" s="80"/>
+      <c r="AE48" s="66"/>
+      <c r="AF48" s="67"/>
       <c r="AG48" s="37"/>
-      <c r="AH48" s="78" t="s">
+      <c r="AH48" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="AI48" s="79"/>
-      <c r="AJ48" s="80"/>
+      <c r="AI48" s="66"/>
+      <c r="AJ48" s="67"/>
       <c r="AK48" s="44"/>
-      <c r="AL48" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="AM48" s="79"/>
-      <c r="AN48" s="80"/>
+      <c r="AL48" s="106" t="s">
+        <v>18</v>
+      </c>
+      <c r="AM48" s="107"/>
+      <c r="AN48" s="108"/>
       <c r="AO48" s="31"/>
       <c r="AP48" s="31"/>
       <c r="AQ48" s="31"/>
       <c r="AR48" s="13"/>
     </row>
     <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="78" t="s">
+      <c r="B49" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="C49" s="79"/>
-      <c r="D49" s="80"/>
+      <c r="C49" s="66"/>
+      <c r="D49" s="67"/>
       <c r="E49" s="35"/>
-      <c r="F49" s="78" t="s">
+      <c r="F49" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="G49" s="79"/>
-      <c r="H49" s="80"/>
+      <c r="G49" s="66"/>
+      <c r="H49" s="67"/>
       <c r="I49" s="44"/>
-      <c r="J49" s="78" t="s">
+      <c r="J49" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="K49" s="79"/>
-      <c r="L49" s="80"/>
+      <c r="K49" s="66"/>
+      <c r="L49" s="67"/>
       <c r="M49" s="5"/>
-      <c r="N49" s="78"/>
-      <c r="O49" s="79"/>
-      <c r="P49" s="80"/>
+      <c r="N49" s="65"/>
+      <c r="O49" s="66"/>
+      <c r="P49" s="67"/>
       <c r="Q49" s="44"/>
-      <c r="R49" s="135" t="s">
+      <c r="R49" s="106" t="s">
         <v>37</v>
       </c>
-      <c r="S49" s="136"/>
-      <c r="T49" s="137"/>
+      <c r="S49" s="107"/>
+      <c r="T49" s="108"/>
       <c r="U49" s="44"/>
-      <c r="V49" s="78" t="s">
+      <c r="V49" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="W49" s="79"/>
-      <c r="X49" s="80"/>
+      <c r="W49" s="66"/>
+      <c r="X49" s="67"/>
       <c r="Y49" s="44"/>
-      <c r="Z49" s="78" t="s">
+      <c r="Z49" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="AA49" s="79"/>
-      <c r="AB49" s="80"/>
+      <c r="AA49" s="66"/>
+      <c r="AB49" s="67"/>
       <c r="AC49" s="35"/>
-      <c r="AD49" s="78" t="s">
+      <c r="AD49" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="AE49" s="79"/>
-      <c r="AF49" s="80"/>
+      <c r="AE49" s="66"/>
+      <c r="AF49" s="67"/>
       <c r="AG49" s="35"/>
-      <c r="AH49" s="78" t="s">
-        <v>15</v>
-      </c>
-      <c r="AI49" s="79"/>
-      <c r="AJ49" s="80"/>
+      <c r="AH49" s="150" t="s">
+        <v>105</v>
+      </c>
+      <c r="AI49" s="151"/>
+      <c r="AJ49" s="152"/>
       <c r="AK49" s="44"/>
-      <c r="AL49" s="78" t="s">
+      <c r="AL49" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="AM49" s="79"/>
-      <c r="AN49" s="80"/>
+      <c r="AM49" s="66"/>
+      <c r="AN49" s="67"/>
       <c r="AO49" s="31"/>
       <c r="AP49" s="31"/>
       <c r="AQ49" s="31"/>
       <c r="AR49" s="13"/>
     </row>
     <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="62" t="s">
+      <c r="B50" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="C50" s="63"/>
-      <c r="D50" s="64"/>
+      <c r="C50" s="72"/>
+      <c r="D50" s="73"/>
       <c r="E50" s="50"/>
-      <c r="F50" s="62" t="s">
+      <c r="F50" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="G50" s="63"/>
-      <c r="H50" s="64"/>
+      <c r="G50" s="72"/>
+      <c r="H50" s="73"/>
       <c r="I50" s="50"/>
-      <c r="J50" s="62" t="s">
+      <c r="J50" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="K50" s="63"/>
-      <c r="L50" s="64"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="73"/>
       <c r="M50" s="5"/>
-      <c r="N50" s="62"/>
-      <c r="O50" s="63"/>
-      <c r="P50" s="64"/>
+      <c r="N50" s="71"/>
+      <c r="O50" s="72"/>
+      <c r="P50" s="73"/>
       <c r="Q50" s="50"/>
-      <c r="R50" s="144" t="s">
+      <c r="R50" s="147" t="s">
         <v>96</v>
       </c>
-      <c r="S50" s="145"/>
-      <c r="T50" s="146"/>
+      <c r="S50" s="148"/>
+      <c r="T50" s="149"/>
       <c r="U50" s="50"/>
-      <c r="V50" s="78" t="s">
+      <c r="V50" s="65" t="s">
         <v>15</v>
       </c>
-      <c r="W50" s="79"/>
-      <c r="X50" s="80"/>
+      <c r="W50" s="66"/>
+      <c r="X50" s="67"/>
       <c r="Y50" s="36"/>
-      <c r="Z50" s="78" t="s">
+      <c r="Z50" s="65" t="s">
         <v>15</v>
       </c>
-      <c r="AA50" s="79"/>
-      <c r="AB50" s="80"/>
+      <c r="AA50" s="66"/>
+      <c r="AB50" s="67"/>
       <c r="AC50" s="50"/>
-      <c r="AD50" s="62" t="s">
+      <c r="AD50" s="71" t="s">
         <v>26</v>
       </c>
-      <c r="AE50" s="63"/>
-      <c r="AF50" s="64"/>
+      <c r="AE50" s="72"/>
+      <c r="AF50" s="73"/>
       <c r="AG50" s="50"/>
-      <c r="AH50" s="62" t="s">
+      <c r="AH50" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="AI50" s="63"/>
-      <c r="AJ50" s="64"/>
+      <c r="AI50" s="72"/>
+      <c r="AJ50" s="73"/>
       <c r="AK50" s="50"/>
-      <c r="AL50" s="62" t="s">
+      <c r="AL50" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="AM50" s="63"/>
-      <c r="AN50" s="64"/>
+      <c r="AM50" s="72"/>
+      <c r="AN50" s="73"/>
       <c r="AO50" s="31"/>
       <c r="AP50" s="31"/>
       <c r="AQ50" s="31"/>
@@ -5018,17 +5047,17 @@
       <c r="S51" s="35"/>
       <c r="T51" s="35"/>
       <c r="U51" s="36"/>
-      <c r="V51" s="62" t="s">
+      <c r="V51" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="W51" s="63"/>
-      <c r="X51" s="64"/>
+      <c r="W51" s="72"/>
+      <c r="X51" s="73"/>
       <c r="Y51" s="37"/>
-      <c r="Z51" s="62" t="s">
+      <c r="Z51" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="AA51" s="63"/>
-      <c r="AB51" s="64"/>
+      <c r="AA51" s="72"/>
+      <c r="AB51" s="73"/>
       <c r="AC51" s="36"/>
       <c r="AD51" s="35"/>
       <c r="AE51" s="35"/>
@@ -5047,34 +5076,34 @@
       <c r="AR51" s="13"/>
     </row>
     <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="65"/>
-      <c r="C52" s="66"/>
+      <c r="B52" s="63"/>
+      <c r="C52" s="64"/>
       <c r="D52" s="57"/>
       <c r="E52" s="36"/>
-      <c r="F52" s="111" t="s">
+      <c r="F52" s="102" t="s">
         <v>89</v>
       </c>
-      <c r="G52" s="112"/>
+      <c r="G52" s="103"/>
       <c r="H52" s="59" t="s">
         <v>90</v>
       </c>
       <c r="I52" s="54"/>
-      <c r="J52" s="65" t="s">
+      <c r="J52" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="K52" s="66"/>
+      <c r="K52" s="64"/>
       <c r="L52" s="57" t="s">
         <v>50</v>
       </c>
       <c r="M52" s="14"/>
-      <c r="N52" s="67"/>
-      <c r="O52" s="68"/>
+      <c r="N52" s="87"/>
+      <c r="O52" s="88"/>
       <c r="P52" s="34"/>
       <c r="Q52" s="31"/>
-      <c r="R52" s="111" t="s">
+      <c r="R52" s="102" t="s">
         <v>89</v>
       </c>
-      <c r="S52" s="112"/>
+      <c r="S52" s="103"/>
       <c r="T52" s="59" t="s">
         <v>94</v>
       </c>
@@ -5087,257 +5116,277 @@
       <c r="AA52" s="35"/>
       <c r="AB52" s="35"/>
       <c r="AC52" s="36"/>
-      <c r="AD52" s="67"/>
-      <c r="AE52" s="68"/>
-      <c r="AF52" s="34"/>
+      <c r="AD52" s="102" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE52" s="103"/>
+      <c r="AF52" s="59" t="s">
+        <v>102</v>
+      </c>
       <c r="AG52" s="36"/>
-      <c r="AH52" s="67"/>
-      <c r="AI52" s="68"/>
-      <c r="AJ52" s="34"/>
+      <c r="AH52" s="102" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI52" s="103"/>
+      <c r="AJ52" s="59" t="s">
+        <v>90</v>
+      </c>
       <c r="AK52" s="54"/>
-      <c r="AL52" s="67"/>
-      <c r="AM52" s="68"/>
+      <c r="AL52" s="87"/>
+      <c r="AM52" s="88"/>
       <c r="AN52" s="34"/>
       <c r="AR52" s="13"/>
     </row>
     <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="84"/>
-      <c r="C53" s="85"/>
-      <c r="D53" s="86"/>
+      <c r="B53" s="78"/>
+      <c r="C53" s="79"/>
+      <c r="D53" s="80"/>
       <c r="E53" s="36"/>
-      <c r="F53" s="84" t="s">
+      <c r="F53" s="78" t="s">
         <v>91</v>
       </c>
-      <c r="G53" s="85"/>
-      <c r="H53" s="86"/>
+      <c r="G53" s="79"/>
+      <c r="H53" s="80"/>
       <c r="I53" s="35"/>
-      <c r="J53" s="84" t="s">
+      <c r="J53" s="78" t="s">
         <v>63</v>
       </c>
-      <c r="K53" s="85"/>
-      <c r="L53" s="86"/>
+      <c r="K53" s="79"/>
+      <c r="L53" s="80"/>
       <c r="M53" s="4"/>
-      <c r="N53" s="69"/>
-      <c r="O53" s="70"/>
-      <c r="P53" s="71"/>
+      <c r="N53" s="92"/>
+      <c r="O53" s="93"/>
+      <c r="P53" s="94"/>
       <c r="Q53" s="32"/>
-      <c r="R53" s="69" t="s">
+      <c r="R53" s="92" t="s">
         <v>95</v>
       </c>
-      <c r="S53" s="70"/>
-      <c r="T53" s="71"/>
+      <c r="S53" s="93"/>
+      <c r="T53" s="94"/>
       <c r="U53" s="43"/>
-      <c r="V53" s="67" t="s">
+      <c r="V53" s="87" t="s">
         <v>82</v>
       </c>
-      <c r="W53" s="68"/>
+      <c r="W53" s="88"/>
       <c r="X53" s="34" t="s">
         <v>66</v>
       </c>
       <c r="Y53" s="35"/>
-      <c r="Z53" s="67"/>
-      <c r="AA53" s="68"/>
+      <c r="Z53" s="87"/>
+      <c r="AA53" s="88"/>
       <c r="AB53" s="34"/>
       <c r="AC53" s="35"/>
-      <c r="AD53" s="69"/>
-      <c r="AE53" s="70"/>
-      <c r="AF53" s="71"/>
+      <c r="AD53" s="92" t="s">
+        <v>101</v>
+      </c>
+      <c r="AE53" s="93"/>
+      <c r="AF53" s="94"/>
       <c r="AG53" s="36"/>
-      <c r="AH53" s="69"/>
-      <c r="AI53" s="70"/>
-      <c r="AJ53" s="71"/>
+      <c r="AH53" s="92" t="s">
+        <v>104</v>
+      </c>
+      <c r="AI53" s="93"/>
+      <c r="AJ53" s="94"/>
       <c r="AK53" s="35"/>
-      <c r="AL53" s="69"/>
-      <c r="AM53" s="70"/>
-      <c r="AN53" s="71"/>
+      <c r="AL53" s="92"/>
+      <c r="AM53" s="93"/>
+      <c r="AN53" s="94"/>
       <c r="AR53" s="13"/>
     </row>
     <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="90"/>
-      <c r="C54" s="91"/>
-      <c r="D54" s="92"/>
+      <c r="B54" s="68"/>
+      <c r="C54" s="69"/>
+      <c r="D54" s="70"/>
       <c r="E54" s="43"/>
-      <c r="F54" s="90"/>
-      <c r="G54" s="91"/>
-      <c r="H54" s="92"/>
+      <c r="F54" s="68"/>
+      <c r="G54" s="69"/>
+      <c r="H54" s="70"/>
       <c r="I54" s="35"/>
-      <c r="J54" s="90"/>
-      <c r="K54" s="91"/>
-      <c r="L54" s="92"/>
+      <c r="J54" s="68"/>
+      <c r="K54" s="69"/>
+      <c r="L54" s="70"/>
       <c r="M54" s="4"/>
-      <c r="N54" s="81"/>
-      <c r="O54" s="82"/>
-      <c r="P54" s="83"/>
+      <c r="N54" s="89"/>
+      <c r="O54" s="90"/>
+      <c r="P54" s="91"/>
       <c r="Q54" s="43"/>
-      <c r="R54" s="81"/>
-      <c r="S54" s="82"/>
-      <c r="T54" s="83"/>
+      <c r="R54" s="89"/>
+      <c r="S54" s="90"/>
+      <c r="T54" s="91"/>
       <c r="U54" s="37"/>
-      <c r="V54" s="69" t="s">
+      <c r="V54" s="92" t="s">
         <v>83</v>
       </c>
-      <c r="W54" s="70"/>
-      <c r="X54" s="71"/>
+      <c r="W54" s="93"/>
+      <c r="X54" s="94"/>
       <c r="Y54" s="40"/>
-      <c r="Z54" s="69"/>
-      <c r="AA54" s="70"/>
-      <c r="AB54" s="71"/>
+      <c r="Z54" s="92"/>
+      <c r="AA54" s="93"/>
+      <c r="AB54" s="94"/>
       <c r="AC54" s="31"/>
-      <c r="AD54" s="81"/>
-      <c r="AE54" s="82"/>
-      <c r="AF54" s="83"/>
+      <c r="AD54" s="89"/>
+      <c r="AE54" s="90"/>
+      <c r="AF54" s="91"/>
       <c r="AG54" s="43"/>
-      <c r="AH54" s="81"/>
-      <c r="AI54" s="82"/>
-      <c r="AJ54" s="83"/>
+      <c r="AH54" s="89"/>
+      <c r="AI54" s="90"/>
+      <c r="AJ54" s="91"/>
       <c r="AK54" s="35"/>
-      <c r="AL54" s="81"/>
-      <c r="AM54" s="82"/>
-      <c r="AN54" s="83"/>
+      <c r="AL54" s="89"/>
+      <c r="AM54" s="90"/>
+      <c r="AN54" s="91"/>
       <c r="AR54" s="13"/>
     </row>
     <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="78"/>
-      <c r="C55" s="79"/>
-      <c r="D55" s="80"/>
+      <c r="B55" s="65"/>
+      <c r="C55" s="66"/>
+      <c r="D55" s="67"/>
       <c r="E55" s="37"/>
-      <c r="F55" s="78" t="s">
+      <c r="F55" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="G55" s="79"/>
-      <c r="H55" s="80"/>
+      <c r="G55" s="66"/>
+      <c r="H55" s="67"/>
       <c r="I55" s="40"/>
-      <c r="J55" s="78" t="s">
+      <c r="J55" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="K55" s="79"/>
-      <c r="L55" s="80"/>
+      <c r="K55" s="66"/>
+      <c r="L55" s="67"/>
       <c r="M55" s="5"/>
-      <c r="N55" s="78"/>
-      <c r="O55" s="79"/>
-      <c r="P55" s="80"/>
+      <c r="N55" s="65"/>
+      <c r="O55" s="66"/>
+      <c r="P55" s="67"/>
       <c r="Q55" s="43"/>
-      <c r="R55" s="78" t="s">
+      <c r="R55" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="S55" s="79"/>
-      <c r="T55" s="80"/>
+      <c r="S55" s="66"/>
+      <c r="T55" s="67"/>
       <c r="U55" s="44"/>
-      <c r="V55" s="81"/>
-      <c r="W55" s="82"/>
-      <c r="X55" s="83"/>
+      <c r="V55" s="89"/>
+      <c r="W55" s="90"/>
+      <c r="X55" s="91"/>
       <c r="Y55" s="44"/>
-      <c r="Z55" s="81"/>
-      <c r="AA55" s="82"/>
-      <c r="AB55" s="83"/>
+      <c r="Z55" s="89"/>
+      <c r="AA55" s="90"/>
+      <c r="AB55" s="91"/>
       <c r="AC55" s="35"/>
-      <c r="AD55" s="78"/>
-      <c r="AE55" s="79"/>
-      <c r="AF55" s="80"/>
+      <c r="AD55" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE55" s="66"/>
+      <c r="AF55" s="67"/>
       <c r="AG55" s="37"/>
-      <c r="AH55" s="78"/>
-      <c r="AI55" s="79"/>
-      <c r="AJ55" s="80"/>
+      <c r="AH55" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="AI55" s="66"/>
+      <c r="AJ55" s="67"/>
       <c r="AK55" s="40"/>
-      <c r="AL55" s="78"/>
-      <c r="AM55" s="79"/>
-      <c r="AN55" s="80"/>
+      <c r="AL55" s="65"/>
+      <c r="AM55" s="66"/>
+      <c r="AN55" s="67"/>
       <c r="AR55" s="13"/>
     </row>
     <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="78"/>
-      <c r="C56" s="79"/>
-      <c r="D56" s="80"/>
+      <c r="B56" s="65"/>
+      <c r="C56" s="66"/>
+      <c r="D56" s="67"/>
       <c r="E56" s="44"/>
-      <c r="F56" s="78" t="s">
+      <c r="F56" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="G56" s="79"/>
-      <c r="H56" s="80"/>
+      <c r="G56" s="66"/>
+      <c r="H56" s="67"/>
       <c r="I56" s="44"/>
-      <c r="J56" s="78" t="s">
+      <c r="J56" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="K56" s="79"/>
-      <c r="L56" s="80"/>
+      <c r="K56" s="66"/>
+      <c r="L56" s="67"/>
       <c r="M56" s="5"/>
-      <c r="N56" s="78"/>
-      <c r="O56" s="79"/>
-      <c r="P56" s="80"/>
+      <c r="N56" s="65"/>
+      <c r="O56" s="66"/>
+      <c r="P56" s="67"/>
       <c r="Q56" s="43"/>
-      <c r="R56" s="78" t="s">
+      <c r="R56" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="S56" s="79"/>
-      <c r="T56" s="80"/>
+      <c r="S56" s="66"/>
+      <c r="T56" s="67"/>
       <c r="U56" s="44"/>
-      <c r="V56" s="78" t="s">
+      <c r="V56" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="W56" s="79"/>
-      <c r="X56" s="80"/>
+      <c r="W56" s="66"/>
+      <c r="X56" s="67"/>
       <c r="Y56" s="50"/>
-      <c r="Z56" s="78"/>
-      <c r="AA56" s="79"/>
-      <c r="AB56" s="80"/>
+      <c r="Z56" s="65"/>
+      <c r="AA56" s="66"/>
+      <c r="AB56" s="67"/>
       <c r="AC56" s="43"/>
-      <c r="AD56" s="78"/>
-      <c r="AE56" s="79"/>
-      <c r="AF56" s="80"/>
+      <c r="AD56" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE56" s="66"/>
+      <c r="AF56" s="67"/>
       <c r="AG56" s="44"/>
-      <c r="AH56" s="78"/>
-      <c r="AI56" s="79"/>
-      <c r="AJ56" s="80"/>
+      <c r="AH56" s="65" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI56" s="66"/>
+      <c r="AJ56" s="67"/>
       <c r="AK56" s="44"/>
-      <c r="AL56" s="78"/>
-      <c r="AM56" s="79"/>
-      <c r="AN56" s="80"/>
+      <c r="AL56" s="65"/>
+      <c r="AM56" s="66"/>
+      <c r="AN56" s="67"/>
       <c r="AR56" s="13"/>
     </row>
     <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="62"/>
-      <c r="C57" s="63"/>
-      <c r="D57" s="64"/>
+      <c r="B57" s="71"/>
+      <c r="C57" s="72"/>
+      <c r="D57" s="73"/>
       <c r="E57" s="35"/>
-      <c r="F57" s="62"/>
-      <c r="G57" s="63"/>
-      <c r="H57" s="64"/>
+      <c r="F57" s="71"/>
+      <c r="G57" s="72"/>
+      <c r="H57" s="73"/>
       <c r="I57" s="50"/>
-      <c r="J57" s="101" t="s">
+      <c r="J57" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="K57" s="102"/>
-      <c r="L57" s="103"/>
+      <c r="K57" s="142"/>
+      <c r="L57" s="143"/>
       <c r="M57" s="5"/>
-      <c r="N57" s="62"/>
-      <c r="O57" s="63"/>
-      <c r="P57" s="64"/>
+      <c r="N57" s="71"/>
+      <c r="O57" s="72"/>
+      <c r="P57" s="73"/>
       <c r="Q57" s="31"/>
-      <c r="R57" s="62"/>
-      <c r="S57" s="63"/>
-      <c r="T57" s="64"/>
+      <c r="R57" s="71"/>
+      <c r="S57" s="72"/>
+      <c r="T57" s="73"/>
       <c r="U57" s="50"/>
-      <c r="V57" s="62" t="s">
+      <c r="V57" s="71" t="s">
         <v>37</v>
       </c>
-      <c r="W57" s="63"/>
-      <c r="X57" s="64"/>
+      <c r="W57" s="72"/>
+      <c r="X57" s="73"/>
       <c r="Y57" s="50"/>
-      <c r="Z57" s="62"/>
-      <c r="AA57" s="63"/>
-      <c r="AB57" s="64"/>
+      <c r="Z57" s="71"/>
+      <c r="AA57" s="72"/>
+      <c r="AB57" s="73"/>
       <c r="AC57" s="31"/>
-      <c r="AD57" s="62"/>
-      <c r="AE57" s="63"/>
-      <c r="AF57" s="64"/>
+      <c r="AD57" s="71"/>
+      <c r="AE57" s="72"/>
+      <c r="AF57" s="73"/>
       <c r="AG57" s="35"/>
-      <c r="AH57" s="62"/>
-      <c r="AI57" s="63"/>
-      <c r="AJ57" s="64"/>
+      <c r="AH57" s="71"/>
+      <c r="AI57" s="72"/>
+      <c r="AJ57" s="73"/>
       <c r="AK57" s="50"/>
-      <c r="AL57" s="62"/>
-      <c r="AM57" s="63"/>
-      <c r="AN57" s="64"/>
+      <c r="AL57" s="71"/>
+      <c r="AM57" s="72"/>
+      <c r="AN57" s="73"/>
       <c r="AR57" s="13"/>
     </row>
     <row r="58" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5383,255 +5432,265 @@
       <c r="AR58" s="13"/>
     </row>
     <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="65"/>
-      <c r="C59" s="66"/>
+      <c r="B59" s="63"/>
+      <c r="C59" s="64"/>
       <c r="D59" s="57"/>
       <c r="E59" s="50"/>
-      <c r="F59" s="65"/>
-      <c r="G59" s="66"/>
+      <c r="F59" s="63"/>
+      <c r="G59" s="64"/>
       <c r="H59" s="57"/>
       <c r="I59" s="32"/>
-      <c r="J59" s="65"/>
-      <c r="K59" s="66"/>
+      <c r="J59" s="63"/>
+      <c r="K59" s="64"/>
       <c r="L59" s="57"/>
       <c r="M59" s="6"/>
-      <c r="N59" s="67"/>
-      <c r="O59" s="68"/>
+      <c r="N59" s="87"/>
+      <c r="O59" s="88"/>
       <c r="P59" s="34"/>
       <c r="Q59" s="36"/>
-      <c r="R59" s="67"/>
-      <c r="S59" s="68"/>
+      <c r="R59" s="87"/>
+      <c r="S59" s="88"/>
       <c r="T59" s="34"/>
       <c r="U59" s="50"/>
-      <c r="V59" s="67"/>
-      <c r="W59" s="68"/>
+      <c r="V59" s="87"/>
+      <c r="W59" s="88"/>
       <c r="X59" s="34"/>
       <c r="Y59" s="32"/>
-      <c r="Z59" s="67"/>
-      <c r="AA59" s="68"/>
+      <c r="Z59" s="87"/>
+      <c r="AA59" s="88"/>
       <c r="AB59" s="34"/>
       <c r="AC59" s="32"/>
-      <c r="AD59" s="67"/>
-      <c r="AE59" s="68"/>
-      <c r="AF59" s="34"/>
+      <c r="AD59" s="102" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE59" s="103"/>
+      <c r="AF59" s="59" t="s">
+        <v>90</v>
+      </c>
       <c r="AG59" s="50"/>
-      <c r="AH59" s="67"/>
-      <c r="AI59" s="68"/>
+      <c r="AH59" s="87"/>
+      <c r="AI59" s="88"/>
       <c r="AJ59" s="34"/>
       <c r="AK59" s="32"/>
-      <c r="AL59" s="67"/>
-      <c r="AM59" s="68"/>
+      <c r="AL59" s="87"/>
+      <c r="AM59" s="88"/>
       <c r="AN59" s="34"/>
       <c r="AR59" s="13"/>
     </row>
     <row r="60" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="84"/>
-      <c r="C60" s="85"/>
-      <c r="D60" s="86"/>
+      <c r="B60" s="78"/>
+      <c r="C60" s="79"/>
+      <c r="D60" s="80"/>
       <c r="E60" s="32"/>
-      <c r="F60" s="84"/>
-      <c r="G60" s="85"/>
-      <c r="H60" s="86"/>
+      <c r="F60" s="78"/>
+      <c r="G60" s="79"/>
+      <c r="H60" s="80"/>
       <c r="I60" s="32"/>
-      <c r="J60" s="84"/>
-      <c r="K60" s="85"/>
-      <c r="L60" s="86"/>
+      <c r="J60" s="78"/>
+      <c r="K60" s="79"/>
+      <c r="L60" s="80"/>
       <c r="M60" s="4"/>
-      <c r="N60" s="69"/>
-      <c r="O60" s="70"/>
-      <c r="P60" s="71"/>
+      <c r="N60" s="92"/>
+      <c r="O60" s="93"/>
+      <c r="P60" s="94"/>
       <c r="Q60" s="43"/>
-      <c r="R60" s="69"/>
-      <c r="S60" s="70"/>
-      <c r="T60" s="71"/>
+      <c r="R60" s="92"/>
+      <c r="S60" s="93"/>
+      <c r="T60" s="94"/>
       <c r="U60" s="32"/>
-      <c r="V60" s="69"/>
-      <c r="W60" s="70"/>
-      <c r="X60" s="71"/>
+      <c r="V60" s="92"/>
+      <c r="W60" s="93"/>
+      <c r="X60" s="94"/>
       <c r="Y60" s="32"/>
-      <c r="Z60" s="69"/>
-      <c r="AA60" s="70"/>
-      <c r="AB60" s="71"/>
+      <c r="Z60" s="92"/>
+      <c r="AA60" s="93"/>
+      <c r="AB60" s="94"/>
       <c r="AC60" s="54"/>
-      <c r="AD60" s="69"/>
-      <c r="AE60" s="70"/>
-      <c r="AF60" s="71"/>
+      <c r="AD60" s="92" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE60" s="93"/>
+      <c r="AF60" s="94"/>
       <c r="AG60" s="32"/>
-      <c r="AH60" s="69"/>
-      <c r="AI60" s="70"/>
-      <c r="AJ60" s="71"/>
+      <c r="AH60" s="92"/>
+      <c r="AI60" s="93"/>
+      <c r="AJ60" s="94"/>
       <c r="AK60" s="32"/>
-      <c r="AL60" s="69"/>
-      <c r="AM60" s="70"/>
-      <c r="AN60" s="71"/>
+      <c r="AL60" s="92"/>
+      <c r="AM60" s="93"/>
+      <c r="AN60" s="94"/>
       <c r="AR60" s="13"/>
     </row>
     <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="90"/>
-      <c r="C61" s="91"/>
-      <c r="D61" s="92"/>
+      <c r="B61" s="68"/>
+      <c r="C61" s="69"/>
+      <c r="D61" s="70"/>
       <c r="E61" s="32"/>
-      <c r="F61" s="90"/>
-      <c r="G61" s="91"/>
-      <c r="H61" s="92"/>
+      <c r="F61" s="68"/>
+      <c r="G61" s="69"/>
+      <c r="H61" s="70"/>
       <c r="I61" s="32"/>
-      <c r="J61" s="90"/>
-      <c r="K61" s="91"/>
-      <c r="L61" s="92"/>
+      <c r="J61" s="68"/>
+      <c r="K61" s="69"/>
+      <c r="L61" s="70"/>
       <c r="M61" s="4"/>
-      <c r="N61" s="81"/>
-      <c r="O61" s="82"/>
-      <c r="P61" s="83"/>
+      <c r="N61" s="89"/>
+      <c r="O61" s="90"/>
+      <c r="P61" s="91"/>
       <c r="Q61" s="37"/>
-      <c r="R61" s="81"/>
-      <c r="S61" s="82"/>
-      <c r="T61" s="83"/>
+      <c r="R61" s="89"/>
+      <c r="S61" s="90"/>
+      <c r="T61" s="91"/>
       <c r="U61" s="32"/>
-      <c r="V61" s="81"/>
-      <c r="W61" s="82"/>
-      <c r="X61" s="83"/>
+      <c r="V61" s="89"/>
+      <c r="W61" s="90"/>
+      <c r="X61" s="91"/>
       <c r="Y61" s="32"/>
-      <c r="Z61" s="81"/>
-      <c r="AA61" s="82"/>
-      <c r="AB61" s="83"/>
+      <c r="Z61" s="89"/>
+      <c r="AA61" s="90"/>
+      <c r="AB61" s="91"/>
       <c r="AC61" s="35"/>
-      <c r="AD61" s="81"/>
-      <c r="AE61" s="82"/>
-      <c r="AF61" s="83"/>
+      <c r="AD61" s="89"/>
+      <c r="AE61" s="90"/>
+      <c r="AF61" s="91"/>
       <c r="AG61" s="32"/>
-      <c r="AH61" s="81"/>
-      <c r="AI61" s="82"/>
-      <c r="AJ61" s="83"/>
+      <c r="AH61" s="89"/>
+      <c r="AI61" s="90"/>
+      <c r="AJ61" s="91"/>
       <c r="AK61" s="32"/>
-      <c r="AL61" s="81"/>
-      <c r="AM61" s="82"/>
-      <c r="AN61" s="83"/>
+      <c r="AL61" s="89"/>
+      <c r="AM61" s="90"/>
+      <c r="AN61" s="91"/>
       <c r="AR61" s="13"/>
     </row>
     <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="87"/>
-      <c r="C62" s="88"/>
-      <c r="D62" s="89"/>
+      <c r="B62" s="81"/>
+      <c r="C62" s="82"/>
+      <c r="D62" s="83"/>
       <c r="E62" s="37"/>
-      <c r="F62" s="87"/>
-      <c r="G62" s="88"/>
-      <c r="H62" s="89"/>
+      <c r="F62" s="81"/>
+      <c r="G62" s="82"/>
+      <c r="H62" s="83"/>
       <c r="I62" s="35"/>
-      <c r="J62" s="87"/>
-      <c r="K62" s="88"/>
-      <c r="L62" s="89"/>
+      <c r="J62" s="81"/>
+      <c r="K62" s="82"/>
+      <c r="L62" s="83"/>
       <c r="M62" s="4"/>
-      <c r="N62" s="78"/>
-      <c r="O62" s="79"/>
-      <c r="P62" s="80"/>
+      <c r="N62" s="65"/>
+      <c r="O62" s="66"/>
+      <c r="P62" s="67"/>
       <c r="Q62" s="44"/>
-      <c r="R62" s="87"/>
-      <c r="S62" s="88"/>
-      <c r="T62" s="89"/>
+      <c r="R62" s="81"/>
+      <c r="S62" s="82"/>
+      <c r="T62" s="83"/>
       <c r="U62" s="37"/>
-      <c r="V62" s="87"/>
-      <c r="W62" s="88"/>
-      <c r="X62" s="89"/>
+      <c r="V62" s="81"/>
+      <c r="W62" s="82"/>
+      <c r="X62" s="83"/>
       <c r="Y62" s="35"/>
-      <c r="Z62" s="78"/>
-      <c r="AA62" s="79"/>
-      <c r="AB62" s="80"/>
+      <c r="Z62" s="65"/>
+      <c r="AA62" s="66"/>
+      <c r="AB62" s="67"/>
       <c r="AC62" s="35"/>
-      <c r="AD62" s="87"/>
-      <c r="AE62" s="88"/>
-      <c r="AF62" s="89"/>
+      <c r="AD62" s="81" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE62" s="82"/>
+      <c r="AF62" s="83"/>
       <c r="AG62" s="37"/>
-      <c r="AH62" s="78"/>
-      <c r="AI62" s="79"/>
-      <c r="AJ62" s="80"/>
+      <c r="AH62" s="65"/>
+      <c r="AI62" s="66"/>
+      <c r="AJ62" s="67"/>
       <c r="AK62" s="35"/>
-      <c r="AL62" s="87"/>
-      <c r="AM62" s="88"/>
-      <c r="AN62" s="89"/>
+      <c r="AL62" s="81"/>
+      <c r="AM62" s="82"/>
+      <c r="AN62" s="83"/>
       <c r="AR62" s="13"/>
     </row>
     <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="78"/>
-      <c r="C63" s="79"/>
-      <c r="D63" s="80"/>
+      <c r="B63" s="65"/>
+      <c r="C63" s="66"/>
+      <c r="D63" s="67"/>
       <c r="E63" s="44"/>
-      <c r="F63" s="78"/>
-      <c r="G63" s="79"/>
-      <c r="H63" s="80"/>
+      <c r="F63" s="65"/>
+      <c r="G63" s="66"/>
+      <c r="H63" s="67"/>
       <c r="I63" s="40"/>
-      <c r="J63" s="78"/>
-      <c r="K63" s="79"/>
-      <c r="L63" s="80"/>
+      <c r="J63" s="65"/>
+      <c r="K63" s="66"/>
+      <c r="L63" s="67"/>
       <c r="M63" s="5"/>
-      <c r="N63" s="78"/>
-      <c r="O63" s="79"/>
-      <c r="P63" s="80"/>
+      <c r="N63" s="65"/>
+      <c r="O63" s="66"/>
+      <c r="P63" s="67"/>
       <c r="Q63" s="44"/>
-      <c r="R63" s="78"/>
-      <c r="S63" s="79"/>
-      <c r="T63" s="80"/>
+      <c r="R63" s="65"/>
+      <c r="S63" s="66"/>
+      <c r="T63" s="67"/>
       <c r="U63" s="44"/>
-      <c r="V63" s="78"/>
-      <c r="W63" s="79"/>
-      <c r="X63" s="80"/>
+      <c r="V63" s="65"/>
+      <c r="W63" s="66"/>
+      <c r="X63" s="67"/>
       <c r="Y63" s="40"/>
-      <c r="Z63" s="78"/>
-      <c r="AA63" s="79"/>
-      <c r="AB63" s="80"/>
+      <c r="Z63" s="65"/>
+      <c r="AA63" s="66"/>
+      <c r="AB63" s="67"/>
       <c r="AC63" s="40"/>
-      <c r="AD63" s="78"/>
-      <c r="AE63" s="79"/>
-      <c r="AF63" s="80"/>
+      <c r="AD63" s="65" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE63" s="66"/>
+      <c r="AF63" s="67"/>
       <c r="AG63" s="44"/>
-      <c r="AH63" s="78"/>
-      <c r="AI63" s="79"/>
-      <c r="AJ63" s="80"/>
+      <c r="AH63" s="65"/>
+      <c r="AI63" s="66"/>
+      <c r="AJ63" s="67"/>
       <c r="AK63" s="40"/>
-      <c r="AL63" s="78"/>
-      <c r="AM63" s="79"/>
-      <c r="AN63" s="80"/>
+      <c r="AL63" s="65"/>
+      <c r="AM63" s="66"/>
+      <c r="AN63" s="67"/>
       <c r="AR63" s="13"/>
     </row>
     <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="62"/>
-      <c r="C64" s="63"/>
-      <c r="D64" s="64"/>
+      <c r="B64" s="71"/>
+      <c r="C64" s="72"/>
+      <c r="D64" s="73"/>
       <c r="E64" s="35"/>
-      <c r="F64" s="62"/>
-      <c r="G64" s="63"/>
-      <c r="H64" s="64"/>
+      <c r="F64" s="71"/>
+      <c r="G64" s="72"/>
+      <c r="H64" s="73"/>
       <c r="I64" s="50"/>
-      <c r="J64" s="62"/>
-      <c r="K64" s="63"/>
-      <c r="L64" s="64"/>
+      <c r="J64" s="71"/>
+      <c r="K64" s="72"/>
+      <c r="L64" s="73"/>
       <c r="M64" s="5"/>
-      <c r="N64" s="62"/>
-      <c r="O64" s="63"/>
-      <c r="P64" s="64"/>
+      <c r="N64" s="71"/>
+      <c r="O64" s="72"/>
+      <c r="P64" s="73"/>
       <c r="Q64" s="50"/>
-      <c r="R64" s="62"/>
-      <c r="S64" s="63"/>
-      <c r="T64" s="64"/>
+      <c r="R64" s="71"/>
+      <c r="S64" s="72"/>
+      <c r="T64" s="73"/>
       <c r="U64" s="35"/>
-      <c r="V64" s="62"/>
-      <c r="W64" s="63"/>
-      <c r="X64" s="64"/>
+      <c r="V64" s="71"/>
+      <c r="W64" s="72"/>
+      <c r="X64" s="73"/>
       <c r="Y64" s="50"/>
-      <c r="Z64" s="62"/>
-      <c r="AA64" s="63"/>
-      <c r="AB64" s="64"/>
+      <c r="Z64" s="71"/>
+      <c r="AA64" s="72"/>
+      <c r="AB64" s="73"/>
       <c r="AC64" s="50"/>
-      <c r="AD64" s="62"/>
-      <c r="AE64" s="63"/>
-      <c r="AF64" s="64"/>
+      <c r="AD64" s="71"/>
+      <c r="AE64" s="72"/>
+      <c r="AF64" s="73"/>
       <c r="AG64" s="35"/>
-      <c r="AH64" s="62"/>
-      <c r="AI64" s="63"/>
-      <c r="AJ64" s="64"/>
+      <c r="AH64" s="71"/>
+      <c r="AI64" s="72"/>
+      <c r="AJ64" s="73"/>
       <c r="AK64" s="50"/>
-      <c r="AL64" s="62"/>
-      <c r="AM64" s="63"/>
-      <c r="AN64" s="64"/>
+      <c r="AL64" s="71"/>
+      <c r="AM64" s="72"/>
+      <c r="AN64" s="73"/>
       <c r="AR64" s="13"/>
     </row>
     <row r="65" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5682,48 +5741,48 @@
     </row>
     <row r="66" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="12"/>
-      <c r="B66" s="65"/>
-      <c r="C66" s="66"/>
+      <c r="B66" s="63"/>
+      <c r="C66" s="64"/>
       <c r="D66" s="57"/>
       <c r="E66" s="36"/>
-      <c r="F66" s="65"/>
-      <c r="G66" s="66"/>
+      <c r="F66" s="63"/>
+      <c r="G66" s="64"/>
       <c r="H66" s="57"/>
       <c r="I66" s="32"/>
-      <c r="J66" s="65"/>
-      <c r="K66" s="66"/>
+      <c r="J66" s="63"/>
+      <c r="K66" s="64"/>
       <c r="L66" s="57"/>
       <c r="M66" s="6"/>
-      <c r="N66" s="67"/>
-      <c r="O66" s="68"/>
+      <c r="N66" s="87"/>
+      <c r="O66" s="88"/>
       <c r="P66" s="34"/>
       <c r="Q66" s="36"/>
-      <c r="R66" s="67"/>
-      <c r="S66" s="68"/>
+      <c r="R66" s="87"/>
+      <c r="S66" s="88"/>
       <c r="T66" s="34"/>
       <c r="U66" s="36"/>
-      <c r="V66" s="111" t="s">
+      <c r="V66" s="102" t="s">
         <v>99</v>
       </c>
-      <c r="W66" s="112"/>
+      <c r="W66" s="103"/>
       <c r="X66" s="59"/>
       <c r="Y66" s="36"/>
-      <c r="Z66" s="111" t="s">
+      <c r="Z66" s="102" t="s">
         <v>99</v>
       </c>
-      <c r="AA66" s="112"/>
+      <c r="AA66" s="103"/>
       <c r="AB66" s="59"/>
       <c r="AC66" s="36"/>
-      <c r="AD66" s="67"/>
-      <c r="AE66" s="68"/>
+      <c r="AD66" s="87"/>
+      <c r="AE66" s="88"/>
       <c r="AF66" s="34"/>
       <c r="AG66" s="36"/>
-      <c r="AH66" s="67"/>
-      <c r="AI66" s="68"/>
+      <c r="AH66" s="87"/>
+      <c r="AI66" s="88"/>
       <c r="AJ66" s="34"/>
       <c r="AK66" s="32"/>
-      <c r="AL66" s="67"/>
-      <c r="AM66" s="68"/>
+      <c r="AL66" s="87"/>
+      <c r="AM66" s="88"/>
       <c r="AN66" s="34"/>
       <c r="AO66" s="17"/>
       <c r="AP66" s="12"/>
@@ -5732,49 +5791,49 @@
     </row>
     <row r="67" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="12"/>
-      <c r="B67" s="84"/>
-      <c r="C67" s="85"/>
-      <c r="D67" s="86"/>
+      <c r="B67" s="78"/>
+      <c r="C67" s="79"/>
+      <c r="D67" s="80"/>
       <c r="E67" s="36"/>
-      <c r="F67" s="84"/>
-      <c r="G67" s="85"/>
-      <c r="H67" s="86"/>
+      <c r="F67" s="78"/>
+      <c r="G67" s="79"/>
+      <c r="H67" s="80"/>
       <c r="I67" s="54"/>
-      <c r="J67" s="84"/>
-      <c r="K67" s="85"/>
-      <c r="L67" s="86"/>
+      <c r="J67" s="78"/>
+      <c r="K67" s="79"/>
+      <c r="L67" s="80"/>
       <c r="M67" s="4"/>
-      <c r="N67" s="69"/>
-      <c r="O67" s="70"/>
-      <c r="P67" s="71"/>
+      <c r="N67" s="92"/>
+      <c r="O67" s="93"/>
+      <c r="P67" s="94"/>
       <c r="Q67" s="37"/>
-      <c r="R67" s="69"/>
-      <c r="S67" s="70"/>
-      <c r="T67" s="71"/>
+      <c r="R67" s="92"/>
+      <c r="S67" s="93"/>
+      <c r="T67" s="94"/>
       <c r="U67" s="36"/>
-      <c r="V67" s="69" t="s">
+      <c r="V67" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="W67" s="70"/>
-      <c r="X67" s="71"/>
+      <c r="W67" s="93"/>
+      <c r="X67" s="94"/>
       <c r="Y67" s="36"/>
-      <c r="Z67" s="69" t="s">
+      <c r="Z67" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="AA67" s="70"/>
-      <c r="AB67" s="71"/>
+      <c r="AA67" s="93"/>
+      <c r="AB67" s="94"/>
       <c r="AC67" s="36"/>
-      <c r="AD67" s="69"/>
-      <c r="AE67" s="70"/>
-      <c r="AF67" s="71"/>
+      <c r="AD67" s="92"/>
+      <c r="AE67" s="93"/>
+      <c r="AF67" s="94"/>
       <c r="AG67" s="36"/>
-      <c r="AH67" s="69"/>
-      <c r="AI67" s="70"/>
-      <c r="AJ67" s="71"/>
+      <c r="AH67" s="92"/>
+      <c r="AI67" s="93"/>
+      <c r="AJ67" s="94"/>
       <c r="AK67" s="54"/>
-      <c r="AL67" s="69"/>
-      <c r="AM67" s="70"/>
-      <c r="AN67" s="71"/>
+      <c r="AL67" s="92"/>
+      <c r="AM67" s="93"/>
+      <c r="AN67" s="94"/>
       <c r="AO67" s="17"/>
       <c r="AP67" s="12"/>
       <c r="AQ67" s="12"/>
@@ -5782,45 +5841,45 @@
     </row>
     <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="12"/>
-      <c r="B68" s="90"/>
-      <c r="C68" s="91"/>
-      <c r="D68" s="92"/>
+      <c r="B68" s="68"/>
+      <c r="C68" s="69"/>
+      <c r="D68" s="70"/>
       <c r="E68" s="43"/>
-      <c r="F68" s="90"/>
-      <c r="G68" s="91"/>
-      <c r="H68" s="92"/>
+      <c r="F68" s="68"/>
+      <c r="G68" s="69"/>
+      <c r="H68" s="70"/>
       <c r="I68" s="35"/>
-      <c r="J68" s="90"/>
-      <c r="K68" s="91"/>
-      <c r="L68" s="92"/>
+      <c r="J68" s="68"/>
+      <c r="K68" s="69"/>
+      <c r="L68" s="70"/>
       <c r="M68" s="4"/>
-      <c r="N68" s="81"/>
-      <c r="O68" s="82"/>
-      <c r="P68" s="83"/>
+      <c r="N68" s="89"/>
+      <c r="O68" s="90"/>
+      <c r="P68" s="91"/>
       <c r="Q68" s="36"/>
-      <c r="R68" s="81"/>
-      <c r="S68" s="82"/>
-      <c r="T68" s="83"/>
+      <c r="R68" s="89"/>
+      <c r="S68" s="90"/>
+      <c r="T68" s="91"/>
       <c r="U68" s="43"/>
-      <c r="V68" s="81"/>
-      <c r="W68" s="82"/>
-      <c r="X68" s="83"/>
+      <c r="V68" s="89"/>
+      <c r="W68" s="90"/>
+      <c r="X68" s="91"/>
       <c r="Y68" s="43"/>
-      <c r="Z68" s="81"/>
-      <c r="AA68" s="82"/>
-      <c r="AB68" s="83"/>
+      <c r="Z68" s="89"/>
+      <c r="AA68" s="90"/>
+      <c r="AB68" s="91"/>
       <c r="AC68" s="35"/>
-      <c r="AD68" s="81"/>
-      <c r="AE68" s="82"/>
-      <c r="AF68" s="83"/>
+      <c r="AD68" s="89"/>
+      <c r="AE68" s="90"/>
+      <c r="AF68" s="91"/>
       <c r="AG68" s="43"/>
-      <c r="AH68" s="81"/>
-      <c r="AI68" s="82"/>
-      <c r="AJ68" s="83"/>
+      <c r="AH68" s="89"/>
+      <c r="AI68" s="90"/>
+      <c r="AJ68" s="91"/>
       <c r="AK68" s="35"/>
-      <c r="AL68" s="81"/>
-      <c r="AM68" s="82"/>
-      <c r="AN68" s="83"/>
+      <c r="AL68" s="89"/>
+      <c r="AM68" s="90"/>
+      <c r="AN68" s="91"/>
       <c r="AO68" s="17"/>
       <c r="AP68" s="27" t="s">
         <v>32</v>
@@ -5830,49 +5889,49 @@
     </row>
     <row r="69" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="12"/>
-      <c r="B69" s="78"/>
-      <c r="C69" s="79"/>
-      <c r="D69" s="80"/>
+      <c r="B69" s="65"/>
+      <c r="C69" s="66"/>
+      <c r="D69" s="67"/>
       <c r="E69" s="37"/>
-      <c r="F69" s="78"/>
-      <c r="G69" s="79"/>
-      <c r="H69" s="80"/>
+      <c r="F69" s="65"/>
+      <c r="G69" s="66"/>
+      <c r="H69" s="67"/>
       <c r="I69" s="37"/>
-      <c r="J69" s="78"/>
-      <c r="K69" s="79"/>
-      <c r="L69" s="80"/>
+      <c r="J69" s="65"/>
+      <c r="K69" s="66"/>
+      <c r="L69" s="67"/>
       <c r="M69" s="4"/>
-      <c r="N69" s="78"/>
-      <c r="O69" s="79"/>
-      <c r="P69" s="80"/>
+      <c r="N69" s="65"/>
+      <c r="O69" s="66"/>
+      <c r="P69" s="67"/>
       <c r="Q69" s="43"/>
-      <c r="R69" s="78"/>
-      <c r="S69" s="79"/>
-      <c r="T69" s="80"/>
+      <c r="R69" s="65"/>
+      <c r="S69" s="66"/>
+      <c r="T69" s="67"/>
       <c r="U69" s="37"/>
-      <c r="V69" s="78" t="s">
+      <c r="V69" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="W69" s="79"/>
-      <c r="X69" s="80"/>
+      <c r="W69" s="66"/>
+      <c r="X69" s="67"/>
       <c r="Y69" s="35"/>
-      <c r="Z69" s="78" t="s">
+      <c r="Z69" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="AA69" s="79"/>
-      <c r="AB69" s="80"/>
+      <c r="AA69" s="66"/>
+      <c r="AB69" s="67"/>
       <c r="AC69" s="43"/>
-      <c r="AD69" s="78"/>
-      <c r="AE69" s="79"/>
-      <c r="AF69" s="80"/>
+      <c r="AD69" s="65"/>
+      <c r="AE69" s="66"/>
+      <c r="AF69" s="67"/>
       <c r="AG69" s="37"/>
-      <c r="AH69" s="87"/>
-      <c r="AI69" s="88"/>
-      <c r="AJ69" s="89"/>
+      <c r="AH69" s="81"/>
+      <c r="AI69" s="82"/>
+      <c r="AJ69" s="83"/>
       <c r="AK69" s="37"/>
-      <c r="AL69" s="78"/>
-      <c r="AM69" s="79"/>
-      <c r="AN69" s="80"/>
+      <c r="AL69" s="65"/>
+      <c r="AM69" s="66"/>
+      <c r="AN69" s="67"/>
       <c r="AO69" s="12"/>
       <c r="AP69" s="27" t="s">
         <v>33</v>
@@ -5882,49 +5941,49 @@
     </row>
     <row r="70" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="12"/>
-      <c r="B70" s="78"/>
-      <c r="C70" s="79"/>
-      <c r="D70" s="80"/>
+      <c r="B70" s="65"/>
+      <c r="C70" s="66"/>
+      <c r="D70" s="67"/>
       <c r="E70" s="44"/>
-      <c r="F70" s="78"/>
-      <c r="G70" s="79"/>
-      <c r="H70" s="80"/>
+      <c r="F70" s="65"/>
+      <c r="G70" s="66"/>
+      <c r="H70" s="67"/>
       <c r="I70" s="44"/>
-      <c r="J70" s="78"/>
-      <c r="K70" s="79"/>
-      <c r="L70" s="80"/>
+      <c r="J70" s="65"/>
+      <c r="K70" s="66"/>
+      <c r="L70" s="67"/>
       <c r="M70" s="9"/>
-      <c r="N70" s="78"/>
-      <c r="O70" s="79"/>
-      <c r="P70" s="80"/>
+      <c r="N70" s="65"/>
+      <c r="O70" s="66"/>
+      <c r="P70" s="67"/>
       <c r="Q70" s="50"/>
-      <c r="R70" s="78"/>
-      <c r="S70" s="79"/>
-      <c r="T70" s="80"/>
+      <c r="R70" s="65"/>
+      <c r="S70" s="66"/>
+      <c r="T70" s="67"/>
       <c r="U70" s="44"/>
-      <c r="V70" s="78" t="s">
+      <c r="V70" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="W70" s="79"/>
-      <c r="X70" s="80"/>
+      <c r="W70" s="66"/>
+      <c r="X70" s="67"/>
       <c r="Y70" s="40"/>
-      <c r="Z70" s="78" t="s">
+      <c r="Z70" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="AA70" s="79"/>
-      <c r="AB70" s="80"/>
+      <c r="AA70" s="66"/>
+      <c r="AB70" s="67"/>
       <c r="AC70" s="44"/>
-      <c r="AD70" s="78"/>
-      <c r="AE70" s="79"/>
-      <c r="AF70" s="80"/>
+      <c r="AD70" s="65"/>
+      <c r="AE70" s="66"/>
+      <c r="AF70" s="67"/>
       <c r="AG70" s="44"/>
-      <c r="AH70" s="78"/>
-      <c r="AI70" s="79"/>
-      <c r="AJ70" s="80"/>
+      <c r="AH70" s="65"/>
+      <c r="AI70" s="66"/>
+      <c r="AJ70" s="67"/>
       <c r="AK70" s="44"/>
-      <c r="AL70" s="78"/>
-      <c r="AM70" s="79"/>
-      <c r="AN70" s="80"/>
+      <c r="AL70" s="65"/>
+      <c r="AM70" s="66"/>
+      <c r="AN70" s="67"/>
       <c r="AO70" s="12"/>
       <c r="AP70" s="27" t="s">
         <v>34</v>
@@ -5934,47 +5993,47 @@
     </row>
     <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A71" s="12"/>
-      <c r="B71" s="62"/>
-      <c r="C71" s="63"/>
-      <c r="D71" s="64"/>
+      <c r="B71" s="71"/>
+      <c r="C71" s="72"/>
+      <c r="D71" s="73"/>
       <c r="E71" s="44"/>
-      <c r="F71" s="62"/>
-      <c r="G71" s="63"/>
-      <c r="H71" s="64"/>
+      <c r="F71" s="71"/>
+      <c r="G71" s="72"/>
+      <c r="H71" s="73"/>
       <c r="I71" s="44"/>
-      <c r="J71" s="62"/>
-      <c r="K71" s="63"/>
-      <c r="L71" s="64"/>
+      <c r="J71" s="71"/>
+      <c r="K71" s="72"/>
+      <c r="L71" s="73"/>
       <c r="M71" s="9"/>
-      <c r="N71" s="62"/>
-      <c r="O71" s="63"/>
-      <c r="P71" s="64"/>
+      <c r="N71" s="71"/>
+      <c r="O71" s="72"/>
+      <c r="P71" s="73"/>
       <c r="Q71" s="50"/>
-      <c r="R71" s="62"/>
-      <c r="S71" s="63"/>
-      <c r="T71" s="64"/>
+      <c r="R71" s="71"/>
+      <c r="S71" s="72"/>
+      <c r="T71" s="73"/>
       <c r="U71" s="44"/>
-      <c r="V71" s="62" t="s">
+      <c r="V71" s="71" t="s">
         <v>26</v>
       </c>
-      <c r="W71" s="63"/>
-      <c r="X71" s="64"/>
+      <c r="W71" s="72"/>
+      <c r="X71" s="73"/>
       <c r="Y71" s="44"/>
-      <c r="Z71" s="62"/>
-      <c r="AA71" s="63"/>
-      <c r="AB71" s="64"/>
+      <c r="Z71" s="71"/>
+      <c r="AA71" s="72"/>
+      <c r="AB71" s="73"/>
       <c r="AC71" s="50"/>
-      <c r="AD71" s="62"/>
-      <c r="AE71" s="63"/>
-      <c r="AF71" s="64"/>
+      <c r="AD71" s="71"/>
+      <c r="AE71" s="72"/>
+      <c r="AF71" s="73"/>
       <c r="AG71" s="44"/>
-      <c r="AH71" s="62"/>
-      <c r="AI71" s="63"/>
-      <c r="AJ71" s="64"/>
+      <c r="AH71" s="71"/>
+      <c r="AI71" s="72"/>
+      <c r="AJ71" s="73"/>
       <c r="AK71" s="44"/>
-      <c r="AL71" s="62"/>
-      <c r="AM71" s="63"/>
-      <c r="AN71" s="64"/>
+      <c r="AL71" s="71"/>
+      <c r="AM71" s="72"/>
+      <c r="AN71" s="73"/>
       <c r="AO71" s="12"/>
       <c r="AP71" s="27" t="s">
         <v>35</v>
@@ -6042,23 +6101,23 @@
       <c r="K73" s="33"/>
       <c r="L73" s="33"/>
       <c r="M73" s="14"/>
-      <c r="N73" s="110" t="s">
+      <c r="N73" s="99" t="s">
         <v>31</v>
       </c>
-      <c r="O73" s="110"/>
-      <c r="P73" s="110"/>
-      <c r="Q73" s="110"/>
-      <c r="R73" s="110"/>
-      <c r="S73" s="110"/>
-      <c r="T73" s="110"/>
-      <c r="U73" s="110"/>
-      <c r="V73" s="110"/>
-      <c r="W73" s="110"/>
-      <c r="X73" s="110"/>
-      <c r="Y73" s="110"/>
-      <c r="Z73" s="110"/>
-      <c r="AA73" s="110"/>
-      <c r="AB73" s="110"/>
+      <c r="O73" s="99"/>
+      <c r="P73" s="99"/>
+      <c r="Q73" s="99"/>
+      <c r="R73" s="99"/>
+      <c r="S73" s="99"/>
+      <c r="T73" s="99"/>
+      <c r="U73" s="99"/>
+      <c r="V73" s="99"/>
+      <c r="W73" s="99"/>
+      <c r="X73" s="99"/>
+      <c r="Y73" s="99"/>
+      <c r="Z73" s="99"/>
+      <c r="AA73" s="99"/>
+      <c r="AB73" s="99"/>
       <c r="AD73" s="40"/>
       <c r="AE73" s="33"/>
       <c r="AF73" s="33"/>
@@ -6089,21 +6148,21 @@
       <c r="K74" s="33"/>
       <c r="L74" s="33"/>
       <c r="M74" s="14"/>
-      <c r="N74" s="110"/>
-      <c r="O74" s="110"/>
-      <c r="P74" s="110"/>
-      <c r="Q74" s="110"/>
-      <c r="R74" s="110"/>
-      <c r="S74" s="110"/>
-      <c r="T74" s="110"/>
-      <c r="U74" s="110"/>
-      <c r="V74" s="110"/>
-      <c r="W74" s="110"/>
-      <c r="X74" s="110"/>
-      <c r="Y74" s="110"/>
-      <c r="Z74" s="110"/>
-      <c r="AA74" s="110"/>
-      <c r="AB74" s="110"/>
+      <c r="N74" s="99"/>
+      <c r="O74" s="99"/>
+      <c r="P74" s="99"/>
+      <c r="Q74" s="99"/>
+      <c r="R74" s="99"/>
+      <c r="S74" s="99"/>
+      <c r="T74" s="99"/>
+      <c r="U74" s="99"/>
+      <c r="V74" s="99"/>
+      <c r="W74" s="99"/>
+      <c r="X74" s="99"/>
+      <c r="Y74" s="99"/>
+      <c r="Z74" s="99"/>
+      <c r="AA74" s="99"/>
+      <c r="AB74" s="99"/>
       <c r="AC74" s="21"/>
       <c r="AD74" s="33"/>
       <c r="AE74" s="33"/>
@@ -6123,68 +6182,68 @@
     </row>
     <row r="75" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="12"/>
-      <c r="B75" s="99" t="s">
+      <c r="B75" s="136" t="s">
         <v>58</v>
       </c>
-      <c r="C75" s="100"/>
+      <c r="C75" s="137"/>
       <c r="D75" s="60"/>
       <c r="E75" s="32"/>
-      <c r="F75" s="99" t="s">
+      <c r="F75" s="136" t="s">
         <v>52</v>
       </c>
-      <c r="G75" s="100"/>
+      <c r="G75" s="137"/>
       <c r="H75" s="60"/>
       <c r="I75" s="32"/>
-      <c r="J75" s="65"/>
-      <c r="K75" s="66"/>
+      <c r="J75" s="63"/>
+      <c r="K75" s="64"/>
       <c r="L75" s="57"/>
       <c r="M75" s="14"/>
-      <c r="N75" s="67"/>
-      <c r="O75" s="68"/>
+      <c r="N75" s="87"/>
+      <c r="O75" s="88"/>
       <c r="P75" s="34"/>
       <c r="Q75" s="44"/>
-      <c r="R75" s="67" t="s">
+      <c r="R75" s="87" t="s">
         <v>78</v>
       </c>
-      <c r="S75" s="68"/>
+      <c r="S75" s="88"/>
       <c r="T75" s="34" t="s">
         <v>64</v>
       </c>
       <c r="U75" s="36"/>
-      <c r="V75" s="67" t="s">
+      <c r="V75" s="87" t="s">
         <v>78</v>
       </c>
-      <c r="W75" s="68"/>
+      <c r="W75" s="88"/>
       <c r="X75" s="34" t="s">
         <v>64</v>
       </c>
       <c r="Y75" s="32"/>
-      <c r="Z75" s="67" t="s">
+      <c r="Z75" s="87" t="s">
         <v>78</v>
       </c>
-      <c r="AA75" s="68"/>
+      <c r="AA75" s="88"/>
       <c r="AB75" s="34" t="s">
         <v>64</v>
       </c>
       <c r="AC75" s="32"/>
-      <c r="AD75" s="67" t="s">
+      <c r="AD75" s="87" t="s">
         <v>78</v>
       </c>
-      <c r="AE75" s="68"/>
+      <c r="AE75" s="88"/>
       <c r="AF75" s="34" t="s">
         <v>64</v>
       </c>
       <c r="AG75" s="32"/>
-      <c r="AH75" s="67" t="s">
+      <c r="AH75" s="87" t="s">
         <v>78</v>
       </c>
-      <c r="AI75" s="68"/>
+      <c r="AI75" s="88"/>
       <c r="AJ75" s="34" t="s">
         <v>64</v>
       </c>
       <c r="AK75" s="32"/>
-      <c r="AL75" s="67"/>
-      <c r="AM75" s="68"/>
+      <c r="AL75" s="87"/>
+      <c r="AM75" s="88"/>
       <c r="AN75" s="34"/>
       <c r="AO75" s="16"/>
       <c r="AP75" s="29"/>
@@ -6193,59 +6252,59 @@
     </row>
     <row r="76" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="12"/>
-      <c r="B76" s="93" t="s">
+      <c r="B76" s="144" t="s">
         <v>92</v>
       </c>
-      <c r="C76" s="94"/>
-      <c r="D76" s="95"/>
+      <c r="C76" s="145"/>
+      <c r="D76" s="146"/>
       <c r="E76" s="32"/>
-      <c r="F76" s="93" t="s">
+      <c r="F76" s="144" t="s">
         <v>92</v>
       </c>
-      <c r="G76" s="94"/>
-      <c r="H76" s="95"/>
+      <c r="G76" s="145"/>
+      <c r="H76" s="146"/>
       <c r="I76" s="32"/>
-      <c r="J76" s="84"/>
-      <c r="K76" s="85"/>
-      <c r="L76" s="86"/>
+      <c r="J76" s="78"/>
+      <c r="K76" s="79"/>
+      <c r="L76" s="80"/>
       <c r="M76" s="4"/>
-      <c r="N76" s="69"/>
-      <c r="O76" s="70"/>
-      <c r="P76" s="71"/>
+      <c r="N76" s="92"/>
+      <c r="O76" s="93"/>
+      <c r="P76" s="94"/>
       <c r="Q76" s="44"/>
-      <c r="R76" s="69" t="s">
+      <c r="R76" s="92" t="s">
         <v>79</v>
       </c>
-      <c r="S76" s="70"/>
-      <c r="T76" s="71"/>
+      <c r="S76" s="93"/>
+      <c r="T76" s="94"/>
       <c r="U76" s="32"/>
-      <c r="V76" s="69" t="s">
+      <c r="V76" s="92" t="s">
         <v>79</v>
       </c>
-      <c r="W76" s="70"/>
-      <c r="X76" s="71"/>
+      <c r="W76" s="93"/>
+      <c r="X76" s="94"/>
       <c r="Y76" s="32"/>
-      <c r="Z76" s="69" t="s">
+      <c r="Z76" s="92" t="s">
         <v>79</v>
       </c>
-      <c r="AA76" s="70"/>
-      <c r="AB76" s="71"/>
+      <c r="AA76" s="93"/>
+      <c r="AB76" s="94"/>
       <c r="AC76" s="35"/>
-      <c r="AD76" s="69" t="s">
+      <c r="AD76" s="92" t="s">
         <v>79</v>
       </c>
-      <c r="AE76" s="70"/>
-      <c r="AF76" s="71"/>
+      <c r="AE76" s="93"/>
+      <c r="AF76" s="94"/>
       <c r="AG76" s="32"/>
-      <c r="AH76" s="69" t="s">
+      <c r="AH76" s="92" t="s">
         <v>79</v>
       </c>
-      <c r="AI76" s="70"/>
-      <c r="AJ76" s="71"/>
+      <c r="AI76" s="93"/>
+      <c r="AJ76" s="94"/>
       <c r="AK76" s="32"/>
-      <c r="AL76" s="69"/>
-      <c r="AM76" s="70"/>
-      <c r="AN76" s="71"/>
+      <c r="AL76" s="92"/>
+      <c r="AM76" s="93"/>
+      <c r="AN76" s="94"/>
       <c r="AO76" s="12"/>
       <c r="AP76" s="29"/>
       <c r="AQ76" s="26"/>
@@ -6253,49 +6312,49 @@
     </row>
     <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="16"/>
-      <c r="B77" s="96" t="s">
+      <c r="B77" s="138" t="s">
         <v>60</v>
       </c>
-      <c r="C77" s="97"/>
-      <c r="D77" s="98"/>
+      <c r="C77" s="139"/>
+      <c r="D77" s="140"/>
       <c r="E77" s="32"/>
-      <c r="F77" s="96" t="s">
+      <c r="F77" s="138" t="s">
         <v>60</v>
       </c>
-      <c r="G77" s="97"/>
-      <c r="H77" s="98"/>
+      <c r="G77" s="139"/>
+      <c r="H77" s="140"/>
       <c r="I77" s="32"/>
-      <c r="J77" s="90"/>
-      <c r="K77" s="91"/>
-      <c r="L77" s="92"/>
+      <c r="J77" s="68"/>
+      <c r="K77" s="69"/>
+      <c r="L77" s="70"/>
       <c r="M77" s="4"/>
-      <c r="N77" s="81"/>
-      <c r="O77" s="82"/>
-      <c r="P77" s="83"/>
+      <c r="N77" s="89"/>
+      <c r="O77" s="90"/>
+      <c r="P77" s="91"/>
       <c r="Q77" s="44"/>
-      <c r="R77" s="81"/>
-      <c r="S77" s="82"/>
-      <c r="T77" s="83"/>
+      <c r="R77" s="89"/>
+      <c r="S77" s="90"/>
+      <c r="T77" s="91"/>
       <c r="U77" s="31"/>
-      <c r="V77" s="81"/>
-      <c r="W77" s="82"/>
-      <c r="X77" s="83"/>
+      <c r="V77" s="89"/>
+      <c r="W77" s="90"/>
+      <c r="X77" s="91"/>
       <c r="Y77" s="32"/>
-      <c r="Z77" s="81"/>
-      <c r="AA77" s="82"/>
-      <c r="AB77" s="83"/>
+      <c r="Z77" s="89"/>
+      <c r="AA77" s="90"/>
+      <c r="AB77" s="91"/>
       <c r="AC77" s="31"/>
-      <c r="AD77" s="81"/>
-      <c r="AE77" s="82"/>
-      <c r="AF77" s="83"/>
+      <c r="AD77" s="89"/>
+      <c r="AE77" s="90"/>
+      <c r="AF77" s="91"/>
       <c r="AG77" s="32"/>
-      <c r="AH77" s="81"/>
-      <c r="AI77" s="82"/>
-      <c r="AJ77" s="83"/>
+      <c r="AH77" s="89"/>
+      <c r="AI77" s="90"/>
+      <c r="AJ77" s="91"/>
       <c r="AK77" s="32"/>
-      <c r="AL77" s="81"/>
-      <c r="AM77" s="82"/>
-      <c r="AN77" s="83"/>
+      <c r="AL77" s="89"/>
+      <c r="AM77" s="90"/>
+      <c r="AN77" s="91"/>
       <c r="AO77" s="12"/>
       <c r="AP77" s="29"/>
       <c r="AQ77" s="26"/>
@@ -6303,59 +6362,59 @@
     </row>
     <row r="78" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="16"/>
-      <c r="B78" s="75" t="s">
+      <c r="B78" s="125" t="s">
         <v>93</v>
       </c>
-      <c r="C78" s="76"/>
-      <c r="D78" s="77"/>
+      <c r="C78" s="126"/>
+      <c r="D78" s="127"/>
       <c r="E78" s="32"/>
-      <c r="F78" s="75" t="s">
+      <c r="F78" s="125" t="s">
         <v>93</v>
       </c>
-      <c r="G78" s="76"/>
-      <c r="H78" s="77"/>
+      <c r="G78" s="126"/>
+      <c r="H78" s="127"/>
       <c r="I78" s="43"/>
-      <c r="J78" s="87"/>
-      <c r="K78" s="88"/>
-      <c r="L78" s="89"/>
+      <c r="J78" s="81"/>
+      <c r="K78" s="82"/>
+      <c r="L78" s="83"/>
       <c r="M78" s="5"/>
-      <c r="N78" s="87"/>
-      <c r="O78" s="88"/>
-      <c r="P78" s="89"/>
+      <c r="N78" s="81"/>
+      <c r="O78" s="82"/>
+      <c r="P78" s="83"/>
       <c r="Q78" s="44"/>
-      <c r="R78" s="87" t="s">
+      <c r="R78" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="S78" s="88"/>
-      <c r="T78" s="89"/>
+      <c r="S78" s="82"/>
+      <c r="T78" s="83"/>
       <c r="U78" s="32"/>
-      <c r="V78" s="87" t="s">
+      <c r="V78" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="W78" s="88"/>
-      <c r="X78" s="89"/>
+      <c r="W78" s="82"/>
+      <c r="X78" s="83"/>
       <c r="Y78" s="32"/>
-      <c r="Z78" s="87" t="s">
+      <c r="Z78" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="AA78" s="88"/>
-      <c r="AB78" s="89"/>
+      <c r="AA78" s="82"/>
+      <c r="AB78" s="83"/>
       <c r="AC78" s="32"/>
-      <c r="AD78" s="87" t="s">
+      <c r="AD78" s="81" t="s">
         <v>29</v>
       </c>
-      <c r="AE78" s="88"/>
-      <c r="AF78" s="89"/>
+      <c r="AE78" s="82"/>
+      <c r="AF78" s="83"/>
       <c r="AG78" s="32"/>
-      <c r="AH78" s="87" t="s">
+      <c r="AH78" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="AI78" s="88"/>
-      <c r="AJ78" s="89"/>
+      <c r="AI78" s="82"/>
+      <c r="AJ78" s="83"/>
       <c r="AK78" s="43"/>
-      <c r="AL78" s="87"/>
-      <c r="AM78" s="88"/>
-      <c r="AN78" s="89"/>
+      <c r="AL78" s="81"/>
+      <c r="AM78" s="82"/>
+      <c r="AN78" s="83"/>
       <c r="AO78" s="12"/>
       <c r="AP78" s="29"/>
       <c r="AQ78" s="26"/>
@@ -6363,49 +6422,49 @@
     </row>
     <row r="79" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A79" s="16"/>
-      <c r="B79" s="72"/>
-      <c r="C79" s="73"/>
-      <c r="D79" s="74"/>
+      <c r="B79" s="128"/>
+      <c r="C79" s="129"/>
+      <c r="D79" s="130"/>
       <c r="E79" s="31"/>
-      <c r="F79" s="72"/>
-      <c r="G79" s="73"/>
-      <c r="H79" s="74"/>
+      <c r="F79" s="128"/>
+      <c r="G79" s="129"/>
+      <c r="H79" s="130"/>
       <c r="I79" s="32"/>
-      <c r="J79" s="62"/>
-      <c r="K79" s="63"/>
-      <c r="L79" s="64"/>
+      <c r="J79" s="71"/>
+      <c r="K79" s="72"/>
+      <c r="L79" s="73"/>
       <c r="M79" s="5"/>
-      <c r="N79" s="62"/>
-      <c r="O79" s="63"/>
-      <c r="P79" s="64"/>
+      <c r="N79" s="71"/>
+      <c r="O79" s="72"/>
+      <c r="P79" s="73"/>
       <c r="Q79" s="31"/>
-      <c r="R79" s="62" t="s">
+      <c r="R79" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="S79" s="63"/>
-      <c r="T79" s="64"/>
+      <c r="S79" s="72"/>
+      <c r="T79" s="73"/>
       <c r="U79" s="32"/>
-      <c r="V79" s="62" t="s">
+      <c r="V79" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="W79" s="63"/>
-      <c r="X79" s="64"/>
+      <c r="W79" s="72"/>
+      <c r="X79" s="73"/>
       <c r="Y79" s="32"/>
-      <c r="Z79" s="62"/>
-      <c r="AA79" s="63"/>
-      <c r="AB79" s="64"/>
+      <c r="Z79" s="71"/>
+      <c r="AA79" s="72"/>
+      <c r="AB79" s="73"/>
       <c r="AC79" s="32"/>
-      <c r="AD79" s="62"/>
-      <c r="AE79" s="63"/>
-      <c r="AF79" s="64"/>
+      <c r="AD79" s="71"/>
+      <c r="AE79" s="72"/>
+      <c r="AF79" s="73"/>
       <c r="AG79" s="31"/>
-      <c r="AH79" s="62"/>
-      <c r="AI79" s="63"/>
-      <c r="AJ79" s="64"/>
+      <c r="AH79" s="71"/>
+      <c r="AI79" s="72"/>
+      <c r="AJ79" s="73"/>
       <c r="AK79" s="32"/>
-      <c r="AL79" s="62"/>
-      <c r="AM79" s="63"/>
-      <c r="AN79" s="64"/>
+      <c r="AL79" s="71"/>
+      <c r="AM79" s="72"/>
+      <c r="AN79" s="73"/>
       <c r="AO79" s="12"/>
       <c r="AP79" s="29"/>
       <c r="AQ79" s="26"/>
@@ -6459,64 +6518,64 @@
     </row>
     <row r="81" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="12"/>
-      <c r="B81" s="65" t="s">
+      <c r="B81" s="63" t="s">
         <v>70</v>
       </c>
-      <c r="C81" s="66"/>
+      <c r="C81" s="64"/>
       <c r="D81" s="57"/>
       <c r="E81" s="32"/>
-      <c r="F81" s="65" t="s">
+      <c r="F81" s="63" t="s">
         <v>70</v>
       </c>
-      <c r="G81" s="66"/>
+      <c r="G81" s="64"/>
       <c r="H81" s="57"/>
       <c r="I81" s="50"/>
-      <c r="J81" s="65" t="s">
+      <c r="J81" s="63" t="s">
         <v>70</v>
       </c>
-      <c r="K81" s="66"/>
+      <c r="K81" s="64"/>
       <c r="L81" s="57"/>
       <c r="M81" s="5"/>
-      <c r="N81" s="67" t="s">
+      <c r="N81" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="O81" s="68"/>
+      <c r="O81" s="88"/>
       <c r="P81" s="34"/>
       <c r="Q81" s="32"/>
-      <c r="R81" s="67" t="s">
+      <c r="R81" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="S81" s="68"/>
+      <c r="S81" s="88"/>
       <c r="T81" s="34"/>
       <c r="U81" s="36"/>
-      <c r="V81" s="67" t="s">
+      <c r="V81" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="W81" s="68"/>
+      <c r="W81" s="88"/>
       <c r="X81" s="34"/>
       <c r="Y81" s="32"/>
-      <c r="Z81" s="67" t="s">
+      <c r="Z81" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="AA81" s="68"/>
+      <c r="AA81" s="88"/>
       <c r="AB81" s="34"/>
       <c r="AC81" s="32"/>
-      <c r="AD81" s="67" t="s">
+      <c r="AD81" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="AE81" s="68"/>
+      <c r="AE81" s="88"/>
       <c r="AF81" s="34"/>
       <c r="AG81" s="32"/>
-      <c r="AH81" s="67" t="s">
+      <c r="AH81" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="AI81" s="68"/>
+      <c r="AI81" s="88"/>
       <c r="AJ81" s="34"/>
       <c r="AK81" s="50"/>
-      <c r="AL81" s="67" t="s">
+      <c r="AL81" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="AM81" s="68"/>
+      <c r="AM81" s="88"/>
       <c r="AN81" s="34"/>
       <c r="AO81" s="12"/>
       <c r="AP81" s="29"/>
@@ -6525,65 +6584,65 @@
     </row>
     <row r="82" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="12"/>
-      <c r="B82" s="84" t="s">
+      <c r="B82" s="78" t="s">
         <v>65</v>
       </c>
-      <c r="C82" s="85"/>
-      <c r="D82" s="86"/>
+      <c r="C82" s="79"/>
+      <c r="D82" s="80"/>
       <c r="E82" s="32"/>
-      <c r="F82" s="84" t="s">
+      <c r="F82" s="78" t="s">
         <v>65</v>
       </c>
-      <c r="G82" s="85"/>
-      <c r="H82" s="86"/>
+      <c r="G82" s="79"/>
+      <c r="H82" s="80"/>
       <c r="I82" s="36"/>
-      <c r="J82" s="84" t="s">
+      <c r="J82" s="78" t="s">
         <v>65</v>
       </c>
-      <c r="K82" s="85"/>
-      <c r="L82" s="86"/>
+      <c r="K82" s="79"/>
+      <c r="L82" s="80"/>
       <c r="M82" s="5"/>
-      <c r="N82" s="69" t="s">
+      <c r="N82" s="92" t="s">
         <v>65</v>
       </c>
-      <c r="O82" s="70"/>
-      <c r="P82" s="71"/>
+      <c r="O82" s="93"/>
+      <c r="P82" s="94"/>
       <c r="Q82" s="35"/>
-      <c r="R82" s="69" t="s">
+      <c r="R82" s="92" t="s">
         <v>65</v>
       </c>
-      <c r="S82" s="70"/>
-      <c r="T82" s="71"/>
+      <c r="S82" s="93"/>
+      <c r="T82" s="94"/>
       <c r="U82" s="32"/>
-      <c r="V82" s="69" t="s">
+      <c r="V82" s="92" t="s">
         <v>65</v>
       </c>
-      <c r="W82" s="70"/>
-      <c r="X82" s="71"/>
+      <c r="W82" s="93"/>
+      <c r="X82" s="94"/>
       <c r="Y82" s="32"/>
-      <c r="Z82" s="69" t="s">
+      <c r="Z82" s="92" t="s">
         <v>65</v>
       </c>
-      <c r="AA82" s="70"/>
-      <c r="AB82" s="71"/>
+      <c r="AA82" s="93"/>
+      <c r="AB82" s="94"/>
       <c r="AC82" s="32"/>
-      <c r="AD82" s="69" t="s">
+      <c r="AD82" s="92" t="s">
         <v>65</v>
       </c>
-      <c r="AE82" s="70"/>
-      <c r="AF82" s="71"/>
+      <c r="AE82" s="93"/>
+      <c r="AF82" s="94"/>
       <c r="AG82" s="32"/>
-      <c r="AH82" s="69" t="s">
+      <c r="AH82" s="92" t="s">
         <v>65</v>
       </c>
-      <c r="AI82" s="70"/>
-      <c r="AJ82" s="71"/>
+      <c r="AI82" s="93"/>
+      <c r="AJ82" s="94"/>
       <c r="AK82" s="36"/>
-      <c r="AL82" s="69" t="s">
+      <c r="AL82" s="92" t="s">
         <v>65</v>
       </c>
-      <c r="AM82" s="70"/>
-      <c r="AN82" s="71"/>
+      <c r="AM82" s="93"/>
+      <c r="AN82" s="94"/>
       <c r="AO82" s="12"/>
       <c r="AP82" s="29"/>
       <c r="AQ82" s="26"/>
@@ -6591,65 +6650,65 @@
     </row>
     <row r="83" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="12"/>
-      <c r="B83" s="90" t="s">
+      <c r="B83" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="C83" s="91"/>
-      <c r="D83" s="92"/>
+      <c r="C83" s="69"/>
+      <c r="D83" s="70"/>
       <c r="E83" s="32"/>
-      <c r="F83" s="90" t="s">
+      <c r="F83" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="G83" s="91"/>
-      <c r="H83" s="92"/>
+      <c r="G83" s="69"/>
+      <c r="H83" s="70"/>
       <c r="I83" s="32"/>
-      <c r="J83" s="90" t="s">
+      <c r="J83" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="K83" s="91"/>
-      <c r="L83" s="92"/>
+      <c r="K83" s="69"/>
+      <c r="L83" s="70"/>
       <c r="M83" s="5"/>
-      <c r="N83" s="81" t="s">
+      <c r="N83" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="O83" s="82"/>
-      <c r="P83" s="83"/>
+      <c r="O83" s="90"/>
+      <c r="P83" s="91"/>
       <c r="Q83" s="31"/>
-      <c r="R83" s="81" t="s">
+      <c r="R83" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="S83" s="82"/>
-      <c r="T83" s="83"/>
+      <c r="S83" s="90"/>
+      <c r="T83" s="91"/>
       <c r="U83" s="31"/>
-      <c r="V83" s="81" t="s">
+      <c r="V83" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="W83" s="82"/>
-      <c r="X83" s="83"/>
+      <c r="W83" s="90"/>
+      <c r="X83" s="91"/>
       <c r="Y83" s="32"/>
-      <c r="Z83" s="81" t="s">
+      <c r="Z83" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="AA83" s="82"/>
-      <c r="AB83" s="83"/>
+      <c r="AA83" s="90"/>
+      <c r="AB83" s="91"/>
       <c r="AC83" s="32"/>
-      <c r="AD83" s="81" t="s">
+      <c r="AD83" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="AE83" s="82"/>
-      <c r="AF83" s="83"/>
+      <c r="AE83" s="90"/>
+      <c r="AF83" s="91"/>
       <c r="AG83" s="32"/>
-      <c r="AH83" s="81" t="s">
+      <c r="AH83" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="AI83" s="82"/>
-      <c r="AJ83" s="83"/>
+      <c r="AI83" s="90"/>
+      <c r="AJ83" s="91"/>
       <c r="AK83" s="32"/>
-      <c r="AL83" s="81" t="s">
+      <c r="AL83" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="AM83" s="82"/>
-      <c r="AN83" s="83"/>
+      <c r="AM83" s="90"/>
+      <c r="AN83" s="91"/>
       <c r="AO83" s="12"/>
       <c r="AP83" s="29"/>
       <c r="AQ83" s="26"/>
@@ -6657,65 +6716,65 @@
     </row>
     <row r="84" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="12"/>
-      <c r="B84" s="87" t="s">
+      <c r="B84" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="C84" s="88"/>
-      <c r="D84" s="89"/>
+      <c r="C84" s="82"/>
+      <c r="D84" s="83"/>
       <c r="E84" s="32"/>
-      <c r="F84" s="87" t="s">
+      <c r="F84" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="G84" s="88"/>
-      <c r="H84" s="89"/>
+      <c r="G84" s="82"/>
+      <c r="H84" s="83"/>
       <c r="I84" s="32"/>
-      <c r="J84" s="87" t="s">
+      <c r="J84" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="K84" s="88"/>
-      <c r="L84" s="89"/>
+      <c r="K84" s="82"/>
+      <c r="L84" s="83"/>
       <c r="M84" s="5"/>
-      <c r="N84" s="87" t="s">
+      <c r="N84" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="O84" s="88"/>
-      <c r="P84" s="89"/>
+      <c r="O84" s="82"/>
+      <c r="P84" s="83"/>
       <c r="Q84" s="32"/>
-      <c r="R84" s="87" t="s">
+      <c r="R84" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="S84" s="88"/>
-      <c r="T84" s="89"/>
+      <c r="S84" s="82"/>
+      <c r="T84" s="83"/>
       <c r="U84" s="32"/>
-      <c r="V84" s="87" t="s">
+      <c r="V84" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="W84" s="88"/>
-      <c r="X84" s="89"/>
+      <c r="W84" s="82"/>
+      <c r="X84" s="83"/>
       <c r="Y84" s="32"/>
-      <c r="Z84" s="87" t="s">
+      <c r="Z84" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="AA84" s="88"/>
-      <c r="AB84" s="89"/>
+      <c r="AA84" s="82"/>
+      <c r="AB84" s="83"/>
       <c r="AC84" s="43"/>
-      <c r="AD84" s="87" t="s">
+      <c r="AD84" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="AE84" s="88"/>
-      <c r="AF84" s="89"/>
+      <c r="AE84" s="82"/>
+      <c r="AF84" s="83"/>
       <c r="AG84" s="32"/>
-      <c r="AH84" s="87" t="s">
+      <c r="AH84" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="AI84" s="88"/>
-      <c r="AJ84" s="89"/>
+      <c r="AI84" s="82"/>
+      <c r="AJ84" s="83"/>
       <c r="AK84" s="32"/>
-      <c r="AL84" s="87" t="s">
+      <c r="AL84" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="AM84" s="88"/>
-      <c r="AN84" s="89"/>
+      <c r="AM84" s="82"/>
+      <c r="AN84" s="83"/>
       <c r="AO84" s="12"/>
       <c r="AP84" s="29"/>
       <c r="AQ84" s="26"/>
@@ -6723,45 +6782,45 @@
     </row>
     <row r="85" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A85" s="12"/>
-      <c r="B85" s="62"/>
-      <c r="C85" s="63"/>
-      <c r="D85" s="64"/>
+      <c r="B85" s="71"/>
+      <c r="C85" s="72"/>
+      <c r="D85" s="73"/>
       <c r="E85" s="31"/>
-      <c r="F85" s="62"/>
-      <c r="G85" s="63"/>
-      <c r="H85" s="64"/>
+      <c r="F85" s="71"/>
+      <c r="G85" s="72"/>
+      <c r="H85" s="73"/>
       <c r="I85" s="32"/>
-      <c r="J85" s="62"/>
-      <c r="K85" s="63"/>
-      <c r="L85" s="64"/>
+      <c r="J85" s="71"/>
+      <c r="K85" s="72"/>
+      <c r="L85" s="73"/>
       <c r="M85" s="6"/>
-      <c r="N85" s="62"/>
-      <c r="O85" s="63"/>
-      <c r="P85" s="64"/>
+      <c r="N85" s="71"/>
+      <c r="O85" s="72"/>
+      <c r="P85" s="73"/>
       <c r="Q85" s="31"/>
-      <c r="R85" s="62"/>
-      <c r="S85" s="63"/>
-      <c r="T85" s="64"/>
+      <c r="R85" s="71"/>
+      <c r="S85" s="72"/>
+      <c r="T85" s="73"/>
       <c r="U85" s="32"/>
-      <c r="V85" s="62"/>
-      <c r="W85" s="63"/>
-      <c r="X85" s="64"/>
+      <c r="V85" s="71"/>
+      <c r="W85" s="72"/>
+      <c r="X85" s="73"/>
       <c r="Y85" s="32"/>
-      <c r="Z85" s="62"/>
-      <c r="AA85" s="63"/>
-      <c r="AB85" s="64"/>
+      <c r="Z85" s="71"/>
+      <c r="AA85" s="72"/>
+      <c r="AB85" s="73"/>
       <c r="AC85" s="43"/>
-      <c r="AD85" s="62"/>
-      <c r="AE85" s="63"/>
-      <c r="AF85" s="64"/>
+      <c r="AD85" s="71"/>
+      <c r="AE85" s="72"/>
+      <c r="AF85" s="73"/>
       <c r="AG85" s="31"/>
-      <c r="AH85" s="62"/>
-      <c r="AI85" s="63"/>
-      <c r="AJ85" s="64"/>
+      <c r="AH85" s="71"/>
+      <c r="AI85" s="72"/>
+      <c r="AJ85" s="73"/>
       <c r="AK85" s="32"/>
-      <c r="AL85" s="62"/>
-      <c r="AM85" s="63"/>
-      <c r="AN85" s="64"/>
+      <c r="AL85" s="71"/>
+      <c r="AM85" s="72"/>
+      <c r="AN85" s="73"/>
       <c r="AO85" s="12"/>
       <c r="AP85" s="29"/>
       <c r="AQ85" s="26"/>
@@ -6815,52 +6874,52 @@
     </row>
     <row r="87" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="12"/>
-      <c r="B87" s="65"/>
-      <c r="C87" s="66"/>
+      <c r="B87" s="63"/>
+      <c r="C87" s="64"/>
       <c r="D87" s="57"/>
       <c r="E87" s="36"/>
-      <c r="F87" s="65"/>
-      <c r="G87" s="66"/>
+      <c r="F87" s="63"/>
+      <c r="G87" s="64"/>
       <c r="H87" s="57"/>
       <c r="I87" s="32"/>
-      <c r="J87" s="65"/>
-      <c r="K87" s="66"/>
+      <c r="J87" s="63"/>
+      <c r="K87" s="64"/>
       <c r="L87" s="57"/>
       <c r="M87" s="6"/>
-      <c r="N87" s="67"/>
-      <c r="O87" s="68"/>
+      <c r="N87" s="87"/>
+      <c r="O87" s="88"/>
       <c r="P87" s="34"/>
       <c r="Q87" s="32"/>
-      <c r="R87" s="67"/>
-      <c r="S87" s="68"/>
+      <c r="R87" s="87"/>
+      <c r="S87" s="88"/>
       <c r="T87" s="34"/>
       <c r="U87" s="36"/>
-      <c r="V87" s="67" t="s">
+      <c r="V87" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="W87" s="68"/>
+      <c r="W87" s="88"/>
       <c r="X87" s="34"/>
       <c r="Y87" s="32"/>
-      <c r="Z87" s="67"/>
-      <c r="AA87" s="68"/>
+      <c r="Z87" s="87"/>
+      <c r="AA87" s="88"/>
       <c r="AB87" s="34"/>
       <c r="AC87" s="32"/>
-      <c r="AD87" s="67" t="s">
+      <c r="AD87" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="AE87" s="68"/>
+      <c r="AE87" s="88"/>
       <c r="AF87" s="34"/>
       <c r="AG87" s="32"/>
-      <c r="AH87" s="67" t="s">
+      <c r="AH87" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="AI87" s="68"/>
+      <c r="AI87" s="88"/>
       <c r="AJ87" s="34"/>
       <c r="AK87" s="32"/>
-      <c r="AL87" s="67" t="s">
+      <c r="AL87" s="87" t="s">
         <v>80</v>
       </c>
-      <c r="AM87" s="68"/>
+      <c r="AM87" s="88"/>
       <c r="AN87" s="34"/>
       <c r="AO87" s="12"/>
       <c r="AP87" s="29"/>
@@ -6869,47 +6928,47 @@
     </row>
     <row r="88" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="12"/>
-      <c r="B88" s="84"/>
-      <c r="C88" s="85"/>
-      <c r="D88" s="86"/>
+      <c r="B88" s="78"/>
+      <c r="C88" s="79"/>
+      <c r="D88" s="80"/>
       <c r="E88" s="32"/>
-      <c r="F88" s="84"/>
-      <c r="G88" s="85"/>
-      <c r="H88" s="86"/>
+      <c r="F88" s="78"/>
+      <c r="G88" s="79"/>
+      <c r="H88" s="80"/>
       <c r="I88" s="32"/>
-      <c r="J88" s="84"/>
-      <c r="K88" s="85"/>
-      <c r="L88" s="86"/>
+      <c r="J88" s="78"/>
+      <c r="K88" s="79"/>
+      <c r="L88" s="80"/>
       <c r="M88" s="6"/>
-      <c r="N88" s="69"/>
-      <c r="O88" s="70"/>
-      <c r="P88" s="71"/>
+      <c r="N88" s="92"/>
+      <c r="O88" s="93"/>
+      <c r="P88" s="94"/>
       <c r="Q88" s="32"/>
-      <c r="R88" s="69"/>
-      <c r="S88" s="70"/>
-      <c r="T88" s="71"/>
+      <c r="R88" s="92"/>
+      <c r="S88" s="93"/>
+      <c r="T88" s="94"/>
       <c r="U88" s="32"/>
-      <c r="V88" s="69"/>
-      <c r="W88" s="70"/>
-      <c r="X88" s="71"/>
+      <c r="V88" s="92"/>
+      <c r="W88" s="93"/>
+      <c r="X88" s="94"/>
       <c r="Y88" s="32"/>
-      <c r="Z88" s="69"/>
-      <c r="AA88" s="70"/>
-      <c r="AB88" s="71"/>
+      <c r="Z88" s="92"/>
+      <c r="AA88" s="93"/>
+      <c r="AB88" s="94"/>
       <c r="AC88" s="35"/>
-      <c r="AD88" s="69"/>
-      <c r="AE88" s="70"/>
-      <c r="AF88" s="71"/>
+      <c r="AD88" s="92"/>
+      <c r="AE88" s="93"/>
+      <c r="AF88" s="94"/>
       <c r="AG88" s="32"/>
-      <c r="AH88" s="69"/>
-      <c r="AI88" s="70"/>
-      <c r="AJ88" s="71"/>
+      <c r="AH88" s="92"/>
+      <c r="AI88" s="93"/>
+      <c r="AJ88" s="94"/>
       <c r="AK88" s="32"/>
-      <c r="AL88" s="69" t="s">
+      <c r="AL88" s="92" t="s">
         <v>81</v>
       </c>
-      <c r="AM88" s="70"/>
-      <c r="AN88" s="71"/>
+      <c r="AM88" s="93"/>
+      <c r="AN88" s="94"/>
       <c r="AO88" s="12"/>
       <c r="AP88" s="29"/>
       <c r="AQ88" s="26"/>
@@ -6917,51 +6976,51 @@
     </row>
     <row r="89" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="12"/>
-      <c r="B89" s="90"/>
-      <c r="C89" s="91"/>
-      <c r="D89" s="92"/>
+      <c r="B89" s="68"/>
+      <c r="C89" s="69"/>
+      <c r="D89" s="70"/>
       <c r="E89" s="31"/>
-      <c r="F89" s="90"/>
-      <c r="G89" s="91"/>
-      <c r="H89" s="92"/>
+      <c r="F89" s="68"/>
+      <c r="G89" s="69"/>
+      <c r="H89" s="70"/>
       <c r="I89" s="32"/>
-      <c r="J89" s="90"/>
-      <c r="K89" s="91"/>
-      <c r="L89" s="92"/>
+      <c r="J89" s="68"/>
+      <c r="K89" s="69"/>
+      <c r="L89" s="70"/>
       <c r="M89" s="6"/>
-      <c r="N89" s="81"/>
-      <c r="O89" s="82"/>
-      <c r="P89" s="83"/>
+      <c r="N89" s="89"/>
+      <c r="O89" s="90"/>
+      <c r="P89" s="91"/>
       <c r="Q89" s="32"/>
-      <c r="R89" s="81"/>
-      <c r="S89" s="82"/>
-      <c r="T89" s="83"/>
+      <c r="R89" s="89"/>
+      <c r="S89" s="90"/>
+      <c r="T89" s="91"/>
       <c r="U89" s="31"/>
-      <c r="V89" s="81" t="s">
+      <c r="V89" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="W89" s="82"/>
-      <c r="X89" s="83"/>
+      <c r="W89" s="90"/>
+      <c r="X89" s="91"/>
       <c r="Y89" s="32"/>
-      <c r="Z89" s="81"/>
-      <c r="AA89" s="82"/>
-      <c r="AB89" s="83"/>
+      <c r="Z89" s="89"/>
+      <c r="AA89" s="90"/>
+      <c r="AB89" s="91"/>
       <c r="AC89" s="31"/>
-      <c r="AD89" s="81" t="s">
+      <c r="AD89" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="AE89" s="82"/>
-      <c r="AF89" s="83"/>
+      <c r="AE89" s="90"/>
+      <c r="AF89" s="91"/>
       <c r="AG89" s="32"/>
-      <c r="AH89" s="81" t="s">
+      <c r="AH89" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="AI89" s="82"/>
-      <c r="AJ89" s="83"/>
+      <c r="AI89" s="90"/>
+      <c r="AJ89" s="91"/>
       <c r="AK89" s="32"/>
-      <c r="AL89" s="81"/>
-      <c r="AM89" s="82"/>
-      <c r="AN89" s="83"/>
+      <c r="AL89" s="89"/>
+      <c r="AM89" s="90"/>
+      <c r="AN89" s="91"/>
       <c r="AO89" s="12"/>
       <c r="AP89" s="29"/>
       <c r="AQ89" s="26"/>
@@ -6969,53 +7028,53 @@
     </row>
     <row r="90" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="12"/>
-      <c r="B90" s="87"/>
-      <c r="C90" s="88"/>
-      <c r="D90" s="89"/>
+      <c r="B90" s="81"/>
+      <c r="C90" s="82"/>
+      <c r="D90" s="83"/>
       <c r="E90" s="32"/>
-      <c r="F90" s="87"/>
-      <c r="G90" s="88"/>
-      <c r="H90" s="89"/>
+      <c r="F90" s="81"/>
+      <c r="G90" s="82"/>
+      <c r="H90" s="83"/>
       <c r="I90" s="32"/>
-      <c r="J90" s="87"/>
-      <c r="K90" s="88"/>
-      <c r="L90" s="89"/>
+      <c r="J90" s="81"/>
+      <c r="K90" s="82"/>
+      <c r="L90" s="83"/>
       <c r="M90" s="6"/>
-      <c r="N90" s="87"/>
-      <c r="O90" s="88"/>
-      <c r="P90" s="89"/>
+      <c r="N90" s="81"/>
+      <c r="O90" s="82"/>
+      <c r="P90" s="83"/>
       <c r="Q90" s="32"/>
-      <c r="R90" s="87"/>
-      <c r="S90" s="88"/>
-      <c r="T90" s="89"/>
+      <c r="R90" s="81"/>
+      <c r="S90" s="82"/>
+      <c r="T90" s="83"/>
       <c r="U90" s="32"/>
-      <c r="V90" s="87" t="s">
+      <c r="V90" s="81" t="s">
         <v>30</v>
       </c>
-      <c r="W90" s="88"/>
-      <c r="X90" s="89"/>
+      <c r="W90" s="82"/>
+      <c r="X90" s="83"/>
       <c r="Y90" s="32"/>
-      <c r="Z90" s="87"/>
-      <c r="AA90" s="88"/>
-      <c r="AB90" s="89"/>
+      <c r="Z90" s="81"/>
+      <c r="AA90" s="82"/>
+      <c r="AB90" s="83"/>
       <c r="AC90" s="32"/>
-      <c r="AD90" s="87" t="s">
+      <c r="AD90" s="81" t="s">
         <v>30</v>
       </c>
-      <c r="AE90" s="88"/>
-      <c r="AF90" s="89"/>
+      <c r="AE90" s="82"/>
+      <c r="AF90" s="83"/>
       <c r="AG90" s="32"/>
-      <c r="AH90" s="87" t="s">
+      <c r="AH90" s="81" t="s">
         <v>30</v>
       </c>
-      <c r="AI90" s="88"/>
-      <c r="AJ90" s="89"/>
+      <c r="AI90" s="82"/>
+      <c r="AJ90" s="83"/>
       <c r="AK90" s="32"/>
-      <c r="AL90" s="87" t="s">
+      <c r="AL90" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="AM90" s="88"/>
-      <c r="AN90" s="89"/>
+      <c r="AM90" s="82"/>
+      <c r="AN90" s="83"/>
       <c r="AO90" s="12"/>
       <c r="AP90" s="29"/>
       <c r="AQ90" s="26"/>
@@ -7023,45 +7082,45 @@
     </row>
     <row r="91" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A91" s="12"/>
-      <c r="B91" s="62"/>
-      <c r="C91" s="63"/>
-      <c r="D91" s="64"/>
+      <c r="B91" s="71"/>
+      <c r="C91" s="72"/>
+      <c r="D91" s="73"/>
       <c r="E91" s="32"/>
-      <c r="F91" s="62"/>
-      <c r="G91" s="63"/>
-      <c r="H91" s="64"/>
+      <c r="F91" s="71"/>
+      <c r="G91" s="72"/>
+      <c r="H91" s="73"/>
       <c r="I91" s="31"/>
-      <c r="J91" s="62"/>
-      <c r="K91" s="63"/>
-      <c r="L91" s="64"/>
+      <c r="J91" s="71"/>
+      <c r="K91" s="72"/>
+      <c r="L91" s="73"/>
       <c r="M91" s="6"/>
-      <c r="N91" s="62"/>
-      <c r="O91" s="63"/>
-      <c r="P91" s="64"/>
+      <c r="N91" s="71"/>
+      <c r="O91" s="72"/>
+      <c r="P91" s="73"/>
       <c r="Q91" s="31"/>
-      <c r="R91" s="62"/>
-      <c r="S91" s="63"/>
-      <c r="T91" s="64"/>
+      <c r="R91" s="71"/>
+      <c r="S91" s="72"/>
+      <c r="T91" s="73"/>
       <c r="U91" s="32"/>
-      <c r="V91" s="62"/>
-      <c r="W91" s="63"/>
-      <c r="X91" s="64"/>
+      <c r="V91" s="71"/>
+      <c r="W91" s="72"/>
+      <c r="X91" s="73"/>
       <c r="Y91" s="32"/>
-      <c r="Z91" s="62"/>
-      <c r="AA91" s="63"/>
-      <c r="AB91" s="64"/>
+      <c r="Z91" s="71"/>
+      <c r="AA91" s="72"/>
+      <c r="AB91" s="73"/>
       <c r="AC91" s="32"/>
-      <c r="AD91" s="62"/>
-      <c r="AE91" s="63"/>
-      <c r="AF91" s="64"/>
+      <c r="AD91" s="71"/>
+      <c r="AE91" s="72"/>
+      <c r="AF91" s="73"/>
       <c r="AG91" s="31"/>
-      <c r="AH91" s="62"/>
-      <c r="AI91" s="63"/>
-      <c r="AJ91" s="64"/>
+      <c r="AH91" s="71"/>
+      <c r="AI91" s="72"/>
+      <c r="AJ91" s="73"/>
       <c r="AK91" s="31"/>
-      <c r="AL91" s="62"/>
-      <c r="AM91" s="63"/>
-      <c r="AN91" s="64"/>
+      <c r="AL91" s="71"/>
+      <c r="AM91" s="72"/>
+      <c r="AN91" s="73"/>
       <c r="AO91" s="12"/>
       <c r="AP91" s="29"/>
       <c r="AQ91" s="26"/>
@@ -7115,44 +7174,44 @@
     </row>
     <row r="93" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="12"/>
-      <c r="B93" s="65"/>
-      <c r="C93" s="66"/>
+      <c r="B93" s="63"/>
+      <c r="C93" s="64"/>
       <c r="D93" s="57"/>
       <c r="E93" s="36"/>
-      <c r="F93" s="65"/>
-      <c r="G93" s="66"/>
+      <c r="F93" s="63"/>
+      <c r="G93" s="64"/>
       <c r="H93" s="57"/>
       <c r="I93" s="32"/>
-      <c r="J93" s="65"/>
-      <c r="K93" s="66"/>
+      <c r="J93" s="63"/>
+      <c r="K93" s="64"/>
       <c r="L93" s="57"/>
       <c r="M93" s="6"/>
-      <c r="N93" s="67"/>
-      <c r="O93" s="68"/>
+      <c r="N93" s="87"/>
+      <c r="O93" s="88"/>
       <c r="P93" s="34"/>
       <c r="Q93" s="44"/>
-      <c r="R93" s="67"/>
-      <c r="S93" s="68"/>
+      <c r="R93" s="87"/>
+      <c r="S93" s="88"/>
       <c r="T93" s="34"/>
       <c r="U93" s="36"/>
-      <c r="V93" s="67"/>
-      <c r="W93" s="68"/>
+      <c r="V93" s="87"/>
+      <c r="W93" s="88"/>
       <c r="X93" s="34"/>
       <c r="Y93" s="32"/>
-      <c r="Z93" s="67"/>
-      <c r="AA93" s="68"/>
+      <c r="Z93" s="87"/>
+      <c r="AA93" s="88"/>
       <c r="AB93" s="34"/>
       <c r="AC93" s="36"/>
-      <c r="AD93" s="67"/>
-      <c r="AE93" s="68"/>
+      <c r="AD93" s="87"/>
+      <c r="AE93" s="88"/>
       <c r="AF93" s="34"/>
       <c r="AG93" s="36"/>
-      <c r="AH93" s="67"/>
-      <c r="AI93" s="68"/>
+      <c r="AH93" s="87"/>
+      <c r="AI93" s="88"/>
       <c r="AJ93" s="34"/>
       <c r="AK93" s="32"/>
-      <c r="AL93" s="67"/>
-      <c r="AM93" s="68"/>
+      <c r="AL93" s="87"/>
+      <c r="AM93" s="88"/>
       <c r="AN93" s="34"/>
       <c r="AO93" s="12"/>
       <c r="AP93" s="29"/>
@@ -7161,45 +7220,45 @@
     </row>
     <row r="94" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="12"/>
-      <c r="B94" s="84"/>
-      <c r="C94" s="85"/>
-      <c r="D94" s="86"/>
+      <c r="B94" s="78"/>
+      <c r="C94" s="79"/>
+      <c r="D94" s="80"/>
       <c r="E94" s="32"/>
-      <c r="F94" s="84"/>
-      <c r="G94" s="85"/>
-      <c r="H94" s="86"/>
+      <c r="F94" s="78"/>
+      <c r="G94" s="79"/>
+      <c r="H94" s="80"/>
       <c r="I94" s="32"/>
-      <c r="J94" s="84"/>
-      <c r="K94" s="85"/>
-      <c r="L94" s="86"/>
+      <c r="J94" s="78"/>
+      <c r="K94" s="79"/>
+      <c r="L94" s="80"/>
       <c r="M94" s="26"/>
-      <c r="N94" s="69"/>
-      <c r="O94" s="70"/>
-      <c r="P94" s="71"/>
+      <c r="N94" s="92"/>
+      <c r="O94" s="93"/>
+      <c r="P94" s="94"/>
       <c r="Q94" s="44"/>
-      <c r="R94" s="69"/>
-      <c r="S94" s="70"/>
-      <c r="T94" s="71"/>
+      <c r="R94" s="92"/>
+      <c r="S94" s="93"/>
+      <c r="T94" s="94"/>
       <c r="U94" s="32"/>
-      <c r="V94" s="69"/>
-      <c r="W94" s="70"/>
-      <c r="X94" s="71"/>
+      <c r="V94" s="92"/>
+      <c r="W94" s="93"/>
+      <c r="X94" s="94"/>
       <c r="Y94" s="32"/>
-      <c r="Z94" s="69"/>
-      <c r="AA94" s="70"/>
-      <c r="AB94" s="71"/>
+      <c r="Z94" s="92"/>
+      <c r="AA94" s="93"/>
+      <c r="AB94" s="94"/>
       <c r="AC94" s="36"/>
-      <c r="AD94" s="69"/>
-      <c r="AE94" s="70"/>
-      <c r="AF94" s="71"/>
+      <c r="AD94" s="92"/>
+      <c r="AE94" s="93"/>
+      <c r="AF94" s="94"/>
       <c r="AG94" s="32"/>
-      <c r="AH94" s="69"/>
-      <c r="AI94" s="70"/>
-      <c r="AJ94" s="71"/>
+      <c r="AH94" s="92"/>
+      <c r="AI94" s="93"/>
+      <c r="AJ94" s="94"/>
       <c r="AK94" s="32"/>
-      <c r="AL94" s="69"/>
-      <c r="AM94" s="70"/>
-      <c r="AN94" s="71"/>
+      <c r="AL94" s="92"/>
+      <c r="AM94" s="93"/>
+      <c r="AN94" s="94"/>
       <c r="AO94" s="12"/>
       <c r="AP94" s="29"/>
       <c r="AQ94" s="26"/>
@@ -7207,45 +7266,45 @@
     </row>
     <row r="95" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="12"/>
-      <c r="B95" s="90"/>
-      <c r="C95" s="91"/>
-      <c r="D95" s="92"/>
+      <c r="B95" s="68"/>
+      <c r="C95" s="69"/>
+      <c r="D95" s="70"/>
       <c r="E95" s="31"/>
-      <c r="F95" s="90"/>
-      <c r="G95" s="91"/>
-      <c r="H95" s="92"/>
+      <c r="F95" s="68"/>
+      <c r="G95" s="69"/>
+      <c r="H95" s="70"/>
       <c r="I95" s="32"/>
-      <c r="J95" s="90"/>
-      <c r="K95" s="91"/>
-      <c r="L95" s="92"/>
+      <c r="J95" s="68"/>
+      <c r="K95" s="69"/>
+      <c r="L95" s="70"/>
       <c r="M95" s="26"/>
-      <c r="N95" s="81"/>
-      <c r="O95" s="82"/>
-      <c r="P95" s="83"/>
+      <c r="N95" s="89"/>
+      <c r="O95" s="90"/>
+      <c r="P95" s="91"/>
       <c r="Q95" s="44"/>
-      <c r="R95" s="81"/>
-      <c r="S95" s="82"/>
-      <c r="T95" s="83"/>
+      <c r="R95" s="89"/>
+      <c r="S95" s="90"/>
+      <c r="T95" s="91"/>
       <c r="U95" s="31"/>
-      <c r="V95" s="81"/>
-      <c r="W95" s="82"/>
-      <c r="X95" s="83"/>
+      <c r="V95" s="89"/>
+      <c r="W95" s="90"/>
+      <c r="X95" s="91"/>
       <c r="Y95" s="32"/>
-      <c r="Z95" s="81"/>
-      <c r="AA95" s="82"/>
-      <c r="AB95" s="83"/>
+      <c r="Z95" s="89"/>
+      <c r="AA95" s="90"/>
+      <c r="AB95" s="91"/>
       <c r="AC95" s="35"/>
-      <c r="AD95" s="81"/>
-      <c r="AE95" s="82"/>
-      <c r="AF95" s="83"/>
+      <c r="AD95" s="89"/>
+      <c r="AE95" s="90"/>
+      <c r="AF95" s="91"/>
       <c r="AG95" s="31"/>
-      <c r="AH95" s="81"/>
-      <c r="AI95" s="82"/>
-      <c r="AJ95" s="83"/>
+      <c r="AH95" s="89"/>
+      <c r="AI95" s="90"/>
+      <c r="AJ95" s="91"/>
       <c r="AK95" s="32"/>
-      <c r="AL95" s="81"/>
-      <c r="AM95" s="82"/>
-      <c r="AN95" s="83"/>
+      <c r="AL95" s="89"/>
+      <c r="AM95" s="90"/>
+      <c r="AN95" s="91"/>
       <c r="AO95" s="12"/>
       <c r="AP95" s="29"/>
       <c r="AQ95" s="26"/>
@@ -7253,45 +7312,45 @@
     </row>
     <row r="96" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="12"/>
-      <c r="B96" s="87"/>
-      <c r="C96" s="88"/>
-      <c r="D96" s="89"/>
+      <c r="B96" s="81"/>
+      <c r="C96" s="82"/>
+      <c r="D96" s="83"/>
       <c r="E96" s="32"/>
-      <c r="F96" s="87"/>
-      <c r="G96" s="88"/>
-      <c r="H96" s="89"/>
+      <c r="F96" s="81"/>
+      <c r="G96" s="82"/>
+      <c r="H96" s="83"/>
       <c r="I96" s="32"/>
-      <c r="J96" s="87"/>
-      <c r="K96" s="88"/>
-      <c r="L96" s="89"/>
+      <c r="J96" s="81"/>
+      <c r="K96" s="82"/>
+      <c r="L96" s="83"/>
       <c r="M96" s="26"/>
-      <c r="N96" s="87"/>
-      <c r="O96" s="88"/>
-      <c r="P96" s="89"/>
+      <c r="N96" s="81"/>
+      <c r="O96" s="82"/>
+      <c r="P96" s="83"/>
       <c r="Q96" s="44"/>
-      <c r="R96" s="87"/>
-      <c r="S96" s="88"/>
-      <c r="T96" s="89"/>
+      <c r="R96" s="81"/>
+      <c r="S96" s="82"/>
+      <c r="T96" s="83"/>
       <c r="U96" s="32"/>
-      <c r="V96" s="87"/>
-      <c r="W96" s="88"/>
-      <c r="X96" s="89"/>
+      <c r="V96" s="81"/>
+      <c r="W96" s="82"/>
+      <c r="X96" s="83"/>
       <c r="Y96" s="32"/>
-      <c r="Z96" s="87"/>
-      <c r="AA96" s="88"/>
-      <c r="AB96" s="89"/>
+      <c r="Z96" s="81"/>
+      <c r="AA96" s="82"/>
+      <c r="AB96" s="83"/>
       <c r="AC96" s="31"/>
-      <c r="AD96" s="87"/>
-      <c r="AE96" s="88"/>
-      <c r="AF96" s="89"/>
+      <c r="AD96" s="81"/>
+      <c r="AE96" s="82"/>
+      <c r="AF96" s="83"/>
       <c r="AG96" s="32"/>
-      <c r="AH96" s="87"/>
-      <c r="AI96" s="88"/>
-      <c r="AJ96" s="89"/>
+      <c r="AH96" s="81"/>
+      <c r="AI96" s="82"/>
+      <c r="AJ96" s="83"/>
       <c r="AK96" s="32"/>
-      <c r="AL96" s="87"/>
-      <c r="AM96" s="88"/>
-      <c r="AN96" s="89"/>
+      <c r="AL96" s="81"/>
+      <c r="AM96" s="82"/>
+      <c r="AN96" s="83"/>
       <c r="AO96" s="12"/>
       <c r="AP96" s="29"/>
       <c r="AQ96" s="26"/>
@@ -7299,45 +7358,45 @@
     </row>
     <row r="97" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A97" s="12"/>
-      <c r="B97" s="62"/>
-      <c r="C97" s="63"/>
-      <c r="D97" s="64"/>
+      <c r="B97" s="71"/>
+      <c r="C97" s="72"/>
+      <c r="D97" s="73"/>
       <c r="E97" s="32"/>
-      <c r="F97" s="62"/>
-      <c r="G97" s="63"/>
-      <c r="H97" s="64"/>
+      <c r="F97" s="71"/>
+      <c r="G97" s="72"/>
+      <c r="H97" s="73"/>
       <c r="I97" s="31"/>
-      <c r="J97" s="62"/>
-      <c r="K97" s="63"/>
-      <c r="L97" s="64"/>
+      <c r="J97" s="71"/>
+      <c r="K97" s="72"/>
+      <c r="L97" s="73"/>
       <c r="M97" s="26"/>
-      <c r="N97" s="62"/>
-      <c r="O97" s="63"/>
-      <c r="P97" s="64"/>
+      <c r="N97" s="71"/>
+      <c r="O97" s="72"/>
+      <c r="P97" s="73"/>
       <c r="Q97" s="31"/>
-      <c r="R97" s="62"/>
-      <c r="S97" s="63"/>
-      <c r="T97" s="64"/>
+      <c r="R97" s="71"/>
+      <c r="S97" s="72"/>
+      <c r="T97" s="73"/>
       <c r="U97" s="32"/>
-      <c r="V97" s="62"/>
-      <c r="W97" s="63"/>
-      <c r="X97" s="64"/>
+      <c r="V97" s="71"/>
+      <c r="W97" s="72"/>
+      <c r="X97" s="73"/>
       <c r="Y97" s="31"/>
-      <c r="Z97" s="62"/>
-      <c r="AA97" s="63"/>
-      <c r="AB97" s="64"/>
+      <c r="Z97" s="71"/>
+      <c r="AA97" s="72"/>
+      <c r="AB97" s="73"/>
       <c r="AC97" s="31"/>
-      <c r="AD97" s="62"/>
-      <c r="AE97" s="63"/>
-      <c r="AF97" s="64"/>
+      <c r="AD97" s="71"/>
+      <c r="AE97" s="72"/>
+      <c r="AF97" s="73"/>
       <c r="AG97" s="32"/>
-      <c r="AH97" s="62"/>
-      <c r="AI97" s="63"/>
-      <c r="AJ97" s="64"/>
+      <c r="AH97" s="71"/>
+      <c r="AI97" s="72"/>
+      <c r="AJ97" s="73"/>
       <c r="AK97" s="31"/>
-      <c r="AL97" s="62"/>
-      <c r="AM97" s="63"/>
-      <c r="AN97" s="64"/>
+      <c r="AL97" s="71"/>
+      <c r="AM97" s="72"/>
+      <c r="AN97" s="73"/>
       <c r="AO97" s="12"/>
       <c r="AP97" s="29"/>
       <c r="AQ97" s="26"/>
@@ -7391,44 +7450,44 @@
     </row>
     <row r="99" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="12"/>
-      <c r="B99" s="65"/>
-      <c r="C99" s="66"/>
+      <c r="B99" s="63"/>
+      <c r="C99" s="64"/>
       <c r="D99" s="57"/>
       <c r="E99" s="32"/>
-      <c r="F99" s="65"/>
-      <c r="G99" s="66"/>
+      <c r="F99" s="63"/>
+      <c r="G99" s="64"/>
       <c r="H99" s="57"/>
       <c r="I99" s="36"/>
-      <c r="J99" s="65"/>
-      <c r="K99" s="66"/>
+      <c r="J99" s="63"/>
+      <c r="K99" s="64"/>
       <c r="L99" s="57"/>
       <c r="M99" s="26"/>
-      <c r="N99" s="67"/>
-      <c r="O99" s="68"/>
+      <c r="N99" s="87"/>
+      <c r="O99" s="88"/>
       <c r="P99" s="34"/>
       <c r="Q99" s="44"/>
-      <c r="R99" s="67"/>
-      <c r="S99" s="68"/>
+      <c r="R99" s="87"/>
+      <c r="S99" s="88"/>
       <c r="T99" s="34"/>
       <c r="U99" s="36"/>
-      <c r="V99" s="67"/>
-      <c r="W99" s="68"/>
+      <c r="V99" s="87"/>
+      <c r="W99" s="88"/>
       <c r="X99" s="34"/>
       <c r="Y99" s="32"/>
-      <c r="Z99" s="67"/>
-      <c r="AA99" s="68"/>
+      <c r="Z99" s="87"/>
+      <c r="AA99" s="88"/>
       <c r="AB99" s="34"/>
       <c r="AC99" s="36"/>
-      <c r="AD99" s="67"/>
-      <c r="AE99" s="68"/>
+      <c r="AD99" s="87"/>
+      <c r="AE99" s="88"/>
       <c r="AF99" s="34"/>
       <c r="AG99" s="32"/>
-      <c r="AH99" s="67"/>
-      <c r="AI99" s="68"/>
+      <c r="AH99" s="87"/>
+      <c r="AI99" s="88"/>
       <c r="AJ99" s="34"/>
       <c r="AK99" s="36"/>
-      <c r="AL99" s="67"/>
-      <c r="AM99" s="68"/>
+      <c r="AL99" s="87"/>
+      <c r="AM99" s="88"/>
       <c r="AN99" s="34"/>
       <c r="AO99" s="12"/>
       <c r="AP99" s="29"/>
@@ -7437,45 +7496,45 @@
     </row>
     <row r="100" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="12"/>
-      <c r="B100" s="90"/>
-      <c r="C100" s="91"/>
-      <c r="D100" s="92"/>
+      <c r="B100" s="68"/>
+      <c r="C100" s="69"/>
+      <c r="D100" s="70"/>
       <c r="E100" s="32"/>
-      <c r="F100" s="90"/>
-      <c r="G100" s="91"/>
-      <c r="H100" s="92"/>
+      <c r="F100" s="68"/>
+      <c r="G100" s="69"/>
+      <c r="H100" s="70"/>
       <c r="I100" s="31"/>
-      <c r="J100" s="90"/>
-      <c r="K100" s="91"/>
-      <c r="L100" s="92"/>
+      <c r="J100" s="68"/>
+      <c r="K100" s="69"/>
+      <c r="L100" s="70"/>
       <c r="M100" s="26"/>
-      <c r="N100" s="81"/>
-      <c r="O100" s="82"/>
-      <c r="P100" s="83"/>
+      <c r="N100" s="89"/>
+      <c r="O100" s="90"/>
+      <c r="P100" s="91"/>
       <c r="Q100" s="31"/>
-      <c r="R100" s="81"/>
-      <c r="S100" s="82"/>
-      <c r="T100" s="83"/>
+      <c r="R100" s="89"/>
+      <c r="S100" s="90"/>
+      <c r="T100" s="91"/>
       <c r="U100" s="31"/>
-      <c r="V100" s="81"/>
-      <c r="W100" s="82"/>
-      <c r="X100" s="83"/>
+      <c r="V100" s="89"/>
+      <c r="W100" s="90"/>
+      <c r="X100" s="91"/>
       <c r="Y100" s="32"/>
-      <c r="Z100" s="81"/>
-      <c r="AA100" s="82"/>
-      <c r="AB100" s="83"/>
+      <c r="Z100" s="89"/>
+      <c r="AA100" s="90"/>
+      <c r="AB100" s="91"/>
       <c r="AC100" s="36"/>
-      <c r="AD100" s="81"/>
-      <c r="AE100" s="82"/>
-      <c r="AF100" s="83"/>
+      <c r="AD100" s="89"/>
+      <c r="AE100" s="90"/>
+      <c r="AF100" s="91"/>
       <c r="AG100" s="32"/>
-      <c r="AH100" s="81"/>
-      <c r="AI100" s="82"/>
-      <c r="AJ100" s="83"/>
+      <c r="AH100" s="89"/>
+      <c r="AI100" s="90"/>
+      <c r="AJ100" s="91"/>
       <c r="AK100" s="31"/>
-      <c r="AL100" s="81"/>
-      <c r="AM100" s="82"/>
-      <c r="AN100" s="83"/>
+      <c r="AL100" s="89"/>
+      <c r="AM100" s="90"/>
+      <c r="AN100" s="91"/>
       <c r="AO100" s="12"/>
       <c r="AP100" s="29"/>
       <c r="AQ100" s="26"/>
@@ -7483,45 +7542,45 @@
     </row>
     <row r="101" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="12"/>
-      <c r="B101" s="87"/>
-      <c r="C101" s="88"/>
-      <c r="D101" s="89"/>
+      <c r="B101" s="81"/>
+      <c r="C101" s="82"/>
+      <c r="D101" s="83"/>
       <c r="E101" s="32"/>
-      <c r="F101" s="87"/>
-      <c r="G101" s="88"/>
-      <c r="H101" s="89"/>
+      <c r="F101" s="81"/>
+      <c r="G101" s="82"/>
+      <c r="H101" s="83"/>
       <c r="I101" s="31"/>
-      <c r="J101" s="87"/>
-      <c r="K101" s="88"/>
-      <c r="L101" s="89"/>
+      <c r="J101" s="81"/>
+      <c r="K101" s="82"/>
+      <c r="L101" s="83"/>
       <c r="M101" s="26"/>
-      <c r="N101" s="87"/>
-      <c r="O101" s="88"/>
-      <c r="P101" s="89"/>
+      <c r="N101" s="81"/>
+      <c r="O101" s="82"/>
+      <c r="P101" s="83"/>
       <c r="Q101" s="31"/>
-      <c r="R101" s="87"/>
-      <c r="S101" s="88"/>
-      <c r="T101" s="89"/>
+      <c r="R101" s="81"/>
+      <c r="S101" s="82"/>
+      <c r="T101" s="83"/>
       <c r="U101" s="32"/>
-      <c r="V101" s="87"/>
-      <c r="W101" s="88"/>
-      <c r="X101" s="89"/>
+      <c r="V101" s="81"/>
+      <c r="W101" s="82"/>
+      <c r="X101" s="83"/>
       <c r="Y101" s="32"/>
-      <c r="Z101" s="87"/>
-      <c r="AA101" s="88"/>
-      <c r="AB101" s="89"/>
+      <c r="Z101" s="81"/>
+      <c r="AA101" s="82"/>
+      <c r="AB101" s="83"/>
       <c r="AC101" s="31"/>
-      <c r="AD101" s="87"/>
-      <c r="AE101" s="88"/>
-      <c r="AF101" s="89"/>
+      <c r="AD101" s="81"/>
+      <c r="AE101" s="82"/>
+      <c r="AF101" s="83"/>
       <c r="AG101" s="32"/>
-      <c r="AH101" s="87"/>
-      <c r="AI101" s="88"/>
-      <c r="AJ101" s="89"/>
+      <c r="AH101" s="81"/>
+      <c r="AI101" s="82"/>
+      <c r="AJ101" s="83"/>
       <c r="AK101" s="31"/>
-      <c r="AL101" s="87"/>
-      <c r="AM101" s="88"/>
-      <c r="AN101" s="89"/>
+      <c r="AL101" s="81"/>
+      <c r="AM101" s="82"/>
+      <c r="AN101" s="83"/>
       <c r="AO101" s="12"/>
       <c r="AP101" s="29"/>
       <c r="AQ101" s="26"/>
@@ -7529,45 +7588,45 @@
     </row>
     <row r="102" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A102" s="12"/>
-      <c r="B102" s="62"/>
-      <c r="C102" s="63"/>
-      <c r="D102" s="64"/>
+      <c r="B102" s="71"/>
+      <c r="C102" s="72"/>
+      <c r="D102" s="73"/>
       <c r="E102" s="31"/>
-      <c r="F102" s="62"/>
-      <c r="G102" s="63"/>
-      <c r="H102" s="64"/>
+      <c r="F102" s="71"/>
+      <c r="G102" s="72"/>
+      <c r="H102" s="73"/>
       <c r="I102" s="32"/>
-      <c r="J102" s="62"/>
-      <c r="K102" s="63"/>
-      <c r="L102" s="64"/>
+      <c r="J102" s="71"/>
+      <c r="K102" s="72"/>
+      <c r="L102" s="73"/>
       <c r="M102" s="26"/>
-      <c r="N102" s="62"/>
-      <c r="O102" s="63"/>
-      <c r="P102" s="64"/>
+      <c r="N102" s="71"/>
+      <c r="O102" s="72"/>
+      <c r="P102" s="73"/>
       <c r="Q102" s="31"/>
-      <c r="R102" s="62"/>
-      <c r="S102" s="63"/>
-      <c r="T102" s="64"/>
+      <c r="R102" s="71"/>
+      <c r="S102" s="72"/>
+      <c r="T102" s="73"/>
       <c r="U102" s="32"/>
-      <c r="V102" s="62"/>
-      <c r="W102" s="63"/>
-      <c r="X102" s="64"/>
+      <c r="V102" s="71"/>
+      <c r="W102" s="72"/>
+      <c r="X102" s="73"/>
       <c r="Y102" s="32"/>
-      <c r="Z102" s="62"/>
-      <c r="AA102" s="63"/>
-      <c r="AB102" s="64"/>
+      <c r="Z102" s="71"/>
+      <c r="AA102" s="72"/>
+      <c r="AB102" s="73"/>
       <c r="AC102" s="32"/>
-      <c r="AD102" s="62"/>
-      <c r="AE102" s="63"/>
-      <c r="AF102" s="64"/>
+      <c r="AD102" s="71"/>
+      <c r="AE102" s="72"/>
+      <c r="AF102" s="73"/>
       <c r="AG102" s="31"/>
-      <c r="AH102" s="62"/>
-      <c r="AI102" s="63"/>
-      <c r="AJ102" s="64"/>
+      <c r="AH102" s="71"/>
+      <c r="AI102" s="72"/>
+      <c r="AJ102" s="73"/>
       <c r="AK102" s="32"/>
-      <c r="AL102" s="62"/>
-      <c r="AM102" s="63"/>
-      <c r="AN102" s="64"/>
+      <c r="AL102" s="71"/>
+      <c r="AM102" s="72"/>
+      <c r="AN102" s="73"/>
       <c r="AO102" s="12"/>
       <c r="AP102" s="29"/>
       <c r="AQ102" s="26"/>
@@ -7637,70 +7696,70 @@
       <c r="AR104" s="26"/>
     </row>
     <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B105" s="67"/>
-      <c r="C105" s="68"/>
+      <c r="B105" s="87"/>
+      <c r="C105" s="88"/>
       <c r="D105" s="34"/>
       <c r="E105" s="32"/>
-      <c r="F105" s="67"/>
-      <c r="G105" s="68"/>
+      <c r="F105" s="87"/>
+      <c r="G105" s="88"/>
       <c r="H105" s="34"/>
       <c r="I105" s="32"/>
-      <c r="J105" s="67"/>
-      <c r="K105" s="68"/>
+      <c r="J105" s="87"/>
+      <c r="K105" s="88"/>
       <c r="L105" s="34"/>
       <c r="AO105" s="26"/>
     </row>
     <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B106" s="69"/>
-      <c r="C106" s="70"/>
-      <c r="D106" s="71"/>
+      <c r="B106" s="92"/>
+      <c r="C106" s="93"/>
+      <c r="D106" s="94"/>
       <c r="E106" s="32"/>
-      <c r="F106" s="69"/>
-      <c r="G106" s="70"/>
-      <c r="H106" s="71"/>
+      <c r="F106" s="92"/>
+      <c r="G106" s="93"/>
+      <c r="H106" s="94"/>
       <c r="I106" s="32"/>
-      <c r="J106" s="69"/>
-      <c r="K106" s="70"/>
-      <c r="L106" s="71"/>
+      <c r="J106" s="92"/>
+      <c r="K106" s="93"/>
+      <c r="L106" s="94"/>
     </row>
     <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B107" s="81"/>
-      <c r="C107" s="82"/>
-      <c r="D107" s="83"/>
+      <c r="B107" s="89"/>
+      <c r="C107" s="90"/>
+      <c r="D107" s="91"/>
       <c r="E107" s="32"/>
-      <c r="F107" s="81"/>
-      <c r="G107" s="82"/>
-      <c r="H107" s="83"/>
+      <c r="F107" s="89"/>
+      <c r="G107" s="90"/>
+      <c r="H107" s="91"/>
       <c r="I107" s="32"/>
-      <c r="J107" s="81"/>
-      <c r="K107" s="82"/>
-      <c r="L107" s="83"/>
+      <c r="J107" s="89"/>
+      <c r="K107" s="90"/>
+      <c r="L107" s="91"/>
     </row>
     <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B108" s="87"/>
-      <c r="C108" s="88"/>
-      <c r="D108" s="89"/>
+      <c r="B108" s="81"/>
+      <c r="C108" s="82"/>
+      <c r="D108" s="83"/>
       <c r="E108" s="32"/>
-      <c r="F108" s="87"/>
-      <c r="G108" s="88"/>
-      <c r="H108" s="89"/>
+      <c r="F108" s="81"/>
+      <c r="G108" s="82"/>
+      <c r="H108" s="83"/>
       <c r="I108" s="31"/>
-      <c r="J108" s="87"/>
-      <c r="K108" s="88"/>
-      <c r="L108" s="89"/>
+      <c r="J108" s="81"/>
+      <c r="K108" s="82"/>
+      <c r="L108" s="83"/>
     </row>
     <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B109" s="62"/>
-      <c r="C109" s="63"/>
-      <c r="D109" s="64"/>
+      <c r="B109" s="71"/>
+      <c r="C109" s="72"/>
+      <c r="D109" s="73"/>
       <c r="E109" s="31"/>
-      <c r="F109" s="62"/>
-      <c r="G109" s="63"/>
-      <c r="H109" s="64"/>
+      <c r="F109" s="71"/>
+      <c r="G109" s="72"/>
+      <c r="H109" s="73"/>
       <c r="I109" s="31"/>
-      <c r="J109" s="62"/>
-      <c r="K109" s="63"/>
-      <c r="L109" s="64"/>
+      <c r="J109" s="71"/>
+      <c r="K109" s="72"/>
+      <c r="L109" s="73"/>
     </row>
     <row r="110" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B110" s="35"/>
@@ -7716,69 +7775,69 @@
       <c r="L110" s="35"/>
     </row>
     <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B111" s="67"/>
-      <c r="C111" s="68"/>
+      <c r="B111" s="87"/>
+      <c r="C111" s="88"/>
       <c r="D111" s="34"/>
       <c r="E111" s="31"/>
-      <c r="F111" s="67"/>
-      <c r="G111" s="68"/>
+      <c r="F111" s="87"/>
+      <c r="G111" s="88"/>
       <c r="H111" s="34"/>
       <c r="I111" s="31"/>
-      <c r="J111" s="67"/>
-      <c r="K111" s="68"/>
+      <c r="J111" s="87"/>
+      <c r="K111" s="88"/>
       <c r="L111" s="34"/>
     </row>
     <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B112" s="69"/>
-      <c r="C112" s="70"/>
-      <c r="D112" s="71"/>
+      <c r="B112" s="92"/>
+      <c r="C112" s="93"/>
+      <c r="D112" s="94"/>
       <c r="E112" s="32"/>
-      <c r="F112" s="69"/>
-      <c r="G112" s="70"/>
-      <c r="H112" s="71"/>
+      <c r="F112" s="92"/>
+      <c r="G112" s="93"/>
+      <c r="H112" s="94"/>
       <c r="I112" s="32"/>
-      <c r="J112" s="69"/>
-      <c r="K112" s="70"/>
-      <c r="L112" s="71"/>
+      <c r="J112" s="92"/>
+      <c r="K112" s="93"/>
+      <c r="L112" s="94"/>
     </row>
     <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B113" s="81"/>
-      <c r="C113" s="82"/>
-      <c r="D113" s="83"/>
+      <c r="B113" s="89"/>
+      <c r="C113" s="90"/>
+      <c r="D113" s="91"/>
       <c r="E113" s="35"/>
-      <c r="F113" s="81"/>
-      <c r="G113" s="82"/>
-      <c r="H113" s="83"/>
+      <c r="F113" s="89"/>
+      <c r="G113" s="90"/>
+      <c r="H113" s="91"/>
       <c r="I113" s="35"/>
-      <c r="J113" s="81"/>
-      <c r="K113" s="82"/>
-      <c r="L113" s="83"/>
+      <c r="J113" s="89"/>
+      <c r="K113" s="90"/>
+      <c r="L113" s="91"/>
     </row>
     <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B114" s="87"/>
-      <c r="C114" s="88"/>
-      <c r="D114" s="89"/>
+      <c r="B114" s="81"/>
+      <c r="C114" s="82"/>
+      <c r="D114" s="83"/>
       <c r="E114" s="32"/>
-      <c r="F114" s="87"/>
-      <c r="G114" s="88"/>
-      <c r="H114" s="89"/>
+      <c r="F114" s="81"/>
+      <c r="G114" s="82"/>
+      <c r="H114" s="83"/>
       <c r="I114" s="32"/>
-      <c r="J114" s="87"/>
-      <c r="K114" s="88"/>
-      <c r="L114" s="89"/>
+      <c r="J114" s="81"/>
+      <c r="K114" s="82"/>
+      <c r="L114" s="83"/>
     </row>
     <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B115" s="62"/>
-      <c r="C115" s="63"/>
-      <c r="D115" s="64"/>
+      <c r="B115" s="71"/>
+      <c r="C115" s="72"/>
+      <c r="D115" s="73"/>
       <c r="E115" s="31"/>
-      <c r="F115" s="62"/>
-      <c r="G115" s="63"/>
-      <c r="H115" s="64"/>
+      <c r="F115" s="71"/>
+      <c r="G115" s="72"/>
+      <c r="H115" s="73"/>
       <c r="I115" s="31"/>
-      <c r="J115" s="62"/>
-      <c r="K115" s="63"/>
-      <c r="L115" s="64"/>
+      <c r="J115" s="71"/>
+      <c r="K115" s="72"/>
+      <c r="L115" s="73"/>
     </row>
     <row r="116" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B116" s="35"/>
@@ -7794,69 +7853,69 @@
       <c r="L116" s="35"/>
     </row>
     <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B117" s="67"/>
-      <c r="C117" s="68"/>
+      <c r="B117" s="87"/>
+      <c r="C117" s="88"/>
       <c r="D117" s="34"/>
       <c r="E117" s="32"/>
-      <c r="F117" s="67"/>
-      <c r="G117" s="68"/>
+      <c r="F117" s="87"/>
+      <c r="G117" s="88"/>
       <c r="H117" s="34"/>
       <c r="I117" s="32"/>
-      <c r="J117" s="67"/>
-      <c r="K117" s="68"/>
+      <c r="J117" s="87"/>
+      <c r="K117" s="88"/>
       <c r="L117" s="34"/>
     </row>
     <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B118" s="69"/>
-      <c r="C118" s="70"/>
-      <c r="D118" s="71"/>
+      <c r="B118" s="92"/>
+      <c r="C118" s="93"/>
+      <c r="D118" s="94"/>
       <c r="E118" s="32"/>
-      <c r="F118" s="69"/>
-      <c r="G118" s="70"/>
-      <c r="H118" s="71"/>
+      <c r="F118" s="92"/>
+      <c r="G118" s="93"/>
+      <c r="H118" s="94"/>
       <c r="I118" s="32"/>
-      <c r="J118" s="69"/>
-      <c r="K118" s="70"/>
-      <c r="L118" s="71"/>
+      <c r="J118" s="92"/>
+      <c r="K118" s="93"/>
+      <c r="L118" s="94"/>
     </row>
     <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B119" s="81"/>
-      <c r="C119" s="82"/>
-      <c r="D119" s="83"/>
+      <c r="B119" s="89"/>
+      <c r="C119" s="90"/>
+      <c r="D119" s="91"/>
       <c r="E119" s="32"/>
-      <c r="F119" s="81"/>
-      <c r="G119" s="82"/>
-      <c r="H119" s="83"/>
+      <c r="F119" s="89"/>
+      <c r="G119" s="90"/>
+      <c r="H119" s="91"/>
       <c r="I119" s="32"/>
-      <c r="J119" s="81"/>
-      <c r="K119" s="82"/>
-      <c r="L119" s="83"/>
+      <c r="J119" s="89"/>
+      <c r="K119" s="90"/>
+      <c r="L119" s="91"/>
     </row>
     <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B120" s="87"/>
-      <c r="C120" s="88"/>
-      <c r="D120" s="89"/>
+      <c r="B120" s="81"/>
+      <c r="C120" s="82"/>
+      <c r="D120" s="83"/>
       <c r="E120" s="32"/>
-      <c r="F120" s="87"/>
-      <c r="G120" s="88"/>
-      <c r="H120" s="89"/>
+      <c r="F120" s="81"/>
+      <c r="G120" s="82"/>
+      <c r="H120" s="83"/>
       <c r="I120" s="32"/>
-      <c r="J120" s="87"/>
-      <c r="K120" s="88"/>
-      <c r="L120" s="89"/>
+      <c r="J120" s="81"/>
+      <c r="K120" s="82"/>
+      <c r="L120" s="83"/>
     </row>
     <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B121" s="62"/>
-      <c r="C121" s="63"/>
-      <c r="D121" s="64"/>
+      <c r="B121" s="71"/>
+      <c r="C121" s="72"/>
+      <c r="D121" s="73"/>
       <c r="E121" s="31"/>
-      <c r="F121" s="62"/>
-      <c r="G121" s="63"/>
-      <c r="H121" s="64"/>
+      <c r="F121" s="71"/>
+      <c r="G121" s="72"/>
+      <c r="H121" s="73"/>
       <c r="I121" s="31"/>
-      <c r="J121" s="62"/>
-      <c r="K121" s="63"/>
-      <c r="L121" s="64"/>
+      <c r="J121" s="71"/>
+      <c r="K121" s="72"/>
+      <c r="L121" s="73"/>
     </row>
     <row r="122" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B122" s="35"/>
@@ -7872,69 +7931,69 @@
       <c r="L122" s="35"/>
     </row>
     <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B123" s="67"/>
-      <c r="C123" s="68"/>
+      <c r="B123" s="87"/>
+      <c r="C123" s="88"/>
       <c r="D123" s="34"/>
       <c r="E123" s="32"/>
-      <c r="F123" s="67"/>
-      <c r="G123" s="68"/>
+      <c r="F123" s="87"/>
+      <c r="G123" s="88"/>
       <c r="H123" s="34"/>
       <c r="I123" s="32"/>
-      <c r="J123" s="67"/>
-      <c r="K123" s="68"/>
+      <c r="J123" s="87"/>
+      <c r="K123" s="88"/>
       <c r="L123" s="34"/>
     </row>
     <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B124" s="69"/>
-      <c r="C124" s="70"/>
-      <c r="D124" s="71"/>
+      <c r="B124" s="92"/>
+      <c r="C124" s="93"/>
+      <c r="D124" s="94"/>
       <c r="E124" s="32"/>
-      <c r="F124" s="69"/>
-      <c r="G124" s="70"/>
-      <c r="H124" s="71"/>
+      <c r="F124" s="92"/>
+      <c r="G124" s="93"/>
+      <c r="H124" s="94"/>
       <c r="I124" s="32"/>
-      <c r="J124" s="69"/>
-      <c r="K124" s="70"/>
-      <c r="L124" s="71"/>
+      <c r="J124" s="92"/>
+      <c r="K124" s="93"/>
+      <c r="L124" s="94"/>
     </row>
     <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B125" s="81"/>
-      <c r="C125" s="82"/>
-      <c r="D125" s="83"/>
+      <c r="B125" s="89"/>
+      <c r="C125" s="90"/>
+      <c r="D125" s="91"/>
       <c r="E125" s="32"/>
-      <c r="F125" s="81"/>
-      <c r="G125" s="82"/>
-      <c r="H125" s="83"/>
+      <c r="F125" s="89"/>
+      <c r="G125" s="90"/>
+      <c r="H125" s="91"/>
       <c r="I125" s="32"/>
-      <c r="J125" s="81"/>
-      <c r="K125" s="82"/>
-      <c r="L125" s="83"/>
+      <c r="J125" s="89"/>
+      <c r="K125" s="90"/>
+      <c r="L125" s="91"/>
     </row>
     <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B126" s="87"/>
-      <c r="C126" s="88"/>
-      <c r="D126" s="89"/>
+      <c r="B126" s="81"/>
+      <c r="C126" s="82"/>
+      <c r="D126" s="83"/>
       <c r="E126" s="32"/>
-      <c r="F126" s="87"/>
-      <c r="G126" s="88"/>
-      <c r="H126" s="89"/>
+      <c r="F126" s="81"/>
+      <c r="G126" s="82"/>
+      <c r="H126" s="83"/>
       <c r="I126" s="31"/>
-      <c r="J126" s="87"/>
-      <c r="K126" s="88"/>
-      <c r="L126" s="89"/>
+      <c r="J126" s="81"/>
+      <c r="K126" s="82"/>
+      <c r="L126" s="83"/>
     </row>
     <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B127" s="62"/>
-      <c r="C127" s="63"/>
-      <c r="D127" s="64"/>
+      <c r="B127" s="71"/>
+      <c r="C127" s="72"/>
+      <c r="D127" s="73"/>
       <c r="E127" s="31"/>
-      <c r="F127" s="62"/>
-      <c r="G127" s="63"/>
-      <c r="H127" s="64"/>
+      <c r="F127" s="71"/>
+      <c r="G127" s="72"/>
+      <c r="H127" s="73"/>
       <c r="I127" s="31"/>
-      <c r="J127" s="62"/>
-      <c r="K127" s="63"/>
-      <c r="L127" s="64"/>
+      <c r="J127" s="71"/>
+      <c r="K127" s="72"/>
+      <c r="L127" s="73"/>
     </row>
     <row r="128" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B128" s="35"/>
@@ -7950,126 +8009,852 @@
       <c r="L128" s="35"/>
     </row>
     <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B129" s="67"/>
-      <c r="C129" s="68"/>
+      <c r="B129" s="87"/>
+      <c r="C129" s="88"/>
       <c r="D129" s="34"/>
       <c r="E129" s="31"/>
-      <c r="F129" s="67"/>
-      <c r="G129" s="68"/>
+      <c r="F129" s="87"/>
+      <c r="G129" s="88"/>
       <c r="H129" s="34"/>
       <c r="I129" s="32"/>
-      <c r="J129" s="67"/>
-      <c r="K129" s="68"/>
+      <c r="J129" s="87"/>
+      <c r="K129" s="88"/>
       <c r="L129" s="34"/>
     </row>
     <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B130" s="69"/>
-      <c r="C130" s="70"/>
-      <c r="D130" s="71"/>
+      <c r="B130" s="92"/>
+      <c r="C130" s="93"/>
+      <c r="D130" s="94"/>
       <c r="E130" s="32"/>
-      <c r="F130" s="69"/>
-      <c r="G130" s="70"/>
-      <c r="H130" s="71"/>
+      <c r="F130" s="92"/>
+      <c r="G130" s="93"/>
+      <c r="H130" s="94"/>
       <c r="I130" s="32"/>
-      <c r="J130" s="69"/>
-      <c r="K130" s="70"/>
-      <c r="L130" s="71"/>
+      <c r="J130" s="92"/>
+      <c r="K130" s="93"/>
+      <c r="L130" s="94"/>
     </row>
     <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B131" s="81"/>
-      <c r="C131" s="82"/>
-      <c r="D131" s="83"/>
+      <c r="B131" s="89"/>
+      <c r="C131" s="90"/>
+      <c r="D131" s="91"/>
       <c r="E131" s="35"/>
-      <c r="F131" s="81"/>
-      <c r="G131" s="82"/>
-      <c r="H131" s="83"/>
+      <c r="F131" s="89"/>
+      <c r="G131" s="90"/>
+      <c r="H131" s="91"/>
       <c r="I131" s="32"/>
-      <c r="J131" s="81"/>
-      <c r="K131" s="82"/>
-      <c r="L131" s="83"/>
+      <c r="J131" s="89"/>
+      <c r="K131" s="90"/>
+      <c r="L131" s="91"/>
     </row>
     <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B132" s="87"/>
-      <c r="C132" s="88"/>
-      <c r="D132" s="89"/>
+      <c r="B132" s="81"/>
+      <c r="C132" s="82"/>
+      <c r="D132" s="83"/>
       <c r="E132" s="35"/>
-      <c r="F132" s="87"/>
-      <c r="G132" s="88"/>
-      <c r="H132" s="89"/>
+      <c r="F132" s="81"/>
+      <c r="G132" s="82"/>
+      <c r="H132" s="83"/>
       <c r="I132" s="31"/>
-      <c r="J132" s="87"/>
-      <c r="K132" s="88"/>
-      <c r="L132" s="89"/>
+      <c r="J132" s="81"/>
+      <c r="K132" s="82"/>
+      <c r="L132" s="83"/>
     </row>
     <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B133" s="62"/>
-      <c r="C133" s="63"/>
-      <c r="D133" s="64"/>
+      <c r="B133" s="71"/>
+      <c r="C133" s="72"/>
+      <c r="D133" s="73"/>
       <c r="E133" s="31"/>
-      <c r="F133" s="62"/>
-      <c r="G133" s="63"/>
-      <c r="H133" s="64"/>
+      <c r="F133" s="71"/>
+      <c r="G133" s="72"/>
+      <c r="H133" s="73"/>
       <c r="I133" s="31"/>
-      <c r="J133" s="62"/>
-      <c r="K133" s="63"/>
-      <c r="L133" s="64"/>
+      <c r="J133" s="71"/>
+      <c r="K133" s="72"/>
+      <c r="L133" s="73"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0" selectUnlockedCells="1"/>
   <dataConsolidate/>
   <mergeCells count="862">
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="F50:H50"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="J39:L39"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="J41:L41"/>
-    <mergeCell ref="J40:L40"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="AL75:AM75"/>
-    <mergeCell ref="AH71:AJ71"/>
-    <mergeCell ref="AD71:AF71"/>
-    <mergeCell ref="Z71:AB71"/>
-    <mergeCell ref="AL66:AM66"/>
-    <mergeCell ref="AD69:AF69"/>
-    <mergeCell ref="AH69:AJ69"/>
-    <mergeCell ref="AD64:AF64"/>
-    <mergeCell ref="AD61:AF61"/>
-    <mergeCell ref="AH61:AJ61"/>
-    <mergeCell ref="Z57:AB57"/>
-    <mergeCell ref="AD54:AF54"/>
-    <mergeCell ref="AD55:AF55"/>
-    <mergeCell ref="AD32:AE32"/>
-    <mergeCell ref="AH32:AI32"/>
-    <mergeCell ref="AL32:AM32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="B97:D97"/>
+    <mergeCell ref="F97:H97"/>
+    <mergeCell ref="J97:L97"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="F99:G99"/>
+    <mergeCell ref="J99:K99"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="J87:K87"/>
+    <mergeCell ref="B91:D91"/>
+    <mergeCell ref="F91:H91"/>
+    <mergeCell ref="J91:L91"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="F93:G93"/>
+    <mergeCell ref="J93:K93"/>
+    <mergeCell ref="AL57:AN57"/>
+    <mergeCell ref="AL59:AM59"/>
+    <mergeCell ref="AL46:AN46"/>
+    <mergeCell ref="F79:H79"/>
+    <mergeCell ref="J79:L79"/>
+    <mergeCell ref="F71:H71"/>
+    <mergeCell ref="J71:L71"/>
+    <mergeCell ref="F64:H64"/>
+    <mergeCell ref="F78:H78"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="R50:T50"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="J48:L48"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="AL56:AN56"/>
+    <mergeCell ref="AL54:AN54"/>
+    <mergeCell ref="AL53:AN53"/>
+    <mergeCell ref="AL49:AN49"/>
+    <mergeCell ref="AL55:AN55"/>
+    <mergeCell ref="F60:H60"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="J60:L60"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R41:T41"/>
+    <mergeCell ref="R40:T40"/>
+    <mergeCell ref="R43:T43"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="R39:T39"/>
+    <mergeCell ref="V38:W38"/>
+    <mergeCell ref="V39:X39"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="V43:X43"/>
+    <mergeCell ref="AD56:AF56"/>
+    <mergeCell ref="AH57:AJ57"/>
+    <mergeCell ref="AH59:AI59"/>
+    <mergeCell ref="AH56:AJ56"/>
+    <mergeCell ref="AH53:AJ53"/>
+    <mergeCell ref="AH47:AJ47"/>
+    <mergeCell ref="AD59:AE59"/>
+    <mergeCell ref="AD53:AF53"/>
+    <mergeCell ref="AD50:AF50"/>
+    <mergeCell ref="AD52:AE52"/>
+    <mergeCell ref="AD57:AF57"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="F82:H82"/>
+    <mergeCell ref="AL50:AN50"/>
+    <mergeCell ref="AL52:AM52"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="F62:H62"/>
+    <mergeCell ref="F61:H61"/>
+    <mergeCell ref="J64:L64"/>
+    <mergeCell ref="F69:H69"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="J66:K66"/>
+    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="F67:H67"/>
+    <mergeCell ref="J67:L67"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="F68:H68"/>
+    <mergeCell ref="J68:L68"/>
+    <mergeCell ref="F63:H63"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="J78:L78"/>
+    <mergeCell ref="J81:K81"/>
+    <mergeCell ref="J82:L82"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B95:D95"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="J70:L70"/>
+    <mergeCell ref="B71:D71"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="F70:H70"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="F76:H76"/>
+    <mergeCell ref="F90:H90"/>
+    <mergeCell ref="F95:H95"/>
+    <mergeCell ref="F89:H89"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="F94:H94"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="B85:D85"/>
+    <mergeCell ref="F85:H85"/>
+    <mergeCell ref="F75:G75"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="F54:H54"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="J100:L100"/>
+    <mergeCell ref="J88:L88"/>
+    <mergeCell ref="J77:L77"/>
+    <mergeCell ref="J76:L76"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="B96:D96"/>
+    <mergeCell ref="F96:H96"/>
+    <mergeCell ref="B100:D100"/>
+    <mergeCell ref="F100:H100"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="F88:H88"/>
+    <mergeCell ref="B89:D89"/>
+    <mergeCell ref="F83:H83"/>
+    <mergeCell ref="F84:H84"/>
+    <mergeCell ref="F77:H77"/>
+    <mergeCell ref="J53:L53"/>
+    <mergeCell ref="J54:L54"/>
+    <mergeCell ref="N91:P91"/>
+    <mergeCell ref="N97:P97"/>
+    <mergeCell ref="J96:L96"/>
+    <mergeCell ref="J90:L90"/>
+    <mergeCell ref="N99:O99"/>
+    <mergeCell ref="N88:P88"/>
+    <mergeCell ref="N83:P83"/>
+    <mergeCell ref="N84:P84"/>
+    <mergeCell ref="N90:P90"/>
+    <mergeCell ref="J89:L89"/>
+    <mergeCell ref="J83:L83"/>
+    <mergeCell ref="J84:L84"/>
+    <mergeCell ref="N89:P89"/>
+    <mergeCell ref="N87:O87"/>
+    <mergeCell ref="N93:O93"/>
+    <mergeCell ref="N85:P85"/>
+    <mergeCell ref="J85:L85"/>
+    <mergeCell ref="R102:T102"/>
+    <mergeCell ref="R100:T100"/>
+    <mergeCell ref="V100:X100"/>
+    <mergeCell ref="R101:T101"/>
+    <mergeCell ref="N100:P100"/>
+    <mergeCell ref="Z100:AB100"/>
+    <mergeCell ref="N94:P94"/>
+    <mergeCell ref="R95:T95"/>
+    <mergeCell ref="N96:P96"/>
+    <mergeCell ref="R99:S99"/>
+    <mergeCell ref="V99:W99"/>
+    <mergeCell ref="Z99:AA99"/>
+    <mergeCell ref="V95:X95"/>
+    <mergeCell ref="Z96:AB96"/>
+    <mergeCell ref="R96:T96"/>
+    <mergeCell ref="N101:P101"/>
+    <mergeCell ref="N95:P95"/>
+    <mergeCell ref="V101:X101"/>
+    <mergeCell ref="Z101:AB101"/>
+    <mergeCell ref="Z94:AB94"/>
+    <mergeCell ref="Z95:AB95"/>
+    <mergeCell ref="B108:D108"/>
+    <mergeCell ref="J102:L102"/>
+    <mergeCell ref="J112:L112"/>
+    <mergeCell ref="J111:K111"/>
+    <mergeCell ref="B106:D106"/>
+    <mergeCell ref="B107:D107"/>
+    <mergeCell ref="F106:H106"/>
+    <mergeCell ref="F105:G105"/>
+    <mergeCell ref="N102:P102"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="F102:H102"/>
+    <mergeCell ref="F107:H107"/>
+    <mergeCell ref="J107:L107"/>
+    <mergeCell ref="J109:L109"/>
+    <mergeCell ref="B120:D120"/>
+    <mergeCell ref="B121:D121"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="F123:G123"/>
+    <mergeCell ref="B119:D119"/>
+    <mergeCell ref="B113:D113"/>
+    <mergeCell ref="F113:H113"/>
+    <mergeCell ref="J113:L113"/>
+    <mergeCell ref="B114:D114"/>
+    <mergeCell ref="F114:H114"/>
+    <mergeCell ref="J114:L114"/>
+    <mergeCell ref="B115:D115"/>
+    <mergeCell ref="F115:H115"/>
+    <mergeCell ref="J115:L115"/>
+    <mergeCell ref="B112:D112"/>
+    <mergeCell ref="F120:H120"/>
+    <mergeCell ref="B126:D126"/>
+    <mergeCell ref="F126:H126"/>
+    <mergeCell ref="J126:L126"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="J117:K117"/>
+    <mergeCell ref="J108:L108"/>
+    <mergeCell ref="F121:H121"/>
+    <mergeCell ref="J123:K123"/>
+    <mergeCell ref="F112:H112"/>
+    <mergeCell ref="B125:D125"/>
+    <mergeCell ref="F125:H125"/>
+    <mergeCell ref="J121:L121"/>
+    <mergeCell ref="J125:L125"/>
+    <mergeCell ref="B118:D118"/>
+    <mergeCell ref="F118:H118"/>
+    <mergeCell ref="B109:D109"/>
+    <mergeCell ref="F109:H109"/>
+    <mergeCell ref="F124:H124"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="F111:G111"/>
+    <mergeCell ref="J124:L124"/>
+    <mergeCell ref="F119:H119"/>
+    <mergeCell ref="J119:L119"/>
+    <mergeCell ref="J101:L101"/>
+    <mergeCell ref="J118:L118"/>
+    <mergeCell ref="B124:D124"/>
+    <mergeCell ref="F108:H108"/>
+    <mergeCell ref="B133:D133"/>
+    <mergeCell ref="F133:H133"/>
+    <mergeCell ref="J133:L133"/>
+    <mergeCell ref="B127:D127"/>
+    <mergeCell ref="F127:H127"/>
+    <mergeCell ref="J127:L127"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="F129:G129"/>
+    <mergeCell ref="J129:K129"/>
+    <mergeCell ref="B130:D130"/>
+    <mergeCell ref="F130:H130"/>
+    <mergeCell ref="J130:L130"/>
+    <mergeCell ref="B132:D132"/>
+    <mergeCell ref="F132:H132"/>
+    <mergeCell ref="J132:L132"/>
+    <mergeCell ref="B131:D131"/>
+    <mergeCell ref="F131:H131"/>
+    <mergeCell ref="J131:L131"/>
+    <mergeCell ref="J120:L120"/>
+    <mergeCell ref="B101:D101"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="N18:AB19"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="R14:T14"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="J105:K105"/>
+    <mergeCell ref="V41:X41"/>
+    <mergeCell ref="V40:X40"/>
+    <mergeCell ref="J106:L106"/>
+    <mergeCell ref="Z102:AB102"/>
+    <mergeCell ref="V102:X102"/>
+    <mergeCell ref="Z55:AB55"/>
+    <mergeCell ref="J75:K75"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="J69:L69"/>
+    <mergeCell ref="N62:P62"/>
+    <mergeCell ref="R62:T62"/>
+    <mergeCell ref="R71:T71"/>
+    <mergeCell ref="R76:T76"/>
+    <mergeCell ref="R63:T63"/>
+    <mergeCell ref="F101:H101"/>
+    <mergeCell ref="R94:T94"/>
+    <mergeCell ref="Z88:AB88"/>
+    <mergeCell ref="J94:L94"/>
+    <mergeCell ref="J95:L95"/>
+    <mergeCell ref="V94:X94"/>
+    <mergeCell ref="V96:X96"/>
+    <mergeCell ref="AH9:AJ9"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="AH21:AI21"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="Z20:AA20"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="V15:X15"/>
+    <mergeCell ref="V16:X16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="V13:W13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="AL9:AN9"/>
+    <mergeCell ref="AD9:AF9"/>
+    <mergeCell ref="AH16:AJ16"/>
+    <mergeCell ref="AL10:AN10"/>
+    <mergeCell ref="AL14:AN14"/>
+    <mergeCell ref="AL16:AN16"/>
+    <mergeCell ref="Z15:AB15"/>
+    <mergeCell ref="AD15:AF15"/>
+    <mergeCell ref="Z13:AA13"/>
+    <mergeCell ref="AL15:AN15"/>
+    <mergeCell ref="AL12:AM12"/>
+    <mergeCell ref="AD16:AF16"/>
+    <mergeCell ref="Z10:AB10"/>
+    <mergeCell ref="AH14:AJ14"/>
+    <mergeCell ref="Z14:AB14"/>
+    <mergeCell ref="AD14:AF14"/>
+    <mergeCell ref="AD13:AE13"/>
+    <mergeCell ref="AH10:AJ10"/>
+    <mergeCell ref="AH15:AJ15"/>
+    <mergeCell ref="AD10:AF10"/>
+    <mergeCell ref="AD12:AE12"/>
+    <mergeCell ref="AH12:AI12"/>
+    <mergeCell ref="Z12:AA12"/>
+    <mergeCell ref="Z16:AB16"/>
+    <mergeCell ref="AH31:AI31"/>
+    <mergeCell ref="AD31:AE31"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="Z21:AA21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="R22:T22"/>
+    <mergeCell ref="V22:X22"/>
+    <mergeCell ref="Z22:AB22"/>
+    <mergeCell ref="AD22:AF22"/>
+    <mergeCell ref="AH22:AJ22"/>
+    <mergeCell ref="AD29:AE29"/>
+    <mergeCell ref="AH29:AI29"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:T23"/>
+    <mergeCell ref="V23:X23"/>
+    <mergeCell ref="V27:W27"/>
+    <mergeCell ref="AD27:AE27"/>
+    <mergeCell ref="V31:W31"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="AL1:AN1"/>
+    <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="AD2:AF2"/>
+    <mergeCell ref="AH2:AJ2"/>
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="AH8:AJ8"/>
+    <mergeCell ref="AL6:AM6"/>
+    <mergeCell ref="AD1:AF1"/>
+    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="AL7:AM7"/>
+    <mergeCell ref="AD8:AF8"/>
+    <mergeCell ref="Z8:AB8"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AH7:AI7"/>
+    <mergeCell ref="AD7:AE7"/>
+    <mergeCell ref="Z7:AA7"/>
+    <mergeCell ref="AL8:AN8"/>
+    <mergeCell ref="AD4:AN5"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="AD6:AE6"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="V1:X1"/>
+    <mergeCell ref="V14:X14"/>
+    <mergeCell ref="R15:T15"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="B4:L5"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="V2:X2"/>
+    <mergeCell ref="N4:AB5"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="R9:T9"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="AH90:AJ90"/>
+    <mergeCell ref="AD42:AF42"/>
+    <mergeCell ref="AD48:AF48"/>
+    <mergeCell ref="Z9:AB9"/>
+    <mergeCell ref="R10:T10"/>
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="AD21:AE21"/>
+    <mergeCell ref="AD49:AF49"/>
+    <mergeCell ref="AD43:AF43"/>
+    <mergeCell ref="AD45:AE45"/>
+    <mergeCell ref="R48:T48"/>
+    <mergeCell ref="Z42:AB42"/>
+    <mergeCell ref="Z43:AB43"/>
+    <mergeCell ref="N36:AB37"/>
+    <mergeCell ref="Z48:AB48"/>
+    <mergeCell ref="Z45:AA45"/>
+    <mergeCell ref="Z46:AB46"/>
+    <mergeCell ref="AD38:AE38"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="AL82:AN82"/>
+    <mergeCell ref="AL102:AN102"/>
+    <mergeCell ref="AL101:AN101"/>
+    <mergeCell ref="AL96:AN96"/>
+    <mergeCell ref="AD102:AF102"/>
+    <mergeCell ref="AH102:AJ102"/>
+    <mergeCell ref="AL90:AN90"/>
+    <mergeCell ref="AL95:AN95"/>
+    <mergeCell ref="AD101:AF101"/>
+    <mergeCell ref="AH101:AJ101"/>
+    <mergeCell ref="AH100:AJ100"/>
+    <mergeCell ref="AL94:AN94"/>
+    <mergeCell ref="AD100:AF100"/>
+    <mergeCell ref="AD96:AF96"/>
+    <mergeCell ref="AD94:AF94"/>
+    <mergeCell ref="AD95:AF95"/>
+    <mergeCell ref="AH96:AJ96"/>
+    <mergeCell ref="AD90:AF90"/>
+    <mergeCell ref="AH95:AJ95"/>
+    <mergeCell ref="V90:X90"/>
+    <mergeCell ref="V88:X88"/>
+    <mergeCell ref="AL77:AN77"/>
+    <mergeCell ref="AL78:AN78"/>
+    <mergeCell ref="AD77:AF77"/>
+    <mergeCell ref="AD79:AF79"/>
+    <mergeCell ref="AH79:AJ79"/>
+    <mergeCell ref="AL79:AN79"/>
+    <mergeCell ref="AD81:AE81"/>
+    <mergeCell ref="AH81:AI81"/>
+    <mergeCell ref="AL81:AM81"/>
+    <mergeCell ref="AH78:AJ78"/>
+    <mergeCell ref="R83:T83"/>
+    <mergeCell ref="AD82:AF82"/>
+    <mergeCell ref="AH83:AJ83"/>
+    <mergeCell ref="AD84:AF84"/>
+    <mergeCell ref="AH84:AJ84"/>
+    <mergeCell ref="AD83:AF83"/>
+    <mergeCell ref="AH94:AJ94"/>
+    <mergeCell ref="AL100:AN100"/>
+    <mergeCell ref="AD97:AF97"/>
+    <mergeCell ref="AH97:AJ97"/>
+    <mergeCell ref="AL97:AN97"/>
+    <mergeCell ref="AH82:AJ82"/>
+    <mergeCell ref="AL88:AN88"/>
+    <mergeCell ref="AL89:AN89"/>
+    <mergeCell ref="AL83:AN83"/>
+    <mergeCell ref="AL84:AN84"/>
+    <mergeCell ref="AD88:AF88"/>
+    <mergeCell ref="AD89:AF89"/>
+    <mergeCell ref="AH87:AI87"/>
+    <mergeCell ref="AL87:AM87"/>
+    <mergeCell ref="R90:T90"/>
+    <mergeCell ref="AH88:AJ88"/>
+    <mergeCell ref="AH89:AJ89"/>
+    <mergeCell ref="AD85:AF85"/>
+    <mergeCell ref="AH85:AJ85"/>
+    <mergeCell ref="AL85:AN85"/>
+    <mergeCell ref="AH75:AI75"/>
+    <mergeCell ref="V89:X89"/>
+    <mergeCell ref="R89:T89"/>
+    <mergeCell ref="R84:T84"/>
+    <mergeCell ref="R85:T85"/>
+    <mergeCell ref="V85:X85"/>
+    <mergeCell ref="Z76:AB76"/>
+    <mergeCell ref="Z77:AB77"/>
+    <mergeCell ref="V76:X76"/>
+    <mergeCell ref="AH77:AJ77"/>
+    <mergeCell ref="AD78:AF78"/>
+    <mergeCell ref="V82:X82"/>
+    <mergeCell ref="R88:T88"/>
+    <mergeCell ref="V77:X77"/>
+    <mergeCell ref="V78:X78"/>
+    <mergeCell ref="R78:T78"/>
+    <mergeCell ref="V84:X84"/>
+    <mergeCell ref="R82:T82"/>
+    <mergeCell ref="V83:X83"/>
+    <mergeCell ref="N78:P78"/>
+    <mergeCell ref="Z78:AB78"/>
+    <mergeCell ref="N79:P79"/>
+    <mergeCell ref="R79:T79"/>
+    <mergeCell ref="V79:X79"/>
+    <mergeCell ref="Z79:AB79"/>
+    <mergeCell ref="N81:O81"/>
+    <mergeCell ref="R81:S81"/>
+    <mergeCell ref="V81:W81"/>
+    <mergeCell ref="N82:P82"/>
+    <mergeCell ref="AH76:AJ76"/>
+    <mergeCell ref="AL76:AN76"/>
+    <mergeCell ref="AD76:AF76"/>
+    <mergeCell ref="Z81:AA81"/>
+    <mergeCell ref="AL62:AN62"/>
+    <mergeCell ref="AL63:AN63"/>
+    <mergeCell ref="AL71:AN71"/>
+    <mergeCell ref="AL70:AN70"/>
+    <mergeCell ref="AL69:AN69"/>
+    <mergeCell ref="N73:AB74"/>
+    <mergeCell ref="N75:O75"/>
+    <mergeCell ref="R75:S75"/>
+    <mergeCell ref="V75:W75"/>
+    <mergeCell ref="Z75:AA75"/>
+    <mergeCell ref="AD75:AE75"/>
+    <mergeCell ref="N64:P64"/>
+    <mergeCell ref="N70:P70"/>
+    <mergeCell ref="AH70:AJ70"/>
+    <mergeCell ref="AD70:AF70"/>
+    <mergeCell ref="Z69:AB69"/>
+    <mergeCell ref="Z70:AB70"/>
+    <mergeCell ref="V71:X71"/>
+    <mergeCell ref="AD63:AF63"/>
+    <mergeCell ref="AH64:AJ64"/>
+    <mergeCell ref="AD67:AF67"/>
+    <mergeCell ref="AL20:AM20"/>
+    <mergeCell ref="AL27:AM27"/>
+    <mergeCell ref="AL21:AM21"/>
+    <mergeCell ref="AH27:AI27"/>
+    <mergeCell ref="AD20:AE20"/>
+    <mergeCell ref="AH20:AI20"/>
+    <mergeCell ref="Z68:AB68"/>
+    <mergeCell ref="AD68:AF68"/>
+    <mergeCell ref="AH68:AJ68"/>
+    <mergeCell ref="AL68:AN68"/>
+    <mergeCell ref="Z63:AB63"/>
+    <mergeCell ref="AL60:AN60"/>
+    <mergeCell ref="AL64:AN64"/>
+    <mergeCell ref="AL61:AN61"/>
+    <mergeCell ref="Z56:AB56"/>
+    <mergeCell ref="AL22:AN22"/>
+    <mergeCell ref="Z23:AB23"/>
+    <mergeCell ref="AD23:AF23"/>
+    <mergeCell ref="AH23:AJ23"/>
+    <mergeCell ref="AL23:AN23"/>
+    <mergeCell ref="AD28:AE28"/>
+    <mergeCell ref="AH28:AI28"/>
+    <mergeCell ref="AL28:AM28"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="N61:P61"/>
+    <mergeCell ref="AD66:AE66"/>
+    <mergeCell ref="AH66:AI66"/>
+    <mergeCell ref="R61:T61"/>
+    <mergeCell ref="V61:X61"/>
+    <mergeCell ref="Z61:AB61"/>
+    <mergeCell ref="Z59:AA59"/>
+    <mergeCell ref="AH63:AJ63"/>
+    <mergeCell ref="AH62:AJ62"/>
+    <mergeCell ref="AD62:AF62"/>
+    <mergeCell ref="AD60:AF60"/>
+    <mergeCell ref="AH60:AJ60"/>
+    <mergeCell ref="V62:X62"/>
+    <mergeCell ref="V63:X63"/>
+    <mergeCell ref="Z64:AB64"/>
+    <mergeCell ref="R60:T60"/>
+    <mergeCell ref="V60:X60"/>
+    <mergeCell ref="Z60:AB60"/>
+    <mergeCell ref="V64:X64"/>
+    <mergeCell ref="R64:T64"/>
+    <mergeCell ref="N63:P63"/>
+    <mergeCell ref="N66:O66"/>
+    <mergeCell ref="N60:P60"/>
+    <mergeCell ref="V33:W33"/>
+    <mergeCell ref="Z33:AA33"/>
+    <mergeCell ref="N32:O32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="V32:W32"/>
+    <mergeCell ref="Z32:AA32"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="N29:O29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="V29:W29"/>
+    <mergeCell ref="Z29:AA29"/>
+    <mergeCell ref="Z27:AA27"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="V30:W30"/>
+    <mergeCell ref="Z31:AA31"/>
+    <mergeCell ref="V50:X50"/>
+    <mergeCell ref="Z53:AA53"/>
+    <mergeCell ref="R49:T49"/>
+    <mergeCell ref="R47:T47"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="J46:L46"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="N45:O45"/>
+    <mergeCell ref="J49:L49"/>
+    <mergeCell ref="J47:L47"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="Z54:AB54"/>
+    <mergeCell ref="Z50:AB50"/>
+    <mergeCell ref="V45:W45"/>
+    <mergeCell ref="V46:X46"/>
+    <mergeCell ref="V47:X47"/>
+    <mergeCell ref="Z49:AB49"/>
+    <mergeCell ref="V49:X49"/>
+    <mergeCell ref="V48:X48"/>
+    <mergeCell ref="AH34:AI34"/>
+    <mergeCell ref="AD46:AF46"/>
+    <mergeCell ref="AD47:AF47"/>
+    <mergeCell ref="AH40:AJ40"/>
+    <mergeCell ref="AH46:AJ46"/>
+    <mergeCell ref="AH45:AI45"/>
+    <mergeCell ref="AH38:AI38"/>
+    <mergeCell ref="AH39:AJ39"/>
+    <mergeCell ref="AD39:AF39"/>
+    <mergeCell ref="AD40:AF40"/>
+    <mergeCell ref="AL45:AM45"/>
+    <mergeCell ref="AL42:AN42"/>
+    <mergeCell ref="Z41:AB41"/>
+    <mergeCell ref="Z40:AB40"/>
+    <mergeCell ref="Z38:AA38"/>
+    <mergeCell ref="Z39:AB39"/>
+    <mergeCell ref="AL34:AM34"/>
+    <mergeCell ref="N55:P55"/>
+    <mergeCell ref="R56:T56"/>
+    <mergeCell ref="N56:P56"/>
+    <mergeCell ref="R54:T54"/>
+    <mergeCell ref="V54:X54"/>
+    <mergeCell ref="V53:W53"/>
+    <mergeCell ref="N54:P54"/>
+    <mergeCell ref="N53:P53"/>
+    <mergeCell ref="R55:T55"/>
+    <mergeCell ref="R53:T53"/>
+    <mergeCell ref="V56:X56"/>
+    <mergeCell ref="V55:X55"/>
+    <mergeCell ref="V42:X42"/>
+    <mergeCell ref="AH52:AI52"/>
+    <mergeCell ref="AH54:AJ54"/>
+    <mergeCell ref="AH55:AJ55"/>
+    <mergeCell ref="R42:T42"/>
+    <mergeCell ref="AL31:AM31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="R87:S87"/>
+    <mergeCell ref="V87:W87"/>
+    <mergeCell ref="Z87:AA87"/>
+    <mergeCell ref="AD87:AE87"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="V34:W34"/>
+    <mergeCell ref="Z34:AA34"/>
+    <mergeCell ref="AD34:AE34"/>
+    <mergeCell ref="R66:S66"/>
+    <mergeCell ref="V66:W66"/>
+    <mergeCell ref="Z66:AA66"/>
+    <mergeCell ref="R67:T67"/>
+    <mergeCell ref="V67:X67"/>
+    <mergeCell ref="Z67:AB67"/>
+    <mergeCell ref="V69:X69"/>
+    <mergeCell ref="R69:T69"/>
+    <mergeCell ref="V70:X70"/>
+    <mergeCell ref="R70:T70"/>
+    <mergeCell ref="R77:T77"/>
+    <mergeCell ref="AD33:AE33"/>
+    <mergeCell ref="AH33:AI33"/>
+    <mergeCell ref="AL33:AM33"/>
+    <mergeCell ref="N76:P76"/>
+    <mergeCell ref="N77:P77"/>
+    <mergeCell ref="R46:T46"/>
+    <mergeCell ref="Z85:AB85"/>
+    <mergeCell ref="Z89:AB89"/>
+    <mergeCell ref="Z90:AB90"/>
+    <mergeCell ref="Z83:AB83"/>
+    <mergeCell ref="Z84:AB84"/>
+    <mergeCell ref="Z82:AB82"/>
+    <mergeCell ref="V51:X51"/>
+    <mergeCell ref="Z51:AB51"/>
+    <mergeCell ref="Z62:AB62"/>
+    <mergeCell ref="N69:P69"/>
+    <mergeCell ref="N68:P68"/>
+    <mergeCell ref="R68:T68"/>
+    <mergeCell ref="V68:X68"/>
+    <mergeCell ref="N67:P67"/>
+    <mergeCell ref="N71:P71"/>
+    <mergeCell ref="N59:O59"/>
+    <mergeCell ref="R59:S59"/>
+    <mergeCell ref="V59:W59"/>
+    <mergeCell ref="N57:P57"/>
+    <mergeCell ref="V57:X57"/>
+    <mergeCell ref="R57:T57"/>
+    <mergeCell ref="AD99:AE99"/>
+    <mergeCell ref="AH99:AI99"/>
+    <mergeCell ref="AL99:AM99"/>
+    <mergeCell ref="R91:T91"/>
+    <mergeCell ref="V91:X91"/>
+    <mergeCell ref="Z91:AB91"/>
+    <mergeCell ref="AD91:AF91"/>
+    <mergeCell ref="AH91:AJ91"/>
+    <mergeCell ref="AL91:AN91"/>
+    <mergeCell ref="R97:T97"/>
+    <mergeCell ref="V97:X97"/>
+    <mergeCell ref="Z97:AB97"/>
+    <mergeCell ref="AD93:AE93"/>
+    <mergeCell ref="AH93:AI93"/>
+    <mergeCell ref="AL93:AM93"/>
+    <mergeCell ref="R93:S93"/>
+    <mergeCell ref="V93:W93"/>
+    <mergeCell ref="Z93:AA93"/>
     <mergeCell ref="AH13:AI13"/>
     <mergeCell ref="AL13:AM13"/>
     <mergeCell ref="AH67:AJ67"/>
@@ -8094,792 +8879,66 @@
     <mergeCell ref="AH43:AJ43"/>
     <mergeCell ref="AH49:AJ49"/>
     <mergeCell ref="Z47:AB47"/>
-    <mergeCell ref="AD99:AE99"/>
-    <mergeCell ref="AH99:AI99"/>
-    <mergeCell ref="AL99:AM99"/>
-    <mergeCell ref="R91:T91"/>
-    <mergeCell ref="V91:X91"/>
-    <mergeCell ref="Z91:AB91"/>
-    <mergeCell ref="AD91:AF91"/>
-    <mergeCell ref="AH91:AJ91"/>
-    <mergeCell ref="AL91:AN91"/>
-    <mergeCell ref="R97:T97"/>
-    <mergeCell ref="V97:X97"/>
-    <mergeCell ref="Z97:AB97"/>
-    <mergeCell ref="AD93:AE93"/>
-    <mergeCell ref="AH93:AI93"/>
-    <mergeCell ref="AL93:AM93"/>
-    <mergeCell ref="R93:S93"/>
-    <mergeCell ref="V93:W93"/>
-    <mergeCell ref="Z93:AA93"/>
-    <mergeCell ref="N76:P76"/>
-    <mergeCell ref="N77:P77"/>
-    <mergeCell ref="R46:T46"/>
-    <mergeCell ref="Z85:AB85"/>
-    <mergeCell ref="Z89:AB89"/>
-    <mergeCell ref="Z90:AB90"/>
-    <mergeCell ref="Z83:AB83"/>
-    <mergeCell ref="Z84:AB84"/>
-    <mergeCell ref="Z82:AB82"/>
-    <mergeCell ref="V51:X51"/>
-    <mergeCell ref="Z51:AB51"/>
-    <mergeCell ref="Z62:AB62"/>
-    <mergeCell ref="N69:P69"/>
-    <mergeCell ref="N68:P68"/>
-    <mergeCell ref="R68:T68"/>
-    <mergeCell ref="V68:X68"/>
-    <mergeCell ref="N67:P67"/>
-    <mergeCell ref="N71:P71"/>
-    <mergeCell ref="AL31:AM31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="R87:S87"/>
-    <mergeCell ref="V87:W87"/>
-    <mergeCell ref="Z87:AA87"/>
-    <mergeCell ref="AD87:AE87"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="V34:W34"/>
-    <mergeCell ref="Z34:AA34"/>
-    <mergeCell ref="AD34:AE34"/>
-    <mergeCell ref="R66:S66"/>
-    <mergeCell ref="V66:W66"/>
-    <mergeCell ref="Z66:AA66"/>
-    <mergeCell ref="R67:T67"/>
-    <mergeCell ref="V67:X67"/>
-    <mergeCell ref="Z67:AB67"/>
-    <mergeCell ref="V69:X69"/>
-    <mergeCell ref="R69:T69"/>
-    <mergeCell ref="V70:X70"/>
-    <mergeCell ref="R70:T70"/>
-    <mergeCell ref="R77:T77"/>
-    <mergeCell ref="AD33:AE33"/>
-    <mergeCell ref="AH33:AI33"/>
-    <mergeCell ref="AL33:AM33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="AL75:AM75"/>
+    <mergeCell ref="AH71:AJ71"/>
+    <mergeCell ref="AD71:AF71"/>
+    <mergeCell ref="Z71:AB71"/>
+    <mergeCell ref="AL66:AM66"/>
+    <mergeCell ref="AD69:AF69"/>
+    <mergeCell ref="AH69:AJ69"/>
+    <mergeCell ref="AD64:AF64"/>
+    <mergeCell ref="AD61:AF61"/>
+    <mergeCell ref="AH61:AJ61"/>
+    <mergeCell ref="Z57:AB57"/>
+    <mergeCell ref="AD54:AF54"/>
+    <mergeCell ref="AD55:AF55"/>
+    <mergeCell ref="AD32:AE32"/>
+    <mergeCell ref="AH32:AI32"/>
+    <mergeCell ref="AL32:AM32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="J32:K32"/>
     <mergeCell ref="AL38:AM38"/>
     <mergeCell ref="AL39:AN39"/>
     <mergeCell ref="AH41:AJ41"/>
     <mergeCell ref="AD41:AF41"/>
     <mergeCell ref="AL43:AN43"/>
-    <mergeCell ref="AL45:AM45"/>
-    <mergeCell ref="AL42:AN42"/>
-    <mergeCell ref="Z41:AB41"/>
-    <mergeCell ref="Z40:AB40"/>
-    <mergeCell ref="Z38:AA38"/>
-    <mergeCell ref="Z39:AB39"/>
-    <mergeCell ref="AL34:AM34"/>
-    <mergeCell ref="N55:P55"/>
-    <mergeCell ref="R56:T56"/>
-    <mergeCell ref="N59:O59"/>
-    <mergeCell ref="N56:P56"/>
-    <mergeCell ref="R54:T54"/>
-    <mergeCell ref="V54:X54"/>
-    <mergeCell ref="V53:W53"/>
-    <mergeCell ref="N54:P54"/>
-    <mergeCell ref="N53:P53"/>
-    <mergeCell ref="R55:T55"/>
-    <mergeCell ref="R59:S59"/>
-    <mergeCell ref="V59:W59"/>
-    <mergeCell ref="R53:T53"/>
-    <mergeCell ref="V56:X56"/>
-    <mergeCell ref="N57:P57"/>
-    <mergeCell ref="V55:X55"/>
-    <mergeCell ref="V57:X57"/>
-    <mergeCell ref="R57:T57"/>
-    <mergeCell ref="V42:X42"/>
-    <mergeCell ref="AH52:AI52"/>
-    <mergeCell ref="AH54:AJ54"/>
-    <mergeCell ref="AH55:AJ55"/>
-    <mergeCell ref="R42:T42"/>
-    <mergeCell ref="Z54:AB54"/>
-    <mergeCell ref="Z50:AB50"/>
-    <mergeCell ref="V45:W45"/>
-    <mergeCell ref="V46:X46"/>
-    <mergeCell ref="V47:X47"/>
-    <mergeCell ref="Z49:AB49"/>
-    <mergeCell ref="V49:X49"/>
-    <mergeCell ref="V48:X48"/>
-    <mergeCell ref="AH34:AI34"/>
-    <mergeCell ref="AD46:AF46"/>
-    <mergeCell ref="AD47:AF47"/>
-    <mergeCell ref="AH40:AJ40"/>
-    <mergeCell ref="AH46:AJ46"/>
-    <mergeCell ref="AH45:AI45"/>
-    <mergeCell ref="AH38:AI38"/>
-    <mergeCell ref="AH39:AJ39"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="J39:L39"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="B50:D50"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="F43:H43"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="J46:L46"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="N45:O45"/>
-    <mergeCell ref="J49:L49"/>
-    <mergeCell ref="J47:L47"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="N60:P60"/>
-    <mergeCell ref="V33:W33"/>
-    <mergeCell ref="Z33:AA33"/>
-    <mergeCell ref="N32:O32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="V32:W32"/>
-    <mergeCell ref="Z32:AA32"/>
-    <mergeCell ref="N34:O34"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="N29:O29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="V29:W29"/>
-    <mergeCell ref="Z29:AA29"/>
-    <mergeCell ref="Z27:AA27"/>
-    <mergeCell ref="N30:O30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="V30:W30"/>
-    <mergeCell ref="Z31:AA31"/>
-    <mergeCell ref="V50:X50"/>
-    <mergeCell ref="Z53:AA53"/>
-    <mergeCell ref="R49:T49"/>
-    <mergeCell ref="R47:T47"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="AL28:AM28"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="N61:P61"/>
-    <mergeCell ref="AD66:AE66"/>
-    <mergeCell ref="AH66:AI66"/>
-    <mergeCell ref="R61:T61"/>
-    <mergeCell ref="V61:X61"/>
-    <mergeCell ref="Z61:AB61"/>
-    <mergeCell ref="Z59:AA59"/>
-    <mergeCell ref="AH63:AJ63"/>
-    <mergeCell ref="AH62:AJ62"/>
-    <mergeCell ref="AD62:AF62"/>
-    <mergeCell ref="AD60:AF60"/>
-    <mergeCell ref="AH60:AJ60"/>
-    <mergeCell ref="V62:X62"/>
-    <mergeCell ref="V63:X63"/>
-    <mergeCell ref="Z64:AB64"/>
-    <mergeCell ref="R60:T60"/>
-    <mergeCell ref="V60:X60"/>
-    <mergeCell ref="Z60:AB60"/>
-    <mergeCell ref="V64:X64"/>
-    <mergeCell ref="R64:T64"/>
-    <mergeCell ref="N63:P63"/>
-    <mergeCell ref="N66:O66"/>
-    <mergeCell ref="AH64:AJ64"/>
-    <mergeCell ref="AD67:AF67"/>
-    <mergeCell ref="AL20:AM20"/>
-    <mergeCell ref="AL27:AM27"/>
-    <mergeCell ref="AL21:AM21"/>
-    <mergeCell ref="AH27:AI27"/>
-    <mergeCell ref="AD20:AE20"/>
-    <mergeCell ref="AH20:AI20"/>
-    <mergeCell ref="Z68:AB68"/>
-    <mergeCell ref="AD68:AF68"/>
-    <mergeCell ref="AH68:AJ68"/>
-    <mergeCell ref="AL68:AN68"/>
-    <mergeCell ref="Z63:AB63"/>
-    <mergeCell ref="AL60:AN60"/>
-    <mergeCell ref="AL64:AN64"/>
-    <mergeCell ref="AL61:AN61"/>
-    <mergeCell ref="Z56:AB56"/>
-    <mergeCell ref="AL22:AN22"/>
-    <mergeCell ref="Z23:AB23"/>
-    <mergeCell ref="AD23:AF23"/>
-    <mergeCell ref="AH23:AJ23"/>
-    <mergeCell ref="AL23:AN23"/>
-    <mergeCell ref="AD28:AE28"/>
-    <mergeCell ref="AH28:AI28"/>
-    <mergeCell ref="N82:P82"/>
-    <mergeCell ref="AH76:AJ76"/>
-    <mergeCell ref="AL76:AN76"/>
-    <mergeCell ref="AD76:AF76"/>
-    <mergeCell ref="Z81:AA81"/>
-    <mergeCell ref="AL62:AN62"/>
-    <mergeCell ref="AL63:AN63"/>
-    <mergeCell ref="AL71:AN71"/>
-    <mergeCell ref="AL70:AN70"/>
-    <mergeCell ref="AL69:AN69"/>
-    <mergeCell ref="N73:AB74"/>
-    <mergeCell ref="N75:O75"/>
-    <mergeCell ref="R75:S75"/>
-    <mergeCell ref="V75:W75"/>
-    <mergeCell ref="Z75:AA75"/>
-    <mergeCell ref="AD75:AE75"/>
-    <mergeCell ref="N64:P64"/>
-    <mergeCell ref="N70:P70"/>
-    <mergeCell ref="AH70:AJ70"/>
-    <mergeCell ref="AD70:AF70"/>
-    <mergeCell ref="Z69:AB69"/>
-    <mergeCell ref="Z70:AB70"/>
-    <mergeCell ref="V71:X71"/>
-    <mergeCell ref="AD63:AF63"/>
-    <mergeCell ref="N78:P78"/>
-    <mergeCell ref="Z78:AB78"/>
-    <mergeCell ref="N79:P79"/>
-    <mergeCell ref="R79:T79"/>
-    <mergeCell ref="V79:X79"/>
-    <mergeCell ref="Z79:AB79"/>
-    <mergeCell ref="N81:O81"/>
-    <mergeCell ref="R81:S81"/>
-    <mergeCell ref="V81:W81"/>
-    <mergeCell ref="AH88:AJ88"/>
-    <mergeCell ref="AH89:AJ89"/>
-    <mergeCell ref="AD85:AF85"/>
-    <mergeCell ref="AH85:AJ85"/>
-    <mergeCell ref="AL85:AN85"/>
-    <mergeCell ref="AH75:AI75"/>
-    <mergeCell ref="V89:X89"/>
-    <mergeCell ref="R89:T89"/>
-    <mergeCell ref="R84:T84"/>
-    <mergeCell ref="R85:T85"/>
-    <mergeCell ref="V85:X85"/>
-    <mergeCell ref="Z76:AB76"/>
-    <mergeCell ref="Z77:AB77"/>
-    <mergeCell ref="V76:X76"/>
-    <mergeCell ref="AH77:AJ77"/>
-    <mergeCell ref="AD78:AF78"/>
-    <mergeCell ref="V82:X82"/>
-    <mergeCell ref="R88:T88"/>
-    <mergeCell ref="V77:X77"/>
-    <mergeCell ref="V78:X78"/>
-    <mergeCell ref="R78:T78"/>
-    <mergeCell ref="V84:X84"/>
-    <mergeCell ref="R82:T82"/>
-    <mergeCell ref="V83:X83"/>
-    <mergeCell ref="R83:T83"/>
-    <mergeCell ref="AD82:AF82"/>
-    <mergeCell ref="AH83:AJ83"/>
-    <mergeCell ref="AD84:AF84"/>
-    <mergeCell ref="AH84:AJ84"/>
-    <mergeCell ref="AD83:AF83"/>
-    <mergeCell ref="AH94:AJ94"/>
-    <mergeCell ref="AL100:AN100"/>
-    <mergeCell ref="AD97:AF97"/>
-    <mergeCell ref="AH97:AJ97"/>
-    <mergeCell ref="AL97:AN97"/>
-    <mergeCell ref="AL77:AN77"/>
-    <mergeCell ref="AL78:AN78"/>
-    <mergeCell ref="AD77:AF77"/>
-    <mergeCell ref="AD79:AF79"/>
-    <mergeCell ref="AH79:AJ79"/>
-    <mergeCell ref="AL79:AN79"/>
-    <mergeCell ref="AD81:AE81"/>
-    <mergeCell ref="AH81:AI81"/>
-    <mergeCell ref="AL81:AM81"/>
-    <mergeCell ref="AH82:AJ82"/>
-    <mergeCell ref="AH78:AJ78"/>
-    <mergeCell ref="AL88:AN88"/>
-    <mergeCell ref="AL89:AN89"/>
-    <mergeCell ref="AL83:AN83"/>
-    <mergeCell ref="AL84:AN84"/>
-    <mergeCell ref="AD88:AF88"/>
-    <mergeCell ref="AD89:AF89"/>
-    <mergeCell ref="AH87:AI87"/>
-    <mergeCell ref="AL87:AM87"/>
-    <mergeCell ref="AD39:AF39"/>
-    <mergeCell ref="AD40:AF40"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="AL82:AN82"/>
-    <mergeCell ref="AL102:AN102"/>
-    <mergeCell ref="AL101:AN101"/>
-    <mergeCell ref="AL96:AN96"/>
-    <mergeCell ref="AD102:AF102"/>
-    <mergeCell ref="AH102:AJ102"/>
-    <mergeCell ref="AL90:AN90"/>
-    <mergeCell ref="AL95:AN95"/>
-    <mergeCell ref="AD101:AF101"/>
-    <mergeCell ref="AH101:AJ101"/>
-    <mergeCell ref="AH100:AJ100"/>
-    <mergeCell ref="AL94:AN94"/>
-    <mergeCell ref="AD100:AF100"/>
-    <mergeCell ref="AD96:AF96"/>
-    <mergeCell ref="AD94:AF94"/>
-    <mergeCell ref="AD95:AF95"/>
-    <mergeCell ref="AH96:AJ96"/>
-    <mergeCell ref="AD90:AF90"/>
-    <mergeCell ref="AH95:AJ95"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="AH90:AJ90"/>
-    <mergeCell ref="AD42:AF42"/>
-    <mergeCell ref="AD48:AF48"/>
-    <mergeCell ref="Z9:AB9"/>
-    <mergeCell ref="R10:T10"/>
-    <mergeCell ref="V10:X10"/>
-    <mergeCell ref="AD21:AE21"/>
-    <mergeCell ref="AD49:AF49"/>
-    <mergeCell ref="AD43:AF43"/>
-    <mergeCell ref="AD45:AE45"/>
-    <mergeCell ref="R48:T48"/>
-    <mergeCell ref="Z42:AB42"/>
-    <mergeCell ref="Z43:AB43"/>
-    <mergeCell ref="N36:AB37"/>
-    <mergeCell ref="Z48:AB48"/>
-    <mergeCell ref="Z45:AA45"/>
-    <mergeCell ref="Z46:AB46"/>
-    <mergeCell ref="AD38:AE38"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="R9:T9"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="V8:X8"/>
-    <mergeCell ref="V9:X9"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="R1:T1"/>
-    <mergeCell ref="V1:X1"/>
-    <mergeCell ref="V14:X14"/>
-    <mergeCell ref="R15:T15"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="B4:L5"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="V2:X2"/>
-    <mergeCell ref="N4:AB5"/>
-    <mergeCell ref="V90:X90"/>
-    <mergeCell ref="V88:X88"/>
-    <mergeCell ref="R90:T90"/>
-    <mergeCell ref="AL1:AN1"/>
-    <mergeCell ref="Z2:AB2"/>
-    <mergeCell ref="AD2:AF2"/>
-    <mergeCell ref="AH2:AJ2"/>
-    <mergeCell ref="AL2:AN2"/>
-    <mergeCell ref="AH8:AJ8"/>
-    <mergeCell ref="AL6:AM6"/>
-    <mergeCell ref="AD1:AF1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="AL7:AM7"/>
-    <mergeCell ref="AD8:AF8"/>
-    <mergeCell ref="Z8:AB8"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AH7:AI7"/>
-    <mergeCell ref="AD7:AE7"/>
-    <mergeCell ref="Z7:AA7"/>
-    <mergeCell ref="AL8:AN8"/>
-    <mergeCell ref="AD4:AN5"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="AD6:AE6"/>
-    <mergeCell ref="AH31:AI31"/>
-    <mergeCell ref="AD31:AE31"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="Z21:AA21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="R22:T22"/>
-    <mergeCell ref="V22:X22"/>
-    <mergeCell ref="Z22:AB22"/>
-    <mergeCell ref="AD22:AF22"/>
-    <mergeCell ref="AH22:AJ22"/>
-    <mergeCell ref="AD29:AE29"/>
-    <mergeCell ref="AH29:AI29"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:T23"/>
-    <mergeCell ref="V23:X23"/>
-    <mergeCell ref="V27:W27"/>
-    <mergeCell ref="AD27:AE27"/>
-    <mergeCell ref="V31:W31"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="AL9:AN9"/>
-    <mergeCell ref="AD9:AF9"/>
-    <mergeCell ref="AH16:AJ16"/>
-    <mergeCell ref="AL10:AN10"/>
-    <mergeCell ref="AL14:AN14"/>
-    <mergeCell ref="AL16:AN16"/>
-    <mergeCell ref="Z15:AB15"/>
-    <mergeCell ref="AD15:AF15"/>
-    <mergeCell ref="Z13:AA13"/>
-    <mergeCell ref="AL15:AN15"/>
-    <mergeCell ref="AL12:AM12"/>
-    <mergeCell ref="AD16:AF16"/>
-    <mergeCell ref="Z10:AB10"/>
-    <mergeCell ref="AH14:AJ14"/>
-    <mergeCell ref="Z14:AB14"/>
-    <mergeCell ref="AD14:AF14"/>
-    <mergeCell ref="AD13:AE13"/>
-    <mergeCell ref="AH10:AJ10"/>
-    <mergeCell ref="AH15:AJ15"/>
-    <mergeCell ref="AD10:AF10"/>
-    <mergeCell ref="AD12:AE12"/>
-    <mergeCell ref="AH12:AI12"/>
-    <mergeCell ref="Z12:AA12"/>
-    <mergeCell ref="Z16:AB16"/>
-    <mergeCell ref="AH9:AJ9"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="AH21:AI21"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="Z20:AA20"/>
-    <mergeCell ref="J15:L15"/>
-    <mergeCell ref="V15:X15"/>
-    <mergeCell ref="V16:X16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="V13:W13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="J50:L50"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="J105:K105"/>
-    <mergeCell ref="V41:X41"/>
-    <mergeCell ref="V40:X40"/>
-    <mergeCell ref="J106:L106"/>
-    <mergeCell ref="Z102:AB102"/>
-    <mergeCell ref="V102:X102"/>
-    <mergeCell ref="Z55:AB55"/>
-    <mergeCell ref="J75:K75"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="J69:L69"/>
-    <mergeCell ref="N62:P62"/>
-    <mergeCell ref="R62:T62"/>
-    <mergeCell ref="R71:T71"/>
-    <mergeCell ref="R76:T76"/>
-    <mergeCell ref="R63:T63"/>
-    <mergeCell ref="F101:H101"/>
-    <mergeCell ref="R94:T94"/>
-    <mergeCell ref="Z88:AB88"/>
-    <mergeCell ref="J94:L94"/>
-    <mergeCell ref="J95:L95"/>
-    <mergeCell ref="V94:X94"/>
-    <mergeCell ref="V96:X96"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="N18:AB19"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="R14:T14"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="J101:L101"/>
-    <mergeCell ref="J118:L118"/>
-    <mergeCell ref="B124:D124"/>
-    <mergeCell ref="F108:H108"/>
-    <mergeCell ref="B133:D133"/>
-    <mergeCell ref="F133:H133"/>
-    <mergeCell ref="J133:L133"/>
-    <mergeCell ref="B127:D127"/>
-    <mergeCell ref="F127:H127"/>
-    <mergeCell ref="J127:L127"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="F129:G129"/>
-    <mergeCell ref="J129:K129"/>
-    <mergeCell ref="B130:D130"/>
-    <mergeCell ref="F130:H130"/>
-    <mergeCell ref="J130:L130"/>
-    <mergeCell ref="B132:D132"/>
-    <mergeCell ref="F132:H132"/>
-    <mergeCell ref="J132:L132"/>
-    <mergeCell ref="B131:D131"/>
-    <mergeCell ref="F131:H131"/>
-    <mergeCell ref="J131:L131"/>
-    <mergeCell ref="J120:L120"/>
-    <mergeCell ref="B101:D101"/>
-    <mergeCell ref="B126:D126"/>
-    <mergeCell ref="F126:H126"/>
-    <mergeCell ref="J126:L126"/>
-    <mergeCell ref="F117:G117"/>
-    <mergeCell ref="J117:K117"/>
-    <mergeCell ref="J108:L108"/>
-    <mergeCell ref="F121:H121"/>
-    <mergeCell ref="J123:K123"/>
-    <mergeCell ref="F112:H112"/>
-    <mergeCell ref="B125:D125"/>
-    <mergeCell ref="F125:H125"/>
-    <mergeCell ref="J121:L121"/>
-    <mergeCell ref="J125:L125"/>
-    <mergeCell ref="B118:D118"/>
-    <mergeCell ref="F118:H118"/>
-    <mergeCell ref="B109:D109"/>
-    <mergeCell ref="F109:H109"/>
-    <mergeCell ref="F124:H124"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="F111:G111"/>
-    <mergeCell ref="J124:L124"/>
-    <mergeCell ref="F119:H119"/>
-    <mergeCell ref="J119:L119"/>
-    <mergeCell ref="J109:L109"/>
-    <mergeCell ref="B120:D120"/>
-    <mergeCell ref="B121:D121"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="F123:G123"/>
-    <mergeCell ref="B119:D119"/>
-    <mergeCell ref="B113:D113"/>
-    <mergeCell ref="F113:H113"/>
-    <mergeCell ref="J113:L113"/>
-    <mergeCell ref="B114:D114"/>
-    <mergeCell ref="F114:H114"/>
-    <mergeCell ref="J114:L114"/>
-    <mergeCell ref="B115:D115"/>
-    <mergeCell ref="F115:H115"/>
-    <mergeCell ref="J115:L115"/>
-    <mergeCell ref="B112:D112"/>
-    <mergeCell ref="F120:H120"/>
-    <mergeCell ref="B108:D108"/>
-    <mergeCell ref="J102:L102"/>
-    <mergeCell ref="J112:L112"/>
-    <mergeCell ref="J111:K111"/>
-    <mergeCell ref="B106:D106"/>
-    <mergeCell ref="B107:D107"/>
-    <mergeCell ref="F106:H106"/>
-    <mergeCell ref="F105:G105"/>
-    <mergeCell ref="N102:P102"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="F102:H102"/>
-    <mergeCell ref="F107:H107"/>
-    <mergeCell ref="J107:L107"/>
-    <mergeCell ref="R102:T102"/>
-    <mergeCell ref="R100:T100"/>
-    <mergeCell ref="V100:X100"/>
-    <mergeCell ref="R101:T101"/>
-    <mergeCell ref="N100:P100"/>
-    <mergeCell ref="Z100:AB100"/>
-    <mergeCell ref="N94:P94"/>
-    <mergeCell ref="R95:T95"/>
-    <mergeCell ref="N96:P96"/>
-    <mergeCell ref="R99:S99"/>
-    <mergeCell ref="V99:W99"/>
-    <mergeCell ref="Z99:AA99"/>
-    <mergeCell ref="V95:X95"/>
-    <mergeCell ref="Z96:AB96"/>
-    <mergeCell ref="R96:T96"/>
-    <mergeCell ref="N101:P101"/>
-    <mergeCell ref="N95:P95"/>
-    <mergeCell ref="V101:X101"/>
-    <mergeCell ref="Z101:AB101"/>
-    <mergeCell ref="Z94:AB94"/>
-    <mergeCell ref="Z95:AB95"/>
-    <mergeCell ref="N91:P91"/>
-    <mergeCell ref="N97:P97"/>
-    <mergeCell ref="J96:L96"/>
-    <mergeCell ref="J90:L90"/>
-    <mergeCell ref="N99:O99"/>
-    <mergeCell ref="N88:P88"/>
-    <mergeCell ref="N83:P83"/>
-    <mergeCell ref="N84:P84"/>
-    <mergeCell ref="N90:P90"/>
-    <mergeCell ref="J89:L89"/>
-    <mergeCell ref="J83:L83"/>
-    <mergeCell ref="J84:L84"/>
-    <mergeCell ref="N89:P89"/>
-    <mergeCell ref="N87:O87"/>
-    <mergeCell ref="N93:O93"/>
-    <mergeCell ref="N85:P85"/>
-    <mergeCell ref="J85:L85"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="F53:H53"/>
-    <mergeCell ref="F54:H54"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="J100:L100"/>
-    <mergeCell ref="J88:L88"/>
-    <mergeCell ref="J77:L77"/>
-    <mergeCell ref="J76:L76"/>
-    <mergeCell ref="J55:L55"/>
-    <mergeCell ref="B96:D96"/>
-    <mergeCell ref="F96:H96"/>
-    <mergeCell ref="B100:D100"/>
-    <mergeCell ref="F100:H100"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="F88:H88"/>
-    <mergeCell ref="B89:D89"/>
-    <mergeCell ref="F83:H83"/>
-    <mergeCell ref="F84:H84"/>
-    <mergeCell ref="F77:H77"/>
-    <mergeCell ref="J53:L53"/>
-    <mergeCell ref="J54:L54"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="J78:L78"/>
-    <mergeCell ref="J81:K81"/>
-    <mergeCell ref="J82:L82"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B95:D95"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="J70:L70"/>
-    <mergeCell ref="B71:D71"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="F70:H70"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="F76:H76"/>
-    <mergeCell ref="F90:H90"/>
-    <mergeCell ref="F95:H95"/>
-    <mergeCell ref="F89:H89"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="F94:H94"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B79:D79"/>
-    <mergeCell ref="B85:D85"/>
-    <mergeCell ref="F85:H85"/>
-    <mergeCell ref="F75:G75"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="F82:H82"/>
-    <mergeCell ref="AL50:AN50"/>
-    <mergeCell ref="AL52:AM52"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="F62:H62"/>
-    <mergeCell ref="F61:H61"/>
-    <mergeCell ref="J64:L64"/>
-    <mergeCell ref="F69:H69"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="J63:L63"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="J66:K66"/>
-    <mergeCell ref="B67:D67"/>
-    <mergeCell ref="F67:H67"/>
-    <mergeCell ref="J67:L67"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="F68:H68"/>
-    <mergeCell ref="J68:L68"/>
-    <mergeCell ref="F63:H63"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="AD56:AF56"/>
-    <mergeCell ref="AH57:AJ57"/>
-    <mergeCell ref="AH59:AI59"/>
-    <mergeCell ref="AH56:AJ56"/>
-    <mergeCell ref="AH53:AJ53"/>
-    <mergeCell ref="AH47:AJ47"/>
-    <mergeCell ref="AD59:AE59"/>
-    <mergeCell ref="AD53:AF53"/>
-    <mergeCell ref="AD50:AF50"/>
-    <mergeCell ref="AD52:AE52"/>
-    <mergeCell ref="AD57:AF57"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="N38:O38"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R41:T41"/>
-    <mergeCell ref="R40:T40"/>
-    <mergeCell ref="R43:T43"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="R39:T39"/>
-    <mergeCell ref="V38:W38"/>
-    <mergeCell ref="V39:X39"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="V43:X43"/>
-    <mergeCell ref="AL57:AN57"/>
-    <mergeCell ref="AL59:AM59"/>
-    <mergeCell ref="AL46:AN46"/>
-    <mergeCell ref="F79:H79"/>
-    <mergeCell ref="J79:L79"/>
-    <mergeCell ref="F71:H71"/>
-    <mergeCell ref="J71:L71"/>
-    <mergeCell ref="F64:H64"/>
-    <mergeCell ref="F78:H78"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="R50:T50"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="J48:L48"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="AL56:AN56"/>
-    <mergeCell ref="AL54:AN54"/>
-    <mergeCell ref="AL53:AN53"/>
-    <mergeCell ref="AL49:AN49"/>
-    <mergeCell ref="AL55:AN55"/>
-    <mergeCell ref="F60:H60"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="J60:L60"/>
-    <mergeCell ref="B97:D97"/>
-    <mergeCell ref="F97:H97"/>
-    <mergeCell ref="J97:L97"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="F99:G99"/>
-    <mergeCell ref="J99:K99"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="J87:K87"/>
-    <mergeCell ref="B91:D91"/>
-    <mergeCell ref="F91:H91"/>
-    <mergeCell ref="J91:L91"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="F93:G93"/>
-    <mergeCell ref="J93:K93"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="D29:D34 AJ29:AJ34 X29:X34 T29:T34 AB29:AB34 AF29:AF34 P29:P34 H29:H34 L29:L34 AN29:AN34">

--- a/Gorev-Listesi.xlsx
+++ b/Gorev-Listesi.xlsx
@@ -20,11 +20,12 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <webPublishing css="0" allowPng="1" codePage="1252"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="109">
   <si>
     <t>CUMA</t>
   </si>
@@ -341,10 +342,16 @@
     <t>???</t>
   </si>
   <si>
-    <t>S.CÜREBAL.</t>
-  </si>
-  <si>
     <t>F.BOZKURT.</t>
+  </si>
+  <si>
+    <t>E.KOL.</t>
+  </si>
+  <si>
+    <t>S.ARAS.</t>
+  </si>
+  <si>
+    <t>A.C.PEHLİVAN.</t>
   </si>
 </sst>
 </file>
@@ -1386,7 +1393,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="163">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1644,6 +1651,15 @@
     <xf numFmtId="49" fontId="11" fillId="7" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="11" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="12" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="13" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1665,25 +1681,67 @@
     <xf numFmtId="49" fontId="40" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="12" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="13" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="14" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="15" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="16" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="11" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="12" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="13" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="40" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="40" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="17" xfId="57" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="12" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="18" xfId="57" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="13" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="19" xfId="57" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1752,12 +1810,6 @@
     <xf numFmtId="49" fontId="7" fillId="9" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="14" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="15" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1767,12 +1819,6 @@
     <xf numFmtId="49" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1807,15 +1853,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="11" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="12" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="13" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2267,65 +2304,65 @@
   <sheetData>
     <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12"/>
-      <c r="B1" s="111" t="s">
+      <c r="B1" s="128" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
       <c r="E1" s="10"/>
-      <c r="F1" s="112" t="s">
+      <c r="F1" s="129" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
       <c r="I1" s="10"/>
-      <c r="J1" s="112" t="s">
+      <c r="J1" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="112"/>
-      <c r="L1" s="113"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="130"/>
       <c r="M1" s="12"/>
-      <c r="N1" s="116" t="s">
+      <c r="N1" s="133" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
+      <c r="O1" s="127"/>
+      <c r="P1" s="127"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="110" t="s">
+      <c r="R1" s="127" t="s">
         <v>4</v>
       </c>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
+      <c r="S1" s="127"/>
+      <c r="T1" s="127"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="110" t="s">
+      <c r="V1" s="127" t="s">
         <v>5</v>
       </c>
-      <c r="W1" s="110"/>
-      <c r="X1" s="110"/>
+      <c r="W1" s="127"/>
+      <c r="X1" s="127"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="110" t="s">
+      <c r="Z1" s="127" t="s">
         <v>6</v>
       </c>
-      <c r="AA1" s="110"/>
-      <c r="AB1" s="110"/>
+      <c r="AA1" s="127"/>
+      <c r="AB1" s="127"/>
       <c r="AC1" s="1"/>
-      <c r="AD1" s="110" t="s">
+      <c r="AD1" s="127" t="s">
         <v>0</v>
       </c>
-      <c r="AE1" s="110"/>
-      <c r="AF1" s="110"/>
+      <c r="AE1" s="127"/>
+      <c r="AF1" s="127"/>
       <c r="AG1" s="1"/>
-      <c r="AH1" s="110" t="s">
+      <c r="AH1" s="127" t="s">
         <v>1</v>
       </c>
-      <c r="AI1" s="110"/>
-      <c r="AJ1" s="110"/>
+      <c r="AI1" s="127"/>
+      <c r="AJ1" s="127"/>
       <c r="AK1" s="1"/>
-      <c r="AL1" s="110" t="s">
+      <c r="AL1" s="127" t="s">
         <v>2</v>
       </c>
-      <c r="AM1" s="110"/>
-      <c r="AN1" s="120"/>
+      <c r="AM1" s="127"/>
+      <c r="AN1" s="137"/>
       <c r="AO1" s="12"/>
       <c r="AP1" s="12"/>
       <c r="AQ1" s="12"/>
@@ -2333,74 +2370,74 @@
     </row>
     <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
-      <c r="B2" s="114">
+      <c r="B2" s="131">
         <f>N2-3</f>
         <v>46276</v>
       </c>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
       <c r="E2" s="11"/>
-      <c r="F2" s="115">
+      <c r="F2" s="132">
         <f>N2-2</f>
         <v>46277</v>
       </c>
-      <c r="G2" s="115"/>
-      <c r="H2" s="115"/>
+      <c r="G2" s="132"/>
+      <c r="H2" s="132"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="115">
+      <c r="J2" s="132">
         <f>N2-1</f>
         <v>46278</v>
       </c>
-      <c r="K2" s="115"/>
-      <c r="L2" s="118"/>
+      <c r="K2" s="132"/>
+      <c r="L2" s="135"/>
       <c r="M2" s="12"/>
-      <c r="N2" s="117">
+      <c r="N2" s="134">
         <v>46279</v>
       </c>
-      <c r="O2" s="109"/>
-      <c r="P2" s="109"/>
+      <c r="O2" s="126"/>
+      <c r="P2" s="126"/>
       <c r="Q2" s="53"/>
-      <c r="R2" s="109">
+      <c r="R2" s="126">
         <f>N2+1</f>
         <v>46280</v>
       </c>
-      <c r="S2" s="109"/>
-      <c r="T2" s="109"/>
+      <c r="S2" s="126"/>
+      <c r="T2" s="126"/>
       <c r="U2" s="53"/>
-      <c r="V2" s="109">
+      <c r="V2" s="126">
         <f>N2+2</f>
         <v>46281</v>
       </c>
-      <c r="W2" s="109"/>
-      <c r="X2" s="109"/>
+      <c r="W2" s="126"/>
+      <c r="X2" s="126"/>
       <c r="Y2" s="53"/>
-      <c r="Z2" s="109">
+      <c r="Z2" s="126">
         <f>N2+3</f>
         <v>46282</v>
       </c>
-      <c r="AA2" s="109"/>
-      <c r="AB2" s="109"/>
+      <c r="AA2" s="126"/>
+      <c r="AB2" s="126"/>
       <c r="AC2" s="53"/>
-      <c r="AD2" s="109">
+      <c r="AD2" s="126">
         <f>N2+4</f>
         <v>46283</v>
       </c>
-      <c r="AE2" s="109"/>
-      <c r="AF2" s="109"/>
+      <c r="AE2" s="126"/>
+      <c r="AF2" s="126"/>
       <c r="AG2" s="53"/>
-      <c r="AH2" s="109">
+      <c r="AH2" s="126">
         <f>N2+5</f>
         <v>46284</v>
       </c>
-      <c r="AI2" s="109"/>
-      <c r="AJ2" s="109"/>
+      <c r="AI2" s="126"/>
+      <c r="AJ2" s="126"/>
       <c r="AK2" s="53"/>
-      <c r="AL2" s="109">
+      <c r="AL2" s="126">
         <f>N2+6</f>
         <v>46285</v>
       </c>
-      <c r="AM2" s="109"/>
-      <c r="AN2" s="121"/>
+      <c r="AM2" s="126"/>
+      <c r="AN2" s="138"/>
       <c r="AO2" s="12"/>
       <c r="AP2" s="12"/>
       <c r="AQ2" s="12"/>
@@ -2454,47 +2491,47 @@
     </row>
     <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="12"/>
-      <c r="B4" s="119"/>
-      <c r="C4" s="119"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="119"/>
-      <c r="L4" s="119"/>
+      <c r="B4" s="136"/>
+      <c r="C4" s="136"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="136"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="136"/>
+      <c r="K4" s="136"/>
+      <c r="L4" s="136"/>
       <c r="M4" s="14"/>
-      <c r="N4" s="99" t="s">
+      <c r="N4" s="102" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="99"/>
-      <c r="P4" s="99"/>
-      <c r="Q4" s="99"/>
-      <c r="R4" s="99"/>
-      <c r="S4" s="99"/>
-      <c r="T4" s="99"/>
-      <c r="U4" s="99"/>
-      <c r="V4" s="99"/>
-      <c r="W4" s="99"/>
-      <c r="X4" s="99"/>
-      <c r="Y4" s="99"/>
-      <c r="Z4" s="99"/>
-      <c r="AA4" s="99"/>
-      <c r="AB4" s="99"/>
+      <c r="O4" s="102"/>
+      <c r="P4" s="102"/>
+      <c r="Q4" s="102"/>
+      <c r="R4" s="102"/>
+      <c r="S4" s="102"/>
+      <c r="T4" s="102"/>
+      <c r="U4" s="102"/>
+      <c r="V4" s="102"/>
+      <c r="W4" s="102"/>
+      <c r="X4" s="102"/>
+      <c r="Y4" s="102"/>
+      <c r="Z4" s="102"/>
+      <c r="AA4" s="102"/>
+      <c r="AB4" s="102"/>
       <c r="AC4" s="33"/>
-      <c r="AD4" s="119"/>
-      <c r="AE4" s="119"/>
-      <c r="AF4" s="119"/>
-      <c r="AG4" s="119"/>
-      <c r="AH4" s="119"/>
-      <c r="AI4" s="119"/>
-      <c r="AJ4" s="119"/>
-      <c r="AK4" s="119"/>
-      <c r="AL4" s="119"/>
-      <c r="AM4" s="119"/>
-      <c r="AN4" s="119"/>
+      <c r="AD4" s="136"/>
+      <c r="AE4" s="136"/>
+      <c r="AF4" s="136"/>
+      <c r="AG4" s="136"/>
+      <c r="AH4" s="136"/>
+      <c r="AI4" s="136"/>
+      <c r="AJ4" s="136"/>
+      <c r="AK4" s="136"/>
+      <c r="AL4" s="136"/>
+      <c r="AM4" s="136"/>
+      <c r="AN4" s="136"/>
       <c r="AO4" s="12"/>
       <c r="AP4" s="12"/>
       <c r="AQ4" s="12"/>
@@ -2502,45 +2539,45 @@
     </row>
     <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12"/>
-      <c r="B5" s="119"/>
-      <c r="C5" s="119"/>
-      <c r="D5" s="119"/>
-      <c r="E5" s="119"/>
-      <c r="F5" s="119"/>
-      <c r="G5" s="119"/>
-      <c r="H5" s="119"/>
-      <c r="I5" s="119"/>
-      <c r="J5" s="119"/>
-      <c r="K5" s="119"/>
-      <c r="L5" s="119"/>
+      <c r="B5" s="136"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="136"/>
+      <c r="F5" s="136"/>
+      <c r="G5" s="136"/>
+      <c r="H5" s="136"/>
+      <c r="I5" s="136"/>
+      <c r="J5" s="136"/>
+      <c r="K5" s="136"/>
+      <c r="L5" s="136"/>
       <c r="M5" s="14"/>
-      <c r="N5" s="99"/>
-      <c r="O5" s="99"/>
-      <c r="P5" s="99"/>
-      <c r="Q5" s="99"/>
-      <c r="R5" s="99"/>
-      <c r="S5" s="99"/>
-      <c r="T5" s="99"/>
-      <c r="U5" s="99"/>
-      <c r="V5" s="99"/>
-      <c r="W5" s="99"/>
-      <c r="X5" s="99"/>
-      <c r="Y5" s="99"/>
-      <c r="Z5" s="99"/>
-      <c r="AA5" s="99"/>
-      <c r="AB5" s="99"/>
+      <c r="N5" s="102"/>
+      <c r="O5" s="102"/>
+      <c r="P5" s="102"/>
+      <c r="Q5" s="102"/>
+      <c r="R5" s="102"/>
+      <c r="S5" s="102"/>
+      <c r="T5" s="102"/>
+      <c r="U5" s="102"/>
+      <c r="V5" s="102"/>
+      <c r="W5" s="102"/>
+      <c r="X5" s="102"/>
+      <c r="Y5" s="102"/>
+      <c r="Z5" s="102"/>
+      <c r="AA5" s="102"/>
+      <c r="AB5" s="102"/>
       <c r="AC5" s="33"/>
-      <c r="AD5" s="119"/>
-      <c r="AE5" s="119"/>
-      <c r="AF5" s="119"/>
-      <c r="AG5" s="119"/>
-      <c r="AH5" s="119"/>
-      <c r="AI5" s="119"/>
-      <c r="AJ5" s="119"/>
-      <c r="AK5" s="119"/>
-      <c r="AL5" s="119"/>
-      <c r="AM5" s="119"/>
-      <c r="AN5" s="119"/>
+      <c r="AD5" s="136"/>
+      <c r="AE5" s="136"/>
+      <c r="AF5" s="136"/>
+      <c r="AG5" s="136"/>
+      <c r="AH5" s="136"/>
+      <c r="AI5" s="136"/>
+      <c r="AJ5" s="136"/>
+      <c r="AK5" s="136"/>
+      <c r="AL5" s="136"/>
+      <c r="AM5" s="136"/>
+      <c r="AN5" s="136"/>
       <c r="AO5" s="12"/>
       <c r="AP5" s="12"/>
       <c r="AQ5" s="12"/>
@@ -2685,11 +2722,11 @@
       <c r="AE8" s="82"/>
       <c r="AF8" s="83"/>
       <c r="AG8" s="35"/>
-      <c r="AH8" s="122" t="s">
+      <c r="AH8" s="139" t="s">
         <v>85</v>
       </c>
-      <c r="AI8" s="123"/>
-      <c r="AJ8" s="124"/>
+      <c r="AI8" s="140"/>
+      <c r="AJ8" s="141"/>
       <c r="AK8" s="37"/>
       <c r="AL8" s="81" t="s">
         <v>12</v>
@@ -2742,11 +2779,11 @@
       <c r="AI9" s="66"/>
       <c r="AJ9" s="67"/>
       <c r="AK9" s="43"/>
-      <c r="AL9" s="106" t="s">
+      <c r="AL9" s="105" t="s">
         <v>15</v>
       </c>
-      <c r="AM9" s="107"/>
-      <c r="AN9" s="108"/>
+      <c r="AM9" s="106"/>
+      <c r="AN9" s="107"/>
       <c r="AP9" s="46" t="s">
         <v>11</v>
       </c>
@@ -2793,11 +2830,11 @@
       <c r="AI10" s="85"/>
       <c r="AJ10" s="86"/>
       <c r="AK10" s="44"/>
-      <c r="AL10" s="133" t="s">
+      <c r="AL10" s="148" t="s">
         <v>96</v>
       </c>
-      <c r="AM10" s="134"/>
-      <c r="AN10" s="135"/>
+      <c r="AM10" s="149"/>
+      <c r="AN10" s="150"/>
       <c r="AP10" s="46" t="s">
         <v>8</v>
       </c>
@@ -2863,10 +2900,10 @@
       <c r="C12" s="64"/>
       <c r="D12" s="57"/>
       <c r="E12" s="39"/>
-      <c r="F12" s="102" t="s">
+      <c r="F12" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="103"/>
+      <c r="G12" s="114"/>
       <c r="H12" s="59" t="s">
         <v>69</v>
       </c>
@@ -3028,11 +3065,11 @@
       <c r="C15" s="66"/>
       <c r="D15" s="67"/>
       <c r="E15" s="44"/>
-      <c r="F15" s="106" t="s">
+      <c r="F15" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="107"/>
-      <c r="H15" s="108"/>
+      <c r="G15" s="106"/>
+      <c r="H15" s="107"/>
       <c r="I15" s="43"/>
       <c r="J15" s="65"/>
       <c r="K15" s="66"/>
@@ -3072,7 +3109,7 @@
       </c>
       <c r="AQ15" s="25">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR15" s="30"/>
     </row>
@@ -3081,11 +3118,11 @@
       <c r="C16" s="85"/>
       <c r="D16" s="86"/>
       <c r="E16" s="44"/>
-      <c r="F16" s="133" t="s">
+      <c r="F16" s="148" t="s">
         <v>88</v>
       </c>
-      <c r="G16" s="134"/>
-      <c r="H16" s="135"/>
+      <c r="G16" s="149"/>
+      <c r="H16" s="150"/>
       <c r="I16" s="44"/>
       <c r="J16" s="84"/>
       <c r="K16" s="85"/>
@@ -3123,7 +3160,7 @@
       </c>
       <c r="AQ16" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR16" s="30"/>
     </row>
@@ -3189,23 +3226,23 @@
       <c r="K18" s="33"/>
       <c r="L18" s="33"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="99" t="s">
+      <c r="N18" s="102" t="s">
         <v>59</v>
       </c>
-      <c r="O18" s="99"/>
-      <c r="P18" s="99"/>
-      <c r="Q18" s="99"/>
-      <c r="R18" s="99"/>
-      <c r="S18" s="99"/>
-      <c r="T18" s="99"/>
-      <c r="U18" s="99"/>
-      <c r="V18" s="99"/>
-      <c r="W18" s="99"/>
-      <c r="X18" s="99"/>
-      <c r="Y18" s="99"/>
-      <c r="Z18" s="99"/>
-      <c r="AA18" s="99"/>
-      <c r="AB18" s="99"/>
+      <c r="O18" s="102"/>
+      <c r="P18" s="102"/>
+      <c r="Q18" s="102"/>
+      <c r="R18" s="102"/>
+      <c r="S18" s="102"/>
+      <c r="T18" s="102"/>
+      <c r="U18" s="102"/>
+      <c r="V18" s="102"/>
+      <c r="W18" s="102"/>
+      <c r="X18" s="102"/>
+      <c r="Y18" s="102"/>
+      <c r="Z18" s="102"/>
+      <c r="AA18" s="102"/>
+      <c r="AB18" s="102"/>
       <c r="AC18" s="33"/>
       <c r="AD18" s="33"/>
       <c r="AE18" s="33"/>
@@ -3240,21 +3277,21 @@
       <c r="K19" s="33"/>
       <c r="L19" s="33"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="99"/>
-      <c r="O19" s="99"/>
-      <c r="P19" s="99"/>
-      <c r="Q19" s="99"/>
-      <c r="R19" s="99"/>
-      <c r="S19" s="99"/>
-      <c r="T19" s="99"/>
-      <c r="U19" s="99"/>
-      <c r="V19" s="99"/>
-      <c r="W19" s="99"/>
-      <c r="X19" s="99"/>
-      <c r="Y19" s="99"/>
-      <c r="Z19" s="99"/>
-      <c r="AA19" s="99"/>
-      <c r="AB19" s="99"/>
+      <c r="N19" s="102"/>
+      <c r="O19" s="102"/>
+      <c r="P19" s="102"/>
+      <c r="Q19" s="102"/>
+      <c r="R19" s="102"/>
+      <c r="S19" s="102"/>
+      <c r="T19" s="102"/>
+      <c r="U19" s="102"/>
+      <c r="V19" s="102"/>
+      <c r="W19" s="102"/>
+      <c r="X19" s="102"/>
+      <c r="Y19" s="102"/>
+      <c r="Z19" s="102"/>
+      <c r="AA19" s="102"/>
+      <c r="AB19" s="102"/>
       <c r="AC19" s="33"/>
       <c r="AD19" s="33"/>
       <c r="AE19" s="33"/>
@@ -3272,7 +3309,7 @@
       </c>
       <c r="AQ19" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR19" s="30"/>
     </row>
@@ -3289,18 +3326,18 @@
       <c r="K20" s="64"/>
       <c r="L20" s="57"/>
       <c r="M20" s="4"/>
-      <c r="N20" s="136" t="s">
+      <c r="N20" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="O20" s="137"/>
+      <c r="O20" s="112"/>
       <c r="P20" s="60" t="s">
         <v>49</v>
       </c>
       <c r="Q20" s="39"/>
-      <c r="R20" s="136" t="s">
+      <c r="R20" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="S20" s="137"/>
+      <c r="S20" s="112"/>
       <c r="T20" s="60" t="s">
         <v>49</v>
       </c>
@@ -3354,16 +3391,16 @@
       <c r="K21" s="69"/>
       <c r="L21" s="61"/>
       <c r="M21" s="15"/>
-      <c r="N21" s="131" t="s">
+      <c r="N21" s="108" t="s">
         <v>92</v>
       </c>
-      <c r="O21" s="132"/>
+      <c r="O21" s="109"/>
       <c r="P21" s="62"/>
       <c r="Q21" s="36"/>
-      <c r="R21" s="131" t="s">
+      <c r="R21" s="108" t="s">
         <v>92</v>
       </c>
-      <c r="S21" s="132"/>
+      <c r="S21" s="109"/>
       <c r="T21" s="62"/>
       <c r="U21" s="36"/>
       <c r="V21" s="89" t="s">
@@ -3411,17 +3448,17 @@
       <c r="K22" s="82"/>
       <c r="L22" s="83"/>
       <c r="M22" s="4"/>
-      <c r="N22" s="125" t="s">
+      <c r="N22" s="142" t="s">
         <v>97</v>
       </c>
-      <c r="O22" s="126"/>
-      <c r="P22" s="127"/>
+      <c r="O22" s="143"/>
+      <c r="P22" s="144"/>
       <c r="Q22" s="35"/>
-      <c r="R22" s="125" t="s">
+      <c r="R22" s="142" t="s">
         <v>98</v>
       </c>
-      <c r="S22" s="126"/>
-      <c r="T22" s="127"/>
+      <c r="S22" s="143"/>
+      <c r="T22" s="144"/>
       <c r="U22" s="37"/>
       <c r="V22" s="81" t="s">
         <v>12</v>
@@ -3437,11 +3474,11 @@
       <c r="AE22" s="82"/>
       <c r="AF22" s="83"/>
       <c r="AG22" s="35"/>
-      <c r="AH22" s="122" t="s">
+      <c r="AH22" s="139" t="s">
         <v>9</v>
       </c>
-      <c r="AI22" s="123"/>
-      <c r="AJ22" s="124"/>
+      <c r="AI22" s="140"/>
+      <c r="AJ22" s="141"/>
       <c r="AK22" s="37"/>
       <c r="AL22" s="81"/>
       <c r="AM22" s="82"/>
@@ -3468,13 +3505,13 @@
       <c r="K23" s="85"/>
       <c r="L23" s="86"/>
       <c r="M23" s="4"/>
-      <c r="N23" s="128"/>
-      <c r="O23" s="129"/>
-      <c r="P23" s="130"/>
+      <c r="N23" s="145"/>
+      <c r="O23" s="146"/>
+      <c r="P23" s="147"/>
       <c r="Q23" s="44"/>
-      <c r="R23" s="128"/>
-      <c r="S23" s="129"/>
-      <c r="T23" s="130"/>
+      <c r="R23" s="145"/>
+      <c r="S23" s="146"/>
+      <c r="T23" s="147"/>
       <c r="U23" s="44"/>
       <c r="V23" s="84"/>
       <c r="W23" s="85"/>
@@ -3568,23 +3605,23 @@
       <c r="K25" s="33"/>
       <c r="L25" s="33"/>
       <c r="M25" s="4"/>
-      <c r="N25" s="99" t="s">
+      <c r="N25" s="102" t="s">
         <v>39</v>
       </c>
-      <c r="O25" s="99"/>
-      <c r="P25" s="99"/>
-      <c r="Q25" s="99"/>
-      <c r="R25" s="99"/>
-      <c r="S25" s="99"/>
-      <c r="T25" s="99"/>
-      <c r="U25" s="99"/>
-      <c r="V25" s="99"/>
-      <c r="W25" s="99"/>
-      <c r="X25" s="99"/>
-      <c r="Y25" s="99"/>
-      <c r="Z25" s="99"/>
-      <c r="AA25" s="99"/>
-      <c r="AB25" s="99"/>
+      <c r="O25" s="102"/>
+      <c r="P25" s="102"/>
+      <c r="Q25" s="102"/>
+      <c r="R25" s="102"/>
+      <c r="S25" s="102"/>
+      <c r="T25" s="102"/>
+      <c r="U25" s="102"/>
+      <c r="V25" s="102"/>
+      <c r="W25" s="102"/>
+      <c r="X25" s="102"/>
+      <c r="Y25" s="102"/>
+      <c r="Z25" s="102"/>
+      <c r="AA25" s="102"/>
+      <c r="AB25" s="102"/>
       <c r="AC25" s="33"/>
       <c r="AD25" s="33"/>
       <c r="AE25" s="33"/>
@@ -3619,21 +3656,21 @@
       <c r="K26" s="33"/>
       <c r="L26" s="33"/>
       <c r="M26" s="4"/>
-      <c r="N26" s="99"/>
-      <c r="O26" s="99"/>
-      <c r="P26" s="99"/>
-      <c r="Q26" s="99"/>
-      <c r="R26" s="99"/>
-      <c r="S26" s="99"/>
-      <c r="T26" s="99"/>
-      <c r="U26" s="99"/>
-      <c r="V26" s="99"/>
-      <c r="W26" s="99"/>
-      <c r="X26" s="99"/>
-      <c r="Y26" s="99"/>
-      <c r="Z26" s="99"/>
-      <c r="AA26" s="99"/>
-      <c r="AB26" s="99"/>
+      <c r="N26" s="102"/>
+      <c r="O26" s="102"/>
+      <c r="P26" s="102"/>
+      <c r="Q26" s="102"/>
+      <c r="R26" s="102"/>
+      <c r="S26" s="102"/>
+      <c r="T26" s="102"/>
+      <c r="U26" s="102"/>
+      <c r="V26" s="102"/>
+      <c r="W26" s="102"/>
+      <c r="X26" s="102"/>
+      <c r="Y26" s="102"/>
+      <c r="Z26" s="102"/>
+      <c r="AA26" s="102"/>
+      <c r="AB26" s="102"/>
       <c r="AC26" s="33"/>
       <c r="AD26" s="33"/>
       <c r="AE26" s="33"/>
@@ -3674,16 +3711,16 @@
       <c r="O27" s="88"/>
       <c r="P27" s="34"/>
       <c r="Q27" s="36"/>
-      <c r="R27" s="104"/>
-      <c r="S27" s="105"/>
+      <c r="R27" s="121"/>
+      <c r="S27" s="122"/>
       <c r="T27" s="55"/>
       <c r="U27" s="36"/>
-      <c r="V27" s="104"/>
-      <c r="W27" s="105"/>
+      <c r="V27" s="121"/>
+      <c r="W27" s="122"/>
       <c r="X27" s="55"/>
       <c r="Y27" s="36"/>
-      <c r="Z27" s="104"/>
-      <c r="AA27" s="105"/>
+      <c r="Z27" s="121"/>
+      <c r="AA27" s="122"/>
       <c r="AB27" s="55"/>
       <c r="AC27" s="36"/>
       <c r="AD27" s="87" t="s">
@@ -3739,12 +3776,12 @@
       <c r="S28" s="90"/>
       <c r="T28" s="18"/>
       <c r="U28" s="38"/>
-      <c r="V28" s="100"/>
-      <c r="W28" s="101"/>
+      <c r="V28" s="103"/>
+      <c r="W28" s="104"/>
       <c r="X28" s="56"/>
       <c r="Y28" s="36"/>
-      <c r="Z28" s="100"/>
-      <c r="AA28" s="101"/>
+      <c r="Z28" s="103"/>
+      <c r="AA28" s="104"/>
       <c r="AB28" s="56"/>
       <c r="AC28" s="36"/>
       <c r="AD28" s="89"/>
@@ -3768,54 +3805,54 @@
       <c r="AR28" s="30"/>
     </row>
     <row r="29" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="95"/>
-      <c r="C29" s="96"/>
+      <c r="B29" s="98"/>
+      <c r="C29" s="99"/>
       <c r="D29" s="41"/>
       <c r="E29" s="37"/>
-      <c r="F29" s="95"/>
-      <c r="G29" s="96"/>
+      <c r="F29" s="98"/>
+      <c r="G29" s="99"/>
       <c r="H29" s="41"/>
       <c r="I29" s="35"/>
-      <c r="J29" s="95"/>
-      <c r="K29" s="96"/>
+      <c r="J29" s="98"/>
+      <c r="K29" s="99"/>
       <c r="L29" s="41"/>
       <c r="M29" s="5"/>
-      <c r="N29" s="95"/>
-      <c r="O29" s="96"/>
+      <c r="N29" s="98"/>
+      <c r="O29" s="99"/>
       <c r="P29" s="41"/>
       <c r="Q29" s="35"/>
-      <c r="R29" s="95"/>
-      <c r="S29" s="96"/>
+      <c r="R29" s="98"/>
+      <c r="S29" s="99"/>
       <c r="T29" s="41"/>
       <c r="U29" s="37"/>
-      <c r="V29" s="95"/>
-      <c r="W29" s="96"/>
+      <c r="V29" s="98"/>
+      <c r="W29" s="99"/>
       <c r="X29" s="41"/>
       <c r="Y29" s="35"/>
-      <c r="Z29" s="95"/>
-      <c r="AA29" s="96"/>
+      <c r="Z29" s="98"/>
+      <c r="AA29" s="99"/>
       <c r="AB29" s="41"/>
       <c r="AC29" s="35"/>
-      <c r="AD29" s="95" t="s">
+      <c r="AD29" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="AE29" s="96"/>
+      <c r="AE29" s="99"/>
       <c r="AF29" s="41" t="s">
         <v>32</v>
       </c>
       <c r="AG29" s="37"/>
-      <c r="AH29" s="95" t="s">
+      <c r="AH29" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="AI29" s="96"/>
+      <c r="AI29" s="99"/>
       <c r="AJ29" s="41" t="s">
         <v>32</v>
       </c>
       <c r="AK29" s="35"/>
-      <c r="AL29" s="95" t="s">
+      <c r="AL29" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="AM29" s="96"/>
+      <c r="AM29" s="99"/>
       <c r="AN29" s="41" t="s">
         <v>32</v>
       </c>
@@ -3829,54 +3866,54 @@
       <c r="AR29" s="30"/>
     </row>
     <row r="30" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="97"/>
-      <c r="C30" s="98"/>
+      <c r="B30" s="100"/>
+      <c r="C30" s="101"/>
       <c r="D30" s="45"/>
       <c r="E30" s="43"/>
-      <c r="F30" s="97"/>
-      <c r="G30" s="98"/>
+      <c r="F30" s="100"/>
+      <c r="G30" s="101"/>
       <c r="H30" s="45"/>
       <c r="I30" s="43"/>
-      <c r="J30" s="97"/>
-      <c r="K30" s="98"/>
+      <c r="J30" s="100"/>
+      <c r="K30" s="101"/>
       <c r="L30" s="45"/>
       <c r="M30" s="5"/>
-      <c r="N30" s="97"/>
-      <c r="O30" s="98"/>
+      <c r="N30" s="100"/>
+      <c r="O30" s="101"/>
       <c r="P30" s="45"/>
       <c r="Q30" s="43"/>
-      <c r="R30" s="97"/>
-      <c r="S30" s="98"/>
+      <c r="R30" s="100"/>
+      <c r="S30" s="101"/>
       <c r="T30" s="45"/>
       <c r="U30" s="43"/>
-      <c r="V30" s="97"/>
-      <c r="W30" s="98"/>
+      <c r="V30" s="100"/>
+      <c r="W30" s="101"/>
       <c r="X30" s="45"/>
       <c r="Y30" s="43"/>
-      <c r="Z30" s="97"/>
-      <c r="AA30" s="98"/>
+      <c r="Z30" s="100"/>
+      <c r="AA30" s="101"/>
       <c r="AB30" s="45"/>
       <c r="AC30" s="43"/>
-      <c r="AD30" s="97" t="s">
+      <c r="AD30" s="100" t="s">
         <v>19</v>
       </c>
-      <c r="AE30" s="98"/>
+      <c r="AE30" s="101"/>
       <c r="AF30" s="45" t="s">
         <v>33</v>
       </c>
       <c r="AG30" s="43"/>
-      <c r="AH30" s="97" t="s">
+      <c r="AH30" s="100" t="s">
         <v>19</v>
       </c>
-      <c r="AI30" s="98"/>
+      <c r="AI30" s="101"/>
       <c r="AJ30" s="45" t="s">
         <v>33</v>
       </c>
       <c r="AK30" s="43"/>
-      <c r="AL30" s="97" t="s">
+      <c r="AL30" s="100" t="s">
         <v>19</v>
       </c>
-      <c r="AM30" s="98"/>
+      <c r="AM30" s="101"/>
       <c r="AN30" s="45" t="s">
         <v>33</v>
       </c>
@@ -4152,23 +4189,23 @@
       <c r="K36" s="33"/>
       <c r="L36" s="33"/>
       <c r="M36" s="4"/>
-      <c r="N36" s="99" t="s">
+      <c r="N36" s="102" t="s">
         <v>36</v>
       </c>
-      <c r="O36" s="99"/>
-      <c r="P36" s="99"/>
-      <c r="Q36" s="99"/>
-      <c r="R36" s="99"/>
-      <c r="S36" s="99"/>
-      <c r="T36" s="99"/>
-      <c r="U36" s="99"/>
-      <c r="V36" s="99"/>
-      <c r="W36" s="99"/>
-      <c r="X36" s="99"/>
-      <c r="Y36" s="99"/>
-      <c r="Z36" s="99"/>
-      <c r="AA36" s="99"/>
-      <c r="AB36" s="99"/>
+      <c r="O36" s="102"/>
+      <c r="P36" s="102"/>
+      <c r="Q36" s="102"/>
+      <c r="R36" s="102"/>
+      <c r="S36" s="102"/>
+      <c r="T36" s="102"/>
+      <c r="U36" s="102"/>
+      <c r="V36" s="102"/>
+      <c r="W36" s="102"/>
+      <c r="X36" s="102"/>
+      <c r="Y36" s="102"/>
+      <c r="Z36" s="102"/>
+      <c r="AA36" s="102"/>
+      <c r="AB36" s="102"/>
       <c r="AC36" s="33"/>
       <c r="AD36" s="33"/>
       <c r="AE36" s="33"/>
@@ -4200,21 +4237,21 @@
       <c r="K37" s="33"/>
       <c r="L37" s="33"/>
       <c r="M37" s="5"/>
-      <c r="N37" s="99"/>
-      <c r="O37" s="99"/>
-      <c r="P37" s="99"/>
-      <c r="Q37" s="99"/>
-      <c r="R37" s="99"/>
-      <c r="S37" s="99"/>
-      <c r="T37" s="99"/>
-      <c r="U37" s="99"/>
-      <c r="V37" s="99"/>
-      <c r="W37" s="99"/>
-      <c r="X37" s="99"/>
-      <c r="Y37" s="99"/>
-      <c r="Z37" s="99"/>
-      <c r="AA37" s="99"/>
-      <c r="AB37" s="99"/>
+      <c r="N37" s="102"/>
+      <c r="O37" s="102"/>
+      <c r="P37" s="102"/>
+      <c r="Q37" s="102"/>
+      <c r="R37" s="102"/>
+      <c r="S37" s="102"/>
+      <c r="T37" s="102"/>
+      <c r="U37" s="102"/>
+      <c r="V37" s="102"/>
+      <c r="W37" s="102"/>
+      <c r="X37" s="102"/>
+      <c r="Y37" s="102"/>
+      <c r="Z37" s="102"/>
+      <c r="AA37" s="102"/>
+      <c r="AB37" s="102"/>
       <c r="AC37" s="33"/>
       <c r="AD37" s="33"/>
       <c r="AE37" s="33"/>
@@ -4468,11 +4505,11 @@
       <c r="AE41" s="66"/>
       <c r="AF41" s="67"/>
       <c r="AG41" s="37"/>
-      <c r="AH41" s="150" t="s">
-        <v>106</v>
-      </c>
-      <c r="AI41" s="151"/>
-      <c r="AJ41" s="152"/>
+      <c r="AH41" s="95" t="s">
+        <v>105</v>
+      </c>
+      <c r="AI41" s="96"/>
+      <c r="AJ41" s="97"/>
       <c r="AK41" s="31"/>
       <c r="AL41" s="65" t="s">
         <v>24</v>
@@ -4890,11 +4927,11 @@
       <c r="AI48" s="66"/>
       <c r="AJ48" s="67"/>
       <c r="AK48" s="44"/>
-      <c r="AL48" s="106" t="s">
-        <v>18</v>
-      </c>
-      <c r="AM48" s="107"/>
-      <c r="AN48" s="108"/>
+      <c r="AL48" s="105" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM48" s="106"/>
+      <c r="AN48" s="107"/>
       <c r="AO48" s="31"/>
       <c r="AP48" s="31"/>
       <c r="AQ48" s="31"/>
@@ -4923,11 +4960,11 @@
       <c r="O49" s="66"/>
       <c r="P49" s="67"/>
       <c r="Q49" s="44"/>
-      <c r="R49" s="106" t="s">
+      <c r="R49" s="105" t="s">
         <v>37</v>
       </c>
-      <c r="S49" s="107"/>
-      <c r="T49" s="108"/>
+      <c r="S49" s="106"/>
+      <c r="T49" s="107"/>
       <c r="U49" s="44"/>
       <c r="V49" s="65" t="s">
         <v>18</v>
@@ -4947,11 +4984,11 @@
       <c r="AE49" s="66"/>
       <c r="AF49" s="67"/>
       <c r="AG49" s="35"/>
-      <c r="AH49" s="150" t="s">
-        <v>105</v>
-      </c>
-      <c r="AI49" s="151"/>
-      <c r="AJ49" s="152"/>
+      <c r="AH49" s="65" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI49" s="66"/>
+      <c r="AJ49" s="67"/>
       <c r="AK49" s="44"/>
       <c r="AL49" s="65" t="s">
         <v>26</v>
@@ -4986,11 +5023,11 @@
       <c r="O50" s="72"/>
       <c r="P50" s="73"/>
       <c r="Q50" s="50"/>
-      <c r="R50" s="147" t="s">
+      <c r="R50" s="160" t="s">
         <v>96</v>
       </c>
-      <c r="S50" s="148"/>
-      <c r="T50" s="149"/>
+      <c r="S50" s="161"/>
+      <c r="T50" s="162"/>
       <c r="U50" s="50"/>
       <c r="V50" s="65" t="s">
         <v>15</v>
@@ -5004,11 +5041,11 @@
       <c r="AA50" s="66"/>
       <c r="AB50" s="67"/>
       <c r="AC50" s="50"/>
-      <c r="AD50" s="71" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE50" s="72"/>
-      <c r="AF50" s="73"/>
+      <c r="AD50" s="160" t="s">
+        <v>108</v>
+      </c>
+      <c r="AE50" s="161"/>
+      <c r="AF50" s="162"/>
       <c r="AG50" s="50"/>
       <c r="AH50" s="71" t="s">
         <v>14</v>
@@ -5080,10 +5117,10 @@
       <c r="C52" s="64"/>
       <c r="D52" s="57"/>
       <c r="E52" s="36"/>
-      <c r="F52" s="102" t="s">
+      <c r="F52" s="113" t="s">
         <v>89</v>
       </c>
-      <c r="G52" s="103"/>
+      <c r="G52" s="114"/>
       <c r="H52" s="59" t="s">
         <v>90</v>
       </c>
@@ -5100,10 +5137,10 @@
       <c r="O52" s="88"/>
       <c r="P52" s="34"/>
       <c r="Q52" s="31"/>
-      <c r="R52" s="102" t="s">
+      <c r="R52" s="113" t="s">
         <v>89</v>
       </c>
-      <c r="S52" s="103"/>
+      <c r="S52" s="114"/>
       <c r="T52" s="59" t="s">
         <v>94</v>
       </c>
@@ -5116,18 +5153,18 @@
       <c r="AA52" s="35"/>
       <c r="AB52" s="35"/>
       <c r="AC52" s="36"/>
-      <c r="AD52" s="102" t="s">
+      <c r="AD52" s="113" t="s">
         <v>89</v>
       </c>
-      <c r="AE52" s="103"/>
+      <c r="AE52" s="114"/>
       <c r="AF52" s="59" t="s">
         <v>102</v>
       </c>
       <c r="AG52" s="36"/>
-      <c r="AH52" s="102" t="s">
+      <c r="AH52" s="113" t="s">
         <v>89</v>
       </c>
-      <c r="AI52" s="103"/>
+      <c r="AI52" s="114"/>
       <c r="AJ52" s="59" t="s">
         <v>90</v>
       </c>
@@ -5333,7 +5370,7 @@
       <c r="AF56" s="67"/>
       <c r="AG56" s="44"/>
       <c r="AH56" s="65" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="AI56" s="66"/>
       <c r="AJ56" s="67"/>
@@ -5352,11 +5389,11 @@
       <c r="G57" s="72"/>
       <c r="H57" s="73"/>
       <c r="I57" s="50"/>
-      <c r="J57" s="141" t="s">
+      <c r="J57" s="154" t="s">
         <v>8</v>
       </c>
-      <c r="K57" s="142"/>
-      <c r="L57" s="143"/>
+      <c r="K57" s="155"/>
+      <c r="L57" s="156"/>
       <c r="M57" s="5"/>
       <c r="N57" s="71"/>
       <c r="O57" s="72"/>
@@ -5460,10 +5497,10 @@
       <c r="AA59" s="88"/>
       <c r="AB59" s="34"/>
       <c r="AC59" s="32"/>
-      <c r="AD59" s="102" t="s">
+      <c r="AD59" s="113" t="s">
         <v>89</v>
       </c>
-      <c r="AE59" s="103"/>
+      <c r="AE59" s="114"/>
       <c r="AF59" s="59" t="s">
         <v>90</v>
       </c>
@@ -5761,16 +5798,16 @@
       <c r="S66" s="88"/>
       <c r="T66" s="34"/>
       <c r="U66" s="36"/>
-      <c r="V66" s="102" t="s">
+      <c r="V66" s="111" t="s">
         <v>99</v>
       </c>
-      <c r="W66" s="103"/>
-      <c r="X66" s="59"/>
+      <c r="W66" s="112"/>
+      <c r="X66" s="60"/>
       <c r="Y66" s="36"/>
-      <c r="Z66" s="102" t="s">
+      <c r="Z66" s="113" t="s">
         <v>99</v>
       </c>
-      <c r="AA66" s="103"/>
+      <c r="AA66" s="114"/>
       <c r="AB66" s="59"/>
       <c r="AC66" s="36"/>
       <c r="AD66" s="87"/>
@@ -5811,11 +5848,11 @@
       <c r="S67" s="93"/>
       <c r="T67" s="94"/>
       <c r="U67" s="36"/>
-      <c r="V67" s="92" t="s">
+      <c r="V67" s="115" t="s">
         <v>100</v>
       </c>
-      <c r="W67" s="93"/>
-      <c r="X67" s="94"/>
+      <c r="W67" s="116"/>
+      <c r="X67" s="117"/>
       <c r="Y67" s="36"/>
       <c r="Z67" s="92" t="s">
         <v>100</v>
@@ -5861,9 +5898,11 @@
       <c r="S68" s="90"/>
       <c r="T68" s="91"/>
       <c r="U68" s="43"/>
-      <c r="V68" s="89"/>
-      <c r="W68" s="90"/>
-      <c r="X68" s="91"/>
+      <c r="V68" s="108" t="s">
+        <v>92</v>
+      </c>
+      <c r="W68" s="109"/>
+      <c r="X68" s="110"/>
       <c r="Y68" s="43"/>
       <c r="Z68" s="89"/>
       <c r="AA68" s="90"/>
@@ -5909,11 +5948,11 @@
       <c r="S69" s="66"/>
       <c r="T69" s="67"/>
       <c r="U69" s="37"/>
-      <c r="V69" s="65" t="s">
-        <v>25</v>
-      </c>
-      <c r="W69" s="66"/>
-      <c r="X69" s="67"/>
+      <c r="V69" s="118" t="s">
+        <v>106</v>
+      </c>
+      <c r="W69" s="119"/>
+      <c r="X69" s="120"/>
       <c r="Y69" s="35"/>
       <c r="Z69" s="65" t="s">
         <v>22</v>
@@ -5961,14 +6000,14 @@
       <c r="S70" s="66"/>
       <c r="T70" s="67"/>
       <c r="U70" s="44"/>
-      <c r="V70" s="65" t="s">
-        <v>24</v>
-      </c>
-      <c r="W70" s="66"/>
-      <c r="X70" s="67"/>
+      <c r="V70" s="118" t="s">
+        <v>107</v>
+      </c>
+      <c r="W70" s="119"/>
+      <c r="X70" s="120"/>
       <c r="Y70" s="40"/>
       <c r="Z70" s="65" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="AA70" s="66"/>
       <c r="AB70" s="67"/>
@@ -6013,15 +6052,17 @@
       <c r="S71" s="72"/>
       <c r="T71" s="73"/>
       <c r="U71" s="44"/>
-      <c r="V71" s="71" t="s">
-        <v>26</v>
-      </c>
-      <c r="W71" s="72"/>
-      <c r="X71" s="73"/>
+      <c r="V71" s="123" t="s">
+        <v>108</v>
+      </c>
+      <c r="W71" s="124"/>
+      <c r="X71" s="125"/>
       <c r="Y71" s="44"/>
-      <c r="Z71" s="71"/>
-      <c r="AA71" s="72"/>
-      <c r="AB71" s="73"/>
+      <c r="Z71" s="160" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA71" s="161"/>
+      <c r="AB71" s="162"/>
       <c r="AC71" s="50"/>
       <c r="AD71" s="71"/>
       <c r="AE71" s="72"/>
@@ -6101,23 +6142,23 @@
       <c r="K73" s="33"/>
       <c r="L73" s="33"/>
       <c r="M73" s="14"/>
-      <c r="N73" s="99" t="s">
+      <c r="N73" s="102" t="s">
         <v>31</v>
       </c>
-      <c r="O73" s="99"/>
-      <c r="P73" s="99"/>
-      <c r="Q73" s="99"/>
-      <c r="R73" s="99"/>
-      <c r="S73" s="99"/>
-      <c r="T73" s="99"/>
-      <c r="U73" s="99"/>
-      <c r="V73" s="99"/>
-      <c r="W73" s="99"/>
-      <c r="X73" s="99"/>
-      <c r="Y73" s="99"/>
-      <c r="Z73" s="99"/>
-      <c r="AA73" s="99"/>
-      <c r="AB73" s="99"/>
+      <c r="O73" s="102"/>
+      <c r="P73" s="102"/>
+      <c r="Q73" s="102"/>
+      <c r="R73" s="102"/>
+      <c r="S73" s="102"/>
+      <c r="T73" s="102"/>
+      <c r="U73" s="102"/>
+      <c r="V73" s="102"/>
+      <c r="W73" s="102"/>
+      <c r="X73" s="102"/>
+      <c r="Y73" s="102"/>
+      <c r="Z73" s="102"/>
+      <c r="AA73" s="102"/>
+      <c r="AB73" s="102"/>
       <c r="AD73" s="40"/>
       <c r="AE73" s="33"/>
       <c r="AF73" s="33"/>
@@ -6148,21 +6189,21 @@
       <c r="K74" s="33"/>
       <c r="L74" s="33"/>
       <c r="M74" s="14"/>
-      <c r="N74" s="99"/>
-      <c r="O74" s="99"/>
-      <c r="P74" s="99"/>
-      <c r="Q74" s="99"/>
-      <c r="R74" s="99"/>
-      <c r="S74" s="99"/>
-      <c r="T74" s="99"/>
-      <c r="U74" s="99"/>
-      <c r="V74" s="99"/>
-      <c r="W74" s="99"/>
-      <c r="X74" s="99"/>
-      <c r="Y74" s="99"/>
-      <c r="Z74" s="99"/>
-      <c r="AA74" s="99"/>
-      <c r="AB74" s="99"/>
+      <c r="N74" s="102"/>
+      <c r="O74" s="102"/>
+      <c r="P74" s="102"/>
+      <c r="Q74" s="102"/>
+      <c r="R74" s="102"/>
+      <c r="S74" s="102"/>
+      <c r="T74" s="102"/>
+      <c r="U74" s="102"/>
+      <c r="V74" s="102"/>
+      <c r="W74" s="102"/>
+      <c r="X74" s="102"/>
+      <c r="Y74" s="102"/>
+      <c r="Z74" s="102"/>
+      <c r="AA74" s="102"/>
+      <c r="AB74" s="102"/>
       <c r="AC74" s="21"/>
       <c r="AD74" s="33"/>
       <c r="AE74" s="33"/>
@@ -6182,16 +6223,16 @@
     </row>
     <row r="75" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="12"/>
-      <c r="B75" s="136" t="s">
+      <c r="B75" s="111" t="s">
         <v>58</v>
       </c>
-      <c r="C75" s="137"/>
+      <c r="C75" s="112"/>
       <c r="D75" s="60"/>
       <c r="E75" s="32"/>
-      <c r="F75" s="136" t="s">
+      <c r="F75" s="111" t="s">
         <v>52</v>
       </c>
-      <c r="G75" s="137"/>
+      <c r="G75" s="112"/>
       <c r="H75" s="60"/>
       <c r="I75" s="32"/>
       <c r="J75" s="63"/>
@@ -6252,17 +6293,17 @@
     </row>
     <row r="76" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="12"/>
-      <c r="B76" s="144" t="s">
+      <c r="B76" s="157" t="s">
         <v>92</v>
       </c>
-      <c r="C76" s="145"/>
-      <c r="D76" s="146"/>
+      <c r="C76" s="158"/>
+      <c r="D76" s="159"/>
       <c r="E76" s="32"/>
-      <c r="F76" s="144" t="s">
+      <c r="F76" s="157" t="s">
         <v>92</v>
       </c>
-      <c r="G76" s="145"/>
-      <c r="H76" s="146"/>
+      <c r="G76" s="158"/>
+      <c r="H76" s="159"/>
       <c r="I76" s="32"/>
       <c r="J76" s="78"/>
       <c r="K76" s="79"/>
@@ -6312,17 +6353,17 @@
     </row>
     <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="16"/>
-      <c r="B77" s="138" t="s">
+      <c r="B77" s="151" t="s">
         <v>60</v>
       </c>
-      <c r="C77" s="139"/>
-      <c r="D77" s="140"/>
+      <c r="C77" s="152"/>
+      <c r="D77" s="153"/>
       <c r="E77" s="32"/>
-      <c r="F77" s="138" t="s">
+      <c r="F77" s="151" t="s">
         <v>60</v>
       </c>
-      <c r="G77" s="139"/>
-      <c r="H77" s="140"/>
+      <c r="G77" s="152"/>
+      <c r="H77" s="153"/>
       <c r="I77" s="32"/>
       <c r="J77" s="68"/>
       <c r="K77" s="69"/>
@@ -6362,17 +6403,17 @@
     </row>
     <row r="78" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="16"/>
-      <c r="B78" s="125" t="s">
+      <c r="B78" s="142" t="s">
         <v>93</v>
       </c>
-      <c r="C78" s="126"/>
-      <c r="D78" s="127"/>
+      <c r="C78" s="143"/>
+      <c r="D78" s="144"/>
       <c r="E78" s="32"/>
-      <c r="F78" s="125" t="s">
+      <c r="F78" s="142" t="s">
         <v>93</v>
       </c>
-      <c r="G78" s="126"/>
-      <c r="H78" s="127"/>
+      <c r="G78" s="143"/>
+      <c r="H78" s="144"/>
       <c r="I78" s="43"/>
       <c r="J78" s="81"/>
       <c r="K78" s="82"/>
@@ -6422,13 +6463,13 @@
     </row>
     <row r="79" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A79" s="16"/>
-      <c r="B79" s="128"/>
-      <c r="C79" s="129"/>
-      <c r="D79" s="130"/>
+      <c r="B79" s="145"/>
+      <c r="C79" s="146"/>
+      <c r="D79" s="147"/>
       <c r="E79" s="31"/>
-      <c r="F79" s="128"/>
-      <c r="G79" s="129"/>
-      <c r="H79" s="130"/>
+      <c r="F79" s="145"/>
+      <c r="G79" s="146"/>
+      <c r="H79" s="147"/>
       <c r="I79" s="32"/>
       <c r="J79" s="71"/>
       <c r="K79" s="72"/>
@@ -8276,6 +8317,7 @@
     <mergeCell ref="F107:H107"/>
     <mergeCell ref="J107:L107"/>
     <mergeCell ref="J109:L109"/>
+    <mergeCell ref="B112:D112"/>
     <mergeCell ref="B120:D120"/>
     <mergeCell ref="B121:D121"/>
     <mergeCell ref="B123:C123"/>
@@ -8290,7 +8332,6 @@
     <mergeCell ref="B115:D115"/>
     <mergeCell ref="F115:H115"/>
     <mergeCell ref="J115:L115"/>
-    <mergeCell ref="B112:D112"/>
     <mergeCell ref="F120:H120"/>
     <mergeCell ref="B126:D126"/>
     <mergeCell ref="F126:H126"/>
@@ -8556,6 +8597,10 @@
     <mergeCell ref="AH95:AJ95"/>
     <mergeCell ref="V90:X90"/>
     <mergeCell ref="V88:X88"/>
+    <mergeCell ref="R90:T90"/>
+    <mergeCell ref="AH88:AJ88"/>
+    <mergeCell ref="AH89:AJ89"/>
+    <mergeCell ref="AD85:AF85"/>
     <mergeCell ref="AL77:AN77"/>
     <mergeCell ref="AL78:AN78"/>
     <mergeCell ref="AD77:AF77"/>
@@ -8566,9 +8611,6 @@
     <mergeCell ref="AH81:AI81"/>
     <mergeCell ref="AL81:AM81"/>
     <mergeCell ref="AH78:AJ78"/>
-    <mergeCell ref="R83:T83"/>
-    <mergeCell ref="AD82:AF82"/>
-    <mergeCell ref="AH83:AJ83"/>
     <mergeCell ref="AD84:AF84"/>
     <mergeCell ref="AH84:AJ84"/>
     <mergeCell ref="AD83:AF83"/>
@@ -8586,10 +8628,6 @@
     <mergeCell ref="AD89:AF89"/>
     <mergeCell ref="AH87:AI87"/>
     <mergeCell ref="AL87:AM87"/>
-    <mergeCell ref="R90:T90"/>
-    <mergeCell ref="AH88:AJ88"/>
-    <mergeCell ref="AH89:AJ89"/>
-    <mergeCell ref="AD85:AF85"/>
     <mergeCell ref="AH85:AJ85"/>
     <mergeCell ref="AL85:AN85"/>
     <mergeCell ref="AH75:AI75"/>
@@ -8611,6 +8649,9 @@
     <mergeCell ref="V84:X84"/>
     <mergeCell ref="R82:T82"/>
     <mergeCell ref="V83:X83"/>
+    <mergeCell ref="R83:T83"/>
+    <mergeCell ref="AD82:AF82"/>
+    <mergeCell ref="AH83:AJ83"/>
     <mergeCell ref="N78:P78"/>
     <mergeCell ref="Z78:AB78"/>
     <mergeCell ref="N79:P79"/>
@@ -8725,7 +8766,6 @@
     <mergeCell ref="F30:G30"/>
     <mergeCell ref="J30:K30"/>
     <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J43:L43"/>
     <mergeCell ref="N47:P47"/>
     <mergeCell ref="F49:H49"/>
     <mergeCell ref="F46:H46"/>
@@ -8747,6 +8787,7 @@
     <mergeCell ref="J47:L47"/>
     <mergeCell ref="B45:C45"/>
     <mergeCell ref="J42:L42"/>
+    <mergeCell ref="F45:G45"/>
     <mergeCell ref="Z54:AB54"/>
     <mergeCell ref="Z50:AB50"/>
     <mergeCell ref="V45:W45"/>
@@ -8915,7 +8956,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="J27:K27"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="F45:G45"/>
     <mergeCell ref="B52:C52"/>
     <mergeCell ref="F41:H41"/>
     <mergeCell ref="B41:D41"/>
@@ -8939,12 +8979,13 @@
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="F43:H43"/>
+    <mergeCell ref="J43:L43"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="D29:D34 AJ29:AJ34 X29:X34 T29:T34 AB29:AB34 AF29:AF34 P29:P34 H29:H34 L29:L34 AN29:AN34">
       <formula1>$AP$68:$AP$71</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="AL41:AN43 AH69:AJ71 AL90:AN91 J48:L50 N29:O34 Z29:AA34 F55:H57 J132:L133 V78:X79 R78:T79 AD96:AF97 Z56:AB57 R69:T71 Z78:AB79 Z48:AB51 Z96:AB97 B55:D57 AH48:AJ50 V8:X10 R101:T102 AD69:AF71 J114:L115 AL78:AN79 AL69:AN71 AH41:AJ43 R8:T10 B41:D43 B108:D109 B62:D64 Z14:AB16 AD41:AF43 R14:T16 F48:H50 AL14:AN16 F62:H64 J55:L57 N78:P79 R62:T64 B8:D10 J120:L121 F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 B126:D127 AD14:AF16 B114:D115 J126:L127 N48:P50 Z101:AB102 AD22:AF23 N84:P85 AD84:AF85 R22:T23 V14:X16 V22:X23 F108:H109 Z22:AB23 AL101:AN102 AL22:AN23 R55:T57 AD90:AF91 AD55:AF57 N22:P23 N90:P91 J22:L23 J62:L64 V48:X51 N96:P97 R84:T85 V96:X97 R41:T43 AD101:AF102 N14:P16 AD62:AF64 AH90:AJ91 V84:X85 Z41:AB43 AH62:AJ64 N101:P102 Z84:AB85 V41:X43 AH78:AJ79 AL84:AN85 AH55:AJ57 V56:X57 B29:C34 J29:K34 AH96:AJ97 AH101:AJ102 AL48:AN50 V90:X91 AL96:AN97 Z8:AB10 AH84:AJ85 AL8:AN10 N62:P64 N8:P10 AD78:AF79 V69:X71 AD8:AF10 V101:X102 V62:X64 AH8:AJ10 N55:P57 R29:S34 Z62:AB64 N41:P43 V29:W34 AL55:AN57 B78:D79 AL62:AN64 F29:G34 AD48:AF50 N69:P71 AL29:AM34 AH22:AJ23 AD29:AE34 AH29:AI34 R96:T97 AH14:AJ16 F22:H23 R90:T91 F8:H10 R48:T50 J8:L10 F14:H16 Z90:AB91 J14:L16 B14:D16 B22:D23 J41:L43 F69:H71 B69:D71 B48:D50 J69:L71 F41:H43 F78:H79 B96:D97 J78:L79 F84:H85 J101:L102 B84:D85 B101:D102 B90:D91 F96:H97 F101:H102 J90:L91 J96:L97 F90:H91 J84:L85 Z69:AB71">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="AL41:AN43 AH69:AJ71 AL90:AN91 J48:L50 N29:O34 Z29:AA34 F55:H57 J132:L133 V78:X79 R78:T79 AD96:AF97 Z56:AB57 R69:T71 Z78:AB79 Z48:AB51 Z96:AB97 B55:D57 AH55:AJ57 V8:X10 R101:T102 AD69:AF71 J114:L115 AL78:AN79 AL69:AN71 AH41:AJ43 R8:T10 B41:D43 B108:D109 B62:D64 Z14:AB16 AD41:AF43 R14:T16 F48:H50 AL14:AN16 F62:H64 J55:L57 N78:P79 R62:T64 B8:D10 J120:L121 F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 B126:D127 AD14:AF16 B114:D115 J126:L127 N48:P50 Z101:AB102 AD22:AF23 N84:P85 AD84:AF85 R22:T23 V14:X16 V22:X23 F108:H109 Z22:AB23 AL101:AN102 AL22:AN23 R55:T57 AD90:AF91 AD55:AF57 N22:P23 N90:P91 J22:L23 J62:L64 V48:X51 N96:P97 R84:T85 V96:X97 R41:T43 AD101:AF102 N14:P16 AD62:AF64 AH90:AJ91 V84:X85 Z41:AB43 AH62:AJ64 N101:P102 Z84:AB85 V41:X43 AH78:AJ79 AL84:AN85 AH48:AJ50 V56:X57 B29:C34 J29:K34 AH96:AJ97 AH101:AJ102 AL48:AN50 V90:X91 AL96:AN97 Z8:AB10 AH84:AJ85 AL8:AN10 N62:P64 N8:P10 AD78:AF79 V69:X71 AD8:AF10 V101:X102 V62:X64 AH8:AJ10 N55:P57 R29:S34 Z62:AB64 N41:P43 V29:W34 AL55:AN57 B78:D79 AL62:AN64 F29:G34 AD48:AF50 N69:P71 AL29:AM34 AH22:AJ23 AD29:AE34 AH29:AI34 R96:T97 AH14:AJ16 F22:H23 R90:T91 F8:H10 R48:T50 J8:L10 F14:H16 Z90:AB91 J14:L16 B14:D16 B22:D23 J41:L43 F69:H71 B69:D71 B48:D50 J69:L71 F41:H43 F78:H79 B96:D97 J78:L79 F84:H85 J101:L102 B84:D85 B101:D102 B90:D91 F96:H97 F101:H102 J90:L91 J96:L97 F90:H91 J84:L85 Z69:AB71">
       <formula1>$AP$6:$AP$30</formula1>
     </dataValidation>
   </dataValidations>

--- a/Gorev-Listesi.xlsx
+++ b/Gorev-Listesi.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="109">
   <si>
     <t>CUMA</t>
   </si>
@@ -1392,7 +1392,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="163">
+  <cellXfs count="166">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1554,6 +1554,30 @@
     <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="14" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1563,10 +1587,43 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="12" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="13" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="7" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1575,6 +1632,24 @@
     <xf numFmtId="49" fontId="11" fillId="7" borderId="9" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="18" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="7" borderId="11" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1584,6 +1659,156 @@
     <xf numFmtId="49" fontId="11" fillId="7" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="11" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="12" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="13" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="12" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="13" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="14" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="15" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="16" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="11" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="12" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="13" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="17" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="18" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="19" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="8" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="9" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="10" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="9" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="9" borderId="17" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1593,73 +1818,31 @@
     <xf numFmtId="49" fontId="7" fillId="9" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="9" xfId="57" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="18" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="18" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="17" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="18" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="12" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="13" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="14" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="19" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="11" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1671,187 +1854,13 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="13" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="17" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="18" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="19" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="18" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="12" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="13" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="8" borderId="8" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="8" borderId="9" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="8" borderId="10" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="14" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="15" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="17" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="18" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="19" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="11" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="12" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="13" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="16" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="11" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="12" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="13" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2226,7 +2235,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="1" width="183" row="2" locked="1">
+  <wetp:taskpane dockstate="right" visibility="1" width="167" row="3" locked="1">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -2303,65 +2312,65 @@
   <sheetData>
     <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12"/>
-      <c r="B1" s="136" t="s">
+      <c r="B1" s="131" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
       <c r="E1" s="10"/>
-      <c r="F1" s="137" t="s">
+      <c r="F1" s="132" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="137"/>
-      <c r="H1" s="137"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
       <c r="I1" s="10"/>
-      <c r="J1" s="137" t="s">
+      <c r="J1" s="132" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="137"/>
-      <c r="L1" s="138"/>
+      <c r="K1" s="132"/>
+      <c r="L1" s="133"/>
       <c r="M1" s="12"/>
-      <c r="N1" s="141" t="s">
+      <c r="N1" s="136" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="131"/>
-      <c r="P1" s="131"/>
+      <c r="O1" s="130"/>
+      <c r="P1" s="130"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="131" t="s">
+      <c r="R1" s="130" t="s">
         <v>4</v>
       </c>
-      <c r="S1" s="131"/>
-      <c r="T1" s="131"/>
+      <c r="S1" s="130"/>
+      <c r="T1" s="130"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="131" t="s">
+      <c r="V1" s="130" t="s">
         <v>5</v>
       </c>
-      <c r="W1" s="131"/>
-      <c r="X1" s="131"/>
+      <c r="W1" s="130"/>
+      <c r="X1" s="130"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="131" t="s">
+      <c r="Z1" s="130" t="s">
         <v>6</v>
       </c>
-      <c r="AA1" s="131"/>
-      <c r="AB1" s="131"/>
+      <c r="AA1" s="130"/>
+      <c r="AB1" s="130"/>
       <c r="AC1" s="1"/>
-      <c r="AD1" s="131" t="s">
+      <c r="AD1" s="130" t="s">
         <v>0</v>
       </c>
-      <c r="AE1" s="131"/>
-      <c r="AF1" s="131"/>
+      <c r="AE1" s="130"/>
+      <c r="AF1" s="130"/>
       <c r="AG1" s="1"/>
-      <c r="AH1" s="131" t="s">
+      <c r="AH1" s="130" t="s">
         <v>1</v>
       </c>
-      <c r="AI1" s="131"/>
-      <c r="AJ1" s="131"/>
+      <c r="AI1" s="130"/>
+      <c r="AJ1" s="130"/>
       <c r="AK1" s="1"/>
-      <c r="AL1" s="131" t="s">
+      <c r="AL1" s="130" t="s">
         <v>2</v>
       </c>
-      <c r="AM1" s="131"/>
-      <c r="AN1" s="132"/>
+      <c r="AM1" s="130"/>
+      <c r="AN1" s="140"/>
       <c r="AO1" s="12"/>
       <c r="AP1" s="12"/>
       <c r="AQ1" s="12"/>
@@ -2369,74 +2378,74 @@
     </row>
     <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12"/>
-      <c r="B2" s="139">
+      <c r="B2" s="134">
         <f>N2-3</f>
         <v>46276</v>
       </c>
-      <c r="C2" s="140"/>
-      <c r="D2" s="140"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
       <c r="E2" s="11"/>
-      <c r="F2" s="140">
+      <c r="F2" s="135">
         <f>N2-2</f>
         <v>46277</v>
       </c>
-      <c r="G2" s="140"/>
-      <c r="H2" s="140"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="140">
+      <c r="J2" s="135">
         <f>N2-1</f>
         <v>46278</v>
       </c>
-      <c r="K2" s="140"/>
-      <c r="L2" s="143"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="138"/>
       <c r="M2" s="12"/>
-      <c r="N2" s="142">
+      <c r="N2" s="137">
         <v>46279</v>
       </c>
-      <c r="O2" s="133"/>
-      <c r="P2" s="133"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
       <c r="Q2" s="53"/>
-      <c r="R2" s="133">
+      <c r="R2" s="129">
         <f>N2+1</f>
         <v>46280</v>
       </c>
-      <c r="S2" s="133"/>
-      <c r="T2" s="133"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="129"/>
       <c r="U2" s="53"/>
-      <c r="V2" s="133">
+      <c r="V2" s="129">
         <f>N2+2</f>
         <v>46281</v>
       </c>
-      <c r="W2" s="133"/>
-      <c r="X2" s="133"/>
+      <c r="W2" s="129"/>
+      <c r="X2" s="129"/>
       <c r="Y2" s="53"/>
-      <c r="Z2" s="133">
+      <c r="Z2" s="129">
         <f>N2+3</f>
         <v>46282</v>
       </c>
-      <c r="AA2" s="133"/>
-      <c r="AB2" s="133"/>
+      <c r="AA2" s="129"/>
+      <c r="AB2" s="129"/>
       <c r="AC2" s="53"/>
-      <c r="AD2" s="133">
+      <c r="AD2" s="129">
         <f>N2+4</f>
         <v>46283</v>
       </c>
-      <c r="AE2" s="133"/>
-      <c r="AF2" s="133"/>
+      <c r="AE2" s="129"/>
+      <c r="AF2" s="129"/>
       <c r="AG2" s="53"/>
-      <c r="AH2" s="133">
+      <c r="AH2" s="129">
         <f>N2+5</f>
         <v>46284</v>
       </c>
-      <c r="AI2" s="133"/>
-      <c r="AJ2" s="133"/>
+      <c r="AI2" s="129"/>
+      <c r="AJ2" s="129"/>
       <c r="AK2" s="53"/>
-      <c r="AL2" s="133">
+      <c r="AL2" s="129">
         <f>N2+6</f>
         <v>46285</v>
       </c>
-      <c r="AM2" s="133"/>
-      <c r="AN2" s="134"/>
+      <c r="AM2" s="129"/>
+      <c r="AN2" s="141"/>
       <c r="AO2" s="12"/>
       <c r="AP2" s="12"/>
       <c r="AQ2" s="12"/>
@@ -2490,47 +2499,47 @@
     </row>
     <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="12"/>
-      <c r="B4" s="135"/>
-      <c r="C4" s="135"/>
-      <c r="D4" s="135"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="135"/>
-      <c r="I4" s="135"/>
-      <c r="J4" s="135"/>
-      <c r="K4" s="135"/>
-      <c r="L4" s="135"/>
+      <c r="B4" s="139"/>
+      <c r="C4" s="139"/>
+      <c r="D4" s="139"/>
+      <c r="E4" s="139"/>
+      <c r="F4" s="139"/>
+      <c r="G4" s="139"/>
+      <c r="H4" s="139"/>
+      <c r="I4" s="139"/>
+      <c r="J4" s="139"/>
+      <c r="K4" s="139"/>
+      <c r="L4" s="139"/>
       <c r="M4" s="14"/>
-      <c r="N4" s="116" t="s">
+      <c r="N4" s="105" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="116"/>
-      <c r="P4" s="116"/>
-      <c r="Q4" s="116"/>
-      <c r="R4" s="116"/>
-      <c r="S4" s="116"/>
-      <c r="T4" s="116"/>
-      <c r="U4" s="116"/>
-      <c r="V4" s="116"/>
-      <c r="W4" s="116"/>
-      <c r="X4" s="116"/>
-      <c r="Y4" s="116"/>
-      <c r="Z4" s="116"/>
-      <c r="AA4" s="116"/>
-      <c r="AB4" s="116"/>
+      <c r="O4" s="105"/>
+      <c r="P4" s="105"/>
+      <c r="Q4" s="105"/>
+      <c r="R4" s="105"/>
+      <c r="S4" s="105"/>
+      <c r="T4" s="105"/>
+      <c r="U4" s="105"/>
+      <c r="V4" s="105"/>
+      <c r="W4" s="105"/>
+      <c r="X4" s="105"/>
+      <c r="Y4" s="105"/>
+      <c r="Z4" s="105"/>
+      <c r="AA4" s="105"/>
+      <c r="AB4" s="105"/>
       <c r="AC4" s="33"/>
-      <c r="AD4" s="135"/>
-      <c r="AE4" s="135"/>
-      <c r="AF4" s="135"/>
-      <c r="AG4" s="135"/>
-      <c r="AH4" s="135"/>
-      <c r="AI4" s="135"/>
-      <c r="AJ4" s="135"/>
-      <c r="AK4" s="135"/>
-      <c r="AL4" s="135"/>
-      <c r="AM4" s="135"/>
-      <c r="AN4" s="135"/>
+      <c r="AD4" s="139"/>
+      <c r="AE4" s="139"/>
+      <c r="AF4" s="139"/>
+      <c r="AG4" s="139"/>
+      <c r="AH4" s="139"/>
+      <c r="AI4" s="139"/>
+      <c r="AJ4" s="139"/>
+      <c r="AK4" s="139"/>
+      <c r="AL4" s="139"/>
+      <c r="AM4" s="139"/>
+      <c r="AN4" s="139"/>
       <c r="AO4" s="12"/>
       <c r="AP4" s="12"/>
       <c r="AQ4" s="12"/>
@@ -2538,95 +2547,99 @@
     </row>
     <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="12"/>
-      <c r="B5" s="135"/>
-      <c r="C5" s="135"/>
-      <c r="D5" s="135"/>
-      <c r="E5" s="135"/>
-      <c r="F5" s="135"/>
-      <c r="G5" s="135"/>
-      <c r="H5" s="135"/>
-      <c r="I5" s="135"/>
-      <c r="J5" s="135"/>
-      <c r="K5" s="135"/>
-      <c r="L5" s="135"/>
+      <c r="B5" s="139"/>
+      <c r="C5" s="139"/>
+      <c r="D5" s="139"/>
+      <c r="E5" s="139"/>
+      <c r="F5" s="139"/>
+      <c r="G5" s="139"/>
+      <c r="H5" s="139"/>
+      <c r="I5" s="139"/>
+      <c r="J5" s="139"/>
+      <c r="K5" s="139"/>
+      <c r="L5" s="139"/>
       <c r="M5" s="14"/>
-      <c r="N5" s="116"/>
-      <c r="O5" s="116"/>
-      <c r="P5" s="116"/>
-      <c r="Q5" s="116"/>
-      <c r="R5" s="116"/>
-      <c r="S5" s="116"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="116"/>
-      <c r="V5" s="116"/>
-      <c r="W5" s="116"/>
-      <c r="X5" s="116"/>
-      <c r="Y5" s="116"/>
-      <c r="Z5" s="116"/>
-      <c r="AA5" s="116"/>
-      <c r="AB5" s="116"/>
+      <c r="N5" s="105"/>
+      <c r="O5" s="105"/>
+      <c r="P5" s="105"/>
+      <c r="Q5" s="105"/>
+      <c r="R5" s="105"/>
+      <c r="S5" s="105"/>
+      <c r="T5" s="105"/>
+      <c r="U5" s="105"/>
+      <c r="V5" s="105"/>
+      <c r="W5" s="105"/>
+      <c r="X5" s="105"/>
+      <c r="Y5" s="105"/>
+      <c r="Z5" s="105"/>
+      <c r="AA5" s="105"/>
+      <c r="AB5" s="105"/>
       <c r="AC5" s="33"/>
-      <c r="AD5" s="135"/>
-      <c r="AE5" s="135"/>
-      <c r="AF5" s="135"/>
-      <c r="AG5" s="135"/>
-      <c r="AH5" s="135"/>
-      <c r="AI5" s="135"/>
-      <c r="AJ5" s="135"/>
-      <c r="AK5" s="135"/>
-      <c r="AL5" s="135"/>
-      <c r="AM5" s="135"/>
-      <c r="AN5" s="135"/>
+      <c r="AD5" s="139"/>
+      <c r="AE5" s="139"/>
+      <c r="AF5" s="139"/>
+      <c r="AG5" s="139"/>
+      <c r="AH5" s="139"/>
+      <c r="AI5" s="139"/>
+      <c r="AJ5" s="139"/>
+      <c r="AK5" s="139"/>
+      <c r="AL5" s="139"/>
+      <c r="AM5" s="139"/>
+      <c r="AN5" s="139"/>
       <c r="AO5" s="12"/>
       <c r="AP5" s="12"/>
       <c r="AQ5" s="12"/>
       <c r="AR5" s="13"/>
     </row>
     <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="66"/>
-      <c r="C6" s="67"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="64"/>
       <c r="D6" s="57"/>
       <c r="E6" s="39"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
       <c r="H6" s="57"/>
       <c r="I6" s="36"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
       <c r="L6" s="57"/>
       <c r="M6" s="3"/>
-      <c r="N6" s="68"/>
-      <c r="O6" s="69"/>
+      <c r="N6" s="87"/>
+      <c r="O6" s="88"/>
       <c r="P6" s="34"/>
       <c r="Q6" s="39"/>
-      <c r="R6" s="68"/>
-      <c r="S6" s="69"/>
+      <c r="R6" s="87"/>
+      <c r="S6" s="88"/>
       <c r="T6" s="34"/>
       <c r="U6" s="36"/>
-      <c r="V6" s="68"/>
-      <c r="W6" s="69"/>
+      <c r="V6" s="87"/>
+      <c r="W6" s="88"/>
       <c r="X6" s="34"/>
       <c r="Y6" s="23"/>
-      <c r="Z6" s="68"/>
-      <c r="AA6" s="69"/>
+      <c r="Z6" s="87"/>
+      <c r="AA6" s="88"/>
       <c r="AB6" s="34"/>
       <c r="AC6" s="36"/>
-      <c r="AD6" s="68"/>
-      <c r="AE6" s="69"/>
-      <c r="AF6" s="34"/>
+      <c r="AD6" s="116" t="s">
+        <v>77</v>
+      </c>
+      <c r="AE6" s="117"/>
+      <c r="AF6" s="59" t="s">
+        <v>68</v>
+      </c>
       <c r="AG6" s="39"/>
-      <c r="AH6" s="68" t="s">
+      <c r="AH6" s="114" t="s">
         <v>77</v>
       </c>
-      <c r="AI6" s="69"/>
-      <c r="AJ6" s="34" t="s">
+      <c r="AI6" s="115"/>
+      <c r="AJ6" s="60" t="s">
         <v>68</v>
       </c>
       <c r="AK6" s="36"/>
-      <c r="AL6" s="68" t="s">
+      <c r="AL6" s="87" t="s">
         <v>77</v>
       </c>
-      <c r="AM6" s="69"/>
+      <c r="AM6" s="88"/>
       <c r="AN6" s="34" t="s">
         <v>68</v>
       </c>
@@ -2640,98 +2653,102 @@
       <c r="AR6" s="30"/>
     </row>
     <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="96"/>
-      <c r="C7" s="97"/>
+      <c r="B7" s="68"/>
+      <c r="C7" s="69"/>
       <c r="D7" s="61"/>
       <c r="E7" s="38"/>
-      <c r="F7" s="96"/>
-      <c r="G7" s="97"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="69"/>
       <c r="H7" s="61"/>
       <c r="I7" s="36"/>
-      <c r="J7" s="96"/>
-      <c r="K7" s="97"/>
+      <c r="J7" s="68"/>
+      <c r="K7" s="69"/>
       <c r="L7" s="61"/>
       <c r="M7" s="3"/>
-      <c r="N7" s="85"/>
-      <c r="O7" s="86"/>
+      <c r="N7" s="92"/>
+      <c r="O7" s="93"/>
       <c r="P7" s="18"/>
       <c r="Q7" s="36"/>
-      <c r="R7" s="85"/>
-      <c r="S7" s="86"/>
+      <c r="R7" s="92"/>
+      <c r="S7" s="93"/>
       <c r="T7" s="18"/>
       <c r="U7" s="36"/>
-      <c r="V7" s="85"/>
-      <c r="W7" s="86"/>
+      <c r="V7" s="92"/>
+      <c r="W7" s="93"/>
       <c r="X7" s="18"/>
       <c r="Y7" s="36"/>
-      <c r="Z7" s="85"/>
-      <c r="AA7" s="86"/>
+      <c r="Z7" s="92"/>
+      <c r="AA7" s="93"/>
       <c r="AB7" s="18"/>
       <c r="AC7" s="36"/>
-      <c r="AD7" s="85"/>
-      <c r="AE7" s="86"/>
+      <c r="AD7" s="92"/>
+      <c r="AE7" s="93"/>
       <c r="AF7" s="18"/>
       <c r="AG7" s="38"/>
-      <c r="AH7" s="85"/>
-      <c r="AI7" s="86"/>
-      <c r="AJ7" s="18"/>
+      <c r="AH7" s="111" t="s">
+        <v>92</v>
+      </c>
+      <c r="AI7" s="112"/>
+      <c r="AJ7" s="62"/>
       <c r="AK7" s="36"/>
-      <c r="AL7" s="85"/>
-      <c r="AM7" s="86"/>
+      <c r="AL7" s="92"/>
+      <c r="AM7" s="93"/>
       <c r="AN7" s="18"/>
       <c r="AP7" s="46" t="s">
         <v>9</v>
       </c>
       <c r="AQ7" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR7" s="30"/>
     </row>
     <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="93"/>
-      <c r="C8" s="94"/>
-      <c r="D8" s="95"/>
+      <c r="B8" s="81"/>
+      <c r="C8" s="82"/>
+      <c r="D8" s="83"/>
       <c r="E8" s="35"/>
-      <c r="F8" s="93"/>
-      <c r="G8" s="94"/>
-      <c r="H8" s="95"/>
+      <c r="F8" s="81"/>
+      <c r="G8" s="82"/>
+      <c r="H8" s="83"/>
       <c r="I8" s="37"/>
-      <c r="J8" s="93"/>
-      <c r="K8" s="94"/>
-      <c r="L8" s="95"/>
+      <c r="J8" s="81"/>
+      <c r="K8" s="82"/>
+      <c r="L8" s="83"/>
       <c r="M8" s="3"/>
-      <c r="N8" s="93"/>
-      <c r="O8" s="94"/>
-      <c r="P8" s="95"/>
+      <c r="N8" s="81"/>
+      <c r="O8" s="82"/>
+      <c r="P8" s="83"/>
       <c r="Q8" s="35"/>
-      <c r="R8" s="93"/>
-      <c r="S8" s="94"/>
-      <c r="T8" s="95"/>
+      <c r="R8" s="81"/>
+      <c r="S8" s="82"/>
+      <c r="T8" s="83"/>
       <c r="U8" s="37"/>
-      <c r="V8" s="93"/>
-      <c r="W8" s="94"/>
-      <c r="X8" s="95"/>
+      <c r="V8" s="81"/>
+      <c r="W8" s="82"/>
+      <c r="X8" s="83"/>
       <c r="Y8" s="35"/>
-      <c r="Z8" s="93"/>
-      <c r="AA8" s="94"/>
-      <c r="AB8" s="95"/>
+      <c r="Z8" s="81"/>
+      <c r="AA8" s="82"/>
+      <c r="AB8" s="83"/>
       <c r="AC8" s="35"/>
-      <c r="AD8" s="93"/>
-      <c r="AE8" s="94"/>
-      <c r="AF8" s="95"/>
+      <c r="AD8" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE8" s="66"/>
+      <c r="AF8" s="67"/>
       <c r="AG8" s="35"/>
-      <c r="AH8" s="122" t="s">
+      <c r="AH8" s="145" t="s">
         <v>85</v>
       </c>
-      <c r="AI8" s="123"/>
-      <c r="AJ8" s="124"/>
+      <c r="AI8" s="146"/>
+      <c r="AJ8" s="147"/>
       <c r="AK8" s="37"/>
-      <c r="AL8" s="93" t="s">
+      <c r="AL8" s="81" t="s">
         <v>12</v>
       </c>
-      <c r="AM8" s="94"/>
-      <c r="AN8" s="95"/>
+      <c r="AM8" s="82"/>
+      <c r="AN8" s="83"/>
       <c r="AP8" s="46" t="s">
         <v>16</v>
       </c>
@@ -2742,47 +2759,47 @@
       <c r="AR8" s="30"/>
     </row>
     <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="82"/>
-      <c r="C9" s="83"/>
-      <c r="D9" s="84"/>
+      <c r="B9" s="65"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="67"/>
       <c r="E9" s="43"/>
-      <c r="F9" s="82"/>
-      <c r="G9" s="83"/>
-      <c r="H9" s="84"/>
+      <c r="F9" s="65"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="67"/>
       <c r="I9" s="43"/>
-      <c r="J9" s="82"/>
-      <c r="K9" s="83"/>
-      <c r="L9" s="84"/>
+      <c r="J9" s="65"/>
+      <c r="K9" s="66"/>
+      <c r="L9" s="67"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="82"/>
-      <c r="O9" s="83"/>
-      <c r="P9" s="84"/>
+      <c r="N9" s="65"/>
+      <c r="O9" s="66"/>
+      <c r="P9" s="67"/>
       <c r="Q9" s="43"/>
-      <c r="R9" s="82"/>
-      <c r="S9" s="83"/>
-      <c r="T9" s="84"/>
+      <c r="R9" s="65"/>
+      <c r="S9" s="66"/>
+      <c r="T9" s="67"/>
       <c r="U9" s="44"/>
-      <c r="V9" s="82"/>
-      <c r="W9" s="83"/>
-      <c r="X9" s="84"/>
+      <c r="V9" s="65"/>
+      <c r="W9" s="66"/>
+      <c r="X9" s="67"/>
       <c r="Y9" s="43"/>
-      <c r="Z9" s="82"/>
-      <c r="AA9" s="83"/>
-      <c r="AB9" s="84"/>
+      <c r="Z9" s="65"/>
+      <c r="AA9" s="66"/>
+      <c r="AB9" s="67"/>
       <c r="AC9" s="43"/>
-      <c r="AD9" s="82"/>
-      <c r="AE9" s="83"/>
-      <c r="AF9" s="84"/>
+      <c r="AD9" s="65"/>
+      <c r="AE9" s="66"/>
+      <c r="AF9" s="67"/>
       <c r="AG9" s="43"/>
-      <c r="AH9" s="82"/>
-      <c r="AI9" s="83"/>
-      <c r="AJ9" s="84"/>
+      <c r="AH9" s="163"/>
+      <c r="AI9" s="164"/>
+      <c r="AJ9" s="165"/>
       <c r="AK9" s="43"/>
-      <c r="AL9" s="117" t="s">
+      <c r="AL9" s="108" t="s">
         <v>15</v>
       </c>
-      <c r="AM9" s="118"/>
-      <c r="AN9" s="119"/>
+      <c r="AM9" s="109"/>
+      <c r="AN9" s="110"/>
       <c r="AP9" s="46" t="s">
         <v>11</v>
       </c>
@@ -2793,47 +2810,47 @@
       <c r="AR9" s="30"/>
     </row>
     <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="113"/>
-      <c r="C10" s="114"/>
-      <c r="D10" s="115"/>
+      <c r="B10" s="84"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="86"/>
       <c r="E10" s="44"/>
-      <c r="F10" s="113"/>
-      <c r="G10" s="114"/>
-      <c r="H10" s="115"/>
+      <c r="F10" s="84"/>
+      <c r="G10" s="85"/>
+      <c r="H10" s="86"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="113"/>
-      <c r="K10" s="114"/>
-      <c r="L10" s="115"/>
+      <c r="J10" s="84"/>
+      <c r="K10" s="85"/>
+      <c r="L10" s="86"/>
       <c r="M10" s="5"/>
-      <c r="N10" s="113"/>
-      <c r="O10" s="114"/>
-      <c r="P10" s="115"/>
+      <c r="N10" s="84"/>
+      <c r="O10" s="85"/>
+      <c r="P10" s="86"/>
       <c r="Q10" s="44"/>
-      <c r="R10" s="113"/>
-      <c r="S10" s="114"/>
-      <c r="T10" s="115"/>
+      <c r="R10" s="84"/>
+      <c r="S10" s="85"/>
+      <c r="T10" s="86"/>
       <c r="U10" s="44"/>
-      <c r="V10" s="113"/>
-      <c r="W10" s="114"/>
-      <c r="X10" s="115"/>
+      <c r="V10" s="84"/>
+      <c r="W10" s="85"/>
+      <c r="X10" s="86"/>
       <c r="Y10" s="44"/>
-      <c r="Z10" s="113"/>
-      <c r="AA10" s="114"/>
-      <c r="AB10" s="115"/>
+      <c r="Z10" s="84"/>
+      <c r="AA10" s="85"/>
+      <c r="AB10" s="86"/>
       <c r="AC10" s="44"/>
-      <c r="AD10" s="113"/>
-      <c r="AE10" s="114"/>
-      <c r="AF10" s="115"/>
+      <c r="AD10" s="84"/>
+      <c r="AE10" s="85"/>
+      <c r="AF10" s="86"/>
       <c r="AG10" s="44"/>
-      <c r="AH10" s="113"/>
-      <c r="AI10" s="114"/>
-      <c r="AJ10" s="115"/>
+      <c r="AH10" s="148"/>
+      <c r="AI10" s="149"/>
+      <c r="AJ10" s="150"/>
       <c r="AK10" s="44"/>
-      <c r="AL10" s="110" t="s">
+      <c r="AL10" s="151" t="s">
         <v>96</v>
       </c>
-      <c r="AM10" s="111"/>
-      <c r="AN10" s="112"/>
+      <c r="AM10" s="152"/>
+      <c r="AN10" s="153"/>
       <c r="AP10" s="46" t="s">
         <v>8</v>
       </c>
@@ -2895,52 +2912,52 @@
       </c>
     </row>
     <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="66"/>
-      <c r="C12" s="67"/>
+      <c r="B12" s="63"/>
+      <c r="C12" s="64"/>
       <c r="D12" s="57"/>
       <c r="E12" s="39"/>
-      <c r="F12" s="91" t="s">
+      <c r="F12" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="92"/>
+      <c r="G12" s="117"/>
       <c r="H12" s="59" t="s">
         <v>69</v>
       </c>
       <c r="I12" s="36"/>
-      <c r="J12" s="66"/>
-      <c r="K12" s="67"/>
+      <c r="J12" s="63"/>
+      <c r="K12" s="64"/>
       <c r="L12" s="57"/>
       <c r="M12" s="5"/>
-      <c r="N12" s="68"/>
-      <c r="O12" s="69"/>
+      <c r="N12" s="87"/>
+      <c r="O12" s="88"/>
       <c r="P12" s="34"/>
       <c r="Q12" s="23"/>
-      <c r="R12" s="68"/>
-      <c r="S12" s="69"/>
+      <c r="R12" s="87"/>
+      <c r="S12" s="88"/>
       <c r="T12" s="34"/>
       <c r="U12" s="36"/>
-      <c r="V12" s="68"/>
-      <c r="W12" s="69"/>
+      <c r="V12" s="87"/>
+      <c r="W12" s="88"/>
       <c r="X12" s="34"/>
       <c r="Y12" s="23"/>
-      <c r="Z12" s="68"/>
-      <c r="AA12" s="69"/>
+      <c r="Z12" s="87"/>
+      <c r="AA12" s="88"/>
       <c r="AB12" s="34"/>
       <c r="AC12" s="36"/>
-      <c r="AD12" s="68"/>
-      <c r="AE12" s="69"/>
+      <c r="AD12" s="87"/>
+      <c r="AE12" s="88"/>
       <c r="AF12" s="34"/>
       <c r="AG12" s="39"/>
-      <c r="AH12" s="68" t="s">
+      <c r="AH12" s="87" t="s">
         <v>41</v>
       </c>
-      <c r="AI12" s="69"/>
+      <c r="AI12" s="88"/>
       <c r="AJ12" s="34" t="s">
         <v>57</v>
       </c>
       <c r="AK12" s="36"/>
-      <c r="AL12" s="68"/>
-      <c r="AM12" s="69"/>
+      <c r="AL12" s="87"/>
+      <c r="AM12" s="88"/>
       <c r="AN12" s="34"/>
       <c r="AP12" s="46" t="s">
         <v>19</v>
@@ -2952,48 +2969,48 @@
       <c r="AR12" s="30"/>
     </row>
     <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="96"/>
-      <c r="C13" s="97"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="69"/>
       <c r="D13" s="61"/>
       <c r="E13" s="38"/>
-      <c r="F13" s="96" t="s">
+      <c r="F13" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="97"/>
+      <c r="G13" s="69"/>
       <c r="H13" s="61" t="s">
         <v>57</v>
       </c>
       <c r="I13" s="36"/>
-      <c r="J13" s="96"/>
-      <c r="K13" s="97"/>
+      <c r="J13" s="68"/>
+      <c r="K13" s="69"/>
       <c r="L13" s="61"/>
       <c r="M13" s="5"/>
-      <c r="N13" s="85"/>
-      <c r="O13" s="86"/>
+      <c r="N13" s="92"/>
+      <c r="O13" s="93"/>
       <c r="P13" s="18"/>
       <c r="Q13" s="36"/>
-      <c r="R13" s="85"/>
-      <c r="S13" s="86"/>
+      <c r="R13" s="92"/>
+      <c r="S13" s="93"/>
       <c r="T13" s="18"/>
       <c r="U13" s="36"/>
-      <c r="V13" s="85"/>
-      <c r="W13" s="86"/>
+      <c r="V13" s="92"/>
+      <c r="W13" s="93"/>
       <c r="X13" s="18"/>
       <c r="Y13" s="36"/>
-      <c r="Z13" s="85"/>
-      <c r="AA13" s="86"/>
+      <c r="Z13" s="92"/>
+      <c r="AA13" s="93"/>
       <c r="AB13" s="18"/>
       <c r="AC13" s="36"/>
-      <c r="AD13" s="85"/>
-      <c r="AE13" s="86"/>
+      <c r="AD13" s="92"/>
+      <c r="AE13" s="93"/>
       <c r="AF13" s="18"/>
       <c r="AG13" s="38"/>
-      <c r="AH13" s="85"/>
-      <c r="AI13" s="86"/>
+      <c r="AH13" s="92"/>
+      <c r="AI13" s="93"/>
       <c r="AJ13" s="18"/>
       <c r="AK13" s="36"/>
-      <c r="AL13" s="85"/>
-      <c r="AM13" s="86"/>
+      <c r="AL13" s="92"/>
+      <c r="AM13" s="93"/>
       <c r="AN13" s="18"/>
       <c r="AP13" s="46" t="s">
         <v>22</v>
@@ -3005,49 +3022,49 @@
       <c r="AR13" s="30"/>
     </row>
     <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="93"/>
-      <c r="C14" s="94"/>
-      <c r="D14" s="95"/>
+      <c r="B14" s="81"/>
+      <c r="C14" s="82"/>
+      <c r="D14" s="83"/>
       <c r="E14" s="37"/>
-      <c r="F14" s="93" t="s">
+      <c r="F14" s="81" t="s">
         <v>37</v>
       </c>
-      <c r="G14" s="94"/>
-      <c r="H14" s="95"/>
+      <c r="G14" s="82"/>
+      <c r="H14" s="83"/>
       <c r="I14" s="35"/>
-      <c r="J14" s="93"/>
-      <c r="K14" s="94"/>
-      <c r="L14" s="95"/>
+      <c r="J14" s="81"/>
+      <c r="K14" s="82"/>
+      <c r="L14" s="83"/>
       <c r="M14" s="3"/>
-      <c r="N14" s="93"/>
-      <c r="O14" s="94"/>
-      <c r="P14" s="95"/>
+      <c r="N14" s="81"/>
+      <c r="O14" s="82"/>
+      <c r="P14" s="83"/>
       <c r="Q14" s="35"/>
-      <c r="R14" s="93"/>
-      <c r="S14" s="94"/>
-      <c r="T14" s="95"/>
+      <c r="R14" s="81"/>
+      <c r="S14" s="82"/>
+      <c r="T14" s="83"/>
       <c r="U14" s="37"/>
-      <c r="V14" s="93"/>
-      <c r="W14" s="94"/>
-      <c r="X14" s="95"/>
+      <c r="V14" s="81"/>
+      <c r="W14" s="82"/>
+      <c r="X14" s="83"/>
       <c r="Y14" s="35"/>
-      <c r="Z14" s="93"/>
-      <c r="AA14" s="94"/>
-      <c r="AB14" s="95"/>
+      <c r="Z14" s="81"/>
+      <c r="AA14" s="82"/>
+      <c r="AB14" s="83"/>
       <c r="AC14" s="37"/>
-      <c r="AD14" s="93"/>
-      <c r="AE14" s="94"/>
-      <c r="AF14" s="95"/>
+      <c r="AD14" s="81"/>
+      <c r="AE14" s="82"/>
+      <c r="AF14" s="83"/>
       <c r="AG14" s="37"/>
-      <c r="AH14" s="93" t="s">
+      <c r="AH14" s="81" t="s">
         <v>37</v>
       </c>
-      <c r="AI14" s="94"/>
-      <c r="AJ14" s="95"/>
+      <c r="AI14" s="82"/>
+      <c r="AJ14" s="83"/>
       <c r="AK14" s="35"/>
-      <c r="AL14" s="93"/>
-      <c r="AM14" s="94"/>
-      <c r="AN14" s="95"/>
+      <c r="AL14" s="81"/>
+      <c r="AM14" s="82"/>
+      <c r="AN14" s="83"/>
       <c r="AP14" s="58" t="s">
         <v>23</v>
       </c>
@@ -3060,49 +3077,49 @@
       </c>
     </row>
     <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="82"/>
-      <c r="C15" s="83"/>
-      <c r="D15" s="84"/>
+      <c r="B15" s="65"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="67"/>
       <c r="E15" s="44"/>
-      <c r="F15" s="117" t="s">
+      <c r="F15" s="108" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="118"/>
-      <c r="H15" s="119"/>
+      <c r="G15" s="109"/>
+      <c r="H15" s="110"/>
       <c r="I15" s="43"/>
-      <c r="J15" s="82"/>
-      <c r="K15" s="83"/>
-      <c r="L15" s="84"/>
+      <c r="J15" s="65"/>
+      <c r="K15" s="66"/>
+      <c r="L15" s="67"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="82"/>
-      <c r="O15" s="83"/>
-      <c r="P15" s="84"/>
+      <c r="N15" s="65"/>
+      <c r="O15" s="66"/>
+      <c r="P15" s="67"/>
       <c r="Q15" s="43"/>
-      <c r="R15" s="82"/>
-      <c r="S15" s="83"/>
-      <c r="T15" s="84"/>
+      <c r="R15" s="65"/>
+      <c r="S15" s="66"/>
+      <c r="T15" s="67"/>
       <c r="U15" s="44"/>
-      <c r="V15" s="82"/>
-      <c r="W15" s="83"/>
-      <c r="X15" s="84"/>
+      <c r="V15" s="65"/>
+      <c r="W15" s="66"/>
+      <c r="X15" s="67"/>
       <c r="Y15" s="43"/>
-      <c r="Z15" s="82"/>
-      <c r="AA15" s="83"/>
-      <c r="AB15" s="84"/>
+      <c r="Z15" s="65"/>
+      <c r="AA15" s="66"/>
+      <c r="AB15" s="67"/>
       <c r="AC15" s="43"/>
-      <c r="AD15" s="82"/>
-      <c r="AE15" s="83"/>
-      <c r="AF15" s="84"/>
+      <c r="AD15" s="65"/>
+      <c r="AE15" s="66"/>
+      <c r="AF15" s="67"/>
       <c r="AG15" s="44"/>
-      <c r="AH15" s="82" t="s">
+      <c r="AH15" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="AI15" s="83"/>
-      <c r="AJ15" s="84"/>
+      <c r="AI15" s="66"/>
+      <c r="AJ15" s="67"/>
       <c r="AK15" s="43"/>
-      <c r="AL15" s="82"/>
-      <c r="AM15" s="83"/>
-      <c r="AN15" s="84"/>
+      <c r="AL15" s="65"/>
+      <c r="AM15" s="66"/>
+      <c r="AN15" s="67"/>
       <c r="AP15" s="46" t="s">
         <v>18</v>
       </c>
@@ -3113,47 +3130,47 @@
       <c r="AR15" s="30"/>
     </row>
     <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="113"/>
-      <c r="C16" s="114"/>
-      <c r="D16" s="115"/>
+      <c r="B16" s="84"/>
+      <c r="C16" s="85"/>
+      <c r="D16" s="86"/>
       <c r="E16" s="44"/>
-      <c r="F16" s="110" t="s">
+      <c r="F16" s="151" t="s">
         <v>88</v>
       </c>
-      <c r="G16" s="111"/>
-      <c r="H16" s="112"/>
+      <c r="G16" s="152"/>
+      <c r="H16" s="153"/>
       <c r="I16" s="44"/>
-      <c r="J16" s="113"/>
-      <c r="K16" s="114"/>
-      <c r="L16" s="115"/>
+      <c r="J16" s="84"/>
+      <c r="K16" s="85"/>
+      <c r="L16" s="86"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="113"/>
-      <c r="O16" s="114"/>
-      <c r="P16" s="115"/>
+      <c r="N16" s="84"/>
+      <c r="O16" s="85"/>
+      <c r="P16" s="86"/>
       <c r="Q16" s="44"/>
-      <c r="R16" s="113"/>
-      <c r="S16" s="114"/>
-      <c r="T16" s="115"/>
+      <c r="R16" s="84"/>
+      <c r="S16" s="85"/>
+      <c r="T16" s="86"/>
       <c r="U16" s="44"/>
-      <c r="V16" s="113"/>
-      <c r="W16" s="114"/>
-      <c r="X16" s="115"/>
+      <c r="V16" s="84"/>
+      <c r="W16" s="85"/>
+      <c r="X16" s="86"/>
       <c r="Y16" s="44"/>
-      <c r="Z16" s="113"/>
-      <c r="AA16" s="114"/>
-      <c r="AB16" s="115"/>
+      <c r="Z16" s="84"/>
+      <c r="AA16" s="85"/>
+      <c r="AB16" s="86"/>
       <c r="AC16" s="44"/>
-      <c r="AD16" s="113"/>
-      <c r="AE16" s="114"/>
-      <c r="AF16" s="115"/>
+      <c r="AD16" s="84"/>
+      <c r="AE16" s="85"/>
+      <c r="AF16" s="86"/>
       <c r="AG16" s="44"/>
-      <c r="AH16" s="113"/>
-      <c r="AI16" s="114"/>
-      <c r="AJ16" s="115"/>
+      <c r="AH16" s="84"/>
+      <c r="AI16" s="85"/>
+      <c r="AJ16" s="86"/>
       <c r="AK16" s="44"/>
-      <c r="AL16" s="113"/>
-      <c r="AM16" s="114"/>
-      <c r="AN16" s="115"/>
+      <c r="AL16" s="84"/>
+      <c r="AM16" s="85"/>
+      <c r="AN16" s="86"/>
       <c r="AP16" s="46" t="s">
         <v>24</v>
       </c>
@@ -3225,23 +3242,23 @@
       <c r="K18" s="33"/>
       <c r="L18" s="33"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="116" t="s">
+      <c r="N18" s="105" t="s">
         <v>59</v>
       </c>
-      <c r="O18" s="116"/>
-      <c r="P18" s="116"/>
-      <c r="Q18" s="116"/>
-      <c r="R18" s="116"/>
-      <c r="S18" s="116"/>
-      <c r="T18" s="116"/>
-      <c r="U18" s="116"/>
-      <c r="V18" s="116"/>
-      <c r="W18" s="116"/>
-      <c r="X18" s="116"/>
-      <c r="Y18" s="116"/>
-      <c r="Z18" s="116"/>
-      <c r="AA18" s="116"/>
-      <c r="AB18" s="116"/>
+      <c r="O18" s="105"/>
+      <c r="P18" s="105"/>
+      <c r="Q18" s="105"/>
+      <c r="R18" s="105"/>
+      <c r="S18" s="105"/>
+      <c r="T18" s="105"/>
+      <c r="U18" s="105"/>
+      <c r="V18" s="105"/>
+      <c r="W18" s="105"/>
+      <c r="X18" s="105"/>
+      <c r="Y18" s="105"/>
+      <c r="Z18" s="105"/>
+      <c r="AA18" s="105"/>
+      <c r="AB18" s="105"/>
       <c r="AC18" s="33"/>
       <c r="AD18" s="33"/>
       <c r="AE18" s="33"/>
@@ -3276,21 +3293,21 @@
       <c r="K19" s="33"/>
       <c r="L19" s="33"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="116"/>
-      <c r="O19" s="116"/>
-      <c r="P19" s="116"/>
-      <c r="Q19" s="116"/>
-      <c r="R19" s="116"/>
-      <c r="S19" s="116"/>
-      <c r="T19" s="116"/>
-      <c r="U19" s="116"/>
-      <c r="V19" s="116"/>
-      <c r="W19" s="116"/>
-      <c r="X19" s="116"/>
-      <c r="Y19" s="116"/>
-      <c r="Z19" s="116"/>
-      <c r="AA19" s="116"/>
-      <c r="AB19" s="116"/>
+      <c r="N19" s="105"/>
+      <c r="O19" s="105"/>
+      <c r="P19" s="105"/>
+      <c r="Q19" s="105"/>
+      <c r="R19" s="105"/>
+      <c r="S19" s="105"/>
+      <c r="T19" s="105"/>
+      <c r="U19" s="105"/>
+      <c r="V19" s="105"/>
+      <c r="W19" s="105"/>
+      <c r="X19" s="105"/>
+      <c r="Y19" s="105"/>
+      <c r="Z19" s="105"/>
+      <c r="AA19" s="105"/>
+      <c r="AB19" s="105"/>
       <c r="AC19" s="33"/>
       <c r="AD19" s="33"/>
       <c r="AE19" s="33"/>
@@ -3313,60 +3330,60 @@
       <c r="AR19" s="30"/>
     </row>
     <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="66"/>
-      <c r="C20" s="67"/>
+      <c r="B20" s="63"/>
+      <c r="C20" s="64"/>
       <c r="D20" s="57"/>
       <c r="E20" s="39"/>
-      <c r="F20" s="66"/>
-      <c r="G20" s="67"/>
+      <c r="F20" s="63"/>
+      <c r="G20" s="64"/>
       <c r="H20" s="57"/>
       <c r="I20" s="36"/>
-      <c r="J20" s="66"/>
-      <c r="K20" s="67"/>
+      <c r="J20" s="63"/>
+      <c r="K20" s="64"/>
       <c r="L20" s="57"/>
       <c r="M20" s="4"/>
-      <c r="N20" s="105" t="s">
+      <c r="N20" s="114" t="s">
         <v>87</v>
       </c>
-      <c r="O20" s="106"/>
+      <c r="O20" s="115"/>
       <c r="P20" s="60" t="s">
         <v>49</v>
       </c>
       <c r="Q20" s="39"/>
-      <c r="R20" s="105" t="s">
+      <c r="R20" s="114" t="s">
         <v>87</v>
       </c>
-      <c r="S20" s="106"/>
+      <c r="S20" s="115"/>
       <c r="T20" s="60" t="s">
         <v>49</v>
       </c>
       <c r="U20" s="36"/>
-      <c r="V20" s="68" t="s">
+      <c r="V20" s="87" t="s">
         <v>56</v>
       </c>
-      <c r="W20" s="69"/>
+      <c r="W20" s="88"/>
       <c r="X20" s="34" t="s">
         <v>55</v>
       </c>
       <c r="Y20" s="23"/>
-      <c r="Z20" s="68"/>
-      <c r="AA20" s="69"/>
+      <c r="Z20" s="87"/>
+      <c r="AA20" s="88"/>
       <c r="AB20" s="34"/>
       <c r="AC20" s="36"/>
-      <c r="AD20" s="68"/>
-      <c r="AE20" s="69"/>
+      <c r="AD20" s="87"/>
+      <c r="AE20" s="88"/>
       <c r="AF20" s="34"/>
       <c r="AG20" s="39"/>
-      <c r="AH20" s="68" t="s">
+      <c r="AH20" s="87" t="s">
         <v>56</v>
       </c>
-      <c r="AI20" s="69"/>
+      <c r="AI20" s="88"/>
       <c r="AJ20" s="34" t="s">
         <v>86</v>
       </c>
       <c r="AK20" s="36"/>
-      <c r="AL20" s="68"/>
-      <c r="AM20" s="69"/>
+      <c r="AL20" s="87"/>
+      <c r="AM20" s="88"/>
       <c r="AN20" s="34"/>
       <c r="AP20" s="46" t="s">
         <v>26</v>
@@ -3378,52 +3395,52 @@
       <c r="AR20" s="30"/>
     </row>
     <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="96"/>
-      <c r="C21" s="97"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="69"/>
       <c r="D21" s="61"/>
       <c r="E21" s="38"/>
-      <c r="F21" s="96"/>
-      <c r="G21" s="97"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="69"/>
       <c r="H21" s="61"/>
       <c r="I21" s="36"/>
-      <c r="J21" s="96"/>
-      <c r="K21" s="97"/>
+      <c r="J21" s="68"/>
+      <c r="K21" s="69"/>
       <c r="L21" s="61"/>
       <c r="M21" s="15"/>
-      <c r="N21" s="129" t="s">
+      <c r="N21" s="111" t="s">
         <v>92</v>
       </c>
-      <c r="O21" s="130"/>
+      <c r="O21" s="112"/>
       <c r="P21" s="62"/>
       <c r="Q21" s="36"/>
-      <c r="R21" s="129" t="s">
+      <c r="R21" s="111" t="s">
         <v>92</v>
       </c>
-      <c r="S21" s="130"/>
+      <c r="S21" s="112"/>
       <c r="T21" s="62"/>
       <c r="U21" s="36"/>
-      <c r="V21" s="85" t="s">
+      <c r="V21" s="92" t="s">
         <v>54</v>
       </c>
-      <c r="W21" s="86"/>
+      <c r="W21" s="93"/>
       <c r="X21" s="18" t="s">
         <v>50</v>
       </c>
       <c r="Y21" s="36"/>
-      <c r="Z21" s="85"/>
-      <c r="AA21" s="86"/>
+      <c r="Z21" s="92"/>
+      <c r="AA21" s="93"/>
       <c r="AB21" s="18"/>
       <c r="AC21" s="36"/>
-      <c r="AD21" s="85"/>
-      <c r="AE21" s="86"/>
+      <c r="AD21" s="92"/>
+      <c r="AE21" s="93"/>
       <c r="AF21" s="18"/>
       <c r="AG21" s="38"/>
-      <c r="AH21" s="85"/>
-      <c r="AI21" s="86"/>
+      <c r="AH21" s="92"/>
+      <c r="AI21" s="93"/>
       <c r="AJ21" s="18"/>
       <c r="AK21" s="36"/>
-      <c r="AL21" s="85"/>
-      <c r="AM21" s="86"/>
+      <c r="AL21" s="92"/>
+      <c r="AM21" s="93"/>
       <c r="AN21" s="18"/>
       <c r="AP21" s="46" t="s">
         <v>12</v>
@@ -3435,53 +3452,53 @@
       <c r="AR21" s="30"/>
     </row>
     <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="93"/>
-      <c r="C22" s="94"/>
-      <c r="D22" s="95"/>
+      <c r="B22" s="81"/>
+      <c r="C22" s="82"/>
+      <c r="D22" s="83"/>
       <c r="E22" s="35"/>
-      <c r="F22" s="93"/>
-      <c r="G22" s="94"/>
-      <c r="H22" s="95"/>
+      <c r="F22" s="81"/>
+      <c r="G22" s="82"/>
+      <c r="H22" s="83"/>
       <c r="I22" s="37"/>
-      <c r="J22" s="93"/>
-      <c r="K22" s="94"/>
-      <c r="L22" s="95"/>
+      <c r="J22" s="81"/>
+      <c r="K22" s="82"/>
+      <c r="L22" s="83"/>
       <c r="M22" s="4"/>
-      <c r="N22" s="76" t="s">
+      <c r="N22" s="145" t="s">
         <v>97</v>
       </c>
-      <c r="O22" s="77"/>
-      <c r="P22" s="78"/>
+      <c r="O22" s="146"/>
+      <c r="P22" s="147"/>
       <c r="Q22" s="35"/>
-      <c r="R22" s="76" t="s">
+      <c r="R22" s="145" t="s">
         <v>98</v>
       </c>
-      <c r="S22" s="77"/>
-      <c r="T22" s="78"/>
+      <c r="S22" s="146"/>
+      <c r="T22" s="147"/>
       <c r="U22" s="37"/>
-      <c r="V22" s="93" t="s">
+      <c r="V22" s="81" t="s">
         <v>12</v>
       </c>
-      <c r="W22" s="94"/>
-      <c r="X22" s="95"/>
+      <c r="W22" s="82"/>
+      <c r="X22" s="83"/>
       <c r="Y22" s="35"/>
-      <c r="Z22" s="93"/>
-      <c r="AA22" s="94"/>
-      <c r="AB22" s="95"/>
+      <c r="Z22" s="81"/>
+      <c r="AA22" s="82"/>
+      <c r="AB22" s="83"/>
       <c r="AC22" s="35"/>
-      <c r="AD22" s="93"/>
-      <c r="AE22" s="94"/>
-      <c r="AF22" s="95"/>
+      <c r="AD22" s="81"/>
+      <c r="AE22" s="82"/>
+      <c r="AF22" s="83"/>
       <c r="AG22" s="35"/>
-      <c r="AH22" s="122" t="s">
+      <c r="AH22" s="142" t="s">
         <v>9</v>
       </c>
-      <c r="AI22" s="123"/>
-      <c r="AJ22" s="124"/>
+      <c r="AI22" s="143"/>
+      <c r="AJ22" s="144"/>
       <c r="AK22" s="37"/>
-      <c r="AL22" s="93"/>
-      <c r="AM22" s="94"/>
-      <c r="AN22" s="95"/>
+      <c r="AL22" s="81"/>
+      <c r="AM22" s="82"/>
+      <c r="AN22" s="83"/>
       <c r="AP22" s="46" t="s">
         <v>15</v>
       </c>
@@ -3492,45 +3509,45 @@
       <c r="AR22" s="30"/>
     </row>
     <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="113"/>
-      <c r="C23" s="114"/>
-      <c r="D23" s="115"/>
+      <c r="B23" s="84"/>
+      <c r="C23" s="85"/>
+      <c r="D23" s="86"/>
       <c r="E23" s="44"/>
-      <c r="F23" s="113"/>
-      <c r="G23" s="114"/>
-      <c r="H23" s="115"/>
+      <c r="F23" s="84"/>
+      <c r="G23" s="85"/>
+      <c r="H23" s="86"/>
       <c r="I23" s="44"/>
-      <c r="J23" s="113"/>
-      <c r="K23" s="114"/>
-      <c r="L23" s="115"/>
+      <c r="J23" s="84"/>
+      <c r="K23" s="85"/>
+      <c r="L23" s="86"/>
       <c r="M23" s="4"/>
-      <c r="N23" s="73"/>
-      <c r="O23" s="74"/>
-      <c r="P23" s="75"/>
+      <c r="N23" s="148"/>
+      <c r="O23" s="149"/>
+      <c r="P23" s="150"/>
       <c r="Q23" s="44"/>
-      <c r="R23" s="73"/>
-      <c r="S23" s="74"/>
-      <c r="T23" s="75"/>
+      <c r="R23" s="148"/>
+      <c r="S23" s="149"/>
+      <c r="T23" s="150"/>
       <c r="U23" s="44"/>
-      <c r="V23" s="113"/>
-      <c r="W23" s="114"/>
-      <c r="X23" s="115"/>
+      <c r="V23" s="84"/>
+      <c r="W23" s="85"/>
+      <c r="X23" s="86"/>
       <c r="Y23" s="44"/>
-      <c r="Z23" s="113"/>
-      <c r="AA23" s="114"/>
-      <c r="AB23" s="115"/>
+      <c r="Z23" s="84"/>
+      <c r="AA23" s="85"/>
+      <c r="AB23" s="86"/>
       <c r="AC23" s="44"/>
-      <c r="AD23" s="113"/>
-      <c r="AE23" s="114"/>
-      <c r="AF23" s="115"/>
+      <c r="AD23" s="84"/>
+      <c r="AE23" s="85"/>
+      <c r="AF23" s="86"/>
       <c r="AG23" s="44"/>
-      <c r="AH23" s="113"/>
-      <c r="AI23" s="114"/>
-      <c r="AJ23" s="115"/>
+      <c r="AH23" s="84"/>
+      <c r="AI23" s="85"/>
+      <c r="AJ23" s="86"/>
       <c r="AK23" s="44"/>
-      <c r="AL23" s="113"/>
-      <c r="AM23" s="114"/>
-      <c r="AN23" s="115"/>
+      <c r="AL23" s="84"/>
+      <c r="AM23" s="85"/>
+      <c r="AN23" s="86"/>
       <c r="AP23" s="58" t="s">
         <v>20</v>
       </c>
@@ -3604,23 +3621,23 @@
       <c r="K25" s="33"/>
       <c r="L25" s="33"/>
       <c r="M25" s="4"/>
-      <c r="N25" s="116" t="s">
+      <c r="N25" s="105" t="s">
         <v>39</v>
       </c>
-      <c r="O25" s="116"/>
-      <c r="P25" s="116"/>
-      <c r="Q25" s="116"/>
-      <c r="R25" s="116"/>
-      <c r="S25" s="116"/>
-      <c r="T25" s="116"/>
-      <c r="U25" s="116"/>
-      <c r="V25" s="116"/>
-      <c r="W25" s="116"/>
-      <c r="X25" s="116"/>
-      <c r="Y25" s="116"/>
-      <c r="Z25" s="116"/>
-      <c r="AA25" s="116"/>
-      <c r="AB25" s="116"/>
+      <c r="O25" s="105"/>
+      <c r="P25" s="105"/>
+      <c r="Q25" s="105"/>
+      <c r="R25" s="105"/>
+      <c r="S25" s="105"/>
+      <c r="T25" s="105"/>
+      <c r="U25" s="105"/>
+      <c r="V25" s="105"/>
+      <c r="W25" s="105"/>
+      <c r="X25" s="105"/>
+      <c r="Y25" s="105"/>
+      <c r="Z25" s="105"/>
+      <c r="AA25" s="105"/>
+      <c r="AB25" s="105"/>
       <c r="AC25" s="33"/>
       <c r="AD25" s="33"/>
       <c r="AE25" s="33"/>
@@ -3655,21 +3672,21 @@
       <c r="K26" s="33"/>
       <c r="L26" s="33"/>
       <c r="M26" s="4"/>
-      <c r="N26" s="116"/>
-      <c r="O26" s="116"/>
-      <c r="P26" s="116"/>
-      <c r="Q26" s="116"/>
-      <c r="R26" s="116"/>
-      <c r="S26" s="116"/>
-      <c r="T26" s="116"/>
-      <c r="U26" s="116"/>
-      <c r="V26" s="116"/>
-      <c r="W26" s="116"/>
-      <c r="X26" s="116"/>
-      <c r="Y26" s="116"/>
-      <c r="Z26" s="116"/>
-      <c r="AA26" s="116"/>
-      <c r="AB26" s="116"/>
+      <c r="N26" s="105"/>
+      <c r="O26" s="105"/>
+      <c r="P26" s="105"/>
+      <c r="Q26" s="105"/>
+      <c r="R26" s="105"/>
+      <c r="S26" s="105"/>
+      <c r="T26" s="105"/>
+      <c r="U26" s="105"/>
+      <c r="V26" s="105"/>
+      <c r="W26" s="105"/>
+      <c r="X26" s="105"/>
+      <c r="Y26" s="105"/>
+      <c r="Z26" s="105"/>
+      <c r="AA26" s="105"/>
+      <c r="AB26" s="105"/>
       <c r="AC26" s="33"/>
       <c r="AD26" s="33"/>
       <c r="AE26" s="33"/>
@@ -3694,54 +3711,54 @@
       </c>
     </row>
     <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="66"/>
-      <c r="C27" s="67"/>
+      <c r="B27" s="63"/>
+      <c r="C27" s="64"/>
       <c r="D27" s="57"/>
       <c r="E27" s="36"/>
-      <c r="F27" s="66"/>
-      <c r="G27" s="67"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="64"/>
       <c r="H27" s="57"/>
       <c r="I27" s="36"/>
-      <c r="J27" s="66"/>
-      <c r="K27" s="67"/>
+      <c r="J27" s="63"/>
+      <c r="K27" s="64"/>
       <c r="L27" s="57"/>
       <c r="M27" s="5"/>
-      <c r="N27" s="68"/>
-      <c r="O27" s="69"/>
+      <c r="N27" s="87"/>
+      <c r="O27" s="88"/>
       <c r="P27" s="34"/>
       <c r="Q27" s="36"/>
-      <c r="R27" s="127"/>
-      <c r="S27" s="128"/>
+      <c r="R27" s="124"/>
+      <c r="S27" s="125"/>
       <c r="T27" s="55"/>
       <c r="U27" s="36"/>
-      <c r="V27" s="127"/>
-      <c r="W27" s="128"/>
+      <c r="V27" s="124"/>
+      <c r="W27" s="125"/>
       <c r="X27" s="55"/>
       <c r="Y27" s="36"/>
-      <c r="Z27" s="127"/>
-      <c r="AA27" s="128"/>
+      <c r="Z27" s="124"/>
+      <c r="AA27" s="125"/>
       <c r="AB27" s="55"/>
       <c r="AC27" s="36"/>
-      <c r="AD27" s="68" t="s">
+      <c r="AD27" s="87" t="s">
         <v>84</v>
       </c>
-      <c r="AE27" s="69"/>
+      <c r="AE27" s="88"/>
       <c r="AF27" s="34" t="s">
         <v>66</v>
       </c>
       <c r="AG27" s="36"/>
-      <c r="AH27" s="68" t="s">
+      <c r="AH27" s="87" t="s">
         <v>84</v>
       </c>
-      <c r="AI27" s="69"/>
+      <c r="AI27" s="88"/>
       <c r="AJ27" s="34" t="s">
         <v>66</v>
       </c>
       <c r="AK27" s="36"/>
-      <c r="AL27" s="68" t="s">
+      <c r="AL27" s="87" t="s">
         <v>84</v>
       </c>
-      <c r="AM27" s="69"/>
+      <c r="AM27" s="88"/>
       <c r="AN27" s="34" t="s">
         <v>66</v>
       </c>
@@ -3755,44 +3772,44 @@
       <c r="AR27" s="30"/>
     </row>
     <row r="28" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="96"/>
-      <c r="C28" s="97"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="69"/>
       <c r="D28" s="61"/>
       <c r="E28" s="38"/>
-      <c r="F28" s="96"/>
-      <c r="G28" s="97"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="69"/>
       <c r="H28" s="61"/>
       <c r="I28" s="36"/>
-      <c r="J28" s="96"/>
-      <c r="K28" s="97"/>
+      <c r="J28" s="68"/>
+      <c r="K28" s="69"/>
       <c r="L28" s="61"/>
       <c r="M28" s="5"/>
-      <c r="N28" s="85"/>
-      <c r="O28" s="86"/>
+      <c r="N28" s="92"/>
+      <c r="O28" s="93"/>
       <c r="P28" s="18"/>
       <c r="Q28" s="38"/>
-      <c r="R28" s="85"/>
-      <c r="S28" s="86"/>
+      <c r="R28" s="92"/>
+      <c r="S28" s="93"/>
       <c r="T28" s="18"/>
       <c r="U28" s="38"/>
-      <c r="V28" s="158"/>
-      <c r="W28" s="159"/>
+      <c r="V28" s="106"/>
+      <c r="W28" s="107"/>
       <c r="X28" s="56"/>
       <c r="Y28" s="36"/>
-      <c r="Z28" s="158"/>
-      <c r="AA28" s="159"/>
+      <c r="Z28" s="106"/>
+      <c r="AA28" s="107"/>
       <c r="AB28" s="56"/>
       <c r="AC28" s="36"/>
-      <c r="AD28" s="85"/>
-      <c r="AE28" s="86"/>
+      <c r="AD28" s="92"/>
+      <c r="AE28" s="93"/>
       <c r="AF28" s="18"/>
       <c r="AG28" s="38"/>
-      <c r="AH28" s="85"/>
-      <c r="AI28" s="86"/>
+      <c r="AH28" s="92"/>
+      <c r="AI28" s="93"/>
       <c r="AJ28" s="18"/>
       <c r="AK28" s="36"/>
-      <c r="AL28" s="85"/>
-      <c r="AM28" s="86"/>
+      <c r="AL28" s="92"/>
+      <c r="AM28" s="93"/>
       <c r="AN28" s="18"/>
       <c r="AP28" s="46" t="s">
         <v>28</v>
@@ -3804,54 +3821,54 @@
       <c r="AR28" s="30"/>
     </row>
     <row r="29" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="125"/>
-      <c r="C29" s="126"/>
+      <c r="B29" s="101"/>
+      <c r="C29" s="102"/>
       <c r="D29" s="41"/>
       <c r="E29" s="37"/>
-      <c r="F29" s="125"/>
-      <c r="G29" s="126"/>
+      <c r="F29" s="101"/>
+      <c r="G29" s="102"/>
       <c r="H29" s="41"/>
       <c r="I29" s="35"/>
-      <c r="J29" s="125"/>
-      <c r="K29" s="126"/>
+      <c r="J29" s="101"/>
+      <c r="K29" s="102"/>
       <c r="L29" s="41"/>
       <c r="M29" s="5"/>
-      <c r="N29" s="125"/>
-      <c r="O29" s="126"/>
+      <c r="N29" s="101"/>
+      <c r="O29" s="102"/>
       <c r="P29" s="41"/>
       <c r="Q29" s="35"/>
-      <c r="R29" s="125"/>
-      <c r="S29" s="126"/>
+      <c r="R29" s="101"/>
+      <c r="S29" s="102"/>
       <c r="T29" s="41"/>
       <c r="U29" s="37"/>
-      <c r="V29" s="125"/>
-      <c r="W29" s="126"/>
+      <c r="V29" s="101"/>
+      <c r="W29" s="102"/>
       <c r="X29" s="41"/>
       <c r="Y29" s="35"/>
-      <c r="Z29" s="125"/>
-      <c r="AA29" s="126"/>
+      <c r="Z29" s="101"/>
+      <c r="AA29" s="102"/>
       <c r="AB29" s="41"/>
       <c r="AC29" s="35"/>
-      <c r="AD29" s="125" t="s">
+      <c r="AD29" s="101" t="s">
         <v>7</v>
       </c>
-      <c r="AE29" s="126"/>
+      <c r="AE29" s="102"/>
       <c r="AF29" s="41" t="s">
         <v>32</v>
       </c>
       <c r="AG29" s="37"/>
-      <c r="AH29" s="125" t="s">
+      <c r="AH29" s="101" t="s">
         <v>7</v>
       </c>
-      <c r="AI29" s="126"/>
+      <c r="AI29" s="102"/>
       <c r="AJ29" s="41" t="s">
         <v>32</v>
       </c>
       <c r="AK29" s="35"/>
-      <c r="AL29" s="125" t="s">
+      <c r="AL29" s="101" t="s">
         <v>7</v>
       </c>
-      <c r="AM29" s="126"/>
+      <c r="AM29" s="102"/>
       <c r="AN29" s="41" t="s">
         <v>32</v>
       </c>
@@ -3865,54 +3882,54 @@
       <c r="AR29" s="30"/>
     </row>
     <row r="30" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="149"/>
-      <c r="C30" s="150"/>
+      <c r="B30" s="103"/>
+      <c r="C30" s="104"/>
       <c r="D30" s="45"/>
       <c r="E30" s="43"/>
-      <c r="F30" s="149"/>
-      <c r="G30" s="150"/>
+      <c r="F30" s="103"/>
+      <c r="G30" s="104"/>
       <c r="H30" s="45"/>
       <c r="I30" s="43"/>
-      <c r="J30" s="149"/>
-      <c r="K30" s="150"/>
+      <c r="J30" s="103"/>
+      <c r="K30" s="104"/>
       <c r="L30" s="45"/>
       <c r="M30" s="5"/>
-      <c r="N30" s="149"/>
-      <c r="O30" s="150"/>
+      <c r="N30" s="103"/>
+      <c r="O30" s="104"/>
       <c r="P30" s="45"/>
       <c r="Q30" s="43"/>
-      <c r="R30" s="149"/>
-      <c r="S30" s="150"/>
+      <c r="R30" s="103"/>
+      <c r="S30" s="104"/>
       <c r="T30" s="45"/>
       <c r="U30" s="43"/>
-      <c r="V30" s="149"/>
-      <c r="W30" s="150"/>
+      <c r="V30" s="103"/>
+      <c r="W30" s="104"/>
       <c r="X30" s="45"/>
       <c r="Y30" s="43"/>
-      <c r="Z30" s="149"/>
-      <c r="AA30" s="150"/>
+      <c r="Z30" s="103"/>
+      <c r="AA30" s="104"/>
       <c r="AB30" s="45"/>
       <c r="AC30" s="43"/>
-      <c r="AD30" s="149" t="s">
+      <c r="AD30" s="103" t="s">
         <v>19</v>
       </c>
-      <c r="AE30" s="150"/>
+      <c r="AE30" s="104"/>
       <c r="AF30" s="45" t="s">
         <v>33</v>
       </c>
       <c r="AG30" s="43"/>
-      <c r="AH30" s="149" t="s">
+      <c r="AH30" s="103" t="s">
         <v>19</v>
       </c>
-      <c r="AI30" s="150"/>
+      <c r="AI30" s="104"/>
       <c r="AJ30" s="45" t="s">
         <v>33</v>
       </c>
       <c r="AK30" s="43"/>
-      <c r="AL30" s="149" t="s">
+      <c r="AL30" s="103" t="s">
         <v>19</v>
       </c>
-      <c r="AM30" s="150"/>
+      <c r="AM30" s="104"/>
       <c r="AN30" s="45" t="s">
         <v>33</v>
       </c>
@@ -3926,54 +3943,54 @@
       <c r="AR30" s="30"/>
     </row>
     <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="120"/>
-      <c r="C31" s="121"/>
+      <c r="B31" s="74"/>
+      <c r="C31" s="75"/>
       <c r="D31" s="45"/>
       <c r="E31" s="43"/>
-      <c r="F31" s="120"/>
-      <c r="G31" s="121"/>
+      <c r="F31" s="74"/>
+      <c r="G31" s="75"/>
       <c r="H31" s="45"/>
       <c r="I31" s="44"/>
-      <c r="J31" s="120"/>
-      <c r="K31" s="121"/>
+      <c r="J31" s="74"/>
+      <c r="K31" s="75"/>
       <c r="L31" s="45"/>
       <c r="M31" s="6"/>
-      <c r="N31" s="120"/>
-      <c r="O31" s="121"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="75"/>
       <c r="P31" s="45"/>
       <c r="Q31" s="43"/>
-      <c r="R31" s="120"/>
-      <c r="S31" s="121"/>
+      <c r="R31" s="74"/>
+      <c r="S31" s="75"/>
       <c r="T31" s="45"/>
       <c r="U31" s="44"/>
-      <c r="V31" s="120"/>
-      <c r="W31" s="121"/>
+      <c r="V31" s="74"/>
+      <c r="W31" s="75"/>
       <c r="X31" s="45"/>
       <c r="Y31" s="43"/>
-      <c r="Z31" s="120"/>
-      <c r="AA31" s="121"/>
+      <c r="Z31" s="74"/>
+      <c r="AA31" s="75"/>
       <c r="AB31" s="45"/>
       <c r="AC31" s="43"/>
-      <c r="AD31" s="120" t="s">
+      <c r="AD31" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="AE31" s="121"/>
+      <c r="AE31" s="75"/>
       <c r="AF31" s="45" t="s">
         <v>34</v>
       </c>
       <c r="AG31" s="43"/>
-      <c r="AH31" s="120" t="s">
+      <c r="AH31" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="AI31" s="121"/>
+      <c r="AI31" s="75"/>
       <c r="AJ31" s="45" t="s">
         <v>34</v>
       </c>
       <c r="AK31" s="44"/>
-      <c r="AL31" s="120" t="s">
+      <c r="AL31" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="AM31" s="121"/>
+      <c r="AM31" s="75"/>
       <c r="AN31" s="45" t="s">
         <v>34</v>
       </c>
@@ -3982,54 +3999,54 @@
       <c r="AR31" s="30"/>
     </row>
     <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="120"/>
-      <c r="C32" s="121"/>
+      <c r="B32" s="74"/>
+      <c r="C32" s="75"/>
       <c r="D32" s="45"/>
       <c r="E32" s="44"/>
-      <c r="F32" s="120"/>
-      <c r="G32" s="121"/>
+      <c r="F32" s="74"/>
+      <c r="G32" s="75"/>
       <c r="H32" s="45"/>
       <c r="I32" s="44"/>
-      <c r="J32" s="120"/>
-      <c r="K32" s="121"/>
+      <c r="J32" s="74"/>
+      <c r="K32" s="75"/>
       <c r="L32" s="45"/>
       <c r="M32" s="5"/>
-      <c r="N32" s="120"/>
-      <c r="O32" s="121"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="75"/>
       <c r="P32" s="45"/>
       <c r="Q32" s="44"/>
-      <c r="R32" s="120"/>
-      <c r="S32" s="121"/>
+      <c r="R32" s="74"/>
+      <c r="S32" s="75"/>
       <c r="T32" s="45"/>
       <c r="U32" s="44"/>
-      <c r="V32" s="120"/>
-      <c r="W32" s="121"/>
+      <c r="V32" s="74"/>
+      <c r="W32" s="75"/>
       <c r="X32" s="45"/>
       <c r="Y32" s="44"/>
-      <c r="Z32" s="120"/>
-      <c r="AA32" s="121"/>
+      <c r="Z32" s="74"/>
+      <c r="AA32" s="75"/>
       <c r="AB32" s="45"/>
       <c r="AC32" s="44"/>
-      <c r="AD32" s="120" t="s">
+      <c r="AD32" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="AE32" s="121"/>
+      <c r="AE32" s="75"/>
       <c r="AF32" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AG32" s="44"/>
-      <c r="AH32" s="120" t="s">
+      <c r="AH32" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="AI32" s="121"/>
+      <c r="AI32" s="75"/>
       <c r="AJ32" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AK32" s="44"/>
-      <c r="AL32" s="120" t="s">
+      <c r="AL32" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="AM32" s="121"/>
+      <c r="AM32" s="75"/>
       <c r="AN32" s="45" t="s">
         <v>35</v>
       </c>
@@ -4038,91 +4055,91 @@
       <c r="AR32" s="30"/>
     </row>
     <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="120"/>
-      <c r="C33" s="121"/>
+      <c r="B33" s="74"/>
+      <c r="C33" s="75"/>
       <c r="D33" s="45"/>
       <c r="E33" s="44"/>
-      <c r="F33" s="120"/>
-      <c r="G33" s="121"/>
+      <c r="F33" s="74"/>
+      <c r="G33" s="75"/>
       <c r="H33" s="45"/>
       <c r="I33" s="44"/>
-      <c r="J33" s="120"/>
-      <c r="K33" s="121"/>
+      <c r="J33" s="74"/>
+      <c r="K33" s="75"/>
       <c r="L33" s="45"/>
       <c r="M33" s="5"/>
-      <c r="N33" s="120"/>
-      <c r="O33" s="121"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="75"/>
       <c r="P33" s="45"/>
       <c r="Q33" s="44"/>
-      <c r="R33" s="120"/>
-      <c r="S33" s="121"/>
+      <c r="R33" s="74"/>
+      <c r="S33" s="75"/>
       <c r="T33" s="45"/>
       <c r="U33" s="44"/>
-      <c r="V33" s="120"/>
-      <c r="W33" s="121"/>
+      <c r="V33" s="74"/>
+      <c r="W33" s="75"/>
       <c r="X33" s="45"/>
       <c r="Y33" s="44"/>
-      <c r="Z33" s="120"/>
-      <c r="AA33" s="121"/>
+      <c r="Z33" s="74"/>
+      <c r="AA33" s="75"/>
       <c r="AB33" s="45"/>
       <c r="AC33" s="44"/>
-      <c r="AD33" s="120" t="s">
+      <c r="AD33" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="AE33" s="121"/>
+      <c r="AE33" s="75"/>
       <c r="AF33" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AG33" s="44"/>
-      <c r="AH33" s="120"/>
-      <c r="AI33" s="121"/>
+      <c r="AH33" s="74"/>
+      <c r="AI33" s="75"/>
       <c r="AJ33" s="45"/>
       <c r="AK33" s="44"/>
-      <c r="AL33" s="120"/>
-      <c r="AM33" s="121"/>
+      <c r="AL33" s="74"/>
+      <c r="AM33" s="75"/>
       <c r="AN33" s="45"/>
       <c r="AR33" s="13"/>
     </row>
     <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="12"/>
-      <c r="B34" s="147"/>
-      <c r="C34" s="148"/>
+      <c r="B34" s="76"/>
+      <c r="C34" s="77"/>
       <c r="D34" s="42"/>
       <c r="E34" s="44"/>
-      <c r="F34" s="147"/>
-      <c r="G34" s="148"/>
+      <c r="F34" s="76"/>
+      <c r="G34" s="77"/>
       <c r="H34" s="42"/>
       <c r="I34" s="44"/>
-      <c r="J34" s="147"/>
-      <c r="K34" s="148"/>
+      <c r="J34" s="76"/>
+      <c r="K34" s="77"/>
       <c r="L34" s="42"/>
       <c r="M34" s="2"/>
-      <c r="N34" s="147"/>
-      <c r="O34" s="148"/>
+      <c r="N34" s="76"/>
+      <c r="O34" s="77"/>
       <c r="P34" s="42"/>
       <c r="Q34" s="44"/>
-      <c r="R34" s="147"/>
-      <c r="S34" s="148"/>
+      <c r="R34" s="76"/>
+      <c r="S34" s="77"/>
       <c r="T34" s="42"/>
       <c r="U34" s="44"/>
-      <c r="V34" s="147"/>
-      <c r="W34" s="148"/>
+      <c r="V34" s="76"/>
+      <c r="W34" s="77"/>
       <c r="X34" s="42"/>
       <c r="Y34" s="44"/>
-      <c r="Z34" s="147"/>
-      <c r="AA34" s="148"/>
+      <c r="Z34" s="76"/>
+      <c r="AA34" s="77"/>
       <c r="AB34" s="42"/>
       <c r="AC34" s="44"/>
-      <c r="AD34" s="147"/>
-      <c r="AE34" s="148"/>
+      <c r="AD34" s="76"/>
+      <c r="AE34" s="77"/>
       <c r="AF34" s="42"/>
       <c r="AG34" s="44"/>
-      <c r="AH34" s="147"/>
-      <c r="AI34" s="148"/>
+      <c r="AH34" s="76"/>
+      <c r="AI34" s="77"/>
       <c r="AJ34" s="42"/>
       <c r="AK34" s="44"/>
-      <c r="AL34" s="147"/>
-      <c r="AM34" s="148"/>
+      <c r="AL34" s="76"/>
+      <c r="AM34" s="77"/>
       <c r="AN34" s="42"/>
       <c r="AO34" s="12"/>
       <c r="AP34" s="12"/>
@@ -4188,23 +4205,23 @@
       <c r="K36" s="33"/>
       <c r="L36" s="33"/>
       <c r="M36" s="4"/>
-      <c r="N36" s="116" t="s">
+      <c r="N36" s="105" t="s">
         <v>36</v>
       </c>
-      <c r="O36" s="116"/>
-      <c r="P36" s="116"/>
-      <c r="Q36" s="116"/>
-      <c r="R36" s="116"/>
-      <c r="S36" s="116"/>
-      <c r="T36" s="116"/>
-      <c r="U36" s="116"/>
-      <c r="V36" s="116"/>
-      <c r="W36" s="116"/>
-      <c r="X36" s="116"/>
-      <c r="Y36" s="116"/>
-      <c r="Z36" s="116"/>
-      <c r="AA36" s="116"/>
-      <c r="AB36" s="116"/>
+      <c r="O36" s="105"/>
+      <c r="P36" s="105"/>
+      <c r="Q36" s="105"/>
+      <c r="R36" s="105"/>
+      <c r="S36" s="105"/>
+      <c r="T36" s="105"/>
+      <c r="U36" s="105"/>
+      <c r="V36" s="105"/>
+      <c r="W36" s="105"/>
+      <c r="X36" s="105"/>
+      <c r="Y36" s="105"/>
+      <c r="Z36" s="105"/>
+      <c r="AA36" s="105"/>
+      <c r="AB36" s="105"/>
       <c r="AC36" s="33"/>
       <c r="AD36" s="33"/>
       <c r="AE36" s="33"/>
@@ -4236,21 +4253,21 @@
       <c r="K37" s="33"/>
       <c r="L37" s="33"/>
       <c r="M37" s="5"/>
-      <c r="N37" s="116"/>
-      <c r="O37" s="116"/>
-      <c r="P37" s="116"/>
-      <c r="Q37" s="116"/>
-      <c r="R37" s="116"/>
-      <c r="S37" s="116"/>
-      <c r="T37" s="116"/>
-      <c r="U37" s="116"/>
-      <c r="V37" s="116"/>
-      <c r="W37" s="116"/>
-      <c r="X37" s="116"/>
-      <c r="Y37" s="116"/>
-      <c r="Z37" s="116"/>
-      <c r="AA37" s="116"/>
-      <c r="AB37" s="116"/>
+      <c r="N37" s="105"/>
+      <c r="O37" s="105"/>
+      <c r="P37" s="105"/>
+      <c r="Q37" s="105"/>
+      <c r="R37" s="105"/>
+      <c r="S37" s="105"/>
+      <c r="T37" s="105"/>
+      <c r="U37" s="105"/>
+      <c r="V37" s="105"/>
+      <c r="W37" s="105"/>
+      <c r="X37" s="105"/>
+      <c r="Y37" s="105"/>
+      <c r="Z37" s="105"/>
+      <c r="AA37" s="105"/>
+      <c r="AB37" s="105"/>
       <c r="AC37" s="33"/>
       <c r="AD37" s="33"/>
       <c r="AE37" s="33"/>
@@ -4270,74 +4287,74 @@
     </row>
     <row r="38" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="12"/>
-      <c r="B38" s="66" t="s">
+      <c r="B38" s="63" t="s">
         <v>51</v>
       </c>
-      <c r="C38" s="67"/>
+      <c r="C38" s="64"/>
       <c r="D38" s="57"/>
       <c r="E38" s="36"/>
-      <c r="F38" s="66" t="s">
+      <c r="F38" s="63" t="s">
         <v>51</v>
       </c>
-      <c r="G38" s="67"/>
+      <c r="G38" s="64"/>
       <c r="H38" s="57"/>
       <c r="I38" s="36"/>
-      <c r="J38" s="66" t="s">
+      <c r="J38" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="K38" s="67"/>
+      <c r="K38" s="64"/>
       <c r="L38" s="57" t="s">
         <v>64</v>
       </c>
       <c r="M38" s="5"/>
-      <c r="N38" s="68"/>
-      <c r="O38" s="69"/>
+      <c r="N38" s="87"/>
+      <c r="O38" s="88"/>
       <c r="P38" s="34"/>
       <c r="Q38" s="36"/>
-      <c r="R38" s="68" t="s">
+      <c r="R38" s="87" t="s">
         <v>76</v>
       </c>
-      <c r="S38" s="69"/>
+      <c r="S38" s="88"/>
       <c r="T38" s="34" t="s">
         <v>67</v>
       </c>
       <c r="U38" s="36"/>
-      <c r="V38" s="68" t="s">
+      <c r="V38" s="87" t="s">
         <v>76</v>
       </c>
-      <c r="W38" s="69"/>
+      <c r="W38" s="88"/>
       <c r="X38" s="34" t="s">
         <v>67</v>
       </c>
       <c r="Y38" s="36"/>
-      <c r="Z38" s="68" t="s">
+      <c r="Z38" s="87" t="s">
         <v>76</v>
       </c>
-      <c r="AA38" s="69"/>
+      <c r="AA38" s="88"/>
       <c r="AB38" s="34" t="s">
         <v>67</v>
       </c>
       <c r="AC38" s="36"/>
-      <c r="AD38" s="68" t="s">
+      <c r="AD38" s="87" t="s">
         <v>76</v>
       </c>
-      <c r="AE38" s="69"/>
+      <c r="AE38" s="88"/>
       <c r="AF38" s="34" t="s">
         <v>67</v>
       </c>
       <c r="AG38" s="36"/>
-      <c r="AH38" s="68" t="s">
+      <c r="AH38" s="87" t="s">
         <v>42</v>
       </c>
-      <c r="AI38" s="69"/>
+      <c r="AI38" s="88"/>
       <c r="AJ38" s="34" t="s">
         <v>49</v>
       </c>
       <c r="AK38" s="36"/>
-      <c r="AL38" s="68" t="s">
+      <c r="AL38" s="87" t="s">
         <v>73</v>
       </c>
-      <c r="AM38" s="69"/>
+      <c r="AM38" s="88"/>
       <c r="AN38" s="34" t="s">
         <v>74</v>
       </c>
@@ -4348,63 +4365,63 @@
     </row>
     <row r="39" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="12"/>
-      <c r="B39" s="88" t="s">
+      <c r="B39" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="C39" s="89"/>
-      <c r="D39" s="90"/>
+      <c r="C39" s="79"/>
+      <c r="D39" s="80"/>
       <c r="E39" s="36"/>
-      <c r="F39" s="88" t="s">
+      <c r="F39" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="G39" s="89"/>
-      <c r="H39" s="90"/>
+      <c r="G39" s="79"/>
+      <c r="H39" s="80"/>
       <c r="I39" s="36"/>
-      <c r="J39" s="88" t="s">
+      <c r="J39" s="78" t="s">
         <v>62</v>
       </c>
-      <c r="K39" s="89"/>
-      <c r="L39" s="90"/>
+      <c r="K39" s="79"/>
+      <c r="L39" s="80"/>
       <c r="M39" s="5"/>
-      <c r="N39" s="70"/>
-      <c r="O39" s="71"/>
-      <c r="P39" s="72"/>
+      <c r="N39" s="95"/>
+      <c r="O39" s="96"/>
+      <c r="P39" s="97"/>
       <c r="Q39" s="36"/>
-      <c r="R39" s="70" t="s">
+      <c r="R39" s="95" t="s">
         <v>63</v>
       </c>
-      <c r="S39" s="71"/>
-      <c r="T39" s="72"/>
+      <c r="S39" s="96"/>
+      <c r="T39" s="97"/>
       <c r="U39" s="36"/>
-      <c r="V39" s="70" t="s">
+      <c r="V39" s="95" t="s">
         <v>63</v>
       </c>
-      <c r="W39" s="71"/>
-      <c r="X39" s="72"/>
+      <c r="W39" s="96"/>
+      <c r="X39" s="97"/>
       <c r="Y39" s="37"/>
-      <c r="Z39" s="70" t="s">
+      <c r="Z39" s="95" t="s">
         <v>63</v>
       </c>
-      <c r="AA39" s="71"/>
-      <c r="AB39" s="72"/>
+      <c r="AA39" s="96"/>
+      <c r="AB39" s="97"/>
       <c r="AC39" s="36"/>
-      <c r="AD39" s="70" t="s">
+      <c r="AD39" s="95" t="s">
         <v>63</v>
       </c>
-      <c r="AE39" s="71"/>
-      <c r="AF39" s="72"/>
+      <c r="AE39" s="96"/>
+      <c r="AF39" s="97"/>
       <c r="AG39" s="36"/>
-      <c r="AH39" s="70" t="s">
+      <c r="AH39" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="AI39" s="71"/>
-      <c r="AJ39" s="72"/>
+      <c r="AI39" s="96"/>
+      <c r="AJ39" s="97"/>
       <c r="AK39" s="36"/>
-      <c r="AL39" s="70" t="s">
+      <c r="AL39" s="95" t="s">
         <v>75</v>
       </c>
-      <c r="AM39" s="71"/>
-      <c r="AN39" s="72"/>
+      <c r="AM39" s="96"/>
+      <c r="AN39" s="97"/>
       <c r="AO39" s="31"/>
       <c r="AP39" s="31"/>
       <c r="AQ39" s="31"/>
@@ -4412,45 +4429,45 @@
     </row>
     <row r="40" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="12"/>
-      <c r="B40" s="96"/>
-      <c r="C40" s="97"/>
-      <c r="D40" s="98"/>
+      <c r="B40" s="68"/>
+      <c r="C40" s="69"/>
+      <c r="D40" s="70"/>
       <c r="E40" s="43"/>
-      <c r="F40" s="96"/>
-      <c r="G40" s="97"/>
-      <c r="H40" s="98"/>
+      <c r="F40" s="68"/>
+      <c r="G40" s="69"/>
+      <c r="H40" s="70"/>
       <c r="I40" s="43"/>
-      <c r="J40" s="96"/>
-      <c r="K40" s="97"/>
-      <c r="L40" s="98"/>
+      <c r="J40" s="68"/>
+      <c r="K40" s="69"/>
+      <c r="L40" s="70"/>
       <c r="M40" s="4"/>
-      <c r="N40" s="85"/>
-      <c r="O40" s="86"/>
-      <c r="P40" s="87"/>
+      <c r="N40" s="92"/>
+      <c r="O40" s="93"/>
+      <c r="P40" s="94"/>
       <c r="Q40" s="43"/>
-      <c r="R40" s="85"/>
-      <c r="S40" s="86"/>
-      <c r="T40" s="87"/>
+      <c r="R40" s="92"/>
+      <c r="S40" s="93"/>
+      <c r="T40" s="94"/>
       <c r="U40" s="35"/>
-      <c r="V40" s="85"/>
-      <c r="W40" s="86"/>
-      <c r="X40" s="87"/>
+      <c r="V40" s="92"/>
+      <c r="W40" s="93"/>
+      <c r="X40" s="94"/>
       <c r="Y40" s="36"/>
-      <c r="Z40" s="85"/>
-      <c r="AA40" s="86"/>
-      <c r="AB40" s="87"/>
+      <c r="Z40" s="92"/>
+      <c r="AA40" s="93"/>
+      <c r="AB40" s="94"/>
       <c r="AC40" s="36"/>
-      <c r="AD40" s="85"/>
-      <c r="AE40" s="86"/>
-      <c r="AF40" s="87"/>
+      <c r="AD40" s="92"/>
+      <c r="AE40" s="93"/>
+      <c r="AF40" s="94"/>
       <c r="AG40" s="43"/>
-      <c r="AH40" s="85"/>
-      <c r="AI40" s="86"/>
-      <c r="AJ40" s="87"/>
+      <c r="AH40" s="92"/>
+      <c r="AI40" s="93"/>
+      <c r="AJ40" s="94"/>
       <c r="AK40" s="43"/>
-      <c r="AL40" s="85"/>
-      <c r="AM40" s="86"/>
-      <c r="AN40" s="87"/>
+      <c r="AL40" s="92"/>
+      <c r="AM40" s="93"/>
+      <c r="AN40" s="94"/>
       <c r="AO40" s="31"/>
       <c r="AP40" s="31"/>
       <c r="AQ40" s="31"/>
@@ -4458,63 +4475,63 @@
     </row>
     <row r="41" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12"/>
-      <c r="B41" s="82" t="s">
+      <c r="B41" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="C41" s="83"/>
-      <c r="D41" s="84"/>
+      <c r="C41" s="66"/>
+      <c r="D41" s="67"/>
       <c r="E41" s="37"/>
-      <c r="F41" s="82" t="s">
+      <c r="F41" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="G41" s="83"/>
-      <c r="H41" s="84"/>
+      <c r="G41" s="66"/>
+      <c r="H41" s="67"/>
       <c r="I41" s="31"/>
-      <c r="J41" s="82" t="s">
+      <c r="J41" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="K41" s="83"/>
-      <c r="L41" s="84"/>
+      <c r="K41" s="66"/>
+      <c r="L41" s="67"/>
       <c r="M41" s="5"/>
-      <c r="N41" s="82"/>
-      <c r="O41" s="83"/>
-      <c r="P41" s="84"/>
+      <c r="N41" s="65"/>
+      <c r="O41" s="66"/>
+      <c r="P41" s="67"/>
       <c r="Q41" s="32"/>
-      <c r="R41" s="82" t="s">
+      <c r="R41" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="S41" s="83"/>
-      <c r="T41" s="84"/>
+      <c r="S41" s="66"/>
+      <c r="T41" s="67"/>
       <c r="U41" s="31"/>
-      <c r="V41" s="82" t="s">
+      <c r="V41" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="W41" s="83"/>
-      <c r="X41" s="84"/>
+      <c r="W41" s="66"/>
+      <c r="X41" s="67"/>
       <c r="Y41" s="32"/>
-      <c r="Z41" s="82" t="s">
+      <c r="Z41" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="AA41" s="83"/>
-      <c r="AB41" s="84"/>
+      <c r="AA41" s="66"/>
+      <c r="AB41" s="67"/>
       <c r="AC41" s="32"/>
-      <c r="AD41" s="82" t="s">
+      <c r="AD41" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="AE41" s="83"/>
-      <c r="AF41" s="84"/>
+      <c r="AE41" s="66"/>
+      <c r="AF41" s="67"/>
       <c r="AG41" s="37"/>
-      <c r="AH41" s="160" t="s">
+      <c r="AH41" s="98" t="s">
         <v>104</v>
       </c>
-      <c r="AI41" s="161"/>
-      <c r="AJ41" s="162"/>
+      <c r="AI41" s="99"/>
+      <c r="AJ41" s="100"/>
       <c r="AK41" s="31"/>
-      <c r="AL41" s="82" t="s">
+      <c r="AL41" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="AM41" s="83"/>
-      <c r="AN41" s="84"/>
+      <c r="AM41" s="66"/>
+      <c r="AN41" s="67"/>
       <c r="AO41" s="31"/>
       <c r="AP41" s="31"/>
       <c r="AQ41" s="31"/>
@@ -4522,63 +4539,63 @@
     </row>
     <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12"/>
-      <c r="B42" s="82" t="s">
+      <c r="B42" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="C42" s="83"/>
-      <c r="D42" s="84"/>
+      <c r="C42" s="66"/>
+      <c r="D42" s="67"/>
       <c r="E42" s="44"/>
-      <c r="F42" s="82" t="s">
+      <c r="F42" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="G42" s="83"/>
-      <c r="H42" s="84"/>
+      <c r="G42" s="66"/>
+      <c r="H42" s="67"/>
       <c r="I42" s="31"/>
-      <c r="J42" s="82" t="s">
+      <c r="J42" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="K42" s="83"/>
-      <c r="L42" s="84"/>
+      <c r="K42" s="66"/>
+      <c r="L42" s="67"/>
       <c r="M42" s="5"/>
-      <c r="N42" s="82"/>
-      <c r="O42" s="83"/>
-      <c r="P42" s="84"/>
+      <c r="N42" s="65"/>
+      <c r="O42" s="66"/>
+      <c r="P42" s="67"/>
       <c r="Q42" s="31"/>
-      <c r="R42" s="82" t="s">
+      <c r="R42" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="S42" s="83"/>
-      <c r="T42" s="84"/>
+      <c r="S42" s="66"/>
+      <c r="T42" s="67"/>
       <c r="U42" s="32"/>
-      <c r="V42" s="82" t="s">
+      <c r="V42" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="W42" s="83"/>
-      <c r="X42" s="84"/>
+      <c r="W42" s="66"/>
+      <c r="X42" s="67"/>
       <c r="Y42" s="32"/>
-      <c r="Z42" s="82" t="s">
+      <c r="Z42" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="AA42" s="83"/>
-      <c r="AB42" s="84"/>
+      <c r="AA42" s="66"/>
+      <c r="AB42" s="67"/>
       <c r="AC42" s="32"/>
-      <c r="AD42" s="82" t="s">
+      <c r="AD42" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="AE42" s="83"/>
-      <c r="AF42" s="84"/>
+      <c r="AE42" s="66"/>
+      <c r="AF42" s="67"/>
       <c r="AG42" s="44"/>
-      <c r="AH42" s="82" t="s">
+      <c r="AH42" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="AI42" s="83"/>
-      <c r="AJ42" s="84"/>
+      <c r="AI42" s="66"/>
+      <c r="AJ42" s="67"/>
       <c r="AK42" s="31"/>
-      <c r="AL42" s="82" t="s">
+      <c r="AL42" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="AM42" s="83"/>
-      <c r="AN42" s="84"/>
+      <c r="AM42" s="66"/>
+      <c r="AN42" s="67"/>
       <c r="AO42" s="31"/>
       <c r="AP42" s="31"/>
       <c r="AQ42" s="31"/>
@@ -4586,51 +4603,51 @@
     </row>
     <row r="43" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="12"/>
-      <c r="B43" s="63" t="s">
+      <c r="B43" s="71" t="s">
         <v>27</v>
       </c>
-      <c r="C43" s="64"/>
-      <c r="D43" s="65"/>
+      <c r="C43" s="72"/>
+      <c r="D43" s="73"/>
       <c r="E43" s="35"/>
-      <c r="F43" s="63" t="s">
+      <c r="F43" s="71" t="s">
         <v>27</v>
       </c>
-      <c r="G43" s="64"/>
-      <c r="H43" s="65"/>
+      <c r="G43" s="72"/>
+      <c r="H43" s="73"/>
       <c r="I43" s="40"/>
-      <c r="J43" s="63"/>
-      <c r="K43" s="64"/>
-      <c r="L43" s="65"/>
+      <c r="J43" s="71"/>
+      <c r="K43" s="72"/>
+      <c r="L43" s="73"/>
       <c r="M43" s="14"/>
-      <c r="N43" s="63"/>
-      <c r="O43" s="64"/>
-      <c r="P43" s="65"/>
+      <c r="N43" s="71"/>
+      <c r="O43" s="72"/>
+      <c r="P43" s="73"/>
       <c r="Q43" s="40"/>
-      <c r="R43" s="63"/>
-      <c r="S43" s="64"/>
-      <c r="T43" s="65"/>
+      <c r="R43" s="71"/>
+      <c r="S43" s="72"/>
+      <c r="T43" s="73"/>
       <c r="U43" s="40"/>
-      <c r="V43" s="63"/>
-      <c r="W43" s="64"/>
-      <c r="X43" s="65"/>
+      <c r="V43" s="71"/>
+      <c r="W43" s="72"/>
+      <c r="X43" s="73"/>
       <c r="Y43" s="40"/>
-      <c r="Z43" s="63"/>
-      <c r="AA43" s="64"/>
-      <c r="AB43" s="65"/>
+      <c r="Z43" s="71"/>
+      <c r="AA43" s="72"/>
+      <c r="AB43" s="73"/>
       <c r="AC43" s="40"/>
-      <c r="AD43" s="63"/>
-      <c r="AE43" s="64"/>
-      <c r="AF43" s="65"/>
+      <c r="AD43" s="71"/>
+      <c r="AE43" s="72"/>
+      <c r="AF43" s="73"/>
       <c r="AG43" s="35"/>
-      <c r="AH43" s="63" t="s">
+      <c r="AH43" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="AI43" s="64"/>
-      <c r="AJ43" s="65"/>
+      <c r="AI43" s="72"/>
+      <c r="AJ43" s="73"/>
       <c r="AK43" s="40"/>
-      <c r="AL43" s="63"/>
-      <c r="AM43" s="64"/>
-      <c r="AN43" s="65"/>
+      <c r="AL43" s="71"/>
+      <c r="AM43" s="72"/>
+      <c r="AN43" s="73"/>
       <c r="AO43" s="31"/>
       <c r="AP43" s="31"/>
       <c r="AQ43" s="31"/>
@@ -4684,74 +4701,74 @@
     </row>
     <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="12"/>
-      <c r="B45" s="66" t="s">
+      <c r="B45" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="C45" s="67"/>
+      <c r="C45" s="64"/>
       <c r="D45" s="57" t="s">
         <v>50</v>
       </c>
       <c r="E45" s="36"/>
-      <c r="F45" s="66" t="s">
+      <c r="F45" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="G45" s="67"/>
+      <c r="G45" s="64"/>
       <c r="H45" s="57" t="s">
         <v>49</v>
       </c>
       <c r="I45" s="32"/>
-      <c r="J45" s="66" t="s">
+      <c r="J45" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="K45" s="67"/>
+      <c r="K45" s="64"/>
       <c r="L45" s="57" t="s">
         <v>50</v>
       </c>
       <c r="M45" s="14"/>
-      <c r="N45" s="68"/>
-      <c r="O45" s="69"/>
+      <c r="N45" s="87"/>
+      <c r="O45" s="88"/>
       <c r="P45" s="34"/>
       <c r="Q45" s="36"/>
-      <c r="R45" s="68" t="s">
+      <c r="R45" s="87" t="s">
         <v>82</v>
       </c>
-      <c r="S45" s="69"/>
+      <c r="S45" s="88"/>
       <c r="T45" s="34" t="s">
         <v>66</v>
       </c>
       <c r="U45" s="36"/>
-      <c r="V45" s="68" t="s">
+      <c r="V45" s="87" t="s">
         <v>53</v>
       </c>
-      <c r="W45" s="69"/>
+      <c r="W45" s="88"/>
       <c r="X45" s="34"/>
       <c r="Y45" s="54"/>
-      <c r="Z45" s="68" t="s">
+      <c r="Z45" s="87" t="s">
         <v>53</v>
       </c>
-      <c r="AA45" s="69"/>
+      <c r="AA45" s="88"/>
       <c r="AB45" s="34"/>
       <c r="AC45" s="36"/>
-      <c r="AD45" s="68" t="s">
+      <c r="AD45" s="87" t="s">
         <v>42</v>
       </c>
-      <c r="AE45" s="69"/>
+      <c r="AE45" s="88"/>
       <c r="AF45" s="34" t="s">
         <v>66</v>
       </c>
       <c r="AG45" s="36"/>
-      <c r="AH45" s="68" t="s">
+      <c r="AH45" s="87" t="s">
         <v>42</v>
       </c>
-      <c r="AI45" s="69"/>
+      <c r="AI45" s="88"/>
       <c r="AJ45" s="34" t="s">
         <v>50</v>
       </c>
       <c r="AK45" s="32"/>
-      <c r="AL45" s="68" t="s">
+      <c r="AL45" s="87" t="s">
         <v>42</v>
       </c>
-      <c r="AM45" s="69"/>
+      <c r="AM45" s="88"/>
       <c r="AN45" s="34" t="s">
         <v>49</v>
       </c>
@@ -4762,63 +4779,63 @@
     </row>
     <row r="46" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="12"/>
-      <c r="B46" s="88" t="s">
+      <c r="B46" s="78" t="s">
         <v>47</v>
       </c>
-      <c r="C46" s="89"/>
-      <c r="D46" s="90"/>
+      <c r="C46" s="79"/>
+      <c r="D46" s="80"/>
       <c r="E46" s="36"/>
-      <c r="F46" s="88" t="s">
+      <c r="F46" s="78" t="s">
         <v>48</v>
       </c>
-      <c r="G46" s="89"/>
-      <c r="H46" s="90"/>
+      <c r="G46" s="79"/>
+      <c r="H46" s="80"/>
       <c r="I46" s="54"/>
-      <c r="J46" s="88" t="s">
+      <c r="J46" s="78" t="s">
         <v>47</v>
       </c>
-      <c r="K46" s="89"/>
-      <c r="L46" s="90"/>
+      <c r="K46" s="79"/>
+      <c r="L46" s="80"/>
       <c r="M46" s="4"/>
-      <c r="N46" s="70"/>
-      <c r="O46" s="71"/>
-      <c r="P46" s="72"/>
+      <c r="N46" s="95"/>
+      <c r="O46" s="96"/>
+      <c r="P46" s="97"/>
       <c r="Q46" s="43"/>
-      <c r="R46" s="70" t="s">
+      <c r="R46" s="95" t="s">
         <v>83</v>
       </c>
-      <c r="S46" s="71"/>
-      <c r="T46" s="72"/>
+      <c r="S46" s="96"/>
+      <c r="T46" s="97"/>
       <c r="U46" s="36"/>
-      <c r="V46" s="70" t="s">
+      <c r="V46" s="95" t="s">
         <v>71</v>
       </c>
-      <c r="W46" s="71"/>
-      <c r="X46" s="72"/>
+      <c r="W46" s="96"/>
+      <c r="X46" s="97"/>
       <c r="Y46" s="35"/>
-      <c r="Z46" s="70" t="s">
+      <c r="Z46" s="95" t="s">
         <v>71</v>
       </c>
-      <c r="AA46" s="71"/>
-      <c r="AB46" s="72"/>
+      <c r="AA46" s="96"/>
+      <c r="AB46" s="97"/>
       <c r="AC46" s="36"/>
-      <c r="AD46" s="70" t="s">
+      <c r="AD46" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="AE46" s="71"/>
-      <c r="AF46" s="72"/>
+      <c r="AE46" s="96"/>
+      <c r="AF46" s="97"/>
       <c r="AG46" s="36"/>
-      <c r="AH46" s="70" t="s">
+      <c r="AH46" s="95" t="s">
         <v>43</v>
       </c>
-      <c r="AI46" s="71"/>
-      <c r="AJ46" s="72"/>
+      <c r="AI46" s="96"/>
+      <c r="AJ46" s="97"/>
       <c r="AK46" s="54"/>
-      <c r="AL46" s="70" t="s">
+      <c r="AL46" s="95" t="s">
         <v>44</v>
       </c>
-      <c r="AM46" s="71"/>
-      <c r="AN46" s="72"/>
+      <c r="AM46" s="96"/>
+      <c r="AN46" s="97"/>
       <c r="AO46" s="31"/>
       <c r="AP46" s="31"/>
       <c r="AQ46" s="31"/>
@@ -4826,47 +4843,47 @@
     </row>
     <row r="47" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="12"/>
-      <c r="B47" s="96"/>
-      <c r="C47" s="97"/>
-      <c r="D47" s="98"/>
+      <c r="B47" s="68"/>
+      <c r="C47" s="69"/>
+      <c r="D47" s="70"/>
       <c r="E47" s="43"/>
-      <c r="F47" s="96"/>
-      <c r="G47" s="97"/>
-      <c r="H47" s="98"/>
+      <c r="F47" s="68"/>
+      <c r="G47" s="69"/>
+      <c r="H47" s="70"/>
       <c r="I47" s="37"/>
-      <c r="J47" s="96"/>
-      <c r="K47" s="97"/>
-      <c r="L47" s="98"/>
+      <c r="J47" s="68"/>
+      <c r="K47" s="69"/>
+      <c r="L47" s="70"/>
       <c r="M47" s="4"/>
-      <c r="N47" s="85"/>
-      <c r="O47" s="86"/>
-      <c r="P47" s="87"/>
+      <c r="N47" s="92"/>
+      <c r="O47" s="93"/>
+      <c r="P47" s="94"/>
       <c r="Q47" s="37"/>
-      <c r="R47" s="85"/>
-      <c r="S47" s="86"/>
-      <c r="T47" s="87"/>
+      <c r="R47" s="92"/>
+      <c r="S47" s="93"/>
+      <c r="T47" s="94"/>
       <c r="U47" s="43"/>
-      <c r="V47" s="85" t="s">
+      <c r="V47" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="W47" s="86"/>
-      <c r="X47" s="87"/>
+      <c r="W47" s="93"/>
+      <c r="X47" s="94"/>
       <c r="Y47" s="35"/>
-      <c r="Z47" s="85"/>
-      <c r="AA47" s="86"/>
-      <c r="AB47" s="87"/>
+      <c r="Z47" s="92"/>
+      <c r="AA47" s="93"/>
+      <c r="AB47" s="94"/>
       <c r="AC47" s="35"/>
-      <c r="AD47" s="85"/>
-      <c r="AE47" s="86"/>
-      <c r="AF47" s="87"/>
+      <c r="AD47" s="92"/>
+      <c r="AE47" s="93"/>
+      <c r="AF47" s="94"/>
       <c r="AG47" s="43"/>
-      <c r="AH47" s="85"/>
-      <c r="AI47" s="86"/>
-      <c r="AJ47" s="87"/>
+      <c r="AH47" s="92"/>
+      <c r="AI47" s="93"/>
+      <c r="AJ47" s="94"/>
       <c r="AK47" s="37"/>
-      <c r="AL47" s="85"/>
-      <c r="AM47" s="86"/>
-      <c r="AN47" s="87"/>
+      <c r="AL47" s="92"/>
+      <c r="AM47" s="93"/>
+      <c r="AN47" s="94"/>
       <c r="AO47" s="31"/>
       <c r="AP47" s="31"/>
       <c r="AQ47" s="31"/>
@@ -4874,189 +4891,189 @@
     </row>
     <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="12"/>
-      <c r="B48" s="82" t="s">
+      <c r="B48" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="83"/>
-      <c r="D48" s="84"/>
+      <c r="C48" s="66"/>
+      <c r="D48" s="67"/>
       <c r="E48" s="37"/>
-      <c r="F48" s="82" t="s">
+      <c r="F48" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="G48" s="83"/>
-      <c r="H48" s="84"/>
+      <c r="G48" s="66"/>
+      <c r="H48" s="67"/>
       <c r="I48" s="44"/>
-      <c r="J48" s="82" t="s">
+      <c r="J48" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="K48" s="83"/>
-      <c r="L48" s="84"/>
+      <c r="K48" s="66"/>
+      <c r="L48" s="67"/>
       <c r="M48" s="5"/>
-      <c r="N48" s="82"/>
-      <c r="O48" s="83"/>
-      <c r="P48" s="84"/>
+      <c r="N48" s="65"/>
+      <c r="O48" s="66"/>
+      <c r="P48" s="67"/>
       <c r="Q48" s="44"/>
-      <c r="R48" s="82" t="s">
+      <c r="R48" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="S48" s="83"/>
-      <c r="T48" s="84"/>
+      <c r="S48" s="66"/>
+      <c r="T48" s="67"/>
       <c r="U48" s="37"/>
-      <c r="V48" s="82" t="s">
+      <c r="V48" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="W48" s="83"/>
-      <c r="X48" s="84"/>
+      <c r="W48" s="66"/>
+      <c r="X48" s="67"/>
       <c r="Y48" s="40"/>
-      <c r="Z48" s="82" t="s">
+      <c r="Z48" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="AA48" s="83"/>
-      <c r="AB48" s="84"/>
+      <c r="AA48" s="66"/>
+      <c r="AB48" s="67"/>
       <c r="AC48" s="43"/>
-      <c r="AD48" s="82" t="s">
+      <c r="AD48" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="AE48" s="83"/>
-      <c r="AF48" s="84"/>
+      <c r="AE48" s="66"/>
+      <c r="AF48" s="67"/>
       <c r="AG48" s="37"/>
-      <c r="AH48" s="82" t="s">
+      <c r="AH48" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="AI48" s="83"/>
-      <c r="AJ48" s="84"/>
+      <c r="AI48" s="66"/>
+      <c r="AJ48" s="67"/>
       <c r="AK48" s="44"/>
-      <c r="AL48" s="117" t="s">
+      <c r="AL48" s="108" t="s">
         <v>10</v>
       </c>
-      <c r="AM48" s="118"/>
-      <c r="AN48" s="119"/>
+      <c r="AM48" s="109"/>
+      <c r="AN48" s="110"/>
       <c r="AO48" s="31"/>
       <c r="AP48" s="31"/>
       <c r="AQ48" s="31"/>
       <c r="AR48" s="13"/>
     </row>
     <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="82" t="s">
+      <c r="B49" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="C49" s="83"/>
-      <c r="D49" s="84"/>
+      <c r="C49" s="66"/>
+      <c r="D49" s="67"/>
       <c r="E49" s="35"/>
-      <c r="F49" s="82" t="s">
+      <c r="F49" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="G49" s="83"/>
-      <c r="H49" s="84"/>
+      <c r="G49" s="66"/>
+      <c r="H49" s="67"/>
       <c r="I49" s="44"/>
-      <c r="J49" s="82" t="s">
+      <c r="J49" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="K49" s="83"/>
-      <c r="L49" s="84"/>
+      <c r="K49" s="66"/>
+      <c r="L49" s="67"/>
       <c r="M49" s="5"/>
-      <c r="N49" s="82"/>
-      <c r="O49" s="83"/>
-      <c r="P49" s="84"/>
+      <c r="N49" s="65"/>
+      <c r="O49" s="66"/>
+      <c r="P49" s="67"/>
       <c r="Q49" s="44"/>
-      <c r="R49" s="117" t="s">
+      <c r="R49" s="108" t="s">
         <v>37</v>
       </c>
-      <c r="S49" s="118"/>
-      <c r="T49" s="119"/>
+      <c r="S49" s="109"/>
+      <c r="T49" s="110"/>
       <c r="U49" s="44"/>
-      <c r="V49" s="82" t="s">
+      <c r="V49" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="W49" s="83"/>
-      <c r="X49" s="84"/>
+      <c r="W49" s="66"/>
+      <c r="X49" s="67"/>
       <c r="Y49" s="44"/>
-      <c r="Z49" s="82" t="s">
+      <c r="Z49" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="AA49" s="83"/>
-      <c r="AB49" s="84"/>
+      <c r="AA49" s="66"/>
+      <c r="AB49" s="67"/>
       <c r="AC49" s="35"/>
-      <c r="AD49" s="82" t="s">
+      <c r="AD49" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="AE49" s="83"/>
-      <c r="AF49" s="84"/>
+      <c r="AE49" s="66"/>
+      <c r="AF49" s="67"/>
       <c r="AG49" s="35"/>
-      <c r="AH49" s="82" t="s">
+      <c r="AH49" s="65" t="s">
         <v>15</v>
       </c>
-      <c r="AI49" s="83"/>
-      <c r="AJ49" s="84"/>
+      <c r="AI49" s="66"/>
+      <c r="AJ49" s="67"/>
       <c r="AK49" s="44"/>
-      <c r="AL49" s="82" t="s">
+      <c r="AL49" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="AM49" s="83"/>
-      <c r="AN49" s="84"/>
+      <c r="AM49" s="66"/>
+      <c r="AN49" s="67"/>
       <c r="AO49" s="31"/>
       <c r="AP49" s="31"/>
       <c r="AQ49" s="31"/>
       <c r="AR49" s="13"/>
     </row>
     <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="63" t="s">
+      <c r="B50" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="C50" s="64"/>
-      <c r="D50" s="65"/>
+      <c r="C50" s="72"/>
+      <c r="D50" s="73"/>
       <c r="E50" s="50"/>
-      <c r="F50" s="63" t="s">
+      <c r="F50" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="G50" s="64"/>
-      <c r="H50" s="65"/>
+      <c r="G50" s="72"/>
+      <c r="H50" s="73"/>
       <c r="I50" s="50"/>
-      <c r="J50" s="63" t="s">
+      <c r="J50" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="K50" s="64"/>
-      <c r="L50" s="65"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="73"/>
       <c r="M50" s="5"/>
-      <c r="N50" s="63"/>
-      <c r="O50" s="64"/>
-      <c r="P50" s="65"/>
+      <c r="N50" s="71"/>
+      <c r="O50" s="72"/>
+      <c r="P50" s="73"/>
       <c r="Q50" s="50"/>
-      <c r="R50" s="79" t="s">
+      <c r="R50" s="89" t="s">
         <v>96</v>
       </c>
-      <c r="S50" s="80"/>
-      <c r="T50" s="81"/>
+      <c r="S50" s="90"/>
+      <c r="T50" s="91"/>
       <c r="U50" s="50"/>
-      <c r="V50" s="82" t="s">
+      <c r="V50" s="65" t="s">
         <v>15</v>
       </c>
-      <c r="W50" s="83"/>
-      <c r="X50" s="84"/>
+      <c r="W50" s="66"/>
+      <c r="X50" s="67"/>
       <c r="Y50" s="36"/>
-      <c r="Z50" s="82" t="s">
+      <c r="Z50" s="65" t="s">
         <v>15</v>
       </c>
-      <c r="AA50" s="83"/>
-      <c r="AB50" s="84"/>
+      <c r="AA50" s="66"/>
+      <c r="AB50" s="67"/>
       <c r="AC50" s="50"/>
-      <c r="AD50" s="79" t="s">
+      <c r="AD50" s="89" t="s">
         <v>107</v>
       </c>
-      <c r="AE50" s="80"/>
-      <c r="AF50" s="81"/>
+      <c r="AE50" s="90"/>
+      <c r="AF50" s="91"/>
       <c r="AG50" s="50"/>
-      <c r="AH50" s="63" t="s">
+      <c r="AH50" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="AI50" s="64"/>
-      <c r="AJ50" s="65"/>
+      <c r="AI50" s="72"/>
+      <c r="AJ50" s="73"/>
       <c r="AK50" s="50"/>
-      <c r="AL50" s="63" t="s">
+      <c r="AL50" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="AM50" s="64"/>
-      <c r="AN50" s="65"/>
+      <c r="AM50" s="72"/>
+      <c r="AN50" s="73"/>
       <c r="AO50" s="31"/>
       <c r="AP50" s="31"/>
       <c r="AQ50" s="31"/>
@@ -5083,17 +5100,17 @@
       <c r="S51" s="35"/>
       <c r="T51" s="35"/>
       <c r="U51" s="36"/>
-      <c r="V51" s="63" t="s">
+      <c r="V51" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="W51" s="64"/>
-      <c r="X51" s="65"/>
+      <c r="W51" s="72"/>
+      <c r="X51" s="73"/>
       <c r="Y51" s="37"/>
-      <c r="Z51" s="63" t="s">
+      <c r="Z51" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="AA51" s="64"/>
-      <c r="AB51" s="65"/>
+      <c r="AA51" s="72"/>
+      <c r="AB51" s="73"/>
       <c r="AC51" s="36"/>
       <c r="AD51" s="35"/>
       <c r="AE51" s="35"/>
@@ -5112,34 +5129,34 @@
       <c r="AR51" s="13"/>
     </row>
     <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="66"/>
-      <c r="C52" s="67"/>
+      <c r="B52" s="63"/>
+      <c r="C52" s="64"/>
       <c r="D52" s="57"/>
       <c r="E52" s="36"/>
-      <c r="F52" s="91" t="s">
+      <c r="F52" s="116" t="s">
         <v>89</v>
       </c>
-      <c r="G52" s="92"/>
+      <c r="G52" s="117"/>
       <c r="H52" s="59" t="s">
         <v>90</v>
       </c>
       <c r="I52" s="54"/>
-      <c r="J52" s="66" t="s">
+      <c r="J52" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="K52" s="67"/>
+      <c r="K52" s="64"/>
       <c r="L52" s="57" t="s">
         <v>50</v>
       </c>
       <c r="M52" s="14"/>
-      <c r="N52" s="68"/>
-      <c r="O52" s="69"/>
+      <c r="N52" s="87"/>
+      <c r="O52" s="88"/>
       <c r="P52" s="34"/>
       <c r="Q52" s="31"/>
-      <c r="R52" s="91" t="s">
+      <c r="R52" s="116" t="s">
         <v>89</v>
       </c>
-      <c r="S52" s="92"/>
+      <c r="S52" s="117"/>
       <c r="T52" s="59" t="s">
         <v>94</v>
       </c>
@@ -5152,277 +5169,277 @@
       <c r="AA52" s="35"/>
       <c r="AB52" s="35"/>
       <c r="AC52" s="36"/>
-      <c r="AD52" s="91" t="s">
+      <c r="AD52" s="116" t="s">
         <v>89</v>
       </c>
-      <c r="AE52" s="92"/>
+      <c r="AE52" s="117"/>
       <c r="AF52" s="59" t="s">
         <v>102</v>
       </c>
       <c r="AG52" s="36"/>
-      <c r="AH52" s="91" t="s">
+      <c r="AH52" s="116" t="s">
         <v>89</v>
       </c>
-      <c r="AI52" s="92"/>
+      <c r="AI52" s="117"/>
       <c r="AJ52" s="59" t="s">
         <v>90</v>
       </c>
       <c r="AK52" s="54"/>
-      <c r="AL52" s="68"/>
-      <c r="AM52" s="69"/>
+      <c r="AL52" s="87"/>
+      <c r="AM52" s="88"/>
       <c r="AN52" s="34"/>
       <c r="AR52" s="13"/>
     </row>
     <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="88"/>
-      <c r="C53" s="89"/>
-      <c r="D53" s="90"/>
+      <c r="B53" s="78"/>
+      <c r="C53" s="79"/>
+      <c r="D53" s="80"/>
       <c r="E53" s="36"/>
-      <c r="F53" s="88" t="s">
+      <c r="F53" s="78" t="s">
         <v>91</v>
       </c>
-      <c r="G53" s="89"/>
-      <c r="H53" s="90"/>
+      <c r="G53" s="79"/>
+      <c r="H53" s="80"/>
       <c r="I53" s="35"/>
-      <c r="J53" s="88" t="s">
+      <c r="J53" s="78" t="s">
         <v>63</v>
       </c>
-      <c r="K53" s="89"/>
-      <c r="L53" s="90"/>
+      <c r="K53" s="79"/>
+      <c r="L53" s="80"/>
       <c r="M53" s="4"/>
-      <c r="N53" s="70"/>
-      <c r="O53" s="71"/>
-      <c r="P53" s="72"/>
+      <c r="N53" s="95"/>
+      <c r="O53" s="96"/>
+      <c r="P53" s="97"/>
       <c r="Q53" s="32"/>
-      <c r="R53" s="70" t="s">
+      <c r="R53" s="95" t="s">
         <v>95</v>
       </c>
-      <c r="S53" s="71"/>
-      <c r="T53" s="72"/>
+      <c r="S53" s="96"/>
+      <c r="T53" s="97"/>
       <c r="U53" s="43"/>
-      <c r="V53" s="68" t="s">
+      <c r="V53" s="87" t="s">
         <v>82</v>
       </c>
-      <c r="W53" s="69"/>
+      <c r="W53" s="88"/>
       <c r="X53" s="34" t="s">
         <v>66</v>
       </c>
       <c r="Y53" s="35"/>
-      <c r="Z53" s="68"/>
-      <c r="AA53" s="69"/>
+      <c r="Z53" s="87"/>
+      <c r="AA53" s="88"/>
       <c r="AB53" s="34"/>
       <c r="AC53" s="35"/>
-      <c r="AD53" s="70" t="s">
+      <c r="AD53" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="AE53" s="71"/>
-      <c r="AF53" s="72"/>
+      <c r="AE53" s="96"/>
+      <c r="AF53" s="97"/>
       <c r="AG53" s="36"/>
-      <c r="AH53" s="70" t="s">
+      <c r="AH53" s="95" t="s">
         <v>108</v>
       </c>
-      <c r="AI53" s="71"/>
-      <c r="AJ53" s="72"/>
+      <c r="AI53" s="96"/>
+      <c r="AJ53" s="97"/>
       <c r="AK53" s="35"/>
-      <c r="AL53" s="70"/>
-      <c r="AM53" s="71"/>
-      <c r="AN53" s="72"/>
+      <c r="AL53" s="95"/>
+      <c r="AM53" s="96"/>
+      <c r="AN53" s="97"/>
       <c r="AR53" s="13"/>
     </row>
     <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="96"/>
-      <c r="C54" s="97"/>
-      <c r="D54" s="98"/>
+      <c r="B54" s="68"/>
+      <c r="C54" s="69"/>
+      <c r="D54" s="70"/>
       <c r="E54" s="43"/>
-      <c r="F54" s="96"/>
-      <c r="G54" s="97"/>
-      <c r="H54" s="98"/>
+      <c r="F54" s="68"/>
+      <c r="G54" s="69"/>
+      <c r="H54" s="70"/>
       <c r="I54" s="35"/>
-      <c r="J54" s="96"/>
-      <c r="K54" s="97"/>
-      <c r="L54" s="98"/>
+      <c r="J54" s="68"/>
+      <c r="K54" s="69"/>
+      <c r="L54" s="70"/>
       <c r="M54" s="4"/>
-      <c r="N54" s="85"/>
-      <c r="O54" s="86"/>
-      <c r="P54" s="87"/>
+      <c r="N54" s="92"/>
+      <c r="O54" s="93"/>
+      <c r="P54" s="94"/>
       <c r="Q54" s="43"/>
-      <c r="R54" s="85"/>
-      <c r="S54" s="86"/>
-      <c r="T54" s="87"/>
+      <c r="R54" s="92"/>
+      <c r="S54" s="93"/>
+      <c r="T54" s="94"/>
       <c r="U54" s="37"/>
-      <c r="V54" s="70" t="s">
+      <c r="V54" s="95" t="s">
         <v>83</v>
       </c>
-      <c r="W54" s="71"/>
-      <c r="X54" s="72"/>
+      <c r="W54" s="96"/>
+      <c r="X54" s="97"/>
       <c r="Y54" s="40"/>
-      <c r="Z54" s="70"/>
-      <c r="AA54" s="71"/>
-      <c r="AB54" s="72"/>
+      <c r="Z54" s="95"/>
+      <c r="AA54" s="96"/>
+      <c r="AB54" s="97"/>
       <c r="AC54" s="31"/>
-      <c r="AD54" s="85"/>
-      <c r="AE54" s="86"/>
-      <c r="AF54" s="87"/>
+      <c r="AD54" s="92"/>
+      <c r="AE54" s="93"/>
+      <c r="AF54" s="94"/>
       <c r="AG54" s="43"/>
-      <c r="AH54" s="85"/>
-      <c r="AI54" s="86"/>
-      <c r="AJ54" s="87"/>
+      <c r="AH54" s="92"/>
+      <c r="AI54" s="93"/>
+      <c r="AJ54" s="94"/>
       <c r="AK54" s="35"/>
-      <c r="AL54" s="85"/>
-      <c r="AM54" s="86"/>
-      <c r="AN54" s="87"/>
+      <c r="AL54" s="92"/>
+      <c r="AM54" s="93"/>
+      <c r="AN54" s="94"/>
       <c r="AR54" s="13"/>
     </row>
     <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="82"/>
-      <c r="C55" s="83"/>
-      <c r="D55" s="84"/>
+      <c r="B55" s="65"/>
+      <c r="C55" s="66"/>
+      <c r="D55" s="67"/>
       <c r="E55" s="37"/>
-      <c r="F55" s="82" t="s">
+      <c r="F55" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="G55" s="83"/>
-      <c r="H55" s="84"/>
+      <c r="G55" s="66"/>
+      <c r="H55" s="67"/>
       <c r="I55" s="40"/>
-      <c r="J55" s="82" t="s">
+      <c r="J55" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="K55" s="83"/>
-      <c r="L55" s="84"/>
+      <c r="K55" s="66"/>
+      <c r="L55" s="67"/>
       <c r="M55" s="5"/>
-      <c r="N55" s="82"/>
-      <c r="O55" s="83"/>
-      <c r="P55" s="84"/>
+      <c r="N55" s="65"/>
+      <c r="O55" s="66"/>
+      <c r="P55" s="67"/>
       <c r="Q55" s="43"/>
-      <c r="R55" s="82" t="s">
+      <c r="R55" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="S55" s="83"/>
-      <c r="T55" s="84"/>
+      <c r="S55" s="66"/>
+      <c r="T55" s="67"/>
       <c r="U55" s="44"/>
-      <c r="V55" s="85"/>
-      <c r="W55" s="86"/>
-      <c r="X55" s="87"/>
+      <c r="V55" s="92"/>
+      <c r="W55" s="93"/>
+      <c r="X55" s="94"/>
       <c r="Y55" s="44"/>
-      <c r="Z55" s="85"/>
-      <c r="AA55" s="86"/>
-      <c r="AB55" s="87"/>
+      <c r="Z55" s="92"/>
+      <c r="AA55" s="93"/>
+      <c r="AB55" s="94"/>
       <c r="AC55" s="35"/>
-      <c r="AD55" s="82" t="s">
+      <c r="AD55" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="AE55" s="83"/>
-      <c r="AF55" s="84"/>
+      <c r="AE55" s="66"/>
+      <c r="AF55" s="67"/>
       <c r="AG55" s="37"/>
-      <c r="AH55" s="82" t="s">
+      <c r="AH55" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="AI55" s="83"/>
-      <c r="AJ55" s="84"/>
+      <c r="AI55" s="66"/>
+      <c r="AJ55" s="67"/>
       <c r="AK55" s="40"/>
-      <c r="AL55" s="82"/>
-      <c r="AM55" s="83"/>
-      <c r="AN55" s="84"/>
+      <c r="AL55" s="65"/>
+      <c r="AM55" s="66"/>
+      <c r="AN55" s="67"/>
       <c r="AR55" s="13"/>
     </row>
     <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="82"/>
-      <c r="C56" s="83"/>
-      <c r="D56" s="84"/>
+      <c r="B56" s="65"/>
+      <c r="C56" s="66"/>
+      <c r="D56" s="67"/>
       <c r="E56" s="44"/>
-      <c r="F56" s="82" t="s">
+      <c r="F56" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="G56" s="83"/>
-      <c r="H56" s="84"/>
+      <c r="G56" s="66"/>
+      <c r="H56" s="67"/>
       <c r="I56" s="44"/>
-      <c r="J56" s="82" t="s">
+      <c r="J56" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="K56" s="83"/>
-      <c r="L56" s="84"/>
+      <c r="K56" s="66"/>
+      <c r="L56" s="67"/>
       <c r="M56" s="5"/>
-      <c r="N56" s="82"/>
-      <c r="O56" s="83"/>
-      <c r="P56" s="84"/>
+      <c r="N56" s="65"/>
+      <c r="O56" s="66"/>
+      <c r="P56" s="67"/>
       <c r="Q56" s="43"/>
-      <c r="R56" s="82" t="s">
+      <c r="R56" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="S56" s="83"/>
-      <c r="T56" s="84"/>
+      <c r="S56" s="66"/>
+      <c r="T56" s="67"/>
       <c r="U56" s="44"/>
-      <c r="V56" s="82" t="s">
+      <c r="V56" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="W56" s="83"/>
-      <c r="X56" s="84"/>
+      <c r="W56" s="66"/>
+      <c r="X56" s="67"/>
       <c r="Y56" s="50"/>
-      <c r="Z56" s="82"/>
-      <c r="AA56" s="83"/>
-      <c r="AB56" s="84"/>
+      <c r="Z56" s="65"/>
+      <c r="AA56" s="66"/>
+      <c r="AB56" s="67"/>
       <c r="AC56" s="43"/>
-      <c r="AD56" s="82" t="s">
+      <c r="AD56" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="AE56" s="83"/>
-      <c r="AF56" s="84"/>
+      <c r="AE56" s="66"/>
+      <c r="AF56" s="67"/>
       <c r="AG56" s="44"/>
-      <c r="AH56" s="82" t="s">
+      <c r="AH56" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="AI56" s="83"/>
-      <c r="AJ56" s="84"/>
+      <c r="AI56" s="66"/>
+      <c r="AJ56" s="67"/>
       <c r="AK56" s="44"/>
-      <c r="AL56" s="82"/>
-      <c r="AM56" s="83"/>
-      <c r="AN56" s="84"/>
+      <c r="AL56" s="65"/>
+      <c r="AM56" s="66"/>
+      <c r="AN56" s="67"/>
       <c r="AR56" s="13"/>
     </row>
     <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="63"/>
-      <c r="C57" s="64"/>
-      <c r="D57" s="65"/>
+      <c r="B57" s="71"/>
+      <c r="C57" s="72"/>
+      <c r="D57" s="73"/>
       <c r="E57" s="35"/>
-      <c r="F57" s="63"/>
-      <c r="G57" s="64"/>
-      <c r="H57" s="65"/>
+      <c r="F57" s="71"/>
+      <c r="G57" s="72"/>
+      <c r="H57" s="73"/>
       <c r="I57" s="50"/>
-      <c r="J57" s="107" t="s">
+      <c r="J57" s="157" t="s">
         <v>8</v>
       </c>
-      <c r="K57" s="108"/>
-      <c r="L57" s="109"/>
+      <c r="K57" s="158"/>
+      <c r="L57" s="159"/>
       <c r="M57" s="5"/>
-      <c r="N57" s="63"/>
-      <c r="O57" s="64"/>
-      <c r="P57" s="65"/>
+      <c r="N57" s="71"/>
+      <c r="O57" s="72"/>
+      <c r="P57" s="73"/>
       <c r="Q57" s="31"/>
-      <c r="R57" s="63"/>
-      <c r="S57" s="64"/>
-      <c r="T57" s="65"/>
+      <c r="R57" s="71"/>
+      <c r="S57" s="72"/>
+      <c r="T57" s="73"/>
       <c r="U57" s="50"/>
-      <c r="V57" s="63" t="s">
+      <c r="V57" s="71" t="s">
         <v>37</v>
       </c>
-      <c r="W57" s="64"/>
-      <c r="X57" s="65"/>
+      <c r="W57" s="72"/>
+      <c r="X57" s="73"/>
       <c r="Y57" s="50"/>
-      <c r="Z57" s="63"/>
-      <c r="AA57" s="64"/>
-      <c r="AB57" s="65"/>
+      <c r="Z57" s="71"/>
+      <c r="AA57" s="72"/>
+      <c r="AB57" s="73"/>
       <c r="AC57" s="31"/>
-      <c r="AD57" s="63"/>
-      <c r="AE57" s="64"/>
-      <c r="AF57" s="65"/>
+      <c r="AD57" s="71"/>
+      <c r="AE57" s="72"/>
+      <c r="AF57" s="73"/>
       <c r="AG57" s="35"/>
-      <c r="AH57" s="63"/>
-      <c r="AI57" s="64"/>
-      <c r="AJ57" s="65"/>
+      <c r="AH57" s="71"/>
+      <c r="AI57" s="72"/>
+      <c r="AJ57" s="73"/>
       <c r="AK57" s="50"/>
-      <c r="AL57" s="63"/>
-      <c r="AM57" s="64"/>
-      <c r="AN57" s="65"/>
+      <c r="AL57" s="71"/>
+      <c r="AM57" s="72"/>
+      <c r="AN57" s="73"/>
       <c r="AR57" s="13"/>
     </row>
     <row r="58" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5468,265 +5485,265 @@
       <c r="AR58" s="13"/>
     </row>
     <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="66"/>
-      <c r="C59" s="67"/>
+      <c r="B59" s="63"/>
+      <c r="C59" s="64"/>
       <c r="D59" s="57"/>
       <c r="E59" s="50"/>
-      <c r="F59" s="66"/>
-      <c r="G59" s="67"/>
+      <c r="F59" s="63"/>
+      <c r="G59" s="64"/>
       <c r="H59" s="57"/>
       <c r="I59" s="32"/>
-      <c r="J59" s="66"/>
-      <c r="K59" s="67"/>
+      <c r="J59" s="63"/>
+      <c r="K59" s="64"/>
       <c r="L59" s="57"/>
       <c r="M59" s="6"/>
-      <c r="N59" s="68"/>
-      <c r="O59" s="69"/>
+      <c r="N59" s="87"/>
+      <c r="O59" s="88"/>
       <c r="P59" s="34"/>
       <c r="Q59" s="36"/>
-      <c r="R59" s="68"/>
-      <c r="S59" s="69"/>
+      <c r="R59" s="87"/>
+      <c r="S59" s="88"/>
       <c r="T59" s="34"/>
       <c r="U59" s="50"/>
-      <c r="V59" s="68"/>
-      <c r="W59" s="69"/>
+      <c r="V59" s="87"/>
+      <c r="W59" s="88"/>
       <c r="X59" s="34"/>
       <c r="Y59" s="32"/>
-      <c r="Z59" s="68"/>
-      <c r="AA59" s="69"/>
+      <c r="Z59" s="87"/>
+      <c r="AA59" s="88"/>
       <c r="AB59" s="34"/>
       <c r="AC59" s="32"/>
-      <c r="AD59" s="91" t="s">
+      <c r="AD59" s="116" t="s">
         <v>89</v>
       </c>
-      <c r="AE59" s="92"/>
+      <c r="AE59" s="117"/>
       <c r="AF59" s="59" t="s">
         <v>90</v>
       </c>
       <c r="AG59" s="50"/>
-      <c r="AH59" s="68"/>
-      <c r="AI59" s="69"/>
+      <c r="AH59" s="87"/>
+      <c r="AI59" s="88"/>
       <c r="AJ59" s="34"/>
       <c r="AK59" s="32"/>
-      <c r="AL59" s="68"/>
-      <c r="AM59" s="69"/>
+      <c r="AL59" s="87"/>
+      <c r="AM59" s="88"/>
       <c r="AN59" s="34"/>
       <c r="AR59" s="13"/>
     </row>
     <row r="60" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="88"/>
-      <c r="C60" s="89"/>
-      <c r="D60" s="90"/>
+      <c r="B60" s="78"/>
+      <c r="C60" s="79"/>
+      <c r="D60" s="80"/>
       <c r="E60" s="32"/>
-      <c r="F60" s="88"/>
-      <c r="G60" s="89"/>
-      <c r="H60" s="90"/>
+      <c r="F60" s="78"/>
+      <c r="G60" s="79"/>
+      <c r="H60" s="80"/>
       <c r="I60" s="32"/>
-      <c r="J60" s="88"/>
-      <c r="K60" s="89"/>
-      <c r="L60" s="90"/>
+      <c r="J60" s="78"/>
+      <c r="K60" s="79"/>
+      <c r="L60" s="80"/>
       <c r="M60" s="4"/>
-      <c r="N60" s="70"/>
-      <c r="O60" s="71"/>
-      <c r="P60" s="72"/>
+      <c r="N60" s="95"/>
+      <c r="O60" s="96"/>
+      <c r="P60" s="97"/>
       <c r="Q60" s="43"/>
-      <c r="R60" s="70"/>
-      <c r="S60" s="71"/>
-      <c r="T60" s="72"/>
+      <c r="R60" s="95"/>
+      <c r="S60" s="96"/>
+      <c r="T60" s="97"/>
       <c r="U60" s="32"/>
-      <c r="V60" s="70"/>
-      <c r="W60" s="71"/>
-      <c r="X60" s="72"/>
+      <c r="V60" s="95"/>
+      <c r="W60" s="96"/>
+      <c r="X60" s="97"/>
       <c r="Y60" s="32"/>
-      <c r="Z60" s="70"/>
-      <c r="AA60" s="71"/>
-      <c r="AB60" s="72"/>
+      <c r="Z60" s="95"/>
+      <c r="AA60" s="96"/>
+      <c r="AB60" s="97"/>
       <c r="AC60" s="54"/>
-      <c r="AD60" s="70" t="s">
+      <c r="AD60" s="95" t="s">
         <v>103</v>
       </c>
-      <c r="AE60" s="71"/>
-      <c r="AF60" s="72"/>
+      <c r="AE60" s="96"/>
+      <c r="AF60" s="97"/>
       <c r="AG60" s="32"/>
-      <c r="AH60" s="70"/>
-      <c r="AI60" s="71"/>
-      <c r="AJ60" s="72"/>
+      <c r="AH60" s="95"/>
+      <c r="AI60" s="96"/>
+      <c r="AJ60" s="97"/>
       <c r="AK60" s="32"/>
-      <c r="AL60" s="70"/>
-      <c r="AM60" s="71"/>
-      <c r="AN60" s="72"/>
+      <c r="AL60" s="95"/>
+      <c r="AM60" s="96"/>
+      <c r="AN60" s="97"/>
       <c r="AR60" s="13"/>
     </row>
     <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="96"/>
-      <c r="C61" s="97"/>
-      <c r="D61" s="98"/>
+      <c r="B61" s="68"/>
+      <c r="C61" s="69"/>
+      <c r="D61" s="70"/>
       <c r="E61" s="32"/>
-      <c r="F61" s="96"/>
-      <c r="G61" s="97"/>
-      <c r="H61" s="98"/>
+      <c r="F61" s="68"/>
+      <c r="G61" s="69"/>
+      <c r="H61" s="70"/>
       <c r="I61" s="32"/>
-      <c r="J61" s="96"/>
-      <c r="K61" s="97"/>
-      <c r="L61" s="98"/>
+      <c r="J61" s="68"/>
+      <c r="K61" s="69"/>
+      <c r="L61" s="70"/>
       <c r="M61" s="4"/>
-      <c r="N61" s="85"/>
-      <c r="O61" s="86"/>
-      <c r="P61" s="87"/>
+      <c r="N61" s="92"/>
+      <c r="O61" s="93"/>
+      <c r="P61" s="94"/>
       <c r="Q61" s="37"/>
-      <c r="R61" s="85"/>
-      <c r="S61" s="86"/>
-      <c r="T61" s="87"/>
+      <c r="R61" s="92"/>
+      <c r="S61" s="93"/>
+      <c r="T61" s="94"/>
       <c r="U61" s="32"/>
-      <c r="V61" s="85"/>
-      <c r="W61" s="86"/>
-      <c r="X61" s="87"/>
+      <c r="V61" s="92"/>
+      <c r="W61" s="93"/>
+      <c r="X61" s="94"/>
       <c r="Y61" s="32"/>
-      <c r="Z61" s="85"/>
-      <c r="AA61" s="86"/>
-      <c r="AB61" s="87"/>
+      <c r="Z61" s="92"/>
+      <c r="AA61" s="93"/>
+      <c r="AB61" s="94"/>
       <c r="AC61" s="35"/>
-      <c r="AD61" s="85"/>
-      <c r="AE61" s="86"/>
-      <c r="AF61" s="87"/>
+      <c r="AD61" s="92"/>
+      <c r="AE61" s="93"/>
+      <c r="AF61" s="94"/>
       <c r="AG61" s="32"/>
-      <c r="AH61" s="85"/>
-      <c r="AI61" s="86"/>
-      <c r="AJ61" s="87"/>
+      <c r="AH61" s="92"/>
+      <c r="AI61" s="93"/>
+      <c r="AJ61" s="94"/>
       <c r="AK61" s="32"/>
-      <c r="AL61" s="85"/>
-      <c r="AM61" s="86"/>
-      <c r="AN61" s="87"/>
+      <c r="AL61" s="92"/>
+      <c r="AM61" s="93"/>
+      <c r="AN61" s="94"/>
       <c r="AR61" s="13"/>
     </row>
     <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="93"/>
-      <c r="C62" s="94"/>
-      <c r="D62" s="95"/>
+      <c r="B62" s="81"/>
+      <c r="C62" s="82"/>
+      <c r="D62" s="83"/>
       <c r="E62" s="37"/>
-      <c r="F62" s="93"/>
-      <c r="G62" s="94"/>
-      <c r="H62" s="95"/>
+      <c r="F62" s="81"/>
+      <c r="G62" s="82"/>
+      <c r="H62" s="83"/>
       <c r="I62" s="35"/>
-      <c r="J62" s="93"/>
-      <c r="K62" s="94"/>
-      <c r="L62" s="95"/>
+      <c r="J62" s="81"/>
+      <c r="K62" s="82"/>
+      <c r="L62" s="83"/>
       <c r="M62" s="4"/>
-      <c r="N62" s="82"/>
-      <c r="O62" s="83"/>
-      <c r="P62" s="84"/>
+      <c r="N62" s="65"/>
+      <c r="O62" s="66"/>
+      <c r="P62" s="67"/>
       <c r="Q62" s="44"/>
-      <c r="R62" s="93"/>
-      <c r="S62" s="94"/>
-      <c r="T62" s="95"/>
+      <c r="R62" s="81"/>
+      <c r="S62" s="82"/>
+      <c r="T62" s="83"/>
       <c r="U62" s="37"/>
-      <c r="V62" s="93"/>
-      <c r="W62" s="94"/>
-      <c r="X62" s="95"/>
+      <c r="V62" s="81"/>
+      <c r="W62" s="82"/>
+      <c r="X62" s="83"/>
       <c r="Y62" s="35"/>
-      <c r="Z62" s="82"/>
-      <c r="AA62" s="83"/>
-      <c r="AB62" s="84"/>
+      <c r="Z62" s="65"/>
+      <c r="AA62" s="66"/>
+      <c r="AB62" s="67"/>
       <c r="AC62" s="35"/>
-      <c r="AD62" s="93" t="s">
+      <c r="AD62" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="AE62" s="94"/>
-      <c r="AF62" s="95"/>
+      <c r="AE62" s="82"/>
+      <c r="AF62" s="83"/>
       <c r="AG62" s="37"/>
-      <c r="AH62" s="82"/>
-      <c r="AI62" s="83"/>
-      <c r="AJ62" s="84"/>
+      <c r="AH62" s="65"/>
+      <c r="AI62" s="66"/>
+      <c r="AJ62" s="67"/>
       <c r="AK62" s="35"/>
-      <c r="AL62" s="93"/>
-      <c r="AM62" s="94"/>
-      <c r="AN62" s="95"/>
+      <c r="AL62" s="81"/>
+      <c r="AM62" s="82"/>
+      <c r="AN62" s="83"/>
       <c r="AR62" s="13"/>
     </row>
     <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="82"/>
-      <c r="C63" s="83"/>
-      <c r="D63" s="84"/>
+      <c r="B63" s="65"/>
+      <c r="C63" s="66"/>
+      <c r="D63" s="67"/>
       <c r="E63" s="44"/>
-      <c r="F63" s="82"/>
-      <c r="G63" s="83"/>
-      <c r="H63" s="84"/>
+      <c r="F63" s="65"/>
+      <c r="G63" s="66"/>
+      <c r="H63" s="67"/>
       <c r="I63" s="40"/>
-      <c r="J63" s="82"/>
-      <c r="K63" s="83"/>
-      <c r="L63" s="84"/>
+      <c r="J63" s="65"/>
+      <c r="K63" s="66"/>
+      <c r="L63" s="67"/>
       <c r="M63" s="5"/>
-      <c r="N63" s="82"/>
-      <c r="O63" s="83"/>
-      <c r="P63" s="84"/>
+      <c r="N63" s="65"/>
+      <c r="O63" s="66"/>
+      <c r="P63" s="67"/>
       <c r="Q63" s="44"/>
-      <c r="R63" s="82"/>
-      <c r="S63" s="83"/>
-      <c r="T63" s="84"/>
+      <c r="R63" s="65"/>
+      <c r="S63" s="66"/>
+      <c r="T63" s="67"/>
       <c r="U63" s="44"/>
-      <c r="V63" s="82"/>
-      <c r="W63" s="83"/>
-      <c r="X63" s="84"/>
+      <c r="V63" s="65"/>
+      <c r="W63" s="66"/>
+      <c r="X63" s="67"/>
       <c r="Y63" s="40"/>
-      <c r="Z63" s="82"/>
-      <c r="AA63" s="83"/>
-      <c r="AB63" s="84"/>
+      <c r="Z63" s="65"/>
+      <c r="AA63" s="66"/>
+      <c r="AB63" s="67"/>
       <c r="AC63" s="40"/>
-      <c r="AD63" s="82" t="s">
+      <c r="AD63" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="AE63" s="83"/>
-      <c r="AF63" s="84"/>
+      <c r="AE63" s="66"/>
+      <c r="AF63" s="67"/>
       <c r="AG63" s="44"/>
-      <c r="AH63" s="82"/>
-      <c r="AI63" s="83"/>
-      <c r="AJ63" s="84"/>
+      <c r="AH63" s="65"/>
+      <c r="AI63" s="66"/>
+      <c r="AJ63" s="67"/>
       <c r="AK63" s="40"/>
-      <c r="AL63" s="82"/>
-      <c r="AM63" s="83"/>
-      <c r="AN63" s="84"/>
+      <c r="AL63" s="65"/>
+      <c r="AM63" s="66"/>
+      <c r="AN63" s="67"/>
       <c r="AR63" s="13"/>
     </row>
     <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="63"/>
-      <c r="C64" s="64"/>
-      <c r="D64" s="65"/>
+      <c r="B64" s="71"/>
+      <c r="C64" s="72"/>
+      <c r="D64" s="73"/>
       <c r="E64" s="35"/>
-      <c r="F64" s="63"/>
-      <c r="G64" s="64"/>
-      <c r="H64" s="65"/>
+      <c r="F64" s="71"/>
+      <c r="G64" s="72"/>
+      <c r="H64" s="73"/>
       <c r="I64" s="50"/>
-      <c r="J64" s="63"/>
-      <c r="K64" s="64"/>
-      <c r="L64" s="65"/>
+      <c r="J64" s="71"/>
+      <c r="K64" s="72"/>
+      <c r="L64" s="73"/>
       <c r="M64" s="5"/>
-      <c r="N64" s="63"/>
-      <c r="O64" s="64"/>
-      <c r="P64" s="65"/>
+      <c r="N64" s="71"/>
+      <c r="O64" s="72"/>
+      <c r="P64" s="73"/>
       <c r="Q64" s="50"/>
-      <c r="R64" s="63"/>
-      <c r="S64" s="64"/>
-      <c r="T64" s="65"/>
+      <c r="R64" s="71"/>
+      <c r="S64" s="72"/>
+      <c r="T64" s="73"/>
       <c r="U64" s="35"/>
-      <c r="V64" s="63"/>
-      <c r="W64" s="64"/>
-      <c r="X64" s="65"/>
+      <c r="V64" s="71"/>
+      <c r="W64" s="72"/>
+      <c r="X64" s="73"/>
       <c r="Y64" s="50"/>
-      <c r="Z64" s="63"/>
-      <c r="AA64" s="64"/>
-      <c r="AB64" s="65"/>
+      <c r="Z64" s="71"/>
+      <c r="AA64" s="72"/>
+      <c r="AB64" s="73"/>
       <c r="AC64" s="50"/>
-      <c r="AD64" s="63"/>
-      <c r="AE64" s="64"/>
-      <c r="AF64" s="65"/>
+      <c r="AD64" s="71"/>
+      <c r="AE64" s="72"/>
+      <c r="AF64" s="73"/>
       <c r="AG64" s="35"/>
-      <c r="AH64" s="63"/>
-      <c r="AI64" s="64"/>
-      <c r="AJ64" s="65"/>
+      <c r="AH64" s="71"/>
+      <c r="AI64" s="72"/>
+      <c r="AJ64" s="73"/>
       <c r="AK64" s="50"/>
-      <c r="AL64" s="63"/>
-      <c r="AM64" s="64"/>
-      <c r="AN64" s="65"/>
+      <c r="AL64" s="71"/>
+      <c r="AM64" s="72"/>
+      <c r="AN64" s="73"/>
       <c r="AR64" s="13"/>
     </row>
     <row r="65" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5777,48 +5794,48 @@
     </row>
     <row r="66" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="12"/>
-      <c r="B66" s="66"/>
-      <c r="C66" s="67"/>
+      <c r="B66" s="63"/>
+      <c r="C66" s="64"/>
       <c r="D66" s="57"/>
       <c r="E66" s="36"/>
-      <c r="F66" s="66"/>
-      <c r="G66" s="67"/>
+      <c r="F66" s="63"/>
+      <c r="G66" s="64"/>
       <c r="H66" s="57"/>
       <c r="I66" s="32"/>
-      <c r="J66" s="66"/>
-      <c r="K66" s="67"/>
+      <c r="J66" s="63"/>
+      <c r="K66" s="64"/>
       <c r="L66" s="57"/>
       <c r="M66" s="6"/>
-      <c r="N66" s="68"/>
-      <c r="O66" s="69"/>
+      <c r="N66" s="87"/>
+      <c r="O66" s="88"/>
       <c r="P66" s="34"/>
       <c r="Q66" s="36"/>
-      <c r="R66" s="68"/>
-      <c r="S66" s="69"/>
+      <c r="R66" s="87"/>
+      <c r="S66" s="88"/>
       <c r="T66" s="34"/>
       <c r="U66" s="36"/>
-      <c r="V66" s="105" t="s">
+      <c r="V66" s="114" t="s">
         <v>99</v>
       </c>
-      <c r="W66" s="106"/>
+      <c r="W66" s="115"/>
       <c r="X66" s="60"/>
       <c r="Y66" s="36"/>
-      <c r="Z66" s="91" t="s">
+      <c r="Z66" s="116" t="s">
         <v>99</v>
       </c>
-      <c r="AA66" s="92"/>
+      <c r="AA66" s="117"/>
       <c r="AB66" s="59"/>
       <c r="AC66" s="36"/>
-      <c r="AD66" s="68"/>
-      <c r="AE66" s="69"/>
+      <c r="AD66" s="87"/>
+      <c r="AE66" s="88"/>
       <c r="AF66" s="34"/>
       <c r="AG66" s="36"/>
-      <c r="AH66" s="68"/>
-      <c r="AI66" s="69"/>
+      <c r="AH66" s="87"/>
+      <c r="AI66" s="88"/>
       <c r="AJ66" s="34"/>
       <c r="AK66" s="32"/>
-      <c r="AL66" s="68"/>
-      <c r="AM66" s="69"/>
+      <c r="AL66" s="87"/>
+      <c r="AM66" s="88"/>
       <c r="AN66" s="34"/>
       <c r="AO66" s="17"/>
       <c r="AP66" s="12"/>
@@ -5827,49 +5844,49 @@
     </row>
     <row r="67" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="12"/>
-      <c r="B67" s="88"/>
-      <c r="C67" s="89"/>
-      <c r="D67" s="90"/>
+      <c r="B67" s="78"/>
+      <c r="C67" s="79"/>
+      <c r="D67" s="80"/>
       <c r="E67" s="36"/>
-      <c r="F67" s="88"/>
-      <c r="G67" s="89"/>
-      <c r="H67" s="90"/>
+      <c r="F67" s="78"/>
+      <c r="G67" s="79"/>
+      <c r="H67" s="80"/>
       <c r="I67" s="54"/>
-      <c r="J67" s="88"/>
-      <c r="K67" s="89"/>
-      <c r="L67" s="90"/>
+      <c r="J67" s="78"/>
+      <c r="K67" s="79"/>
+      <c r="L67" s="80"/>
       <c r="M67" s="4"/>
-      <c r="N67" s="70"/>
-      <c r="O67" s="71"/>
-      <c r="P67" s="72"/>
+      <c r="N67" s="95"/>
+      <c r="O67" s="96"/>
+      <c r="P67" s="97"/>
       <c r="Q67" s="37"/>
-      <c r="R67" s="70"/>
-      <c r="S67" s="71"/>
-      <c r="T67" s="72"/>
+      <c r="R67" s="95"/>
+      <c r="S67" s="96"/>
+      <c r="T67" s="97"/>
       <c r="U67" s="36"/>
-      <c r="V67" s="151" t="s">
+      <c r="V67" s="118" t="s">
         <v>100</v>
       </c>
-      <c r="W67" s="152"/>
-      <c r="X67" s="153"/>
+      <c r="W67" s="119"/>
+      <c r="X67" s="120"/>
       <c r="Y67" s="36"/>
-      <c r="Z67" s="70" t="s">
+      <c r="Z67" s="95" t="s">
         <v>100</v>
       </c>
-      <c r="AA67" s="71"/>
-      <c r="AB67" s="72"/>
+      <c r="AA67" s="96"/>
+      <c r="AB67" s="97"/>
       <c r="AC67" s="36"/>
-      <c r="AD67" s="70"/>
-      <c r="AE67" s="71"/>
-      <c r="AF67" s="72"/>
+      <c r="AD67" s="95"/>
+      <c r="AE67" s="96"/>
+      <c r="AF67" s="97"/>
       <c r="AG67" s="36"/>
-      <c r="AH67" s="70"/>
-      <c r="AI67" s="71"/>
-      <c r="AJ67" s="72"/>
+      <c r="AH67" s="95"/>
+      <c r="AI67" s="96"/>
+      <c r="AJ67" s="97"/>
       <c r="AK67" s="54"/>
-      <c r="AL67" s="70"/>
-      <c r="AM67" s="71"/>
-      <c r="AN67" s="72"/>
+      <c r="AL67" s="95"/>
+      <c r="AM67" s="96"/>
+      <c r="AN67" s="97"/>
       <c r="AO67" s="17"/>
       <c r="AP67" s="12"/>
       <c r="AQ67" s="12"/>
@@ -5877,47 +5894,47 @@
     </row>
     <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="12"/>
-      <c r="B68" s="96"/>
-      <c r="C68" s="97"/>
-      <c r="D68" s="98"/>
+      <c r="B68" s="68"/>
+      <c r="C68" s="69"/>
+      <c r="D68" s="70"/>
       <c r="E68" s="43"/>
-      <c r="F68" s="96"/>
-      <c r="G68" s="97"/>
-      <c r="H68" s="98"/>
+      <c r="F68" s="68"/>
+      <c r="G68" s="69"/>
+      <c r="H68" s="70"/>
       <c r="I68" s="35"/>
-      <c r="J68" s="96"/>
-      <c r="K68" s="97"/>
-      <c r="L68" s="98"/>
+      <c r="J68" s="68"/>
+      <c r="K68" s="69"/>
+      <c r="L68" s="70"/>
       <c r="M68" s="4"/>
-      <c r="N68" s="85"/>
-      <c r="O68" s="86"/>
-      <c r="P68" s="87"/>
+      <c r="N68" s="92"/>
+      <c r="O68" s="93"/>
+      <c r="P68" s="94"/>
       <c r="Q68" s="36"/>
-      <c r="R68" s="85"/>
-      <c r="S68" s="86"/>
-      <c r="T68" s="87"/>
+      <c r="R68" s="92"/>
+      <c r="S68" s="93"/>
+      <c r="T68" s="94"/>
       <c r="U68" s="43"/>
-      <c r="V68" s="129" t="s">
+      <c r="V68" s="111" t="s">
         <v>92</v>
       </c>
-      <c r="W68" s="130"/>
-      <c r="X68" s="157"/>
+      <c r="W68" s="112"/>
+      <c r="X68" s="113"/>
       <c r="Y68" s="43"/>
-      <c r="Z68" s="85"/>
-      <c r="AA68" s="86"/>
-      <c r="AB68" s="87"/>
+      <c r="Z68" s="92"/>
+      <c r="AA68" s="93"/>
+      <c r="AB68" s="94"/>
       <c r="AC68" s="35"/>
-      <c r="AD68" s="85"/>
-      <c r="AE68" s="86"/>
-      <c r="AF68" s="87"/>
+      <c r="AD68" s="92"/>
+      <c r="AE68" s="93"/>
+      <c r="AF68" s="94"/>
       <c r="AG68" s="43"/>
-      <c r="AH68" s="85"/>
-      <c r="AI68" s="86"/>
-      <c r="AJ68" s="87"/>
+      <c r="AH68" s="92"/>
+      <c r="AI68" s="93"/>
+      <c r="AJ68" s="94"/>
       <c r="AK68" s="35"/>
-      <c r="AL68" s="85"/>
-      <c r="AM68" s="86"/>
-      <c r="AN68" s="87"/>
+      <c r="AL68" s="92"/>
+      <c r="AM68" s="93"/>
+      <c r="AN68" s="94"/>
       <c r="AO68" s="17"/>
       <c r="AP68" s="27" t="s">
         <v>32</v>
@@ -5927,49 +5944,49 @@
     </row>
     <row r="69" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="12"/>
-      <c r="B69" s="82"/>
-      <c r="C69" s="83"/>
-      <c r="D69" s="84"/>
+      <c r="B69" s="65"/>
+      <c r="C69" s="66"/>
+      <c r="D69" s="67"/>
       <c r="E69" s="37"/>
-      <c r="F69" s="82"/>
-      <c r="G69" s="83"/>
-      <c r="H69" s="84"/>
+      <c r="F69" s="65"/>
+      <c r="G69" s="66"/>
+      <c r="H69" s="67"/>
       <c r="I69" s="37"/>
-      <c r="J69" s="82"/>
-      <c r="K69" s="83"/>
-      <c r="L69" s="84"/>
+      <c r="J69" s="65"/>
+      <c r="K69" s="66"/>
+      <c r="L69" s="67"/>
       <c r="M69" s="4"/>
-      <c r="N69" s="82"/>
-      <c r="O69" s="83"/>
-      <c r="P69" s="84"/>
+      <c r="N69" s="65"/>
+      <c r="O69" s="66"/>
+      <c r="P69" s="67"/>
       <c r="Q69" s="43"/>
-      <c r="R69" s="82"/>
-      <c r="S69" s="83"/>
-      <c r="T69" s="84"/>
+      <c r="R69" s="65"/>
+      <c r="S69" s="66"/>
+      <c r="T69" s="67"/>
       <c r="U69" s="37"/>
-      <c r="V69" s="154" t="s">
+      <c r="V69" s="121" t="s">
         <v>105</v>
       </c>
-      <c r="W69" s="155"/>
-      <c r="X69" s="156"/>
+      <c r="W69" s="122"/>
+      <c r="X69" s="123"/>
       <c r="Y69" s="35"/>
-      <c r="Z69" s="82" t="s">
+      <c r="Z69" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="AA69" s="83"/>
-      <c r="AB69" s="84"/>
+      <c r="AA69" s="66"/>
+      <c r="AB69" s="67"/>
       <c r="AC69" s="43"/>
-      <c r="AD69" s="82"/>
-      <c r="AE69" s="83"/>
-      <c r="AF69" s="84"/>
+      <c r="AD69" s="65"/>
+      <c r="AE69" s="66"/>
+      <c r="AF69" s="67"/>
       <c r="AG69" s="37"/>
-      <c r="AH69" s="93"/>
-      <c r="AI69" s="94"/>
-      <c r="AJ69" s="95"/>
+      <c r="AH69" s="81"/>
+      <c r="AI69" s="82"/>
+      <c r="AJ69" s="83"/>
       <c r="AK69" s="37"/>
-      <c r="AL69" s="82"/>
-      <c r="AM69" s="83"/>
-      <c r="AN69" s="84"/>
+      <c r="AL69" s="65"/>
+      <c r="AM69" s="66"/>
+      <c r="AN69" s="67"/>
       <c r="AO69" s="12"/>
       <c r="AP69" s="27" t="s">
         <v>33</v>
@@ -5979,49 +5996,49 @@
     </row>
     <row r="70" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="12"/>
-      <c r="B70" s="82"/>
-      <c r="C70" s="83"/>
-      <c r="D70" s="84"/>
+      <c r="B70" s="65"/>
+      <c r="C70" s="66"/>
+      <c r="D70" s="67"/>
       <c r="E70" s="44"/>
-      <c r="F70" s="82"/>
-      <c r="G70" s="83"/>
-      <c r="H70" s="84"/>
+      <c r="F70" s="65"/>
+      <c r="G70" s="66"/>
+      <c r="H70" s="67"/>
       <c r="I70" s="44"/>
-      <c r="J70" s="82"/>
-      <c r="K70" s="83"/>
-      <c r="L70" s="84"/>
+      <c r="J70" s="65"/>
+      <c r="K70" s="66"/>
+      <c r="L70" s="67"/>
       <c r="M70" s="9"/>
-      <c r="N70" s="82"/>
-      <c r="O70" s="83"/>
-      <c r="P70" s="84"/>
+      <c r="N70" s="65"/>
+      <c r="O70" s="66"/>
+      <c r="P70" s="67"/>
       <c r="Q70" s="50"/>
-      <c r="R70" s="82"/>
-      <c r="S70" s="83"/>
-      <c r="T70" s="84"/>
+      <c r="R70" s="65"/>
+      <c r="S70" s="66"/>
+      <c r="T70" s="67"/>
       <c r="U70" s="44"/>
-      <c r="V70" s="154" t="s">
+      <c r="V70" s="121" t="s">
         <v>106</v>
       </c>
-      <c r="W70" s="155"/>
-      <c r="X70" s="156"/>
+      <c r="W70" s="122"/>
+      <c r="X70" s="123"/>
       <c r="Y70" s="40"/>
-      <c r="Z70" s="82" t="s">
+      <c r="Z70" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="AA70" s="83"/>
-      <c r="AB70" s="84"/>
+      <c r="AA70" s="66"/>
+      <c r="AB70" s="67"/>
       <c r="AC70" s="44"/>
-      <c r="AD70" s="82"/>
-      <c r="AE70" s="83"/>
-      <c r="AF70" s="84"/>
+      <c r="AD70" s="65"/>
+      <c r="AE70" s="66"/>
+      <c r="AF70" s="67"/>
       <c r="AG70" s="44"/>
-      <c r="AH70" s="82"/>
-      <c r="AI70" s="83"/>
-      <c r="AJ70" s="84"/>
+      <c r="AH70" s="65"/>
+      <c r="AI70" s="66"/>
+      <c r="AJ70" s="67"/>
       <c r="AK70" s="44"/>
-      <c r="AL70" s="82"/>
-      <c r="AM70" s="83"/>
-      <c r="AN70" s="84"/>
+      <c r="AL70" s="65"/>
+      <c r="AM70" s="66"/>
+      <c r="AN70" s="67"/>
       <c r="AO70" s="12"/>
       <c r="AP70" s="27" t="s">
         <v>34</v>
@@ -6031,49 +6048,49 @@
     </row>
     <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="12"/>
-      <c r="B71" s="63"/>
-      <c r="C71" s="64"/>
-      <c r="D71" s="65"/>
+      <c r="B71" s="71"/>
+      <c r="C71" s="72"/>
+      <c r="D71" s="73"/>
       <c r="E71" s="44"/>
-      <c r="F71" s="63"/>
-      <c r="G71" s="64"/>
-      <c r="H71" s="65"/>
+      <c r="F71" s="71"/>
+      <c r="G71" s="72"/>
+      <c r="H71" s="73"/>
       <c r="I71" s="44"/>
-      <c r="J71" s="63"/>
-      <c r="K71" s="64"/>
-      <c r="L71" s="65"/>
+      <c r="J71" s="71"/>
+      <c r="K71" s="72"/>
+      <c r="L71" s="73"/>
       <c r="M71" s="9"/>
-      <c r="N71" s="63"/>
-      <c r="O71" s="64"/>
-      <c r="P71" s="65"/>
+      <c r="N71" s="71"/>
+      <c r="O71" s="72"/>
+      <c r="P71" s="73"/>
       <c r="Q71" s="50"/>
-      <c r="R71" s="63"/>
-      <c r="S71" s="64"/>
-      <c r="T71" s="65"/>
+      <c r="R71" s="71"/>
+      <c r="S71" s="72"/>
+      <c r="T71" s="73"/>
       <c r="U71" s="44"/>
-      <c r="V71" s="144" t="s">
+      <c r="V71" s="126" t="s">
         <v>107</v>
       </c>
-      <c r="W71" s="145"/>
-      <c r="X71" s="146"/>
+      <c r="W71" s="127"/>
+      <c r="X71" s="128"/>
       <c r="Y71" s="44"/>
-      <c r="Z71" s="79" t="s">
+      <c r="Z71" s="89" t="s">
         <v>96</v>
       </c>
-      <c r="AA71" s="80"/>
-      <c r="AB71" s="81"/>
+      <c r="AA71" s="90"/>
+      <c r="AB71" s="91"/>
       <c r="AC71" s="50"/>
-      <c r="AD71" s="63"/>
-      <c r="AE71" s="64"/>
-      <c r="AF71" s="65"/>
+      <c r="AD71" s="71"/>
+      <c r="AE71" s="72"/>
+      <c r="AF71" s="73"/>
       <c r="AG71" s="44"/>
-      <c r="AH71" s="63"/>
-      <c r="AI71" s="64"/>
-      <c r="AJ71" s="65"/>
+      <c r="AH71" s="71"/>
+      <c r="AI71" s="72"/>
+      <c r="AJ71" s="73"/>
       <c r="AK71" s="44"/>
-      <c r="AL71" s="63"/>
-      <c r="AM71" s="64"/>
-      <c r="AN71" s="65"/>
+      <c r="AL71" s="71"/>
+      <c r="AM71" s="72"/>
+      <c r="AN71" s="73"/>
       <c r="AO71" s="12"/>
       <c r="AP71" s="27" t="s">
         <v>35</v>
@@ -6141,23 +6158,23 @@
       <c r="K73" s="33"/>
       <c r="L73" s="33"/>
       <c r="M73" s="14"/>
-      <c r="N73" s="116" t="s">
+      <c r="N73" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="O73" s="116"/>
-      <c r="P73" s="116"/>
-      <c r="Q73" s="116"/>
-      <c r="R73" s="116"/>
-      <c r="S73" s="116"/>
-      <c r="T73" s="116"/>
-      <c r="U73" s="116"/>
-      <c r="V73" s="116"/>
-      <c r="W73" s="116"/>
-      <c r="X73" s="116"/>
-      <c r="Y73" s="116"/>
-      <c r="Z73" s="116"/>
-      <c r="AA73" s="116"/>
-      <c r="AB73" s="116"/>
+      <c r="O73" s="105"/>
+      <c r="P73" s="105"/>
+      <c r="Q73" s="105"/>
+      <c r="R73" s="105"/>
+      <c r="S73" s="105"/>
+      <c r="T73" s="105"/>
+      <c r="U73" s="105"/>
+      <c r="V73" s="105"/>
+      <c r="W73" s="105"/>
+      <c r="X73" s="105"/>
+      <c r="Y73" s="105"/>
+      <c r="Z73" s="105"/>
+      <c r="AA73" s="105"/>
+      <c r="AB73" s="105"/>
       <c r="AD73" s="40"/>
       <c r="AE73" s="33"/>
       <c r="AF73" s="33"/>
@@ -6188,21 +6205,21 @@
       <c r="K74" s="33"/>
       <c r="L74" s="33"/>
       <c r="M74" s="14"/>
-      <c r="N74" s="116"/>
-      <c r="O74" s="116"/>
-      <c r="P74" s="116"/>
-      <c r="Q74" s="116"/>
-      <c r="R74" s="116"/>
-      <c r="S74" s="116"/>
-      <c r="T74" s="116"/>
-      <c r="U74" s="116"/>
-      <c r="V74" s="116"/>
-      <c r="W74" s="116"/>
-      <c r="X74" s="116"/>
-      <c r="Y74" s="116"/>
-      <c r="Z74" s="116"/>
-      <c r="AA74" s="116"/>
-      <c r="AB74" s="116"/>
+      <c r="N74" s="105"/>
+      <c r="O74" s="105"/>
+      <c r="P74" s="105"/>
+      <c r="Q74" s="105"/>
+      <c r="R74" s="105"/>
+      <c r="S74" s="105"/>
+      <c r="T74" s="105"/>
+      <c r="U74" s="105"/>
+      <c r="V74" s="105"/>
+      <c r="W74" s="105"/>
+      <c r="X74" s="105"/>
+      <c r="Y74" s="105"/>
+      <c r="Z74" s="105"/>
+      <c r="AA74" s="105"/>
+      <c r="AB74" s="105"/>
       <c r="AC74" s="21"/>
       <c r="AD74" s="33"/>
       <c r="AE74" s="33"/>
@@ -6222,68 +6239,68 @@
     </row>
     <row r="75" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="12"/>
-      <c r="B75" s="105" t="s">
+      <c r="B75" s="114" t="s">
         <v>58</v>
       </c>
-      <c r="C75" s="106"/>
+      <c r="C75" s="115"/>
       <c r="D75" s="60"/>
       <c r="E75" s="32"/>
-      <c r="F75" s="105" t="s">
+      <c r="F75" s="114" t="s">
         <v>52</v>
       </c>
-      <c r="G75" s="106"/>
+      <c r="G75" s="115"/>
       <c r="H75" s="60"/>
       <c r="I75" s="32"/>
-      <c r="J75" s="66"/>
-      <c r="K75" s="67"/>
+      <c r="J75" s="63"/>
+      <c r="K75" s="64"/>
       <c r="L75" s="57"/>
       <c r="M75" s="14"/>
-      <c r="N75" s="68"/>
-      <c r="O75" s="69"/>
+      <c r="N75" s="87"/>
+      <c r="O75" s="88"/>
       <c r="P75" s="34"/>
       <c r="Q75" s="44"/>
-      <c r="R75" s="68" t="s">
+      <c r="R75" s="87" t="s">
         <v>78</v>
       </c>
-      <c r="S75" s="69"/>
+      <c r="S75" s="88"/>
       <c r="T75" s="34" t="s">
         <v>64</v>
       </c>
       <c r="U75" s="36"/>
-      <c r="V75" s="68" t="s">
+      <c r="V75" s="87" t="s">
         <v>78</v>
       </c>
-      <c r="W75" s="69"/>
+      <c r="W75" s="88"/>
       <c r="X75" s="34" t="s">
         <v>64</v>
       </c>
       <c r="Y75" s="32"/>
-      <c r="Z75" s="68" t="s">
+      <c r="Z75" s="87" t="s">
         <v>78</v>
       </c>
-      <c r="AA75" s="69"/>
+      <c r="AA75" s="88"/>
       <c r="AB75" s="34" t="s">
         <v>64</v>
       </c>
       <c r="AC75" s="32"/>
-      <c r="AD75" s="68" t="s">
+      <c r="AD75" s="87" t="s">
         <v>78</v>
       </c>
-      <c r="AE75" s="69"/>
+      <c r="AE75" s="88"/>
       <c r="AF75" s="34" t="s">
         <v>64</v>
       </c>
       <c r="AG75" s="32"/>
-      <c r="AH75" s="68" t="s">
+      <c r="AH75" s="87" t="s">
         <v>78</v>
       </c>
-      <c r="AI75" s="69"/>
+      <c r="AI75" s="88"/>
       <c r="AJ75" s="34" t="s">
         <v>64</v>
       </c>
       <c r="AK75" s="32"/>
-      <c r="AL75" s="68"/>
-      <c r="AM75" s="69"/>
+      <c r="AL75" s="87"/>
+      <c r="AM75" s="88"/>
       <c r="AN75" s="34"/>
       <c r="AO75" s="16"/>
       <c r="AP75" s="29"/>
@@ -6292,59 +6309,59 @@
     </row>
     <row r="76" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="12"/>
-      <c r="B76" s="99" t="s">
+      <c r="B76" s="160" t="s">
         <v>92</v>
       </c>
-      <c r="C76" s="100"/>
-      <c r="D76" s="101"/>
+      <c r="C76" s="161"/>
+      <c r="D76" s="162"/>
       <c r="E76" s="32"/>
-      <c r="F76" s="99" t="s">
+      <c r="F76" s="160" t="s">
         <v>92</v>
       </c>
-      <c r="G76" s="100"/>
-      <c r="H76" s="101"/>
+      <c r="G76" s="161"/>
+      <c r="H76" s="162"/>
       <c r="I76" s="32"/>
-      <c r="J76" s="88"/>
-      <c r="K76" s="89"/>
-      <c r="L76" s="90"/>
+      <c r="J76" s="78"/>
+      <c r="K76" s="79"/>
+      <c r="L76" s="80"/>
       <c r="M76" s="4"/>
-      <c r="N76" s="70"/>
-      <c r="O76" s="71"/>
-      <c r="P76" s="72"/>
+      <c r="N76" s="95"/>
+      <c r="O76" s="96"/>
+      <c r="P76" s="97"/>
       <c r="Q76" s="44"/>
-      <c r="R76" s="70" t="s">
+      <c r="R76" s="95" t="s">
         <v>79</v>
       </c>
-      <c r="S76" s="71"/>
-      <c r="T76" s="72"/>
+      <c r="S76" s="96"/>
+      <c r="T76" s="97"/>
       <c r="U76" s="32"/>
-      <c r="V76" s="70" t="s">
+      <c r="V76" s="95" t="s">
         <v>79</v>
       </c>
-      <c r="W76" s="71"/>
-      <c r="X76" s="72"/>
+      <c r="W76" s="96"/>
+      <c r="X76" s="97"/>
       <c r="Y76" s="32"/>
-      <c r="Z76" s="70" t="s">
+      <c r="Z76" s="95" t="s">
         <v>79</v>
       </c>
-      <c r="AA76" s="71"/>
-      <c r="AB76" s="72"/>
+      <c r="AA76" s="96"/>
+      <c r="AB76" s="97"/>
       <c r="AC76" s="35"/>
-      <c r="AD76" s="70" t="s">
+      <c r="AD76" s="95" t="s">
         <v>79</v>
       </c>
-      <c r="AE76" s="71"/>
-      <c r="AF76" s="72"/>
+      <c r="AE76" s="96"/>
+      <c r="AF76" s="97"/>
       <c r="AG76" s="32"/>
-      <c r="AH76" s="70" t="s">
+      <c r="AH76" s="95" t="s">
         <v>79</v>
       </c>
-      <c r="AI76" s="71"/>
-      <c r="AJ76" s="72"/>
+      <c r="AI76" s="96"/>
+      <c r="AJ76" s="97"/>
       <c r="AK76" s="32"/>
-      <c r="AL76" s="70"/>
-      <c r="AM76" s="71"/>
-      <c r="AN76" s="72"/>
+      <c r="AL76" s="95"/>
+      <c r="AM76" s="96"/>
+      <c r="AN76" s="97"/>
       <c r="AO76" s="12"/>
       <c r="AP76" s="29"/>
       <c r="AQ76" s="26"/>
@@ -6352,49 +6369,49 @@
     </row>
     <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="16"/>
-      <c r="B77" s="102" t="s">
+      <c r="B77" s="154" t="s">
         <v>60</v>
       </c>
-      <c r="C77" s="103"/>
-      <c r="D77" s="104"/>
+      <c r="C77" s="155"/>
+      <c r="D77" s="156"/>
       <c r="E77" s="32"/>
-      <c r="F77" s="102" t="s">
+      <c r="F77" s="154" t="s">
         <v>60</v>
       </c>
-      <c r="G77" s="103"/>
-      <c r="H77" s="104"/>
+      <c r="G77" s="155"/>
+      <c r="H77" s="156"/>
       <c r="I77" s="32"/>
-      <c r="J77" s="96"/>
-      <c r="K77" s="97"/>
-      <c r="L77" s="98"/>
+      <c r="J77" s="68"/>
+      <c r="K77" s="69"/>
+      <c r="L77" s="70"/>
       <c r="M77" s="4"/>
-      <c r="N77" s="85"/>
-      <c r="O77" s="86"/>
-      <c r="P77" s="87"/>
+      <c r="N77" s="92"/>
+      <c r="O77" s="93"/>
+      <c r="P77" s="94"/>
       <c r="Q77" s="44"/>
-      <c r="R77" s="85"/>
-      <c r="S77" s="86"/>
-      <c r="T77" s="87"/>
+      <c r="R77" s="92"/>
+      <c r="S77" s="93"/>
+      <c r="T77" s="94"/>
       <c r="U77" s="31"/>
-      <c r="V77" s="85"/>
-      <c r="W77" s="86"/>
-      <c r="X77" s="87"/>
+      <c r="V77" s="92"/>
+      <c r="W77" s="93"/>
+      <c r="X77" s="94"/>
       <c r="Y77" s="32"/>
-      <c r="Z77" s="85"/>
-      <c r="AA77" s="86"/>
-      <c r="AB77" s="87"/>
+      <c r="Z77" s="92"/>
+      <c r="AA77" s="93"/>
+      <c r="AB77" s="94"/>
       <c r="AC77" s="31"/>
-      <c r="AD77" s="85"/>
-      <c r="AE77" s="86"/>
-      <c r="AF77" s="87"/>
+      <c r="AD77" s="92"/>
+      <c r="AE77" s="93"/>
+      <c r="AF77" s="94"/>
       <c r="AG77" s="32"/>
-      <c r="AH77" s="85"/>
-      <c r="AI77" s="86"/>
-      <c r="AJ77" s="87"/>
+      <c r="AH77" s="92"/>
+      <c r="AI77" s="93"/>
+      <c r="AJ77" s="94"/>
       <c r="AK77" s="32"/>
-      <c r="AL77" s="85"/>
-      <c r="AM77" s="86"/>
-      <c r="AN77" s="87"/>
+      <c r="AL77" s="92"/>
+      <c r="AM77" s="93"/>
+      <c r="AN77" s="94"/>
       <c r="AO77" s="12"/>
       <c r="AP77" s="29"/>
       <c r="AQ77" s="26"/>
@@ -6402,59 +6419,59 @@
     </row>
     <row r="78" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="16"/>
-      <c r="B78" s="76" t="s">
+      <c r="B78" s="145" t="s">
         <v>93</v>
       </c>
-      <c r="C78" s="77"/>
-      <c r="D78" s="78"/>
+      <c r="C78" s="146"/>
+      <c r="D78" s="147"/>
       <c r="E78" s="32"/>
-      <c r="F78" s="76" t="s">
+      <c r="F78" s="145" t="s">
         <v>93</v>
       </c>
-      <c r="G78" s="77"/>
-      <c r="H78" s="78"/>
+      <c r="G78" s="146"/>
+      <c r="H78" s="147"/>
       <c r="I78" s="43"/>
-      <c r="J78" s="93"/>
-      <c r="K78" s="94"/>
-      <c r="L78" s="95"/>
+      <c r="J78" s="81"/>
+      <c r="K78" s="82"/>
+      <c r="L78" s="83"/>
       <c r="M78" s="5"/>
-      <c r="N78" s="93"/>
-      <c r="O78" s="94"/>
-      <c r="P78" s="95"/>
+      <c r="N78" s="81"/>
+      <c r="O78" s="82"/>
+      <c r="P78" s="83"/>
       <c r="Q78" s="44"/>
-      <c r="R78" s="93" t="s">
+      <c r="R78" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="S78" s="94"/>
-      <c r="T78" s="95"/>
+      <c r="S78" s="82"/>
+      <c r="T78" s="83"/>
       <c r="U78" s="32"/>
-      <c r="V78" s="93" t="s">
+      <c r="V78" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="W78" s="94"/>
-      <c r="X78" s="95"/>
+      <c r="W78" s="82"/>
+      <c r="X78" s="83"/>
       <c r="Y78" s="32"/>
-      <c r="Z78" s="93" t="s">
+      <c r="Z78" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="AA78" s="94"/>
-      <c r="AB78" s="95"/>
+      <c r="AA78" s="82"/>
+      <c r="AB78" s="83"/>
       <c r="AC78" s="32"/>
-      <c r="AD78" s="93" t="s">
+      <c r="AD78" s="81" t="s">
         <v>29</v>
       </c>
-      <c r="AE78" s="94"/>
-      <c r="AF78" s="95"/>
+      <c r="AE78" s="82"/>
+      <c r="AF78" s="83"/>
       <c r="AG78" s="32"/>
-      <c r="AH78" s="93" t="s">
+      <c r="AH78" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="AI78" s="94"/>
-      <c r="AJ78" s="95"/>
+      <c r="AI78" s="82"/>
+      <c r="AJ78" s="83"/>
       <c r="AK78" s="43"/>
-      <c r="AL78" s="93"/>
-      <c r="AM78" s="94"/>
-      <c r="AN78" s="95"/>
+      <c r="AL78" s="81"/>
+      <c r="AM78" s="82"/>
+      <c r="AN78" s="83"/>
       <c r="AO78" s="12"/>
       <c r="AP78" s="29"/>
       <c r="AQ78" s="26"/>
@@ -6462,49 +6479,49 @@
     </row>
     <row r="79" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="16"/>
-      <c r="B79" s="73"/>
-      <c r="C79" s="74"/>
-      <c r="D79" s="75"/>
+      <c r="B79" s="148"/>
+      <c r="C79" s="149"/>
+      <c r="D79" s="150"/>
       <c r="E79" s="31"/>
-      <c r="F79" s="73"/>
-      <c r="G79" s="74"/>
-      <c r="H79" s="75"/>
+      <c r="F79" s="148"/>
+      <c r="G79" s="149"/>
+      <c r="H79" s="150"/>
       <c r="I79" s="32"/>
-      <c r="J79" s="63"/>
-      <c r="K79" s="64"/>
-      <c r="L79" s="65"/>
+      <c r="J79" s="71"/>
+      <c r="K79" s="72"/>
+      <c r="L79" s="73"/>
       <c r="M79" s="5"/>
-      <c r="N79" s="63"/>
-      <c r="O79" s="64"/>
-      <c r="P79" s="65"/>
+      <c r="N79" s="71"/>
+      <c r="O79" s="72"/>
+      <c r="P79" s="73"/>
       <c r="Q79" s="31"/>
-      <c r="R79" s="63" t="s">
+      <c r="R79" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="S79" s="64"/>
-      <c r="T79" s="65"/>
+      <c r="S79" s="72"/>
+      <c r="T79" s="73"/>
       <c r="U79" s="32"/>
-      <c r="V79" s="63" t="s">
+      <c r="V79" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="W79" s="64"/>
-      <c r="X79" s="65"/>
+      <c r="W79" s="72"/>
+      <c r="X79" s="73"/>
       <c r="Y79" s="32"/>
-      <c r="Z79" s="63"/>
-      <c r="AA79" s="64"/>
-      <c r="AB79" s="65"/>
+      <c r="Z79" s="71"/>
+      <c r="AA79" s="72"/>
+      <c r="AB79" s="73"/>
       <c r="AC79" s="32"/>
-      <c r="AD79" s="63"/>
-      <c r="AE79" s="64"/>
-      <c r="AF79" s="65"/>
+      <c r="AD79" s="71"/>
+      <c r="AE79" s="72"/>
+      <c r="AF79" s="73"/>
       <c r="AG79" s="31"/>
-      <c r="AH79" s="63"/>
-      <c r="AI79" s="64"/>
-      <c r="AJ79" s="65"/>
+      <c r="AH79" s="71"/>
+      <c r="AI79" s="72"/>
+      <c r="AJ79" s="73"/>
       <c r="AK79" s="32"/>
-      <c r="AL79" s="63"/>
-      <c r="AM79" s="64"/>
-      <c r="AN79" s="65"/>
+      <c r="AL79" s="71"/>
+      <c r="AM79" s="72"/>
+      <c r="AN79" s="73"/>
       <c r="AO79" s="12"/>
       <c r="AP79" s="29"/>
       <c r="AQ79" s="26"/>
@@ -6558,64 +6575,64 @@
     </row>
     <row r="81" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12"/>
-      <c r="B81" s="66" t="s">
+      <c r="B81" s="63" t="s">
         <v>70</v>
       </c>
-      <c r="C81" s="67"/>
+      <c r="C81" s="64"/>
       <c r="D81" s="57"/>
       <c r="E81" s="32"/>
-      <c r="F81" s="66" t="s">
+      <c r="F81" s="63" t="s">
         <v>70</v>
       </c>
-      <c r="G81" s="67"/>
+      <c r="G81" s="64"/>
       <c r="H81" s="57"/>
       <c r="I81" s="50"/>
-      <c r="J81" s="66" t="s">
+      <c r="J81" s="63" t="s">
         <v>70</v>
       </c>
-      <c r="K81" s="67"/>
+      <c r="K81" s="64"/>
       <c r="L81" s="57"/>
       <c r="M81" s="5"/>
-      <c r="N81" s="68" t="s">
+      <c r="N81" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="O81" s="69"/>
+      <c r="O81" s="88"/>
       <c r="P81" s="34"/>
       <c r="Q81" s="32"/>
-      <c r="R81" s="68" t="s">
+      <c r="R81" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="S81" s="69"/>
+      <c r="S81" s="88"/>
       <c r="T81" s="34"/>
       <c r="U81" s="36"/>
-      <c r="V81" s="68" t="s">
+      <c r="V81" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="W81" s="69"/>
+      <c r="W81" s="88"/>
       <c r="X81" s="34"/>
       <c r="Y81" s="32"/>
-      <c r="Z81" s="68" t="s">
+      <c r="Z81" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="AA81" s="69"/>
+      <c r="AA81" s="88"/>
       <c r="AB81" s="34"/>
       <c r="AC81" s="32"/>
-      <c r="AD81" s="68" t="s">
+      <c r="AD81" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="AE81" s="69"/>
+      <c r="AE81" s="88"/>
       <c r="AF81" s="34"/>
       <c r="AG81" s="32"/>
-      <c r="AH81" s="68" t="s">
+      <c r="AH81" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="AI81" s="69"/>
+      <c r="AI81" s="88"/>
       <c r="AJ81" s="34"/>
       <c r="AK81" s="50"/>
-      <c r="AL81" s="68" t="s">
+      <c r="AL81" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="AM81" s="69"/>
+      <c r="AM81" s="88"/>
       <c r="AN81" s="34"/>
       <c r="AO81" s="12"/>
       <c r="AP81" s="29"/>
@@ -6624,65 +6641,65 @@
     </row>
     <row r="82" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="12"/>
-      <c r="B82" s="88" t="s">
+      <c r="B82" s="78" t="s">
         <v>65</v>
       </c>
-      <c r="C82" s="89"/>
-      <c r="D82" s="90"/>
+      <c r="C82" s="79"/>
+      <c r="D82" s="80"/>
       <c r="E82" s="32"/>
-      <c r="F82" s="88" t="s">
+      <c r="F82" s="78" t="s">
         <v>65</v>
       </c>
-      <c r="G82" s="89"/>
-      <c r="H82" s="90"/>
+      <c r="G82" s="79"/>
+      <c r="H82" s="80"/>
       <c r="I82" s="36"/>
-      <c r="J82" s="88" t="s">
+      <c r="J82" s="78" t="s">
         <v>65</v>
       </c>
-      <c r="K82" s="89"/>
-      <c r="L82" s="90"/>
+      <c r="K82" s="79"/>
+      <c r="L82" s="80"/>
       <c r="M82" s="5"/>
-      <c r="N82" s="70" t="s">
+      <c r="N82" s="95" t="s">
         <v>65</v>
       </c>
-      <c r="O82" s="71"/>
-      <c r="P82" s="72"/>
+      <c r="O82" s="96"/>
+      <c r="P82" s="97"/>
       <c r="Q82" s="35"/>
-      <c r="R82" s="70" t="s">
+      <c r="R82" s="95" t="s">
         <v>65</v>
       </c>
-      <c r="S82" s="71"/>
-      <c r="T82" s="72"/>
+      <c r="S82" s="96"/>
+      <c r="T82" s="97"/>
       <c r="U82" s="32"/>
-      <c r="V82" s="70" t="s">
+      <c r="V82" s="95" t="s">
         <v>65</v>
       </c>
-      <c r="W82" s="71"/>
-      <c r="X82" s="72"/>
+      <c r="W82" s="96"/>
+      <c r="X82" s="97"/>
       <c r="Y82" s="32"/>
-      <c r="Z82" s="70" t="s">
+      <c r="Z82" s="95" t="s">
         <v>65</v>
       </c>
-      <c r="AA82" s="71"/>
-      <c r="AB82" s="72"/>
+      <c r="AA82" s="96"/>
+      <c r="AB82" s="97"/>
       <c r="AC82" s="32"/>
-      <c r="AD82" s="70" t="s">
+      <c r="AD82" s="95" t="s">
         <v>65</v>
       </c>
-      <c r="AE82" s="71"/>
-      <c r="AF82" s="72"/>
+      <c r="AE82" s="96"/>
+      <c r="AF82" s="97"/>
       <c r="AG82" s="32"/>
-      <c r="AH82" s="70" t="s">
+      <c r="AH82" s="95" t="s">
         <v>65</v>
       </c>
-      <c r="AI82" s="71"/>
-      <c r="AJ82" s="72"/>
+      <c r="AI82" s="96"/>
+      <c r="AJ82" s="97"/>
       <c r="AK82" s="36"/>
-      <c r="AL82" s="70" t="s">
+      <c r="AL82" s="95" t="s">
         <v>65</v>
       </c>
-      <c r="AM82" s="71"/>
-      <c r="AN82" s="72"/>
+      <c r="AM82" s="96"/>
+      <c r="AN82" s="97"/>
       <c r="AO82" s="12"/>
       <c r="AP82" s="29"/>
       <c r="AQ82" s="26"/>
@@ -6690,65 +6707,65 @@
     </row>
     <row r="83" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="12"/>
-      <c r="B83" s="96" t="s">
+      <c r="B83" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="C83" s="97"/>
-      <c r="D83" s="98"/>
+      <c r="C83" s="69"/>
+      <c r="D83" s="70"/>
       <c r="E83" s="32"/>
-      <c r="F83" s="96" t="s">
+      <c r="F83" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="G83" s="97"/>
-      <c r="H83" s="98"/>
+      <c r="G83" s="69"/>
+      <c r="H83" s="70"/>
       <c r="I83" s="32"/>
-      <c r="J83" s="96" t="s">
+      <c r="J83" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="K83" s="97"/>
-      <c r="L83" s="98"/>
+      <c r="K83" s="69"/>
+      <c r="L83" s="70"/>
       <c r="M83" s="5"/>
-      <c r="N83" s="85" t="s">
+      <c r="N83" s="92" t="s">
         <v>60</v>
       </c>
-      <c r="O83" s="86"/>
-      <c r="P83" s="87"/>
+      <c r="O83" s="93"/>
+      <c r="P83" s="94"/>
       <c r="Q83" s="31"/>
-      <c r="R83" s="85" t="s">
+      <c r="R83" s="92" t="s">
         <v>60</v>
       </c>
-      <c r="S83" s="86"/>
-      <c r="T83" s="87"/>
+      <c r="S83" s="93"/>
+      <c r="T83" s="94"/>
       <c r="U83" s="31"/>
-      <c r="V83" s="85" t="s">
+      <c r="V83" s="92" t="s">
         <v>60</v>
       </c>
-      <c r="W83" s="86"/>
-      <c r="X83" s="87"/>
+      <c r="W83" s="93"/>
+      <c r="X83" s="94"/>
       <c r="Y83" s="32"/>
-      <c r="Z83" s="85" t="s">
+      <c r="Z83" s="92" t="s">
         <v>60</v>
       </c>
-      <c r="AA83" s="86"/>
-      <c r="AB83" s="87"/>
+      <c r="AA83" s="93"/>
+      <c r="AB83" s="94"/>
       <c r="AC83" s="32"/>
-      <c r="AD83" s="85" t="s">
+      <c r="AD83" s="92" t="s">
         <v>60</v>
       </c>
-      <c r="AE83" s="86"/>
-      <c r="AF83" s="87"/>
+      <c r="AE83" s="93"/>
+      <c r="AF83" s="94"/>
       <c r="AG83" s="32"/>
-      <c r="AH83" s="85" t="s">
+      <c r="AH83" s="92" t="s">
         <v>60</v>
       </c>
-      <c r="AI83" s="86"/>
-      <c r="AJ83" s="87"/>
+      <c r="AI83" s="93"/>
+      <c r="AJ83" s="94"/>
       <c r="AK83" s="32"/>
-      <c r="AL83" s="85" t="s">
+      <c r="AL83" s="92" t="s">
         <v>60</v>
       </c>
-      <c r="AM83" s="86"/>
-      <c r="AN83" s="87"/>
+      <c r="AM83" s="93"/>
+      <c r="AN83" s="94"/>
       <c r="AO83" s="12"/>
       <c r="AP83" s="29"/>
       <c r="AQ83" s="26"/>
@@ -6756,65 +6773,65 @@
     </row>
     <row r="84" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12"/>
-      <c r="B84" s="93" t="s">
+      <c r="B84" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="C84" s="94"/>
-      <c r="D84" s="95"/>
+      <c r="C84" s="82"/>
+      <c r="D84" s="83"/>
       <c r="E84" s="32"/>
-      <c r="F84" s="93" t="s">
+      <c r="F84" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="G84" s="94"/>
-      <c r="H84" s="95"/>
+      <c r="G84" s="82"/>
+      <c r="H84" s="83"/>
       <c r="I84" s="32"/>
-      <c r="J84" s="93" t="s">
+      <c r="J84" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="K84" s="94"/>
-      <c r="L84" s="95"/>
+      <c r="K84" s="82"/>
+      <c r="L84" s="83"/>
       <c r="M84" s="5"/>
-      <c r="N84" s="93" t="s">
+      <c r="N84" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="O84" s="94"/>
-      <c r="P84" s="95"/>
+      <c r="O84" s="82"/>
+      <c r="P84" s="83"/>
       <c r="Q84" s="32"/>
-      <c r="R84" s="93" t="s">
+      <c r="R84" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="S84" s="94"/>
-      <c r="T84" s="95"/>
+      <c r="S84" s="82"/>
+      <c r="T84" s="83"/>
       <c r="U84" s="32"/>
-      <c r="V84" s="93" t="s">
+      <c r="V84" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="W84" s="94"/>
-      <c r="X84" s="95"/>
+      <c r="W84" s="82"/>
+      <c r="X84" s="83"/>
       <c r="Y84" s="32"/>
-      <c r="Z84" s="93" t="s">
+      <c r="Z84" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="AA84" s="94"/>
-      <c r="AB84" s="95"/>
+      <c r="AA84" s="82"/>
+      <c r="AB84" s="83"/>
       <c r="AC84" s="43"/>
-      <c r="AD84" s="93" t="s">
+      <c r="AD84" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="AE84" s="94"/>
-      <c r="AF84" s="95"/>
+      <c r="AE84" s="82"/>
+      <c r="AF84" s="83"/>
       <c r="AG84" s="32"/>
-      <c r="AH84" s="93" t="s">
+      <c r="AH84" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="AI84" s="94"/>
-      <c r="AJ84" s="95"/>
+      <c r="AI84" s="82"/>
+      <c r="AJ84" s="83"/>
       <c r="AK84" s="32"/>
-      <c r="AL84" s="93" t="s">
+      <c r="AL84" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="AM84" s="94"/>
-      <c r="AN84" s="95"/>
+      <c r="AM84" s="82"/>
+      <c r="AN84" s="83"/>
       <c r="AO84" s="12"/>
       <c r="AP84" s="29"/>
       <c r="AQ84" s="26"/>
@@ -6822,45 +6839,45 @@
     </row>
     <row r="85" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="12"/>
-      <c r="B85" s="63"/>
-      <c r="C85" s="64"/>
-      <c r="D85" s="65"/>
+      <c r="B85" s="71"/>
+      <c r="C85" s="72"/>
+      <c r="D85" s="73"/>
       <c r="E85" s="31"/>
-      <c r="F85" s="63"/>
-      <c r="G85" s="64"/>
-      <c r="H85" s="65"/>
+      <c r="F85" s="71"/>
+      <c r="G85" s="72"/>
+      <c r="H85" s="73"/>
       <c r="I85" s="32"/>
-      <c r="J85" s="63"/>
-      <c r="K85" s="64"/>
-      <c r="L85" s="65"/>
+      <c r="J85" s="71"/>
+      <c r="K85" s="72"/>
+      <c r="L85" s="73"/>
       <c r="M85" s="6"/>
-      <c r="N85" s="63"/>
-      <c r="O85" s="64"/>
-      <c r="P85" s="65"/>
+      <c r="N85" s="71"/>
+      <c r="O85" s="72"/>
+      <c r="P85" s="73"/>
       <c r="Q85" s="31"/>
-      <c r="R85" s="63"/>
-      <c r="S85" s="64"/>
-      <c r="T85" s="65"/>
+      <c r="R85" s="71"/>
+      <c r="S85" s="72"/>
+      <c r="T85" s="73"/>
       <c r="U85" s="32"/>
-      <c r="V85" s="63"/>
-      <c r="W85" s="64"/>
-      <c r="X85" s="65"/>
+      <c r="V85" s="71"/>
+      <c r="W85" s="72"/>
+      <c r="X85" s="73"/>
       <c r="Y85" s="32"/>
-      <c r="Z85" s="63"/>
-      <c r="AA85" s="64"/>
-      <c r="AB85" s="65"/>
+      <c r="Z85" s="71"/>
+      <c r="AA85" s="72"/>
+      <c r="AB85" s="73"/>
       <c r="AC85" s="43"/>
-      <c r="AD85" s="63"/>
-      <c r="AE85" s="64"/>
-      <c r="AF85" s="65"/>
+      <c r="AD85" s="71"/>
+      <c r="AE85" s="72"/>
+      <c r="AF85" s="73"/>
       <c r="AG85" s="31"/>
-      <c r="AH85" s="63"/>
-      <c r="AI85" s="64"/>
-      <c r="AJ85" s="65"/>
+      <c r="AH85" s="71"/>
+      <c r="AI85" s="72"/>
+      <c r="AJ85" s="73"/>
       <c r="AK85" s="32"/>
-      <c r="AL85" s="63"/>
-      <c r="AM85" s="64"/>
-      <c r="AN85" s="65"/>
+      <c r="AL85" s="71"/>
+      <c r="AM85" s="72"/>
+      <c r="AN85" s="73"/>
       <c r="AO85" s="12"/>
       <c r="AP85" s="29"/>
       <c r="AQ85" s="26"/>
@@ -6914,52 +6931,52 @@
     </row>
     <row r="87" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="12"/>
-      <c r="B87" s="66"/>
-      <c r="C87" s="67"/>
+      <c r="B87" s="63"/>
+      <c r="C87" s="64"/>
       <c r="D87" s="57"/>
       <c r="E87" s="36"/>
-      <c r="F87" s="66"/>
-      <c r="G87" s="67"/>
+      <c r="F87" s="63"/>
+      <c r="G87" s="64"/>
       <c r="H87" s="57"/>
       <c r="I87" s="32"/>
-      <c r="J87" s="66"/>
-      <c r="K87" s="67"/>
+      <c r="J87" s="63"/>
+      <c r="K87" s="64"/>
       <c r="L87" s="57"/>
       <c r="M87" s="6"/>
-      <c r="N87" s="68"/>
-      <c r="O87" s="69"/>
+      <c r="N87" s="87"/>
+      <c r="O87" s="88"/>
       <c r="P87" s="34"/>
       <c r="Q87" s="32"/>
-      <c r="R87" s="68"/>
-      <c r="S87" s="69"/>
+      <c r="R87" s="87"/>
+      <c r="S87" s="88"/>
       <c r="T87" s="34"/>
       <c r="U87" s="36"/>
-      <c r="V87" s="68" t="s">
+      <c r="V87" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="W87" s="69"/>
+      <c r="W87" s="88"/>
       <c r="X87" s="34"/>
       <c r="Y87" s="32"/>
-      <c r="Z87" s="68"/>
-      <c r="AA87" s="69"/>
+      <c r="Z87" s="87"/>
+      <c r="AA87" s="88"/>
       <c r="AB87" s="34"/>
       <c r="AC87" s="32"/>
-      <c r="AD87" s="68" t="s">
+      <c r="AD87" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="AE87" s="69"/>
+      <c r="AE87" s="88"/>
       <c r="AF87" s="34"/>
       <c r="AG87" s="32"/>
-      <c r="AH87" s="68" t="s">
+      <c r="AH87" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="AI87" s="69"/>
+      <c r="AI87" s="88"/>
       <c r="AJ87" s="34"/>
       <c r="AK87" s="32"/>
-      <c r="AL87" s="68" t="s">
+      <c r="AL87" s="87" t="s">
         <v>80</v>
       </c>
-      <c r="AM87" s="69"/>
+      <c r="AM87" s="88"/>
       <c r="AN87" s="34"/>
       <c r="AO87" s="12"/>
       <c r="AP87" s="29"/>
@@ -6968,47 +6985,47 @@
     </row>
     <row r="88" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="12"/>
-      <c r="B88" s="88"/>
-      <c r="C88" s="89"/>
-      <c r="D88" s="90"/>
+      <c r="B88" s="78"/>
+      <c r="C88" s="79"/>
+      <c r="D88" s="80"/>
       <c r="E88" s="32"/>
-      <c r="F88" s="88"/>
-      <c r="G88" s="89"/>
-      <c r="H88" s="90"/>
+      <c r="F88" s="78"/>
+      <c r="G88" s="79"/>
+      <c r="H88" s="80"/>
       <c r="I88" s="32"/>
-      <c r="J88" s="88"/>
-      <c r="K88" s="89"/>
-      <c r="L88" s="90"/>
+      <c r="J88" s="78"/>
+      <c r="K88" s="79"/>
+      <c r="L88" s="80"/>
       <c r="M88" s="6"/>
-      <c r="N88" s="70"/>
-      <c r="O88" s="71"/>
-      <c r="P88" s="72"/>
+      <c r="N88" s="95"/>
+      <c r="O88" s="96"/>
+      <c r="P88" s="97"/>
       <c r="Q88" s="32"/>
-      <c r="R88" s="70"/>
-      <c r="S88" s="71"/>
-      <c r="T88" s="72"/>
+      <c r="R88" s="95"/>
+      <c r="S88" s="96"/>
+      <c r="T88" s="97"/>
       <c r="U88" s="32"/>
-      <c r="V88" s="70"/>
-      <c r="W88" s="71"/>
-      <c r="X88" s="72"/>
+      <c r="V88" s="95"/>
+      <c r="W88" s="96"/>
+      <c r="X88" s="97"/>
       <c r="Y88" s="32"/>
-      <c r="Z88" s="70"/>
-      <c r="AA88" s="71"/>
-      <c r="AB88" s="72"/>
+      <c r="Z88" s="95"/>
+      <c r="AA88" s="96"/>
+      <c r="AB88" s="97"/>
       <c r="AC88" s="35"/>
-      <c r="AD88" s="70"/>
-      <c r="AE88" s="71"/>
-      <c r="AF88" s="72"/>
+      <c r="AD88" s="95"/>
+      <c r="AE88" s="96"/>
+      <c r="AF88" s="97"/>
       <c r="AG88" s="32"/>
-      <c r="AH88" s="70"/>
-      <c r="AI88" s="71"/>
-      <c r="AJ88" s="72"/>
+      <c r="AH88" s="95"/>
+      <c r="AI88" s="96"/>
+      <c r="AJ88" s="97"/>
       <c r="AK88" s="32"/>
-      <c r="AL88" s="70" t="s">
+      <c r="AL88" s="95" t="s">
         <v>81</v>
       </c>
-      <c r="AM88" s="71"/>
-      <c r="AN88" s="72"/>
+      <c r="AM88" s="96"/>
+      <c r="AN88" s="97"/>
       <c r="AO88" s="12"/>
       <c r="AP88" s="29"/>
       <c r="AQ88" s="26"/>
@@ -7016,51 +7033,51 @@
     </row>
     <row r="89" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="12"/>
-      <c r="B89" s="96"/>
-      <c r="C89" s="97"/>
-      <c r="D89" s="98"/>
+      <c r="B89" s="68"/>
+      <c r="C89" s="69"/>
+      <c r="D89" s="70"/>
       <c r="E89" s="31"/>
-      <c r="F89" s="96"/>
-      <c r="G89" s="97"/>
-      <c r="H89" s="98"/>
+      <c r="F89" s="68"/>
+      <c r="G89" s="69"/>
+      <c r="H89" s="70"/>
       <c r="I89" s="32"/>
-      <c r="J89" s="96"/>
-      <c r="K89" s="97"/>
-      <c r="L89" s="98"/>
+      <c r="J89" s="68"/>
+      <c r="K89" s="69"/>
+      <c r="L89" s="70"/>
       <c r="M89" s="6"/>
-      <c r="N89" s="85"/>
-      <c r="O89" s="86"/>
-      <c r="P89" s="87"/>
+      <c r="N89" s="92"/>
+      <c r="O89" s="93"/>
+      <c r="P89" s="94"/>
       <c r="Q89" s="32"/>
-      <c r="R89" s="85"/>
-      <c r="S89" s="86"/>
-      <c r="T89" s="87"/>
+      <c r="R89" s="92"/>
+      <c r="S89" s="93"/>
+      <c r="T89" s="94"/>
       <c r="U89" s="31"/>
-      <c r="V89" s="85" t="s">
+      <c r="V89" s="92" t="s">
         <v>60</v>
       </c>
-      <c r="W89" s="86"/>
-      <c r="X89" s="87"/>
+      <c r="W89" s="93"/>
+      <c r="X89" s="94"/>
       <c r="Y89" s="32"/>
-      <c r="Z89" s="85"/>
-      <c r="AA89" s="86"/>
-      <c r="AB89" s="87"/>
+      <c r="Z89" s="92"/>
+      <c r="AA89" s="93"/>
+      <c r="AB89" s="94"/>
       <c r="AC89" s="31"/>
-      <c r="AD89" s="85" t="s">
+      <c r="AD89" s="92" t="s">
         <v>60</v>
       </c>
-      <c r="AE89" s="86"/>
-      <c r="AF89" s="87"/>
+      <c r="AE89" s="93"/>
+      <c r="AF89" s="94"/>
       <c r="AG89" s="32"/>
-      <c r="AH89" s="85" t="s">
+      <c r="AH89" s="92" t="s">
         <v>60</v>
       </c>
-      <c r="AI89" s="86"/>
-      <c r="AJ89" s="87"/>
+      <c r="AI89" s="93"/>
+      <c r="AJ89" s="94"/>
       <c r="AK89" s="32"/>
-      <c r="AL89" s="85"/>
-      <c r="AM89" s="86"/>
-      <c r="AN89" s="87"/>
+      <c r="AL89" s="92"/>
+      <c r="AM89" s="93"/>
+      <c r="AN89" s="94"/>
       <c r="AO89" s="12"/>
       <c r="AP89" s="29"/>
       <c r="AQ89" s="26"/>
@@ -7068,53 +7085,53 @@
     </row>
     <row r="90" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="12"/>
-      <c r="B90" s="93"/>
-      <c r="C90" s="94"/>
-      <c r="D90" s="95"/>
+      <c r="B90" s="81"/>
+      <c r="C90" s="82"/>
+      <c r="D90" s="83"/>
       <c r="E90" s="32"/>
-      <c r="F90" s="93"/>
-      <c r="G90" s="94"/>
-      <c r="H90" s="95"/>
+      <c r="F90" s="81"/>
+      <c r="G90" s="82"/>
+      <c r="H90" s="83"/>
       <c r="I90" s="32"/>
-      <c r="J90" s="93"/>
-      <c r="K90" s="94"/>
-      <c r="L90" s="95"/>
+      <c r="J90" s="81"/>
+      <c r="K90" s="82"/>
+      <c r="L90" s="83"/>
       <c r="M90" s="6"/>
-      <c r="N90" s="93"/>
-      <c r="O90" s="94"/>
-      <c r="P90" s="95"/>
+      <c r="N90" s="81"/>
+      <c r="O90" s="82"/>
+      <c r="P90" s="83"/>
       <c r="Q90" s="32"/>
-      <c r="R90" s="93"/>
-      <c r="S90" s="94"/>
-      <c r="T90" s="95"/>
+      <c r="R90" s="81"/>
+      <c r="S90" s="82"/>
+      <c r="T90" s="83"/>
       <c r="U90" s="32"/>
-      <c r="V90" s="93" t="s">
+      <c r="V90" s="81" t="s">
         <v>30</v>
       </c>
-      <c r="W90" s="94"/>
-      <c r="X90" s="95"/>
+      <c r="W90" s="82"/>
+      <c r="X90" s="83"/>
       <c r="Y90" s="32"/>
-      <c r="Z90" s="93"/>
-      <c r="AA90" s="94"/>
-      <c r="AB90" s="95"/>
+      <c r="Z90" s="81"/>
+      <c r="AA90" s="82"/>
+      <c r="AB90" s="83"/>
       <c r="AC90" s="32"/>
-      <c r="AD90" s="93" t="s">
+      <c r="AD90" s="81" t="s">
         <v>30</v>
       </c>
-      <c r="AE90" s="94"/>
-      <c r="AF90" s="95"/>
+      <c r="AE90" s="82"/>
+      <c r="AF90" s="83"/>
       <c r="AG90" s="32"/>
-      <c r="AH90" s="93" t="s">
+      <c r="AH90" s="81" t="s">
         <v>30</v>
       </c>
-      <c r="AI90" s="94"/>
-      <c r="AJ90" s="95"/>
+      <c r="AI90" s="82"/>
+      <c r="AJ90" s="83"/>
       <c r="AK90" s="32"/>
-      <c r="AL90" s="93" t="s">
+      <c r="AL90" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="AM90" s="94"/>
-      <c r="AN90" s="95"/>
+      <c r="AM90" s="82"/>
+      <c r="AN90" s="83"/>
       <c r="AO90" s="12"/>
       <c r="AP90" s="29"/>
       <c r="AQ90" s="26"/>
@@ -7122,45 +7139,45 @@
     </row>
     <row r="91" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="12"/>
-      <c r="B91" s="63"/>
-      <c r="C91" s="64"/>
-      <c r="D91" s="65"/>
+      <c r="B91" s="71"/>
+      <c r="C91" s="72"/>
+      <c r="D91" s="73"/>
       <c r="E91" s="32"/>
-      <c r="F91" s="63"/>
-      <c r="G91" s="64"/>
-      <c r="H91" s="65"/>
+      <c r="F91" s="71"/>
+      <c r="G91" s="72"/>
+      <c r="H91" s="73"/>
       <c r="I91" s="31"/>
-      <c r="J91" s="63"/>
-      <c r="K91" s="64"/>
-      <c r="L91" s="65"/>
+      <c r="J91" s="71"/>
+      <c r="K91" s="72"/>
+      <c r="L91" s="73"/>
       <c r="M91" s="6"/>
-      <c r="N91" s="63"/>
-      <c r="O91" s="64"/>
-      <c r="P91" s="65"/>
+      <c r="N91" s="71"/>
+      <c r="O91" s="72"/>
+      <c r="P91" s="73"/>
       <c r="Q91" s="31"/>
-      <c r="R91" s="63"/>
-      <c r="S91" s="64"/>
-      <c r="T91" s="65"/>
+      <c r="R91" s="71"/>
+      <c r="S91" s="72"/>
+      <c r="T91" s="73"/>
       <c r="U91" s="32"/>
-      <c r="V91" s="63"/>
-      <c r="W91" s="64"/>
-      <c r="X91" s="65"/>
+      <c r="V91" s="71"/>
+      <c r="W91" s="72"/>
+      <c r="X91" s="73"/>
       <c r="Y91" s="32"/>
-      <c r="Z91" s="63"/>
-      <c r="AA91" s="64"/>
-      <c r="AB91" s="65"/>
+      <c r="Z91" s="71"/>
+      <c r="AA91" s="72"/>
+      <c r="AB91" s="73"/>
       <c r="AC91" s="32"/>
-      <c r="AD91" s="63"/>
-      <c r="AE91" s="64"/>
-      <c r="AF91" s="65"/>
+      <c r="AD91" s="71"/>
+      <c r="AE91" s="72"/>
+      <c r="AF91" s="73"/>
       <c r="AG91" s="31"/>
-      <c r="AH91" s="63"/>
-      <c r="AI91" s="64"/>
-      <c r="AJ91" s="65"/>
+      <c r="AH91" s="71"/>
+      <c r="AI91" s="72"/>
+      <c r="AJ91" s="73"/>
       <c r="AK91" s="31"/>
-      <c r="AL91" s="63"/>
-      <c r="AM91" s="64"/>
-      <c r="AN91" s="65"/>
+      <c r="AL91" s="71"/>
+      <c r="AM91" s="72"/>
+      <c r="AN91" s="73"/>
       <c r="AO91" s="12"/>
       <c r="AP91" s="29"/>
       <c r="AQ91" s="26"/>
@@ -7214,44 +7231,44 @@
     </row>
     <row r="93" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="12"/>
-      <c r="B93" s="66"/>
-      <c r="C93" s="67"/>
+      <c r="B93" s="63"/>
+      <c r="C93" s="64"/>
       <c r="D93" s="57"/>
       <c r="E93" s="36"/>
-      <c r="F93" s="66"/>
-      <c r="G93" s="67"/>
+      <c r="F93" s="63"/>
+      <c r="G93" s="64"/>
       <c r="H93" s="57"/>
       <c r="I93" s="32"/>
-      <c r="J93" s="66"/>
-      <c r="K93" s="67"/>
+      <c r="J93" s="63"/>
+      <c r="K93" s="64"/>
       <c r="L93" s="57"/>
       <c r="M93" s="6"/>
-      <c r="N93" s="68"/>
-      <c r="O93" s="69"/>
+      <c r="N93" s="87"/>
+      <c r="O93" s="88"/>
       <c r="P93" s="34"/>
       <c r="Q93" s="44"/>
-      <c r="R93" s="68"/>
-      <c r="S93" s="69"/>
+      <c r="R93" s="87"/>
+      <c r="S93" s="88"/>
       <c r="T93" s="34"/>
       <c r="U93" s="36"/>
-      <c r="V93" s="68"/>
-      <c r="W93" s="69"/>
+      <c r="V93" s="87"/>
+      <c r="W93" s="88"/>
       <c r="X93" s="34"/>
       <c r="Y93" s="32"/>
-      <c r="Z93" s="68"/>
-      <c r="AA93" s="69"/>
+      <c r="Z93" s="87"/>
+      <c r="AA93" s="88"/>
       <c r="AB93" s="34"/>
       <c r="AC93" s="36"/>
-      <c r="AD93" s="68"/>
-      <c r="AE93" s="69"/>
+      <c r="AD93" s="87"/>
+      <c r="AE93" s="88"/>
       <c r="AF93" s="34"/>
       <c r="AG93" s="36"/>
-      <c r="AH93" s="68"/>
-      <c r="AI93" s="69"/>
+      <c r="AH93" s="87"/>
+      <c r="AI93" s="88"/>
       <c r="AJ93" s="34"/>
       <c r="AK93" s="32"/>
-      <c r="AL93" s="68"/>
-      <c r="AM93" s="69"/>
+      <c r="AL93" s="87"/>
+      <c r="AM93" s="88"/>
       <c r="AN93" s="34"/>
       <c r="AO93" s="12"/>
       <c r="AP93" s="29"/>
@@ -7260,45 +7277,45 @@
     </row>
     <row r="94" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="12"/>
-      <c r="B94" s="88"/>
-      <c r="C94" s="89"/>
-      <c r="D94" s="90"/>
+      <c r="B94" s="78"/>
+      <c r="C94" s="79"/>
+      <c r="D94" s="80"/>
       <c r="E94" s="32"/>
-      <c r="F94" s="88"/>
-      <c r="G94" s="89"/>
-      <c r="H94" s="90"/>
+      <c r="F94" s="78"/>
+      <c r="G94" s="79"/>
+      <c r="H94" s="80"/>
       <c r="I94" s="32"/>
-      <c r="J94" s="88"/>
-      <c r="K94" s="89"/>
-      <c r="L94" s="90"/>
+      <c r="J94" s="78"/>
+      <c r="K94" s="79"/>
+      <c r="L94" s="80"/>
       <c r="M94" s="26"/>
-      <c r="N94" s="70"/>
-      <c r="O94" s="71"/>
-      <c r="P94" s="72"/>
+      <c r="N94" s="95"/>
+      <c r="O94" s="96"/>
+      <c r="P94" s="97"/>
       <c r="Q94" s="44"/>
-      <c r="R94" s="70"/>
-      <c r="S94" s="71"/>
-      <c r="T94" s="72"/>
+      <c r="R94" s="95"/>
+      <c r="S94" s="96"/>
+      <c r="T94" s="97"/>
       <c r="U94" s="32"/>
-      <c r="V94" s="70"/>
-      <c r="W94" s="71"/>
-      <c r="X94" s="72"/>
+      <c r="V94" s="95"/>
+      <c r="W94" s="96"/>
+      <c r="X94" s="97"/>
       <c r="Y94" s="32"/>
-      <c r="Z94" s="70"/>
-      <c r="AA94" s="71"/>
-      <c r="AB94" s="72"/>
+      <c r="Z94" s="95"/>
+      <c r="AA94" s="96"/>
+      <c r="AB94" s="97"/>
       <c r="AC94" s="36"/>
-      <c r="AD94" s="70"/>
-      <c r="AE94" s="71"/>
-      <c r="AF94" s="72"/>
+      <c r="AD94" s="95"/>
+      <c r="AE94" s="96"/>
+      <c r="AF94" s="97"/>
       <c r="AG94" s="32"/>
-      <c r="AH94" s="70"/>
-      <c r="AI94" s="71"/>
-      <c r="AJ94" s="72"/>
+      <c r="AH94" s="95"/>
+      <c r="AI94" s="96"/>
+      <c r="AJ94" s="97"/>
       <c r="AK94" s="32"/>
-      <c r="AL94" s="70"/>
-      <c r="AM94" s="71"/>
-      <c r="AN94" s="72"/>
+      <c r="AL94" s="95"/>
+      <c r="AM94" s="96"/>
+      <c r="AN94" s="97"/>
       <c r="AO94" s="12"/>
       <c r="AP94" s="29"/>
       <c r="AQ94" s="26"/>
@@ -7306,45 +7323,45 @@
     </row>
     <row r="95" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="12"/>
-      <c r="B95" s="96"/>
-      <c r="C95" s="97"/>
-      <c r="D95" s="98"/>
+      <c r="B95" s="68"/>
+      <c r="C95" s="69"/>
+      <c r="D95" s="70"/>
       <c r="E95" s="31"/>
-      <c r="F95" s="96"/>
-      <c r="G95" s="97"/>
-      <c r="H95" s="98"/>
+      <c r="F95" s="68"/>
+      <c r="G95" s="69"/>
+      <c r="H95" s="70"/>
       <c r="I95" s="32"/>
-      <c r="J95" s="96"/>
-      <c r="K95" s="97"/>
-      <c r="L95" s="98"/>
+      <c r="J95" s="68"/>
+      <c r="K95" s="69"/>
+      <c r="L95" s="70"/>
       <c r="M95" s="26"/>
-      <c r="N95" s="85"/>
-      <c r="O95" s="86"/>
-      <c r="P95" s="87"/>
+      <c r="N95" s="92"/>
+      <c r="O95" s="93"/>
+      <c r="P95" s="94"/>
       <c r="Q95" s="44"/>
-      <c r="R95" s="85"/>
-      <c r="S95" s="86"/>
-      <c r="T95" s="87"/>
+      <c r="R95" s="92"/>
+      <c r="S95" s="93"/>
+      <c r="T95" s="94"/>
       <c r="U95" s="31"/>
-      <c r="V95" s="85"/>
-      <c r="W95" s="86"/>
-      <c r="X95" s="87"/>
+      <c r="V95" s="92"/>
+      <c r="W95" s="93"/>
+      <c r="X95" s="94"/>
       <c r="Y95" s="32"/>
-      <c r="Z95" s="85"/>
-      <c r="AA95" s="86"/>
-      <c r="AB95" s="87"/>
+      <c r="Z95" s="92"/>
+      <c r="AA95" s="93"/>
+      <c r="AB95" s="94"/>
       <c r="AC95" s="35"/>
-      <c r="AD95" s="85"/>
-      <c r="AE95" s="86"/>
-      <c r="AF95" s="87"/>
+      <c r="AD95" s="92"/>
+      <c r="AE95" s="93"/>
+      <c r="AF95" s="94"/>
       <c r="AG95" s="31"/>
-      <c r="AH95" s="85"/>
-      <c r="AI95" s="86"/>
-      <c r="AJ95" s="87"/>
+      <c r="AH95" s="92"/>
+      <c r="AI95" s="93"/>
+      <c r="AJ95" s="94"/>
       <c r="AK95" s="32"/>
-      <c r="AL95" s="85"/>
-      <c r="AM95" s="86"/>
-      <c r="AN95" s="87"/>
+      <c r="AL95" s="92"/>
+      <c r="AM95" s="93"/>
+      <c r="AN95" s="94"/>
       <c r="AO95" s="12"/>
       <c r="AP95" s="29"/>
       <c r="AQ95" s="26"/>
@@ -7352,45 +7369,45 @@
     </row>
     <row r="96" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="12"/>
-      <c r="B96" s="93"/>
-      <c r="C96" s="94"/>
-      <c r="D96" s="95"/>
+      <c r="B96" s="81"/>
+      <c r="C96" s="82"/>
+      <c r="D96" s="83"/>
       <c r="E96" s="32"/>
-      <c r="F96" s="93"/>
-      <c r="G96" s="94"/>
-      <c r="H96" s="95"/>
+      <c r="F96" s="81"/>
+      <c r="G96" s="82"/>
+      <c r="H96" s="83"/>
       <c r="I96" s="32"/>
-      <c r="J96" s="93"/>
-      <c r="K96" s="94"/>
-      <c r="L96" s="95"/>
+      <c r="J96" s="81"/>
+      <c r="K96" s="82"/>
+      <c r="L96" s="83"/>
       <c r="M96" s="26"/>
-      <c r="N96" s="93"/>
-      <c r="O96" s="94"/>
-      <c r="P96" s="95"/>
+      <c r="N96" s="81"/>
+      <c r="O96" s="82"/>
+      <c r="P96" s="83"/>
       <c r="Q96" s="44"/>
-      <c r="R96" s="93"/>
-      <c r="S96" s="94"/>
-      <c r="T96" s="95"/>
+      <c r="R96" s="81"/>
+      <c r="S96" s="82"/>
+      <c r="T96" s="83"/>
       <c r="U96" s="32"/>
-      <c r="V96" s="93"/>
-      <c r="W96" s="94"/>
-      <c r="X96" s="95"/>
+      <c r="V96" s="81"/>
+      <c r="W96" s="82"/>
+      <c r="X96" s="83"/>
       <c r="Y96" s="32"/>
-      <c r="Z96" s="93"/>
-      <c r="AA96" s="94"/>
-      <c r="AB96" s="95"/>
+      <c r="Z96" s="81"/>
+      <c r="AA96" s="82"/>
+      <c r="AB96" s="83"/>
       <c r="AC96" s="31"/>
-      <c r="AD96" s="93"/>
-      <c r="AE96" s="94"/>
-      <c r="AF96" s="95"/>
+      <c r="AD96" s="81"/>
+      <c r="AE96" s="82"/>
+      <c r="AF96" s="83"/>
       <c r="AG96" s="32"/>
-      <c r="AH96" s="93"/>
-      <c r="AI96" s="94"/>
-      <c r="AJ96" s="95"/>
+      <c r="AH96" s="81"/>
+      <c r="AI96" s="82"/>
+      <c r="AJ96" s="83"/>
       <c r="AK96" s="32"/>
-      <c r="AL96" s="93"/>
-      <c r="AM96" s="94"/>
-      <c r="AN96" s="95"/>
+      <c r="AL96" s="81"/>
+      <c r="AM96" s="82"/>
+      <c r="AN96" s="83"/>
       <c r="AO96" s="12"/>
       <c r="AP96" s="29"/>
       <c r="AQ96" s="26"/>
@@ -7398,45 +7415,45 @@
     </row>
     <row r="97" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="12"/>
-      <c r="B97" s="63"/>
-      <c r="C97" s="64"/>
-      <c r="D97" s="65"/>
+      <c r="B97" s="71"/>
+      <c r="C97" s="72"/>
+      <c r="D97" s="73"/>
       <c r="E97" s="32"/>
-      <c r="F97" s="63"/>
-      <c r="G97" s="64"/>
-      <c r="H97" s="65"/>
+      <c r="F97" s="71"/>
+      <c r="G97" s="72"/>
+      <c r="H97" s="73"/>
       <c r="I97" s="31"/>
-      <c r="J97" s="63"/>
-      <c r="K97" s="64"/>
-      <c r="L97" s="65"/>
+      <c r="J97" s="71"/>
+      <c r="K97" s="72"/>
+      <c r="L97" s="73"/>
       <c r="M97" s="26"/>
-      <c r="N97" s="63"/>
-      <c r="O97" s="64"/>
-      <c r="P97" s="65"/>
+      <c r="N97" s="71"/>
+      <c r="O97" s="72"/>
+      <c r="P97" s="73"/>
       <c r="Q97" s="31"/>
-      <c r="R97" s="63"/>
-      <c r="S97" s="64"/>
-      <c r="T97" s="65"/>
+      <c r="R97" s="71"/>
+      <c r="S97" s="72"/>
+      <c r="T97" s="73"/>
       <c r="U97" s="32"/>
-      <c r="V97" s="63"/>
-      <c r="W97" s="64"/>
-      <c r="X97" s="65"/>
+      <c r="V97" s="71"/>
+      <c r="W97" s="72"/>
+      <c r="X97" s="73"/>
       <c r="Y97" s="31"/>
-      <c r="Z97" s="63"/>
-      <c r="AA97" s="64"/>
-      <c r="AB97" s="65"/>
+      <c r="Z97" s="71"/>
+      <c r="AA97" s="72"/>
+      <c r="AB97" s="73"/>
       <c r="AC97" s="31"/>
-      <c r="AD97" s="63"/>
-      <c r="AE97" s="64"/>
-      <c r="AF97" s="65"/>
+      <c r="AD97" s="71"/>
+      <c r="AE97" s="72"/>
+      <c r="AF97" s="73"/>
       <c r="AG97" s="32"/>
-      <c r="AH97" s="63"/>
-      <c r="AI97" s="64"/>
-      <c r="AJ97" s="65"/>
+      <c r="AH97" s="71"/>
+      <c r="AI97" s="72"/>
+      <c r="AJ97" s="73"/>
       <c r="AK97" s="31"/>
-      <c r="AL97" s="63"/>
-      <c r="AM97" s="64"/>
-      <c r="AN97" s="65"/>
+      <c r="AL97" s="71"/>
+      <c r="AM97" s="72"/>
+      <c r="AN97" s="73"/>
       <c r="AO97" s="12"/>
       <c r="AP97" s="29"/>
       <c r="AQ97" s="26"/>
@@ -7490,44 +7507,44 @@
     </row>
     <row r="99" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="12"/>
-      <c r="B99" s="66"/>
-      <c r="C99" s="67"/>
+      <c r="B99" s="63"/>
+      <c r="C99" s="64"/>
       <c r="D99" s="57"/>
       <c r="E99" s="32"/>
-      <c r="F99" s="66"/>
-      <c r="G99" s="67"/>
+      <c r="F99" s="63"/>
+      <c r="G99" s="64"/>
       <c r="H99" s="57"/>
       <c r="I99" s="36"/>
-      <c r="J99" s="66"/>
-      <c r="K99" s="67"/>
+      <c r="J99" s="63"/>
+      <c r="K99" s="64"/>
       <c r="L99" s="57"/>
       <c r="M99" s="26"/>
-      <c r="N99" s="68"/>
-      <c r="O99" s="69"/>
+      <c r="N99" s="87"/>
+      <c r="O99" s="88"/>
       <c r="P99" s="34"/>
       <c r="Q99" s="44"/>
-      <c r="R99" s="68"/>
-      <c r="S99" s="69"/>
+      <c r="R99" s="87"/>
+      <c r="S99" s="88"/>
       <c r="T99" s="34"/>
       <c r="U99" s="36"/>
-      <c r="V99" s="68"/>
-      <c r="W99" s="69"/>
+      <c r="V99" s="87"/>
+      <c r="W99" s="88"/>
       <c r="X99" s="34"/>
       <c r="Y99" s="32"/>
-      <c r="Z99" s="68"/>
-      <c r="AA99" s="69"/>
+      <c r="Z99" s="87"/>
+      <c r="AA99" s="88"/>
       <c r="AB99" s="34"/>
       <c r="AC99" s="36"/>
-      <c r="AD99" s="68"/>
-      <c r="AE99" s="69"/>
+      <c r="AD99" s="87"/>
+      <c r="AE99" s="88"/>
       <c r="AF99" s="34"/>
       <c r="AG99" s="32"/>
-      <c r="AH99" s="68"/>
-      <c r="AI99" s="69"/>
+      <c r="AH99" s="87"/>
+      <c r="AI99" s="88"/>
       <c r="AJ99" s="34"/>
       <c r="AK99" s="36"/>
-      <c r="AL99" s="68"/>
-      <c r="AM99" s="69"/>
+      <c r="AL99" s="87"/>
+      <c r="AM99" s="88"/>
       <c r="AN99" s="34"/>
       <c r="AO99" s="12"/>
       <c r="AP99" s="29"/>
@@ -7536,45 +7553,45 @@
     </row>
     <row r="100" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12"/>
-      <c r="B100" s="96"/>
-      <c r="C100" s="97"/>
-      <c r="D100" s="98"/>
+      <c r="B100" s="68"/>
+      <c r="C100" s="69"/>
+      <c r="D100" s="70"/>
       <c r="E100" s="32"/>
-      <c r="F100" s="96"/>
-      <c r="G100" s="97"/>
-      <c r="H100" s="98"/>
+      <c r="F100" s="68"/>
+      <c r="G100" s="69"/>
+      <c r="H100" s="70"/>
       <c r="I100" s="31"/>
-      <c r="J100" s="96"/>
-      <c r="K100" s="97"/>
-      <c r="L100" s="98"/>
+      <c r="J100" s="68"/>
+      <c r="K100" s="69"/>
+      <c r="L100" s="70"/>
       <c r="M100" s="26"/>
-      <c r="N100" s="85"/>
-      <c r="O100" s="86"/>
-      <c r="P100" s="87"/>
+      <c r="N100" s="92"/>
+      <c r="O100" s="93"/>
+      <c r="P100" s="94"/>
       <c r="Q100" s="31"/>
-      <c r="R100" s="85"/>
-      <c r="S100" s="86"/>
-      <c r="T100" s="87"/>
+      <c r="R100" s="92"/>
+      <c r="S100" s="93"/>
+      <c r="T100" s="94"/>
       <c r="U100" s="31"/>
-      <c r="V100" s="85"/>
-      <c r="W100" s="86"/>
-      <c r="X100" s="87"/>
+      <c r="V100" s="92"/>
+      <c r="W100" s="93"/>
+      <c r="X100" s="94"/>
       <c r="Y100" s="32"/>
-      <c r="Z100" s="85"/>
-      <c r="AA100" s="86"/>
-      <c r="AB100" s="87"/>
+      <c r="Z100" s="92"/>
+      <c r="AA100" s="93"/>
+      <c r="AB100" s="94"/>
       <c r="AC100" s="36"/>
-      <c r="AD100" s="85"/>
-      <c r="AE100" s="86"/>
-      <c r="AF100" s="87"/>
+      <c r="AD100" s="92"/>
+      <c r="AE100" s="93"/>
+      <c r="AF100" s="94"/>
       <c r="AG100" s="32"/>
-      <c r="AH100" s="85"/>
-      <c r="AI100" s="86"/>
-      <c r="AJ100" s="87"/>
+      <c r="AH100" s="92"/>
+      <c r="AI100" s="93"/>
+      <c r="AJ100" s="94"/>
       <c r="AK100" s="31"/>
-      <c r="AL100" s="85"/>
-      <c r="AM100" s="86"/>
-      <c r="AN100" s="87"/>
+      <c r="AL100" s="92"/>
+      <c r="AM100" s="93"/>
+      <c r="AN100" s="94"/>
       <c r="AO100" s="12"/>
       <c r="AP100" s="29"/>
       <c r="AQ100" s="26"/>
@@ -7582,45 +7599,45 @@
     </row>
     <row r="101" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="12"/>
-      <c r="B101" s="93"/>
-      <c r="C101" s="94"/>
-      <c r="D101" s="95"/>
+      <c r="B101" s="81"/>
+      <c r="C101" s="82"/>
+      <c r="D101" s="83"/>
       <c r="E101" s="32"/>
-      <c r="F101" s="93"/>
-      <c r="G101" s="94"/>
-      <c r="H101" s="95"/>
+      <c r="F101" s="81"/>
+      <c r="G101" s="82"/>
+      <c r="H101" s="83"/>
       <c r="I101" s="31"/>
-      <c r="J101" s="93"/>
-      <c r="K101" s="94"/>
-      <c r="L101" s="95"/>
+      <c r="J101" s="81"/>
+      <c r="K101" s="82"/>
+      <c r="L101" s="83"/>
       <c r="M101" s="26"/>
-      <c r="N101" s="93"/>
-      <c r="O101" s="94"/>
-      <c r="P101" s="95"/>
+      <c r="N101" s="81"/>
+      <c r="O101" s="82"/>
+      <c r="P101" s="83"/>
       <c r="Q101" s="31"/>
-      <c r="R101" s="93"/>
-      <c r="S101" s="94"/>
-      <c r="T101" s="95"/>
+      <c r="R101" s="81"/>
+      <c r="S101" s="82"/>
+      <c r="T101" s="83"/>
       <c r="U101" s="32"/>
-      <c r="V101" s="93"/>
-      <c r="W101" s="94"/>
-      <c r="X101" s="95"/>
+      <c r="V101" s="81"/>
+      <c r="W101" s="82"/>
+      <c r="X101" s="83"/>
       <c r="Y101" s="32"/>
-      <c r="Z101" s="93"/>
-      <c r="AA101" s="94"/>
-      <c r="AB101" s="95"/>
+      <c r="Z101" s="81"/>
+      <c r="AA101" s="82"/>
+      <c r="AB101" s="83"/>
       <c r="AC101" s="31"/>
-      <c r="AD101" s="93"/>
-      <c r="AE101" s="94"/>
-      <c r="AF101" s="95"/>
+      <c r="AD101" s="81"/>
+      <c r="AE101" s="82"/>
+      <c r="AF101" s="83"/>
       <c r="AG101" s="32"/>
-      <c r="AH101" s="93"/>
-      <c r="AI101" s="94"/>
-      <c r="AJ101" s="95"/>
+      <c r="AH101" s="81"/>
+      <c r="AI101" s="82"/>
+      <c r="AJ101" s="83"/>
       <c r="AK101" s="31"/>
-      <c r="AL101" s="93"/>
-      <c r="AM101" s="94"/>
-      <c r="AN101" s="95"/>
+      <c r="AL101" s="81"/>
+      <c r="AM101" s="82"/>
+      <c r="AN101" s="83"/>
       <c r="AO101" s="12"/>
       <c r="AP101" s="29"/>
       <c r="AQ101" s="26"/>
@@ -7628,45 +7645,45 @@
     </row>
     <row r="102" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="12"/>
-      <c r="B102" s="63"/>
-      <c r="C102" s="64"/>
-      <c r="D102" s="65"/>
+      <c r="B102" s="71"/>
+      <c r="C102" s="72"/>
+      <c r="D102" s="73"/>
       <c r="E102" s="31"/>
-      <c r="F102" s="63"/>
-      <c r="G102" s="64"/>
-      <c r="H102" s="65"/>
+      <c r="F102" s="71"/>
+      <c r="G102" s="72"/>
+      <c r="H102" s="73"/>
       <c r="I102" s="32"/>
-      <c r="J102" s="63"/>
-      <c r="K102" s="64"/>
-      <c r="L102" s="65"/>
+      <c r="J102" s="71"/>
+      <c r="K102" s="72"/>
+      <c r="L102" s="73"/>
       <c r="M102" s="26"/>
-      <c r="N102" s="63"/>
-      <c r="O102" s="64"/>
-      <c r="P102" s="65"/>
+      <c r="N102" s="71"/>
+      <c r="O102" s="72"/>
+      <c r="P102" s="73"/>
       <c r="Q102" s="31"/>
-      <c r="R102" s="63"/>
-      <c r="S102" s="64"/>
-      <c r="T102" s="65"/>
+      <c r="R102" s="71"/>
+      <c r="S102" s="72"/>
+      <c r="T102" s="73"/>
       <c r="U102" s="32"/>
-      <c r="V102" s="63"/>
-      <c r="W102" s="64"/>
-      <c r="X102" s="65"/>
+      <c r="V102" s="71"/>
+      <c r="W102" s="72"/>
+      <c r="X102" s="73"/>
       <c r="Y102" s="32"/>
-      <c r="Z102" s="63"/>
-      <c r="AA102" s="64"/>
-      <c r="AB102" s="65"/>
+      <c r="Z102" s="71"/>
+      <c r="AA102" s="72"/>
+      <c r="AB102" s="73"/>
       <c r="AC102" s="32"/>
-      <c r="AD102" s="63"/>
-      <c r="AE102" s="64"/>
-      <c r="AF102" s="65"/>
+      <c r="AD102" s="71"/>
+      <c r="AE102" s="72"/>
+      <c r="AF102" s="73"/>
       <c r="AG102" s="31"/>
-      <c r="AH102" s="63"/>
-      <c r="AI102" s="64"/>
-      <c r="AJ102" s="65"/>
+      <c r="AH102" s="71"/>
+      <c r="AI102" s="72"/>
+      <c r="AJ102" s="73"/>
       <c r="AK102" s="32"/>
-      <c r="AL102" s="63"/>
-      <c r="AM102" s="64"/>
-      <c r="AN102" s="65"/>
+      <c r="AL102" s="71"/>
+      <c r="AM102" s="72"/>
+      <c r="AN102" s="73"/>
       <c r="AO102" s="12"/>
       <c r="AP102" s="29"/>
       <c r="AQ102" s="26"/>
@@ -7736,70 +7753,70 @@
       <c r="AR104" s="26"/>
     </row>
     <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B105" s="68"/>
-      <c r="C105" s="69"/>
+      <c r="B105" s="87"/>
+      <c r="C105" s="88"/>
       <c r="D105" s="34"/>
       <c r="E105" s="32"/>
-      <c r="F105" s="68"/>
-      <c r="G105" s="69"/>
+      <c r="F105" s="87"/>
+      <c r="G105" s="88"/>
       <c r="H105" s="34"/>
       <c r="I105" s="32"/>
-      <c r="J105" s="68"/>
-      <c r="K105" s="69"/>
+      <c r="J105" s="87"/>
+      <c r="K105" s="88"/>
       <c r="L105" s="34"/>
       <c r="AO105" s="26"/>
     </row>
     <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B106" s="70"/>
-      <c r="C106" s="71"/>
-      <c r="D106" s="72"/>
+      <c r="B106" s="95"/>
+      <c r="C106" s="96"/>
+      <c r="D106" s="97"/>
       <c r="E106" s="32"/>
-      <c r="F106" s="70"/>
-      <c r="G106" s="71"/>
-      <c r="H106" s="72"/>
+      <c r="F106" s="95"/>
+      <c r="G106" s="96"/>
+      <c r="H106" s="97"/>
       <c r="I106" s="32"/>
-      <c r="J106" s="70"/>
-      <c r="K106" s="71"/>
-      <c r="L106" s="72"/>
+      <c r="J106" s="95"/>
+      <c r="K106" s="96"/>
+      <c r="L106" s="97"/>
     </row>
     <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B107" s="85"/>
-      <c r="C107" s="86"/>
-      <c r="D107" s="87"/>
+      <c r="B107" s="92"/>
+      <c r="C107" s="93"/>
+      <c r="D107" s="94"/>
       <c r="E107" s="32"/>
-      <c r="F107" s="85"/>
-      <c r="G107" s="86"/>
-      <c r="H107" s="87"/>
+      <c r="F107" s="92"/>
+      <c r="G107" s="93"/>
+      <c r="H107" s="94"/>
       <c r="I107" s="32"/>
-      <c r="J107" s="85"/>
-      <c r="K107" s="86"/>
-      <c r="L107" s="87"/>
+      <c r="J107" s="92"/>
+      <c r="K107" s="93"/>
+      <c r="L107" s="94"/>
     </row>
     <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B108" s="93"/>
-      <c r="C108" s="94"/>
-      <c r="D108" s="95"/>
+      <c r="B108" s="81"/>
+      <c r="C108" s="82"/>
+      <c r="D108" s="83"/>
       <c r="E108" s="32"/>
-      <c r="F108" s="93"/>
-      <c r="G108" s="94"/>
-      <c r="H108" s="95"/>
+      <c r="F108" s="81"/>
+      <c r="G108" s="82"/>
+      <c r="H108" s="83"/>
       <c r="I108" s="31"/>
-      <c r="J108" s="93"/>
-      <c r="K108" s="94"/>
-      <c r="L108" s="95"/>
+      <c r="J108" s="81"/>
+      <c r="K108" s="82"/>
+      <c r="L108" s="83"/>
     </row>
     <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B109" s="63"/>
-      <c r="C109" s="64"/>
-      <c r="D109" s="65"/>
+      <c r="B109" s="71"/>
+      <c r="C109" s="72"/>
+      <c r="D109" s="73"/>
       <c r="E109" s="31"/>
-      <c r="F109" s="63"/>
-      <c r="G109" s="64"/>
-      <c r="H109" s="65"/>
+      <c r="F109" s="71"/>
+      <c r="G109" s="72"/>
+      <c r="H109" s="73"/>
       <c r="I109" s="31"/>
-      <c r="J109" s="63"/>
-      <c r="K109" s="64"/>
-      <c r="L109" s="65"/>
+      <c r="J109" s="71"/>
+      <c r="K109" s="72"/>
+      <c r="L109" s="73"/>
     </row>
     <row r="110" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B110" s="35"/>
@@ -7815,69 +7832,69 @@
       <c r="L110" s="35"/>
     </row>
     <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B111" s="68"/>
-      <c r="C111" s="69"/>
+      <c r="B111" s="87"/>
+      <c r="C111" s="88"/>
       <c r="D111" s="34"/>
       <c r="E111" s="31"/>
-      <c r="F111" s="68"/>
-      <c r="G111" s="69"/>
+      <c r="F111" s="87"/>
+      <c r="G111" s="88"/>
       <c r="H111" s="34"/>
       <c r="I111" s="31"/>
-      <c r="J111" s="68"/>
-      <c r="K111" s="69"/>
+      <c r="J111" s="87"/>
+      <c r="K111" s="88"/>
       <c r="L111" s="34"/>
     </row>
     <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B112" s="70"/>
-      <c r="C112" s="71"/>
-      <c r="D112" s="72"/>
+      <c r="B112" s="95"/>
+      <c r="C112" s="96"/>
+      <c r="D112" s="97"/>
       <c r="E112" s="32"/>
-      <c r="F112" s="70"/>
-      <c r="G112" s="71"/>
-      <c r="H112" s="72"/>
+      <c r="F112" s="95"/>
+      <c r="G112" s="96"/>
+      <c r="H112" s="97"/>
       <c r="I112" s="32"/>
-      <c r="J112" s="70"/>
-      <c r="K112" s="71"/>
-      <c r="L112" s="72"/>
+      <c r="J112" s="95"/>
+      <c r="K112" s="96"/>
+      <c r="L112" s="97"/>
     </row>
     <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B113" s="85"/>
-      <c r="C113" s="86"/>
-      <c r="D113" s="87"/>
+      <c r="B113" s="92"/>
+      <c r="C113" s="93"/>
+      <c r="D113" s="94"/>
       <c r="E113" s="35"/>
-      <c r="F113" s="85"/>
-      <c r="G113" s="86"/>
-      <c r="H113" s="87"/>
+      <c r="F113" s="92"/>
+      <c r="G113" s="93"/>
+      <c r="H113" s="94"/>
       <c r="I113" s="35"/>
-      <c r="J113" s="85"/>
-      <c r="K113" s="86"/>
-      <c r="L113" s="87"/>
+      <c r="J113" s="92"/>
+      <c r="K113" s="93"/>
+      <c r="L113" s="94"/>
     </row>
     <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B114" s="93"/>
-      <c r="C114" s="94"/>
-      <c r="D114" s="95"/>
+      <c r="B114" s="81"/>
+      <c r="C114" s="82"/>
+      <c r="D114" s="83"/>
       <c r="E114" s="32"/>
-      <c r="F114" s="93"/>
-      <c r="G114" s="94"/>
-      <c r="H114" s="95"/>
+      <c r="F114" s="81"/>
+      <c r="G114" s="82"/>
+      <c r="H114" s="83"/>
       <c r="I114" s="32"/>
-      <c r="J114" s="93"/>
-      <c r="K114" s="94"/>
-      <c r="L114" s="95"/>
+      <c r="J114" s="81"/>
+      <c r="K114" s="82"/>
+      <c r="L114" s="83"/>
     </row>
     <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B115" s="63"/>
-      <c r="C115" s="64"/>
-      <c r="D115" s="65"/>
+      <c r="B115" s="71"/>
+      <c r="C115" s="72"/>
+      <c r="D115" s="73"/>
       <c r="E115" s="31"/>
-      <c r="F115" s="63"/>
-      <c r="G115" s="64"/>
-      <c r="H115" s="65"/>
+      <c r="F115" s="71"/>
+      <c r="G115" s="72"/>
+      <c r="H115" s="73"/>
       <c r="I115" s="31"/>
-      <c r="J115" s="63"/>
-      <c r="K115" s="64"/>
-      <c r="L115" s="65"/>
+      <c r="J115" s="71"/>
+      <c r="K115" s="72"/>
+      <c r="L115" s="73"/>
     </row>
     <row r="116" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B116" s="35"/>
@@ -7893,69 +7910,69 @@
       <c r="L116" s="35"/>
     </row>
     <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="68"/>
-      <c r="C117" s="69"/>
+      <c r="B117" s="87"/>
+      <c r="C117" s="88"/>
       <c r="D117" s="34"/>
       <c r="E117" s="32"/>
-      <c r="F117" s="68"/>
-      <c r="G117" s="69"/>
+      <c r="F117" s="87"/>
+      <c r="G117" s="88"/>
       <c r="H117" s="34"/>
       <c r="I117" s="32"/>
-      <c r="J117" s="68"/>
-      <c r="K117" s="69"/>
+      <c r="J117" s="87"/>
+      <c r="K117" s="88"/>
       <c r="L117" s="34"/>
     </row>
     <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B118" s="70"/>
-      <c r="C118" s="71"/>
-      <c r="D118" s="72"/>
+      <c r="B118" s="95"/>
+      <c r="C118" s="96"/>
+      <c r="D118" s="97"/>
       <c r="E118" s="32"/>
-      <c r="F118" s="70"/>
-      <c r="G118" s="71"/>
-      <c r="H118" s="72"/>
+      <c r="F118" s="95"/>
+      <c r="G118" s="96"/>
+      <c r="H118" s="97"/>
       <c r="I118" s="32"/>
-      <c r="J118" s="70"/>
-      <c r="K118" s="71"/>
-      <c r="L118" s="72"/>
+      <c r="J118" s="95"/>
+      <c r="K118" s="96"/>
+      <c r="L118" s="97"/>
     </row>
     <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B119" s="85"/>
-      <c r="C119" s="86"/>
-      <c r="D119" s="87"/>
+      <c r="B119" s="92"/>
+      <c r="C119" s="93"/>
+      <c r="D119" s="94"/>
       <c r="E119" s="32"/>
-      <c r="F119" s="85"/>
-      <c r="G119" s="86"/>
-      <c r="H119" s="87"/>
+      <c r="F119" s="92"/>
+      <c r="G119" s="93"/>
+      <c r="H119" s="94"/>
       <c r="I119" s="32"/>
-      <c r="J119" s="85"/>
-      <c r="K119" s="86"/>
-      <c r="L119" s="87"/>
+      <c r="J119" s="92"/>
+      <c r="K119" s="93"/>
+      <c r="L119" s="94"/>
     </row>
     <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B120" s="93"/>
-      <c r="C120" s="94"/>
-      <c r="D120" s="95"/>
+      <c r="B120" s="81"/>
+      <c r="C120" s="82"/>
+      <c r="D120" s="83"/>
       <c r="E120" s="32"/>
-      <c r="F120" s="93"/>
-      <c r="G120" s="94"/>
-      <c r="H120" s="95"/>
+      <c r="F120" s="81"/>
+      <c r="G120" s="82"/>
+      <c r="H120" s="83"/>
       <c r="I120" s="32"/>
-      <c r="J120" s="93"/>
-      <c r="K120" s="94"/>
-      <c r="L120" s="95"/>
+      <c r="J120" s="81"/>
+      <c r="K120" s="82"/>
+      <c r="L120" s="83"/>
     </row>
     <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B121" s="63"/>
-      <c r="C121" s="64"/>
-      <c r="D121" s="65"/>
+      <c r="B121" s="71"/>
+      <c r="C121" s="72"/>
+      <c r="D121" s="73"/>
       <c r="E121" s="31"/>
-      <c r="F121" s="63"/>
-      <c r="G121" s="64"/>
-      <c r="H121" s="65"/>
+      <c r="F121" s="71"/>
+      <c r="G121" s="72"/>
+      <c r="H121" s="73"/>
       <c r="I121" s="31"/>
-      <c r="J121" s="63"/>
-      <c r="K121" s="64"/>
-      <c r="L121" s="65"/>
+      <c r="J121" s="71"/>
+      <c r="K121" s="72"/>
+      <c r="L121" s="73"/>
     </row>
     <row r="122" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B122" s="35"/>
@@ -7971,69 +7988,69 @@
       <c r="L122" s="35"/>
     </row>
     <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="68"/>
-      <c r="C123" s="69"/>
+      <c r="B123" s="87"/>
+      <c r="C123" s="88"/>
       <c r="D123" s="34"/>
       <c r="E123" s="32"/>
-      <c r="F123" s="68"/>
-      <c r="G123" s="69"/>
+      <c r="F123" s="87"/>
+      <c r="G123" s="88"/>
       <c r="H123" s="34"/>
       <c r="I123" s="32"/>
-      <c r="J123" s="68"/>
-      <c r="K123" s="69"/>
+      <c r="J123" s="87"/>
+      <c r="K123" s="88"/>
       <c r="L123" s="34"/>
     </row>
     <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B124" s="70"/>
-      <c r="C124" s="71"/>
-      <c r="D124" s="72"/>
+      <c r="B124" s="95"/>
+      <c r="C124" s="96"/>
+      <c r="D124" s="97"/>
       <c r="E124" s="32"/>
-      <c r="F124" s="70"/>
-      <c r="G124" s="71"/>
-      <c r="H124" s="72"/>
+      <c r="F124" s="95"/>
+      <c r="G124" s="96"/>
+      <c r="H124" s="97"/>
       <c r="I124" s="32"/>
-      <c r="J124" s="70"/>
-      <c r="K124" s="71"/>
-      <c r="L124" s="72"/>
+      <c r="J124" s="95"/>
+      <c r="K124" s="96"/>
+      <c r="L124" s="97"/>
     </row>
     <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="85"/>
-      <c r="C125" s="86"/>
-      <c r="D125" s="87"/>
+      <c r="B125" s="92"/>
+      <c r="C125" s="93"/>
+      <c r="D125" s="94"/>
       <c r="E125" s="32"/>
-      <c r="F125" s="85"/>
-      <c r="G125" s="86"/>
-      <c r="H125" s="87"/>
+      <c r="F125" s="92"/>
+      <c r="G125" s="93"/>
+      <c r="H125" s="94"/>
       <c r="I125" s="32"/>
-      <c r="J125" s="85"/>
-      <c r="K125" s="86"/>
-      <c r="L125" s="87"/>
+      <c r="J125" s="92"/>
+      <c r="K125" s="93"/>
+      <c r="L125" s="94"/>
     </row>
     <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B126" s="93"/>
-      <c r="C126" s="94"/>
-      <c r="D126" s="95"/>
+      <c r="B126" s="81"/>
+      <c r="C126" s="82"/>
+      <c r="D126" s="83"/>
       <c r="E126" s="32"/>
-      <c r="F126" s="93"/>
-      <c r="G126" s="94"/>
-      <c r="H126" s="95"/>
+      <c r="F126" s="81"/>
+      <c r="G126" s="82"/>
+      <c r="H126" s="83"/>
       <c r="I126" s="31"/>
-      <c r="J126" s="93"/>
-      <c r="K126" s="94"/>
-      <c r="L126" s="95"/>
+      <c r="J126" s="81"/>
+      <c r="K126" s="82"/>
+      <c r="L126" s="83"/>
     </row>
     <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B127" s="63"/>
-      <c r="C127" s="64"/>
-      <c r="D127" s="65"/>
+      <c r="B127" s="71"/>
+      <c r="C127" s="72"/>
+      <c r="D127" s="73"/>
       <c r="E127" s="31"/>
-      <c r="F127" s="63"/>
-      <c r="G127" s="64"/>
-      <c r="H127" s="65"/>
+      <c r="F127" s="71"/>
+      <c r="G127" s="72"/>
+      <c r="H127" s="73"/>
       <c r="I127" s="31"/>
-      <c r="J127" s="63"/>
-      <c r="K127" s="64"/>
-      <c r="L127" s="65"/>
+      <c r="J127" s="71"/>
+      <c r="K127" s="72"/>
+      <c r="L127" s="73"/>
     </row>
     <row r="128" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B128" s="35"/>
@@ -8049,74 +8066,912 @@
       <c r="L128" s="35"/>
     </row>
     <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B129" s="68"/>
-      <c r="C129" s="69"/>
+      <c r="B129" s="87"/>
+      <c r="C129" s="88"/>
       <c r="D129" s="34"/>
       <c r="E129" s="31"/>
-      <c r="F129" s="68"/>
-      <c r="G129" s="69"/>
+      <c r="F129" s="87"/>
+      <c r="G129" s="88"/>
       <c r="H129" s="34"/>
       <c r="I129" s="32"/>
-      <c r="J129" s="68"/>
-      <c r="K129" s="69"/>
+      <c r="J129" s="87"/>
+      <c r="K129" s="88"/>
       <c r="L129" s="34"/>
     </row>
     <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B130" s="70"/>
-      <c r="C130" s="71"/>
-      <c r="D130" s="72"/>
+      <c r="B130" s="95"/>
+      <c r="C130" s="96"/>
+      <c r="D130" s="97"/>
       <c r="E130" s="32"/>
-      <c r="F130" s="70"/>
-      <c r="G130" s="71"/>
-      <c r="H130" s="72"/>
+      <c r="F130" s="95"/>
+      <c r="G130" s="96"/>
+      <c r="H130" s="97"/>
       <c r="I130" s="32"/>
-      <c r="J130" s="70"/>
-      <c r="K130" s="71"/>
-      <c r="L130" s="72"/>
+      <c r="J130" s="95"/>
+      <c r="K130" s="96"/>
+      <c r="L130" s="97"/>
     </row>
     <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B131" s="85"/>
-      <c r="C131" s="86"/>
-      <c r="D131" s="87"/>
+      <c r="B131" s="92"/>
+      <c r="C131" s="93"/>
+      <c r="D131" s="94"/>
       <c r="E131" s="35"/>
-      <c r="F131" s="85"/>
-      <c r="G131" s="86"/>
-      <c r="H131" s="87"/>
+      <c r="F131" s="92"/>
+      <c r="G131" s="93"/>
+      <c r="H131" s="94"/>
       <c r="I131" s="32"/>
-      <c r="J131" s="85"/>
-      <c r="K131" s="86"/>
-      <c r="L131" s="87"/>
+      <c r="J131" s="92"/>
+      <c r="K131" s="93"/>
+      <c r="L131" s="94"/>
     </row>
     <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B132" s="93"/>
-      <c r="C132" s="94"/>
-      <c r="D132" s="95"/>
+      <c r="B132" s="81"/>
+      <c r="C132" s="82"/>
+      <c r="D132" s="83"/>
       <c r="E132" s="35"/>
-      <c r="F132" s="93"/>
-      <c r="G132" s="94"/>
-      <c r="H132" s="95"/>
+      <c r="F132" s="81"/>
+      <c r="G132" s="82"/>
+      <c r="H132" s="83"/>
       <c r="I132" s="31"/>
-      <c r="J132" s="93"/>
-      <c r="K132" s="94"/>
-      <c r="L132" s="95"/>
+      <c r="J132" s="81"/>
+      <c r="K132" s="82"/>
+      <c r="L132" s="83"/>
     </row>
     <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B133" s="63"/>
-      <c r="C133" s="64"/>
-      <c r="D133" s="65"/>
+      <c r="B133" s="71"/>
+      <c r="C133" s="72"/>
+      <c r="D133" s="73"/>
       <c r="E133" s="31"/>
-      <c r="F133" s="63"/>
-      <c r="G133" s="64"/>
-      <c r="H133" s="65"/>
+      <c r="F133" s="71"/>
+      <c r="G133" s="72"/>
+      <c r="H133" s="73"/>
       <c r="I133" s="31"/>
-      <c r="J133" s="63"/>
-      <c r="K133" s="64"/>
-      <c r="L133" s="65"/>
+      <c r="J133" s="71"/>
+      <c r="K133" s="72"/>
+      <c r="L133" s="73"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0" selectUnlockedCells="1"/>
   <dataConsolidate/>
   <mergeCells count="862">
+    <mergeCell ref="B97:D97"/>
+    <mergeCell ref="F97:H97"/>
+    <mergeCell ref="J97:L97"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="F99:G99"/>
+    <mergeCell ref="J99:K99"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="J87:K87"/>
+    <mergeCell ref="B91:D91"/>
+    <mergeCell ref="F91:H91"/>
+    <mergeCell ref="J91:L91"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="F93:G93"/>
+    <mergeCell ref="J93:K93"/>
+    <mergeCell ref="AL57:AN57"/>
+    <mergeCell ref="AL59:AM59"/>
+    <mergeCell ref="AL46:AN46"/>
+    <mergeCell ref="F79:H79"/>
+    <mergeCell ref="J79:L79"/>
+    <mergeCell ref="F71:H71"/>
+    <mergeCell ref="J71:L71"/>
+    <mergeCell ref="F64:H64"/>
+    <mergeCell ref="F78:H78"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="R50:T50"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="J48:L48"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="AL56:AN56"/>
+    <mergeCell ref="AL54:AN54"/>
+    <mergeCell ref="AL53:AN53"/>
+    <mergeCell ref="AL49:AN49"/>
+    <mergeCell ref="AL55:AN55"/>
+    <mergeCell ref="F60:H60"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="J60:L60"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R41:T41"/>
+    <mergeCell ref="R40:T40"/>
+    <mergeCell ref="R43:T43"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="R39:T39"/>
+    <mergeCell ref="V38:W38"/>
+    <mergeCell ref="V39:X39"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="V43:X43"/>
+    <mergeCell ref="AD56:AF56"/>
+    <mergeCell ref="AH57:AJ57"/>
+    <mergeCell ref="AH59:AI59"/>
+    <mergeCell ref="AH56:AJ56"/>
+    <mergeCell ref="AH53:AJ53"/>
+    <mergeCell ref="AH47:AJ47"/>
+    <mergeCell ref="AD59:AE59"/>
+    <mergeCell ref="AD53:AF53"/>
+    <mergeCell ref="AD50:AF50"/>
+    <mergeCell ref="AD52:AE52"/>
+    <mergeCell ref="AD57:AF57"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="F82:H82"/>
+    <mergeCell ref="AL50:AN50"/>
+    <mergeCell ref="AL52:AM52"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="F62:H62"/>
+    <mergeCell ref="F61:H61"/>
+    <mergeCell ref="J64:L64"/>
+    <mergeCell ref="F69:H69"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="J66:K66"/>
+    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="F67:H67"/>
+    <mergeCell ref="J67:L67"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="F68:H68"/>
+    <mergeCell ref="J68:L68"/>
+    <mergeCell ref="F63:H63"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="J78:L78"/>
+    <mergeCell ref="J81:K81"/>
+    <mergeCell ref="J82:L82"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B95:D95"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="J70:L70"/>
+    <mergeCell ref="B71:D71"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="F70:H70"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="F76:H76"/>
+    <mergeCell ref="F90:H90"/>
+    <mergeCell ref="F95:H95"/>
+    <mergeCell ref="F89:H89"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="F94:H94"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="B85:D85"/>
+    <mergeCell ref="F85:H85"/>
+    <mergeCell ref="F75:G75"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="F54:H54"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="J100:L100"/>
+    <mergeCell ref="J88:L88"/>
+    <mergeCell ref="J77:L77"/>
+    <mergeCell ref="J76:L76"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="B96:D96"/>
+    <mergeCell ref="F96:H96"/>
+    <mergeCell ref="B100:D100"/>
+    <mergeCell ref="F100:H100"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="F88:H88"/>
+    <mergeCell ref="B89:D89"/>
+    <mergeCell ref="F83:H83"/>
+    <mergeCell ref="F84:H84"/>
+    <mergeCell ref="F77:H77"/>
+    <mergeCell ref="J53:L53"/>
+    <mergeCell ref="J54:L54"/>
+    <mergeCell ref="N91:P91"/>
+    <mergeCell ref="N97:P97"/>
+    <mergeCell ref="J96:L96"/>
+    <mergeCell ref="J90:L90"/>
+    <mergeCell ref="N99:O99"/>
+    <mergeCell ref="N88:P88"/>
+    <mergeCell ref="N83:P83"/>
+    <mergeCell ref="N84:P84"/>
+    <mergeCell ref="N90:P90"/>
+    <mergeCell ref="J89:L89"/>
+    <mergeCell ref="J83:L83"/>
+    <mergeCell ref="J84:L84"/>
+    <mergeCell ref="N89:P89"/>
+    <mergeCell ref="N87:O87"/>
+    <mergeCell ref="N93:O93"/>
+    <mergeCell ref="N85:P85"/>
+    <mergeCell ref="J85:L85"/>
+    <mergeCell ref="R102:T102"/>
+    <mergeCell ref="R100:T100"/>
+    <mergeCell ref="V100:X100"/>
+    <mergeCell ref="R101:T101"/>
+    <mergeCell ref="N100:P100"/>
+    <mergeCell ref="Z100:AB100"/>
+    <mergeCell ref="N94:P94"/>
+    <mergeCell ref="R95:T95"/>
+    <mergeCell ref="N96:P96"/>
+    <mergeCell ref="R99:S99"/>
+    <mergeCell ref="V99:W99"/>
+    <mergeCell ref="Z99:AA99"/>
+    <mergeCell ref="V95:X95"/>
+    <mergeCell ref="Z96:AB96"/>
+    <mergeCell ref="R96:T96"/>
+    <mergeCell ref="N101:P101"/>
+    <mergeCell ref="N95:P95"/>
+    <mergeCell ref="V101:X101"/>
+    <mergeCell ref="Z101:AB101"/>
+    <mergeCell ref="Z94:AB94"/>
+    <mergeCell ref="Z95:AB95"/>
+    <mergeCell ref="B108:D108"/>
+    <mergeCell ref="J102:L102"/>
+    <mergeCell ref="J112:L112"/>
+    <mergeCell ref="J111:K111"/>
+    <mergeCell ref="B106:D106"/>
+    <mergeCell ref="B107:D107"/>
+    <mergeCell ref="F106:H106"/>
+    <mergeCell ref="F105:G105"/>
+    <mergeCell ref="N102:P102"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="F102:H102"/>
+    <mergeCell ref="F107:H107"/>
+    <mergeCell ref="J107:L107"/>
+    <mergeCell ref="J109:L109"/>
+    <mergeCell ref="B112:D112"/>
+    <mergeCell ref="B120:D120"/>
+    <mergeCell ref="B121:D121"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="F123:G123"/>
+    <mergeCell ref="B119:D119"/>
+    <mergeCell ref="B113:D113"/>
+    <mergeCell ref="F113:H113"/>
+    <mergeCell ref="J113:L113"/>
+    <mergeCell ref="B114:D114"/>
+    <mergeCell ref="F114:H114"/>
+    <mergeCell ref="J114:L114"/>
+    <mergeCell ref="B115:D115"/>
+    <mergeCell ref="F115:H115"/>
+    <mergeCell ref="J115:L115"/>
+    <mergeCell ref="F120:H120"/>
+    <mergeCell ref="B126:D126"/>
+    <mergeCell ref="F126:H126"/>
+    <mergeCell ref="J126:L126"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="J117:K117"/>
+    <mergeCell ref="J108:L108"/>
+    <mergeCell ref="F121:H121"/>
+    <mergeCell ref="J123:K123"/>
+    <mergeCell ref="F112:H112"/>
+    <mergeCell ref="B125:D125"/>
+    <mergeCell ref="F125:H125"/>
+    <mergeCell ref="J121:L121"/>
+    <mergeCell ref="J125:L125"/>
+    <mergeCell ref="B118:D118"/>
+    <mergeCell ref="F118:H118"/>
+    <mergeCell ref="B109:D109"/>
+    <mergeCell ref="F109:H109"/>
+    <mergeCell ref="F124:H124"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="F111:G111"/>
+    <mergeCell ref="J124:L124"/>
+    <mergeCell ref="F119:H119"/>
+    <mergeCell ref="J119:L119"/>
+    <mergeCell ref="J101:L101"/>
+    <mergeCell ref="J118:L118"/>
+    <mergeCell ref="B124:D124"/>
+    <mergeCell ref="F108:H108"/>
+    <mergeCell ref="B133:D133"/>
+    <mergeCell ref="F133:H133"/>
+    <mergeCell ref="J133:L133"/>
+    <mergeCell ref="B127:D127"/>
+    <mergeCell ref="F127:H127"/>
+    <mergeCell ref="J127:L127"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="F129:G129"/>
+    <mergeCell ref="J129:K129"/>
+    <mergeCell ref="B130:D130"/>
+    <mergeCell ref="F130:H130"/>
+    <mergeCell ref="J130:L130"/>
+    <mergeCell ref="B132:D132"/>
+    <mergeCell ref="F132:H132"/>
+    <mergeCell ref="J132:L132"/>
+    <mergeCell ref="B131:D131"/>
+    <mergeCell ref="F131:H131"/>
+    <mergeCell ref="J131:L131"/>
+    <mergeCell ref="J120:L120"/>
+    <mergeCell ref="B101:D101"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="N18:AB19"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="R14:T14"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="J105:K105"/>
+    <mergeCell ref="V41:X41"/>
+    <mergeCell ref="V40:X40"/>
+    <mergeCell ref="J106:L106"/>
+    <mergeCell ref="Z102:AB102"/>
+    <mergeCell ref="V102:X102"/>
+    <mergeCell ref="Z55:AB55"/>
+    <mergeCell ref="J75:K75"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="J69:L69"/>
+    <mergeCell ref="N62:P62"/>
+    <mergeCell ref="R62:T62"/>
+    <mergeCell ref="R71:T71"/>
+    <mergeCell ref="R76:T76"/>
+    <mergeCell ref="R63:T63"/>
+    <mergeCell ref="F101:H101"/>
+    <mergeCell ref="R94:T94"/>
+    <mergeCell ref="Z88:AB88"/>
+    <mergeCell ref="J94:L94"/>
+    <mergeCell ref="J95:L95"/>
+    <mergeCell ref="V94:X94"/>
+    <mergeCell ref="V96:X96"/>
+    <mergeCell ref="AH9:AJ9"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="AH21:AI21"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="Z20:AA20"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="V15:X15"/>
+    <mergeCell ref="V16:X16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="V13:W13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="AL9:AN9"/>
+    <mergeCell ref="AD9:AF9"/>
+    <mergeCell ref="AH16:AJ16"/>
+    <mergeCell ref="AL10:AN10"/>
+    <mergeCell ref="AL14:AN14"/>
+    <mergeCell ref="AL16:AN16"/>
+    <mergeCell ref="Z15:AB15"/>
+    <mergeCell ref="AD15:AF15"/>
+    <mergeCell ref="Z13:AA13"/>
+    <mergeCell ref="AL15:AN15"/>
+    <mergeCell ref="AL12:AM12"/>
+    <mergeCell ref="AD16:AF16"/>
+    <mergeCell ref="Z10:AB10"/>
+    <mergeCell ref="AH14:AJ14"/>
+    <mergeCell ref="Z14:AB14"/>
+    <mergeCell ref="AD14:AF14"/>
+    <mergeCell ref="AD13:AE13"/>
+    <mergeCell ref="AH10:AJ10"/>
+    <mergeCell ref="AH15:AJ15"/>
+    <mergeCell ref="AD10:AF10"/>
+    <mergeCell ref="AD12:AE12"/>
+    <mergeCell ref="AH12:AI12"/>
+    <mergeCell ref="Z12:AA12"/>
+    <mergeCell ref="Z16:AB16"/>
+    <mergeCell ref="AH31:AI31"/>
+    <mergeCell ref="AD31:AE31"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="Z21:AA21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="R22:T22"/>
+    <mergeCell ref="V22:X22"/>
+    <mergeCell ref="Z22:AB22"/>
+    <mergeCell ref="AD22:AF22"/>
+    <mergeCell ref="AH22:AJ22"/>
+    <mergeCell ref="AD29:AE29"/>
+    <mergeCell ref="AH29:AI29"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:T23"/>
+    <mergeCell ref="V23:X23"/>
+    <mergeCell ref="V27:W27"/>
+    <mergeCell ref="AD27:AE27"/>
+    <mergeCell ref="V31:W31"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="AL1:AN1"/>
+    <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="AD2:AF2"/>
+    <mergeCell ref="AH2:AJ2"/>
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="AH8:AJ8"/>
+    <mergeCell ref="AL6:AM6"/>
+    <mergeCell ref="AD1:AF1"/>
+    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="AL7:AM7"/>
+    <mergeCell ref="AD8:AF8"/>
+    <mergeCell ref="Z8:AB8"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AH7:AI7"/>
+    <mergeCell ref="AD7:AE7"/>
+    <mergeCell ref="Z7:AA7"/>
+    <mergeCell ref="AL8:AN8"/>
+    <mergeCell ref="AD4:AN5"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="AD6:AE6"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="V1:X1"/>
+    <mergeCell ref="V14:X14"/>
+    <mergeCell ref="R15:T15"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="B4:L5"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="V2:X2"/>
+    <mergeCell ref="N4:AB5"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="R9:T9"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="AH90:AJ90"/>
+    <mergeCell ref="AD42:AF42"/>
+    <mergeCell ref="AD48:AF48"/>
+    <mergeCell ref="Z9:AB9"/>
+    <mergeCell ref="R10:T10"/>
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="AD21:AE21"/>
+    <mergeCell ref="AD49:AF49"/>
+    <mergeCell ref="AD43:AF43"/>
+    <mergeCell ref="AD45:AE45"/>
+    <mergeCell ref="R48:T48"/>
+    <mergeCell ref="Z42:AB42"/>
+    <mergeCell ref="Z43:AB43"/>
+    <mergeCell ref="N36:AB37"/>
+    <mergeCell ref="Z48:AB48"/>
+    <mergeCell ref="Z45:AA45"/>
+    <mergeCell ref="Z46:AB46"/>
+    <mergeCell ref="AD38:AE38"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="AL82:AN82"/>
+    <mergeCell ref="AL102:AN102"/>
+    <mergeCell ref="AL101:AN101"/>
+    <mergeCell ref="AL96:AN96"/>
+    <mergeCell ref="AD102:AF102"/>
+    <mergeCell ref="AH102:AJ102"/>
+    <mergeCell ref="AL90:AN90"/>
+    <mergeCell ref="AL95:AN95"/>
+    <mergeCell ref="AD101:AF101"/>
+    <mergeCell ref="AH101:AJ101"/>
+    <mergeCell ref="AH100:AJ100"/>
+    <mergeCell ref="AL94:AN94"/>
+    <mergeCell ref="AD100:AF100"/>
+    <mergeCell ref="AD96:AF96"/>
+    <mergeCell ref="AD94:AF94"/>
+    <mergeCell ref="AD95:AF95"/>
+    <mergeCell ref="AH96:AJ96"/>
+    <mergeCell ref="AD90:AF90"/>
+    <mergeCell ref="AH95:AJ95"/>
+    <mergeCell ref="V90:X90"/>
+    <mergeCell ref="V88:X88"/>
+    <mergeCell ref="R90:T90"/>
+    <mergeCell ref="AH88:AJ88"/>
+    <mergeCell ref="AH89:AJ89"/>
+    <mergeCell ref="AD85:AF85"/>
+    <mergeCell ref="AL77:AN77"/>
+    <mergeCell ref="AL78:AN78"/>
+    <mergeCell ref="AD77:AF77"/>
+    <mergeCell ref="AD79:AF79"/>
+    <mergeCell ref="AH79:AJ79"/>
+    <mergeCell ref="AL79:AN79"/>
+    <mergeCell ref="AD81:AE81"/>
+    <mergeCell ref="AH81:AI81"/>
+    <mergeCell ref="AL81:AM81"/>
+    <mergeCell ref="AH78:AJ78"/>
+    <mergeCell ref="AD84:AF84"/>
+    <mergeCell ref="AH84:AJ84"/>
+    <mergeCell ref="AD83:AF83"/>
+    <mergeCell ref="AL100:AN100"/>
+    <mergeCell ref="AD97:AF97"/>
+    <mergeCell ref="AH97:AJ97"/>
+    <mergeCell ref="AL97:AN97"/>
+    <mergeCell ref="AH82:AJ82"/>
+    <mergeCell ref="AL88:AN88"/>
+    <mergeCell ref="AL89:AN89"/>
+    <mergeCell ref="AL83:AN83"/>
+    <mergeCell ref="AL84:AN84"/>
+    <mergeCell ref="AD88:AF88"/>
+    <mergeCell ref="AD89:AF89"/>
+    <mergeCell ref="AH87:AI87"/>
+    <mergeCell ref="AL87:AM87"/>
+    <mergeCell ref="AH85:AJ85"/>
+    <mergeCell ref="AL85:AN85"/>
+    <mergeCell ref="AD99:AE99"/>
+    <mergeCell ref="AH99:AI99"/>
+    <mergeCell ref="AL99:AM99"/>
+    <mergeCell ref="AH75:AI75"/>
+    <mergeCell ref="V89:X89"/>
+    <mergeCell ref="R89:T89"/>
+    <mergeCell ref="R84:T84"/>
+    <mergeCell ref="R85:T85"/>
+    <mergeCell ref="V85:X85"/>
+    <mergeCell ref="Z76:AB76"/>
+    <mergeCell ref="Z77:AB77"/>
+    <mergeCell ref="V76:X76"/>
+    <mergeCell ref="AH77:AJ77"/>
+    <mergeCell ref="AD78:AF78"/>
+    <mergeCell ref="V82:X82"/>
+    <mergeCell ref="R88:T88"/>
+    <mergeCell ref="V77:X77"/>
+    <mergeCell ref="V78:X78"/>
+    <mergeCell ref="R78:T78"/>
+    <mergeCell ref="V84:X84"/>
+    <mergeCell ref="R82:T82"/>
+    <mergeCell ref="V83:X83"/>
+    <mergeCell ref="R83:T83"/>
+    <mergeCell ref="AD82:AF82"/>
+    <mergeCell ref="AH83:AJ83"/>
+    <mergeCell ref="N78:P78"/>
+    <mergeCell ref="Z78:AB78"/>
+    <mergeCell ref="N79:P79"/>
+    <mergeCell ref="R79:T79"/>
+    <mergeCell ref="V79:X79"/>
+    <mergeCell ref="Z79:AB79"/>
+    <mergeCell ref="N81:O81"/>
+    <mergeCell ref="R81:S81"/>
+    <mergeCell ref="V81:W81"/>
+    <mergeCell ref="N82:P82"/>
+    <mergeCell ref="AH76:AJ76"/>
+    <mergeCell ref="AL76:AN76"/>
+    <mergeCell ref="AD76:AF76"/>
+    <mergeCell ref="Z81:AA81"/>
+    <mergeCell ref="AL62:AN62"/>
+    <mergeCell ref="AL63:AN63"/>
+    <mergeCell ref="AL71:AN71"/>
+    <mergeCell ref="AL70:AN70"/>
+    <mergeCell ref="AL69:AN69"/>
+    <mergeCell ref="N73:AB74"/>
+    <mergeCell ref="N75:O75"/>
+    <mergeCell ref="R75:S75"/>
+    <mergeCell ref="V75:W75"/>
+    <mergeCell ref="Z75:AA75"/>
+    <mergeCell ref="AD75:AE75"/>
+    <mergeCell ref="N64:P64"/>
+    <mergeCell ref="N70:P70"/>
+    <mergeCell ref="AH70:AJ70"/>
+    <mergeCell ref="AD70:AF70"/>
+    <mergeCell ref="Z69:AB69"/>
+    <mergeCell ref="Z70:AB70"/>
+    <mergeCell ref="V71:X71"/>
+    <mergeCell ref="AD63:AF63"/>
+    <mergeCell ref="AH64:AJ64"/>
+    <mergeCell ref="AD67:AF67"/>
+    <mergeCell ref="AL20:AM20"/>
+    <mergeCell ref="AL27:AM27"/>
+    <mergeCell ref="AL21:AM21"/>
+    <mergeCell ref="AH27:AI27"/>
+    <mergeCell ref="AD20:AE20"/>
+    <mergeCell ref="AH20:AI20"/>
+    <mergeCell ref="Z68:AB68"/>
+    <mergeCell ref="AD68:AF68"/>
+    <mergeCell ref="AH68:AJ68"/>
+    <mergeCell ref="AL68:AN68"/>
+    <mergeCell ref="Z63:AB63"/>
+    <mergeCell ref="AL60:AN60"/>
+    <mergeCell ref="AL64:AN64"/>
+    <mergeCell ref="AL61:AN61"/>
+    <mergeCell ref="Z56:AB56"/>
+    <mergeCell ref="AL22:AN22"/>
+    <mergeCell ref="Z23:AB23"/>
+    <mergeCell ref="AD23:AF23"/>
+    <mergeCell ref="AH23:AJ23"/>
+    <mergeCell ref="AL23:AN23"/>
+    <mergeCell ref="AD28:AE28"/>
+    <mergeCell ref="AH28:AI28"/>
+    <mergeCell ref="AL28:AM28"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="N61:P61"/>
+    <mergeCell ref="AD66:AE66"/>
+    <mergeCell ref="AH66:AI66"/>
+    <mergeCell ref="R61:T61"/>
+    <mergeCell ref="V61:X61"/>
+    <mergeCell ref="Z61:AB61"/>
+    <mergeCell ref="Z59:AA59"/>
+    <mergeCell ref="AH63:AJ63"/>
+    <mergeCell ref="AH62:AJ62"/>
+    <mergeCell ref="AD62:AF62"/>
+    <mergeCell ref="AD60:AF60"/>
+    <mergeCell ref="AH60:AJ60"/>
+    <mergeCell ref="V62:X62"/>
+    <mergeCell ref="V63:X63"/>
+    <mergeCell ref="Z64:AB64"/>
+    <mergeCell ref="R60:T60"/>
+    <mergeCell ref="V60:X60"/>
+    <mergeCell ref="Z60:AB60"/>
+    <mergeCell ref="V64:X64"/>
+    <mergeCell ref="R64:T64"/>
+    <mergeCell ref="N63:P63"/>
+    <mergeCell ref="N66:O66"/>
+    <mergeCell ref="N60:P60"/>
+    <mergeCell ref="V33:W33"/>
+    <mergeCell ref="Z33:AA33"/>
+    <mergeCell ref="N32:O32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="V32:W32"/>
+    <mergeCell ref="Z32:AA32"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="N29:O29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="V29:W29"/>
+    <mergeCell ref="Z29:AA29"/>
+    <mergeCell ref="Z27:AA27"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="V30:W30"/>
+    <mergeCell ref="Z31:AA31"/>
+    <mergeCell ref="V50:X50"/>
+    <mergeCell ref="Z53:AA53"/>
+    <mergeCell ref="R49:T49"/>
+    <mergeCell ref="R47:T47"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="J46:L46"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="N45:O45"/>
+    <mergeCell ref="J49:L49"/>
+    <mergeCell ref="J47:L47"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="Z54:AB54"/>
+    <mergeCell ref="Z50:AB50"/>
+    <mergeCell ref="V45:W45"/>
+    <mergeCell ref="V46:X46"/>
+    <mergeCell ref="V47:X47"/>
+    <mergeCell ref="Z49:AB49"/>
+    <mergeCell ref="V49:X49"/>
+    <mergeCell ref="V48:X48"/>
+    <mergeCell ref="AH34:AI34"/>
+    <mergeCell ref="AD46:AF46"/>
+    <mergeCell ref="AD47:AF47"/>
+    <mergeCell ref="AH40:AJ40"/>
+    <mergeCell ref="AH46:AJ46"/>
+    <mergeCell ref="AH45:AI45"/>
+    <mergeCell ref="AH38:AI38"/>
+    <mergeCell ref="AH39:AJ39"/>
+    <mergeCell ref="AD39:AF39"/>
+    <mergeCell ref="AD40:AF40"/>
+    <mergeCell ref="AL45:AM45"/>
+    <mergeCell ref="AL42:AN42"/>
+    <mergeCell ref="Z41:AB41"/>
+    <mergeCell ref="Z40:AB40"/>
+    <mergeCell ref="Z38:AA38"/>
+    <mergeCell ref="Z39:AB39"/>
+    <mergeCell ref="AL34:AM34"/>
+    <mergeCell ref="N55:P55"/>
+    <mergeCell ref="R56:T56"/>
+    <mergeCell ref="N56:P56"/>
+    <mergeCell ref="R54:T54"/>
+    <mergeCell ref="V54:X54"/>
+    <mergeCell ref="V53:W53"/>
+    <mergeCell ref="N54:P54"/>
+    <mergeCell ref="N53:P53"/>
+    <mergeCell ref="R55:T55"/>
+    <mergeCell ref="R53:T53"/>
+    <mergeCell ref="V56:X56"/>
+    <mergeCell ref="V55:X55"/>
+    <mergeCell ref="V42:X42"/>
+    <mergeCell ref="AH52:AI52"/>
+    <mergeCell ref="AH54:AJ54"/>
+    <mergeCell ref="AH55:AJ55"/>
+    <mergeCell ref="R42:T42"/>
+    <mergeCell ref="AL31:AM31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="R87:S87"/>
+    <mergeCell ref="V87:W87"/>
+    <mergeCell ref="Z87:AA87"/>
+    <mergeCell ref="AD87:AE87"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="V34:W34"/>
+    <mergeCell ref="Z34:AA34"/>
+    <mergeCell ref="AD34:AE34"/>
+    <mergeCell ref="R66:S66"/>
+    <mergeCell ref="V66:W66"/>
+    <mergeCell ref="Z66:AA66"/>
+    <mergeCell ref="R67:T67"/>
+    <mergeCell ref="V67:X67"/>
+    <mergeCell ref="Z67:AB67"/>
+    <mergeCell ref="V69:X69"/>
+    <mergeCell ref="R69:T69"/>
+    <mergeCell ref="V70:X70"/>
+    <mergeCell ref="R70:T70"/>
+    <mergeCell ref="R77:T77"/>
+    <mergeCell ref="AD33:AE33"/>
+    <mergeCell ref="AH33:AI33"/>
+    <mergeCell ref="AL33:AM33"/>
+    <mergeCell ref="N76:P76"/>
+    <mergeCell ref="N77:P77"/>
+    <mergeCell ref="R46:T46"/>
+    <mergeCell ref="Z85:AB85"/>
+    <mergeCell ref="Z89:AB89"/>
+    <mergeCell ref="Z90:AB90"/>
+    <mergeCell ref="Z83:AB83"/>
+    <mergeCell ref="Z84:AB84"/>
+    <mergeCell ref="Z82:AB82"/>
+    <mergeCell ref="V51:X51"/>
+    <mergeCell ref="Z51:AB51"/>
+    <mergeCell ref="Z62:AB62"/>
+    <mergeCell ref="N69:P69"/>
+    <mergeCell ref="N68:P68"/>
+    <mergeCell ref="R68:T68"/>
+    <mergeCell ref="V68:X68"/>
+    <mergeCell ref="N67:P67"/>
+    <mergeCell ref="N71:P71"/>
+    <mergeCell ref="N59:O59"/>
+    <mergeCell ref="R59:S59"/>
+    <mergeCell ref="V59:W59"/>
+    <mergeCell ref="N57:P57"/>
+    <mergeCell ref="V57:X57"/>
+    <mergeCell ref="R57:T57"/>
+    <mergeCell ref="R91:T91"/>
+    <mergeCell ref="V91:X91"/>
+    <mergeCell ref="Z91:AB91"/>
+    <mergeCell ref="AD91:AF91"/>
+    <mergeCell ref="AH91:AJ91"/>
+    <mergeCell ref="AL91:AN91"/>
+    <mergeCell ref="R97:T97"/>
+    <mergeCell ref="V97:X97"/>
+    <mergeCell ref="Z97:AB97"/>
+    <mergeCell ref="AD93:AE93"/>
+    <mergeCell ref="AH93:AI93"/>
+    <mergeCell ref="AL93:AM93"/>
+    <mergeCell ref="R93:S93"/>
+    <mergeCell ref="V93:W93"/>
+    <mergeCell ref="Z93:AA93"/>
+    <mergeCell ref="AH94:AJ94"/>
+    <mergeCell ref="AH13:AI13"/>
+    <mergeCell ref="AL13:AM13"/>
+    <mergeCell ref="AH67:AJ67"/>
+    <mergeCell ref="AL67:AN67"/>
+    <mergeCell ref="AH48:AJ48"/>
+    <mergeCell ref="AH50:AJ50"/>
+    <mergeCell ref="AL29:AM29"/>
+    <mergeCell ref="Z30:AA30"/>
+    <mergeCell ref="AD30:AE30"/>
+    <mergeCell ref="AH30:AI30"/>
+    <mergeCell ref="AL30:AM30"/>
+    <mergeCell ref="N25:AB26"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="V28:W28"/>
+    <mergeCell ref="Z28:AA28"/>
+    <mergeCell ref="AL40:AN40"/>
+    <mergeCell ref="AL41:AN41"/>
+    <mergeCell ref="AL47:AN47"/>
+    <mergeCell ref="AL48:AN48"/>
+    <mergeCell ref="AH42:AJ42"/>
+    <mergeCell ref="AH43:AJ43"/>
+    <mergeCell ref="AH49:AJ49"/>
+    <mergeCell ref="Z47:AB47"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="AL75:AM75"/>
+    <mergeCell ref="AH71:AJ71"/>
+    <mergeCell ref="AD71:AF71"/>
+    <mergeCell ref="Z71:AB71"/>
+    <mergeCell ref="AL66:AM66"/>
+    <mergeCell ref="AD69:AF69"/>
+    <mergeCell ref="AH69:AJ69"/>
+    <mergeCell ref="AD64:AF64"/>
+    <mergeCell ref="AD61:AF61"/>
+    <mergeCell ref="AH61:AJ61"/>
+    <mergeCell ref="Z57:AB57"/>
+    <mergeCell ref="AD54:AF54"/>
+    <mergeCell ref="AD55:AF55"/>
+    <mergeCell ref="AD32:AE32"/>
+    <mergeCell ref="AH32:AI32"/>
+    <mergeCell ref="AL32:AM32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="AL38:AM38"/>
+    <mergeCell ref="AL39:AN39"/>
+    <mergeCell ref="AH41:AJ41"/>
+    <mergeCell ref="AD41:AF41"/>
+    <mergeCell ref="AL43:AN43"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="B27:C27"/>
     <mergeCell ref="B52:C52"/>
     <mergeCell ref="F41:H41"/>
     <mergeCell ref="B41:D41"/>
@@ -8141,850 +8996,12 @@
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="F43:H43"/>
     <mergeCell ref="J43:L43"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="AL75:AM75"/>
-    <mergeCell ref="AH71:AJ71"/>
-    <mergeCell ref="AD71:AF71"/>
-    <mergeCell ref="Z71:AB71"/>
-    <mergeCell ref="AL66:AM66"/>
-    <mergeCell ref="AD69:AF69"/>
-    <mergeCell ref="AH69:AJ69"/>
-    <mergeCell ref="AD64:AF64"/>
-    <mergeCell ref="AD61:AF61"/>
-    <mergeCell ref="AH61:AJ61"/>
-    <mergeCell ref="Z57:AB57"/>
-    <mergeCell ref="AD54:AF54"/>
-    <mergeCell ref="AD55:AF55"/>
-    <mergeCell ref="AD32:AE32"/>
-    <mergeCell ref="AH32:AI32"/>
-    <mergeCell ref="AL32:AM32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="AL38:AM38"/>
-    <mergeCell ref="AL39:AN39"/>
-    <mergeCell ref="AH41:AJ41"/>
-    <mergeCell ref="AD41:AF41"/>
-    <mergeCell ref="AL43:AN43"/>
-    <mergeCell ref="AH13:AI13"/>
-    <mergeCell ref="AL13:AM13"/>
-    <mergeCell ref="AH67:AJ67"/>
-    <mergeCell ref="AL67:AN67"/>
-    <mergeCell ref="AH48:AJ48"/>
-    <mergeCell ref="AH50:AJ50"/>
-    <mergeCell ref="AL29:AM29"/>
-    <mergeCell ref="Z30:AA30"/>
-    <mergeCell ref="AD30:AE30"/>
-    <mergeCell ref="AH30:AI30"/>
-    <mergeCell ref="AL30:AM30"/>
-    <mergeCell ref="N25:AB26"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="V28:W28"/>
-    <mergeCell ref="Z28:AA28"/>
-    <mergeCell ref="AL40:AN40"/>
-    <mergeCell ref="AL41:AN41"/>
-    <mergeCell ref="AL47:AN47"/>
-    <mergeCell ref="AL48:AN48"/>
-    <mergeCell ref="AH42:AJ42"/>
-    <mergeCell ref="AH43:AJ43"/>
-    <mergeCell ref="AH49:AJ49"/>
-    <mergeCell ref="Z47:AB47"/>
-    <mergeCell ref="R91:T91"/>
-    <mergeCell ref="V91:X91"/>
-    <mergeCell ref="Z91:AB91"/>
-    <mergeCell ref="AD91:AF91"/>
-    <mergeCell ref="AH91:AJ91"/>
-    <mergeCell ref="AL91:AN91"/>
-    <mergeCell ref="R97:T97"/>
-    <mergeCell ref="V97:X97"/>
-    <mergeCell ref="Z97:AB97"/>
-    <mergeCell ref="AD93:AE93"/>
-    <mergeCell ref="AH93:AI93"/>
-    <mergeCell ref="AL93:AM93"/>
-    <mergeCell ref="R93:S93"/>
-    <mergeCell ref="V93:W93"/>
-    <mergeCell ref="Z93:AA93"/>
-    <mergeCell ref="N76:P76"/>
-    <mergeCell ref="N77:P77"/>
-    <mergeCell ref="R46:T46"/>
-    <mergeCell ref="Z85:AB85"/>
-    <mergeCell ref="Z89:AB89"/>
-    <mergeCell ref="Z90:AB90"/>
-    <mergeCell ref="Z83:AB83"/>
-    <mergeCell ref="Z84:AB84"/>
-    <mergeCell ref="Z82:AB82"/>
-    <mergeCell ref="V51:X51"/>
-    <mergeCell ref="Z51:AB51"/>
-    <mergeCell ref="Z62:AB62"/>
-    <mergeCell ref="N69:P69"/>
-    <mergeCell ref="N68:P68"/>
-    <mergeCell ref="R68:T68"/>
-    <mergeCell ref="V68:X68"/>
-    <mergeCell ref="N67:P67"/>
-    <mergeCell ref="N71:P71"/>
-    <mergeCell ref="N59:O59"/>
-    <mergeCell ref="R59:S59"/>
-    <mergeCell ref="V59:W59"/>
-    <mergeCell ref="N57:P57"/>
-    <mergeCell ref="V57:X57"/>
-    <mergeCell ref="R57:T57"/>
-    <mergeCell ref="AL31:AM31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="R87:S87"/>
-    <mergeCell ref="V87:W87"/>
-    <mergeCell ref="Z87:AA87"/>
-    <mergeCell ref="AD87:AE87"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="V34:W34"/>
-    <mergeCell ref="Z34:AA34"/>
-    <mergeCell ref="AD34:AE34"/>
-    <mergeCell ref="R66:S66"/>
-    <mergeCell ref="V66:W66"/>
-    <mergeCell ref="Z66:AA66"/>
-    <mergeCell ref="R67:T67"/>
-    <mergeCell ref="V67:X67"/>
-    <mergeCell ref="Z67:AB67"/>
-    <mergeCell ref="V69:X69"/>
-    <mergeCell ref="R69:T69"/>
-    <mergeCell ref="V70:X70"/>
-    <mergeCell ref="R70:T70"/>
-    <mergeCell ref="R77:T77"/>
-    <mergeCell ref="AD33:AE33"/>
-    <mergeCell ref="AH33:AI33"/>
-    <mergeCell ref="AL33:AM33"/>
-    <mergeCell ref="AL45:AM45"/>
-    <mergeCell ref="AL42:AN42"/>
-    <mergeCell ref="Z41:AB41"/>
-    <mergeCell ref="Z40:AB40"/>
-    <mergeCell ref="Z38:AA38"/>
-    <mergeCell ref="Z39:AB39"/>
-    <mergeCell ref="AL34:AM34"/>
-    <mergeCell ref="N55:P55"/>
-    <mergeCell ref="R56:T56"/>
-    <mergeCell ref="N56:P56"/>
-    <mergeCell ref="R54:T54"/>
-    <mergeCell ref="V54:X54"/>
-    <mergeCell ref="V53:W53"/>
-    <mergeCell ref="N54:P54"/>
-    <mergeCell ref="N53:P53"/>
-    <mergeCell ref="R55:T55"/>
-    <mergeCell ref="R53:T53"/>
-    <mergeCell ref="V56:X56"/>
-    <mergeCell ref="V55:X55"/>
-    <mergeCell ref="V42:X42"/>
-    <mergeCell ref="AH52:AI52"/>
-    <mergeCell ref="AH54:AJ54"/>
-    <mergeCell ref="AH55:AJ55"/>
-    <mergeCell ref="R42:T42"/>
-    <mergeCell ref="Z54:AB54"/>
-    <mergeCell ref="Z50:AB50"/>
-    <mergeCell ref="V45:W45"/>
-    <mergeCell ref="V46:X46"/>
-    <mergeCell ref="V47:X47"/>
-    <mergeCell ref="Z49:AB49"/>
-    <mergeCell ref="V49:X49"/>
-    <mergeCell ref="V48:X48"/>
-    <mergeCell ref="AH34:AI34"/>
-    <mergeCell ref="AD46:AF46"/>
-    <mergeCell ref="AD47:AF47"/>
-    <mergeCell ref="AH40:AJ40"/>
-    <mergeCell ref="AH46:AJ46"/>
-    <mergeCell ref="AH45:AI45"/>
-    <mergeCell ref="AH38:AI38"/>
-    <mergeCell ref="AH39:AJ39"/>
-    <mergeCell ref="AD39:AF39"/>
-    <mergeCell ref="AD40:AF40"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="J46:L46"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="N45:O45"/>
-    <mergeCell ref="J49:L49"/>
-    <mergeCell ref="J47:L47"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="N60:P60"/>
-    <mergeCell ref="V33:W33"/>
-    <mergeCell ref="Z33:AA33"/>
-    <mergeCell ref="N32:O32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="V32:W32"/>
-    <mergeCell ref="Z32:AA32"/>
-    <mergeCell ref="N34:O34"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="N29:O29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="V29:W29"/>
-    <mergeCell ref="Z29:AA29"/>
-    <mergeCell ref="Z27:AA27"/>
-    <mergeCell ref="N30:O30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="V30:W30"/>
-    <mergeCell ref="Z31:AA31"/>
-    <mergeCell ref="V50:X50"/>
-    <mergeCell ref="Z53:AA53"/>
-    <mergeCell ref="R49:T49"/>
-    <mergeCell ref="R47:T47"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="AL28:AM28"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="N61:P61"/>
-    <mergeCell ref="AD66:AE66"/>
-    <mergeCell ref="AH66:AI66"/>
-    <mergeCell ref="R61:T61"/>
-    <mergeCell ref="V61:X61"/>
-    <mergeCell ref="Z61:AB61"/>
-    <mergeCell ref="Z59:AA59"/>
-    <mergeCell ref="AH63:AJ63"/>
-    <mergeCell ref="AH62:AJ62"/>
-    <mergeCell ref="AD62:AF62"/>
-    <mergeCell ref="AD60:AF60"/>
-    <mergeCell ref="AH60:AJ60"/>
-    <mergeCell ref="V62:X62"/>
-    <mergeCell ref="V63:X63"/>
-    <mergeCell ref="Z64:AB64"/>
-    <mergeCell ref="R60:T60"/>
-    <mergeCell ref="V60:X60"/>
-    <mergeCell ref="Z60:AB60"/>
-    <mergeCell ref="V64:X64"/>
-    <mergeCell ref="R64:T64"/>
-    <mergeCell ref="N63:P63"/>
-    <mergeCell ref="N66:O66"/>
-    <mergeCell ref="AH64:AJ64"/>
-    <mergeCell ref="AD67:AF67"/>
-    <mergeCell ref="AL20:AM20"/>
-    <mergeCell ref="AL27:AM27"/>
-    <mergeCell ref="AL21:AM21"/>
-    <mergeCell ref="AH27:AI27"/>
-    <mergeCell ref="AD20:AE20"/>
-    <mergeCell ref="AH20:AI20"/>
-    <mergeCell ref="Z68:AB68"/>
-    <mergeCell ref="AD68:AF68"/>
-    <mergeCell ref="AH68:AJ68"/>
-    <mergeCell ref="AL68:AN68"/>
-    <mergeCell ref="Z63:AB63"/>
-    <mergeCell ref="AL60:AN60"/>
-    <mergeCell ref="AL64:AN64"/>
-    <mergeCell ref="AL61:AN61"/>
-    <mergeCell ref="Z56:AB56"/>
-    <mergeCell ref="AL22:AN22"/>
-    <mergeCell ref="Z23:AB23"/>
-    <mergeCell ref="AD23:AF23"/>
-    <mergeCell ref="AH23:AJ23"/>
-    <mergeCell ref="AL23:AN23"/>
-    <mergeCell ref="AD28:AE28"/>
-    <mergeCell ref="AH28:AI28"/>
-    <mergeCell ref="N82:P82"/>
-    <mergeCell ref="AH76:AJ76"/>
-    <mergeCell ref="AL76:AN76"/>
-    <mergeCell ref="AD76:AF76"/>
-    <mergeCell ref="Z81:AA81"/>
-    <mergeCell ref="AL62:AN62"/>
-    <mergeCell ref="AL63:AN63"/>
-    <mergeCell ref="AL71:AN71"/>
-    <mergeCell ref="AL70:AN70"/>
-    <mergeCell ref="AL69:AN69"/>
-    <mergeCell ref="N73:AB74"/>
-    <mergeCell ref="N75:O75"/>
-    <mergeCell ref="R75:S75"/>
-    <mergeCell ref="V75:W75"/>
-    <mergeCell ref="Z75:AA75"/>
-    <mergeCell ref="AD75:AE75"/>
-    <mergeCell ref="N64:P64"/>
-    <mergeCell ref="N70:P70"/>
-    <mergeCell ref="AH70:AJ70"/>
-    <mergeCell ref="AD70:AF70"/>
-    <mergeCell ref="Z69:AB69"/>
-    <mergeCell ref="Z70:AB70"/>
-    <mergeCell ref="V71:X71"/>
-    <mergeCell ref="AD63:AF63"/>
-    <mergeCell ref="N78:P78"/>
-    <mergeCell ref="Z78:AB78"/>
-    <mergeCell ref="N79:P79"/>
-    <mergeCell ref="R79:T79"/>
-    <mergeCell ref="V79:X79"/>
-    <mergeCell ref="Z79:AB79"/>
-    <mergeCell ref="N81:O81"/>
-    <mergeCell ref="R81:S81"/>
-    <mergeCell ref="V81:W81"/>
-    <mergeCell ref="AH75:AI75"/>
-    <mergeCell ref="V89:X89"/>
-    <mergeCell ref="R89:T89"/>
-    <mergeCell ref="R84:T84"/>
-    <mergeCell ref="R85:T85"/>
-    <mergeCell ref="V85:X85"/>
-    <mergeCell ref="Z76:AB76"/>
-    <mergeCell ref="Z77:AB77"/>
-    <mergeCell ref="V76:X76"/>
-    <mergeCell ref="AH77:AJ77"/>
-    <mergeCell ref="AD78:AF78"/>
-    <mergeCell ref="V82:X82"/>
-    <mergeCell ref="R88:T88"/>
-    <mergeCell ref="V77:X77"/>
-    <mergeCell ref="V78:X78"/>
-    <mergeCell ref="R78:T78"/>
-    <mergeCell ref="V84:X84"/>
-    <mergeCell ref="R82:T82"/>
-    <mergeCell ref="V83:X83"/>
-    <mergeCell ref="R83:T83"/>
-    <mergeCell ref="AD82:AF82"/>
-    <mergeCell ref="AH83:AJ83"/>
-    <mergeCell ref="AH94:AJ94"/>
-    <mergeCell ref="AL100:AN100"/>
-    <mergeCell ref="AD97:AF97"/>
-    <mergeCell ref="AH97:AJ97"/>
-    <mergeCell ref="AL97:AN97"/>
-    <mergeCell ref="AH82:AJ82"/>
-    <mergeCell ref="AL88:AN88"/>
-    <mergeCell ref="AL89:AN89"/>
-    <mergeCell ref="AL83:AN83"/>
-    <mergeCell ref="AL84:AN84"/>
-    <mergeCell ref="AD88:AF88"/>
-    <mergeCell ref="AD89:AF89"/>
-    <mergeCell ref="AH87:AI87"/>
-    <mergeCell ref="AL87:AM87"/>
-    <mergeCell ref="AH85:AJ85"/>
-    <mergeCell ref="AL85:AN85"/>
-    <mergeCell ref="AD99:AE99"/>
-    <mergeCell ref="AH99:AI99"/>
-    <mergeCell ref="AL99:AM99"/>
-    <mergeCell ref="R90:T90"/>
-    <mergeCell ref="AH88:AJ88"/>
-    <mergeCell ref="AH89:AJ89"/>
-    <mergeCell ref="AD85:AF85"/>
-    <mergeCell ref="AL77:AN77"/>
-    <mergeCell ref="AL78:AN78"/>
-    <mergeCell ref="AD77:AF77"/>
-    <mergeCell ref="AD79:AF79"/>
-    <mergeCell ref="AH79:AJ79"/>
-    <mergeCell ref="AL79:AN79"/>
-    <mergeCell ref="AD81:AE81"/>
-    <mergeCell ref="AH81:AI81"/>
-    <mergeCell ref="AL81:AM81"/>
-    <mergeCell ref="AH78:AJ78"/>
-    <mergeCell ref="AD84:AF84"/>
-    <mergeCell ref="AH84:AJ84"/>
-    <mergeCell ref="AD83:AF83"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="AL82:AN82"/>
-    <mergeCell ref="AL102:AN102"/>
-    <mergeCell ref="AL101:AN101"/>
-    <mergeCell ref="AL96:AN96"/>
-    <mergeCell ref="AD102:AF102"/>
-    <mergeCell ref="AH102:AJ102"/>
-    <mergeCell ref="AL90:AN90"/>
-    <mergeCell ref="AL95:AN95"/>
-    <mergeCell ref="AD101:AF101"/>
-    <mergeCell ref="AH101:AJ101"/>
-    <mergeCell ref="AH100:AJ100"/>
-    <mergeCell ref="AL94:AN94"/>
-    <mergeCell ref="AD100:AF100"/>
-    <mergeCell ref="AD96:AF96"/>
-    <mergeCell ref="AD94:AF94"/>
-    <mergeCell ref="AD95:AF95"/>
-    <mergeCell ref="AH96:AJ96"/>
-    <mergeCell ref="AD90:AF90"/>
-    <mergeCell ref="AH95:AJ95"/>
-    <mergeCell ref="V90:X90"/>
-    <mergeCell ref="V88:X88"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="AH90:AJ90"/>
-    <mergeCell ref="AD42:AF42"/>
-    <mergeCell ref="AD48:AF48"/>
-    <mergeCell ref="Z9:AB9"/>
-    <mergeCell ref="R10:T10"/>
-    <mergeCell ref="V10:X10"/>
-    <mergeCell ref="AD21:AE21"/>
-    <mergeCell ref="AD49:AF49"/>
-    <mergeCell ref="AD43:AF43"/>
-    <mergeCell ref="AD45:AE45"/>
-    <mergeCell ref="R48:T48"/>
-    <mergeCell ref="Z42:AB42"/>
-    <mergeCell ref="Z43:AB43"/>
-    <mergeCell ref="N36:AB37"/>
-    <mergeCell ref="Z48:AB48"/>
-    <mergeCell ref="Z45:AA45"/>
-    <mergeCell ref="Z46:AB46"/>
-    <mergeCell ref="AD38:AE38"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="R9:T9"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="V8:X8"/>
-    <mergeCell ref="V9:X9"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="R1:T1"/>
-    <mergeCell ref="V1:X1"/>
-    <mergeCell ref="V14:X14"/>
-    <mergeCell ref="R15:T15"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="B4:L5"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="V2:X2"/>
-    <mergeCell ref="N4:AB5"/>
-    <mergeCell ref="AL1:AN1"/>
-    <mergeCell ref="Z2:AB2"/>
-    <mergeCell ref="AD2:AF2"/>
-    <mergeCell ref="AH2:AJ2"/>
-    <mergeCell ref="AL2:AN2"/>
-    <mergeCell ref="AH8:AJ8"/>
-    <mergeCell ref="AL6:AM6"/>
-    <mergeCell ref="AD1:AF1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="AL7:AM7"/>
-    <mergeCell ref="AD8:AF8"/>
-    <mergeCell ref="Z8:AB8"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AH7:AI7"/>
-    <mergeCell ref="AD7:AE7"/>
-    <mergeCell ref="Z7:AA7"/>
-    <mergeCell ref="AL8:AN8"/>
-    <mergeCell ref="AD4:AN5"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="AD6:AE6"/>
-    <mergeCell ref="AH31:AI31"/>
-    <mergeCell ref="AD31:AE31"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="Z21:AA21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="R22:T22"/>
-    <mergeCell ref="V22:X22"/>
-    <mergeCell ref="Z22:AB22"/>
-    <mergeCell ref="AD22:AF22"/>
-    <mergeCell ref="AH22:AJ22"/>
-    <mergeCell ref="AD29:AE29"/>
-    <mergeCell ref="AH29:AI29"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:T23"/>
-    <mergeCell ref="V23:X23"/>
-    <mergeCell ref="V27:W27"/>
-    <mergeCell ref="AD27:AE27"/>
-    <mergeCell ref="V31:W31"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="AL9:AN9"/>
-    <mergeCell ref="AD9:AF9"/>
-    <mergeCell ref="AH16:AJ16"/>
-    <mergeCell ref="AL10:AN10"/>
-    <mergeCell ref="AL14:AN14"/>
-    <mergeCell ref="AL16:AN16"/>
-    <mergeCell ref="Z15:AB15"/>
-    <mergeCell ref="AD15:AF15"/>
-    <mergeCell ref="Z13:AA13"/>
-    <mergeCell ref="AL15:AN15"/>
-    <mergeCell ref="AL12:AM12"/>
-    <mergeCell ref="AD16:AF16"/>
-    <mergeCell ref="Z10:AB10"/>
-    <mergeCell ref="AH14:AJ14"/>
-    <mergeCell ref="Z14:AB14"/>
-    <mergeCell ref="AD14:AF14"/>
-    <mergeCell ref="AD13:AE13"/>
-    <mergeCell ref="AH10:AJ10"/>
-    <mergeCell ref="AH15:AJ15"/>
-    <mergeCell ref="AD10:AF10"/>
-    <mergeCell ref="AD12:AE12"/>
-    <mergeCell ref="AH12:AI12"/>
-    <mergeCell ref="Z12:AA12"/>
-    <mergeCell ref="Z16:AB16"/>
-    <mergeCell ref="AH9:AJ9"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="AH21:AI21"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="Z20:AA20"/>
-    <mergeCell ref="J15:L15"/>
-    <mergeCell ref="V15:X15"/>
-    <mergeCell ref="V16:X16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="V13:W13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="J50:L50"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="J105:K105"/>
-    <mergeCell ref="V41:X41"/>
-    <mergeCell ref="V40:X40"/>
-    <mergeCell ref="J106:L106"/>
-    <mergeCell ref="Z102:AB102"/>
-    <mergeCell ref="V102:X102"/>
-    <mergeCell ref="Z55:AB55"/>
-    <mergeCell ref="J75:K75"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="J69:L69"/>
-    <mergeCell ref="N62:P62"/>
-    <mergeCell ref="R62:T62"/>
-    <mergeCell ref="R71:T71"/>
-    <mergeCell ref="R76:T76"/>
-    <mergeCell ref="R63:T63"/>
-    <mergeCell ref="F101:H101"/>
-    <mergeCell ref="R94:T94"/>
-    <mergeCell ref="Z88:AB88"/>
-    <mergeCell ref="J94:L94"/>
-    <mergeCell ref="J95:L95"/>
-    <mergeCell ref="V94:X94"/>
-    <mergeCell ref="V96:X96"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="N18:AB19"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="R14:T14"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="J101:L101"/>
-    <mergeCell ref="J118:L118"/>
-    <mergeCell ref="B124:D124"/>
-    <mergeCell ref="F108:H108"/>
-    <mergeCell ref="B133:D133"/>
-    <mergeCell ref="F133:H133"/>
-    <mergeCell ref="J133:L133"/>
-    <mergeCell ref="B127:D127"/>
-    <mergeCell ref="F127:H127"/>
-    <mergeCell ref="J127:L127"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="F129:G129"/>
-    <mergeCell ref="J129:K129"/>
-    <mergeCell ref="B130:D130"/>
-    <mergeCell ref="F130:H130"/>
-    <mergeCell ref="J130:L130"/>
-    <mergeCell ref="B132:D132"/>
-    <mergeCell ref="F132:H132"/>
-    <mergeCell ref="J132:L132"/>
-    <mergeCell ref="B131:D131"/>
-    <mergeCell ref="F131:H131"/>
-    <mergeCell ref="J131:L131"/>
-    <mergeCell ref="J120:L120"/>
-    <mergeCell ref="B101:D101"/>
-    <mergeCell ref="B126:D126"/>
-    <mergeCell ref="F126:H126"/>
-    <mergeCell ref="J126:L126"/>
-    <mergeCell ref="F117:G117"/>
-    <mergeCell ref="J117:K117"/>
-    <mergeCell ref="J108:L108"/>
-    <mergeCell ref="F121:H121"/>
-    <mergeCell ref="J123:K123"/>
-    <mergeCell ref="F112:H112"/>
-    <mergeCell ref="B125:D125"/>
-    <mergeCell ref="F125:H125"/>
-    <mergeCell ref="J121:L121"/>
-    <mergeCell ref="J125:L125"/>
-    <mergeCell ref="B118:D118"/>
-    <mergeCell ref="F118:H118"/>
-    <mergeCell ref="B109:D109"/>
-    <mergeCell ref="F109:H109"/>
-    <mergeCell ref="F124:H124"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="F111:G111"/>
-    <mergeCell ref="J124:L124"/>
-    <mergeCell ref="F119:H119"/>
-    <mergeCell ref="J119:L119"/>
-    <mergeCell ref="B120:D120"/>
-    <mergeCell ref="B121:D121"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="F123:G123"/>
-    <mergeCell ref="B119:D119"/>
-    <mergeCell ref="B113:D113"/>
-    <mergeCell ref="F113:H113"/>
-    <mergeCell ref="J113:L113"/>
-    <mergeCell ref="B114:D114"/>
-    <mergeCell ref="F114:H114"/>
-    <mergeCell ref="J114:L114"/>
-    <mergeCell ref="B115:D115"/>
-    <mergeCell ref="F115:H115"/>
-    <mergeCell ref="J115:L115"/>
-    <mergeCell ref="F120:H120"/>
-    <mergeCell ref="B108:D108"/>
-    <mergeCell ref="J102:L102"/>
-    <mergeCell ref="J112:L112"/>
-    <mergeCell ref="J111:K111"/>
-    <mergeCell ref="B106:D106"/>
-    <mergeCell ref="B107:D107"/>
-    <mergeCell ref="F106:H106"/>
-    <mergeCell ref="F105:G105"/>
-    <mergeCell ref="N102:P102"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="F102:H102"/>
-    <mergeCell ref="F107:H107"/>
-    <mergeCell ref="J107:L107"/>
-    <mergeCell ref="J109:L109"/>
-    <mergeCell ref="B112:D112"/>
-    <mergeCell ref="R102:T102"/>
-    <mergeCell ref="R100:T100"/>
-    <mergeCell ref="V100:X100"/>
-    <mergeCell ref="R101:T101"/>
-    <mergeCell ref="N100:P100"/>
-    <mergeCell ref="Z100:AB100"/>
-    <mergeCell ref="N94:P94"/>
-    <mergeCell ref="R95:T95"/>
-    <mergeCell ref="N96:P96"/>
-    <mergeCell ref="R99:S99"/>
-    <mergeCell ref="V99:W99"/>
-    <mergeCell ref="Z99:AA99"/>
-    <mergeCell ref="V95:X95"/>
-    <mergeCell ref="Z96:AB96"/>
-    <mergeCell ref="R96:T96"/>
-    <mergeCell ref="N101:P101"/>
-    <mergeCell ref="N95:P95"/>
-    <mergeCell ref="V101:X101"/>
-    <mergeCell ref="Z101:AB101"/>
-    <mergeCell ref="Z94:AB94"/>
-    <mergeCell ref="Z95:AB95"/>
-    <mergeCell ref="N91:P91"/>
-    <mergeCell ref="N97:P97"/>
-    <mergeCell ref="J96:L96"/>
-    <mergeCell ref="J90:L90"/>
-    <mergeCell ref="N99:O99"/>
-    <mergeCell ref="N88:P88"/>
-    <mergeCell ref="N83:P83"/>
-    <mergeCell ref="N84:P84"/>
-    <mergeCell ref="N90:P90"/>
-    <mergeCell ref="J89:L89"/>
-    <mergeCell ref="J83:L83"/>
-    <mergeCell ref="J84:L84"/>
-    <mergeCell ref="N89:P89"/>
-    <mergeCell ref="N87:O87"/>
-    <mergeCell ref="N93:O93"/>
-    <mergeCell ref="N85:P85"/>
-    <mergeCell ref="J85:L85"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="F53:H53"/>
-    <mergeCell ref="F54:H54"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="J100:L100"/>
-    <mergeCell ref="J88:L88"/>
-    <mergeCell ref="J77:L77"/>
-    <mergeCell ref="J76:L76"/>
-    <mergeCell ref="J55:L55"/>
-    <mergeCell ref="B96:D96"/>
-    <mergeCell ref="F96:H96"/>
-    <mergeCell ref="B100:D100"/>
-    <mergeCell ref="F100:H100"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="F88:H88"/>
-    <mergeCell ref="B89:D89"/>
-    <mergeCell ref="F83:H83"/>
-    <mergeCell ref="F84:H84"/>
-    <mergeCell ref="F77:H77"/>
-    <mergeCell ref="J53:L53"/>
-    <mergeCell ref="J54:L54"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="J78:L78"/>
-    <mergeCell ref="J81:K81"/>
-    <mergeCell ref="J82:L82"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B95:D95"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="J70:L70"/>
-    <mergeCell ref="B71:D71"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="F70:H70"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="F76:H76"/>
-    <mergeCell ref="F90:H90"/>
-    <mergeCell ref="F95:H95"/>
-    <mergeCell ref="F89:H89"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="F94:H94"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B79:D79"/>
-    <mergeCell ref="B85:D85"/>
-    <mergeCell ref="F85:H85"/>
-    <mergeCell ref="F75:G75"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="F82:H82"/>
-    <mergeCell ref="AL50:AN50"/>
-    <mergeCell ref="AL52:AM52"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="F62:H62"/>
-    <mergeCell ref="F61:H61"/>
-    <mergeCell ref="J64:L64"/>
-    <mergeCell ref="F69:H69"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="J63:L63"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="J66:K66"/>
-    <mergeCell ref="B67:D67"/>
-    <mergeCell ref="F67:H67"/>
-    <mergeCell ref="J67:L67"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="F68:H68"/>
-    <mergeCell ref="J68:L68"/>
-    <mergeCell ref="F63:H63"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="AD56:AF56"/>
-    <mergeCell ref="AH57:AJ57"/>
-    <mergeCell ref="AH59:AI59"/>
-    <mergeCell ref="AH56:AJ56"/>
-    <mergeCell ref="AH53:AJ53"/>
-    <mergeCell ref="AH47:AJ47"/>
-    <mergeCell ref="AD59:AE59"/>
-    <mergeCell ref="AD53:AF53"/>
-    <mergeCell ref="AD50:AF50"/>
-    <mergeCell ref="AD52:AE52"/>
-    <mergeCell ref="AD57:AF57"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="N38:O38"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R41:T41"/>
-    <mergeCell ref="R40:T40"/>
-    <mergeCell ref="R43:T43"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="R39:T39"/>
-    <mergeCell ref="V38:W38"/>
-    <mergeCell ref="V39:X39"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="V43:X43"/>
-    <mergeCell ref="AL57:AN57"/>
-    <mergeCell ref="AL59:AM59"/>
-    <mergeCell ref="AL46:AN46"/>
-    <mergeCell ref="F79:H79"/>
-    <mergeCell ref="J79:L79"/>
-    <mergeCell ref="F71:H71"/>
-    <mergeCell ref="J71:L71"/>
-    <mergeCell ref="F64:H64"/>
-    <mergeCell ref="F78:H78"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="R50:T50"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="J48:L48"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="AL56:AN56"/>
-    <mergeCell ref="AL54:AN54"/>
-    <mergeCell ref="AL53:AN53"/>
-    <mergeCell ref="AL49:AN49"/>
-    <mergeCell ref="AL55:AN55"/>
-    <mergeCell ref="F60:H60"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="J60:L60"/>
-    <mergeCell ref="B97:D97"/>
-    <mergeCell ref="F97:H97"/>
-    <mergeCell ref="J97:L97"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="F99:G99"/>
-    <mergeCell ref="J99:K99"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="J87:K87"/>
-    <mergeCell ref="B91:D91"/>
-    <mergeCell ref="F91:H91"/>
-    <mergeCell ref="J91:L91"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="F93:G93"/>
-    <mergeCell ref="J93:K93"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="D29:D34 AJ29:AJ34 X29:X34 T29:T34 AB29:AB34 AF29:AF34 P29:P34 H29:H34 L29:L34 AN29:AN34">
       <formula1>$AP$68:$AP$71</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="AL41:AN43 AH69:AJ71 AL90:AN91 J48:L50 N29:O34 Z29:AA34 F55:H57 J132:L133 V78:X79 R78:T79 AD96:AF97 Z56:AB57 R69:T71 Z78:AB79 Z48:AB51 Z96:AB97 B55:D57 AH55:AJ57 V8:X10 R101:T102 AD69:AF71 J114:L115 AL78:AN79 AL69:AN71 AH41:AJ43 R8:T10 B41:D43 B108:D109 B62:D64 Z14:AB16 AD41:AF43 R14:T16 F48:H50 AL14:AN16 F62:H64 J55:L57 N78:P79 R62:T64 B8:D10 J120:L121 F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 B126:D127 AD14:AF16 B114:D115 J126:L127 N48:P50 Z101:AB102 AD22:AF23 N84:P85 AD84:AF85 R22:T23 V14:X16 V22:X23 F108:H109 Z22:AB23 AL101:AN102 AL22:AN23 R55:T57 AD90:AF91 AD55:AF57 N22:P23 N90:P91 J22:L23 J62:L64 V48:X51 N96:P97 R84:T85 V96:X97 R41:T43 AD101:AF102 N14:P16 AD62:AF64 AH90:AJ91 V84:X85 Z41:AB43 AH62:AJ64 N101:P102 Z84:AB85 V41:X43 AH78:AJ79 AL84:AN85 AH48:AJ50 V56:X57 B29:C34 J29:K34 AH96:AJ97 AH101:AJ102 AL48:AN50 V90:X91 AL96:AN97 Z8:AB10 AH84:AJ85 AL8:AN10 N62:P64 N8:P10 AD78:AF79 V69:X71 AD8:AF10 V101:X102 V62:X64 AH8:AJ10 N55:P57 R29:S34 Z62:AB64 N41:P43 V29:W34 AL55:AN57 B78:D79 AL62:AN64 F29:G34 AD48:AF50 N69:P71 AL29:AM34 AH22:AJ23 AD29:AE34 AH29:AI34 R96:T97 AH14:AJ16 F22:H23 R90:T91 F8:H10 R48:T50 J8:L10 F14:H16 Z90:AB91 J14:L16 B14:D16 B22:D23 J41:L43 F69:H71 B69:D71 B48:D50 J69:L71 F41:H43 F78:H79 B96:D97 J78:L79 F84:H85 J101:L102 B84:D85 B101:D102 B90:D91 F96:H97 F101:H102 J90:L91 J96:L97 F90:H91 J84:L85 Z69:AB71">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="AL41:AN43 AH69:AJ71 AL90:AN91 J48:L50 N29:O34 Z29:AA34 F55:H57 J132:L133 V78:X79 R78:T79 AD96:AF97 Z56:AB57 R69:T71 Z78:AB79 Z48:AB51 Z96:AB97 B55:D57 AH55:AJ57 V8:X10 R101:T102 AD69:AF71 J114:L115 AL78:AN79 AL69:AN71 AH41:AJ43 R8:T10 B41:D43 B108:D109 B62:D64 Z14:AB16 AD41:AF43 R14:T16 F48:H50 AL14:AN16 F62:H64 J55:L57 N78:P79 R62:T64 B8:D10 J120:L121 F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 B126:D127 AD14:AF16 B114:D115 J126:L127 N48:P50 Z101:AB102 AD22:AF23 N84:P85 AD84:AF85 R22:T23 V14:X16 V22:X23 F108:H109 Z22:AB23 AL101:AN102 AL22:AN23 R55:T57 AD90:AF91 AD55:AF57 N22:P23 N90:P91 J22:L23 J62:L64 V48:X51 N96:P97 R84:T85 V96:X97 R41:T43 AD101:AF102 N14:P16 AD62:AF64 AH90:AJ91 V84:X85 Z41:AB43 AH62:AJ64 N101:P102 Z84:AB85 V41:X43 AH78:AJ79 AL84:AN85 AH48:AJ50 V56:X57 B29:C34 J29:K34 AH96:AJ97 AH101:AJ102 AL48:AN50 V90:X91 AL96:AN97 Z8:AB10 AH84:AJ85 AL8:AN10 N62:P64 N8:P10 AD78:AF79 V69:X71 Z69:AB71 V101:X102 V62:X64 AH8:AJ10 N55:P57 R29:S34 Z62:AB64 N41:P43 V29:W34 AL55:AN57 B78:D79 AL62:AN64 F29:G34 AD48:AF50 N69:P71 AL29:AM34 AH22:AJ23 AD29:AE34 AH29:AI34 R96:T97 AH14:AJ16 F22:H23 R90:T91 F8:H10 R48:T50 J8:L10 F14:H16 Z90:AB91 J14:L16 B14:D16 B22:D23 J41:L43 F69:H71 B69:D71 B48:D50 J69:L71 F41:H43 F78:H79 B96:D97 J78:L79 F84:H85 J101:L102 B84:D85 B101:D102 B90:D91 F96:H97 F101:H102 J90:L91 J96:L97 F90:H91 J84:L85 AD8:AF10">
       <formula1>$AP$6:$AP$30</formula1>
     </dataValidation>
   </dataValidations>

--- a/Gorev-Listesi.xlsx
+++ b/Gorev-Listesi.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="110">
   <si>
     <t>CUMA</t>
   </si>
@@ -284,9 +284,6 @@
     <t>A.KOÇ.</t>
   </si>
   <si>
-    <t>14.30</t>
-  </si>
-  <si>
     <t>KUR'AN BİZE NE SÖYLER</t>
   </si>
   <si>
@@ -351,6 +348,12 @@
   </si>
   <si>
     <t>Haliç Kongre Merkezi</t>
+  </si>
+  <si>
+    <t>Sancaktepe</t>
+  </si>
+  <si>
+    <t>13.30</t>
   </si>
 </sst>
 </file>
@@ -1791,6 +1794,15 @@
     <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="9" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="8" borderId="8" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1800,15 +1812,6 @@
     <xf numFmtId="49" fontId="7" fillId="8" borderId="10" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="9" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="7" fillId="9" borderId="17" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1827,6 +1830,15 @@
     <xf numFmtId="49" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1852,15 +1864,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="13" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2235,7 +2238,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="1" width="167" row="3" locked="1">
+  <wetp:taskpane dockstate="right" visibility="1" width="104" row="3" locked="1">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -2686,7 +2689,7 @@
       <c r="AF7" s="18"/>
       <c r="AG7" s="38"/>
       <c r="AH7" s="111" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI7" s="112"/>
       <c r="AJ7" s="62"/>
@@ -2738,11 +2741,11 @@
       <c r="AE8" s="66"/>
       <c r="AF8" s="67"/>
       <c r="AG8" s="35"/>
-      <c r="AH8" s="145" t="s">
+      <c r="AH8" s="142" t="s">
         <v>85</v>
       </c>
-      <c r="AI8" s="146"/>
-      <c r="AJ8" s="147"/>
+      <c r="AI8" s="143"/>
+      <c r="AJ8" s="144"/>
       <c r="AK8" s="37"/>
       <c r="AL8" s="81" t="s">
         <v>12</v>
@@ -2791,9 +2794,9 @@
       <c r="AE9" s="66"/>
       <c r="AF9" s="67"/>
       <c r="AG9" s="43"/>
-      <c r="AH9" s="163"/>
-      <c r="AI9" s="164"/>
-      <c r="AJ9" s="165"/>
+      <c r="AH9" s="154"/>
+      <c r="AI9" s="155"/>
+      <c r="AJ9" s="156"/>
       <c r="AK9" s="43"/>
       <c r="AL9" s="108" t="s">
         <v>15</v>
@@ -2847,7 +2850,7 @@
       <c r="AJ10" s="150"/>
       <c r="AK10" s="44"/>
       <c r="AL10" s="151" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AM10" s="152"/>
       <c r="AN10" s="153"/>
@@ -3125,7 +3128,7 @@
       </c>
       <c r="AQ15" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR15" s="30"/>
     </row>
@@ -3135,7 +3138,7 @@
       <c r="D16" s="86"/>
       <c r="E16" s="44"/>
       <c r="F16" s="151" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G16" s="152"/>
       <c r="H16" s="153"/>
@@ -3343,7 +3346,7 @@
       <c r="L20" s="57"/>
       <c r="M20" s="4"/>
       <c r="N20" s="114" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O20" s="115"/>
       <c r="P20" s="60" t="s">
@@ -3351,7 +3354,7 @@
       </c>
       <c r="Q20" s="39"/>
       <c r="R20" s="114" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="S20" s="115"/>
       <c r="T20" s="60" t="s">
@@ -3378,8 +3381,8 @@
         <v>56</v>
       </c>
       <c r="AI20" s="88"/>
-      <c r="AJ20" s="34" t="s">
-        <v>86</v>
+      <c r="AJ20" s="59" t="s">
+        <v>109</v>
       </c>
       <c r="AK20" s="36"/>
       <c r="AL20" s="87"/>
@@ -3390,7 +3393,7 @@
       </c>
       <c r="AQ20" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR20" s="30"/>
     </row>
@@ -3408,13 +3411,13 @@
       <c r="L21" s="61"/>
       <c r="M21" s="15"/>
       <c r="N21" s="111" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O21" s="112"/>
       <c r="P21" s="62"/>
       <c r="Q21" s="36"/>
       <c r="R21" s="111" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="S21" s="112"/>
       <c r="T21" s="62"/>
@@ -3464,17 +3467,17 @@
       <c r="K22" s="82"/>
       <c r="L22" s="83"/>
       <c r="M22" s="4"/>
-      <c r="N22" s="145" t="s">
+      <c r="N22" s="142" t="s">
+        <v>96</v>
+      </c>
+      <c r="O22" s="143"/>
+      <c r="P22" s="144"/>
+      <c r="Q22" s="35"/>
+      <c r="R22" s="142" t="s">
         <v>97</v>
       </c>
-      <c r="O22" s="146"/>
-      <c r="P22" s="147"/>
-      <c r="Q22" s="35"/>
-      <c r="R22" s="145" t="s">
-        <v>98</v>
-      </c>
-      <c r="S22" s="146"/>
-      <c r="T22" s="147"/>
+      <c r="S22" s="143"/>
+      <c r="T22" s="144"/>
       <c r="U22" s="37"/>
       <c r="V22" s="81" t="s">
         <v>12</v>
@@ -3490,11 +3493,11 @@
       <c r="AE22" s="82"/>
       <c r="AF22" s="83"/>
       <c r="AG22" s="35"/>
-      <c r="AH22" s="142" t="s">
+      <c r="AH22" s="145" t="s">
         <v>9</v>
       </c>
-      <c r="AI22" s="143"/>
-      <c r="AJ22" s="144"/>
+      <c r="AI22" s="146"/>
+      <c r="AJ22" s="147"/>
       <c r="AK22" s="37"/>
       <c r="AL22" s="81"/>
       <c r="AM22" s="82"/>
@@ -4522,7 +4525,7 @@
       <c r="AF41" s="67"/>
       <c r="AG41" s="37"/>
       <c r="AH41" s="98" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AI41" s="99"/>
       <c r="AJ41" s="100"/>
@@ -5040,7 +5043,7 @@
       <c r="P50" s="73"/>
       <c r="Q50" s="50"/>
       <c r="R50" s="89" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S50" s="90"/>
       <c r="T50" s="91"/>
@@ -5058,7 +5061,7 @@
       <c r="AB50" s="67"/>
       <c r="AC50" s="50"/>
       <c r="AD50" s="89" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AE50" s="90"/>
       <c r="AF50" s="91"/>
@@ -5134,11 +5137,11 @@
       <c r="D52" s="57"/>
       <c r="E52" s="36"/>
       <c r="F52" s="116" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G52" s="117"/>
       <c r="H52" s="59" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I52" s="54"/>
       <c r="J52" s="63" t="s">
@@ -5154,11 +5157,11 @@
       <c r="P52" s="34"/>
       <c r="Q52" s="31"/>
       <c r="R52" s="116" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S52" s="117"/>
       <c r="T52" s="59" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U52" s="35"/>
       <c r="V52" s="35"/>
@@ -5170,19 +5173,19 @@
       <c r="AB52" s="35"/>
       <c r="AC52" s="36"/>
       <c r="AD52" s="116" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AE52" s="117"/>
       <c r="AF52" s="59" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AG52" s="36"/>
       <c r="AH52" s="116" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI52" s="117"/>
       <c r="AJ52" s="59" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AK52" s="54"/>
       <c r="AL52" s="87"/>
@@ -5196,7 +5199,7 @@
       <c r="D53" s="80"/>
       <c r="E53" s="36"/>
       <c r="F53" s="78" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G53" s="79"/>
       <c r="H53" s="80"/>
@@ -5212,7 +5215,7 @@
       <c r="P53" s="97"/>
       <c r="Q53" s="32"/>
       <c r="R53" s="95" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="S53" s="96"/>
       <c r="T53" s="97"/>
@@ -5230,13 +5233,13 @@
       <c r="AB53" s="34"/>
       <c r="AC53" s="35"/>
       <c r="AD53" s="95" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AE53" s="96"/>
       <c r="AF53" s="97"/>
       <c r="AG53" s="36"/>
       <c r="AH53" s="95" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AI53" s="96"/>
       <c r="AJ53" s="97"/>
@@ -5405,11 +5408,11 @@
       <c r="G57" s="72"/>
       <c r="H57" s="73"/>
       <c r="I57" s="50"/>
-      <c r="J57" s="157" t="s">
+      <c r="J57" s="160" t="s">
         <v>8</v>
       </c>
-      <c r="K57" s="158"/>
-      <c r="L57" s="159"/>
+      <c r="K57" s="161"/>
+      <c r="L57" s="162"/>
       <c r="M57" s="5"/>
       <c r="N57" s="71"/>
       <c r="O57" s="72"/>
@@ -5514,11 +5517,11 @@
       <c r="AB59" s="34"/>
       <c r="AC59" s="32"/>
       <c r="AD59" s="116" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AE59" s="117"/>
       <c r="AF59" s="59" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AG59" s="50"/>
       <c r="AH59" s="87"/>
@@ -5560,7 +5563,7 @@
       <c r="AB60" s="97"/>
       <c r="AC60" s="54"/>
       <c r="AD60" s="95" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AE60" s="96"/>
       <c r="AF60" s="97"/>
@@ -5815,20 +5818,24 @@
       <c r="T66" s="34"/>
       <c r="U66" s="36"/>
       <c r="V66" s="114" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="W66" s="115"/>
       <c r="X66" s="60"/>
       <c r="Y66" s="36"/>
       <c r="Z66" s="116" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AA66" s="117"/>
       <c r="AB66" s="59"/>
       <c r="AC66" s="36"/>
-      <c r="AD66" s="87"/>
-      <c r="AE66" s="88"/>
-      <c r="AF66" s="34"/>
+      <c r="AD66" s="116" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE66" s="117"/>
+      <c r="AF66" s="59" t="s">
+        <v>66</v>
+      </c>
       <c r="AG66" s="36"/>
       <c r="AH66" s="87"/>
       <c r="AI66" s="88"/>
@@ -5865,18 +5872,20 @@
       <c r="T67" s="97"/>
       <c r="U67" s="36"/>
       <c r="V67" s="118" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="W67" s="119"/>
       <c r="X67" s="120"/>
       <c r="Y67" s="36"/>
       <c r="Z67" s="95" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AA67" s="96"/>
       <c r="AB67" s="97"/>
       <c r="AC67" s="36"/>
-      <c r="AD67" s="95"/>
+      <c r="AD67" s="95" t="s">
+        <v>108</v>
+      </c>
       <c r="AE67" s="96"/>
       <c r="AF67" s="97"/>
       <c r="AG67" s="36"/>
@@ -5915,7 +5924,7 @@
       <c r="T68" s="94"/>
       <c r="U68" s="43"/>
       <c r="V68" s="111" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W68" s="112"/>
       <c r="X68" s="113"/>
@@ -5965,7 +5974,7 @@
       <c r="T69" s="67"/>
       <c r="U69" s="37"/>
       <c r="V69" s="121" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="W69" s="122"/>
       <c r="X69" s="123"/>
@@ -5976,7 +5985,9 @@
       <c r="AA69" s="66"/>
       <c r="AB69" s="67"/>
       <c r="AC69" s="43"/>
-      <c r="AD69" s="65"/>
+      <c r="AD69" s="65" t="s">
+        <v>18</v>
+      </c>
       <c r="AE69" s="66"/>
       <c r="AF69" s="67"/>
       <c r="AG69" s="37"/>
@@ -6017,7 +6028,7 @@
       <c r="T70" s="67"/>
       <c r="U70" s="44"/>
       <c r="V70" s="121" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="W70" s="122"/>
       <c r="X70" s="123"/>
@@ -6028,7 +6039,9 @@
       <c r="AA70" s="66"/>
       <c r="AB70" s="67"/>
       <c r="AC70" s="44"/>
-      <c r="AD70" s="65"/>
+      <c r="AD70" s="65" t="s">
+        <v>26</v>
+      </c>
       <c r="AE70" s="66"/>
       <c r="AF70" s="67"/>
       <c r="AG70" s="44"/>
@@ -6069,13 +6082,13 @@
       <c r="T71" s="73"/>
       <c r="U71" s="44"/>
       <c r="V71" s="126" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W71" s="127"/>
       <c r="X71" s="128"/>
       <c r="Y71" s="44"/>
       <c r="Z71" s="89" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AA71" s="90"/>
       <c r="AB71" s="91"/>
@@ -6309,17 +6322,17 @@
     </row>
     <row r="76" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="12"/>
-      <c r="B76" s="160" t="s">
-        <v>92</v>
-      </c>
-      <c r="C76" s="161"/>
-      <c r="D76" s="162"/>
+      <c r="B76" s="163" t="s">
+        <v>91</v>
+      </c>
+      <c r="C76" s="164"/>
+      <c r="D76" s="165"/>
       <c r="E76" s="32"/>
-      <c r="F76" s="160" t="s">
-        <v>92</v>
-      </c>
-      <c r="G76" s="161"/>
-      <c r="H76" s="162"/>
+      <c r="F76" s="163" t="s">
+        <v>91</v>
+      </c>
+      <c r="G76" s="164"/>
+      <c r="H76" s="165"/>
       <c r="I76" s="32"/>
       <c r="J76" s="78"/>
       <c r="K76" s="79"/>
@@ -6369,17 +6382,17 @@
     </row>
     <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="16"/>
-      <c r="B77" s="154" t="s">
+      <c r="B77" s="157" t="s">
         <v>60</v>
       </c>
-      <c r="C77" s="155"/>
-      <c r="D77" s="156"/>
+      <c r="C77" s="158"/>
+      <c r="D77" s="159"/>
       <c r="E77" s="32"/>
-      <c r="F77" s="154" t="s">
+      <c r="F77" s="157" t="s">
         <v>60</v>
       </c>
-      <c r="G77" s="155"/>
-      <c r="H77" s="156"/>
+      <c r="G77" s="158"/>
+      <c r="H77" s="159"/>
       <c r="I77" s="32"/>
       <c r="J77" s="68"/>
       <c r="K77" s="69"/>
@@ -6419,17 +6432,17 @@
     </row>
     <row r="78" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="16"/>
-      <c r="B78" s="145" t="s">
-        <v>93</v>
-      </c>
-      <c r="C78" s="146"/>
-      <c r="D78" s="147"/>
+      <c r="B78" s="142" t="s">
+        <v>92</v>
+      </c>
+      <c r="C78" s="143"/>
+      <c r="D78" s="144"/>
       <c r="E78" s="32"/>
-      <c r="F78" s="145" t="s">
-        <v>93</v>
-      </c>
-      <c r="G78" s="146"/>
-      <c r="H78" s="147"/>
+      <c r="F78" s="142" t="s">
+        <v>92</v>
+      </c>
+      <c r="G78" s="143"/>
+      <c r="H78" s="144"/>
       <c r="I78" s="43"/>
       <c r="J78" s="81"/>
       <c r="K78" s="82"/>

--- a/Gorev-Listesi.xlsx
+++ b/Gorev-Listesi.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="112">
   <si>
     <t>CUMA</t>
   </si>
@@ -354,6 +354,12 @@
   </si>
   <si>
     <t>13.30</t>
+  </si>
+  <si>
+    <t>S.CÜREBAL.</t>
+  </si>
+  <si>
+    <t>Atatürk Havalimanı</t>
   </si>
 </sst>
 </file>
@@ -2238,7 +2244,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="1" width="104" row="3" locked="1">
+  <wetp:taskpane dockstate="right" visibility="1" width="176" row="1" locked="1">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -2639,11 +2645,11 @@
         <v>68</v>
       </c>
       <c r="AK6" s="36"/>
-      <c r="AL6" s="87" t="s">
+      <c r="AL6" s="114" t="s">
         <v>77</v>
       </c>
-      <c r="AM6" s="88"/>
-      <c r="AN6" s="34" t="s">
+      <c r="AM6" s="115"/>
+      <c r="AN6" s="60" t="s">
         <v>68</v>
       </c>
       <c r="AP6" s="46" t="s">
@@ -2694,9 +2700,11 @@
       <c r="AI7" s="112"/>
       <c r="AJ7" s="62"/>
       <c r="AK7" s="36"/>
-      <c r="AL7" s="92"/>
-      <c r="AM7" s="93"/>
-      <c r="AN7" s="18"/>
+      <c r="AL7" s="111" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM7" s="112"/>
+      <c r="AN7" s="62"/>
       <c r="AP7" s="46" t="s">
         <v>9</v>
       </c>
@@ -2747,11 +2755,11 @@
       <c r="AI8" s="143"/>
       <c r="AJ8" s="144"/>
       <c r="AK8" s="37"/>
-      <c r="AL8" s="81" t="s">
-        <v>12</v>
-      </c>
-      <c r="AM8" s="82"/>
-      <c r="AN8" s="83"/>
+      <c r="AL8" s="142" t="s">
+        <v>97</v>
+      </c>
+      <c r="AM8" s="143"/>
+      <c r="AN8" s="144"/>
       <c r="AP8" s="46" t="s">
         <v>16</v>
       </c>
@@ -2798,11 +2806,11 @@
       <c r="AI9" s="155"/>
       <c r="AJ9" s="156"/>
       <c r="AK9" s="43"/>
-      <c r="AL9" s="108" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM9" s="109"/>
-      <c r="AN9" s="110"/>
+      <c r="AL9" s="121" t="s">
+        <v>110</v>
+      </c>
+      <c r="AM9" s="122"/>
+      <c r="AN9" s="123"/>
       <c r="AP9" s="46" t="s">
         <v>11</v>
       </c>
@@ -5009,11 +5017,11 @@
       <c r="AI49" s="66"/>
       <c r="AJ49" s="67"/>
       <c r="AK49" s="44"/>
-      <c r="AL49" s="65" t="s">
-        <v>26</v>
-      </c>
-      <c r="AM49" s="66"/>
-      <c r="AN49" s="67"/>
+      <c r="AL49" s="108" t="s">
+        <v>12</v>
+      </c>
+      <c r="AM49" s="109"/>
+      <c r="AN49" s="110"/>
       <c r="AO49" s="31"/>
       <c r="AP49" s="31"/>
       <c r="AQ49" s="31"/>
@@ -5188,9 +5196,11 @@
         <v>89</v>
       </c>
       <c r="AK52" s="54"/>
-      <c r="AL52" s="87"/>
-      <c r="AM52" s="88"/>
-      <c r="AN52" s="34"/>
+      <c r="AL52" s="116" t="s">
+        <v>88</v>
+      </c>
+      <c r="AM52" s="117"/>
+      <c r="AN52" s="59"/>
       <c r="AR52" s="13"/>
     </row>
     <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5244,7 +5254,9 @@
       <c r="AI53" s="96"/>
       <c r="AJ53" s="97"/>
       <c r="AK53" s="35"/>
-      <c r="AL53" s="95"/>
+      <c r="AL53" s="95" t="s">
+        <v>111</v>
+      </c>
       <c r="AM53" s="96"/>
       <c r="AN53" s="97"/>
       <c r="AR53" s="13"/>
@@ -5340,7 +5352,9 @@
       <c r="AI55" s="66"/>
       <c r="AJ55" s="67"/>
       <c r="AK55" s="40"/>
-      <c r="AL55" s="65"/>
+      <c r="AL55" s="65" t="s">
+        <v>26</v>
+      </c>
       <c r="AM55" s="66"/>
       <c r="AN55" s="67"/>
       <c r="AR55" s="13"/>
@@ -5394,7 +5408,9 @@
       <c r="AI56" s="66"/>
       <c r="AJ56" s="67"/>
       <c r="AK56" s="44"/>
-      <c r="AL56" s="65"/>
+      <c r="AL56" s="65" t="s">
+        <v>15</v>
+      </c>
       <c r="AM56" s="66"/>
       <c r="AN56" s="67"/>
       <c r="AR56" s="13"/>

--- a/Gorev-Listesi.xlsx
+++ b/Gorev-Listesi.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23676" windowHeight="10992" tabRatio="515"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23670" windowHeight="10995" tabRatio="515"/>
   </bookViews>
   <sheets>
     <sheet name="SES SERVİSİ ÇALIŞMA PLANI" sheetId="2" r:id="rId1"/>
@@ -1575,6 +1575,60 @@
     <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="12" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="13" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="9" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="11" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="12" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="14" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1584,6 +1638,24 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="12" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="13" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1593,78 +1665,6 @@
     <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="12" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="13" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="14" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="11" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="12" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="9" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="12" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="13" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1839,6 +1839,15 @@
     <xf numFmtId="49" fontId="7" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="11" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="12" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="13" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1846,15 +1855,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="11" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="12" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="13" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2229,7 +2229,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="1" width="182" row="1" locked="1">
+  <wetp:taskpane dockstate="right" visibility="1" width="350" row="1" locked="1">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -2255,56 +2255,56 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AR133"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.6640625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="2.6640625" style="26" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="26" customWidth="1"/>
-    <col min="4" max="4" width="6.6640625" style="26" customWidth="1"/>
-    <col min="5" max="5" width="1.6640625" style="26" customWidth="1"/>
-    <col min="6" max="6" width="2.6640625" style="26" customWidth="1"/>
-    <col min="7" max="7" width="20.6640625" style="26" customWidth="1"/>
-    <col min="8" max="8" width="6.6640625" style="26" customWidth="1"/>
-    <col min="9" max="9" width="1.6640625" style="26" customWidth="1"/>
-    <col min="10" max="10" width="2.6640625" style="26" customWidth="1"/>
-    <col min="11" max="11" width="20.6640625" style="26" customWidth="1"/>
-    <col min="12" max="12" width="6.6640625" style="26" customWidth="1"/>
-    <col min="13" max="13" width="1.6640625" style="26" customWidth="1"/>
-    <col min="14" max="14" width="2.6640625" customWidth="1"/>
-    <col min="15" max="15" width="20.6640625" customWidth="1"/>
-    <col min="16" max="16" width="6.6640625" customWidth="1"/>
-    <col min="17" max="17" width="1.6640625" customWidth="1"/>
-    <col min="18" max="18" width="2.6640625" customWidth="1"/>
-    <col min="19" max="19" width="20.6640625" customWidth="1"/>
-    <col min="20" max="20" width="6.6640625" customWidth="1"/>
-    <col min="21" max="21" width="1.6640625" customWidth="1"/>
-    <col min="22" max="22" width="2.6640625" customWidth="1"/>
-    <col min="23" max="23" width="20.6640625" customWidth="1"/>
-    <col min="24" max="24" width="6.6640625" customWidth="1"/>
-    <col min="25" max="25" width="1.6640625" customWidth="1"/>
-    <col min="26" max="26" width="2.6640625" customWidth="1"/>
-    <col min="27" max="27" width="20.6640625" customWidth="1"/>
-    <col min="28" max="28" width="6.6640625" customWidth="1"/>
-    <col min="29" max="29" width="1.6640625" customWidth="1"/>
-    <col min="30" max="30" width="2.6640625" customWidth="1"/>
-    <col min="31" max="31" width="20.6640625" customWidth="1"/>
-    <col min="32" max="32" width="6.6640625" customWidth="1"/>
-    <col min="33" max="33" width="1.6640625" customWidth="1"/>
-    <col min="34" max="34" width="2.6640625" customWidth="1"/>
-    <col min="35" max="35" width="20.6640625" customWidth="1"/>
-    <col min="36" max="36" width="6.6640625" customWidth="1"/>
-    <col min="37" max="37" width="1.6640625" customWidth="1"/>
-    <col min="38" max="38" width="2.6640625" customWidth="1"/>
-    <col min="39" max="39" width="20.6640625" customWidth="1"/>
-    <col min="40" max="40" width="6.6640625" customWidth="1"/>
-    <col min="41" max="41" width="2.6640625" customWidth="1"/>
-    <col min="42" max="42" width="16.6640625" customWidth="1"/>
-    <col min="43" max="43" width="3.6640625" customWidth="1"/>
-    <col min="44" max="44" width="8.33203125" customWidth="1"/>
+    <col min="1" max="1" width="1.7109375" style="26" customWidth="1"/>
+    <col min="2" max="2" width="2.7109375" style="26" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" style="26" customWidth="1"/>
+    <col min="4" max="4" width="6.7109375" style="26" customWidth="1"/>
+    <col min="5" max="5" width="1.7109375" style="26" customWidth="1"/>
+    <col min="6" max="6" width="2.7109375" style="26" customWidth="1"/>
+    <col min="7" max="7" width="20.7109375" style="26" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="26" customWidth="1"/>
+    <col min="9" max="9" width="1.7109375" style="26" customWidth="1"/>
+    <col min="10" max="10" width="2.7109375" style="26" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" style="26" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" style="26" customWidth="1"/>
+    <col min="13" max="13" width="1.7109375" style="26" customWidth="1"/>
+    <col min="14" max="14" width="2.7109375" customWidth="1"/>
+    <col min="15" max="15" width="20.7109375" customWidth="1"/>
+    <col min="16" max="16" width="6.7109375" customWidth="1"/>
+    <col min="17" max="17" width="1.7109375" customWidth="1"/>
+    <col min="18" max="18" width="2.7109375" customWidth="1"/>
+    <col min="19" max="19" width="20.7109375" customWidth="1"/>
+    <col min="20" max="20" width="6.7109375" customWidth="1"/>
+    <col min="21" max="21" width="1.7109375" customWidth="1"/>
+    <col min="22" max="22" width="2.7109375" customWidth="1"/>
+    <col min="23" max="23" width="20.7109375" customWidth="1"/>
+    <col min="24" max="24" width="6.7109375" customWidth="1"/>
+    <col min="25" max="25" width="1.7109375" customWidth="1"/>
+    <col min="26" max="26" width="2.7109375" customWidth="1"/>
+    <col min="27" max="27" width="20.7109375" customWidth="1"/>
+    <col min="28" max="28" width="6.7109375" customWidth="1"/>
+    <col min="29" max="29" width="1.7109375" customWidth="1"/>
+    <col min="30" max="30" width="2.7109375" customWidth="1"/>
+    <col min="31" max="31" width="20.7109375" customWidth="1"/>
+    <col min="32" max="32" width="6.7109375" customWidth="1"/>
+    <col min="33" max="33" width="1.7109375" customWidth="1"/>
+    <col min="34" max="34" width="2.7109375" customWidth="1"/>
+    <col min="35" max="35" width="20.7109375" customWidth="1"/>
+    <col min="36" max="36" width="6.7109375" customWidth="1"/>
+    <col min="37" max="37" width="1.7109375" customWidth="1"/>
+    <col min="38" max="38" width="2.7109375" customWidth="1"/>
+    <col min="39" max="39" width="20.7109375" customWidth="1"/>
+    <col min="40" max="40" width="6.7109375" customWidth="1"/>
+    <col min="41" max="41" width="2.7109375" customWidth="1"/>
+    <col min="42" max="42" width="16.7109375" customWidth="1"/>
+    <col min="43" max="43" width="3.7109375" customWidth="1"/>
+    <col min="44" max="44" width="8.28515625" customWidth="1"/>
     <col min="45" max="48" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12"/>
       <c r="B1" s="107" t="s">
         <v>0</v>
@@ -2370,7 +2370,7 @@
       <c r="AQ1" s="12"/>
       <c r="AR1" s="13"/>
     </row>
-    <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="110">
         <f>N2-3</f>
@@ -2445,7 +2445,7 @@
       <c r="AQ2" s="12"/>
       <c r="AR2" s="13"/>
     </row>
-    <row r="3" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="12"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -2491,7 +2491,7 @@
       <c r="AQ3" s="12"/>
       <c r="AR3" s="13"/>
     </row>
-    <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="12"/>
       <c r="B4" s="106"/>
       <c r="C4" s="106"/>
@@ -2539,7 +2539,7 @@
       <c r="AQ4" s="12"/>
       <c r="AR4" s="13"/>
     </row>
-    <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12"/>
       <c r="B5" s="106"/>
       <c r="C5" s="106"/>
@@ -2585,11 +2585,11 @@
       <c r="AQ5" s="12"/>
       <c r="AR5" s="13"/>
     </row>
-    <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="74" t="s">
+    <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="65" t="s">
         <v>57</v>
       </c>
-      <c r="C6" s="75"/>
+      <c r="C6" s="66"/>
       <c r="D6" s="57" t="s">
         <v>55</v>
       </c>
@@ -2610,42 +2610,42 @@
         <v>55</v>
       </c>
       <c r="M6" s="3"/>
-      <c r="N6" s="87"/>
-      <c r="O6" s="88"/>
+      <c r="N6" s="70"/>
+      <c r="O6" s="71"/>
       <c r="P6" s="34"/>
       <c r="Q6" s="39"/>
-      <c r="R6" s="87"/>
-      <c r="S6" s="88"/>
+      <c r="R6" s="70"/>
+      <c r="S6" s="71"/>
       <c r="T6" s="34"/>
       <c r="U6" s="36"/>
-      <c r="V6" s="87"/>
-      <c r="W6" s="88"/>
+      <c r="V6" s="70"/>
+      <c r="W6" s="71"/>
       <c r="X6" s="34"/>
       <c r="Y6" s="23"/>
-      <c r="Z6" s="87" t="s">
+      <c r="Z6" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="AA6" s="88"/>
+      <c r="AA6" s="71"/>
       <c r="AB6" s="34" t="s">
         <v>85</v>
       </c>
       <c r="AC6" s="36"/>
-      <c r="AD6" s="87"/>
-      <c r="AE6" s="88"/>
+      <c r="AD6" s="70"/>
+      <c r="AE6" s="71"/>
       <c r="AF6" s="34"/>
       <c r="AG6" s="39"/>
-      <c r="AH6" s="87" t="s">
+      <c r="AH6" s="70" t="s">
         <v>57</v>
       </c>
-      <c r="AI6" s="88"/>
+      <c r="AI6" s="71"/>
       <c r="AJ6" s="34" t="s">
         <v>55</v>
       </c>
       <c r="AK6" s="36"/>
-      <c r="AL6" s="87" t="s">
+      <c r="AL6" s="70" t="s">
         <v>57</v>
       </c>
-      <c r="AM6" s="88"/>
+      <c r="AM6" s="71"/>
       <c r="AN6" s="34" t="s">
         <v>55</v>
       </c>
@@ -2658,9 +2658,9 @@
       </c>
       <c r="AR6" s="30"/>
     </row>
-    <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="81"/>
-      <c r="C7" s="82"/>
+    <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="77"/>
+      <c r="C7" s="78"/>
       <c r="D7" s="61"/>
       <c r="E7" s="38"/>
       <c r="F7" s="113" t="s">
@@ -2675,34 +2675,34 @@
       <c r="K7" s="114"/>
       <c r="L7" s="60"/>
       <c r="M7" s="3"/>
-      <c r="N7" s="71"/>
-      <c r="O7" s="72"/>
+      <c r="N7" s="83"/>
+      <c r="O7" s="84"/>
       <c r="P7" s="18"/>
       <c r="Q7" s="36"/>
-      <c r="R7" s="71"/>
-      <c r="S7" s="72"/>
+      <c r="R7" s="83"/>
+      <c r="S7" s="84"/>
       <c r="T7" s="18"/>
       <c r="U7" s="36"/>
-      <c r="V7" s="71"/>
-      <c r="W7" s="72"/>
+      <c r="V7" s="83"/>
+      <c r="W7" s="84"/>
       <c r="X7" s="18"/>
       <c r="Y7" s="36"/>
-      <c r="Z7" s="71" t="s">
+      <c r="Z7" s="83" t="s">
         <v>84</v>
       </c>
-      <c r="AA7" s="72"/>
+      <c r="AA7" s="84"/>
       <c r="AB7" s="18"/>
       <c r="AC7" s="36"/>
-      <c r="AD7" s="71"/>
-      <c r="AE7" s="72"/>
+      <c r="AD7" s="83"/>
+      <c r="AE7" s="84"/>
       <c r="AF7" s="18"/>
       <c r="AG7" s="38"/>
-      <c r="AH7" s="71"/>
-      <c r="AI7" s="72"/>
+      <c r="AH7" s="83"/>
+      <c r="AI7" s="84"/>
       <c r="AJ7" s="18"/>
       <c r="AK7" s="36"/>
-      <c r="AL7" s="71"/>
-      <c r="AM7" s="72"/>
+      <c r="AL7" s="83"/>
+      <c r="AM7" s="84"/>
       <c r="AN7" s="18"/>
       <c r="AP7" s="46" t="s">
         <v>9</v>
@@ -2713,12 +2713,12 @@
       </c>
       <c r="AR7" s="30"/>
     </row>
-    <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="68" t="s">
+    <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="69"/>
-      <c r="D8" s="70"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="69"/>
       <c r="E8" s="35"/>
       <c r="F8" s="116" t="s">
         <v>87</v>
@@ -2732,39 +2732,39 @@
       <c r="K8" s="117"/>
       <c r="L8" s="118"/>
       <c r="M8" s="3"/>
-      <c r="N8" s="65"/>
-      <c r="O8" s="66"/>
-      <c r="P8" s="67"/>
+      <c r="N8" s="89"/>
+      <c r="O8" s="90"/>
+      <c r="P8" s="91"/>
       <c r="Q8" s="35"/>
-      <c r="R8" s="65"/>
-      <c r="S8" s="66"/>
-      <c r="T8" s="67"/>
+      <c r="R8" s="89"/>
+      <c r="S8" s="90"/>
+      <c r="T8" s="91"/>
       <c r="U8" s="37"/>
-      <c r="V8" s="65"/>
-      <c r="W8" s="66"/>
-      <c r="X8" s="67"/>
+      <c r="V8" s="89"/>
+      <c r="W8" s="90"/>
+      <c r="X8" s="91"/>
       <c r="Y8" s="35"/>
-      <c r="Z8" s="65" t="s">
+      <c r="Z8" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="AA8" s="66"/>
-      <c r="AB8" s="67"/>
+      <c r="AA8" s="90"/>
+      <c r="AB8" s="91"/>
       <c r="AC8" s="35"/>
-      <c r="AD8" s="65"/>
-      <c r="AE8" s="66"/>
-      <c r="AF8" s="67"/>
+      <c r="AD8" s="89"/>
+      <c r="AE8" s="90"/>
+      <c r="AF8" s="91"/>
       <c r="AG8" s="35"/>
-      <c r="AH8" s="65" t="s">
+      <c r="AH8" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="AI8" s="66"/>
-      <c r="AJ8" s="67"/>
+      <c r="AI8" s="90"/>
+      <c r="AJ8" s="91"/>
       <c r="AK8" s="37"/>
-      <c r="AL8" s="65" t="s">
+      <c r="AL8" s="89" t="s">
         <v>37</v>
       </c>
-      <c r="AM8" s="66"/>
-      <c r="AN8" s="67"/>
+      <c r="AM8" s="90"/>
+      <c r="AN8" s="91"/>
       <c r="AP8" s="46" t="s">
         <v>16</v>
       </c>
@@ -2774,10 +2774,10 @@
       </c>
       <c r="AR8" s="30"/>
     </row>
-    <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="68"/>
-      <c r="C9" s="69"/>
-      <c r="D9" s="70"/>
+    <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="67"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="69"/>
       <c r="E9" s="43"/>
       <c r="F9" s="128"/>
       <c r="G9" s="129"/>
@@ -2789,37 +2789,37 @@
       <c r="K9" s="126"/>
       <c r="L9" s="127"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="68"/>
-      <c r="O9" s="69"/>
-      <c r="P9" s="70"/>
+      <c r="N9" s="67"/>
+      <c r="O9" s="68"/>
+      <c r="P9" s="69"/>
       <c r="Q9" s="43"/>
-      <c r="R9" s="68"/>
-      <c r="S9" s="69"/>
-      <c r="T9" s="70"/>
+      <c r="R9" s="67"/>
+      <c r="S9" s="68"/>
+      <c r="T9" s="69"/>
       <c r="U9" s="44"/>
-      <c r="V9" s="68"/>
-      <c r="W9" s="69"/>
-      <c r="X9" s="70"/>
+      <c r="V9" s="67"/>
+      <c r="W9" s="68"/>
+      <c r="X9" s="69"/>
       <c r="Y9" s="43"/>
-      <c r="Z9" s="68"/>
-      <c r="AA9" s="69"/>
-      <c r="AB9" s="70"/>
+      <c r="Z9" s="67"/>
+      <c r="AA9" s="68"/>
+      <c r="AB9" s="69"/>
       <c r="AC9" s="43"/>
-      <c r="AD9" s="68"/>
-      <c r="AE9" s="69"/>
-      <c r="AF9" s="70"/>
+      <c r="AD9" s="67"/>
+      <c r="AE9" s="68"/>
+      <c r="AF9" s="69"/>
       <c r="AG9" s="43"/>
-      <c r="AH9" s="68" t="s">
+      <c r="AH9" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="AI9" s="69"/>
-      <c r="AJ9" s="70"/>
+      <c r="AI9" s="68"/>
+      <c r="AJ9" s="69"/>
       <c r="AK9" s="43"/>
-      <c r="AL9" s="68" t="s">
+      <c r="AL9" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="AM9" s="69"/>
-      <c r="AN9" s="70"/>
+      <c r="AM9" s="68"/>
+      <c r="AN9" s="69"/>
       <c r="AP9" s="46" t="s">
         <v>11</v>
       </c>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AR9" s="30"/>
     </row>
-    <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="92"/>
       <c r="C10" s="93"/>
       <c r="D10" s="94"/>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="AR10" s="30"/>
     </row>
-    <row r="11" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="33"/>
       <c r="C11" s="33"/>
       <c r="D11" s="33"/>
@@ -2929,53 +2929,53 @@
       </c>
       <c r="AR11" s="30"/>
     </row>
-    <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="79"/>
-      <c r="C12" s="80"/>
+    <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="75"/>
+      <c r="C12" s="76"/>
       <c r="D12" s="55"/>
       <c r="E12" s="39"/>
-      <c r="F12" s="79" t="s">
+      <c r="F12" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="80"/>
+      <c r="G12" s="76"/>
       <c r="H12" s="55" t="s">
         <v>48</v>
       </c>
       <c r="I12" s="36"/>
-      <c r="J12" s="79"/>
-      <c r="K12" s="80"/>
+      <c r="J12" s="75"/>
+      <c r="K12" s="76"/>
       <c r="L12" s="55"/>
       <c r="M12" s="5"/>
-      <c r="N12" s="87"/>
-      <c r="O12" s="88"/>
+      <c r="N12" s="70"/>
+      <c r="O12" s="71"/>
       <c r="P12" s="34"/>
       <c r="Q12" s="23"/>
-      <c r="R12" s="87"/>
-      <c r="S12" s="88"/>
+      <c r="R12" s="70"/>
+      <c r="S12" s="71"/>
       <c r="T12" s="34"/>
       <c r="U12" s="36"/>
-      <c r="V12" s="87"/>
-      <c r="W12" s="88"/>
+      <c r="V12" s="70"/>
+      <c r="W12" s="71"/>
       <c r="X12" s="34"/>
       <c r="Y12" s="23"/>
-      <c r="Z12" s="87"/>
-      <c r="AA12" s="88"/>
+      <c r="Z12" s="70"/>
+      <c r="AA12" s="71"/>
       <c r="AB12" s="34"/>
       <c r="AC12" s="36"/>
-      <c r="AD12" s="87"/>
-      <c r="AE12" s="88"/>
+      <c r="AD12" s="70"/>
+      <c r="AE12" s="71"/>
       <c r="AF12" s="34"/>
       <c r="AG12" s="39"/>
-      <c r="AH12" s="87" t="s">
+      <c r="AH12" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="AI12" s="88"/>
+      <c r="AI12" s="71"/>
       <c r="AJ12" s="34" t="s">
         <v>48</v>
       </c>
       <c r="AK12" s="36"/>
-      <c r="AL12" s="87"/>
-      <c r="AM12" s="88"/>
+      <c r="AL12" s="70"/>
+      <c r="AM12" s="71"/>
       <c r="AN12" s="34"/>
       <c r="AP12" s="46" t="s">
         <v>19</v>
@@ -2986,45 +2986,45 @@
       </c>
       <c r="AR12" s="30"/>
     </row>
-    <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="81"/>
-      <c r="C13" s="82"/>
+    <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="77"/>
+      <c r="C13" s="78"/>
       <c r="D13" s="61"/>
       <c r="E13" s="38"/>
-      <c r="F13" s="81"/>
-      <c r="G13" s="82"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="78"/>
       <c r="H13" s="61"/>
       <c r="I13" s="36"/>
-      <c r="J13" s="81"/>
-      <c r="K13" s="82"/>
+      <c r="J13" s="77"/>
+      <c r="K13" s="78"/>
       <c r="L13" s="61"/>
       <c r="M13" s="5"/>
-      <c r="N13" s="71"/>
-      <c r="O13" s="72"/>
+      <c r="N13" s="83"/>
+      <c r="O13" s="84"/>
       <c r="P13" s="18"/>
       <c r="Q13" s="36"/>
-      <c r="R13" s="71"/>
-      <c r="S13" s="72"/>
+      <c r="R13" s="83"/>
+      <c r="S13" s="84"/>
       <c r="T13" s="18"/>
       <c r="U13" s="36"/>
-      <c r="V13" s="71"/>
-      <c r="W13" s="72"/>
+      <c r="V13" s="83"/>
+      <c r="W13" s="84"/>
       <c r="X13" s="18"/>
       <c r="Y13" s="36"/>
-      <c r="Z13" s="71"/>
-      <c r="AA13" s="72"/>
+      <c r="Z13" s="83"/>
+      <c r="AA13" s="84"/>
       <c r="AB13" s="18"/>
       <c r="AC13" s="36"/>
-      <c r="AD13" s="71"/>
-      <c r="AE13" s="72"/>
+      <c r="AD13" s="83"/>
+      <c r="AE13" s="84"/>
       <c r="AF13" s="18"/>
       <c r="AG13" s="38"/>
-      <c r="AH13" s="71"/>
-      <c r="AI13" s="72"/>
+      <c r="AH13" s="83"/>
+      <c r="AI13" s="84"/>
       <c r="AJ13" s="18"/>
       <c r="AK13" s="36"/>
-      <c r="AL13" s="71"/>
-      <c r="AM13" s="72"/>
+      <c r="AL13" s="83"/>
+      <c r="AM13" s="84"/>
       <c r="AN13" s="18"/>
       <c r="AP13" s="46" t="s">
         <v>22</v>
@@ -3035,50 +3035,50 @@
       </c>
       <c r="AR13" s="30"/>
     </row>
-    <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="65"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="67"/>
+    <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="89"/>
+      <c r="C14" s="90"/>
+      <c r="D14" s="91"/>
       <c r="E14" s="37"/>
-      <c r="F14" s="65" t="s">
+      <c r="F14" s="89" t="s">
         <v>37</v>
       </c>
-      <c r="G14" s="66"/>
-      <c r="H14" s="67"/>
+      <c r="G14" s="90"/>
+      <c r="H14" s="91"/>
       <c r="I14" s="35"/>
-      <c r="J14" s="65"/>
-      <c r="K14" s="66"/>
-      <c r="L14" s="67"/>
+      <c r="J14" s="89"/>
+      <c r="K14" s="90"/>
+      <c r="L14" s="91"/>
       <c r="M14" s="3"/>
-      <c r="N14" s="65"/>
-      <c r="O14" s="66"/>
-      <c r="P14" s="67"/>
+      <c r="N14" s="89"/>
+      <c r="O14" s="90"/>
+      <c r="P14" s="91"/>
       <c r="Q14" s="35"/>
-      <c r="R14" s="65"/>
-      <c r="S14" s="66"/>
-      <c r="T14" s="67"/>
+      <c r="R14" s="89"/>
+      <c r="S14" s="90"/>
+      <c r="T14" s="91"/>
       <c r="U14" s="37"/>
-      <c r="V14" s="65"/>
-      <c r="W14" s="66"/>
-      <c r="X14" s="67"/>
+      <c r="V14" s="89"/>
+      <c r="W14" s="90"/>
+      <c r="X14" s="91"/>
       <c r="Y14" s="35"/>
-      <c r="Z14" s="65"/>
-      <c r="AA14" s="66"/>
-      <c r="AB14" s="67"/>
+      <c r="Z14" s="89"/>
+      <c r="AA14" s="90"/>
+      <c r="AB14" s="91"/>
       <c r="AC14" s="37"/>
-      <c r="AD14" s="65"/>
-      <c r="AE14" s="66"/>
-      <c r="AF14" s="67"/>
+      <c r="AD14" s="89"/>
+      <c r="AE14" s="90"/>
+      <c r="AF14" s="91"/>
       <c r="AG14" s="37"/>
-      <c r="AH14" s="65" t="s">
+      <c r="AH14" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="AI14" s="66"/>
-      <c r="AJ14" s="67"/>
+      <c r="AI14" s="90"/>
+      <c r="AJ14" s="91"/>
       <c r="AK14" s="35"/>
-      <c r="AL14" s="65"/>
-      <c r="AM14" s="66"/>
-      <c r="AN14" s="67"/>
+      <c r="AL14" s="89"/>
+      <c r="AM14" s="90"/>
+      <c r="AN14" s="91"/>
       <c r="AP14" s="46" t="s">
         <v>23</v>
       </c>
@@ -3088,50 +3088,50 @@
       </c>
       <c r="AR14" s="30"/>
     </row>
-    <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="68"/>
-      <c r="C15" s="69"/>
-      <c r="D15" s="70"/>
+    <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="67"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="69"/>
       <c r="E15" s="44"/>
-      <c r="F15" s="68" t="s">
+      <c r="F15" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="G15" s="69"/>
-      <c r="H15" s="70"/>
+      <c r="G15" s="68"/>
+      <c r="H15" s="69"/>
       <c r="I15" s="43"/>
-      <c r="J15" s="68"/>
-      <c r="K15" s="69"/>
-      <c r="L15" s="70"/>
+      <c r="J15" s="67"/>
+      <c r="K15" s="68"/>
+      <c r="L15" s="69"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="68"/>
-      <c r="O15" s="69"/>
-      <c r="P15" s="70"/>
+      <c r="N15" s="67"/>
+      <c r="O15" s="68"/>
+      <c r="P15" s="69"/>
       <c r="Q15" s="43"/>
-      <c r="R15" s="68"/>
-      <c r="S15" s="69"/>
-      <c r="T15" s="70"/>
+      <c r="R15" s="67"/>
+      <c r="S15" s="68"/>
+      <c r="T15" s="69"/>
       <c r="U15" s="44"/>
-      <c r="V15" s="68"/>
-      <c r="W15" s="69"/>
-      <c r="X15" s="70"/>
+      <c r="V15" s="67"/>
+      <c r="W15" s="68"/>
+      <c r="X15" s="69"/>
       <c r="Y15" s="43"/>
-      <c r="Z15" s="68"/>
-      <c r="AA15" s="69"/>
-      <c r="AB15" s="70"/>
+      <c r="Z15" s="67"/>
+      <c r="AA15" s="68"/>
+      <c r="AB15" s="69"/>
       <c r="AC15" s="43"/>
-      <c r="AD15" s="68"/>
-      <c r="AE15" s="69"/>
-      <c r="AF15" s="70"/>
+      <c r="AD15" s="67"/>
+      <c r="AE15" s="68"/>
+      <c r="AF15" s="69"/>
       <c r="AG15" s="44"/>
-      <c r="AH15" s="68" t="s">
+      <c r="AH15" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="AI15" s="69"/>
-      <c r="AJ15" s="70"/>
+      <c r="AI15" s="68"/>
+      <c r="AJ15" s="69"/>
       <c r="AK15" s="43"/>
-      <c r="AL15" s="68"/>
-      <c r="AM15" s="69"/>
-      <c r="AN15" s="70"/>
+      <c r="AL15" s="67"/>
+      <c r="AM15" s="68"/>
+      <c r="AN15" s="69"/>
       <c r="AP15" s="46" t="s">
         <v>18</v>
       </c>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="AR15" s="30"/>
     </row>
-    <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B16" s="92"/>
       <c r="C16" s="93"/>
       <c r="D16" s="94"/>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="AR16" s="30"/>
     </row>
-    <row r="17" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="33"/>
       <c r="C17" s="33"/>
       <c r="D17" s="33"/>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="AR17" s="30"/>
     </row>
-    <row r="18" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="33"/>
       <c r="C18" s="33"/>
       <c r="D18" s="33"/>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="AR18" s="30"/>
     </row>
-    <row r="19" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="33"/>
       <c r="C19" s="33"/>
       <c r="D19" s="33"/>
@@ -3339,57 +3339,57 @@
       </c>
       <c r="AR19" s="30"/>
     </row>
-    <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="79"/>
-      <c r="C20" s="80"/>
+    <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="75"/>
+      <c r="C20" s="76"/>
       <c r="D20" s="55"/>
       <c r="E20" s="39"/>
-      <c r="F20" s="79" t="s">
+      <c r="F20" s="75" t="s">
         <v>47</v>
       </c>
-      <c r="G20" s="80"/>
+      <c r="G20" s="76"/>
       <c r="H20" s="57" t="s">
         <v>89</v>
       </c>
       <c r="I20" s="36"/>
-      <c r="J20" s="79"/>
-      <c r="K20" s="80"/>
+      <c r="J20" s="75"/>
+      <c r="K20" s="76"/>
       <c r="L20" s="55"/>
       <c r="M20" s="4"/>
-      <c r="N20" s="87"/>
-      <c r="O20" s="88"/>
+      <c r="N20" s="70"/>
+      <c r="O20" s="71"/>
       <c r="P20" s="34"/>
       <c r="Q20" s="39"/>
-      <c r="R20" s="87"/>
-      <c r="S20" s="88"/>
+      <c r="R20" s="70"/>
+      <c r="S20" s="71"/>
       <c r="T20" s="34"/>
       <c r="U20" s="36"/>
-      <c r="V20" s="87" t="s">
+      <c r="V20" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="W20" s="88"/>
+      <c r="W20" s="71"/>
       <c r="X20" s="34" t="s">
         <v>46</v>
       </c>
       <c r="Y20" s="23"/>
-      <c r="Z20" s="87"/>
-      <c r="AA20" s="88"/>
+      <c r="Z20" s="70"/>
+      <c r="AA20" s="71"/>
       <c r="AB20" s="34"/>
       <c r="AC20" s="36"/>
-      <c r="AD20" s="87"/>
-      <c r="AE20" s="88"/>
+      <c r="AD20" s="70"/>
+      <c r="AE20" s="71"/>
       <c r="AF20" s="34"/>
       <c r="AG20" s="39"/>
-      <c r="AH20" s="87" t="s">
+      <c r="AH20" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="AI20" s="88"/>
+      <c r="AI20" s="71"/>
       <c r="AJ20" s="34" t="s">
         <v>65</v>
       </c>
       <c r="AK20" s="36"/>
-      <c r="AL20" s="87"/>
-      <c r="AM20" s="88"/>
+      <c r="AL20" s="70"/>
+      <c r="AM20" s="71"/>
       <c r="AN20" s="34"/>
       <c r="AP20" s="46" t="s">
         <v>26</v>
@@ -3400,49 +3400,49 @@
       </c>
       <c r="AR20" s="30"/>
     </row>
-    <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="81"/>
-      <c r="C21" s="82"/>
+    <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="77"/>
+      <c r="C21" s="78"/>
       <c r="D21" s="61"/>
       <c r="E21" s="38"/>
-      <c r="F21" s="81"/>
-      <c r="G21" s="82"/>
+      <c r="F21" s="77"/>
+      <c r="G21" s="78"/>
       <c r="H21" s="61"/>
       <c r="I21" s="36"/>
-      <c r="J21" s="81"/>
-      <c r="K21" s="82"/>
+      <c r="J21" s="77"/>
+      <c r="K21" s="78"/>
       <c r="L21" s="61"/>
       <c r="M21" s="15"/>
-      <c r="N21" s="71"/>
-      <c r="O21" s="72"/>
+      <c r="N21" s="83"/>
+      <c r="O21" s="84"/>
       <c r="P21" s="18"/>
       <c r="Q21" s="36"/>
-      <c r="R21" s="71"/>
-      <c r="S21" s="72"/>
+      <c r="R21" s="83"/>
+      <c r="S21" s="84"/>
       <c r="T21" s="18"/>
       <c r="U21" s="36"/>
-      <c r="V21" s="71" t="s">
+      <c r="V21" s="83" t="s">
         <v>45</v>
       </c>
-      <c r="W21" s="72"/>
+      <c r="W21" s="84"/>
       <c r="X21" s="18" t="s">
         <v>43</v>
       </c>
       <c r="Y21" s="36"/>
-      <c r="Z21" s="71"/>
-      <c r="AA21" s="72"/>
+      <c r="Z21" s="83"/>
+      <c r="AA21" s="84"/>
       <c r="AB21" s="18"/>
       <c r="AC21" s="36"/>
-      <c r="AD21" s="71"/>
-      <c r="AE21" s="72"/>
+      <c r="AD21" s="83"/>
+      <c r="AE21" s="84"/>
       <c r="AF21" s="18"/>
       <c r="AG21" s="38"/>
-      <c r="AH21" s="71"/>
-      <c r="AI21" s="72"/>
+      <c r="AH21" s="83"/>
+      <c r="AI21" s="84"/>
       <c r="AJ21" s="18"/>
       <c r="AK21" s="36"/>
-      <c r="AL21" s="71"/>
-      <c r="AM21" s="72"/>
+      <c r="AL21" s="83"/>
+      <c r="AM21" s="84"/>
       <c r="AN21" s="18"/>
       <c r="AP21" s="46" t="s">
         <v>12</v>
@@ -3453,10 +3453,10 @@
       </c>
       <c r="AR21" s="30"/>
     </row>
-    <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="65"/>
-      <c r="C22" s="66"/>
-      <c r="D22" s="67"/>
+    <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="89"/>
+      <c r="C22" s="90"/>
+      <c r="D22" s="91"/>
       <c r="E22" s="35"/>
       <c r="F22" s="134" t="s">
         <v>9</v>
@@ -3464,41 +3464,41 @@
       <c r="G22" s="135"/>
       <c r="H22" s="136"/>
       <c r="I22" s="37"/>
-      <c r="J22" s="65"/>
-      <c r="K22" s="66"/>
-      <c r="L22" s="67"/>
+      <c r="J22" s="89"/>
+      <c r="K22" s="90"/>
+      <c r="L22" s="91"/>
       <c r="M22" s="4"/>
-      <c r="N22" s="65"/>
-      <c r="O22" s="66"/>
-      <c r="P22" s="67"/>
+      <c r="N22" s="89"/>
+      <c r="O22" s="90"/>
+      <c r="P22" s="91"/>
       <c r="Q22" s="35"/>
-      <c r="R22" s="65"/>
-      <c r="S22" s="66"/>
-      <c r="T22" s="67"/>
+      <c r="R22" s="89"/>
+      <c r="S22" s="90"/>
+      <c r="T22" s="91"/>
       <c r="U22" s="37"/>
-      <c r="V22" s="65" t="s">
+      <c r="V22" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="W22" s="66"/>
-      <c r="X22" s="67"/>
+      <c r="W22" s="90"/>
+      <c r="X22" s="91"/>
       <c r="Y22" s="35"/>
-      <c r="Z22" s="65"/>
-      <c r="AA22" s="66"/>
-      <c r="AB22" s="67"/>
+      <c r="Z22" s="89"/>
+      <c r="AA22" s="90"/>
+      <c r="AB22" s="91"/>
       <c r="AC22" s="35"/>
-      <c r="AD22" s="65"/>
-      <c r="AE22" s="66"/>
-      <c r="AF22" s="67"/>
+      <c r="AD22" s="89"/>
+      <c r="AE22" s="90"/>
+      <c r="AF22" s="91"/>
       <c r="AG22" s="35"/>
-      <c r="AH22" s="65" t="s">
+      <c r="AH22" s="89" t="s">
         <v>113</v>
       </c>
-      <c r="AI22" s="66"/>
-      <c r="AJ22" s="67"/>
+      <c r="AI22" s="90"/>
+      <c r="AJ22" s="91"/>
       <c r="AK22" s="37"/>
-      <c r="AL22" s="65"/>
-      <c r="AM22" s="66"/>
-      <c r="AN22" s="67"/>
+      <c r="AL22" s="89"/>
+      <c r="AM22" s="90"/>
+      <c r="AN22" s="91"/>
       <c r="AP22" s="46" t="s">
         <v>15</v>
       </c>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AR22" s="30"/>
     </row>
-    <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B23" s="92"/>
       <c r="C23" s="93"/>
       <c r="D23" s="94"/>
@@ -3561,7 +3561,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="33"/>
       <c r="C24" s="33"/>
       <c r="D24" s="33"/>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="AR24" s="30"/>
     </row>
-    <row r="25" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="33"/>
       <c r="C25" s="33"/>
       <c r="D25" s="33"/>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="AR25" s="30"/>
     </row>
-    <row r="26" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="33"/>
       <c r="C26" s="33"/>
       <c r="D26" s="33"/>
@@ -3710,77 +3710,77 @@
       </c>
       <c r="AR26" s="30"/>
     </row>
-    <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="79" t="s">
+    <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="75" t="s">
         <v>64</v>
       </c>
-      <c r="C27" s="80"/>
+      <c r="C27" s="76"/>
       <c r="D27" s="55" t="s">
         <v>54</v>
       </c>
       <c r="E27" s="36"/>
-      <c r="F27" s="79" t="s">
+      <c r="F27" s="75" t="s">
         <v>64</v>
       </c>
-      <c r="G27" s="80"/>
+      <c r="G27" s="76"/>
       <c r="H27" s="55" t="s">
         <v>54</v>
       </c>
       <c r="I27" s="36"/>
-      <c r="J27" s="79" t="s">
+      <c r="J27" s="75" t="s">
         <v>64</v>
       </c>
-      <c r="K27" s="80"/>
+      <c r="K27" s="76"/>
       <c r="L27" s="55" t="s">
         <v>54</v>
       </c>
       <c r="M27" s="5"/>
-      <c r="N27" s="87" t="s">
+      <c r="N27" s="70" t="s">
         <v>64</v>
       </c>
-      <c r="O27" s="88"/>
+      <c r="O27" s="71"/>
       <c r="P27" s="34" t="s">
         <v>54</v>
       </c>
       <c r="Q27" s="36"/>
-      <c r="R27" s="87" t="s">
+      <c r="R27" s="70" t="s">
         <v>64</v>
       </c>
-      <c r="S27" s="88"/>
+      <c r="S27" s="71"/>
       <c r="T27" s="34" t="s">
         <v>54</v>
       </c>
       <c r="U27" s="36"/>
-      <c r="V27" s="87" t="s">
+      <c r="V27" s="70" t="s">
         <v>64</v>
       </c>
-      <c r="W27" s="88"/>
+      <c r="W27" s="71"/>
       <c r="X27" s="34" t="s">
         <v>54</v>
       </c>
       <c r="Y27" s="36"/>
-      <c r="Z27" s="87" t="s">
+      <c r="Z27" s="70" t="s">
         <v>64</v>
       </c>
-      <c r="AA27" s="88"/>
+      <c r="AA27" s="71"/>
       <c r="AB27" s="34" t="s">
         <v>54</v>
       </c>
       <c r="AC27" s="36"/>
-      <c r="AD27" s="87" t="s">
+      <c r="AD27" s="70" t="s">
         <v>64</v>
       </c>
-      <c r="AE27" s="88"/>
+      <c r="AE27" s="71"/>
       <c r="AF27" s="34" t="s">
         <v>54</v>
       </c>
       <c r="AG27" s="36"/>
-      <c r="AH27" s="87"/>
-      <c r="AI27" s="88"/>
+      <c r="AH27" s="70"/>
+      <c r="AI27" s="71"/>
       <c r="AJ27" s="34"/>
       <c r="AK27" s="36"/>
-      <c r="AL27" s="87"/>
-      <c r="AM27" s="88"/>
+      <c r="AL27" s="70"/>
+      <c r="AM27" s="71"/>
       <c r="AN27" s="34"/>
       <c r="AP27" s="46" t="s">
         <v>13</v>
@@ -3791,45 +3791,45 @@
       </c>
       <c r="AR27" s="30"/>
     </row>
-    <row r="28" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="81"/>
-      <c r="C28" s="82"/>
+    <row r="28" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="77"/>
+      <c r="C28" s="78"/>
       <c r="D28" s="61"/>
       <c r="E28" s="38"/>
-      <c r="F28" s="81"/>
-      <c r="G28" s="82"/>
+      <c r="F28" s="77"/>
+      <c r="G28" s="78"/>
       <c r="H28" s="61"/>
       <c r="I28" s="36"/>
-      <c r="J28" s="81"/>
-      <c r="K28" s="82"/>
+      <c r="J28" s="77"/>
+      <c r="K28" s="78"/>
       <c r="L28" s="61"/>
       <c r="M28" s="5"/>
-      <c r="N28" s="71"/>
-      <c r="O28" s="72"/>
+      <c r="N28" s="83"/>
+      <c r="O28" s="84"/>
       <c r="P28" s="18"/>
       <c r="Q28" s="38"/>
-      <c r="R28" s="71"/>
-      <c r="S28" s="72"/>
+      <c r="R28" s="83"/>
+      <c r="S28" s="84"/>
       <c r="T28" s="18"/>
       <c r="U28" s="38"/>
-      <c r="V28" s="71"/>
-      <c r="W28" s="72"/>
+      <c r="V28" s="83"/>
+      <c r="W28" s="84"/>
       <c r="X28" s="18"/>
       <c r="Y28" s="36"/>
-      <c r="Z28" s="71"/>
-      <c r="AA28" s="72"/>
+      <c r="Z28" s="83"/>
+      <c r="AA28" s="84"/>
       <c r="AB28" s="18"/>
       <c r="AC28" s="36"/>
-      <c r="AD28" s="71"/>
-      <c r="AE28" s="72"/>
+      <c r="AD28" s="83"/>
+      <c r="AE28" s="84"/>
       <c r="AF28" s="18"/>
       <c r="AG28" s="38"/>
       <c r="AH28" s="137"/>
       <c r="AI28" s="138"/>
       <c r="AJ28" s="18"/>
       <c r="AK28" s="36"/>
-      <c r="AL28" s="71"/>
-      <c r="AM28" s="72"/>
+      <c r="AL28" s="83"/>
+      <c r="AM28" s="84"/>
       <c r="AN28" s="18"/>
       <c r="AP28" s="46" t="s">
         <v>28</v>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="AR28" s="30"/>
     </row>
-    <row r="29" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="97" t="s">
         <v>7</v>
       </c>
@@ -3923,7 +3923,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B30" s="99" t="s">
         <v>19</v>
       </c>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="AR30" s="30"/>
     </row>
-    <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="95" t="s">
         <v>37</v>
       </c>
@@ -4080,7 +4080,7 @@
       <c r="AQ31" s="49"/>
       <c r="AR31" s="30"/>
     </row>
-    <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="95" t="s">
         <v>21</v>
       </c>
@@ -4156,7 +4156,7 @@
       <c r="AQ32" s="52"/>
       <c r="AR32" s="30"/>
     </row>
-    <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B33" s="95" t="s">
         <v>14</v>
       </c>
@@ -4206,7 +4206,7 @@
       <c r="AN33" s="45"/>
       <c r="AR33" s="13"/>
     </row>
-    <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="12"/>
       <c r="B34" s="142"/>
       <c r="C34" s="143"/>
@@ -4252,7 +4252,7 @@
       <c r="AQ34" s="12"/>
       <c r="AR34" s="13"/>
     </row>
-    <row r="35" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="12"/>
       <c r="B35" s="33"/>
       <c r="C35" s="33"/>
@@ -4297,7 +4297,7 @@
       <c r="AQ35" s="12"/>
       <c r="AR35" s="13"/>
     </row>
-    <row r="36" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="12"/>
       <c r="B36" s="33"/>
       <c r="C36" s="33"/>
@@ -4345,7 +4345,7 @@
       <c r="AQ36" s="31"/>
       <c r="AR36" s="13"/>
     </row>
-    <row r="37" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="12"/>
       <c r="B37" s="33"/>
       <c r="C37" s="33"/>
@@ -4391,76 +4391,76 @@
       <c r="AQ37" s="31"/>
       <c r="AR37" s="13"/>
     </row>
-    <row r="38" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12"/>
-      <c r="B38" s="79" t="s">
+      <c r="B38" s="75" t="s">
         <v>90</v>
       </c>
-      <c r="C38" s="80"/>
+      <c r="C38" s="76"/>
       <c r="D38" s="55" t="s">
         <v>77</v>
       </c>
       <c r="E38" s="36"/>
-      <c r="F38" s="79" t="s">
+      <c r="F38" s="75" t="s">
         <v>91</v>
       </c>
-      <c r="G38" s="80"/>
+      <c r="G38" s="76"/>
       <c r="H38" s="55" t="s">
         <v>83</v>
       </c>
       <c r="I38" s="36"/>
-      <c r="J38" s="79" t="s">
+      <c r="J38" s="75" t="s">
         <v>92</v>
       </c>
-      <c r="K38" s="80"/>
+      <c r="K38" s="76"/>
       <c r="L38" s="55" t="s">
         <v>93</v>
       </c>
       <c r="M38" s="5"/>
-      <c r="N38" s="87" t="s">
+      <c r="N38" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="O38" s="88"/>
+      <c r="O38" s="71"/>
       <c r="P38" s="34"/>
       <c r="Q38" s="36"/>
-      <c r="R38" s="87" t="s">
+      <c r="R38" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="S38" s="88"/>
+      <c r="S38" s="71"/>
       <c r="T38" s="34" t="s">
         <v>77</v>
       </c>
       <c r="U38" s="36"/>
-      <c r="V38" s="87" t="s">
+      <c r="V38" s="70" t="s">
         <v>70</v>
       </c>
-      <c r="W38" s="88"/>
+      <c r="W38" s="71"/>
       <c r="X38" s="34" t="s">
         <v>52</v>
       </c>
       <c r="Y38" s="36"/>
-      <c r="Z38" s="87"/>
-      <c r="AA38" s="88"/>
+      <c r="Z38" s="70"/>
+      <c r="AA38" s="71"/>
       <c r="AB38" s="34"/>
       <c r="AC38" s="36"/>
-      <c r="AD38" s="87" t="s">
+      <c r="AD38" s="70" t="s">
         <v>71</v>
       </c>
-      <c r="AE38" s="88"/>
+      <c r="AE38" s="71"/>
       <c r="AF38" s="34"/>
       <c r="AG38" s="36"/>
-      <c r="AH38" s="87" t="s">
+      <c r="AH38" s="70" t="s">
         <v>71</v>
       </c>
-      <c r="AI38" s="88"/>
+      <c r="AI38" s="71"/>
       <c r="AJ38" s="34" t="s">
         <v>76</v>
       </c>
       <c r="AK38" s="36"/>
-      <c r="AL38" s="87" t="s">
+      <c r="AL38" s="70" t="s">
         <v>72</v>
       </c>
-      <c r="AM38" s="88"/>
+      <c r="AM38" s="71"/>
       <c r="AN38" s="34" t="s">
         <v>55</v>
       </c>
@@ -4469,161 +4469,161 @@
       <c r="AQ38" s="31"/>
       <c r="AR38" s="13"/>
     </row>
-    <row r="39" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12"/>
-      <c r="B39" s="76" t="s">
+      <c r="B39" s="62" t="s">
         <v>51</v>
       </c>
-      <c r="C39" s="77"/>
-      <c r="D39" s="78"/>
+      <c r="C39" s="63"/>
+      <c r="D39" s="64"/>
       <c r="E39" s="36"/>
-      <c r="F39" s="76" t="s">
+      <c r="F39" s="62" t="s">
         <v>94</v>
       </c>
-      <c r="G39" s="77"/>
-      <c r="H39" s="78"/>
+      <c r="G39" s="63"/>
+      <c r="H39" s="64"/>
       <c r="I39" s="36"/>
-      <c r="J39" s="76" t="s">
+      <c r="J39" s="62" t="s">
         <v>95</v>
       </c>
-      <c r="K39" s="77"/>
-      <c r="L39" s="78"/>
+      <c r="K39" s="63"/>
+      <c r="L39" s="64"/>
       <c r="M39" s="5"/>
-      <c r="N39" s="84" t="s">
+      <c r="N39" s="72" t="s">
         <v>68</v>
       </c>
-      <c r="O39" s="85"/>
-      <c r="P39" s="86"/>
+      <c r="O39" s="73"/>
+      <c r="P39" s="74"/>
       <c r="Q39" s="36"/>
-      <c r="R39" s="84" t="s">
+      <c r="R39" s="72" t="s">
         <v>68</v>
       </c>
-      <c r="S39" s="85"/>
-      <c r="T39" s="86"/>
+      <c r="S39" s="73"/>
+      <c r="T39" s="74"/>
       <c r="U39" s="36"/>
-      <c r="V39" s="84" t="s">
+      <c r="V39" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="W39" s="85"/>
-      <c r="X39" s="86"/>
+      <c r="W39" s="73"/>
+      <c r="X39" s="74"/>
       <c r="Y39" s="37"/>
-      <c r="Z39" s="84"/>
-      <c r="AA39" s="85"/>
-      <c r="AB39" s="86"/>
+      <c r="Z39" s="72"/>
+      <c r="AA39" s="73"/>
+      <c r="AB39" s="74"/>
       <c r="AC39" s="36"/>
-      <c r="AD39" s="84" t="s">
+      <c r="AD39" s="72" t="s">
         <v>74</v>
       </c>
-      <c r="AE39" s="85"/>
-      <c r="AF39" s="86"/>
+      <c r="AE39" s="73"/>
+      <c r="AF39" s="74"/>
       <c r="AG39" s="36"/>
-      <c r="AH39" s="84" t="s">
+      <c r="AH39" s="72" t="s">
         <v>74</v>
       </c>
-      <c r="AI39" s="85"/>
-      <c r="AJ39" s="86"/>
+      <c r="AI39" s="73"/>
+      <c r="AJ39" s="74"/>
       <c r="AK39" s="36"/>
-      <c r="AL39" s="84" t="s">
+      <c r="AL39" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="AM39" s="85"/>
-      <c r="AN39" s="86"/>
+      <c r="AM39" s="73"/>
+      <c r="AN39" s="74"/>
       <c r="AO39" s="31"/>
       <c r="AP39" s="31"/>
       <c r="AQ39" s="31"/>
       <c r="AR39" s="13"/>
     </row>
-    <row r="40" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12"/>
-      <c r="B40" s="81"/>
-      <c r="C40" s="82"/>
-      <c r="D40" s="83"/>
+      <c r="B40" s="77"/>
+      <c r="C40" s="78"/>
+      <c r="D40" s="79"/>
       <c r="E40" s="43"/>
-      <c r="F40" s="81"/>
-      <c r="G40" s="82"/>
-      <c r="H40" s="83"/>
+      <c r="F40" s="77"/>
+      <c r="G40" s="78"/>
+      <c r="H40" s="79"/>
       <c r="I40" s="43"/>
-      <c r="J40" s="81"/>
-      <c r="K40" s="82"/>
-      <c r="L40" s="83"/>
+      <c r="J40" s="77"/>
+      <c r="K40" s="78"/>
+      <c r="L40" s="79"/>
       <c r="M40" s="4"/>
-      <c r="N40" s="71" t="s">
+      <c r="N40" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="O40" s="72"/>
-      <c r="P40" s="73"/>
+      <c r="O40" s="84"/>
+      <c r="P40" s="85"/>
       <c r="Q40" s="43"/>
-      <c r="R40" s="71"/>
-      <c r="S40" s="72"/>
-      <c r="T40" s="73"/>
+      <c r="R40" s="83"/>
+      <c r="S40" s="84"/>
+      <c r="T40" s="85"/>
       <c r="U40" s="35"/>
-      <c r="V40" s="71"/>
-      <c r="W40" s="72"/>
-      <c r="X40" s="73"/>
+      <c r="V40" s="83"/>
+      <c r="W40" s="84"/>
+      <c r="X40" s="85"/>
       <c r="Y40" s="36"/>
-      <c r="Z40" s="71"/>
-      <c r="AA40" s="72"/>
-      <c r="AB40" s="73"/>
+      <c r="Z40" s="83"/>
+      <c r="AA40" s="84"/>
+      <c r="AB40" s="85"/>
       <c r="AC40" s="36"/>
-      <c r="AD40" s="71" t="s">
+      <c r="AD40" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="AE40" s="72"/>
-      <c r="AF40" s="73"/>
+      <c r="AE40" s="84"/>
+      <c r="AF40" s="85"/>
       <c r="AG40" s="43"/>
-      <c r="AH40" s="71"/>
-      <c r="AI40" s="72"/>
-      <c r="AJ40" s="73"/>
+      <c r="AH40" s="83"/>
+      <c r="AI40" s="84"/>
+      <c r="AJ40" s="85"/>
       <c r="AK40" s="43"/>
-      <c r="AL40" s="71"/>
-      <c r="AM40" s="72"/>
-      <c r="AN40" s="73"/>
+      <c r="AL40" s="83"/>
+      <c r="AM40" s="84"/>
+      <c r="AN40" s="85"/>
       <c r="AO40" s="31"/>
       <c r="AP40" s="31"/>
       <c r="AQ40" s="31"/>
       <c r="AR40" s="13"/>
     </row>
-    <row r="41" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12"/>
-      <c r="B41" s="68" t="s">
+      <c r="B41" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="C41" s="69"/>
-      <c r="D41" s="70"/>
+      <c r="C41" s="68"/>
+      <c r="D41" s="69"/>
       <c r="E41" s="37"/>
-      <c r="F41" s="153" t="s">
+      <c r="F41" s="150" t="s">
         <v>96</v>
       </c>
-      <c r="G41" s="154"/>
-      <c r="H41" s="155"/>
+      <c r="G41" s="151"/>
+      <c r="H41" s="152"/>
       <c r="I41" s="31"/>
-      <c r="J41" s="68" t="s">
+      <c r="J41" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="K41" s="69"/>
-      <c r="L41" s="70"/>
+      <c r="K41" s="68"/>
+      <c r="L41" s="69"/>
       <c r="M41" s="5"/>
-      <c r="N41" s="68" t="s">
+      <c r="N41" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="O41" s="69"/>
-      <c r="P41" s="70"/>
+      <c r="O41" s="68"/>
+      <c r="P41" s="69"/>
       <c r="Q41" s="32"/>
-      <c r="R41" s="68" t="s">
+      <c r="R41" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="S41" s="69"/>
-      <c r="T41" s="70"/>
+      <c r="S41" s="68"/>
+      <c r="T41" s="69"/>
       <c r="U41" s="31"/>
-      <c r="V41" s="68" t="s">
+      <c r="V41" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="W41" s="69"/>
-      <c r="X41" s="70"/>
+      <c r="W41" s="68"/>
+      <c r="X41" s="69"/>
       <c r="Y41" s="32"/>
-      <c r="Z41" s="68"/>
-      <c r="AA41" s="69"/>
-      <c r="AB41" s="70"/>
+      <c r="Z41" s="67"/>
+      <c r="AA41" s="68"/>
+      <c r="AB41" s="69"/>
       <c r="AC41" s="32"/>
       <c r="AD41" s="139" t="s">
         <v>24</v>
@@ -4631,143 +4631,143 @@
       <c r="AE41" s="140"/>
       <c r="AF41" s="141"/>
       <c r="AG41" s="37"/>
-      <c r="AH41" s="68" t="s">
+      <c r="AH41" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="AI41" s="69"/>
-      <c r="AJ41" s="70"/>
+      <c r="AI41" s="68"/>
+      <c r="AJ41" s="69"/>
       <c r="AK41" s="31"/>
-      <c r="AL41" s="68" t="s">
+      <c r="AL41" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="AM41" s="69"/>
-      <c r="AN41" s="70"/>
+      <c r="AM41" s="68"/>
+      <c r="AN41" s="69"/>
       <c r="AO41" s="31"/>
       <c r="AP41" s="31"/>
       <c r="AQ41" s="31"/>
       <c r="AR41" s="13"/>
     </row>
-    <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12"/>
-      <c r="B42" s="68" t="s">
+      <c r="B42" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="C42" s="69"/>
-      <c r="D42" s="70"/>
+      <c r="C42" s="68"/>
+      <c r="D42" s="69"/>
       <c r="E42" s="44"/>
-      <c r="F42" s="68" t="s">
+      <c r="F42" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="G42" s="69"/>
-      <c r="H42" s="70"/>
+      <c r="G42" s="68"/>
+      <c r="H42" s="69"/>
       <c r="I42" s="31"/>
-      <c r="J42" s="68" t="s">
+      <c r="J42" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="K42" s="69"/>
-      <c r="L42" s="70"/>
+      <c r="K42" s="68"/>
+      <c r="L42" s="69"/>
       <c r="M42" s="5"/>
-      <c r="N42" s="68" t="s">
+      <c r="N42" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="O42" s="69"/>
-      <c r="P42" s="70"/>
+      <c r="O42" s="68"/>
+      <c r="P42" s="69"/>
       <c r="Q42" s="31"/>
-      <c r="R42" s="68" t="s">
+      <c r="R42" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="S42" s="69"/>
-      <c r="T42" s="70"/>
+      <c r="S42" s="68"/>
+      <c r="T42" s="69"/>
       <c r="U42" s="32"/>
-      <c r="V42" s="68" t="s">
+      <c r="V42" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="W42" s="69"/>
-      <c r="X42" s="70"/>
+      <c r="W42" s="68"/>
+      <c r="X42" s="69"/>
       <c r="Y42" s="32"/>
-      <c r="Z42" s="68"/>
-      <c r="AA42" s="69"/>
-      <c r="AB42" s="70"/>
+      <c r="Z42" s="67"/>
+      <c r="AA42" s="68"/>
+      <c r="AB42" s="69"/>
       <c r="AC42" s="32"/>
-      <c r="AD42" s="68" t="s">
+      <c r="AD42" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="AE42" s="69"/>
-      <c r="AF42" s="70"/>
+      <c r="AE42" s="68"/>
+      <c r="AF42" s="69"/>
       <c r="AG42" s="44"/>
-      <c r="AH42" s="68" t="s">
+      <c r="AH42" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="AI42" s="69"/>
-      <c r="AJ42" s="70"/>
+      <c r="AI42" s="68"/>
+      <c r="AJ42" s="69"/>
       <c r="AK42" s="31"/>
-      <c r="AL42" s="68" t="s">
+      <c r="AL42" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="AM42" s="69"/>
-      <c r="AN42" s="70"/>
+      <c r="AM42" s="68"/>
+      <c r="AN42" s="69"/>
       <c r="AO42" s="31"/>
       <c r="AP42" s="31"/>
       <c r="AQ42" s="31"/>
       <c r="AR42" s="13"/>
     </row>
-    <row r="43" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12"/>
-      <c r="B43" s="62"/>
-      <c r="C43" s="63"/>
-      <c r="D43" s="64"/>
+      <c r="B43" s="80"/>
+      <c r="C43" s="81"/>
+      <c r="D43" s="82"/>
       <c r="E43" s="35"/>
-      <c r="F43" s="62" t="s">
+      <c r="F43" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="G43" s="63"/>
-      <c r="H43" s="64"/>
+      <c r="G43" s="81"/>
+      <c r="H43" s="82"/>
       <c r="I43" s="40"/>
-      <c r="J43" s="62"/>
-      <c r="K43" s="63"/>
-      <c r="L43" s="64"/>
+      <c r="J43" s="80"/>
+      <c r="K43" s="81"/>
+      <c r="L43" s="82"/>
       <c r="M43" s="14"/>
-      <c r="N43" s="68" t="s">
+      <c r="N43" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="O43" s="69"/>
-      <c r="P43" s="70"/>
+      <c r="O43" s="68"/>
+      <c r="P43" s="69"/>
       <c r="Q43" s="40"/>
-      <c r="R43" s="68" t="s">
+      <c r="R43" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="S43" s="69"/>
-      <c r="T43" s="70"/>
+      <c r="S43" s="68"/>
+      <c r="T43" s="69"/>
       <c r="U43" s="40"/>
-      <c r="V43" s="62"/>
-      <c r="W43" s="63"/>
-      <c r="X43" s="64"/>
+      <c r="V43" s="80"/>
+      <c r="W43" s="81"/>
+      <c r="X43" s="82"/>
       <c r="Y43" s="40"/>
-      <c r="Z43" s="62"/>
-      <c r="AA43" s="63"/>
-      <c r="AB43" s="64"/>
+      <c r="Z43" s="80"/>
+      <c r="AA43" s="81"/>
+      <c r="AB43" s="82"/>
       <c r="AC43" s="40"/>
-      <c r="AD43" s="68" t="s">
+      <c r="AD43" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="AE43" s="69"/>
-      <c r="AF43" s="70"/>
+      <c r="AE43" s="68"/>
+      <c r="AF43" s="69"/>
       <c r="AG43" s="35"/>
-      <c r="AH43" s="68" t="s">
+      <c r="AH43" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="AI43" s="69"/>
-      <c r="AJ43" s="70"/>
+      <c r="AI43" s="68"/>
+      <c r="AJ43" s="69"/>
       <c r="AK43" s="40"/>
-      <c r="AL43" s="62"/>
-      <c r="AM43" s="63"/>
-      <c r="AN43" s="64"/>
+      <c r="AL43" s="80"/>
+      <c r="AM43" s="81"/>
+      <c r="AN43" s="82"/>
       <c r="AO43" s="31"/>
       <c r="AP43" s="31"/>
       <c r="AQ43" s="31"/>
       <c r="AR43" s="13"/>
     </row>
-    <row r="44" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="12"/>
       <c r="B44" s="35"/>
       <c r="C44" s="35"/>
@@ -4781,15 +4781,15 @@
       <c r="K44" s="35"/>
       <c r="L44" s="35"/>
       <c r="M44" s="14"/>
-      <c r="N44" s="68"/>
-      <c r="O44" s="69"/>
-      <c r="P44" s="70"/>
+      <c r="N44" s="67"/>
+      <c r="O44" s="68"/>
+      <c r="P44" s="69"/>
       <c r="Q44" s="36"/>
-      <c r="R44" s="68" t="s">
+      <c r="R44" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="S44" s="69"/>
-      <c r="T44" s="70"/>
+      <c r="S44" s="68"/>
+      <c r="T44" s="69"/>
       <c r="U44" s="50"/>
       <c r="V44" s="35"/>
       <c r="W44" s="35"/>
@@ -4799,17 +4799,17 @@
       <c r="AA44" s="35"/>
       <c r="AB44" s="35"/>
       <c r="AC44" s="36"/>
-      <c r="AD44" s="62" t="s">
+      <c r="AD44" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="AE44" s="63"/>
-      <c r="AF44" s="64"/>
+      <c r="AE44" s="81"/>
+      <c r="AF44" s="82"/>
       <c r="AG44" s="50"/>
-      <c r="AH44" s="62" t="s">
+      <c r="AH44" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="AI44" s="63"/>
-      <c r="AJ44" s="64"/>
+      <c r="AI44" s="81"/>
+      <c r="AJ44" s="82"/>
       <c r="AK44" s="32"/>
       <c r="AL44" s="35"/>
       <c r="AM44" s="35"/>
@@ -4819,52 +4819,52 @@
       <c r="AQ44" s="31"/>
       <c r="AR44" s="13"/>
     </row>
-    <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="12"/>
-      <c r="B45" s="79" t="s">
+      <c r="B45" s="75" t="s">
         <v>91</v>
       </c>
-      <c r="C45" s="80"/>
+      <c r="C45" s="76"/>
       <c r="D45" s="55" t="s">
         <v>54</v>
       </c>
       <c r="E45" s="36"/>
-      <c r="F45" s="79" t="s">
+      <c r="F45" s="75" t="s">
         <v>91</v>
       </c>
-      <c r="G45" s="80"/>
+      <c r="G45" s="76"/>
       <c r="H45" s="55" t="s">
         <v>43</v>
       </c>
       <c r="I45" s="32"/>
-      <c r="J45" s="79" t="s">
+      <c r="J45" s="75" t="s">
         <v>91</v>
       </c>
-      <c r="K45" s="80"/>
+      <c r="K45" s="76"/>
       <c r="L45" s="55" t="s">
         <v>83</v>
       </c>
       <c r="M45" s="14"/>
-      <c r="N45" s="62"/>
-      <c r="O45" s="63"/>
-      <c r="P45" s="64"/>
+      <c r="N45" s="80"/>
+      <c r="O45" s="81"/>
+      <c r="P45" s="82"/>
       <c r="Q45" s="36"/>
-      <c r="R45" s="62" t="s">
+      <c r="R45" s="80" t="s">
         <v>14</v>
       </c>
-      <c r="S45" s="63"/>
-      <c r="T45" s="64"/>
+      <c r="S45" s="81"/>
+      <c r="T45" s="82"/>
       <c r="U45" s="36"/>
-      <c r="V45" s="87" t="s">
+      <c r="V45" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="W45" s="88"/>
+      <c r="W45" s="71"/>
       <c r="X45" s="34" t="s">
         <v>83</v>
       </c>
       <c r="Y45" s="36"/>
-      <c r="Z45" s="87"/>
-      <c r="AA45" s="88"/>
+      <c r="Z45" s="70"/>
+      <c r="AA45" s="71"/>
       <c r="AB45" s="34"/>
       <c r="AC45" s="36"/>
       <c r="AD45" s="35"/>
@@ -4875,10 +4875,10 @@
       <c r="AI45" s="35"/>
       <c r="AJ45" s="35"/>
       <c r="AK45" s="32"/>
-      <c r="AL45" s="87" t="s">
+      <c r="AL45" s="70" t="s">
         <v>72</v>
       </c>
-      <c r="AM45" s="88"/>
+      <c r="AM45" s="71"/>
       <c r="AN45" s="34" t="s">
         <v>54</v>
       </c>
@@ -4887,25 +4887,25 @@
       <c r="AQ45" s="31"/>
       <c r="AR45" s="13"/>
     </row>
-    <row r="46" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12"/>
-      <c r="B46" s="76" t="s">
+      <c r="B46" s="62" t="s">
         <v>97</v>
       </c>
-      <c r="C46" s="77"/>
-      <c r="D46" s="78"/>
+      <c r="C46" s="63"/>
+      <c r="D46" s="64"/>
       <c r="E46" s="36"/>
-      <c r="F46" s="76" t="s">
+      <c r="F46" s="62" t="s">
         <v>98</v>
       </c>
-      <c r="G46" s="77"/>
-      <c r="H46" s="78"/>
+      <c r="G46" s="63"/>
+      <c r="H46" s="64"/>
       <c r="I46" s="54"/>
-      <c r="J46" s="76" t="s">
+      <c r="J46" s="62" t="s">
         <v>99</v>
       </c>
-      <c r="K46" s="77"/>
-      <c r="L46" s="78"/>
+      <c r="K46" s="63"/>
+      <c r="L46" s="64"/>
       <c r="M46" s="4"/>
       <c r="N46" s="35"/>
       <c r="O46" s="35"/>
@@ -4915,251 +4915,251 @@
       <c r="S46" s="35"/>
       <c r="T46" s="58"/>
       <c r="U46" s="36"/>
-      <c r="V46" s="84" t="s">
+      <c r="V46" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="W46" s="85"/>
-      <c r="X46" s="86"/>
+      <c r="W46" s="73"/>
+      <c r="X46" s="74"/>
       <c r="Y46" s="36"/>
-      <c r="Z46" s="84"/>
-      <c r="AA46" s="85"/>
-      <c r="AB46" s="86"/>
+      <c r="Z46" s="72"/>
+      <c r="AA46" s="73"/>
+      <c r="AB46" s="74"/>
       <c r="AC46" s="36"/>
-      <c r="AD46" s="87"/>
-      <c r="AE46" s="88"/>
+      <c r="AD46" s="70"/>
+      <c r="AE46" s="71"/>
       <c r="AF46" s="34"/>
       <c r="AG46" s="36"/>
-      <c r="AH46" s="87"/>
-      <c r="AI46" s="88"/>
+      <c r="AH46" s="70"/>
+      <c r="AI46" s="71"/>
       <c r="AJ46" s="34"/>
       <c r="AK46" s="54"/>
-      <c r="AL46" s="84" t="s">
+      <c r="AL46" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="AM46" s="85"/>
-      <c r="AN46" s="86"/>
+      <c r="AM46" s="73"/>
+      <c r="AN46" s="74"/>
       <c r="AO46" s="31"/>
       <c r="AP46" s="31"/>
       <c r="AQ46" s="31"/>
       <c r="AR46" s="13"/>
     </row>
-    <row r="47" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12"/>
-      <c r="B47" s="81"/>
-      <c r="C47" s="82"/>
-      <c r="D47" s="83"/>
+      <c r="B47" s="77"/>
+      <c r="C47" s="78"/>
+      <c r="D47" s="79"/>
       <c r="E47" s="43"/>
-      <c r="F47" s="81"/>
-      <c r="G47" s="82"/>
-      <c r="H47" s="83"/>
+      <c r="F47" s="77"/>
+      <c r="G47" s="78"/>
+      <c r="H47" s="79"/>
       <c r="I47" s="37"/>
-      <c r="J47" s="81"/>
-      <c r="K47" s="82"/>
-      <c r="L47" s="83"/>
+      <c r="J47" s="77"/>
+      <c r="K47" s="78"/>
+      <c r="L47" s="79"/>
       <c r="M47" s="4"/>
-      <c r="N47" s="87" t="s">
+      <c r="N47" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="O47" s="88"/>
+      <c r="O47" s="71"/>
       <c r="P47" s="34" t="s">
         <v>83</v>
       </c>
       <c r="Q47" s="37"/>
-      <c r="R47" s="87"/>
-      <c r="S47" s="88"/>
+      <c r="R47" s="70"/>
+      <c r="S47" s="71"/>
       <c r="T47" s="34"/>
       <c r="U47" s="43"/>
-      <c r="V47" s="71"/>
-      <c r="W47" s="72"/>
-      <c r="X47" s="73"/>
+      <c r="V47" s="83"/>
+      <c r="W47" s="84"/>
+      <c r="X47" s="85"/>
       <c r="Y47" s="43"/>
-      <c r="Z47" s="71"/>
-      <c r="AA47" s="72"/>
-      <c r="AB47" s="73"/>
+      <c r="Z47" s="83"/>
+      <c r="AA47" s="84"/>
+      <c r="AB47" s="85"/>
       <c r="AC47" s="35"/>
-      <c r="AD47" s="84"/>
-      <c r="AE47" s="85"/>
-      <c r="AF47" s="86"/>
+      <c r="AD47" s="72"/>
+      <c r="AE47" s="73"/>
+      <c r="AF47" s="74"/>
       <c r="AG47" s="43"/>
-      <c r="AH47" s="84"/>
-      <c r="AI47" s="85"/>
-      <c r="AJ47" s="86"/>
+      <c r="AH47" s="72"/>
+      <c r="AI47" s="73"/>
+      <c r="AJ47" s="74"/>
       <c r="AK47" s="37"/>
-      <c r="AL47" s="71"/>
-      <c r="AM47" s="72"/>
-      <c r="AN47" s="73"/>
+      <c r="AL47" s="83"/>
+      <c r="AM47" s="84"/>
+      <c r="AN47" s="85"/>
       <c r="AO47" s="31"/>
       <c r="AP47" s="31"/>
       <c r="AQ47" s="31"/>
       <c r="AR47" s="13"/>
     </row>
-    <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12"/>
-      <c r="B48" s="68" t="s">
+      <c r="B48" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="C48" s="69"/>
-      <c r="D48" s="70"/>
+      <c r="C48" s="68"/>
+      <c r="D48" s="69"/>
       <c r="E48" s="37"/>
-      <c r="F48" s="68" t="s">
+      <c r="F48" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G48" s="69"/>
-      <c r="H48" s="70"/>
+      <c r="G48" s="68"/>
+      <c r="H48" s="69"/>
       <c r="I48" s="44"/>
-      <c r="J48" s="89" t="s">
+      <c r="J48" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="K48" s="90"/>
-      <c r="L48" s="91"/>
+      <c r="K48" s="87"/>
+      <c r="L48" s="88"/>
       <c r="M48" s="5"/>
-      <c r="N48" s="84" t="s">
+      <c r="N48" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="O48" s="85"/>
-      <c r="P48" s="86"/>
+      <c r="O48" s="73"/>
+      <c r="P48" s="74"/>
       <c r="Q48" s="44"/>
-      <c r="R48" s="84"/>
-      <c r="S48" s="85"/>
-      <c r="T48" s="86"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="73"/>
+      <c r="T48" s="74"/>
       <c r="U48" s="37"/>
-      <c r="V48" s="65" t="s">
+      <c r="V48" s="89" t="s">
         <v>37</v>
       </c>
-      <c r="W48" s="66"/>
-      <c r="X48" s="67"/>
+      <c r="W48" s="90"/>
+      <c r="X48" s="91"/>
       <c r="Y48" s="37"/>
-      <c r="Z48" s="68"/>
-      <c r="AA48" s="69"/>
-      <c r="AB48" s="70"/>
+      <c r="Z48" s="67"/>
+      <c r="AA48" s="68"/>
+      <c r="AB48" s="69"/>
       <c r="AC48" s="43"/>
-      <c r="AD48" s="71"/>
-      <c r="AE48" s="72"/>
-      <c r="AF48" s="73"/>
+      <c r="AD48" s="83"/>
+      <c r="AE48" s="84"/>
+      <c r="AF48" s="85"/>
       <c r="AG48" s="37"/>
-      <c r="AH48" s="71"/>
-      <c r="AI48" s="72"/>
-      <c r="AJ48" s="73"/>
+      <c r="AH48" s="83"/>
+      <c r="AI48" s="84"/>
+      <c r="AJ48" s="85"/>
       <c r="AK48" s="44"/>
-      <c r="AL48" s="68" t="s">
+      <c r="AL48" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="AM48" s="69"/>
-      <c r="AN48" s="70"/>
+      <c r="AM48" s="68"/>
+      <c r="AN48" s="69"/>
       <c r="AO48" s="31"/>
       <c r="AP48" s="31"/>
       <c r="AQ48" s="31"/>
       <c r="AR48" s="13"/>
     </row>
-    <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="68" t="s">
+    <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="C49" s="69"/>
-      <c r="D49" s="70"/>
+      <c r="C49" s="68"/>
+      <c r="D49" s="69"/>
       <c r="E49" s="35"/>
-      <c r="F49" s="68" t="s">
+      <c r="F49" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="G49" s="69"/>
-      <c r="H49" s="70"/>
+      <c r="G49" s="68"/>
+      <c r="H49" s="69"/>
       <c r="I49" s="44"/>
-      <c r="J49" s="89" t="s">
+      <c r="J49" s="86" t="s">
         <v>12</v>
       </c>
-      <c r="K49" s="90"/>
-      <c r="L49" s="91"/>
+      <c r="K49" s="87"/>
+      <c r="L49" s="88"/>
       <c r="M49" s="5"/>
-      <c r="N49" s="71"/>
-      <c r="O49" s="72"/>
-      <c r="P49" s="73"/>
+      <c r="N49" s="83"/>
+      <c r="O49" s="84"/>
+      <c r="P49" s="85"/>
       <c r="Q49" s="44"/>
-      <c r="R49" s="71"/>
-      <c r="S49" s="72"/>
-      <c r="T49" s="73"/>
+      <c r="R49" s="83"/>
+      <c r="S49" s="84"/>
+      <c r="T49" s="85"/>
       <c r="U49" s="44"/>
-      <c r="V49" s="68" t="s">
+      <c r="V49" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="W49" s="69"/>
-      <c r="X49" s="70"/>
+      <c r="W49" s="68"/>
+      <c r="X49" s="69"/>
       <c r="Y49" s="35"/>
-      <c r="Z49" s="68"/>
-      <c r="AA49" s="69"/>
-      <c r="AB49" s="70"/>
+      <c r="Z49" s="67"/>
+      <c r="AA49" s="68"/>
+      <c r="AB49" s="69"/>
       <c r="AC49" s="35"/>
-      <c r="AD49" s="68"/>
-      <c r="AE49" s="69"/>
-      <c r="AF49" s="70"/>
+      <c r="AD49" s="67"/>
+      <c r="AE49" s="68"/>
+      <c r="AF49" s="69"/>
       <c r="AG49" s="35"/>
-      <c r="AH49" s="68"/>
-      <c r="AI49" s="69"/>
-      <c r="AJ49" s="70"/>
+      <c r="AH49" s="67"/>
+      <c r="AI49" s="68"/>
+      <c r="AJ49" s="69"/>
       <c r="AK49" s="44"/>
-      <c r="AL49" s="68" t="s">
+      <c r="AL49" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="AM49" s="69"/>
-      <c r="AN49" s="70"/>
+      <c r="AM49" s="68"/>
+      <c r="AN49" s="69"/>
       <c r="AO49" s="31"/>
       <c r="AP49" s="31"/>
       <c r="AQ49" s="31"/>
       <c r="AR49" s="13"/>
     </row>
-    <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="150" t="s">
+    <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="153" t="s">
         <v>100</v>
       </c>
-      <c r="C50" s="151"/>
-      <c r="D50" s="152"/>
+      <c r="C50" s="154"/>
+      <c r="D50" s="155"/>
       <c r="E50" s="50"/>
-      <c r="F50" s="62" t="s">
+      <c r="F50" s="80" t="s">
         <v>14</v>
       </c>
-      <c r="G50" s="63"/>
-      <c r="H50" s="64"/>
+      <c r="G50" s="81"/>
+      <c r="H50" s="82"/>
       <c r="I50" s="50"/>
-      <c r="J50" s="62" t="s">
+      <c r="J50" s="80" t="s">
         <v>29</v>
       </c>
-      <c r="K50" s="63"/>
-      <c r="L50" s="64"/>
+      <c r="K50" s="81"/>
+      <c r="L50" s="82"/>
       <c r="M50" s="5"/>
-      <c r="N50" s="65" t="s">
+      <c r="N50" s="89" t="s">
         <v>37</v>
       </c>
-      <c r="O50" s="66"/>
-      <c r="P50" s="67"/>
+      <c r="O50" s="90"/>
+      <c r="P50" s="91"/>
       <c r="Q50" s="50"/>
-      <c r="R50" s="68"/>
-      <c r="S50" s="69"/>
-      <c r="T50" s="70"/>
+      <c r="R50" s="67"/>
+      <c r="S50" s="68"/>
+      <c r="T50" s="69"/>
       <c r="U50" s="50"/>
-      <c r="V50" s="62"/>
-      <c r="W50" s="63"/>
-      <c r="X50" s="64"/>
+      <c r="V50" s="80"/>
+      <c r="W50" s="81"/>
+      <c r="X50" s="82"/>
       <c r="Y50" s="50"/>
-      <c r="Z50" s="62"/>
-      <c r="AA50" s="63"/>
-      <c r="AB50" s="64"/>
+      <c r="Z50" s="80"/>
+      <c r="AA50" s="81"/>
+      <c r="AB50" s="82"/>
       <c r="AC50" s="50"/>
-      <c r="AD50" s="62"/>
-      <c r="AE50" s="63"/>
-      <c r="AF50" s="64"/>
+      <c r="AD50" s="80"/>
+      <c r="AE50" s="81"/>
+      <c r="AF50" s="82"/>
       <c r="AG50" s="50"/>
-      <c r="AH50" s="62"/>
-      <c r="AI50" s="63"/>
-      <c r="AJ50" s="64"/>
+      <c r="AH50" s="80"/>
+      <c r="AI50" s="81"/>
+      <c r="AJ50" s="82"/>
       <c r="AK50" s="50"/>
-      <c r="AL50" s="62"/>
-      <c r="AM50" s="63"/>
-      <c r="AN50" s="64"/>
+      <c r="AL50" s="80"/>
+      <c r="AM50" s="81"/>
+      <c r="AN50" s="82"/>
       <c r="AO50" s="31"/>
       <c r="AP50" s="31"/>
       <c r="AQ50" s="31"/>
       <c r="AR50" s="13"/>
     </row>
-    <row r="51" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B51" s="35"/>
       <c r="C51" s="35"/>
       <c r="D51" s="35"/>
@@ -5172,15 +5172,15 @@
       <c r="K51" s="35"/>
       <c r="L51" s="35"/>
       <c r="M51" s="14"/>
-      <c r="N51" s="62" t="s">
+      <c r="N51" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="O51" s="63"/>
-      <c r="P51" s="64"/>
+      <c r="O51" s="81"/>
+      <c r="P51" s="82"/>
       <c r="Q51" s="35"/>
-      <c r="R51" s="62"/>
-      <c r="S51" s="63"/>
-      <c r="T51" s="64"/>
+      <c r="R51" s="80"/>
+      <c r="S51" s="81"/>
+      <c r="T51" s="82"/>
       <c r="U51" s="36"/>
       <c r="V51" s="35"/>
       <c r="W51" s="35"/>
@@ -5206,27 +5206,27 @@
       <c r="AQ51" s="31"/>
       <c r="AR51" s="13"/>
     </row>
-    <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="74" t="s">
+    <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B52" s="65" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="75"/>
+      <c r="C52" s="66"/>
       <c r="D52" s="57" t="s">
         <v>85</v>
       </c>
       <c r="E52" s="36"/>
-      <c r="F52" s="74" t="s">
+      <c r="F52" s="65" t="s">
         <v>101</v>
       </c>
-      <c r="G52" s="75"/>
+      <c r="G52" s="66"/>
       <c r="H52" s="57" t="s">
         <v>102</v>
       </c>
       <c r="I52" s="54"/>
-      <c r="J52" s="74" t="s">
+      <c r="J52" s="65" t="s">
         <v>101</v>
       </c>
-      <c r="K52" s="75"/>
+      <c r="K52" s="66"/>
       <c r="L52" s="57" t="s">
         <v>93</v>
       </c>
@@ -5239,256 +5239,256 @@
       <c r="S52" s="35"/>
       <c r="T52" s="35"/>
       <c r="U52" s="35"/>
-      <c r="V52" s="87"/>
-      <c r="W52" s="88"/>
+      <c r="V52" s="70"/>
+      <c r="W52" s="71"/>
       <c r="X52" s="34"/>
       <c r="Y52" s="36"/>
-      <c r="Z52" s="87"/>
-      <c r="AA52" s="88"/>
+      <c r="Z52" s="70"/>
+      <c r="AA52" s="71"/>
       <c r="AB52" s="34"/>
       <c r="AC52" s="36"/>
-      <c r="AD52" s="87"/>
-      <c r="AE52" s="88"/>
+      <c r="AD52" s="70"/>
+      <c r="AE52" s="71"/>
       <c r="AF52" s="34"/>
       <c r="AG52" s="36"/>
-      <c r="AH52" s="87"/>
-      <c r="AI52" s="88"/>
+      <c r="AH52" s="70"/>
+      <c r="AI52" s="71"/>
       <c r="AJ52" s="34"/>
       <c r="AK52" s="54"/>
-      <c r="AL52" s="87"/>
-      <c r="AM52" s="88"/>
+      <c r="AL52" s="70"/>
+      <c r="AM52" s="71"/>
       <c r="AN52" s="34"/>
       <c r="AR52" s="13"/>
     </row>
-    <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="76" t="s">
+    <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B53" s="62" t="s">
         <v>103</v>
       </c>
-      <c r="C53" s="77"/>
-      <c r="D53" s="78"/>
+      <c r="C53" s="63"/>
+      <c r="D53" s="64"/>
       <c r="E53" s="36"/>
-      <c r="F53" s="76" t="s">
+      <c r="F53" s="62" t="s">
         <v>104</v>
       </c>
-      <c r="G53" s="77"/>
-      <c r="H53" s="78"/>
+      <c r="G53" s="63"/>
+      <c r="H53" s="64"/>
       <c r="I53" s="35"/>
-      <c r="J53" s="76" t="s">
+      <c r="J53" s="62" t="s">
         <v>114</v>
       </c>
-      <c r="K53" s="77"/>
-      <c r="L53" s="78"/>
+      <c r="K53" s="63"/>
+      <c r="L53" s="64"/>
       <c r="M53" s="4"/>
-      <c r="N53" s="87"/>
-      <c r="O53" s="88"/>
+      <c r="N53" s="70"/>
+      <c r="O53" s="71"/>
       <c r="P53" s="34"/>
       <c r="Q53" s="32"/>
-      <c r="R53" s="87"/>
-      <c r="S53" s="88"/>
+      <c r="R53" s="70"/>
+      <c r="S53" s="71"/>
       <c r="T53" s="34"/>
       <c r="U53" s="43"/>
-      <c r="V53" s="84"/>
-      <c r="W53" s="85"/>
-      <c r="X53" s="86"/>
+      <c r="V53" s="72"/>
+      <c r="W53" s="73"/>
+      <c r="X53" s="74"/>
       <c r="Y53" s="36"/>
-      <c r="Z53" s="84"/>
-      <c r="AA53" s="85"/>
-      <c r="AB53" s="86"/>
+      <c r="Z53" s="72"/>
+      <c r="AA53" s="73"/>
+      <c r="AB53" s="74"/>
       <c r="AC53" s="35"/>
-      <c r="AD53" s="84"/>
-      <c r="AE53" s="85"/>
-      <c r="AF53" s="86"/>
+      <c r="AD53" s="72"/>
+      <c r="AE53" s="73"/>
+      <c r="AF53" s="74"/>
       <c r="AG53" s="36"/>
-      <c r="AH53" s="84"/>
-      <c r="AI53" s="85"/>
-      <c r="AJ53" s="86"/>
+      <c r="AH53" s="72"/>
+      <c r="AI53" s="73"/>
+      <c r="AJ53" s="74"/>
       <c r="AK53" s="35"/>
-      <c r="AL53" s="84"/>
-      <c r="AM53" s="85"/>
-      <c r="AN53" s="86"/>
+      <c r="AL53" s="72"/>
+      <c r="AM53" s="73"/>
+      <c r="AN53" s="74"/>
       <c r="AR53" s="13"/>
     </row>
-    <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="81"/>
-      <c r="C54" s="82"/>
-      <c r="D54" s="83"/>
+    <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B54" s="77"/>
+      <c r="C54" s="78"/>
+      <c r="D54" s="79"/>
       <c r="E54" s="43"/>
-      <c r="F54" s="81"/>
-      <c r="G54" s="82"/>
-      <c r="H54" s="83"/>
+      <c r="F54" s="77"/>
+      <c r="G54" s="78"/>
+      <c r="H54" s="79"/>
       <c r="I54" s="35"/>
-      <c r="J54" s="81"/>
-      <c r="K54" s="82"/>
-      <c r="L54" s="83"/>
+      <c r="J54" s="77"/>
+      <c r="K54" s="78"/>
+      <c r="L54" s="79"/>
       <c r="M54" s="4"/>
-      <c r="N54" s="84"/>
-      <c r="O54" s="85"/>
-      <c r="P54" s="86"/>
+      <c r="N54" s="72"/>
+      <c r="O54" s="73"/>
+      <c r="P54" s="74"/>
       <c r="Q54" s="43"/>
-      <c r="R54" s="84"/>
-      <c r="S54" s="85"/>
-      <c r="T54" s="86"/>
+      <c r="R54" s="72"/>
+      <c r="S54" s="73"/>
+      <c r="T54" s="74"/>
       <c r="U54" s="37"/>
-      <c r="V54" s="71"/>
-      <c r="W54" s="72"/>
-      <c r="X54" s="73"/>
+      <c r="V54" s="83"/>
+      <c r="W54" s="84"/>
+      <c r="X54" s="85"/>
       <c r="Y54" s="43"/>
-      <c r="Z54" s="71"/>
-      <c r="AA54" s="72"/>
-      <c r="AB54" s="73"/>
+      <c r="Z54" s="83"/>
+      <c r="AA54" s="84"/>
+      <c r="AB54" s="85"/>
       <c r="AC54" s="31"/>
-      <c r="AD54" s="71"/>
-      <c r="AE54" s="72"/>
-      <c r="AF54" s="73"/>
+      <c r="AD54" s="83"/>
+      <c r="AE54" s="84"/>
+      <c r="AF54" s="85"/>
       <c r="AG54" s="43"/>
-      <c r="AH54" s="71"/>
-      <c r="AI54" s="72"/>
-      <c r="AJ54" s="73"/>
+      <c r="AH54" s="83"/>
+      <c r="AI54" s="84"/>
+      <c r="AJ54" s="85"/>
       <c r="AK54" s="35"/>
-      <c r="AL54" s="71"/>
-      <c r="AM54" s="72"/>
-      <c r="AN54" s="73"/>
+      <c r="AL54" s="83"/>
+      <c r="AM54" s="84"/>
+      <c r="AN54" s="85"/>
       <c r="AR54" s="13"/>
     </row>
-    <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="68" t="s">
+    <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="C55" s="69"/>
-      <c r="D55" s="70"/>
+      <c r="C55" s="68"/>
+      <c r="D55" s="69"/>
       <c r="E55" s="37"/>
-      <c r="F55" s="68" t="s">
+      <c r="F55" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="G55" s="69"/>
-      <c r="H55" s="70"/>
+      <c r="G55" s="68"/>
+      <c r="H55" s="69"/>
       <c r="I55" s="40"/>
-      <c r="J55" s="68" t="s">
+      <c r="J55" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="K55" s="69"/>
-      <c r="L55" s="70"/>
+      <c r="K55" s="68"/>
+      <c r="L55" s="69"/>
       <c r="M55" s="5"/>
-      <c r="N55" s="71"/>
-      <c r="O55" s="72"/>
-      <c r="P55" s="73"/>
+      <c r="N55" s="83"/>
+      <c r="O55" s="84"/>
+      <c r="P55" s="85"/>
       <c r="Q55" s="43"/>
-      <c r="R55" s="71"/>
-      <c r="S55" s="72"/>
-      <c r="T55" s="73"/>
+      <c r="R55" s="83"/>
+      <c r="S55" s="84"/>
+      <c r="T55" s="85"/>
       <c r="U55" s="44"/>
-      <c r="V55" s="68"/>
-      <c r="W55" s="69"/>
-      <c r="X55" s="70"/>
+      <c r="V55" s="67"/>
+      <c r="W55" s="68"/>
+      <c r="X55" s="69"/>
       <c r="Y55" s="37"/>
-      <c r="Z55" s="68"/>
-      <c r="AA55" s="69"/>
-      <c r="AB55" s="70"/>
+      <c r="Z55" s="67"/>
+      <c r="AA55" s="68"/>
+      <c r="AB55" s="69"/>
       <c r="AC55" s="35"/>
-      <c r="AD55" s="68"/>
-      <c r="AE55" s="69"/>
-      <c r="AF55" s="70"/>
+      <c r="AD55" s="67"/>
+      <c r="AE55" s="68"/>
+      <c r="AF55" s="69"/>
       <c r="AG55" s="37"/>
-      <c r="AH55" s="68"/>
-      <c r="AI55" s="69"/>
-      <c r="AJ55" s="70"/>
+      <c r="AH55" s="67"/>
+      <c r="AI55" s="68"/>
+      <c r="AJ55" s="69"/>
       <c r="AK55" s="40"/>
-      <c r="AL55" s="68"/>
-      <c r="AM55" s="69"/>
-      <c r="AN55" s="70"/>
+      <c r="AL55" s="67"/>
+      <c r="AM55" s="68"/>
+      <c r="AN55" s="69"/>
       <c r="AR55" s="13"/>
     </row>
-    <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="68" t="s">
+    <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B56" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="C56" s="69"/>
-      <c r="D56" s="70"/>
+      <c r="C56" s="68"/>
+      <c r="D56" s="69"/>
       <c r="E56" s="44"/>
-      <c r="F56" s="68" t="s">
+      <c r="F56" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="G56" s="69"/>
-      <c r="H56" s="70"/>
+      <c r="G56" s="68"/>
+      <c r="H56" s="69"/>
       <c r="I56" s="44"/>
-      <c r="J56" s="68" t="s">
+      <c r="J56" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="K56" s="69"/>
-      <c r="L56" s="70"/>
+      <c r="K56" s="68"/>
+      <c r="L56" s="69"/>
       <c r="M56" s="5"/>
-      <c r="N56" s="68"/>
-      <c r="O56" s="69"/>
-      <c r="P56" s="70"/>
+      <c r="N56" s="67"/>
+      <c r="O56" s="68"/>
+      <c r="P56" s="69"/>
       <c r="Q56" s="43"/>
-      <c r="R56" s="68"/>
-      <c r="S56" s="69"/>
-      <c r="T56" s="70"/>
+      <c r="R56" s="67"/>
+      <c r="S56" s="68"/>
+      <c r="T56" s="69"/>
       <c r="U56" s="44"/>
-      <c r="V56" s="68"/>
-      <c r="W56" s="69"/>
-      <c r="X56" s="70"/>
+      <c r="V56" s="67"/>
+      <c r="W56" s="68"/>
+      <c r="X56" s="69"/>
       <c r="Y56" s="44"/>
-      <c r="Z56" s="68"/>
-      <c r="AA56" s="69"/>
-      <c r="AB56" s="70"/>
+      <c r="Z56" s="67"/>
+      <c r="AA56" s="68"/>
+      <c r="AB56" s="69"/>
       <c r="AC56" s="43"/>
-      <c r="AD56" s="68"/>
-      <c r="AE56" s="69"/>
-      <c r="AF56" s="70"/>
+      <c r="AD56" s="67"/>
+      <c r="AE56" s="68"/>
+      <c r="AF56" s="69"/>
       <c r="AG56" s="44"/>
-      <c r="AH56" s="68"/>
-      <c r="AI56" s="69"/>
-      <c r="AJ56" s="70"/>
+      <c r="AH56" s="67"/>
+      <c r="AI56" s="68"/>
+      <c r="AJ56" s="69"/>
       <c r="AK56" s="44"/>
-      <c r="AL56" s="68"/>
-      <c r="AM56" s="69"/>
-      <c r="AN56" s="70"/>
+      <c r="AL56" s="67"/>
+      <c r="AM56" s="68"/>
+      <c r="AN56" s="69"/>
       <c r="AR56" s="13"/>
     </row>
-    <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="62"/>
-      <c r="C57" s="63"/>
-      <c r="D57" s="64"/>
+    <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="80"/>
+      <c r="C57" s="81"/>
+      <c r="D57" s="82"/>
       <c r="E57" s="35"/>
-      <c r="F57" s="62"/>
-      <c r="G57" s="63"/>
-      <c r="H57" s="64"/>
+      <c r="F57" s="80"/>
+      <c r="G57" s="81"/>
+      <c r="H57" s="82"/>
       <c r="I57" s="50"/>
-      <c r="J57" s="62"/>
-      <c r="K57" s="63"/>
-      <c r="L57" s="64"/>
+      <c r="J57" s="80"/>
+      <c r="K57" s="81"/>
+      <c r="L57" s="82"/>
       <c r="M57" s="5"/>
-      <c r="N57" s="62"/>
-      <c r="O57" s="63"/>
-      <c r="P57" s="64"/>
+      <c r="N57" s="80"/>
+      <c r="O57" s="81"/>
+      <c r="P57" s="82"/>
       <c r="Q57" s="31"/>
-      <c r="R57" s="62"/>
-      <c r="S57" s="63"/>
-      <c r="T57" s="64"/>
+      <c r="R57" s="80"/>
+      <c r="S57" s="81"/>
+      <c r="T57" s="82"/>
       <c r="U57" s="50"/>
-      <c r="V57" s="62"/>
-      <c r="W57" s="63"/>
-      <c r="X57" s="64"/>
+      <c r="V57" s="80"/>
+      <c r="W57" s="81"/>
+      <c r="X57" s="82"/>
       <c r="Y57" s="35"/>
-      <c r="Z57" s="62"/>
-      <c r="AA57" s="63"/>
-      <c r="AB57" s="64"/>
+      <c r="Z57" s="80"/>
+      <c r="AA57" s="81"/>
+      <c r="AB57" s="82"/>
       <c r="AC57" s="31"/>
-      <c r="AD57" s="62"/>
-      <c r="AE57" s="63"/>
-      <c r="AF57" s="64"/>
+      <c r="AD57" s="80"/>
+      <c r="AE57" s="81"/>
+      <c r="AF57" s="82"/>
       <c r="AG57" s="35"/>
-      <c r="AH57" s="62"/>
-      <c r="AI57" s="63"/>
-      <c r="AJ57" s="64"/>
+      <c r="AH57" s="80"/>
+      <c r="AI57" s="81"/>
+      <c r="AJ57" s="82"/>
       <c r="AK57" s="50"/>
-      <c r="AL57" s="62"/>
-      <c r="AM57" s="63"/>
-      <c r="AN57" s="64"/>
+      <c r="AL57" s="80"/>
+      <c r="AM57" s="81"/>
+      <c r="AN57" s="82"/>
       <c r="AR57" s="13"/>
     </row>
-    <row r="58" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B58" s="35"/>
       <c r="C58" s="35"/>
       <c r="D58" s="35"/>
@@ -5530,269 +5530,269 @@
       <c r="AN58" s="35"/>
       <c r="AR58" s="13"/>
     </row>
-    <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="74" t="s">
+    <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B59" s="65" t="s">
         <v>101</v>
       </c>
-      <c r="C59" s="75"/>
+      <c r="C59" s="66"/>
       <c r="D59" s="57" t="s">
         <v>102</v>
       </c>
       <c r="E59" s="50"/>
-      <c r="F59" s="79"/>
-      <c r="G59" s="80"/>
+      <c r="F59" s="75"/>
+      <c r="G59" s="76"/>
       <c r="H59" s="55"/>
       <c r="I59" s="32"/>
-      <c r="J59" s="79"/>
-      <c r="K59" s="80"/>
+      <c r="J59" s="75"/>
+      <c r="K59" s="76"/>
       <c r="L59" s="55"/>
       <c r="M59" s="6"/>
-      <c r="N59" s="87"/>
-      <c r="O59" s="88"/>
+      <c r="N59" s="70"/>
+      <c r="O59" s="71"/>
       <c r="P59" s="34"/>
       <c r="Q59" s="36"/>
-      <c r="R59" s="87"/>
-      <c r="S59" s="88"/>
+      <c r="R59" s="70"/>
+      <c r="S59" s="71"/>
       <c r="T59" s="34"/>
       <c r="U59" s="50"/>
-      <c r="V59" s="87"/>
-      <c r="W59" s="88"/>
+      <c r="V59" s="70"/>
+      <c r="W59" s="71"/>
       <c r="X59" s="34"/>
       <c r="Y59" s="32"/>
-      <c r="Z59" s="87"/>
-      <c r="AA59" s="88"/>
+      <c r="Z59" s="70"/>
+      <c r="AA59" s="71"/>
       <c r="AB59" s="34"/>
       <c r="AC59" s="32"/>
-      <c r="AD59" s="87"/>
-      <c r="AE59" s="88"/>
+      <c r="AD59" s="70"/>
+      <c r="AE59" s="71"/>
       <c r="AF59" s="34"/>
       <c r="AG59" s="50"/>
-      <c r="AH59" s="87"/>
-      <c r="AI59" s="88"/>
+      <c r="AH59" s="70"/>
+      <c r="AI59" s="71"/>
       <c r="AJ59" s="34"/>
       <c r="AK59" s="32"/>
-      <c r="AL59" s="87"/>
-      <c r="AM59" s="88"/>
+      <c r="AL59" s="70"/>
+      <c r="AM59" s="71"/>
       <c r="AN59" s="34"/>
       <c r="AR59" s="13"/>
     </row>
-    <row r="60" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="76" t="s">
+    <row r="60" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B60" s="62" t="s">
         <v>105</v>
       </c>
-      <c r="C60" s="77"/>
-      <c r="D60" s="78"/>
+      <c r="C60" s="63"/>
+      <c r="D60" s="64"/>
       <c r="E60" s="32"/>
-      <c r="F60" s="76"/>
-      <c r="G60" s="77"/>
-      <c r="H60" s="78"/>
+      <c r="F60" s="62"/>
+      <c r="G60" s="63"/>
+      <c r="H60" s="64"/>
       <c r="I60" s="32"/>
-      <c r="J60" s="76"/>
-      <c r="K60" s="77"/>
-      <c r="L60" s="78"/>
+      <c r="J60" s="62"/>
+      <c r="K60" s="63"/>
+      <c r="L60" s="64"/>
       <c r="M60" s="4"/>
-      <c r="N60" s="84"/>
-      <c r="O60" s="85"/>
-      <c r="P60" s="86"/>
+      <c r="N60" s="72"/>
+      <c r="O60" s="73"/>
+      <c r="P60" s="74"/>
       <c r="Q60" s="43"/>
-      <c r="R60" s="84"/>
-      <c r="S60" s="85"/>
-      <c r="T60" s="86"/>
+      <c r="R60" s="72"/>
+      <c r="S60" s="73"/>
+      <c r="T60" s="74"/>
       <c r="U60" s="32"/>
-      <c r="V60" s="84"/>
-      <c r="W60" s="85"/>
-      <c r="X60" s="86"/>
+      <c r="V60" s="72"/>
+      <c r="W60" s="73"/>
+      <c r="X60" s="74"/>
       <c r="Y60" s="32"/>
-      <c r="Z60" s="84"/>
-      <c r="AA60" s="85"/>
-      <c r="AB60" s="86"/>
+      <c r="Z60" s="72"/>
+      <c r="AA60" s="73"/>
+      <c r="AB60" s="74"/>
       <c r="AC60" s="54"/>
-      <c r="AD60" s="84"/>
-      <c r="AE60" s="85"/>
-      <c r="AF60" s="86"/>
+      <c r="AD60" s="72"/>
+      <c r="AE60" s="73"/>
+      <c r="AF60" s="74"/>
       <c r="AG60" s="32"/>
-      <c r="AH60" s="84"/>
-      <c r="AI60" s="85"/>
-      <c r="AJ60" s="86"/>
+      <c r="AH60" s="72"/>
+      <c r="AI60" s="73"/>
+      <c r="AJ60" s="74"/>
       <c r="AK60" s="32"/>
-      <c r="AL60" s="84"/>
-      <c r="AM60" s="85"/>
-      <c r="AN60" s="86"/>
+      <c r="AL60" s="72"/>
+      <c r="AM60" s="73"/>
+      <c r="AN60" s="74"/>
       <c r="AR60" s="13"/>
     </row>
-    <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="81"/>
-      <c r="C61" s="82"/>
-      <c r="D61" s="83"/>
+    <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B61" s="77"/>
+      <c r="C61" s="78"/>
+      <c r="D61" s="79"/>
       <c r="E61" s="32"/>
-      <c r="F61" s="81"/>
-      <c r="G61" s="82"/>
-      <c r="H61" s="83"/>
+      <c r="F61" s="77"/>
+      <c r="G61" s="78"/>
+      <c r="H61" s="79"/>
       <c r="I61" s="32"/>
-      <c r="J61" s="81"/>
-      <c r="K61" s="82"/>
-      <c r="L61" s="83"/>
+      <c r="J61" s="77"/>
+      <c r="K61" s="78"/>
+      <c r="L61" s="79"/>
       <c r="M61" s="4"/>
-      <c r="N61" s="71"/>
-      <c r="O61" s="72"/>
-      <c r="P61" s="73"/>
+      <c r="N61" s="83"/>
+      <c r="O61" s="84"/>
+      <c r="P61" s="85"/>
       <c r="Q61" s="37"/>
-      <c r="R61" s="71"/>
-      <c r="S61" s="72"/>
-      <c r="T61" s="73"/>
+      <c r="R61" s="83"/>
+      <c r="S61" s="84"/>
+      <c r="T61" s="85"/>
       <c r="U61" s="32"/>
-      <c r="V61" s="71"/>
-      <c r="W61" s="72"/>
-      <c r="X61" s="73"/>
+      <c r="V61" s="83"/>
+      <c r="W61" s="84"/>
+      <c r="X61" s="85"/>
       <c r="Y61" s="32"/>
-      <c r="Z61" s="71"/>
-      <c r="AA61" s="72"/>
-      <c r="AB61" s="73"/>
+      <c r="Z61" s="83"/>
+      <c r="AA61" s="84"/>
+      <c r="AB61" s="85"/>
       <c r="AC61" s="35"/>
-      <c r="AD61" s="71"/>
-      <c r="AE61" s="72"/>
-      <c r="AF61" s="73"/>
+      <c r="AD61" s="83"/>
+      <c r="AE61" s="84"/>
+      <c r="AF61" s="85"/>
       <c r="AG61" s="32"/>
-      <c r="AH61" s="71"/>
-      <c r="AI61" s="72"/>
-      <c r="AJ61" s="73"/>
+      <c r="AH61" s="83"/>
+      <c r="AI61" s="84"/>
+      <c r="AJ61" s="85"/>
       <c r="AK61" s="32"/>
-      <c r="AL61" s="71"/>
-      <c r="AM61" s="72"/>
-      <c r="AN61" s="73"/>
+      <c r="AL61" s="83"/>
+      <c r="AM61" s="84"/>
+      <c r="AN61" s="85"/>
       <c r="AR61" s="13"/>
     </row>
-    <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="65" t="s">
+    <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="C62" s="66"/>
-      <c r="D62" s="67"/>
+      <c r="C62" s="90"/>
+      <c r="D62" s="91"/>
       <c r="E62" s="37"/>
-      <c r="F62" s="68"/>
-      <c r="G62" s="69"/>
-      <c r="H62" s="70"/>
+      <c r="F62" s="67"/>
+      <c r="G62" s="68"/>
+      <c r="H62" s="69"/>
       <c r="I62" s="35"/>
-      <c r="J62" s="65"/>
-      <c r="K62" s="66"/>
-      <c r="L62" s="67"/>
+      <c r="J62" s="89"/>
+      <c r="K62" s="90"/>
+      <c r="L62" s="91"/>
       <c r="M62" s="4"/>
-      <c r="N62" s="68"/>
-      <c r="O62" s="69"/>
-      <c r="P62" s="70"/>
+      <c r="N62" s="67"/>
+      <c r="O62" s="68"/>
+      <c r="P62" s="69"/>
       <c r="Q62" s="44"/>
-      <c r="R62" s="65"/>
-      <c r="S62" s="66"/>
-      <c r="T62" s="67"/>
+      <c r="R62" s="89"/>
+      <c r="S62" s="90"/>
+      <c r="T62" s="91"/>
       <c r="U62" s="37"/>
-      <c r="V62" s="65"/>
-      <c r="W62" s="66"/>
-      <c r="X62" s="67"/>
+      <c r="V62" s="89"/>
+      <c r="W62" s="90"/>
+      <c r="X62" s="91"/>
       <c r="Y62" s="35"/>
-      <c r="Z62" s="68"/>
-      <c r="AA62" s="69"/>
-      <c r="AB62" s="70"/>
+      <c r="Z62" s="67"/>
+      <c r="AA62" s="68"/>
+      <c r="AB62" s="69"/>
       <c r="AC62" s="35"/>
-      <c r="AD62" s="65"/>
-      <c r="AE62" s="66"/>
-      <c r="AF62" s="67"/>
+      <c r="AD62" s="89"/>
+      <c r="AE62" s="90"/>
+      <c r="AF62" s="91"/>
       <c r="AG62" s="37"/>
-      <c r="AH62" s="68"/>
-      <c r="AI62" s="69"/>
-      <c r="AJ62" s="70"/>
+      <c r="AH62" s="67"/>
+      <c r="AI62" s="68"/>
+      <c r="AJ62" s="69"/>
       <c r="AK62" s="35"/>
-      <c r="AL62" s="65"/>
-      <c r="AM62" s="66"/>
-      <c r="AN62" s="67"/>
+      <c r="AL62" s="89"/>
+      <c r="AM62" s="90"/>
+      <c r="AN62" s="91"/>
       <c r="AR62" s="13"/>
     </row>
-    <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="68" t="s">
+    <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B63" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="C63" s="69"/>
-      <c r="D63" s="70"/>
+      <c r="C63" s="68"/>
+      <c r="D63" s="69"/>
       <c r="E63" s="44"/>
-      <c r="F63" s="68"/>
-      <c r="G63" s="69"/>
-      <c r="H63" s="70"/>
+      <c r="F63" s="67"/>
+      <c r="G63" s="68"/>
+      <c r="H63" s="69"/>
       <c r="I63" s="40"/>
-      <c r="J63" s="68"/>
-      <c r="K63" s="69"/>
-      <c r="L63" s="70"/>
+      <c r="J63" s="67"/>
+      <c r="K63" s="68"/>
+      <c r="L63" s="69"/>
       <c r="M63" s="5"/>
-      <c r="N63" s="68"/>
-      <c r="O63" s="69"/>
-      <c r="P63" s="70"/>
+      <c r="N63" s="67"/>
+      <c r="O63" s="68"/>
+      <c r="P63" s="69"/>
       <c r="Q63" s="44"/>
-      <c r="R63" s="68"/>
-      <c r="S63" s="69"/>
-      <c r="T63" s="70"/>
+      <c r="R63" s="67"/>
+      <c r="S63" s="68"/>
+      <c r="T63" s="69"/>
       <c r="U63" s="44"/>
-      <c r="V63" s="68"/>
-      <c r="W63" s="69"/>
-      <c r="X63" s="70"/>
+      <c r="V63" s="67"/>
+      <c r="W63" s="68"/>
+      <c r="X63" s="69"/>
       <c r="Y63" s="40"/>
-      <c r="Z63" s="68"/>
-      <c r="AA63" s="69"/>
-      <c r="AB63" s="70"/>
+      <c r="Z63" s="67"/>
+      <c r="AA63" s="68"/>
+      <c r="AB63" s="69"/>
       <c r="AC63" s="40"/>
-      <c r="AD63" s="68"/>
-      <c r="AE63" s="69"/>
-      <c r="AF63" s="70"/>
+      <c r="AD63" s="67"/>
+      <c r="AE63" s="68"/>
+      <c r="AF63" s="69"/>
       <c r="AG63" s="44"/>
-      <c r="AH63" s="68"/>
-      <c r="AI63" s="69"/>
-      <c r="AJ63" s="70"/>
+      <c r="AH63" s="67"/>
+      <c r="AI63" s="68"/>
+      <c r="AJ63" s="69"/>
       <c r="AK63" s="40"/>
-      <c r="AL63" s="68"/>
-      <c r="AM63" s="69"/>
-      <c r="AN63" s="70"/>
+      <c r="AL63" s="67"/>
+      <c r="AM63" s="68"/>
+      <c r="AN63" s="69"/>
       <c r="AR63" s="13"/>
     </row>
-    <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="62"/>
-      <c r="C64" s="63"/>
-      <c r="D64" s="64"/>
+    <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="80"/>
+      <c r="C64" s="81"/>
+      <c r="D64" s="82"/>
       <c r="E64" s="35"/>
-      <c r="F64" s="62"/>
-      <c r="G64" s="63"/>
-      <c r="H64" s="64"/>
+      <c r="F64" s="80"/>
+      <c r="G64" s="81"/>
+      <c r="H64" s="82"/>
       <c r="I64" s="50"/>
-      <c r="J64" s="62"/>
-      <c r="K64" s="63"/>
-      <c r="L64" s="64"/>
+      <c r="J64" s="80"/>
+      <c r="K64" s="81"/>
+      <c r="L64" s="82"/>
       <c r="M64" s="5"/>
-      <c r="N64" s="62"/>
-      <c r="O64" s="63"/>
-      <c r="P64" s="64"/>
+      <c r="N64" s="80"/>
+      <c r="O64" s="81"/>
+      <c r="P64" s="82"/>
       <c r="Q64" s="50"/>
-      <c r="R64" s="62"/>
-      <c r="S64" s="63"/>
-      <c r="T64" s="64"/>
+      <c r="R64" s="80"/>
+      <c r="S64" s="81"/>
+      <c r="T64" s="82"/>
       <c r="U64" s="35"/>
-      <c r="V64" s="62"/>
-      <c r="W64" s="63"/>
-      <c r="X64" s="64"/>
+      <c r="V64" s="80"/>
+      <c r="W64" s="81"/>
+      <c r="X64" s="82"/>
       <c r="Y64" s="50"/>
-      <c r="Z64" s="62"/>
-      <c r="AA64" s="63"/>
-      <c r="AB64" s="64"/>
+      <c r="Z64" s="80"/>
+      <c r="AA64" s="81"/>
+      <c r="AB64" s="82"/>
       <c r="AC64" s="50"/>
-      <c r="AD64" s="62"/>
-      <c r="AE64" s="63"/>
-      <c r="AF64" s="64"/>
+      <c r="AD64" s="80"/>
+      <c r="AE64" s="81"/>
+      <c r="AF64" s="82"/>
       <c r="AG64" s="35"/>
-      <c r="AH64" s="62"/>
-      <c r="AI64" s="63"/>
-      <c r="AJ64" s="64"/>
+      <c r="AH64" s="80"/>
+      <c r="AI64" s="81"/>
+      <c r="AJ64" s="82"/>
       <c r="AK64" s="50"/>
-      <c r="AL64" s="62"/>
-      <c r="AM64" s="63"/>
-      <c r="AN64" s="64"/>
+      <c r="AL64" s="80"/>
+      <c r="AM64" s="81"/>
+      <c r="AN64" s="82"/>
       <c r="AR64" s="13"/>
     </row>
-    <row r="65" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="12"/>
       <c r="B65" s="35"/>
       <c r="C65" s="35"/>
@@ -5838,48 +5838,48 @@
       <c r="AQ65" s="12"/>
       <c r="AR65" s="13"/>
     </row>
-    <row r="66" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="12"/>
-      <c r="B66" s="74" t="s">
+      <c r="B66" s="65" t="s">
         <v>101</v>
       </c>
-      <c r="C66" s="75"/>
+      <c r="C66" s="66"/>
       <c r="D66" s="57" t="s">
         <v>54</v>
       </c>
       <c r="E66" s="36"/>
-      <c r="F66" s="79"/>
-      <c r="G66" s="80"/>
+      <c r="F66" s="75"/>
+      <c r="G66" s="76"/>
       <c r="H66" s="55"/>
       <c r="I66" s="32"/>
-      <c r="J66" s="79"/>
-      <c r="K66" s="80"/>
+      <c r="J66" s="75"/>
+      <c r="K66" s="76"/>
       <c r="L66" s="55"/>
       <c r="M66" s="6"/>
-      <c r="N66" s="87" t="s">
+      <c r="N66" s="70" t="s">
         <v>107</v>
       </c>
-      <c r="O66" s="88"/>
+      <c r="O66" s="71"/>
       <c r="P66" s="34"/>
       <c r="Q66" s="36"/>
-      <c r="R66" s="87"/>
-      <c r="S66" s="88"/>
+      <c r="R66" s="70"/>
+      <c r="S66" s="71"/>
       <c r="T66" s="34"/>
       <c r="U66" s="36"/>
-      <c r="V66" s="87"/>
-      <c r="W66" s="88"/>
+      <c r="V66" s="70"/>
+      <c r="W66" s="71"/>
       <c r="X66" s="34"/>
       <c r="Y66" s="36"/>
-      <c r="Z66" s="87"/>
-      <c r="AA66" s="88"/>
+      <c r="Z66" s="70"/>
+      <c r="AA66" s="71"/>
       <c r="AB66" s="34"/>
       <c r="AC66" s="36"/>
-      <c r="AD66" s="87"/>
-      <c r="AE66" s="88"/>
+      <c r="AD66" s="70"/>
+      <c r="AE66" s="71"/>
       <c r="AF66" s="34"/>
       <c r="AG66" s="36"/>
-      <c r="AH66" s="87"/>
-      <c r="AI66" s="88"/>
+      <c r="AH66" s="70"/>
+      <c r="AI66" s="71"/>
       <c r="AJ66" s="34"/>
       <c r="AK66" s="32"/>
       <c r="AL66" s="119" t="s">
@@ -5892,47 +5892,47 @@
       <c r="AQ66" s="12"/>
       <c r="AR66" s="13"/>
     </row>
-    <row r="67" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="12"/>
-      <c r="B67" s="76" t="s">
+      <c r="B67" s="62" t="s">
         <v>106</v>
       </c>
-      <c r="C67" s="77"/>
-      <c r="D67" s="78"/>
+      <c r="C67" s="63"/>
+      <c r="D67" s="64"/>
       <c r="E67" s="36"/>
-      <c r="F67" s="76"/>
-      <c r="G67" s="77"/>
-      <c r="H67" s="78"/>
+      <c r="F67" s="62"/>
+      <c r="G67" s="63"/>
+      <c r="H67" s="64"/>
       <c r="I67" s="54"/>
-      <c r="J67" s="76"/>
-      <c r="K67" s="77"/>
-      <c r="L67" s="78"/>
+      <c r="J67" s="62"/>
+      <c r="K67" s="63"/>
+      <c r="L67" s="64"/>
       <c r="M67" s="4"/>
-      <c r="N67" s="84" t="s">
+      <c r="N67" s="72" t="s">
         <v>108</v>
       </c>
-      <c r="O67" s="85"/>
-      <c r="P67" s="86"/>
+      <c r="O67" s="73"/>
+      <c r="P67" s="74"/>
       <c r="Q67" s="37"/>
-      <c r="R67" s="84"/>
-      <c r="S67" s="85"/>
-      <c r="T67" s="86"/>
+      <c r="R67" s="72"/>
+      <c r="S67" s="73"/>
+      <c r="T67" s="74"/>
       <c r="U67" s="36"/>
-      <c r="V67" s="84"/>
-      <c r="W67" s="85"/>
-      <c r="X67" s="86"/>
+      <c r="V67" s="72"/>
+      <c r="W67" s="73"/>
+      <c r="X67" s="74"/>
       <c r="Y67" s="36"/>
-      <c r="Z67" s="84"/>
-      <c r="AA67" s="85"/>
-      <c r="AB67" s="86"/>
+      <c r="Z67" s="72"/>
+      <c r="AA67" s="73"/>
+      <c r="AB67" s="74"/>
       <c r="AC67" s="36"/>
-      <c r="AD67" s="84"/>
-      <c r="AE67" s="85"/>
-      <c r="AF67" s="86"/>
+      <c r="AD67" s="72"/>
+      <c r="AE67" s="73"/>
+      <c r="AF67" s="74"/>
       <c r="AG67" s="36"/>
-      <c r="AH67" s="84"/>
-      <c r="AI67" s="85"/>
-      <c r="AJ67" s="86"/>
+      <c r="AH67" s="72"/>
+      <c r="AI67" s="73"/>
+      <c r="AJ67" s="74"/>
       <c r="AK67" s="54"/>
       <c r="AL67" s="145" t="s">
         <v>51</v>
@@ -5944,43 +5944,43 @@
       <c r="AQ67" s="12"/>
       <c r="AR67" s="13"/>
     </row>
-    <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="12"/>
-      <c r="B68" s="81"/>
-      <c r="C68" s="82"/>
-      <c r="D68" s="83"/>
+      <c r="B68" s="77"/>
+      <c r="C68" s="78"/>
+      <c r="D68" s="79"/>
       <c r="E68" s="43"/>
-      <c r="F68" s="81"/>
-      <c r="G68" s="82"/>
-      <c r="H68" s="83"/>
+      <c r="F68" s="77"/>
+      <c r="G68" s="78"/>
+      <c r="H68" s="79"/>
       <c r="I68" s="35"/>
-      <c r="J68" s="81"/>
-      <c r="K68" s="82"/>
-      <c r="L68" s="83"/>
+      <c r="J68" s="77"/>
+      <c r="K68" s="78"/>
+      <c r="L68" s="79"/>
       <c r="M68" s="4"/>
-      <c r="N68" s="71"/>
-      <c r="O68" s="72"/>
-      <c r="P68" s="73"/>
+      <c r="N68" s="83"/>
+      <c r="O68" s="84"/>
+      <c r="P68" s="85"/>
       <c r="Q68" s="36"/>
-      <c r="R68" s="71"/>
-      <c r="S68" s="72"/>
-      <c r="T68" s="73"/>
+      <c r="R68" s="83"/>
+      <c r="S68" s="84"/>
+      <c r="T68" s="85"/>
       <c r="U68" s="43"/>
-      <c r="V68" s="71"/>
-      <c r="W68" s="72"/>
-      <c r="X68" s="73"/>
+      <c r="V68" s="83"/>
+      <c r="W68" s="84"/>
+      <c r="X68" s="85"/>
       <c r="Y68" s="43"/>
-      <c r="Z68" s="71"/>
-      <c r="AA68" s="72"/>
-      <c r="AB68" s="73"/>
+      <c r="Z68" s="83"/>
+      <c r="AA68" s="84"/>
+      <c r="AB68" s="85"/>
       <c r="AC68" s="35"/>
-      <c r="AD68" s="71"/>
-      <c r="AE68" s="72"/>
-      <c r="AF68" s="73"/>
+      <c r="AD68" s="83"/>
+      <c r="AE68" s="84"/>
+      <c r="AF68" s="85"/>
       <c r="AG68" s="43"/>
-      <c r="AH68" s="71"/>
-      <c r="AI68" s="72"/>
-      <c r="AJ68" s="73"/>
+      <c r="AH68" s="83"/>
+      <c r="AI68" s="84"/>
+      <c r="AJ68" s="85"/>
       <c r="AK68" s="35"/>
       <c r="AL68" s="113" t="s">
         <v>78</v>
@@ -5994,53 +5994,53 @@
       <c r="AQ68" s="12"/>
       <c r="AR68" s="13"/>
     </row>
-    <row r="69" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="12"/>
-      <c r="B69" s="68" t="s">
+      <c r="B69" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="C69" s="69"/>
-      <c r="D69" s="70"/>
+      <c r="C69" s="68"/>
+      <c r="D69" s="69"/>
       <c r="E69" s="37"/>
-      <c r="F69" s="65"/>
-      <c r="G69" s="66"/>
-      <c r="H69" s="67"/>
+      <c r="F69" s="89"/>
+      <c r="G69" s="90"/>
+      <c r="H69" s="91"/>
       <c r="I69" s="37"/>
-      <c r="J69" s="68"/>
-      <c r="K69" s="69"/>
-      <c r="L69" s="70"/>
+      <c r="J69" s="67"/>
+      <c r="K69" s="68"/>
+      <c r="L69" s="69"/>
       <c r="M69" s="4"/>
-      <c r="N69" s="68" t="s">
+      <c r="N69" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="O69" s="69"/>
-      <c r="P69" s="70"/>
+      <c r="O69" s="68"/>
+      <c r="P69" s="69"/>
       <c r="Q69" s="43"/>
-      <c r="R69" s="68"/>
-      <c r="S69" s="69"/>
-      <c r="T69" s="70"/>
+      <c r="R69" s="67"/>
+      <c r="S69" s="68"/>
+      <c r="T69" s="69"/>
       <c r="U69" s="37"/>
-      <c r="V69" s="65"/>
-      <c r="W69" s="66"/>
-      <c r="X69" s="67"/>
+      <c r="V69" s="89"/>
+      <c r="W69" s="90"/>
+      <c r="X69" s="91"/>
       <c r="Y69" s="35"/>
-      <c r="Z69" s="65"/>
-      <c r="AA69" s="66"/>
-      <c r="AB69" s="67"/>
+      <c r="Z69" s="89"/>
+      <c r="AA69" s="90"/>
+      <c r="AB69" s="91"/>
       <c r="AC69" s="43"/>
-      <c r="AD69" s="68"/>
-      <c r="AE69" s="69"/>
-      <c r="AF69" s="70"/>
+      <c r="AD69" s="67"/>
+      <c r="AE69" s="68"/>
+      <c r="AF69" s="69"/>
       <c r="AG69" s="37"/>
-      <c r="AH69" s="65"/>
-      <c r="AI69" s="66"/>
-      <c r="AJ69" s="67"/>
+      <c r="AH69" s="89"/>
+      <c r="AI69" s="90"/>
+      <c r="AJ69" s="91"/>
       <c r="AK69" s="37"/>
-      <c r="AL69" s="68" t="s">
+      <c r="AL69" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="AM69" s="69"/>
-      <c r="AN69" s="70"/>
+      <c r="AM69" s="68"/>
+      <c r="AN69" s="69"/>
       <c r="AO69" s="12"/>
       <c r="AP69" s="27" t="s">
         <v>33</v>
@@ -6048,51 +6048,51 @@
       <c r="AQ69" s="12"/>
       <c r="AR69" s="13"/>
     </row>
-    <row r="70" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="12"/>
-      <c r="B70" s="68" t="s">
+      <c r="B70" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="C70" s="69"/>
-      <c r="D70" s="70"/>
+      <c r="C70" s="68"/>
+      <c r="D70" s="69"/>
       <c r="E70" s="44"/>
-      <c r="F70" s="68"/>
-      <c r="G70" s="69"/>
-      <c r="H70" s="70"/>
+      <c r="F70" s="67"/>
+      <c r="G70" s="68"/>
+      <c r="H70" s="69"/>
       <c r="I70" s="44"/>
-      <c r="J70" s="68"/>
-      <c r="K70" s="69"/>
-      <c r="L70" s="70"/>
+      <c r="J70" s="67"/>
+      <c r="K70" s="68"/>
+      <c r="L70" s="69"/>
       <c r="M70" s="9"/>
-      <c r="N70" s="68"/>
-      <c r="O70" s="69"/>
-      <c r="P70" s="70"/>
+      <c r="N70" s="67"/>
+      <c r="O70" s="68"/>
+      <c r="P70" s="69"/>
       <c r="Q70" s="50"/>
-      <c r="R70" s="68"/>
-      <c r="S70" s="69"/>
-      <c r="T70" s="70"/>
+      <c r="R70" s="67"/>
+      <c r="S70" s="68"/>
+      <c r="T70" s="69"/>
       <c r="U70" s="44"/>
-      <c r="V70" s="68"/>
-      <c r="W70" s="69"/>
-      <c r="X70" s="70"/>
+      <c r="V70" s="67"/>
+      <c r="W70" s="68"/>
+      <c r="X70" s="69"/>
       <c r="Y70" s="40"/>
-      <c r="Z70" s="68"/>
-      <c r="AA70" s="69"/>
-      <c r="AB70" s="70"/>
+      <c r="Z70" s="67"/>
+      <c r="AA70" s="68"/>
+      <c r="AB70" s="69"/>
       <c r="AC70" s="44"/>
-      <c r="AD70" s="68"/>
-      <c r="AE70" s="69"/>
-      <c r="AF70" s="70"/>
+      <c r="AD70" s="67"/>
+      <c r="AE70" s="68"/>
+      <c r="AF70" s="69"/>
       <c r="AG70" s="44"/>
-      <c r="AH70" s="68"/>
-      <c r="AI70" s="69"/>
-      <c r="AJ70" s="70"/>
+      <c r="AH70" s="67"/>
+      <c r="AI70" s="68"/>
+      <c r="AJ70" s="69"/>
       <c r="AK70" s="44"/>
-      <c r="AL70" s="68" t="s">
+      <c r="AL70" s="67" t="s">
         <v>81</v>
       </c>
-      <c r="AM70" s="69"/>
-      <c r="AN70" s="70"/>
+      <c r="AM70" s="68"/>
+      <c r="AN70" s="69"/>
       <c r="AO70" s="12"/>
       <c r="AP70" s="27" t="s">
         <v>34</v>
@@ -6100,49 +6100,49 @@
       <c r="AQ70" s="12"/>
       <c r="AR70" s="13"/>
     </row>
-    <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A71" s="12"/>
-      <c r="B71" s="62"/>
-      <c r="C71" s="63"/>
-      <c r="D71" s="64"/>
+      <c r="B71" s="80"/>
+      <c r="C71" s="81"/>
+      <c r="D71" s="82"/>
       <c r="E71" s="44"/>
-      <c r="F71" s="62"/>
-      <c r="G71" s="63"/>
-      <c r="H71" s="64"/>
+      <c r="F71" s="80"/>
+      <c r="G71" s="81"/>
+      <c r="H71" s="82"/>
       <c r="I71" s="44"/>
-      <c r="J71" s="62"/>
-      <c r="K71" s="63"/>
-      <c r="L71" s="64"/>
+      <c r="J71" s="80"/>
+      <c r="K71" s="81"/>
+      <c r="L71" s="82"/>
       <c r="M71" s="9"/>
-      <c r="N71" s="62"/>
-      <c r="O71" s="63"/>
-      <c r="P71" s="64"/>
+      <c r="N71" s="80"/>
+      <c r="O71" s="81"/>
+      <c r="P71" s="82"/>
       <c r="Q71" s="50"/>
-      <c r="R71" s="62"/>
-      <c r="S71" s="63"/>
-      <c r="T71" s="64"/>
+      <c r="R71" s="80"/>
+      <c r="S71" s="81"/>
+      <c r="T71" s="82"/>
       <c r="U71" s="44"/>
-      <c r="V71" s="62"/>
-      <c r="W71" s="63"/>
-      <c r="X71" s="64"/>
+      <c r="V71" s="80"/>
+      <c r="W71" s="81"/>
+      <c r="X71" s="82"/>
       <c r="Y71" s="44"/>
-      <c r="Z71" s="62"/>
-      <c r="AA71" s="63"/>
-      <c r="AB71" s="64"/>
+      <c r="Z71" s="80"/>
+      <c r="AA71" s="81"/>
+      <c r="AB71" s="82"/>
       <c r="AC71" s="50"/>
-      <c r="AD71" s="62"/>
-      <c r="AE71" s="63"/>
-      <c r="AF71" s="64"/>
+      <c r="AD71" s="80"/>
+      <c r="AE71" s="81"/>
+      <c r="AF71" s="82"/>
       <c r="AG71" s="44"/>
-      <c r="AH71" s="62"/>
-      <c r="AI71" s="63"/>
-      <c r="AJ71" s="64"/>
+      <c r="AH71" s="80"/>
+      <c r="AI71" s="81"/>
+      <c r="AJ71" s="82"/>
       <c r="AK71" s="44"/>
-      <c r="AL71" s="62" t="s">
+      <c r="AL71" s="80" t="s">
         <v>82</v>
       </c>
-      <c r="AM71" s="63"/>
-      <c r="AN71" s="64"/>
+      <c r="AM71" s="81"/>
+      <c r="AN71" s="82"/>
       <c r="AO71" s="12"/>
       <c r="AP71" s="27" t="s">
         <v>35</v>
@@ -6150,7 +6150,7 @@
       <c r="AQ71" s="12"/>
       <c r="AR71" s="13"/>
     </row>
-    <row r="72" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="12"/>
       <c r="B72" s="33"/>
       <c r="C72" s="33"/>
@@ -6196,7 +6196,7 @@
       <c r="AQ72" s="12"/>
       <c r="AR72" s="13"/>
     </row>
-    <row r="73" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="12"/>
       <c r="B73" s="40"/>
       <c r="C73" s="33"/>
@@ -6243,7 +6243,7 @@
       <c r="AQ73" s="12"/>
       <c r="AR73" s="13"/>
     </row>
-    <row r="74" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="12"/>
       <c r="B74" s="33"/>
       <c r="C74" s="33"/>
@@ -6289,301 +6289,301 @@
       <c r="AQ74" s="12"/>
       <c r="AR74" s="13"/>
     </row>
-    <row r="75" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="12"/>
-      <c r="B75" s="79" t="s">
+      <c r="B75" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="C75" s="80"/>
+      <c r="C75" s="76"/>
       <c r="D75" s="55" t="s">
         <v>52</v>
       </c>
       <c r="E75" s="32"/>
-      <c r="F75" s="79" t="s">
+      <c r="F75" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="G75" s="80"/>
+      <c r="G75" s="76"/>
       <c r="H75" s="55" t="s">
         <v>52</v>
       </c>
       <c r="I75" s="32"/>
-      <c r="J75" s="79"/>
-      <c r="K75" s="80"/>
+      <c r="J75" s="75"/>
+      <c r="K75" s="76"/>
       <c r="L75" s="55"/>
       <c r="M75" s="14"/>
-      <c r="N75" s="87" t="s">
+      <c r="N75" s="70" t="s">
         <v>58</v>
       </c>
-      <c r="O75" s="88"/>
+      <c r="O75" s="71"/>
       <c r="P75" s="34" t="s">
         <v>52</v>
       </c>
       <c r="Q75" s="44"/>
-      <c r="R75" s="87" t="s">
+      <c r="R75" s="70" t="s">
         <v>58</v>
       </c>
-      <c r="S75" s="88"/>
+      <c r="S75" s="71"/>
       <c r="T75" s="34" t="s">
         <v>52</v>
       </c>
       <c r="U75" s="36"/>
-      <c r="V75" s="87" t="s">
+      <c r="V75" s="70" t="s">
         <v>58</v>
       </c>
-      <c r="W75" s="88"/>
+      <c r="W75" s="71"/>
       <c r="X75" s="34" t="s">
         <v>52</v>
       </c>
       <c r="Y75" s="32"/>
-      <c r="Z75" s="87" t="s">
+      <c r="Z75" s="70" t="s">
         <v>58</v>
       </c>
-      <c r="AA75" s="88"/>
+      <c r="AA75" s="71"/>
       <c r="AB75" s="34" t="s">
         <v>52</v>
       </c>
       <c r="AC75" s="32"/>
-      <c r="AD75" s="87" t="s">
+      <c r="AD75" s="70" t="s">
         <v>58</v>
       </c>
-      <c r="AE75" s="88"/>
+      <c r="AE75" s="71"/>
       <c r="AF75" s="34" t="s">
         <v>52</v>
       </c>
       <c r="AG75" s="32"/>
-      <c r="AH75" s="87" t="s">
+      <c r="AH75" s="70" t="s">
         <v>58</v>
       </c>
-      <c r="AI75" s="88"/>
+      <c r="AI75" s="71"/>
       <c r="AJ75" s="34" t="s">
         <v>52</v>
       </c>
       <c r="AK75" s="32"/>
-      <c r="AL75" s="87"/>
-      <c r="AM75" s="88"/>
+      <c r="AL75" s="70"/>
+      <c r="AM75" s="71"/>
       <c r="AN75" s="34"/>
       <c r="AO75" s="16"/>
       <c r="AP75" s="29"/>
       <c r="AQ75" s="26"/>
       <c r="AR75" s="24"/>
     </row>
-    <row r="76" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="12"/>
-      <c r="B76" s="76" t="s">
+      <c r="B76" s="62" t="s">
         <v>59</v>
       </c>
-      <c r="C76" s="77"/>
-      <c r="D76" s="78"/>
+      <c r="C76" s="63"/>
+      <c r="D76" s="64"/>
       <c r="E76" s="32"/>
-      <c r="F76" s="76" t="s">
+      <c r="F76" s="62" t="s">
         <v>59</v>
       </c>
-      <c r="G76" s="77"/>
-      <c r="H76" s="78"/>
+      <c r="G76" s="63"/>
+      <c r="H76" s="64"/>
       <c r="I76" s="32"/>
-      <c r="J76" s="76"/>
-      <c r="K76" s="77"/>
-      <c r="L76" s="78"/>
+      <c r="J76" s="62"/>
+      <c r="K76" s="63"/>
+      <c r="L76" s="64"/>
       <c r="M76" s="4"/>
-      <c r="N76" s="84" t="s">
+      <c r="N76" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="O76" s="85"/>
-      <c r="P76" s="86"/>
+      <c r="O76" s="73"/>
+      <c r="P76" s="74"/>
       <c r="Q76" s="44"/>
-      <c r="R76" s="84" t="s">
+      <c r="R76" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="S76" s="85"/>
-      <c r="T76" s="86"/>
+      <c r="S76" s="73"/>
+      <c r="T76" s="74"/>
       <c r="U76" s="32"/>
-      <c r="V76" s="84" t="s">
+      <c r="V76" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="W76" s="85"/>
-      <c r="X76" s="86"/>
+      <c r="W76" s="73"/>
+      <c r="X76" s="74"/>
       <c r="Y76" s="32"/>
-      <c r="Z76" s="84" t="s">
+      <c r="Z76" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="AA76" s="85"/>
-      <c r="AB76" s="86"/>
+      <c r="AA76" s="73"/>
+      <c r="AB76" s="74"/>
       <c r="AC76" s="35"/>
-      <c r="AD76" s="84" t="s">
+      <c r="AD76" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="AE76" s="85"/>
-      <c r="AF76" s="86"/>
+      <c r="AE76" s="73"/>
+      <c r="AF76" s="74"/>
       <c r="AG76" s="32"/>
-      <c r="AH76" s="84" t="s">
+      <c r="AH76" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="AI76" s="85"/>
-      <c r="AJ76" s="86"/>
+      <c r="AI76" s="73"/>
+      <c r="AJ76" s="74"/>
       <c r="AK76" s="32"/>
-      <c r="AL76" s="84"/>
-      <c r="AM76" s="85"/>
-      <c r="AN76" s="86"/>
+      <c r="AL76" s="72"/>
+      <c r="AM76" s="73"/>
+      <c r="AN76" s="74"/>
       <c r="AO76" s="12"/>
       <c r="AP76" s="29"/>
       <c r="AQ76" s="26"/>
       <c r="AR76" s="24"/>
     </row>
-    <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="16"/>
-      <c r="B77" s="81"/>
-      <c r="C77" s="82"/>
-      <c r="D77" s="83"/>
+      <c r="B77" s="77"/>
+      <c r="C77" s="78"/>
+      <c r="D77" s="79"/>
       <c r="E77" s="32"/>
-      <c r="F77" s="81"/>
-      <c r="G77" s="82"/>
-      <c r="H77" s="83"/>
+      <c r="F77" s="77"/>
+      <c r="G77" s="78"/>
+      <c r="H77" s="79"/>
       <c r="I77" s="32"/>
-      <c r="J77" s="81"/>
-      <c r="K77" s="82"/>
-      <c r="L77" s="83"/>
+      <c r="J77" s="77"/>
+      <c r="K77" s="78"/>
+      <c r="L77" s="79"/>
       <c r="M77" s="4"/>
-      <c r="N77" s="71"/>
-      <c r="O77" s="72"/>
-      <c r="P77" s="73"/>
+      <c r="N77" s="83"/>
+      <c r="O77" s="84"/>
+      <c r="P77" s="85"/>
       <c r="Q77" s="44"/>
-      <c r="R77" s="71"/>
-      <c r="S77" s="72"/>
-      <c r="T77" s="73"/>
+      <c r="R77" s="83"/>
+      <c r="S77" s="84"/>
+      <c r="T77" s="85"/>
       <c r="U77" s="31"/>
-      <c r="V77" s="71"/>
-      <c r="W77" s="72"/>
-      <c r="X77" s="73"/>
+      <c r="V77" s="83"/>
+      <c r="W77" s="84"/>
+      <c r="X77" s="85"/>
       <c r="Y77" s="32"/>
-      <c r="Z77" s="71"/>
-      <c r="AA77" s="72"/>
-      <c r="AB77" s="73"/>
+      <c r="Z77" s="83"/>
+      <c r="AA77" s="84"/>
+      <c r="AB77" s="85"/>
       <c r="AC77" s="31"/>
-      <c r="AD77" s="71"/>
-      <c r="AE77" s="72"/>
-      <c r="AF77" s="73"/>
+      <c r="AD77" s="83"/>
+      <c r="AE77" s="84"/>
+      <c r="AF77" s="85"/>
       <c r="AG77" s="32"/>
-      <c r="AH77" s="71"/>
-      <c r="AI77" s="72"/>
-      <c r="AJ77" s="73"/>
+      <c r="AH77" s="83"/>
+      <c r="AI77" s="84"/>
+      <c r="AJ77" s="85"/>
       <c r="AK77" s="32"/>
-      <c r="AL77" s="71"/>
-      <c r="AM77" s="72"/>
-      <c r="AN77" s="73"/>
+      <c r="AL77" s="83"/>
+      <c r="AM77" s="84"/>
+      <c r="AN77" s="85"/>
       <c r="AO77" s="12"/>
       <c r="AP77" s="29"/>
       <c r="AQ77" s="26"/>
       <c r="AR77" s="24"/>
     </row>
-    <row r="78" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="16"/>
-      <c r="B78" s="65" t="s">
+      <c r="B78" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="C78" s="66"/>
-      <c r="D78" s="67"/>
+      <c r="C78" s="90"/>
+      <c r="D78" s="91"/>
       <c r="E78" s="32"/>
-      <c r="F78" s="65" t="s">
+      <c r="F78" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="G78" s="66"/>
-      <c r="H78" s="67"/>
+      <c r="G78" s="90"/>
+      <c r="H78" s="91"/>
       <c r="I78" s="43"/>
-      <c r="J78" s="65"/>
-      <c r="K78" s="66"/>
-      <c r="L78" s="67"/>
+      <c r="J78" s="89"/>
+      <c r="K78" s="90"/>
+      <c r="L78" s="91"/>
       <c r="M78" s="5"/>
-      <c r="N78" s="65" t="s">
+      <c r="N78" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="O78" s="66"/>
-      <c r="P78" s="67"/>
+      <c r="O78" s="90"/>
+      <c r="P78" s="91"/>
       <c r="Q78" s="44"/>
-      <c r="R78" s="65" t="s">
+      <c r="R78" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="S78" s="66"/>
-      <c r="T78" s="67"/>
+      <c r="S78" s="90"/>
+      <c r="T78" s="91"/>
       <c r="U78" s="32"/>
-      <c r="V78" s="65" t="s">
+      <c r="V78" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="W78" s="66"/>
-      <c r="X78" s="67"/>
+      <c r="W78" s="90"/>
+      <c r="X78" s="91"/>
       <c r="Y78" s="32"/>
-      <c r="Z78" s="65" t="s">
+      <c r="Z78" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="AA78" s="66"/>
-      <c r="AB78" s="67"/>
+      <c r="AA78" s="90"/>
+      <c r="AB78" s="91"/>
       <c r="AC78" s="32"/>
-      <c r="AD78" s="65" t="s">
+      <c r="AD78" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="AE78" s="66"/>
-      <c r="AF78" s="67"/>
+      <c r="AE78" s="90"/>
+      <c r="AF78" s="91"/>
       <c r="AG78" s="32"/>
-      <c r="AH78" s="65" t="s">
+      <c r="AH78" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="AI78" s="66"/>
-      <c r="AJ78" s="67"/>
+      <c r="AI78" s="90"/>
+      <c r="AJ78" s="91"/>
       <c r="AK78" s="43"/>
-      <c r="AL78" s="65"/>
-      <c r="AM78" s="66"/>
-      <c r="AN78" s="67"/>
+      <c r="AL78" s="89"/>
+      <c r="AM78" s="90"/>
+      <c r="AN78" s="91"/>
       <c r="AO78" s="12"/>
       <c r="AP78" s="29"/>
       <c r="AQ78" s="26"/>
       <c r="AR78" s="24"/>
     </row>
-    <row r="79" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A79" s="16"/>
-      <c r="B79" s="62"/>
-      <c r="C79" s="63"/>
-      <c r="D79" s="64"/>
+      <c r="B79" s="80"/>
+      <c r="C79" s="81"/>
+      <c r="D79" s="82"/>
       <c r="E79" s="31"/>
-      <c r="F79" s="62"/>
-      <c r="G79" s="63"/>
-      <c r="H79" s="64"/>
+      <c r="F79" s="80"/>
+      <c r="G79" s="81"/>
+      <c r="H79" s="82"/>
       <c r="I79" s="32"/>
-      <c r="J79" s="62"/>
-      <c r="K79" s="63"/>
-      <c r="L79" s="64"/>
+      <c r="J79" s="80"/>
+      <c r="K79" s="81"/>
+      <c r="L79" s="82"/>
       <c r="M79" s="5"/>
-      <c r="N79" s="62"/>
-      <c r="O79" s="63"/>
-      <c r="P79" s="64"/>
+      <c r="N79" s="80"/>
+      <c r="O79" s="81"/>
+      <c r="P79" s="82"/>
       <c r="Q79" s="31"/>
-      <c r="R79" s="62"/>
-      <c r="S79" s="63"/>
-      <c r="T79" s="64"/>
+      <c r="R79" s="80"/>
+      <c r="S79" s="81"/>
+      <c r="T79" s="82"/>
       <c r="U79" s="32"/>
-      <c r="V79" s="62"/>
-      <c r="W79" s="63"/>
-      <c r="X79" s="64"/>
+      <c r="V79" s="80"/>
+      <c r="W79" s="81"/>
+      <c r="X79" s="82"/>
       <c r="Y79" s="32"/>
-      <c r="Z79" s="62"/>
-      <c r="AA79" s="63"/>
-      <c r="AB79" s="64"/>
+      <c r="Z79" s="80"/>
+      <c r="AA79" s="81"/>
+      <c r="AB79" s="82"/>
       <c r="AC79" s="32"/>
-      <c r="AD79" s="62"/>
-      <c r="AE79" s="63"/>
-      <c r="AF79" s="64"/>
+      <c r="AD79" s="80"/>
+      <c r="AE79" s="81"/>
+      <c r="AF79" s="82"/>
       <c r="AG79" s="31"/>
-      <c r="AH79" s="62"/>
-      <c r="AI79" s="63"/>
-      <c r="AJ79" s="64"/>
+      <c r="AH79" s="80"/>
+      <c r="AI79" s="81"/>
+      <c r="AJ79" s="82"/>
       <c r="AK79" s="32"/>
-      <c r="AL79" s="62"/>
-      <c r="AM79" s="63"/>
-      <c r="AN79" s="64"/>
+      <c r="AL79" s="80"/>
+      <c r="AM79" s="81"/>
+      <c r="AN79" s="82"/>
       <c r="AO79" s="12"/>
       <c r="AP79" s="29"/>
       <c r="AQ79" s="26"/>
       <c r="AR79" s="24"/>
     </row>
-    <row r="80" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="12"/>
       <c r="B80" s="35"/>
       <c r="C80" s="35"/>
@@ -6629,301 +6629,301 @@
       <c r="AQ80" s="26"/>
       <c r="AR80" s="24"/>
     </row>
-    <row r="81" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="12"/>
-      <c r="B81" s="79" t="s">
+      <c r="B81" s="75" t="s">
         <v>56</v>
       </c>
-      <c r="C81" s="80"/>
+      <c r="C81" s="76"/>
       <c r="D81" s="55"/>
       <c r="E81" s="32"/>
-      <c r="F81" s="79" t="s">
+      <c r="F81" s="75" t="s">
         <v>56</v>
       </c>
-      <c r="G81" s="80"/>
+      <c r="G81" s="76"/>
       <c r="H81" s="55"/>
       <c r="I81" s="50"/>
-      <c r="J81" s="79" t="s">
+      <c r="J81" s="75" t="s">
         <v>56</v>
       </c>
-      <c r="K81" s="80"/>
+      <c r="K81" s="76"/>
       <c r="L81" s="55"/>
       <c r="M81" s="5"/>
-      <c r="N81" s="87" t="s">
+      <c r="N81" s="70" t="s">
         <v>56</v>
       </c>
-      <c r="O81" s="88"/>
+      <c r="O81" s="71"/>
       <c r="P81" s="34"/>
       <c r="Q81" s="50"/>
-      <c r="R81" s="87" t="s">
+      <c r="R81" s="70" t="s">
         <v>56</v>
       </c>
-      <c r="S81" s="88"/>
+      <c r="S81" s="71"/>
       <c r="T81" s="34"/>
       <c r="U81" s="36"/>
-      <c r="V81" s="87" t="s">
+      <c r="V81" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="W81" s="88"/>
+      <c r="W81" s="71"/>
       <c r="X81" s="34"/>
       <c r="Y81" s="32"/>
-      <c r="Z81" s="87" t="s">
+      <c r="Z81" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="AA81" s="88"/>
+      <c r="AA81" s="71"/>
       <c r="AB81" s="34"/>
       <c r="AC81" s="32"/>
-      <c r="AD81" s="87" t="s">
+      <c r="AD81" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="AE81" s="88"/>
+      <c r="AE81" s="71"/>
       <c r="AF81" s="34"/>
       <c r="AG81" s="32"/>
-      <c r="AH81" s="87" t="s">
+      <c r="AH81" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="AI81" s="88"/>
+      <c r="AI81" s="71"/>
       <c r="AJ81" s="34"/>
       <c r="AK81" s="50"/>
-      <c r="AL81" s="87"/>
-      <c r="AM81" s="88"/>
+      <c r="AL81" s="70"/>
+      <c r="AM81" s="71"/>
       <c r="AN81" s="34"/>
       <c r="AO81" s="12"/>
       <c r="AP81" s="29"/>
       <c r="AQ81" s="26"/>
       <c r="AR81" s="24"/>
     </row>
-    <row r="82" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="12"/>
-      <c r="B82" s="76" t="s">
+      <c r="B82" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="C82" s="77"/>
-      <c r="D82" s="78"/>
+      <c r="C82" s="63"/>
+      <c r="D82" s="64"/>
       <c r="E82" s="32"/>
-      <c r="F82" s="76" t="s">
+      <c r="F82" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="G82" s="77"/>
-      <c r="H82" s="78"/>
+      <c r="G82" s="63"/>
+      <c r="H82" s="64"/>
       <c r="I82" s="36"/>
-      <c r="J82" s="76" t="s">
+      <c r="J82" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="K82" s="77"/>
-      <c r="L82" s="78"/>
+      <c r="K82" s="63"/>
+      <c r="L82" s="64"/>
       <c r="M82" s="5"/>
-      <c r="N82" s="84" t="s">
+      <c r="N82" s="72" t="s">
         <v>53</v>
       </c>
-      <c r="O82" s="85"/>
-      <c r="P82" s="86"/>
+      <c r="O82" s="73"/>
+      <c r="P82" s="74"/>
       <c r="Q82" s="36"/>
-      <c r="R82" s="84" t="s">
+      <c r="R82" s="72" t="s">
         <v>53</v>
       </c>
-      <c r="S82" s="85"/>
-      <c r="T82" s="86"/>
+      <c r="S82" s="73"/>
+      <c r="T82" s="74"/>
       <c r="U82" s="32"/>
-      <c r="V82" s="84"/>
-      <c r="W82" s="85"/>
-      <c r="X82" s="86"/>
+      <c r="V82" s="72"/>
+      <c r="W82" s="73"/>
+      <c r="X82" s="74"/>
       <c r="Y82" s="32"/>
-      <c r="Z82" s="84"/>
-      <c r="AA82" s="85"/>
-      <c r="AB82" s="86"/>
+      <c r="Z82" s="72"/>
+      <c r="AA82" s="73"/>
+      <c r="AB82" s="74"/>
       <c r="AC82" s="32"/>
-      <c r="AD82" s="84"/>
-      <c r="AE82" s="85"/>
-      <c r="AF82" s="86"/>
+      <c r="AD82" s="72"/>
+      <c r="AE82" s="73"/>
+      <c r="AF82" s="74"/>
       <c r="AG82" s="32"/>
-      <c r="AH82" s="84"/>
-      <c r="AI82" s="85"/>
-      <c r="AJ82" s="86"/>
+      <c r="AH82" s="72"/>
+      <c r="AI82" s="73"/>
+      <c r="AJ82" s="74"/>
       <c r="AK82" s="36"/>
-      <c r="AL82" s="84"/>
-      <c r="AM82" s="85"/>
-      <c r="AN82" s="86"/>
+      <c r="AL82" s="72"/>
+      <c r="AM82" s="73"/>
+      <c r="AN82" s="74"/>
       <c r="AO82" s="12"/>
       <c r="AP82" s="29"/>
       <c r="AQ82" s="26"/>
       <c r="AR82" s="24"/>
     </row>
-    <row r="83" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="12"/>
-      <c r="B83" s="81" t="s">
+      <c r="B83" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="C83" s="82"/>
-      <c r="D83" s="83"/>
+      <c r="C83" s="78"/>
+      <c r="D83" s="79"/>
       <c r="E83" s="32"/>
-      <c r="F83" s="81" t="s">
+      <c r="F83" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="G83" s="82"/>
-      <c r="H83" s="83"/>
+      <c r="G83" s="78"/>
+      <c r="H83" s="79"/>
       <c r="I83" s="32"/>
-      <c r="J83" s="81" t="s">
+      <c r="J83" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="K83" s="82"/>
-      <c r="L83" s="83"/>
+      <c r="K83" s="78"/>
+      <c r="L83" s="79"/>
       <c r="M83" s="5"/>
-      <c r="N83" s="71" t="s">
+      <c r="N83" s="83" t="s">
         <v>50</v>
       </c>
-      <c r="O83" s="72"/>
-      <c r="P83" s="73"/>
+      <c r="O83" s="84"/>
+      <c r="P83" s="85"/>
       <c r="Q83" s="32"/>
-      <c r="R83" s="71" t="s">
+      <c r="R83" s="83" t="s">
         <v>50</v>
       </c>
-      <c r="S83" s="72"/>
-      <c r="T83" s="73"/>
+      <c r="S83" s="84"/>
+      <c r="T83" s="85"/>
       <c r="U83" s="31"/>
-      <c r="V83" s="71" t="s">
+      <c r="V83" s="83" t="s">
         <v>50</v>
       </c>
-      <c r="W83" s="72"/>
-      <c r="X83" s="73"/>
+      <c r="W83" s="84"/>
+      <c r="X83" s="85"/>
       <c r="Y83" s="32"/>
-      <c r="Z83" s="71" t="s">
+      <c r="Z83" s="83" t="s">
         <v>50</v>
       </c>
-      <c r="AA83" s="72"/>
-      <c r="AB83" s="73"/>
+      <c r="AA83" s="84"/>
+      <c r="AB83" s="85"/>
       <c r="AC83" s="32"/>
-      <c r="AD83" s="71" t="s">
+      <c r="AD83" s="83" t="s">
         <v>50</v>
       </c>
-      <c r="AE83" s="72"/>
-      <c r="AF83" s="73"/>
+      <c r="AE83" s="84"/>
+      <c r="AF83" s="85"/>
       <c r="AG83" s="32"/>
-      <c r="AH83" s="71" t="s">
+      <c r="AH83" s="83" t="s">
         <v>50</v>
       </c>
-      <c r="AI83" s="72"/>
-      <c r="AJ83" s="73"/>
+      <c r="AI83" s="84"/>
+      <c r="AJ83" s="85"/>
       <c r="AK83" s="32"/>
-      <c r="AL83" s="71"/>
-      <c r="AM83" s="72"/>
-      <c r="AN83" s="73"/>
+      <c r="AL83" s="83"/>
+      <c r="AM83" s="84"/>
+      <c r="AN83" s="85"/>
       <c r="AO83" s="12"/>
       <c r="AP83" s="29"/>
       <c r="AQ83" s="26"/>
       <c r="AR83" s="24"/>
     </row>
-    <row r="84" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="12"/>
-      <c r="B84" s="65" t="s">
+      <c r="B84" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="C84" s="66"/>
-      <c r="D84" s="67"/>
+      <c r="C84" s="90"/>
+      <c r="D84" s="91"/>
       <c r="E84" s="32"/>
-      <c r="F84" s="65" t="s">
+      <c r="F84" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="G84" s="66"/>
-      <c r="H84" s="67"/>
+      <c r="G84" s="90"/>
+      <c r="H84" s="91"/>
       <c r="I84" s="32"/>
-      <c r="J84" s="65" t="s">
+      <c r="J84" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="K84" s="66"/>
-      <c r="L84" s="67"/>
+      <c r="K84" s="90"/>
+      <c r="L84" s="91"/>
       <c r="M84" s="5"/>
-      <c r="N84" s="65" t="s">
+      <c r="N84" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="O84" s="66"/>
-      <c r="P84" s="67"/>
+      <c r="O84" s="90"/>
+      <c r="P84" s="91"/>
       <c r="Q84" s="32"/>
-      <c r="R84" s="65" t="s">
+      <c r="R84" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="S84" s="66"/>
-      <c r="T84" s="67"/>
+      <c r="S84" s="90"/>
+      <c r="T84" s="91"/>
       <c r="U84" s="32"/>
-      <c r="V84" s="65" t="s">
+      <c r="V84" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="W84" s="66"/>
-      <c r="X84" s="67"/>
+      <c r="W84" s="90"/>
+      <c r="X84" s="91"/>
       <c r="Y84" s="32"/>
-      <c r="Z84" s="65" t="s">
+      <c r="Z84" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="AA84" s="66"/>
-      <c r="AB84" s="67"/>
+      <c r="AA84" s="90"/>
+      <c r="AB84" s="91"/>
       <c r="AC84" s="43"/>
-      <c r="AD84" s="65" t="s">
+      <c r="AD84" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="AE84" s="66"/>
-      <c r="AF84" s="67"/>
+      <c r="AE84" s="90"/>
+      <c r="AF84" s="91"/>
       <c r="AG84" s="32"/>
-      <c r="AH84" s="65" t="s">
+      <c r="AH84" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="AI84" s="66"/>
-      <c r="AJ84" s="67"/>
+      <c r="AI84" s="90"/>
+      <c r="AJ84" s="91"/>
       <c r="AK84" s="32"/>
-      <c r="AL84" s="65"/>
-      <c r="AM84" s="66"/>
-      <c r="AN84" s="67"/>
+      <c r="AL84" s="89"/>
+      <c r="AM84" s="90"/>
+      <c r="AN84" s="91"/>
       <c r="AO84" s="12"/>
       <c r="AP84" s="29"/>
       <c r="AQ84" s="26"/>
       <c r="AR84" s="24"/>
     </row>
-    <row r="85" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A85" s="12"/>
-      <c r="B85" s="62"/>
-      <c r="C85" s="63"/>
-      <c r="D85" s="64"/>
+      <c r="B85" s="80"/>
+      <c r="C85" s="81"/>
+      <c r="D85" s="82"/>
       <c r="E85" s="31"/>
-      <c r="F85" s="62"/>
-      <c r="G85" s="63"/>
-      <c r="H85" s="64"/>
+      <c r="F85" s="80"/>
+      <c r="G85" s="81"/>
+      <c r="H85" s="82"/>
       <c r="I85" s="32"/>
-      <c r="J85" s="62"/>
-      <c r="K85" s="63"/>
-      <c r="L85" s="64"/>
+      <c r="J85" s="80"/>
+      <c r="K85" s="81"/>
+      <c r="L85" s="82"/>
       <c r="M85" s="6"/>
-      <c r="N85" s="62"/>
-      <c r="O85" s="63"/>
-      <c r="P85" s="64"/>
+      <c r="N85" s="80"/>
+      <c r="O85" s="81"/>
+      <c r="P85" s="82"/>
       <c r="Q85" s="31"/>
-      <c r="R85" s="62"/>
-      <c r="S85" s="63"/>
-      <c r="T85" s="64"/>
+      <c r="R85" s="80"/>
+      <c r="S85" s="81"/>
+      <c r="T85" s="82"/>
       <c r="U85" s="32"/>
-      <c r="V85" s="62"/>
-      <c r="W85" s="63"/>
-      <c r="X85" s="64"/>
+      <c r="V85" s="80"/>
+      <c r="W85" s="81"/>
+      <c r="X85" s="82"/>
       <c r="Y85" s="32"/>
-      <c r="Z85" s="62"/>
-      <c r="AA85" s="63"/>
-      <c r="AB85" s="64"/>
+      <c r="Z85" s="80"/>
+      <c r="AA85" s="81"/>
+      <c r="AB85" s="82"/>
       <c r="AC85" s="43"/>
-      <c r="AD85" s="62"/>
-      <c r="AE85" s="63"/>
-      <c r="AF85" s="64"/>
+      <c r="AD85" s="80"/>
+      <c r="AE85" s="81"/>
+      <c r="AF85" s="82"/>
       <c r="AG85" s="31"/>
-      <c r="AH85" s="62"/>
-      <c r="AI85" s="63"/>
-      <c r="AJ85" s="64"/>
+      <c r="AH85" s="80"/>
+      <c r="AI85" s="81"/>
+      <c r="AJ85" s="82"/>
       <c r="AK85" s="32"/>
-      <c r="AL85" s="62"/>
-      <c r="AM85" s="63"/>
-      <c r="AN85" s="64"/>
+      <c r="AL85" s="80"/>
+      <c r="AM85" s="81"/>
+      <c r="AN85" s="82"/>
       <c r="AO85" s="12"/>
       <c r="AP85" s="29"/>
       <c r="AQ85" s="26"/>
       <c r="AR85" s="24"/>
     </row>
-    <row r="86" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="12"/>
       <c r="B86" s="35"/>
       <c r="C86" s="35"/>
@@ -6969,279 +6969,279 @@
       <c r="AQ86" s="26"/>
       <c r="AR86" s="24"/>
     </row>
-    <row r="87" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="12"/>
-      <c r="B87" s="79" t="s">
+      <c r="B87" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="C87" s="80"/>
+      <c r="C87" s="76"/>
       <c r="D87" s="55"/>
       <c r="E87" s="32"/>
-      <c r="F87" s="79" t="s">
+      <c r="F87" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="G87" s="80"/>
+      <c r="G87" s="76"/>
       <c r="H87" s="55"/>
       <c r="I87" s="32"/>
-      <c r="J87" s="79" t="s">
+      <c r="J87" s="75" t="s">
         <v>60</v>
       </c>
-      <c r="K87" s="80"/>
+      <c r="K87" s="76"/>
       <c r="L87" s="55"/>
       <c r="M87" s="6"/>
-      <c r="N87" s="87" t="s">
+      <c r="N87" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="O87" s="88"/>
+      <c r="O87" s="71"/>
       <c r="P87" s="34"/>
       <c r="Q87" s="32"/>
-      <c r="R87" s="87" t="s">
+      <c r="R87" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="S87" s="88"/>
+      <c r="S87" s="71"/>
       <c r="T87" s="34"/>
       <c r="U87" s="36"/>
-      <c r="V87" s="87" t="s">
+      <c r="V87" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="W87" s="88"/>
+      <c r="W87" s="71"/>
       <c r="X87" s="34"/>
       <c r="Y87" s="32"/>
-      <c r="Z87" s="87" t="s">
+      <c r="Z87" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="AA87" s="88"/>
+      <c r="AA87" s="71"/>
       <c r="AB87" s="34"/>
       <c r="AC87" s="32"/>
-      <c r="AD87" s="87"/>
-      <c r="AE87" s="88"/>
+      <c r="AD87" s="70"/>
+      <c r="AE87" s="71"/>
       <c r="AF87" s="34"/>
       <c r="AG87" s="32"/>
-      <c r="AH87" s="87"/>
-      <c r="AI87" s="88"/>
+      <c r="AH87" s="70"/>
+      <c r="AI87" s="71"/>
       <c r="AJ87" s="34"/>
       <c r="AK87" s="32"/>
-      <c r="AL87" s="87"/>
-      <c r="AM87" s="88"/>
+      <c r="AL87" s="70"/>
+      <c r="AM87" s="71"/>
       <c r="AN87" s="34"/>
       <c r="AO87" s="12"/>
       <c r="AP87" s="29"/>
       <c r="AQ87" s="26"/>
       <c r="AR87" s="24"/>
     </row>
-    <row r="88" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="12"/>
-      <c r="B88" s="76"/>
-      <c r="C88" s="77"/>
-      <c r="D88" s="78"/>
+      <c r="B88" s="62"/>
+      <c r="C88" s="63"/>
+      <c r="D88" s="64"/>
       <c r="E88" s="32"/>
-      <c r="F88" s="76"/>
-      <c r="G88" s="77"/>
-      <c r="H88" s="78"/>
+      <c r="F88" s="62"/>
+      <c r="G88" s="63"/>
+      <c r="H88" s="64"/>
       <c r="I88" s="32"/>
-      <c r="J88" s="76" t="s">
+      <c r="J88" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="K88" s="77"/>
-      <c r="L88" s="78"/>
+      <c r="K88" s="63"/>
+      <c r="L88" s="64"/>
       <c r="M88" s="6"/>
-      <c r="N88" s="84" t="s">
+      <c r="N88" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="O88" s="85"/>
-      <c r="P88" s="86"/>
+      <c r="O88" s="73"/>
+      <c r="P88" s="74"/>
       <c r="Q88" s="35"/>
-      <c r="R88" s="84" t="s">
+      <c r="R88" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="S88" s="85"/>
-      <c r="T88" s="86"/>
+      <c r="S88" s="73"/>
+      <c r="T88" s="74"/>
       <c r="U88" s="32"/>
-      <c r="V88" s="84" t="s">
+      <c r="V88" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="W88" s="85"/>
-      <c r="X88" s="86"/>
+      <c r="W88" s="73"/>
+      <c r="X88" s="74"/>
       <c r="Y88" s="32"/>
-      <c r="Z88" s="84" t="s">
+      <c r="Z88" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="AA88" s="85"/>
-      <c r="AB88" s="86"/>
+      <c r="AA88" s="73"/>
+      <c r="AB88" s="74"/>
       <c r="AC88" s="35"/>
-      <c r="AD88" s="84"/>
-      <c r="AE88" s="85"/>
-      <c r="AF88" s="86"/>
+      <c r="AD88" s="72"/>
+      <c r="AE88" s="73"/>
+      <c r="AF88" s="74"/>
       <c r="AG88" s="32"/>
-      <c r="AH88" s="84"/>
-      <c r="AI88" s="85"/>
-      <c r="AJ88" s="86"/>
+      <c r="AH88" s="72"/>
+      <c r="AI88" s="73"/>
+      <c r="AJ88" s="74"/>
       <c r="AK88" s="32"/>
-      <c r="AL88" s="84"/>
-      <c r="AM88" s="85"/>
-      <c r="AN88" s="86"/>
+      <c r="AL88" s="72"/>
+      <c r="AM88" s="73"/>
+      <c r="AN88" s="74"/>
       <c r="AO88" s="12"/>
       <c r="AP88" s="29"/>
       <c r="AQ88" s="26"/>
       <c r="AR88" s="24"/>
     </row>
-    <row r="89" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="12"/>
-      <c r="B89" s="81" t="s">
+      <c r="B89" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="C89" s="82"/>
-      <c r="D89" s="83"/>
+      <c r="C89" s="78"/>
+      <c r="D89" s="79"/>
       <c r="E89" s="32"/>
-      <c r="F89" s="81" t="s">
+      <c r="F89" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="G89" s="82"/>
-      <c r="H89" s="83"/>
+      <c r="G89" s="78"/>
+      <c r="H89" s="79"/>
       <c r="I89" s="32"/>
-      <c r="J89" s="81"/>
-      <c r="K89" s="82"/>
-      <c r="L89" s="83"/>
+      <c r="J89" s="77"/>
+      <c r="K89" s="78"/>
+      <c r="L89" s="79"/>
       <c r="M89" s="6"/>
-      <c r="N89" s="71"/>
-      <c r="O89" s="72"/>
-      <c r="P89" s="73"/>
+      <c r="N89" s="83"/>
+      <c r="O89" s="84"/>
+      <c r="P89" s="85"/>
       <c r="Q89" s="31"/>
-      <c r="R89" s="71"/>
-      <c r="S89" s="72"/>
-      <c r="T89" s="73"/>
+      <c r="R89" s="83"/>
+      <c r="S89" s="84"/>
+      <c r="T89" s="85"/>
       <c r="U89" s="31"/>
-      <c r="V89" s="71"/>
-      <c r="W89" s="72"/>
-      <c r="X89" s="73"/>
+      <c r="V89" s="83"/>
+      <c r="W89" s="84"/>
+      <c r="X89" s="85"/>
       <c r="Y89" s="32"/>
-      <c r="Z89" s="71"/>
-      <c r="AA89" s="72"/>
-      <c r="AB89" s="73"/>
+      <c r="Z89" s="83"/>
+      <c r="AA89" s="84"/>
+      <c r="AB89" s="85"/>
       <c r="AC89" s="31"/>
-      <c r="AD89" s="71"/>
-      <c r="AE89" s="72"/>
-      <c r="AF89" s="73"/>
+      <c r="AD89" s="83"/>
+      <c r="AE89" s="84"/>
+      <c r="AF89" s="85"/>
       <c r="AG89" s="32"/>
-      <c r="AH89" s="71"/>
-      <c r="AI89" s="72"/>
-      <c r="AJ89" s="73"/>
+      <c r="AH89" s="83"/>
+      <c r="AI89" s="84"/>
+      <c r="AJ89" s="85"/>
       <c r="AK89" s="32"/>
-      <c r="AL89" s="71"/>
-      <c r="AM89" s="72"/>
-      <c r="AN89" s="73"/>
+      <c r="AL89" s="83"/>
+      <c r="AM89" s="84"/>
+      <c r="AN89" s="85"/>
       <c r="AO89" s="12"/>
       <c r="AP89" s="29"/>
       <c r="AQ89" s="26"/>
       <c r="AR89" s="24"/>
     </row>
-    <row r="90" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="12"/>
-      <c r="B90" s="65" t="s">
+      <c r="B90" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="C90" s="66"/>
-      <c r="D90" s="67"/>
+      <c r="C90" s="90"/>
+      <c r="D90" s="91"/>
       <c r="E90" s="32"/>
-      <c r="F90" s="65" t="s">
+      <c r="F90" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="G90" s="66"/>
-      <c r="H90" s="67"/>
+      <c r="G90" s="90"/>
+      <c r="H90" s="91"/>
       <c r="I90" s="32"/>
-      <c r="J90" s="65" t="s">
+      <c r="J90" s="89" t="s">
         <v>17</v>
       </c>
-      <c r="K90" s="66"/>
-      <c r="L90" s="67"/>
+      <c r="K90" s="90"/>
+      <c r="L90" s="91"/>
       <c r="M90" s="6"/>
-      <c r="N90" s="65" t="s">
+      <c r="N90" s="89" t="s">
         <v>17</v>
       </c>
-      <c r="O90" s="66"/>
-      <c r="P90" s="67"/>
+      <c r="O90" s="90"/>
+      <c r="P90" s="91"/>
       <c r="Q90" s="32"/>
-      <c r="R90" s="65" t="s">
+      <c r="R90" s="89" t="s">
         <v>17</v>
       </c>
-      <c r="S90" s="66"/>
-      <c r="T90" s="67"/>
+      <c r="S90" s="90"/>
+      <c r="T90" s="91"/>
       <c r="U90" s="32"/>
-      <c r="V90" s="65" t="s">
+      <c r="V90" s="89" t="s">
         <v>17</v>
       </c>
-      <c r="W90" s="66"/>
-      <c r="X90" s="67"/>
+      <c r="W90" s="90"/>
+      <c r="X90" s="91"/>
       <c r="Y90" s="32"/>
-      <c r="Z90" s="65" t="s">
+      <c r="Z90" s="89" t="s">
         <v>17</v>
       </c>
-      <c r="AA90" s="66"/>
-      <c r="AB90" s="67"/>
+      <c r="AA90" s="90"/>
+      <c r="AB90" s="91"/>
       <c r="AC90" s="32"/>
-      <c r="AD90" s="65"/>
-      <c r="AE90" s="66"/>
-      <c r="AF90" s="67"/>
+      <c r="AD90" s="89"/>
+      <c r="AE90" s="90"/>
+      <c r="AF90" s="91"/>
       <c r="AG90" s="32"/>
-      <c r="AH90" s="65"/>
-      <c r="AI90" s="66"/>
-      <c r="AJ90" s="67"/>
+      <c r="AH90" s="89"/>
+      <c r="AI90" s="90"/>
+      <c r="AJ90" s="91"/>
       <c r="AK90" s="32"/>
-      <c r="AL90" s="65"/>
-      <c r="AM90" s="66"/>
-      <c r="AN90" s="67"/>
+      <c r="AL90" s="89"/>
+      <c r="AM90" s="90"/>
+      <c r="AN90" s="91"/>
       <c r="AO90" s="12"/>
       <c r="AP90" s="29"/>
       <c r="AQ90" s="26"/>
       <c r="AR90" s="24"/>
     </row>
-    <row r="91" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A91" s="12"/>
-      <c r="B91" s="62"/>
-      <c r="C91" s="63"/>
-      <c r="D91" s="64"/>
+      <c r="B91" s="80"/>
+      <c r="C91" s="81"/>
+      <c r="D91" s="82"/>
       <c r="E91" s="31"/>
-      <c r="F91" s="62"/>
-      <c r="G91" s="63"/>
-      <c r="H91" s="64"/>
+      <c r="F91" s="80"/>
+      <c r="G91" s="81"/>
+      <c r="H91" s="82"/>
       <c r="I91" s="31"/>
-      <c r="J91" s="62"/>
-      <c r="K91" s="63"/>
-      <c r="L91" s="64"/>
+      <c r="J91" s="80"/>
+      <c r="K91" s="81"/>
+      <c r="L91" s="82"/>
       <c r="M91" s="6"/>
-      <c r="N91" s="62"/>
-      <c r="O91" s="63"/>
-      <c r="P91" s="64"/>
+      <c r="N91" s="80"/>
+      <c r="O91" s="81"/>
+      <c r="P91" s="82"/>
       <c r="Q91" s="31"/>
-      <c r="R91" s="62"/>
-      <c r="S91" s="63"/>
-      <c r="T91" s="64"/>
+      <c r="R91" s="80"/>
+      <c r="S91" s="81"/>
+      <c r="T91" s="82"/>
       <c r="U91" s="32"/>
-      <c r="V91" s="62"/>
-      <c r="W91" s="63"/>
-      <c r="X91" s="64"/>
+      <c r="V91" s="80"/>
+      <c r="W91" s="81"/>
+      <c r="X91" s="82"/>
       <c r="Y91" s="32"/>
-      <c r="Z91" s="62"/>
-      <c r="AA91" s="63"/>
-      <c r="AB91" s="64"/>
+      <c r="Z91" s="80"/>
+      <c r="AA91" s="81"/>
+      <c r="AB91" s="82"/>
       <c r="AC91" s="32"/>
-      <c r="AD91" s="62"/>
-      <c r="AE91" s="63"/>
-      <c r="AF91" s="64"/>
+      <c r="AD91" s="80"/>
+      <c r="AE91" s="81"/>
+      <c r="AF91" s="82"/>
       <c r="AG91" s="31"/>
-      <c r="AH91" s="62"/>
-      <c r="AI91" s="63"/>
-      <c r="AJ91" s="64"/>
+      <c r="AH91" s="80"/>
+      <c r="AI91" s="81"/>
+      <c r="AJ91" s="82"/>
       <c r="AK91" s="31"/>
-      <c r="AL91" s="62"/>
-      <c r="AM91" s="63"/>
-      <c r="AN91" s="64"/>
+      <c r="AL91" s="80"/>
+      <c r="AM91" s="81"/>
+      <c r="AN91" s="82"/>
       <c r="AO91" s="12"/>
       <c r="AP91" s="29"/>
       <c r="AQ91" s="26"/>
       <c r="AR91" s="24"/>
     </row>
-    <row r="92" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="12"/>
       <c r="B92" s="35"/>
       <c r="C92" s="35"/>
@@ -7287,273 +7287,273 @@
       <c r="AQ92" s="26"/>
       <c r="AR92" s="24"/>
     </row>
-    <row r="93" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="12"/>
-      <c r="B93" s="79"/>
-      <c r="C93" s="80"/>
+      <c r="B93" s="75"/>
+      <c r="C93" s="76"/>
       <c r="D93" s="55"/>
       <c r="E93" s="36"/>
-      <c r="F93" s="79"/>
-      <c r="G93" s="80"/>
+      <c r="F93" s="75"/>
+      <c r="G93" s="76"/>
       <c r="H93" s="55"/>
       <c r="I93" s="32"/>
-      <c r="J93" s="79"/>
-      <c r="K93" s="80"/>
+      <c r="J93" s="75"/>
+      <c r="K93" s="76"/>
       <c r="L93" s="55"/>
       <c r="M93" s="6"/>
-      <c r="N93" s="87"/>
-      <c r="O93" s="88"/>
+      <c r="N93" s="70"/>
+      <c r="O93" s="71"/>
       <c r="P93" s="34"/>
       <c r="Q93" s="32"/>
-      <c r="R93" s="87" t="s">
+      <c r="R93" s="70" t="s">
         <v>67</v>
       </c>
-      <c r="S93" s="88"/>
+      <c r="S93" s="71"/>
       <c r="T93" s="34"/>
       <c r="U93" s="36"/>
-      <c r="V93" s="87" t="s">
+      <c r="V93" s="70" t="s">
         <v>67</v>
       </c>
-      <c r="W93" s="88"/>
+      <c r="W93" s="71"/>
       <c r="X93" s="34"/>
       <c r="Y93" s="32"/>
-      <c r="Z93" s="87" t="s">
+      <c r="Z93" s="70" t="s">
         <v>67</v>
       </c>
-      <c r="AA93" s="88"/>
+      <c r="AA93" s="71"/>
       <c r="AB93" s="34"/>
       <c r="AC93" s="32"/>
-      <c r="AD93" s="87" t="s">
+      <c r="AD93" s="70" t="s">
         <v>67</v>
       </c>
-      <c r="AE93" s="88"/>
+      <c r="AE93" s="71"/>
       <c r="AF93" s="34"/>
       <c r="AG93" s="32"/>
-      <c r="AH93" s="87" t="s">
+      <c r="AH93" s="70" t="s">
         <v>67</v>
       </c>
-      <c r="AI93" s="88"/>
+      <c r="AI93" s="71"/>
       <c r="AJ93" s="34"/>
       <c r="AK93" s="32"/>
-      <c r="AL93" s="87" t="s">
+      <c r="AL93" s="70" t="s">
         <v>67</v>
       </c>
-      <c r="AM93" s="88"/>
+      <c r="AM93" s="71"/>
       <c r="AN93" s="34"/>
       <c r="AO93" s="12"/>
       <c r="AP93" s="29"/>
       <c r="AQ93" s="26"/>
       <c r="AR93" s="24"/>
     </row>
-    <row r="94" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="12"/>
-      <c r="B94" s="76"/>
-      <c r="C94" s="77"/>
-      <c r="D94" s="78"/>
+      <c r="B94" s="62"/>
+      <c r="C94" s="63"/>
+      <c r="D94" s="64"/>
       <c r="E94" s="32"/>
-      <c r="F94" s="76"/>
-      <c r="G94" s="77"/>
-      <c r="H94" s="78"/>
+      <c r="F94" s="62"/>
+      <c r="G94" s="63"/>
+      <c r="H94" s="64"/>
       <c r="I94" s="32"/>
-      <c r="J94" s="76"/>
-      <c r="K94" s="77"/>
-      <c r="L94" s="78"/>
+      <c r="J94" s="62"/>
+      <c r="K94" s="63"/>
+      <c r="L94" s="64"/>
       <c r="M94" s="26"/>
-      <c r="N94" s="84"/>
-      <c r="O94" s="85"/>
-      <c r="P94" s="86"/>
+      <c r="N94" s="72"/>
+      <c r="O94" s="73"/>
+      <c r="P94" s="74"/>
       <c r="Q94" s="32"/>
-      <c r="R94" s="84" t="s">
+      <c r="R94" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="S94" s="85"/>
-      <c r="T94" s="86"/>
+      <c r="S94" s="73"/>
+      <c r="T94" s="74"/>
       <c r="U94" s="32"/>
-      <c r="V94" s="84" t="s">
+      <c r="V94" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="W94" s="85"/>
-      <c r="X94" s="86"/>
+      <c r="W94" s="73"/>
+      <c r="X94" s="74"/>
       <c r="Y94" s="32"/>
-      <c r="Z94" s="84" t="s">
+      <c r="Z94" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="AA94" s="85"/>
-      <c r="AB94" s="86"/>
+      <c r="AA94" s="73"/>
+      <c r="AB94" s="74"/>
       <c r="AC94" s="35"/>
-      <c r="AD94" s="84" t="s">
+      <c r="AD94" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="AE94" s="85"/>
-      <c r="AF94" s="86"/>
+      <c r="AE94" s="73"/>
+      <c r="AF94" s="74"/>
       <c r="AG94" s="32"/>
-      <c r="AH94" s="84" t="s">
+      <c r="AH94" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="AI94" s="85"/>
-      <c r="AJ94" s="86"/>
+      <c r="AI94" s="73"/>
+      <c r="AJ94" s="74"/>
       <c r="AK94" s="32"/>
-      <c r="AL94" s="84" t="s">
+      <c r="AL94" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="AM94" s="85"/>
-      <c r="AN94" s="86"/>
+      <c r="AM94" s="73"/>
+      <c r="AN94" s="74"/>
       <c r="AO94" s="12"/>
       <c r="AP94" s="29"/>
       <c r="AQ94" s="26"/>
       <c r="AR94" s="24"/>
     </row>
-    <row r="95" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="12"/>
-      <c r="B95" s="81"/>
-      <c r="C95" s="82"/>
-      <c r="D95" s="83"/>
+      <c r="B95" s="77"/>
+      <c r="C95" s="78"/>
+      <c r="D95" s="79"/>
       <c r="E95" s="31"/>
-      <c r="F95" s="81"/>
-      <c r="G95" s="82"/>
-      <c r="H95" s="83"/>
+      <c r="F95" s="77"/>
+      <c r="G95" s="78"/>
+      <c r="H95" s="79"/>
       <c r="I95" s="32"/>
-      <c r="J95" s="81"/>
-      <c r="K95" s="82"/>
-      <c r="L95" s="83"/>
+      <c r="J95" s="77"/>
+      <c r="K95" s="78"/>
+      <c r="L95" s="79"/>
       <c r="M95" s="26"/>
-      <c r="N95" s="71"/>
-      <c r="O95" s="72"/>
-      <c r="P95" s="73"/>
+      <c r="N95" s="83"/>
+      <c r="O95" s="84"/>
+      <c r="P95" s="85"/>
       <c r="Q95" s="32"/>
-      <c r="R95" s="71"/>
-      <c r="S95" s="72"/>
-      <c r="T95" s="73"/>
+      <c r="R95" s="83"/>
+      <c r="S95" s="84"/>
+      <c r="T95" s="85"/>
       <c r="U95" s="31"/>
-      <c r="V95" s="71"/>
-      <c r="W95" s="72"/>
-      <c r="X95" s="73"/>
+      <c r="V95" s="83"/>
+      <c r="W95" s="84"/>
+      <c r="X95" s="85"/>
       <c r="Y95" s="32"/>
-      <c r="Z95" s="71"/>
-      <c r="AA95" s="72"/>
-      <c r="AB95" s="73"/>
+      <c r="Z95" s="83"/>
+      <c r="AA95" s="84"/>
+      <c r="AB95" s="85"/>
       <c r="AC95" s="31"/>
-      <c r="AD95" s="71"/>
-      <c r="AE95" s="72"/>
-      <c r="AF95" s="73"/>
+      <c r="AD95" s="83"/>
+      <c r="AE95" s="84"/>
+      <c r="AF95" s="85"/>
       <c r="AG95" s="32"/>
-      <c r="AH95" s="71"/>
-      <c r="AI95" s="72"/>
-      <c r="AJ95" s="73"/>
+      <c r="AH95" s="83"/>
+      <c r="AI95" s="84"/>
+      <c r="AJ95" s="85"/>
       <c r="AK95" s="32"/>
-      <c r="AL95" s="71"/>
-      <c r="AM95" s="72"/>
-      <c r="AN95" s="73"/>
+      <c r="AL95" s="83"/>
+      <c r="AM95" s="84"/>
+      <c r="AN95" s="85"/>
       <c r="AO95" s="12"/>
       <c r="AP95" s="29"/>
       <c r="AQ95" s="26"/>
       <c r="AR95" s="24"/>
     </row>
-    <row r="96" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="12"/>
-      <c r="B96" s="65"/>
-      <c r="C96" s="66"/>
-      <c r="D96" s="67"/>
+      <c r="B96" s="89"/>
+      <c r="C96" s="90"/>
+      <c r="D96" s="91"/>
       <c r="E96" s="32"/>
-      <c r="F96" s="65"/>
-      <c r="G96" s="66"/>
-      <c r="H96" s="67"/>
+      <c r="F96" s="89"/>
+      <c r="G96" s="90"/>
+      <c r="H96" s="91"/>
       <c r="I96" s="32"/>
-      <c r="J96" s="65"/>
-      <c r="K96" s="66"/>
-      <c r="L96" s="67"/>
+      <c r="J96" s="89"/>
+      <c r="K96" s="90"/>
+      <c r="L96" s="91"/>
       <c r="M96" s="26"/>
-      <c r="N96" s="65"/>
-      <c r="O96" s="66"/>
-      <c r="P96" s="67"/>
+      <c r="N96" s="89"/>
+      <c r="O96" s="90"/>
+      <c r="P96" s="91"/>
       <c r="Q96" s="32"/>
-      <c r="R96" s="65" t="s">
+      <c r="R96" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="S96" s="66"/>
-      <c r="T96" s="67"/>
+      <c r="S96" s="90"/>
+      <c r="T96" s="91"/>
       <c r="U96" s="32"/>
-      <c r="V96" s="65" t="s">
+      <c r="V96" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="W96" s="66"/>
-      <c r="X96" s="67"/>
+      <c r="W96" s="90"/>
+      <c r="X96" s="91"/>
       <c r="Y96" s="32"/>
-      <c r="Z96" s="65" t="s">
+      <c r="Z96" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="AA96" s="66"/>
-      <c r="AB96" s="67"/>
+      <c r="AA96" s="90"/>
+      <c r="AB96" s="91"/>
       <c r="AC96" s="32"/>
-      <c r="AD96" s="65" t="s">
+      <c r="AD96" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="AE96" s="66"/>
-      <c r="AF96" s="67"/>
+      <c r="AE96" s="90"/>
+      <c r="AF96" s="91"/>
       <c r="AG96" s="32"/>
-      <c r="AH96" s="65" t="s">
+      <c r="AH96" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="AI96" s="66"/>
-      <c r="AJ96" s="67"/>
+      <c r="AI96" s="90"/>
+      <c r="AJ96" s="91"/>
       <c r="AK96" s="32"/>
-      <c r="AL96" s="65" t="s">
+      <c r="AL96" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="AM96" s="66"/>
-      <c r="AN96" s="67"/>
+      <c r="AM96" s="90"/>
+      <c r="AN96" s="91"/>
       <c r="AO96" s="12"/>
       <c r="AP96" s="29"/>
       <c r="AQ96" s="26"/>
       <c r="AR96" s="24"/>
     </row>
-    <row r="97" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A97" s="12"/>
-      <c r="B97" s="62"/>
-      <c r="C97" s="63"/>
-      <c r="D97" s="64"/>
+      <c r="B97" s="80"/>
+      <c r="C97" s="81"/>
+      <c r="D97" s="82"/>
       <c r="E97" s="32"/>
-      <c r="F97" s="62"/>
-      <c r="G97" s="63"/>
-      <c r="H97" s="64"/>
+      <c r="F97" s="80"/>
+      <c r="G97" s="81"/>
+      <c r="H97" s="82"/>
       <c r="I97" s="31"/>
-      <c r="J97" s="62"/>
-      <c r="K97" s="63"/>
-      <c r="L97" s="64"/>
+      <c r="J97" s="80"/>
+      <c r="K97" s="81"/>
+      <c r="L97" s="82"/>
       <c r="M97" s="26"/>
-      <c r="N97" s="62"/>
-      <c r="O97" s="63"/>
-      <c r="P97" s="64"/>
+      <c r="N97" s="80"/>
+      <c r="O97" s="81"/>
+      <c r="P97" s="82"/>
       <c r="Q97" s="31"/>
-      <c r="R97" s="62"/>
-      <c r="S97" s="63"/>
-      <c r="T97" s="64"/>
+      <c r="R97" s="80"/>
+      <c r="S97" s="81"/>
+      <c r="T97" s="82"/>
       <c r="U97" s="32"/>
-      <c r="V97" s="62"/>
-      <c r="W97" s="63"/>
-      <c r="X97" s="64"/>
+      <c r="V97" s="80"/>
+      <c r="W97" s="81"/>
+      <c r="X97" s="82"/>
       <c r="Y97" s="31"/>
-      <c r="Z97" s="62"/>
-      <c r="AA97" s="63"/>
-      <c r="AB97" s="64"/>
+      <c r="Z97" s="80"/>
+      <c r="AA97" s="81"/>
+      <c r="AB97" s="82"/>
       <c r="AC97" s="31"/>
-      <c r="AD97" s="62"/>
-      <c r="AE97" s="63"/>
-      <c r="AF97" s="64"/>
+      <c r="AD97" s="80"/>
+      <c r="AE97" s="81"/>
+      <c r="AF97" s="82"/>
       <c r="AG97" s="32"/>
-      <c r="AH97" s="62"/>
-      <c r="AI97" s="63"/>
-      <c r="AJ97" s="64"/>
+      <c r="AH97" s="80"/>
+      <c r="AI97" s="81"/>
+      <c r="AJ97" s="82"/>
       <c r="AK97" s="31"/>
-      <c r="AL97" s="62"/>
-      <c r="AM97" s="63"/>
-      <c r="AN97" s="64"/>
+      <c r="AL97" s="80"/>
+      <c r="AM97" s="81"/>
+      <c r="AN97" s="82"/>
       <c r="AO97" s="12"/>
       <c r="AP97" s="29"/>
       <c r="AQ97" s="26"/>
       <c r="AR97" s="24"/>
     </row>
-    <row r="98" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="12"/>
       <c r="B98" s="35"/>
       <c r="C98" s="35"/>
@@ -7599,199 +7599,199 @@
       <c r="AQ98" s="26"/>
       <c r="AR98" s="24"/>
     </row>
-    <row r="99" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="12"/>
-      <c r="B99" s="79"/>
-      <c r="C99" s="80"/>
+      <c r="B99" s="75"/>
+      <c r="C99" s="76"/>
       <c r="D99" s="55"/>
       <c r="E99" s="32"/>
-      <c r="F99" s="79"/>
-      <c r="G99" s="80"/>
+      <c r="F99" s="75"/>
+      <c r="G99" s="76"/>
       <c r="H99" s="55"/>
       <c r="I99" s="36"/>
-      <c r="J99" s="79"/>
-      <c r="K99" s="80"/>
+      <c r="J99" s="75"/>
+      <c r="K99" s="76"/>
       <c r="L99" s="55"/>
       <c r="M99" s="26"/>
-      <c r="N99" s="87"/>
-      <c r="O99" s="88"/>
+      <c r="N99" s="70"/>
+      <c r="O99" s="71"/>
       <c r="P99" s="34"/>
       <c r="Q99" s="44"/>
-      <c r="R99" s="87" t="s">
+      <c r="R99" s="70" t="s">
         <v>110</v>
       </c>
-      <c r="S99" s="88"/>
+      <c r="S99" s="71"/>
       <c r="T99" s="34" t="s">
         <v>111</v>
       </c>
       <c r="U99" s="36"/>
-      <c r="V99" s="87"/>
-      <c r="W99" s="88"/>
+      <c r="V99" s="70"/>
+      <c r="W99" s="71"/>
       <c r="X99" s="34"/>
       <c r="Y99" s="32"/>
-      <c r="Z99" s="87"/>
-      <c r="AA99" s="88"/>
+      <c r="Z99" s="70"/>
+      <c r="AA99" s="71"/>
       <c r="AB99" s="34"/>
       <c r="AC99" s="36"/>
-      <c r="AD99" s="87"/>
-      <c r="AE99" s="88"/>
+      <c r="AD99" s="70"/>
+      <c r="AE99" s="71"/>
       <c r="AF99" s="34"/>
       <c r="AG99" s="32"/>
-      <c r="AH99" s="87"/>
-      <c r="AI99" s="88"/>
+      <c r="AH99" s="70"/>
+      <c r="AI99" s="71"/>
       <c r="AJ99" s="34"/>
       <c r="AK99" s="36"/>
-      <c r="AL99" s="87"/>
-      <c r="AM99" s="88"/>
+      <c r="AL99" s="70"/>
+      <c r="AM99" s="71"/>
       <c r="AN99" s="34"/>
       <c r="AO99" s="12"/>
       <c r="AP99" s="29"/>
       <c r="AQ99" s="26"/>
       <c r="AR99" s="24"/>
     </row>
-    <row r="100" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="12"/>
-      <c r="B100" s="81"/>
-      <c r="C100" s="82"/>
-      <c r="D100" s="83"/>
+      <c r="B100" s="77"/>
+      <c r="C100" s="78"/>
+      <c r="D100" s="79"/>
       <c r="E100" s="32"/>
-      <c r="F100" s="81"/>
-      <c r="G100" s="82"/>
-      <c r="H100" s="83"/>
+      <c r="F100" s="77"/>
+      <c r="G100" s="78"/>
+      <c r="H100" s="79"/>
       <c r="I100" s="31"/>
-      <c r="J100" s="81"/>
-      <c r="K100" s="82"/>
-      <c r="L100" s="83"/>
+      <c r="J100" s="77"/>
+      <c r="K100" s="78"/>
+      <c r="L100" s="79"/>
       <c r="M100" s="26"/>
-      <c r="N100" s="71"/>
-      <c r="O100" s="72"/>
-      <c r="P100" s="73"/>
+      <c r="N100" s="83"/>
+      <c r="O100" s="84"/>
+      <c r="P100" s="85"/>
       <c r="Q100" s="31"/>
-      <c r="R100" s="84" t="s">
+      <c r="R100" s="72" t="s">
         <v>112</v>
       </c>
-      <c r="S100" s="85"/>
-      <c r="T100" s="86"/>
+      <c r="S100" s="73"/>
+      <c r="T100" s="74"/>
       <c r="U100" s="31"/>
-      <c r="V100" s="71"/>
-      <c r="W100" s="72"/>
-      <c r="X100" s="73"/>
+      <c r="V100" s="83"/>
+      <c r="W100" s="84"/>
+      <c r="X100" s="85"/>
       <c r="Y100" s="32"/>
-      <c r="Z100" s="71"/>
-      <c r="AA100" s="72"/>
-      <c r="AB100" s="73"/>
+      <c r="Z100" s="83"/>
+      <c r="AA100" s="84"/>
+      <c r="AB100" s="85"/>
       <c r="AC100" s="36"/>
-      <c r="AD100" s="71"/>
-      <c r="AE100" s="72"/>
-      <c r="AF100" s="73"/>
+      <c r="AD100" s="83"/>
+      <c r="AE100" s="84"/>
+      <c r="AF100" s="85"/>
       <c r="AG100" s="32"/>
-      <c r="AH100" s="71"/>
-      <c r="AI100" s="72"/>
-      <c r="AJ100" s="73"/>
+      <c r="AH100" s="83"/>
+      <c r="AI100" s="84"/>
+      <c r="AJ100" s="85"/>
       <c r="AK100" s="31"/>
-      <c r="AL100" s="71"/>
-      <c r="AM100" s="72"/>
-      <c r="AN100" s="73"/>
+      <c r="AL100" s="83"/>
+      <c r="AM100" s="84"/>
+      <c r="AN100" s="85"/>
       <c r="AO100" s="12"/>
       <c r="AP100" s="29"/>
       <c r="AQ100" s="26"/>
       <c r="AR100" s="24"/>
     </row>
-    <row r="101" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="12"/>
-      <c r="B101" s="65"/>
-      <c r="C101" s="66"/>
-      <c r="D101" s="67"/>
+      <c r="B101" s="89"/>
+      <c r="C101" s="90"/>
+      <c r="D101" s="91"/>
       <c r="E101" s="32"/>
-      <c r="F101" s="65"/>
-      <c r="G101" s="66"/>
-      <c r="H101" s="67"/>
+      <c r="F101" s="89"/>
+      <c r="G101" s="90"/>
+      <c r="H101" s="91"/>
       <c r="I101" s="31"/>
-      <c r="J101" s="65"/>
-      <c r="K101" s="66"/>
-      <c r="L101" s="67"/>
+      <c r="J101" s="89"/>
+      <c r="K101" s="90"/>
+      <c r="L101" s="91"/>
       <c r="M101" s="26"/>
-      <c r="N101" s="65"/>
-      <c r="O101" s="66"/>
-      <c r="P101" s="67"/>
+      <c r="N101" s="89"/>
+      <c r="O101" s="90"/>
+      <c r="P101" s="91"/>
       <c r="Q101" s="31"/>
-      <c r="R101" s="65" t="s">
+      <c r="R101" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="S101" s="66"/>
-      <c r="T101" s="67"/>
+      <c r="S101" s="90"/>
+      <c r="T101" s="91"/>
       <c r="U101" s="32"/>
-      <c r="V101" s="65"/>
-      <c r="W101" s="66"/>
-      <c r="X101" s="67"/>
+      <c r="V101" s="89"/>
+      <c r="W101" s="90"/>
+      <c r="X101" s="91"/>
       <c r="Y101" s="32"/>
-      <c r="Z101" s="65"/>
-      <c r="AA101" s="66"/>
-      <c r="AB101" s="67"/>
+      <c r="Z101" s="89"/>
+      <c r="AA101" s="90"/>
+      <c r="AB101" s="91"/>
       <c r="AC101" s="31"/>
-      <c r="AD101" s="65"/>
-      <c r="AE101" s="66"/>
-      <c r="AF101" s="67"/>
+      <c r="AD101" s="89"/>
+      <c r="AE101" s="90"/>
+      <c r="AF101" s="91"/>
       <c r="AG101" s="32"/>
-      <c r="AH101" s="65"/>
-      <c r="AI101" s="66"/>
-      <c r="AJ101" s="67"/>
+      <c r="AH101" s="89"/>
+      <c r="AI101" s="90"/>
+      <c r="AJ101" s="91"/>
       <c r="AK101" s="31"/>
-      <c r="AL101" s="65"/>
-      <c r="AM101" s="66"/>
-      <c r="AN101" s="67"/>
+      <c r="AL101" s="89"/>
+      <c r="AM101" s="90"/>
+      <c r="AN101" s="91"/>
       <c r="AO101" s="12"/>
       <c r="AP101" s="29"/>
       <c r="AQ101" s="26"/>
       <c r="AR101" s="24"/>
     </row>
-    <row r="102" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A102" s="12"/>
-      <c r="B102" s="62"/>
-      <c r="C102" s="63"/>
-      <c r="D102" s="64"/>
+      <c r="B102" s="80"/>
+      <c r="C102" s="81"/>
+      <c r="D102" s="82"/>
       <c r="E102" s="31"/>
-      <c r="F102" s="62"/>
-      <c r="G102" s="63"/>
-      <c r="H102" s="64"/>
+      <c r="F102" s="80"/>
+      <c r="G102" s="81"/>
+      <c r="H102" s="82"/>
       <c r="I102" s="32"/>
-      <c r="J102" s="62"/>
-      <c r="K102" s="63"/>
-      <c r="L102" s="64"/>
+      <c r="J102" s="80"/>
+      <c r="K102" s="81"/>
+      <c r="L102" s="82"/>
       <c r="M102" s="26"/>
-      <c r="N102" s="62"/>
-      <c r="O102" s="63"/>
-      <c r="P102" s="64"/>
+      <c r="N102" s="80"/>
+      <c r="O102" s="81"/>
+      <c r="P102" s="82"/>
       <c r="Q102" s="31"/>
-      <c r="R102" s="62"/>
-      <c r="S102" s="63"/>
-      <c r="T102" s="64"/>
+      <c r="R102" s="80"/>
+      <c r="S102" s="81"/>
+      <c r="T102" s="82"/>
       <c r="U102" s="32"/>
-      <c r="V102" s="62"/>
-      <c r="W102" s="63"/>
-      <c r="X102" s="64"/>
+      <c r="V102" s="80"/>
+      <c r="W102" s="81"/>
+      <c r="X102" s="82"/>
       <c r="Y102" s="32"/>
-      <c r="Z102" s="62"/>
-      <c r="AA102" s="63"/>
-      <c r="AB102" s="64"/>
+      <c r="Z102" s="80"/>
+      <c r="AA102" s="81"/>
+      <c r="AB102" s="82"/>
       <c r="AC102" s="32"/>
-      <c r="AD102" s="62"/>
-      <c r="AE102" s="63"/>
-      <c r="AF102" s="64"/>
+      <c r="AD102" s="80"/>
+      <c r="AE102" s="81"/>
+      <c r="AF102" s="82"/>
       <c r="AG102" s="31"/>
-      <c r="AH102" s="62"/>
-      <c r="AI102" s="63"/>
-      <c r="AJ102" s="64"/>
+      <c r="AH102" s="80"/>
+      <c r="AI102" s="81"/>
+      <c r="AJ102" s="82"/>
       <c r="AK102" s="32"/>
-      <c r="AL102" s="62"/>
-      <c r="AM102" s="63"/>
-      <c r="AN102" s="64"/>
+      <c r="AL102" s="80"/>
+      <c r="AM102" s="81"/>
+      <c r="AN102" s="82"/>
       <c r="AO102" s="12"/>
       <c r="AP102" s="29"/>
       <c r="AQ102" s="26"/>
       <c r="AR102" s="24"/>
     </row>
-    <row r="103" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="12"/>
       <c r="B103" s="40"/>
       <c r="C103" s="33"/>
@@ -7837,7 +7837,7 @@
       <c r="AQ103" s="26"/>
       <c r="AR103" s="26"/>
     </row>
-    <row r="104" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B104" s="33"/>
       <c r="C104" s="33"/>
       <c r="D104" s="33"/>
@@ -7854,73 +7854,73 @@
       <c r="AQ104" s="26"/>
       <c r="AR104" s="26"/>
     </row>
-    <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B105" s="87"/>
-      <c r="C105" s="88"/>
+    <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B105" s="70"/>
+      <c r="C105" s="71"/>
       <c r="D105" s="34"/>
       <c r="E105" s="32"/>
-      <c r="F105" s="87"/>
-      <c r="G105" s="88"/>
+      <c r="F105" s="70"/>
+      <c r="G105" s="71"/>
       <c r="H105" s="34"/>
       <c r="I105" s="32"/>
-      <c r="J105" s="87"/>
-      <c r="K105" s="88"/>
+      <c r="J105" s="70"/>
+      <c r="K105" s="71"/>
       <c r="L105" s="34"/>
       <c r="AO105" s="26"/>
     </row>
-    <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B106" s="84"/>
-      <c r="C106" s="85"/>
-      <c r="D106" s="86"/>
+    <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B106" s="72"/>
+      <c r="C106" s="73"/>
+      <c r="D106" s="74"/>
       <c r="E106" s="32"/>
-      <c r="F106" s="84"/>
-      <c r="G106" s="85"/>
-      <c r="H106" s="86"/>
+      <c r="F106" s="72"/>
+      <c r="G106" s="73"/>
+      <c r="H106" s="74"/>
       <c r="I106" s="32"/>
-      <c r="J106" s="84"/>
-      <c r="K106" s="85"/>
-      <c r="L106" s="86"/>
-    </row>
-    <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B107" s="71"/>
-      <c r="C107" s="72"/>
-      <c r="D107" s="73"/>
+      <c r="J106" s="72"/>
+      <c r="K106" s="73"/>
+      <c r="L106" s="74"/>
+    </row>
+    <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B107" s="83"/>
+      <c r="C107" s="84"/>
+      <c r="D107" s="85"/>
       <c r="E107" s="32"/>
-      <c r="F107" s="71"/>
-      <c r="G107" s="72"/>
-      <c r="H107" s="73"/>
+      <c r="F107" s="83"/>
+      <c r="G107" s="84"/>
+      <c r="H107" s="85"/>
       <c r="I107" s="32"/>
-      <c r="J107" s="71"/>
-      <c r="K107" s="72"/>
-      <c r="L107" s="73"/>
-    </row>
-    <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B108" s="65"/>
-      <c r="C108" s="66"/>
-      <c r="D108" s="67"/>
+      <c r="J107" s="83"/>
+      <c r="K107" s="84"/>
+      <c r="L107" s="85"/>
+    </row>
+    <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B108" s="89"/>
+      <c r="C108" s="90"/>
+      <c r="D108" s="91"/>
       <c r="E108" s="32"/>
-      <c r="F108" s="65"/>
-      <c r="G108" s="66"/>
-      <c r="H108" s="67"/>
+      <c r="F108" s="89"/>
+      <c r="G108" s="90"/>
+      <c r="H108" s="91"/>
       <c r="I108" s="31"/>
-      <c r="J108" s="65"/>
-      <c r="K108" s="66"/>
-      <c r="L108" s="67"/>
-    </row>
-    <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B109" s="62"/>
-      <c r="C109" s="63"/>
-      <c r="D109" s="64"/>
+      <c r="J108" s="89"/>
+      <c r="K108" s="90"/>
+      <c r="L108" s="91"/>
+    </row>
+    <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B109" s="80"/>
+      <c r="C109" s="81"/>
+      <c r="D109" s="82"/>
       <c r="E109" s="31"/>
-      <c r="F109" s="62"/>
-      <c r="G109" s="63"/>
-      <c r="H109" s="64"/>
+      <c r="F109" s="80"/>
+      <c r="G109" s="81"/>
+      <c r="H109" s="82"/>
       <c r="I109" s="31"/>
-      <c r="J109" s="62"/>
-      <c r="K109" s="63"/>
-      <c r="L109" s="64"/>
-    </row>
-    <row r="110" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J109" s="80"/>
+      <c r="K109" s="81"/>
+      <c r="L109" s="82"/>
+    </row>
+    <row r="110" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B110" s="35"/>
       <c r="C110" s="35"/>
       <c r="D110" s="35"/>
@@ -7933,72 +7933,72 @@
       <c r="K110" s="35"/>
       <c r="L110" s="35"/>
     </row>
-    <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B111" s="87"/>
-      <c r="C111" s="88"/>
+    <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B111" s="70"/>
+      <c r="C111" s="71"/>
       <c r="D111" s="34"/>
       <c r="E111" s="31"/>
-      <c r="F111" s="87"/>
-      <c r="G111" s="88"/>
+      <c r="F111" s="70"/>
+      <c r="G111" s="71"/>
       <c r="H111" s="34"/>
       <c r="I111" s="31"/>
-      <c r="J111" s="87"/>
-      <c r="K111" s="88"/>
+      <c r="J111" s="70"/>
+      <c r="K111" s="71"/>
       <c r="L111" s="34"/>
     </row>
-    <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B112" s="84"/>
-      <c r="C112" s="85"/>
-      <c r="D112" s="86"/>
+    <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B112" s="72"/>
+      <c r="C112" s="73"/>
+      <c r="D112" s="74"/>
       <c r="E112" s="32"/>
-      <c r="F112" s="84"/>
-      <c r="G112" s="85"/>
-      <c r="H112" s="86"/>
+      <c r="F112" s="72"/>
+      <c r="G112" s="73"/>
+      <c r="H112" s="74"/>
       <c r="I112" s="32"/>
-      <c r="J112" s="84"/>
-      <c r="K112" s="85"/>
-      <c r="L112" s="86"/>
-    </row>
-    <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B113" s="71"/>
-      <c r="C113" s="72"/>
-      <c r="D113" s="73"/>
+      <c r="J112" s="72"/>
+      <c r="K112" s="73"/>
+      <c r="L112" s="74"/>
+    </row>
+    <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B113" s="83"/>
+      <c r="C113" s="84"/>
+      <c r="D113" s="85"/>
       <c r="E113" s="35"/>
-      <c r="F113" s="71"/>
-      <c r="G113" s="72"/>
-      <c r="H113" s="73"/>
+      <c r="F113" s="83"/>
+      <c r="G113" s="84"/>
+      <c r="H113" s="85"/>
       <c r="I113" s="35"/>
-      <c r="J113" s="71"/>
-      <c r="K113" s="72"/>
-      <c r="L113" s="73"/>
-    </row>
-    <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B114" s="65"/>
-      <c r="C114" s="66"/>
-      <c r="D114" s="67"/>
+      <c r="J113" s="83"/>
+      <c r="K113" s="84"/>
+      <c r="L113" s="85"/>
+    </row>
+    <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B114" s="89"/>
+      <c r="C114" s="90"/>
+      <c r="D114" s="91"/>
       <c r="E114" s="32"/>
-      <c r="F114" s="65"/>
-      <c r="G114" s="66"/>
-      <c r="H114" s="67"/>
+      <c r="F114" s="89"/>
+      <c r="G114" s="90"/>
+      <c r="H114" s="91"/>
       <c r="I114" s="32"/>
-      <c r="J114" s="65"/>
-      <c r="K114" s="66"/>
-      <c r="L114" s="67"/>
-    </row>
-    <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B115" s="62"/>
-      <c r="C115" s="63"/>
-      <c r="D115" s="64"/>
+      <c r="J114" s="89"/>
+      <c r="K114" s="90"/>
+      <c r="L114" s="91"/>
+    </row>
+    <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B115" s="80"/>
+      <c r="C115" s="81"/>
+      <c r="D115" s="82"/>
       <c r="E115" s="31"/>
-      <c r="F115" s="62"/>
-      <c r="G115" s="63"/>
-      <c r="H115" s="64"/>
+      <c r="F115" s="80"/>
+      <c r="G115" s="81"/>
+      <c r="H115" s="82"/>
       <c r="I115" s="31"/>
-      <c r="J115" s="62"/>
-      <c r="K115" s="63"/>
-      <c r="L115" s="64"/>
-    </row>
-    <row r="116" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J115" s="80"/>
+      <c r="K115" s="81"/>
+      <c r="L115" s="82"/>
+    </row>
+    <row r="116" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B116" s="35"/>
       <c r="C116" s="35"/>
       <c r="D116" s="35"/>
@@ -8011,72 +8011,72 @@
       <c r="K116" s="35"/>
       <c r="L116" s="35"/>
     </row>
-    <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="87"/>
-      <c r="C117" s="88"/>
+    <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B117" s="70"/>
+      <c r="C117" s="71"/>
       <c r="D117" s="34"/>
       <c r="E117" s="32"/>
-      <c r="F117" s="87"/>
-      <c r="G117" s="88"/>
+      <c r="F117" s="70"/>
+      <c r="G117" s="71"/>
       <c r="H117" s="34"/>
       <c r="I117" s="32"/>
-      <c r="J117" s="87"/>
-      <c r="K117" s="88"/>
+      <c r="J117" s="70"/>
+      <c r="K117" s="71"/>
       <c r="L117" s="34"/>
     </row>
-    <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B118" s="84"/>
-      <c r="C118" s="85"/>
-      <c r="D118" s="86"/>
+    <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B118" s="72"/>
+      <c r="C118" s="73"/>
+      <c r="D118" s="74"/>
       <c r="E118" s="32"/>
-      <c r="F118" s="84"/>
-      <c r="G118" s="85"/>
-      <c r="H118" s="86"/>
+      <c r="F118" s="72"/>
+      <c r="G118" s="73"/>
+      <c r="H118" s="74"/>
       <c r="I118" s="32"/>
-      <c r="J118" s="84"/>
-      <c r="K118" s="85"/>
-      <c r="L118" s="86"/>
-    </row>
-    <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B119" s="71"/>
-      <c r="C119" s="72"/>
-      <c r="D119" s="73"/>
+      <c r="J118" s="72"/>
+      <c r="K118" s="73"/>
+      <c r="L118" s="74"/>
+    </row>
+    <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B119" s="83"/>
+      <c r="C119" s="84"/>
+      <c r="D119" s="85"/>
       <c r="E119" s="32"/>
-      <c r="F119" s="71"/>
-      <c r="G119" s="72"/>
-      <c r="H119" s="73"/>
+      <c r="F119" s="83"/>
+      <c r="G119" s="84"/>
+      <c r="H119" s="85"/>
       <c r="I119" s="32"/>
-      <c r="J119" s="71"/>
-      <c r="K119" s="72"/>
-      <c r="L119" s="73"/>
-    </row>
-    <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B120" s="65"/>
-      <c r="C120" s="66"/>
-      <c r="D120" s="67"/>
+      <c r="J119" s="83"/>
+      <c r="K119" s="84"/>
+      <c r="L119" s="85"/>
+    </row>
+    <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B120" s="89"/>
+      <c r="C120" s="90"/>
+      <c r="D120" s="91"/>
       <c r="E120" s="32"/>
-      <c r="F120" s="65"/>
-      <c r="G120" s="66"/>
-      <c r="H120" s="67"/>
+      <c r="F120" s="89"/>
+      <c r="G120" s="90"/>
+      <c r="H120" s="91"/>
       <c r="I120" s="32"/>
-      <c r="J120" s="65"/>
-      <c r="K120" s="66"/>
-      <c r="L120" s="67"/>
-    </row>
-    <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B121" s="62"/>
-      <c r="C121" s="63"/>
-      <c r="D121" s="64"/>
+      <c r="J120" s="89"/>
+      <c r="K120" s="90"/>
+      <c r="L120" s="91"/>
+    </row>
+    <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B121" s="80"/>
+      <c r="C121" s="81"/>
+      <c r="D121" s="82"/>
       <c r="E121" s="31"/>
-      <c r="F121" s="62"/>
-      <c r="G121" s="63"/>
-      <c r="H121" s="64"/>
+      <c r="F121" s="80"/>
+      <c r="G121" s="81"/>
+      <c r="H121" s="82"/>
       <c r="I121" s="31"/>
-      <c r="J121" s="62"/>
-      <c r="K121" s="63"/>
-      <c r="L121" s="64"/>
-    </row>
-    <row r="122" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J121" s="80"/>
+      <c r="K121" s="81"/>
+      <c r="L121" s="82"/>
+    </row>
+    <row r="122" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B122" s="35"/>
       <c r="C122" s="35"/>
       <c r="D122" s="35"/>
@@ -8089,72 +8089,72 @@
       <c r="K122" s="35"/>
       <c r="L122" s="35"/>
     </row>
-    <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="87"/>
-      <c r="C123" s="88"/>
+    <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B123" s="70"/>
+      <c r="C123" s="71"/>
       <c r="D123" s="34"/>
       <c r="E123" s="32"/>
-      <c r="F123" s="87"/>
-      <c r="G123" s="88"/>
+      <c r="F123" s="70"/>
+      <c r="G123" s="71"/>
       <c r="H123" s="34"/>
       <c r="I123" s="32"/>
-      <c r="J123" s="87"/>
-      <c r="K123" s="88"/>
+      <c r="J123" s="70"/>
+      <c r="K123" s="71"/>
       <c r="L123" s="34"/>
     </row>
-    <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B124" s="84"/>
-      <c r="C124" s="85"/>
-      <c r="D124" s="86"/>
+    <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B124" s="72"/>
+      <c r="C124" s="73"/>
+      <c r="D124" s="74"/>
       <c r="E124" s="32"/>
-      <c r="F124" s="84"/>
-      <c r="G124" s="85"/>
-      <c r="H124" s="86"/>
+      <c r="F124" s="72"/>
+      <c r="G124" s="73"/>
+      <c r="H124" s="74"/>
       <c r="I124" s="32"/>
-      <c r="J124" s="84"/>
-      <c r="K124" s="85"/>
-      <c r="L124" s="86"/>
-    </row>
-    <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="71"/>
-      <c r="C125" s="72"/>
-      <c r="D125" s="73"/>
+      <c r="J124" s="72"/>
+      <c r="K124" s="73"/>
+      <c r="L124" s="74"/>
+    </row>
+    <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B125" s="83"/>
+      <c r="C125" s="84"/>
+      <c r="D125" s="85"/>
       <c r="E125" s="32"/>
-      <c r="F125" s="71"/>
-      <c r="G125" s="72"/>
-      <c r="H125" s="73"/>
+      <c r="F125" s="83"/>
+      <c r="G125" s="84"/>
+      <c r="H125" s="85"/>
       <c r="I125" s="32"/>
-      <c r="J125" s="71"/>
-      <c r="K125" s="72"/>
-      <c r="L125" s="73"/>
-    </row>
-    <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B126" s="65"/>
-      <c r="C126" s="66"/>
-      <c r="D126" s="67"/>
+      <c r="J125" s="83"/>
+      <c r="K125" s="84"/>
+      <c r="L125" s="85"/>
+    </row>
+    <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B126" s="89"/>
+      <c r="C126" s="90"/>
+      <c r="D126" s="91"/>
       <c r="E126" s="32"/>
-      <c r="F126" s="65"/>
-      <c r="G126" s="66"/>
-      <c r="H126" s="67"/>
+      <c r="F126" s="89"/>
+      <c r="G126" s="90"/>
+      <c r="H126" s="91"/>
       <c r="I126" s="31"/>
-      <c r="J126" s="65"/>
-      <c r="K126" s="66"/>
-      <c r="L126" s="67"/>
-    </row>
-    <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B127" s="62"/>
-      <c r="C127" s="63"/>
-      <c r="D127" s="64"/>
+      <c r="J126" s="89"/>
+      <c r="K126" s="90"/>
+      <c r="L126" s="91"/>
+    </row>
+    <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B127" s="80"/>
+      <c r="C127" s="81"/>
+      <c r="D127" s="82"/>
       <c r="E127" s="31"/>
-      <c r="F127" s="62"/>
-      <c r="G127" s="63"/>
-      <c r="H127" s="64"/>
+      <c r="F127" s="80"/>
+      <c r="G127" s="81"/>
+      <c r="H127" s="82"/>
       <c r="I127" s="31"/>
-      <c r="J127" s="62"/>
-      <c r="K127" s="63"/>
-      <c r="L127" s="64"/>
-    </row>
-    <row r="128" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J127" s="80"/>
+      <c r="K127" s="81"/>
+      <c r="L127" s="82"/>
+    </row>
+    <row r="128" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B128" s="35"/>
       <c r="C128" s="35"/>
       <c r="D128" s="35"/>
@@ -8167,78 +8167,75 @@
       <c r="K128" s="35"/>
       <c r="L128" s="35"/>
     </row>
-    <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B129" s="87"/>
-      <c r="C129" s="88"/>
+    <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B129" s="70"/>
+      <c r="C129" s="71"/>
       <c r="D129" s="34"/>
       <c r="E129" s="31"/>
-      <c r="F129" s="87"/>
-      <c r="G129" s="88"/>
+      <c r="F129" s="70"/>
+      <c r="G129" s="71"/>
       <c r="H129" s="34"/>
       <c r="I129" s="32"/>
-      <c r="J129" s="87"/>
-      <c r="K129" s="88"/>
+      <c r="J129" s="70"/>
+      <c r="K129" s="71"/>
       <c r="L129" s="34"/>
     </row>
-    <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B130" s="84"/>
-      <c r="C130" s="85"/>
-      <c r="D130" s="86"/>
+    <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B130" s="72"/>
+      <c r="C130" s="73"/>
+      <c r="D130" s="74"/>
       <c r="E130" s="32"/>
-      <c r="F130" s="84"/>
-      <c r="G130" s="85"/>
-      <c r="H130" s="86"/>
+      <c r="F130" s="72"/>
+      <c r="G130" s="73"/>
+      <c r="H130" s="74"/>
       <c r="I130" s="32"/>
-      <c r="J130" s="84"/>
-      <c r="K130" s="85"/>
-      <c r="L130" s="86"/>
-    </row>
-    <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B131" s="71"/>
-      <c r="C131" s="72"/>
-      <c r="D131" s="73"/>
+      <c r="J130" s="72"/>
+      <c r="K130" s="73"/>
+      <c r="L130" s="74"/>
+    </row>
+    <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B131" s="83"/>
+      <c r="C131" s="84"/>
+      <c r="D131" s="85"/>
       <c r="E131" s="35"/>
-      <c r="F131" s="71"/>
-      <c r="G131" s="72"/>
-      <c r="H131" s="73"/>
+      <c r="F131" s="83"/>
+      <c r="G131" s="84"/>
+      <c r="H131" s="85"/>
       <c r="I131" s="32"/>
-      <c r="J131" s="71"/>
-      <c r="K131" s="72"/>
-      <c r="L131" s="73"/>
-    </row>
-    <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B132" s="65"/>
-      <c r="C132" s="66"/>
-      <c r="D132" s="67"/>
+      <c r="J131" s="83"/>
+      <c r="K131" s="84"/>
+      <c r="L131" s="85"/>
+    </row>
+    <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B132" s="89"/>
+      <c r="C132" s="90"/>
+      <c r="D132" s="91"/>
       <c r="E132" s="35"/>
-      <c r="F132" s="65"/>
-      <c r="G132" s="66"/>
-      <c r="H132" s="67"/>
+      <c r="F132" s="89"/>
+      <c r="G132" s="90"/>
+      <c r="H132" s="91"/>
       <c r="I132" s="31"/>
-      <c r="J132" s="65"/>
-      <c r="K132" s="66"/>
-      <c r="L132" s="67"/>
-    </row>
-    <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B133" s="62"/>
-      <c r="C133" s="63"/>
-      <c r="D133" s="64"/>
+      <c r="J132" s="89"/>
+      <c r="K132" s="90"/>
+      <c r="L132" s="91"/>
+    </row>
+    <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B133" s="80"/>
+      <c r="C133" s="81"/>
+      <c r="D133" s="82"/>
       <c r="E133" s="31"/>
-      <c r="F133" s="62"/>
-      <c r="G133" s="63"/>
-      <c r="H133" s="64"/>
+      <c r="F133" s="80"/>
+      <c r="G133" s="81"/>
+      <c r="H133" s="82"/>
       <c r="I133" s="31"/>
-      <c r="J133" s="62"/>
-      <c r="K133" s="63"/>
-      <c r="L133" s="64"/>
+      <c r="J133" s="80"/>
+      <c r="K133" s="81"/>
+      <c r="L133" s="82"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0" selectUnlockedCells="1"/>
   <dataConsolidate/>
   <mergeCells count="862">
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="F48:H48"/>
     <mergeCell ref="B46:D46"/>
     <mergeCell ref="F97:H97"/>
     <mergeCell ref="J97:L97"/>
@@ -8260,7 +8257,6 @@
     <mergeCell ref="F95:H95"/>
     <mergeCell ref="F94:H94"/>
     <mergeCell ref="B52:C52"/>
-    <mergeCell ref="F41:H41"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="F40:H40"/>
@@ -8283,17 +8279,8 @@
     <mergeCell ref="B42:D42"/>
     <mergeCell ref="F42:H42"/>
     <mergeCell ref="R44:T44"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="J39:L39"/>
-    <mergeCell ref="F45:G45"/>
     <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="F46:H46"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="F23:H23"/>
     <mergeCell ref="J23:L23"/>
@@ -8316,6 +8303,17 @@
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="B34:C34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="J39:L39"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="F41:H41"/>
     <mergeCell ref="AD69:AF69"/>
     <mergeCell ref="AH69:AJ69"/>
     <mergeCell ref="AD64:AF64"/>
@@ -8868,9 +8866,6 @@
     <mergeCell ref="R88:T88"/>
     <mergeCell ref="V84:X84"/>
     <mergeCell ref="J84:L84"/>
-    <mergeCell ref="V41:X41"/>
-    <mergeCell ref="V40:X40"/>
-    <mergeCell ref="J106:L106"/>
     <mergeCell ref="V102:X102"/>
     <mergeCell ref="R68:T68"/>
     <mergeCell ref="V68:X68"/>
@@ -8884,6 +8879,12 @@
     <mergeCell ref="N87:O87"/>
     <mergeCell ref="J88:L88"/>
     <mergeCell ref="J85:L85"/>
+    <mergeCell ref="J101:L101"/>
+    <mergeCell ref="R102:T102"/>
+    <mergeCell ref="R100:T100"/>
+    <mergeCell ref="V100:X100"/>
+    <mergeCell ref="R101:T101"/>
+    <mergeCell ref="N100:P100"/>
     <mergeCell ref="Z12:AA12"/>
     <mergeCell ref="B133:D133"/>
     <mergeCell ref="F133:H133"/>
@@ -8908,9 +8909,6 @@
     <mergeCell ref="J126:L126"/>
     <mergeCell ref="F117:G117"/>
     <mergeCell ref="J117:K117"/>
-    <mergeCell ref="F121:H121"/>
-    <mergeCell ref="J123:K123"/>
-    <mergeCell ref="F112:H112"/>
     <mergeCell ref="B125:D125"/>
     <mergeCell ref="F125:H125"/>
     <mergeCell ref="J121:L121"/>
@@ -8920,13 +8918,10 @@
     <mergeCell ref="B115:D115"/>
     <mergeCell ref="F115:H115"/>
     <mergeCell ref="J115:L115"/>
-    <mergeCell ref="B112:D112"/>
     <mergeCell ref="F120:H120"/>
     <mergeCell ref="J120:L120"/>
-    <mergeCell ref="J101:L101"/>
     <mergeCell ref="J118:L118"/>
     <mergeCell ref="B124:D124"/>
-    <mergeCell ref="F108:H108"/>
     <mergeCell ref="F124:H124"/>
     <mergeCell ref="B117:C117"/>
     <mergeCell ref="B111:C111"/>
@@ -8946,6 +8941,10 @@
     <mergeCell ref="B114:D114"/>
     <mergeCell ref="F114:H114"/>
     <mergeCell ref="J114:L114"/>
+    <mergeCell ref="F121:H121"/>
+    <mergeCell ref="J123:K123"/>
+    <mergeCell ref="F112:H112"/>
+    <mergeCell ref="B112:D112"/>
     <mergeCell ref="F107:H107"/>
     <mergeCell ref="J102:L102"/>
     <mergeCell ref="J112:L112"/>
@@ -8964,11 +8963,8 @@
     <mergeCell ref="F109:H109"/>
     <mergeCell ref="B108:D108"/>
     <mergeCell ref="J105:K105"/>
-    <mergeCell ref="R102:T102"/>
-    <mergeCell ref="R100:T100"/>
-    <mergeCell ref="V100:X100"/>
-    <mergeCell ref="R101:T101"/>
-    <mergeCell ref="N100:P100"/>
+    <mergeCell ref="F108:H108"/>
+    <mergeCell ref="J106:L106"/>
     <mergeCell ref="Z100:AB100"/>
     <mergeCell ref="N94:P94"/>
     <mergeCell ref="R95:T95"/>
@@ -9002,7 +8998,6 @@
     <mergeCell ref="F79:H79"/>
     <mergeCell ref="F71:H71"/>
     <mergeCell ref="F85:H85"/>
-    <mergeCell ref="F75:G75"/>
     <mergeCell ref="B100:D100"/>
     <mergeCell ref="F100:H100"/>
     <mergeCell ref="B83:D83"/>
@@ -9059,12 +9054,18 @@
     <mergeCell ref="J56:L56"/>
     <mergeCell ref="N61:P61"/>
     <mergeCell ref="R57:T57"/>
-    <mergeCell ref="N38:O38"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R41:T41"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R42:T42"/>
-    <mergeCell ref="V52:W52"/>
+    <mergeCell ref="F64:H64"/>
+    <mergeCell ref="F78:H78"/>
+    <mergeCell ref="F60:H60"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="R71:T71"/>
+    <mergeCell ref="N71:P71"/>
+    <mergeCell ref="R76:T76"/>
+    <mergeCell ref="N69:P69"/>
+    <mergeCell ref="R63:T63"/>
+    <mergeCell ref="N68:P68"/>
+    <mergeCell ref="F75:G75"/>
     <mergeCell ref="J81:K81"/>
     <mergeCell ref="J77:L77"/>
     <mergeCell ref="J76:L76"/>
@@ -9076,28 +9077,27 @@
     <mergeCell ref="J47:L47"/>
     <mergeCell ref="J79:L79"/>
     <mergeCell ref="J71:L71"/>
-    <mergeCell ref="F64:H64"/>
-    <mergeCell ref="F78:H78"/>
     <mergeCell ref="R50:T50"/>
     <mergeCell ref="N49:P49"/>
     <mergeCell ref="N50:P50"/>
     <mergeCell ref="J52:K52"/>
-    <mergeCell ref="F60:H60"/>
-    <mergeCell ref="F57:H57"/>
     <mergeCell ref="J60:L60"/>
     <mergeCell ref="J78:L78"/>
     <mergeCell ref="J59:K59"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="R71:T71"/>
-    <mergeCell ref="N71:P71"/>
-    <mergeCell ref="R76:T76"/>
-    <mergeCell ref="N69:P69"/>
-    <mergeCell ref="R63:T63"/>
-    <mergeCell ref="N68:P68"/>
     <mergeCell ref="J53:L53"/>
     <mergeCell ref="F53:H53"/>
     <mergeCell ref="F52:G52"/>
     <mergeCell ref="F49:H49"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R41:T41"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R42:T42"/>
+    <mergeCell ref="V52:W52"/>
+    <mergeCell ref="V41:X41"/>
+    <mergeCell ref="V40:X40"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="F48:H48"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="D29:D34 AJ29:AJ34 T29:T34 P29:P34 X29:X34 AF29:AF34 AN29:AN34 H29:H34 L29:L34 AB29:AB34">

--- a/Gorev-Listesi.xlsx
+++ b/Gorev-Listesi.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="118">
   <si>
     <t>CUMA</t>
   </si>
@@ -362,9 +362,6 @@
     <t>09.30</t>
   </si>
   <si>
-    <t>Ulus</t>
-  </si>
-  <si>
     <t>D.A.SALTIK.</t>
   </si>
   <si>
@@ -372,6 +369,28 @@
   </si>
   <si>
     <t>VOLEYBOL (EUROCUP)</t>
+  </si>
+  <si>
+    <t>E.SAVAŞ.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ulus   </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>İPTAL</t>
+    </r>
+  </si>
+  <si>
+    <t>BİR ROMAN KAHRAMANI GİBİ</t>
   </si>
 </sst>
 </file>
@@ -1416,7 +1435,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1584,6 +1603,39 @@
     <xf numFmtId="49" fontId="11" fillId="4" borderId="13" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="14" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1605,6 +1657,75 @@
     <xf numFmtId="49" fontId="11" fillId="7" borderId="9" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="12" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="13" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="18" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="11" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="12" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="13" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="7" borderId="11" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1614,247 +1735,163 @@
     <xf numFmtId="49" fontId="11" fillId="7" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="14" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="14" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="15" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="16" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="37" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="12" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="38" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="13" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="8" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="9" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="10" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="17" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="18" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="11" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="12" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="13" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="18" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="9" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="14" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="15" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="9" xfId="57" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="11" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="12" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="18" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="11" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="12" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="13" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="17" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="18" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="8" borderId="8" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="8" borderId="9" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="8" borderId="10" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="37" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="38" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="16" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="11" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="12" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="13" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="18" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="13" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2306,65 +2343,65 @@
   <sheetData>
     <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12"/>
-      <c r="B1" s="107" t="s">
+      <c r="B1" s="145" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
       <c r="E1" s="10"/>
-      <c r="F1" s="108" t="s">
+      <c r="F1" s="146" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
+      <c r="G1" s="146"/>
+      <c r="H1" s="146"/>
       <c r="I1" s="10"/>
-      <c r="J1" s="108" t="s">
+      <c r="J1" s="146" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="108"/>
-      <c r="L1" s="109"/>
+      <c r="K1" s="146"/>
+      <c r="L1" s="147"/>
       <c r="M1" s="12"/>
-      <c r="N1" s="112" t="s">
+      <c r="N1" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
+      <c r="O1" s="144"/>
+      <c r="P1" s="144"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="102" t="s">
+      <c r="R1" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
+      <c r="S1" s="144"/>
+      <c r="T1" s="144"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="102" t="s">
+      <c r="V1" s="144" t="s">
         <v>5</v>
       </c>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
+      <c r="W1" s="144"/>
+      <c r="X1" s="144"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="102" t="s">
+      <c r="Z1" s="144" t="s">
         <v>6</v>
       </c>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
+      <c r="AA1" s="144"/>
+      <c r="AB1" s="144"/>
       <c r="AC1" s="1"/>
-      <c r="AD1" s="102" t="s">
+      <c r="AD1" s="144" t="s">
         <v>0</v>
       </c>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="102"/>
+      <c r="AE1" s="144"/>
+      <c r="AF1" s="144"/>
       <c r="AG1" s="1"/>
-      <c r="AH1" s="102" t="s">
+      <c r="AH1" s="144" t="s">
         <v>1</v>
       </c>
-      <c r="AI1" s="102"/>
-      <c r="AJ1" s="102"/>
+      <c r="AI1" s="144"/>
+      <c r="AJ1" s="144"/>
       <c r="AK1" s="1"/>
-      <c r="AL1" s="102" t="s">
+      <c r="AL1" s="144" t="s">
         <v>2</v>
       </c>
-      <c r="AM1" s="102"/>
-      <c r="AN1" s="103"/>
+      <c r="AM1" s="144"/>
+      <c r="AN1" s="154"/>
       <c r="AO1" s="12"/>
       <c r="AP1" s="12"/>
       <c r="AQ1" s="12"/>
@@ -2372,74 +2409,74 @@
     </row>
     <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
-      <c r="B2" s="110">
+      <c r="B2" s="148">
         <f>N2-3</f>
         <v>46283</v>
       </c>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
       <c r="E2" s="11"/>
-      <c r="F2" s="111">
+      <c r="F2" s="149">
         <f>N2-2</f>
         <v>46284</v>
       </c>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="111">
+      <c r="J2" s="149">
         <f>N2-1</f>
         <v>46285</v>
       </c>
-      <c r="K2" s="111"/>
-      <c r="L2" s="121"/>
+      <c r="K2" s="149"/>
+      <c r="L2" s="152"/>
       <c r="M2" s="12"/>
-      <c r="N2" s="115">
+      <c r="N2" s="151">
         <v>46286</v>
       </c>
-      <c r="O2" s="104"/>
-      <c r="P2" s="104"/>
+      <c r="O2" s="137"/>
+      <c r="P2" s="137"/>
       <c r="Q2" s="53"/>
-      <c r="R2" s="104">
+      <c r="R2" s="137">
         <f>N2+1</f>
         <v>46287</v>
       </c>
-      <c r="S2" s="104"/>
-      <c r="T2" s="104"/>
+      <c r="S2" s="137"/>
+      <c r="T2" s="137"/>
       <c r="U2" s="53"/>
-      <c r="V2" s="104">
+      <c r="V2" s="137">
         <f>N2+2</f>
         <v>46288</v>
       </c>
-      <c r="W2" s="104"/>
-      <c r="X2" s="104"/>
+      <c r="W2" s="137"/>
+      <c r="X2" s="137"/>
       <c r="Y2" s="53"/>
-      <c r="Z2" s="104">
+      <c r="Z2" s="137">
         <f>N2+3</f>
         <v>46289</v>
       </c>
-      <c r="AA2" s="104"/>
-      <c r="AB2" s="104"/>
+      <c r="AA2" s="137"/>
+      <c r="AB2" s="137"/>
       <c r="AC2" s="53"/>
-      <c r="AD2" s="104">
+      <c r="AD2" s="137">
         <f>N2+4</f>
         <v>46290</v>
       </c>
-      <c r="AE2" s="104"/>
-      <c r="AF2" s="104"/>
+      <c r="AE2" s="137"/>
+      <c r="AF2" s="137"/>
       <c r="AG2" s="53"/>
-      <c r="AH2" s="104">
+      <c r="AH2" s="137">
         <f>N2+5</f>
         <v>46291</v>
       </c>
-      <c r="AI2" s="104"/>
-      <c r="AJ2" s="104"/>
+      <c r="AI2" s="137"/>
+      <c r="AJ2" s="137"/>
       <c r="AK2" s="53"/>
-      <c r="AL2" s="104">
+      <c r="AL2" s="137">
         <f>N2+6</f>
         <v>46292</v>
       </c>
-      <c r="AM2" s="104"/>
-      <c r="AN2" s="105"/>
+      <c r="AM2" s="137"/>
+      <c r="AN2" s="155"/>
       <c r="AO2" s="12"/>
       <c r="AP2" s="12"/>
       <c r="AQ2" s="12"/>
@@ -2493,47 +2530,47 @@
     </row>
     <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="12"/>
-      <c r="B4" s="106"/>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="106"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="106"/>
-      <c r="K4" s="106"/>
-      <c r="L4" s="106"/>
+      <c r="B4" s="153"/>
+      <c r="C4" s="153"/>
+      <c r="D4" s="153"/>
+      <c r="E4" s="153"/>
+      <c r="F4" s="153"/>
+      <c r="G4" s="153"/>
+      <c r="H4" s="153"/>
+      <c r="I4" s="153"/>
+      <c r="J4" s="153"/>
+      <c r="K4" s="153"/>
+      <c r="L4" s="153"/>
       <c r="M4" s="14"/>
-      <c r="N4" s="101" t="s">
+      <c r="N4" s="124" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="101"/>
-      <c r="P4" s="101"/>
-      <c r="Q4" s="101"/>
-      <c r="R4" s="101"/>
-      <c r="S4" s="101"/>
-      <c r="T4" s="101"/>
-      <c r="U4" s="101"/>
-      <c r="V4" s="101"/>
-      <c r="W4" s="101"/>
-      <c r="X4" s="101"/>
-      <c r="Y4" s="101"/>
-      <c r="Z4" s="101"/>
-      <c r="AA4" s="101"/>
-      <c r="AB4" s="101"/>
+      <c r="O4" s="124"/>
+      <c r="P4" s="124"/>
+      <c r="Q4" s="124"/>
+      <c r="R4" s="124"/>
+      <c r="S4" s="124"/>
+      <c r="T4" s="124"/>
+      <c r="U4" s="124"/>
+      <c r="V4" s="124"/>
+      <c r="W4" s="124"/>
+      <c r="X4" s="124"/>
+      <c r="Y4" s="124"/>
+      <c r="Z4" s="124"/>
+      <c r="AA4" s="124"/>
+      <c r="AB4" s="124"/>
       <c r="AC4" s="33"/>
-      <c r="AD4" s="106"/>
-      <c r="AE4" s="106"/>
-      <c r="AF4" s="106"/>
-      <c r="AG4" s="106"/>
-      <c r="AH4" s="106"/>
-      <c r="AI4" s="106"/>
-      <c r="AJ4" s="106"/>
-      <c r="AK4" s="106"/>
-      <c r="AL4" s="106"/>
-      <c r="AM4" s="106"/>
-      <c r="AN4" s="106"/>
+      <c r="AD4" s="153"/>
+      <c r="AE4" s="153"/>
+      <c r="AF4" s="153"/>
+      <c r="AG4" s="153"/>
+      <c r="AH4" s="153"/>
+      <c r="AI4" s="153"/>
+      <c r="AJ4" s="153"/>
+      <c r="AK4" s="153"/>
+      <c r="AL4" s="153"/>
+      <c r="AM4" s="153"/>
+      <c r="AN4" s="153"/>
       <c r="AO4" s="12"/>
       <c r="AP4" s="12"/>
       <c r="AQ4" s="12"/>
@@ -2541,111 +2578,111 @@
     </row>
     <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12"/>
-      <c r="B5" s="106"/>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="106"/>
-      <c r="F5" s="106"/>
-      <c r="G5" s="106"/>
-      <c r="H5" s="106"/>
-      <c r="I5" s="106"/>
-      <c r="J5" s="106"/>
-      <c r="K5" s="106"/>
-      <c r="L5" s="106"/>
+      <c r="B5" s="153"/>
+      <c r="C5" s="153"/>
+      <c r="D5" s="153"/>
+      <c r="E5" s="153"/>
+      <c r="F5" s="153"/>
+      <c r="G5" s="153"/>
+      <c r="H5" s="153"/>
+      <c r="I5" s="153"/>
+      <c r="J5" s="153"/>
+      <c r="K5" s="153"/>
+      <c r="L5" s="153"/>
       <c r="M5" s="14"/>
-      <c r="N5" s="101"/>
-      <c r="O5" s="101"/>
-      <c r="P5" s="101"/>
-      <c r="Q5" s="101"/>
-      <c r="R5" s="101"/>
-      <c r="S5" s="101"/>
-      <c r="T5" s="101"/>
-      <c r="U5" s="101"/>
-      <c r="V5" s="101"/>
-      <c r="W5" s="101"/>
-      <c r="X5" s="101"/>
-      <c r="Y5" s="101"/>
-      <c r="Z5" s="101"/>
-      <c r="AA5" s="101"/>
-      <c r="AB5" s="101"/>
+      <c r="N5" s="124"/>
+      <c r="O5" s="124"/>
+      <c r="P5" s="124"/>
+      <c r="Q5" s="124"/>
+      <c r="R5" s="124"/>
+      <c r="S5" s="124"/>
+      <c r="T5" s="124"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="124"/>
+      <c r="W5" s="124"/>
+      <c r="X5" s="124"/>
+      <c r="Y5" s="124"/>
+      <c r="Z5" s="124"/>
+      <c r="AA5" s="124"/>
+      <c r="AB5" s="124"/>
       <c r="AC5" s="33"/>
-      <c r="AD5" s="106"/>
-      <c r="AE5" s="106"/>
-      <c r="AF5" s="106"/>
-      <c r="AG5" s="106"/>
-      <c r="AH5" s="106"/>
-      <c r="AI5" s="106"/>
-      <c r="AJ5" s="106"/>
-      <c r="AK5" s="106"/>
-      <c r="AL5" s="106"/>
-      <c r="AM5" s="106"/>
-      <c r="AN5" s="106"/>
+      <c r="AD5" s="153"/>
+      <c r="AE5" s="153"/>
+      <c r="AF5" s="153"/>
+      <c r="AG5" s="153"/>
+      <c r="AH5" s="153"/>
+      <c r="AI5" s="153"/>
+      <c r="AJ5" s="153"/>
+      <c r="AK5" s="153"/>
+      <c r="AL5" s="153"/>
+      <c r="AM5" s="153"/>
+      <c r="AN5" s="153"/>
       <c r="AO5" s="12"/>
       <c r="AP5" s="12"/>
       <c r="AQ5" s="12"/>
       <c r="AR5" s="13"/>
     </row>
     <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="65" t="s">
+      <c r="B6" s="76" t="s">
         <v>57</v>
       </c>
-      <c r="C6" s="66"/>
+      <c r="C6" s="77"/>
       <c r="D6" s="57" t="s">
         <v>55</v>
       </c>
       <c r="E6" s="39"/>
-      <c r="F6" s="119" t="s">
+      <c r="F6" s="117" t="s">
         <v>57</v>
       </c>
-      <c r="G6" s="120"/>
+      <c r="G6" s="118"/>
       <c r="H6" s="59" t="s">
         <v>55</v>
       </c>
       <c r="I6" s="36"/>
-      <c r="J6" s="119" t="s">
+      <c r="J6" s="117" t="s">
         <v>57</v>
       </c>
-      <c r="K6" s="120"/>
+      <c r="K6" s="118"/>
       <c r="L6" s="59" t="s">
         <v>55</v>
       </c>
       <c r="M6" s="3"/>
-      <c r="N6" s="70"/>
-      <c r="O6" s="71"/>
+      <c r="N6" s="81"/>
+      <c r="O6" s="82"/>
       <c r="P6" s="34"/>
       <c r="Q6" s="39"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="71"/>
+      <c r="R6" s="81"/>
+      <c r="S6" s="82"/>
       <c r="T6" s="34"/>
       <c r="U6" s="36"/>
-      <c r="V6" s="70"/>
-      <c r="W6" s="71"/>
+      <c r="V6" s="81"/>
+      <c r="W6" s="82"/>
       <c r="X6" s="34"/>
       <c r="Y6" s="23"/>
-      <c r="Z6" s="70" t="s">
+      <c r="Z6" s="81" t="s">
         <v>44</v>
       </c>
-      <c r="AA6" s="71"/>
+      <c r="AA6" s="82"/>
       <c r="AB6" s="34" t="s">
         <v>85</v>
       </c>
       <c r="AC6" s="36"/>
-      <c r="AD6" s="70"/>
-      <c r="AE6" s="71"/>
+      <c r="AD6" s="81"/>
+      <c r="AE6" s="82"/>
       <c r="AF6" s="34"/>
       <c r="AG6" s="39"/>
-      <c r="AH6" s="70" t="s">
+      <c r="AH6" s="81" t="s">
         <v>57</v>
       </c>
-      <c r="AI6" s="71"/>
+      <c r="AI6" s="82"/>
       <c r="AJ6" s="34" t="s">
         <v>55</v>
       </c>
       <c r="AK6" s="36"/>
-      <c r="AL6" s="70" t="s">
+      <c r="AL6" s="81" t="s">
         <v>57</v>
       </c>
-      <c r="AM6" s="71"/>
+      <c r="AM6" s="82"/>
       <c r="AN6" s="34" t="s">
         <v>55</v>
       </c>
@@ -2659,20 +2696,20 @@
       <c r="AR6" s="30"/>
     </row>
     <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="77"/>
-      <c r="C7" s="78"/>
+      <c r="B7" s="73"/>
+      <c r="C7" s="74"/>
       <c r="D7" s="61"/>
       <c r="E7" s="38"/>
-      <c r="F7" s="113" t="s">
+      <c r="F7" s="114" t="s">
         <v>86</v>
       </c>
-      <c r="G7" s="114"/>
+      <c r="G7" s="115"/>
       <c r="H7" s="60"/>
       <c r="I7" s="36"/>
-      <c r="J7" s="113" t="s">
+      <c r="J7" s="114" t="s">
         <v>86</v>
       </c>
-      <c r="K7" s="114"/>
+      <c r="K7" s="115"/>
       <c r="L7" s="60"/>
       <c r="M7" s="3"/>
       <c r="N7" s="83"/>
@@ -2714,57 +2751,57 @@
       <c r="AR7" s="30"/>
     </row>
     <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="67" t="s">
+      <c r="B8" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="69"/>
+      <c r="C8" s="79"/>
+      <c r="D8" s="80"/>
       <c r="E8" s="35"/>
-      <c r="F8" s="116" t="s">
+      <c r="F8" s="141" t="s">
         <v>87</v>
       </c>
-      <c r="G8" s="117"/>
-      <c r="H8" s="118"/>
+      <c r="G8" s="142"/>
+      <c r="H8" s="143"/>
       <c r="I8" s="37"/>
-      <c r="J8" s="116" t="s">
+      <c r="J8" s="141" t="s">
         <v>109</v>
       </c>
-      <c r="K8" s="117"/>
-      <c r="L8" s="118"/>
+      <c r="K8" s="142"/>
+      <c r="L8" s="143"/>
       <c r="M8" s="3"/>
-      <c r="N8" s="89"/>
-      <c r="O8" s="90"/>
-      <c r="P8" s="91"/>
+      <c r="N8" s="70"/>
+      <c r="O8" s="71"/>
+      <c r="P8" s="72"/>
       <c r="Q8" s="35"/>
-      <c r="R8" s="89"/>
-      <c r="S8" s="90"/>
-      <c r="T8" s="91"/>
+      <c r="R8" s="70"/>
+      <c r="S8" s="71"/>
+      <c r="T8" s="72"/>
       <c r="U8" s="37"/>
-      <c r="V8" s="89"/>
-      <c r="W8" s="90"/>
-      <c r="X8" s="91"/>
+      <c r="V8" s="70"/>
+      <c r="W8" s="71"/>
+      <c r="X8" s="72"/>
       <c r="Y8" s="35"/>
-      <c r="Z8" s="89" t="s">
+      <c r="Z8" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="AA8" s="90"/>
-      <c r="AB8" s="91"/>
+      <c r="AA8" s="71"/>
+      <c r="AB8" s="72"/>
       <c r="AC8" s="35"/>
-      <c r="AD8" s="89"/>
-      <c r="AE8" s="90"/>
-      <c r="AF8" s="91"/>
+      <c r="AD8" s="70"/>
+      <c r="AE8" s="71"/>
+      <c r="AF8" s="72"/>
       <c r="AG8" s="35"/>
-      <c r="AH8" s="89" t="s">
+      <c r="AH8" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="AI8" s="90"/>
-      <c r="AJ8" s="91"/>
+      <c r="AI8" s="71"/>
+      <c r="AJ8" s="72"/>
       <c r="AK8" s="37"/>
-      <c r="AL8" s="89" t="s">
+      <c r="AL8" s="70" t="s">
         <v>37</v>
       </c>
-      <c r="AM8" s="90"/>
-      <c r="AN8" s="91"/>
+      <c r="AM8" s="71"/>
+      <c r="AN8" s="72"/>
       <c r="AP8" s="46" t="s">
         <v>16</v>
       </c>
@@ -2775,51 +2812,51 @@
       <c r="AR8" s="30"/>
     </row>
     <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="67"/>
-      <c r="C9" s="68"/>
-      <c r="D9" s="69"/>
+      <c r="B9" s="78"/>
+      <c r="C9" s="79"/>
+      <c r="D9" s="80"/>
       <c r="E9" s="43"/>
       <c r="F9" s="128"/>
       <c r="G9" s="129"/>
       <c r="H9" s="130"/>
       <c r="I9" s="43"/>
-      <c r="J9" s="125" t="s">
+      <c r="J9" s="134" t="s">
         <v>79</v>
       </c>
-      <c r="K9" s="126"/>
-      <c r="L9" s="127"/>
+      <c r="K9" s="135"/>
+      <c r="L9" s="136"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="67"/>
-      <c r="O9" s="68"/>
-      <c r="P9" s="69"/>
+      <c r="N9" s="78"/>
+      <c r="O9" s="79"/>
+      <c r="P9" s="80"/>
       <c r="Q9" s="43"/>
-      <c r="R9" s="67"/>
-      <c r="S9" s="68"/>
-      <c r="T9" s="69"/>
+      <c r="R9" s="78"/>
+      <c r="S9" s="79"/>
+      <c r="T9" s="80"/>
       <c r="U9" s="44"/>
-      <c r="V9" s="67"/>
-      <c r="W9" s="68"/>
-      <c r="X9" s="69"/>
+      <c r="V9" s="78"/>
+      <c r="W9" s="79"/>
+      <c r="X9" s="80"/>
       <c r="Y9" s="43"/>
-      <c r="Z9" s="67"/>
-      <c r="AA9" s="68"/>
-      <c r="AB9" s="69"/>
+      <c r="Z9" s="78"/>
+      <c r="AA9" s="79"/>
+      <c r="AB9" s="80"/>
       <c r="AC9" s="43"/>
-      <c r="AD9" s="67"/>
-      <c r="AE9" s="68"/>
-      <c r="AF9" s="69"/>
+      <c r="AD9" s="78"/>
+      <c r="AE9" s="79"/>
+      <c r="AF9" s="80"/>
       <c r="AG9" s="43"/>
-      <c r="AH9" s="67" t="s">
+      <c r="AH9" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="AI9" s="68"/>
-      <c r="AJ9" s="69"/>
+      <c r="AI9" s="79"/>
+      <c r="AJ9" s="80"/>
       <c r="AK9" s="43"/>
-      <c r="AL9" s="67" t="s">
+      <c r="AL9" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="AM9" s="68"/>
-      <c r="AN9" s="69"/>
+      <c r="AM9" s="79"/>
+      <c r="AN9" s="80"/>
       <c r="AP9" s="46" t="s">
         <v>11</v>
       </c>
@@ -2838,11 +2875,11 @@
       <c r="G10" s="132"/>
       <c r="H10" s="133"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="122" t="s">
+      <c r="J10" s="138" t="s">
         <v>88</v>
       </c>
-      <c r="K10" s="123"/>
-      <c r="L10" s="124"/>
+      <c r="K10" s="139"/>
+      <c r="L10" s="140"/>
       <c r="M10" s="5"/>
       <c r="N10" s="92"/>
       <c r="O10" s="93"/>
@@ -2930,52 +2967,52 @@
       <c r="AR11" s="30"/>
     </row>
     <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="75"/>
-      <c r="C12" s="76"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="69"/>
       <c r="D12" s="55"/>
       <c r="E12" s="39"/>
-      <c r="F12" s="75" t="s">
+      <c r="F12" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="76"/>
+      <c r="G12" s="69"/>
       <c r="H12" s="55" t="s">
         <v>48</v>
       </c>
       <c r="I12" s="36"/>
-      <c r="J12" s="75"/>
-      <c r="K12" s="76"/>
+      <c r="J12" s="68"/>
+      <c r="K12" s="69"/>
       <c r="L12" s="55"/>
       <c r="M12" s="5"/>
-      <c r="N12" s="70"/>
-      <c r="O12" s="71"/>
+      <c r="N12" s="81"/>
+      <c r="O12" s="82"/>
       <c r="P12" s="34"/>
       <c r="Q12" s="23"/>
-      <c r="R12" s="70"/>
-      <c r="S12" s="71"/>
+      <c r="R12" s="81"/>
+      <c r="S12" s="82"/>
       <c r="T12" s="34"/>
       <c r="U12" s="36"/>
-      <c r="V12" s="70"/>
-      <c r="W12" s="71"/>
+      <c r="V12" s="81"/>
+      <c r="W12" s="82"/>
       <c r="X12" s="34"/>
       <c r="Y12" s="23"/>
-      <c r="Z12" s="70"/>
-      <c r="AA12" s="71"/>
+      <c r="Z12" s="81"/>
+      <c r="AA12" s="82"/>
       <c r="AB12" s="34"/>
       <c r="AC12" s="36"/>
-      <c r="AD12" s="70"/>
-      <c r="AE12" s="71"/>
+      <c r="AD12" s="81"/>
+      <c r="AE12" s="82"/>
       <c r="AF12" s="34"/>
       <c r="AG12" s="39"/>
-      <c r="AH12" s="70" t="s">
+      <c r="AH12" s="81" t="s">
         <v>41</v>
       </c>
-      <c r="AI12" s="71"/>
+      <c r="AI12" s="82"/>
       <c r="AJ12" s="34" t="s">
         <v>48</v>
       </c>
       <c r="AK12" s="36"/>
-      <c r="AL12" s="70"/>
-      <c r="AM12" s="71"/>
+      <c r="AL12" s="81"/>
+      <c r="AM12" s="82"/>
       <c r="AN12" s="34"/>
       <c r="AP12" s="46" t="s">
         <v>19</v>
@@ -2987,16 +3024,16 @@
       <c r="AR12" s="30"/>
     </row>
     <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="77"/>
-      <c r="C13" s="78"/>
+      <c r="B13" s="73"/>
+      <c r="C13" s="74"/>
       <c r="D13" s="61"/>
       <c r="E13" s="38"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="78"/>
+      <c r="F13" s="73"/>
+      <c r="G13" s="74"/>
       <c r="H13" s="61"/>
       <c r="I13" s="36"/>
-      <c r="J13" s="77"/>
-      <c r="K13" s="78"/>
+      <c r="J13" s="73"/>
+      <c r="K13" s="74"/>
       <c r="L13" s="61"/>
       <c r="M13" s="5"/>
       <c r="N13" s="83"/>
@@ -3036,49 +3073,49 @@
       <c r="AR13" s="30"/>
     </row>
     <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="89"/>
-      <c r="C14" s="90"/>
-      <c r="D14" s="91"/>
+      <c r="B14" s="70"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="72"/>
       <c r="E14" s="37"/>
-      <c r="F14" s="89" t="s">
+      <c r="F14" s="70" t="s">
         <v>37</v>
       </c>
-      <c r="G14" s="90"/>
-      <c r="H14" s="91"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="72"/>
       <c r="I14" s="35"/>
-      <c r="J14" s="89"/>
-      <c r="K14" s="90"/>
-      <c r="L14" s="91"/>
+      <c r="J14" s="70"/>
+      <c r="K14" s="71"/>
+      <c r="L14" s="72"/>
       <c r="M14" s="3"/>
-      <c r="N14" s="89"/>
-      <c r="O14" s="90"/>
-      <c r="P14" s="91"/>
+      <c r="N14" s="70"/>
+      <c r="O14" s="71"/>
+      <c r="P14" s="72"/>
       <c r="Q14" s="35"/>
-      <c r="R14" s="89"/>
-      <c r="S14" s="90"/>
-      <c r="T14" s="91"/>
+      <c r="R14" s="70"/>
+      <c r="S14" s="71"/>
+      <c r="T14" s="72"/>
       <c r="U14" s="37"/>
-      <c r="V14" s="89"/>
-      <c r="W14" s="90"/>
-      <c r="X14" s="91"/>
+      <c r="V14" s="70"/>
+      <c r="W14" s="71"/>
+      <c r="X14" s="72"/>
       <c r="Y14" s="35"/>
-      <c r="Z14" s="89"/>
-      <c r="AA14" s="90"/>
-      <c r="AB14" s="91"/>
+      <c r="Z14" s="70"/>
+      <c r="AA14" s="71"/>
+      <c r="AB14" s="72"/>
       <c r="AC14" s="37"/>
-      <c r="AD14" s="89"/>
-      <c r="AE14" s="90"/>
-      <c r="AF14" s="91"/>
+      <c r="AD14" s="70"/>
+      <c r="AE14" s="71"/>
+      <c r="AF14" s="72"/>
       <c r="AG14" s="37"/>
-      <c r="AH14" s="89" t="s">
+      <c r="AH14" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="AI14" s="90"/>
-      <c r="AJ14" s="91"/>
+      <c r="AI14" s="71"/>
+      <c r="AJ14" s="72"/>
       <c r="AK14" s="35"/>
-      <c r="AL14" s="89"/>
-      <c r="AM14" s="90"/>
-      <c r="AN14" s="91"/>
+      <c r="AL14" s="70"/>
+      <c r="AM14" s="71"/>
+      <c r="AN14" s="72"/>
       <c r="AP14" s="46" t="s">
         <v>23</v>
       </c>
@@ -3089,49 +3126,49 @@
       <c r="AR14" s="30"/>
     </row>
     <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="67"/>
-      <c r="C15" s="68"/>
-      <c r="D15" s="69"/>
+      <c r="B15" s="78"/>
+      <c r="C15" s="79"/>
+      <c r="D15" s="80"/>
       <c r="E15" s="44"/>
-      <c r="F15" s="67" t="s">
+      <c r="F15" s="78" t="s">
         <v>29</v>
       </c>
-      <c r="G15" s="68"/>
-      <c r="H15" s="69"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="80"/>
       <c r="I15" s="43"/>
-      <c r="J15" s="67"/>
-      <c r="K15" s="68"/>
-      <c r="L15" s="69"/>
+      <c r="J15" s="78"/>
+      <c r="K15" s="79"/>
+      <c r="L15" s="80"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="67"/>
-      <c r="O15" s="68"/>
-      <c r="P15" s="69"/>
+      <c r="N15" s="78"/>
+      <c r="O15" s="79"/>
+      <c r="P15" s="80"/>
       <c r="Q15" s="43"/>
-      <c r="R15" s="67"/>
-      <c r="S15" s="68"/>
-      <c r="T15" s="69"/>
+      <c r="R15" s="78"/>
+      <c r="S15" s="79"/>
+      <c r="T15" s="80"/>
       <c r="U15" s="44"/>
-      <c r="V15" s="67"/>
-      <c r="W15" s="68"/>
-      <c r="X15" s="69"/>
+      <c r="V15" s="78"/>
+      <c r="W15" s="79"/>
+      <c r="X15" s="80"/>
       <c r="Y15" s="43"/>
-      <c r="Z15" s="67"/>
-      <c r="AA15" s="68"/>
-      <c r="AB15" s="69"/>
+      <c r="Z15" s="78"/>
+      <c r="AA15" s="79"/>
+      <c r="AB15" s="80"/>
       <c r="AC15" s="43"/>
-      <c r="AD15" s="67"/>
-      <c r="AE15" s="68"/>
-      <c r="AF15" s="69"/>
+      <c r="AD15" s="78"/>
+      <c r="AE15" s="79"/>
+      <c r="AF15" s="80"/>
       <c r="AG15" s="44"/>
-      <c r="AH15" s="67" t="s">
+      <c r="AH15" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="AI15" s="68"/>
-      <c r="AJ15" s="69"/>
+      <c r="AI15" s="79"/>
+      <c r="AJ15" s="80"/>
       <c r="AK15" s="43"/>
-      <c r="AL15" s="67"/>
-      <c r="AM15" s="68"/>
-      <c r="AN15" s="69"/>
+      <c r="AL15" s="78"/>
+      <c r="AM15" s="79"/>
+      <c r="AN15" s="80"/>
       <c r="AP15" s="46" t="s">
         <v>18</v>
       </c>
@@ -3252,23 +3289,23 @@
       <c r="K18" s="33"/>
       <c r="L18" s="33"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="101" t="s">
+      <c r="N18" s="124" t="s">
         <v>49</v>
       </c>
-      <c r="O18" s="101"/>
-      <c r="P18" s="101"/>
-      <c r="Q18" s="101"/>
-      <c r="R18" s="101"/>
-      <c r="S18" s="101"/>
-      <c r="T18" s="101"/>
-      <c r="U18" s="101"/>
-      <c r="V18" s="101"/>
-      <c r="W18" s="101"/>
-      <c r="X18" s="101"/>
-      <c r="Y18" s="101"/>
-      <c r="Z18" s="101"/>
-      <c r="AA18" s="101"/>
-      <c r="AB18" s="101"/>
+      <c r="O18" s="124"/>
+      <c r="P18" s="124"/>
+      <c r="Q18" s="124"/>
+      <c r="R18" s="124"/>
+      <c r="S18" s="124"/>
+      <c r="T18" s="124"/>
+      <c r="U18" s="124"/>
+      <c r="V18" s="124"/>
+      <c r="W18" s="124"/>
+      <c r="X18" s="124"/>
+      <c r="Y18" s="124"/>
+      <c r="Z18" s="124"/>
+      <c r="AA18" s="124"/>
+      <c r="AB18" s="124"/>
       <c r="AC18" s="33"/>
       <c r="AD18" s="33"/>
       <c r="AE18" s="33"/>
@@ -3303,21 +3340,21 @@
       <c r="K19" s="33"/>
       <c r="L19" s="33"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="101"/>
-      <c r="O19" s="101"/>
-      <c r="P19" s="101"/>
-      <c r="Q19" s="101"/>
-      <c r="R19" s="101"/>
-      <c r="S19" s="101"/>
-      <c r="T19" s="101"/>
-      <c r="U19" s="101"/>
-      <c r="V19" s="101"/>
-      <c r="W19" s="101"/>
-      <c r="X19" s="101"/>
-      <c r="Y19" s="101"/>
-      <c r="Z19" s="101"/>
-      <c r="AA19" s="101"/>
-      <c r="AB19" s="101"/>
+      <c r="N19" s="124"/>
+      <c r="O19" s="124"/>
+      <c r="P19" s="124"/>
+      <c r="Q19" s="124"/>
+      <c r="R19" s="124"/>
+      <c r="S19" s="124"/>
+      <c r="T19" s="124"/>
+      <c r="U19" s="124"/>
+      <c r="V19" s="124"/>
+      <c r="W19" s="124"/>
+      <c r="X19" s="124"/>
+      <c r="Y19" s="124"/>
+      <c r="Z19" s="124"/>
+      <c r="AA19" s="124"/>
+      <c r="AB19" s="124"/>
       <c r="AC19" s="33"/>
       <c r="AD19" s="33"/>
       <c r="AE19" s="33"/>
@@ -3340,56 +3377,56 @@
       <c r="AR19" s="30"/>
     </row>
     <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="75"/>
-      <c r="C20" s="76"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="69"/>
       <c r="D20" s="55"/>
       <c r="E20" s="39"/>
-      <c r="F20" s="75" t="s">
+      <c r="F20" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="G20" s="76"/>
+      <c r="G20" s="69"/>
       <c r="H20" s="57" t="s">
         <v>89</v>
       </c>
       <c r="I20" s="36"/>
-      <c r="J20" s="75"/>
-      <c r="K20" s="76"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="69"/>
       <c r="L20" s="55"/>
       <c r="M20" s="4"/>
-      <c r="N20" s="70"/>
-      <c r="O20" s="71"/>
+      <c r="N20" s="81"/>
+      <c r="O20" s="82"/>
       <c r="P20" s="34"/>
       <c r="Q20" s="39"/>
-      <c r="R20" s="70"/>
-      <c r="S20" s="71"/>
+      <c r="R20" s="81"/>
+      <c r="S20" s="82"/>
       <c r="T20" s="34"/>
       <c r="U20" s="36"/>
-      <c r="V20" s="70" t="s">
+      <c r="V20" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="W20" s="71"/>
+      <c r="W20" s="82"/>
       <c r="X20" s="34" t="s">
         <v>46</v>
       </c>
       <c r="Y20" s="23"/>
-      <c r="Z20" s="70"/>
-      <c r="AA20" s="71"/>
+      <c r="Z20" s="81"/>
+      <c r="AA20" s="82"/>
       <c r="AB20" s="34"/>
       <c r="AC20" s="36"/>
-      <c r="AD20" s="70"/>
-      <c r="AE20" s="71"/>
+      <c r="AD20" s="81"/>
+      <c r="AE20" s="82"/>
       <c r="AF20" s="34"/>
       <c r="AG20" s="39"/>
-      <c r="AH20" s="70" t="s">
+      <c r="AH20" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="AI20" s="71"/>
+      <c r="AI20" s="82"/>
       <c r="AJ20" s="34" t="s">
         <v>65</v>
       </c>
       <c r="AK20" s="36"/>
-      <c r="AL20" s="70"/>
-      <c r="AM20" s="71"/>
+      <c r="AL20" s="81"/>
+      <c r="AM20" s="82"/>
       <c r="AN20" s="34"/>
       <c r="AP20" s="46" t="s">
         <v>26</v>
@@ -3401,16 +3438,16 @@
       <c r="AR20" s="30"/>
     </row>
     <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="77"/>
-      <c r="C21" s="78"/>
+      <c r="B21" s="73"/>
+      <c r="C21" s="74"/>
       <c r="D21" s="61"/>
       <c r="E21" s="38"/>
-      <c r="F21" s="77"/>
-      <c r="G21" s="78"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="74"/>
       <c r="H21" s="61"/>
       <c r="I21" s="36"/>
-      <c r="J21" s="77"/>
-      <c r="K21" s="78"/>
+      <c r="J21" s="73"/>
+      <c r="K21" s="74"/>
       <c r="L21" s="61"/>
       <c r="M21" s="15"/>
       <c r="N21" s="83"/>
@@ -3454,51 +3491,51 @@
       <c r="AR21" s="30"/>
     </row>
     <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="89"/>
-      <c r="C22" s="90"/>
-      <c r="D22" s="91"/>
+      <c r="B22" s="70"/>
+      <c r="C22" s="71"/>
+      <c r="D22" s="72"/>
       <c r="E22" s="35"/>
-      <c r="F22" s="134" t="s">
+      <c r="F22" s="125" t="s">
         <v>9</v>
       </c>
-      <c r="G22" s="135"/>
-      <c r="H22" s="136"/>
+      <c r="G22" s="126"/>
+      <c r="H22" s="127"/>
       <c r="I22" s="37"/>
-      <c r="J22" s="89"/>
-      <c r="K22" s="90"/>
-      <c r="L22" s="91"/>
+      <c r="J22" s="70"/>
+      <c r="K22" s="71"/>
+      <c r="L22" s="72"/>
       <c r="M22" s="4"/>
-      <c r="N22" s="89"/>
-      <c r="O22" s="90"/>
-      <c r="P22" s="91"/>
+      <c r="N22" s="70"/>
+      <c r="O22" s="71"/>
+      <c r="P22" s="72"/>
       <c r="Q22" s="35"/>
-      <c r="R22" s="89"/>
-      <c r="S22" s="90"/>
-      <c r="T22" s="91"/>
+      <c r="R22" s="70"/>
+      <c r="S22" s="71"/>
+      <c r="T22" s="72"/>
       <c r="U22" s="37"/>
-      <c r="V22" s="89" t="s">
+      <c r="V22" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="W22" s="90"/>
-      <c r="X22" s="91"/>
+      <c r="W22" s="71"/>
+      <c r="X22" s="72"/>
       <c r="Y22" s="35"/>
-      <c r="Z22" s="89"/>
-      <c r="AA22" s="90"/>
-      <c r="AB22" s="91"/>
+      <c r="Z22" s="70"/>
+      <c r="AA22" s="71"/>
+      <c r="AB22" s="72"/>
       <c r="AC22" s="35"/>
-      <c r="AD22" s="89"/>
-      <c r="AE22" s="90"/>
-      <c r="AF22" s="91"/>
+      <c r="AD22" s="70"/>
+      <c r="AE22" s="71"/>
+      <c r="AF22" s="72"/>
       <c r="AG22" s="35"/>
-      <c r="AH22" s="89" t="s">
-        <v>113</v>
-      </c>
-      <c r="AI22" s="90"/>
-      <c r="AJ22" s="91"/>
+      <c r="AH22" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="AI22" s="71"/>
+      <c r="AJ22" s="72"/>
       <c r="AK22" s="37"/>
-      <c r="AL22" s="89"/>
-      <c r="AM22" s="90"/>
-      <c r="AN22" s="91"/>
+      <c r="AL22" s="70"/>
+      <c r="AM22" s="71"/>
+      <c r="AN22" s="72"/>
       <c r="AP22" s="46" t="s">
         <v>15</v>
       </c>
@@ -3623,23 +3660,23 @@
       <c r="K25" s="33"/>
       <c r="L25" s="33"/>
       <c r="M25" s="4"/>
-      <c r="N25" s="101" t="s">
+      <c r="N25" s="124" t="s">
         <v>39</v>
       </c>
-      <c r="O25" s="101"/>
-      <c r="P25" s="101"/>
-      <c r="Q25" s="101"/>
-      <c r="R25" s="101"/>
-      <c r="S25" s="101"/>
-      <c r="T25" s="101"/>
-      <c r="U25" s="101"/>
-      <c r="V25" s="101"/>
-      <c r="W25" s="101"/>
-      <c r="X25" s="101"/>
-      <c r="Y25" s="101"/>
-      <c r="Z25" s="101"/>
-      <c r="AA25" s="101"/>
-      <c r="AB25" s="101"/>
+      <c r="O25" s="124"/>
+      <c r="P25" s="124"/>
+      <c r="Q25" s="124"/>
+      <c r="R25" s="124"/>
+      <c r="S25" s="124"/>
+      <c r="T25" s="124"/>
+      <c r="U25" s="124"/>
+      <c r="V25" s="124"/>
+      <c r="W25" s="124"/>
+      <c r="X25" s="124"/>
+      <c r="Y25" s="124"/>
+      <c r="Z25" s="124"/>
+      <c r="AA25" s="124"/>
+      <c r="AB25" s="124"/>
       <c r="AC25" s="33"/>
       <c r="AD25" s="33"/>
       <c r="AE25" s="33"/>
@@ -3674,21 +3711,21 @@
       <c r="K26" s="33"/>
       <c r="L26" s="33"/>
       <c r="M26" s="4"/>
-      <c r="N26" s="101"/>
-      <c r="O26" s="101"/>
-      <c r="P26" s="101"/>
-      <c r="Q26" s="101"/>
-      <c r="R26" s="101"/>
-      <c r="S26" s="101"/>
-      <c r="T26" s="101"/>
-      <c r="U26" s="101"/>
-      <c r="V26" s="101"/>
-      <c r="W26" s="101"/>
-      <c r="X26" s="101"/>
-      <c r="Y26" s="101"/>
-      <c r="Z26" s="101"/>
-      <c r="AA26" s="101"/>
-      <c r="AB26" s="101"/>
+      <c r="N26" s="124"/>
+      <c r="O26" s="124"/>
+      <c r="P26" s="124"/>
+      <c r="Q26" s="124"/>
+      <c r="R26" s="124"/>
+      <c r="S26" s="124"/>
+      <c r="T26" s="124"/>
+      <c r="U26" s="124"/>
+      <c r="V26" s="124"/>
+      <c r="W26" s="124"/>
+      <c r="X26" s="124"/>
+      <c r="Y26" s="124"/>
+      <c r="Z26" s="124"/>
+      <c r="AA26" s="124"/>
+      <c r="AB26" s="124"/>
       <c r="AC26" s="33"/>
       <c r="AD26" s="33"/>
       <c r="AE26" s="33"/>
@@ -3711,76 +3748,76 @@
       <c r="AR26" s="30"/>
     </row>
     <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="75" t="s">
+      <c r="B27" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="C27" s="76"/>
+      <c r="C27" s="69"/>
       <c r="D27" s="55" t="s">
         <v>54</v>
       </c>
       <c r="E27" s="36"/>
-      <c r="F27" s="75" t="s">
+      <c r="F27" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="G27" s="76"/>
+      <c r="G27" s="69"/>
       <c r="H27" s="55" t="s">
         <v>54</v>
       </c>
       <c r="I27" s="36"/>
-      <c r="J27" s="75" t="s">
+      <c r="J27" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="K27" s="76"/>
+      <c r="K27" s="69"/>
       <c r="L27" s="55" t="s">
         <v>54</v>
       </c>
       <c r="M27" s="5"/>
-      <c r="N27" s="70" t="s">
+      <c r="N27" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="O27" s="71"/>
+      <c r="O27" s="82"/>
       <c r="P27" s="34" t="s">
         <v>54</v>
       </c>
       <c r="Q27" s="36"/>
-      <c r="R27" s="70" t="s">
+      <c r="R27" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="S27" s="71"/>
+      <c r="S27" s="82"/>
       <c r="T27" s="34" t="s">
         <v>54</v>
       </c>
       <c r="U27" s="36"/>
-      <c r="V27" s="70" t="s">
+      <c r="V27" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="W27" s="71"/>
+      <c r="W27" s="82"/>
       <c r="X27" s="34" t="s">
         <v>54</v>
       </c>
       <c r="Y27" s="36"/>
-      <c r="Z27" s="70" t="s">
+      <c r="Z27" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="AA27" s="71"/>
+      <c r="AA27" s="82"/>
       <c r="AB27" s="34" t="s">
         <v>54</v>
       </c>
       <c r="AC27" s="36"/>
-      <c r="AD27" s="70" t="s">
+      <c r="AD27" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="AE27" s="71"/>
+      <c r="AE27" s="82"/>
       <c r="AF27" s="34" t="s">
         <v>54</v>
       </c>
       <c r="AG27" s="36"/>
-      <c r="AH27" s="70"/>
-      <c r="AI27" s="71"/>
+      <c r="AH27" s="81"/>
+      <c r="AI27" s="82"/>
       <c r="AJ27" s="34"/>
       <c r="AK27" s="36"/>
-      <c r="AL27" s="70"/>
-      <c r="AM27" s="71"/>
+      <c r="AL27" s="81"/>
+      <c r="AM27" s="82"/>
       <c r="AN27" s="34"/>
       <c r="AP27" s="46" t="s">
         <v>13</v>
@@ -3792,16 +3829,16 @@
       <c r="AR27" s="30"/>
     </row>
     <row r="28" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="77"/>
-      <c r="C28" s="78"/>
+      <c r="B28" s="73"/>
+      <c r="C28" s="74"/>
       <c r="D28" s="61"/>
       <c r="E28" s="38"/>
-      <c r="F28" s="77"/>
-      <c r="G28" s="78"/>
+      <c r="F28" s="73"/>
+      <c r="G28" s="74"/>
       <c r="H28" s="61"/>
       <c r="I28" s="36"/>
-      <c r="J28" s="77"/>
-      <c r="K28" s="78"/>
+      <c r="J28" s="73"/>
+      <c r="K28" s="74"/>
       <c r="L28" s="61"/>
       <c r="M28" s="5"/>
       <c r="N28" s="83"/>
@@ -3824,8 +3861,8 @@
       <c r="AE28" s="84"/>
       <c r="AF28" s="18"/>
       <c r="AG28" s="38"/>
-      <c r="AH28" s="137"/>
-      <c r="AI28" s="138"/>
+      <c r="AH28" s="122"/>
+      <c r="AI28" s="123"/>
       <c r="AJ28" s="18"/>
       <c r="AK28" s="36"/>
       <c r="AL28" s="83"/>
@@ -3841,76 +3878,76 @@
       <c r="AR28" s="30"/>
     </row>
     <row r="29" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="97" t="s">
+      <c r="B29" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="C29" s="98"/>
+      <c r="C29" s="96"/>
       <c r="D29" s="41" t="s">
         <v>32</v>
       </c>
       <c r="E29" s="37"/>
-      <c r="F29" s="97" t="s">
+      <c r="F29" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="G29" s="98"/>
+      <c r="G29" s="96"/>
       <c r="H29" s="41" t="s">
         <v>32</v>
       </c>
       <c r="I29" s="35"/>
-      <c r="J29" s="97" t="s">
+      <c r="J29" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="K29" s="98"/>
+      <c r="K29" s="96"/>
       <c r="L29" s="41" t="s">
         <v>32</v>
       </c>
       <c r="M29" s="5"/>
-      <c r="N29" s="97" t="s">
+      <c r="N29" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="O29" s="98"/>
+      <c r="O29" s="96"/>
       <c r="P29" s="41" t="s">
         <v>32</v>
       </c>
       <c r="Q29" s="35"/>
-      <c r="R29" s="97" t="s">
+      <c r="R29" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="S29" s="98"/>
+      <c r="S29" s="96"/>
       <c r="T29" s="41" t="s">
         <v>32</v>
       </c>
       <c r="U29" s="37"/>
-      <c r="V29" s="97" t="s">
+      <c r="V29" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="W29" s="98"/>
+      <c r="W29" s="96"/>
       <c r="X29" s="41" t="s">
         <v>32</v>
       </c>
       <c r="Y29" s="35"/>
-      <c r="Z29" s="97" t="s">
+      <c r="Z29" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="AA29" s="98"/>
+      <c r="AA29" s="96"/>
       <c r="AB29" s="41" t="s">
         <v>32</v>
       </c>
       <c r="AC29" s="35"/>
-      <c r="AD29" s="97" t="s">
+      <c r="AD29" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="AE29" s="98"/>
+      <c r="AE29" s="96"/>
       <c r="AF29" s="41" t="s">
         <v>32</v>
       </c>
       <c r="AG29" s="37"/>
-      <c r="AH29" s="97"/>
-      <c r="AI29" s="98"/>
+      <c r="AH29" s="95"/>
+      <c r="AI29" s="96"/>
       <c r="AJ29" s="41"/>
       <c r="AK29" s="35"/>
-      <c r="AL29" s="97"/>
-      <c r="AM29" s="98"/>
+      <c r="AL29" s="95"/>
+      <c r="AM29" s="96"/>
       <c r="AN29" s="41"/>
       <c r="AP29" s="56" t="s">
         <v>29</v>
@@ -3924,328 +3961,328 @@
       </c>
     </row>
     <row r="30" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="99" t="s">
+      <c r="B30" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="C30" s="100"/>
+      <c r="C30" s="98"/>
       <c r="D30" s="45" t="s">
         <v>33</v>
       </c>
       <c r="E30" s="43"/>
-      <c r="F30" s="99" t="s">
+      <c r="F30" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="G30" s="100"/>
+      <c r="G30" s="98"/>
       <c r="H30" s="45" t="s">
         <v>33</v>
       </c>
       <c r="I30" s="43"/>
-      <c r="J30" s="99" t="s">
+      <c r="J30" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="K30" s="100"/>
+      <c r="K30" s="98"/>
       <c r="L30" s="45" t="s">
         <v>33</v>
       </c>
       <c r="M30" s="5"/>
-      <c r="N30" s="99" t="s">
+      <c r="N30" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="O30" s="100"/>
+      <c r="O30" s="98"/>
       <c r="P30" s="45" t="s">
         <v>33</v>
       </c>
       <c r="Q30" s="43"/>
-      <c r="R30" s="99" t="s">
+      <c r="R30" s="97" t="s">
         <v>16</v>
       </c>
-      <c r="S30" s="100"/>
+      <c r="S30" s="98"/>
       <c r="T30" s="45" t="s">
         <v>33</v>
       </c>
       <c r="U30" s="43"/>
-      <c r="V30" s="99" t="s">
+      <c r="V30" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="W30" s="100"/>
+      <c r="W30" s="98"/>
       <c r="X30" s="45" t="s">
         <v>33</v>
       </c>
       <c r="Y30" s="43"/>
-      <c r="Z30" s="99" t="s">
+      <c r="Z30" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="AA30" s="100"/>
+      <c r="AA30" s="98"/>
       <c r="AB30" s="45" t="s">
         <v>33</v>
       </c>
       <c r="AC30" s="43"/>
-      <c r="AD30" s="99" t="s">
+      <c r="AD30" s="97" t="s">
         <v>16</v>
       </c>
-      <c r="AE30" s="100"/>
+      <c r="AE30" s="98"/>
       <c r="AF30" s="45" t="s">
         <v>33</v>
       </c>
       <c r="AG30" s="43"/>
-      <c r="AH30" s="148"/>
-      <c r="AI30" s="149"/>
+      <c r="AH30" s="112"/>
+      <c r="AI30" s="113"/>
       <c r="AJ30" s="45"/>
       <c r="AK30" s="43"/>
-      <c r="AL30" s="99"/>
-      <c r="AM30" s="100"/>
+      <c r="AL30" s="97"/>
+      <c r="AM30" s="98"/>
       <c r="AN30" s="45"/>
       <c r="AP30" s="46" t="s">
         <v>30</v>
       </c>
       <c r="AQ30" s="47">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AR30" s="30"/>
     </row>
     <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="95" t="s">
+      <c r="B31" s="99" t="s">
         <v>37</v>
       </c>
-      <c r="C31" s="96"/>
+      <c r="C31" s="100"/>
       <c r="D31" s="45" t="s">
         <v>34</v>
       </c>
       <c r="E31" s="43"/>
-      <c r="F31" s="95" t="s">
+      <c r="F31" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="G31" s="96"/>
+      <c r="G31" s="100"/>
       <c r="H31" s="45" t="s">
         <v>34</v>
       </c>
       <c r="I31" s="44"/>
-      <c r="J31" s="95" t="s">
+      <c r="J31" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="K31" s="96"/>
+      <c r="K31" s="100"/>
       <c r="L31" s="45" t="s">
         <v>34</v>
       </c>
       <c r="M31" s="6"/>
-      <c r="N31" s="95" t="s">
+      <c r="N31" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="O31" s="96"/>
+      <c r="O31" s="100"/>
       <c r="P31" s="45" t="s">
         <v>34</v>
       </c>
       <c r="Q31" s="43"/>
-      <c r="R31" s="95" t="s">
+      <c r="R31" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="S31" s="96"/>
+      <c r="S31" s="100"/>
       <c r="T31" s="45" t="s">
         <v>34</v>
       </c>
       <c r="U31" s="44"/>
-      <c r="V31" s="95" t="s">
+      <c r="V31" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="W31" s="96"/>
+      <c r="W31" s="100"/>
       <c r="X31" s="45" t="s">
         <v>34</v>
       </c>
       <c r="Y31" s="43"/>
-      <c r="Z31" s="95" t="s">
+      <c r="Z31" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="AA31" s="96"/>
+      <c r="AA31" s="100"/>
       <c r="AB31" s="45" t="s">
         <v>34</v>
       </c>
       <c r="AC31" s="43"/>
-      <c r="AD31" s="95" t="s">
+      <c r="AD31" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="AE31" s="96"/>
+      <c r="AE31" s="100"/>
       <c r="AF31" s="45" t="s">
         <v>34</v>
       </c>
       <c r="AG31" s="43"/>
-      <c r="AH31" s="95"/>
-      <c r="AI31" s="96"/>
+      <c r="AH31" s="99"/>
+      <c r="AI31" s="100"/>
       <c r="AJ31" s="45"/>
       <c r="AK31" s="44"/>
-      <c r="AL31" s="95"/>
-      <c r="AM31" s="96"/>
+      <c r="AL31" s="99"/>
+      <c r="AM31" s="100"/>
       <c r="AN31" s="45"/>
       <c r="AP31" s="48"/>
       <c r="AQ31" s="49"/>
       <c r="AR31" s="30"/>
     </row>
     <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="95" t="s">
+      <c r="B32" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="C32" s="96"/>
+      <c r="C32" s="100"/>
       <c r="D32" s="45" t="s">
         <v>35</v>
       </c>
       <c r="E32" s="44"/>
-      <c r="F32" s="95" t="s">
+      <c r="F32" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="96"/>
+      <c r="G32" s="100"/>
       <c r="H32" s="45" t="s">
         <v>35</v>
       </c>
       <c r="I32" s="44"/>
-      <c r="J32" s="95" t="s">
+      <c r="J32" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="K32" s="96"/>
+      <c r="K32" s="100"/>
       <c r="L32" s="45" t="s">
         <v>35</v>
       </c>
       <c r="M32" s="5"/>
-      <c r="N32" s="95" t="s">
+      <c r="N32" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="O32" s="96"/>
+      <c r="O32" s="100"/>
       <c r="P32" s="45" t="s">
         <v>35</v>
       </c>
       <c r="Q32" s="44"/>
-      <c r="R32" s="95" t="s">
+      <c r="R32" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="S32" s="96"/>
+      <c r="S32" s="100"/>
       <c r="T32" s="45" t="s">
         <v>35</v>
       </c>
       <c r="U32" s="44"/>
-      <c r="V32" s="95" t="s">
+      <c r="V32" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="W32" s="96"/>
+      <c r="W32" s="100"/>
       <c r="X32" s="45" t="s">
         <v>35</v>
       </c>
       <c r="Y32" s="44"/>
-      <c r="Z32" s="95" t="s">
+      <c r="Z32" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="AA32" s="96"/>
+      <c r="AA32" s="100"/>
       <c r="AB32" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AC32" s="44"/>
-      <c r="AD32" s="95" t="s">
+      <c r="AD32" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="AE32" s="96"/>
+      <c r="AE32" s="100"/>
       <c r="AF32" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AG32" s="44"/>
-      <c r="AH32" s="95"/>
-      <c r="AI32" s="96"/>
+      <c r="AH32" s="99"/>
+      <c r="AI32" s="100"/>
       <c r="AJ32" s="45"/>
       <c r="AK32" s="44"/>
-      <c r="AL32" s="95"/>
-      <c r="AM32" s="96"/>
+      <c r="AL32" s="99"/>
+      <c r="AM32" s="100"/>
       <c r="AN32" s="45"/>
       <c r="AP32" s="51"/>
       <c r="AQ32" s="52"/>
       <c r="AR32" s="30"/>
     </row>
     <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="95" t="s">
+      <c r="B33" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="96"/>
+      <c r="C33" s="100"/>
       <c r="D33" s="45" t="s">
         <v>35</v>
       </c>
       <c r="E33" s="44"/>
-      <c r="F33" s="95"/>
-      <c r="G33" s="96"/>
+      <c r="F33" s="99"/>
+      <c r="G33" s="100"/>
       <c r="H33" s="45"/>
       <c r="I33" s="44"/>
-      <c r="J33" s="95"/>
-      <c r="K33" s="96"/>
+      <c r="J33" s="99"/>
+      <c r="K33" s="100"/>
       <c r="L33" s="45"/>
       <c r="M33" s="5"/>
-      <c r="N33" s="95"/>
-      <c r="O33" s="96"/>
+      <c r="N33" s="99"/>
+      <c r="O33" s="100"/>
       <c r="P33" s="45"/>
       <c r="Q33" s="44"/>
-      <c r="R33" s="95"/>
-      <c r="S33" s="96"/>
+      <c r="R33" s="99"/>
+      <c r="S33" s="100"/>
       <c r="T33" s="45"/>
       <c r="U33" s="44"/>
-      <c r="V33" s="95"/>
-      <c r="W33" s="96"/>
+      <c r="V33" s="99"/>
+      <c r="W33" s="100"/>
       <c r="X33" s="45"/>
       <c r="Y33" s="44"/>
-      <c r="Z33" s="95"/>
-      <c r="AA33" s="96"/>
+      <c r="Z33" s="99"/>
+      <c r="AA33" s="100"/>
       <c r="AB33" s="45"/>
       <c r="AC33" s="44"/>
-      <c r="AD33" s="95" t="s">
+      <c r="AD33" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="AE33" s="96"/>
+      <c r="AE33" s="100"/>
       <c r="AF33" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AG33" s="44"/>
-      <c r="AH33" s="95"/>
-      <c r="AI33" s="96"/>
+      <c r="AH33" s="99"/>
+      <c r="AI33" s="100"/>
       <c r="AJ33" s="45"/>
       <c r="AK33" s="44"/>
-      <c r="AL33" s="95"/>
-      <c r="AM33" s="96"/>
+      <c r="AL33" s="99"/>
+      <c r="AM33" s="100"/>
       <c r="AN33" s="45"/>
       <c r="AR33" s="13"/>
     </row>
     <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="12"/>
-      <c r="B34" s="142"/>
-      <c r="C34" s="143"/>
+      <c r="B34" s="101"/>
+      <c r="C34" s="102"/>
       <c r="D34" s="42"/>
       <c r="E34" s="44"/>
-      <c r="F34" s="142"/>
-      <c r="G34" s="143"/>
+      <c r="F34" s="101"/>
+      <c r="G34" s="102"/>
       <c r="H34" s="42"/>
       <c r="I34" s="44"/>
-      <c r="J34" s="142"/>
-      <c r="K34" s="143"/>
+      <c r="J34" s="101"/>
+      <c r="K34" s="102"/>
       <c r="L34" s="42"/>
       <c r="M34" s="2"/>
-      <c r="N34" s="142"/>
-      <c r="O34" s="143"/>
+      <c r="N34" s="101"/>
+      <c r="O34" s="102"/>
       <c r="P34" s="42"/>
       <c r="Q34" s="44"/>
-      <c r="R34" s="142"/>
-      <c r="S34" s="143"/>
+      <c r="R34" s="101"/>
+      <c r="S34" s="102"/>
       <c r="T34" s="42"/>
       <c r="U34" s="44"/>
-      <c r="V34" s="142"/>
-      <c r="W34" s="143"/>
+      <c r="V34" s="101"/>
+      <c r="W34" s="102"/>
       <c r="X34" s="42"/>
       <c r="Y34" s="44"/>
-      <c r="Z34" s="142"/>
-      <c r="AA34" s="143"/>
+      <c r="Z34" s="101"/>
+      <c r="AA34" s="102"/>
       <c r="AB34" s="42"/>
       <c r="AC34" s="44"/>
-      <c r="AD34" s="142"/>
-      <c r="AE34" s="143"/>
+      <c r="AD34" s="101"/>
+      <c r="AE34" s="102"/>
       <c r="AF34" s="42"/>
       <c r="AG34" s="44"/>
-      <c r="AH34" s="142"/>
-      <c r="AI34" s="143"/>
+      <c r="AH34" s="101"/>
+      <c r="AI34" s="102"/>
       <c r="AJ34" s="42"/>
       <c r="AK34" s="44"/>
-      <c r="AL34" s="142"/>
-      <c r="AM34" s="143"/>
+      <c r="AL34" s="101"/>
+      <c r="AM34" s="102"/>
       <c r="AN34" s="42"/>
       <c r="AO34" s="12"/>
       <c r="AP34" s="12"/>
@@ -4311,23 +4348,23 @@
       <c r="K36" s="33"/>
       <c r="L36" s="33"/>
       <c r="M36" s="4"/>
-      <c r="N36" s="101" t="s">
+      <c r="N36" s="124" t="s">
         <v>36</v>
       </c>
-      <c r="O36" s="101"/>
-      <c r="P36" s="101"/>
-      <c r="Q36" s="101"/>
-      <c r="R36" s="101"/>
-      <c r="S36" s="101"/>
-      <c r="T36" s="101"/>
-      <c r="U36" s="101"/>
-      <c r="V36" s="101"/>
-      <c r="W36" s="101"/>
-      <c r="X36" s="101"/>
-      <c r="Y36" s="101"/>
-      <c r="Z36" s="101"/>
-      <c r="AA36" s="101"/>
-      <c r="AB36" s="101"/>
+      <c r="O36" s="124"/>
+      <c r="P36" s="124"/>
+      <c r="Q36" s="124"/>
+      <c r="R36" s="124"/>
+      <c r="S36" s="124"/>
+      <c r="T36" s="124"/>
+      <c r="U36" s="124"/>
+      <c r="V36" s="124"/>
+      <c r="W36" s="124"/>
+      <c r="X36" s="124"/>
+      <c r="Y36" s="124"/>
+      <c r="Z36" s="124"/>
+      <c r="AA36" s="124"/>
+      <c r="AB36" s="124"/>
       <c r="AC36" s="33"/>
       <c r="AD36" s="33"/>
       <c r="AE36" s="33"/>
@@ -4359,21 +4396,21 @@
       <c r="K37" s="33"/>
       <c r="L37" s="33"/>
       <c r="M37" s="5"/>
-      <c r="N37" s="101"/>
-      <c r="O37" s="101"/>
-      <c r="P37" s="101"/>
-      <c r="Q37" s="101"/>
-      <c r="R37" s="101"/>
-      <c r="S37" s="101"/>
-      <c r="T37" s="101"/>
-      <c r="U37" s="101"/>
-      <c r="V37" s="101"/>
-      <c r="W37" s="101"/>
-      <c r="X37" s="101"/>
-      <c r="Y37" s="101"/>
-      <c r="Z37" s="101"/>
-      <c r="AA37" s="101"/>
-      <c r="AB37" s="101"/>
+      <c r="N37" s="124"/>
+      <c r="O37" s="124"/>
+      <c r="P37" s="124"/>
+      <c r="Q37" s="124"/>
+      <c r="R37" s="124"/>
+      <c r="S37" s="124"/>
+      <c r="T37" s="124"/>
+      <c r="U37" s="124"/>
+      <c r="V37" s="124"/>
+      <c r="W37" s="124"/>
+      <c r="X37" s="124"/>
+      <c r="Y37" s="124"/>
+      <c r="Z37" s="124"/>
+      <c r="AA37" s="124"/>
+      <c r="AB37" s="124"/>
       <c r="AC37" s="33"/>
       <c r="AD37" s="33"/>
       <c r="AE37" s="33"/>
@@ -4393,74 +4430,74 @@
     </row>
     <row r="38" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12"/>
-      <c r="B38" s="75" t="s">
+      <c r="B38" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="C38" s="76"/>
+      <c r="C38" s="69"/>
       <c r="D38" s="55" t="s">
         <v>77</v>
       </c>
       <c r="E38" s="36"/>
-      <c r="F38" s="75" t="s">
+      <c r="F38" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="G38" s="76"/>
+      <c r="G38" s="69"/>
       <c r="H38" s="55" t="s">
         <v>83</v>
       </c>
       <c r="I38" s="36"/>
-      <c r="J38" s="75" t="s">
+      <c r="J38" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="K38" s="76"/>
+      <c r="K38" s="69"/>
       <c r="L38" s="55" t="s">
         <v>93</v>
       </c>
       <c r="M38" s="5"/>
-      <c r="N38" s="70" t="s">
+      <c r="N38" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="O38" s="71"/>
+      <c r="O38" s="82"/>
       <c r="P38" s="34"/>
       <c r="Q38" s="36"/>
-      <c r="R38" s="70" t="s">
+      <c r="R38" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="S38" s="71"/>
+      <c r="S38" s="82"/>
       <c r="T38" s="34" t="s">
         <v>77</v>
       </c>
       <c r="U38" s="36"/>
-      <c r="V38" s="70" t="s">
+      <c r="V38" s="81" t="s">
         <v>70</v>
       </c>
-      <c r="W38" s="71"/>
+      <c r="W38" s="82"/>
       <c r="X38" s="34" t="s">
         <v>52</v>
       </c>
       <c r="Y38" s="36"/>
-      <c r="Z38" s="70"/>
-      <c r="AA38" s="71"/>
+      <c r="Z38" s="81"/>
+      <c r="AA38" s="82"/>
       <c r="AB38" s="34"/>
       <c r="AC38" s="36"/>
-      <c r="AD38" s="70" t="s">
+      <c r="AD38" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="AE38" s="71"/>
+      <c r="AE38" s="82"/>
       <c r="AF38" s="34"/>
       <c r="AG38" s="36"/>
-      <c r="AH38" s="70" t="s">
+      <c r="AH38" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="AI38" s="71"/>
+      <c r="AI38" s="82"/>
       <c r="AJ38" s="34" t="s">
         <v>76</v>
       </c>
       <c r="AK38" s="36"/>
-      <c r="AL38" s="70" t="s">
+      <c r="AL38" s="81" t="s">
         <v>72</v>
       </c>
-      <c r="AM38" s="71"/>
+      <c r="AM38" s="82"/>
       <c r="AN38" s="34" t="s">
         <v>55</v>
       </c>
@@ -4489,45 +4526,45 @@
       <c r="K39" s="63"/>
       <c r="L39" s="64"/>
       <c r="M39" s="5"/>
-      <c r="N39" s="72" t="s">
+      <c r="N39" s="106" t="s">
         <v>68</v>
       </c>
-      <c r="O39" s="73"/>
-      <c r="P39" s="74"/>
+      <c r="O39" s="107"/>
+      <c r="P39" s="108"/>
       <c r="Q39" s="36"/>
-      <c r="R39" s="72" t="s">
+      <c r="R39" s="106" t="s">
         <v>68</v>
       </c>
-      <c r="S39" s="73"/>
-      <c r="T39" s="74"/>
+      <c r="S39" s="107"/>
+      <c r="T39" s="108"/>
       <c r="U39" s="36"/>
-      <c r="V39" s="72" t="s">
+      <c r="V39" s="106" t="s">
         <v>73</v>
       </c>
-      <c r="W39" s="73"/>
-      <c r="X39" s="74"/>
+      <c r="W39" s="107"/>
+      <c r="X39" s="108"/>
       <c r="Y39" s="37"/>
-      <c r="Z39" s="72"/>
-      <c r="AA39" s="73"/>
-      <c r="AB39" s="74"/>
+      <c r="Z39" s="106"/>
+      <c r="AA39" s="107"/>
+      <c r="AB39" s="108"/>
       <c r="AC39" s="36"/>
-      <c r="AD39" s="72" t="s">
+      <c r="AD39" s="106" t="s">
         <v>74</v>
       </c>
-      <c r="AE39" s="73"/>
-      <c r="AF39" s="74"/>
+      <c r="AE39" s="107"/>
+      <c r="AF39" s="108"/>
       <c r="AG39" s="36"/>
-      <c r="AH39" s="72" t="s">
+      <c r="AH39" s="106" t="s">
         <v>74</v>
       </c>
-      <c r="AI39" s="73"/>
-      <c r="AJ39" s="74"/>
+      <c r="AI39" s="107"/>
+      <c r="AJ39" s="108"/>
       <c r="AK39" s="36"/>
-      <c r="AL39" s="72" t="s">
+      <c r="AL39" s="106" t="s">
         <v>75</v>
       </c>
-      <c r="AM39" s="73"/>
-      <c r="AN39" s="74"/>
+      <c r="AM39" s="107"/>
+      <c r="AN39" s="108"/>
       <c r="AO39" s="31"/>
       <c r="AP39" s="31"/>
       <c r="AQ39" s="31"/>
@@ -4535,17 +4572,17 @@
     </row>
     <row r="40" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12"/>
-      <c r="B40" s="77"/>
-      <c r="C40" s="78"/>
-      <c r="D40" s="79"/>
+      <c r="B40" s="73"/>
+      <c r="C40" s="74"/>
+      <c r="D40" s="75"/>
       <c r="E40" s="43"/>
-      <c r="F40" s="77"/>
-      <c r="G40" s="78"/>
-      <c r="H40" s="79"/>
+      <c r="F40" s="73"/>
+      <c r="G40" s="74"/>
+      <c r="H40" s="75"/>
       <c r="I40" s="43"/>
-      <c r="J40" s="77"/>
-      <c r="K40" s="78"/>
-      <c r="L40" s="79"/>
+      <c r="J40" s="73"/>
+      <c r="K40" s="74"/>
+      <c r="L40" s="75"/>
       <c r="M40" s="4"/>
       <c r="N40" s="83" t="s">
         <v>42</v>
@@ -4585,63 +4622,63 @@
     </row>
     <row r="41" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12"/>
-      <c r="B41" s="67" t="s">
+      <c r="B41" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="C41" s="68"/>
-      <c r="D41" s="69"/>
+      <c r="C41" s="79"/>
+      <c r="D41" s="80"/>
       <c r="E41" s="37"/>
-      <c r="F41" s="150" t="s">
+      <c r="F41" s="103" t="s">
         <v>96</v>
       </c>
-      <c r="G41" s="151"/>
-      <c r="H41" s="152"/>
+      <c r="G41" s="104"/>
+      <c r="H41" s="105"/>
       <c r="I41" s="31"/>
-      <c r="J41" s="67" t="s">
+      <c r="J41" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="K41" s="68"/>
-      <c r="L41" s="69"/>
+      <c r="K41" s="79"/>
+      <c r="L41" s="80"/>
       <c r="M41" s="5"/>
-      <c r="N41" s="67" t="s">
+      <c r="N41" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="O41" s="68"/>
-      <c r="P41" s="69"/>
+      <c r="O41" s="79"/>
+      <c r="P41" s="80"/>
       <c r="Q41" s="32"/>
-      <c r="R41" s="67" t="s">
+      <c r="R41" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="S41" s="68"/>
-      <c r="T41" s="69"/>
+      <c r="S41" s="79"/>
+      <c r="T41" s="80"/>
       <c r="U41" s="31"/>
-      <c r="V41" s="67" t="s">
+      <c r="V41" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="W41" s="68"/>
-      <c r="X41" s="69"/>
+      <c r="W41" s="79"/>
+      <c r="X41" s="80"/>
       <c r="Y41" s="32"/>
-      <c r="Z41" s="67"/>
-      <c r="AA41" s="68"/>
-      <c r="AB41" s="69"/>
+      <c r="Z41" s="78"/>
+      <c r="AA41" s="79"/>
+      <c r="AB41" s="80"/>
       <c r="AC41" s="32"/>
-      <c r="AD41" s="139" t="s">
+      <c r="AD41" s="119" t="s">
         <v>24</v>
       </c>
-      <c r="AE41" s="140"/>
-      <c r="AF41" s="141"/>
+      <c r="AE41" s="120"/>
+      <c r="AF41" s="121"/>
       <c r="AG41" s="37"/>
-      <c r="AH41" s="67" t="s">
+      <c r="AH41" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="AI41" s="68"/>
-      <c r="AJ41" s="69"/>
+      <c r="AI41" s="79"/>
+      <c r="AJ41" s="80"/>
       <c r="AK41" s="31"/>
-      <c r="AL41" s="67" t="s">
+      <c r="AL41" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="AM41" s="68"/>
-      <c r="AN41" s="69"/>
+      <c r="AM41" s="79"/>
+      <c r="AN41" s="80"/>
       <c r="AO41" s="31"/>
       <c r="AP41" s="31"/>
       <c r="AQ41" s="31"/>
@@ -4649,63 +4686,63 @@
     </row>
     <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12"/>
-      <c r="B42" s="67" t="s">
+      <c r="B42" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="C42" s="68"/>
-      <c r="D42" s="69"/>
+      <c r="C42" s="79"/>
+      <c r="D42" s="80"/>
       <c r="E42" s="44"/>
-      <c r="F42" s="67" t="s">
+      <c r="F42" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="G42" s="68"/>
-      <c r="H42" s="69"/>
+      <c r="G42" s="79"/>
+      <c r="H42" s="80"/>
       <c r="I42" s="31"/>
-      <c r="J42" s="67" t="s">
+      <c r="J42" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="K42" s="68"/>
-      <c r="L42" s="69"/>
+      <c r="K42" s="79"/>
+      <c r="L42" s="80"/>
       <c r="M42" s="5"/>
-      <c r="N42" s="67" t="s">
+      <c r="N42" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="O42" s="68"/>
-      <c r="P42" s="69"/>
+      <c r="O42" s="79"/>
+      <c r="P42" s="80"/>
       <c r="Q42" s="31"/>
-      <c r="R42" s="67" t="s">
+      <c r="R42" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="S42" s="68"/>
-      <c r="T42" s="69"/>
+      <c r="S42" s="79"/>
+      <c r="T42" s="80"/>
       <c r="U42" s="32"/>
-      <c r="V42" s="67" t="s">
+      <c r="V42" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="W42" s="68"/>
-      <c r="X42" s="69"/>
+      <c r="W42" s="79"/>
+      <c r="X42" s="80"/>
       <c r="Y42" s="32"/>
-      <c r="Z42" s="67"/>
-      <c r="AA42" s="68"/>
-      <c r="AB42" s="69"/>
+      <c r="Z42" s="78"/>
+      <c r="AA42" s="79"/>
+      <c r="AB42" s="80"/>
       <c r="AC42" s="32"/>
-      <c r="AD42" s="67" t="s">
+      <c r="AD42" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="AE42" s="68"/>
-      <c r="AF42" s="69"/>
+      <c r="AE42" s="79"/>
+      <c r="AF42" s="80"/>
       <c r="AG42" s="44"/>
-      <c r="AH42" s="67" t="s">
+      <c r="AH42" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="AI42" s="68"/>
-      <c r="AJ42" s="69"/>
+      <c r="AI42" s="79"/>
+      <c r="AJ42" s="80"/>
       <c r="AK42" s="31"/>
-      <c r="AL42" s="67" t="s">
+      <c r="AL42" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="AM42" s="68"/>
-      <c r="AN42" s="69"/>
+      <c r="AM42" s="79"/>
+      <c r="AN42" s="80"/>
       <c r="AO42" s="31"/>
       <c r="AP42" s="31"/>
       <c r="AQ42" s="31"/>
@@ -4713,55 +4750,55 @@
     </row>
     <row r="43" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12"/>
-      <c r="B43" s="80"/>
-      <c r="C43" s="81"/>
-      <c r="D43" s="82"/>
+      <c r="B43" s="65"/>
+      <c r="C43" s="66"/>
+      <c r="D43" s="67"/>
       <c r="E43" s="35"/>
-      <c r="F43" s="80" t="s">
+      <c r="F43" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="G43" s="81"/>
-      <c r="H43" s="82"/>
+      <c r="G43" s="66"/>
+      <c r="H43" s="67"/>
       <c r="I43" s="40"/>
-      <c r="J43" s="80"/>
-      <c r="K43" s="81"/>
-      <c r="L43" s="82"/>
+      <c r="J43" s="65"/>
+      <c r="K43" s="66"/>
+      <c r="L43" s="67"/>
       <c r="M43" s="14"/>
-      <c r="N43" s="67" t="s">
+      <c r="N43" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="O43" s="68"/>
-      <c r="P43" s="69"/>
+      <c r="O43" s="79"/>
+      <c r="P43" s="80"/>
       <c r="Q43" s="40"/>
-      <c r="R43" s="67" t="s">
+      <c r="R43" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="S43" s="68"/>
-      <c r="T43" s="69"/>
+      <c r="S43" s="79"/>
+      <c r="T43" s="80"/>
       <c r="U43" s="40"/>
-      <c r="V43" s="80"/>
-      <c r="W43" s="81"/>
-      <c r="X43" s="82"/>
+      <c r="V43" s="65"/>
+      <c r="W43" s="66"/>
+      <c r="X43" s="67"/>
       <c r="Y43" s="40"/>
-      <c r="Z43" s="80"/>
-      <c r="AA43" s="81"/>
-      <c r="AB43" s="82"/>
+      <c r="Z43" s="65"/>
+      <c r="AA43" s="66"/>
+      <c r="AB43" s="67"/>
       <c r="AC43" s="40"/>
-      <c r="AD43" s="67" t="s">
+      <c r="AD43" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="AE43" s="68"/>
-      <c r="AF43" s="69"/>
+      <c r="AE43" s="79"/>
+      <c r="AF43" s="80"/>
       <c r="AG43" s="35"/>
-      <c r="AH43" s="67" t="s">
+      <c r="AH43" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="AI43" s="68"/>
-      <c r="AJ43" s="69"/>
+      <c r="AI43" s="79"/>
+      <c r="AJ43" s="80"/>
       <c r="AK43" s="40"/>
-      <c r="AL43" s="80"/>
-      <c r="AM43" s="81"/>
-      <c r="AN43" s="82"/>
+      <c r="AL43" s="65"/>
+      <c r="AM43" s="66"/>
+      <c r="AN43" s="67"/>
       <c r="AO43" s="31"/>
       <c r="AP43" s="31"/>
       <c r="AQ43" s="31"/>
@@ -4781,15 +4818,15 @@
       <c r="K44" s="35"/>
       <c r="L44" s="35"/>
       <c r="M44" s="14"/>
-      <c r="N44" s="67"/>
-      <c r="O44" s="68"/>
-      <c r="P44" s="69"/>
+      <c r="N44" s="78"/>
+      <c r="O44" s="79"/>
+      <c r="P44" s="80"/>
       <c r="Q44" s="36"/>
-      <c r="R44" s="67" t="s">
+      <c r="R44" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="S44" s="68"/>
-      <c r="T44" s="69"/>
+      <c r="S44" s="79"/>
+      <c r="T44" s="80"/>
       <c r="U44" s="50"/>
       <c r="V44" s="35"/>
       <c r="W44" s="35"/>
@@ -4799,17 +4836,17 @@
       <c r="AA44" s="35"/>
       <c r="AB44" s="35"/>
       <c r="AC44" s="36"/>
-      <c r="AD44" s="80" t="s">
+      <c r="AD44" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="AE44" s="81"/>
-      <c r="AF44" s="82"/>
+      <c r="AE44" s="66"/>
+      <c r="AF44" s="67"/>
       <c r="AG44" s="50"/>
-      <c r="AH44" s="80" t="s">
+      <c r="AH44" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="AI44" s="81"/>
-      <c r="AJ44" s="82"/>
+      <c r="AI44" s="66"/>
+      <c r="AJ44" s="67"/>
       <c r="AK44" s="32"/>
       <c r="AL44" s="35"/>
       <c r="AM44" s="35"/>
@@ -4821,50 +4858,50 @@
     </row>
     <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="12"/>
-      <c r="B45" s="75" t="s">
+      <c r="B45" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="C45" s="76"/>
+      <c r="C45" s="69"/>
       <c r="D45" s="55" t="s">
         <v>54</v>
       </c>
       <c r="E45" s="36"/>
-      <c r="F45" s="75" t="s">
+      <c r="F45" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="G45" s="76"/>
+      <c r="G45" s="69"/>
       <c r="H45" s="55" t="s">
         <v>43</v>
       </c>
       <c r="I45" s="32"/>
-      <c r="J45" s="75" t="s">
+      <c r="J45" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="K45" s="76"/>
+      <c r="K45" s="69"/>
       <c r="L45" s="55" t="s">
         <v>83</v>
       </c>
       <c r="M45" s="14"/>
-      <c r="N45" s="80"/>
-      <c r="O45" s="81"/>
-      <c r="P45" s="82"/>
+      <c r="N45" s="65"/>
+      <c r="O45" s="66"/>
+      <c r="P45" s="67"/>
       <c r="Q45" s="36"/>
-      <c r="R45" s="80" t="s">
+      <c r="R45" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="S45" s="81"/>
-      <c r="T45" s="82"/>
+      <c r="S45" s="66"/>
+      <c r="T45" s="67"/>
       <c r="U45" s="36"/>
-      <c r="V45" s="70" t="s">
+      <c r="V45" s="81" t="s">
         <v>62</v>
       </c>
-      <c r="W45" s="71"/>
+      <c r="W45" s="82"/>
       <c r="X45" s="34" t="s">
         <v>83</v>
       </c>
       <c r="Y45" s="36"/>
-      <c r="Z45" s="70"/>
-      <c r="AA45" s="71"/>
+      <c r="Z45" s="81"/>
+      <c r="AA45" s="82"/>
       <c r="AB45" s="34"/>
       <c r="AC45" s="36"/>
       <c r="AD45" s="35"/>
@@ -4875,10 +4912,10 @@
       <c r="AI45" s="35"/>
       <c r="AJ45" s="35"/>
       <c r="AK45" s="32"/>
-      <c r="AL45" s="70" t="s">
+      <c r="AL45" s="81" t="s">
         <v>72</v>
       </c>
-      <c r="AM45" s="71"/>
+      <c r="AM45" s="82"/>
       <c r="AN45" s="34" t="s">
         <v>54</v>
       </c>
@@ -4915,29 +4952,29 @@
       <c r="S46" s="35"/>
       <c r="T46" s="58"/>
       <c r="U46" s="36"/>
-      <c r="V46" s="72" t="s">
+      <c r="V46" s="106" t="s">
         <v>63</v>
       </c>
-      <c r="W46" s="73"/>
-      <c r="X46" s="74"/>
+      <c r="W46" s="107"/>
+      <c r="X46" s="108"/>
       <c r="Y46" s="36"/>
-      <c r="Z46" s="72"/>
-      <c r="AA46" s="73"/>
-      <c r="AB46" s="74"/>
+      <c r="Z46" s="106"/>
+      <c r="AA46" s="107"/>
+      <c r="AB46" s="108"/>
       <c r="AC46" s="36"/>
-      <c r="AD46" s="70"/>
-      <c r="AE46" s="71"/>
+      <c r="AD46" s="81"/>
+      <c r="AE46" s="82"/>
       <c r="AF46" s="34"/>
       <c r="AG46" s="36"/>
-      <c r="AH46" s="70"/>
-      <c r="AI46" s="71"/>
+      <c r="AH46" s="81"/>
+      <c r="AI46" s="82"/>
       <c r="AJ46" s="34"/>
       <c r="AK46" s="54"/>
-      <c r="AL46" s="72" t="s">
+      <c r="AL46" s="106" t="s">
         <v>51</v>
       </c>
-      <c r="AM46" s="73"/>
-      <c r="AN46" s="74"/>
+      <c r="AM46" s="107"/>
+      <c r="AN46" s="108"/>
       <c r="AO46" s="31"/>
       <c r="AP46" s="31"/>
       <c r="AQ46" s="31"/>
@@ -4945,28 +4982,28 @@
     </row>
     <row r="47" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12"/>
-      <c r="B47" s="77"/>
-      <c r="C47" s="78"/>
-      <c r="D47" s="79"/>
+      <c r="B47" s="73"/>
+      <c r="C47" s="74"/>
+      <c r="D47" s="75"/>
       <c r="E47" s="43"/>
-      <c r="F47" s="77"/>
-      <c r="G47" s="78"/>
-      <c r="H47" s="79"/>
+      <c r="F47" s="73"/>
+      <c r="G47" s="74"/>
+      <c r="H47" s="75"/>
       <c r="I47" s="37"/>
-      <c r="J47" s="77"/>
-      <c r="K47" s="78"/>
-      <c r="L47" s="79"/>
+      <c r="J47" s="73"/>
+      <c r="K47" s="74"/>
+      <c r="L47" s="75"/>
       <c r="M47" s="4"/>
-      <c r="N47" s="70" t="s">
+      <c r="N47" s="81" t="s">
         <v>62</v>
       </c>
-      <c r="O47" s="71"/>
+      <c r="O47" s="82"/>
       <c r="P47" s="34" t="s">
         <v>83</v>
       </c>
       <c r="Q47" s="37"/>
-      <c r="R47" s="70"/>
-      <c r="S47" s="71"/>
+      <c r="R47" s="81"/>
+      <c r="S47" s="82"/>
       <c r="T47" s="34"/>
       <c r="U47" s="43"/>
       <c r="V47" s="83"/>
@@ -4977,13 +5014,13 @@
       <c r="AA47" s="84"/>
       <c r="AB47" s="85"/>
       <c r="AC47" s="35"/>
-      <c r="AD47" s="72"/>
-      <c r="AE47" s="73"/>
-      <c r="AF47" s="74"/>
+      <c r="AD47" s="106"/>
+      <c r="AE47" s="107"/>
+      <c r="AF47" s="108"/>
       <c r="AG47" s="43"/>
-      <c r="AH47" s="72"/>
-      <c r="AI47" s="73"/>
-      <c r="AJ47" s="74"/>
+      <c r="AH47" s="106"/>
+      <c r="AI47" s="107"/>
+      <c r="AJ47" s="108"/>
       <c r="AK47" s="37"/>
       <c r="AL47" s="83"/>
       <c r="AM47" s="84"/>
@@ -4995,17 +5032,17 @@
     </row>
     <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12"/>
-      <c r="B48" s="67" t="s">
+      <c r="B48" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="C48" s="68"/>
-      <c r="D48" s="69"/>
+      <c r="C48" s="79"/>
+      <c r="D48" s="80"/>
       <c r="E48" s="37"/>
-      <c r="F48" s="67" t="s">
+      <c r="F48" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="G48" s="68"/>
-      <c r="H48" s="69"/>
+      <c r="G48" s="79"/>
+      <c r="H48" s="80"/>
       <c r="I48" s="44"/>
       <c r="J48" s="86" t="s">
         <v>10</v>
@@ -5013,25 +5050,25 @@
       <c r="K48" s="87"/>
       <c r="L48" s="88"/>
       <c r="M48" s="5"/>
-      <c r="N48" s="72" t="s">
+      <c r="N48" s="106" t="s">
         <v>63</v>
       </c>
-      <c r="O48" s="73"/>
-      <c r="P48" s="74"/>
+      <c r="O48" s="107"/>
+      <c r="P48" s="108"/>
       <c r="Q48" s="44"/>
-      <c r="R48" s="72"/>
-      <c r="S48" s="73"/>
-      <c r="T48" s="74"/>
+      <c r="R48" s="106"/>
+      <c r="S48" s="107"/>
+      <c r="T48" s="108"/>
       <c r="U48" s="37"/>
-      <c r="V48" s="89" t="s">
+      <c r="V48" s="70" t="s">
         <v>37</v>
       </c>
-      <c r="W48" s="90"/>
-      <c r="X48" s="91"/>
+      <c r="W48" s="71"/>
+      <c r="X48" s="72"/>
       <c r="Y48" s="37"/>
-      <c r="Z48" s="67"/>
-      <c r="AA48" s="68"/>
-      <c r="AB48" s="69"/>
+      <c r="Z48" s="78"/>
+      <c r="AA48" s="79"/>
+      <c r="AB48" s="80"/>
       <c r="AC48" s="43"/>
       <c r="AD48" s="83"/>
       <c r="AE48" s="84"/>
@@ -5041,28 +5078,28 @@
       <c r="AI48" s="84"/>
       <c r="AJ48" s="85"/>
       <c r="AK48" s="44"/>
-      <c r="AL48" s="67" t="s">
+      <c r="AL48" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="AM48" s="68"/>
-      <c r="AN48" s="69"/>
+      <c r="AM48" s="79"/>
+      <c r="AN48" s="80"/>
       <c r="AO48" s="31"/>
       <c r="AP48" s="31"/>
       <c r="AQ48" s="31"/>
       <c r="AR48" s="13"/>
     </row>
     <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="67" t="s">
+      <c r="B49" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="C49" s="68"/>
-      <c r="D49" s="69"/>
+      <c r="C49" s="79"/>
+      <c r="D49" s="80"/>
       <c r="E49" s="35"/>
-      <c r="F49" s="67" t="s">
+      <c r="F49" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="G49" s="68"/>
-      <c r="H49" s="69"/>
+      <c r="G49" s="79"/>
+      <c r="H49" s="80"/>
       <c r="I49" s="44"/>
       <c r="J49" s="86" t="s">
         <v>12</v>
@@ -5078,82 +5115,82 @@
       <c r="S49" s="84"/>
       <c r="T49" s="85"/>
       <c r="U49" s="44"/>
-      <c r="V49" s="67" t="s">
+      <c r="V49" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="W49" s="68"/>
-      <c r="X49" s="69"/>
+      <c r="W49" s="79"/>
+      <c r="X49" s="80"/>
       <c r="Y49" s="35"/>
-      <c r="Z49" s="67"/>
-      <c r="AA49" s="68"/>
-      <c r="AB49" s="69"/>
+      <c r="Z49" s="78"/>
+      <c r="AA49" s="79"/>
+      <c r="AB49" s="80"/>
       <c r="AC49" s="35"/>
-      <c r="AD49" s="67"/>
-      <c r="AE49" s="68"/>
-      <c r="AF49" s="69"/>
+      <c r="AD49" s="78"/>
+      <c r="AE49" s="79"/>
+      <c r="AF49" s="80"/>
       <c r="AG49" s="35"/>
-      <c r="AH49" s="67"/>
-      <c r="AI49" s="68"/>
-      <c r="AJ49" s="69"/>
+      <c r="AH49" s="78"/>
+      <c r="AI49" s="79"/>
+      <c r="AJ49" s="80"/>
       <c r="AK49" s="44"/>
-      <c r="AL49" s="67" t="s">
+      <c r="AL49" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="AM49" s="68"/>
-      <c r="AN49" s="69"/>
+      <c r="AM49" s="79"/>
+      <c r="AN49" s="80"/>
       <c r="AO49" s="31"/>
       <c r="AP49" s="31"/>
       <c r="AQ49" s="31"/>
       <c r="AR49" s="13"/>
     </row>
     <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="153" t="s">
+      <c r="B50" s="89" t="s">
         <v>100</v>
       </c>
-      <c r="C50" s="154"/>
-      <c r="D50" s="155"/>
+      <c r="C50" s="90"/>
+      <c r="D50" s="91"/>
       <c r="E50" s="50"/>
-      <c r="F50" s="80" t="s">
+      <c r="F50" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="G50" s="81"/>
-      <c r="H50" s="82"/>
+      <c r="G50" s="66"/>
+      <c r="H50" s="67"/>
       <c r="I50" s="50"/>
-      <c r="J50" s="80" t="s">
+      <c r="J50" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="K50" s="81"/>
-      <c r="L50" s="82"/>
+      <c r="K50" s="66"/>
+      <c r="L50" s="67"/>
       <c r="M50" s="5"/>
-      <c r="N50" s="89" t="s">
+      <c r="N50" s="70" t="s">
         <v>37</v>
       </c>
-      <c r="O50" s="90"/>
-      <c r="P50" s="91"/>
+      <c r="O50" s="71"/>
+      <c r="P50" s="72"/>
       <c r="Q50" s="50"/>
-      <c r="R50" s="67"/>
-      <c r="S50" s="68"/>
-      <c r="T50" s="69"/>
+      <c r="R50" s="78"/>
+      <c r="S50" s="79"/>
+      <c r="T50" s="80"/>
       <c r="U50" s="50"/>
-      <c r="V50" s="80"/>
-      <c r="W50" s="81"/>
-      <c r="X50" s="82"/>
+      <c r="V50" s="65"/>
+      <c r="W50" s="66"/>
+      <c r="X50" s="67"/>
       <c r="Y50" s="50"/>
-      <c r="Z50" s="80"/>
-      <c r="AA50" s="81"/>
-      <c r="AB50" s="82"/>
+      <c r="Z50" s="65"/>
+      <c r="AA50" s="66"/>
+      <c r="AB50" s="67"/>
       <c r="AC50" s="50"/>
-      <c r="AD50" s="80"/>
-      <c r="AE50" s="81"/>
-      <c r="AF50" s="82"/>
+      <c r="AD50" s="65"/>
+      <c r="AE50" s="66"/>
+      <c r="AF50" s="67"/>
       <c r="AG50" s="50"/>
-      <c r="AH50" s="80"/>
-      <c r="AI50" s="81"/>
-      <c r="AJ50" s="82"/>
+      <c r="AH50" s="65"/>
+      <c r="AI50" s="66"/>
+      <c r="AJ50" s="67"/>
       <c r="AK50" s="50"/>
-      <c r="AL50" s="80"/>
-      <c r="AM50" s="81"/>
-      <c r="AN50" s="82"/>
+      <c r="AL50" s="65"/>
+      <c r="AM50" s="66"/>
+      <c r="AN50" s="67"/>
       <c r="AO50" s="31"/>
       <c r="AP50" s="31"/>
       <c r="AQ50" s="31"/>
@@ -5172,15 +5209,15 @@
       <c r="K51" s="35"/>
       <c r="L51" s="35"/>
       <c r="M51" s="14"/>
-      <c r="N51" s="80" t="s">
+      <c r="N51" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="O51" s="81"/>
-      <c r="P51" s="82"/>
+      <c r="O51" s="66"/>
+      <c r="P51" s="67"/>
       <c r="Q51" s="35"/>
-      <c r="R51" s="80"/>
-      <c r="S51" s="81"/>
-      <c r="T51" s="82"/>
+      <c r="R51" s="65"/>
+      <c r="S51" s="66"/>
+      <c r="T51" s="67"/>
       <c r="U51" s="36"/>
       <c r="V51" s="35"/>
       <c r="W51" s="35"/>
@@ -5207,26 +5244,26 @@
       <c r="AR51" s="13"/>
     </row>
     <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="65" t="s">
+      <c r="B52" s="76" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="66"/>
+      <c r="C52" s="77"/>
       <c r="D52" s="57" t="s">
         <v>85</v>
       </c>
       <c r="E52" s="36"/>
-      <c r="F52" s="65" t="s">
+      <c r="F52" s="76" t="s">
         <v>101</v>
       </c>
-      <c r="G52" s="66"/>
+      <c r="G52" s="77"/>
       <c r="H52" s="57" t="s">
         <v>102</v>
       </c>
       <c r="I52" s="54"/>
-      <c r="J52" s="65" t="s">
+      <c r="J52" s="76" t="s">
         <v>101</v>
       </c>
-      <c r="K52" s="66"/>
+      <c r="K52" s="77"/>
       <c r="L52" s="57" t="s">
         <v>93</v>
       </c>
@@ -5239,24 +5276,24 @@
       <c r="S52" s="35"/>
       <c r="T52" s="35"/>
       <c r="U52" s="35"/>
-      <c r="V52" s="70"/>
-      <c r="W52" s="71"/>
+      <c r="V52" s="81"/>
+      <c r="W52" s="82"/>
       <c r="X52" s="34"/>
       <c r="Y52" s="36"/>
-      <c r="Z52" s="70"/>
-      <c r="AA52" s="71"/>
+      <c r="Z52" s="81"/>
+      <c r="AA52" s="82"/>
       <c r="AB52" s="34"/>
       <c r="AC52" s="36"/>
-      <c r="AD52" s="70"/>
-      <c r="AE52" s="71"/>
+      <c r="AD52" s="81"/>
+      <c r="AE52" s="82"/>
       <c r="AF52" s="34"/>
       <c r="AG52" s="36"/>
-      <c r="AH52" s="70"/>
-      <c r="AI52" s="71"/>
+      <c r="AH52" s="81"/>
+      <c r="AI52" s="82"/>
       <c r="AJ52" s="34"/>
       <c r="AK52" s="54"/>
-      <c r="AL52" s="70"/>
-      <c r="AM52" s="71"/>
+      <c r="AL52" s="81"/>
+      <c r="AM52" s="82"/>
       <c r="AN52" s="34"/>
       <c r="AR52" s="13"/>
     </row>
@@ -5274,60 +5311,60 @@
       <c r="H53" s="64"/>
       <c r="I53" s="35"/>
       <c r="J53" s="62" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K53" s="63"/>
       <c r="L53" s="64"/>
       <c r="M53" s="4"/>
-      <c r="N53" s="70"/>
-      <c r="O53" s="71"/>
+      <c r="N53" s="81"/>
+      <c r="O53" s="82"/>
       <c r="P53" s="34"/>
       <c r="Q53" s="32"/>
-      <c r="R53" s="70"/>
-      <c r="S53" s="71"/>
+      <c r="R53" s="81"/>
+      <c r="S53" s="82"/>
       <c r="T53" s="34"/>
       <c r="U53" s="43"/>
-      <c r="V53" s="72"/>
-      <c r="W53" s="73"/>
-      <c r="X53" s="74"/>
+      <c r="V53" s="106"/>
+      <c r="W53" s="107"/>
+      <c r="X53" s="108"/>
       <c r="Y53" s="36"/>
-      <c r="Z53" s="72"/>
-      <c r="AA53" s="73"/>
-      <c r="AB53" s="74"/>
+      <c r="Z53" s="106"/>
+      <c r="AA53" s="107"/>
+      <c r="AB53" s="108"/>
       <c r="AC53" s="35"/>
-      <c r="AD53" s="72"/>
-      <c r="AE53" s="73"/>
-      <c r="AF53" s="74"/>
+      <c r="AD53" s="106"/>
+      <c r="AE53" s="107"/>
+      <c r="AF53" s="108"/>
       <c r="AG53" s="36"/>
-      <c r="AH53" s="72"/>
-      <c r="AI53" s="73"/>
-      <c r="AJ53" s="74"/>
+      <c r="AH53" s="106"/>
+      <c r="AI53" s="107"/>
+      <c r="AJ53" s="108"/>
       <c r="AK53" s="35"/>
-      <c r="AL53" s="72"/>
-      <c r="AM53" s="73"/>
-      <c r="AN53" s="74"/>
+      <c r="AL53" s="106"/>
+      <c r="AM53" s="107"/>
+      <c r="AN53" s="108"/>
       <c r="AR53" s="13"/>
     </row>
     <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="77"/>
-      <c r="C54" s="78"/>
-      <c r="D54" s="79"/>
+      <c r="B54" s="73"/>
+      <c r="C54" s="74"/>
+      <c r="D54" s="75"/>
       <c r="E54" s="43"/>
-      <c r="F54" s="77"/>
-      <c r="G54" s="78"/>
-      <c r="H54" s="79"/>
+      <c r="F54" s="73"/>
+      <c r="G54" s="74"/>
+      <c r="H54" s="75"/>
       <c r="I54" s="35"/>
-      <c r="J54" s="77"/>
-      <c r="K54" s="78"/>
-      <c r="L54" s="79"/>
+      <c r="J54" s="73"/>
+      <c r="K54" s="74"/>
+      <c r="L54" s="75"/>
       <c r="M54" s="4"/>
-      <c r="N54" s="72"/>
-      <c r="O54" s="73"/>
-      <c r="P54" s="74"/>
+      <c r="N54" s="106"/>
+      <c r="O54" s="107"/>
+      <c r="P54" s="108"/>
       <c r="Q54" s="43"/>
-      <c r="R54" s="72"/>
-      <c r="S54" s="73"/>
-      <c r="T54" s="74"/>
+      <c r="R54" s="106"/>
+      <c r="S54" s="107"/>
+      <c r="T54" s="108"/>
       <c r="U54" s="37"/>
       <c r="V54" s="83"/>
       <c r="W54" s="84"/>
@@ -5351,23 +5388,23 @@
       <c r="AR54" s="13"/>
     </row>
     <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="67" t="s">
+      <c r="B55" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="C55" s="68"/>
-      <c r="D55" s="69"/>
+      <c r="C55" s="79"/>
+      <c r="D55" s="80"/>
       <c r="E55" s="37"/>
-      <c r="F55" s="67" t="s">
+      <c r="F55" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="G55" s="68"/>
-      <c r="H55" s="69"/>
+      <c r="G55" s="79"/>
+      <c r="H55" s="80"/>
       <c r="I55" s="40"/>
-      <c r="J55" s="67" t="s">
+      <c r="J55" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="K55" s="68"/>
-      <c r="L55" s="69"/>
+      <c r="K55" s="79"/>
+      <c r="L55" s="80"/>
       <c r="M55" s="5"/>
       <c r="N55" s="83"/>
       <c r="O55" s="84"/>
@@ -5377,115 +5414,115 @@
       <c r="S55" s="84"/>
       <c r="T55" s="85"/>
       <c r="U55" s="44"/>
-      <c r="V55" s="67"/>
-      <c r="W55" s="68"/>
-      <c r="X55" s="69"/>
+      <c r="V55" s="78"/>
+      <c r="W55" s="79"/>
+      <c r="X55" s="80"/>
       <c r="Y55" s="37"/>
-      <c r="Z55" s="67"/>
-      <c r="AA55" s="68"/>
-      <c r="AB55" s="69"/>
+      <c r="Z55" s="78"/>
+      <c r="AA55" s="79"/>
+      <c r="AB55" s="80"/>
       <c r="AC55" s="35"/>
-      <c r="AD55" s="67"/>
-      <c r="AE55" s="68"/>
-      <c r="AF55" s="69"/>
+      <c r="AD55" s="78"/>
+      <c r="AE55" s="79"/>
+      <c r="AF55" s="80"/>
       <c r="AG55" s="37"/>
-      <c r="AH55" s="67"/>
-      <c r="AI55" s="68"/>
-      <c r="AJ55" s="69"/>
+      <c r="AH55" s="78"/>
+      <c r="AI55" s="79"/>
+      <c r="AJ55" s="80"/>
       <c r="AK55" s="40"/>
-      <c r="AL55" s="67"/>
-      <c r="AM55" s="68"/>
-      <c r="AN55" s="69"/>
+      <c r="AL55" s="78"/>
+      <c r="AM55" s="79"/>
+      <c r="AN55" s="80"/>
       <c r="AR55" s="13"/>
     </row>
     <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="67" t="s">
+      <c r="B56" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="C56" s="68"/>
-      <c r="D56" s="69"/>
+      <c r="C56" s="79"/>
+      <c r="D56" s="80"/>
       <c r="E56" s="44"/>
-      <c r="F56" s="67" t="s">
+      <c r="F56" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="G56" s="68"/>
-      <c r="H56" s="69"/>
+      <c r="G56" s="79"/>
+      <c r="H56" s="80"/>
       <c r="I56" s="44"/>
-      <c r="J56" s="67" t="s">
+      <c r="J56" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="K56" s="68"/>
-      <c r="L56" s="69"/>
+      <c r="K56" s="79"/>
+      <c r="L56" s="80"/>
       <c r="M56" s="5"/>
-      <c r="N56" s="67"/>
-      <c r="O56" s="68"/>
-      <c r="P56" s="69"/>
+      <c r="N56" s="78"/>
+      <c r="O56" s="79"/>
+      <c r="P56" s="80"/>
       <c r="Q56" s="43"/>
-      <c r="R56" s="67"/>
-      <c r="S56" s="68"/>
-      <c r="T56" s="69"/>
+      <c r="R56" s="78"/>
+      <c r="S56" s="79"/>
+      <c r="T56" s="80"/>
       <c r="U56" s="44"/>
-      <c r="V56" s="67"/>
-      <c r="W56" s="68"/>
-      <c r="X56" s="69"/>
+      <c r="V56" s="78"/>
+      <c r="W56" s="79"/>
+      <c r="X56" s="80"/>
       <c r="Y56" s="44"/>
-      <c r="Z56" s="67"/>
-      <c r="AA56" s="68"/>
-      <c r="AB56" s="69"/>
+      <c r="Z56" s="78"/>
+      <c r="AA56" s="79"/>
+      <c r="AB56" s="80"/>
       <c r="AC56" s="43"/>
-      <c r="AD56" s="67"/>
-      <c r="AE56" s="68"/>
-      <c r="AF56" s="69"/>
+      <c r="AD56" s="78"/>
+      <c r="AE56" s="79"/>
+      <c r="AF56" s="80"/>
       <c r="AG56" s="44"/>
-      <c r="AH56" s="67"/>
-      <c r="AI56" s="68"/>
-      <c r="AJ56" s="69"/>
+      <c r="AH56" s="78"/>
+      <c r="AI56" s="79"/>
+      <c r="AJ56" s="80"/>
       <c r="AK56" s="44"/>
-      <c r="AL56" s="67"/>
-      <c r="AM56" s="68"/>
-      <c r="AN56" s="69"/>
+      <c r="AL56" s="78"/>
+      <c r="AM56" s="79"/>
+      <c r="AN56" s="80"/>
       <c r="AR56" s="13"/>
     </row>
     <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="80"/>
-      <c r="C57" s="81"/>
-      <c r="D57" s="82"/>
+      <c r="B57" s="65"/>
+      <c r="C57" s="66"/>
+      <c r="D57" s="67"/>
       <c r="E57" s="35"/>
-      <c r="F57" s="80"/>
-      <c r="G57" s="81"/>
-      <c r="H57" s="82"/>
+      <c r="F57" s="65"/>
+      <c r="G57" s="66"/>
+      <c r="H57" s="67"/>
       <c r="I57" s="50"/>
-      <c r="J57" s="80"/>
-      <c r="K57" s="81"/>
-      <c r="L57" s="82"/>
+      <c r="J57" s="65"/>
+      <c r="K57" s="66"/>
+      <c r="L57" s="67"/>
       <c r="M57" s="5"/>
-      <c r="N57" s="80"/>
-      <c r="O57" s="81"/>
-      <c r="P57" s="82"/>
+      <c r="N57" s="65"/>
+      <c r="O57" s="66"/>
+      <c r="P57" s="67"/>
       <c r="Q57" s="31"/>
-      <c r="R57" s="80"/>
-      <c r="S57" s="81"/>
-      <c r="T57" s="82"/>
+      <c r="R57" s="65"/>
+      <c r="S57" s="66"/>
+      <c r="T57" s="67"/>
       <c r="U57" s="50"/>
-      <c r="V57" s="80"/>
-      <c r="W57" s="81"/>
-      <c r="X57" s="82"/>
+      <c r="V57" s="65"/>
+      <c r="W57" s="66"/>
+      <c r="X57" s="67"/>
       <c r="Y57" s="35"/>
-      <c r="Z57" s="80"/>
-      <c r="AA57" s="81"/>
-      <c r="AB57" s="82"/>
+      <c r="Z57" s="65"/>
+      <c r="AA57" s="66"/>
+      <c r="AB57" s="67"/>
       <c r="AC57" s="31"/>
-      <c r="AD57" s="80"/>
-      <c r="AE57" s="81"/>
-      <c r="AF57" s="82"/>
+      <c r="AD57" s="65"/>
+      <c r="AE57" s="66"/>
+      <c r="AF57" s="67"/>
       <c r="AG57" s="35"/>
-      <c r="AH57" s="80"/>
-      <c r="AI57" s="81"/>
-      <c r="AJ57" s="82"/>
+      <c r="AH57" s="65"/>
+      <c r="AI57" s="66"/>
+      <c r="AJ57" s="67"/>
       <c r="AK57" s="50"/>
-      <c r="AL57" s="80"/>
-      <c r="AM57" s="81"/>
-      <c r="AN57" s="82"/>
+      <c r="AL57" s="65"/>
+      <c r="AM57" s="66"/>
+      <c r="AN57" s="67"/>
       <c r="AR57" s="13"/>
     </row>
     <row r="58" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5531,48 +5568,48 @@
       <c r="AR58" s="13"/>
     </row>
     <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="65" t="s">
+      <c r="B59" s="76" t="s">
         <v>101</v>
       </c>
-      <c r="C59" s="66"/>
+      <c r="C59" s="77"/>
       <c r="D59" s="57" t="s">
         <v>102</v>
       </c>
       <c r="E59" s="50"/>
-      <c r="F59" s="75"/>
-      <c r="G59" s="76"/>
+      <c r="F59" s="68"/>
+      <c r="G59" s="69"/>
       <c r="H59" s="55"/>
       <c r="I59" s="32"/>
-      <c r="J59" s="75"/>
-      <c r="K59" s="76"/>
+      <c r="J59" s="68"/>
+      <c r="K59" s="69"/>
       <c r="L59" s="55"/>
       <c r="M59" s="6"/>
-      <c r="N59" s="70"/>
-      <c r="O59" s="71"/>
+      <c r="N59" s="81"/>
+      <c r="O59" s="82"/>
       <c r="P59" s="34"/>
       <c r="Q59" s="36"/>
-      <c r="R59" s="70"/>
-      <c r="S59" s="71"/>
+      <c r="R59" s="81"/>
+      <c r="S59" s="82"/>
       <c r="T59" s="34"/>
       <c r="U59" s="50"/>
-      <c r="V59" s="70"/>
-      <c r="W59" s="71"/>
+      <c r="V59" s="81"/>
+      <c r="W59" s="82"/>
       <c r="X59" s="34"/>
       <c r="Y59" s="32"/>
-      <c r="Z59" s="70"/>
-      <c r="AA59" s="71"/>
+      <c r="Z59" s="81"/>
+      <c r="AA59" s="82"/>
       <c r="AB59" s="34"/>
       <c r="AC59" s="32"/>
-      <c r="AD59" s="70"/>
-      <c r="AE59" s="71"/>
+      <c r="AD59" s="81"/>
+      <c r="AE59" s="82"/>
       <c r="AF59" s="34"/>
       <c r="AG59" s="50"/>
-      <c r="AH59" s="70"/>
-      <c r="AI59" s="71"/>
+      <c r="AH59" s="81"/>
+      <c r="AI59" s="82"/>
       <c r="AJ59" s="34"/>
       <c r="AK59" s="32"/>
-      <c r="AL59" s="70"/>
-      <c r="AM59" s="71"/>
+      <c r="AL59" s="81"/>
+      <c r="AM59" s="82"/>
       <c r="AN59" s="34"/>
       <c r="AR59" s="13"/>
     </row>
@@ -5591,47 +5628,47 @@
       <c r="K60" s="63"/>
       <c r="L60" s="64"/>
       <c r="M60" s="4"/>
-      <c r="N60" s="72"/>
-      <c r="O60" s="73"/>
-      <c r="P60" s="74"/>
+      <c r="N60" s="106"/>
+      <c r="O60" s="107"/>
+      <c r="P60" s="108"/>
       <c r="Q60" s="43"/>
-      <c r="R60" s="72"/>
-      <c r="S60" s="73"/>
-      <c r="T60" s="74"/>
+      <c r="R60" s="106"/>
+      <c r="S60" s="107"/>
+      <c r="T60" s="108"/>
       <c r="U60" s="32"/>
-      <c r="V60" s="72"/>
-      <c r="W60" s="73"/>
-      <c r="X60" s="74"/>
+      <c r="V60" s="106"/>
+      <c r="W60" s="107"/>
+      <c r="X60" s="108"/>
       <c r="Y60" s="32"/>
-      <c r="Z60" s="72"/>
-      <c r="AA60" s="73"/>
-      <c r="AB60" s="74"/>
+      <c r="Z60" s="106"/>
+      <c r="AA60" s="107"/>
+      <c r="AB60" s="108"/>
       <c r="AC60" s="54"/>
-      <c r="AD60" s="72"/>
-      <c r="AE60" s="73"/>
-      <c r="AF60" s="74"/>
+      <c r="AD60" s="106"/>
+      <c r="AE60" s="107"/>
+      <c r="AF60" s="108"/>
       <c r="AG60" s="32"/>
-      <c r="AH60" s="72"/>
-      <c r="AI60" s="73"/>
-      <c r="AJ60" s="74"/>
+      <c r="AH60" s="106"/>
+      <c r="AI60" s="107"/>
+      <c r="AJ60" s="108"/>
       <c r="AK60" s="32"/>
-      <c r="AL60" s="72"/>
-      <c r="AM60" s="73"/>
-      <c r="AN60" s="74"/>
+      <c r="AL60" s="106"/>
+      <c r="AM60" s="107"/>
+      <c r="AN60" s="108"/>
       <c r="AR60" s="13"/>
     </row>
     <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="77"/>
-      <c r="C61" s="78"/>
-      <c r="D61" s="79"/>
+      <c r="B61" s="73"/>
+      <c r="C61" s="74"/>
+      <c r="D61" s="75"/>
       <c r="E61" s="32"/>
-      <c r="F61" s="77"/>
-      <c r="G61" s="78"/>
-      <c r="H61" s="79"/>
+      <c r="F61" s="73"/>
+      <c r="G61" s="74"/>
+      <c r="H61" s="75"/>
       <c r="I61" s="32"/>
-      <c r="J61" s="77"/>
-      <c r="K61" s="78"/>
-      <c r="L61" s="79"/>
+      <c r="J61" s="73"/>
+      <c r="K61" s="74"/>
+      <c r="L61" s="75"/>
       <c r="M61" s="4"/>
       <c r="N61" s="83"/>
       <c r="O61" s="84"/>
@@ -5663,133 +5700,133 @@
       <c r="AR61" s="13"/>
     </row>
     <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="89" t="s">
+      <c r="B62" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="C62" s="90"/>
-      <c r="D62" s="91"/>
+      <c r="C62" s="71"/>
+      <c r="D62" s="72"/>
       <c r="E62" s="37"/>
-      <c r="F62" s="67"/>
-      <c r="G62" s="68"/>
-      <c r="H62" s="69"/>
+      <c r="F62" s="78"/>
+      <c r="G62" s="79"/>
+      <c r="H62" s="80"/>
       <c r="I62" s="35"/>
-      <c r="J62" s="89"/>
-      <c r="K62" s="90"/>
-      <c r="L62" s="91"/>
+      <c r="J62" s="70"/>
+      <c r="K62" s="71"/>
+      <c r="L62" s="72"/>
       <c r="M62" s="4"/>
-      <c r="N62" s="67"/>
-      <c r="O62" s="68"/>
-      <c r="P62" s="69"/>
+      <c r="N62" s="78"/>
+      <c r="O62" s="79"/>
+      <c r="P62" s="80"/>
       <c r="Q62" s="44"/>
-      <c r="R62" s="89"/>
-      <c r="S62" s="90"/>
-      <c r="T62" s="91"/>
+      <c r="R62" s="70"/>
+      <c r="S62" s="71"/>
+      <c r="T62" s="72"/>
       <c r="U62" s="37"/>
-      <c r="V62" s="89"/>
-      <c r="W62" s="90"/>
-      <c r="X62" s="91"/>
+      <c r="V62" s="70"/>
+      <c r="W62" s="71"/>
+      <c r="X62" s="72"/>
       <c r="Y62" s="35"/>
-      <c r="Z62" s="67"/>
-      <c r="AA62" s="68"/>
-      <c r="AB62" s="69"/>
+      <c r="Z62" s="78"/>
+      <c r="AA62" s="79"/>
+      <c r="AB62" s="80"/>
       <c r="AC62" s="35"/>
-      <c r="AD62" s="89"/>
-      <c r="AE62" s="90"/>
-      <c r="AF62" s="91"/>
+      <c r="AD62" s="70"/>
+      <c r="AE62" s="71"/>
+      <c r="AF62" s="72"/>
       <c r="AG62" s="37"/>
-      <c r="AH62" s="67"/>
-      <c r="AI62" s="68"/>
-      <c r="AJ62" s="69"/>
+      <c r="AH62" s="78"/>
+      <c r="AI62" s="79"/>
+      <c r="AJ62" s="80"/>
       <c r="AK62" s="35"/>
-      <c r="AL62" s="89"/>
-      <c r="AM62" s="90"/>
-      <c r="AN62" s="91"/>
+      <c r="AL62" s="70"/>
+      <c r="AM62" s="71"/>
+      <c r="AN62" s="72"/>
       <c r="AR62" s="13"/>
     </row>
     <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="67" t="s">
+      <c r="B63" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="C63" s="68"/>
-      <c r="D63" s="69"/>
+      <c r="C63" s="79"/>
+      <c r="D63" s="80"/>
       <c r="E63" s="44"/>
-      <c r="F63" s="67"/>
-      <c r="G63" s="68"/>
-      <c r="H63" s="69"/>
+      <c r="F63" s="78"/>
+      <c r="G63" s="79"/>
+      <c r="H63" s="80"/>
       <c r="I63" s="40"/>
-      <c r="J63" s="67"/>
-      <c r="K63" s="68"/>
-      <c r="L63" s="69"/>
+      <c r="J63" s="78"/>
+      <c r="K63" s="79"/>
+      <c r="L63" s="80"/>
       <c r="M63" s="5"/>
-      <c r="N63" s="67"/>
-      <c r="O63" s="68"/>
-      <c r="P63" s="69"/>
+      <c r="N63" s="78"/>
+      <c r="O63" s="79"/>
+      <c r="P63" s="80"/>
       <c r="Q63" s="44"/>
-      <c r="R63" s="67"/>
-      <c r="S63" s="68"/>
-      <c r="T63" s="69"/>
+      <c r="R63" s="78"/>
+      <c r="S63" s="79"/>
+      <c r="T63" s="80"/>
       <c r="U63" s="44"/>
-      <c r="V63" s="67"/>
-      <c r="W63" s="68"/>
-      <c r="X63" s="69"/>
+      <c r="V63" s="78"/>
+      <c r="W63" s="79"/>
+      <c r="X63" s="80"/>
       <c r="Y63" s="40"/>
-      <c r="Z63" s="67"/>
-      <c r="AA63" s="68"/>
-      <c r="AB63" s="69"/>
+      <c r="Z63" s="78"/>
+      <c r="AA63" s="79"/>
+      <c r="AB63" s="80"/>
       <c r="AC63" s="40"/>
-      <c r="AD63" s="67"/>
-      <c r="AE63" s="68"/>
-      <c r="AF63" s="69"/>
+      <c r="AD63" s="78"/>
+      <c r="AE63" s="79"/>
+      <c r="AF63" s="80"/>
       <c r="AG63" s="44"/>
-      <c r="AH63" s="67"/>
-      <c r="AI63" s="68"/>
-      <c r="AJ63" s="69"/>
+      <c r="AH63" s="78"/>
+      <c r="AI63" s="79"/>
+      <c r="AJ63" s="80"/>
       <c r="AK63" s="40"/>
-      <c r="AL63" s="67"/>
-      <c r="AM63" s="68"/>
-      <c r="AN63" s="69"/>
+      <c r="AL63" s="78"/>
+      <c r="AM63" s="79"/>
+      <c r="AN63" s="80"/>
       <c r="AR63" s="13"/>
     </row>
     <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="80"/>
-      <c r="C64" s="81"/>
-      <c r="D64" s="82"/>
+      <c r="B64" s="65"/>
+      <c r="C64" s="66"/>
+      <c r="D64" s="67"/>
       <c r="E64" s="35"/>
-      <c r="F64" s="80"/>
-      <c r="G64" s="81"/>
-      <c r="H64" s="82"/>
+      <c r="F64" s="65"/>
+      <c r="G64" s="66"/>
+      <c r="H64" s="67"/>
       <c r="I64" s="50"/>
-      <c r="J64" s="80"/>
-      <c r="K64" s="81"/>
-      <c r="L64" s="82"/>
+      <c r="J64" s="65"/>
+      <c r="K64" s="66"/>
+      <c r="L64" s="67"/>
       <c r="M64" s="5"/>
-      <c r="N64" s="80"/>
-      <c r="O64" s="81"/>
-      <c r="P64" s="82"/>
+      <c r="N64" s="65"/>
+      <c r="O64" s="66"/>
+      <c r="P64" s="67"/>
       <c r="Q64" s="50"/>
-      <c r="R64" s="80"/>
-      <c r="S64" s="81"/>
-      <c r="T64" s="82"/>
+      <c r="R64" s="65"/>
+      <c r="S64" s="66"/>
+      <c r="T64" s="67"/>
       <c r="U64" s="35"/>
-      <c r="V64" s="80"/>
-      <c r="W64" s="81"/>
-      <c r="X64" s="82"/>
+      <c r="V64" s="65"/>
+      <c r="W64" s="66"/>
+      <c r="X64" s="67"/>
       <c r="Y64" s="50"/>
-      <c r="Z64" s="80"/>
-      <c r="AA64" s="81"/>
-      <c r="AB64" s="82"/>
+      <c r="Z64" s="65"/>
+      <c r="AA64" s="66"/>
+      <c r="AB64" s="67"/>
       <c r="AC64" s="50"/>
-      <c r="AD64" s="80"/>
-      <c r="AE64" s="81"/>
-      <c r="AF64" s="82"/>
+      <c r="AD64" s="65"/>
+      <c r="AE64" s="66"/>
+      <c r="AF64" s="67"/>
       <c r="AG64" s="35"/>
-      <c r="AH64" s="80"/>
-      <c r="AI64" s="81"/>
-      <c r="AJ64" s="82"/>
+      <c r="AH64" s="65"/>
+      <c r="AI64" s="66"/>
+      <c r="AJ64" s="67"/>
       <c r="AK64" s="50"/>
-      <c r="AL64" s="80"/>
-      <c r="AM64" s="81"/>
-      <c r="AN64" s="82"/>
+      <c r="AL64" s="65"/>
+      <c r="AM64" s="66"/>
+      <c r="AN64" s="67"/>
       <c r="AR64" s="13"/>
     </row>
     <row r="65" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5840,52 +5877,52 @@
     </row>
     <row r="66" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="12"/>
-      <c r="B66" s="65" t="s">
+      <c r="B66" s="76" t="s">
         <v>101</v>
       </c>
-      <c r="C66" s="66"/>
+      <c r="C66" s="77"/>
       <c r="D66" s="57" t="s">
         <v>54</v>
       </c>
       <c r="E66" s="36"/>
-      <c r="F66" s="75"/>
-      <c r="G66" s="76"/>
+      <c r="F66" s="68"/>
+      <c r="G66" s="69"/>
       <c r="H66" s="55"/>
       <c r="I66" s="32"/>
-      <c r="J66" s="75"/>
-      <c r="K66" s="76"/>
+      <c r="J66" s="68"/>
+      <c r="K66" s="69"/>
       <c r="L66" s="55"/>
       <c r="M66" s="6"/>
-      <c r="N66" s="70" t="s">
+      <c r="N66" s="81" t="s">
         <v>107</v>
       </c>
-      <c r="O66" s="71"/>
+      <c r="O66" s="82"/>
       <c r="P66" s="34"/>
       <c r="Q66" s="36"/>
-      <c r="R66" s="70"/>
-      <c r="S66" s="71"/>
+      <c r="R66" s="81"/>
+      <c r="S66" s="82"/>
       <c r="T66" s="34"/>
       <c r="U66" s="36"/>
-      <c r="V66" s="70"/>
-      <c r="W66" s="71"/>
+      <c r="V66" s="81"/>
+      <c r="W66" s="82"/>
       <c r="X66" s="34"/>
       <c r="Y66" s="36"/>
-      <c r="Z66" s="70"/>
-      <c r="AA66" s="71"/>
+      <c r="Z66" s="81"/>
+      <c r="AA66" s="82"/>
       <c r="AB66" s="34"/>
       <c r="AC66" s="36"/>
-      <c r="AD66" s="70"/>
-      <c r="AE66" s="71"/>
+      <c r="AD66" s="81"/>
+      <c r="AE66" s="82"/>
       <c r="AF66" s="34"/>
       <c r="AG66" s="36"/>
-      <c r="AH66" s="70"/>
-      <c r="AI66" s="71"/>
+      <c r="AH66" s="81"/>
+      <c r="AI66" s="82"/>
       <c r="AJ66" s="34"/>
       <c r="AK66" s="32"/>
-      <c r="AL66" s="119" t="s">
-        <v>115</v>
-      </c>
-      <c r="AM66" s="120"/>
+      <c r="AL66" s="117" t="s">
+        <v>114</v>
+      </c>
+      <c r="AM66" s="118"/>
       <c r="AN66" s="59"/>
       <c r="AO66" s="17"/>
       <c r="AP66" s="12"/>
@@ -5908,37 +5945,37 @@
       <c r="K67" s="63"/>
       <c r="L67" s="64"/>
       <c r="M67" s="4"/>
-      <c r="N67" s="72" t="s">
+      <c r="N67" s="106" t="s">
         <v>108</v>
       </c>
-      <c r="O67" s="73"/>
-      <c r="P67" s="74"/>
+      <c r="O67" s="107"/>
+      <c r="P67" s="108"/>
       <c r="Q67" s="37"/>
-      <c r="R67" s="72"/>
-      <c r="S67" s="73"/>
-      <c r="T67" s="74"/>
+      <c r="R67" s="106"/>
+      <c r="S67" s="107"/>
+      <c r="T67" s="108"/>
       <c r="U67" s="36"/>
-      <c r="V67" s="72"/>
-      <c r="W67" s="73"/>
-      <c r="X67" s="74"/>
+      <c r="V67" s="106"/>
+      <c r="W67" s="107"/>
+      <c r="X67" s="108"/>
       <c r="Y67" s="36"/>
-      <c r="Z67" s="72"/>
-      <c r="AA67" s="73"/>
-      <c r="AB67" s="74"/>
+      <c r="Z67" s="106"/>
+      <c r="AA67" s="107"/>
+      <c r="AB67" s="108"/>
       <c r="AC67" s="36"/>
-      <c r="AD67" s="72"/>
-      <c r="AE67" s="73"/>
-      <c r="AF67" s="74"/>
+      <c r="AD67" s="106"/>
+      <c r="AE67" s="107"/>
+      <c r="AF67" s="108"/>
       <c r="AG67" s="36"/>
-      <c r="AH67" s="72"/>
-      <c r="AI67" s="73"/>
-      <c r="AJ67" s="74"/>
+      <c r="AH67" s="106"/>
+      <c r="AI67" s="107"/>
+      <c r="AJ67" s="108"/>
       <c r="AK67" s="54"/>
-      <c r="AL67" s="145" t="s">
+      <c r="AL67" s="109" t="s">
         <v>51</v>
       </c>
-      <c r="AM67" s="146"/>
-      <c r="AN67" s="147"/>
+      <c r="AM67" s="110"/>
+      <c r="AN67" s="111"/>
       <c r="AO67" s="17"/>
       <c r="AP67" s="12"/>
       <c r="AQ67" s="12"/>
@@ -5946,17 +5983,17 @@
     </row>
     <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="12"/>
-      <c r="B68" s="77"/>
-      <c r="C68" s="78"/>
-      <c r="D68" s="79"/>
+      <c r="B68" s="73"/>
+      <c r="C68" s="74"/>
+      <c r="D68" s="75"/>
       <c r="E68" s="43"/>
-      <c r="F68" s="77"/>
-      <c r="G68" s="78"/>
-      <c r="H68" s="79"/>
+      <c r="F68" s="73"/>
+      <c r="G68" s="74"/>
+      <c r="H68" s="75"/>
       <c r="I68" s="35"/>
-      <c r="J68" s="77"/>
-      <c r="K68" s="78"/>
-      <c r="L68" s="79"/>
+      <c r="J68" s="73"/>
+      <c r="K68" s="74"/>
+      <c r="L68" s="75"/>
       <c r="M68" s="4"/>
       <c r="N68" s="83"/>
       <c r="O68" s="84"/>
@@ -5982,11 +6019,11 @@
       <c r="AI68" s="84"/>
       <c r="AJ68" s="85"/>
       <c r="AK68" s="35"/>
-      <c r="AL68" s="113" t="s">
+      <c r="AL68" s="114" t="s">
         <v>78</v>
       </c>
-      <c r="AM68" s="114"/>
-      <c r="AN68" s="144"/>
+      <c r="AM68" s="115"/>
+      <c r="AN68" s="116"/>
       <c r="AO68" s="17"/>
       <c r="AP68" s="27" t="s">
         <v>32</v>
@@ -5996,51 +6033,51 @@
     </row>
     <row r="69" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="12"/>
-      <c r="B69" s="67" t="s">
+      <c r="B69" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="C69" s="68"/>
-      <c r="D69" s="69"/>
+      <c r="C69" s="79"/>
+      <c r="D69" s="80"/>
       <c r="E69" s="37"/>
-      <c r="F69" s="89"/>
-      <c r="G69" s="90"/>
-      <c r="H69" s="91"/>
+      <c r="F69" s="70"/>
+      <c r="G69" s="71"/>
+      <c r="H69" s="72"/>
       <c r="I69" s="37"/>
-      <c r="J69" s="67"/>
-      <c r="K69" s="68"/>
-      <c r="L69" s="69"/>
+      <c r="J69" s="78"/>
+      <c r="K69" s="79"/>
+      <c r="L69" s="80"/>
       <c r="M69" s="4"/>
-      <c r="N69" s="67" t="s">
+      <c r="N69" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="O69" s="68"/>
-      <c r="P69" s="69"/>
+      <c r="O69" s="79"/>
+      <c r="P69" s="80"/>
       <c r="Q69" s="43"/>
-      <c r="R69" s="67"/>
-      <c r="S69" s="68"/>
-      <c r="T69" s="69"/>
+      <c r="R69" s="78"/>
+      <c r="S69" s="79"/>
+      <c r="T69" s="80"/>
       <c r="U69" s="37"/>
-      <c r="V69" s="89"/>
-      <c r="W69" s="90"/>
-      <c r="X69" s="91"/>
+      <c r="V69" s="70"/>
+      <c r="W69" s="71"/>
+      <c r="X69" s="72"/>
       <c r="Y69" s="35"/>
-      <c r="Z69" s="89"/>
-      <c r="AA69" s="90"/>
-      <c r="AB69" s="91"/>
+      <c r="Z69" s="70"/>
+      <c r="AA69" s="71"/>
+      <c r="AB69" s="72"/>
       <c r="AC69" s="43"/>
-      <c r="AD69" s="67"/>
-      <c r="AE69" s="68"/>
-      <c r="AF69" s="69"/>
+      <c r="AD69" s="78"/>
+      <c r="AE69" s="79"/>
+      <c r="AF69" s="80"/>
       <c r="AG69" s="37"/>
-      <c r="AH69" s="89"/>
-      <c r="AI69" s="90"/>
-      <c r="AJ69" s="91"/>
+      <c r="AH69" s="70"/>
+      <c r="AI69" s="71"/>
+      <c r="AJ69" s="72"/>
       <c r="AK69" s="37"/>
-      <c r="AL69" s="67" t="s">
+      <c r="AL69" s="78" t="s">
         <v>80</v>
       </c>
-      <c r="AM69" s="68"/>
-      <c r="AN69" s="69"/>
+      <c r="AM69" s="79"/>
+      <c r="AN69" s="80"/>
       <c r="AO69" s="12"/>
       <c r="AP69" s="27" t="s">
         <v>33</v>
@@ -6050,49 +6087,49 @@
     </row>
     <row r="70" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="12"/>
-      <c r="B70" s="67" t="s">
+      <c r="B70" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="C70" s="68"/>
-      <c r="D70" s="69"/>
+      <c r="C70" s="79"/>
+      <c r="D70" s="80"/>
       <c r="E70" s="44"/>
-      <c r="F70" s="67"/>
-      <c r="G70" s="68"/>
-      <c r="H70" s="69"/>
+      <c r="F70" s="78"/>
+      <c r="G70" s="79"/>
+      <c r="H70" s="80"/>
       <c r="I70" s="44"/>
-      <c r="J70" s="67"/>
-      <c r="K70" s="68"/>
-      <c r="L70" s="69"/>
+      <c r="J70" s="78"/>
+      <c r="K70" s="79"/>
+      <c r="L70" s="80"/>
       <c r="M70" s="9"/>
-      <c r="N70" s="67"/>
-      <c r="O70" s="68"/>
-      <c r="P70" s="69"/>
+      <c r="N70" s="78"/>
+      <c r="O70" s="79"/>
+      <c r="P70" s="80"/>
       <c r="Q70" s="50"/>
-      <c r="R70" s="67"/>
-      <c r="S70" s="68"/>
-      <c r="T70" s="69"/>
+      <c r="R70" s="78"/>
+      <c r="S70" s="79"/>
+      <c r="T70" s="80"/>
       <c r="U70" s="44"/>
-      <c r="V70" s="67"/>
-      <c r="W70" s="68"/>
-      <c r="X70" s="69"/>
+      <c r="V70" s="78"/>
+      <c r="W70" s="79"/>
+      <c r="X70" s="80"/>
       <c r="Y70" s="40"/>
-      <c r="Z70" s="67"/>
-      <c r="AA70" s="68"/>
-      <c r="AB70" s="69"/>
+      <c r="Z70" s="78"/>
+      <c r="AA70" s="79"/>
+      <c r="AB70" s="80"/>
       <c r="AC70" s="44"/>
-      <c r="AD70" s="67"/>
-      <c r="AE70" s="68"/>
-      <c r="AF70" s="69"/>
+      <c r="AD70" s="78"/>
+      <c r="AE70" s="79"/>
+      <c r="AF70" s="80"/>
       <c r="AG70" s="44"/>
-      <c r="AH70" s="67"/>
-      <c r="AI70" s="68"/>
-      <c r="AJ70" s="69"/>
+      <c r="AH70" s="78"/>
+      <c r="AI70" s="79"/>
+      <c r="AJ70" s="80"/>
       <c r="AK70" s="44"/>
-      <c r="AL70" s="67" t="s">
+      <c r="AL70" s="78" t="s">
         <v>81</v>
       </c>
-      <c r="AM70" s="68"/>
-      <c r="AN70" s="69"/>
+      <c r="AM70" s="79"/>
+      <c r="AN70" s="80"/>
       <c r="AO70" s="12"/>
       <c r="AP70" s="27" t="s">
         <v>34</v>
@@ -6102,47 +6139,47 @@
     </row>
     <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A71" s="12"/>
-      <c r="B71" s="80"/>
-      <c r="C71" s="81"/>
-      <c r="D71" s="82"/>
+      <c r="B71" s="65"/>
+      <c r="C71" s="66"/>
+      <c r="D71" s="67"/>
       <c r="E71" s="44"/>
-      <c r="F71" s="80"/>
-      <c r="G71" s="81"/>
-      <c r="H71" s="82"/>
+      <c r="F71" s="65"/>
+      <c r="G71" s="66"/>
+      <c r="H71" s="67"/>
       <c r="I71" s="44"/>
-      <c r="J71" s="80"/>
-      <c r="K71" s="81"/>
-      <c r="L71" s="82"/>
+      <c r="J71" s="65"/>
+      <c r="K71" s="66"/>
+      <c r="L71" s="67"/>
       <c r="M71" s="9"/>
-      <c r="N71" s="80"/>
-      <c r="O71" s="81"/>
-      <c r="P71" s="82"/>
+      <c r="N71" s="65"/>
+      <c r="O71" s="66"/>
+      <c r="P71" s="67"/>
       <c r="Q71" s="50"/>
-      <c r="R71" s="80"/>
-      <c r="S71" s="81"/>
-      <c r="T71" s="82"/>
+      <c r="R71" s="65"/>
+      <c r="S71" s="66"/>
+      <c r="T71" s="67"/>
       <c r="U71" s="44"/>
-      <c r="V71" s="80"/>
-      <c r="W71" s="81"/>
-      <c r="X71" s="82"/>
+      <c r="V71" s="65"/>
+      <c r="W71" s="66"/>
+      <c r="X71" s="67"/>
       <c r="Y71" s="44"/>
-      <c r="Z71" s="80"/>
-      <c r="AA71" s="81"/>
-      <c r="AB71" s="82"/>
+      <c r="Z71" s="65"/>
+      <c r="AA71" s="66"/>
+      <c r="AB71" s="67"/>
       <c r="AC71" s="50"/>
-      <c r="AD71" s="80"/>
-      <c r="AE71" s="81"/>
-      <c r="AF71" s="82"/>
+      <c r="AD71" s="65"/>
+      <c r="AE71" s="66"/>
+      <c r="AF71" s="67"/>
       <c r="AG71" s="44"/>
-      <c r="AH71" s="80"/>
-      <c r="AI71" s="81"/>
-      <c r="AJ71" s="82"/>
+      <c r="AH71" s="65"/>
+      <c r="AI71" s="66"/>
+      <c r="AJ71" s="67"/>
       <c r="AK71" s="44"/>
-      <c r="AL71" s="80" t="s">
+      <c r="AL71" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="AM71" s="81"/>
-      <c r="AN71" s="82"/>
+      <c r="AM71" s="66"/>
+      <c r="AN71" s="67"/>
       <c r="AO71" s="12"/>
       <c r="AP71" s="27" t="s">
         <v>35</v>
@@ -6210,23 +6247,23 @@
       <c r="K73" s="33"/>
       <c r="L73" s="33"/>
       <c r="M73" s="14"/>
-      <c r="N73" s="101" t="s">
+      <c r="N73" s="124" t="s">
         <v>31</v>
       </c>
-      <c r="O73" s="101"/>
-      <c r="P73" s="101"/>
-      <c r="Q73" s="101"/>
-      <c r="R73" s="101"/>
-      <c r="S73" s="101"/>
-      <c r="T73" s="101"/>
-      <c r="U73" s="101"/>
-      <c r="V73" s="101"/>
-      <c r="W73" s="101"/>
-      <c r="X73" s="101"/>
-      <c r="Y73" s="101"/>
-      <c r="Z73" s="101"/>
-      <c r="AA73" s="101"/>
-      <c r="AB73" s="101"/>
+      <c r="O73" s="124"/>
+      <c r="P73" s="124"/>
+      <c r="Q73" s="124"/>
+      <c r="R73" s="124"/>
+      <c r="S73" s="124"/>
+      <c r="T73" s="124"/>
+      <c r="U73" s="124"/>
+      <c r="V73" s="124"/>
+      <c r="W73" s="124"/>
+      <c r="X73" s="124"/>
+      <c r="Y73" s="124"/>
+      <c r="Z73" s="124"/>
+      <c r="AA73" s="124"/>
+      <c r="AB73" s="124"/>
       <c r="AD73" s="40"/>
       <c r="AE73" s="33"/>
       <c r="AF73" s="33"/>
@@ -6257,21 +6294,21 @@
       <c r="K74" s="33"/>
       <c r="L74" s="33"/>
       <c r="M74" s="14"/>
-      <c r="N74" s="101"/>
-      <c r="O74" s="101"/>
-      <c r="P74" s="101"/>
-      <c r="Q74" s="101"/>
-      <c r="R74" s="101"/>
-      <c r="S74" s="101"/>
-      <c r="T74" s="101"/>
-      <c r="U74" s="101"/>
-      <c r="V74" s="101"/>
-      <c r="W74" s="101"/>
-      <c r="X74" s="101"/>
-      <c r="Y74" s="101"/>
-      <c r="Z74" s="101"/>
-      <c r="AA74" s="101"/>
-      <c r="AB74" s="101"/>
+      <c r="N74" s="124"/>
+      <c r="O74" s="124"/>
+      <c r="P74" s="124"/>
+      <c r="Q74" s="124"/>
+      <c r="R74" s="124"/>
+      <c r="S74" s="124"/>
+      <c r="T74" s="124"/>
+      <c r="U74" s="124"/>
+      <c r="V74" s="124"/>
+      <c r="W74" s="124"/>
+      <c r="X74" s="124"/>
+      <c r="Y74" s="124"/>
+      <c r="Z74" s="124"/>
+      <c r="AA74" s="124"/>
+      <c r="AB74" s="124"/>
       <c r="AC74" s="21"/>
       <c r="AD74" s="33"/>
       <c r="AE74" s="33"/>
@@ -6291,76 +6328,76 @@
     </row>
     <row r="75" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="12"/>
-      <c r="B75" s="75" t="s">
+      <c r="B75" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="C75" s="76"/>
+      <c r="C75" s="69"/>
       <c r="D75" s="55" t="s">
         <v>52</v>
       </c>
       <c r="E75" s="32"/>
-      <c r="F75" s="75" t="s">
+      <c r="F75" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="G75" s="76"/>
+      <c r="G75" s="69"/>
       <c r="H75" s="55" t="s">
         <v>52</v>
       </c>
       <c r="I75" s="32"/>
-      <c r="J75" s="75"/>
-      <c r="K75" s="76"/>
+      <c r="J75" s="68"/>
+      <c r="K75" s="69"/>
       <c r="L75" s="55"/>
       <c r="M75" s="14"/>
-      <c r="N75" s="70" t="s">
+      <c r="N75" s="81" t="s">
         <v>58</v>
       </c>
-      <c r="O75" s="71"/>
+      <c r="O75" s="82"/>
       <c r="P75" s="34" t="s">
         <v>52</v>
       </c>
       <c r="Q75" s="44"/>
-      <c r="R75" s="70" t="s">
+      <c r="R75" s="81" t="s">
         <v>58</v>
       </c>
-      <c r="S75" s="71"/>
+      <c r="S75" s="82"/>
       <c r="T75" s="34" t="s">
         <v>52</v>
       </c>
       <c r="U75" s="36"/>
-      <c r="V75" s="70" t="s">
+      <c r="V75" s="81" t="s">
         <v>58</v>
       </c>
-      <c r="W75" s="71"/>
+      <c r="W75" s="82"/>
       <c r="X75" s="34" t="s">
         <v>52</v>
       </c>
       <c r="Y75" s="32"/>
-      <c r="Z75" s="70" t="s">
+      <c r="Z75" s="81" t="s">
         <v>58</v>
       </c>
-      <c r="AA75" s="71"/>
+      <c r="AA75" s="82"/>
       <c r="AB75" s="34" t="s">
         <v>52</v>
       </c>
       <c r="AC75" s="32"/>
-      <c r="AD75" s="70" t="s">
+      <c r="AD75" s="81" t="s">
         <v>58</v>
       </c>
-      <c r="AE75" s="71"/>
+      <c r="AE75" s="82"/>
       <c r="AF75" s="34" t="s">
         <v>52</v>
       </c>
       <c r="AG75" s="32"/>
-      <c r="AH75" s="70" t="s">
+      <c r="AH75" s="81" t="s">
         <v>58</v>
       </c>
-      <c r="AI75" s="71"/>
+      <c r="AI75" s="82"/>
       <c r="AJ75" s="34" t="s">
         <v>52</v>
       </c>
       <c r="AK75" s="32"/>
-      <c r="AL75" s="70"/>
-      <c r="AM75" s="71"/>
+      <c r="AL75" s="81"/>
+      <c r="AM75" s="82"/>
       <c r="AN75" s="34"/>
       <c r="AO75" s="16"/>
       <c r="AP75" s="29"/>
@@ -6385,45 +6422,45 @@
       <c r="K76" s="63"/>
       <c r="L76" s="64"/>
       <c r="M76" s="4"/>
-      <c r="N76" s="72" t="s">
+      <c r="N76" s="106" t="s">
         <v>59</v>
       </c>
-      <c r="O76" s="73"/>
-      <c r="P76" s="74"/>
+      <c r="O76" s="107"/>
+      <c r="P76" s="108"/>
       <c r="Q76" s="44"/>
-      <c r="R76" s="72" t="s">
+      <c r="R76" s="106" t="s">
         <v>59</v>
       </c>
-      <c r="S76" s="73"/>
-      <c r="T76" s="74"/>
+      <c r="S76" s="107"/>
+      <c r="T76" s="108"/>
       <c r="U76" s="32"/>
-      <c r="V76" s="72" t="s">
+      <c r="V76" s="106" t="s">
         <v>59</v>
       </c>
-      <c r="W76" s="73"/>
-      <c r="X76" s="74"/>
+      <c r="W76" s="107"/>
+      <c r="X76" s="108"/>
       <c r="Y76" s="32"/>
-      <c r="Z76" s="72" t="s">
+      <c r="Z76" s="106" t="s">
         <v>59</v>
       </c>
-      <c r="AA76" s="73"/>
-      <c r="AB76" s="74"/>
+      <c r="AA76" s="107"/>
+      <c r="AB76" s="108"/>
       <c r="AC76" s="35"/>
-      <c r="AD76" s="72" t="s">
+      <c r="AD76" s="106" t="s">
         <v>59</v>
       </c>
-      <c r="AE76" s="73"/>
-      <c r="AF76" s="74"/>
+      <c r="AE76" s="107"/>
+      <c r="AF76" s="108"/>
       <c r="AG76" s="32"/>
-      <c r="AH76" s="72" t="s">
+      <c r="AH76" s="106" t="s">
         <v>59</v>
       </c>
-      <c r="AI76" s="73"/>
-      <c r="AJ76" s="74"/>
+      <c r="AI76" s="107"/>
+      <c r="AJ76" s="108"/>
       <c r="AK76" s="32"/>
-      <c r="AL76" s="72"/>
-      <c r="AM76" s="73"/>
-      <c r="AN76" s="74"/>
+      <c r="AL76" s="106"/>
+      <c r="AM76" s="107"/>
+      <c r="AN76" s="108"/>
       <c r="AO76" s="12"/>
       <c r="AP76" s="29"/>
       <c r="AQ76" s="26"/>
@@ -6431,17 +6468,17 @@
     </row>
     <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="16"/>
-      <c r="B77" s="77"/>
-      <c r="C77" s="78"/>
-      <c r="D77" s="79"/>
+      <c r="B77" s="73"/>
+      <c r="C77" s="74"/>
+      <c r="D77" s="75"/>
       <c r="E77" s="32"/>
-      <c r="F77" s="77"/>
-      <c r="G77" s="78"/>
-      <c r="H77" s="79"/>
+      <c r="F77" s="73"/>
+      <c r="G77" s="74"/>
+      <c r="H77" s="75"/>
       <c r="I77" s="32"/>
-      <c r="J77" s="77"/>
-      <c r="K77" s="78"/>
-      <c r="L77" s="79"/>
+      <c r="J77" s="73"/>
+      <c r="K77" s="74"/>
+      <c r="L77" s="75"/>
       <c r="M77" s="4"/>
       <c r="N77" s="83"/>
       <c r="O77" s="84"/>
@@ -6477,61 +6514,61 @@
     </row>
     <row r="78" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="16"/>
-      <c r="B78" s="89" t="s">
+      <c r="B78" s="70" t="s">
         <v>29</v>
       </c>
-      <c r="C78" s="90"/>
-      <c r="D78" s="91"/>
+      <c r="C78" s="71"/>
+      <c r="D78" s="72"/>
       <c r="E78" s="32"/>
-      <c r="F78" s="89" t="s">
+      <c r="F78" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="G78" s="90"/>
-      <c r="H78" s="91"/>
+      <c r="G78" s="71"/>
+      <c r="H78" s="72"/>
       <c r="I78" s="43"/>
-      <c r="J78" s="89"/>
-      <c r="K78" s="90"/>
-      <c r="L78" s="91"/>
+      <c r="J78" s="70"/>
+      <c r="K78" s="71"/>
+      <c r="L78" s="72"/>
       <c r="M78" s="5"/>
-      <c r="N78" s="89" t="s">
+      <c r="N78" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="O78" s="90"/>
-      <c r="P78" s="91"/>
+      <c r="O78" s="71"/>
+      <c r="P78" s="72"/>
       <c r="Q78" s="44"/>
-      <c r="R78" s="89" t="s">
+      <c r="R78" s="70" t="s">
         <v>29</v>
       </c>
-      <c r="S78" s="90"/>
-      <c r="T78" s="91"/>
+      <c r="S78" s="71"/>
+      <c r="T78" s="72"/>
       <c r="U78" s="32"/>
-      <c r="V78" s="89" t="s">
+      <c r="V78" s="70" t="s">
         <v>29</v>
       </c>
-      <c r="W78" s="90"/>
-      <c r="X78" s="91"/>
+      <c r="W78" s="71"/>
+      <c r="X78" s="72"/>
       <c r="Y78" s="32"/>
-      <c r="Z78" s="89" t="s">
+      <c r="Z78" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="AA78" s="90"/>
-      <c r="AB78" s="91"/>
+      <c r="AA78" s="71"/>
+      <c r="AB78" s="72"/>
       <c r="AC78" s="32"/>
-      <c r="AD78" s="89" t="s">
+      <c r="AD78" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="AE78" s="90"/>
-      <c r="AF78" s="91"/>
+      <c r="AE78" s="71"/>
+      <c r="AF78" s="72"/>
       <c r="AG78" s="32"/>
-      <c r="AH78" s="89" t="s">
+      <c r="AH78" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="AI78" s="90"/>
-      <c r="AJ78" s="91"/>
+      <c r="AI78" s="71"/>
+      <c r="AJ78" s="72"/>
       <c r="AK78" s="43"/>
-      <c r="AL78" s="89"/>
-      <c r="AM78" s="90"/>
-      <c r="AN78" s="91"/>
+      <c r="AL78" s="70"/>
+      <c r="AM78" s="71"/>
+      <c r="AN78" s="72"/>
       <c r="AO78" s="12"/>
       <c r="AP78" s="29"/>
       <c r="AQ78" s="26"/>
@@ -6539,45 +6576,45 @@
     </row>
     <row r="79" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A79" s="16"/>
-      <c r="B79" s="80"/>
-      <c r="C79" s="81"/>
-      <c r="D79" s="82"/>
+      <c r="B79" s="65"/>
+      <c r="C79" s="66"/>
+      <c r="D79" s="67"/>
       <c r="E79" s="31"/>
-      <c r="F79" s="80"/>
-      <c r="G79" s="81"/>
-      <c r="H79" s="82"/>
+      <c r="F79" s="65"/>
+      <c r="G79" s="66"/>
+      <c r="H79" s="67"/>
       <c r="I79" s="32"/>
-      <c r="J79" s="80"/>
-      <c r="K79" s="81"/>
-      <c r="L79" s="82"/>
+      <c r="J79" s="65"/>
+      <c r="K79" s="66"/>
+      <c r="L79" s="67"/>
       <c r="M79" s="5"/>
-      <c r="N79" s="80"/>
-      <c r="O79" s="81"/>
-      <c r="P79" s="82"/>
+      <c r="N79" s="65"/>
+      <c r="O79" s="66"/>
+      <c r="P79" s="67"/>
       <c r="Q79" s="31"/>
-      <c r="R79" s="80"/>
-      <c r="S79" s="81"/>
-      <c r="T79" s="82"/>
+      <c r="R79" s="65"/>
+      <c r="S79" s="66"/>
+      <c r="T79" s="67"/>
       <c r="U79" s="32"/>
-      <c r="V79" s="80"/>
-      <c r="W79" s="81"/>
-      <c r="X79" s="82"/>
+      <c r="V79" s="65"/>
+      <c r="W79" s="66"/>
+      <c r="X79" s="67"/>
       <c r="Y79" s="32"/>
-      <c r="Z79" s="80"/>
-      <c r="AA79" s="81"/>
-      <c r="AB79" s="82"/>
+      <c r="Z79" s="65"/>
+      <c r="AA79" s="66"/>
+      <c r="AB79" s="67"/>
       <c r="AC79" s="32"/>
-      <c r="AD79" s="80"/>
-      <c r="AE79" s="81"/>
-      <c r="AF79" s="82"/>
+      <c r="AD79" s="65"/>
+      <c r="AE79" s="66"/>
+      <c r="AF79" s="67"/>
       <c r="AG79" s="31"/>
-      <c r="AH79" s="80"/>
-      <c r="AI79" s="81"/>
-      <c r="AJ79" s="82"/>
+      <c r="AH79" s="65"/>
+      <c r="AI79" s="66"/>
+      <c r="AJ79" s="67"/>
       <c r="AK79" s="32"/>
-      <c r="AL79" s="80"/>
-      <c r="AM79" s="81"/>
-      <c r="AN79" s="82"/>
+      <c r="AL79" s="65"/>
+      <c r="AM79" s="66"/>
+      <c r="AN79" s="67"/>
       <c r="AO79" s="12"/>
       <c r="AP79" s="29"/>
       <c r="AQ79" s="26"/>
@@ -6631,62 +6668,62 @@
     </row>
     <row r="81" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="12"/>
-      <c r="B81" s="75" t="s">
+      <c r="B81" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="C81" s="76"/>
+      <c r="C81" s="69"/>
       <c r="D81" s="55"/>
       <c r="E81" s="32"/>
-      <c r="F81" s="75" t="s">
+      <c r="F81" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="G81" s="76"/>
+      <c r="G81" s="69"/>
       <c r="H81" s="55"/>
       <c r="I81" s="50"/>
-      <c r="J81" s="75" t="s">
+      <c r="J81" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="K81" s="76"/>
+      <c r="K81" s="69"/>
       <c r="L81" s="55"/>
       <c r="M81" s="5"/>
-      <c r="N81" s="70" t="s">
+      <c r="N81" s="81" t="s">
         <v>56</v>
       </c>
-      <c r="O81" s="71"/>
+      <c r="O81" s="82"/>
       <c r="P81" s="34"/>
       <c r="Q81" s="50"/>
-      <c r="R81" s="70" t="s">
+      <c r="R81" s="81" t="s">
         <v>56</v>
       </c>
-      <c r="S81" s="71"/>
+      <c r="S81" s="82"/>
       <c r="T81" s="34"/>
       <c r="U81" s="36"/>
-      <c r="V81" s="70" t="s">
+      <c r="V81" s="117" t="s">
         <v>44</v>
       </c>
-      <c r="W81" s="71"/>
-      <c r="X81" s="34"/>
+      <c r="W81" s="118"/>
+      <c r="X81" s="59"/>
       <c r="Y81" s="32"/>
-      <c r="Z81" s="70" t="s">
+      <c r="Z81" s="76" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA81" s="77"/>
+      <c r="AB81" s="57"/>
+      <c r="AC81" s="32"/>
+      <c r="AD81" s="81" t="s">
         <v>44</v>
       </c>
-      <c r="AA81" s="71"/>
-      <c r="AB81" s="34"/>
-      <c r="AC81" s="32"/>
-      <c r="AD81" s="70" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE81" s="71"/>
+      <c r="AE81" s="82"/>
       <c r="AF81" s="34"/>
       <c r="AG81" s="32"/>
-      <c r="AH81" s="70" t="s">
+      <c r="AH81" s="117" t="s">
         <v>44</v>
       </c>
-      <c r="AI81" s="71"/>
-      <c r="AJ81" s="34"/>
+      <c r="AI81" s="118"/>
+      <c r="AJ81" s="59"/>
       <c r="AK81" s="50"/>
-      <c r="AL81" s="70"/>
-      <c r="AM81" s="71"/>
+      <c r="AL81" s="81"/>
+      <c r="AM81" s="82"/>
       <c r="AN81" s="34"/>
       <c r="AO81" s="12"/>
       <c r="AP81" s="29"/>
@@ -6713,37 +6750,41 @@
       <c r="K82" s="63"/>
       <c r="L82" s="64"/>
       <c r="M82" s="5"/>
-      <c r="N82" s="72" t="s">
+      <c r="N82" s="106" t="s">
         <v>53</v>
       </c>
-      <c r="O82" s="73"/>
-      <c r="P82" s="74"/>
+      <c r="O82" s="107"/>
+      <c r="P82" s="108"/>
       <c r="Q82" s="36"/>
-      <c r="R82" s="72" t="s">
+      <c r="R82" s="106" t="s">
         <v>53</v>
       </c>
-      <c r="S82" s="73"/>
-      <c r="T82" s="74"/>
+      <c r="S82" s="107"/>
+      <c r="T82" s="108"/>
       <c r="U82" s="32"/>
-      <c r="V82" s="72"/>
-      <c r="W82" s="73"/>
-      <c r="X82" s="74"/>
+      <c r="V82" s="159" t="s">
+        <v>86</v>
+      </c>
+      <c r="W82" s="160"/>
+      <c r="X82" s="161"/>
       <c r="Y82" s="32"/>
-      <c r="Z82" s="72"/>
-      <c r="AA82" s="73"/>
-      <c r="AB82" s="74"/>
+      <c r="Z82" s="106"/>
+      <c r="AA82" s="107"/>
+      <c r="AB82" s="108"/>
       <c r="AC82" s="32"/>
-      <c r="AD82" s="72"/>
-      <c r="AE82" s="73"/>
-      <c r="AF82" s="74"/>
+      <c r="AD82" s="106"/>
+      <c r="AE82" s="107"/>
+      <c r="AF82" s="108"/>
       <c r="AG82" s="32"/>
-      <c r="AH82" s="72"/>
-      <c r="AI82" s="73"/>
-      <c r="AJ82" s="74"/>
+      <c r="AH82" s="159" t="s">
+        <v>86</v>
+      </c>
+      <c r="AI82" s="160"/>
+      <c r="AJ82" s="161"/>
       <c r="AK82" s="36"/>
-      <c r="AL82" s="72"/>
-      <c r="AM82" s="73"/>
-      <c r="AN82" s="74"/>
+      <c r="AL82" s="106"/>
+      <c r="AM82" s="107"/>
+      <c r="AN82" s="108"/>
       <c r="AO82" s="12"/>
       <c r="AP82" s="29"/>
       <c r="AQ82" s="26"/>
@@ -6751,23 +6792,23 @@
     </row>
     <row r="83" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="12"/>
-      <c r="B83" s="77" t="s">
+      <c r="B83" s="73" t="s">
         <v>50</v>
       </c>
-      <c r="C83" s="78"/>
-      <c r="D83" s="79"/>
+      <c r="C83" s="74"/>
+      <c r="D83" s="75"/>
       <c r="E83" s="32"/>
-      <c r="F83" s="77" t="s">
+      <c r="F83" s="73" t="s">
         <v>50</v>
       </c>
-      <c r="G83" s="78"/>
-      <c r="H83" s="79"/>
+      <c r="G83" s="74"/>
+      <c r="H83" s="75"/>
       <c r="I83" s="32"/>
-      <c r="J83" s="77" t="s">
+      <c r="J83" s="73" t="s">
         <v>50</v>
       </c>
-      <c r="K83" s="78"/>
-      <c r="L83" s="79"/>
+      <c r="K83" s="74"/>
+      <c r="L83" s="75"/>
       <c r="M83" s="5"/>
       <c r="N83" s="83" t="s">
         <v>50</v>
@@ -6781,11 +6822,11 @@
       <c r="S83" s="84"/>
       <c r="T83" s="85"/>
       <c r="U83" s="31"/>
-      <c r="V83" s="83" t="s">
+      <c r="V83" s="156" t="s">
         <v>50</v>
       </c>
-      <c r="W83" s="84"/>
-      <c r="X83" s="85"/>
+      <c r="W83" s="157"/>
+      <c r="X83" s="158"/>
       <c r="Y83" s="32"/>
       <c r="Z83" s="83" t="s">
         <v>50</v>
@@ -6799,11 +6840,11 @@
       <c r="AE83" s="84"/>
       <c r="AF83" s="85"/>
       <c r="AG83" s="32"/>
-      <c r="AH83" s="83" t="s">
+      <c r="AH83" s="156" t="s">
         <v>50</v>
       </c>
-      <c r="AI83" s="84"/>
-      <c r="AJ83" s="85"/>
+      <c r="AI83" s="157"/>
+      <c r="AJ83" s="158"/>
       <c r="AK83" s="32"/>
       <c r="AL83" s="83"/>
       <c r="AM83" s="84"/>
@@ -6815,63 +6856,63 @@
     </row>
     <row r="84" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="12"/>
-      <c r="B84" s="89" t="s">
+      <c r="B84" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="C84" s="90"/>
-      <c r="D84" s="91"/>
+      <c r="C84" s="71"/>
+      <c r="D84" s="72"/>
       <c r="E84" s="32"/>
-      <c r="F84" s="89" t="s">
+      <c r="F84" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="G84" s="90"/>
-      <c r="H84" s="91"/>
+      <c r="G84" s="71"/>
+      <c r="H84" s="72"/>
       <c r="I84" s="32"/>
-      <c r="J84" s="89" t="s">
+      <c r="J84" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="K84" s="90"/>
-      <c r="L84" s="91"/>
+      <c r="K84" s="71"/>
+      <c r="L84" s="72"/>
       <c r="M84" s="5"/>
-      <c r="N84" s="89" t="s">
+      <c r="N84" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="O84" s="90"/>
-      <c r="P84" s="91"/>
+      <c r="O84" s="71"/>
+      <c r="P84" s="72"/>
       <c r="Q84" s="32"/>
-      <c r="R84" s="89" t="s">
+      <c r="R84" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="S84" s="90"/>
-      <c r="T84" s="91"/>
+      <c r="S84" s="71"/>
+      <c r="T84" s="72"/>
       <c r="U84" s="32"/>
-      <c r="V84" s="89" t="s">
+      <c r="V84" s="141" t="s">
+        <v>115</v>
+      </c>
+      <c r="W84" s="142"/>
+      <c r="X84" s="143"/>
+      <c r="Y84" s="32"/>
+      <c r="Z84" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="W84" s="90"/>
-      <c r="X84" s="91"/>
-      <c r="Y84" s="32"/>
-      <c r="Z84" s="89" t="s">
+      <c r="AA84" s="71"/>
+      <c r="AB84" s="72"/>
+      <c r="AC84" s="43"/>
+      <c r="AD84" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="AA84" s="90"/>
-      <c r="AB84" s="91"/>
-      <c r="AC84" s="43"/>
-      <c r="AD84" s="89" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE84" s="90"/>
-      <c r="AF84" s="91"/>
+      <c r="AE84" s="71"/>
+      <c r="AF84" s="72"/>
       <c r="AG84" s="32"/>
-      <c r="AH84" s="89" t="s">
-        <v>30</v>
-      </c>
-      <c r="AI84" s="90"/>
-      <c r="AJ84" s="91"/>
+      <c r="AH84" s="141" t="s">
+        <v>115</v>
+      </c>
+      <c r="AI84" s="142"/>
+      <c r="AJ84" s="143"/>
       <c r="AK84" s="32"/>
-      <c r="AL84" s="89"/>
-      <c r="AM84" s="90"/>
-      <c r="AN84" s="91"/>
+      <c r="AL84" s="70"/>
+      <c r="AM84" s="71"/>
+      <c r="AN84" s="72"/>
       <c r="AO84" s="12"/>
       <c r="AP84" s="29"/>
       <c r="AQ84" s="26"/>
@@ -6879,45 +6920,45 @@
     </row>
     <row r="85" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A85" s="12"/>
-      <c r="B85" s="80"/>
-      <c r="C85" s="81"/>
-      <c r="D85" s="82"/>
+      <c r="B85" s="65"/>
+      <c r="C85" s="66"/>
+      <c r="D85" s="67"/>
       <c r="E85" s="31"/>
-      <c r="F85" s="80"/>
-      <c r="G85" s="81"/>
-      <c r="H85" s="82"/>
+      <c r="F85" s="65"/>
+      <c r="G85" s="66"/>
+      <c r="H85" s="67"/>
       <c r="I85" s="32"/>
-      <c r="J85" s="80"/>
-      <c r="K85" s="81"/>
-      <c r="L85" s="82"/>
+      <c r="J85" s="65"/>
+      <c r="K85" s="66"/>
+      <c r="L85" s="67"/>
       <c r="M85" s="6"/>
-      <c r="N85" s="80"/>
-      <c r="O85" s="81"/>
-      <c r="P85" s="82"/>
+      <c r="N85" s="65"/>
+      <c r="O85" s="66"/>
+      <c r="P85" s="67"/>
       <c r="Q85" s="31"/>
-      <c r="R85" s="80"/>
-      <c r="S85" s="81"/>
-      <c r="T85" s="82"/>
+      <c r="R85" s="65"/>
+      <c r="S85" s="66"/>
+      <c r="T85" s="67"/>
       <c r="U85" s="32"/>
-      <c r="V85" s="80"/>
-      <c r="W85" s="81"/>
-      <c r="X85" s="82"/>
+      <c r="V85" s="131"/>
+      <c r="W85" s="132"/>
+      <c r="X85" s="133"/>
       <c r="Y85" s="32"/>
-      <c r="Z85" s="80"/>
-      <c r="AA85" s="81"/>
-      <c r="AB85" s="82"/>
+      <c r="Z85" s="65"/>
+      <c r="AA85" s="66"/>
+      <c r="AB85" s="67"/>
       <c r="AC85" s="43"/>
-      <c r="AD85" s="80"/>
-      <c r="AE85" s="81"/>
-      <c r="AF85" s="82"/>
+      <c r="AD85" s="65"/>
+      <c r="AE85" s="66"/>
+      <c r="AF85" s="67"/>
       <c r="AG85" s="31"/>
-      <c r="AH85" s="80"/>
-      <c r="AI85" s="81"/>
-      <c r="AJ85" s="82"/>
+      <c r="AH85" s="131"/>
+      <c r="AI85" s="132"/>
+      <c r="AJ85" s="133"/>
       <c r="AK85" s="32"/>
-      <c r="AL85" s="80"/>
-      <c r="AM85" s="81"/>
-      <c r="AN85" s="82"/>
+      <c r="AL85" s="65"/>
+      <c r="AM85" s="66"/>
+      <c r="AN85" s="67"/>
       <c r="AO85" s="12"/>
       <c r="AP85" s="29"/>
       <c r="AQ85" s="26"/>
@@ -6971,58 +7012,58 @@
     </row>
     <row r="87" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="12"/>
-      <c r="B87" s="75" t="s">
+      <c r="B87" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="C87" s="76"/>
+      <c r="C87" s="69"/>
       <c r="D87" s="55"/>
       <c r="E87" s="32"/>
-      <c r="F87" s="75" t="s">
+      <c r="F87" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="G87" s="76"/>
+      <c r="G87" s="69"/>
       <c r="H87" s="55"/>
       <c r="I87" s="32"/>
-      <c r="J87" s="75" t="s">
+      <c r="J87" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="K87" s="76"/>
+      <c r="K87" s="69"/>
       <c r="L87" s="55"/>
       <c r="M87" s="6"/>
-      <c r="N87" s="70" t="s">
+      <c r="N87" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="O87" s="71"/>
+      <c r="O87" s="82"/>
       <c r="P87" s="34"/>
       <c r="Q87" s="32"/>
-      <c r="R87" s="70" t="s">
+      <c r="R87" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="S87" s="71"/>
+      <c r="S87" s="82"/>
       <c r="T87" s="34"/>
       <c r="U87" s="36"/>
-      <c r="V87" s="70" t="s">
+      <c r="V87" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="W87" s="71"/>
+      <c r="W87" s="82"/>
       <c r="X87" s="34"/>
       <c r="Y87" s="32"/>
-      <c r="Z87" s="70" t="s">
+      <c r="Z87" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="AA87" s="71"/>
+      <c r="AA87" s="82"/>
       <c r="AB87" s="34"/>
       <c r="AC87" s="32"/>
-      <c r="AD87" s="70"/>
-      <c r="AE87" s="71"/>
+      <c r="AD87" s="81"/>
+      <c r="AE87" s="82"/>
       <c r="AF87" s="34"/>
       <c r="AG87" s="32"/>
-      <c r="AH87" s="70"/>
-      <c r="AI87" s="71"/>
+      <c r="AH87" s="81"/>
+      <c r="AI87" s="82"/>
       <c r="AJ87" s="34"/>
       <c r="AK87" s="32"/>
-      <c r="AL87" s="70"/>
-      <c r="AM87" s="71"/>
+      <c r="AL87" s="81"/>
+      <c r="AM87" s="82"/>
       <c r="AN87" s="34"/>
       <c r="AO87" s="12"/>
       <c r="AP87" s="29"/>
@@ -7045,41 +7086,41 @@
       <c r="K88" s="63"/>
       <c r="L88" s="64"/>
       <c r="M88" s="6"/>
-      <c r="N88" s="72" t="s">
+      <c r="N88" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="O88" s="73"/>
-      <c r="P88" s="74"/>
+      <c r="O88" s="107"/>
+      <c r="P88" s="108"/>
       <c r="Q88" s="35"/>
-      <c r="R88" s="72" t="s">
+      <c r="R88" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="S88" s="73"/>
-      <c r="T88" s="74"/>
+      <c r="S88" s="107"/>
+      <c r="T88" s="108"/>
       <c r="U88" s="32"/>
-      <c r="V88" s="72" t="s">
+      <c r="V88" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="W88" s="73"/>
-      <c r="X88" s="74"/>
+      <c r="W88" s="107"/>
+      <c r="X88" s="108"/>
       <c r="Y88" s="32"/>
-      <c r="Z88" s="72" t="s">
+      <c r="Z88" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="AA88" s="73"/>
-      <c r="AB88" s="74"/>
+      <c r="AA88" s="107"/>
+      <c r="AB88" s="108"/>
       <c r="AC88" s="35"/>
-      <c r="AD88" s="72"/>
-      <c r="AE88" s="73"/>
-      <c r="AF88" s="74"/>
+      <c r="AD88" s="106"/>
+      <c r="AE88" s="107"/>
+      <c r="AF88" s="108"/>
       <c r="AG88" s="32"/>
-      <c r="AH88" s="72"/>
-      <c r="AI88" s="73"/>
-      <c r="AJ88" s="74"/>
+      <c r="AH88" s="106"/>
+      <c r="AI88" s="107"/>
+      <c r="AJ88" s="108"/>
       <c r="AK88" s="32"/>
-      <c r="AL88" s="72"/>
-      <c r="AM88" s="73"/>
-      <c r="AN88" s="74"/>
+      <c r="AL88" s="106"/>
+      <c r="AM88" s="107"/>
+      <c r="AN88" s="108"/>
       <c r="AO88" s="12"/>
       <c r="AP88" s="29"/>
       <c r="AQ88" s="26"/>
@@ -7087,21 +7128,21 @@
     </row>
     <row r="89" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="12"/>
-      <c r="B89" s="77" t="s">
+      <c r="B89" s="73" t="s">
         <v>50</v>
       </c>
-      <c r="C89" s="78"/>
-      <c r="D89" s="79"/>
+      <c r="C89" s="74"/>
+      <c r="D89" s="75"/>
       <c r="E89" s="32"/>
-      <c r="F89" s="77" t="s">
+      <c r="F89" s="73" t="s">
         <v>50</v>
       </c>
-      <c r="G89" s="78"/>
-      <c r="H89" s="79"/>
+      <c r="G89" s="74"/>
+      <c r="H89" s="75"/>
       <c r="I89" s="32"/>
-      <c r="J89" s="77"/>
-      <c r="K89" s="78"/>
-      <c r="L89" s="79"/>
+      <c r="J89" s="73"/>
+      <c r="K89" s="74"/>
+      <c r="L89" s="75"/>
       <c r="M89" s="6"/>
       <c r="N89" s="83"/>
       <c r="O89" s="84"/>
@@ -7137,59 +7178,59 @@
     </row>
     <row r="90" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="12"/>
-      <c r="B90" s="89" t="s">
+      <c r="B90" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="C90" s="90"/>
-      <c r="D90" s="91"/>
+      <c r="C90" s="71"/>
+      <c r="D90" s="72"/>
       <c r="E90" s="32"/>
-      <c r="F90" s="89" t="s">
+      <c r="F90" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="G90" s="90"/>
-      <c r="H90" s="91"/>
+      <c r="G90" s="71"/>
+      <c r="H90" s="72"/>
       <c r="I90" s="32"/>
-      <c r="J90" s="89" t="s">
+      <c r="J90" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="K90" s="90"/>
-      <c r="L90" s="91"/>
+      <c r="K90" s="71"/>
+      <c r="L90" s="72"/>
       <c r="M90" s="6"/>
-      <c r="N90" s="89" t="s">
+      <c r="N90" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="O90" s="90"/>
-      <c r="P90" s="91"/>
+      <c r="O90" s="71"/>
+      <c r="P90" s="72"/>
       <c r="Q90" s="32"/>
-      <c r="R90" s="89" t="s">
+      <c r="R90" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="S90" s="90"/>
-      <c r="T90" s="91"/>
+      <c r="S90" s="71"/>
+      <c r="T90" s="72"/>
       <c r="U90" s="32"/>
-      <c r="V90" s="89" t="s">
+      <c r="V90" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="W90" s="90"/>
-      <c r="X90" s="91"/>
+      <c r="W90" s="71"/>
+      <c r="X90" s="72"/>
       <c r="Y90" s="32"/>
-      <c r="Z90" s="89" t="s">
+      <c r="Z90" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="AA90" s="90"/>
-      <c r="AB90" s="91"/>
+      <c r="AA90" s="71"/>
+      <c r="AB90" s="72"/>
       <c r="AC90" s="32"/>
-      <c r="AD90" s="89"/>
-      <c r="AE90" s="90"/>
-      <c r="AF90" s="91"/>
+      <c r="AD90" s="70"/>
+      <c r="AE90" s="71"/>
+      <c r="AF90" s="72"/>
       <c r="AG90" s="32"/>
-      <c r="AH90" s="89"/>
-      <c r="AI90" s="90"/>
-      <c r="AJ90" s="91"/>
+      <c r="AH90" s="70"/>
+      <c r="AI90" s="71"/>
+      <c r="AJ90" s="72"/>
       <c r="AK90" s="32"/>
-      <c r="AL90" s="89"/>
-      <c r="AM90" s="90"/>
-      <c r="AN90" s="91"/>
+      <c r="AL90" s="70"/>
+      <c r="AM90" s="71"/>
+      <c r="AN90" s="72"/>
       <c r="AO90" s="12"/>
       <c r="AP90" s="29"/>
       <c r="AQ90" s="26"/>
@@ -7197,45 +7238,45 @@
     </row>
     <row r="91" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A91" s="12"/>
-      <c r="B91" s="80"/>
-      <c r="C91" s="81"/>
-      <c r="D91" s="82"/>
+      <c r="B91" s="65"/>
+      <c r="C91" s="66"/>
+      <c r="D91" s="67"/>
       <c r="E91" s="31"/>
-      <c r="F91" s="80"/>
-      <c r="G91" s="81"/>
-      <c r="H91" s="82"/>
+      <c r="F91" s="65"/>
+      <c r="G91" s="66"/>
+      <c r="H91" s="67"/>
       <c r="I91" s="31"/>
-      <c r="J91" s="80"/>
-      <c r="K91" s="81"/>
-      <c r="L91" s="82"/>
+      <c r="J91" s="65"/>
+      <c r="K91" s="66"/>
+      <c r="L91" s="67"/>
       <c r="M91" s="6"/>
-      <c r="N91" s="80"/>
-      <c r="O91" s="81"/>
-      <c r="P91" s="82"/>
+      <c r="N91" s="65"/>
+      <c r="O91" s="66"/>
+      <c r="P91" s="67"/>
       <c r="Q91" s="31"/>
-      <c r="R91" s="80"/>
-      <c r="S91" s="81"/>
-      <c r="T91" s="82"/>
+      <c r="R91" s="65"/>
+      <c r="S91" s="66"/>
+      <c r="T91" s="67"/>
       <c r="U91" s="32"/>
-      <c r="V91" s="80"/>
-      <c r="W91" s="81"/>
-      <c r="X91" s="82"/>
+      <c r="V91" s="65"/>
+      <c r="W91" s="66"/>
+      <c r="X91" s="67"/>
       <c r="Y91" s="32"/>
-      <c r="Z91" s="80"/>
-      <c r="AA91" s="81"/>
-      <c r="AB91" s="82"/>
+      <c r="Z91" s="65"/>
+      <c r="AA91" s="66"/>
+      <c r="AB91" s="67"/>
       <c r="AC91" s="32"/>
-      <c r="AD91" s="80"/>
-      <c r="AE91" s="81"/>
-      <c r="AF91" s="82"/>
+      <c r="AD91" s="65"/>
+      <c r="AE91" s="66"/>
+      <c r="AF91" s="67"/>
       <c r="AG91" s="31"/>
-      <c r="AH91" s="80"/>
-      <c r="AI91" s="81"/>
-      <c r="AJ91" s="82"/>
+      <c r="AH91" s="65"/>
+      <c r="AI91" s="66"/>
+      <c r="AJ91" s="67"/>
       <c r="AK91" s="31"/>
-      <c r="AL91" s="80"/>
-      <c r="AM91" s="81"/>
-      <c r="AN91" s="82"/>
+      <c r="AL91" s="65"/>
+      <c r="AM91" s="66"/>
+      <c r="AN91" s="67"/>
       <c r="AO91" s="12"/>
       <c r="AP91" s="29"/>
       <c r="AQ91" s="26"/>
@@ -7289,56 +7330,56 @@
     </row>
     <row r="93" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="12"/>
-      <c r="B93" s="75"/>
-      <c r="C93" s="76"/>
+      <c r="B93" s="68"/>
+      <c r="C93" s="69"/>
       <c r="D93" s="55"/>
       <c r="E93" s="36"/>
-      <c r="F93" s="75"/>
-      <c r="G93" s="76"/>
+      <c r="F93" s="68"/>
+      <c r="G93" s="69"/>
       <c r="H93" s="55"/>
       <c r="I93" s="32"/>
-      <c r="J93" s="75"/>
-      <c r="K93" s="76"/>
+      <c r="J93" s="68"/>
+      <c r="K93" s="69"/>
       <c r="L93" s="55"/>
       <c r="M93" s="6"/>
-      <c r="N93" s="70"/>
-      <c r="O93" s="71"/>
+      <c r="N93" s="81"/>
+      <c r="O93" s="82"/>
       <c r="P93" s="34"/>
       <c r="Q93" s="32"/>
-      <c r="R93" s="70" t="s">
+      <c r="R93" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="S93" s="71"/>
+      <c r="S93" s="82"/>
       <c r="T93" s="34"/>
       <c r="U93" s="36"/>
-      <c r="V93" s="70" t="s">
+      <c r="V93" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="W93" s="71"/>
+      <c r="W93" s="82"/>
       <c r="X93" s="34"/>
       <c r="Y93" s="32"/>
-      <c r="Z93" s="70" t="s">
+      <c r="Z93" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="AA93" s="71"/>
+      <c r="AA93" s="82"/>
       <c r="AB93" s="34"/>
       <c r="AC93" s="32"/>
-      <c r="AD93" s="70" t="s">
+      <c r="AD93" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="AE93" s="71"/>
+      <c r="AE93" s="82"/>
       <c r="AF93" s="34"/>
       <c r="AG93" s="32"/>
-      <c r="AH93" s="70" t="s">
+      <c r="AH93" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="AI93" s="71"/>
+      <c r="AI93" s="82"/>
       <c r="AJ93" s="34"/>
       <c r="AK93" s="32"/>
-      <c r="AL93" s="70" t="s">
+      <c r="AL93" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="AM93" s="71"/>
+      <c r="AM93" s="82"/>
       <c r="AN93" s="34"/>
       <c r="AO93" s="12"/>
       <c r="AP93" s="29"/>
@@ -7359,45 +7400,45 @@
       <c r="K94" s="63"/>
       <c r="L94" s="64"/>
       <c r="M94" s="26"/>
-      <c r="N94" s="72"/>
-      <c r="O94" s="73"/>
-      <c r="P94" s="74"/>
+      <c r="N94" s="106"/>
+      <c r="O94" s="107"/>
+      <c r="P94" s="108"/>
       <c r="Q94" s="32"/>
-      <c r="R94" s="72" t="s">
+      <c r="R94" s="106" t="s">
         <v>66</v>
       </c>
-      <c r="S94" s="73"/>
-      <c r="T94" s="74"/>
+      <c r="S94" s="107"/>
+      <c r="T94" s="108"/>
       <c r="U94" s="32"/>
-      <c r="V94" s="72" t="s">
+      <c r="V94" s="106" t="s">
         <v>66</v>
       </c>
-      <c r="W94" s="73"/>
-      <c r="X94" s="74"/>
+      <c r="W94" s="107"/>
+      <c r="X94" s="108"/>
       <c r="Y94" s="32"/>
-      <c r="Z94" s="72" t="s">
+      <c r="Z94" s="106" t="s">
         <v>66</v>
       </c>
-      <c r="AA94" s="73"/>
-      <c r="AB94" s="74"/>
+      <c r="AA94" s="107"/>
+      <c r="AB94" s="108"/>
       <c r="AC94" s="35"/>
-      <c r="AD94" s="72" t="s">
+      <c r="AD94" s="106" t="s">
         <v>66</v>
       </c>
-      <c r="AE94" s="73"/>
-      <c r="AF94" s="74"/>
+      <c r="AE94" s="107"/>
+      <c r="AF94" s="108"/>
       <c r="AG94" s="32"/>
-      <c r="AH94" s="72" t="s">
+      <c r="AH94" s="106" t="s">
         <v>66</v>
       </c>
-      <c r="AI94" s="73"/>
-      <c r="AJ94" s="74"/>
+      <c r="AI94" s="107"/>
+      <c r="AJ94" s="108"/>
       <c r="AK94" s="32"/>
-      <c r="AL94" s="72" t="s">
+      <c r="AL94" s="106" t="s">
         <v>66</v>
       </c>
-      <c r="AM94" s="73"/>
-      <c r="AN94" s="74"/>
+      <c r="AM94" s="107"/>
+      <c r="AN94" s="108"/>
       <c r="AO94" s="12"/>
       <c r="AP94" s="29"/>
       <c r="AQ94" s="26"/>
@@ -7405,17 +7446,17 @@
     </row>
     <row r="95" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="12"/>
-      <c r="B95" s="77"/>
-      <c r="C95" s="78"/>
-      <c r="D95" s="79"/>
+      <c r="B95" s="73"/>
+      <c r="C95" s="74"/>
+      <c r="D95" s="75"/>
       <c r="E95" s="31"/>
-      <c r="F95" s="77"/>
-      <c r="G95" s="78"/>
-      <c r="H95" s="79"/>
+      <c r="F95" s="73"/>
+      <c r="G95" s="74"/>
+      <c r="H95" s="75"/>
       <c r="I95" s="32"/>
-      <c r="J95" s="77"/>
-      <c r="K95" s="78"/>
-      <c r="L95" s="79"/>
+      <c r="J95" s="73"/>
+      <c r="K95" s="74"/>
+      <c r="L95" s="75"/>
       <c r="M95" s="26"/>
       <c r="N95" s="83"/>
       <c r="O95" s="84"/>
@@ -7451,57 +7492,57 @@
     </row>
     <row r="96" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="12"/>
-      <c r="B96" s="89"/>
-      <c r="C96" s="90"/>
-      <c r="D96" s="91"/>
+      <c r="B96" s="70"/>
+      <c r="C96" s="71"/>
+      <c r="D96" s="72"/>
       <c r="E96" s="32"/>
-      <c r="F96" s="89"/>
-      <c r="G96" s="90"/>
-      <c r="H96" s="91"/>
+      <c r="F96" s="70"/>
+      <c r="G96" s="71"/>
+      <c r="H96" s="72"/>
       <c r="I96" s="32"/>
-      <c r="J96" s="89"/>
-      <c r="K96" s="90"/>
-      <c r="L96" s="91"/>
+      <c r="J96" s="70"/>
+      <c r="K96" s="71"/>
+      <c r="L96" s="72"/>
       <c r="M96" s="26"/>
-      <c r="N96" s="89"/>
-      <c r="O96" s="90"/>
-      <c r="P96" s="91"/>
+      <c r="N96" s="70"/>
+      <c r="O96" s="71"/>
+      <c r="P96" s="72"/>
       <c r="Q96" s="32"/>
-      <c r="R96" s="89" t="s">
+      <c r="R96" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="S96" s="90"/>
-      <c r="T96" s="91"/>
+      <c r="S96" s="71"/>
+      <c r="T96" s="72"/>
       <c r="U96" s="32"/>
-      <c r="V96" s="89" t="s">
+      <c r="V96" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="W96" s="90"/>
-      <c r="X96" s="91"/>
+      <c r="W96" s="71"/>
+      <c r="X96" s="72"/>
       <c r="Y96" s="32"/>
-      <c r="Z96" s="89" t="s">
+      <c r="Z96" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="AA96" s="90"/>
-      <c r="AB96" s="91"/>
+      <c r="AA96" s="71"/>
+      <c r="AB96" s="72"/>
       <c r="AC96" s="32"/>
-      <c r="AD96" s="89" t="s">
+      <c r="AD96" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="AE96" s="90"/>
-      <c r="AF96" s="91"/>
+      <c r="AE96" s="71"/>
+      <c r="AF96" s="72"/>
       <c r="AG96" s="32"/>
-      <c r="AH96" s="89" t="s">
+      <c r="AH96" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="AI96" s="90"/>
-      <c r="AJ96" s="91"/>
+      <c r="AI96" s="71"/>
+      <c r="AJ96" s="72"/>
       <c r="AK96" s="32"/>
-      <c r="AL96" s="89" t="s">
+      <c r="AL96" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="AM96" s="90"/>
-      <c r="AN96" s="91"/>
+      <c r="AM96" s="71"/>
+      <c r="AN96" s="72"/>
       <c r="AO96" s="12"/>
       <c r="AP96" s="29"/>
       <c r="AQ96" s="26"/>
@@ -7509,45 +7550,45 @@
     </row>
     <row r="97" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A97" s="12"/>
-      <c r="B97" s="80"/>
-      <c r="C97" s="81"/>
-      <c r="D97" s="82"/>
+      <c r="B97" s="65"/>
+      <c r="C97" s="66"/>
+      <c r="D97" s="67"/>
       <c r="E97" s="32"/>
-      <c r="F97" s="80"/>
-      <c r="G97" s="81"/>
-      <c r="H97" s="82"/>
+      <c r="F97" s="65"/>
+      <c r="G97" s="66"/>
+      <c r="H97" s="67"/>
       <c r="I97" s="31"/>
-      <c r="J97" s="80"/>
-      <c r="K97" s="81"/>
-      <c r="L97" s="82"/>
+      <c r="J97" s="65"/>
+      <c r="K97" s="66"/>
+      <c r="L97" s="67"/>
       <c r="M97" s="26"/>
-      <c r="N97" s="80"/>
-      <c r="O97" s="81"/>
-      <c r="P97" s="82"/>
+      <c r="N97" s="65"/>
+      <c r="O97" s="66"/>
+      <c r="P97" s="67"/>
       <c r="Q97" s="31"/>
-      <c r="R97" s="80"/>
-      <c r="S97" s="81"/>
-      <c r="T97" s="82"/>
+      <c r="R97" s="65"/>
+      <c r="S97" s="66"/>
+      <c r="T97" s="67"/>
       <c r="U97" s="32"/>
-      <c r="V97" s="80"/>
-      <c r="W97" s="81"/>
-      <c r="X97" s="82"/>
+      <c r="V97" s="65"/>
+      <c r="W97" s="66"/>
+      <c r="X97" s="67"/>
       <c r="Y97" s="31"/>
-      <c r="Z97" s="80"/>
-      <c r="AA97" s="81"/>
-      <c r="AB97" s="82"/>
+      <c r="Z97" s="65"/>
+      <c r="AA97" s="66"/>
+      <c r="AB97" s="67"/>
       <c r="AC97" s="31"/>
-      <c r="AD97" s="80"/>
-      <c r="AE97" s="81"/>
-      <c r="AF97" s="82"/>
+      <c r="AD97" s="65"/>
+      <c r="AE97" s="66"/>
+      <c r="AF97" s="67"/>
       <c r="AG97" s="32"/>
-      <c r="AH97" s="80"/>
-      <c r="AI97" s="81"/>
-      <c r="AJ97" s="82"/>
+      <c r="AH97" s="65"/>
+      <c r="AI97" s="66"/>
+      <c r="AJ97" s="67"/>
       <c r="AK97" s="31"/>
-      <c r="AL97" s="80"/>
-      <c r="AM97" s="81"/>
-      <c r="AN97" s="82"/>
+      <c r="AL97" s="65"/>
+      <c r="AM97" s="66"/>
+      <c r="AN97" s="67"/>
       <c r="AO97" s="12"/>
       <c r="AP97" s="29"/>
       <c r="AQ97" s="26"/>
@@ -7601,48 +7642,50 @@
     </row>
     <row r="99" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="12"/>
-      <c r="B99" s="75"/>
-      <c r="C99" s="76"/>
+      <c r="B99" s="68"/>
+      <c r="C99" s="69"/>
       <c r="D99" s="55"/>
       <c r="E99" s="32"/>
-      <c r="F99" s="75"/>
-      <c r="G99" s="76"/>
+      <c r="F99" s="68"/>
+      <c r="G99" s="69"/>
       <c r="H99" s="55"/>
       <c r="I99" s="36"/>
-      <c r="J99" s="75"/>
-      <c r="K99" s="76"/>
+      <c r="J99" s="68"/>
+      <c r="K99" s="69"/>
       <c r="L99" s="55"/>
       <c r="M99" s="26"/>
-      <c r="N99" s="70"/>
-      <c r="O99" s="71"/>
+      <c r="N99" s="81"/>
+      <c r="O99" s="82"/>
       <c r="P99" s="34"/>
       <c r="Q99" s="44"/>
-      <c r="R99" s="70" t="s">
+      <c r="R99" s="117" t="s">
         <v>110</v>
       </c>
-      <c r="S99" s="71"/>
-      <c r="T99" s="34" t="s">
+      <c r="S99" s="118"/>
+      <c r="T99" s="59" t="s">
         <v>111</v>
       </c>
       <c r="U99" s="36"/>
-      <c r="V99" s="70"/>
-      <c r="W99" s="71"/>
+      <c r="V99" s="81"/>
+      <c r="W99" s="82"/>
       <c r="X99" s="34"/>
       <c r="Y99" s="32"/>
-      <c r="Z99" s="70"/>
-      <c r="AA99" s="71"/>
-      <c r="AB99" s="34"/>
+      <c r="Z99" s="117" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA99" s="118"/>
+      <c r="AB99" s="59"/>
       <c r="AC99" s="36"/>
-      <c r="AD99" s="70"/>
-      <c r="AE99" s="71"/>
+      <c r="AD99" s="81"/>
+      <c r="AE99" s="82"/>
       <c r="AF99" s="34"/>
       <c r="AG99" s="32"/>
-      <c r="AH99" s="70"/>
-      <c r="AI99" s="71"/>
+      <c r="AH99" s="81"/>
+      <c r="AI99" s="82"/>
       <c r="AJ99" s="34"/>
       <c r="AK99" s="36"/>
-      <c r="AL99" s="70"/>
-      <c r="AM99" s="71"/>
+      <c r="AL99" s="81"/>
+      <c r="AM99" s="82"/>
       <c r="AN99" s="34"/>
       <c r="AO99" s="12"/>
       <c r="AP99" s="29"/>
@@ -7651,35 +7694,37 @@
     </row>
     <row r="100" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="12"/>
-      <c r="B100" s="77"/>
-      <c r="C100" s="78"/>
-      <c r="D100" s="79"/>
+      <c r="B100" s="73"/>
+      <c r="C100" s="74"/>
+      <c r="D100" s="75"/>
       <c r="E100" s="32"/>
-      <c r="F100" s="77"/>
-      <c r="G100" s="78"/>
-      <c r="H100" s="79"/>
+      <c r="F100" s="73"/>
+      <c r="G100" s="74"/>
+      <c r="H100" s="75"/>
       <c r="I100" s="31"/>
-      <c r="J100" s="77"/>
-      <c r="K100" s="78"/>
-      <c r="L100" s="79"/>
+      <c r="J100" s="73"/>
+      <c r="K100" s="74"/>
+      <c r="L100" s="75"/>
       <c r="M100" s="26"/>
       <c r="N100" s="83"/>
       <c r="O100" s="84"/>
       <c r="P100" s="85"/>
       <c r="Q100" s="31"/>
-      <c r="R100" s="72" t="s">
-        <v>112</v>
-      </c>
-      <c r="S100" s="73"/>
-      <c r="T100" s="74"/>
+      <c r="R100" s="109" t="s">
+        <v>116</v>
+      </c>
+      <c r="S100" s="110"/>
+      <c r="T100" s="111"/>
       <c r="U100" s="31"/>
       <c r="V100" s="83"/>
       <c r="W100" s="84"/>
       <c r="X100" s="85"/>
       <c r="Y100" s="32"/>
-      <c r="Z100" s="83"/>
-      <c r="AA100" s="84"/>
-      <c r="AB100" s="85"/>
+      <c r="Z100" s="159" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA100" s="160"/>
+      <c r="AB100" s="161"/>
       <c r="AC100" s="36"/>
       <c r="AD100" s="83"/>
       <c r="AE100" s="84"/>
@@ -7699,47 +7744,49 @@
     </row>
     <row r="101" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="12"/>
-      <c r="B101" s="89"/>
-      <c r="C101" s="90"/>
-      <c r="D101" s="91"/>
+      <c r="B101" s="70"/>
+      <c r="C101" s="71"/>
+      <c r="D101" s="72"/>
       <c r="E101" s="32"/>
-      <c r="F101" s="89"/>
-      <c r="G101" s="90"/>
-      <c r="H101" s="91"/>
+      <c r="F101" s="70"/>
+      <c r="G101" s="71"/>
+      <c r="H101" s="72"/>
       <c r="I101" s="31"/>
-      <c r="J101" s="89"/>
-      <c r="K101" s="90"/>
-      <c r="L101" s="91"/>
+      <c r="J101" s="70"/>
+      <c r="K101" s="71"/>
+      <c r="L101" s="72"/>
       <c r="M101" s="26"/>
-      <c r="N101" s="89"/>
-      <c r="O101" s="90"/>
-      <c r="P101" s="91"/>
+      <c r="N101" s="70"/>
+      <c r="O101" s="71"/>
+      <c r="P101" s="72"/>
       <c r="Q101" s="31"/>
-      <c r="R101" s="89" t="s">
-        <v>30</v>
-      </c>
-      <c r="S101" s="90"/>
-      <c r="T101" s="91"/>
+      <c r="R101" s="141" t="s">
+        <v>115</v>
+      </c>
+      <c r="S101" s="142"/>
+      <c r="T101" s="143"/>
       <c r="U101" s="32"/>
-      <c r="V101" s="89"/>
-      <c r="W101" s="90"/>
-      <c r="X101" s="91"/>
+      <c r="V101" s="70"/>
+      <c r="W101" s="71"/>
+      <c r="X101" s="72"/>
       <c r="Y101" s="32"/>
-      <c r="Z101" s="89"/>
-      <c r="AA101" s="90"/>
-      <c r="AB101" s="91"/>
+      <c r="Z101" s="141" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA101" s="142"/>
+      <c r="AB101" s="143"/>
       <c r="AC101" s="31"/>
-      <c r="AD101" s="89"/>
-      <c r="AE101" s="90"/>
-      <c r="AF101" s="91"/>
+      <c r="AD101" s="70"/>
+      <c r="AE101" s="71"/>
+      <c r="AF101" s="72"/>
       <c r="AG101" s="32"/>
-      <c r="AH101" s="89"/>
-      <c r="AI101" s="90"/>
-      <c r="AJ101" s="91"/>
+      <c r="AH101" s="70"/>
+      <c r="AI101" s="71"/>
+      <c r="AJ101" s="72"/>
       <c r="AK101" s="31"/>
-      <c r="AL101" s="89"/>
-      <c r="AM101" s="90"/>
-      <c r="AN101" s="91"/>
+      <c r="AL101" s="70"/>
+      <c r="AM101" s="71"/>
+      <c r="AN101" s="72"/>
       <c r="AO101" s="12"/>
       <c r="AP101" s="29"/>
       <c r="AQ101" s="26"/>
@@ -7747,45 +7794,45 @@
     </row>
     <row r="102" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A102" s="12"/>
-      <c r="B102" s="80"/>
-      <c r="C102" s="81"/>
-      <c r="D102" s="82"/>
+      <c r="B102" s="65"/>
+      <c r="C102" s="66"/>
+      <c r="D102" s="67"/>
       <c r="E102" s="31"/>
-      <c r="F102" s="80"/>
-      <c r="G102" s="81"/>
-      <c r="H102" s="82"/>
+      <c r="F102" s="65"/>
+      <c r="G102" s="66"/>
+      <c r="H102" s="67"/>
       <c r="I102" s="32"/>
-      <c r="J102" s="80"/>
-      <c r="K102" s="81"/>
-      <c r="L102" s="82"/>
+      <c r="J102" s="65"/>
+      <c r="K102" s="66"/>
+      <c r="L102" s="67"/>
       <c r="M102" s="26"/>
-      <c r="N102" s="80"/>
-      <c r="O102" s="81"/>
-      <c r="P102" s="82"/>
+      <c r="N102" s="65"/>
+      <c r="O102" s="66"/>
+      <c r="P102" s="67"/>
       <c r="Q102" s="31"/>
-      <c r="R102" s="80"/>
-      <c r="S102" s="81"/>
-      <c r="T102" s="82"/>
+      <c r="R102" s="131"/>
+      <c r="S102" s="132"/>
+      <c r="T102" s="133"/>
       <c r="U102" s="32"/>
-      <c r="V102" s="80"/>
-      <c r="W102" s="81"/>
-      <c r="X102" s="82"/>
+      <c r="V102" s="65"/>
+      <c r="W102" s="66"/>
+      <c r="X102" s="67"/>
       <c r="Y102" s="32"/>
-      <c r="Z102" s="80"/>
-      <c r="AA102" s="81"/>
-      <c r="AB102" s="82"/>
+      <c r="Z102" s="131"/>
+      <c r="AA102" s="132"/>
+      <c r="AB102" s="133"/>
       <c r="AC102" s="32"/>
-      <c r="AD102" s="80"/>
-      <c r="AE102" s="81"/>
-      <c r="AF102" s="82"/>
+      <c r="AD102" s="65"/>
+      <c r="AE102" s="66"/>
+      <c r="AF102" s="67"/>
       <c r="AG102" s="31"/>
-      <c r="AH102" s="80"/>
-      <c r="AI102" s="81"/>
-      <c r="AJ102" s="82"/>
+      <c r="AH102" s="65"/>
+      <c r="AI102" s="66"/>
+      <c r="AJ102" s="67"/>
       <c r="AK102" s="32"/>
-      <c r="AL102" s="80"/>
-      <c r="AM102" s="81"/>
-      <c r="AN102" s="82"/>
+      <c r="AL102" s="65"/>
+      <c r="AM102" s="66"/>
+      <c r="AN102" s="67"/>
       <c r="AO102" s="12"/>
       <c r="AP102" s="29"/>
       <c r="AQ102" s="26"/>
@@ -7855,31 +7902,31 @@
       <c r="AR104" s="26"/>
     </row>
     <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B105" s="70"/>
-      <c r="C105" s="71"/>
+      <c r="B105" s="81"/>
+      <c r="C105" s="82"/>
       <c r="D105" s="34"/>
       <c r="E105" s="32"/>
-      <c r="F105" s="70"/>
-      <c r="G105" s="71"/>
+      <c r="F105" s="81"/>
+      <c r="G105" s="82"/>
       <c r="H105" s="34"/>
       <c r="I105" s="32"/>
-      <c r="J105" s="70"/>
-      <c r="K105" s="71"/>
+      <c r="J105" s="81"/>
+      <c r="K105" s="82"/>
       <c r="L105" s="34"/>
       <c r="AO105" s="26"/>
     </row>
     <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B106" s="72"/>
-      <c r="C106" s="73"/>
-      <c r="D106" s="74"/>
+      <c r="B106" s="106"/>
+      <c r="C106" s="107"/>
+      <c r="D106" s="108"/>
       <c r="E106" s="32"/>
-      <c r="F106" s="72"/>
-      <c r="G106" s="73"/>
-      <c r="H106" s="74"/>
+      <c r="F106" s="106"/>
+      <c r="G106" s="107"/>
+      <c r="H106" s="108"/>
       <c r="I106" s="32"/>
-      <c r="J106" s="72"/>
-      <c r="K106" s="73"/>
-      <c r="L106" s="74"/>
+      <c r="J106" s="106"/>
+      <c r="K106" s="107"/>
+      <c r="L106" s="108"/>
     </row>
     <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B107" s="83"/>
@@ -7895,30 +7942,30 @@
       <c r="L107" s="85"/>
     </row>
     <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B108" s="89"/>
-      <c r="C108" s="90"/>
-      <c r="D108" s="91"/>
+      <c r="B108" s="70"/>
+      <c r="C108" s="71"/>
+      <c r="D108" s="72"/>
       <c r="E108" s="32"/>
-      <c r="F108" s="89"/>
-      <c r="G108" s="90"/>
-      <c r="H108" s="91"/>
+      <c r="F108" s="70"/>
+      <c r="G108" s="71"/>
+      <c r="H108" s="72"/>
       <c r="I108" s="31"/>
-      <c r="J108" s="89"/>
-      <c r="K108" s="90"/>
-      <c r="L108" s="91"/>
+      <c r="J108" s="70"/>
+      <c r="K108" s="71"/>
+      <c r="L108" s="72"/>
     </row>
     <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B109" s="80"/>
-      <c r="C109" s="81"/>
-      <c r="D109" s="82"/>
+      <c r="B109" s="65"/>
+      <c r="C109" s="66"/>
+      <c r="D109" s="67"/>
       <c r="E109" s="31"/>
-      <c r="F109" s="80"/>
-      <c r="G109" s="81"/>
-      <c r="H109" s="82"/>
+      <c r="F109" s="65"/>
+      <c r="G109" s="66"/>
+      <c r="H109" s="67"/>
       <c r="I109" s="31"/>
-      <c r="J109" s="80"/>
-      <c r="K109" s="81"/>
-      <c r="L109" s="82"/>
+      <c r="J109" s="65"/>
+      <c r="K109" s="66"/>
+      <c r="L109" s="67"/>
     </row>
     <row r="110" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B110" s="35"/>
@@ -7934,30 +7981,30 @@
       <c r="L110" s="35"/>
     </row>
     <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B111" s="70"/>
-      <c r="C111" s="71"/>
+      <c r="B111" s="81"/>
+      <c r="C111" s="82"/>
       <c r="D111" s="34"/>
       <c r="E111" s="31"/>
-      <c r="F111" s="70"/>
-      <c r="G111" s="71"/>
+      <c r="F111" s="81"/>
+      <c r="G111" s="82"/>
       <c r="H111" s="34"/>
       <c r="I111" s="31"/>
-      <c r="J111" s="70"/>
-      <c r="K111" s="71"/>
+      <c r="J111" s="81"/>
+      <c r="K111" s="82"/>
       <c r="L111" s="34"/>
     </row>
     <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B112" s="72"/>
-      <c r="C112" s="73"/>
-      <c r="D112" s="74"/>
+      <c r="B112" s="106"/>
+      <c r="C112" s="107"/>
+      <c r="D112" s="108"/>
       <c r="E112" s="32"/>
-      <c r="F112" s="72"/>
-      <c r="G112" s="73"/>
-      <c r="H112" s="74"/>
+      <c r="F112" s="106"/>
+      <c r="G112" s="107"/>
+      <c r="H112" s="108"/>
       <c r="I112" s="32"/>
-      <c r="J112" s="72"/>
-      <c r="K112" s="73"/>
-      <c r="L112" s="74"/>
+      <c r="J112" s="106"/>
+      <c r="K112" s="107"/>
+      <c r="L112" s="108"/>
     </row>
     <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B113" s="83"/>
@@ -7973,30 +8020,30 @@
       <c r="L113" s="85"/>
     </row>
     <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B114" s="89"/>
-      <c r="C114" s="90"/>
-      <c r="D114" s="91"/>
+      <c r="B114" s="70"/>
+      <c r="C114" s="71"/>
+      <c r="D114" s="72"/>
       <c r="E114" s="32"/>
-      <c r="F114" s="89"/>
-      <c r="G114" s="90"/>
-      <c r="H114" s="91"/>
+      <c r="F114" s="70"/>
+      <c r="G114" s="71"/>
+      <c r="H114" s="72"/>
       <c r="I114" s="32"/>
-      <c r="J114" s="89"/>
-      <c r="K114" s="90"/>
-      <c r="L114" s="91"/>
+      <c r="J114" s="70"/>
+      <c r="K114" s="71"/>
+      <c r="L114" s="72"/>
     </row>
     <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B115" s="80"/>
-      <c r="C115" s="81"/>
-      <c r="D115" s="82"/>
+      <c r="B115" s="65"/>
+      <c r="C115" s="66"/>
+      <c r="D115" s="67"/>
       <c r="E115" s="31"/>
-      <c r="F115" s="80"/>
-      <c r="G115" s="81"/>
-      <c r="H115" s="82"/>
+      <c r="F115" s="65"/>
+      <c r="G115" s="66"/>
+      <c r="H115" s="67"/>
       <c r="I115" s="31"/>
-      <c r="J115" s="80"/>
-      <c r="K115" s="81"/>
-      <c r="L115" s="82"/>
+      <c r="J115" s="65"/>
+      <c r="K115" s="66"/>
+      <c r="L115" s="67"/>
     </row>
     <row r="116" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B116" s="35"/>
@@ -8012,30 +8059,30 @@
       <c r="L116" s="35"/>
     </row>
     <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B117" s="70"/>
-      <c r="C117" s="71"/>
+      <c r="B117" s="81"/>
+      <c r="C117" s="82"/>
       <c r="D117" s="34"/>
       <c r="E117" s="32"/>
-      <c r="F117" s="70"/>
-      <c r="G117" s="71"/>
+      <c r="F117" s="81"/>
+      <c r="G117" s="82"/>
       <c r="H117" s="34"/>
       <c r="I117" s="32"/>
-      <c r="J117" s="70"/>
-      <c r="K117" s="71"/>
+      <c r="J117" s="81"/>
+      <c r="K117" s="82"/>
       <c r="L117" s="34"/>
     </row>
     <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B118" s="72"/>
-      <c r="C118" s="73"/>
-      <c r="D118" s="74"/>
+      <c r="B118" s="106"/>
+      <c r="C118" s="107"/>
+      <c r="D118" s="108"/>
       <c r="E118" s="32"/>
-      <c r="F118" s="72"/>
-      <c r="G118" s="73"/>
-      <c r="H118" s="74"/>
+      <c r="F118" s="106"/>
+      <c r="G118" s="107"/>
+      <c r="H118" s="108"/>
       <c r="I118" s="32"/>
-      <c r="J118" s="72"/>
-      <c r="K118" s="73"/>
-      <c r="L118" s="74"/>
+      <c r="J118" s="106"/>
+      <c r="K118" s="107"/>
+      <c r="L118" s="108"/>
     </row>
     <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B119" s="83"/>
@@ -8051,30 +8098,30 @@
       <c r="L119" s="85"/>
     </row>
     <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B120" s="89"/>
-      <c r="C120" s="90"/>
-      <c r="D120" s="91"/>
+      <c r="B120" s="70"/>
+      <c r="C120" s="71"/>
+      <c r="D120" s="72"/>
       <c r="E120" s="32"/>
-      <c r="F120" s="89"/>
-      <c r="G120" s="90"/>
-      <c r="H120" s="91"/>
+      <c r="F120" s="70"/>
+      <c r="G120" s="71"/>
+      <c r="H120" s="72"/>
       <c r="I120" s="32"/>
-      <c r="J120" s="89"/>
-      <c r="K120" s="90"/>
-      <c r="L120" s="91"/>
+      <c r="J120" s="70"/>
+      <c r="K120" s="71"/>
+      <c r="L120" s="72"/>
     </row>
     <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B121" s="80"/>
-      <c r="C121" s="81"/>
-      <c r="D121" s="82"/>
+      <c r="B121" s="65"/>
+      <c r="C121" s="66"/>
+      <c r="D121" s="67"/>
       <c r="E121" s="31"/>
-      <c r="F121" s="80"/>
-      <c r="G121" s="81"/>
-      <c r="H121" s="82"/>
+      <c r="F121" s="65"/>
+      <c r="G121" s="66"/>
+      <c r="H121" s="67"/>
       <c r="I121" s="31"/>
-      <c r="J121" s="80"/>
-      <c r="K121" s="81"/>
-      <c r="L121" s="82"/>
+      <c r="J121" s="65"/>
+      <c r="K121" s="66"/>
+      <c r="L121" s="67"/>
     </row>
     <row r="122" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B122" s="35"/>
@@ -8090,30 +8137,30 @@
       <c r="L122" s="35"/>
     </row>
     <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B123" s="70"/>
-      <c r="C123" s="71"/>
+      <c r="B123" s="81"/>
+      <c r="C123" s="82"/>
       <c r="D123" s="34"/>
       <c r="E123" s="32"/>
-      <c r="F123" s="70"/>
-      <c r="G123" s="71"/>
+      <c r="F123" s="81"/>
+      <c r="G123" s="82"/>
       <c r="H123" s="34"/>
       <c r="I123" s="32"/>
-      <c r="J123" s="70"/>
-      <c r="K123" s="71"/>
+      <c r="J123" s="81"/>
+      <c r="K123" s="82"/>
       <c r="L123" s="34"/>
     </row>
     <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B124" s="72"/>
-      <c r="C124" s="73"/>
-      <c r="D124" s="74"/>
+      <c r="B124" s="106"/>
+      <c r="C124" s="107"/>
+      <c r="D124" s="108"/>
       <c r="E124" s="32"/>
-      <c r="F124" s="72"/>
-      <c r="G124" s="73"/>
-      <c r="H124" s="74"/>
+      <c r="F124" s="106"/>
+      <c r="G124" s="107"/>
+      <c r="H124" s="108"/>
       <c r="I124" s="32"/>
-      <c r="J124" s="72"/>
-      <c r="K124" s="73"/>
-      <c r="L124" s="74"/>
+      <c r="J124" s="106"/>
+      <c r="K124" s="107"/>
+      <c r="L124" s="108"/>
     </row>
     <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B125" s="83"/>
@@ -8129,30 +8176,30 @@
       <c r="L125" s="85"/>
     </row>
     <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B126" s="89"/>
-      <c r="C126" s="90"/>
-      <c r="D126" s="91"/>
+      <c r="B126" s="70"/>
+      <c r="C126" s="71"/>
+      <c r="D126" s="72"/>
       <c r="E126" s="32"/>
-      <c r="F126" s="89"/>
-      <c r="G126" s="90"/>
-      <c r="H126" s="91"/>
+      <c r="F126" s="70"/>
+      <c r="G126" s="71"/>
+      <c r="H126" s="72"/>
       <c r="I126" s="31"/>
-      <c r="J126" s="89"/>
-      <c r="K126" s="90"/>
-      <c r="L126" s="91"/>
+      <c r="J126" s="70"/>
+      <c r="K126" s="71"/>
+      <c r="L126" s="72"/>
     </row>
     <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B127" s="80"/>
-      <c r="C127" s="81"/>
-      <c r="D127" s="82"/>
+      <c r="B127" s="65"/>
+      <c r="C127" s="66"/>
+      <c r="D127" s="67"/>
       <c r="E127" s="31"/>
-      <c r="F127" s="80"/>
-      <c r="G127" s="81"/>
-      <c r="H127" s="82"/>
+      <c r="F127" s="65"/>
+      <c r="G127" s="66"/>
+      <c r="H127" s="67"/>
       <c r="I127" s="31"/>
-      <c r="J127" s="80"/>
-      <c r="K127" s="81"/>
-      <c r="L127" s="82"/>
+      <c r="J127" s="65"/>
+      <c r="K127" s="66"/>
+      <c r="L127" s="67"/>
     </row>
     <row r="128" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B128" s="35"/>
@@ -8168,30 +8215,30 @@
       <c r="L128" s="35"/>
     </row>
     <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B129" s="70"/>
-      <c r="C129" s="71"/>
+      <c r="B129" s="81"/>
+      <c r="C129" s="82"/>
       <c r="D129" s="34"/>
       <c r="E129" s="31"/>
-      <c r="F129" s="70"/>
-      <c r="G129" s="71"/>
+      <c r="F129" s="81"/>
+      <c r="G129" s="82"/>
       <c r="H129" s="34"/>
       <c r="I129" s="32"/>
-      <c r="J129" s="70"/>
-      <c r="K129" s="71"/>
+      <c r="J129" s="81"/>
+      <c r="K129" s="82"/>
       <c r="L129" s="34"/>
     </row>
     <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B130" s="72"/>
-      <c r="C130" s="73"/>
-      <c r="D130" s="74"/>
+      <c r="B130" s="106"/>
+      <c r="C130" s="107"/>
+      <c r="D130" s="108"/>
       <c r="E130" s="32"/>
-      <c r="F130" s="72"/>
-      <c r="G130" s="73"/>
-      <c r="H130" s="74"/>
+      <c r="F130" s="106"/>
+      <c r="G130" s="107"/>
+      <c r="H130" s="108"/>
       <c r="I130" s="32"/>
-      <c r="J130" s="72"/>
-      <c r="K130" s="73"/>
-      <c r="L130" s="74"/>
+      <c r="J130" s="106"/>
+      <c r="K130" s="107"/>
+      <c r="L130" s="108"/>
     </row>
     <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B131" s="83"/>
@@ -8207,56 +8254,849 @@
       <c r="L131" s="85"/>
     </row>
     <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B132" s="89"/>
-      <c r="C132" s="90"/>
-      <c r="D132" s="91"/>
+      <c r="B132" s="70"/>
+      <c r="C132" s="71"/>
+      <c r="D132" s="72"/>
       <c r="E132" s="35"/>
-      <c r="F132" s="89"/>
-      <c r="G132" s="90"/>
-      <c r="H132" s="91"/>
+      <c r="F132" s="70"/>
+      <c r="G132" s="71"/>
+      <c r="H132" s="72"/>
       <c r="I132" s="31"/>
-      <c r="J132" s="89"/>
-      <c r="K132" s="90"/>
-      <c r="L132" s="91"/>
+      <c r="J132" s="70"/>
+      <c r="K132" s="71"/>
+      <c r="L132" s="72"/>
     </row>
     <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B133" s="80"/>
-      <c r="C133" s="81"/>
-      <c r="D133" s="82"/>
+      <c r="B133" s="65"/>
+      <c r="C133" s="66"/>
+      <c r="D133" s="67"/>
       <c r="E133" s="31"/>
-      <c r="F133" s="80"/>
-      <c r="G133" s="81"/>
-      <c r="H133" s="82"/>
+      <c r="F133" s="65"/>
+      <c r="G133" s="66"/>
+      <c r="H133" s="67"/>
       <c r="I133" s="31"/>
-      <c r="J133" s="80"/>
-      <c r="K133" s="81"/>
-      <c r="L133" s="82"/>
+      <c r="J133" s="65"/>
+      <c r="K133" s="66"/>
+      <c r="L133" s="67"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0" selectUnlockedCells="1"/>
   <dataConsolidate/>
   <mergeCells count="862">
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="F97:H97"/>
-    <mergeCell ref="J97:L97"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="F99:G99"/>
-    <mergeCell ref="J99:K99"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="J87:K87"/>
-    <mergeCell ref="B91:D91"/>
-    <mergeCell ref="F91:H91"/>
-    <mergeCell ref="J91:L91"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="F93:G93"/>
-    <mergeCell ref="J93:K93"/>
-    <mergeCell ref="J90:L90"/>
-    <mergeCell ref="B96:D96"/>
-    <mergeCell ref="F96:H96"/>
-    <mergeCell ref="F95:H95"/>
-    <mergeCell ref="F94:H94"/>
-    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R41:T41"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R42:T42"/>
+    <mergeCell ref="V52:W52"/>
+    <mergeCell ref="V41:X41"/>
+    <mergeCell ref="V40:X40"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="J81:K81"/>
+    <mergeCell ref="J77:L77"/>
+    <mergeCell ref="J76:L76"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="V50:X50"/>
+    <mergeCell ref="R49:T49"/>
+    <mergeCell ref="J49:L49"/>
+    <mergeCell ref="J47:L47"/>
+    <mergeCell ref="J79:L79"/>
+    <mergeCell ref="J71:L71"/>
+    <mergeCell ref="R50:T50"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="J60:L60"/>
+    <mergeCell ref="J78:L78"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="J53:L53"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="R71:T71"/>
+    <mergeCell ref="N71:P71"/>
+    <mergeCell ref="R76:T76"/>
+    <mergeCell ref="N69:P69"/>
+    <mergeCell ref="R63:T63"/>
+    <mergeCell ref="N68:P68"/>
+    <mergeCell ref="F75:G75"/>
+    <mergeCell ref="AL50:AN50"/>
+    <mergeCell ref="AL52:AM52"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="F62:H62"/>
+    <mergeCell ref="F61:H61"/>
+    <mergeCell ref="J64:L64"/>
+    <mergeCell ref="F69:H69"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="J66:K66"/>
+    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="F67:H67"/>
+    <mergeCell ref="J67:L67"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="F68:H68"/>
+    <mergeCell ref="J68:L68"/>
+    <mergeCell ref="F63:H63"/>
+    <mergeCell ref="Z55:AB55"/>
+    <mergeCell ref="N63:P63"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="F54:H54"/>
+    <mergeCell ref="B100:D100"/>
+    <mergeCell ref="F100:H100"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="F88:H88"/>
+    <mergeCell ref="B89:D89"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="J75:K75"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="J82:L82"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B95:D95"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="J70:L70"/>
+    <mergeCell ref="B71:D71"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="Z102:AB102"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="F70:H70"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="F76:H76"/>
+    <mergeCell ref="F90:H90"/>
+    <mergeCell ref="F89:H89"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="F82:H82"/>
+    <mergeCell ref="F83:H83"/>
+    <mergeCell ref="F84:H84"/>
+    <mergeCell ref="F77:H77"/>
+    <mergeCell ref="B85:D85"/>
+    <mergeCell ref="F79:H79"/>
+    <mergeCell ref="F71:H71"/>
+    <mergeCell ref="F85:H85"/>
+    <mergeCell ref="Z100:AB100"/>
+    <mergeCell ref="N94:P94"/>
+    <mergeCell ref="R95:T95"/>
+    <mergeCell ref="N96:P96"/>
+    <mergeCell ref="R99:S99"/>
+    <mergeCell ref="V99:W99"/>
+    <mergeCell ref="Z99:AA99"/>
+    <mergeCell ref="N97:P97"/>
+    <mergeCell ref="N99:O99"/>
+    <mergeCell ref="F107:H107"/>
+    <mergeCell ref="J102:L102"/>
+    <mergeCell ref="J112:L112"/>
+    <mergeCell ref="J111:K111"/>
+    <mergeCell ref="B106:D106"/>
+    <mergeCell ref="B107:D107"/>
+    <mergeCell ref="F106:H106"/>
+    <mergeCell ref="F105:G105"/>
+    <mergeCell ref="N102:P102"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="F102:H102"/>
+    <mergeCell ref="J107:L107"/>
+    <mergeCell ref="J108:L108"/>
+    <mergeCell ref="B109:D109"/>
+    <mergeCell ref="F109:H109"/>
+    <mergeCell ref="B108:D108"/>
+    <mergeCell ref="J105:K105"/>
+    <mergeCell ref="F108:H108"/>
+    <mergeCell ref="J106:L106"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="F111:G111"/>
+    <mergeCell ref="J124:L124"/>
+    <mergeCell ref="F119:H119"/>
+    <mergeCell ref="J119:L119"/>
+    <mergeCell ref="J109:L109"/>
+    <mergeCell ref="B120:D120"/>
+    <mergeCell ref="B121:D121"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="F123:G123"/>
+    <mergeCell ref="B119:D119"/>
+    <mergeCell ref="B113:D113"/>
+    <mergeCell ref="F113:H113"/>
+    <mergeCell ref="J113:L113"/>
+    <mergeCell ref="B114:D114"/>
+    <mergeCell ref="F114:H114"/>
+    <mergeCell ref="J114:L114"/>
+    <mergeCell ref="F121:H121"/>
+    <mergeCell ref="J123:K123"/>
+    <mergeCell ref="F112:H112"/>
+    <mergeCell ref="B112:D112"/>
+    <mergeCell ref="B125:D125"/>
+    <mergeCell ref="F125:H125"/>
+    <mergeCell ref="J121:L121"/>
+    <mergeCell ref="J125:L125"/>
+    <mergeCell ref="B118:D118"/>
+    <mergeCell ref="F118:H118"/>
+    <mergeCell ref="B115:D115"/>
+    <mergeCell ref="F115:H115"/>
+    <mergeCell ref="J115:L115"/>
+    <mergeCell ref="F120:H120"/>
+    <mergeCell ref="J120:L120"/>
+    <mergeCell ref="J118:L118"/>
+    <mergeCell ref="B124:D124"/>
+    <mergeCell ref="F124:H124"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="Z12:AA12"/>
+    <mergeCell ref="B133:D133"/>
+    <mergeCell ref="F133:H133"/>
+    <mergeCell ref="J133:L133"/>
+    <mergeCell ref="B127:D127"/>
+    <mergeCell ref="F127:H127"/>
+    <mergeCell ref="J127:L127"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="F129:G129"/>
+    <mergeCell ref="J129:K129"/>
+    <mergeCell ref="B130:D130"/>
+    <mergeCell ref="F130:H130"/>
+    <mergeCell ref="J130:L130"/>
+    <mergeCell ref="B132:D132"/>
+    <mergeCell ref="F132:H132"/>
+    <mergeCell ref="J132:L132"/>
+    <mergeCell ref="B131:D131"/>
+    <mergeCell ref="F131:H131"/>
+    <mergeCell ref="J131:L131"/>
+    <mergeCell ref="B126:D126"/>
+    <mergeCell ref="F126:H126"/>
+    <mergeCell ref="J126:L126"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="J117:K117"/>
+    <mergeCell ref="V102:X102"/>
+    <mergeCell ref="R68:T68"/>
+    <mergeCell ref="V68:X68"/>
+    <mergeCell ref="N66:O66"/>
+    <mergeCell ref="N67:P67"/>
+    <mergeCell ref="N60:P60"/>
+    <mergeCell ref="J69:L69"/>
+    <mergeCell ref="N62:P62"/>
+    <mergeCell ref="R62:T62"/>
+    <mergeCell ref="N89:P89"/>
+    <mergeCell ref="N87:O87"/>
+    <mergeCell ref="J88:L88"/>
+    <mergeCell ref="J85:L85"/>
+    <mergeCell ref="J101:L101"/>
+    <mergeCell ref="R102:T102"/>
+    <mergeCell ref="R100:T100"/>
+    <mergeCell ref="V100:X100"/>
+    <mergeCell ref="R101:T101"/>
+    <mergeCell ref="N100:P100"/>
+    <mergeCell ref="N81:O81"/>
+    <mergeCell ref="R81:S81"/>
+    <mergeCell ref="V81:W81"/>
+    <mergeCell ref="V82:X82"/>
+    <mergeCell ref="N82:P82"/>
+    <mergeCell ref="F101:H101"/>
+    <mergeCell ref="R94:T94"/>
+    <mergeCell ref="V64:X64"/>
+    <mergeCell ref="R64:T64"/>
+    <mergeCell ref="R61:T61"/>
+    <mergeCell ref="R60:T60"/>
+    <mergeCell ref="R87:S87"/>
+    <mergeCell ref="V87:W87"/>
+    <mergeCell ref="N91:P91"/>
+    <mergeCell ref="J96:L96"/>
+    <mergeCell ref="N83:P83"/>
+    <mergeCell ref="N84:P84"/>
+    <mergeCell ref="N90:P90"/>
+    <mergeCell ref="J89:L89"/>
+    <mergeCell ref="J83:L83"/>
+    <mergeCell ref="V89:X89"/>
+    <mergeCell ref="R89:T89"/>
+    <mergeCell ref="R84:T84"/>
+    <mergeCell ref="N85:P85"/>
+    <mergeCell ref="R85:T85"/>
+    <mergeCell ref="V85:X85"/>
+    <mergeCell ref="R88:T88"/>
+    <mergeCell ref="V84:X84"/>
+    <mergeCell ref="J84:L84"/>
+    <mergeCell ref="AL9:AN9"/>
+    <mergeCell ref="AD9:AF9"/>
+    <mergeCell ref="AH16:AJ16"/>
+    <mergeCell ref="AL10:AN10"/>
+    <mergeCell ref="AL14:AN14"/>
+    <mergeCell ref="AL16:AN16"/>
+    <mergeCell ref="Z15:AB15"/>
+    <mergeCell ref="AD15:AF15"/>
+    <mergeCell ref="Z13:AA13"/>
+    <mergeCell ref="AL15:AN15"/>
+    <mergeCell ref="AL12:AM12"/>
+    <mergeCell ref="AD16:AF16"/>
+    <mergeCell ref="Z10:AB10"/>
+    <mergeCell ref="AH14:AJ14"/>
+    <mergeCell ref="Z14:AB14"/>
+    <mergeCell ref="AD14:AF14"/>
+    <mergeCell ref="AD13:AE13"/>
+    <mergeCell ref="AH10:AJ10"/>
+    <mergeCell ref="AH15:AJ15"/>
+    <mergeCell ref="AD10:AF10"/>
+    <mergeCell ref="AD12:AE12"/>
+    <mergeCell ref="AH12:AI12"/>
+    <mergeCell ref="AH9:AJ9"/>
+    <mergeCell ref="Z16:AB16"/>
+    <mergeCell ref="AH21:AI21"/>
+    <mergeCell ref="AH31:AI31"/>
+    <mergeCell ref="AD31:AE31"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="Z21:AA21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="R22:T22"/>
+    <mergeCell ref="V22:X22"/>
+    <mergeCell ref="Z22:AB22"/>
+    <mergeCell ref="AD22:AF22"/>
+    <mergeCell ref="AH22:AJ22"/>
+    <mergeCell ref="AD29:AE29"/>
+    <mergeCell ref="AH29:AI29"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:T23"/>
+    <mergeCell ref="V23:X23"/>
+    <mergeCell ref="V27:W27"/>
+    <mergeCell ref="AD27:AE27"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="N29:O29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="Z30:AA30"/>
+    <mergeCell ref="N25:AB26"/>
+    <mergeCell ref="Z88:AB88"/>
+    <mergeCell ref="J94:L94"/>
+    <mergeCell ref="J95:L95"/>
+    <mergeCell ref="V94:X94"/>
+    <mergeCell ref="V96:X96"/>
+    <mergeCell ref="V95:X95"/>
+    <mergeCell ref="Z96:AB96"/>
+    <mergeCell ref="R96:T96"/>
+    <mergeCell ref="B101:D101"/>
+    <mergeCell ref="N101:P101"/>
+    <mergeCell ref="N95:P95"/>
+    <mergeCell ref="V101:X101"/>
+    <mergeCell ref="Z101:AB101"/>
+    <mergeCell ref="Z94:AB94"/>
+    <mergeCell ref="Z95:AB95"/>
+    <mergeCell ref="V90:X90"/>
+    <mergeCell ref="V88:X88"/>
+    <mergeCell ref="R90:T90"/>
+    <mergeCell ref="Z89:AB89"/>
+    <mergeCell ref="Z90:AB90"/>
+    <mergeCell ref="N88:P88"/>
+    <mergeCell ref="N93:O93"/>
+    <mergeCell ref="J100:L100"/>
+    <mergeCell ref="B97:D97"/>
+    <mergeCell ref="AL1:AN1"/>
+    <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="AD2:AF2"/>
+    <mergeCell ref="AH2:AJ2"/>
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="AH8:AJ8"/>
+    <mergeCell ref="AL6:AM6"/>
+    <mergeCell ref="AD1:AF1"/>
+    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="AL7:AM7"/>
+    <mergeCell ref="AD8:AF8"/>
+    <mergeCell ref="Z8:AB8"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AH7:AI7"/>
+    <mergeCell ref="AD7:AE7"/>
+    <mergeCell ref="Z7:AA7"/>
+    <mergeCell ref="AL8:AN8"/>
+    <mergeCell ref="AD4:AN5"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="AD6:AE6"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="V1:X1"/>
+    <mergeCell ref="V14:X14"/>
+    <mergeCell ref="R15:T15"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="B4:L5"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="V2:X2"/>
+    <mergeCell ref="N4:AB5"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="R9:T9"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="N18:AB19"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="R14:T14"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="V15:X15"/>
+    <mergeCell ref="V16:X16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="Z20:AA20"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="V28:W28"/>
+    <mergeCell ref="Z28:AA28"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="Z27:AA27"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="V13:W13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="Z9:AB9"/>
+    <mergeCell ref="R10:T10"/>
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="AD21:AE21"/>
+    <mergeCell ref="AD49:AF49"/>
+    <mergeCell ref="AD43:AF43"/>
+    <mergeCell ref="R48:T48"/>
+    <mergeCell ref="Z42:AB42"/>
+    <mergeCell ref="Z43:AB43"/>
+    <mergeCell ref="N36:AB37"/>
+    <mergeCell ref="Z48:AB48"/>
+    <mergeCell ref="Z45:AA45"/>
+    <mergeCell ref="Z46:AB46"/>
+    <mergeCell ref="AD38:AE38"/>
+    <mergeCell ref="AD39:AF39"/>
+    <mergeCell ref="AD40:AF40"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="V49:X49"/>
+    <mergeCell ref="V48:X48"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="AL102:AN102"/>
+    <mergeCell ref="AL101:AN101"/>
+    <mergeCell ref="AL96:AN96"/>
+    <mergeCell ref="AD102:AF102"/>
+    <mergeCell ref="AH102:AJ102"/>
+    <mergeCell ref="AL90:AN90"/>
+    <mergeCell ref="AL95:AN95"/>
+    <mergeCell ref="AD101:AF101"/>
+    <mergeCell ref="AH101:AJ101"/>
+    <mergeCell ref="AH100:AJ100"/>
+    <mergeCell ref="AL94:AN94"/>
+    <mergeCell ref="AD100:AF100"/>
+    <mergeCell ref="AD96:AF96"/>
+    <mergeCell ref="AD94:AF94"/>
+    <mergeCell ref="AD95:AF95"/>
+    <mergeCell ref="AH96:AJ96"/>
+    <mergeCell ref="AD90:AF90"/>
+    <mergeCell ref="AH95:AJ95"/>
+    <mergeCell ref="AH94:AJ94"/>
+    <mergeCell ref="AL100:AN100"/>
+    <mergeCell ref="AD97:AF97"/>
+    <mergeCell ref="AH97:AJ97"/>
+    <mergeCell ref="AL97:AN97"/>
+    <mergeCell ref="AH90:AJ90"/>
+    <mergeCell ref="AD82:AF82"/>
+    <mergeCell ref="AH83:AJ83"/>
+    <mergeCell ref="AD84:AF84"/>
+    <mergeCell ref="AH84:AJ84"/>
+    <mergeCell ref="AD83:AF83"/>
+    <mergeCell ref="Z84:AB84"/>
+    <mergeCell ref="Z82:AB82"/>
+    <mergeCell ref="AL77:AN77"/>
+    <mergeCell ref="AL78:AN78"/>
+    <mergeCell ref="AD77:AF77"/>
+    <mergeCell ref="AD79:AF79"/>
+    <mergeCell ref="AH79:AJ79"/>
+    <mergeCell ref="AL79:AN79"/>
+    <mergeCell ref="AD81:AE81"/>
+    <mergeCell ref="AH81:AI81"/>
+    <mergeCell ref="AL81:AM81"/>
+    <mergeCell ref="AL82:AN82"/>
+    <mergeCell ref="AL88:AN88"/>
+    <mergeCell ref="AL89:AN89"/>
+    <mergeCell ref="AL83:AN83"/>
+    <mergeCell ref="AL84:AN84"/>
+    <mergeCell ref="AD88:AF88"/>
+    <mergeCell ref="AD89:AF89"/>
+    <mergeCell ref="AH87:AI87"/>
+    <mergeCell ref="AL87:AM87"/>
+    <mergeCell ref="AH88:AJ88"/>
+    <mergeCell ref="AH89:AJ89"/>
+    <mergeCell ref="AD85:AF85"/>
+    <mergeCell ref="AH85:AJ85"/>
+    <mergeCell ref="AL85:AN85"/>
+    <mergeCell ref="Z76:AB76"/>
+    <mergeCell ref="Z77:AB77"/>
+    <mergeCell ref="V76:X76"/>
+    <mergeCell ref="N78:P78"/>
+    <mergeCell ref="Z78:AB78"/>
+    <mergeCell ref="N79:P79"/>
+    <mergeCell ref="R79:T79"/>
+    <mergeCell ref="V79:X79"/>
+    <mergeCell ref="Z79:AB79"/>
+    <mergeCell ref="V78:X78"/>
+    <mergeCell ref="R78:T78"/>
+    <mergeCell ref="AL76:AN76"/>
+    <mergeCell ref="AD76:AF76"/>
+    <mergeCell ref="Z81:AA81"/>
+    <mergeCell ref="AL62:AN62"/>
+    <mergeCell ref="AL63:AN63"/>
+    <mergeCell ref="AL71:AN71"/>
+    <mergeCell ref="AL70:AN70"/>
+    <mergeCell ref="AL69:AN69"/>
+    <mergeCell ref="N73:AB74"/>
+    <mergeCell ref="N75:O75"/>
+    <mergeCell ref="R75:S75"/>
+    <mergeCell ref="V75:W75"/>
+    <mergeCell ref="Z75:AA75"/>
+    <mergeCell ref="AD75:AE75"/>
+    <mergeCell ref="N64:P64"/>
+    <mergeCell ref="N70:P70"/>
+    <mergeCell ref="AH70:AJ70"/>
+    <mergeCell ref="AD70:AF70"/>
+    <mergeCell ref="Z69:AB69"/>
+    <mergeCell ref="Z70:AB70"/>
+    <mergeCell ref="V71:X71"/>
+    <mergeCell ref="AD63:AF63"/>
+    <mergeCell ref="AH64:AJ64"/>
+    <mergeCell ref="AH75:AI75"/>
+    <mergeCell ref="AH23:AJ23"/>
+    <mergeCell ref="AL23:AN23"/>
+    <mergeCell ref="AD28:AE28"/>
+    <mergeCell ref="AH28:AI28"/>
+    <mergeCell ref="AL28:AM28"/>
+    <mergeCell ref="AH52:AI52"/>
+    <mergeCell ref="AH54:AJ54"/>
+    <mergeCell ref="AH55:AJ55"/>
+    <mergeCell ref="AD56:AF56"/>
+    <mergeCell ref="AH56:AJ56"/>
+    <mergeCell ref="AH53:AJ53"/>
+    <mergeCell ref="AH47:AJ47"/>
+    <mergeCell ref="AD42:AF42"/>
+    <mergeCell ref="AD48:AF48"/>
+    <mergeCell ref="AD53:AF53"/>
+    <mergeCell ref="AD50:AF50"/>
+    <mergeCell ref="AD52:AE52"/>
+    <mergeCell ref="AL33:AM33"/>
+    <mergeCell ref="AD47:AF47"/>
+    <mergeCell ref="AH40:AJ40"/>
+    <mergeCell ref="AH38:AI38"/>
+    <mergeCell ref="AH39:AJ39"/>
+    <mergeCell ref="AL38:AM38"/>
+    <mergeCell ref="AL39:AN39"/>
+    <mergeCell ref="AL20:AM20"/>
+    <mergeCell ref="AL27:AM27"/>
+    <mergeCell ref="AL21:AM21"/>
+    <mergeCell ref="AH27:AI27"/>
+    <mergeCell ref="AD20:AE20"/>
+    <mergeCell ref="AH20:AI20"/>
+    <mergeCell ref="AD59:AE59"/>
+    <mergeCell ref="V57:X57"/>
+    <mergeCell ref="V61:X61"/>
+    <mergeCell ref="Z61:AB61"/>
+    <mergeCell ref="AD60:AF60"/>
+    <mergeCell ref="AH60:AJ60"/>
+    <mergeCell ref="V60:X60"/>
+    <mergeCell ref="Z60:AB60"/>
+    <mergeCell ref="V30:W30"/>
+    <mergeCell ref="Z31:AA31"/>
+    <mergeCell ref="V29:W29"/>
+    <mergeCell ref="Z29:AA29"/>
+    <mergeCell ref="AL60:AN60"/>
+    <mergeCell ref="AL61:AN61"/>
+    <mergeCell ref="Z56:AB56"/>
+    <mergeCell ref="AL22:AN22"/>
+    <mergeCell ref="Z23:AB23"/>
+    <mergeCell ref="AD23:AF23"/>
+    <mergeCell ref="AL57:AN57"/>
+    <mergeCell ref="AL59:AM59"/>
+    <mergeCell ref="AL56:AN56"/>
+    <mergeCell ref="AL54:AN54"/>
+    <mergeCell ref="AL53:AN53"/>
+    <mergeCell ref="AL55:AN55"/>
+    <mergeCell ref="Z59:AA59"/>
+    <mergeCell ref="R56:T56"/>
+    <mergeCell ref="V53:X53"/>
+    <mergeCell ref="R57:T57"/>
+    <mergeCell ref="AH61:AJ61"/>
+    <mergeCell ref="J54:L54"/>
+    <mergeCell ref="N56:P56"/>
+    <mergeCell ref="R54:T54"/>
+    <mergeCell ref="V54:X54"/>
+    <mergeCell ref="N54:P54"/>
+    <mergeCell ref="R55:T55"/>
+    <mergeCell ref="V59:W59"/>
+    <mergeCell ref="V55:X55"/>
+    <mergeCell ref="AD57:AF57"/>
+    <mergeCell ref="Z54:AB54"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="N61:P61"/>
+    <mergeCell ref="AD41:AF41"/>
+    <mergeCell ref="AL43:AN43"/>
+    <mergeCell ref="AL45:AM45"/>
+    <mergeCell ref="AL42:AN42"/>
+    <mergeCell ref="Z41:AB41"/>
+    <mergeCell ref="Z40:AB40"/>
+    <mergeCell ref="Z38:AA38"/>
+    <mergeCell ref="Z39:AB39"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="V31:W31"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="R39:T39"/>
+    <mergeCell ref="V38:W38"/>
+    <mergeCell ref="V39:X39"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="Z47:AB47"/>
+    <mergeCell ref="AH34:AI34"/>
+    <mergeCell ref="V42:X42"/>
+    <mergeCell ref="V43:X43"/>
+    <mergeCell ref="V45:W45"/>
+    <mergeCell ref="V46:X46"/>
+    <mergeCell ref="V47:X47"/>
+    <mergeCell ref="N32:O32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="V32:W32"/>
+    <mergeCell ref="Z32:AA32"/>
+    <mergeCell ref="AD32:AE32"/>
+    <mergeCell ref="AH32:AI32"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="V33:W33"/>
+    <mergeCell ref="Z33:AA33"/>
+    <mergeCell ref="AD33:AE33"/>
+    <mergeCell ref="AH33:AI33"/>
+    <mergeCell ref="AD46:AE46"/>
+    <mergeCell ref="AH44:AJ44"/>
+    <mergeCell ref="AH46:AI46"/>
+    <mergeCell ref="AH41:AJ41"/>
+    <mergeCell ref="AL75:AM75"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="N47:O47"/>
+    <mergeCell ref="AL32:AM32"/>
+    <mergeCell ref="AL31:AM31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="AD87:AE87"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="V34:W34"/>
+    <mergeCell ref="Z34:AA34"/>
+    <mergeCell ref="AD34:AE34"/>
+    <mergeCell ref="R66:S66"/>
+    <mergeCell ref="V66:W66"/>
+    <mergeCell ref="Z66:AA66"/>
+    <mergeCell ref="R67:T67"/>
+    <mergeCell ref="V67:X67"/>
+    <mergeCell ref="Z67:AB67"/>
+    <mergeCell ref="V69:X69"/>
+    <mergeCell ref="R69:T69"/>
+    <mergeCell ref="V70:X70"/>
+    <mergeCell ref="R70:T70"/>
+    <mergeCell ref="R77:T77"/>
+    <mergeCell ref="V77:X77"/>
+    <mergeCell ref="AL49:AN49"/>
+    <mergeCell ref="AH66:AI66"/>
+    <mergeCell ref="Z64:AB64"/>
+    <mergeCell ref="Z68:AB68"/>
+    <mergeCell ref="AD68:AF68"/>
+    <mergeCell ref="Z62:AB62"/>
+    <mergeCell ref="Z57:AB57"/>
+    <mergeCell ref="AD54:AF54"/>
+    <mergeCell ref="AD55:AF55"/>
+    <mergeCell ref="Z50:AB50"/>
+    <mergeCell ref="Z49:AB49"/>
+    <mergeCell ref="AD67:AF67"/>
+    <mergeCell ref="AH63:AJ63"/>
+    <mergeCell ref="AH62:AJ62"/>
+    <mergeCell ref="AD62:AF62"/>
+    <mergeCell ref="AH68:AJ68"/>
+    <mergeCell ref="AL68:AN68"/>
+    <mergeCell ref="Z63:AB63"/>
+    <mergeCell ref="AL64:AN64"/>
+    <mergeCell ref="AH57:AJ57"/>
+    <mergeCell ref="AL66:AM66"/>
+    <mergeCell ref="Z52:AA52"/>
+    <mergeCell ref="Z53:AB53"/>
+    <mergeCell ref="AD61:AF61"/>
+    <mergeCell ref="Z87:AA87"/>
+    <mergeCell ref="AH71:AJ71"/>
+    <mergeCell ref="AD71:AF71"/>
+    <mergeCell ref="Z71:AB71"/>
+    <mergeCell ref="N77:P77"/>
+    <mergeCell ref="N55:P55"/>
+    <mergeCell ref="Z85:AB85"/>
+    <mergeCell ref="Z83:AB83"/>
+    <mergeCell ref="N59:O59"/>
+    <mergeCell ref="N76:P76"/>
+    <mergeCell ref="V56:X56"/>
+    <mergeCell ref="N57:P57"/>
+    <mergeCell ref="R59:S59"/>
+    <mergeCell ref="V62:X62"/>
+    <mergeCell ref="V63:X63"/>
+    <mergeCell ref="AH59:AI59"/>
+    <mergeCell ref="AH76:AJ76"/>
+    <mergeCell ref="AH77:AJ77"/>
+    <mergeCell ref="AD78:AF78"/>
+    <mergeCell ref="AH82:AJ82"/>
+    <mergeCell ref="AH78:AJ78"/>
+    <mergeCell ref="R82:T82"/>
+    <mergeCell ref="V83:X83"/>
+    <mergeCell ref="R83:T83"/>
+    <mergeCell ref="AD99:AE99"/>
+    <mergeCell ref="AH99:AI99"/>
+    <mergeCell ref="AL99:AM99"/>
+    <mergeCell ref="R91:T91"/>
+    <mergeCell ref="V91:X91"/>
+    <mergeCell ref="Z91:AB91"/>
+    <mergeCell ref="AD91:AF91"/>
+    <mergeCell ref="AH91:AJ91"/>
+    <mergeCell ref="AL91:AN91"/>
+    <mergeCell ref="R97:T97"/>
+    <mergeCell ref="V97:X97"/>
+    <mergeCell ref="Z97:AB97"/>
+    <mergeCell ref="AD93:AE93"/>
+    <mergeCell ref="AH93:AI93"/>
+    <mergeCell ref="AL93:AM93"/>
+    <mergeCell ref="R93:S93"/>
+    <mergeCell ref="V93:W93"/>
+    <mergeCell ref="Z93:AA93"/>
+    <mergeCell ref="AD69:AF69"/>
+    <mergeCell ref="AH69:AJ69"/>
+    <mergeCell ref="AD64:AF64"/>
+    <mergeCell ref="AH13:AI13"/>
+    <mergeCell ref="AL13:AM13"/>
+    <mergeCell ref="AH67:AJ67"/>
+    <mergeCell ref="AL67:AN67"/>
+    <mergeCell ref="AH48:AJ48"/>
+    <mergeCell ref="AH50:AJ50"/>
+    <mergeCell ref="AL29:AM29"/>
+    <mergeCell ref="AD30:AE30"/>
+    <mergeCell ref="AH30:AI30"/>
+    <mergeCell ref="AL30:AM30"/>
+    <mergeCell ref="AD66:AE66"/>
+    <mergeCell ref="AL34:AM34"/>
+    <mergeCell ref="AL40:AN40"/>
+    <mergeCell ref="AL41:AN41"/>
+    <mergeCell ref="AL47:AN47"/>
+    <mergeCell ref="AL48:AN48"/>
+    <mergeCell ref="AH42:AJ42"/>
+    <mergeCell ref="AH43:AJ43"/>
+    <mergeCell ref="AH49:AJ49"/>
+    <mergeCell ref="AD44:AF44"/>
+    <mergeCell ref="AL46:AN46"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="J46:L46"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="J39:L39"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="B27:C27"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="F40:H40"/>
@@ -8281,829 +9121,36 @@
     <mergeCell ref="R44:T44"/>
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="F46:H46"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="J46:L46"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="J39:L39"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="AD69:AF69"/>
-    <mergeCell ref="AH69:AJ69"/>
-    <mergeCell ref="AD64:AF64"/>
-    <mergeCell ref="AH13:AI13"/>
-    <mergeCell ref="AL13:AM13"/>
-    <mergeCell ref="AH67:AJ67"/>
-    <mergeCell ref="AL67:AN67"/>
-    <mergeCell ref="AH48:AJ48"/>
-    <mergeCell ref="AH50:AJ50"/>
-    <mergeCell ref="AL29:AM29"/>
-    <mergeCell ref="AD30:AE30"/>
-    <mergeCell ref="AH30:AI30"/>
-    <mergeCell ref="AL30:AM30"/>
-    <mergeCell ref="AD66:AE66"/>
-    <mergeCell ref="AL34:AM34"/>
-    <mergeCell ref="AL40:AN40"/>
-    <mergeCell ref="AL41:AN41"/>
-    <mergeCell ref="AL47:AN47"/>
-    <mergeCell ref="AL48:AN48"/>
-    <mergeCell ref="AH42:AJ42"/>
-    <mergeCell ref="AH43:AJ43"/>
-    <mergeCell ref="AH49:AJ49"/>
-    <mergeCell ref="AD44:AF44"/>
-    <mergeCell ref="AL46:AN46"/>
-    <mergeCell ref="AD99:AE99"/>
-    <mergeCell ref="AH99:AI99"/>
-    <mergeCell ref="AL99:AM99"/>
-    <mergeCell ref="R91:T91"/>
-    <mergeCell ref="V91:X91"/>
-    <mergeCell ref="Z91:AB91"/>
-    <mergeCell ref="AD91:AF91"/>
-    <mergeCell ref="AH91:AJ91"/>
-    <mergeCell ref="AL91:AN91"/>
-    <mergeCell ref="R97:T97"/>
-    <mergeCell ref="V97:X97"/>
-    <mergeCell ref="Z97:AB97"/>
-    <mergeCell ref="AD93:AE93"/>
-    <mergeCell ref="AH93:AI93"/>
-    <mergeCell ref="AL93:AM93"/>
-    <mergeCell ref="R93:S93"/>
-    <mergeCell ref="V93:W93"/>
-    <mergeCell ref="Z93:AA93"/>
-    <mergeCell ref="Z87:AA87"/>
-    <mergeCell ref="AH71:AJ71"/>
-    <mergeCell ref="AD71:AF71"/>
-    <mergeCell ref="Z71:AB71"/>
-    <mergeCell ref="N77:P77"/>
-    <mergeCell ref="N55:P55"/>
-    <mergeCell ref="Z85:AB85"/>
-    <mergeCell ref="Z83:AB83"/>
-    <mergeCell ref="N59:O59"/>
-    <mergeCell ref="N76:P76"/>
-    <mergeCell ref="V56:X56"/>
-    <mergeCell ref="N57:P57"/>
-    <mergeCell ref="R59:S59"/>
-    <mergeCell ref="V62:X62"/>
-    <mergeCell ref="V63:X63"/>
-    <mergeCell ref="AH59:AI59"/>
-    <mergeCell ref="AH76:AJ76"/>
-    <mergeCell ref="AH77:AJ77"/>
-    <mergeCell ref="AD78:AF78"/>
-    <mergeCell ref="AH82:AJ82"/>
-    <mergeCell ref="AH78:AJ78"/>
-    <mergeCell ref="R82:T82"/>
-    <mergeCell ref="V83:X83"/>
-    <mergeCell ref="R83:T83"/>
-    <mergeCell ref="AL49:AN49"/>
-    <mergeCell ref="AH66:AI66"/>
-    <mergeCell ref="Z64:AB64"/>
-    <mergeCell ref="Z68:AB68"/>
-    <mergeCell ref="AD68:AF68"/>
-    <mergeCell ref="Z62:AB62"/>
-    <mergeCell ref="Z57:AB57"/>
-    <mergeCell ref="AD54:AF54"/>
-    <mergeCell ref="AD55:AF55"/>
-    <mergeCell ref="Z50:AB50"/>
-    <mergeCell ref="Z49:AB49"/>
-    <mergeCell ref="AD67:AF67"/>
-    <mergeCell ref="AH63:AJ63"/>
-    <mergeCell ref="AH62:AJ62"/>
-    <mergeCell ref="AD62:AF62"/>
-    <mergeCell ref="AH68:AJ68"/>
-    <mergeCell ref="AL68:AN68"/>
-    <mergeCell ref="Z63:AB63"/>
-    <mergeCell ref="AL64:AN64"/>
-    <mergeCell ref="AH57:AJ57"/>
-    <mergeCell ref="AL66:AM66"/>
-    <mergeCell ref="Z52:AA52"/>
-    <mergeCell ref="Z53:AB53"/>
-    <mergeCell ref="AD61:AF61"/>
-    <mergeCell ref="AL75:AM75"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="N47:O47"/>
-    <mergeCell ref="AL32:AM32"/>
-    <mergeCell ref="AL31:AM31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="AD87:AE87"/>
-    <mergeCell ref="N34:O34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="V34:W34"/>
-    <mergeCell ref="Z34:AA34"/>
-    <mergeCell ref="AD34:AE34"/>
-    <mergeCell ref="R66:S66"/>
-    <mergeCell ref="V66:W66"/>
-    <mergeCell ref="Z66:AA66"/>
-    <mergeCell ref="R67:T67"/>
-    <mergeCell ref="V67:X67"/>
-    <mergeCell ref="Z67:AB67"/>
-    <mergeCell ref="V69:X69"/>
-    <mergeCell ref="R69:T69"/>
-    <mergeCell ref="V70:X70"/>
-    <mergeCell ref="R70:T70"/>
-    <mergeCell ref="R77:T77"/>
-    <mergeCell ref="V77:X77"/>
-    <mergeCell ref="Z47:AB47"/>
-    <mergeCell ref="AH34:AI34"/>
-    <mergeCell ref="V42:X42"/>
-    <mergeCell ref="V43:X43"/>
-    <mergeCell ref="V45:W45"/>
-    <mergeCell ref="V46:X46"/>
-    <mergeCell ref="V47:X47"/>
-    <mergeCell ref="N32:O32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="V32:W32"/>
-    <mergeCell ref="Z32:AA32"/>
-    <mergeCell ref="AD32:AE32"/>
-    <mergeCell ref="AH32:AI32"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="V33:W33"/>
-    <mergeCell ref="Z33:AA33"/>
-    <mergeCell ref="AD33:AE33"/>
-    <mergeCell ref="AH33:AI33"/>
-    <mergeCell ref="AD46:AE46"/>
-    <mergeCell ref="AH44:AJ44"/>
-    <mergeCell ref="AH46:AI46"/>
-    <mergeCell ref="AH41:AJ41"/>
-    <mergeCell ref="AD41:AF41"/>
-    <mergeCell ref="AL43:AN43"/>
-    <mergeCell ref="AL45:AM45"/>
-    <mergeCell ref="AL42:AN42"/>
-    <mergeCell ref="Z41:AB41"/>
-    <mergeCell ref="Z40:AB40"/>
-    <mergeCell ref="Z38:AA38"/>
-    <mergeCell ref="Z39:AB39"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="V31:W31"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="R39:T39"/>
-    <mergeCell ref="V38:W38"/>
-    <mergeCell ref="V39:X39"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J41:L41"/>
-    <mergeCell ref="J40:L40"/>
-    <mergeCell ref="AH61:AJ61"/>
-    <mergeCell ref="J54:L54"/>
-    <mergeCell ref="N56:P56"/>
-    <mergeCell ref="R54:T54"/>
-    <mergeCell ref="V54:X54"/>
-    <mergeCell ref="N54:P54"/>
-    <mergeCell ref="R55:T55"/>
-    <mergeCell ref="V59:W59"/>
-    <mergeCell ref="V55:X55"/>
-    <mergeCell ref="AD57:AF57"/>
-    <mergeCell ref="Z54:AB54"/>
-    <mergeCell ref="AL57:AN57"/>
-    <mergeCell ref="AL59:AM59"/>
-    <mergeCell ref="AL56:AN56"/>
-    <mergeCell ref="AL54:AN54"/>
-    <mergeCell ref="AL53:AN53"/>
-    <mergeCell ref="AL55:AN55"/>
-    <mergeCell ref="Z59:AA59"/>
-    <mergeCell ref="R56:T56"/>
-    <mergeCell ref="V53:X53"/>
-    <mergeCell ref="AL20:AM20"/>
-    <mergeCell ref="AL27:AM27"/>
-    <mergeCell ref="AL21:AM21"/>
-    <mergeCell ref="AH27:AI27"/>
-    <mergeCell ref="AD20:AE20"/>
-    <mergeCell ref="AH20:AI20"/>
-    <mergeCell ref="AD59:AE59"/>
-    <mergeCell ref="V57:X57"/>
-    <mergeCell ref="V61:X61"/>
-    <mergeCell ref="Z61:AB61"/>
-    <mergeCell ref="AD60:AF60"/>
-    <mergeCell ref="AH60:AJ60"/>
-    <mergeCell ref="V60:X60"/>
-    <mergeCell ref="Z60:AB60"/>
-    <mergeCell ref="V30:W30"/>
-    <mergeCell ref="Z31:AA31"/>
-    <mergeCell ref="V29:W29"/>
-    <mergeCell ref="Z29:AA29"/>
-    <mergeCell ref="AL60:AN60"/>
-    <mergeCell ref="AL61:AN61"/>
-    <mergeCell ref="Z56:AB56"/>
-    <mergeCell ref="AL22:AN22"/>
-    <mergeCell ref="Z23:AB23"/>
-    <mergeCell ref="AD23:AF23"/>
-    <mergeCell ref="AH23:AJ23"/>
-    <mergeCell ref="AL23:AN23"/>
-    <mergeCell ref="AD28:AE28"/>
-    <mergeCell ref="AH28:AI28"/>
-    <mergeCell ref="AL28:AM28"/>
-    <mergeCell ref="AH52:AI52"/>
-    <mergeCell ref="AH54:AJ54"/>
-    <mergeCell ref="AH55:AJ55"/>
-    <mergeCell ref="AD56:AF56"/>
-    <mergeCell ref="AH56:AJ56"/>
-    <mergeCell ref="AH53:AJ53"/>
-    <mergeCell ref="AH47:AJ47"/>
-    <mergeCell ref="AD42:AF42"/>
-    <mergeCell ref="AD48:AF48"/>
-    <mergeCell ref="AD53:AF53"/>
-    <mergeCell ref="AD50:AF50"/>
-    <mergeCell ref="AD52:AE52"/>
-    <mergeCell ref="AL33:AM33"/>
-    <mergeCell ref="AD47:AF47"/>
-    <mergeCell ref="AH40:AJ40"/>
-    <mergeCell ref="AH38:AI38"/>
-    <mergeCell ref="AH39:AJ39"/>
-    <mergeCell ref="AL38:AM38"/>
-    <mergeCell ref="AL39:AN39"/>
-    <mergeCell ref="AL76:AN76"/>
-    <mergeCell ref="AD76:AF76"/>
-    <mergeCell ref="Z81:AA81"/>
-    <mergeCell ref="AL62:AN62"/>
-    <mergeCell ref="AL63:AN63"/>
-    <mergeCell ref="AL71:AN71"/>
-    <mergeCell ref="AL70:AN70"/>
-    <mergeCell ref="AL69:AN69"/>
-    <mergeCell ref="N73:AB74"/>
-    <mergeCell ref="N75:O75"/>
-    <mergeCell ref="R75:S75"/>
-    <mergeCell ref="V75:W75"/>
-    <mergeCell ref="Z75:AA75"/>
-    <mergeCell ref="AD75:AE75"/>
-    <mergeCell ref="N64:P64"/>
-    <mergeCell ref="N70:P70"/>
-    <mergeCell ref="AH70:AJ70"/>
-    <mergeCell ref="AD70:AF70"/>
-    <mergeCell ref="Z69:AB69"/>
-    <mergeCell ref="Z70:AB70"/>
-    <mergeCell ref="V71:X71"/>
-    <mergeCell ref="AD63:AF63"/>
-    <mergeCell ref="AH64:AJ64"/>
-    <mergeCell ref="AH75:AI75"/>
-    <mergeCell ref="Z76:AB76"/>
-    <mergeCell ref="Z77:AB77"/>
-    <mergeCell ref="V76:X76"/>
-    <mergeCell ref="N78:P78"/>
-    <mergeCell ref="Z78:AB78"/>
-    <mergeCell ref="N79:P79"/>
-    <mergeCell ref="R79:T79"/>
-    <mergeCell ref="V79:X79"/>
-    <mergeCell ref="Z79:AB79"/>
-    <mergeCell ref="V78:X78"/>
-    <mergeCell ref="R78:T78"/>
-    <mergeCell ref="AL88:AN88"/>
-    <mergeCell ref="AL89:AN89"/>
-    <mergeCell ref="AL83:AN83"/>
-    <mergeCell ref="AL84:AN84"/>
-    <mergeCell ref="AD88:AF88"/>
-    <mergeCell ref="AD89:AF89"/>
-    <mergeCell ref="AH87:AI87"/>
-    <mergeCell ref="AL87:AM87"/>
-    <mergeCell ref="AH88:AJ88"/>
-    <mergeCell ref="AH89:AJ89"/>
-    <mergeCell ref="AD85:AF85"/>
-    <mergeCell ref="AH85:AJ85"/>
-    <mergeCell ref="AL85:AN85"/>
-    <mergeCell ref="AD82:AF82"/>
-    <mergeCell ref="AH83:AJ83"/>
-    <mergeCell ref="AD84:AF84"/>
-    <mergeCell ref="AH84:AJ84"/>
-    <mergeCell ref="AD83:AF83"/>
-    <mergeCell ref="Z84:AB84"/>
-    <mergeCell ref="Z82:AB82"/>
-    <mergeCell ref="AL77:AN77"/>
-    <mergeCell ref="AL78:AN78"/>
-    <mergeCell ref="AD77:AF77"/>
-    <mergeCell ref="AD79:AF79"/>
-    <mergeCell ref="AH79:AJ79"/>
-    <mergeCell ref="AL79:AN79"/>
-    <mergeCell ref="AD81:AE81"/>
-    <mergeCell ref="AH81:AI81"/>
-    <mergeCell ref="AL81:AM81"/>
-    <mergeCell ref="AL82:AN82"/>
-    <mergeCell ref="AL102:AN102"/>
-    <mergeCell ref="AL101:AN101"/>
-    <mergeCell ref="AL96:AN96"/>
-    <mergeCell ref="AD102:AF102"/>
-    <mergeCell ref="AH102:AJ102"/>
-    <mergeCell ref="AL90:AN90"/>
-    <mergeCell ref="AL95:AN95"/>
-    <mergeCell ref="AD101:AF101"/>
-    <mergeCell ref="AH101:AJ101"/>
-    <mergeCell ref="AH100:AJ100"/>
-    <mergeCell ref="AL94:AN94"/>
-    <mergeCell ref="AD100:AF100"/>
-    <mergeCell ref="AD96:AF96"/>
-    <mergeCell ref="AD94:AF94"/>
-    <mergeCell ref="AD95:AF95"/>
-    <mergeCell ref="AH96:AJ96"/>
-    <mergeCell ref="AD90:AF90"/>
-    <mergeCell ref="AH95:AJ95"/>
-    <mergeCell ref="AH94:AJ94"/>
-    <mergeCell ref="AL100:AN100"/>
-    <mergeCell ref="AD97:AF97"/>
-    <mergeCell ref="AH97:AJ97"/>
-    <mergeCell ref="AL97:AN97"/>
-    <mergeCell ref="AH90:AJ90"/>
-    <mergeCell ref="Z9:AB9"/>
-    <mergeCell ref="R10:T10"/>
-    <mergeCell ref="V10:X10"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="AD21:AE21"/>
-    <mergeCell ref="AD49:AF49"/>
-    <mergeCell ref="AD43:AF43"/>
-    <mergeCell ref="R48:T48"/>
-    <mergeCell ref="Z42:AB42"/>
-    <mergeCell ref="Z43:AB43"/>
-    <mergeCell ref="N36:AB37"/>
-    <mergeCell ref="Z48:AB48"/>
-    <mergeCell ref="Z45:AA45"/>
-    <mergeCell ref="Z46:AB46"/>
-    <mergeCell ref="AD38:AE38"/>
-    <mergeCell ref="AD39:AF39"/>
-    <mergeCell ref="AD40:AF40"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="V49:X49"/>
-    <mergeCell ref="V48:X48"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="Z20:AA20"/>
-    <mergeCell ref="J15:L15"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="V28:W28"/>
-    <mergeCell ref="Z28:AA28"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="Z27:AA27"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="V13:W13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="N18:AB19"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="R14:T14"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="V15:X15"/>
-    <mergeCell ref="V16:X16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="R9:T9"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="V8:X8"/>
-    <mergeCell ref="V9:X9"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="R1:T1"/>
-    <mergeCell ref="V1:X1"/>
-    <mergeCell ref="V14:X14"/>
-    <mergeCell ref="R15:T15"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="B4:L5"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="V2:X2"/>
-    <mergeCell ref="N4:AB5"/>
-    <mergeCell ref="AL1:AN1"/>
-    <mergeCell ref="Z2:AB2"/>
-    <mergeCell ref="AD2:AF2"/>
-    <mergeCell ref="AH2:AJ2"/>
-    <mergeCell ref="AL2:AN2"/>
-    <mergeCell ref="AH8:AJ8"/>
-    <mergeCell ref="AL6:AM6"/>
-    <mergeCell ref="AD1:AF1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="AL7:AM7"/>
-    <mergeCell ref="AD8:AF8"/>
-    <mergeCell ref="Z8:AB8"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AH7:AI7"/>
-    <mergeCell ref="AD7:AE7"/>
-    <mergeCell ref="Z7:AA7"/>
-    <mergeCell ref="AL8:AN8"/>
-    <mergeCell ref="AD4:AN5"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="AD6:AE6"/>
-    <mergeCell ref="Z88:AB88"/>
-    <mergeCell ref="J94:L94"/>
-    <mergeCell ref="J95:L95"/>
-    <mergeCell ref="V94:X94"/>
-    <mergeCell ref="V96:X96"/>
-    <mergeCell ref="V95:X95"/>
-    <mergeCell ref="Z96:AB96"/>
-    <mergeCell ref="R96:T96"/>
-    <mergeCell ref="B101:D101"/>
-    <mergeCell ref="N101:P101"/>
-    <mergeCell ref="N95:P95"/>
-    <mergeCell ref="V101:X101"/>
-    <mergeCell ref="Z101:AB101"/>
-    <mergeCell ref="Z94:AB94"/>
-    <mergeCell ref="Z95:AB95"/>
-    <mergeCell ref="V90:X90"/>
-    <mergeCell ref="V88:X88"/>
-    <mergeCell ref="R90:T90"/>
-    <mergeCell ref="Z89:AB89"/>
-    <mergeCell ref="Z90:AB90"/>
-    <mergeCell ref="N88:P88"/>
-    <mergeCell ref="N93:O93"/>
-    <mergeCell ref="J100:L100"/>
-    <mergeCell ref="B97:D97"/>
-    <mergeCell ref="AH21:AI21"/>
-    <mergeCell ref="AH31:AI31"/>
-    <mergeCell ref="AD31:AE31"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="Z21:AA21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="R22:T22"/>
-    <mergeCell ref="V22:X22"/>
-    <mergeCell ref="Z22:AB22"/>
-    <mergeCell ref="AD22:AF22"/>
-    <mergeCell ref="AH22:AJ22"/>
-    <mergeCell ref="AD29:AE29"/>
-    <mergeCell ref="AH29:AI29"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:T23"/>
-    <mergeCell ref="V23:X23"/>
-    <mergeCell ref="V27:W27"/>
-    <mergeCell ref="AD27:AE27"/>
-    <mergeCell ref="N30:O30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="N29:O29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="Z30:AA30"/>
-    <mergeCell ref="N25:AB26"/>
-    <mergeCell ref="AL9:AN9"/>
-    <mergeCell ref="AD9:AF9"/>
-    <mergeCell ref="AH16:AJ16"/>
-    <mergeCell ref="AL10:AN10"/>
-    <mergeCell ref="AL14:AN14"/>
-    <mergeCell ref="AL16:AN16"/>
-    <mergeCell ref="Z15:AB15"/>
-    <mergeCell ref="AD15:AF15"/>
-    <mergeCell ref="Z13:AA13"/>
-    <mergeCell ref="AL15:AN15"/>
-    <mergeCell ref="AL12:AM12"/>
-    <mergeCell ref="AD16:AF16"/>
-    <mergeCell ref="Z10:AB10"/>
-    <mergeCell ref="AH14:AJ14"/>
-    <mergeCell ref="Z14:AB14"/>
-    <mergeCell ref="AD14:AF14"/>
-    <mergeCell ref="AD13:AE13"/>
-    <mergeCell ref="AH10:AJ10"/>
-    <mergeCell ref="AH15:AJ15"/>
-    <mergeCell ref="AD10:AF10"/>
-    <mergeCell ref="AD12:AE12"/>
-    <mergeCell ref="AH12:AI12"/>
-    <mergeCell ref="AH9:AJ9"/>
-    <mergeCell ref="Z16:AB16"/>
-    <mergeCell ref="F101:H101"/>
-    <mergeCell ref="R94:T94"/>
-    <mergeCell ref="V64:X64"/>
-    <mergeCell ref="R64:T64"/>
-    <mergeCell ref="R61:T61"/>
-    <mergeCell ref="R60:T60"/>
-    <mergeCell ref="R87:S87"/>
-    <mergeCell ref="V87:W87"/>
-    <mergeCell ref="N91:P91"/>
-    <mergeCell ref="J96:L96"/>
-    <mergeCell ref="N83:P83"/>
-    <mergeCell ref="N84:P84"/>
-    <mergeCell ref="N90:P90"/>
-    <mergeCell ref="J89:L89"/>
-    <mergeCell ref="J83:L83"/>
-    <mergeCell ref="V89:X89"/>
-    <mergeCell ref="R89:T89"/>
-    <mergeCell ref="R84:T84"/>
-    <mergeCell ref="N85:P85"/>
-    <mergeCell ref="R85:T85"/>
-    <mergeCell ref="V85:X85"/>
-    <mergeCell ref="R88:T88"/>
-    <mergeCell ref="V84:X84"/>
-    <mergeCell ref="J84:L84"/>
-    <mergeCell ref="V102:X102"/>
-    <mergeCell ref="R68:T68"/>
-    <mergeCell ref="V68:X68"/>
-    <mergeCell ref="N66:O66"/>
-    <mergeCell ref="N67:P67"/>
-    <mergeCell ref="N60:P60"/>
-    <mergeCell ref="J69:L69"/>
-    <mergeCell ref="N62:P62"/>
-    <mergeCell ref="R62:T62"/>
-    <mergeCell ref="N89:P89"/>
-    <mergeCell ref="N87:O87"/>
-    <mergeCell ref="J88:L88"/>
-    <mergeCell ref="J85:L85"/>
-    <mergeCell ref="J101:L101"/>
-    <mergeCell ref="R102:T102"/>
-    <mergeCell ref="R100:T100"/>
-    <mergeCell ref="V100:X100"/>
-    <mergeCell ref="R101:T101"/>
-    <mergeCell ref="N100:P100"/>
-    <mergeCell ref="Z12:AA12"/>
-    <mergeCell ref="B133:D133"/>
-    <mergeCell ref="F133:H133"/>
-    <mergeCell ref="J133:L133"/>
-    <mergeCell ref="B127:D127"/>
-    <mergeCell ref="F127:H127"/>
-    <mergeCell ref="J127:L127"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="F129:G129"/>
-    <mergeCell ref="J129:K129"/>
-    <mergeCell ref="B130:D130"/>
-    <mergeCell ref="F130:H130"/>
-    <mergeCell ref="J130:L130"/>
-    <mergeCell ref="B132:D132"/>
-    <mergeCell ref="F132:H132"/>
-    <mergeCell ref="J132:L132"/>
-    <mergeCell ref="B131:D131"/>
-    <mergeCell ref="F131:H131"/>
-    <mergeCell ref="J131:L131"/>
-    <mergeCell ref="B126:D126"/>
-    <mergeCell ref="F126:H126"/>
-    <mergeCell ref="J126:L126"/>
-    <mergeCell ref="F117:G117"/>
-    <mergeCell ref="J117:K117"/>
-    <mergeCell ref="B125:D125"/>
-    <mergeCell ref="F125:H125"/>
-    <mergeCell ref="J121:L121"/>
-    <mergeCell ref="J125:L125"/>
-    <mergeCell ref="B118:D118"/>
-    <mergeCell ref="F118:H118"/>
-    <mergeCell ref="B115:D115"/>
-    <mergeCell ref="F115:H115"/>
-    <mergeCell ref="J115:L115"/>
-    <mergeCell ref="F120:H120"/>
-    <mergeCell ref="J120:L120"/>
-    <mergeCell ref="J118:L118"/>
-    <mergeCell ref="B124:D124"/>
-    <mergeCell ref="F124:H124"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="F111:G111"/>
-    <mergeCell ref="J124:L124"/>
-    <mergeCell ref="F119:H119"/>
-    <mergeCell ref="J119:L119"/>
-    <mergeCell ref="J109:L109"/>
-    <mergeCell ref="B120:D120"/>
-    <mergeCell ref="B121:D121"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="F123:G123"/>
-    <mergeCell ref="B119:D119"/>
-    <mergeCell ref="B113:D113"/>
-    <mergeCell ref="F113:H113"/>
-    <mergeCell ref="J113:L113"/>
-    <mergeCell ref="B114:D114"/>
-    <mergeCell ref="F114:H114"/>
-    <mergeCell ref="J114:L114"/>
-    <mergeCell ref="F121:H121"/>
-    <mergeCell ref="J123:K123"/>
-    <mergeCell ref="F112:H112"/>
-    <mergeCell ref="B112:D112"/>
-    <mergeCell ref="F107:H107"/>
-    <mergeCell ref="J102:L102"/>
-    <mergeCell ref="J112:L112"/>
-    <mergeCell ref="J111:K111"/>
-    <mergeCell ref="B106:D106"/>
-    <mergeCell ref="B107:D107"/>
-    <mergeCell ref="F106:H106"/>
-    <mergeCell ref="F105:G105"/>
-    <mergeCell ref="N102:P102"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="F102:H102"/>
-    <mergeCell ref="J107:L107"/>
-    <mergeCell ref="J108:L108"/>
-    <mergeCell ref="B109:D109"/>
-    <mergeCell ref="F109:H109"/>
-    <mergeCell ref="B108:D108"/>
-    <mergeCell ref="J105:K105"/>
-    <mergeCell ref="F108:H108"/>
-    <mergeCell ref="J106:L106"/>
-    <mergeCell ref="Z100:AB100"/>
-    <mergeCell ref="N94:P94"/>
-    <mergeCell ref="R95:T95"/>
-    <mergeCell ref="N96:P96"/>
-    <mergeCell ref="R99:S99"/>
-    <mergeCell ref="V99:W99"/>
-    <mergeCell ref="Z99:AA99"/>
-    <mergeCell ref="N97:P97"/>
-    <mergeCell ref="N99:O99"/>
-    <mergeCell ref="Z102:AB102"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="F70:H70"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="F76:H76"/>
-    <mergeCell ref="F90:H90"/>
-    <mergeCell ref="F89:H89"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B79:D79"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="F82:H82"/>
-    <mergeCell ref="F83:H83"/>
-    <mergeCell ref="F84:H84"/>
-    <mergeCell ref="F77:H77"/>
-    <mergeCell ref="B85:D85"/>
-    <mergeCell ref="F79:H79"/>
-    <mergeCell ref="F71:H71"/>
-    <mergeCell ref="F85:H85"/>
-    <mergeCell ref="B100:D100"/>
-    <mergeCell ref="F100:H100"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="F88:H88"/>
-    <mergeCell ref="B89:D89"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="J75:K75"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="J82:L82"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B95:D95"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="J70:L70"/>
-    <mergeCell ref="B71:D71"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="AL50:AN50"/>
-    <mergeCell ref="AL52:AM52"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="F62:H62"/>
-    <mergeCell ref="F61:H61"/>
-    <mergeCell ref="J64:L64"/>
-    <mergeCell ref="F69:H69"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="J63:L63"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="J66:K66"/>
-    <mergeCell ref="B67:D67"/>
-    <mergeCell ref="F67:H67"/>
-    <mergeCell ref="J67:L67"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="F68:H68"/>
-    <mergeCell ref="J68:L68"/>
-    <mergeCell ref="F63:H63"/>
-    <mergeCell ref="Z55:AB55"/>
-    <mergeCell ref="N63:P63"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="F54:H54"/>
-    <mergeCell ref="N81:O81"/>
-    <mergeCell ref="R81:S81"/>
-    <mergeCell ref="V81:W81"/>
-    <mergeCell ref="V82:X82"/>
-    <mergeCell ref="N82:P82"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="N61:P61"/>
-    <mergeCell ref="R57:T57"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="F97:H97"/>
+    <mergeCell ref="J97:L97"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="F99:G99"/>
+    <mergeCell ref="J99:K99"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="J87:K87"/>
+    <mergeCell ref="B91:D91"/>
+    <mergeCell ref="F91:H91"/>
+    <mergeCell ref="J91:L91"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="F93:G93"/>
+    <mergeCell ref="J93:K93"/>
+    <mergeCell ref="J90:L90"/>
+    <mergeCell ref="B96:D96"/>
+    <mergeCell ref="F96:H96"/>
+    <mergeCell ref="F95:H95"/>
+    <mergeCell ref="F94:H94"/>
+    <mergeCell ref="B52:C52"/>
     <mergeCell ref="F64:H64"/>
     <mergeCell ref="F78:H78"/>
     <mergeCell ref="F60:H60"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="R71:T71"/>
-    <mergeCell ref="N71:P71"/>
-    <mergeCell ref="R76:T76"/>
-    <mergeCell ref="N69:P69"/>
-    <mergeCell ref="R63:T63"/>
-    <mergeCell ref="N68:P68"/>
-    <mergeCell ref="F75:G75"/>
-    <mergeCell ref="J81:K81"/>
-    <mergeCell ref="J77:L77"/>
-    <mergeCell ref="J76:L76"/>
-    <mergeCell ref="J55:L55"/>
-    <mergeCell ref="J50:L50"/>
-    <mergeCell ref="V50:X50"/>
-    <mergeCell ref="R49:T49"/>
-    <mergeCell ref="J49:L49"/>
-    <mergeCell ref="J47:L47"/>
-    <mergeCell ref="J79:L79"/>
-    <mergeCell ref="J71:L71"/>
-    <mergeCell ref="R50:T50"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="J60:L60"/>
-    <mergeCell ref="J78:L78"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="J53:L53"/>
-    <mergeCell ref="F53:H53"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="N38:O38"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R41:T41"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R42:T42"/>
-    <mergeCell ref="V52:W52"/>
-    <mergeCell ref="V41:X41"/>
-    <mergeCell ref="V40:X40"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="F48:H48"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="D29:D34 AJ29:AJ34 T29:T34 P29:P34 X29:X34 AF29:AF34 AN29:AN34 H29:H34 L29:L34 AB29:AB34">
       <formula1>$AP$68:$AP$71</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="V62:X64 AH41:AJ44 AH14:AJ16 B89:D90 AH69:AJ71 V29:W34 B101:D102 J132:L133 AD41:AF44 AH90:AJ91 R96:T97 V96:X97 R69:T71 R78:T79 Z90:AB91 Z8:AB10 J101:L102 AD49:AF50 V8:X10 N41:P45 AD69:AF71 J114:L115 AL78:AN79 AL69:AN71 AH8:AJ10 R8:T10 F89:H90 B108:D109 B95:D96 Z14:AB16 Z55:AB57 R14:T16 F101:H102 AL14:AN16 J95:L96 F95:H96 R29:S34 N96:P97 F55:H57 J120:L121 F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 B126:D127 AD14:AF16 B114:D115 J126:L127 V48:X50 Z101:AB102 AD22:AF23 R84:T85 AH84:AJ85 R22:T23 V14:X16 V22:X23 F108:H109 Z22:AB23 AL101:AN102 AL22:AN23 V69:X71 Z78:AB79 AD55:AF57 N22:P23 Z29:AA34 B41:D43 J89:L90 V55:X57 AH96:AJ97 AD78:AF79 Z96:AB97 N29:O34 AD101:AF102 N14:P16 AD62:AF64 R90:T91 AL90:AN91 Z41:AB43 AH62:AJ64 N101:P102 Z84:AB85 V41:X43 AH78:AJ79 AL84:AN85 AH55:AJ57 AH49:AJ50 B29:C34 J29:K34 AL96:AN97 AH101:AJ102 AD90:AF91 N90:P91 AD84:AF85 N50:P51 AD96:AF97 AH22:AJ23 N62:P64 N8:P10 N78:P79 Z69:AB71 AD8:AF10 V101:X102 AL41:AN43 N84:P85 R41:T45 V84:X85 Z62:AB64 R62:T64 V90:X91 AL55:AN57 N56:P57 AL62:AN64 F69:H71 J55:L57 N69:P71 AL29:AM34 AL48:AN50 V78:X79 AH29:AI34 J41:L43 F14:H16 F22:H23 B78:D79 B69:D71 J78:L79 J69:L71 F41:H43 R56:T57 J14:L16 B14:D16 B22:D23 F84:H85 J22:L23 B55:D57 B84:D85 B62:D64 F8:H10 F48:H50 J8:L10 F62:H64 F78:H79 B8:D10 F29:G34 AL8:AN10 J62:L64 J84:L85 B48:D50 AD29:AE34 Z48:AB50 R50:T51 J48:L50 R101:T102">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="V62:X64 AH41:AJ44 AH14:AJ16 B89:D90 AH69:AJ71 V29:W34 B101:D102 J132:L133 AD41:AF44 AH90:AJ91 R96:T97 V96:X97 R69:T71 R78:T79 Z90:AB91 Z8:AB10 J101:L102 AD49:AF50 V8:X10 N41:P45 AD69:AF71 J114:L115 AL78:AN79 AL69:AN71 AH8:AJ10 R8:T10 F89:H90 B108:D109 B95:D96 Z14:AB16 Z55:AB57 R14:T16 F101:H102 AL14:AN16 J95:L96 F95:H96 R29:S34 N96:P97 F55:H57 J120:L121 F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 B126:D127 AD14:AF16 B114:D115 J126:L127 V48:X50 R101:T102 AD22:AF23 R84:T85 Z101:AB102 R22:T23 V14:X16 V22:X23 F108:H109 Z22:AB23 AL101:AN102 AL22:AN23 V69:X71 Z78:AB79 AD55:AF57 N22:P23 Z29:AA34 B41:D43 J89:L90 V55:X57 AH96:AJ97 AD78:AF79 Z96:AB97 N29:O34 AD101:AF102 N14:P16 AD62:AF64 R90:T91 AL90:AN91 Z41:AB43 AH62:AJ64 N101:P102 AH84:AJ85 V41:X43 AH78:AJ79 AL84:AN85 AH55:AJ57 AH49:AJ50 B29:C34 J29:K34 AL96:AN97 AH101:AJ102 AD90:AF91 N90:P91 AD84:AF85 N50:P51 AD96:AF97 AH22:AJ23 N62:P64 N8:P10 N78:P79 Z69:AB71 AD8:AF10 V101:X102 AL41:AN43 N84:P85 R41:T45 V84:X85 Z62:AB64 R62:T64 V90:X91 AL55:AN57 N56:P57 AL62:AN64 F69:H71 J55:L57 N69:P71 AL29:AM34 AL48:AN50 V78:X79 AH29:AI34 J41:L43 F14:H16 F22:H23 B78:D79 B69:D71 J78:L79 J69:L71 F41:H43 R56:T57 J14:L16 B14:D16 B22:D23 F84:H85 J22:L23 B55:D57 B84:D85 B62:D64 F8:H10 F48:H50 J8:L10 F62:H64 F78:H79 B8:D10 F29:G34 AL8:AN10 J62:L64 J84:L85 B48:D50 AD29:AE34 Z48:AB50 R50:T51 J48:L50 Z84:AB85">
       <formula1>$AP$6:$AP$30</formula1>
     </dataValidation>
   </dataValidations>

--- a/Gorev-Listesi.xlsx
+++ b/Gorev-Listesi.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23670" windowHeight="10995" tabRatio="515"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23676" windowHeight="10992" tabRatio="515"/>
   </bookViews>
   <sheets>
     <sheet name="SES SERVİSİ ÇALIŞMA PLANI" sheetId="2" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="119">
   <si>
     <t>CUMA</t>
   </si>
@@ -391,6 +391,9 @@
   </si>
   <si>
     <t>BİR ROMAN KAHRAMANI GİBİ</t>
+  </si>
+  <si>
+    <t>BİR MEKANDAN FAZLASI</t>
   </si>
 </sst>
 </file>
@@ -1759,6 +1762,33 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="16" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="11" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="12" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="13" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="11" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="12" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="13" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1774,6 +1804,15 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="17" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="18" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="7" borderId="37" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1783,6 +1822,15 @@
     <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="9" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="8" borderId="8" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1801,24 +1849,6 @@
     <xf numFmtId="49" fontId="7" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="17" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="18" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="11" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="12" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="13" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1831,15 +1861,6 @@
     <xf numFmtId="49" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="9" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1875,24 +1896,6 @@
     </xf>
     <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="11" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="12" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="13" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="58">
@@ -2266,7 +2269,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="1" width="350" row="1" locked="1">
+  <wetp:taskpane dockstate="right" visibility="1" width="184" row="1" locked="1">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -2292,197 +2295,197 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AR133"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="26" customWidth="1"/>
-    <col min="2" max="2" width="2.7109375" style="26" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" style="26" customWidth="1"/>
-    <col min="4" max="4" width="6.7109375" style="26" customWidth="1"/>
-    <col min="5" max="5" width="1.7109375" style="26" customWidth="1"/>
-    <col min="6" max="6" width="2.7109375" style="26" customWidth="1"/>
-    <col min="7" max="7" width="20.7109375" style="26" customWidth="1"/>
-    <col min="8" max="8" width="6.7109375" style="26" customWidth="1"/>
-    <col min="9" max="9" width="1.7109375" style="26" customWidth="1"/>
-    <col min="10" max="10" width="2.7109375" style="26" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" style="26" customWidth="1"/>
-    <col min="12" max="12" width="6.7109375" style="26" customWidth="1"/>
-    <col min="13" max="13" width="1.7109375" style="26" customWidth="1"/>
-    <col min="14" max="14" width="2.7109375" customWidth="1"/>
-    <col min="15" max="15" width="20.7109375" customWidth="1"/>
-    <col min="16" max="16" width="6.7109375" customWidth="1"/>
-    <col min="17" max="17" width="1.7109375" customWidth="1"/>
-    <col min="18" max="18" width="2.7109375" customWidth="1"/>
-    <col min="19" max="19" width="20.7109375" customWidth="1"/>
-    <col min="20" max="20" width="6.7109375" customWidth="1"/>
-    <col min="21" max="21" width="1.7109375" customWidth="1"/>
-    <col min="22" max="22" width="2.7109375" customWidth="1"/>
-    <col min="23" max="23" width="20.7109375" customWidth="1"/>
-    <col min="24" max="24" width="6.7109375" customWidth="1"/>
-    <col min="25" max="25" width="1.7109375" customWidth="1"/>
-    <col min="26" max="26" width="2.7109375" customWidth="1"/>
-    <col min="27" max="27" width="20.7109375" customWidth="1"/>
-    <col min="28" max="28" width="6.7109375" customWidth="1"/>
-    <col min="29" max="29" width="1.7109375" customWidth="1"/>
-    <col min="30" max="30" width="2.7109375" customWidth="1"/>
-    <col min="31" max="31" width="20.7109375" customWidth="1"/>
-    <col min="32" max="32" width="6.7109375" customWidth="1"/>
-    <col min="33" max="33" width="1.7109375" customWidth="1"/>
-    <col min="34" max="34" width="2.7109375" customWidth="1"/>
-    <col min="35" max="35" width="20.7109375" customWidth="1"/>
-    <col min="36" max="36" width="6.7109375" customWidth="1"/>
-    <col min="37" max="37" width="1.7109375" customWidth="1"/>
-    <col min="38" max="38" width="2.7109375" customWidth="1"/>
-    <col min="39" max="39" width="20.7109375" customWidth="1"/>
-    <col min="40" max="40" width="6.7109375" customWidth="1"/>
-    <col min="41" max="41" width="2.7109375" customWidth="1"/>
-    <col min="42" max="42" width="16.7109375" customWidth="1"/>
-    <col min="43" max="43" width="3.7109375" customWidth="1"/>
-    <col min="44" max="44" width="8.28515625" customWidth="1"/>
+    <col min="1" max="1" width="1.6640625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="2.6640625" style="26" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="26" customWidth="1"/>
+    <col min="4" max="4" width="6.6640625" style="26" customWidth="1"/>
+    <col min="5" max="5" width="1.6640625" style="26" customWidth="1"/>
+    <col min="6" max="6" width="2.6640625" style="26" customWidth="1"/>
+    <col min="7" max="7" width="20.6640625" style="26" customWidth="1"/>
+    <col min="8" max="8" width="6.6640625" style="26" customWidth="1"/>
+    <col min="9" max="9" width="1.6640625" style="26" customWidth="1"/>
+    <col min="10" max="10" width="2.6640625" style="26" customWidth="1"/>
+    <col min="11" max="11" width="20.6640625" style="26" customWidth="1"/>
+    <col min="12" max="12" width="6.6640625" style="26" customWidth="1"/>
+    <col min="13" max="13" width="1.6640625" style="26" customWidth="1"/>
+    <col min="14" max="14" width="2.6640625" customWidth="1"/>
+    <col min="15" max="15" width="20.6640625" customWidth="1"/>
+    <col min="16" max="16" width="6.6640625" customWidth="1"/>
+    <col min="17" max="17" width="1.6640625" customWidth="1"/>
+    <col min="18" max="18" width="2.6640625" customWidth="1"/>
+    <col min="19" max="19" width="20.6640625" customWidth="1"/>
+    <col min="20" max="20" width="6.6640625" customWidth="1"/>
+    <col min="21" max="21" width="1.6640625" customWidth="1"/>
+    <col min="22" max="22" width="2.6640625" customWidth="1"/>
+    <col min="23" max="23" width="20.6640625" customWidth="1"/>
+    <col min="24" max="24" width="6.6640625" customWidth="1"/>
+    <col min="25" max="25" width="1.6640625" customWidth="1"/>
+    <col min="26" max="26" width="2.6640625" customWidth="1"/>
+    <col min="27" max="27" width="20.6640625" customWidth="1"/>
+    <col min="28" max="28" width="6.6640625" customWidth="1"/>
+    <col min="29" max="29" width="1.6640625" customWidth="1"/>
+    <col min="30" max="30" width="2.6640625" customWidth="1"/>
+    <col min="31" max="31" width="20.6640625" customWidth="1"/>
+    <col min="32" max="32" width="6.6640625" customWidth="1"/>
+    <col min="33" max="33" width="1.6640625" customWidth="1"/>
+    <col min="34" max="34" width="2.6640625" customWidth="1"/>
+    <col min="35" max="35" width="20.6640625" customWidth="1"/>
+    <col min="36" max="36" width="6.6640625" customWidth="1"/>
+    <col min="37" max="37" width="1.6640625" customWidth="1"/>
+    <col min="38" max="38" width="2.6640625" customWidth="1"/>
+    <col min="39" max="39" width="20.6640625" customWidth="1"/>
+    <col min="40" max="40" width="6.6640625" customWidth="1"/>
+    <col min="41" max="41" width="2.6640625" customWidth="1"/>
+    <col min="42" max="42" width="16.6640625" customWidth="1"/>
+    <col min="43" max="43" width="3.6640625" customWidth="1"/>
+    <col min="44" max="44" width="8.33203125" customWidth="1"/>
     <col min="45" max="48" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12"/>
-      <c r="B1" s="145" t="s">
+      <c r="B1" s="151" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
       <c r="E1" s="10"/>
-      <c r="F1" s="146" t="s">
+      <c r="F1" s="152" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="146"/>
-      <c r="H1" s="146"/>
+      <c r="G1" s="152"/>
+      <c r="H1" s="152"/>
       <c r="I1" s="10"/>
-      <c r="J1" s="146" t="s">
+      <c r="J1" s="152" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="146"/>
-      <c r="L1" s="147"/>
+      <c r="K1" s="152"/>
+      <c r="L1" s="153"/>
       <c r="M1" s="12"/>
-      <c r="N1" s="150" t="s">
+      <c r="N1" s="156" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="144"/>
-      <c r="P1" s="144"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="150"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="144" t="s">
+      <c r="R1" s="150" t="s">
         <v>4</v>
       </c>
-      <c r="S1" s="144"/>
-      <c r="T1" s="144"/>
+      <c r="S1" s="150"/>
+      <c r="T1" s="150"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="144" t="s">
+      <c r="V1" s="150" t="s">
         <v>5</v>
       </c>
-      <c r="W1" s="144"/>
-      <c r="X1" s="144"/>
+      <c r="W1" s="150"/>
+      <c r="X1" s="150"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="144" t="s">
+      <c r="Z1" s="150" t="s">
         <v>6</v>
       </c>
-      <c r="AA1" s="144"/>
-      <c r="AB1" s="144"/>
+      <c r="AA1" s="150"/>
+      <c r="AB1" s="150"/>
       <c r="AC1" s="1"/>
-      <c r="AD1" s="144" t="s">
+      <c r="AD1" s="150" t="s">
         <v>0</v>
       </c>
-      <c r="AE1" s="144"/>
-      <c r="AF1" s="144"/>
+      <c r="AE1" s="150"/>
+      <c r="AF1" s="150"/>
       <c r="AG1" s="1"/>
-      <c r="AH1" s="144" t="s">
+      <c r="AH1" s="150" t="s">
         <v>1</v>
       </c>
-      <c r="AI1" s="144"/>
-      <c r="AJ1" s="144"/>
+      <c r="AI1" s="150"/>
+      <c r="AJ1" s="150"/>
       <c r="AK1" s="1"/>
-      <c r="AL1" s="144" t="s">
+      <c r="AL1" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="AM1" s="144"/>
-      <c r="AN1" s="154"/>
+      <c r="AM1" s="150"/>
+      <c r="AN1" s="160"/>
       <c r="AO1" s="12"/>
       <c r="AP1" s="12"/>
       <c r="AQ1" s="12"/>
       <c r="AR1" s="13"/>
     </row>
-    <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12"/>
-      <c r="B2" s="148">
+      <c r="B2" s="154">
         <f>N2-3</f>
         <v>46283</v>
       </c>
-      <c r="C2" s="149"/>
-      <c r="D2" s="149"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
       <c r="E2" s="11"/>
-      <c r="F2" s="149">
+      <c r="F2" s="155">
         <f>N2-2</f>
         <v>46284</v>
       </c>
-      <c r="G2" s="149"/>
-      <c r="H2" s="149"/>
+      <c r="G2" s="155"/>
+      <c r="H2" s="155"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="149">
+      <c r="J2" s="155">
         <f>N2-1</f>
         <v>46285</v>
       </c>
-      <c r="K2" s="149"/>
-      <c r="L2" s="152"/>
+      <c r="K2" s="155"/>
+      <c r="L2" s="158"/>
       <c r="M2" s="12"/>
-      <c r="N2" s="151">
+      <c r="N2" s="157">
         <v>46286</v>
       </c>
-      <c r="O2" s="137"/>
-      <c r="P2" s="137"/>
+      <c r="O2" s="146"/>
+      <c r="P2" s="146"/>
       <c r="Q2" s="53"/>
-      <c r="R2" s="137">
+      <c r="R2" s="146">
         <f>N2+1</f>
         <v>46287</v>
       </c>
-      <c r="S2" s="137"/>
-      <c r="T2" s="137"/>
+      <c r="S2" s="146"/>
+      <c r="T2" s="146"/>
       <c r="U2" s="53"/>
-      <c r="V2" s="137">
+      <c r="V2" s="146">
         <f>N2+2</f>
         <v>46288</v>
       </c>
-      <c r="W2" s="137"/>
-      <c r="X2" s="137"/>
+      <c r="W2" s="146"/>
+      <c r="X2" s="146"/>
       <c r="Y2" s="53"/>
-      <c r="Z2" s="137">
+      <c r="Z2" s="146">
         <f>N2+3</f>
         <v>46289</v>
       </c>
-      <c r="AA2" s="137"/>
-      <c r="AB2" s="137"/>
+      <c r="AA2" s="146"/>
+      <c r="AB2" s="146"/>
       <c r="AC2" s="53"/>
-      <c r="AD2" s="137">
+      <c r="AD2" s="146">
         <f>N2+4</f>
         <v>46290</v>
       </c>
-      <c r="AE2" s="137"/>
-      <c r="AF2" s="137"/>
+      <c r="AE2" s="146"/>
+      <c r="AF2" s="146"/>
       <c r="AG2" s="53"/>
-      <c r="AH2" s="137">
+      <c r="AH2" s="146">
         <f>N2+5</f>
         <v>46291</v>
       </c>
-      <c r="AI2" s="137"/>
-      <c r="AJ2" s="137"/>
+      <c r="AI2" s="146"/>
+      <c r="AJ2" s="146"/>
       <c r="AK2" s="53"/>
-      <c r="AL2" s="137">
+      <c r="AL2" s="146">
         <f>N2+6</f>
         <v>46292</v>
       </c>
-      <c r="AM2" s="137"/>
-      <c r="AN2" s="155"/>
+      <c r="AM2" s="146"/>
+      <c r="AN2" s="161"/>
       <c r="AO2" s="12"/>
       <c r="AP2" s="12"/>
       <c r="AQ2" s="12"/>
       <c r="AR2" s="13"/>
     </row>
-    <row r="3" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="12"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -2528,101 +2531,101 @@
       <c r="AQ3" s="12"/>
       <c r="AR3" s="13"/>
     </row>
-    <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="12"/>
-      <c r="B4" s="153"/>
-      <c r="C4" s="153"/>
-      <c r="D4" s="153"/>
-      <c r="E4" s="153"/>
-      <c r="F4" s="153"/>
-      <c r="G4" s="153"/>
-      <c r="H4" s="153"/>
-      <c r="I4" s="153"/>
-      <c r="J4" s="153"/>
-      <c r="K4" s="153"/>
-      <c r="L4" s="153"/>
+      <c r="B4" s="159"/>
+      <c r="C4" s="159"/>
+      <c r="D4" s="159"/>
+      <c r="E4" s="159"/>
+      <c r="F4" s="159"/>
+      <c r="G4" s="159"/>
+      <c r="H4" s="159"/>
+      <c r="I4" s="159"/>
+      <c r="J4" s="159"/>
+      <c r="K4" s="159"/>
+      <c r="L4" s="159"/>
       <c r="M4" s="14"/>
-      <c r="N4" s="124" t="s">
+      <c r="N4" s="136" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="124"/>
-      <c r="P4" s="124"/>
-      <c r="Q4" s="124"/>
-      <c r="R4" s="124"/>
-      <c r="S4" s="124"/>
-      <c r="T4" s="124"/>
-      <c r="U4" s="124"/>
-      <c r="V4" s="124"/>
-      <c r="W4" s="124"/>
-      <c r="X4" s="124"/>
-      <c r="Y4" s="124"/>
-      <c r="Z4" s="124"/>
-      <c r="AA4" s="124"/>
-      <c r="AB4" s="124"/>
+      <c r="O4" s="136"/>
+      <c r="P4" s="136"/>
+      <c r="Q4" s="136"/>
+      <c r="R4" s="136"/>
+      <c r="S4" s="136"/>
+      <c r="T4" s="136"/>
+      <c r="U4" s="136"/>
+      <c r="V4" s="136"/>
+      <c r="W4" s="136"/>
+      <c r="X4" s="136"/>
+      <c r="Y4" s="136"/>
+      <c r="Z4" s="136"/>
+      <c r="AA4" s="136"/>
+      <c r="AB4" s="136"/>
       <c r="AC4" s="33"/>
-      <c r="AD4" s="153"/>
-      <c r="AE4" s="153"/>
-      <c r="AF4" s="153"/>
-      <c r="AG4" s="153"/>
-      <c r="AH4" s="153"/>
-      <c r="AI4" s="153"/>
-      <c r="AJ4" s="153"/>
-      <c r="AK4" s="153"/>
-      <c r="AL4" s="153"/>
-      <c r="AM4" s="153"/>
-      <c r="AN4" s="153"/>
+      <c r="AD4" s="159"/>
+      <c r="AE4" s="159"/>
+      <c r="AF4" s="159"/>
+      <c r="AG4" s="159"/>
+      <c r="AH4" s="159"/>
+      <c r="AI4" s="159"/>
+      <c r="AJ4" s="159"/>
+      <c r="AK4" s="159"/>
+      <c r="AL4" s="159"/>
+      <c r="AM4" s="159"/>
+      <c r="AN4" s="159"/>
       <c r="AO4" s="12"/>
       <c r="AP4" s="12"/>
       <c r="AQ4" s="12"/>
       <c r="AR4" s="13"/>
     </row>
-    <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="12"/>
-      <c r="B5" s="153"/>
-      <c r="C5" s="153"/>
-      <c r="D5" s="153"/>
-      <c r="E5" s="153"/>
-      <c r="F5" s="153"/>
-      <c r="G5" s="153"/>
-      <c r="H5" s="153"/>
-      <c r="I5" s="153"/>
-      <c r="J5" s="153"/>
-      <c r="K5" s="153"/>
-      <c r="L5" s="153"/>
+      <c r="B5" s="159"/>
+      <c r="C5" s="159"/>
+      <c r="D5" s="159"/>
+      <c r="E5" s="159"/>
+      <c r="F5" s="159"/>
+      <c r="G5" s="159"/>
+      <c r="H5" s="159"/>
+      <c r="I5" s="159"/>
+      <c r="J5" s="159"/>
+      <c r="K5" s="159"/>
+      <c r="L5" s="159"/>
       <c r="M5" s="14"/>
-      <c r="N5" s="124"/>
-      <c r="O5" s="124"/>
-      <c r="P5" s="124"/>
-      <c r="Q5" s="124"/>
-      <c r="R5" s="124"/>
-      <c r="S5" s="124"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="124"/>
-      <c r="W5" s="124"/>
-      <c r="X5" s="124"/>
-      <c r="Y5" s="124"/>
-      <c r="Z5" s="124"/>
-      <c r="AA5" s="124"/>
-      <c r="AB5" s="124"/>
+      <c r="N5" s="136"/>
+      <c r="O5" s="136"/>
+      <c r="P5" s="136"/>
+      <c r="Q5" s="136"/>
+      <c r="R5" s="136"/>
+      <c r="S5" s="136"/>
+      <c r="T5" s="136"/>
+      <c r="U5" s="136"/>
+      <c r="V5" s="136"/>
+      <c r="W5" s="136"/>
+      <c r="X5" s="136"/>
+      <c r="Y5" s="136"/>
+      <c r="Z5" s="136"/>
+      <c r="AA5" s="136"/>
+      <c r="AB5" s="136"/>
       <c r="AC5" s="33"/>
-      <c r="AD5" s="153"/>
-      <c r="AE5" s="153"/>
-      <c r="AF5" s="153"/>
-      <c r="AG5" s="153"/>
-      <c r="AH5" s="153"/>
-      <c r="AI5" s="153"/>
-      <c r="AJ5" s="153"/>
-      <c r="AK5" s="153"/>
-      <c r="AL5" s="153"/>
-      <c r="AM5" s="153"/>
-      <c r="AN5" s="153"/>
+      <c r="AD5" s="159"/>
+      <c r="AE5" s="159"/>
+      <c r="AF5" s="159"/>
+      <c r="AG5" s="159"/>
+      <c r="AH5" s="159"/>
+      <c r="AI5" s="159"/>
+      <c r="AJ5" s="159"/>
+      <c r="AK5" s="159"/>
+      <c r="AL5" s="159"/>
+      <c r="AM5" s="159"/>
+      <c r="AN5" s="159"/>
       <c r="AO5" s="12"/>
       <c r="AP5" s="12"/>
       <c r="AQ5" s="12"/>
       <c r="AR5" s="13"/>
     </row>
-    <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="76" t="s">
         <v>57</v>
       </c>
@@ -2631,18 +2634,18 @@
         <v>55</v>
       </c>
       <c r="E6" s="39"/>
-      <c r="F6" s="117" t="s">
+      <c r="F6" s="126" t="s">
         <v>57</v>
       </c>
-      <c r="G6" s="118"/>
+      <c r="G6" s="127"/>
       <c r="H6" s="59" t="s">
         <v>55</v>
       </c>
       <c r="I6" s="36"/>
-      <c r="J6" s="117" t="s">
+      <c r="J6" s="126" t="s">
         <v>57</v>
       </c>
-      <c r="K6" s="118"/>
+      <c r="K6" s="127"/>
       <c r="L6" s="59" t="s">
         <v>55</v>
       </c>
@@ -2695,7 +2698,7 @@
       </c>
       <c r="AR6" s="30"/>
     </row>
-    <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="73"/>
       <c r="C7" s="74"/>
       <c r="D7" s="61"/>
@@ -2750,24 +2753,24 @@
       </c>
       <c r="AR7" s="30"/>
     </row>
-    <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="78" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="79"/>
       <c r="D8" s="80"/>
       <c r="E8" s="35"/>
-      <c r="F8" s="141" t="s">
+      <c r="F8" s="137" t="s">
         <v>87</v>
       </c>
-      <c r="G8" s="142"/>
-      <c r="H8" s="143"/>
+      <c r="G8" s="138"/>
+      <c r="H8" s="139"/>
       <c r="I8" s="37"/>
-      <c r="J8" s="141" t="s">
+      <c r="J8" s="137" t="s">
         <v>109</v>
       </c>
-      <c r="K8" s="142"/>
-      <c r="L8" s="143"/>
+      <c r="K8" s="138"/>
+      <c r="L8" s="139"/>
       <c r="M8" s="3"/>
       <c r="N8" s="70"/>
       <c r="O8" s="71"/>
@@ -2811,20 +2814,20 @@
       </c>
       <c r="AR8" s="30"/>
     </row>
-    <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="78"/>
       <c r="C9" s="79"/>
       <c r="D9" s="80"/>
       <c r="E9" s="43"/>
-      <c r="F9" s="128"/>
-      <c r="G9" s="129"/>
-      <c r="H9" s="130"/>
+      <c r="F9" s="143"/>
+      <c r="G9" s="144"/>
+      <c r="H9" s="145"/>
       <c r="I9" s="43"/>
-      <c r="J9" s="134" t="s">
+      <c r="J9" s="117" t="s">
         <v>79</v>
       </c>
-      <c r="K9" s="135"/>
-      <c r="L9" s="136"/>
+      <c r="K9" s="118"/>
+      <c r="L9" s="119"/>
       <c r="M9" s="3"/>
       <c r="N9" s="78"/>
       <c r="O9" s="79"/>
@@ -2866,7 +2869,7 @@
       </c>
       <c r="AR9" s="30"/>
     </row>
-    <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="92"/>
       <c r="C10" s="93"/>
       <c r="D10" s="94"/>
@@ -2875,11 +2878,11 @@
       <c r="G10" s="132"/>
       <c r="H10" s="133"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="138" t="s">
+      <c r="J10" s="147" t="s">
         <v>88</v>
       </c>
-      <c r="K10" s="139"/>
-      <c r="L10" s="140"/>
+      <c r="K10" s="148"/>
+      <c r="L10" s="149"/>
       <c r="M10" s="5"/>
       <c r="N10" s="92"/>
       <c r="O10" s="93"/>
@@ -2917,7 +2920,7 @@
       </c>
       <c r="AR10" s="30"/>
     </row>
-    <row r="11" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="33"/>
       <c r="C11" s="33"/>
       <c r="D11" s="33"/>
@@ -2966,7 +2969,7 @@
       </c>
       <c r="AR11" s="30"/>
     </row>
-    <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
       <c r="D12" s="55"/>
@@ -3023,7 +3026,7 @@
       </c>
       <c r="AR12" s="30"/>
     </row>
-    <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="73"/>
       <c r="C13" s="74"/>
       <c r="D13" s="61"/>
@@ -3068,11 +3071,11 @@
       </c>
       <c r="AQ13" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR13" s="30"/>
     </row>
-    <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="70"/>
       <c r="C14" s="71"/>
       <c r="D14" s="72"/>
@@ -3125,7 +3128,7 @@
       </c>
       <c r="AR14" s="30"/>
     </row>
-    <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="78"/>
       <c r="C15" s="79"/>
       <c r="D15" s="80"/>
@@ -3178,7 +3181,7 @@
       </c>
       <c r="AR15" s="30"/>
     </row>
-    <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="92"/>
       <c r="C16" s="93"/>
       <c r="D16" s="94"/>
@@ -3227,7 +3230,7 @@
       </c>
       <c r="AR16" s="30"/>
     </row>
-    <row r="17" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="33"/>
       <c r="C17" s="33"/>
       <c r="D17" s="33"/>
@@ -3272,11 +3275,11 @@
       </c>
       <c r="AQ17" s="25">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR17" s="30"/>
     </row>
-    <row r="18" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="33"/>
       <c r="C18" s="33"/>
       <c r="D18" s="33"/>
@@ -3289,23 +3292,23 @@
       <c r="K18" s="33"/>
       <c r="L18" s="33"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="124" t="s">
+      <c r="N18" s="136" t="s">
         <v>49</v>
       </c>
-      <c r="O18" s="124"/>
-      <c r="P18" s="124"/>
-      <c r="Q18" s="124"/>
-      <c r="R18" s="124"/>
-      <c r="S18" s="124"/>
-      <c r="T18" s="124"/>
-      <c r="U18" s="124"/>
-      <c r="V18" s="124"/>
-      <c r="W18" s="124"/>
-      <c r="X18" s="124"/>
-      <c r="Y18" s="124"/>
-      <c r="Z18" s="124"/>
-      <c r="AA18" s="124"/>
-      <c r="AB18" s="124"/>
+      <c r="O18" s="136"/>
+      <c r="P18" s="136"/>
+      <c r="Q18" s="136"/>
+      <c r="R18" s="136"/>
+      <c r="S18" s="136"/>
+      <c r="T18" s="136"/>
+      <c r="U18" s="136"/>
+      <c r="V18" s="136"/>
+      <c r="W18" s="136"/>
+      <c r="X18" s="136"/>
+      <c r="Y18" s="136"/>
+      <c r="Z18" s="136"/>
+      <c r="AA18" s="136"/>
+      <c r="AB18" s="136"/>
       <c r="AC18" s="33"/>
       <c r="AD18" s="33"/>
       <c r="AE18" s="33"/>
@@ -3327,7 +3330,7 @@
       </c>
       <c r="AR18" s="30"/>
     </row>
-    <row r="19" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="33"/>
       <c r="C19" s="33"/>
       <c r="D19" s="33"/>
@@ -3340,21 +3343,21 @@
       <c r="K19" s="33"/>
       <c r="L19" s="33"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="124"/>
-      <c r="O19" s="124"/>
-      <c r="P19" s="124"/>
-      <c r="Q19" s="124"/>
-      <c r="R19" s="124"/>
-      <c r="S19" s="124"/>
-      <c r="T19" s="124"/>
-      <c r="U19" s="124"/>
-      <c r="V19" s="124"/>
-      <c r="W19" s="124"/>
-      <c r="X19" s="124"/>
-      <c r="Y19" s="124"/>
-      <c r="Z19" s="124"/>
-      <c r="AA19" s="124"/>
-      <c r="AB19" s="124"/>
+      <c r="N19" s="136"/>
+      <c r="O19" s="136"/>
+      <c r="P19" s="136"/>
+      <c r="Q19" s="136"/>
+      <c r="R19" s="136"/>
+      <c r="S19" s="136"/>
+      <c r="T19" s="136"/>
+      <c r="U19" s="136"/>
+      <c r="V19" s="136"/>
+      <c r="W19" s="136"/>
+      <c r="X19" s="136"/>
+      <c r="Y19" s="136"/>
+      <c r="Z19" s="136"/>
+      <c r="AA19" s="136"/>
+      <c r="AB19" s="136"/>
       <c r="AC19" s="33"/>
       <c r="AD19" s="33"/>
       <c r="AE19" s="33"/>
@@ -3376,7 +3379,7 @@
       </c>
       <c r="AR19" s="30"/>
     </row>
-    <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="68"/>
       <c r="C20" s="69"/>
       <c r="D20" s="55"/>
@@ -3437,7 +3440,7 @@
       </c>
       <c r="AR20" s="30"/>
     </row>
-    <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="73"/>
       <c r="C21" s="74"/>
       <c r="D21" s="61"/>
@@ -3490,16 +3493,16 @@
       </c>
       <c r="AR21" s="30"/>
     </row>
-    <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="70"/>
       <c r="C22" s="71"/>
       <c r="D22" s="72"/>
       <c r="E22" s="35"/>
-      <c r="F22" s="125" t="s">
+      <c r="F22" s="140" t="s">
         <v>9</v>
       </c>
-      <c r="G22" s="126"/>
-      <c r="H22" s="127"/>
+      <c r="G22" s="141"/>
+      <c r="H22" s="142"/>
       <c r="I22" s="37"/>
       <c r="J22" s="70"/>
       <c r="K22" s="71"/>
@@ -3545,7 +3548,7 @@
       </c>
       <c r="AR22" s="30"/>
     </row>
-    <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="92"/>
       <c r="C23" s="93"/>
       <c r="D23" s="94"/>
@@ -3598,7 +3601,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="33"/>
       <c r="C24" s="33"/>
       <c r="D24" s="33"/>
@@ -3647,7 +3650,7 @@
       </c>
       <c r="AR24" s="30"/>
     </row>
-    <row r="25" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="33"/>
       <c r="C25" s="33"/>
       <c r="D25" s="33"/>
@@ -3660,23 +3663,23 @@
       <c r="K25" s="33"/>
       <c r="L25" s="33"/>
       <c r="M25" s="4"/>
-      <c r="N25" s="124" t="s">
+      <c r="N25" s="136" t="s">
         <v>39</v>
       </c>
-      <c r="O25" s="124"/>
-      <c r="P25" s="124"/>
-      <c r="Q25" s="124"/>
-      <c r="R25" s="124"/>
-      <c r="S25" s="124"/>
-      <c r="T25" s="124"/>
-      <c r="U25" s="124"/>
-      <c r="V25" s="124"/>
-      <c r="W25" s="124"/>
-      <c r="X25" s="124"/>
-      <c r="Y25" s="124"/>
-      <c r="Z25" s="124"/>
-      <c r="AA25" s="124"/>
-      <c r="AB25" s="124"/>
+      <c r="O25" s="136"/>
+      <c r="P25" s="136"/>
+      <c r="Q25" s="136"/>
+      <c r="R25" s="136"/>
+      <c r="S25" s="136"/>
+      <c r="T25" s="136"/>
+      <c r="U25" s="136"/>
+      <c r="V25" s="136"/>
+      <c r="W25" s="136"/>
+      <c r="X25" s="136"/>
+      <c r="Y25" s="136"/>
+      <c r="Z25" s="136"/>
+      <c r="AA25" s="136"/>
+      <c r="AB25" s="136"/>
       <c r="AC25" s="33"/>
       <c r="AD25" s="33"/>
       <c r="AE25" s="33"/>
@@ -3698,7 +3701,7 @@
       </c>
       <c r="AR25" s="30"/>
     </row>
-    <row r="26" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="33"/>
       <c r="C26" s="33"/>
       <c r="D26" s="33"/>
@@ -3711,21 +3714,21 @@
       <c r="K26" s="33"/>
       <c r="L26" s="33"/>
       <c r="M26" s="4"/>
-      <c r="N26" s="124"/>
-      <c r="O26" s="124"/>
-      <c r="P26" s="124"/>
-      <c r="Q26" s="124"/>
-      <c r="R26" s="124"/>
-      <c r="S26" s="124"/>
-      <c r="T26" s="124"/>
-      <c r="U26" s="124"/>
-      <c r="V26" s="124"/>
-      <c r="W26" s="124"/>
-      <c r="X26" s="124"/>
-      <c r="Y26" s="124"/>
-      <c r="Z26" s="124"/>
-      <c r="AA26" s="124"/>
-      <c r="AB26" s="124"/>
+      <c r="N26" s="136"/>
+      <c r="O26" s="136"/>
+      <c r="P26" s="136"/>
+      <c r="Q26" s="136"/>
+      <c r="R26" s="136"/>
+      <c r="S26" s="136"/>
+      <c r="T26" s="136"/>
+      <c r="U26" s="136"/>
+      <c r="V26" s="136"/>
+      <c r="W26" s="136"/>
+      <c r="X26" s="136"/>
+      <c r="Y26" s="136"/>
+      <c r="Z26" s="136"/>
+      <c r="AA26" s="136"/>
+      <c r="AB26" s="136"/>
       <c r="AC26" s="33"/>
       <c r="AD26" s="33"/>
       <c r="AE26" s="33"/>
@@ -3747,7 +3750,7 @@
       </c>
       <c r="AR26" s="30"/>
     </row>
-    <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="68" t="s">
         <v>64</v>
       </c>
@@ -3828,7 +3831,7 @@
       </c>
       <c r="AR27" s="30"/>
     </row>
-    <row r="28" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="73"/>
       <c r="C28" s="74"/>
       <c r="D28" s="61"/>
@@ -3861,8 +3864,8 @@
       <c r="AE28" s="84"/>
       <c r="AF28" s="18"/>
       <c r="AG28" s="38"/>
-      <c r="AH28" s="122"/>
-      <c r="AI28" s="123"/>
+      <c r="AH28" s="134"/>
+      <c r="AI28" s="135"/>
       <c r="AJ28" s="18"/>
       <c r="AK28" s="36"/>
       <c r="AL28" s="83"/>
@@ -3877,7 +3880,7 @@
       </c>
       <c r="AR28" s="30"/>
     </row>
-    <row r="29" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="95" t="s">
         <v>7</v>
       </c>
@@ -3960,7 +3963,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="97" t="s">
         <v>19</v>
       </c>
@@ -4041,7 +4044,7 @@
       </c>
       <c r="AR30" s="30"/>
     </row>
-    <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="99" t="s">
         <v>37</v>
       </c>
@@ -4117,7 +4120,7 @@
       <c r="AQ31" s="49"/>
       <c r="AR31" s="30"/>
     </row>
-    <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B32" s="99" t="s">
         <v>21</v>
       </c>
@@ -4193,7 +4196,7 @@
       <c r="AQ32" s="52"/>
       <c r="AR32" s="30"/>
     </row>
-    <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="99" t="s">
         <v>14</v>
       </c>
@@ -4243,7 +4246,7 @@
       <c r="AN33" s="45"/>
       <c r="AR33" s="13"/>
     </row>
-    <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="12"/>
       <c r="B34" s="101"/>
       <c r="C34" s="102"/>
@@ -4289,7 +4292,7 @@
       <c r="AQ34" s="12"/>
       <c r="AR34" s="13"/>
     </row>
-    <row r="35" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="12"/>
       <c r="B35" s="33"/>
       <c r="C35" s="33"/>
@@ -4334,7 +4337,7 @@
       <c r="AQ35" s="12"/>
       <c r="AR35" s="13"/>
     </row>
-    <row r="36" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="12"/>
       <c r="B36" s="33"/>
       <c r="C36" s="33"/>
@@ -4348,23 +4351,23 @@
       <c r="K36" s="33"/>
       <c r="L36" s="33"/>
       <c r="M36" s="4"/>
-      <c r="N36" s="124" t="s">
+      <c r="N36" s="136" t="s">
         <v>36</v>
       </c>
-      <c r="O36" s="124"/>
-      <c r="P36" s="124"/>
-      <c r="Q36" s="124"/>
-      <c r="R36" s="124"/>
-      <c r="S36" s="124"/>
-      <c r="T36" s="124"/>
-      <c r="U36" s="124"/>
-      <c r="V36" s="124"/>
-      <c r="W36" s="124"/>
-      <c r="X36" s="124"/>
-      <c r="Y36" s="124"/>
-      <c r="Z36" s="124"/>
-      <c r="AA36" s="124"/>
-      <c r="AB36" s="124"/>
+      <c r="O36" s="136"/>
+      <c r="P36" s="136"/>
+      <c r="Q36" s="136"/>
+      <c r="R36" s="136"/>
+      <c r="S36" s="136"/>
+      <c r="T36" s="136"/>
+      <c r="U36" s="136"/>
+      <c r="V36" s="136"/>
+      <c r="W36" s="136"/>
+      <c r="X36" s="136"/>
+      <c r="Y36" s="136"/>
+      <c r="Z36" s="136"/>
+      <c r="AA36" s="136"/>
+      <c r="AB36" s="136"/>
       <c r="AC36" s="33"/>
       <c r="AD36" s="33"/>
       <c r="AE36" s="33"/>
@@ -4382,7 +4385,7 @@
       <c r="AQ36" s="31"/>
       <c r="AR36" s="13"/>
     </row>
-    <row r="37" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="12"/>
       <c r="B37" s="33"/>
       <c r="C37" s="33"/>
@@ -4396,21 +4399,21 @@
       <c r="K37" s="33"/>
       <c r="L37" s="33"/>
       <c r="M37" s="5"/>
-      <c r="N37" s="124"/>
-      <c r="O37" s="124"/>
-      <c r="P37" s="124"/>
-      <c r="Q37" s="124"/>
-      <c r="R37" s="124"/>
-      <c r="S37" s="124"/>
-      <c r="T37" s="124"/>
-      <c r="U37" s="124"/>
-      <c r="V37" s="124"/>
-      <c r="W37" s="124"/>
-      <c r="X37" s="124"/>
-      <c r="Y37" s="124"/>
-      <c r="Z37" s="124"/>
-      <c r="AA37" s="124"/>
-      <c r="AB37" s="124"/>
+      <c r="N37" s="136"/>
+      <c r="O37" s="136"/>
+      <c r="P37" s="136"/>
+      <c r="Q37" s="136"/>
+      <c r="R37" s="136"/>
+      <c r="S37" s="136"/>
+      <c r="T37" s="136"/>
+      <c r="U37" s="136"/>
+      <c r="V37" s="136"/>
+      <c r="W37" s="136"/>
+      <c r="X37" s="136"/>
+      <c r="Y37" s="136"/>
+      <c r="Z37" s="136"/>
+      <c r="AA37" s="136"/>
+      <c r="AB37" s="136"/>
       <c r="AC37" s="33"/>
       <c r="AD37" s="33"/>
       <c r="AE37" s="33"/>
@@ -4428,7 +4431,7 @@
       <c r="AQ37" s="31"/>
       <c r="AR37" s="13"/>
     </row>
-    <row r="38" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="12"/>
       <c r="B38" s="68" t="s">
         <v>90</v>
@@ -4494,11 +4497,11 @@
         <v>76</v>
       </c>
       <c r="AK38" s="36"/>
-      <c r="AL38" s="81" t="s">
+      <c r="AL38" s="126" t="s">
         <v>72</v>
       </c>
-      <c r="AM38" s="82"/>
-      <c r="AN38" s="34" t="s">
+      <c r="AM38" s="127"/>
+      <c r="AN38" s="59" t="s">
         <v>55</v>
       </c>
       <c r="AO38" s="31"/>
@@ -4506,7 +4509,7 @@
       <c r="AQ38" s="31"/>
       <c r="AR38" s="13"/>
     </row>
-    <row r="39" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="12"/>
       <c r="B39" s="62" t="s">
         <v>51</v>
@@ -4560,17 +4563,17 @@
       <c r="AI39" s="107"/>
       <c r="AJ39" s="108"/>
       <c r="AK39" s="36"/>
-      <c r="AL39" s="106" t="s">
+      <c r="AL39" s="109" t="s">
         <v>75</v>
       </c>
-      <c r="AM39" s="107"/>
-      <c r="AN39" s="108"/>
+      <c r="AM39" s="110"/>
+      <c r="AN39" s="111"/>
       <c r="AO39" s="31"/>
       <c r="AP39" s="31"/>
       <c r="AQ39" s="31"/>
       <c r="AR39" s="13"/>
     </row>
-    <row r="40" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="12"/>
       <c r="B40" s="73"/>
       <c r="C40" s="74"/>
@@ -4612,15 +4615,17 @@
       <c r="AI40" s="84"/>
       <c r="AJ40" s="85"/>
       <c r="AK40" s="43"/>
-      <c r="AL40" s="83"/>
-      <c r="AM40" s="84"/>
-      <c r="AN40" s="85"/>
+      <c r="AL40" s="114" t="s">
+        <v>86</v>
+      </c>
+      <c r="AM40" s="115"/>
+      <c r="AN40" s="116"/>
       <c r="AO40" s="31"/>
       <c r="AP40" s="31"/>
       <c r="AQ40" s="31"/>
       <c r="AR40" s="13"/>
     </row>
-    <row r="41" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12"/>
       <c r="B41" s="78" t="s">
         <v>16</v>
@@ -4662,11 +4667,11 @@
       <c r="AA41" s="79"/>
       <c r="AB41" s="80"/>
       <c r="AC41" s="32"/>
-      <c r="AD41" s="119" t="s">
+      <c r="AD41" s="128" t="s">
         <v>24</v>
       </c>
-      <c r="AE41" s="120"/>
-      <c r="AF41" s="121"/>
+      <c r="AE41" s="129"/>
+      <c r="AF41" s="130"/>
       <c r="AG41" s="37"/>
       <c r="AH41" s="78" t="s">
         <v>24</v>
@@ -4674,17 +4679,17 @@
       <c r="AI41" s="79"/>
       <c r="AJ41" s="80"/>
       <c r="AK41" s="31"/>
-      <c r="AL41" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="AM41" s="79"/>
-      <c r="AN41" s="80"/>
+      <c r="AL41" s="117" t="s">
+        <v>96</v>
+      </c>
+      <c r="AM41" s="118"/>
+      <c r="AN41" s="119"/>
       <c r="AO41" s="31"/>
       <c r="AP41" s="31"/>
       <c r="AQ41" s="31"/>
       <c r="AR41" s="13"/>
     </row>
-    <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12"/>
       <c r="B42" s="78" t="s">
         <v>11</v>
@@ -4738,17 +4743,17 @@
       <c r="AI42" s="79"/>
       <c r="AJ42" s="80"/>
       <c r="AK42" s="31"/>
-      <c r="AL42" s="78" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM42" s="79"/>
-      <c r="AN42" s="80"/>
+      <c r="AL42" s="117" t="s">
+        <v>88</v>
+      </c>
+      <c r="AM42" s="118"/>
+      <c r="AN42" s="119"/>
       <c r="AO42" s="31"/>
       <c r="AP42" s="31"/>
       <c r="AQ42" s="31"/>
       <c r="AR42" s="13"/>
     </row>
-    <row r="43" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="12"/>
       <c r="B43" s="65"/>
       <c r="C43" s="66"/>
@@ -4784,11 +4789,11 @@
       <c r="AA43" s="66"/>
       <c r="AB43" s="67"/>
       <c r="AC43" s="40"/>
-      <c r="AD43" s="78" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE43" s="79"/>
-      <c r="AF43" s="80"/>
+      <c r="AD43" s="103" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE43" s="104"/>
+      <c r="AF43" s="105"/>
       <c r="AG43" s="35"/>
       <c r="AH43" s="78" t="s">
         <v>10</v>
@@ -4796,15 +4801,15 @@
       <c r="AI43" s="79"/>
       <c r="AJ43" s="80"/>
       <c r="AK43" s="40"/>
-      <c r="AL43" s="65"/>
-      <c r="AM43" s="66"/>
-      <c r="AN43" s="67"/>
+      <c r="AL43" s="131"/>
+      <c r="AM43" s="132"/>
+      <c r="AN43" s="133"/>
       <c r="AO43" s="31"/>
       <c r="AP43" s="31"/>
       <c r="AQ43" s="31"/>
       <c r="AR43" s="13"/>
     </row>
-    <row r="44" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="12"/>
       <c r="B44" s="35"/>
       <c r="C44" s="35"/>
@@ -4856,7 +4861,7 @@
       <c r="AQ44" s="31"/>
       <c r="AR44" s="13"/>
     </row>
-    <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="12"/>
       <c r="B45" s="68" t="s">
         <v>91</v>
@@ -4924,7 +4929,7 @@
       <c r="AQ45" s="31"/>
       <c r="AR45" s="13"/>
     </row>
-    <row r="46" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="12"/>
       <c r="B46" s="62" t="s">
         <v>97</v>
@@ -4980,7 +4985,7 @@
       <c r="AQ46" s="31"/>
       <c r="AR46" s="13"/>
     </row>
-    <row r="47" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="12"/>
       <c r="B47" s="73"/>
       <c r="C47" s="74"/>
@@ -5030,7 +5035,7 @@
       <c r="AQ47" s="31"/>
       <c r="AR47" s="13"/>
     </row>
-    <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="12"/>
       <c r="B48" s="78" t="s">
         <v>25</v>
@@ -5088,7 +5093,7 @@
       <c r="AQ48" s="31"/>
       <c r="AR48" s="13"/>
     </row>
-    <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="78" t="s">
         <v>24</v>
       </c>
@@ -5143,7 +5148,7 @@
       <c r="AQ49" s="31"/>
       <c r="AR49" s="13"/>
     </row>
-    <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="89" t="s">
         <v>100</v>
       </c>
@@ -5196,7 +5201,7 @@
       <c r="AQ50" s="31"/>
       <c r="AR50" s="13"/>
     </row>
-    <row r="51" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="35"/>
       <c r="C51" s="35"/>
       <c r="D51" s="35"/>
@@ -5243,7 +5248,7 @@
       <c r="AQ51" s="31"/>
       <c r="AR51" s="13"/>
     </row>
-    <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="76" t="s">
         <v>101</v>
       </c>
@@ -5297,7 +5302,7 @@
       <c r="AN52" s="34"/>
       <c r="AR52" s="13"/>
     </row>
-    <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="62" t="s">
         <v>103</v>
       </c>
@@ -5345,7 +5350,7 @@
       <c r="AN53" s="108"/>
       <c r="AR53" s="13"/>
     </row>
-    <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="73"/>
       <c r="C54" s="74"/>
       <c r="D54" s="75"/>
@@ -5387,7 +5392,7 @@
       <c r="AN54" s="85"/>
       <c r="AR54" s="13"/>
     </row>
-    <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="78" t="s">
         <v>10</v>
       </c>
@@ -5435,7 +5440,7 @@
       <c r="AN55" s="80"/>
       <c r="AR55" s="13"/>
     </row>
-    <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="78" t="s">
         <v>12</v>
       </c>
@@ -5483,7 +5488,7 @@
       <c r="AN56" s="80"/>
       <c r="AR56" s="13"/>
     </row>
-    <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="65"/>
       <c r="C57" s="66"/>
       <c r="D57" s="67"/>
@@ -5525,7 +5530,7 @@
       <c r="AN57" s="67"/>
       <c r="AR57" s="13"/>
     </row>
-    <row r="58" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="35"/>
       <c r="C58" s="35"/>
       <c r="D58" s="35"/>
@@ -5567,7 +5572,7 @@
       <c r="AN58" s="35"/>
       <c r="AR58" s="13"/>
     </row>
-    <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="76" t="s">
         <v>101</v>
       </c>
@@ -5613,7 +5618,7 @@
       <c r="AN59" s="34"/>
       <c r="AR59" s="13"/>
     </row>
-    <row r="60" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="62" t="s">
         <v>105</v>
       </c>
@@ -5657,7 +5662,7 @@
       <c r="AN60" s="108"/>
       <c r="AR60" s="13"/>
     </row>
-    <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="73"/>
       <c r="C61" s="74"/>
       <c r="D61" s="75"/>
@@ -5699,7 +5704,7 @@
       <c r="AN61" s="85"/>
       <c r="AR61" s="13"/>
     </row>
-    <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="70" t="s">
         <v>22</v>
       </c>
@@ -5743,7 +5748,7 @@
       <c r="AN62" s="72"/>
       <c r="AR62" s="13"/>
     </row>
-    <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="78" t="s">
         <v>8</v>
       </c>
@@ -5787,7 +5792,7 @@
       <c r="AN63" s="80"/>
       <c r="AR63" s="13"/>
     </row>
-    <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B64" s="65"/>
       <c r="C64" s="66"/>
       <c r="D64" s="67"/>
@@ -5829,7 +5834,7 @@
       <c r="AN64" s="67"/>
       <c r="AR64" s="13"/>
     </row>
-    <row r="65" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="12"/>
       <c r="B65" s="35"/>
       <c r="C65" s="35"/>
@@ -5875,7 +5880,7 @@
       <c r="AQ65" s="12"/>
       <c r="AR65" s="13"/>
     </row>
-    <row r="66" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="12"/>
       <c r="B66" s="76" t="s">
         <v>101</v>
@@ -5919,17 +5924,17 @@
       <c r="AI66" s="82"/>
       <c r="AJ66" s="34"/>
       <c r="AK66" s="32"/>
-      <c r="AL66" s="117" t="s">
+      <c r="AL66" s="126" t="s">
         <v>114</v>
       </c>
-      <c r="AM66" s="118"/>
+      <c r="AM66" s="127"/>
       <c r="AN66" s="59"/>
       <c r="AO66" s="17"/>
       <c r="AP66" s="12"/>
       <c r="AQ66" s="12"/>
       <c r="AR66" s="13"/>
     </row>
-    <row r="67" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="12"/>
       <c r="B67" s="62" t="s">
         <v>106</v>
@@ -5981,7 +5986,7 @@
       <c r="AQ67" s="12"/>
       <c r="AR67" s="13"/>
     </row>
-    <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="12"/>
       <c r="B68" s="73"/>
       <c r="C68" s="74"/>
@@ -6031,7 +6036,7 @@
       <c r="AQ68" s="12"/>
       <c r="AR68" s="13"/>
     </row>
-    <row r="69" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="12"/>
       <c r="B69" s="78" t="s">
         <v>18</v>
@@ -6085,7 +6090,7 @@
       <c r="AQ69" s="12"/>
       <c r="AR69" s="13"/>
     </row>
-    <row r="70" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="12"/>
       <c r="B70" s="78" t="s">
         <v>26</v>
@@ -6137,7 +6142,7 @@
       <c r="AQ70" s="12"/>
       <c r="AR70" s="13"/>
     </row>
-    <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="12"/>
       <c r="B71" s="65"/>
       <c r="C71" s="66"/>
@@ -6187,7 +6192,7 @@
       <c r="AQ71" s="12"/>
       <c r="AR71" s="13"/>
     </row>
-    <row r="72" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="12"/>
       <c r="B72" s="33"/>
       <c r="C72" s="33"/>
@@ -6233,7 +6238,7 @@
       <c r="AQ72" s="12"/>
       <c r="AR72" s="13"/>
     </row>
-    <row r="73" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="12"/>
       <c r="B73" s="40"/>
       <c r="C73" s="33"/>
@@ -6247,23 +6252,23 @@
       <c r="K73" s="33"/>
       <c r="L73" s="33"/>
       <c r="M73" s="14"/>
-      <c r="N73" s="124" t="s">
+      <c r="N73" s="136" t="s">
         <v>31</v>
       </c>
-      <c r="O73" s="124"/>
-      <c r="P73" s="124"/>
-      <c r="Q73" s="124"/>
-      <c r="R73" s="124"/>
-      <c r="S73" s="124"/>
-      <c r="T73" s="124"/>
-      <c r="U73" s="124"/>
-      <c r="V73" s="124"/>
-      <c r="W73" s="124"/>
-      <c r="X73" s="124"/>
-      <c r="Y73" s="124"/>
-      <c r="Z73" s="124"/>
-      <c r="AA73" s="124"/>
-      <c r="AB73" s="124"/>
+      <c r="O73" s="136"/>
+      <c r="P73" s="136"/>
+      <c r="Q73" s="136"/>
+      <c r="R73" s="136"/>
+      <c r="S73" s="136"/>
+      <c r="T73" s="136"/>
+      <c r="U73" s="136"/>
+      <c r="V73" s="136"/>
+      <c r="W73" s="136"/>
+      <c r="X73" s="136"/>
+      <c r="Y73" s="136"/>
+      <c r="Z73" s="136"/>
+      <c r="AA73" s="136"/>
+      <c r="AB73" s="136"/>
       <c r="AD73" s="40"/>
       <c r="AE73" s="33"/>
       <c r="AF73" s="33"/>
@@ -6280,7 +6285,7 @@
       <c r="AQ73" s="12"/>
       <c r="AR73" s="13"/>
     </row>
-    <row r="74" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="12"/>
       <c r="B74" s="33"/>
       <c r="C74" s="33"/>
@@ -6294,21 +6299,21 @@
       <c r="K74" s="33"/>
       <c r="L74" s="33"/>
       <c r="M74" s="14"/>
-      <c r="N74" s="124"/>
-      <c r="O74" s="124"/>
-      <c r="P74" s="124"/>
-      <c r="Q74" s="124"/>
-      <c r="R74" s="124"/>
-      <c r="S74" s="124"/>
-      <c r="T74" s="124"/>
-      <c r="U74" s="124"/>
-      <c r="V74" s="124"/>
-      <c r="W74" s="124"/>
-      <c r="X74" s="124"/>
-      <c r="Y74" s="124"/>
-      <c r="Z74" s="124"/>
-      <c r="AA74" s="124"/>
-      <c r="AB74" s="124"/>
+      <c r="N74" s="136"/>
+      <c r="O74" s="136"/>
+      <c r="P74" s="136"/>
+      <c r="Q74" s="136"/>
+      <c r="R74" s="136"/>
+      <c r="S74" s="136"/>
+      <c r="T74" s="136"/>
+      <c r="U74" s="136"/>
+      <c r="V74" s="136"/>
+      <c r="W74" s="136"/>
+      <c r="X74" s="136"/>
+      <c r="Y74" s="136"/>
+      <c r="Z74" s="136"/>
+      <c r="AA74" s="136"/>
+      <c r="AB74" s="136"/>
       <c r="AC74" s="21"/>
       <c r="AD74" s="33"/>
       <c r="AE74" s="33"/>
@@ -6326,7 +6331,7 @@
       <c r="AQ74" s="12"/>
       <c r="AR74" s="13"/>
     </row>
-    <row r="75" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="12"/>
       <c r="B75" s="68" t="s">
         <v>58</v>
@@ -6404,7 +6409,7 @@
       <c r="AQ75" s="26"/>
       <c r="AR75" s="24"/>
     </row>
-    <row r="76" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="12"/>
       <c r="B76" s="62" t="s">
         <v>59</v>
@@ -6466,7 +6471,7 @@
       <c r="AQ76" s="26"/>
       <c r="AR76" s="24"/>
     </row>
-    <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="16"/>
       <c r="B77" s="73"/>
       <c r="C77" s="74"/>
@@ -6512,7 +6517,7 @@
       <c r="AQ77" s="26"/>
       <c r="AR77" s="24"/>
     </row>
-    <row r="78" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="16"/>
       <c r="B78" s="70" t="s">
         <v>29</v>
@@ -6574,7 +6579,7 @@
       <c r="AQ78" s="26"/>
       <c r="AR78" s="24"/>
     </row>
-    <row r="79" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="16"/>
       <c r="B79" s="65"/>
       <c r="C79" s="66"/>
@@ -6620,7 +6625,7 @@
       <c r="AQ79" s="26"/>
       <c r="AR79" s="24"/>
     </row>
-    <row r="80" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="12"/>
       <c r="B80" s="35"/>
       <c r="C80" s="35"/>
@@ -6666,7 +6671,7 @@
       <c r="AQ80" s="26"/>
       <c r="AR80" s="24"/>
     </row>
-    <row r="81" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12"/>
       <c r="B81" s="68" t="s">
         <v>56</v>
@@ -6698,10 +6703,10 @@
       <c r="S81" s="82"/>
       <c r="T81" s="34"/>
       <c r="U81" s="36"/>
-      <c r="V81" s="117" t="s">
+      <c r="V81" s="126" t="s">
         <v>44</v>
       </c>
-      <c r="W81" s="118"/>
+      <c r="W81" s="127"/>
       <c r="X81" s="59"/>
       <c r="Y81" s="32"/>
       <c r="Z81" s="76" t="s">
@@ -6716,10 +6721,10 @@
       <c r="AE81" s="82"/>
       <c r="AF81" s="34"/>
       <c r="AG81" s="32"/>
-      <c r="AH81" s="117" t="s">
+      <c r="AH81" s="126" t="s">
         <v>44</v>
       </c>
-      <c r="AI81" s="118"/>
+      <c r="AI81" s="127"/>
       <c r="AJ81" s="59"/>
       <c r="AK81" s="50"/>
       <c r="AL81" s="81"/>
@@ -6730,7 +6735,7 @@
       <c r="AQ81" s="26"/>
       <c r="AR81" s="24"/>
     </row>
-    <row r="82" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="12"/>
       <c r="B82" s="62" t="s">
         <v>53</v>
@@ -6762,11 +6767,11 @@
       <c r="S82" s="107"/>
       <c r="T82" s="108"/>
       <c r="U82" s="32"/>
-      <c r="V82" s="159" t="s">
+      <c r="V82" s="120" t="s">
         <v>86</v>
       </c>
-      <c r="W82" s="160"/>
-      <c r="X82" s="161"/>
+      <c r="W82" s="121"/>
+      <c r="X82" s="122"/>
       <c r="Y82" s="32"/>
       <c r="Z82" s="106"/>
       <c r="AA82" s="107"/>
@@ -6776,11 +6781,11 @@
       <c r="AE82" s="107"/>
       <c r="AF82" s="108"/>
       <c r="AG82" s="32"/>
-      <c r="AH82" s="159" t="s">
+      <c r="AH82" s="120" t="s">
         <v>86</v>
       </c>
-      <c r="AI82" s="160"/>
-      <c r="AJ82" s="161"/>
+      <c r="AI82" s="121"/>
+      <c r="AJ82" s="122"/>
       <c r="AK82" s="36"/>
       <c r="AL82" s="106"/>
       <c r="AM82" s="107"/>
@@ -6790,7 +6795,7 @@
       <c r="AQ82" s="26"/>
       <c r="AR82" s="24"/>
     </row>
-    <row r="83" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="12"/>
       <c r="B83" s="73" t="s">
         <v>50</v>
@@ -6822,11 +6827,11 @@
       <c r="S83" s="84"/>
       <c r="T83" s="85"/>
       <c r="U83" s="31"/>
-      <c r="V83" s="156" t="s">
+      <c r="V83" s="123" t="s">
         <v>50</v>
       </c>
-      <c r="W83" s="157"/>
-      <c r="X83" s="158"/>
+      <c r="W83" s="124"/>
+      <c r="X83" s="125"/>
       <c r="Y83" s="32"/>
       <c r="Z83" s="83" t="s">
         <v>50</v>
@@ -6840,11 +6845,11 @@
       <c r="AE83" s="84"/>
       <c r="AF83" s="85"/>
       <c r="AG83" s="32"/>
-      <c r="AH83" s="156" t="s">
+      <c r="AH83" s="123" t="s">
         <v>50</v>
       </c>
-      <c r="AI83" s="157"/>
-      <c r="AJ83" s="158"/>
+      <c r="AI83" s="124"/>
+      <c r="AJ83" s="125"/>
       <c r="AK83" s="32"/>
       <c r="AL83" s="83"/>
       <c r="AM83" s="84"/>
@@ -6854,7 +6859,7 @@
       <c r="AQ83" s="26"/>
       <c r="AR83" s="24"/>
     </row>
-    <row r="84" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12"/>
       <c r="B84" s="70" t="s">
         <v>13</v>
@@ -6886,11 +6891,11 @@
       <c r="S84" s="71"/>
       <c r="T84" s="72"/>
       <c r="U84" s="32"/>
-      <c r="V84" s="141" t="s">
+      <c r="V84" s="137" t="s">
         <v>115</v>
       </c>
-      <c r="W84" s="142"/>
-      <c r="X84" s="143"/>
+      <c r="W84" s="138"/>
+      <c r="X84" s="139"/>
       <c r="Y84" s="32"/>
       <c r="Z84" s="70" t="s">
         <v>30</v>
@@ -6904,11 +6909,11 @@
       <c r="AE84" s="71"/>
       <c r="AF84" s="72"/>
       <c r="AG84" s="32"/>
-      <c r="AH84" s="141" t="s">
+      <c r="AH84" s="137" t="s">
         <v>115</v>
       </c>
-      <c r="AI84" s="142"/>
-      <c r="AJ84" s="143"/>
+      <c r="AI84" s="138"/>
+      <c r="AJ84" s="139"/>
       <c r="AK84" s="32"/>
       <c r="AL84" s="70"/>
       <c r="AM84" s="71"/>
@@ -6918,7 +6923,7 @@
       <c r="AQ84" s="26"/>
       <c r="AR84" s="24"/>
     </row>
-    <row r="85" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="12"/>
       <c r="B85" s="65"/>
       <c r="C85" s="66"/>
@@ -6964,7 +6969,7 @@
       <c r="AQ85" s="26"/>
       <c r="AR85" s="24"/>
     </row>
-    <row r="86" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="12"/>
       <c r="B86" s="35"/>
       <c r="C86" s="35"/>
@@ -7010,7 +7015,7 @@
       <c r="AQ86" s="26"/>
       <c r="AR86" s="24"/>
     </row>
-    <row r="87" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="12"/>
       <c r="B87" s="68" t="s">
         <v>44</v>
@@ -7054,9 +7059,11 @@
       <c r="AA87" s="82"/>
       <c r="AB87" s="34"/>
       <c r="AC87" s="32"/>
-      <c r="AD87" s="81"/>
-      <c r="AE87" s="82"/>
-      <c r="AF87" s="34"/>
+      <c r="AD87" s="76" t="s">
+        <v>118</v>
+      </c>
+      <c r="AE87" s="77"/>
+      <c r="AF87" s="57"/>
       <c r="AG87" s="32"/>
       <c r="AH87" s="81"/>
       <c r="AI87" s="82"/>
@@ -7070,7 +7077,7 @@
       <c r="AQ87" s="26"/>
       <c r="AR87" s="24"/>
     </row>
-    <row r="88" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="12"/>
       <c r="B88" s="62"/>
       <c r="C88" s="63"/>
@@ -7126,7 +7133,7 @@
       <c r="AQ88" s="26"/>
       <c r="AR88" s="24"/>
     </row>
-    <row r="89" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="12"/>
       <c r="B89" s="73" t="s">
         <v>50</v>
@@ -7160,7 +7167,9 @@
       <c r="AA89" s="84"/>
       <c r="AB89" s="85"/>
       <c r="AC89" s="31"/>
-      <c r="AD89" s="83"/>
+      <c r="AD89" s="83" t="s">
+        <v>50</v>
+      </c>
       <c r="AE89" s="84"/>
       <c r="AF89" s="85"/>
       <c r="AG89" s="32"/>
@@ -7176,7 +7185,7 @@
       <c r="AQ89" s="26"/>
       <c r="AR89" s="24"/>
     </row>
-    <row r="90" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="12"/>
       <c r="B90" s="70" t="s">
         <v>30</v>
@@ -7220,7 +7229,9 @@
       <c r="AA90" s="71"/>
       <c r="AB90" s="72"/>
       <c r="AC90" s="32"/>
-      <c r="AD90" s="70"/>
+      <c r="AD90" s="70" t="s">
+        <v>10</v>
+      </c>
       <c r="AE90" s="71"/>
       <c r="AF90" s="72"/>
       <c r="AG90" s="32"/>
@@ -7236,7 +7247,7 @@
       <c r="AQ90" s="26"/>
       <c r="AR90" s="24"/>
     </row>
-    <row r="91" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="12"/>
       <c r="B91" s="65"/>
       <c r="C91" s="66"/>
@@ -7282,7 +7293,7 @@
       <c r="AQ91" s="26"/>
       <c r="AR91" s="24"/>
     </row>
-    <row r="92" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="12"/>
       <c r="B92" s="35"/>
       <c r="C92" s="35"/>
@@ -7328,7 +7339,7 @@
       <c r="AQ92" s="26"/>
       <c r="AR92" s="24"/>
     </row>
-    <row r="93" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="12"/>
       <c r="B93" s="68"/>
       <c r="C93" s="69"/>
@@ -7386,7 +7397,7 @@
       <c r="AQ93" s="26"/>
       <c r="AR93" s="24"/>
     </row>
-    <row r="94" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="12"/>
       <c r="B94" s="62"/>
       <c r="C94" s="63"/>
@@ -7444,7 +7455,7 @@
       <c r="AQ94" s="26"/>
       <c r="AR94" s="24"/>
     </row>
-    <row r="95" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="12"/>
       <c r="B95" s="73"/>
       <c r="C95" s="74"/>
@@ -7490,7 +7501,7 @@
       <c r="AQ95" s="26"/>
       <c r="AR95" s="24"/>
     </row>
-    <row r="96" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="12"/>
       <c r="B96" s="70"/>
       <c r="C96" s="71"/>
@@ -7548,7 +7559,7 @@
       <c r="AQ96" s="26"/>
       <c r="AR96" s="24"/>
     </row>
-    <row r="97" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="12"/>
       <c r="B97" s="65"/>
       <c r="C97" s="66"/>
@@ -7594,7 +7605,7 @@
       <c r="AQ97" s="26"/>
       <c r="AR97" s="24"/>
     </row>
-    <row r="98" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="12"/>
       <c r="B98" s="35"/>
       <c r="C98" s="35"/>
@@ -7640,7 +7651,7 @@
       <c r="AQ98" s="26"/>
       <c r="AR98" s="24"/>
     </row>
-    <row r="99" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="12"/>
       <c r="B99" s="68"/>
       <c r="C99" s="69"/>
@@ -7658,10 +7669,10 @@
       <c r="O99" s="82"/>
       <c r="P99" s="34"/>
       <c r="Q99" s="44"/>
-      <c r="R99" s="117" t="s">
+      <c r="R99" s="126" t="s">
         <v>110</v>
       </c>
-      <c r="S99" s="118"/>
+      <c r="S99" s="127"/>
       <c r="T99" s="59" t="s">
         <v>111</v>
       </c>
@@ -7670,10 +7681,10 @@
       <c r="W99" s="82"/>
       <c r="X99" s="34"/>
       <c r="Y99" s="32"/>
-      <c r="Z99" s="117" t="s">
+      <c r="Z99" s="126" t="s">
         <v>44</v>
       </c>
-      <c r="AA99" s="118"/>
+      <c r="AA99" s="127"/>
       <c r="AB99" s="59"/>
       <c r="AC99" s="36"/>
       <c r="AD99" s="81"/>
@@ -7692,7 +7703,7 @@
       <c r="AQ99" s="26"/>
       <c r="AR99" s="24"/>
     </row>
-    <row r="100" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12"/>
       <c r="B100" s="73"/>
       <c r="C100" s="74"/>
@@ -7720,11 +7731,11 @@
       <c r="W100" s="84"/>
       <c r="X100" s="85"/>
       <c r="Y100" s="32"/>
-      <c r="Z100" s="159" t="s">
+      <c r="Z100" s="120" t="s">
         <v>86</v>
       </c>
-      <c r="AA100" s="160"/>
-      <c r="AB100" s="161"/>
+      <c r="AA100" s="121"/>
+      <c r="AB100" s="122"/>
       <c r="AC100" s="36"/>
       <c r="AD100" s="83"/>
       <c r="AE100" s="84"/>
@@ -7742,7 +7753,7 @@
       <c r="AQ100" s="26"/>
       <c r="AR100" s="24"/>
     </row>
-    <row r="101" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="12"/>
       <c r="B101" s="70"/>
       <c r="C101" s="71"/>
@@ -7760,21 +7771,21 @@
       <c r="O101" s="71"/>
       <c r="P101" s="72"/>
       <c r="Q101" s="31"/>
-      <c r="R101" s="141" t="s">
+      <c r="R101" s="137" t="s">
         <v>115</v>
       </c>
-      <c r="S101" s="142"/>
-      <c r="T101" s="143"/>
+      <c r="S101" s="138"/>
+      <c r="T101" s="139"/>
       <c r="U101" s="32"/>
       <c r="V101" s="70"/>
       <c r="W101" s="71"/>
       <c r="X101" s="72"/>
       <c r="Y101" s="32"/>
-      <c r="Z101" s="141" t="s">
+      <c r="Z101" s="137" t="s">
         <v>115</v>
       </c>
-      <c r="AA101" s="142"/>
-      <c r="AB101" s="143"/>
+      <c r="AA101" s="138"/>
+      <c r="AB101" s="139"/>
       <c r="AC101" s="31"/>
       <c r="AD101" s="70"/>
       <c r="AE101" s="71"/>
@@ -7792,7 +7803,7 @@
       <c r="AQ101" s="26"/>
       <c r="AR101" s="24"/>
     </row>
-    <row r="102" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="12"/>
       <c r="B102" s="65"/>
       <c r="C102" s="66"/>
@@ -7838,7 +7849,7 @@
       <c r="AQ102" s="26"/>
       <c r="AR102" s="24"/>
     </row>
-    <row r="103" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="12"/>
       <c r="B103" s="40"/>
       <c r="C103" s="33"/>
@@ -7884,7 +7895,7 @@
       <c r="AQ103" s="26"/>
       <c r="AR103" s="26"/>
     </row>
-    <row r="104" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B104" s="33"/>
       <c r="C104" s="33"/>
       <c r="D104" s="33"/>
@@ -7901,7 +7912,7 @@
       <c r="AQ104" s="26"/>
       <c r="AR104" s="26"/>
     </row>
-    <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B105" s="81"/>
       <c r="C105" s="82"/>
       <c r="D105" s="34"/>
@@ -7915,7 +7926,7 @@
       <c r="L105" s="34"/>
       <c r="AO105" s="26"/>
     </row>
-    <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B106" s="106"/>
       <c r="C106" s="107"/>
       <c r="D106" s="108"/>
@@ -7928,7 +7939,7 @@
       <c r="K106" s="107"/>
       <c r="L106" s="108"/>
     </row>
-    <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B107" s="83"/>
       <c r="C107" s="84"/>
       <c r="D107" s="85"/>
@@ -7941,7 +7952,7 @@
       <c r="K107" s="84"/>
       <c r="L107" s="85"/>
     </row>
-    <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B108" s="70"/>
       <c r="C108" s="71"/>
       <c r="D108" s="72"/>
@@ -7954,7 +7965,7 @@
       <c r="K108" s="71"/>
       <c r="L108" s="72"/>
     </row>
-    <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B109" s="65"/>
       <c r="C109" s="66"/>
       <c r="D109" s="67"/>
@@ -7967,7 +7978,7 @@
       <c r="K109" s="66"/>
       <c r="L109" s="67"/>
     </row>
-    <row r="110" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B110" s="35"/>
       <c r="C110" s="35"/>
       <c r="D110" s="35"/>
@@ -7980,7 +7991,7 @@
       <c r="K110" s="35"/>
       <c r="L110" s="35"/>
     </row>
-    <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B111" s="81"/>
       <c r="C111" s="82"/>
       <c r="D111" s="34"/>
@@ -7993,7 +8004,7 @@
       <c r="K111" s="82"/>
       <c r="L111" s="34"/>
     </row>
-    <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" s="106"/>
       <c r="C112" s="107"/>
       <c r="D112" s="108"/>
@@ -8006,7 +8017,7 @@
       <c r="K112" s="107"/>
       <c r="L112" s="108"/>
     </row>
-    <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B113" s="83"/>
       <c r="C113" s="84"/>
       <c r="D113" s="85"/>
@@ -8019,7 +8030,7 @@
       <c r="K113" s="84"/>
       <c r="L113" s="85"/>
     </row>
-    <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B114" s="70"/>
       <c r="C114" s="71"/>
       <c r="D114" s="72"/>
@@ -8032,7 +8043,7 @@
       <c r="K114" s="71"/>
       <c r="L114" s="72"/>
     </row>
-    <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B115" s="65"/>
       <c r="C115" s="66"/>
       <c r="D115" s="67"/>
@@ -8045,7 +8056,7 @@
       <c r="K115" s="66"/>
       <c r="L115" s="67"/>
     </row>
-    <row r="116" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B116" s="35"/>
       <c r="C116" s="35"/>
       <c r="D116" s="35"/>
@@ -8058,7 +8069,7 @@
       <c r="K116" s="35"/>
       <c r="L116" s="35"/>
     </row>
-    <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B117" s="81"/>
       <c r="C117" s="82"/>
       <c r="D117" s="34"/>
@@ -8071,7 +8082,7 @@
       <c r="K117" s="82"/>
       <c r="L117" s="34"/>
     </row>
-    <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B118" s="106"/>
       <c r="C118" s="107"/>
       <c r="D118" s="108"/>
@@ -8084,7 +8095,7 @@
       <c r="K118" s="107"/>
       <c r="L118" s="108"/>
     </row>
-    <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B119" s="83"/>
       <c r="C119" s="84"/>
       <c r="D119" s="85"/>
@@ -8097,7 +8108,7 @@
       <c r="K119" s="84"/>
       <c r="L119" s="85"/>
     </row>
-    <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B120" s="70"/>
       <c r="C120" s="71"/>
       <c r="D120" s="72"/>
@@ -8110,7 +8121,7 @@
       <c r="K120" s="71"/>
       <c r="L120" s="72"/>
     </row>
-    <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B121" s="65"/>
       <c r="C121" s="66"/>
       <c r="D121" s="67"/>
@@ -8123,7 +8134,7 @@
       <c r="K121" s="66"/>
       <c r="L121" s="67"/>
     </row>
-    <row r="122" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B122" s="35"/>
       <c r="C122" s="35"/>
       <c r="D122" s="35"/>
@@ -8136,7 +8147,7 @@
       <c r="K122" s="35"/>
       <c r="L122" s="35"/>
     </row>
-    <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B123" s="81"/>
       <c r="C123" s="82"/>
       <c r="D123" s="34"/>
@@ -8149,7 +8160,7 @@
       <c r="K123" s="82"/>
       <c r="L123" s="34"/>
     </row>
-    <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B124" s="106"/>
       <c r="C124" s="107"/>
       <c r="D124" s="108"/>
@@ -8162,7 +8173,7 @@
       <c r="K124" s="107"/>
       <c r="L124" s="108"/>
     </row>
-    <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B125" s="83"/>
       <c r="C125" s="84"/>
       <c r="D125" s="85"/>
@@ -8175,7 +8186,7 @@
       <c r="K125" s="84"/>
       <c r="L125" s="85"/>
     </row>
-    <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B126" s="70"/>
       <c r="C126" s="71"/>
       <c r="D126" s="72"/>
@@ -8188,7 +8199,7 @@
       <c r="K126" s="71"/>
       <c r="L126" s="72"/>
     </row>
-    <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B127" s="65"/>
       <c r="C127" s="66"/>
       <c r="D127" s="67"/>
@@ -8201,7 +8212,7 @@
       <c r="K127" s="66"/>
       <c r="L127" s="67"/>
     </row>
-    <row r="128" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B128" s="35"/>
       <c r="C128" s="35"/>
       <c r="D128" s="35"/>
@@ -8214,7 +8225,7 @@
       <c r="K128" s="35"/>
       <c r="L128" s="35"/>
     </row>
-    <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B129" s="81"/>
       <c r="C129" s="82"/>
       <c r="D129" s="34"/>
@@ -8227,7 +8238,7 @@
       <c r="K129" s="82"/>
       <c r="L129" s="34"/>
     </row>
-    <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B130" s="106"/>
       <c r="C130" s="107"/>
       <c r="D130" s="108"/>
@@ -8240,7 +8251,7 @@
       <c r="K130" s="107"/>
       <c r="L130" s="108"/>
     </row>
-    <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B131" s="83"/>
       <c r="C131" s="84"/>
       <c r="D131" s="85"/>
@@ -8253,7 +8264,7 @@
       <c r="K131" s="84"/>
       <c r="L131" s="85"/>
     </row>
-    <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B132" s="70"/>
       <c r="C132" s="71"/>
       <c r="D132" s="72"/>
@@ -8266,7 +8277,7 @@
       <c r="K132" s="71"/>
       <c r="L132" s="72"/>
     </row>
-    <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B133" s="65"/>
       <c r="C133" s="66"/>
       <c r="D133" s="67"/>
@@ -8427,9 +8438,6 @@
     <mergeCell ref="J106:L106"/>
     <mergeCell ref="B111:C111"/>
     <mergeCell ref="F111:G111"/>
-    <mergeCell ref="J124:L124"/>
-    <mergeCell ref="F119:H119"/>
-    <mergeCell ref="J119:L119"/>
     <mergeCell ref="J109:L109"/>
     <mergeCell ref="B120:D120"/>
     <mergeCell ref="B121:D121"/>
@@ -8461,6 +8469,9 @@
     <mergeCell ref="B124:D124"/>
     <mergeCell ref="F124:H124"/>
     <mergeCell ref="B117:C117"/>
+    <mergeCell ref="J124:L124"/>
+    <mergeCell ref="F119:H119"/>
+    <mergeCell ref="J119:L119"/>
     <mergeCell ref="Z12:AA12"/>
     <mergeCell ref="B133:D133"/>
     <mergeCell ref="F133:H133"/>

--- a/Gorev-Listesi.xlsx
+++ b/Gorev-Listesi.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="119">
   <si>
     <t>CUMA</t>
   </si>
@@ -1606,6 +1606,39 @@
     <xf numFmtId="49" fontId="11" fillId="4" borderId="13" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="14" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1627,6 +1660,75 @@
     <xf numFmtId="49" fontId="11" fillId="7" borderId="9" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="12" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="13" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="18" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="11" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="12" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="13" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="7" borderId="11" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1636,55 +1738,70 @@
     <xf numFmtId="49" fontId="11" fillId="7" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="14" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="14" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="15" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="16" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="11" xfId="57" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="12" xfId="57" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="13" xfId="57" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="11" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="12" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="13" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="12" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="13" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="9" borderId="17" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1696,29 +1813,14 @@
     <xf numFmtId="49" fontId="7" fillId="9" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="11" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="37" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="12" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="38" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="13" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1729,173 +1831,71 @@
     <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="8" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="9" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="10" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="18" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="14" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="15" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="18" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="11" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="12" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="13" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="8" borderId="8" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="8" borderId="9" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="8" borderId="10" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="11" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="12" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="13" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="37" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="38" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="16" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="18" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="58">
@@ -2346,65 +2346,65 @@
   <sheetData>
     <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12"/>
-      <c r="B1" s="121" t="s">
+      <c r="B1" s="151" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
       <c r="E1" s="10"/>
-      <c r="F1" s="122" t="s">
+      <c r="F1" s="152" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
+      <c r="G1" s="152"/>
+      <c r="H1" s="152"/>
       <c r="I1" s="10"/>
-      <c r="J1" s="122" t="s">
+      <c r="J1" s="152" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="122"/>
-      <c r="L1" s="123"/>
+      <c r="K1" s="152"/>
+      <c r="L1" s="153"/>
       <c r="M1" s="12"/>
-      <c r="N1" s="126" t="s">
+      <c r="N1" s="156" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="150"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="116" t="s">
+      <c r="R1" s="150" t="s">
         <v>4</v>
       </c>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
+      <c r="S1" s="150"/>
+      <c r="T1" s="150"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="116" t="s">
+      <c r="V1" s="150" t="s">
         <v>5</v>
       </c>
-      <c r="W1" s="116"/>
-      <c r="X1" s="116"/>
+      <c r="W1" s="150"/>
+      <c r="X1" s="150"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="116" t="s">
+      <c r="Z1" s="150" t="s">
         <v>6</v>
       </c>
-      <c r="AA1" s="116"/>
-      <c r="AB1" s="116"/>
+      <c r="AA1" s="150"/>
+      <c r="AB1" s="150"/>
       <c r="AC1" s="1"/>
-      <c r="AD1" s="116" t="s">
+      <c r="AD1" s="150" t="s">
         <v>0</v>
       </c>
-      <c r="AE1" s="116"/>
-      <c r="AF1" s="116"/>
+      <c r="AE1" s="150"/>
+      <c r="AF1" s="150"/>
       <c r="AG1" s="1"/>
-      <c r="AH1" s="116" t="s">
+      <c r="AH1" s="150" t="s">
         <v>1</v>
       </c>
-      <c r="AI1" s="116"/>
-      <c r="AJ1" s="116"/>
+      <c r="AI1" s="150"/>
+      <c r="AJ1" s="150"/>
       <c r="AK1" s="1"/>
-      <c r="AL1" s="116" t="s">
+      <c r="AL1" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="AM1" s="116"/>
-      <c r="AN1" s="117"/>
+      <c r="AM1" s="150"/>
+      <c r="AN1" s="160"/>
       <c r="AO1" s="12"/>
       <c r="AP1" s="12"/>
       <c r="AQ1" s="12"/>
@@ -2412,74 +2412,74 @@
     </row>
     <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
-      <c r="B2" s="124">
+      <c r="B2" s="154">
         <f>N2-3</f>
         <v>46283</v>
       </c>
-      <c r="C2" s="125"/>
-      <c r="D2" s="125"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
       <c r="E2" s="11"/>
-      <c r="F2" s="125">
+      <c r="F2" s="155">
         <f>N2-2</f>
         <v>46284</v>
       </c>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
+      <c r="G2" s="155"/>
+      <c r="H2" s="155"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="125">
+      <c r="J2" s="155">
         <f>N2-1</f>
         <v>46285</v>
       </c>
-      <c r="K2" s="125"/>
-      <c r="L2" s="130"/>
+      <c r="K2" s="155"/>
+      <c r="L2" s="158"/>
       <c r="M2" s="12"/>
-      <c r="N2" s="129">
+      <c r="N2" s="157">
         <v>46286</v>
       </c>
-      <c r="O2" s="118"/>
-      <c r="P2" s="118"/>
+      <c r="O2" s="146"/>
+      <c r="P2" s="146"/>
       <c r="Q2" s="53"/>
-      <c r="R2" s="118">
+      <c r="R2" s="146">
         <f>N2+1</f>
         <v>46287</v>
       </c>
-      <c r="S2" s="118"/>
-      <c r="T2" s="118"/>
+      <c r="S2" s="146"/>
+      <c r="T2" s="146"/>
       <c r="U2" s="53"/>
-      <c r="V2" s="118">
+      <c r="V2" s="146">
         <f>N2+2</f>
         <v>46288</v>
       </c>
-      <c r="W2" s="118"/>
-      <c r="X2" s="118"/>
+      <c r="W2" s="146"/>
+      <c r="X2" s="146"/>
       <c r="Y2" s="53"/>
-      <c r="Z2" s="118">
+      <c r="Z2" s="146">
         <f>N2+3</f>
         <v>46289</v>
       </c>
-      <c r="AA2" s="118"/>
-      <c r="AB2" s="118"/>
+      <c r="AA2" s="146"/>
+      <c r="AB2" s="146"/>
       <c r="AC2" s="53"/>
-      <c r="AD2" s="118">
+      <c r="AD2" s="146">
         <f>N2+4</f>
         <v>46290</v>
       </c>
-      <c r="AE2" s="118"/>
-      <c r="AF2" s="118"/>
+      <c r="AE2" s="146"/>
+      <c r="AF2" s="146"/>
       <c r="AG2" s="53"/>
-      <c r="AH2" s="118">
+      <c r="AH2" s="146">
         <f>N2+5</f>
         <v>46291</v>
       </c>
-      <c r="AI2" s="118"/>
-      <c r="AJ2" s="118"/>
+      <c r="AI2" s="146"/>
+      <c r="AJ2" s="146"/>
       <c r="AK2" s="53"/>
-      <c r="AL2" s="118">
+      <c r="AL2" s="146">
         <f>N2+6</f>
         <v>46292</v>
       </c>
-      <c r="AM2" s="118"/>
-      <c r="AN2" s="119"/>
+      <c r="AM2" s="146"/>
+      <c r="AN2" s="161"/>
       <c r="AO2" s="12"/>
       <c r="AP2" s="12"/>
       <c r="AQ2" s="12"/>
@@ -2533,47 +2533,47 @@
     </row>
     <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="12"/>
-      <c r="B4" s="120"/>
-      <c r="C4" s="120"/>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="120"/>
-      <c r="L4" s="120"/>
+      <c r="B4" s="159"/>
+      <c r="C4" s="159"/>
+      <c r="D4" s="159"/>
+      <c r="E4" s="159"/>
+      <c r="F4" s="159"/>
+      <c r="G4" s="159"/>
+      <c r="H4" s="159"/>
+      <c r="I4" s="159"/>
+      <c r="J4" s="159"/>
+      <c r="K4" s="159"/>
+      <c r="L4" s="159"/>
       <c r="M4" s="14"/>
-      <c r="N4" s="115" t="s">
+      <c r="N4" s="136" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="115"/>
-      <c r="P4" s="115"/>
-      <c r="Q4" s="115"/>
-      <c r="R4" s="115"/>
-      <c r="S4" s="115"/>
-      <c r="T4" s="115"/>
-      <c r="U4" s="115"/>
-      <c r="V4" s="115"/>
-      <c r="W4" s="115"/>
-      <c r="X4" s="115"/>
-      <c r="Y4" s="115"/>
-      <c r="Z4" s="115"/>
-      <c r="AA4" s="115"/>
-      <c r="AB4" s="115"/>
+      <c r="O4" s="136"/>
+      <c r="P4" s="136"/>
+      <c r="Q4" s="136"/>
+      <c r="R4" s="136"/>
+      <c r="S4" s="136"/>
+      <c r="T4" s="136"/>
+      <c r="U4" s="136"/>
+      <c r="V4" s="136"/>
+      <c r="W4" s="136"/>
+      <c r="X4" s="136"/>
+      <c r="Y4" s="136"/>
+      <c r="Z4" s="136"/>
+      <c r="AA4" s="136"/>
+      <c r="AB4" s="136"/>
       <c r="AC4" s="33"/>
-      <c r="AD4" s="120"/>
-      <c r="AE4" s="120"/>
-      <c r="AF4" s="120"/>
-      <c r="AG4" s="120"/>
-      <c r="AH4" s="120"/>
-      <c r="AI4" s="120"/>
-      <c r="AJ4" s="120"/>
-      <c r="AK4" s="120"/>
-      <c r="AL4" s="120"/>
-      <c r="AM4" s="120"/>
-      <c r="AN4" s="120"/>
+      <c r="AD4" s="159"/>
+      <c r="AE4" s="159"/>
+      <c r="AF4" s="159"/>
+      <c r="AG4" s="159"/>
+      <c r="AH4" s="159"/>
+      <c r="AI4" s="159"/>
+      <c r="AJ4" s="159"/>
+      <c r="AK4" s="159"/>
+      <c r="AL4" s="159"/>
+      <c r="AM4" s="159"/>
+      <c r="AN4" s="159"/>
       <c r="AO4" s="12"/>
       <c r="AP4" s="12"/>
       <c r="AQ4" s="12"/>
@@ -2581,111 +2581,111 @@
     </row>
     <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12"/>
-      <c r="B5" s="120"/>
-      <c r="C5" s="120"/>
-      <c r="D5" s="120"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="120"/>
-      <c r="G5" s="120"/>
-      <c r="H5" s="120"/>
-      <c r="I5" s="120"/>
-      <c r="J5" s="120"/>
-      <c r="K5" s="120"/>
-      <c r="L5" s="120"/>
+      <c r="B5" s="159"/>
+      <c r="C5" s="159"/>
+      <c r="D5" s="159"/>
+      <c r="E5" s="159"/>
+      <c r="F5" s="159"/>
+      <c r="G5" s="159"/>
+      <c r="H5" s="159"/>
+      <c r="I5" s="159"/>
+      <c r="J5" s="159"/>
+      <c r="K5" s="159"/>
+      <c r="L5" s="159"/>
       <c r="M5" s="14"/>
-      <c r="N5" s="115"/>
-      <c r="O5" s="115"/>
-      <c r="P5" s="115"/>
-      <c r="Q5" s="115"/>
-      <c r="R5" s="115"/>
-      <c r="S5" s="115"/>
-      <c r="T5" s="115"/>
-      <c r="U5" s="115"/>
-      <c r="V5" s="115"/>
-      <c r="W5" s="115"/>
-      <c r="X5" s="115"/>
-      <c r="Y5" s="115"/>
-      <c r="Z5" s="115"/>
-      <c r="AA5" s="115"/>
-      <c r="AB5" s="115"/>
+      <c r="N5" s="136"/>
+      <c r="O5" s="136"/>
+      <c r="P5" s="136"/>
+      <c r="Q5" s="136"/>
+      <c r="R5" s="136"/>
+      <c r="S5" s="136"/>
+      <c r="T5" s="136"/>
+      <c r="U5" s="136"/>
+      <c r="V5" s="136"/>
+      <c r="W5" s="136"/>
+      <c r="X5" s="136"/>
+      <c r="Y5" s="136"/>
+      <c r="Z5" s="136"/>
+      <c r="AA5" s="136"/>
+      <c r="AB5" s="136"/>
       <c r="AC5" s="33"/>
-      <c r="AD5" s="120"/>
-      <c r="AE5" s="120"/>
-      <c r="AF5" s="120"/>
-      <c r="AG5" s="120"/>
-      <c r="AH5" s="120"/>
-      <c r="AI5" s="120"/>
-      <c r="AJ5" s="120"/>
-      <c r="AK5" s="120"/>
-      <c r="AL5" s="120"/>
-      <c r="AM5" s="120"/>
-      <c r="AN5" s="120"/>
+      <c r="AD5" s="159"/>
+      <c r="AE5" s="159"/>
+      <c r="AF5" s="159"/>
+      <c r="AG5" s="159"/>
+      <c r="AH5" s="159"/>
+      <c r="AI5" s="159"/>
+      <c r="AJ5" s="159"/>
+      <c r="AK5" s="159"/>
+      <c r="AL5" s="159"/>
+      <c r="AM5" s="159"/>
+      <c r="AN5" s="159"/>
       <c r="AO5" s="12"/>
       <c r="AP5" s="12"/>
       <c r="AQ5" s="12"/>
       <c r="AR5" s="13"/>
     </row>
     <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="65" t="s">
+      <c r="B6" s="76" t="s">
         <v>57</v>
       </c>
-      <c r="C6" s="66"/>
+      <c r="C6" s="77"/>
       <c r="D6" s="57" t="s">
         <v>55</v>
       </c>
       <c r="E6" s="39"/>
-      <c r="F6" s="98" t="s">
+      <c r="F6" s="126" t="s">
         <v>57</v>
       </c>
-      <c r="G6" s="99"/>
+      <c r="G6" s="127"/>
       <c r="H6" s="59" t="s">
         <v>55</v>
       </c>
       <c r="I6" s="36"/>
-      <c r="J6" s="98" t="s">
+      <c r="J6" s="126" t="s">
         <v>57</v>
       </c>
-      <c r="K6" s="99"/>
+      <c r="K6" s="127"/>
       <c r="L6" s="59" t="s">
         <v>55</v>
       </c>
       <c r="M6" s="3"/>
-      <c r="N6" s="70"/>
-      <c r="O6" s="71"/>
+      <c r="N6" s="81"/>
+      <c r="O6" s="82"/>
       <c r="P6" s="34"/>
       <c r="Q6" s="39"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="71"/>
+      <c r="R6" s="81"/>
+      <c r="S6" s="82"/>
       <c r="T6" s="34"/>
       <c r="U6" s="36"/>
-      <c r="V6" s="70"/>
-      <c r="W6" s="71"/>
+      <c r="V6" s="81"/>
+      <c r="W6" s="82"/>
       <c r="X6" s="34"/>
       <c r="Y6" s="23"/>
-      <c r="Z6" s="70" t="s">
+      <c r="Z6" s="81" t="s">
         <v>44</v>
       </c>
-      <c r="AA6" s="71"/>
+      <c r="AA6" s="82"/>
       <c r="AB6" s="34" t="s">
         <v>85</v>
       </c>
       <c r="AC6" s="36"/>
-      <c r="AD6" s="70"/>
-      <c r="AE6" s="71"/>
+      <c r="AD6" s="81"/>
+      <c r="AE6" s="82"/>
       <c r="AF6" s="34"/>
       <c r="AG6" s="39"/>
-      <c r="AH6" s="70" t="s">
+      <c r="AH6" s="81" t="s">
         <v>57</v>
       </c>
-      <c r="AI6" s="71"/>
+      <c r="AI6" s="82"/>
       <c r="AJ6" s="34" t="s">
         <v>55</v>
       </c>
       <c r="AK6" s="36"/>
-      <c r="AL6" s="70" t="s">
+      <c r="AL6" s="81" t="s">
         <v>57</v>
       </c>
-      <c r="AM6" s="71"/>
+      <c r="AM6" s="82"/>
       <c r="AN6" s="34" t="s">
         <v>55</v>
       </c>
@@ -2699,50 +2699,50 @@
       <c r="AR6" s="30"/>
     </row>
     <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="78"/>
-      <c r="C7" s="79"/>
+      <c r="B7" s="73"/>
+      <c r="C7" s="74"/>
       <c r="D7" s="61"/>
       <c r="E7" s="38"/>
-      <c r="F7" s="127" t="s">
+      <c r="F7" s="114" t="s">
         <v>86</v>
       </c>
-      <c r="G7" s="128"/>
+      <c r="G7" s="115"/>
       <c r="H7" s="60"/>
       <c r="I7" s="36"/>
-      <c r="J7" s="127" t="s">
+      <c r="J7" s="114" t="s">
         <v>86</v>
       </c>
-      <c r="K7" s="128"/>
+      <c r="K7" s="115"/>
       <c r="L7" s="60"/>
       <c r="M7" s="3"/>
-      <c r="N7" s="75"/>
-      <c r="O7" s="76"/>
+      <c r="N7" s="83"/>
+      <c r="O7" s="84"/>
       <c r="P7" s="18"/>
       <c r="Q7" s="36"/>
-      <c r="R7" s="75"/>
-      <c r="S7" s="76"/>
+      <c r="R7" s="83"/>
+      <c r="S7" s="84"/>
       <c r="T7" s="18"/>
       <c r="U7" s="36"/>
-      <c r="V7" s="75"/>
-      <c r="W7" s="76"/>
+      <c r="V7" s="83"/>
+      <c r="W7" s="84"/>
       <c r="X7" s="18"/>
       <c r="Y7" s="36"/>
-      <c r="Z7" s="75" t="s">
+      <c r="Z7" s="83" t="s">
         <v>84</v>
       </c>
-      <c r="AA7" s="76"/>
+      <c r="AA7" s="84"/>
       <c r="AB7" s="18"/>
       <c r="AC7" s="36"/>
-      <c r="AD7" s="75"/>
-      <c r="AE7" s="76"/>
+      <c r="AD7" s="83"/>
+      <c r="AE7" s="84"/>
       <c r="AF7" s="18"/>
       <c r="AG7" s="38"/>
-      <c r="AH7" s="75"/>
-      <c r="AI7" s="76"/>
+      <c r="AH7" s="83"/>
+      <c r="AI7" s="84"/>
       <c r="AJ7" s="18"/>
       <c r="AK7" s="36"/>
-      <c r="AL7" s="75"/>
-      <c r="AM7" s="76"/>
+      <c r="AL7" s="83"/>
+      <c r="AM7" s="84"/>
       <c r="AN7" s="18"/>
       <c r="AP7" s="46" t="s">
         <v>9</v>
@@ -2754,57 +2754,57 @@
       <c r="AR7" s="30"/>
     </row>
     <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="67" t="s">
+      <c r="B8" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="69"/>
+      <c r="C8" s="79"/>
+      <c r="D8" s="80"/>
       <c r="E8" s="35"/>
-      <c r="F8" s="103" t="s">
+      <c r="F8" s="137" t="s">
         <v>87</v>
       </c>
-      <c r="G8" s="104"/>
-      <c r="H8" s="105"/>
+      <c r="G8" s="138"/>
+      <c r="H8" s="139"/>
       <c r="I8" s="37"/>
-      <c r="J8" s="103" t="s">
+      <c r="J8" s="137" t="s">
         <v>109</v>
       </c>
-      <c r="K8" s="104"/>
-      <c r="L8" s="105"/>
+      <c r="K8" s="138"/>
+      <c r="L8" s="139"/>
       <c r="M8" s="3"/>
-      <c r="N8" s="89"/>
-      <c r="O8" s="90"/>
-      <c r="P8" s="91"/>
+      <c r="N8" s="70"/>
+      <c r="O8" s="71"/>
+      <c r="P8" s="72"/>
       <c r="Q8" s="35"/>
-      <c r="R8" s="89"/>
-      <c r="S8" s="90"/>
-      <c r="T8" s="91"/>
+      <c r="R8" s="70"/>
+      <c r="S8" s="71"/>
+      <c r="T8" s="72"/>
       <c r="U8" s="37"/>
-      <c r="V8" s="89"/>
-      <c r="W8" s="90"/>
-      <c r="X8" s="91"/>
+      <c r="V8" s="70"/>
+      <c r="W8" s="71"/>
+      <c r="X8" s="72"/>
       <c r="Y8" s="35"/>
-      <c r="Z8" s="89" t="s">
+      <c r="Z8" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="AA8" s="90"/>
-      <c r="AB8" s="91"/>
+      <c r="AA8" s="71"/>
+      <c r="AB8" s="72"/>
       <c r="AC8" s="35"/>
-      <c r="AD8" s="89"/>
-      <c r="AE8" s="90"/>
-      <c r="AF8" s="91"/>
+      <c r="AD8" s="70"/>
+      <c r="AE8" s="71"/>
+      <c r="AF8" s="72"/>
       <c r="AG8" s="35"/>
-      <c r="AH8" s="89" t="s">
+      <c r="AH8" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="AI8" s="90"/>
-      <c r="AJ8" s="91"/>
+      <c r="AI8" s="71"/>
+      <c r="AJ8" s="72"/>
       <c r="AK8" s="37"/>
-      <c r="AL8" s="89" t="s">
+      <c r="AL8" s="70" t="s">
         <v>37</v>
       </c>
-      <c r="AM8" s="90"/>
-      <c r="AN8" s="91"/>
+      <c r="AM8" s="71"/>
+      <c r="AN8" s="72"/>
       <c r="AP8" s="46" t="s">
         <v>16</v>
       </c>
@@ -2815,51 +2815,51 @@
       <c r="AR8" s="30"/>
     </row>
     <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="67"/>
-      <c r="C9" s="68"/>
-      <c r="D9" s="69"/>
+      <c r="B9" s="78"/>
+      <c r="C9" s="79"/>
+      <c r="D9" s="80"/>
       <c r="E9" s="43"/>
-      <c r="F9" s="137"/>
-      <c r="G9" s="138"/>
-      <c r="H9" s="139"/>
+      <c r="F9" s="143"/>
+      <c r="G9" s="144"/>
+      <c r="H9" s="145"/>
       <c r="I9" s="43"/>
-      <c r="J9" s="134" t="s">
+      <c r="J9" s="117" t="s">
         <v>79</v>
       </c>
-      <c r="K9" s="135"/>
-      <c r="L9" s="136"/>
+      <c r="K9" s="118"/>
+      <c r="L9" s="119"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="67"/>
-      <c r="O9" s="68"/>
-      <c r="P9" s="69"/>
+      <c r="N9" s="78"/>
+      <c r="O9" s="79"/>
+      <c r="P9" s="80"/>
       <c r="Q9" s="43"/>
-      <c r="R9" s="67"/>
-      <c r="S9" s="68"/>
-      <c r="T9" s="69"/>
+      <c r="R9" s="78"/>
+      <c r="S9" s="79"/>
+      <c r="T9" s="80"/>
       <c r="U9" s="44"/>
-      <c r="V9" s="67"/>
-      <c r="W9" s="68"/>
-      <c r="X9" s="69"/>
+      <c r="V9" s="78"/>
+      <c r="W9" s="79"/>
+      <c r="X9" s="80"/>
       <c r="Y9" s="43"/>
-      <c r="Z9" s="67"/>
-      <c r="AA9" s="68"/>
-      <c r="AB9" s="69"/>
+      <c r="Z9" s="78"/>
+      <c r="AA9" s="79"/>
+      <c r="AB9" s="80"/>
       <c r="AC9" s="43"/>
-      <c r="AD9" s="67"/>
-      <c r="AE9" s="68"/>
-      <c r="AF9" s="69"/>
+      <c r="AD9" s="78"/>
+      <c r="AE9" s="79"/>
+      <c r="AF9" s="80"/>
       <c r="AG9" s="43"/>
-      <c r="AH9" s="67" t="s">
+      <c r="AH9" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="AI9" s="68"/>
-      <c r="AJ9" s="69"/>
+      <c r="AI9" s="79"/>
+      <c r="AJ9" s="80"/>
       <c r="AK9" s="43"/>
-      <c r="AL9" s="67" t="s">
+      <c r="AL9" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="AM9" s="68"/>
-      <c r="AN9" s="69"/>
+      <c r="AM9" s="79"/>
+      <c r="AN9" s="80"/>
       <c r="AP9" s="46" t="s">
         <v>11</v>
       </c>
@@ -2870,47 +2870,47 @@
       <c r="AR9" s="30"/>
     </row>
     <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="106"/>
-      <c r="C10" s="107"/>
-      <c r="D10" s="108"/>
+      <c r="B10" s="92"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="94"/>
       <c r="E10" s="44"/>
-      <c r="F10" s="92"/>
-      <c r="G10" s="93"/>
-      <c r="H10" s="94"/>
+      <c r="F10" s="131"/>
+      <c r="G10" s="132"/>
+      <c r="H10" s="133"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="131" t="s">
+      <c r="J10" s="147" t="s">
         <v>88</v>
       </c>
-      <c r="K10" s="132"/>
-      <c r="L10" s="133"/>
+      <c r="K10" s="148"/>
+      <c r="L10" s="149"/>
       <c r="M10" s="5"/>
-      <c r="N10" s="106"/>
-      <c r="O10" s="107"/>
-      <c r="P10" s="108"/>
+      <c r="N10" s="92"/>
+      <c r="O10" s="93"/>
+      <c r="P10" s="94"/>
       <c r="Q10" s="44"/>
-      <c r="R10" s="106"/>
-      <c r="S10" s="107"/>
-      <c r="T10" s="108"/>
+      <c r="R10" s="92"/>
+      <c r="S10" s="93"/>
+      <c r="T10" s="94"/>
       <c r="U10" s="44"/>
-      <c r="V10" s="106"/>
-      <c r="W10" s="107"/>
-      <c r="X10" s="108"/>
+      <c r="V10" s="92"/>
+      <c r="W10" s="93"/>
+      <c r="X10" s="94"/>
       <c r="Y10" s="44"/>
-      <c r="Z10" s="106"/>
-      <c r="AA10" s="107"/>
-      <c r="AB10" s="108"/>
+      <c r="Z10" s="92"/>
+      <c r="AA10" s="93"/>
+      <c r="AB10" s="94"/>
       <c r="AC10" s="44"/>
-      <c r="AD10" s="106"/>
-      <c r="AE10" s="107"/>
-      <c r="AF10" s="108"/>
+      <c r="AD10" s="92"/>
+      <c r="AE10" s="93"/>
+      <c r="AF10" s="94"/>
       <c r="AG10" s="44"/>
-      <c r="AH10" s="106"/>
-      <c r="AI10" s="107"/>
-      <c r="AJ10" s="108"/>
+      <c r="AH10" s="92"/>
+      <c r="AI10" s="93"/>
+      <c r="AJ10" s="94"/>
       <c r="AK10" s="44"/>
-      <c r="AL10" s="106"/>
-      <c r="AM10" s="107"/>
-      <c r="AN10" s="108"/>
+      <c r="AL10" s="92"/>
+      <c r="AM10" s="93"/>
+      <c r="AN10" s="94"/>
       <c r="AP10" s="46" t="s">
         <v>8</v>
       </c>
@@ -2970,52 +2970,52 @@
       <c r="AR11" s="30"/>
     </row>
     <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="81"/>
-      <c r="C12" s="82"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="69"/>
       <c r="D12" s="55"/>
       <c r="E12" s="39"/>
-      <c r="F12" s="81" t="s">
+      <c r="F12" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="82"/>
+      <c r="G12" s="69"/>
       <c r="H12" s="55" t="s">
         <v>48</v>
       </c>
       <c r="I12" s="36"/>
-      <c r="J12" s="81"/>
-      <c r="K12" s="82"/>
+      <c r="J12" s="68"/>
+      <c r="K12" s="69"/>
       <c r="L12" s="55"/>
       <c r="M12" s="5"/>
-      <c r="N12" s="70"/>
-      <c r="O12" s="71"/>
+      <c r="N12" s="81"/>
+      <c r="O12" s="82"/>
       <c r="P12" s="34"/>
       <c r="Q12" s="23"/>
-      <c r="R12" s="70"/>
-      <c r="S12" s="71"/>
+      <c r="R12" s="81"/>
+      <c r="S12" s="82"/>
       <c r="T12" s="34"/>
       <c r="U12" s="36"/>
-      <c r="V12" s="70"/>
-      <c r="W12" s="71"/>
+      <c r="V12" s="81"/>
+      <c r="W12" s="82"/>
       <c r="X12" s="34"/>
       <c r="Y12" s="23"/>
-      <c r="Z12" s="70"/>
-      <c r="AA12" s="71"/>
+      <c r="Z12" s="81"/>
+      <c r="AA12" s="82"/>
       <c r="AB12" s="34"/>
       <c r="AC12" s="36"/>
-      <c r="AD12" s="70"/>
-      <c r="AE12" s="71"/>
+      <c r="AD12" s="81"/>
+      <c r="AE12" s="82"/>
       <c r="AF12" s="34"/>
       <c r="AG12" s="39"/>
-      <c r="AH12" s="70" t="s">
+      <c r="AH12" s="81" t="s">
         <v>41</v>
       </c>
-      <c r="AI12" s="71"/>
+      <c r="AI12" s="82"/>
       <c r="AJ12" s="34" t="s">
         <v>48</v>
       </c>
       <c r="AK12" s="36"/>
-      <c r="AL12" s="70"/>
-      <c r="AM12" s="71"/>
+      <c r="AL12" s="81"/>
+      <c r="AM12" s="82"/>
       <c r="AN12" s="34"/>
       <c r="AP12" s="46" t="s">
         <v>19</v>
@@ -3027,44 +3027,44 @@
       <c r="AR12" s="30"/>
     </row>
     <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="78"/>
-      <c r="C13" s="79"/>
+      <c r="B13" s="73"/>
+      <c r="C13" s="74"/>
       <c r="D13" s="61"/>
       <c r="E13" s="38"/>
-      <c r="F13" s="78"/>
-      <c r="G13" s="79"/>
+      <c r="F13" s="73"/>
+      <c r="G13" s="74"/>
       <c r="H13" s="61"/>
       <c r="I13" s="36"/>
-      <c r="J13" s="78"/>
-      <c r="K13" s="79"/>
+      <c r="J13" s="73"/>
+      <c r="K13" s="74"/>
       <c r="L13" s="61"/>
       <c r="M13" s="5"/>
-      <c r="N13" s="75"/>
-      <c r="O13" s="76"/>
+      <c r="N13" s="83"/>
+      <c r="O13" s="84"/>
       <c r="P13" s="18"/>
       <c r="Q13" s="36"/>
-      <c r="R13" s="75"/>
-      <c r="S13" s="76"/>
+      <c r="R13" s="83"/>
+      <c r="S13" s="84"/>
       <c r="T13" s="18"/>
       <c r="U13" s="36"/>
-      <c r="V13" s="75"/>
-      <c r="W13" s="76"/>
+      <c r="V13" s="83"/>
+      <c r="W13" s="84"/>
       <c r="X13" s="18"/>
       <c r="Y13" s="36"/>
-      <c r="Z13" s="75"/>
-      <c r="AA13" s="76"/>
+      <c r="Z13" s="83"/>
+      <c r="AA13" s="84"/>
       <c r="AB13" s="18"/>
       <c r="AC13" s="36"/>
-      <c r="AD13" s="75"/>
-      <c r="AE13" s="76"/>
+      <c r="AD13" s="83"/>
+      <c r="AE13" s="84"/>
       <c r="AF13" s="18"/>
       <c r="AG13" s="38"/>
-      <c r="AH13" s="75"/>
-      <c r="AI13" s="76"/>
+      <c r="AH13" s="83"/>
+      <c r="AI13" s="84"/>
       <c r="AJ13" s="18"/>
       <c r="AK13" s="36"/>
-      <c r="AL13" s="75"/>
-      <c r="AM13" s="76"/>
+      <c r="AL13" s="83"/>
+      <c r="AM13" s="84"/>
       <c r="AN13" s="18"/>
       <c r="AP13" s="46" t="s">
         <v>22</v>
@@ -3076,49 +3076,49 @@
       <c r="AR13" s="30"/>
     </row>
     <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="89"/>
-      <c r="C14" s="90"/>
-      <c r="D14" s="91"/>
+      <c r="B14" s="70"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="72"/>
       <c r="E14" s="37"/>
-      <c r="F14" s="89" t="s">
+      <c r="F14" s="70" t="s">
         <v>37</v>
       </c>
-      <c r="G14" s="90"/>
-      <c r="H14" s="91"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="72"/>
       <c r="I14" s="35"/>
-      <c r="J14" s="89"/>
-      <c r="K14" s="90"/>
-      <c r="L14" s="91"/>
+      <c r="J14" s="70"/>
+      <c r="K14" s="71"/>
+      <c r="L14" s="72"/>
       <c r="M14" s="3"/>
-      <c r="N14" s="89"/>
-      <c r="O14" s="90"/>
-      <c r="P14" s="91"/>
+      <c r="N14" s="70"/>
+      <c r="O14" s="71"/>
+      <c r="P14" s="72"/>
       <c r="Q14" s="35"/>
-      <c r="R14" s="89"/>
-      <c r="S14" s="90"/>
-      <c r="T14" s="91"/>
+      <c r="R14" s="70"/>
+      <c r="S14" s="71"/>
+      <c r="T14" s="72"/>
       <c r="U14" s="37"/>
-      <c r="V14" s="89"/>
-      <c r="W14" s="90"/>
-      <c r="X14" s="91"/>
+      <c r="V14" s="70"/>
+      <c r="W14" s="71"/>
+      <c r="X14" s="72"/>
       <c r="Y14" s="35"/>
-      <c r="Z14" s="89"/>
-      <c r="AA14" s="90"/>
-      <c r="AB14" s="91"/>
+      <c r="Z14" s="70"/>
+      <c r="AA14" s="71"/>
+      <c r="AB14" s="72"/>
       <c r="AC14" s="37"/>
-      <c r="AD14" s="89"/>
-      <c r="AE14" s="90"/>
-      <c r="AF14" s="91"/>
+      <c r="AD14" s="70"/>
+      <c r="AE14" s="71"/>
+      <c r="AF14" s="72"/>
       <c r="AG14" s="37"/>
-      <c r="AH14" s="89" t="s">
+      <c r="AH14" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="AI14" s="90"/>
-      <c r="AJ14" s="91"/>
+      <c r="AI14" s="71"/>
+      <c r="AJ14" s="72"/>
       <c r="AK14" s="35"/>
-      <c r="AL14" s="89"/>
-      <c r="AM14" s="90"/>
-      <c r="AN14" s="91"/>
+      <c r="AL14" s="70"/>
+      <c r="AM14" s="71"/>
+      <c r="AN14" s="72"/>
       <c r="AP14" s="46" t="s">
         <v>23</v>
       </c>
@@ -3129,49 +3129,49 @@
       <c r="AR14" s="30"/>
     </row>
     <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="67"/>
-      <c r="C15" s="68"/>
-      <c r="D15" s="69"/>
+      <c r="B15" s="78"/>
+      <c r="C15" s="79"/>
+      <c r="D15" s="80"/>
       <c r="E15" s="44"/>
-      <c r="F15" s="67" t="s">
+      <c r="F15" s="78" t="s">
         <v>29</v>
       </c>
-      <c r="G15" s="68"/>
-      <c r="H15" s="69"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="80"/>
       <c r="I15" s="43"/>
-      <c r="J15" s="67"/>
-      <c r="K15" s="68"/>
-      <c r="L15" s="69"/>
+      <c r="J15" s="78"/>
+      <c r="K15" s="79"/>
+      <c r="L15" s="80"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="67"/>
-      <c r="O15" s="68"/>
-      <c r="P15" s="69"/>
+      <c r="N15" s="78"/>
+      <c r="O15" s="79"/>
+      <c r="P15" s="80"/>
       <c r="Q15" s="43"/>
-      <c r="R15" s="67"/>
-      <c r="S15" s="68"/>
-      <c r="T15" s="69"/>
+      <c r="R15" s="78"/>
+      <c r="S15" s="79"/>
+      <c r="T15" s="80"/>
       <c r="U15" s="44"/>
-      <c r="V15" s="67"/>
-      <c r="W15" s="68"/>
-      <c r="X15" s="69"/>
+      <c r="V15" s="78"/>
+      <c r="W15" s="79"/>
+      <c r="X15" s="80"/>
       <c r="Y15" s="43"/>
-      <c r="Z15" s="67"/>
-      <c r="AA15" s="68"/>
-      <c r="AB15" s="69"/>
+      <c r="Z15" s="78"/>
+      <c r="AA15" s="79"/>
+      <c r="AB15" s="80"/>
       <c r="AC15" s="43"/>
-      <c r="AD15" s="67"/>
-      <c r="AE15" s="68"/>
-      <c r="AF15" s="69"/>
+      <c r="AD15" s="78"/>
+      <c r="AE15" s="79"/>
+      <c r="AF15" s="80"/>
       <c r="AG15" s="44"/>
-      <c r="AH15" s="67" t="s">
+      <c r="AH15" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="AI15" s="68"/>
-      <c r="AJ15" s="69"/>
+      <c r="AI15" s="79"/>
+      <c r="AJ15" s="80"/>
       <c r="AK15" s="43"/>
-      <c r="AL15" s="67"/>
-      <c r="AM15" s="68"/>
-      <c r="AN15" s="69"/>
+      <c r="AL15" s="78"/>
+      <c r="AM15" s="79"/>
+      <c r="AN15" s="80"/>
       <c r="AP15" s="46" t="s">
         <v>18</v>
       </c>
@@ -3182,45 +3182,45 @@
       <c r="AR15" s="30"/>
     </row>
     <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="106"/>
-      <c r="C16" s="107"/>
-      <c r="D16" s="108"/>
+      <c r="B16" s="92"/>
+      <c r="C16" s="93"/>
+      <c r="D16" s="94"/>
       <c r="E16" s="44"/>
-      <c r="F16" s="106"/>
-      <c r="G16" s="107"/>
-      <c r="H16" s="108"/>
+      <c r="F16" s="92"/>
+      <c r="G16" s="93"/>
+      <c r="H16" s="94"/>
       <c r="I16" s="44"/>
-      <c r="J16" s="106"/>
-      <c r="K16" s="107"/>
-      <c r="L16" s="108"/>
+      <c r="J16" s="92"/>
+      <c r="K16" s="93"/>
+      <c r="L16" s="94"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="106"/>
-      <c r="O16" s="107"/>
-      <c r="P16" s="108"/>
+      <c r="N16" s="92"/>
+      <c r="O16" s="93"/>
+      <c r="P16" s="94"/>
       <c r="Q16" s="44"/>
-      <c r="R16" s="106"/>
-      <c r="S16" s="107"/>
-      <c r="T16" s="108"/>
+      <c r="R16" s="92"/>
+      <c r="S16" s="93"/>
+      <c r="T16" s="94"/>
       <c r="U16" s="44"/>
-      <c r="V16" s="106"/>
-      <c r="W16" s="107"/>
-      <c r="X16" s="108"/>
+      <c r="V16" s="92"/>
+      <c r="W16" s="93"/>
+      <c r="X16" s="94"/>
       <c r="Y16" s="44"/>
-      <c r="Z16" s="106"/>
-      <c r="AA16" s="107"/>
-      <c r="AB16" s="108"/>
+      <c r="Z16" s="92"/>
+      <c r="AA16" s="93"/>
+      <c r="AB16" s="94"/>
       <c r="AC16" s="44"/>
-      <c r="AD16" s="106"/>
-      <c r="AE16" s="107"/>
-      <c r="AF16" s="108"/>
+      <c r="AD16" s="92"/>
+      <c r="AE16" s="93"/>
+      <c r="AF16" s="94"/>
       <c r="AG16" s="44"/>
-      <c r="AH16" s="106"/>
-      <c r="AI16" s="107"/>
-      <c r="AJ16" s="108"/>
+      <c r="AH16" s="92"/>
+      <c r="AI16" s="93"/>
+      <c r="AJ16" s="94"/>
       <c r="AK16" s="44"/>
-      <c r="AL16" s="106"/>
-      <c r="AM16" s="107"/>
-      <c r="AN16" s="108"/>
+      <c r="AL16" s="92"/>
+      <c r="AM16" s="93"/>
+      <c r="AN16" s="94"/>
       <c r="AP16" s="46" t="s">
         <v>24</v>
       </c>
@@ -3292,23 +3292,23 @@
       <c r="K18" s="33"/>
       <c r="L18" s="33"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="115" t="s">
+      <c r="N18" s="136" t="s">
         <v>49</v>
       </c>
-      <c r="O18" s="115"/>
-      <c r="P18" s="115"/>
-      <c r="Q18" s="115"/>
-      <c r="R18" s="115"/>
-      <c r="S18" s="115"/>
-      <c r="T18" s="115"/>
-      <c r="U18" s="115"/>
-      <c r="V18" s="115"/>
-      <c r="W18" s="115"/>
-      <c r="X18" s="115"/>
-      <c r="Y18" s="115"/>
-      <c r="Z18" s="115"/>
-      <c r="AA18" s="115"/>
-      <c r="AB18" s="115"/>
+      <c r="O18" s="136"/>
+      <c r="P18" s="136"/>
+      <c r="Q18" s="136"/>
+      <c r="R18" s="136"/>
+      <c r="S18" s="136"/>
+      <c r="T18" s="136"/>
+      <c r="U18" s="136"/>
+      <c r="V18" s="136"/>
+      <c r="W18" s="136"/>
+      <c r="X18" s="136"/>
+      <c r="Y18" s="136"/>
+      <c r="Z18" s="136"/>
+      <c r="AA18" s="136"/>
+      <c r="AB18" s="136"/>
       <c r="AC18" s="33"/>
       <c r="AD18" s="33"/>
       <c r="AE18" s="33"/>
@@ -3343,21 +3343,21 @@
       <c r="K19" s="33"/>
       <c r="L19" s="33"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="115"/>
-      <c r="O19" s="115"/>
-      <c r="P19" s="115"/>
-      <c r="Q19" s="115"/>
-      <c r="R19" s="115"/>
-      <c r="S19" s="115"/>
-      <c r="T19" s="115"/>
-      <c r="U19" s="115"/>
-      <c r="V19" s="115"/>
-      <c r="W19" s="115"/>
-      <c r="X19" s="115"/>
-      <c r="Y19" s="115"/>
-      <c r="Z19" s="115"/>
-      <c r="AA19" s="115"/>
-      <c r="AB19" s="115"/>
+      <c r="N19" s="136"/>
+      <c r="O19" s="136"/>
+      <c r="P19" s="136"/>
+      <c r="Q19" s="136"/>
+      <c r="R19" s="136"/>
+      <c r="S19" s="136"/>
+      <c r="T19" s="136"/>
+      <c r="U19" s="136"/>
+      <c r="V19" s="136"/>
+      <c r="W19" s="136"/>
+      <c r="X19" s="136"/>
+      <c r="Y19" s="136"/>
+      <c r="Z19" s="136"/>
+      <c r="AA19" s="136"/>
+      <c r="AB19" s="136"/>
       <c r="AC19" s="33"/>
       <c r="AD19" s="33"/>
       <c r="AE19" s="33"/>
@@ -3380,56 +3380,56 @@
       <c r="AR19" s="30"/>
     </row>
     <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="81"/>
-      <c r="C20" s="82"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="69"/>
       <c r="D20" s="55"/>
       <c r="E20" s="39"/>
-      <c r="F20" s="81" t="s">
+      <c r="F20" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="G20" s="82"/>
+      <c r="G20" s="69"/>
       <c r="H20" s="57" t="s">
         <v>89</v>
       </c>
       <c r="I20" s="36"/>
-      <c r="J20" s="81"/>
-      <c r="K20" s="82"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="69"/>
       <c r="L20" s="55"/>
       <c r="M20" s="4"/>
-      <c r="N20" s="70"/>
-      <c r="O20" s="71"/>
+      <c r="N20" s="81"/>
+      <c r="O20" s="82"/>
       <c r="P20" s="34"/>
       <c r="Q20" s="39"/>
-      <c r="R20" s="70"/>
-      <c r="S20" s="71"/>
+      <c r="R20" s="81"/>
+      <c r="S20" s="82"/>
       <c r="T20" s="34"/>
       <c r="U20" s="36"/>
-      <c r="V20" s="70" t="s">
+      <c r="V20" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="W20" s="71"/>
+      <c r="W20" s="82"/>
       <c r="X20" s="34" t="s">
         <v>46</v>
       </c>
       <c r="Y20" s="23"/>
-      <c r="Z20" s="70"/>
-      <c r="AA20" s="71"/>
+      <c r="Z20" s="81"/>
+      <c r="AA20" s="82"/>
       <c r="AB20" s="34"/>
       <c r="AC20" s="36"/>
-      <c r="AD20" s="70"/>
-      <c r="AE20" s="71"/>
+      <c r="AD20" s="81"/>
+      <c r="AE20" s="82"/>
       <c r="AF20" s="34"/>
       <c r="AG20" s="39"/>
-      <c r="AH20" s="70" t="s">
+      <c r="AH20" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="AI20" s="71"/>
+      <c r="AI20" s="82"/>
       <c r="AJ20" s="34" t="s">
         <v>65</v>
       </c>
       <c r="AK20" s="36"/>
-      <c r="AL20" s="70"/>
-      <c r="AM20" s="71"/>
+      <c r="AL20" s="81"/>
+      <c r="AM20" s="82"/>
       <c r="AN20" s="34"/>
       <c r="AP20" s="46" t="s">
         <v>26</v>
@@ -3441,48 +3441,48 @@
       <c r="AR20" s="30"/>
     </row>
     <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="78"/>
-      <c r="C21" s="79"/>
+      <c r="B21" s="73"/>
+      <c r="C21" s="74"/>
       <c r="D21" s="61"/>
       <c r="E21" s="38"/>
-      <c r="F21" s="78"/>
-      <c r="G21" s="79"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="74"/>
       <c r="H21" s="61"/>
       <c r="I21" s="36"/>
-      <c r="J21" s="78"/>
-      <c r="K21" s="79"/>
+      <c r="J21" s="73"/>
+      <c r="K21" s="74"/>
       <c r="L21" s="61"/>
       <c r="M21" s="15"/>
-      <c r="N21" s="75"/>
-      <c r="O21" s="76"/>
+      <c r="N21" s="83"/>
+      <c r="O21" s="84"/>
       <c r="P21" s="18"/>
       <c r="Q21" s="36"/>
-      <c r="R21" s="75"/>
-      <c r="S21" s="76"/>
+      <c r="R21" s="83"/>
+      <c r="S21" s="84"/>
       <c r="T21" s="18"/>
       <c r="U21" s="36"/>
-      <c r="V21" s="75" t="s">
+      <c r="V21" s="83" t="s">
         <v>45</v>
       </c>
-      <c r="W21" s="76"/>
+      <c r="W21" s="84"/>
       <c r="X21" s="18" t="s">
         <v>43</v>
       </c>
       <c r="Y21" s="36"/>
-      <c r="Z21" s="75"/>
-      <c r="AA21" s="76"/>
+      <c r="Z21" s="83"/>
+      <c r="AA21" s="84"/>
       <c r="AB21" s="18"/>
       <c r="AC21" s="36"/>
-      <c r="AD21" s="75"/>
-      <c r="AE21" s="76"/>
+      <c r="AD21" s="83"/>
+      <c r="AE21" s="84"/>
       <c r="AF21" s="18"/>
       <c r="AG21" s="38"/>
-      <c r="AH21" s="75"/>
-      <c r="AI21" s="76"/>
+      <c r="AH21" s="83"/>
+      <c r="AI21" s="84"/>
       <c r="AJ21" s="18"/>
       <c r="AK21" s="36"/>
-      <c r="AL21" s="75"/>
-      <c r="AM21" s="76"/>
+      <c r="AL21" s="83"/>
+      <c r="AM21" s="84"/>
       <c r="AN21" s="18"/>
       <c r="AP21" s="46" t="s">
         <v>12</v>
@@ -3494,9 +3494,9 @@
       <c r="AR21" s="30"/>
     </row>
     <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="89"/>
-      <c r="C22" s="90"/>
-      <c r="D22" s="91"/>
+      <c r="B22" s="70"/>
+      <c r="C22" s="71"/>
+      <c r="D22" s="72"/>
       <c r="E22" s="35"/>
       <c r="F22" s="140" t="s">
         <v>9</v>
@@ -3504,41 +3504,41 @@
       <c r="G22" s="141"/>
       <c r="H22" s="142"/>
       <c r="I22" s="37"/>
-      <c r="J22" s="89"/>
-      <c r="K22" s="90"/>
-      <c r="L22" s="91"/>
+      <c r="J22" s="70"/>
+      <c r="K22" s="71"/>
+      <c r="L22" s="72"/>
       <c r="M22" s="4"/>
-      <c r="N22" s="89"/>
-      <c r="O22" s="90"/>
-      <c r="P22" s="91"/>
+      <c r="N22" s="70"/>
+      <c r="O22" s="71"/>
+      <c r="P22" s="72"/>
       <c r="Q22" s="35"/>
-      <c r="R22" s="89"/>
-      <c r="S22" s="90"/>
-      <c r="T22" s="91"/>
+      <c r="R22" s="70"/>
+      <c r="S22" s="71"/>
+      <c r="T22" s="72"/>
       <c r="U22" s="37"/>
-      <c r="V22" s="89" t="s">
+      <c r="V22" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="W22" s="90"/>
-      <c r="X22" s="91"/>
+      <c r="W22" s="71"/>
+      <c r="X22" s="72"/>
       <c r="Y22" s="35"/>
-      <c r="Z22" s="89"/>
-      <c r="AA22" s="90"/>
-      <c r="AB22" s="91"/>
+      <c r="Z22" s="70"/>
+      <c r="AA22" s="71"/>
+      <c r="AB22" s="72"/>
       <c r="AC22" s="35"/>
-      <c r="AD22" s="89"/>
-      <c r="AE22" s="90"/>
-      <c r="AF22" s="91"/>
+      <c r="AD22" s="70"/>
+      <c r="AE22" s="71"/>
+      <c r="AF22" s="72"/>
       <c r="AG22" s="35"/>
-      <c r="AH22" s="89" t="s">
+      <c r="AH22" s="70" t="s">
         <v>112</v>
       </c>
-      <c r="AI22" s="90"/>
-      <c r="AJ22" s="91"/>
+      <c r="AI22" s="71"/>
+      <c r="AJ22" s="72"/>
       <c r="AK22" s="37"/>
-      <c r="AL22" s="89"/>
-      <c r="AM22" s="90"/>
-      <c r="AN22" s="91"/>
+      <c r="AL22" s="70"/>
+      <c r="AM22" s="71"/>
+      <c r="AN22" s="72"/>
       <c r="AP22" s="46" t="s">
         <v>15</v>
       </c>
@@ -3549,47 +3549,47 @@
       <c r="AR22" s="30"/>
     </row>
     <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="106"/>
-      <c r="C23" s="107"/>
-      <c r="D23" s="108"/>
+      <c r="B23" s="92"/>
+      <c r="C23" s="93"/>
+      <c r="D23" s="94"/>
       <c r="E23" s="44"/>
-      <c r="F23" s="106"/>
-      <c r="G23" s="107"/>
-      <c r="H23" s="108"/>
+      <c r="F23" s="92"/>
+      <c r="G23" s="93"/>
+      <c r="H23" s="94"/>
       <c r="I23" s="44"/>
-      <c r="J23" s="106"/>
-      <c r="K23" s="107"/>
-      <c r="L23" s="108"/>
+      <c r="J23" s="92"/>
+      <c r="K23" s="93"/>
+      <c r="L23" s="94"/>
       <c r="M23" s="4"/>
-      <c r="N23" s="106"/>
-      <c r="O23" s="107"/>
-      <c r="P23" s="108"/>
+      <c r="N23" s="92"/>
+      <c r="O23" s="93"/>
+      <c r="P23" s="94"/>
       <c r="Q23" s="44"/>
-      <c r="R23" s="106"/>
-      <c r="S23" s="107"/>
-      <c r="T23" s="108"/>
+      <c r="R23" s="92"/>
+      <c r="S23" s="93"/>
+      <c r="T23" s="94"/>
       <c r="U23" s="44"/>
-      <c r="V23" s="106"/>
-      <c r="W23" s="107"/>
-      <c r="X23" s="108"/>
+      <c r="V23" s="92"/>
+      <c r="W23" s="93"/>
+      <c r="X23" s="94"/>
       <c r="Y23" s="44"/>
-      <c r="Z23" s="106"/>
-      <c r="AA23" s="107"/>
-      <c r="AB23" s="108"/>
+      <c r="Z23" s="92"/>
+      <c r="AA23" s="93"/>
+      <c r="AB23" s="94"/>
       <c r="AC23" s="44"/>
-      <c r="AD23" s="106"/>
-      <c r="AE23" s="107"/>
-      <c r="AF23" s="108"/>
+      <c r="AD23" s="92"/>
+      <c r="AE23" s="93"/>
+      <c r="AF23" s="94"/>
       <c r="AG23" s="44"/>
-      <c r="AH23" s="106" t="s">
+      <c r="AH23" s="92" t="s">
         <v>79</v>
       </c>
-      <c r="AI23" s="107"/>
-      <c r="AJ23" s="108"/>
+      <c r="AI23" s="93"/>
+      <c r="AJ23" s="94"/>
       <c r="AK23" s="44"/>
-      <c r="AL23" s="106"/>
-      <c r="AM23" s="107"/>
-      <c r="AN23" s="108"/>
+      <c r="AL23" s="92"/>
+      <c r="AM23" s="93"/>
+      <c r="AN23" s="94"/>
       <c r="AP23" s="56" t="s">
         <v>20</v>
       </c>
@@ -3663,23 +3663,23 @@
       <c r="K25" s="33"/>
       <c r="L25" s="33"/>
       <c r="M25" s="4"/>
-      <c r="N25" s="115" t="s">
+      <c r="N25" s="136" t="s">
         <v>39</v>
       </c>
-      <c r="O25" s="115"/>
-      <c r="P25" s="115"/>
-      <c r="Q25" s="115"/>
-      <c r="R25" s="115"/>
-      <c r="S25" s="115"/>
-      <c r="T25" s="115"/>
-      <c r="U25" s="115"/>
-      <c r="V25" s="115"/>
-      <c r="W25" s="115"/>
-      <c r="X25" s="115"/>
-      <c r="Y25" s="115"/>
-      <c r="Z25" s="115"/>
-      <c r="AA25" s="115"/>
-      <c r="AB25" s="115"/>
+      <c r="O25" s="136"/>
+      <c r="P25" s="136"/>
+      <c r="Q25" s="136"/>
+      <c r="R25" s="136"/>
+      <c r="S25" s="136"/>
+      <c r="T25" s="136"/>
+      <c r="U25" s="136"/>
+      <c r="V25" s="136"/>
+      <c r="W25" s="136"/>
+      <c r="X25" s="136"/>
+      <c r="Y25" s="136"/>
+      <c r="Z25" s="136"/>
+      <c r="AA25" s="136"/>
+      <c r="AB25" s="136"/>
       <c r="AC25" s="33"/>
       <c r="AD25" s="33"/>
       <c r="AE25" s="33"/>
@@ -3714,21 +3714,21 @@
       <c r="K26" s="33"/>
       <c r="L26" s="33"/>
       <c r="M26" s="4"/>
-      <c r="N26" s="115"/>
-      <c r="O26" s="115"/>
-      <c r="P26" s="115"/>
-      <c r="Q26" s="115"/>
-      <c r="R26" s="115"/>
-      <c r="S26" s="115"/>
-      <c r="T26" s="115"/>
-      <c r="U26" s="115"/>
-      <c r="V26" s="115"/>
-      <c r="W26" s="115"/>
-      <c r="X26" s="115"/>
-      <c r="Y26" s="115"/>
-      <c r="Z26" s="115"/>
-      <c r="AA26" s="115"/>
-      <c r="AB26" s="115"/>
+      <c r="N26" s="136"/>
+      <c r="O26" s="136"/>
+      <c r="P26" s="136"/>
+      <c r="Q26" s="136"/>
+      <c r="R26" s="136"/>
+      <c r="S26" s="136"/>
+      <c r="T26" s="136"/>
+      <c r="U26" s="136"/>
+      <c r="V26" s="136"/>
+      <c r="W26" s="136"/>
+      <c r="X26" s="136"/>
+      <c r="Y26" s="136"/>
+      <c r="Z26" s="136"/>
+      <c r="AA26" s="136"/>
+      <c r="AB26" s="136"/>
       <c r="AC26" s="33"/>
       <c r="AD26" s="33"/>
       <c r="AE26" s="33"/>
@@ -3751,76 +3751,76 @@
       <c r="AR26" s="30"/>
     </row>
     <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="81" t="s">
+      <c r="B27" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="C27" s="82"/>
+      <c r="C27" s="69"/>
       <c r="D27" s="55" t="s">
         <v>54</v>
       </c>
       <c r="E27" s="36"/>
-      <c r="F27" s="81" t="s">
+      <c r="F27" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="G27" s="82"/>
+      <c r="G27" s="69"/>
       <c r="H27" s="55" t="s">
         <v>54</v>
       </c>
       <c r="I27" s="36"/>
-      <c r="J27" s="81" t="s">
+      <c r="J27" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="K27" s="82"/>
+      <c r="K27" s="69"/>
       <c r="L27" s="55" t="s">
         <v>54</v>
       </c>
       <c r="M27" s="5"/>
-      <c r="N27" s="70" t="s">
+      <c r="N27" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="O27" s="71"/>
+      <c r="O27" s="82"/>
       <c r="P27" s="34" t="s">
         <v>54</v>
       </c>
       <c r="Q27" s="36"/>
-      <c r="R27" s="70" t="s">
+      <c r="R27" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="S27" s="71"/>
+      <c r="S27" s="82"/>
       <c r="T27" s="34" t="s">
         <v>54</v>
       </c>
       <c r="U27" s="36"/>
-      <c r="V27" s="70" t="s">
+      <c r="V27" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="W27" s="71"/>
+      <c r="W27" s="82"/>
       <c r="X27" s="34" t="s">
         <v>54</v>
       </c>
       <c r="Y27" s="36"/>
-      <c r="Z27" s="70" t="s">
+      <c r="Z27" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="AA27" s="71"/>
+      <c r="AA27" s="82"/>
       <c r="AB27" s="34" t="s">
         <v>54</v>
       </c>
       <c r="AC27" s="36"/>
-      <c r="AD27" s="70" t="s">
+      <c r="AD27" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="AE27" s="71"/>
+      <c r="AE27" s="82"/>
       <c r="AF27" s="34" t="s">
         <v>54</v>
       </c>
       <c r="AG27" s="36"/>
-      <c r="AH27" s="70"/>
-      <c r="AI27" s="71"/>
+      <c r="AH27" s="81"/>
+      <c r="AI27" s="82"/>
       <c r="AJ27" s="34"/>
       <c r="AK27" s="36"/>
-      <c r="AL27" s="70"/>
-      <c r="AM27" s="71"/>
+      <c r="AL27" s="81"/>
+      <c r="AM27" s="82"/>
       <c r="AN27" s="34"/>
       <c r="AP27" s="46" t="s">
         <v>13</v>
@@ -3832,44 +3832,44 @@
       <c r="AR27" s="30"/>
     </row>
     <row r="28" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="78"/>
-      <c r="C28" s="79"/>
+      <c r="B28" s="73"/>
+      <c r="C28" s="74"/>
       <c r="D28" s="61"/>
       <c r="E28" s="38"/>
-      <c r="F28" s="78"/>
-      <c r="G28" s="79"/>
+      <c r="F28" s="73"/>
+      <c r="G28" s="74"/>
       <c r="H28" s="61"/>
       <c r="I28" s="36"/>
-      <c r="J28" s="78"/>
-      <c r="K28" s="79"/>
+      <c r="J28" s="73"/>
+      <c r="K28" s="74"/>
       <c r="L28" s="61"/>
       <c r="M28" s="5"/>
-      <c r="N28" s="75"/>
-      <c r="O28" s="76"/>
+      <c r="N28" s="83"/>
+      <c r="O28" s="84"/>
       <c r="P28" s="18"/>
       <c r="Q28" s="38"/>
-      <c r="R28" s="75"/>
-      <c r="S28" s="76"/>
+      <c r="R28" s="83"/>
+      <c r="S28" s="84"/>
       <c r="T28" s="18"/>
       <c r="U28" s="38"/>
-      <c r="V28" s="75"/>
-      <c r="W28" s="76"/>
+      <c r="V28" s="83"/>
+      <c r="W28" s="84"/>
       <c r="X28" s="18"/>
       <c r="Y28" s="36"/>
-      <c r="Z28" s="75"/>
-      <c r="AA28" s="76"/>
+      <c r="Z28" s="83"/>
+      <c r="AA28" s="84"/>
       <c r="AB28" s="18"/>
       <c r="AC28" s="36"/>
-      <c r="AD28" s="75"/>
-      <c r="AE28" s="76"/>
+      <c r="AD28" s="83"/>
+      <c r="AE28" s="84"/>
       <c r="AF28" s="18"/>
       <c r="AG28" s="38"/>
-      <c r="AH28" s="149"/>
-      <c r="AI28" s="150"/>
+      <c r="AH28" s="134"/>
+      <c r="AI28" s="135"/>
       <c r="AJ28" s="18"/>
       <c r="AK28" s="36"/>
-      <c r="AL28" s="75"/>
-      <c r="AM28" s="76"/>
+      <c r="AL28" s="83"/>
+      <c r="AM28" s="84"/>
       <c r="AN28" s="18"/>
       <c r="AP28" s="46" t="s">
         <v>28</v>
@@ -3881,76 +3881,76 @@
       <c r="AR28" s="30"/>
     </row>
     <row r="29" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="111" t="s">
+      <c r="B29" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="C29" s="112"/>
+      <c r="C29" s="96"/>
       <c r="D29" s="41" t="s">
         <v>32</v>
       </c>
       <c r="E29" s="37"/>
-      <c r="F29" s="111" t="s">
+      <c r="F29" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="G29" s="112"/>
+      <c r="G29" s="96"/>
       <c r="H29" s="41" t="s">
         <v>32</v>
       </c>
       <c r="I29" s="35"/>
-      <c r="J29" s="111" t="s">
+      <c r="J29" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="K29" s="112"/>
+      <c r="K29" s="96"/>
       <c r="L29" s="41" t="s">
         <v>32</v>
       </c>
       <c r="M29" s="5"/>
-      <c r="N29" s="111" t="s">
+      <c r="N29" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="O29" s="112"/>
+      <c r="O29" s="96"/>
       <c r="P29" s="41" t="s">
         <v>32</v>
       </c>
       <c r="Q29" s="35"/>
-      <c r="R29" s="111" t="s">
+      <c r="R29" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="S29" s="112"/>
+      <c r="S29" s="96"/>
       <c r="T29" s="41" t="s">
         <v>32</v>
       </c>
       <c r="U29" s="37"/>
-      <c r="V29" s="111" t="s">
+      <c r="V29" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="W29" s="112"/>
+      <c r="W29" s="96"/>
       <c r="X29" s="41" t="s">
         <v>32</v>
       </c>
       <c r="Y29" s="35"/>
-      <c r="Z29" s="111" t="s">
+      <c r="Z29" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="AA29" s="112"/>
+      <c r="AA29" s="96"/>
       <c r="AB29" s="41" t="s">
         <v>32</v>
       </c>
       <c r="AC29" s="35"/>
-      <c r="AD29" s="111" t="s">
+      <c r="AD29" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="AE29" s="112"/>
+      <c r="AE29" s="96"/>
       <c r="AF29" s="41" t="s">
         <v>32</v>
       </c>
       <c r="AG29" s="37"/>
-      <c r="AH29" s="111"/>
-      <c r="AI29" s="112"/>
+      <c r="AH29" s="95"/>
+      <c r="AI29" s="96"/>
       <c r="AJ29" s="41"/>
       <c r="AK29" s="35"/>
-      <c r="AL29" s="111"/>
-      <c r="AM29" s="112"/>
+      <c r="AL29" s="95"/>
+      <c r="AM29" s="96"/>
       <c r="AN29" s="41"/>
       <c r="AP29" s="56" t="s">
         <v>29</v>
@@ -3964,328 +3964,328 @@
       </c>
     </row>
     <row r="30" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="113" t="s">
+      <c r="B30" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="C30" s="114"/>
+      <c r="C30" s="98"/>
       <c r="D30" s="45" t="s">
         <v>33</v>
       </c>
       <c r="E30" s="43"/>
-      <c r="F30" s="113" t="s">
+      <c r="F30" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="G30" s="114"/>
+      <c r="G30" s="98"/>
       <c r="H30" s="45" t="s">
         <v>33</v>
       </c>
       <c r="I30" s="43"/>
-      <c r="J30" s="113" t="s">
+      <c r="J30" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="K30" s="114"/>
+      <c r="K30" s="98"/>
       <c r="L30" s="45" t="s">
         <v>33</v>
       </c>
       <c r="M30" s="5"/>
-      <c r="N30" s="113" t="s">
+      <c r="N30" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="O30" s="114"/>
+      <c r="O30" s="98"/>
       <c r="P30" s="45" t="s">
         <v>33</v>
       </c>
       <c r="Q30" s="43"/>
-      <c r="R30" s="113" t="s">
+      <c r="R30" s="97" t="s">
         <v>16</v>
       </c>
-      <c r="S30" s="114"/>
+      <c r="S30" s="98"/>
       <c r="T30" s="45" t="s">
         <v>33</v>
       </c>
       <c r="U30" s="43"/>
-      <c r="V30" s="113" t="s">
+      <c r="V30" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="W30" s="114"/>
+      <c r="W30" s="98"/>
       <c r="X30" s="45" t="s">
         <v>33</v>
       </c>
       <c r="Y30" s="43"/>
-      <c r="Z30" s="113" t="s">
+      <c r="Z30" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="AA30" s="114"/>
+      <c r="AA30" s="98"/>
       <c r="AB30" s="45" t="s">
         <v>33</v>
       </c>
       <c r="AC30" s="43"/>
-      <c r="AD30" s="113" t="s">
+      <c r="AD30" s="97" t="s">
         <v>16</v>
       </c>
-      <c r="AE30" s="114"/>
+      <c r="AE30" s="98"/>
       <c r="AF30" s="45" t="s">
         <v>33</v>
       </c>
       <c r="AG30" s="43"/>
-      <c r="AH30" s="157"/>
-      <c r="AI30" s="158"/>
+      <c r="AH30" s="112"/>
+      <c r="AI30" s="113"/>
       <c r="AJ30" s="45"/>
       <c r="AK30" s="43"/>
-      <c r="AL30" s="113"/>
-      <c r="AM30" s="114"/>
+      <c r="AL30" s="97"/>
+      <c r="AM30" s="98"/>
       <c r="AN30" s="45"/>
       <c r="AP30" s="46" t="s">
         <v>30</v>
       </c>
       <c r="AQ30" s="47">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR30" s="30"/>
     </row>
     <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="109" t="s">
+      <c r="B31" s="99" t="s">
         <v>37</v>
       </c>
-      <c r="C31" s="110"/>
+      <c r="C31" s="100"/>
       <c r="D31" s="45" t="s">
         <v>34</v>
       </c>
       <c r="E31" s="43"/>
-      <c r="F31" s="109" t="s">
+      <c r="F31" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="G31" s="110"/>
+      <c r="G31" s="100"/>
       <c r="H31" s="45" t="s">
         <v>34</v>
       </c>
       <c r="I31" s="44"/>
-      <c r="J31" s="109" t="s">
+      <c r="J31" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="K31" s="110"/>
+      <c r="K31" s="100"/>
       <c r="L31" s="45" t="s">
         <v>34</v>
       </c>
       <c r="M31" s="6"/>
-      <c r="N31" s="109" t="s">
+      <c r="N31" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="O31" s="110"/>
+      <c r="O31" s="100"/>
       <c r="P31" s="45" t="s">
         <v>34</v>
       </c>
       <c r="Q31" s="43"/>
-      <c r="R31" s="109" t="s">
+      <c r="R31" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="S31" s="110"/>
+      <c r="S31" s="100"/>
       <c r="T31" s="45" t="s">
         <v>34</v>
       </c>
       <c r="U31" s="44"/>
-      <c r="V31" s="109" t="s">
+      <c r="V31" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="W31" s="110"/>
+      <c r="W31" s="100"/>
       <c r="X31" s="45" t="s">
         <v>34</v>
       </c>
       <c r="Y31" s="43"/>
-      <c r="Z31" s="109" t="s">
+      <c r="Z31" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="AA31" s="110"/>
+      <c r="AA31" s="100"/>
       <c r="AB31" s="45" t="s">
         <v>34</v>
       </c>
       <c r="AC31" s="43"/>
-      <c r="AD31" s="109" t="s">
+      <c r="AD31" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="AE31" s="110"/>
+      <c r="AE31" s="100"/>
       <c r="AF31" s="45" t="s">
         <v>34</v>
       </c>
       <c r="AG31" s="43"/>
-      <c r="AH31" s="109"/>
-      <c r="AI31" s="110"/>
+      <c r="AH31" s="99"/>
+      <c r="AI31" s="100"/>
       <c r="AJ31" s="45"/>
       <c r="AK31" s="44"/>
-      <c r="AL31" s="109"/>
-      <c r="AM31" s="110"/>
+      <c r="AL31" s="99"/>
+      <c r="AM31" s="100"/>
       <c r="AN31" s="45"/>
       <c r="AP31" s="48"/>
       <c r="AQ31" s="49"/>
       <c r="AR31" s="30"/>
     </row>
     <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="109" t="s">
+      <c r="B32" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="C32" s="110"/>
+      <c r="C32" s="100"/>
       <c r="D32" s="45" t="s">
         <v>35</v>
       </c>
       <c r="E32" s="44"/>
-      <c r="F32" s="109" t="s">
+      <c r="F32" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="110"/>
+      <c r="G32" s="100"/>
       <c r="H32" s="45" t="s">
         <v>35</v>
       </c>
       <c r="I32" s="44"/>
-      <c r="J32" s="109" t="s">
+      <c r="J32" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="K32" s="110"/>
+      <c r="K32" s="100"/>
       <c r="L32" s="45" t="s">
         <v>35</v>
       </c>
       <c r="M32" s="5"/>
-      <c r="N32" s="109" t="s">
+      <c r="N32" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="O32" s="110"/>
+      <c r="O32" s="100"/>
       <c r="P32" s="45" t="s">
         <v>35</v>
       </c>
       <c r="Q32" s="44"/>
-      <c r="R32" s="109" t="s">
+      <c r="R32" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="S32" s="110"/>
+      <c r="S32" s="100"/>
       <c r="T32" s="45" t="s">
         <v>35</v>
       </c>
       <c r="U32" s="44"/>
-      <c r="V32" s="109" t="s">
+      <c r="V32" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="W32" s="110"/>
+      <c r="W32" s="100"/>
       <c r="X32" s="45" t="s">
         <v>35</v>
       </c>
       <c r="Y32" s="44"/>
-      <c r="Z32" s="109" t="s">
+      <c r="Z32" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="AA32" s="110"/>
+      <c r="AA32" s="100"/>
       <c r="AB32" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AC32" s="44"/>
-      <c r="AD32" s="109" t="s">
+      <c r="AD32" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="AE32" s="110"/>
+      <c r="AE32" s="100"/>
       <c r="AF32" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AG32" s="44"/>
-      <c r="AH32" s="109"/>
-      <c r="AI32" s="110"/>
+      <c r="AH32" s="99"/>
+      <c r="AI32" s="100"/>
       <c r="AJ32" s="45"/>
       <c r="AK32" s="44"/>
-      <c r="AL32" s="109"/>
-      <c r="AM32" s="110"/>
+      <c r="AL32" s="99"/>
+      <c r="AM32" s="100"/>
       <c r="AN32" s="45"/>
       <c r="AP32" s="51"/>
       <c r="AQ32" s="52"/>
       <c r="AR32" s="30"/>
     </row>
     <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="109" t="s">
+      <c r="B33" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="110"/>
+      <c r="C33" s="100"/>
       <c r="D33" s="45" t="s">
         <v>35</v>
       </c>
       <c r="E33" s="44"/>
-      <c r="F33" s="109"/>
-      <c r="G33" s="110"/>
+      <c r="F33" s="99"/>
+      <c r="G33" s="100"/>
       <c r="H33" s="45"/>
       <c r="I33" s="44"/>
-      <c r="J33" s="109"/>
-      <c r="K33" s="110"/>
+      <c r="J33" s="99"/>
+      <c r="K33" s="100"/>
       <c r="L33" s="45"/>
       <c r="M33" s="5"/>
-      <c r="N33" s="109"/>
-      <c r="O33" s="110"/>
+      <c r="N33" s="99"/>
+      <c r="O33" s="100"/>
       <c r="P33" s="45"/>
       <c r="Q33" s="44"/>
-      <c r="R33" s="109"/>
-      <c r="S33" s="110"/>
+      <c r="R33" s="99"/>
+      <c r="S33" s="100"/>
       <c r="T33" s="45"/>
       <c r="U33" s="44"/>
-      <c r="V33" s="109"/>
-      <c r="W33" s="110"/>
+      <c r="V33" s="99"/>
+      <c r="W33" s="100"/>
       <c r="X33" s="45"/>
       <c r="Y33" s="44"/>
-      <c r="Z33" s="109"/>
-      <c r="AA33" s="110"/>
+      <c r="Z33" s="99"/>
+      <c r="AA33" s="100"/>
       <c r="AB33" s="45"/>
       <c r="AC33" s="44"/>
-      <c r="AD33" s="109" t="s">
+      <c r="AD33" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="AE33" s="110"/>
+      <c r="AE33" s="100"/>
       <c r="AF33" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AG33" s="44"/>
-      <c r="AH33" s="109"/>
-      <c r="AI33" s="110"/>
+      <c r="AH33" s="99"/>
+      <c r="AI33" s="100"/>
       <c r="AJ33" s="45"/>
       <c r="AK33" s="44"/>
-      <c r="AL33" s="109"/>
-      <c r="AM33" s="110"/>
+      <c r="AL33" s="99"/>
+      <c r="AM33" s="100"/>
       <c r="AN33" s="45"/>
       <c r="AR33" s="13"/>
     </row>
     <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="12"/>
-      <c r="B34" s="154"/>
-      <c r="C34" s="155"/>
+      <c r="B34" s="101"/>
+      <c r="C34" s="102"/>
       <c r="D34" s="42"/>
       <c r="E34" s="44"/>
-      <c r="F34" s="154"/>
-      <c r="G34" s="155"/>
+      <c r="F34" s="101"/>
+      <c r="G34" s="102"/>
       <c r="H34" s="42"/>
       <c r="I34" s="44"/>
-      <c r="J34" s="154"/>
-      <c r="K34" s="155"/>
+      <c r="J34" s="101"/>
+      <c r="K34" s="102"/>
       <c r="L34" s="42"/>
       <c r="M34" s="2"/>
-      <c r="N34" s="154"/>
-      <c r="O34" s="155"/>
+      <c r="N34" s="101"/>
+      <c r="O34" s="102"/>
       <c r="P34" s="42"/>
       <c r="Q34" s="44"/>
-      <c r="R34" s="154"/>
-      <c r="S34" s="155"/>
+      <c r="R34" s="101"/>
+      <c r="S34" s="102"/>
       <c r="T34" s="42"/>
       <c r="U34" s="44"/>
-      <c r="V34" s="154"/>
-      <c r="W34" s="155"/>
+      <c r="V34" s="101"/>
+      <c r="W34" s="102"/>
       <c r="X34" s="42"/>
       <c r="Y34" s="44"/>
-      <c r="Z34" s="154"/>
-      <c r="AA34" s="155"/>
+      <c r="Z34" s="101"/>
+      <c r="AA34" s="102"/>
       <c r="AB34" s="42"/>
       <c r="AC34" s="44"/>
-      <c r="AD34" s="154"/>
-      <c r="AE34" s="155"/>
+      <c r="AD34" s="101"/>
+      <c r="AE34" s="102"/>
       <c r="AF34" s="42"/>
       <c r="AG34" s="44"/>
-      <c r="AH34" s="154"/>
-      <c r="AI34" s="155"/>
+      <c r="AH34" s="101"/>
+      <c r="AI34" s="102"/>
       <c r="AJ34" s="42"/>
       <c r="AK34" s="44"/>
-      <c r="AL34" s="154"/>
-      <c r="AM34" s="155"/>
+      <c r="AL34" s="101"/>
+      <c r="AM34" s="102"/>
       <c r="AN34" s="42"/>
       <c r="AO34" s="12"/>
       <c r="AP34" s="12"/>
@@ -4351,23 +4351,23 @@
       <c r="K36" s="33"/>
       <c r="L36" s="33"/>
       <c r="M36" s="4"/>
-      <c r="N36" s="115" t="s">
+      <c r="N36" s="136" t="s">
         <v>36</v>
       </c>
-      <c r="O36" s="115"/>
-      <c r="P36" s="115"/>
-      <c r="Q36" s="115"/>
-      <c r="R36" s="115"/>
-      <c r="S36" s="115"/>
-      <c r="T36" s="115"/>
-      <c r="U36" s="115"/>
-      <c r="V36" s="115"/>
-      <c r="W36" s="115"/>
-      <c r="X36" s="115"/>
-      <c r="Y36" s="115"/>
-      <c r="Z36" s="115"/>
-      <c r="AA36" s="115"/>
-      <c r="AB36" s="115"/>
+      <c r="O36" s="136"/>
+      <c r="P36" s="136"/>
+      <c r="Q36" s="136"/>
+      <c r="R36" s="136"/>
+      <c r="S36" s="136"/>
+      <c r="T36" s="136"/>
+      <c r="U36" s="136"/>
+      <c r="V36" s="136"/>
+      <c r="W36" s="136"/>
+      <c r="X36" s="136"/>
+      <c r="Y36" s="136"/>
+      <c r="Z36" s="136"/>
+      <c r="AA36" s="136"/>
+      <c r="AB36" s="136"/>
       <c r="AC36" s="33"/>
       <c r="AD36" s="33"/>
       <c r="AE36" s="33"/>
@@ -4399,21 +4399,21 @@
       <c r="K37" s="33"/>
       <c r="L37" s="33"/>
       <c r="M37" s="5"/>
-      <c r="N37" s="115"/>
-      <c r="O37" s="115"/>
-      <c r="P37" s="115"/>
-      <c r="Q37" s="115"/>
-      <c r="R37" s="115"/>
-      <c r="S37" s="115"/>
-      <c r="T37" s="115"/>
-      <c r="U37" s="115"/>
-      <c r="V37" s="115"/>
-      <c r="W37" s="115"/>
-      <c r="X37" s="115"/>
-      <c r="Y37" s="115"/>
-      <c r="Z37" s="115"/>
-      <c r="AA37" s="115"/>
-      <c r="AB37" s="115"/>
+      <c r="N37" s="136"/>
+      <c r="O37" s="136"/>
+      <c r="P37" s="136"/>
+      <c r="Q37" s="136"/>
+      <c r="R37" s="136"/>
+      <c r="S37" s="136"/>
+      <c r="T37" s="136"/>
+      <c r="U37" s="136"/>
+      <c r="V37" s="136"/>
+      <c r="W37" s="136"/>
+      <c r="X37" s="136"/>
+      <c r="Y37" s="136"/>
+      <c r="Z37" s="136"/>
+      <c r="AA37" s="136"/>
+      <c r="AB37" s="136"/>
       <c r="AC37" s="33"/>
       <c r="AD37" s="33"/>
       <c r="AE37" s="33"/>
@@ -4433,74 +4433,74 @@
     </row>
     <row r="38" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12"/>
-      <c r="B38" s="81" t="s">
+      <c r="B38" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="C38" s="82"/>
+      <c r="C38" s="69"/>
       <c r="D38" s="55" t="s">
         <v>77</v>
       </c>
       <c r="E38" s="36"/>
-      <c r="F38" s="81" t="s">
+      <c r="F38" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="G38" s="82"/>
+      <c r="G38" s="69"/>
       <c r="H38" s="55" t="s">
         <v>83</v>
       </c>
       <c r="I38" s="36"/>
-      <c r="J38" s="81" t="s">
+      <c r="J38" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="K38" s="82"/>
+      <c r="K38" s="69"/>
       <c r="L38" s="55" t="s">
         <v>93</v>
       </c>
       <c r="M38" s="5"/>
-      <c r="N38" s="70" t="s">
+      <c r="N38" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="O38" s="71"/>
+      <c r="O38" s="82"/>
       <c r="P38" s="34"/>
       <c r="Q38" s="36"/>
-      <c r="R38" s="70" t="s">
+      <c r="R38" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="S38" s="71"/>
+      <c r="S38" s="82"/>
       <c r="T38" s="34" t="s">
         <v>77</v>
       </c>
       <c r="U38" s="36"/>
-      <c r="V38" s="70" t="s">
+      <c r="V38" s="81" t="s">
         <v>70</v>
       </c>
-      <c r="W38" s="71"/>
+      <c r="W38" s="82"/>
       <c r="X38" s="34" t="s">
         <v>52</v>
       </c>
       <c r="Y38" s="36"/>
-      <c r="Z38" s="70"/>
-      <c r="AA38" s="71"/>
+      <c r="Z38" s="81"/>
+      <c r="AA38" s="82"/>
       <c r="AB38" s="34"/>
       <c r="AC38" s="36"/>
-      <c r="AD38" s="70" t="s">
+      <c r="AD38" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="AE38" s="71"/>
+      <c r="AE38" s="82"/>
       <c r="AF38" s="34"/>
       <c r="AG38" s="36"/>
-      <c r="AH38" s="70" t="s">
+      <c r="AH38" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="AI38" s="71"/>
+      <c r="AI38" s="82"/>
       <c r="AJ38" s="34" t="s">
         <v>76</v>
       </c>
       <c r="AK38" s="36"/>
-      <c r="AL38" s="98" t="s">
+      <c r="AL38" s="126" t="s">
         <v>72</v>
       </c>
-      <c r="AM38" s="99"/>
+      <c r="AM38" s="127"/>
       <c r="AN38" s="59" t="s">
         <v>55</v>
       </c>
@@ -4529,45 +4529,45 @@
       <c r="K39" s="63"/>
       <c r="L39" s="64"/>
       <c r="M39" s="5"/>
-      <c r="N39" s="72" t="s">
+      <c r="N39" s="106" t="s">
         <v>68</v>
       </c>
-      <c r="O39" s="73"/>
-      <c r="P39" s="74"/>
+      <c r="O39" s="107"/>
+      <c r="P39" s="108"/>
       <c r="Q39" s="36"/>
-      <c r="R39" s="72" t="s">
+      <c r="R39" s="106" t="s">
         <v>68</v>
       </c>
-      <c r="S39" s="73"/>
-      <c r="T39" s="74"/>
+      <c r="S39" s="107"/>
+      <c r="T39" s="108"/>
       <c r="U39" s="36"/>
-      <c r="V39" s="72" t="s">
+      <c r="V39" s="106" t="s">
         <v>73</v>
       </c>
-      <c r="W39" s="73"/>
-      <c r="X39" s="74"/>
+      <c r="W39" s="107"/>
+      <c r="X39" s="108"/>
       <c r="Y39" s="37"/>
-      <c r="Z39" s="72"/>
-      <c r="AA39" s="73"/>
-      <c r="AB39" s="74"/>
+      <c r="Z39" s="106"/>
+      <c r="AA39" s="107"/>
+      <c r="AB39" s="108"/>
       <c r="AC39" s="36"/>
-      <c r="AD39" s="72" t="s">
+      <c r="AD39" s="106" t="s">
         <v>74</v>
       </c>
-      <c r="AE39" s="73"/>
-      <c r="AF39" s="74"/>
+      <c r="AE39" s="107"/>
+      <c r="AF39" s="108"/>
       <c r="AG39" s="36"/>
-      <c r="AH39" s="72" t="s">
+      <c r="AH39" s="106" t="s">
         <v>74</v>
       </c>
-      <c r="AI39" s="73"/>
-      <c r="AJ39" s="74"/>
+      <c r="AI39" s="107"/>
+      <c r="AJ39" s="108"/>
       <c r="AK39" s="36"/>
-      <c r="AL39" s="100" t="s">
+      <c r="AL39" s="109" t="s">
         <v>75</v>
       </c>
-      <c r="AM39" s="101"/>
-      <c r="AN39" s="102"/>
+      <c r="AM39" s="110"/>
+      <c r="AN39" s="111"/>
       <c r="AO39" s="31"/>
       <c r="AP39" s="31"/>
       <c r="AQ39" s="31"/>
@@ -4575,51 +4575,51 @@
     </row>
     <row r="40" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12"/>
-      <c r="B40" s="78"/>
-      <c r="C40" s="79"/>
-      <c r="D40" s="80"/>
+      <c r="B40" s="73"/>
+      <c r="C40" s="74"/>
+      <c r="D40" s="75"/>
       <c r="E40" s="43"/>
-      <c r="F40" s="78"/>
-      <c r="G40" s="79"/>
-      <c r="H40" s="80"/>
+      <c r="F40" s="73"/>
+      <c r="G40" s="74"/>
+      <c r="H40" s="75"/>
       <c r="I40" s="43"/>
-      <c r="J40" s="78"/>
-      <c r="K40" s="79"/>
-      <c r="L40" s="80"/>
+      <c r="J40" s="73"/>
+      <c r="K40" s="74"/>
+      <c r="L40" s="75"/>
       <c r="M40" s="4"/>
-      <c r="N40" s="75" t="s">
+      <c r="N40" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="O40" s="76"/>
-      <c r="P40" s="77"/>
+      <c r="O40" s="84"/>
+      <c r="P40" s="85"/>
       <c r="Q40" s="43"/>
-      <c r="R40" s="75"/>
-      <c r="S40" s="76"/>
-      <c r="T40" s="77"/>
+      <c r="R40" s="83"/>
+      <c r="S40" s="84"/>
+      <c r="T40" s="85"/>
       <c r="U40" s="35"/>
-      <c r="V40" s="75"/>
-      <c r="W40" s="76"/>
-      <c r="X40" s="77"/>
+      <c r="V40" s="83"/>
+      <c r="W40" s="84"/>
+      <c r="X40" s="85"/>
       <c r="Y40" s="36"/>
-      <c r="Z40" s="75"/>
-      <c r="AA40" s="76"/>
-      <c r="AB40" s="77"/>
+      <c r="Z40" s="83"/>
+      <c r="AA40" s="84"/>
+      <c r="AB40" s="85"/>
       <c r="AC40" s="36"/>
-      <c r="AD40" s="75" t="s">
+      <c r="AD40" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="AE40" s="76"/>
-      <c r="AF40" s="77"/>
+      <c r="AE40" s="84"/>
+      <c r="AF40" s="85"/>
       <c r="AG40" s="43"/>
-      <c r="AH40" s="75"/>
-      <c r="AI40" s="76"/>
-      <c r="AJ40" s="77"/>
+      <c r="AH40" s="83"/>
+      <c r="AI40" s="84"/>
+      <c r="AJ40" s="85"/>
       <c r="AK40" s="43"/>
-      <c r="AL40" s="127" t="s">
+      <c r="AL40" s="114" t="s">
         <v>86</v>
       </c>
-      <c r="AM40" s="128"/>
-      <c r="AN40" s="156"/>
+      <c r="AM40" s="115"/>
+      <c r="AN40" s="116"/>
       <c r="AO40" s="31"/>
       <c r="AP40" s="31"/>
       <c r="AQ40" s="31"/>
@@ -4627,63 +4627,63 @@
     </row>
     <row r="41" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12"/>
-      <c r="B41" s="67" t="s">
+      <c r="B41" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="C41" s="68"/>
-      <c r="D41" s="69"/>
+      <c r="C41" s="79"/>
+      <c r="D41" s="80"/>
       <c r="E41" s="37"/>
-      <c r="F41" s="143" t="s">
+      <c r="F41" s="103" t="s">
         <v>96</v>
       </c>
-      <c r="G41" s="144"/>
-      <c r="H41" s="145"/>
+      <c r="G41" s="104"/>
+      <c r="H41" s="105"/>
       <c r="I41" s="31"/>
-      <c r="J41" s="67" t="s">
+      <c r="J41" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="K41" s="68"/>
-      <c r="L41" s="69"/>
+      <c r="K41" s="79"/>
+      <c r="L41" s="80"/>
       <c r="M41" s="5"/>
-      <c r="N41" s="67" t="s">
+      <c r="N41" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="O41" s="68"/>
-      <c r="P41" s="69"/>
+      <c r="O41" s="79"/>
+      <c r="P41" s="80"/>
       <c r="Q41" s="32"/>
-      <c r="R41" s="67" t="s">
+      <c r="R41" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="S41" s="68"/>
-      <c r="T41" s="69"/>
+      <c r="S41" s="79"/>
+      <c r="T41" s="80"/>
       <c r="U41" s="31"/>
-      <c r="V41" s="67" t="s">
+      <c r="V41" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="W41" s="68"/>
-      <c r="X41" s="69"/>
+      <c r="W41" s="79"/>
+      <c r="X41" s="80"/>
       <c r="Y41" s="32"/>
-      <c r="Z41" s="67"/>
-      <c r="AA41" s="68"/>
-      <c r="AB41" s="69"/>
+      <c r="Z41" s="78"/>
+      <c r="AA41" s="79"/>
+      <c r="AB41" s="80"/>
       <c r="AC41" s="32"/>
-      <c r="AD41" s="151" t="s">
+      <c r="AD41" s="128" t="s">
         <v>24</v>
       </c>
-      <c r="AE41" s="152"/>
-      <c r="AF41" s="153"/>
+      <c r="AE41" s="129"/>
+      <c r="AF41" s="130"/>
       <c r="AG41" s="37"/>
-      <c r="AH41" s="67" t="s">
+      <c r="AH41" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="AI41" s="68"/>
-      <c r="AJ41" s="69"/>
+      <c r="AI41" s="79"/>
+      <c r="AJ41" s="80"/>
       <c r="AK41" s="31"/>
-      <c r="AL41" s="134" t="s">
+      <c r="AL41" s="117" t="s">
         <v>96</v>
       </c>
-      <c r="AM41" s="135"/>
-      <c r="AN41" s="136"/>
+      <c r="AM41" s="118"/>
+      <c r="AN41" s="119"/>
       <c r="AO41" s="31"/>
       <c r="AP41" s="31"/>
       <c r="AQ41" s="31"/>
@@ -4691,63 +4691,63 @@
     </row>
     <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12"/>
-      <c r="B42" s="67" t="s">
+      <c r="B42" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="C42" s="68"/>
-      <c r="D42" s="69"/>
+      <c r="C42" s="79"/>
+      <c r="D42" s="80"/>
       <c r="E42" s="44"/>
-      <c r="F42" s="67" t="s">
+      <c r="F42" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="G42" s="68"/>
-      <c r="H42" s="69"/>
+      <c r="G42" s="79"/>
+      <c r="H42" s="80"/>
       <c r="I42" s="31"/>
-      <c r="J42" s="67" t="s">
+      <c r="J42" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="K42" s="68"/>
-      <c r="L42" s="69"/>
+      <c r="K42" s="79"/>
+      <c r="L42" s="80"/>
       <c r="M42" s="5"/>
-      <c r="N42" s="67" t="s">
+      <c r="N42" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="O42" s="68"/>
-      <c r="P42" s="69"/>
+      <c r="O42" s="79"/>
+      <c r="P42" s="80"/>
       <c r="Q42" s="31"/>
-      <c r="R42" s="67" t="s">
+      <c r="R42" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="S42" s="68"/>
-      <c r="T42" s="69"/>
+      <c r="S42" s="79"/>
+      <c r="T42" s="80"/>
       <c r="U42" s="32"/>
-      <c r="V42" s="67" t="s">
+      <c r="V42" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="W42" s="68"/>
-      <c r="X42" s="69"/>
+      <c r="W42" s="79"/>
+      <c r="X42" s="80"/>
       <c r="Y42" s="32"/>
-      <c r="Z42" s="67"/>
-      <c r="AA42" s="68"/>
-      <c r="AB42" s="69"/>
+      <c r="Z42" s="78"/>
+      <c r="AA42" s="79"/>
+      <c r="AB42" s="80"/>
       <c r="AC42" s="32"/>
-      <c r="AD42" s="67" t="s">
+      <c r="AD42" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="AE42" s="68"/>
-      <c r="AF42" s="69"/>
+      <c r="AE42" s="79"/>
+      <c r="AF42" s="80"/>
       <c r="AG42" s="44"/>
-      <c r="AH42" s="67" t="s">
+      <c r="AH42" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="AI42" s="68"/>
-      <c r="AJ42" s="69"/>
+      <c r="AI42" s="79"/>
+      <c r="AJ42" s="80"/>
       <c r="AK42" s="31"/>
-      <c r="AL42" s="134" t="s">
+      <c r="AL42" s="117" t="s">
         <v>88</v>
       </c>
-      <c r="AM42" s="135"/>
-      <c r="AN42" s="136"/>
+      <c r="AM42" s="118"/>
+      <c r="AN42" s="119"/>
       <c r="AO42" s="31"/>
       <c r="AP42" s="31"/>
       <c r="AQ42" s="31"/>
@@ -4755,55 +4755,55 @@
     </row>
     <row r="43" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12"/>
-      <c r="B43" s="83"/>
-      <c r="C43" s="84"/>
-      <c r="D43" s="85"/>
+      <c r="B43" s="65"/>
+      <c r="C43" s="66"/>
+      <c r="D43" s="67"/>
       <c r="E43" s="35"/>
-      <c r="F43" s="83" t="s">
+      <c r="F43" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="G43" s="84"/>
-      <c r="H43" s="85"/>
+      <c r="G43" s="66"/>
+      <c r="H43" s="67"/>
       <c r="I43" s="40"/>
-      <c r="J43" s="83"/>
-      <c r="K43" s="84"/>
-      <c r="L43" s="85"/>
+      <c r="J43" s="65"/>
+      <c r="K43" s="66"/>
+      <c r="L43" s="67"/>
       <c r="M43" s="14"/>
-      <c r="N43" s="67" t="s">
+      <c r="N43" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="O43" s="68"/>
-      <c r="P43" s="69"/>
+      <c r="O43" s="79"/>
+      <c r="P43" s="80"/>
       <c r="Q43" s="40"/>
-      <c r="R43" s="67" t="s">
+      <c r="R43" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="S43" s="68"/>
-      <c r="T43" s="69"/>
+      <c r="S43" s="79"/>
+      <c r="T43" s="80"/>
       <c r="U43" s="40"/>
-      <c r="V43" s="83"/>
-      <c r="W43" s="84"/>
-      <c r="X43" s="85"/>
+      <c r="V43" s="65"/>
+      <c r="W43" s="66"/>
+      <c r="X43" s="67"/>
       <c r="Y43" s="40"/>
-      <c r="Z43" s="83"/>
-      <c r="AA43" s="84"/>
-      <c r="AB43" s="85"/>
+      <c r="Z43" s="65"/>
+      <c r="AA43" s="66"/>
+      <c r="AB43" s="67"/>
       <c r="AC43" s="40"/>
-      <c r="AD43" s="143" t="s">
-        <v>88</v>
-      </c>
-      <c r="AE43" s="144"/>
-      <c r="AF43" s="145"/>
+      <c r="AD43" s="78" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE43" s="79"/>
+      <c r="AF43" s="80"/>
       <c r="AG43" s="35"/>
-      <c r="AH43" s="67" t="s">
+      <c r="AH43" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="AI43" s="68"/>
-      <c r="AJ43" s="69"/>
+      <c r="AI43" s="79"/>
+      <c r="AJ43" s="80"/>
       <c r="AK43" s="40"/>
-      <c r="AL43" s="92"/>
-      <c r="AM43" s="93"/>
-      <c r="AN43" s="94"/>
+      <c r="AL43" s="131"/>
+      <c r="AM43" s="132"/>
+      <c r="AN43" s="133"/>
       <c r="AO43" s="31"/>
       <c r="AP43" s="31"/>
       <c r="AQ43" s="31"/>
@@ -4823,15 +4823,15 @@
       <c r="K44" s="35"/>
       <c r="L44" s="35"/>
       <c r="M44" s="14"/>
-      <c r="N44" s="67"/>
-      <c r="O44" s="68"/>
-      <c r="P44" s="69"/>
+      <c r="N44" s="78"/>
+      <c r="O44" s="79"/>
+      <c r="P44" s="80"/>
       <c r="Q44" s="36"/>
-      <c r="R44" s="67" t="s">
+      <c r="R44" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="S44" s="68"/>
-      <c r="T44" s="69"/>
+      <c r="S44" s="79"/>
+      <c r="T44" s="80"/>
       <c r="U44" s="50"/>
       <c r="V44" s="35"/>
       <c r="W44" s="35"/>
@@ -4841,17 +4841,17 @@
       <c r="AA44" s="35"/>
       <c r="AB44" s="35"/>
       <c r="AC44" s="36"/>
-      <c r="AD44" s="83" t="s">
+      <c r="AD44" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="AE44" s="84"/>
-      <c r="AF44" s="85"/>
+      <c r="AE44" s="66"/>
+      <c r="AF44" s="67"/>
       <c r="AG44" s="50"/>
-      <c r="AH44" s="83" t="s">
+      <c r="AH44" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="AI44" s="84"/>
-      <c r="AJ44" s="85"/>
+      <c r="AI44" s="66"/>
+      <c r="AJ44" s="67"/>
       <c r="AK44" s="32"/>
       <c r="AL44" s="35"/>
       <c r="AM44" s="35"/>
@@ -4863,50 +4863,50 @@
     </row>
     <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="12"/>
-      <c r="B45" s="81" t="s">
+      <c r="B45" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="C45" s="82"/>
+      <c r="C45" s="69"/>
       <c r="D45" s="55" t="s">
         <v>54</v>
       </c>
       <c r="E45" s="36"/>
-      <c r="F45" s="81" t="s">
+      <c r="F45" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="G45" s="82"/>
+      <c r="G45" s="69"/>
       <c r="H45" s="55" t="s">
         <v>43</v>
       </c>
       <c r="I45" s="32"/>
-      <c r="J45" s="81" t="s">
+      <c r="J45" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="K45" s="82"/>
+      <c r="K45" s="69"/>
       <c r="L45" s="55" t="s">
         <v>83</v>
       </c>
       <c r="M45" s="14"/>
-      <c r="N45" s="83"/>
-      <c r="O45" s="84"/>
-      <c r="P45" s="85"/>
+      <c r="N45" s="65"/>
+      <c r="O45" s="66"/>
+      <c r="P45" s="67"/>
       <c r="Q45" s="36"/>
-      <c r="R45" s="83" t="s">
+      <c r="R45" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="S45" s="84"/>
-      <c r="T45" s="85"/>
+      <c r="S45" s="66"/>
+      <c r="T45" s="67"/>
       <c r="U45" s="36"/>
-      <c r="V45" s="70" t="s">
+      <c r="V45" s="81" t="s">
         <v>62</v>
       </c>
-      <c r="W45" s="71"/>
+      <c r="W45" s="82"/>
       <c r="X45" s="34" t="s">
         <v>83</v>
       </c>
       <c r="Y45" s="36"/>
-      <c r="Z45" s="70"/>
-      <c r="AA45" s="71"/>
+      <c r="Z45" s="81"/>
+      <c r="AA45" s="82"/>
       <c r="AB45" s="34"/>
       <c r="AC45" s="36"/>
       <c r="AD45" s="35"/>
@@ -4917,10 +4917,10 @@
       <c r="AI45" s="35"/>
       <c r="AJ45" s="35"/>
       <c r="AK45" s="32"/>
-      <c r="AL45" s="70" t="s">
+      <c r="AL45" s="81" t="s">
         <v>72</v>
       </c>
-      <c r="AM45" s="71"/>
+      <c r="AM45" s="82"/>
       <c r="AN45" s="34" t="s">
         <v>54</v>
       </c>
@@ -4957,29 +4957,29 @@
       <c r="S46" s="35"/>
       <c r="T46" s="58"/>
       <c r="U46" s="36"/>
-      <c r="V46" s="72" t="s">
+      <c r="V46" s="106" t="s">
         <v>63</v>
       </c>
-      <c r="W46" s="73"/>
-      <c r="X46" s="74"/>
+      <c r="W46" s="107"/>
+      <c r="X46" s="108"/>
       <c r="Y46" s="36"/>
-      <c r="Z46" s="72"/>
-      <c r="AA46" s="73"/>
-      <c r="AB46" s="74"/>
+      <c r="Z46" s="106"/>
+      <c r="AA46" s="107"/>
+      <c r="AB46" s="108"/>
       <c r="AC46" s="36"/>
-      <c r="AD46" s="70"/>
-      <c r="AE46" s="71"/>
+      <c r="AD46" s="81"/>
+      <c r="AE46" s="82"/>
       <c r="AF46" s="34"/>
       <c r="AG46" s="36"/>
-      <c r="AH46" s="70"/>
-      <c r="AI46" s="71"/>
+      <c r="AH46" s="81"/>
+      <c r="AI46" s="82"/>
       <c r="AJ46" s="34"/>
       <c r="AK46" s="54"/>
-      <c r="AL46" s="72" t="s">
+      <c r="AL46" s="106" t="s">
         <v>51</v>
       </c>
-      <c r="AM46" s="73"/>
-      <c r="AN46" s="74"/>
+      <c r="AM46" s="107"/>
+      <c r="AN46" s="108"/>
       <c r="AO46" s="31"/>
       <c r="AP46" s="31"/>
       <c r="AQ46" s="31"/>
@@ -4987,49 +4987,49 @@
     </row>
     <row r="47" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12"/>
-      <c r="B47" s="78"/>
-      <c r="C47" s="79"/>
-      <c r="D47" s="80"/>
+      <c r="B47" s="73"/>
+      <c r="C47" s="74"/>
+      <c r="D47" s="75"/>
       <c r="E47" s="43"/>
-      <c r="F47" s="78"/>
-      <c r="G47" s="79"/>
-      <c r="H47" s="80"/>
+      <c r="F47" s="73"/>
+      <c r="G47" s="74"/>
+      <c r="H47" s="75"/>
       <c r="I47" s="37"/>
-      <c r="J47" s="78"/>
-      <c r="K47" s="79"/>
-      <c r="L47" s="80"/>
+      <c r="J47" s="73"/>
+      <c r="K47" s="74"/>
+      <c r="L47" s="75"/>
       <c r="M47" s="4"/>
-      <c r="N47" s="70" t="s">
+      <c r="N47" s="81" t="s">
         <v>62</v>
       </c>
-      <c r="O47" s="71"/>
+      <c r="O47" s="82"/>
       <c r="P47" s="34" t="s">
         <v>83</v>
       </c>
       <c r="Q47" s="37"/>
-      <c r="R47" s="70"/>
-      <c r="S47" s="71"/>
+      <c r="R47" s="81"/>
+      <c r="S47" s="82"/>
       <c r="T47" s="34"/>
       <c r="U47" s="43"/>
-      <c r="V47" s="75"/>
-      <c r="W47" s="76"/>
-      <c r="X47" s="77"/>
+      <c r="V47" s="83"/>
+      <c r="W47" s="84"/>
+      <c r="X47" s="85"/>
       <c r="Y47" s="43"/>
-      <c r="Z47" s="75"/>
-      <c r="AA47" s="76"/>
-      <c r="AB47" s="77"/>
+      <c r="Z47" s="83"/>
+      <c r="AA47" s="84"/>
+      <c r="AB47" s="85"/>
       <c r="AC47" s="35"/>
-      <c r="AD47" s="72"/>
-      <c r="AE47" s="73"/>
-      <c r="AF47" s="74"/>
+      <c r="AD47" s="106"/>
+      <c r="AE47" s="107"/>
+      <c r="AF47" s="108"/>
       <c r="AG47" s="43"/>
-      <c r="AH47" s="72"/>
-      <c r="AI47" s="73"/>
-      <c r="AJ47" s="74"/>
+      <c r="AH47" s="106"/>
+      <c r="AI47" s="107"/>
+      <c r="AJ47" s="108"/>
       <c r="AK47" s="37"/>
-      <c r="AL47" s="75"/>
-      <c r="AM47" s="76"/>
-      <c r="AN47" s="77"/>
+      <c r="AL47" s="83"/>
+      <c r="AM47" s="84"/>
+      <c r="AN47" s="85"/>
       <c r="AO47" s="31"/>
       <c r="AP47" s="31"/>
       <c r="AQ47" s="31"/>
@@ -5037,17 +5037,17 @@
     </row>
     <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12"/>
-      <c r="B48" s="67" t="s">
+      <c r="B48" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="C48" s="68"/>
-      <c r="D48" s="69"/>
+      <c r="C48" s="79"/>
+      <c r="D48" s="80"/>
       <c r="E48" s="37"/>
-      <c r="F48" s="67" t="s">
+      <c r="F48" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="G48" s="68"/>
-      <c r="H48" s="69"/>
+      <c r="G48" s="79"/>
+      <c r="H48" s="80"/>
       <c r="I48" s="44"/>
       <c r="J48" s="86" t="s">
         <v>10</v>
@@ -5055,56 +5055,56 @@
       <c r="K48" s="87"/>
       <c r="L48" s="88"/>
       <c r="M48" s="5"/>
-      <c r="N48" s="72" t="s">
+      <c r="N48" s="106" t="s">
         <v>63</v>
       </c>
-      <c r="O48" s="73"/>
-      <c r="P48" s="74"/>
+      <c r="O48" s="107"/>
+      <c r="P48" s="108"/>
       <c r="Q48" s="44"/>
-      <c r="R48" s="72"/>
-      <c r="S48" s="73"/>
-      <c r="T48" s="74"/>
+      <c r="R48" s="106"/>
+      <c r="S48" s="107"/>
+      <c r="T48" s="108"/>
       <c r="U48" s="37"/>
-      <c r="V48" s="89" t="s">
+      <c r="V48" s="70" t="s">
         <v>37</v>
       </c>
-      <c r="W48" s="90"/>
-      <c r="X48" s="91"/>
+      <c r="W48" s="71"/>
+      <c r="X48" s="72"/>
       <c r="Y48" s="37"/>
-      <c r="Z48" s="67"/>
-      <c r="AA48" s="68"/>
-      <c r="AB48" s="69"/>
+      <c r="Z48" s="78"/>
+      <c r="AA48" s="79"/>
+      <c r="AB48" s="80"/>
       <c r="AC48" s="43"/>
-      <c r="AD48" s="75"/>
-      <c r="AE48" s="76"/>
-      <c r="AF48" s="77"/>
+      <c r="AD48" s="83"/>
+      <c r="AE48" s="84"/>
+      <c r="AF48" s="85"/>
       <c r="AG48" s="37"/>
-      <c r="AH48" s="75"/>
-      <c r="AI48" s="76"/>
-      <c r="AJ48" s="77"/>
+      <c r="AH48" s="83"/>
+      <c r="AI48" s="84"/>
+      <c r="AJ48" s="85"/>
       <c r="AK48" s="44"/>
-      <c r="AL48" s="67" t="s">
+      <c r="AL48" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="AM48" s="68"/>
-      <c r="AN48" s="69"/>
+      <c r="AM48" s="79"/>
+      <c r="AN48" s="80"/>
       <c r="AO48" s="31"/>
       <c r="AP48" s="31"/>
       <c r="AQ48" s="31"/>
       <c r="AR48" s="13"/>
     </row>
     <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="67" t="s">
+      <c r="B49" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="C49" s="68"/>
-      <c r="D49" s="69"/>
+      <c r="C49" s="79"/>
+      <c r="D49" s="80"/>
       <c r="E49" s="35"/>
-      <c r="F49" s="67" t="s">
+      <c r="F49" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="G49" s="68"/>
-      <c r="H49" s="69"/>
+      <c r="G49" s="79"/>
+      <c r="H49" s="80"/>
       <c r="I49" s="44"/>
       <c r="J49" s="86" t="s">
         <v>12</v>
@@ -5112,90 +5112,90 @@
       <c r="K49" s="87"/>
       <c r="L49" s="88"/>
       <c r="M49" s="5"/>
-      <c r="N49" s="75"/>
-      <c r="O49" s="76"/>
-      <c r="P49" s="77"/>
+      <c r="N49" s="83"/>
+      <c r="O49" s="84"/>
+      <c r="P49" s="85"/>
       <c r="Q49" s="44"/>
-      <c r="R49" s="75"/>
-      <c r="S49" s="76"/>
-      <c r="T49" s="77"/>
+      <c r="R49" s="83"/>
+      <c r="S49" s="84"/>
+      <c r="T49" s="85"/>
       <c r="U49" s="44"/>
-      <c r="V49" s="67" t="s">
+      <c r="V49" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="W49" s="68"/>
-      <c r="X49" s="69"/>
+      <c r="W49" s="79"/>
+      <c r="X49" s="80"/>
       <c r="Y49" s="35"/>
-      <c r="Z49" s="67"/>
-      <c r="AA49" s="68"/>
-      <c r="AB49" s="69"/>
+      <c r="Z49" s="78"/>
+      <c r="AA49" s="79"/>
+      <c r="AB49" s="80"/>
       <c r="AC49" s="35"/>
-      <c r="AD49" s="67"/>
-      <c r="AE49" s="68"/>
-      <c r="AF49" s="69"/>
+      <c r="AD49" s="78"/>
+      <c r="AE49" s="79"/>
+      <c r="AF49" s="80"/>
       <c r="AG49" s="35"/>
-      <c r="AH49" s="67"/>
-      <c r="AI49" s="68"/>
-      <c r="AJ49" s="69"/>
+      <c r="AH49" s="78"/>
+      <c r="AI49" s="79"/>
+      <c r="AJ49" s="80"/>
       <c r="AK49" s="44"/>
-      <c r="AL49" s="67" t="s">
+      <c r="AL49" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="AM49" s="68"/>
-      <c r="AN49" s="69"/>
+      <c r="AM49" s="79"/>
+      <c r="AN49" s="80"/>
       <c r="AO49" s="31"/>
       <c r="AP49" s="31"/>
       <c r="AQ49" s="31"/>
       <c r="AR49" s="13"/>
     </row>
     <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="159" t="s">
+      <c r="B50" s="89" t="s">
         <v>100</v>
       </c>
-      <c r="C50" s="160"/>
-      <c r="D50" s="161"/>
+      <c r="C50" s="90"/>
+      <c r="D50" s="91"/>
       <c r="E50" s="50"/>
-      <c r="F50" s="83" t="s">
+      <c r="F50" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="G50" s="84"/>
-      <c r="H50" s="85"/>
+      <c r="G50" s="66"/>
+      <c r="H50" s="67"/>
       <c r="I50" s="50"/>
-      <c r="J50" s="83" t="s">
+      <c r="J50" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="K50" s="84"/>
-      <c r="L50" s="85"/>
+      <c r="K50" s="66"/>
+      <c r="L50" s="67"/>
       <c r="M50" s="5"/>
-      <c r="N50" s="89" t="s">
+      <c r="N50" s="70" t="s">
         <v>37</v>
       </c>
-      <c r="O50" s="90"/>
-      <c r="P50" s="91"/>
+      <c r="O50" s="71"/>
+      <c r="P50" s="72"/>
       <c r="Q50" s="50"/>
-      <c r="R50" s="67"/>
-      <c r="S50" s="68"/>
-      <c r="T50" s="69"/>
+      <c r="R50" s="78"/>
+      <c r="S50" s="79"/>
+      <c r="T50" s="80"/>
       <c r="U50" s="50"/>
-      <c r="V50" s="83"/>
-      <c r="W50" s="84"/>
-      <c r="X50" s="85"/>
+      <c r="V50" s="65"/>
+      <c r="W50" s="66"/>
+      <c r="X50" s="67"/>
       <c r="Y50" s="50"/>
-      <c r="Z50" s="83"/>
-      <c r="AA50" s="84"/>
-      <c r="AB50" s="85"/>
+      <c r="Z50" s="65"/>
+      <c r="AA50" s="66"/>
+      <c r="AB50" s="67"/>
       <c r="AC50" s="50"/>
-      <c r="AD50" s="83"/>
-      <c r="AE50" s="84"/>
-      <c r="AF50" s="85"/>
+      <c r="AD50" s="65"/>
+      <c r="AE50" s="66"/>
+      <c r="AF50" s="67"/>
       <c r="AG50" s="50"/>
-      <c r="AH50" s="83"/>
-      <c r="AI50" s="84"/>
-      <c r="AJ50" s="85"/>
+      <c r="AH50" s="65"/>
+      <c r="AI50" s="66"/>
+      <c r="AJ50" s="67"/>
       <c r="AK50" s="50"/>
-      <c r="AL50" s="83"/>
-      <c r="AM50" s="84"/>
-      <c r="AN50" s="85"/>
+      <c r="AL50" s="65"/>
+      <c r="AM50" s="66"/>
+      <c r="AN50" s="67"/>
       <c r="AO50" s="31"/>
       <c r="AP50" s="31"/>
       <c r="AQ50" s="31"/>
@@ -5214,15 +5214,15 @@
       <c r="K51" s="35"/>
       <c r="L51" s="35"/>
       <c r="M51" s="14"/>
-      <c r="N51" s="83" t="s">
+      <c r="N51" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="O51" s="84"/>
-      <c r="P51" s="85"/>
+      <c r="O51" s="66"/>
+      <c r="P51" s="67"/>
       <c r="Q51" s="35"/>
-      <c r="R51" s="83"/>
-      <c r="S51" s="84"/>
-      <c r="T51" s="85"/>
+      <c r="R51" s="65"/>
+      <c r="S51" s="66"/>
+      <c r="T51" s="67"/>
       <c r="U51" s="36"/>
       <c r="V51" s="35"/>
       <c r="W51" s="35"/>
@@ -5249,26 +5249,26 @@
       <c r="AR51" s="13"/>
     </row>
     <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="65" t="s">
+      <c r="B52" s="76" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="66"/>
+      <c r="C52" s="77"/>
       <c r="D52" s="57" t="s">
         <v>85</v>
       </c>
       <c r="E52" s="36"/>
-      <c r="F52" s="65" t="s">
+      <c r="F52" s="76" t="s">
         <v>101</v>
       </c>
-      <c r="G52" s="66"/>
+      <c r="G52" s="77"/>
       <c r="H52" s="57" t="s">
         <v>102</v>
       </c>
       <c r="I52" s="54"/>
-      <c r="J52" s="65" t="s">
+      <c r="J52" s="76" t="s">
         <v>101</v>
       </c>
-      <c r="K52" s="66"/>
+      <c r="K52" s="77"/>
       <c r="L52" s="57" t="s">
         <v>93</v>
       </c>
@@ -5281,24 +5281,24 @@
       <c r="S52" s="35"/>
       <c r="T52" s="35"/>
       <c r="U52" s="35"/>
-      <c r="V52" s="70"/>
-      <c r="W52" s="71"/>
+      <c r="V52" s="81"/>
+      <c r="W52" s="82"/>
       <c r="X52" s="34"/>
       <c r="Y52" s="36"/>
-      <c r="Z52" s="70"/>
-      <c r="AA52" s="71"/>
+      <c r="Z52" s="81"/>
+      <c r="AA52" s="82"/>
       <c r="AB52" s="34"/>
       <c r="AC52" s="36"/>
-      <c r="AD52" s="70"/>
-      <c r="AE52" s="71"/>
+      <c r="AD52" s="81"/>
+      <c r="AE52" s="82"/>
       <c r="AF52" s="34"/>
       <c r="AG52" s="36"/>
-      <c r="AH52" s="70"/>
-      <c r="AI52" s="71"/>
+      <c r="AH52" s="81"/>
+      <c r="AI52" s="82"/>
       <c r="AJ52" s="34"/>
       <c r="AK52" s="54"/>
-      <c r="AL52" s="70"/>
-      <c r="AM52" s="71"/>
+      <c r="AL52" s="81"/>
+      <c r="AM52" s="82"/>
       <c r="AN52" s="34"/>
       <c r="AR52" s="13"/>
     </row>
@@ -5321,213 +5321,213 @@
       <c r="K53" s="63"/>
       <c r="L53" s="64"/>
       <c r="M53" s="4"/>
-      <c r="N53" s="70"/>
-      <c r="O53" s="71"/>
+      <c r="N53" s="81"/>
+      <c r="O53" s="82"/>
       <c r="P53" s="34"/>
       <c r="Q53" s="32"/>
-      <c r="R53" s="70"/>
-      <c r="S53" s="71"/>
+      <c r="R53" s="81"/>
+      <c r="S53" s="82"/>
       <c r="T53" s="34"/>
       <c r="U53" s="43"/>
-      <c r="V53" s="72"/>
-      <c r="W53" s="73"/>
-      <c r="X53" s="74"/>
+      <c r="V53" s="106"/>
+      <c r="W53" s="107"/>
+      <c r="X53" s="108"/>
       <c r="Y53" s="36"/>
-      <c r="Z53" s="72"/>
-      <c r="AA53" s="73"/>
-      <c r="AB53" s="74"/>
+      <c r="Z53" s="106"/>
+      <c r="AA53" s="107"/>
+      <c r="AB53" s="108"/>
       <c r="AC53" s="35"/>
-      <c r="AD53" s="72"/>
-      <c r="AE53" s="73"/>
-      <c r="AF53" s="74"/>
+      <c r="AD53" s="106"/>
+      <c r="AE53" s="107"/>
+      <c r="AF53" s="108"/>
       <c r="AG53" s="36"/>
-      <c r="AH53" s="72"/>
-      <c r="AI53" s="73"/>
-      <c r="AJ53" s="74"/>
+      <c r="AH53" s="106"/>
+      <c r="AI53" s="107"/>
+      <c r="AJ53" s="108"/>
       <c r="AK53" s="35"/>
-      <c r="AL53" s="72"/>
-      <c r="AM53" s="73"/>
-      <c r="AN53" s="74"/>
+      <c r="AL53" s="106"/>
+      <c r="AM53" s="107"/>
+      <c r="AN53" s="108"/>
       <c r="AR53" s="13"/>
     </row>
     <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="78"/>
-      <c r="C54" s="79"/>
-      <c r="D54" s="80"/>
+      <c r="B54" s="73"/>
+      <c r="C54" s="74"/>
+      <c r="D54" s="75"/>
       <c r="E54" s="43"/>
-      <c r="F54" s="78"/>
-      <c r="G54" s="79"/>
-      <c r="H54" s="80"/>
+      <c r="F54" s="73"/>
+      <c r="G54" s="74"/>
+      <c r="H54" s="75"/>
       <c r="I54" s="35"/>
-      <c r="J54" s="78"/>
-      <c r="K54" s="79"/>
-      <c r="L54" s="80"/>
+      <c r="J54" s="73"/>
+      <c r="K54" s="74"/>
+      <c r="L54" s="75"/>
       <c r="M54" s="4"/>
-      <c r="N54" s="72"/>
-      <c r="O54" s="73"/>
-      <c r="P54" s="74"/>
+      <c r="N54" s="106"/>
+      <c r="O54" s="107"/>
+      <c r="P54" s="108"/>
       <c r="Q54" s="43"/>
-      <c r="R54" s="72"/>
-      <c r="S54" s="73"/>
-      <c r="T54" s="74"/>
+      <c r="R54" s="106"/>
+      <c r="S54" s="107"/>
+      <c r="T54" s="108"/>
       <c r="U54" s="37"/>
-      <c r="V54" s="75"/>
-      <c r="W54" s="76"/>
-      <c r="X54" s="77"/>
+      <c r="V54" s="83"/>
+      <c r="W54" s="84"/>
+      <c r="X54" s="85"/>
       <c r="Y54" s="43"/>
-      <c r="Z54" s="75"/>
-      <c r="AA54" s="76"/>
-      <c r="AB54" s="77"/>
+      <c r="Z54" s="83"/>
+      <c r="AA54" s="84"/>
+      <c r="AB54" s="85"/>
       <c r="AC54" s="31"/>
-      <c r="AD54" s="75"/>
-      <c r="AE54" s="76"/>
-      <c r="AF54" s="77"/>
+      <c r="AD54" s="83"/>
+      <c r="AE54" s="84"/>
+      <c r="AF54" s="85"/>
       <c r="AG54" s="43"/>
-      <c r="AH54" s="75"/>
-      <c r="AI54" s="76"/>
-      <c r="AJ54" s="77"/>
+      <c r="AH54" s="83"/>
+      <c r="AI54" s="84"/>
+      <c r="AJ54" s="85"/>
       <c r="AK54" s="35"/>
-      <c r="AL54" s="75"/>
-      <c r="AM54" s="76"/>
-      <c r="AN54" s="77"/>
+      <c r="AL54" s="83"/>
+      <c r="AM54" s="84"/>
+      <c r="AN54" s="85"/>
       <c r="AR54" s="13"/>
     </row>
     <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="67" t="s">
+      <c r="B55" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="C55" s="68"/>
-      <c r="D55" s="69"/>
+      <c r="C55" s="79"/>
+      <c r="D55" s="80"/>
       <c r="E55" s="37"/>
-      <c r="F55" s="67" t="s">
+      <c r="F55" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="G55" s="68"/>
-      <c r="H55" s="69"/>
+      <c r="G55" s="79"/>
+      <c r="H55" s="80"/>
       <c r="I55" s="40"/>
-      <c r="J55" s="67" t="s">
+      <c r="J55" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="K55" s="68"/>
-      <c r="L55" s="69"/>
+      <c r="K55" s="79"/>
+      <c r="L55" s="80"/>
       <c r="M55" s="5"/>
-      <c r="N55" s="75"/>
-      <c r="O55" s="76"/>
-      <c r="P55" s="77"/>
+      <c r="N55" s="83"/>
+      <c r="O55" s="84"/>
+      <c r="P55" s="85"/>
       <c r="Q55" s="43"/>
-      <c r="R55" s="75"/>
-      <c r="S55" s="76"/>
-      <c r="T55" s="77"/>
+      <c r="R55" s="83"/>
+      <c r="S55" s="84"/>
+      <c r="T55" s="85"/>
       <c r="U55" s="44"/>
-      <c r="V55" s="67"/>
-      <c r="W55" s="68"/>
-      <c r="X55" s="69"/>
+      <c r="V55" s="78"/>
+      <c r="W55" s="79"/>
+      <c r="X55" s="80"/>
       <c r="Y55" s="37"/>
-      <c r="Z55" s="67"/>
-      <c r="AA55" s="68"/>
-      <c r="AB55" s="69"/>
+      <c r="Z55" s="78"/>
+      <c r="AA55" s="79"/>
+      <c r="AB55" s="80"/>
       <c r="AC55" s="35"/>
-      <c r="AD55" s="67"/>
-      <c r="AE55" s="68"/>
-      <c r="AF55" s="69"/>
+      <c r="AD55" s="78"/>
+      <c r="AE55" s="79"/>
+      <c r="AF55" s="80"/>
       <c r="AG55" s="37"/>
-      <c r="AH55" s="67"/>
-      <c r="AI55" s="68"/>
-      <c r="AJ55" s="69"/>
+      <c r="AH55" s="78"/>
+      <c r="AI55" s="79"/>
+      <c r="AJ55" s="80"/>
       <c r="AK55" s="40"/>
-      <c r="AL55" s="67"/>
-      <c r="AM55" s="68"/>
-      <c r="AN55" s="69"/>
+      <c r="AL55" s="78"/>
+      <c r="AM55" s="79"/>
+      <c r="AN55" s="80"/>
       <c r="AR55" s="13"/>
     </row>
     <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="67" t="s">
+      <c r="B56" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="C56" s="68"/>
-      <c r="D56" s="69"/>
+      <c r="C56" s="79"/>
+      <c r="D56" s="80"/>
       <c r="E56" s="44"/>
-      <c r="F56" s="67" t="s">
+      <c r="F56" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="G56" s="68"/>
-      <c r="H56" s="69"/>
+      <c r="G56" s="79"/>
+      <c r="H56" s="80"/>
       <c r="I56" s="44"/>
-      <c r="J56" s="67" t="s">
+      <c r="J56" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="K56" s="68"/>
-      <c r="L56" s="69"/>
+      <c r="K56" s="79"/>
+      <c r="L56" s="80"/>
       <c r="M56" s="5"/>
-      <c r="N56" s="67"/>
-      <c r="O56" s="68"/>
-      <c r="P56" s="69"/>
+      <c r="N56" s="78"/>
+      <c r="O56" s="79"/>
+      <c r="P56" s="80"/>
       <c r="Q56" s="43"/>
-      <c r="R56" s="67"/>
-      <c r="S56" s="68"/>
-      <c r="T56" s="69"/>
+      <c r="R56" s="78"/>
+      <c r="S56" s="79"/>
+      <c r="T56" s="80"/>
       <c r="U56" s="44"/>
-      <c r="V56" s="67"/>
-      <c r="W56" s="68"/>
-      <c r="X56" s="69"/>
+      <c r="V56" s="78"/>
+      <c r="W56" s="79"/>
+      <c r="X56" s="80"/>
       <c r="Y56" s="44"/>
-      <c r="Z56" s="67"/>
-      <c r="AA56" s="68"/>
-      <c r="AB56" s="69"/>
+      <c r="Z56" s="78"/>
+      <c r="AA56" s="79"/>
+      <c r="AB56" s="80"/>
       <c r="AC56" s="43"/>
-      <c r="AD56" s="67"/>
-      <c r="AE56" s="68"/>
-      <c r="AF56" s="69"/>
+      <c r="AD56" s="78"/>
+      <c r="AE56" s="79"/>
+      <c r="AF56" s="80"/>
       <c r="AG56" s="44"/>
-      <c r="AH56" s="67"/>
-      <c r="AI56" s="68"/>
-      <c r="AJ56" s="69"/>
+      <c r="AH56" s="78"/>
+      <c r="AI56" s="79"/>
+      <c r="AJ56" s="80"/>
       <c r="AK56" s="44"/>
-      <c r="AL56" s="67"/>
-      <c r="AM56" s="68"/>
-      <c r="AN56" s="69"/>
+      <c r="AL56" s="78"/>
+      <c r="AM56" s="79"/>
+      <c r="AN56" s="80"/>
       <c r="AR56" s="13"/>
     </row>
     <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="83"/>
-      <c r="C57" s="84"/>
-      <c r="D57" s="85"/>
+      <c r="B57" s="65"/>
+      <c r="C57" s="66"/>
+      <c r="D57" s="67"/>
       <c r="E57" s="35"/>
-      <c r="F57" s="83"/>
-      <c r="G57" s="84"/>
-      <c r="H57" s="85"/>
+      <c r="F57" s="65"/>
+      <c r="G57" s="66"/>
+      <c r="H57" s="67"/>
       <c r="I57" s="50"/>
-      <c r="J57" s="83"/>
-      <c r="K57" s="84"/>
-      <c r="L57" s="85"/>
+      <c r="J57" s="65"/>
+      <c r="K57" s="66"/>
+      <c r="L57" s="67"/>
       <c r="M57" s="5"/>
-      <c r="N57" s="83"/>
-      <c r="O57" s="84"/>
-      <c r="P57" s="85"/>
+      <c r="N57" s="65"/>
+      <c r="O57" s="66"/>
+      <c r="P57" s="67"/>
       <c r="Q57" s="31"/>
-      <c r="R57" s="83"/>
-      <c r="S57" s="84"/>
-      <c r="T57" s="85"/>
+      <c r="R57" s="65"/>
+      <c r="S57" s="66"/>
+      <c r="T57" s="67"/>
       <c r="U57" s="50"/>
-      <c r="V57" s="83"/>
-      <c r="W57" s="84"/>
-      <c r="X57" s="85"/>
+      <c r="V57" s="65"/>
+      <c r="W57" s="66"/>
+      <c r="X57" s="67"/>
       <c r="Y57" s="35"/>
-      <c r="Z57" s="83"/>
-      <c r="AA57" s="84"/>
-      <c r="AB57" s="85"/>
+      <c r="Z57" s="65"/>
+      <c r="AA57" s="66"/>
+      <c r="AB57" s="67"/>
       <c r="AC57" s="31"/>
-      <c r="AD57" s="83"/>
-      <c r="AE57" s="84"/>
-      <c r="AF57" s="85"/>
+      <c r="AD57" s="65"/>
+      <c r="AE57" s="66"/>
+      <c r="AF57" s="67"/>
       <c r="AG57" s="35"/>
-      <c r="AH57" s="83"/>
-      <c r="AI57" s="84"/>
-      <c r="AJ57" s="85"/>
+      <c r="AH57" s="65"/>
+      <c r="AI57" s="66"/>
+      <c r="AJ57" s="67"/>
       <c r="AK57" s="50"/>
-      <c r="AL57" s="83"/>
-      <c r="AM57" s="84"/>
-      <c r="AN57" s="85"/>
+      <c r="AL57" s="65"/>
+      <c r="AM57" s="66"/>
+      <c r="AN57" s="67"/>
       <c r="AR57" s="13"/>
     </row>
     <row r="58" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5573,48 +5573,48 @@
       <c r="AR58" s="13"/>
     </row>
     <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="65" t="s">
+      <c r="B59" s="76" t="s">
         <v>101</v>
       </c>
-      <c r="C59" s="66"/>
+      <c r="C59" s="77"/>
       <c r="D59" s="57" t="s">
         <v>102</v>
       </c>
       <c r="E59" s="50"/>
-      <c r="F59" s="81"/>
-      <c r="G59" s="82"/>
+      <c r="F59" s="68"/>
+      <c r="G59" s="69"/>
       <c r="H59" s="55"/>
       <c r="I59" s="32"/>
-      <c r="J59" s="81"/>
-      <c r="K59" s="82"/>
+      <c r="J59" s="68"/>
+      <c r="K59" s="69"/>
       <c r="L59" s="55"/>
       <c r="M59" s="6"/>
-      <c r="N59" s="70"/>
-      <c r="O59" s="71"/>
+      <c r="N59" s="81"/>
+      <c r="O59" s="82"/>
       <c r="P59" s="34"/>
       <c r="Q59" s="36"/>
-      <c r="R59" s="70"/>
-      <c r="S59" s="71"/>
+      <c r="R59" s="81"/>
+      <c r="S59" s="82"/>
       <c r="T59" s="34"/>
       <c r="U59" s="50"/>
-      <c r="V59" s="70"/>
-      <c r="W59" s="71"/>
+      <c r="V59" s="81"/>
+      <c r="W59" s="82"/>
       <c r="X59" s="34"/>
       <c r="Y59" s="32"/>
-      <c r="Z59" s="70"/>
-      <c r="AA59" s="71"/>
+      <c r="Z59" s="81"/>
+      <c r="AA59" s="82"/>
       <c r="AB59" s="34"/>
       <c r="AC59" s="32"/>
-      <c r="AD59" s="70"/>
-      <c r="AE59" s="71"/>
+      <c r="AD59" s="81"/>
+      <c r="AE59" s="82"/>
       <c r="AF59" s="34"/>
       <c r="AG59" s="50"/>
-      <c r="AH59" s="70"/>
-      <c r="AI59" s="71"/>
+      <c r="AH59" s="81"/>
+      <c r="AI59" s="82"/>
       <c r="AJ59" s="34"/>
       <c r="AK59" s="32"/>
-      <c r="AL59" s="70"/>
-      <c r="AM59" s="71"/>
+      <c r="AL59" s="81"/>
+      <c r="AM59" s="82"/>
       <c r="AN59" s="34"/>
       <c r="AR59" s="13"/>
     </row>
@@ -5633,205 +5633,205 @@
       <c r="K60" s="63"/>
       <c r="L60" s="64"/>
       <c r="M60" s="4"/>
-      <c r="N60" s="72"/>
-      <c r="O60" s="73"/>
-      <c r="P60" s="74"/>
+      <c r="N60" s="106"/>
+      <c r="O60" s="107"/>
+      <c r="P60" s="108"/>
       <c r="Q60" s="43"/>
-      <c r="R60" s="72"/>
-      <c r="S60" s="73"/>
-      <c r="T60" s="74"/>
+      <c r="R60" s="106"/>
+      <c r="S60" s="107"/>
+      <c r="T60" s="108"/>
       <c r="U60" s="32"/>
-      <c r="V60" s="72"/>
-      <c r="W60" s="73"/>
-      <c r="X60" s="74"/>
+      <c r="V60" s="106"/>
+      <c r="W60" s="107"/>
+      <c r="X60" s="108"/>
       <c r="Y60" s="32"/>
-      <c r="Z60" s="72"/>
-      <c r="AA60" s="73"/>
-      <c r="AB60" s="74"/>
+      <c r="Z60" s="106"/>
+      <c r="AA60" s="107"/>
+      <c r="AB60" s="108"/>
       <c r="AC60" s="54"/>
-      <c r="AD60" s="72"/>
-      <c r="AE60" s="73"/>
-      <c r="AF60" s="74"/>
+      <c r="AD60" s="106"/>
+      <c r="AE60" s="107"/>
+      <c r="AF60" s="108"/>
       <c r="AG60" s="32"/>
-      <c r="AH60" s="72"/>
-      <c r="AI60" s="73"/>
-      <c r="AJ60" s="74"/>
+      <c r="AH60" s="106"/>
+      <c r="AI60" s="107"/>
+      <c r="AJ60" s="108"/>
       <c r="AK60" s="32"/>
-      <c r="AL60" s="72"/>
-      <c r="AM60" s="73"/>
-      <c r="AN60" s="74"/>
+      <c r="AL60" s="106"/>
+      <c r="AM60" s="107"/>
+      <c r="AN60" s="108"/>
       <c r="AR60" s="13"/>
     </row>
     <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="78"/>
-      <c r="C61" s="79"/>
-      <c r="D61" s="80"/>
+      <c r="B61" s="73"/>
+      <c r="C61" s="74"/>
+      <c r="D61" s="75"/>
       <c r="E61" s="32"/>
-      <c r="F61" s="78"/>
-      <c r="G61" s="79"/>
-      <c r="H61" s="80"/>
+      <c r="F61" s="73"/>
+      <c r="G61" s="74"/>
+      <c r="H61" s="75"/>
       <c r="I61" s="32"/>
-      <c r="J61" s="78"/>
-      <c r="K61" s="79"/>
-      <c r="L61" s="80"/>
+      <c r="J61" s="73"/>
+      <c r="K61" s="74"/>
+      <c r="L61" s="75"/>
       <c r="M61" s="4"/>
-      <c r="N61" s="75"/>
-      <c r="O61" s="76"/>
-      <c r="P61" s="77"/>
+      <c r="N61" s="83"/>
+      <c r="O61" s="84"/>
+      <c r="P61" s="85"/>
       <c r="Q61" s="37"/>
-      <c r="R61" s="75"/>
-      <c r="S61" s="76"/>
-      <c r="T61" s="77"/>
+      <c r="R61" s="83"/>
+      <c r="S61" s="84"/>
+      <c r="T61" s="85"/>
       <c r="U61" s="32"/>
-      <c r="V61" s="75"/>
-      <c r="W61" s="76"/>
-      <c r="X61" s="77"/>
+      <c r="V61" s="83"/>
+      <c r="W61" s="84"/>
+      <c r="X61" s="85"/>
       <c r="Y61" s="32"/>
-      <c r="Z61" s="75"/>
-      <c r="AA61" s="76"/>
-      <c r="AB61" s="77"/>
+      <c r="Z61" s="83"/>
+      <c r="AA61" s="84"/>
+      <c r="AB61" s="85"/>
       <c r="AC61" s="35"/>
-      <c r="AD61" s="75"/>
-      <c r="AE61" s="76"/>
-      <c r="AF61" s="77"/>
+      <c r="AD61" s="83"/>
+      <c r="AE61" s="84"/>
+      <c r="AF61" s="85"/>
       <c r="AG61" s="32"/>
-      <c r="AH61" s="75"/>
-      <c r="AI61" s="76"/>
-      <c r="AJ61" s="77"/>
+      <c r="AH61" s="83"/>
+      <c r="AI61" s="84"/>
+      <c r="AJ61" s="85"/>
       <c r="AK61" s="32"/>
-      <c r="AL61" s="75"/>
-      <c r="AM61" s="76"/>
-      <c r="AN61" s="77"/>
+      <c r="AL61" s="83"/>
+      <c r="AM61" s="84"/>
+      <c r="AN61" s="85"/>
       <c r="AR61" s="13"/>
     </row>
     <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="89" t="s">
+      <c r="B62" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="C62" s="90"/>
-      <c r="D62" s="91"/>
+      <c r="C62" s="71"/>
+      <c r="D62" s="72"/>
       <c r="E62" s="37"/>
-      <c r="F62" s="67"/>
-      <c r="G62" s="68"/>
-      <c r="H62" s="69"/>
+      <c r="F62" s="78"/>
+      <c r="G62" s="79"/>
+      <c r="H62" s="80"/>
       <c r="I62" s="35"/>
-      <c r="J62" s="89"/>
-      <c r="K62" s="90"/>
-      <c r="L62" s="91"/>
+      <c r="J62" s="70"/>
+      <c r="K62" s="71"/>
+      <c r="L62" s="72"/>
       <c r="M62" s="4"/>
-      <c r="N62" s="67"/>
-      <c r="O62" s="68"/>
-      <c r="P62" s="69"/>
+      <c r="N62" s="78"/>
+      <c r="O62" s="79"/>
+      <c r="P62" s="80"/>
       <c r="Q62" s="44"/>
-      <c r="R62" s="89"/>
-      <c r="S62" s="90"/>
-      <c r="T62" s="91"/>
+      <c r="R62" s="70"/>
+      <c r="S62" s="71"/>
+      <c r="T62" s="72"/>
       <c r="U62" s="37"/>
-      <c r="V62" s="89"/>
-      <c r="W62" s="90"/>
-      <c r="X62" s="91"/>
+      <c r="V62" s="70"/>
+      <c r="W62" s="71"/>
+      <c r="X62" s="72"/>
       <c r="Y62" s="35"/>
-      <c r="Z62" s="67"/>
-      <c r="AA62" s="68"/>
-      <c r="AB62" s="69"/>
+      <c r="Z62" s="78"/>
+      <c r="AA62" s="79"/>
+      <c r="AB62" s="80"/>
       <c r="AC62" s="35"/>
-      <c r="AD62" s="89"/>
-      <c r="AE62" s="90"/>
-      <c r="AF62" s="91"/>
+      <c r="AD62" s="70"/>
+      <c r="AE62" s="71"/>
+      <c r="AF62" s="72"/>
       <c r="AG62" s="37"/>
-      <c r="AH62" s="67"/>
-      <c r="AI62" s="68"/>
-      <c r="AJ62" s="69"/>
+      <c r="AH62" s="78"/>
+      <c r="AI62" s="79"/>
+      <c r="AJ62" s="80"/>
       <c r="AK62" s="35"/>
-      <c r="AL62" s="89"/>
-      <c r="AM62" s="90"/>
-      <c r="AN62" s="91"/>
+      <c r="AL62" s="70"/>
+      <c r="AM62" s="71"/>
+      <c r="AN62" s="72"/>
       <c r="AR62" s="13"/>
     </row>
     <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="67" t="s">
+      <c r="B63" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="C63" s="68"/>
-      <c r="D63" s="69"/>
+      <c r="C63" s="79"/>
+      <c r="D63" s="80"/>
       <c r="E63" s="44"/>
-      <c r="F63" s="67"/>
-      <c r="G63" s="68"/>
-      <c r="H63" s="69"/>
+      <c r="F63" s="78"/>
+      <c r="G63" s="79"/>
+      <c r="H63" s="80"/>
       <c r="I63" s="40"/>
-      <c r="J63" s="67"/>
-      <c r="K63" s="68"/>
-      <c r="L63" s="69"/>
+      <c r="J63" s="78"/>
+      <c r="K63" s="79"/>
+      <c r="L63" s="80"/>
       <c r="M63" s="5"/>
-      <c r="N63" s="67"/>
-      <c r="O63" s="68"/>
-      <c r="P63" s="69"/>
+      <c r="N63" s="78"/>
+      <c r="O63" s="79"/>
+      <c r="P63" s="80"/>
       <c r="Q63" s="44"/>
-      <c r="R63" s="67"/>
-      <c r="S63" s="68"/>
-      <c r="T63" s="69"/>
+      <c r="R63" s="78"/>
+      <c r="S63" s="79"/>
+      <c r="T63" s="80"/>
       <c r="U63" s="44"/>
-      <c r="V63" s="67"/>
-      <c r="W63" s="68"/>
-      <c r="X63" s="69"/>
+      <c r="V63" s="78"/>
+      <c r="W63" s="79"/>
+      <c r="X63" s="80"/>
       <c r="Y63" s="40"/>
-      <c r="Z63" s="67"/>
-      <c r="AA63" s="68"/>
-      <c r="AB63" s="69"/>
+      <c r="Z63" s="78"/>
+      <c r="AA63" s="79"/>
+      <c r="AB63" s="80"/>
       <c r="AC63" s="40"/>
-      <c r="AD63" s="67"/>
-      <c r="AE63" s="68"/>
-      <c r="AF63" s="69"/>
+      <c r="AD63" s="78"/>
+      <c r="AE63" s="79"/>
+      <c r="AF63" s="80"/>
       <c r="AG63" s="44"/>
-      <c r="AH63" s="67"/>
-      <c r="AI63" s="68"/>
-      <c r="AJ63" s="69"/>
+      <c r="AH63" s="78"/>
+      <c r="AI63" s="79"/>
+      <c r="AJ63" s="80"/>
       <c r="AK63" s="40"/>
-      <c r="AL63" s="67"/>
-      <c r="AM63" s="68"/>
-      <c r="AN63" s="69"/>
+      <c r="AL63" s="78"/>
+      <c r="AM63" s="79"/>
+      <c r="AN63" s="80"/>
       <c r="AR63" s="13"/>
     </row>
     <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="83"/>
-      <c r="C64" s="84"/>
-      <c r="D64" s="85"/>
+      <c r="B64" s="65"/>
+      <c r="C64" s="66"/>
+      <c r="D64" s="67"/>
       <c r="E64" s="35"/>
-      <c r="F64" s="83"/>
-      <c r="G64" s="84"/>
-      <c r="H64" s="85"/>
+      <c r="F64" s="65"/>
+      <c r="G64" s="66"/>
+      <c r="H64" s="67"/>
       <c r="I64" s="50"/>
-      <c r="J64" s="83"/>
-      <c r="K64" s="84"/>
-      <c r="L64" s="85"/>
+      <c r="J64" s="65"/>
+      <c r="K64" s="66"/>
+      <c r="L64" s="67"/>
       <c r="M64" s="5"/>
-      <c r="N64" s="83"/>
-      <c r="O64" s="84"/>
-      <c r="P64" s="85"/>
+      <c r="N64" s="65"/>
+      <c r="O64" s="66"/>
+      <c r="P64" s="67"/>
       <c r="Q64" s="50"/>
-      <c r="R64" s="83"/>
-      <c r="S64" s="84"/>
-      <c r="T64" s="85"/>
+      <c r="R64" s="65"/>
+      <c r="S64" s="66"/>
+      <c r="T64" s="67"/>
       <c r="U64" s="35"/>
-      <c r="V64" s="83"/>
-      <c r="W64" s="84"/>
-      <c r="X64" s="85"/>
+      <c r="V64" s="65"/>
+      <c r="W64" s="66"/>
+      <c r="X64" s="67"/>
       <c r="Y64" s="50"/>
-      <c r="Z64" s="83"/>
-      <c r="AA64" s="84"/>
-      <c r="AB64" s="85"/>
+      <c r="Z64" s="65"/>
+      <c r="AA64" s="66"/>
+      <c r="AB64" s="67"/>
       <c r="AC64" s="50"/>
-      <c r="AD64" s="83"/>
-      <c r="AE64" s="84"/>
-      <c r="AF64" s="85"/>
+      <c r="AD64" s="65"/>
+      <c r="AE64" s="66"/>
+      <c r="AF64" s="67"/>
       <c r="AG64" s="35"/>
-      <c r="AH64" s="83"/>
-      <c r="AI64" s="84"/>
-      <c r="AJ64" s="85"/>
+      <c r="AH64" s="65"/>
+      <c r="AI64" s="66"/>
+      <c r="AJ64" s="67"/>
       <c r="AK64" s="50"/>
-      <c r="AL64" s="83"/>
-      <c r="AM64" s="84"/>
-      <c r="AN64" s="85"/>
+      <c r="AL64" s="65"/>
+      <c r="AM64" s="66"/>
+      <c r="AN64" s="67"/>
       <c r="AR64" s="13"/>
     </row>
     <row r="65" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5882,52 +5882,52 @@
     </row>
     <row r="66" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="12"/>
-      <c r="B66" s="65" t="s">
+      <c r="B66" s="76" t="s">
         <v>101</v>
       </c>
-      <c r="C66" s="66"/>
+      <c r="C66" s="77"/>
       <c r="D66" s="57" t="s">
         <v>54</v>
       </c>
       <c r="E66" s="36"/>
-      <c r="F66" s="81"/>
-      <c r="G66" s="82"/>
+      <c r="F66" s="68"/>
+      <c r="G66" s="69"/>
       <c r="H66" s="55"/>
       <c r="I66" s="32"/>
-      <c r="J66" s="81"/>
-      <c r="K66" s="82"/>
+      <c r="J66" s="68"/>
+      <c r="K66" s="69"/>
       <c r="L66" s="55"/>
       <c r="M66" s="6"/>
-      <c r="N66" s="70" t="s">
+      <c r="N66" s="81" t="s">
         <v>107</v>
       </c>
-      <c r="O66" s="71"/>
+      <c r="O66" s="82"/>
       <c r="P66" s="34"/>
       <c r="Q66" s="36"/>
-      <c r="R66" s="70"/>
-      <c r="S66" s="71"/>
+      <c r="R66" s="81"/>
+      <c r="S66" s="82"/>
       <c r="T66" s="34"/>
       <c r="U66" s="36"/>
-      <c r="V66" s="70"/>
-      <c r="W66" s="71"/>
+      <c r="V66" s="81"/>
+      <c r="W66" s="82"/>
       <c r="X66" s="34"/>
       <c r="Y66" s="36"/>
-      <c r="Z66" s="70"/>
-      <c r="AA66" s="71"/>
+      <c r="Z66" s="81"/>
+      <c r="AA66" s="82"/>
       <c r="AB66" s="34"/>
       <c r="AC66" s="36"/>
-      <c r="AD66" s="70"/>
-      <c r="AE66" s="71"/>
+      <c r="AD66" s="81"/>
+      <c r="AE66" s="82"/>
       <c r="AF66" s="34"/>
       <c r="AG66" s="36"/>
-      <c r="AH66" s="70"/>
-      <c r="AI66" s="71"/>
+      <c r="AH66" s="81"/>
+      <c r="AI66" s="82"/>
       <c r="AJ66" s="34"/>
       <c r="AK66" s="32"/>
-      <c r="AL66" s="98" t="s">
+      <c r="AL66" s="126" t="s">
         <v>114</v>
       </c>
-      <c r="AM66" s="99"/>
+      <c r="AM66" s="127"/>
       <c r="AN66" s="59"/>
       <c r="AO66" s="17"/>
       <c r="AP66" s="12"/>
@@ -5950,37 +5950,37 @@
       <c r="K67" s="63"/>
       <c r="L67" s="64"/>
       <c r="M67" s="4"/>
-      <c r="N67" s="72" t="s">
+      <c r="N67" s="106" t="s">
         <v>108</v>
       </c>
-      <c r="O67" s="73"/>
-      <c r="P67" s="74"/>
+      <c r="O67" s="107"/>
+      <c r="P67" s="108"/>
       <c r="Q67" s="37"/>
-      <c r="R67" s="72"/>
-      <c r="S67" s="73"/>
-      <c r="T67" s="74"/>
+      <c r="R67" s="106"/>
+      <c r="S67" s="107"/>
+      <c r="T67" s="108"/>
       <c r="U67" s="36"/>
-      <c r="V67" s="72"/>
-      <c r="W67" s="73"/>
-      <c r="X67" s="74"/>
+      <c r="V67" s="106"/>
+      <c r="W67" s="107"/>
+      <c r="X67" s="108"/>
       <c r="Y67" s="36"/>
-      <c r="Z67" s="72"/>
-      <c r="AA67" s="73"/>
-      <c r="AB67" s="74"/>
+      <c r="Z67" s="106"/>
+      <c r="AA67" s="107"/>
+      <c r="AB67" s="108"/>
       <c r="AC67" s="36"/>
-      <c r="AD67" s="72"/>
-      <c r="AE67" s="73"/>
-      <c r="AF67" s="74"/>
+      <c r="AD67" s="106"/>
+      <c r="AE67" s="107"/>
+      <c r="AF67" s="108"/>
       <c r="AG67" s="36"/>
-      <c r="AH67" s="72"/>
-      <c r="AI67" s="73"/>
-      <c r="AJ67" s="74"/>
+      <c r="AH67" s="106"/>
+      <c r="AI67" s="107"/>
+      <c r="AJ67" s="108"/>
       <c r="AK67" s="54"/>
-      <c r="AL67" s="100" t="s">
+      <c r="AL67" s="109" t="s">
         <v>51</v>
       </c>
-      <c r="AM67" s="101"/>
-      <c r="AN67" s="102"/>
+      <c r="AM67" s="110"/>
+      <c r="AN67" s="111"/>
       <c r="AO67" s="17"/>
       <c r="AP67" s="12"/>
       <c r="AQ67" s="12"/>
@@ -5988,47 +5988,47 @@
     </row>
     <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="12"/>
-      <c r="B68" s="78"/>
-      <c r="C68" s="79"/>
-      <c r="D68" s="80"/>
+      <c r="B68" s="73"/>
+      <c r="C68" s="74"/>
+      <c r="D68" s="75"/>
       <c r="E68" s="43"/>
-      <c r="F68" s="78"/>
-      <c r="G68" s="79"/>
-      <c r="H68" s="80"/>
+      <c r="F68" s="73"/>
+      <c r="G68" s="74"/>
+      <c r="H68" s="75"/>
       <c r="I68" s="35"/>
-      <c r="J68" s="78"/>
-      <c r="K68" s="79"/>
-      <c r="L68" s="80"/>
+      <c r="J68" s="73"/>
+      <c r="K68" s="74"/>
+      <c r="L68" s="75"/>
       <c r="M68" s="4"/>
-      <c r="N68" s="75"/>
-      <c r="O68" s="76"/>
-      <c r="P68" s="77"/>
+      <c r="N68" s="83"/>
+      <c r="O68" s="84"/>
+      <c r="P68" s="85"/>
       <c r="Q68" s="36"/>
-      <c r="R68" s="75"/>
-      <c r="S68" s="76"/>
-      <c r="T68" s="77"/>
+      <c r="R68" s="83"/>
+      <c r="S68" s="84"/>
+      <c r="T68" s="85"/>
       <c r="U68" s="43"/>
-      <c r="V68" s="75"/>
-      <c r="W68" s="76"/>
-      <c r="X68" s="77"/>
+      <c r="V68" s="83"/>
+      <c r="W68" s="84"/>
+      <c r="X68" s="85"/>
       <c r="Y68" s="43"/>
-      <c r="Z68" s="75"/>
-      <c r="AA68" s="76"/>
-      <c r="AB68" s="77"/>
+      <c r="Z68" s="83"/>
+      <c r="AA68" s="84"/>
+      <c r="AB68" s="85"/>
       <c r="AC68" s="35"/>
-      <c r="AD68" s="75"/>
-      <c r="AE68" s="76"/>
-      <c r="AF68" s="77"/>
+      <c r="AD68" s="83"/>
+      <c r="AE68" s="84"/>
+      <c r="AF68" s="85"/>
       <c r="AG68" s="43"/>
-      <c r="AH68" s="75"/>
-      <c r="AI68" s="76"/>
-      <c r="AJ68" s="77"/>
+      <c r="AH68" s="83"/>
+      <c r="AI68" s="84"/>
+      <c r="AJ68" s="85"/>
       <c r="AK68" s="35"/>
-      <c r="AL68" s="127" t="s">
+      <c r="AL68" s="114" t="s">
         <v>78</v>
       </c>
-      <c r="AM68" s="128"/>
-      <c r="AN68" s="156"/>
+      <c r="AM68" s="115"/>
+      <c r="AN68" s="116"/>
       <c r="AO68" s="17"/>
       <c r="AP68" s="27" t="s">
         <v>32</v>
@@ -6038,51 +6038,51 @@
     </row>
     <row r="69" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="12"/>
-      <c r="B69" s="67" t="s">
+      <c r="B69" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="C69" s="68"/>
-      <c r="D69" s="69"/>
+      <c r="C69" s="79"/>
+      <c r="D69" s="80"/>
       <c r="E69" s="37"/>
-      <c r="F69" s="89"/>
-      <c r="G69" s="90"/>
-      <c r="H69" s="91"/>
+      <c r="F69" s="70"/>
+      <c r="G69" s="71"/>
+      <c r="H69" s="72"/>
       <c r="I69" s="37"/>
-      <c r="J69" s="67"/>
-      <c r="K69" s="68"/>
-      <c r="L69" s="69"/>
+      <c r="J69" s="78"/>
+      <c r="K69" s="79"/>
+      <c r="L69" s="80"/>
       <c r="M69" s="4"/>
-      <c r="N69" s="67" t="s">
+      <c r="N69" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="O69" s="68"/>
-      <c r="P69" s="69"/>
+      <c r="O69" s="79"/>
+      <c r="P69" s="80"/>
       <c r="Q69" s="43"/>
-      <c r="R69" s="67"/>
-      <c r="S69" s="68"/>
-      <c r="T69" s="69"/>
+      <c r="R69" s="78"/>
+      <c r="S69" s="79"/>
+      <c r="T69" s="80"/>
       <c r="U69" s="37"/>
-      <c r="V69" s="89"/>
-      <c r="W69" s="90"/>
-      <c r="X69" s="91"/>
+      <c r="V69" s="70"/>
+      <c r="W69" s="71"/>
+      <c r="X69" s="72"/>
       <c r="Y69" s="35"/>
-      <c r="Z69" s="89"/>
-      <c r="AA69" s="90"/>
-      <c r="AB69" s="91"/>
+      <c r="Z69" s="70"/>
+      <c r="AA69" s="71"/>
+      <c r="AB69" s="72"/>
       <c r="AC69" s="43"/>
-      <c r="AD69" s="67"/>
-      <c r="AE69" s="68"/>
-      <c r="AF69" s="69"/>
+      <c r="AD69" s="78"/>
+      <c r="AE69" s="79"/>
+      <c r="AF69" s="80"/>
       <c r="AG69" s="37"/>
-      <c r="AH69" s="89"/>
-      <c r="AI69" s="90"/>
-      <c r="AJ69" s="91"/>
+      <c r="AH69" s="70"/>
+      <c r="AI69" s="71"/>
+      <c r="AJ69" s="72"/>
       <c r="AK69" s="37"/>
-      <c r="AL69" s="67" t="s">
+      <c r="AL69" s="78" t="s">
         <v>80</v>
       </c>
-      <c r="AM69" s="68"/>
-      <c r="AN69" s="69"/>
+      <c r="AM69" s="79"/>
+      <c r="AN69" s="80"/>
       <c r="AO69" s="12"/>
       <c r="AP69" s="27" t="s">
         <v>33</v>
@@ -6092,49 +6092,49 @@
     </row>
     <row r="70" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="12"/>
-      <c r="B70" s="67" t="s">
+      <c r="B70" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="C70" s="68"/>
-      <c r="D70" s="69"/>
+      <c r="C70" s="79"/>
+      <c r="D70" s="80"/>
       <c r="E70" s="44"/>
-      <c r="F70" s="67"/>
-      <c r="G70" s="68"/>
-      <c r="H70" s="69"/>
+      <c r="F70" s="78"/>
+      <c r="G70" s="79"/>
+      <c r="H70" s="80"/>
       <c r="I70" s="44"/>
-      <c r="J70" s="67"/>
-      <c r="K70" s="68"/>
-      <c r="L70" s="69"/>
+      <c r="J70" s="78"/>
+      <c r="K70" s="79"/>
+      <c r="L70" s="80"/>
       <c r="M70" s="9"/>
-      <c r="N70" s="67"/>
-      <c r="O70" s="68"/>
-      <c r="P70" s="69"/>
+      <c r="N70" s="78"/>
+      <c r="O70" s="79"/>
+      <c r="P70" s="80"/>
       <c r="Q70" s="50"/>
-      <c r="R70" s="67"/>
-      <c r="S70" s="68"/>
-      <c r="T70" s="69"/>
+      <c r="R70" s="78"/>
+      <c r="S70" s="79"/>
+      <c r="T70" s="80"/>
       <c r="U70" s="44"/>
-      <c r="V70" s="67"/>
-      <c r="W70" s="68"/>
-      <c r="X70" s="69"/>
+      <c r="V70" s="78"/>
+      <c r="W70" s="79"/>
+      <c r="X70" s="80"/>
       <c r="Y70" s="40"/>
-      <c r="Z70" s="67"/>
-      <c r="AA70" s="68"/>
-      <c r="AB70" s="69"/>
+      <c r="Z70" s="78"/>
+      <c r="AA70" s="79"/>
+      <c r="AB70" s="80"/>
       <c r="AC70" s="44"/>
-      <c r="AD70" s="67"/>
-      <c r="AE70" s="68"/>
-      <c r="AF70" s="69"/>
+      <c r="AD70" s="78"/>
+      <c r="AE70" s="79"/>
+      <c r="AF70" s="80"/>
       <c r="AG70" s="44"/>
-      <c r="AH70" s="67"/>
-      <c r="AI70" s="68"/>
-      <c r="AJ70" s="69"/>
+      <c r="AH70" s="78"/>
+      <c r="AI70" s="79"/>
+      <c r="AJ70" s="80"/>
       <c r="AK70" s="44"/>
-      <c r="AL70" s="67" t="s">
+      <c r="AL70" s="78" t="s">
         <v>81</v>
       </c>
-      <c r="AM70" s="68"/>
-      <c r="AN70" s="69"/>
+      <c r="AM70" s="79"/>
+      <c r="AN70" s="80"/>
       <c r="AO70" s="12"/>
       <c r="AP70" s="27" t="s">
         <v>34</v>
@@ -6144,47 +6144,47 @@
     </row>
     <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A71" s="12"/>
-      <c r="B71" s="83"/>
-      <c r="C71" s="84"/>
-      <c r="D71" s="85"/>
+      <c r="B71" s="65"/>
+      <c r="C71" s="66"/>
+      <c r="D71" s="67"/>
       <c r="E71" s="44"/>
-      <c r="F71" s="83"/>
-      <c r="G71" s="84"/>
-      <c r="H71" s="85"/>
+      <c r="F71" s="65"/>
+      <c r="G71" s="66"/>
+      <c r="H71" s="67"/>
       <c r="I71" s="44"/>
-      <c r="J71" s="83"/>
-      <c r="K71" s="84"/>
-      <c r="L71" s="85"/>
+      <c r="J71" s="65"/>
+      <c r="K71" s="66"/>
+      <c r="L71" s="67"/>
       <c r="M71" s="9"/>
-      <c r="N71" s="83"/>
-      <c r="O71" s="84"/>
-      <c r="P71" s="85"/>
+      <c r="N71" s="65"/>
+      <c r="O71" s="66"/>
+      <c r="P71" s="67"/>
       <c r="Q71" s="50"/>
-      <c r="R71" s="83"/>
-      <c r="S71" s="84"/>
-      <c r="T71" s="85"/>
+      <c r="R71" s="65"/>
+      <c r="S71" s="66"/>
+      <c r="T71" s="67"/>
       <c r="U71" s="44"/>
-      <c r="V71" s="83"/>
-      <c r="W71" s="84"/>
-      <c r="X71" s="85"/>
+      <c r="V71" s="65"/>
+      <c r="W71" s="66"/>
+      <c r="X71" s="67"/>
       <c r="Y71" s="44"/>
-      <c r="Z71" s="83"/>
-      <c r="AA71" s="84"/>
-      <c r="AB71" s="85"/>
+      <c r="Z71" s="65"/>
+      <c r="AA71" s="66"/>
+      <c r="AB71" s="67"/>
       <c r="AC71" s="50"/>
-      <c r="AD71" s="83"/>
-      <c r="AE71" s="84"/>
-      <c r="AF71" s="85"/>
+      <c r="AD71" s="65"/>
+      <c r="AE71" s="66"/>
+      <c r="AF71" s="67"/>
       <c r="AG71" s="44"/>
-      <c r="AH71" s="83"/>
-      <c r="AI71" s="84"/>
-      <c r="AJ71" s="85"/>
+      <c r="AH71" s="65"/>
+      <c r="AI71" s="66"/>
+      <c r="AJ71" s="67"/>
       <c r="AK71" s="44"/>
-      <c r="AL71" s="83" t="s">
+      <c r="AL71" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="AM71" s="84"/>
-      <c r="AN71" s="85"/>
+      <c r="AM71" s="66"/>
+      <c r="AN71" s="67"/>
       <c r="AO71" s="12"/>
       <c r="AP71" s="27" t="s">
         <v>35</v>
@@ -6252,23 +6252,23 @@
       <c r="K73" s="33"/>
       <c r="L73" s="33"/>
       <c r="M73" s="14"/>
-      <c r="N73" s="115" t="s">
+      <c r="N73" s="136" t="s">
         <v>31</v>
       </c>
-      <c r="O73" s="115"/>
-      <c r="P73" s="115"/>
-      <c r="Q73" s="115"/>
-      <c r="R73" s="115"/>
-      <c r="S73" s="115"/>
-      <c r="T73" s="115"/>
-      <c r="U73" s="115"/>
-      <c r="V73" s="115"/>
-      <c r="W73" s="115"/>
-      <c r="X73" s="115"/>
-      <c r="Y73" s="115"/>
-      <c r="Z73" s="115"/>
-      <c r="AA73" s="115"/>
-      <c r="AB73" s="115"/>
+      <c r="O73" s="136"/>
+      <c r="P73" s="136"/>
+      <c r="Q73" s="136"/>
+      <c r="R73" s="136"/>
+      <c r="S73" s="136"/>
+      <c r="T73" s="136"/>
+      <c r="U73" s="136"/>
+      <c r="V73" s="136"/>
+      <c r="W73" s="136"/>
+      <c r="X73" s="136"/>
+      <c r="Y73" s="136"/>
+      <c r="Z73" s="136"/>
+      <c r="AA73" s="136"/>
+      <c r="AB73" s="136"/>
       <c r="AD73" s="40"/>
       <c r="AE73" s="33"/>
       <c r="AF73" s="33"/>
@@ -6299,21 +6299,21 @@
       <c r="K74" s="33"/>
       <c r="L74" s="33"/>
       <c r="M74" s="14"/>
-      <c r="N74" s="115"/>
-      <c r="O74" s="115"/>
-      <c r="P74" s="115"/>
-      <c r="Q74" s="115"/>
-      <c r="R74" s="115"/>
-      <c r="S74" s="115"/>
-      <c r="T74" s="115"/>
-      <c r="U74" s="115"/>
-      <c r="V74" s="115"/>
-      <c r="W74" s="115"/>
-      <c r="X74" s="115"/>
-      <c r="Y74" s="115"/>
-      <c r="Z74" s="115"/>
-      <c r="AA74" s="115"/>
-      <c r="AB74" s="115"/>
+      <c r="N74" s="136"/>
+      <c r="O74" s="136"/>
+      <c r="P74" s="136"/>
+      <c r="Q74" s="136"/>
+      <c r="R74" s="136"/>
+      <c r="S74" s="136"/>
+      <c r="T74" s="136"/>
+      <c r="U74" s="136"/>
+      <c r="V74" s="136"/>
+      <c r="W74" s="136"/>
+      <c r="X74" s="136"/>
+      <c r="Y74" s="136"/>
+      <c r="Z74" s="136"/>
+      <c r="AA74" s="136"/>
+      <c r="AB74" s="136"/>
       <c r="AC74" s="21"/>
       <c r="AD74" s="33"/>
       <c r="AE74" s="33"/>
@@ -6333,76 +6333,76 @@
     </row>
     <row r="75" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="12"/>
-      <c r="B75" s="81" t="s">
+      <c r="B75" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="C75" s="82"/>
+      <c r="C75" s="69"/>
       <c r="D75" s="55" t="s">
         <v>52</v>
       </c>
       <c r="E75" s="32"/>
-      <c r="F75" s="81" t="s">
+      <c r="F75" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="G75" s="82"/>
+      <c r="G75" s="69"/>
       <c r="H75" s="55" t="s">
         <v>52</v>
       </c>
       <c r="I75" s="32"/>
-      <c r="J75" s="81"/>
-      <c r="K75" s="82"/>
+      <c r="J75" s="68"/>
+      <c r="K75" s="69"/>
       <c r="L75" s="55"/>
       <c r="M75" s="14"/>
-      <c r="N75" s="70" t="s">
+      <c r="N75" s="81" t="s">
         <v>58</v>
       </c>
-      <c r="O75" s="71"/>
+      <c r="O75" s="82"/>
       <c r="P75" s="34" t="s">
         <v>52</v>
       </c>
       <c r="Q75" s="44"/>
-      <c r="R75" s="70" t="s">
+      <c r="R75" s="81" t="s">
         <v>58</v>
       </c>
-      <c r="S75" s="71"/>
+      <c r="S75" s="82"/>
       <c r="T75" s="34" t="s">
         <v>52</v>
       </c>
       <c r="U75" s="36"/>
-      <c r="V75" s="70" t="s">
+      <c r="V75" s="81" t="s">
         <v>58</v>
       </c>
-      <c r="W75" s="71"/>
+      <c r="W75" s="82"/>
       <c r="X75" s="34" t="s">
         <v>52</v>
       </c>
       <c r="Y75" s="32"/>
-      <c r="Z75" s="70" t="s">
+      <c r="Z75" s="81" t="s">
         <v>58</v>
       </c>
-      <c r="AA75" s="71"/>
+      <c r="AA75" s="82"/>
       <c r="AB75" s="34" t="s">
         <v>52</v>
       </c>
       <c r="AC75" s="32"/>
-      <c r="AD75" s="70" t="s">
+      <c r="AD75" s="81" t="s">
         <v>58</v>
       </c>
-      <c r="AE75" s="71"/>
+      <c r="AE75" s="82"/>
       <c r="AF75" s="34" t="s">
         <v>52</v>
       </c>
       <c r="AG75" s="32"/>
-      <c r="AH75" s="70" t="s">
+      <c r="AH75" s="81" t="s">
         <v>58</v>
       </c>
-      <c r="AI75" s="71"/>
+      <c r="AI75" s="82"/>
       <c r="AJ75" s="34" t="s">
         <v>52</v>
       </c>
       <c r="AK75" s="32"/>
-      <c r="AL75" s="70"/>
-      <c r="AM75" s="71"/>
+      <c r="AL75" s="81"/>
+      <c r="AM75" s="82"/>
       <c r="AN75" s="34"/>
       <c r="AO75" s="16"/>
       <c r="AP75" s="29"/>
@@ -6427,45 +6427,45 @@
       <c r="K76" s="63"/>
       <c r="L76" s="64"/>
       <c r="M76" s="4"/>
-      <c r="N76" s="72" t="s">
+      <c r="N76" s="106" t="s">
         <v>59</v>
       </c>
-      <c r="O76" s="73"/>
-      <c r="P76" s="74"/>
+      <c r="O76" s="107"/>
+      <c r="P76" s="108"/>
       <c r="Q76" s="44"/>
-      <c r="R76" s="72" t="s">
+      <c r="R76" s="106" t="s">
         <v>59</v>
       </c>
-      <c r="S76" s="73"/>
-      <c r="T76" s="74"/>
+      <c r="S76" s="107"/>
+      <c r="T76" s="108"/>
       <c r="U76" s="32"/>
-      <c r="V76" s="72" t="s">
+      <c r="V76" s="106" t="s">
         <v>59</v>
       </c>
-      <c r="W76" s="73"/>
-      <c r="X76" s="74"/>
+      <c r="W76" s="107"/>
+      <c r="X76" s="108"/>
       <c r="Y76" s="32"/>
-      <c r="Z76" s="72" t="s">
+      <c r="Z76" s="106" t="s">
         <v>59</v>
       </c>
-      <c r="AA76" s="73"/>
-      <c r="AB76" s="74"/>
+      <c r="AA76" s="107"/>
+      <c r="AB76" s="108"/>
       <c r="AC76" s="35"/>
-      <c r="AD76" s="72" t="s">
+      <c r="AD76" s="106" t="s">
         <v>59</v>
       </c>
-      <c r="AE76" s="73"/>
-      <c r="AF76" s="74"/>
+      <c r="AE76" s="107"/>
+      <c r="AF76" s="108"/>
       <c r="AG76" s="32"/>
-      <c r="AH76" s="72" t="s">
+      <c r="AH76" s="106" t="s">
         <v>59</v>
       </c>
-      <c r="AI76" s="73"/>
-      <c r="AJ76" s="74"/>
+      <c r="AI76" s="107"/>
+      <c r="AJ76" s="108"/>
       <c r="AK76" s="32"/>
-      <c r="AL76" s="72"/>
-      <c r="AM76" s="73"/>
-      <c r="AN76" s="74"/>
+      <c r="AL76" s="106"/>
+      <c r="AM76" s="107"/>
+      <c r="AN76" s="108"/>
       <c r="AO76" s="12"/>
       <c r="AP76" s="29"/>
       <c r="AQ76" s="26"/>
@@ -6473,45 +6473,45 @@
     </row>
     <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="16"/>
-      <c r="B77" s="78"/>
-      <c r="C77" s="79"/>
-      <c r="D77" s="80"/>
+      <c r="B77" s="73"/>
+      <c r="C77" s="74"/>
+      <c r="D77" s="75"/>
       <c r="E77" s="32"/>
-      <c r="F77" s="78"/>
-      <c r="G77" s="79"/>
-      <c r="H77" s="80"/>
+      <c r="F77" s="73"/>
+      <c r="G77" s="74"/>
+      <c r="H77" s="75"/>
       <c r="I77" s="32"/>
-      <c r="J77" s="78"/>
-      <c r="K77" s="79"/>
-      <c r="L77" s="80"/>
+      <c r="J77" s="73"/>
+      <c r="K77" s="74"/>
+      <c r="L77" s="75"/>
       <c r="M77" s="4"/>
-      <c r="N77" s="75"/>
-      <c r="O77" s="76"/>
-      <c r="P77" s="77"/>
+      <c r="N77" s="83"/>
+      <c r="O77" s="84"/>
+      <c r="P77" s="85"/>
       <c r="Q77" s="44"/>
-      <c r="R77" s="75"/>
-      <c r="S77" s="76"/>
-      <c r="T77" s="77"/>
+      <c r="R77" s="83"/>
+      <c r="S77" s="84"/>
+      <c r="T77" s="85"/>
       <c r="U77" s="31"/>
-      <c r="V77" s="75"/>
-      <c r="W77" s="76"/>
-      <c r="X77" s="77"/>
+      <c r="V77" s="83"/>
+      <c r="W77" s="84"/>
+      <c r="X77" s="85"/>
       <c r="Y77" s="32"/>
-      <c r="Z77" s="75"/>
-      <c r="AA77" s="76"/>
-      <c r="AB77" s="77"/>
+      <c r="Z77" s="83"/>
+      <c r="AA77" s="84"/>
+      <c r="AB77" s="85"/>
       <c r="AC77" s="31"/>
-      <c r="AD77" s="75"/>
-      <c r="AE77" s="76"/>
-      <c r="AF77" s="77"/>
+      <c r="AD77" s="83"/>
+      <c r="AE77" s="84"/>
+      <c r="AF77" s="85"/>
       <c r="AG77" s="32"/>
-      <c r="AH77" s="75"/>
-      <c r="AI77" s="76"/>
-      <c r="AJ77" s="77"/>
+      <c r="AH77" s="83"/>
+      <c r="AI77" s="84"/>
+      <c r="AJ77" s="85"/>
       <c r="AK77" s="32"/>
-      <c r="AL77" s="75"/>
-      <c r="AM77" s="76"/>
-      <c r="AN77" s="77"/>
+      <c r="AL77" s="83"/>
+      <c r="AM77" s="84"/>
+      <c r="AN77" s="85"/>
       <c r="AO77" s="12"/>
       <c r="AP77" s="29"/>
       <c r="AQ77" s="26"/>
@@ -6519,61 +6519,61 @@
     </row>
     <row r="78" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="16"/>
-      <c r="B78" s="89" t="s">
+      <c r="B78" s="70" t="s">
         <v>29</v>
       </c>
-      <c r="C78" s="90"/>
-      <c r="D78" s="91"/>
+      <c r="C78" s="71"/>
+      <c r="D78" s="72"/>
       <c r="E78" s="32"/>
-      <c r="F78" s="89" t="s">
+      <c r="F78" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="G78" s="90"/>
-      <c r="H78" s="91"/>
+      <c r="G78" s="71"/>
+      <c r="H78" s="72"/>
       <c r="I78" s="43"/>
-      <c r="J78" s="89"/>
-      <c r="K78" s="90"/>
-      <c r="L78" s="91"/>
+      <c r="J78" s="70"/>
+      <c r="K78" s="71"/>
+      <c r="L78" s="72"/>
       <c r="M78" s="5"/>
-      <c r="N78" s="89" t="s">
+      <c r="N78" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="O78" s="90"/>
-      <c r="P78" s="91"/>
+      <c r="O78" s="71"/>
+      <c r="P78" s="72"/>
       <c r="Q78" s="44"/>
-      <c r="R78" s="89" t="s">
+      <c r="R78" s="70" t="s">
         <v>29</v>
       </c>
-      <c r="S78" s="90"/>
-      <c r="T78" s="91"/>
+      <c r="S78" s="71"/>
+      <c r="T78" s="72"/>
       <c r="U78" s="32"/>
-      <c r="V78" s="89" t="s">
+      <c r="V78" s="70" t="s">
         <v>29</v>
       </c>
-      <c r="W78" s="90"/>
-      <c r="X78" s="91"/>
+      <c r="W78" s="71"/>
+      <c r="X78" s="72"/>
       <c r="Y78" s="32"/>
-      <c r="Z78" s="89" t="s">
+      <c r="Z78" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="AA78" s="90"/>
-      <c r="AB78" s="91"/>
+      <c r="AA78" s="71"/>
+      <c r="AB78" s="72"/>
       <c r="AC78" s="32"/>
-      <c r="AD78" s="89" t="s">
+      <c r="AD78" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="AE78" s="90"/>
-      <c r="AF78" s="91"/>
+      <c r="AE78" s="71"/>
+      <c r="AF78" s="72"/>
       <c r="AG78" s="32"/>
-      <c r="AH78" s="89" t="s">
+      <c r="AH78" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="AI78" s="90"/>
-      <c r="AJ78" s="91"/>
+      <c r="AI78" s="71"/>
+      <c r="AJ78" s="72"/>
       <c r="AK78" s="43"/>
-      <c r="AL78" s="89"/>
-      <c r="AM78" s="90"/>
-      <c r="AN78" s="91"/>
+      <c r="AL78" s="70"/>
+      <c r="AM78" s="71"/>
+      <c r="AN78" s="72"/>
       <c r="AO78" s="12"/>
       <c r="AP78" s="29"/>
       <c r="AQ78" s="26"/>
@@ -6581,45 +6581,45 @@
     </row>
     <row r="79" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A79" s="16"/>
-      <c r="B79" s="83"/>
-      <c r="C79" s="84"/>
-      <c r="D79" s="85"/>
+      <c r="B79" s="65"/>
+      <c r="C79" s="66"/>
+      <c r="D79" s="67"/>
       <c r="E79" s="31"/>
-      <c r="F79" s="83"/>
-      <c r="G79" s="84"/>
-      <c r="H79" s="85"/>
+      <c r="F79" s="65"/>
+      <c r="G79" s="66"/>
+      <c r="H79" s="67"/>
       <c r="I79" s="32"/>
-      <c r="J79" s="83"/>
-      <c r="K79" s="84"/>
-      <c r="L79" s="85"/>
+      <c r="J79" s="65"/>
+      <c r="K79" s="66"/>
+      <c r="L79" s="67"/>
       <c r="M79" s="5"/>
-      <c r="N79" s="83"/>
-      <c r="O79" s="84"/>
-      <c r="P79" s="85"/>
+      <c r="N79" s="65"/>
+      <c r="O79" s="66"/>
+      <c r="P79" s="67"/>
       <c r="Q79" s="31"/>
-      <c r="R79" s="83"/>
-      <c r="S79" s="84"/>
-      <c r="T79" s="85"/>
+      <c r="R79" s="65"/>
+      <c r="S79" s="66"/>
+      <c r="T79" s="67"/>
       <c r="U79" s="32"/>
-      <c r="V79" s="83"/>
-      <c r="W79" s="84"/>
-      <c r="X79" s="85"/>
+      <c r="V79" s="65"/>
+      <c r="W79" s="66"/>
+      <c r="X79" s="67"/>
       <c r="Y79" s="32"/>
-      <c r="Z79" s="83"/>
-      <c r="AA79" s="84"/>
-      <c r="AB79" s="85"/>
+      <c r="Z79" s="65"/>
+      <c r="AA79" s="66"/>
+      <c r="AB79" s="67"/>
       <c r="AC79" s="32"/>
-      <c r="AD79" s="83"/>
-      <c r="AE79" s="84"/>
-      <c r="AF79" s="85"/>
+      <c r="AD79" s="65"/>
+      <c r="AE79" s="66"/>
+      <c r="AF79" s="67"/>
       <c r="AG79" s="31"/>
-      <c r="AH79" s="83"/>
-      <c r="AI79" s="84"/>
-      <c r="AJ79" s="85"/>
+      <c r="AH79" s="65"/>
+      <c r="AI79" s="66"/>
+      <c r="AJ79" s="67"/>
       <c r="AK79" s="32"/>
-      <c r="AL79" s="83"/>
-      <c r="AM79" s="84"/>
-      <c r="AN79" s="85"/>
+      <c r="AL79" s="65"/>
+      <c r="AM79" s="66"/>
+      <c r="AN79" s="67"/>
       <c r="AO79" s="12"/>
       <c r="AP79" s="29"/>
       <c r="AQ79" s="26"/>
@@ -6673,62 +6673,62 @@
     </row>
     <row r="81" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="12"/>
-      <c r="B81" s="81" t="s">
+      <c r="B81" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="C81" s="82"/>
+      <c r="C81" s="69"/>
       <c r="D81" s="55"/>
       <c r="E81" s="32"/>
-      <c r="F81" s="81" t="s">
+      <c r="F81" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="G81" s="82"/>
+      <c r="G81" s="69"/>
       <c r="H81" s="55"/>
       <c r="I81" s="50"/>
-      <c r="J81" s="81" t="s">
+      <c r="J81" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="K81" s="82"/>
+      <c r="K81" s="69"/>
       <c r="L81" s="55"/>
       <c r="M81" s="5"/>
-      <c r="N81" s="70" t="s">
+      <c r="N81" s="81" t="s">
         <v>56</v>
       </c>
-      <c r="O81" s="71"/>
+      <c r="O81" s="82"/>
       <c r="P81" s="34"/>
       <c r="Q81" s="50"/>
-      <c r="R81" s="70" t="s">
+      <c r="R81" s="81" t="s">
         <v>56</v>
       </c>
-      <c r="S81" s="71"/>
+      <c r="S81" s="82"/>
       <c r="T81" s="34"/>
       <c r="U81" s="36"/>
-      <c r="V81" s="98" t="s">
+      <c r="V81" s="126" t="s">
         <v>44</v>
       </c>
-      <c r="W81" s="99"/>
+      <c r="W81" s="127"/>
       <c r="X81" s="59"/>
       <c r="Y81" s="32"/>
-      <c r="Z81" s="65" t="s">
+      <c r="Z81" s="76" t="s">
         <v>117</v>
       </c>
-      <c r="AA81" s="66"/>
+      <c r="AA81" s="77"/>
       <c r="AB81" s="57"/>
       <c r="AC81" s="32"/>
-      <c r="AD81" s="98" t="s">
+      <c r="AD81" s="126" t="s">
         <v>44</v>
       </c>
-      <c r="AE81" s="99"/>
+      <c r="AE81" s="127"/>
       <c r="AF81" s="59"/>
       <c r="AG81" s="32"/>
-      <c r="AH81" s="98" t="s">
+      <c r="AH81" s="126" t="s">
         <v>44</v>
       </c>
-      <c r="AI81" s="99"/>
+      <c r="AI81" s="127"/>
       <c r="AJ81" s="59"/>
       <c r="AK81" s="50"/>
-      <c r="AL81" s="70"/>
-      <c r="AM81" s="71"/>
+      <c r="AL81" s="81"/>
+      <c r="AM81" s="82"/>
       <c r="AN81" s="34"/>
       <c r="AO81" s="12"/>
       <c r="AP81" s="29"/>
@@ -6755,43 +6755,43 @@
       <c r="K82" s="63"/>
       <c r="L82" s="64"/>
       <c r="M82" s="5"/>
-      <c r="N82" s="72" t="s">
+      <c r="N82" s="106" t="s">
         <v>53</v>
       </c>
-      <c r="O82" s="73"/>
-      <c r="P82" s="74"/>
+      <c r="O82" s="107"/>
+      <c r="P82" s="108"/>
       <c r="Q82" s="36"/>
-      <c r="R82" s="72" t="s">
+      <c r="R82" s="106" t="s">
         <v>53</v>
       </c>
-      <c r="S82" s="73"/>
-      <c r="T82" s="74"/>
+      <c r="S82" s="107"/>
+      <c r="T82" s="108"/>
       <c r="U82" s="32"/>
-      <c r="V82" s="95" t="s">
+      <c r="V82" s="120" t="s">
         <v>86</v>
       </c>
-      <c r="W82" s="96"/>
-      <c r="X82" s="97"/>
+      <c r="W82" s="121"/>
+      <c r="X82" s="122"/>
       <c r="Y82" s="32"/>
-      <c r="Z82" s="72"/>
-      <c r="AA82" s="73"/>
-      <c r="AB82" s="74"/>
+      <c r="Z82" s="106"/>
+      <c r="AA82" s="107"/>
+      <c r="AB82" s="108"/>
       <c r="AC82" s="32"/>
-      <c r="AD82" s="95" t="s">
+      <c r="AD82" s="120" t="s">
         <v>86</v>
       </c>
-      <c r="AE82" s="96"/>
-      <c r="AF82" s="97"/>
+      <c r="AE82" s="121"/>
+      <c r="AF82" s="122"/>
       <c r="AG82" s="32"/>
-      <c r="AH82" s="95" t="s">
+      <c r="AH82" s="120" t="s">
         <v>86</v>
       </c>
-      <c r="AI82" s="96"/>
-      <c r="AJ82" s="97"/>
+      <c r="AI82" s="121"/>
+      <c r="AJ82" s="122"/>
       <c r="AK82" s="36"/>
-      <c r="AL82" s="72"/>
-      <c r="AM82" s="73"/>
-      <c r="AN82" s="74"/>
+      <c r="AL82" s="106"/>
+      <c r="AM82" s="107"/>
+      <c r="AN82" s="108"/>
       <c r="AO82" s="12"/>
       <c r="AP82" s="29"/>
       <c r="AQ82" s="26"/>
@@ -6799,63 +6799,63 @@
     </row>
     <row r="83" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="12"/>
-      <c r="B83" s="78" t="s">
+      <c r="B83" s="73" t="s">
         <v>50</v>
       </c>
-      <c r="C83" s="79"/>
-      <c r="D83" s="80"/>
+      <c r="C83" s="74"/>
+      <c r="D83" s="75"/>
       <c r="E83" s="32"/>
-      <c r="F83" s="78" t="s">
+      <c r="F83" s="73" t="s">
         <v>50</v>
       </c>
-      <c r="G83" s="79"/>
-      <c r="H83" s="80"/>
+      <c r="G83" s="74"/>
+      <c r="H83" s="75"/>
       <c r="I83" s="32"/>
-      <c r="J83" s="78" t="s">
+      <c r="J83" s="73" t="s">
         <v>50</v>
       </c>
-      <c r="K83" s="79"/>
-      <c r="L83" s="80"/>
+      <c r="K83" s="74"/>
+      <c r="L83" s="75"/>
       <c r="M83" s="5"/>
-      <c r="N83" s="75" t="s">
+      <c r="N83" s="83" t="s">
         <v>50</v>
       </c>
-      <c r="O83" s="76"/>
-      <c r="P83" s="77"/>
+      <c r="O83" s="84"/>
+      <c r="P83" s="85"/>
       <c r="Q83" s="32"/>
-      <c r="R83" s="75" t="s">
+      <c r="R83" s="83" t="s">
         <v>50</v>
       </c>
-      <c r="S83" s="76"/>
-      <c r="T83" s="77"/>
+      <c r="S83" s="84"/>
+      <c r="T83" s="85"/>
       <c r="U83" s="31"/>
-      <c r="V83" s="146" t="s">
+      <c r="V83" s="123" t="s">
         <v>50</v>
       </c>
-      <c r="W83" s="147"/>
-      <c r="X83" s="148"/>
+      <c r="W83" s="124"/>
+      <c r="X83" s="125"/>
       <c r="Y83" s="32"/>
-      <c r="Z83" s="75" t="s">
+      <c r="Z83" s="83" t="s">
         <v>50</v>
       </c>
-      <c r="AA83" s="76"/>
-      <c r="AB83" s="77"/>
+      <c r="AA83" s="84"/>
+      <c r="AB83" s="85"/>
       <c r="AC83" s="32"/>
-      <c r="AD83" s="146" t="s">
+      <c r="AD83" s="123" t="s">
         <v>50</v>
       </c>
-      <c r="AE83" s="147"/>
-      <c r="AF83" s="148"/>
+      <c r="AE83" s="124"/>
+      <c r="AF83" s="125"/>
       <c r="AG83" s="32"/>
-      <c r="AH83" s="146" t="s">
+      <c r="AH83" s="123" t="s">
         <v>50</v>
       </c>
-      <c r="AI83" s="147"/>
-      <c r="AJ83" s="148"/>
+      <c r="AI83" s="124"/>
+      <c r="AJ83" s="125"/>
       <c r="AK83" s="32"/>
-      <c r="AL83" s="75"/>
-      <c r="AM83" s="76"/>
-      <c r="AN83" s="77"/>
+      <c r="AL83" s="83"/>
+      <c r="AM83" s="84"/>
+      <c r="AN83" s="85"/>
       <c r="AO83" s="12"/>
       <c r="AP83" s="29"/>
       <c r="AQ83" s="26"/>
@@ -6863,63 +6863,63 @@
     </row>
     <row r="84" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="12"/>
-      <c r="B84" s="89" t="s">
+      <c r="B84" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="C84" s="90"/>
-      <c r="D84" s="91"/>
+      <c r="C84" s="71"/>
+      <c r="D84" s="72"/>
       <c r="E84" s="32"/>
-      <c r="F84" s="89" t="s">
+      <c r="F84" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="G84" s="90"/>
-      <c r="H84" s="91"/>
+      <c r="G84" s="71"/>
+      <c r="H84" s="72"/>
       <c r="I84" s="32"/>
-      <c r="J84" s="89" t="s">
+      <c r="J84" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="K84" s="90"/>
-      <c r="L84" s="91"/>
+      <c r="K84" s="71"/>
+      <c r="L84" s="72"/>
       <c r="M84" s="5"/>
-      <c r="N84" s="89" t="s">
+      <c r="N84" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="O84" s="90"/>
-      <c r="P84" s="91"/>
+      <c r="O84" s="71"/>
+      <c r="P84" s="72"/>
       <c r="Q84" s="32"/>
-      <c r="R84" s="89" t="s">
+      <c r="R84" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="S84" s="90"/>
-      <c r="T84" s="91"/>
+      <c r="S84" s="71"/>
+      <c r="T84" s="72"/>
       <c r="U84" s="32"/>
-      <c r="V84" s="103" t="s">
+      <c r="V84" s="137" t="s">
         <v>115</v>
       </c>
-      <c r="W84" s="104"/>
-      <c r="X84" s="105"/>
+      <c r="W84" s="138"/>
+      <c r="X84" s="139"/>
       <c r="Y84" s="32"/>
-      <c r="Z84" s="89" t="s">
+      <c r="Z84" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="AA84" s="90"/>
-      <c r="AB84" s="91"/>
+      <c r="AA84" s="71"/>
+      <c r="AB84" s="72"/>
       <c r="AC84" s="43"/>
-      <c r="AD84" s="103" t="s">
+      <c r="AD84" s="137" t="s">
         <v>115</v>
       </c>
-      <c r="AE84" s="104"/>
-      <c r="AF84" s="105"/>
+      <c r="AE84" s="138"/>
+      <c r="AF84" s="139"/>
       <c r="AG84" s="32"/>
-      <c r="AH84" s="103" t="s">
+      <c r="AH84" s="137" t="s">
         <v>115</v>
       </c>
-      <c r="AI84" s="104"/>
-      <c r="AJ84" s="105"/>
+      <c r="AI84" s="138"/>
+      <c r="AJ84" s="139"/>
       <c r="AK84" s="32"/>
-      <c r="AL84" s="89"/>
-      <c r="AM84" s="90"/>
-      <c r="AN84" s="91"/>
+      <c r="AL84" s="70"/>
+      <c r="AM84" s="71"/>
+      <c r="AN84" s="72"/>
       <c r="AO84" s="12"/>
       <c r="AP84" s="29"/>
       <c r="AQ84" s="26"/>
@@ -6927,45 +6927,45 @@
     </row>
     <row r="85" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A85" s="12"/>
-      <c r="B85" s="83"/>
-      <c r="C85" s="84"/>
-      <c r="D85" s="85"/>
+      <c r="B85" s="65"/>
+      <c r="C85" s="66"/>
+      <c r="D85" s="67"/>
       <c r="E85" s="31"/>
-      <c r="F85" s="83"/>
-      <c r="G85" s="84"/>
-      <c r="H85" s="85"/>
+      <c r="F85" s="65"/>
+      <c r="G85" s="66"/>
+      <c r="H85" s="67"/>
       <c r="I85" s="32"/>
-      <c r="J85" s="83"/>
-      <c r="K85" s="84"/>
-      <c r="L85" s="85"/>
+      <c r="J85" s="65"/>
+      <c r="K85" s="66"/>
+      <c r="L85" s="67"/>
       <c r="M85" s="6"/>
-      <c r="N85" s="83"/>
-      <c r="O85" s="84"/>
-      <c r="P85" s="85"/>
+      <c r="N85" s="65"/>
+      <c r="O85" s="66"/>
+      <c r="P85" s="67"/>
       <c r="Q85" s="31"/>
-      <c r="R85" s="83"/>
-      <c r="S85" s="84"/>
-      <c r="T85" s="85"/>
+      <c r="R85" s="65"/>
+      <c r="S85" s="66"/>
+      <c r="T85" s="67"/>
       <c r="U85" s="32"/>
-      <c r="V85" s="92"/>
-      <c r="W85" s="93"/>
-      <c r="X85" s="94"/>
+      <c r="V85" s="131"/>
+      <c r="W85" s="132"/>
+      <c r="X85" s="133"/>
       <c r="Y85" s="32"/>
-      <c r="Z85" s="83"/>
-      <c r="AA85" s="84"/>
-      <c r="AB85" s="85"/>
+      <c r="Z85" s="65"/>
+      <c r="AA85" s="66"/>
+      <c r="AB85" s="67"/>
       <c r="AC85" s="43"/>
-      <c r="AD85" s="92"/>
-      <c r="AE85" s="93"/>
-      <c r="AF85" s="94"/>
+      <c r="AD85" s="131"/>
+      <c r="AE85" s="132"/>
+      <c r="AF85" s="133"/>
       <c r="AG85" s="31"/>
-      <c r="AH85" s="92"/>
-      <c r="AI85" s="93"/>
-      <c r="AJ85" s="94"/>
+      <c r="AH85" s="131"/>
+      <c r="AI85" s="132"/>
+      <c r="AJ85" s="133"/>
       <c r="AK85" s="32"/>
-      <c r="AL85" s="83"/>
-      <c r="AM85" s="84"/>
-      <c r="AN85" s="85"/>
+      <c r="AL85" s="65"/>
+      <c r="AM85" s="66"/>
+      <c r="AN85" s="67"/>
       <c r="AO85" s="12"/>
       <c r="AP85" s="29"/>
       <c r="AQ85" s="26"/>
@@ -7019,60 +7019,60 @@
     </row>
     <row r="87" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="12"/>
-      <c r="B87" s="81" t="s">
+      <c r="B87" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="C87" s="82"/>
+      <c r="C87" s="69"/>
       <c r="D87" s="55"/>
       <c r="E87" s="32"/>
-      <c r="F87" s="81" t="s">
+      <c r="F87" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="G87" s="82"/>
+      <c r="G87" s="69"/>
       <c r="H87" s="55"/>
       <c r="I87" s="32"/>
-      <c r="J87" s="81" t="s">
+      <c r="J87" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="K87" s="82"/>
+      <c r="K87" s="69"/>
       <c r="L87" s="55"/>
       <c r="M87" s="6"/>
-      <c r="N87" s="70" t="s">
+      <c r="N87" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="O87" s="71"/>
+      <c r="O87" s="82"/>
       <c r="P87" s="34"/>
       <c r="Q87" s="32"/>
-      <c r="R87" s="70" t="s">
+      <c r="R87" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="S87" s="71"/>
+      <c r="S87" s="82"/>
       <c r="T87" s="34"/>
       <c r="U87" s="36"/>
-      <c r="V87" s="70" t="s">
+      <c r="V87" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="W87" s="71"/>
+      <c r="W87" s="82"/>
       <c r="X87" s="34"/>
       <c r="Y87" s="32"/>
-      <c r="Z87" s="70" t="s">
+      <c r="Z87" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="AA87" s="71"/>
+      <c r="AA87" s="82"/>
       <c r="AB87" s="34"/>
       <c r="AC87" s="32"/>
-      <c r="AD87" s="65" t="s">
+      <c r="AD87" s="76" t="s">
         <v>118</v>
       </c>
-      <c r="AE87" s="66"/>
+      <c r="AE87" s="77"/>
       <c r="AF87" s="57"/>
       <c r="AG87" s="32"/>
-      <c r="AH87" s="70"/>
-      <c r="AI87" s="71"/>
+      <c r="AH87" s="81"/>
+      <c r="AI87" s="82"/>
       <c r="AJ87" s="34"/>
       <c r="AK87" s="32"/>
-      <c r="AL87" s="70"/>
-      <c r="AM87" s="71"/>
+      <c r="AL87" s="81"/>
+      <c r="AM87" s="82"/>
       <c r="AN87" s="34"/>
       <c r="AO87" s="12"/>
       <c r="AP87" s="29"/>
@@ -7095,41 +7095,41 @@
       <c r="K88" s="63"/>
       <c r="L88" s="64"/>
       <c r="M88" s="6"/>
-      <c r="N88" s="72" t="s">
+      <c r="N88" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="O88" s="73"/>
-      <c r="P88" s="74"/>
+      <c r="O88" s="107"/>
+      <c r="P88" s="108"/>
       <c r="Q88" s="35"/>
-      <c r="R88" s="72" t="s">
+      <c r="R88" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="S88" s="73"/>
-      <c r="T88" s="74"/>
+      <c r="S88" s="107"/>
+      <c r="T88" s="108"/>
       <c r="U88" s="32"/>
-      <c r="V88" s="72" t="s">
+      <c r="V88" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="W88" s="73"/>
-      <c r="X88" s="74"/>
+      <c r="W88" s="107"/>
+      <c r="X88" s="108"/>
       <c r="Y88" s="32"/>
-      <c r="Z88" s="72" t="s">
+      <c r="Z88" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="AA88" s="73"/>
-      <c r="AB88" s="74"/>
+      <c r="AA88" s="107"/>
+      <c r="AB88" s="108"/>
       <c r="AC88" s="35"/>
-      <c r="AD88" s="72"/>
-      <c r="AE88" s="73"/>
-      <c r="AF88" s="74"/>
+      <c r="AD88" s="106"/>
+      <c r="AE88" s="107"/>
+      <c r="AF88" s="108"/>
       <c r="AG88" s="32"/>
-      <c r="AH88" s="72"/>
-      <c r="AI88" s="73"/>
-      <c r="AJ88" s="74"/>
+      <c r="AH88" s="106"/>
+      <c r="AI88" s="107"/>
+      <c r="AJ88" s="108"/>
       <c r="AK88" s="32"/>
-      <c r="AL88" s="72"/>
-      <c r="AM88" s="73"/>
-      <c r="AN88" s="74"/>
+      <c r="AL88" s="106"/>
+      <c r="AM88" s="107"/>
+      <c r="AN88" s="108"/>
       <c r="AO88" s="12"/>
       <c r="AP88" s="29"/>
       <c r="AQ88" s="26"/>
@@ -7137,51 +7137,51 @@
     </row>
     <row r="89" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="12"/>
-      <c r="B89" s="78" t="s">
+      <c r="B89" s="73" t="s">
         <v>50</v>
       </c>
-      <c r="C89" s="79"/>
-      <c r="D89" s="80"/>
+      <c r="C89" s="74"/>
+      <c r="D89" s="75"/>
       <c r="E89" s="32"/>
-      <c r="F89" s="78" t="s">
+      <c r="F89" s="73" t="s">
         <v>50</v>
       </c>
-      <c r="G89" s="79"/>
-      <c r="H89" s="80"/>
+      <c r="G89" s="74"/>
+      <c r="H89" s="75"/>
       <c r="I89" s="32"/>
-      <c r="J89" s="78"/>
-      <c r="K89" s="79"/>
-      <c r="L89" s="80"/>
+      <c r="J89" s="73"/>
+      <c r="K89" s="74"/>
+      <c r="L89" s="75"/>
       <c r="M89" s="6"/>
-      <c r="N89" s="75"/>
-      <c r="O89" s="76"/>
-      <c r="P89" s="77"/>
+      <c r="N89" s="83"/>
+      <c r="O89" s="84"/>
+      <c r="P89" s="85"/>
       <c r="Q89" s="31"/>
-      <c r="R89" s="75"/>
-      <c r="S89" s="76"/>
-      <c r="T89" s="77"/>
+      <c r="R89" s="83"/>
+      <c r="S89" s="84"/>
+      <c r="T89" s="85"/>
       <c r="U89" s="31"/>
-      <c r="V89" s="75"/>
-      <c r="W89" s="76"/>
-      <c r="X89" s="77"/>
+      <c r="V89" s="83"/>
+      <c r="W89" s="84"/>
+      <c r="X89" s="85"/>
       <c r="Y89" s="32"/>
-      <c r="Z89" s="75"/>
-      <c r="AA89" s="76"/>
-      <c r="AB89" s="77"/>
+      <c r="Z89" s="83"/>
+      <c r="AA89" s="84"/>
+      <c r="AB89" s="85"/>
       <c r="AC89" s="31"/>
-      <c r="AD89" s="75" t="s">
+      <c r="AD89" s="83" t="s">
         <v>50</v>
       </c>
-      <c r="AE89" s="76"/>
-      <c r="AF89" s="77"/>
+      <c r="AE89" s="84"/>
+      <c r="AF89" s="85"/>
       <c r="AG89" s="32"/>
-      <c r="AH89" s="75"/>
-      <c r="AI89" s="76"/>
-      <c r="AJ89" s="77"/>
+      <c r="AH89" s="83"/>
+      <c r="AI89" s="84"/>
+      <c r="AJ89" s="85"/>
       <c r="AK89" s="32"/>
-      <c r="AL89" s="75"/>
-      <c r="AM89" s="76"/>
-      <c r="AN89" s="77"/>
+      <c r="AL89" s="83"/>
+      <c r="AM89" s="84"/>
+      <c r="AN89" s="85"/>
       <c r="AO89" s="12"/>
       <c r="AP89" s="29"/>
       <c r="AQ89" s="26"/>
@@ -7189,61 +7189,61 @@
     </row>
     <row r="90" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="12"/>
-      <c r="B90" s="89" t="s">
+      <c r="B90" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="C90" s="90"/>
-      <c r="D90" s="91"/>
+      <c r="C90" s="71"/>
+      <c r="D90" s="72"/>
       <c r="E90" s="32"/>
-      <c r="F90" s="89" t="s">
+      <c r="F90" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="G90" s="90"/>
-      <c r="H90" s="91"/>
+      <c r="G90" s="71"/>
+      <c r="H90" s="72"/>
       <c r="I90" s="32"/>
-      <c r="J90" s="89" t="s">
+      <c r="J90" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="K90" s="90"/>
-      <c r="L90" s="91"/>
+      <c r="K90" s="71"/>
+      <c r="L90" s="72"/>
       <c r="M90" s="6"/>
-      <c r="N90" s="89" t="s">
+      <c r="N90" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="O90" s="90"/>
-      <c r="P90" s="91"/>
+      <c r="O90" s="71"/>
+      <c r="P90" s="72"/>
       <c r="Q90" s="32"/>
-      <c r="R90" s="89" t="s">
+      <c r="R90" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="S90" s="90"/>
-      <c r="T90" s="91"/>
+      <c r="S90" s="71"/>
+      <c r="T90" s="72"/>
       <c r="U90" s="32"/>
-      <c r="V90" s="89" t="s">
+      <c r="V90" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="W90" s="90"/>
-      <c r="X90" s="91"/>
+      <c r="W90" s="71"/>
+      <c r="X90" s="72"/>
       <c r="Y90" s="32"/>
-      <c r="Z90" s="89" t="s">
+      <c r="Z90" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="AA90" s="90"/>
-      <c r="AB90" s="91"/>
+      <c r="AA90" s="71"/>
+      <c r="AB90" s="72"/>
       <c r="AC90" s="32"/>
-      <c r="AD90" s="89" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE90" s="90"/>
-      <c r="AF90" s="91"/>
+      <c r="AD90" s="70" t="s">
+        <v>30</v>
+      </c>
+      <c r="AE90" s="71"/>
+      <c r="AF90" s="72"/>
       <c r="AG90" s="32"/>
-      <c r="AH90" s="89"/>
-      <c r="AI90" s="90"/>
-      <c r="AJ90" s="91"/>
+      <c r="AH90" s="70"/>
+      <c r="AI90" s="71"/>
+      <c r="AJ90" s="72"/>
       <c r="AK90" s="32"/>
-      <c r="AL90" s="89"/>
-      <c r="AM90" s="90"/>
-      <c r="AN90" s="91"/>
+      <c r="AL90" s="70"/>
+      <c r="AM90" s="71"/>
+      <c r="AN90" s="72"/>
       <c r="AO90" s="12"/>
       <c r="AP90" s="29"/>
       <c r="AQ90" s="26"/>
@@ -7251,45 +7251,47 @@
     </row>
     <row r="91" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A91" s="12"/>
-      <c r="B91" s="83"/>
-      <c r="C91" s="84"/>
-      <c r="D91" s="85"/>
+      <c r="B91" s="65"/>
+      <c r="C91" s="66"/>
+      <c r="D91" s="67"/>
       <c r="E91" s="31"/>
-      <c r="F91" s="83"/>
-      <c r="G91" s="84"/>
-      <c r="H91" s="85"/>
+      <c r="F91" s="65"/>
+      <c r="G91" s="66"/>
+      <c r="H91" s="67"/>
       <c r="I91" s="31"/>
-      <c r="J91" s="83"/>
-      <c r="K91" s="84"/>
-      <c r="L91" s="85"/>
+      <c r="J91" s="65"/>
+      <c r="K91" s="66"/>
+      <c r="L91" s="67"/>
       <c r="M91" s="6"/>
-      <c r="N91" s="83"/>
-      <c r="O91" s="84"/>
-      <c r="P91" s="85"/>
+      <c r="N91" s="65"/>
+      <c r="O91" s="66"/>
+      <c r="P91" s="67"/>
       <c r="Q91" s="31"/>
-      <c r="R91" s="83"/>
-      <c r="S91" s="84"/>
-      <c r="T91" s="85"/>
+      <c r="R91" s="65"/>
+      <c r="S91" s="66"/>
+      <c r="T91" s="67"/>
       <c r="U91" s="32"/>
-      <c r="V91" s="83"/>
-      <c r="W91" s="84"/>
-      <c r="X91" s="85"/>
+      <c r="V91" s="65"/>
+      <c r="W91" s="66"/>
+      <c r="X91" s="67"/>
       <c r="Y91" s="32"/>
-      <c r="Z91" s="83"/>
-      <c r="AA91" s="84"/>
-      <c r="AB91" s="85"/>
+      <c r="Z91" s="65"/>
+      <c r="AA91" s="66"/>
+      <c r="AB91" s="67"/>
       <c r="AC91" s="32"/>
-      <c r="AD91" s="83"/>
-      <c r="AE91" s="84"/>
-      <c r="AF91" s="85"/>
+      <c r="AD91" s="89" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE91" s="90"/>
+      <c r="AF91" s="91"/>
       <c r="AG91" s="31"/>
-      <c r="AH91" s="83"/>
-      <c r="AI91" s="84"/>
-      <c r="AJ91" s="85"/>
+      <c r="AH91" s="65"/>
+      <c r="AI91" s="66"/>
+      <c r="AJ91" s="67"/>
       <c r="AK91" s="31"/>
-      <c r="AL91" s="83"/>
-      <c r="AM91" s="84"/>
-      <c r="AN91" s="85"/>
+      <c r="AL91" s="65"/>
+      <c r="AM91" s="66"/>
+      <c r="AN91" s="67"/>
       <c r="AO91" s="12"/>
       <c r="AP91" s="29"/>
       <c r="AQ91" s="26"/>
@@ -7343,56 +7345,56 @@
     </row>
     <row r="93" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="12"/>
-      <c r="B93" s="81"/>
-      <c r="C93" s="82"/>
+      <c r="B93" s="68"/>
+      <c r="C93" s="69"/>
       <c r="D93" s="55"/>
       <c r="E93" s="36"/>
-      <c r="F93" s="81"/>
-      <c r="G93" s="82"/>
+      <c r="F93" s="68"/>
+      <c r="G93" s="69"/>
       <c r="H93" s="55"/>
       <c r="I93" s="32"/>
-      <c r="J93" s="81"/>
-      <c r="K93" s="82"/>
+      <c r="J93" s="68"/>
+      <c r="K93" s="69"/>
       <c r="L93" s="55"/>
       <c r="M93" s="6"/>
-      <c r="N93" s="70"/>
-      <c r="O93" s="71"/>
+      <c r="N93" s="81"/>
+      <c r="O93" s="82"/>
       <c r="P93" s="34"/>
       <c r="Q93" s="32"/>
-      <c r="R93" s="70" t="s">
+      <c r="R93" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="S93" s="71"/>
+      <c r="S93" s="82"/>
       <c r="T93" s="34"/>
       <c r="U93" s="36"/>
-      <c r="V93" s="70" t="s">
+      <c r="V93" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="W93" s="71"/>
+      <c r="W93" s="82"/>
       <c r="X93" s="34"/>
       <c r="Y93" s="32"/>
-      <c r="Z93" s="70" t="s">
+      <c r="Z93" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="AA93" s="71"/>
+      <c r="AA93" s="82"/>
       <c r="AB93" s="34"/>
       <c r="AC93" s="32"/>
-      <c r="AD93" s="70" t="s">
+      <c r="AD93" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="AE93" s="71"/>
+      <c r="AE93" s="82"/>
       <c r="AF93" s="34"/>
       <c r="AG93" s="32"/>
-      <c r="AH93" s="70" t="s">
+      <c r="AH93" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="AI93" s="71"/>
+      <c r="AI93" s="82"/>
       <c r="AJ93" s="34"/>
       <c r="AK93" s="32"/>
-      <c r="AL93" s="70" t="s">
+      <c r="AL93" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="AM93" s="71"/>
+      <c r="AM93" s="82"/>
       <c r="AN93" s="34"/>
       <c r="AO93" s="12"/>
       <c r="AP93" s="29"/>
@@ -7413,45 +7415,45 @@
       <c r="K94" s="63"/>
       <c r="L94" s="64"/>
       <c r="M94" s="26"/>
-      <c r="N94" s="72"/>
-      <c r="O94" s="73"/>
-      <c r="P94" s="74"/>
+      <c r="N94" s="106"/>
+      <c r="O94" s="107"/>
+      <c r="P94" s="108"/>
       <c r="Q94" s="32"/>
-      <c r="R94" s="72" t="s">
+      <c r="R94" s="106" t="s">
         <v>66</v>
       </c>
-      <c r="S94" s="73"/>
-      <c r="T94" s="74"/>
+      <c r="S94" s="107"/>
+      <c r="T94" s="108"/>
       <c r="U94" s="32"/>
-      <c r="V94" s="72" t="s">
+      <c r="V94" s="106" t="s">
         <v>66</v>
       </c>
-      <c r="W94" s="73"/>
-      <c r="X94" s="74"/>
+      <c r="W94" s="107"/>
+      <c r="X94" s="108"/>
       <c r="Y94" s="32"/>
-      <c r="Z94" s="72" t="s">
+      <c r="Z94" s="106" t="s">
         <v>66</v>
       </c>
-      <c r="AA94" s="73"/>
-      <c r="AB94" s="74"/>
+      <c r="AA94" s="107"/>
+      <c r="AB94" s="108"/>
       <c r="AC94" s="35"/>
-      <c r="AD94" s="72" t="s">
+      <c r="AD94" s="106" t="s">
         <v>66</v>
       </c>
-      <c r="AE94" s="73"/>
-      <c r="AF94" s="74"/>
+      <c r="AE94" s="107"/>
+      <c r="AF94" s="108"/>
       <c r="AG94" s="32"/>
-      <c r="AH94" s="72" t="s">
+      <c r="AH94" s="106" t="s">
         <v>66</v>
       </c>
-      <c r="AI94" s="73"/>
-      <c r="AJ94" s="74"/>
+      <c r="AI94" s="107"/>
+      <c r="AJ94" s="108"/>
       <c r="AK94" s="32"/>
-      <c r="AL94" s="72" t="s">
+      <c r="AL94" s="106" t="s">
         <v>66</v>
       </c>
-      <c r="AM94" s="73"/>
-      <c r="AN94" s="74"/>
+      <c r="AM94" s="107"/>
+      <c r="AN94" s="108"/>
       <c r="AO94" s="12"/>
       <c r="AP94" s="29"/>
       <c r="AQ94" s="26"/>
@@ -7459,45 +7461,45 @@
     </row>
     <row r="95" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="12"/>
-      <c r="B95" s="78"/>
-      <c r="C95" s="79"/>
-      <c r="D95" s="80"/>
+      <c r="B95" s="73"/>
+      <c r="C95" s="74"/>
+      <c r="D95" s="75"/>
       <c r="E95" s="31"/>
-      <c r="F95" s="78"/>
-      <c r="G95" s="79"/>
-      <c r="H95" s="80"/>
+      <c r="F95" s="73"/>
+      <c r="G95" s="74"/>
+      <c r="H95" s="75"/>
       <c r="I95" s="32"/>
-      <c r="J95" s="78"/>
-      <c r="K95" s="79"/>
-      <c r="L95" s="80"/>
+      <c r="J95" s="73"/>
+      <c r="K95" s="74"/>
+      <c r="L95" s="75"/>
       <c r="M95" s="26"/>
-      <c r="N95" s="75"/>
-      <c r="O95" s="76"/>
-      <c r="P95" s="77"/>
+      <c r="N95" s="83"/>
+      <c r="O95" s="84"/>
+      <c r="P95" s="85"/>
       <c r="Q95" s="32"/>
-      <c r="R95" s="75"/>
-      <c r="S95" s="76"/>
-      <c r="T95" s="77"/>
+      <c r="R95" s="83"/>
+      <c r="S95" s="84"/>
+      <c r="T95" s="85"/>
       <c r="U95" s="31"/>
-      <c r="V95" s="75"/>
-      <c r="W95" s="76"/>
-      <c r="X95" s="77"/>
+      <c r="V95" s="83"/>
+      <c r="W95" s="84"/>
+      <c r="X95" s="85"/>
       <c r="Y95" s="32"/>
-      <c r="Z95" s="75"/>
-      <c r="AA95" s="76"/>
-      <c r="AB95" s="77"/>
+      <c r="Z95" s="83"/>
+      <c r="AA95" s="84"/>
+      <c r="AB95" s="85"/>
       <c r="AC95" s="31"/>
-      <c r="AD95" s="75"/>
-      <c r="AE95" s="76"/>
-      <c r="AF95" s="77"/>
+      <c r="AD95" s="83"/>
+      <c r="AE95" s="84"/>
+      <c r="AF95" s="85"/>
       <c r="AG95" s="32"/>
-      <c r="AH95" s="75"/>
-      <c r="AI95" s="76"/>
-      <c r="AJ95" s="77"/>
+      <c r="AH95" s="83"/>
+      <c r="AI95" s="84"/>
+      <c r="AJ95" s="85"/>
       <c r="AK95" s="32"/>
-      <c r="AL95" s="75"/>
-      <c r="AM95" s="76"/>
-      <c r="AN95" s="77"/>
+      <c r="AL95" s="83"/>
+      <c r="AM95" s="84"/>
+      <c r="AN95" s="85"/>
       <c r="AO95" s="12"/>
       <c r="AP95" s="29"/>
       <c r="AQ95" s="26"/>
@@ -7505,57 +7507,57 @@
     </row>
     <row r="96" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="12"/>
-      <c r="B96" s="89"/>
-      <c r="C96" s="90"/>
-      <c r="D96" s="91"/>
+      <c r="B96" s="70"/>
+      <c r="C96" s="71"/>
+      <c r="D96" s="72"/>
       <c r="E96" s="32"/>
-      <c r="F96" s="89"/>
-      <c r="G96" s="90"/>
-      <c r="H96" s="91"/>
+      <c r="F96" s="70"/>
+      <c r="G96" s="71"/>
+      <c r="H96" s="72"/>
       <c r="I96" s="32"/>
-      <c r="J96" s="89"/>
-      <c r="K96" s="90"/>
-      <c r="L96" s="91"/>
+      <c r="J96" s="70"/>
+      <c r="K96" s="71"/>
+      <c r="L96" s="72"/>
       <c r="M96" s="26"/>
-      <c r="N96" s="89"/>
-      <c r="O96" s="90"/>
-      <c r="P96" s="91"/>
+      <c r="N96" s="70"/>
+      <c r="O96" s="71"/>
+      <c r="P96" s="72"/>
       <c r="Q96" s="32"/>
-      <c r="R96" s="89" t="s">
+      <c r="R96" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="S96" s="90"/>
-      <c r="T96" s="91"/>
+      <c r="S96" s="71"/>
+      <c r="T96" s="72"/>
       <c r="U96" s="32"/>
-      <c r="V96" s="89" t="s">
+      <c r="V96" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="W96" s="90"/>
-      <c r="X96" s="91"/>
+      <c r="W96" s="71"/>
+      <c r="X96" s="72"/>
       <c r="Y96" s="32"/>
-      <c r="Z96" s="89" t="s">
+      <c r="Z96" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="AA96" s="90"/>
-      <c r="AB96" s="91"/>
+      <c r="AA96" s="71"/>
+      <c r="AB96" s="72"/>
       <c r="AC96" s="32"/>
-      <c r="AD96" s="89" t="s">
+      <c r="AD96" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="AE96" s="90"/>
-      <c r="AF96" s="91"/>
+      <c r="AE96" s="71"/>
+      <c r="AF96" s="72"/>
       <c r="AG96" s="32"/>
-      <c r="AH96" s="89" t="s">
+      <c r="AH96" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="AI96" s="90"/>
-      <c r="AJ96" s="91"/>
+      <c r="AI96" s="71"/>
+      <c r="AJ96" s="72"/>
       <c r="AK96" s="32"/>
-      <c r="AL96" s="89" t="s">
+      <c r="AL96" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="AM96" s="90"/>
-      <c r="AN96" s="91"/>
+      <c r="AM96" s="71"/>
+      <c r="AN96" s="72"/>
       <c r="AO96" s="12"/>
       <c r="AP96" s="29"/>
       <c r="AQ96" s="26"/>
@@ -7563,45 +7565,45 @@
     </row>
     <row r="97" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A97" s="12"/>
-      <c r="B97" s="83"/>
-      <c r="C97" s="84"/>
-      <c r="D97" s="85"/>
+      <c r="B97" s="65"/>
+      <c r="C97" s="66"/>
+      <c r="D97" s="67"/>
       <c r="E97" s="32"/>
-      <c r="F97" s="83"/>
-      <c r="G97" s="84"/>
-      <c r="H97" s="85"/>
+      <c r="F97" s="65"/>
+      <c r="G97" s="66"/>
+      <c r="H97" s="67"/>
       <c r="I97" s="31"/>
-      <c r="J97" s="83"/>
-      <c r="K97" s="84"/>
-      <c r="L97" s="85"/>
+      <c r="J97" s="65"/>
+      <c r="K97" s="66"/>
+      <c r="L97" s="67"/>
       <c r="M97" s="26"/>
-      <c r="N97" s="83"/>
-      <c r="O97" s="84"/>
-      <c r="P97" s="85"/>
+      <c r="N97" s="65"/>
+      <c r="O97" s="66"/>
+      <c r="P97" s="67"/>
       <c r="Q97" s="31"/>
-      <c r="R97" s="83"/>
-      <c r="S97" s="84"/>
-      <c r="T97" s="85"/>
+      <c r="R97" s="65"/>
+      <c r="S97" s="66"/>
+      <c r="T97" s="67"/>
       <c r="U97" s="32"/>
-      <c r="V97" s="83"/>
-      <c r="W97" s="84"/>
-      <c r="X97" s="85"/>
+      <c r="V97" s="65"/>
+      <c r="W97" s="66"/>
+      <c r="X97" s="67"/>
       <c r="Y97" s="31"/>
-      <c r="Z97" s="83"/>
-      <c r="AA97" s="84"/>
-      <c r="AB97" s="85"/>
+      <c r="Z97" s="65"/>
+      <c r="AA97" s="66"/>
+      <c r="AB97" s="67"/>
       <c r="AC97" s="31"/>
-      <c r="AD97" s="83"/>
-      <c r="AE97" s="84"/>
-      <c r="AF97" s="85"/>
+      <c r="AD97" s="65"/>
+      <c r="AE97" s="66"/>
+      <c r="AF97" s="67"/>
       <c r="AG97" s="32"/>
-      <c r="AH97" s="83"/>
-      <c r="AI97" s="84"/>
-      <c r="AJ97" s="85"/>
+      <c r="AH97" s="65"/>
+      <c r="AI97" s="66"/>
+      <c r="AJ97" s="67"/>
       <c r="AK97" s="31"/>
-      <c r="AL97" s="83"/>
-      <c r="AM97" s="84"/>
-      <c r="AN97" s="85"/>
+      <c r="AL97" s="65"/>
+      <c r="AM97" s="66"/>
+      <c r="AN97" s="67"/>
       <c r="AO97" s="12"/>
       <c r="AP97" s="29"/>
       <c r="AQ97" s="26"/>
@@ -7655,50 +7657,50 @@
     </row>
     <row r="99" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="12"/>
-      <c r="B99" s="81"/>
-      <c r="C99" s="82"/>
+      <c r="B99" s="68"/>
+      <c r="C99" s="69"/>
       <c r="D99" s="55"/>
       <c r="E99" s="32"/>
-      <c r="F99" s="81"/>
-      <c r="G99" s="82"/>
+      <c r="F99" s="68"/>
+      <c r="G99" s="69"/>
       <c r="H99" s="55"/>
       <c r="I99" s="36"/>
-      <c r="J99" s="81"/>
-      <c r="K99" s="82"/>
+      <c r="J99" s="68"/>
+      <c r="K99" s="69"/>
       <c r="L99" s="55"/>
       <c r="M99" s="26"/>
-      <c r="N99" s="70"/>
-      <c r="O99" s="71"/>
+      <c r="N99" s="81"/>
+      <c r="O99" s="82"/>
       <c r="P99" s="34"/>
       <c r="Q99" s="44"/>
-      <c r="R99" s="98" t="s">
+      <c r="R99" s="126" t="s">
         <v>110</v>
       </c>
-      <c r="S99" s="99"/>
+      <c r="S99" s="127"/>
       <c r="T99" s="59" t="s">
         <v>111</v>
       </c>
       <c r="U99" s="36"/>
-      <c r="V99" s="70"/>
-      <c r="W99" s="71"/>
+      <c r="V99" s="81"/>
+      <c r="W99" s="82"/>
       <c r="X99" s="34"/>
       <c r="Y99" s="32"/>
-      <c r="Z99" s="98" t="s">
+      <c r="Z99" s="126" t="s">
         <v>44</v>
       </c>
-      <c r="AA99" s="99"/>
+      <c r="AA99" s="127"/>
       <c r="AB99" s="59"/>
       <c r="AC99" s="36"/>
-      <c r="AD99" s="70"/>
-      <c r="AE99" s="71"/>
+      <c r="AD99" s="81"/>
+      <c r="AE99" s="82"/>
       <c r="AF99" s="34"/>
       <c r="AG99" s="32"/>
-      <c r="AH99" s="70"/>
-      <c r="AI99" s="71"/>
+      <c r="AH99" s="81"/>
+      <c r="AI99" s="82"/>
       <c r="AJ99" s="34"/>
       <c r="AK99" s="36"/>
-      <c r="AL99" s="70"/>
-      <c r="AM99" s="71"/>
+      <c r="AL99" s="81"/>
+      <c r="AM99" s="82"/>
       <c r="AN99" s="34"/>
       <c r="AO99" s="12"/>
       <c r="AP99" s="29"/>
@@ -7707,49 +7709,49 @@
     </row>
     <row r="100" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="12"/>
-      <c r="B100" s="78"/>
-      <c r="C100" s="79"/>
-      <c r="D100" s="80"/>
+      <c r="B100" s="73"/>
+      <c r="C100" s="74"/>
+      <c r="D100" s="75"/>
       <c r="E100" s="32"/>
-      <c r="F100" s="78"/>
-      <c r="G100" s="79"/>
-      <c r="H100" s="80"/>
+      <c r="F100" s="73"/>
+      <c r="G100" s="74"/>
+      <c r="H100" s="75"/>
       <c r="I100" s="31"/>
-      <c r="J100" s="78"/>
-      <c r="K100" s="79"/>
-      <c r="L100" s="80"/>
+      <c r="J100" s="73"/>
+      <c r="K100" s="74"/>
+      <c r="L100" s="75"/>
       <c r="M100" s="26"/>
-      <c r="N100" s="75"/>
-      <c r="O100" s="76"/>
-      <c r="P100" s="77"/>
+      <c r="N100" s="83"/>
+      <c r="O100" s="84"/>
+      <c r="P100" s="85"/>
       <c r="Q100" s="31"/>
-      <c r="R100" s="100" t="s">
+      <c r="R100" s="109" t="s">
         <v>116</v>
       </c>
-      <c r="S100" s="101"/>
-      <c r="T100" s="102"/>
+      <c r="S100" s="110"/>
+      <c r="T100" s="111"/>
       <c r="U100" s="31"/>
-      <c r="V100" s="75"/>
-      <c r="W100" s="76"/>
-      <c r="X100" s="77"/>
+      <c r="V100" s="83"/>
+      <c r="W100" s="84"/>
+      <c r="X100" s="85"/>
       <c r="Y100" s="32"/>
-      <c r="Z100" s="95" t="s">
+      <c r="Z100" s="120" t="s">
         <v>86</v>
       </c>
-      <c r="AA100" s="96"/>
-      <c r="AB100" s="97"/>
+      <c r="AA100" s="121"/>
+      <c r="AB100" s="122"/>
       <c r="AC100" s="36"/>
-      <c r="AD100" s="75"/>
-      <c r="AE100" s="76"/>
-      <c r="AF100" s="77"/>
+      <c r="AD100" s="83"/>
+      <c r="AE100" s="84"/>
+      <c r="AF100" s="85"/>
       <c r="AG100" s="32"/>
-      <c r="AH100" s="75"/>
-      <c r="AI100" s="76"/>
-      <c r="AJ100" s="77"/>
+      <c r="AH100" s="83"/>
+      <c r="AI100" s="84"/>
+      <c r="AJ100" s="85"/>
       <c r="AK100" s="31"/>
-      <c r="AL100" s="75"/>
-      <c r="AM100" s="76"/>
-      <c r="AN100" s="77"/>
+      <c r="AL100" s="83"/>
+      <c r="AM100" s="84"/>
+      <c r="AN100" s="85"/>
       <c r="AO100" s="12"/>
       <c r="AP100" s="29"/>
       <c r="AQ100" s="26"/>
@@ -7757,49 +7759,49 @@
     </row>
     <row r="101" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="12"/>
-      <c r="B101" s="89"/>
-      <c r="C101" s="90"/>
-      <c r="D101" s="91"/>
+      <c r="B101" s="70"/>
+      <c r="C101" s="71"/>
+      <c r="D101" s="72"/>
       <c r="E101" s="32"/>
-      <c r="F101" s="89"/>
-      <c r="G101" s="90"/>
-      <c r="H101" s="91"/>
+      <c r="F101" s="70"/>
+      <c r="G101" s="71"/>
+      <c r="H101" s="72"/>
       <c r="I101" s="31"/>
-      <c r="J101" s="89"/>
-      <c r="K101" s="90"/>
-      <c r="L101" s="91"/>
+      <c r="J101" s="70"/>
+      <c r="K101" s="71"/>
+      <c r="L101" s="72"/>
       <c r="M101" s="26"/>
-      <c r="N101" s="89"/>
-      <c r="O101" s="90"/>
-      <c r="P101" s="91"/>
+      <c r="N101" s="70"/>
+      <c r="O101" s="71"/>
+      <c r="P101" s="72"/>
       <c r="Q101" s="31"/>
-      <c r="R101" s="103" t="s">
+      <c r="R101" s="137" t="s">
         <v>115</v>
       </c>
-      <c r="S101" s="104"/>
-      <c r="T101" s="105"/>
+      <c r="S101" s="138"/>
+      <c r="T101" s="139"/>
       <c r="U101" s="32"/>
-      <c r="V101" s="89"/>
-      <c r="W101" s="90"/>
-      <c r="X101" s="91"/>
+      <c r="V101" s="70"/>
+      <c r="W101" s="71"/>
+      <c r="X101" s="72"/>
       <c r="Y101" s="32"/>
-      <c r="Z101" s="103" t="s">
+      <c r="Z101" s="137" t="s">
         <v>115</v>
       </c>
-      <c r="AA101" s="104"/>
-      <c r="AB101" s="105"/>
+      <c r="AA101" s="138"/>
+      <c r="AB101" s="139"/>
       <c r="AC101" s="31"/>
-      <c r="AD101" s="89"/>
-      <c r="AE101" s="90"/>
-      <c r="AF101" s="91"/>
+      <c r="AD101" s="70"/>
+      <c r="AE101" s="71"/>
+      <c r="AF101" s="72"/>
       <c r="AG101" s="32"/>
-      <c r="AH101" s="89"/>
-      <c r="AI101" s="90"/>
-      <c r="AJ101" s="91"/>
+      <c r="AH101" s="70"/>
+      <c r="AI101" s="71"/>
+      <c r="AJ101" s="72"/>
       <c r="AK101" s="31"/>
-      <c r="AL101" s="89"/>
-      <c r="AM101" s="90"/>
-      <c r="AN101" s="91"/>
+      <c r="AL101" s="70"/>
+      <c r="AM101" s="71"/>
+      <c r="AN101" s="72"/>
       <c r="AO101" s="12"/>
       <c r="AP101" s="29"/>
       <c r="AQ101" s="26"/>
@@ -7807,45 +7809,45 @@
     </row>
     <row r="102" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A102" s="12"/>
-      <c r="B102" s="83"/>
-      <c r="C102" s="84"/>
-      <c r="D102" s="85"/>
+      <c r="B102" s="65"/>
+      <c r="C102" s="66"/>
+      <c r="D102" s="67"/>
       <c r="E102" s="31"/>
-      <c r="F102" s="83"/>
-      <c r="G102" s="84"/>
-      <c r="H102" s="85"/>
+      <c r="F102" s="65"/>
+      <c r="G102" s="66"/>
+      <c r="H102" s="67"/>
       <c r="I102" s="32"/>
-      <c r="J102" s="83"/>
-      <c r="K102" s="84"/>
-      <c r="L102" s="85"/>
+      <c r="J102" s="65"/>
+      <c r="K102" s="66"/>
+      <c r="L102" s="67"/>
       <c r="M102" s="26"/>
-      <c r="N102" s="83"/>
-      <c r="O102" s="84"/>
-      <c r="P102" s="85"/>
+      <c r="N102" s="65"/>
+      <c r="O102" s="66"/>
+      <c r="P102" s="67"/>
       <c r="Q102" s="31"/>
-      <c r="R102" s="92"/>
-      <c r="S102" s="93"/>
-      <c r="T102" s="94"/>
+      <c r="R102" s="131"/>
+      <c r="S102" s="132"/>
+      <c r="T102" s="133"/>
       <c r="U102" s="32"/>
-      <c r="V102" s="83"/>
-      <c r="W102" s="84"/>
-      <c r="X102" s="85"/>
+      <c r="V102" s="65"/>
+      <c r="W102" s="66"/>
+      <c r="X102" s="67"/>
       <c r="Y102" s="32"/>
-      <c r="Z102" s="92"/>
-      <c r="AA102" s="93"/>
-      <c r="AB102" s="94"/>
+      <c r="Z102" s="131"/>
+      <c r="AA102" s="132"/>
+      <c r="AB102" s="133"/>
       <c r="AC102" s="32"/>
-      <c r="AD102" s="83"/>
-      <c r="AE102" s="84"/>
-      <c r="AF102" s="85"/>
+      <c r="AD102" s="65"/>
+      <c r="AE102" s="66"/>
+      <c r="AF102" s="67"/>
       <c r="AG102" s="31"/>
-      <c r="AH102" s="83"/>
-      <c r="AI102" s="84"/>
-      <c r="AJ102" s="85"/>
+      <c r="AH102" s="65"/>
+      <c r="AI102" s="66"/>
+      <c r="AJ102" s="67"/>
       <c r="AK102" s="32"/>
-      <c r="AL102" s="83"/>
-      <c r="AM102" s="84"/>
-      <c r="AN102" s="85"/>
+      <c r="AL102" s="65"/>
+      <c r="AM102" s="66"/>
+      <c r="AN102" s="67"/>
       <c r="AO102" s="12"/>
       <c r="AP102" s="29"/>
       <c r="AQ102" s="26"/>
@@ -7915,70 +7917,70 @@
       <c r="AR104" s="26"/>
     </row>
     <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B105" s="70"/>
-      <c r="C105" s="71"/>
+      <c r="B105" s="81"/>
+      <c r="C105" s="82"/>
       <c r="D105" s="34"/>
       <c r="E105" s="32"/>
-      <c r="F105" s="70"/>
-      <c r="G105" s="71"/>
+      <c r="F105" s="81"/>
+      <c r="G105" s="82"/>
       <c r="H105" s="34"/>
       <c r="I105" s="32"/>
-      <c r="J105" s="70"/>
-      <c r="K105" s="71"/>
+      <c r="J105" s="81"/>
+      <c r="K105" s="82"/>
       <c r="L105" s="34"/>
       <c r="AO105" s="26"/>
     </row>
     <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B106" s="72"/>
-      <c r="C106" s="73"/>
-      <c r="D106" s="74"/>
+      <c r="B106" s="106"/>
+      <c r="C106" s="107"/>
+      <c r="D106" s="108"/>
       <c r="E106" s="32"/>
-      <c r="F106" s="72"/>
-      <c r="G106" s="73"/>
-      <c r="H106" s="74"/>
+      <c r="F106" s="106"/>
+      <c r="G106" s="107"/>
+      <c r="H106" s="108"/>
       <c r="I106" s="32"/>
-      <c r="J106" s="72"/>
-      <c r="K106" s="73"/>
-      <c r="L106" s="74"/>
+      <c r="J106" s="106"/>
+      <c r="K106" s="107"/>
+      <c r="L106" s="108"/>
     </row>
     <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B107" s="75"/>
-      <c r="C107" s="76"/>
-      <c r="D107" s="77"/>
+      <c r="B107" s="83"/>
+      <c r="C107" s="84"/>
+      <c r="D107" s="85"/>
       <c r="E107" s="32"/>
-      <c r="F107" s="75"/>
-      <c r="G107" s="76"/>
-      <c r="H107" s="77"/>
+      <c r="F107" s="83"/>
+      <c r="G107" s="84"/>
+      <c r="H107" s="85"/>
       <c r="I107" s="32"/>
-      <c r="J107" s="75"/>
-      <c r="K107" s="76"/>
-      <c r="L107" s="77"/>
+      <c r="J107" s="83"/>
+      <c r="K107" s="84"/>
+      <c r="L107" s="85"/>
     </row>
     <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B108" s="89"/>
-      <c r="C108" s="90"/>
-      <c r="D108" s="91"/>
+      <c r="B108" s="70"/>
+      <c r="C108" s="71"/>
+      <c r="D108" s="72"/>
       <c r="E108" s="32"/>
-      <c r="F108" s="89"/>
-      <c r="G108" s="90"/>
-      <c r="H108" s="91"/>
+      <c r="F108" s="70"/>
+      <c r="G108" s="71"/>
+      <c r="H108" s="72"/>
       <c r="I108" s="31"/>
-      <c r="J108" s="89"/>
-      <c r="K108" s="90"/>
-      <c r="L108" s="91"/>
+      <c r="J108" s="70"/>
+      <c r="K108" s="71"/>
+      <c r="L108" s="72"/>
     </row>
     <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B109" s="83"/>
-      <c r="C109" s="84"/>
-      <c r="D109" s="85"/>
+      <c r="B109" s="65"/>
+      <c r="C109" s="66"/>
+      <c r="D109" s="67"/>
       <c r="E109" s="31"/>
-      <c r="F109" s="83"/>
-      <c r="G109" s="84"/>
-      <c r="H109" s="85"/>
+      <c r="F109" s="65"/>
+      <c r="G109" s="66"/>
+      <c r="H109" s="67"/>
       <c r="I109" s="31"/>
-      <c r="J109" s="83"/>
-      <c r="K109" s="84"/>
-      <c r="L109" s="85"/>
+      <c r="J109" s="65"/>
+      <c r="K109" s="66"/>
+      <c r="L109" s="67"/>
     </row>
     <row r="110" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B110" s="35"/>
@@ -7994,69 +7996,69 @@
       <c r="L110" s="35"/>
     </row>
     <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B111" s="70"/>
-      <c r="C111" s="71"/>
+      <c r="B111" s="81"/>
+      <c r="C111" s="82"/>
       <c r="D111" s="34"/>
       <c r="E111" s="31"/>
-      <c r="F111" s="70"/>
-      <c r="G111" s="71"/>
+      <c r="F111" s="81"/>
+      <c r="G111" s="82"/>
       <c r="H111" s="34"/>
       <c r="I111" s="31"/>
-      <c r="J111" s="70"/>
-      <c r="K111" s="71"/>
+      <c r="J111" s="81"/>
+      <c r="K111" s="82"/>
       <c r="L111" s="34"/>
     </row>
     <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B112" s="72"/>
-      <c r="C112" s="73"/>
-      <c r="D112" s="74"/>
+      <c r="B112" s="106"/>
+      <c r="C112" s="107"/>
+      <c r="D112" s="108"/>
       <c r="E112" s="32"/>
-      <c r="F112" s="72"/>
-      <c r="G112" s="73"/>
-      <c r="H112" s="74"/>
+      <c r="F112" s="106"/>
+      <c r="G112" s="107"/>
+      <c r="H112" s="108"/>
       <c r="I112" s="32"/>
-      <c r="J112" s="72"/>
-      <c r="K112" s="73"/>
-      <c r="L112" s="74"/>
+      <c r="J112" s="106"/>
+      <c r="K112" s="107"/>
+      <c r="L112" s="108"/>
     </row>
     <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B113" s="75"/>
-      <c r="C113" s="76"/>
-      <c r="D113" s="77"/>
+      <c r="B113" s="83"/>
+      <c r="C113" s="84"/>
+      <c r="D113" s="85"/>
       <c r="E113" s="35"/>
-      <c r="F113" s="75"/>
-      <c r="G113" s="76"/>
-      <c r="H113" s="77"/>
+      <c r="F113" s="83"/>
+      <c r="G113" s="84"/>
+      <c r="H113" s="85"/>
       <c r="I113" s="35"/>
-      <c r="J113" s="75"/>
-      <c r="K113" s="76"/>
-      <c r="L113" s="77"/>
+      <c r="J113" s="83"/>
+      <c r="K113" s="84"/>
+      <c r="L113" s="85"/>
     </row>
     <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B114" s="89"/>
-      <c r="C114" s="90"/>
-      <c r="D114" s="91"/>
+      <c r="B114" s="70"/>
+      <c r="C114" s="71"/>
+      <c r="D114" s="72"/>
       <c r="E114" s="32"/>
-      <c r="F114" s="89"/>
-      <c r="G114" s="90"/>
-      <c r="H114" s="91"/>
+      <c r="F114" s="70"/>
+      <c r="G114" s="71"/>
+      <c r="H114" s="72"/>
       <c r="I114" s="32"/>
-      <c r="J114" s="89"/>
-      <c r="K114" s="90"/>
-      <c r="L114" s="91"/>
+      <c r="J114" s="70"/>
+      <c r="K114" s="71"/>
+      <c r="L114" s="72"/>
     </row>
     <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B115" s="83"/>
-      <c r="C115" s="84"/>
-      <c r="D115" s="85"/>
+      <c r="B115" s="65"/>
+      <c r="C115" s="66"/>
+      <c r="D115" s="67"/>
       <c r="E115" s="31"/>
-      <c r="F115" s="83"/>
-      <c r="G115" s="84"/>
-      <c r="H115" s="85"/>
+      <c r="F115" s="65"/>
+      <c r="G115" s="66"/>
+      <c r="H115" s="67"/>
       <c r="I115" s="31"/>
-      <c r="J115" s="83"/>
-      <c r="K115" s="84"/>
-      <c r="L115" s="85"/>
+      <c r="J115" s="65"/>
+      <c r="K115" s="66"/>
+      <c r="L115" s="67"/>
     </row>
     <row r="116" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B116" s="35"/>
@@ -8072,69 +8074,69 @@
       <c r="L116" s="35"/>
     </row>
     <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B117" s="70"/>
-      <c r="C117" s="71"/>
+      <c r="B117" s="81"/>
+      <c r="C117" s="82"/>
       <c r="D117" s="34"/>
       <c r="E117" s="32"/>
-      <c r="F117" s="70"/>
-      <c r="G117" s="71"/>
+      <c r="F117" s="81"/>
+      <c r="G117" s="82"/>
       <c r="H117" s="34"/>
       <c r="I117" s="32"/>
-      <c r="J117" s="70"/>
-      <c r="K117" s="71"/>
+      <c r="J117" s="81"/>
+      <c r="K117" s="82"/>
       <c r="L117" s="34"/>
     </row>
     <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B118" s="72"/>
-      <c r="C118" s="73"/>
-      <c r="D118" s="74"/>
+      <c r="B118" s="106"/>
+      <c r="C118" s="107"/>
+      <c r="D118" s="108"/>
       <c r="E118" s="32"/>
-      <c r="F118" s="72"/>
-      <c r="G118" s="73"/>
-      <c r="H118" s="74"/>
+      <c r="F118" s="106"/>
+      <c r="G118" s="107"/>
+      <c r="H118" s="108"/>
       <c r="I118" s="32"/>
-      <c r="J118" s="72"/>
-      <c r="K118" s="73"/>
-      <c r="L118" s="74"/>
+      <c r="J118" s="106"/>
+      <c r="K118" s="107"/>
+      <c r="L118" s="108"/>
     </row>
     <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B119" s="75"/>
-      <c r="C119" s="76"/>
-      <c r="D119" s="77"/>
+      <c r="B119" s="83"/>
+      <c r="C119" s="84"/>
+      <c r="D119" s="85"/>
       <c r="E119" s="32"/>
-      <c r="F119" s="75"/>
-      <c r="G119" s="76"/>
-      <c r="H119" s="77"/>
+      <c r="F119" s="83"/>
+      <c r="G119" s="84"/>
+      <c r="H119" s="85"/>
       <c r="I119" s="32"/>
-      <c r="J119" s="75"/>
-      <c r="K119" s="76"/>
-      <c r="L119" s="77"/>
+      <c r="J119" s="83"/>
+      <c r="K119" s="84"/>
+      <c r="L119" s="85"/>
     </row>
     <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B120" s="89"/>
-      <c r="C120" s="90"/>
-      <c r="D120" s="91"/>
+      <c r="B120" s="70"/>
+      <c r="C120" s="71"/>
+      <c r="D120" s="72"/>
       <c r="E120" s="32"/>
-      <c r="F120" s="89"/>
-      <c r="G120" s="90"/>
-      <c r="H120" s="91"/>
+      <c r="F120" s="70"/>
+      <c r="G120" s="71"/>
+      <c r="H120" s="72"/>
       <c r="I120" s="32"/>
-      <c r="J120" s="89"/>
-      <c r="K120" s="90"/>
-      <c r="L120" s="91"/>
+      <c r="J120" s="70"/>
+      <c r="K120" s="71"/>
+      <c r="L120" s="72"/>
     </row>
     <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B121" s="83"/>
-      <c r="C121" s="84"/>
-      <c r="D121" s="85"/>
+      <c r="B121" s="65"/>
+      <c r="C121" s="66"/>
+      <c r="D121" s="67"/>
       <c r="E121" s="31"/>
-      <c r="F121" s="83"/>
-      <c r="G121" s="84"/>
-      <c r="H121" s="85"/>
+      <c r="F121" s="65"/>
+      <c r="G121" s="66"/>
+      <c r="H121" s="67"/>
       <c r="I121" s="31"/>
-      <c r="J121" s="83"/>
-      <c r="K121" s="84"/>
-      <c r="L121" s="85"/>
+      <c r="J121" s="65"/>
+      <c r="K121" s="66"/>
+      <c r="L121" s="67"/>
     </row>
     <row r="122" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B122" s="35"/>
@@ -8150,69 +8152,69 @@
       <c r="L122" s="35"/>
     </row>
     <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B123" s="70"/>
-      <c r="C123" s="71"/>
+      <c r="B123" s="81"/>
+      <c r="C123" s="82"/>
       <c r="D123" s="34"/>
       <c r="E123" s="32"/>
-      <c r="F123" s="70"/>
-      <c r="G123" s="71"/>
+      <c r="F123" s="81"/>
+      <c r="G123" s="82"/>
       <c r="H123" s="34"/>
       <c r="I123" s="32"/>
-      <c r="J123" s="70"/>
-      <c r="K123" s="71"/>
+      <c r="J123" s="81"/>
+      <c r="K123" s="82"/>
       <c r="L123" s="34"/>
     </row>
     <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B124" s="72"/>
-      <c r="C124" s="73"/>
-      <c r="D124" s="74"/>
+      <c r="B124" s="106"/>
+      <c r="C124" s="107"/>
+      <c r="D124" s="108"/>
       <c r="E124" s="32"/>
-      <c r="F124" s="72"/>
-      <c r="G124" s="73"/>
-      <c r="H124" s="74"/>
+      <c r="F124" s="106"/>
+      <c r="G124" s="107"/>
+      <c r="H124" s="108"/>
       <c r="I124" s="32"/>
-      <c r="J124" s="72"/>
-      <c r="K124" s="73"/>
-      <c r="L124" s="74"/>
+      <c r="J124" s="106"/>
+      <c r="K124" s="107"/>
+      <c r="L124" s="108"/>
     </row>
     <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B125" s="75"/>
-      <c r="C125" s="76"/>
-      <c r="D125" s="77"/>
+      <c r="B125" s="83"/>
+      <c r="C125" s="84"/>
+      <c r="D125" s="85"/>
       <c r="E125" s="32"/>
-      <c r="F125" s="75"/>
-      <c r="G125" s="76"/>
-      <c r="H125" s="77"/>
+      <c r="F125" s="83"/>
+      <c r="G125" s="84"/>
+      <c r="H125" s="85"/>
       <c r="I125" s="32"/>
-      <c r="J125" s="75"/>
-      <c r="K125" s="76"/>
-      <c r="L125" s="77"/>
+      <c r="J125" s="83"/>
+      <c r="K125" s="84"/>
+      <c r="L125" s="85"/>
     </row>
     <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B126" s="89"/>
-      <c r="C126" s="90"/>
-      <c r="D126" s="91"/>
+      <c r="B126" s="70"/>
+      <c r="C126" s="71"/>
+      <c r="D126" s="72"/>
       <c r="E126" s="32"/>
-      <c r="F126" s="89"/>
-      <c r="G126" s="90"/>
-      <c r="H126" s="91"/>
+      <c r="F126" s="70"/>
+      <c r="G126" s="71"/>
+      <c r="H126" s="72"/>
       <c r="I126" s="31"/>
-      <c r="J126" s="89"/>
-      <c r="K126" s="90"/>
-      <c r="L126" s="91"/>
+      <c r="J126" s="70"/>
+      <c r="K126" s="71"/>
+      <c r="L126" s="72"/>
     </row>
     <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B127" s="83"/>
-      <c r="C127" s="84"/>
-      <c r="D127" s="85"/>
+      <c r="B127" s="65"/>
+      <c r="C127" s="66"/>
+      <c r="D127" s="67"/>
       <c r="E127" s="31"/>
-      <c r="F127" s="83"/>
-      <c r="G127" s="84"/>
-      <c r="H127" s="85"/>
+      <c r="F127" s="65"/>
+      <c r="G127" s="66"/>
+      <c r="H127" s="67"/>
       <c r="I127" s="31"/>
-      <c r="J127" s="83"/>
-      <c r="K127" s="84"/>
-      <c r="L127" s="85"/>
+      <c r="J127" s="65"/>
+      <c r="K127" s="66"/>
+      <c r="L127" s="67"/>
     </row>
     <row r="128" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B128" s="35"/>
@@ -8228,74 +8230,912 @@
       <c r="L128" s="35"/>
     </row>
     <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B129" s="70"/>
-      <c r="C129" s="71"/>
+      <c r="B129" s="81"/>
+      <c r="C129" s="82"/>
       <c r="D129" s="34"/>
       <c r="E129" s="31"/>
-      <c r="F129" s="70"/>
-      <c r="G129" s="71"/>
+      <c r="F129" s="81"/>
+      <c r="G129" s="82"/>
       <c r="H129" s="34"/>
       <c r="I129" s="32"/>
-      <c r="J129" s="70"/>
-      <c r="K129" s="71"/>
+      <c r="J129" s="81"/>
+      <c r="K129" s="82"/>
       <c r="L129" s="34"/>
     </row>
     <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B130" s="72"/>
-      <c r="C130" s="73"/>
-      <c r="D130" s="74"/>
+      <c r="B130" s="106"/>
+      <c r="C130" s="107"/>
+      <c r="D130" s="108"/>
       <c r="E130" s="32"/>
-      <c r="F130" s="72"/>
-      <c r="G130" s="73"/>
-      <c r="H130" s="74"/>
+      <c r="F130" s="106"/>
+      <c r="G130" s="107"/>
+      <c r="H130" s="108"/>
       <c r="I130" s="32"/>
-      <c r="J130" s="72"/>
-      <c r="K130" s="73"/>
-      <c r="L130" s="74"/>
+      <c r="J130" s="106"/>
+      <c r="K130" s="107"/>
+      <c r="L130" s="108"/>
     </row>
     <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B131" s="75"/>
-      <c r="C131" s="76"/>
-      <c r="D131" s="77"/>
+      <c r="B131" s="83"/>
+      <c r="C131" s="84"/>
+      <c r="D131" s="85"/>
       <c r="E131" s="35"/>
-      <c r="F131" s="75"/>
-      <c r="G131" s="76"/>
-      <c r="H131" s="77"/>
+      <c r="F131" s="83"/>
+      <c r="G131" s="84"/>
+      <c r="H131" s="85"/>
       <c r="I131" s="32"/>
-      <c r="J131" s="75"/>
-      <c r="K131" s="76"/>
-      <c r="L131" s="77"/>
+      <c r="J131" s="83"/>
+      <c r="K131" s="84"/>
+      <c r="L131" s="85"/>
     </row>
     <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B132" s="89"/>
-      <c r="C132" s="90"/>
-      <c r="D132" s="91"/>
+      <c r="B132" s="70"/>
+      <c r="C132" s="71"/>
+      <c r="D132" s="72"/>
       <c r="E132" s="35"/>
-      <c r="F132" s="89"/>
-      <c r="G132" s="90"/>
-      <c r="H132" s="91"/>
+      <c r="F132" s="70"/>
+      <c r="G132" s="71"/>
+      <c r="H132" s="72"/>
       <c r="I132" s="31"/>
-      <c r="J132" s="89"/>
-      <c r="K132" s="90"/>
-      <c r="L132" s="91"/>
+      <c r="J132" s="70"/>
+      <c r="K132" s="71"/>
+      <c r="L132" s="72"/>
     </row>
     <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B133" s="83"/>
-      <c r="C133" s="84"/>
-      <c r="D133" s="85"/>
+      <c r="B133" s="65"/>
+      <c r="C133" s="66"/>
+      <c r="D133" s="67"/>
       <c r="E133" s="31"/>
-      <c r="F133" s="83"/>
-      <c r="G133" s="84"/>
-      <c r="H133" s="85"/>
+      <c r="F133" s="65"/>
+      <c r="G133" s="66"/>
+      <c r="H133" s="67"/>
       <c r="I133" s="31"/>
-      <c r="J133" s="83"/>
-      <c r="K133" s="84"/>
-      <c r="L133" s="85"/>
+      <c r="J133" s="65"/>
+      <c r="K133" s="66"/>
+      <c r="L133" s="67"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0" selectUnlockedCells="1"/>
   <dataConsolidate/>
   <mergeCells count="862">
+    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R41:T41"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R42:T42"/>
+    <mergeCell ref="V52:W52"/>
+    <mergeCell ref="V41:X41"/>
+    <mergeCell ref="V40:X40"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="J81:K81"/>
+    <mergeCell ref="J77:L77"/>
+    <mergeCell ref="J76:L76"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="V50:X50"/>
+    <mergeCell ref="R49:T49"/>
+    <mergeCell ref="J49:L49"/>
+    <mergeCell ref="J47:L47"/>
+    <mergeCell ref="J79:L79"/>
+    <mergeCell ref="J71:L71"/>
+    <mergeCell ref="R50:T50"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="J60:L60"/>
+    <mergeCell ref="J78:L78"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="J53:L53"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="R71:T71"/>
+    <mergeCell ref="N71:P71"/>
+    <mergeCell ref="R76:T76"/>
+    <mergeCell ref="N69:P69"/>
+    <mergeCell ref="R63:T63"/>
+    <mergeCell ref="N68:P68"/>
+    <mergeCell ref="F75:G75"/>
+    <mergeCell ref="AL50:AN50"/>
+    <mergeCell ref="AL52:AM52"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="F62:H62"/>
+    <mergeCell ref="F61:H61"/>
+    <mergeCell ref="J64:L64"/>
+    <mergeCell ref="F69:H69"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="J66:K66"/>
+    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="F67:H67"/>
+    <mergeCell ref="J67:L67"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="F68:H68"/>
+    <mergeCell ref="J68:L68"/>
+    <mergeCell ref="F63:H63"/>
+    <mergeCell ref="Z55:AB55"/>
+    <mergeCell ref="N63:P63"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="F54:H54"/>
+    <mergeCell ref="B100:D100"/>
+    <mergeCell ref="F100:H100"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="F88:H88"/>
+    <mergeCell ref="B89:D89"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="J75:K75"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="J82:L82"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B95:D95"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="J70:L70"/>
+    <mergeCell ref="B71:D71"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="Z102:AB102"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="F70:H70"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="F76:H76"/>
+    <mergeCell ref="F90:H90"/>
+    <mergeCell ref="F89:H89"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="F82:H82"/>
+    <mergeCell ref="F83:H83"/>
+    <mergeCell ref="F84:H84"/>
+    <mergeCell ref="F77:H77"/>
+    <mergeCell ref="B85:D85"/>
+    <mergeCell ref="F79:H79"/>
+    <mergeCell ref="F71:H71"/>
+    <mergeCell ref="F85:H85"/>
+    <mergeCell ref="Z100:AB100"/>
+    <mergeCell ref="N94:P94"/>
+    <mergeCell ref="R95:T95"/>
+    <mergeCell ref="N96:P96"/>
+    <mergeCell ref="R99:S99"/>
+    <mergeCell ref="V99:W99"/>
+    <mergeCell ref="Z99:AA99"/>
+    <mergeCell ref="N97:P97"/>
+    <mergeCell ref="N99:O99"/>
+    <mergeCell ref="J102:L102"/>
+    <mergeCell ref="J112:L112"/>
+    <mergeCell ref="J111:K111"/>
+    <mergeCell ref="B106:D106"/>
+    <mergeCell ref="B107:D107"/>
+    <mergeCell ref="F106:H106"/>
+    <mergeCell ref="F105:G105"/>
+    <mergeCell ref="N102:P102"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="F102:H102"/>
+    <mergeCell ref="J107:L107"/>
+    <mergeCell ref="J108:L108"/>
+    <mergeCell ref="B109:D109"/>
+    <mergeCell ref="F109:H109"/>
+    <mergeCell ref="B108:D108"/>
+    <mergeCell ref="J105:K105"/>
+    <mergeCell ref="F108:H108"/>
+    <mergeCell ref="J106:L106"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="F111:G111"/>
+    <mergeCell ref="J109:L109"/>
+    <mergeCell ref="F112:H112"/>
+    <mergeCell ref="B113:D113"/>
+    <mergeCell ref="F113:H113"/>
+    <mergeCell ref="J113:L113"/>
+    <mergeCell ref="B114:D114"/>
+    <mergeCell ref="F114:H114"/>
+    <mergeCell ref="J114:L114"/>
+    <mergeCell ref="F121:H121"/>
+    <mergeCell ref="J123:K123"/>
+    <mergeCell ref="F107:H107"/>
+    <mergeCell ref="B112:D112"/>
+    <mergeCell ref="B125:D125"/>
+    <mergeCell ref="F125:H125"/>
+    <mergeCell ref="J121:L121"/>
+    <mergeCell ref="J125:L125"/>
+    <mergeCell ref="B118:D118"/>
+    <mergeCell ref="F118:H118"/>
+    <mergeCell ref="B115:D115"/>
+    <mergeCell ref="F115:H115"/>
+    <mergeCell ref="J115:L115"/>
+    <mergeCell ref="F120:H120"/>
+    <mergeCell ref="J120:L120"/>
+    <mergeCell ref="J118:L118"/>
+    <mergeCell ref="B124:D124"/>
+    <mergeCell ref="F124:H124"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="J124:L124"/>
+    <mergeCell ref="F119:H119"/>
+    <mergeCell ref="J119:L119"/>
+    <mergeCell ref="B120:D120"/>
+    <mergeCell ref="B121:D121"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="F123:G123"/>
+    <mergeCell ref="B119:D119"/>
+    <mergeCell ref="Z12:AA12"/>
+    <mergeCell ref="B133:D133"/>
+    <mergeCell ref="F133:H133"/>
+    <mergeCell ref="J133:L133"/>
+    <mergeCell ref="B127:D127"/>
+    <mergeCell ref="F127:H127"/>
+    <mergeCell ref="J127:L127"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="F129:G129"/>
+    <mergeCell ref="J129:K129"/>
+    <mergeCell ref="B130:D130"/>
+    <mergeCell ref="F130:H130"/>
+    <mergeCell ref="J130:L130"/>
+    <mergeCell ref="B132:D132"/>
+    <mergeCell ref="F132:H132"/>
+    <mergeCell ref="J132:L132"/>
+    <mergeCell ref="B131:D131"/>
+    <mergeCell ref="F131:H131"/>
+    <mergeCell ref="J131:L131"/>
+    <mergeCell ref="B126:D126"/>
+    <mergeCell ref="F126:H126"/>
+    <mergeCell ref="J126:L126"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="J117:K117"/>
+    <mergeCell ref="V102:X102"/>
+    <mergeCell ref="R68:T68"/>
+    <mergeCell ref="V68:X68"/>
+    <mergeCell ref="N66:O66"/>
+    <mergeCell ref="N67:P67"/>
+    <mergeCell ref="N60:P60"/>
+    <mergeCell ref="J69:L69"/>
+    <mergeCell ref="N62:P62"/>
+    <mergeCell ref="R62:T62"/>
+    <mergeCell ref="N89:P89"/>
+    <mergeCell ref="N87:O87"/>
+    <mergeCell ref="J88:L88"/>
+    <mergeCell ref="J85:L85"/>
+    <mergeCell ref="J101:L101"/>
+    <mergeCell ref="R102:T102"/>
+    <mergeCell ref="R100:T100"/>
+    <mergeCell ref="V100:X100"/>
+    <mergeCell ref="R101:T101"/>
+    <mergeCell ref="N100:P100"/>
+    <mergeCell ref="N81:O81"/>
+    <mergeCell ref="R81:S81"/>
+    <mergeCell ref="V81:W81"/>
+    <mergeCell ref="V82:X82"/>
+    <mergeCell ref="N82:P82"/>
+    <mergeCell ref="F101:H101"/>
+    <mergeCell ref="R94:T94"/>
+    <mergeCell ref="V64:X64"/>
+    <mergeCell ref="R64:T64"/>
+    <mergeCell ref="R61:T61"/>
+    <mergeCell ref="R60:T60"/>
+    <mergeCell ref="R87:S87"/>
+    <mergeCell ref="V87:W87"/>
+    <mergeCell ref="N91:P91"/>
+    <mergeCell ref="J96:L96"/>
+    <mergeCell ref="N83:P83"/>
+    <mergeCell ref="N84:P84"/>
+    <mergeCell ref="N90:P90"/>
+    <mergeCell ref="J89:L89"/>
+    <mergeCell ref="J83:L83"/>
+    <mergeCell ref="V89:X89"/>
+    <mergeCell ref="R89:T89"/>
+    <mergeCell ref="R84:T84"/>
+    <mergeCell ref="N85:P85"/>
+    <mergeCell ref="R85:T85"/>
+    <mergeCell ref="V85:X85"/>
+    <mergeCell ref="R88:T88"/>
+    <mergeCell ref="V84:X84"/>
+    <mergeCell ref="J84:L84"/>
+    <mergeCell ref="AL9:AN9"/>
+    <mergeCell ref="AD9:AF9"/>
+    <mergeCell ref="AH16:AJ16"/>
+    <mergeCell ref="AL10:AN10"/>
+    <mergeCell ref="AL14:AN14"/>
+    <mergeCell ref="AL16:AN16"/>
+    <mergeCell ref="Z15:AB15"/>
+    <mergeCell ref="AD15:AF15"/>
+    <mergeCell ref="Z13:AA13"/>
+    <mergeCell ref="AL15:AN15"/>
+    <mergeCell ref="AL12:AM12"/>
+    <mergeCell ref="AD16:AF16"/>
+    <mergeCell ref="Z10:AB10"/>
+    <mergeCell ref="AH14:AJ14"/>
+    <mergeCell ref="Z14:AB14"/>
+    <mergeCell ref="AD14:AF14"/>
+    <mergeCell ref="AD13:AE13"/>
+    <mergeCell ref="AH10:AJ10"/>
+    <mergeCell ref="AH15:AJ15"/>
+    <mergeCell ref="AD10:AF10"/>
+    <mergeCell ref="AD12:AE12"/>
+    <mergeCell ref="AH12:AI12"/>
+    <mergeCell ref="AH9:AJ9"/>
+    <mergeCell ref="Z16:AB16"/>
+    <mergeCell ref="AH21:AI21"/>
+    <mergeCell ref="AH31:AI31"/>
+    <mergeCell ref="AD31:AE31"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="Z21:AA21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="R22:T22"/>
+    <mergeCell ref="V22:X22"/>
+    <mergeCell ref="Z22:AB22"/>
+    <mergeCell ref="AD22:AF22"/>
+    <mergeCell ref="AH22:AJ22"/>
+    <mergeCell ref="AD29:AE29"/>
+    <mergeCell ref="AH29:AI29"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:T23"/>
+    <mergeCell ref="V23:X23"/>
+    <mergeCell ref="V27:W27"/>
+    <mergeCell ref="AD27:AE27"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="N29:O29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="Z30:AA30"/>
+    <mergeCell ref="N25:AB26"/>
+    <mergeCell ref="Z88:AB88"/>
+    <mergeCell ref="J94:L94"/>
+    <mergeCell ref="J95:L95"/>
+    <mergeCell ref="V94:X94"/>
+    <mergeCell ref="V96:X96"/>
+    <mergeCell ref="V95:X95"/>
+    <mergeCell ref="Z96:AB96"/>
+    <mergeCell ref="R96:T96"/>
+    <mergeCell ref="B101:D101"/>
+    <mergeCell ref="N101:P101"/>
+    <mergeCell ref="N95:P95"/>
+    <mergeCell ref="V101:X101"/>
+    <mergeCell ref="Z101:AB101"/>
+    <mergeCell ref="Z94:AB94"/>
+    <mergeCell ref="Z95:AB95"/>
+    <mergeCell ref="V90:X90"/>
+    <mergeCell ref="V88:X88"/>
+    <mergeCell ref="R90:T90"/>
+    <mergeCell ref="Z89:AB89"/>
+    <mergeCell ref="Z90:AB90"/>
+    <mergeCell ref="N88:P88"/>
+    <mergeCell ref="N93:O93"/>
+    <mergeCell ref="J100:L100"/>
+    <mergeCell ref="B97:D97"/>
+    <mergeCell ref="AL1:AN1"/>
+    <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="AD2:AF2"/>
+    <mergeCell ref="AH2:AJ2"/>
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="AH8:AJ8"/>
+    <mergeCell ref="AL6:AM6"/>
+    <mergeCell ref="AD1:AF1"/>
+    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="AL7:AM7"/>
+    <mergeCell ref="AD8:AF8"/>
+    <mergeCell ref="Z8:AB8"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AH7:AI7"/>
+    <mergeCell ref="AD7:AE7"/>
+    <mergeCell ref="Z7:AA7"/>
+    <mergeCell ref="AL8:AN8"/>
+    <mergeCell ref="AD4:AN5"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="AD6:AE6"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="V1:X1"/>
+    <mergeCell ref="V14:X14"/>
+    <mergeCell ref="R15:T15"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="B4:L5"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="V2:X2"/>
+    <mergeCell ref="N4:AB5"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="R9:T9"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="N18:AB19"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="R14:T14"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="V15:X15"/>
+    <mergeCell ref="V16:X16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="Z20:AA20"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="V28:W28"/>
+    <mergeCell ref="Z28:AA28"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="Z27:AA27"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="V13:W13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="Z9:AB9"/>
+    <mergeCell ref="R10:T10"/>
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="AD21:AE21"/>
+    <mergeCell ref="AD49:AF49"/>
+    <mergeCell ref="AD43:AF43"/>
+    <mergeCell ref="R48:T48"/>
+    <mergeCell ref="Z42:AB42"/>
+    <mergeCell ref="Z43:AB43"/>
+    <mergeCell ref="N36:AB37"/>
+    <mergeCell ref="Z48:AB48"/>
+    <mergeCell ref="Z45:AA45"/>
+    <mergeCell ref="Z46:AB46"/>
+    <mergeCell ref="AD38:AE38"/>
+    <mergeCell ref="AD39:AF39"/>
+    <mergeCell ref="AD40:AF40"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="V49:X49"/>
+    <mergeCell ref="V48:X48"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="AL102:AN102"/>
+    <mergeCell ref="AL101:AN101"/>
+    <mergeCell ref="AL96:AN96"/>
+    <mergeCell ref="AD102:AF102"/>
+    <mergeCell ref="AH102:AJ102"/>
+    <mergeCell ref="AL90:AN90"/>
+    <mergeCell ref="AL95:AN95"/>
+    <mergeCell ref="AD101:AF101"/>
+    <mergeCell ref="AH101:AJ101"/>
+    <mergeCell ref="AH100:AJ100"/>
+    <mergeCell ref="AL94:AN94"/>
+    <mergeCell ref="AD100:AF100"/>
+    <mergeCell ref="AD96:AF96"/>
+    <mergeCell ref="AD94:AF94"/>
+    <mergeCell ref="AD95:AF95"/>
+    <mergeCell ref="AH96:AJ96"/>
+    <mergeCell ref="AD90:AF90"/>
+    <mergeCell ref="AH95:AJ95"/>
+    <mergeCell ref="AH94:AJ94"/>
+    <mergeCell ref="AL100:AN100"/>
+    <mergeCell ref="AD97:AF97"/>
+    <mergeCell ref="AH97:AJ97"/>
+    <mergeCell ref="AL97:AN97"/>
+    <mergeCell ref="AH90:AJ90"/>
+    <mergeCell ref="AD82:AF82"/>
+    <mergeCell ref="AH83:AJ83"/>
+    <mergeCell ref="AD84:AF84"/>
+    <mergeCell ref="AH84:AJ84"/>
+    <mergeCell ref="AD83:AF83"/>
+    <mergeCell ref="Z84:AB84"/>
+    <mergeCell ref="Z82:AB82"/>
+    <mergeCell ref="AL77:AN77"/>
+    <mergeCell ref="AL78:AN78"/>
+    <mergeCell ref="AD77:AF77"/>
+    <mergeCell ref="AD79:AF79"/>
+    <mergeCell ref="AH79:AJ79"/>
+    <mergeCell ref="AL79:AN79"/>
+    <mergeCell ref="AD81:AE81"/>
+    <mergeCell ref="AH81:AI81"/>
+    <mergeCell ref="AL81:AM81"/>
+    <mergeCell ref="AL82:AN82"/>
+    <mergeCell ref="AL88:AN88"/>
+    <mergeCell ref="AL89:AN89"/>
+    <mergeCell ref="AL83:AN83"/>
+    <mergeCell ref="AL84:AN84"/>
+    <mergeCell ref="AD88:AF88"/>
+    <mergeCell ref="AD89:AF89"/>
+    <mergeCell ref="AH87:AI87"/>
+    <mergeCell ref="AL87:AM87"/>
+    <mergeCell ref="AH88:AJ88"/>
+    <mergeCell ref="AH89:AJ89"/>
+    <mergeCell ref="AD85:AF85"/>
+    <mergeCell ref="AH85:AJ85"/>
+    <mergeCell ref="AL85:AN85"/>
+    <mergeCell ref="Z76:AB76"/>
+    <mergeCell ref="Z77:AB77"/>
+    <mergeCell ref="V76:X76"/>
+    <mergeCell ref="N78:P78"/>
+    <mergeCell ref="Z78:AB78"/>
+    <mergeCell ref="N79:P79"/>
+    <mergeCell ref="R79:T79"/>
+    <mergeCell ref="V79:X79"/>
+    <mergeCell ref="Z79:AB79"/>
+    <mergeCell ref="V78:X78"/>
+    <mergeCell ref="R78:T78"/>
+    <mergeCell ref="AL76:AN76"/>
+    <mergeCell ref="AD76:AF76"/>
+    <mergeCell ref="Z81:AA81"/>
+    <mergeCell ref="AL62:AN62"/>
+    <mergeCell ref="AL63:AN63"/>
+    <mergeCell ref="AL71:AN71"/>
+    <mergeCell ref="AL70:AN70"/>
+    <mergeCell ref="AL69:AN69"/>
+    <mergeCell ref="N73:AB74"/>
+    <mergeCell ref="N75:O75"/>
+    <mergeCell ref="R75:S75"/>
+    <mergeCell ref="V75:W75"/>
+    <mergeCell ref="Z75:AA75"/>
+    <mergeCell ref="AD75:AE75"/>
+    <mergeCell ref="N64:P64"/>
+    <mergeCell ref="N70:P70"/>
+    <mergeCell ref="AH70:AJ70"/>
+    <mergeCell ref="AD70:AF70"/>
+    <mergeCell ref="Z69:AB69"/>
+    <mergeCell ref="Z70:AB70"/>
+    <mergeCell ref="V71:X71"/>
+    <mergeCell ref="AD63:AF63"/>
+    <mergeCell ref="AH64:AJ64"/>
+    <mergeCell ref="AH75:AI75"/>
+    <mergeCell ref="AH23:AJ23"/>
+    <mergeCell ref="AL23:AN23"/>
+    <mergeCell ref="AD28:AE28"/>
+    <mergeCell ref="AH28:AI28"/>
+    <mergeCell ref="AL28:AM28"/>
+    <mergeCell ref="AH52:AI52"/>
+    <mergeCell ref="AH54:AJ54"/>
+    <mergeCell ref="AH55:AJ55"/>
+    <mergeCell ref="AD56:AF56"/>
+    <mergeCell ref="AH56:AJ56"/>
+    <mergeCell ref="AH53:AJ53"/>
+    <mergeCell ref="AH47:AJ47"/>
+    <mergeCell ref="AD42:AF42"/>
+    <mergeCell ref="AD48:AF48"/>
+    <mergeCell ref="AD53:AF53"/>
+    <mergeCell ref="AD50:AF50"/>
+    <mergeCell ref="AD52:AE52"/>
+    <mergeCell ref="AL33:AM33"/>
+    <mergeCell ref="AD47:AF47"/>
+    <mergeCell ref="AH40:AJ40"/>
+    <mergeCell ref="AH38:AI38"/>
+    <mergeCell ref="AH39:AJ39"/>
+    <mergeCell ref="AL38:AM38"/>
+    <mergeCell ref="AL39:AN39"/>
+    <mergeCell ref="AL20:AM20"/>
+    <mergeCell ref="AL27:AM27"/>
+    <mergeCell ref="AL21:AM21"/>
+    <mergeCell ref="AH27:AI27"/>
+    <mergeCell ref="AD20:AE20"/>
+    <mergeCell ref="AH20:AI20"/>
+    <mergeCell ref="AD59:AE59"/>
+    <mergeCell ref="V57:X57"/>
+    <mergeCell ref="V61:X61"/>
+    <mergeCell ref="Z61:AB61"/>
+    <mergeCell ref="AD60:AF60"/>
+    <mergeCell ref="AH60:AJ60"/>
+    <mergeCell ref="V60:X60"/>
+    <mergeCell ref="Z60:AB60"/>
+    <mergeCell ref="V30:W30"/>
+    <mergeCell ref="Z31:AA31"/>
+    <mergeCell ref="V29:W29"/>
+    <mergeCell ref="Z29:AA29"/>
+    <mergeCell ref="AL60:AN60"/>
+    <mergeCell ref="AL61:AN61"/>
+    <mergeCell ref="Z56:AB56"/>
+    <mergeCell ref="AL22:AN22"/>
+    <mergeCell ref="Z23:AB23"/>
+    <mergeCell ref="AD23:AF23"/>
+    <mergeCell ref="AL57:AN57"/>
+    <mergeCell ref="AL59:AM59"/>
+    <mergeCell ref="AL56:AN56"/>
+    <mergeCell ref="AL54:AN54"/>
+    <mergeCell ref="AL53:AN53"/>
+    <mergeCell ref="AL55:AN55"/>
+    <mergeCell ref="Z59:AA59"/>
+    <mergeCell ref="R56:T56"/>
+    <mergeCell ref="V53:X53"/>
+    <mergeCell ref="R57:T57"/>
+    <mergeCell ref="AH61:AJ61"/>
+    <mergeCell ref="J54:L54"/>
+    <mergeCell ref="N56:P56"/>
+    <mergeCell ref="R54:T54"/>
+    <mergeCell ref="V54:X54"/>
+    <mergeCell ref="N54:P54"/>
+    <mergeCell ref="R55:T55"/>
+    <mergeCell ref="V59:W59"/>
+    <mergeCell ref="V55:X55"/>
+    <mergeCell ref="AD57:AF57"/>
+    <mergeCell ref="Z54:AB54"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="N61:P61"/>
+    <mergeCell ref="AD41:AF41"/>
+    <mergeCell ref="AL43:AN43"/>
+    <mergeCell ref="AL45:AM45"/>
+    <mergeCell ref="AL42:AN42"/>
+    <mergeCell ref="Z41:AB41"/>
+    <mergeCell ref="Z40:AB40"/>
+    <mergeCell ref="Z38:AA38"/>
+    <mergeCell ref="Z39:AB39"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="V31:W31"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="R39:T39"/>
+    <mergeCell ref="V38:W38"/>
+    <mergeCell ref="V39:X39"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="Z47:AB47"/>
+    <mergeCell ref="AH34:AI34"/>
+    <mergeCell ref="V42:X42"/>
+    <mergeCell ref="V43:X43"/>
+    <mergeCell ref="V45:W45"/>
+    <mergeCell ref="V46:X46"/>
+    <mergeCell ref="V47:X47"/>
+    <mergeCell ref="N32:O32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="V32:W32"/>
+    <mergeCell ref="Z32:AA32"/>
+    <mergeCell ref="AD32:AE32"/>
+    <mergeCell ref="AH32:AI32"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="V33:W33"/>
+    <mergeCell ref="Z33:AA33"/>
+    <mergeCell ref="AD33:AE33"/>
+    <mergeCell ref="AH33:AI33"/>
+    <mergeCell ref="AD46:AE46"/>
+    <mergeCell ref="AH44:AJ44"/>
+    <mergeCell ref="AH46:AI46"/>
+    <mergeCell ref="AH41:AJ41"/>
+    <mergeCell ref="AL75:AM75"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="N47:O47"/>
+    <mergeCell ref="AL32:AM32"/>
+    <mergeCell ref="AL31:AM31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="AD87:AE87"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="V34:W34"/>
+    <mergeCell ref="Z34:AA34"/>
+    <mergeCell ref="AD34:AE34"/>
+    <mergeCell ref="R66:S66"/>
+    <mergeCell ref="V66:W66"/>
+    <mergeCell ref="Z66:AA66"/>
+    <mergeCell ref="R67:T67"/>
+    <mergeCell ref="V67:X67"/>
+    <mergeCell ref="Z67:AB67"/>
+    <mergeCell ref="V69:X69"/>
+    <mergeCell ref="R69:T69"/>
+    <mergeCell ref="V70:X70"/>
+    <mergeCell ref="R70:T70"/>
+    <mergeCell ref="R77:T77"/>
+    <mergeCell ref="V77:X77"/>
+    <mergeCell ref="AL49:AN49"/>
+    <mergeCell ref="AH66:AI66"/>
+    <mergeCell ref="Z64:AB64"/>
+    <mergeCell ref="Z68:AB68"/>
+    <mergeCell ref="AD68:AF68"/>
+    <mergeCell ref="Z62:AB62"/>
+    <mergeCell ref="Z57:AB57"/>
+    <mergeCell ref="AD54:AF54"/>
+    <mergeCell ref="AD55:AF55"/>
+    <mergeCell ref="Z50:AB50"/>
+    <mergeCell ref="Z49:AB49"/>
+    <mergeCell ref="AD67:AF67"/>
+    <mergeCell ref="AH63:AJ63"/>
+    <mergeCell ref="AH62:AJ62"/>
+    <mergeCell ref="AD62:AF62"/>
+    <mergeCell ref="AH68:AJ68"/>
+    <mergeCell ref="AL68:AN68"/>
+    <mergeCell ref="Z63:AB63"/>
+    <mergeCell ref="AL64:AN64"/>
+    <mergeCell ref="AH57:AJ57"/>
+    <mergeCell ref="AL66:AM66"/>
+    <mergeCell ref="Z52:AA52"/>
+    <mergeCell ref="Z53:AB53"/>
+    <mergeCell ref="AD61:AF61"/>
+    <mergeCell ref="Z87:AA87"/>
+    <mergeCell ref="AH71:AJ71"/>
+    <mergeCell ref="AD71:AF71"/>
+    <mergeCell ref="Z71:AB71"/>
+    <mergeCell ref="N77:P77"/>
+    <mergeCell ref="N55:P55"/>
+    <mergeCell ref="Z85:AB85"/>
+    <mergeCell ref="Z83:AB83"/>
+    <mergeCell ref="N59:O59"/>
+    <mergeCell ref="N76:P76"/>
+    <mergeCell ref="V56:X56"/>
+    <mergeCell ref="N57:P57"/>
+    <mergeCell ref="R59:S59"/>
+    <mergeCell ref="V62:X62"/>
+    <mergeCell ref="V63:X63"/>
+    <mergeCell ref="AH59:AI59"/>
+    <mergeCell ref="AH76:AJ76"/>
+    <mergeCell ref="AH77:AJ77"/>
+    <mergeCell ref="AD78:AF78"/>
+    <mergeCell ref="AH82:AJ82"/>
+    <mergeCell ref="AH78:AJ78"/>
+    <mergeCell ref="R82:T82"/>
+    <mergeCell ref="V83:X83"/>
+    <mergeCell ref="R83:T83"/>
+    <mergeCell ref="AD99:AE99"/>
+    <mergeCell ref="AH99:AI99"/>
+    <mergeCell ref="AL99:AM99"/>
+    <mergeCell ref="R91:T91"/>
+    <mergeCell ref="V91:X91"/>
+    <mergeCell ref="Z91:AB91"/>
+    <mergeCell ref="AD91:AF91"/>
+    <mergeCell ref="AH91:AJ91"/>
+    <mergeCell ref="AL91:AN91"/>
+    <mergeCell ref="R97:T97"/>
+    <mergeCell ref="V97:X97"/>
+    <mergeCell ref="Z97:AB97"/>
+    <mergeCell ref="AD93:AE93"/>
+    <mergeCell ref="AH93:AI93"/>
+    <mergeCell ref="AL93:AM93"/>
+    <mergeCell ref="R93:S93"/>
+    <mergeCell ref="V93:W93"/>
+    <mergeCell ref="Z93:AA93"/>
+    <mergeCell ref="AD69:AF69"/>
+    <mergeCell ref="AH69:AJ69"/>
+    <mergeCell ref="AD64:AF64"/>
+    <mergeCell ref="AH13:AI13"/>
+    <mergeCell ref="AL13:AM13"/>
+    <mergeCell ref="AH67:AJ67"/>
+    <mergeCell ref="AL67:AN67"/>
+    <mergeCell ref="AH48:AJ48"/>
+    <mergeCell ref="AH50:AJ50"/>
+    <mergeCell ref="AL29:AM29"/>
+    <mergeCell ref="AD30:AE30"/>
+    <mergeCell ref="AH30:AI30"/>
+    <mergeCell ref="AL30:AM30"/>
+    <mergeCell ref="AD66:AE66"/>
+    <mergeCell ref="AL34:AM34"/>
+    <mergeCell ref="AL40:AN40"/>
+    <mergeCell ref="AL41:AN41"/>
+    <mergeCell ref="AL47:AN47"/>
+    <mergeCell ref="AL48:AN48"/>
+    <mergeCell ref="AH42:AJ42"/>
+    <mergeCell ref="AH43:AJ43"/>
+    <mergeCell ref="AH49:AJ49"/>
+    <mergeCell ref="AD44:AF44"/>
+    <mergeCell ref="AL46:AN46"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="J46:L46"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="J39:L39"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="N53:O53"/>
+    <mergeCell ref="R45:T45"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="R51:T51"/>
+    <mergeCell ref="R53:S53"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="J48:L48"/>
+    <mergeCell ref="R40:T40"/>
+    <mergeCell ref="R43:T43"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="R44:T44"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="F46:H46"/>
     <mergeCell ref="B46:D46"/>
     <mergeCell ref="F97:H97"/>
     <mergeCell ref="J97:L97"/>
@@ -8320,850 +9160,12 @@
     <mergeCell ref="F64:H64"/>
     <mergeCell ref="F78:H78"/>
     <mergeCell ref="F60:H60"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="F50:H50"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="N53:O53"/>
-    <mergeCell ref="R45:T45"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="R51:T51"/>
-    <mergeCell ref="R53:S53"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="J48:L48"/>
-    <mergeCell ref="R40:T40"/>
-    <mergeCell ref="R43:T43"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="R44:T44"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="J46:L46"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="J39:L39"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="AD69:AF69"/>
-    <mergeCell ref="AH69:AJ69"/>
-    <mergeCell ref="AD64:AF64"/>
-    <mergeCell ref="AH13:AI13"/>
-    <mergeCell ref="AL13:AM13"/>
-    <mergeCell ref="AH67:AJ67"/>
-    <mergeCell ref="AL67:AN67"/>
-    <mergeCell ref="AH48:AJ48"/>
-    <mergeCell ref="AH50:AJ50"/>
-    <mergeCell ref="AL29:AM29"/>
-    <mergeCell ref="AD30:AE30"/>
-    <mergeCell ref="AH30:AI30"/>
-    <mergeCell ref="AL30:AM30"/>
-    <mergeCell ref="AD66:AE66"/>
-    <mergeCell ref="AL34:AM34"/>
-    <mergeCell ref="AL40:AN40"/>
-    <mergeCell ref="AL41:AN41"/>
-    <mergeCell ref="AL47:AN47"/>
-    <mergeCell ref="AL48:AN48"/>
-    <mergeCell ref="AH42:AJ42"/>
-    <mergeCell ref="AH43:AJ43"/>
-    <mergeCell ref="AH49:AJ49"/>
-    <mergeCell ref="AD44:AF44"/>
-    <mergeCell ref="AL46:AN46"/>
-    <mergeCell ref="AD99:AE99"/>
-    <mergeCell ref="AH99:AI99"/>
-    <mergeCell ref="AL99:AM99"/>
-    <mergeCell ref="R91:T91"/>
-    <mergeCell ref="V91:X91"/>
-    <mergeCell ref="Z91:AB91"/>
-    <mergeCell ref="AD91:AF91"/>
-    <mergeCell ref="AH91:AJ91"/>
-    <mergeCell ref="AL91:AN91"/>
-    <mergeCell ref="R97:T97"/>
-    <mergeCell ref="V97:X97"/>
-    <mergeCell ref="Z97:AB97"/>
-    <mergeCell ref="AD93:AE93"/>
-    <mergeCell ref="AH93:AI93"/>
-    <mergeCell ref="AL93:AM93"/>
-    <mergeCell ref="R93:S93"/>
-    <mergeCell ref="V93:W93"/>
-    <mergeCell ref="Z93:AA93"/>
-    <mergeCell ref="Z87:AA87"/>
-    <mergeCell ref="AH71:AJ71"/>
-    <mergeCell ref="AD71:AF71"/>
-    <mergeCell ref="Z71:AB71"/>
-    <mergeCell ref="N77:P77"/>
-    <mergeCell ref="N55:P55"/>
-    <mergeCell ref="Z85:AB85"/>
-    <mergeCell ref="Z83:AB83"/>
-    <mergeCell ref="N59:O59"/>
-    <mergeCell ref="N76:P76"/>
-    <mergeCell ref="V56:X56"/>
-    <mergeCell ref="N57:P57"/>
-    <mergeCell ref="R59:S59"/>
-    <mergeCell ref="V62:X62"/>
-    <mergeCell ref="V63:X63"/>
-    <mergeCell ref="AH59:AI59"/>
-    <mergeCell ref="AH76:AJ76"/>
-    <mergeCell ref="AH77:AJ77"/>
-    <mergeCell ref="AD78:AF78"/>
-    <mergeCell ref="AH82:AJ82"/>
-    <mergeCell ref="AH78:AJ78"/>
-    <mergeCell ref="R82:T82"/>
-    <mergeCell ref="V83:X83"/>
-    <mergeCell ref="R83:T83"/>
-    <mergeCell ref="AL49:AN49"/>
-    <mergeCell ref="AH66:AI66"/>
-    <mergeCell ref="Z64:AB64"/>
-    <mergeCell ref="Z68:AB68"/>
-    <mergeCell ref="AD68:AF68"/>
-    <mergeCell ref="Z62:AB62"/>
-    <mergeCell ref="Z57:AB57"/>
-    <mergeCell ref="AD54:AF54"/>
-    <mergeCell ref="AD55:AF55"/>
-    <mergeCell ref="Z50:AB50"/>
-    <mergeCell ref="Z49:AB49"/>
-    <mergeCell ref="AD67:AF67"/>
-    <mergeCell ref="AH63:AJ63"/>
-    <mergeCell ref="AH62:AJ62"/>
-    <mergeCell ref="AD62:AF62"/>
-    <mergeCell ref="AH68:AJ68"/>
-    <mergeCell ref="AL68:AN68"/>
-    <mergeCell ref="Z63:AB63"/>
-    <mergeCell ref="AL64:AN64"/>
-    <mergeCell ref="AH57:AJ57"/>
-    <mergeCell ref="AL66:AM66"/>
-    <mergeCell ref="Z52:AA52"/>
-    <mergeCell ref="Z53:AB53"/>
-    <mergeCell ref="AD61:AF61"/>
-    <mergeCell ref="AL75:AM75"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="N47:O47"/>
-    <mergeCell ref="AL32:AM32"/>
-    <mergeCell ref="AL31:AM31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="AD87:AE87"/>
-    <mergeCell ref="N34:O34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="V34:W34"/>
-    <mergeCell ref="Z34:AA34"/>
-    <mergeCell ref="AD34:AE34"/>
-    <mergeCell ref="R66:S66"/>
-    <mergeCell ref="V66:W66"/>
-    <mergeCell ref="Z66:AA66"/>
-    <mergeCell ref="R67:T67"/>
-    <mergeCell ref="V67:X67"/>
-    <mergeCell ref="Z67:AB67"/>
-    <mergeCell ref="V69:X69"/>
-    <mergeCell ref="R69:T69"/>
-    <mergeCell ref="V70:X70"/>
-    <mergeCell ref="R70:T70"/>
-    <mergeCell ref="R77:T77"/>
-    <mergeCell ref="V77:X77"/>
-    <mergeCell ref="Z47:AB47"/>
-    <mergeCell ref="AH34:AI34"/>
-    <mergeCell ref="V42:X42"/>
-    <mergeCell ref="V43:X43"/>
-    <mergeCell ref="V45:W45"/>
-    <mergeCell ref="V46:X46"/>
-    <mergeCell ref="V47:X47"/>
-    <mergeCell ref="N32:O32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="V32:W32"/>
-    <mergeCell ref="Z32:AA32"/>
-    <mergeCell ref="AD32:AE32"/>
-    <mergeCell ref="AH32:AI32"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="V33:W33"/>
-    <mergeCell ref="Z33:AA33"/>
-    <mergeCell ref="AD33:AE33"/>
-    <mergeCell ref="AH33:AI33"/>
-    <mergeCell ref="AD46:AE46"/>
-    <mergeCell ref="AH44:AJ44"/>
-    <mergeCell ref="AH46:AI46"/>
-    <mergeCell ref="AH41:AJ41"/>
-    <mergeCell ref="AD41:AF41"/>
-    <mergeCell ref="AL43:AN43"/>
-    <mergeCell ref="AL45:AM45"/>
-    <mergeCell ref="AL42:AN42"/>
-    <mergeCell ref="Z41:AB41"/>
-    <mergeCell ref="Z40:AB40"/>
-    <mergeCell ref="Z38:AA38"/>
-    <mergeCell ref="Z39:AB39"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="V31:W31"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="R39:T39"/>
-    <mergeCell ref="V38:W38"/>
-    <mergeCell ref="V39:X39"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J41:L41"/>
-    <mergeCell ref="J40:L40"/>
-    <mergeCell ref="AH61:AJ61"/>
-    <mergeCell ref="J54:L54"/>
-    <mergeCell ref="N56:P56"/>
-    <mergeCell ref="R54:T54"/>
-    <mergeCell ref="V54:X54"/>
-    <mergeCell ref="N54:P54"/>
-    <mergeCell ref="R55:T55"/>
-    <mergeCell ref="V59:W59"/>
-    <mergeCell ref="V55:X55"/>
-    <mergeCell ref="AD57:AF57"/>
-    <mergeCell ref="Z54:AB54"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="N61:P61"/>
-    <mergeCell ref="AL57:AN57"/>
-    <mergeCell ref="AL59:AM59"/>
-    <mergeCell ref="AL56:AN56"/>
-    <mergeCell ref="AL54:AN54"/>
-    <mergeCell ref="AL53:AN53"/>
-    <mergeCell ref="AL55:AN55"/>
-    <mergeCell ref="Z59:AA59"/>
-    <mergeCell ref="R56:T56"/>
-    <mergeCell ref="V53:X53"/>
-    <mergeCell ref="R57:T57"/>
-    <mergeCell ref="AL20:AM20"/>
-    <mergeCell ref="AL27:AM27"/>
-    <mergeCell ref="AL21:AM21"/>
-    <mergeCell ref="AH27:AI27"/>
-    <mergeCell ref="AD20:AE20"/>
-    <mergeCell ref="AH20:AI20"/>
-    <mergeCell ref="AD59:AE59"/>
-    <mergeCell ref="V57:X57"/>
-    <mergeCell ref="V61:X61"/>
-    <mergeCell ref="Z61:AB61"/>
-    <mergeCell ref="AD60:AF60"/>
-    <mergeCell ref="AH60:AJ60"/>
-    <mergeCell ref="V60:X60"/>
-    <mergeCell ref="Z60:AB60"/>
-    <mergeCell ref="V30:W30"/>
-    <mergeCell ref="Z31:AA31"/>
-    <mergeCell ref="V29:W29"/>
-    <mergeCell ref="Z29:AA29"/>
-    <mergeCell ref="AL60:AN60"/>
-    <mergeCell ref="AL61:AN61"/>
-    <mergeCell ref="Z56:AB56"/>
-    <mergeCell ref="AL22:AN22"/>
-    <mergeCell ref="Z23:AB23"/>
-    <mergeCell ref="AD23:AF23"/>
-    <mergeCell ref="AH23:AJ23"/>
-    <mergeCell ref="AL23:AN23"/>
-    <mergeCell ref="AD28:AE28"/>
-    <mergeCell ref="AH28:AI28"/>
-    <mergeCell ref="AL28:AM28"/>
-    <mergeCell ref="AH52:AI52"/>
-    <mergeCell ref="AH54:AJ54"/>
-    <mergeCell ref="AH55:AJ55"/>
-    <mergeCell ref="AD56:AF56"/>
-    <mergeCell ref="AH56:AJ56"/>
-    <mergeCell ref="AH53:AJ53"/>
-    <mergeCell ref="AH47:AJ47"/>
-    <mergeCell ref="AD42:AF42"/>
-    <mergeCell ref="AD48:AF48"/>
-    <mergeCell ref="AD53:AF53"/>
-    <mergeCell ref="AD50:AF50"/>
-    <mergeCell ref="AD52:AE52"/>
-    <mergeCell ref="AL33:AM33"/>
-    <mergeCell ref="AD47:AF47"/>
-    <mergeCell ref="AH40:AJ40"/>
-    <mergeCell ref="AH38:AI38"/>
-    <mergeCell ref="AH39:AJ39"/>
-    <mergeCell ref="AL38:AM38"/>
-    <mergeCell ref="AL39:AN39"/>
-    <mergeCell ref="AL76:AN76"/>
-    <mergeCell ref="AD76:AF76"/>
-    <mergeCell ref="Z81:AA81"/>
-    <mergeCell ref="AL62:AN62"/>
-    <mergeCell ref="AL63:AN63"/>
-    <mergeCell ref="AL71:AN71"/>
-    <mergeCell ref="AL70:AN70"/>
-    <mergeCell ref="AL69:AN69"/>
-    <mergeCell ref="N73:AB74"/>
-    <mergeCell ref="N75:O75"/>
-    <mergeCell ref="R75:S75"/>
-    <mergeCell ref="V75:W75"/>
-    <mergeCell ref="Z75:AA75"/>
-    <mergeCell ref="AD75:AE75"/>
-    <mergeCell ref="N64:P64"/>
-    <mergeCell ref="N70:P70"/>
-    <mergeCell ref="AH70:AJ70"/>
-    <mergeCell ref="AD70:AF70"/>
-    <mergeCell ref="Z69:AB69"/>
-    <mergeCell ref="Z70:AB70"/>
-    <mergeCell ref="V71:X71"/>
-    <mergeCell ref="AD63:AF63"/>
-    <mergeCell ref="AH64:AJ64"/>
-    <mergeCell ref="AH75:AI75"/>
-    <mergeCell ref="Z76:AB76"/>
-    <mergeCell ref="Z77:AB77"/>
-    <mergeCell ref="V76:X76"/>
-    <mergeCell ref="N78:P78"/>
-    <mergeCell ref="Z78:AB78"/>
-    <mergeCell ref="N79:P79"/>
-    <mergeCell ref="R79:T79"/>
-    <mergeCell ref="V79:X79"/>
-    <mergeCell ref="Z79:AB79"/>
-    <mergeCell ref="V78:X78"/>
-    <mergeCell ref="R78:T78"/>
-    <mergeCell ref="AL88:AN88"/>
-    <mergeCell ref="AL89:AN89"/>
-    <mergeCell ref="AL83:AN83"/>
-    <mergeCell ref="AL84:AN84"/>
-    <mergeCell ref="AD88:AF88"/>
-    <mergeCell ref="AD89:AF89"/>
-    <mergeCell ref="AH87:AI87"/>
-    <mergeCell ref="AL87:AM87"/>
-    <mergeCell ref="AH88:AJ88"/>
-    <mergeCell ref="AH89:AJ89"/>
-    <mergeCell ref="AD85:AF85"/>
-    <mergeCell ref="AH85:AJ85"/>
-    <mergeCell ref="AL85:AN85"/>
-    <mergeCell ref="AD82:AF82"/>
-    <mergeCell ref="AH83:AJ83"/>
-    <mergeCell ref="AD84:AF84"/>
-    <mergeCell ref="AH84:AJ84"/>
-    <mergeCell ref="AD83:AF83"/>
-    <mergeCell ref="Z84:AB84"/>
-    <mergeCell ref="Z82:AB82"/>
-    <mergeCell ref="AL77:AN77"/>
-    <mergeCell ref="AL78:AN78"/>
-    <mergeCell ref="AD77:AF77"/>
-    <mergeCell ref="AD79:AF79"/>
-    <mergeCell ref="AH79:AJ79"/>
-    <mergeCell ref="AL79:AN79"/>
-    <mergeCell ref="AD81:AE81"/>
-    <mergeCell ref="AH81:AI81"/>
-    <mergeCell ref="AL81:AM81"/>
-    <mergeCell ref="AL82:AN82"/>
-    <mergeCell ref="AL102:AN102"/>
-    <mergeCell ref="AL101:AN101"/>
-    <mergeCell ref="AL96:AN96"/>
-    <mergeCell ref="AD102:AF102"/>
-    <mergeCell ref="AH102:AJ102"/>
-    <mergeCell ref="AL90:AN90"/>
-    <mergeCell ref="AL95:AN95"/>
-    <mergeCell ref="AD101:AF101"/>
-    <mergeCell ref="AH101:AJ101"/>
-    <mergeCell ref="AH100:AJ100"/>
-    <mergeCell ref="AL94:AN94"/>
-    <mergeCell ref="AD100:AF100"/>
-    <mergeCell ref="AD96:AF96"/>
-    <mergeCell ref="AD94:AF94"/>
-    <mergeCell ref="AD95:AF95"/>
-    <mergeCell ref="AH96:AJ96"/>
-    <mergeCell ref="AD90:AF90"/>
-    <mergeCell ref="AH95:AJ95"/>
-    <mergeCell ref="AH94:AJ94"/>
-    <mergeCell ref="AL100:AN100"/>
-    <mergeCell ref="AD97:AF97"/>
-    <mergeCell ref="AH97:AJ97"/>
-    <mergeCell ref="AL97:AN97"/>
-    <mergeCell ref="AH90:AJ90"/>
-    <mergeCell ref="Z9:AB9"/>
-    <mergeCell ref="R10:T10"/>
-    <mergeCell ref="V10:X10"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="AD21:AE21"/>
-    <mergeCell ref="AD49:AF49"/>
-    <mergeCell ref="AD43:AF43"/>
-    <mergeCell ref="R48:T48"/>
-    <mergeCell ref="Z42:AB42"/>
-    <mergeCell ref="Z43:AB43"/>
-    <mergeCell ref="N36:AB37"/>
-    <mergeCell ref="Z48:AB48"/>
-    <mergeCell ref="Z45:AA45"/>
-    <mergeCell ref="Z46:AB46"/>
-    <mergeCell ref="AD38:AE38"/>
-    <mergeCell ref="AD39:AF39"/>
-    <mergeCell ref="AD40:AF40"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="V49:X49"/>
-    <mergeCell ref="V48:X48"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="Z20:AA20"/>
-    <mergeCell ref="J15:L15"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="V28:W28"/>
-    <mergeCell ref="Z28:AA28"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="Z27:AA27"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="V13:W13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="N18:AB19"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="R14:T14"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="V15:X15"/>
-    <mergeCell ref="V16:X16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="R9:T9"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="V8:X8"/>
-    <mergeCell ref="V9:X9"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="R1:T1"/>
-    <mergeCell ref="V1:X1"/>
-    <mergeCell ref="V14:X14"/>
-    <mergeCell ref="R15:T15"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="B4:L5"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="V2:X2"/>
-    <mergeCell ref="N4:AB5"/>
-    <mergeCell ref="AL1:AN1"/>
-    <mergeCell ref="Z2:AB2"/>
-    <mergeCell ref="AD2:AF2"/>
-    <mergeCell ref="AH2:AJ2"/>
-    <mergeCell ref="AL2:AN2"/>
-    <mergeCell ref="AH8:AJ8"/>
-    <mergeCell ref="AL6:AM6"/>
-    <mergeCell ref="AD1:AF1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="AL7:AM7"/>
-    <mergeCell ref="AD8:AF8"/>
-    <mergeCell ref="Z8:AB8"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AH7:AI7"/>
-    <mergeCell ref="AD7:AE7"/>
-    <mergeCell ref="Z7:AA7"/>
-    <mergeCell ref="AL8:AN8"/>
-    <mergeCell ref="AD4:AN5"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="AD6:AE6"/>
-    <mergeCell ref="Z88:AB88"/>
-    <mergeCell ref="J94:L94"/>
-    <mergeCell ref="J95:L95"/>
-    <mergeCell ref="V94:X94"/>
-    <mergeCell ref="V96:X96"/>
-    <mergeCell ref="V95:X95"/>
-    <mergeCell ref="Z96:AB96"/>
-    <mergeCell ref="R96:T96"/>
-    <mergeCell ref="B101:D101"/>
-    <mergeCell ref="N101:P101"/>
-    <mergeCell ref="N95:P95"/>
-    <mergeCell ref="V101:X101"/>
-    <mergeCell ref="Z101:AB101"/>
-    <mergeCell ref="Z94:AB94"/>
-    <mergeCell ref="Z95:AB95"/>
-    <mergeCell ref="V90:X90"/>
-    <mergeCell ref="V88:X88"/>
-    <mergeCell ref="R90:T90"/>
-    <mergeCell ref="Z89:AB89"/>
-    <mergeCell ref="Z90:AB90"/>
-    <mergeCell ref="N88:P88"/>
-    <mergeCell ref="N93:O93"/>
-    <mergeCell ref="J100:L100"/>
-    <mergeCell ref="B97:D97"/>
-    <mergeCell ref="AH21:AI21"/>
-    <mergeCell ref="AH31:AI31"/>
-    <mergeCell ref="AD31:AE31"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="Z21:AA21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="R22:T22"/>
-    <mergeCell ref="V22:X22"/>
-    <mergeCell ref="Z22:AB22"/>
-    <mergeCell ref="AD22:AF22"/>
-    <mergeCell ref="AH22:AJ22"/>
-    <mergeCell ref="AD29:AE29"/>
-    <mergeCell ref="AH29:AI29"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:T23"/>
-    <mergeCell ref="V23:X23"/>
-    <mergeCell ref="V27:W27"/>
-    <mergeCell ref="AD27:AE27"/>
-    <mergeCell ref="N30:O30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="N29:O29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="Z30:AA30"/>
-    <mergeCell ref="N25:AB26"/>
-    <mergeCell ref="AL9:AN9"/>
-    <mergeCell ref="AD9:AF9"/>
-    <mergeCell ref="AH16:AJ16"/>
-    <mergeCell ref="AL10:AN10"/>
-    <mergeCell ref="AL14:AN14"/>
-    <mergeCell ref="AL16:AN16"/>
-    <mergeCell ref="Z15:AB15"/>
-    <mergeCell ref="AD15:AF15"/>
-    <mergeCell ref="Z13:AA13"/>
-    <mergeCell ref="AL15:AN15"/>
-    <mergeCell ref="AL12:AM12"/>
-    <mergeCell ref="AD16:AF16"/>
-    <mergeCell ref="Z10:AB10"/>
-    <mergeCell ref="AH14:AJ14"/>
-    <mergeCell ref="Z14:AB14"/>
-    <mergeCell ref="AD14:AF14"/>
-    <mergeCell ref="AD13:AE13"/>
-    <mergeCell ref="AH10:AJ10"/>
-    <mergeCell ref="AH15:AJ15"/>
-    <mergeCell ref="AD10:AF10"/>
-    <mergeCell ref="AD12:AE12"/>
-    <mergeCell ref="AH12:AI12"/>
-    <mergeCell ref="AH9:AJ9"/>
-    <mergeCell ref="Z16:AB16"/>
-    <mergeCell ref="F101:H101"/>
-    <mergeCell ref="R94:T94"/>
-    <mergeCell ref="V64:X64"/>
-    <mergeCell ref="R64:T64"/>
-    <mergeCell ref="R61:T61"/>
-    <mergeCell ref="R60:T60"/>
-    <mergeCell ref="R87:S87"/>
-    <mergeCell ref="V87:W87"/>
-    <mergeCell ref="N91:P91"/>
-    <mergeCell ref="J96:L96"/>
-    <mergeCell ref="N83:P83"/>
-    <mergeCell ref="N84:P84"/>
-    <mergeCell ref="N90:P90"/>
-    <mergeCell ref="J89:L89"/>
-    <mergeCell ref="J83:L83"/>
-    <mergeCell ref="V89:X89"/>
-    <mergeCell ref="R89:T89"/>
-    <mergeCell ref="R84:T84"/>
-    <mergeCell ref="N85:P85"/>
-    <mergeCell ref="R85:T85"/>
-    <mergeCell ref="V85:X85"/>
-    <mergeCell ref="R88:T88"/>
-    <mergeCell ref="V84:X84"/>
-    <mergeCell ref="J84:L84"/>
-    <mergeCell ref="V102:X102"/>
-    <mergeCell ref="R68:T68"/>
-    <mergeCell ref="V68:X68"/>
-    <mergeCell ref="N66:O66"/>
-    <mergeCell ref="N67:P67"/>
-    <mergeCell ref="N60:P60"/>
-    <mergeCell ref="J69:L69"/>
-    <mergeCell ref="N62:P62"/>
-    <mergeCell ref="R62:T62"/>
-    <mergeCell ref="N89:P89"/>
-    <mergeCell ref="N87:O87"/>
-    <mergeCell ref="J88:L88"/>
-    <mergeCell ref="J85:L85"/>
-    <mergeCell ref="J101:L101"/>
-    <mergeCell ref="R102:T102"/>
-    <mergeCell ref="R100:T100"/>
-    <mergeCell ref="V100:X100"/>
-    <mergeCell ref="R101:T101"/>
-    <mergeCell ref="N100:P100"/>
-    <mergeCell ref="N81:O81"/>
-    <mergeCell ref="R81:S81"/>
-    <mergeCell ref="V81:W81"/>
-    <mergeCell ref="V82:X82"/>
-    <mergeCell ref="N82:P82"/>
-    <mergeCell ref="Z12:AA12"/>
-    <mergeCell ref="B133:D133"/>
-    <mergeCell ref="F133:H133"/>
-    <mergeCell ref="J133:L133"/>
-    <mergeCell ref="B127:D127"/>
-    <mergeCell ref="F127:H127"/>
-    <mergeCell ref="J127:L127"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="F129:G129"/>
-    <mergeCell ref="J129:K129"/>
-    <mergeCell ref="B130:D130"/>
-    <mergeCell ref="F130:H130"/>
-    <mergeCell ref="J130:L130"/>
-    <mergeCell ref="B132:D132"/>
-    <mergeCell ref="F132:H132"/>
-    <mergeCell ref="J132:L132"/>
-    <mergeCell ref="B131:D131"/>
-    <mergeCell ref="F131:H131"/>
-    <mergeCell ref="J131:L131"/>
-    <mergeCell ref="B126:D126"/>
-    <mergeCell ref="F126:H126"/>
-    <mergeCell ref="J126:L126"/>
-    <mergeCell ref="F117:G117"/>
-    <mergeCell ref="J117:K117"/>
-    <mergeCell ref="B112:D112"/>
-    <mergeCell ref="B125:D125"/>
-    <mergeCell ref="F125:H125"/>
-    <mergeCell ref="J121:L121"/>
-    <mergeCell ref="J125:L125"/>
-    <mergeCell ref="B118:D118"/>
-    <mergeCell ref="F118:H118"/>
-    <mergeCell ref="B115:D115"/>
-    <mergeCell ref="F115:H115"/>
-    <mergeCell ref="J115:L115"/>
-    <mergeCell ref="F120:H120"/>
-    <mergeCell ref="J120:L120"/>
-    <mergeCell ref="J118:L118"/>
-    <mergeCell ref="B124:D124"/>
-    <mergeCell ref="F124:H124"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="J124:L124"/>
-    <mergeCell ref="F119:H119"/>
-    <mergeCell ref="J119:L119"/>
-    <mergeCell ref="B120:D120"/>
-    <mergeCell ref="B121:D121"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="F123:G123"/>
-    <mergeCell ref="B119:D119"/>
-    <mergeCell ref="B113:D113"/>
-    <mergeCell ref="F113:H113"/>
-    <mergeCell ref="J113:L113"/>
-    <mergeCell ref="B114:D114"/>
-    <mergeCell ref="F114:H114"/>
-    <mergeCell ref="J114:L114"/>
-    <mergeCell ref="F121:H121"/>
-    <mergeCell ref="J123:K123"/>
-    <mergeCell ref="F107:H107"/>
-    <mergeCell ref="J102:L102"/>
-    <mergeCell ref="J112:L112"/>
-    <mergeCell ref="J111:K111"/>
-    <mergeCell ref="B106:D106"/>
-    <mergeCell ref="B107:D107"/>
-    <mergeCell ref="F106:H106"/>
-    <mergeCell ref="F105:G105"/>
-    <mergeCell ref="N102:P102"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="F102:H102"/>
-    <mergeCell ref="J107:L107"/>
-    <mergeCell ref="J108:L108"/>
-    <mergeCell ref="B109:D109"/>
-    <mergeCell ref="F109:H109"/>
-    <mergeCell ref="B108:D108"/>
-    <mergeCell ref="J105:K105"/>
-    <mergeCell ref="F108:H108"/>
-    <mergeCell ref="J106:L106"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="F111:G111"/>
-    <mergeCell ref="J109:L109"/>
-    <mergeCell ref="F112:H112"/>
-    <mergeCell ref="Z100:AB100"/>
-    <mergeCell ref="N94:P94"/>
-    <mergeCell ref="R95:T95"/>
-    <mergeCell ref="N96:P96"/>
-    <mergeCell ref="R99:S99"/>
-    <mergeCell ref="V99:W99"/>
-    <mergeCell ref="Z99:AA99"/>
-    <mergeCell ref="N97:P97"/>
-    <mergeCell ref="N99:O99"/>
-    <mergeCell ref="Z102:AB102"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="F70:H70"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="F76:H76"/>
-    <mergeCell ref="F90:H90"/>
-    <mergeCell ref="F89:H89"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B79:D79"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="F82:H82"/>
-    <mergeCell ref="F83:H83"/>
-    <mergeCell ref="F84:H84"/>
-    <mergeCell ref="F77:H77"/>
-    <mergeCell ref="B85:D85"/>
-    <mergeCell ref="F79:H79"/>
-    <mergeCell ref="F71:H71"/>
-    <mergeCell ref="F85:H85"/>
-    <mergeCell ref="B100:D100"/>
-    <mergeCell ref="F100:H100"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="F88:H88"/>
-    <mergeCell ref="B89:D89"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="J75:K75"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="J82:L82"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B95:D95"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="J70:L70"/>
-    <mergeCell ref="B71:D71"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="AL50:AN50"/>
-    <mergeCell ref="AL52:AM52"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="F62:H62"/>
-    <mergeCell ref="F61:H61"/>
-    <mergeCell ref="J64:L64"/>
-    <mergeCell ref="F69:H69"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="J63:L63"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="J66:K66"/>
-    <mergeCell ref="B67:D67"/>
-    <mergeCell ref="F67:H67"/>
-    <mergeCell ref="J67:L67"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="F68:H68"/>
-    <mergeCell ref="J68:L68"/>
-    <mergeCell ref="F63:H63"/>
-    <mergeCell ref="Z55:AB55"/>
-    <mergeCell ref="N63:P63"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="F54:H54"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="R71:T71"/>
-    <mergeCell ref="N71:P71"/>
-    <mergeCell ref="R76:T76"/>
-    <mergeCell ref="N69:P69"/>
-    <mergeCell ref="R63:T63"/>
-    <mergeCell ref="N68:P68"/>
-    <mergeCell ref="F75:G75"/>
-    <mergeCell ref="J81:K81"/>
-    <mergeCell ref="J77:L77"/>
-    <mergeCell ref="J76:L76"/>
-    <mergeCell ref="J55:L55"/>
-    <mergeCell ref="J50:L50"/>
-    <mergeCell ref="V50:X50"/>
-    <mergeCell ref="R49:T49"/>
-    <mergeCell ref="J49:L49"/>
-    <mergeCell ref="J47:L47"/>
-    <mergeCell ref="J79:L79"/>
-    <mergeCell ref="J71:L71"/>
-    <mergeCell ref="R50:T50"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="J60:L60"/>
-    <mergeCell ref="J78:L78"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="J53:L53"/>
-    <mergeCell ref="F53:H53"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="N38:O38"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R41:T41"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R42:T42"/>
-    <mergeCell ref="V52:W52"/>
-    <mergeCell ref="V41:X41"/>
-    <mergeCell ref="V40:X40"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="F48:H48"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="D29:D34 AJ29:AJ34 T29:T34 P29:P34 X29:X34 AF29:AF34 AN29:AN34 H29:H34 L29:L34 AB29:AB34">
       <formula1>$AP$68:$AP$71</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="V62:X64 AH41:AJ44 AH14:AJ16 B89:D90 AH69:AJ71 V29:W34 B101:D102 J132:L133 AD41:AF44 AH90:AJ91 R96:T97 V96:X97 R69:T71 R78:T79 Z90:AB91 Z8:AB10 J101:L102 AD49:AF50 V8:X10 N41:P45 AD69:AF71 J114:L115 AL78:AN79 AL69:AN71 AH8:AJ10 R8:T10 F89:H90 B108:D109 B95:D96 Z14:AB16 Z55:AB57 R14:T16 F101:H102 AL14:AN16 J95:L96 F95:H96 R29:S34 N96:P97 F55:H57 J120:L121 F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 B126:D127 AD14:AF16 B114:D115 J126:L127 V48:X50 R101:T102 AD22:AF23 R84:T85 Z101:AB102 R22:T23 V14:X16 V22:X23 F108:H109 Z22:AB23 AL101:AN102 AL22:AN23 V69:X71 Z78:AB79 AD55:AF57 N22:P23 Z29:AA34 B41:D43 J89:L90 V55:X57 AH96:AJ97 AD78:AF79 Z96:AB97 N29:O34 AD101:AF102 N14:P16 AD62:AF64 R90:T91 AL90:AN91 Z41:AB43 AH62:AJ64 N101:P102 AH84:AJ85 V41:X43 AH78:AJ79 AL84:AN85 AH55:AJ57 AH49:AJ50 B29:C34 J29:K34 AL96:AN97 AH101:AJ102 AD90:AF91 N90:P91 Z84:AB85 N50:P51 AD96:AF97 AH22:AJ23 N62:P64 N8:P10 N78:P79 Z69:AB71 AD8:AF10 V101:X102 AL41:AN43 N84:P85 R41:T45 V84:X85 Z62:AB64 R62:T64 V90:X91 AL55:AN57 N56:P57 AL62:AN64 F69:H71 J55:L57 N69:P71 AL29:AM34 AL48:AN50 V78:X79 AH29:AI34 J41:L43 F14:H16 F22:H23 B78:D79 B69:D71 J78:L79 J69:L71 F41:H43 R56:T57 J14:L16 B14:D16 B22:D23 F84:H85 J22:L23 B55:D57 B84:D85 B62:D64 F8:H10 F48:H50 J8:L10 F62:H64 F78:H79 B8:D10 F29:G34 AL8:AN10 J62:L64 J84:L85 B48:D50 AD29:AE34 Z48:AB50 R50:T51 J48:L50 AD84:AF85">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="V62:X64 AH41:AJ44 AH14:AJ16 B89:D90 AH69:AJ71 V29:W34 B101:D102 J132:L133 AD84:AF85 AH90:AJ91 R96:T97 V96:X97 R69:T71 R78:T79 Z90:AB91 Z8:AB10 J101:L102 AD49:AF50 V8:X10 N41:P45 AD69:AF71 J114:L115 AL78:AN79 AL69:AN71 AH8:AJ10 R8:T10 F89:H90 B108:D109 B95:D96 Z14:AB16 Z55:AB57 R14:T16 F101:H102 AL14:AN16 J95:L96 F95:H96 R29:S34 N96:P97 F55:H57 J120:L121 F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 B126:D127 AD14:AF16 B114:D115 J126:L127 V48:X50 R101:T102 AD22:AF23 R84:T85 Z101:AB102 R22:T23 V14:X16 V22:X23 F108:H109 Z22:AB23 AL101:AN102 AL22:AN23 V69:X71 Z78:AB79 AD55:AF57 N22:P23 Z29:AA34 B41:D43 J89:L90 V55:X57 AH96:AJ97 AD78:AF79 Z96:AB97 N29:O34 AD101:AF102 N14:P16 AD62:AF64 R90:T91 AL90:AN91 Z41:AB43 AH62:AJ64 N101:P102 AH84:AJ85 V41:X43 AH78:AJ79 AL84:AN85 AH55:AJ57 AH49:AJ50 B29:C34 J29:K34 AL96:AN97 AH101:AJ102 AD41:AF44 N90:P91 Z84:AB85 N50:P51 AD96:AF97 AH22:AJ23 N62:P64 N8:P10 N78:P79 Z69:AB71 AD8:AF10 V101:X102 AL41:AN43 N84:P85 R41:T45 V84:X85 Z62:AB64 R62:T64 V90:X91 AL55:AN57 N56:P57 AL62:AN64 F69:H71 J55:L57 N69:P71 AL29:AM34 AL48:AN50 V78:X79 AH29:AI34 J41:L43 F14:H16 F22:H23 B78:D79 B69:D71 J78:L79 J69:L71 F41:H43 R56:T57 J14:L16 B14:D16 B22:D23 F84:H85 J22:L23 B55:D57 B84:D85 B62:D64 F8:H10 F48:H50 J8:L10 F62:H64 F78:H79 B8:D10 F29:G34 AL8:AN10 J62:L64 J84:L85 B48:D50 AD29:AE34 Z48:AB50 R50:T51 J48:L50 AD90:AF91">
       <formula1>$AP$6:$AP$30</formula1>
     </dataValidation>
   </dataValidations>

--- a/Gorev-Listesi.xlsx
+++ b/Gorev-Listesi.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="100">
   <si>
     <t>CUMA</t>
   </si>
@@ -152,254 +152,178 @@
     <t>GÜNDEM ÖTESİ</t>
   </si>
   <si>
+    <t>20.00</t>
+  </si>
+  <si>
+    <t>EVDE KONUŞURUZ</t>
+  </si>
+  <si>
+    <t>HABERİN OLSUN</t>
+  </si>
+  <si>
+    <t>17.30</t>
+  </si>
+  <si>
+    <t>RÜZGAR GÜLÜ</t>
+  </si>
+  <si>
+    <t>23.30</t>
+  </si>
+  <si>
+    <t>TRT2 SANAL STÜDYO - AYAZAĞA</t>
+  </si>
+  <si>
+    <t>AKTÜEL</t>
+  </si>
+  <si>
+    <t>Bursa</t>
+  </si>
+  <si>
+    <t>15.00</t>
+  </si>
+  <si>
+    <t>16.00</t>
+  </si>
+  <si>
+    <t>13.00</t>
+  </si>
+  <si>
+    <t>İSTANBUL STÜDYOSU</t>
+  </si>
+  <si>
+    <t>GENÇLİĞİN RİTMİ</t>
+  </si>
+  <si>
+    <t>Canavar Stüdyoları</t>
+  </si>
+  <si>
+    <t>BAŞKA BİR SAHNE</t>
+  </si>
+  <si>
+    <t>14.30</t>
+  </si>
+  <si>
+    <t>TATLI NOTALAR</t>
+  </si>
+  <si>
+    <t>Sinan Erdem</t>
+  </si>
+  <si>
+    <t>BASKETBOL</t>
+  </si>
+  <si>
+    <t>VOLEYBOL</t>
+  </si>
+  <si>
+    <t>Burhan Felek</t>
+  </si>
+  <si>
+    <t>19.30</t>
+  </si>
+  <si>
+    <t>Sıcak Prova</t>
+  </si>
+  <si>
+    <t>10.00</t>
+  </si>
+  <si>
+    <t>14.00</t>
+  </si>
+  <si>
+    <t>VOLEYBOL (EUROCUP)</t>
+  </si>
+  <si>
+    <t>METİN ŞENTÜRK İLE</t>
+  </si>
+  <si>
+    <t>19.00</t>
+  </si>
+  <si>
+    <t>Vakıfbank</t>
+  </si>
+  <si>
+    <t>Erzurum</t>
+  </si>
+  <si>
+    <t>YENİ KAMYON</t>
+  </si>
+  <si>
+    <t>ESKİ TIR</t>
+  </si>
+  <si>
+    <t>EDEBİYATIMIZI ÇİZMEK</t>
+  </si>
+  <si>
+    <t>Kocaeli</t>
+  </si>
+  <si>
+    <t>05.10.2026 Pazartesi</t>
+  </si>
+  <si>
+    <t>HENTBOL</t>
+  </si>
+  <si>
+    <t>EĞİTİM</t>
+  </si>
+  <si>
+    <t>Ayazağa Yemekhane</t>
+  </si>
+  <si>
+    <t>23.50</t>
+  </si>
+  <si>
+    <t>S.ARAS.</t>
+  </si>
+  <si>
+    <t>ENSTRÜMAN KAYDI</t>
+  </si>
+  <si>
+    <t>H.HEKİMHAN.</t>
+  </si>
+  <si>
+    <t>İPTAL</t>
+  </si>
+  <si>
+    <t>D.A.SALTIK.</t>
+  </si>
+  <si>
+    <t>D.YÖNDEM.</t>
+  </si>
+  <si>
+    <t>S.CÜREBAL.</t>
+  </si>
+  <si>
+    <t>KOLİVA İLE</t>
+  </si>
+  <si>
+    <t>TEST</t>
+  </si>
+  <si>
+    <t>YAĞLI GÜREŞ</t>
+  </si>
+  <si>
+    <t>12.30</t>
+  </si>
+  <si>
+    <t>Atatürk Havalimanı Millet Bahçesi</t>
+  </si>
+  <si>
     <t>KURULUM</t>
   </si>
   <si>
-    <t>20.00</t>
-  </si>
-  <si>
-    <t>EVDE KONUŞURUZ</t>
-  </si>
-  <si>
-    <t>HABERİN OLSUN</t>
-  </si>
-  <si>
-    <t>17.30</t>
-  </si>
-  <si>
-    <t>RÜZGAR GÜLÜ</t>
-  </si>
-  <si>
-    <t>23.30</t>
-  </si>
-  <si>
-    <t>TRT2 SANAL STÜDYO - AYAZAĞA</t>
-  </si>
-  <si>
-    <t>AKTÜEL</t>
-  </si>
-  <si>
-    <t>Bursa</t>
-  </si>
-  <si>
-    <t>15.00</t>
-  </si>
-  <si>
-    <t>Rize, Erzurum</t>
-  </si>
-  <si>
-    <t>16.00</t>
-  </si>
-  <si>
-    <t>13.00</t>
-  </si>
-  <si>
-    <t>NOTASIZ SEYYAH</t>
-  </si>
-  <si>
-    <t>İSTANBUL STÜDYOSU</t>
-  </si>
-  <si>
-    <t>GENÇLİĞİN RİTMİ</t>
-  </si>
-  <si>
-    <t>Canavar Stüdyoları</t>
-  </si>
-  <si>
-    <t>BAŞKA BİR SAHNE</t>
-  </si>
-  <si>
-    <t>Antalya</t>
-  </si>
-  <si>
-    <t>HİLALİN GÖLGESİNDE</t>
-  </si>
-  <si>
-    <t>Boğaziçi Eğitim Salonu</t>
-  </si>
-  <si>
-    <t>KOLİVA İLE</t>
-  </si>
-  <si>
-    <t>14.30</t>
+    <t>F.BOZKURT.</t>
+  </si>
+  <si>
+    <t>M.DİNER.</t>
+  </si>
+  <si>
+    <t>E.SAVAŞ.</t>
+  </si>
+  <si>
+    <t>BİR MEKANDAN FAZLASI</t>
   </si>
   <si>
     <t>Isparta</t>
-  </si>
-  <si>
-    <t>TATLI NOTALAR</t>
-  </si>
-  <si>
-    <t>Sinan Erdem</t>
-  </si>
-  <si>
-    <t>BASKETBOL</t>
-  </si>
-  <si>
-    <t>HENTBOL</t>
-  </si>
-  <si>
-    <t>YAĞLI GÜREŞ</t>
-  </si>
-  <si>
-    <t>VOLEYBOL</t>
-  </si>
-  <si>
-    <t>Beykoz</t>
-  </si>
-  <si>
-    <t>Atatürk Havalimanı Millet Bahçesi</t>
-  </si>
-  <si>
-    <t>Burhan Felek</t>
-  </si>
-  <si>
-    <t>12.30</t>
-  </si>
-  <si>
-    <t>19.30</t>
-  </si>
-  <si>
-    <t>28.09.2026 YOL</t>
-  </si>
-  <si>
-    <t>S.CÜREBAL.</t>
-  </si>
-  <si>
-    <t>S.ARAS.</t>
-  </si>
-  <si>
-    <t>E.KOL.</t>
-  </si>
-  <si>
-    <t>K.GÜNGÖR. / A.KORUN.</t>
-  </si>
-  <si>
-    <t>17.00</t>
-  </si>
-  <si>
-    <t>Sıcak Prova</t>
-  </si>
-  <si>
-    <t>10.00</t>
-  </si>
-  <si>
-    <t>İPTAL</t>
-  </si>
-  <si>
-    <t>A.KOÇ.</t>
-  </si>
-  <si>
-    <t>M.DİNER.</t>
-  </si>
-  <si>
-    <t>13.30</t>
-  </si>
-  <si>
-    <t>BURSA ŞEHRENGİZİ</t>
-  </si>
-  <si>
-    <t>FUTBOL</t>
-  </si>
-  <si>
-    <t>PAZAR KONSERİ</t>
-  </si>
-  <si>
-    <t>11.30</t>
-  </si>
-  <si>
-    <t>Sarıyer</t>
-  </si>
-  <si>
-    <t>AKM</t>
-  </si>
-  <si>
-    <t>F.BOZKURT.</t>
-  </si>
-  <si>
-    <t>Bandırma</t>
-  </si>
-  <si>
-    <t>Esenler</t>
-  </si>
-  <si>
-    <t>Pendik</t>
-  </si>
-  <si>
-    <t>A.C.PEHLİVAN.</t>
-  </si>
-  <si>
-    <t>HABER HİZMETİ</t>
-  </si>
-  <si>
-    <t>14.00</t>
-  </si>
-  <si>
-    <t>Sultanahmet</t>
-  </si>
-  <si>
-    <t>Haliç Kongre Merkezi</t>
-  </si>
-  <si>
-    <t>İstanbul Havalimanı</t>
-  </si>
-  <si>
-    <t>Sancaktepe</t>
-  </si>
-  <si>
-    <t>NY TEST</t>
-  </si>
-  <si>
-    <t>Çekmeköy</t>
-  </si>
-  <si>
-    <t>T.ERDEN.</t>
-  </si>
-  <si>
-    <t>CİTİZEN TALKS</t>
-  </si>
-  <si>
-    <t>09.30</t>
-  </si>
-  <si>
-    <t>D.A.SALTIK.</t>
-  </si>
-  <si>
-    <t>Atatürk Havalimanı</t>
-  </si>
-  <si>
-    <t>VOLEYBOL (EUROCUP)</t>
-  </si>
-  <si>
-    <t>E.SAVAŞ.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Ulus   </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t>İPTAL</t>
-    </r>
-  </si>
-  <si>
-    <t>BİR ROMAN KAHRAMANI GİBİ</t>
-  </si>
-  <si>
-    <t>BİR MEKANDAN FAZLASI</t>
-  </si>
-  <si>
-    <t>TEST</t>
-  </si>
-  <si>
-    <t>D.YÖNDEM.</t>
   </si>
 </sst>
 </file>
@@ -1444,7 +1368,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="162">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1603,6 +1527,72 @@
     <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="11" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="12" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="9" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="14" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1618,79 +1608,109 @@
     <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="14" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="15" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="9" xfId="57" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="9" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="11" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="11" xfId="57" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="12" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="12" xfId="57" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="14" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="12" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="13" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="13" xfId="57" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="9" borderId="17" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1702,6 +1722,57 @@
     <xf numFmtId="49" fontId="7" fillId="9" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="37" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="38" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="18" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="16" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="11" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1711,196 +1782,10 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="13" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="37" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="9" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="14" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="15" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="18" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="11" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="12" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="13" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="8" borderId="8" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="8" borderId="9" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="8" borderId="10" xfId="31" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="37" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="38" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="16" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="18" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="11" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="12" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="13" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="38" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2275,7 +2160,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="1" width="145" row="2" locked="1">
+  <wetp:taskpane dockstate="right" visibility="1" width="269" row="1" locked="1">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -2288,7 +2173,7 @@
     <we:reference id="wa104379804" version="1.0.0.0" store="wa104379804" storeType="OMEX"/>
   </we:alternateReferences>
   <we:properties>
-    <we:property name="listState" value="&quot;{\&quot;listName\&quot;:\&quot;Talepler\&quot;,\&quot;listItems\&quot;:[{\&quot;isChecked\&quot;:false,\&quot;text\&quot;:\&quot;Ahmet: 26-27.09.2026 izin.\&quot;,\&quot;key\&quot;:623},{\&quot;isChecked\&quot;:false,\&quot;text\&quot;:\&quot;Eren: 26.09.2026 izin.\&quot;,\&quot;key\&quot;:624}],\&quot;counter\&quot;:624}&quot;"/>
+    <we:property name="listState" value="&quot;{\&quot;listName\&quot;:\&quot;Talepler\&quot;,\&quot;listItems\&quot;:[{\&quot;isChecked\&quot;:false,\&quot;text\&quot;:\&quot;Cengiz: 28.09.2026 izin.\&quot;,\&quot;key\&quot;:625},{\&quot;isChecked\&quot;:false,\&quot;text\&quot;:\&quot;Cengiz: 04.10.2026 izin.\&quot;,\&quot;key\&quot;:626},{\&quot;isChecked\&quot;:false,\&quot;text\&quot;:\&quot;Esvet: 28.09.2026 izin.\&quot;,\&quot;key\&quot;:627},{\&quot;isChecked\&quot;:false,\&quot;text\&quot;:\&quot;Özgür: 29.09.2026 izin.\&quot;,\&quot;key\&quot;:628},{\&quot;isChecked\&quot;:false,\&quot;text\&quot;:\&quot;Özgür: 03.10.2026 izin.\&quot;,\&quot;key\&quot;:629}],\&quot;counter\&quot;:629}&quot;"/>
   </we:properties>
   <we:bindings/>
   <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
@@ -2352,65 +2237,65 @@
   <sheetData>
     <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12"/>
-      <c r="B1" s="121" t="s">
+      <c r="B1" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
       <c r="E1" s="10"/>
-      <c r="F1" s="122" t="s">
+      <c r="F1" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
       <c r="I1" s="10"/>
-      <c r="J1" s="122" t="s">
+      <c r="J1" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="122"/>
-      <c r="L1" s="123"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="110"/>
       <c r="M1" s="12"/>
-      <c r="N1" s="126" t="s">
+      <c r="N1" s="113" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="116" t="s">
+      <c r="R1" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
+      <c r="S1" s="103"/>
+      <c r="T1" s="103"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="116" t="s">
+      <c r="V1" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="W1" s="116"/>
-      <c r="X1" s="116"/>
+      <c r="W1" s="103"/>
+      <c r="X1" s="103"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="116" t="s">
+      <c r="Z1" s="103" t="s">
         <v>6</v>
       </c>
-      <c r="AA1" s="116"/>
-      <c r="AB1" s="116"/>
+      <c r="AA1" s="103"/>
+      <c r="AB1" s="103"/>
       <c r="AC1" s="1"/>
-      <c r="AD1" s="116" t="s">
+      <c r="AD1" s="103" t="s">
         <v>0</v>
       </c>
-      <c r="AE1" s="116"/>
-      <c r="AF1" s="116"/>
+      <c r="AE1" s="103"/>
+      <c r="AF1" s="103"/>
       <c r="AG1" s="1"/>
-      <c r="AH1" s="116" t="s">
+      <c r="AH1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="AI1" s="116"/>
-      <c r="AJ1" s="116"/>
+      <c r="AI1" s="103"/>
+      <c r="AJ1" s="103"/>
       <c r="AK1" s="1"/>
-      <c r="AL1" s="116" t="s">
+      <c r="AL1" s="103" t="s">
         <v>2</v>
       </c>
-      <c r="AM1" s="116"/>
-      <c r="AN1" s="117"/>
+      <c r="AM1" s="103"/>
+      <c r="AN1" s="104"/>
       <c r="AO1" s="12"/>
       <c r="AP1" s="12"/>
       <c r="AQ1" s="12"/>
@@ -2418,74 +2303,74 @@
     </row>
     <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12"/>
-      <c r="B2" s="124">
+      <c r="B2" s="111">
         <f>N2-3</f>
-        <v>46283</v>
-      </c>
-      <c r="C2" s="125"/>
-      <c r="D2" s="125"/>
+        <v>46290</v>
+      </c>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
       <c r="E2" s="11"/>
-      <c r="F2" s="125">
+      <c r="F2" s="112">
         <f>N2-2</f>
-        <v>46284</v>
-      </c>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
+        <v>46291</v>
+      </c>
+      <c r="G2" s="112"/>
+      <c r="H2" s="112"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="125">
+      <c r="J2" s="112">
         <f>N2-1</f>
-        <v>46285</v>
-      </c>
-      <c r="K2" s="125"/>
-      <c r="L2" s="130"/>
+        <v>46292</v>
+      </c>
+      <c r="K2" s="112"/>
+      <c r="L2" s="120"/>
       <c r="M2" s="12"/>
-      <c r="N2" s="129">
-        <v>46286</v>
-      </c>
-      <c r="O2" s="118"/>
-      <c r="P2" s="118"/>
+      <c r="N2" s="116">
+        <v>46293</v>
+      </c>
+      <c r="O2" s="105"/>
+      <c r="P2" s="105"/>
       <c r="Q2" s="53"/>
-      <c r="R2" s="118">
+      <c r="R2" s="105">
         <f>N2+1</f>
-        <v>46287</v>
-      </c>
-      <c r="S2" s="118"/>
-      <c r="T2" s="118"/>
+        <v>46294</v>
+      </c>
+      <c r="S2" s="105"/>
+      <c r="T2" s="105"/>
       <c r="U2" s="53"/>
-      <c r="V2" s="118">
+      <c r="V2" s="105">
         <f>N2+2</f>
-        <v>46288</v>
-      </c>
-      <c r="W2" s="118"/>
-      <c r="X2" s="118"/>
+        <v>46295</v>
+      </c>
+      <c r="W2" s="105"/>
+      <c r="X2" s="105"/>
       <c r="Y2" s="53"/>
-      <c r="Z2" s="118">
+      <c r="Z2" s="105">
         <f>N2+3</f>
-        <v>46289</v>
-      </c>
-      <c r="AA2" s="118"/>
-      <c r="AB2" s="118"/>
+        <v>46296</v>
+      </c>
+      <c r="AA2" s="105"/>
+      <c r="AB2" s="105"/>
       <c r="AC2" s="53"/>
-      <c r="AD2" s="118">
+      <c r="AD2" s="105">
         <f>N2+4</f>
-        <v>46290</v>
-      </c>
-      <c r="AE2" s="118"/>
-      <c r="AF2" s="118"/>
+        <v>46297</v>
+      </c>
+      <c r="AE2" s="105"/>
+      <c r="AF2" s="105"/>
       <c r="AG2" s="53"/>
-      <c r="AH2" s="118">
+      <c r="AH2" s="105">
         <f>N2+5</f>
-        <v>46291</v>
-      </c>
-      <c r="AI2" s="118"/>
-      <c r="AJ2" s="118"/>
+        <v>46298</v>
+      </c>
+      <c r="AI2" s="105"/>
+      <c r="AJ2" s="105"/>
       <c r="AK2" s="53"/>
-      <c r="AL2" s="118">
+      <c r="AL2" s="105">
         <f>N2+6</f>
-        <v>46292</v>
-      </c>
-      <c r="AM2" s="118"/>
-      <c r="AN2" s="119"/>
+        <v>46299</v>
+      </c>
+      <c r="AM2" s="105"/>
+      <c r="AN2" s="106"/>
       <c r="AO2" s="12"/>
       <c r="AP2" s="12"/>
       <c r="AQ2" s="12"/>
@@ -2539,47 +2424,47 @@
     </row>
     <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="12"/>
-      <c r="B4" s="120"/>
-      <c r="C4" s="120"/>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="120"/>
-      <c r="L4" s="120"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="107"/>
+      <c r="K4" s="107"/>
+      <c r="L4" s="107"/>
       <c r="M4" s="14"/>
-      <c r="N4" s="115" t="s">
+      <c r="N4" s="102" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="115"/>
-      <c r="P4" s="115"/>
-      <c r="Q4" s="115"/>
-      <c r="R4" s="115"/>
-      <c r="S4" s="115"/>
-      <c r="T4" s="115"/>
-      <c r="U4" s="115"/>
-      <c r="V4" s="115"/>
-      <c r="W4" s="115"/>
-      <c r="X4" s="115"/>
-      <c r="Y4" s="115"/>
-      <c r="Z4" s="115"/>
-      <c r="AA4" s="115"/>
-      <c r="AB4" s="115"/>
+      <c r="O4" s="102"/>
+      <c r="P4" s="102"/>
+      <c r="Q4" s="102"/>
+      <c r="R4" s="102"/>
+      <c r="S4" s="102"/>
+      <c r="T4" s="102"/>
+      <c r="U4" s="102"/>
+      <c r="V4" s="102"/>
+      <c r="W4" s="102"/>
+      <c r="X4" s="102"/>
+      <c r="Y4" s="102"/>
+      <c r="Z4" s="102"/>
+      <c r="AA4" s="102"/>
+      <c r="AB4" s="102"/>
       <c r="AC4" s="33"/>
-      <c r="AD4" s="120"/>
-      <c r="AE4" s="120"/>
-      <c r="AF4" s="120"/>
-      <c r="AG4" s="120"/>
-      <c r="AH4" s="120"/>
-      <c r="AI4" s="120"/>
-      <c r="AJ4" s="120"/>
-      <c r="AK4" s="120"/>
-      <c r="AL4" s="120"/>
-      <c r="AM4" s="120"/>
-      <c r="AN4" s="120"/>
+      <c r="AD4" s="107"/>
+      <c r="AE4" s="107"/>
+      <c r="AF4" s="107"/>
+      <c r="AG4" s="107"/>
+      <c r="AH4" s="107"/>
+      <c r="AI4" s="107"/>
+      <c r="AJ4" s="107"/>
+      <c r="AK4" s="107"/>
+      <c r="AL4" s="107"/>
+      <c r="AM4" s="107"/>
+      <c r="AN4" s="107"/>
       <c r="AO4" s="12"/>
       <c r="AP4" s="12"/>
       <c r="AQ4" s="12"/>
@@ -2587,289 +2472,283 @@
     </row>
     <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="12"/>
-      <c r="B5" s="120"/>
-      <c r="C5" s="120"/>
-      <c r="D5" s="120"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="120"/>
-      <c r="G5" s="120"/>
-      <c r="H5" s="120"/>
-      <c r="I5" s="120"/>
-      <c r="J5" s="120"/>
-      <c r="K5" s="120"/>
-      <c r="L5" s="120"/>
+      <c r="B5" s="107"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="107"/>
+      <c r="G5" s="107"/>
+      <c r="H5" s="107"/>
+      <c r="I5" s="107"/>
+      <c r="J5" s="107"/>
+      <c r="K5" s="107"/>
+      <c r="L5" s="107"/>
       <c r="M5" s="14"/>
-      <c r="N5" s="115"/>
-      <c r="O5" s="115"/>
-      <c r="P5" s="115"/>
-      <c r="Q5" s="115"/>
-      <c r="R5" s="115"/>
-      <c r="S5" s="115"/>
-      <c r="T5" s="115"/>
-      <c r="U5" s="115"/>
-      <c r="V5" s="115"/>
-      <c r="W5" s="115"/>
-      <c r="X5" s="115"/>
-      <c r="Y5" s="115"/>
-      <c r="Z5" s="115"/>
-      <c r="AA5" s="115"/>
-      <c r="AB5" s="115"/>
+      <c r="N5" s="102"/>
+      <c r="O5" s="102"/>
+      <c r="P5" s="102"/>
+      <c r="Q5" s="102"/>
+      <c r="R5" s="102"/>
+      <c r="S5" s="102"/>
+      <c r="T5" s="102"/>
+      <c r="U5" s="102"/>
+      <c r="V5" s="102"/>
+      <c r="W5" s="102"/>
+      <c r="X5" s="102"/>
+      <c r="Y5" s="102"/>
+      <c r="Z5" s="102"/>
+      <c r="AA5" s="102"/>
+      <c r="AB5" s="102"/>
       <c r="AC5" s="33"/>
-      <c r="AD5" s="120"/>
-      <c r="AE5" s="120"/>
-      <c r="AF5" s="120"/>
-      <c r="AG5" s="120"/>
-      <c r="AH5" s="120"/>
-      <c r="AI5" s="120"/>
-      <c r="AJ5" s="120"/>
-      <c r="AK5" s="120"/>
-      <c r="AL5" s="120"/>
-      <c r="AM5" s="120"/>
-      <c r="AN5" s="120"/>
+      <c r="AD5" s="107"/>
+      <c r="AE5" s="107"/>
+      <c r="AF5" s="107"/>
+      <c r="AG5" s="107"/>
+      <c r="AH5" s="107"/>
+      <c r="AI5" s="107"/>
+      <c r="AJ5" s="107"/>
+      <c r="AK5" s="107"/>
+      <c r="AL5" s="107"/>
+      <c r="AM5" s="107"/>
+      <c r="AN5" s="107"/>
       <c r="AO5" s="12"/>
       <c r="AP5" s="12"/>
       <c r="AQ5" s="12"/>
       <c r="AR5" s="13"/>
     </row>
     <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="65" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="66"/>
-      <c r="D6" s="57" t="s">
-        <v>55</v>
-      </c>
+      <c r="B6" s="79"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="55"/>
       <c r="E6" s="39"/>
-      <c r="F6" s="98" t="s">
-        <v>57</v>
-      </c>
-      <c r="G6" s="99"/>
+      <c r="F6" s="92" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" s="93"/>
       <c r="H6" s="59" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I6" s="36"/>
-      <c r="J6" s="98" t="s">
-        <v>57</v>
-      </c>
-      <c r="K6" s="99"/>
+      <c r="J6" s="92" t="s">
+        <v>54</v>
+      </c>
+      <c r="K6" s="93"/>
       <c r="L6" s="59" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M6" s="3"/>
-      <c r="N6" s="70"/>
-      <c r="O6" s="71"/>
+      <c r="N6" s="74"/>
+      <c r="O6" s="75"/>
       <c r="P6" s="34"/>
       <c r="Q6" s="39"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="71"/>
+      <c r="R6" s="74"/>
+      <c r="S6" s="75"/>
       <c r="T6" s="34"/>
       <c r="U6" s="36"/>
-      <c r="V6" s="70"/>
-      <c r="W6" s="71"/>
+      <c r="V6" s="74"/>
+      <c r="W6" s="75"/>
       <c r="X6" s="34"/>
       <c r="Y6" s="23"/>
-      <c r="Z6" s="70" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA6" s="71"/>
+      <c r="Z6" s="74" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA6" s="75"/>
       <c r="AB6" s="34" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="AC6" s="36"/>
-      <c r="AD6" s="70"/>
-      <c r="AE6" s="71"/>
+      <c r="AD6" s="74"/>
+      <c r="AE6" s="75"/>
       <c r="AF6" s="34"/>
       <c r="AG6" s="39"/>
-      <c r="AH6" s="98" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI6" s="99"/>
-      <c r="AJ6" s="59" t="s">
-        <v>55</v>
+      <c r="AH6" s="74" t="s">
+        <v>54</v>
+      </c>
+      <c r="AI6" s="75"/>
+      <c r="AJ6" s="34" t="s">
+        <v>53</v>
       </c>
       <c r="AK6" s="36"/>
-      <c r="AL6" s="98" t="s">
-        <v>57</v>
-      </c>
-      <c r="AM6" s="99"/>
-      <c r="AN6" s="59" t="s">
-        <v>55</v>
+      <c r="AL6" s="74" t="s">
+        <v>54</v>
+      </c>
+      <c r="AM6" s="75"/>
+      <c r="AN6" s="34" t="s">
+        <v>53</v>
       </c>
       <c r="AP6" s="46" t="s">
         <v>7</v>
       </c>
       <c r="AQ6" s="25">
         <f t="shared" ref="AQ6:AQ30" si="0">COUNTIF(N:AN,AP6)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR6" s="30"/>
     </row>
     <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="78"/>
-      <c r="C7" s="79"/>
+      <c r="B7" s="81"/>
+      <c r="C7" s="82"/>
       <c r="D7" s="61"/>
       <c r="E7" s="38"/>
-      <c r="F7" s="127" t="s">
-        <v>86</v>
-      </c>
-      <c r="G7" s="128"/>
+      <c r="F7" s="114" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" s="115"/>
       <c r="H7" s="60"/>
       <c r="I7" s="36"/>
-      <c r="J7" s="127" t="s">
-        <v>86</v>
-      </c>
-      <c r="K7" s="128"/>
+      <c r="J7" s="114" t="s">
+        <v>85</v>
+      </c>
+      <c r="K7" s="115"/>
       <c r="L7" s="60"/>
       <c r="M7" s="3"/>
-      <c r="N7" s="75"/>
-      <c r="O7" s="76"/>
+      <c r="N7" s="71"/>
+      <c r="O7" s="72"/>
       <c r="P7" s="18"/>
       <c r="Q7" s="36"/>
-      <c r="R7" s="75"/>
-      <c r="S7" s="76"/>
+      <c r="R7" s="71"/>
+      <c r="S7" s="72"/>
       <c r="T7" s="18"/>
       <c r="U7" s="36"/>
-      <c r="V7" s="75"/>
-      <c r="W7" s="76"/>
+      <c r="V7" s="71"/>
+      <c r="W7" s="72"/>
       <c r="X7" s="18"/>
       <c r="Y7" s="36"/>
-      <c r="Z7" s="75" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA7" s="76"/>
+      <c r="Z7" s="71" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA7" s="72"/>
       <c r="AB7" s="18"/>
       <c r="AC7" s="36"/>
-      <c r="AD7" s="75"/>
-      <c r="AE7" s="76"/>
+      <c r="AD7" s="71"/>
+      <c r="AE7" s="72"/>
       <c r="AF7" s="18"/>
       <c r="AG7" s="38"/>
-      <c r="AH7" s="127" t="s">
-        <v>86</v>
-      </c>
-      <c r="AI7" s="128"/>
-      <c r="AJ7" s="60"/>
+      <c r="AH7" s="71"/>
+      <c r="AI7" s="72"/>
+      <c r="AJ7" s="18"/>
       <c r="AK7" s="36"/>
-      <c r="AL7" s="127" t="s">
-        <v>86</v>
-      </c>
-      <c r="AM7" s="128"/>
-      <c r="AN7" s="60"/>
+      <c r="AL7" s="71"/>
+      <c r="AM7" s="72"/>
+      <c r="AN7" s="18"/>
       <c r="AP7" s="46" t="s">
         <v>9</v>
       </c>
       <c r="AQ7" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR7" s="30"/>
     </row>
     <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="67" t="s">
+      <c r="B8" s="76"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="78"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G8" s="118"/>
+      <c r="H8" s="119"/>
+      <c r="I8" s="37"/>
+      <c r="J8" s="117" t="s">
+        <v>87</v>
+      </c>
+      <c r="K8" s="118"/>
+      <c r="L8" s="119"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="76"/>
+      <c r="O8" s="77"/>
+      <c r="P8" s="78"/>
+      <c r="Q8" s="35"/>
+      <c r="R8" s="76"/>
+      <c r="S8" s="77"/>
+      <c r="T8" s="78"/>
+      <c r="U8" s="37"/>
+      <c r="V8" s="76"/>
+      <c r="W8" s="77"/>
+      <c r="X8" s="78"/>
+      <c r="Y8" s="35"/>
+      <c r="Z8" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="103" t="s">
-        <v>87</v>
-      </c>
-      <c r="G8" s="104"/>
-      <c r="H8" s="105"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="103" t="s">
-        <v>109</v>
-      </c>
-      <c r="K8" s="104"/>
-      <c r="L8" s="105"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="89"/>
-      <c r="O8" s="90"/>
-      <c r="P8" s="91"/>
-      <c r="Q8" s="35"/>
-      <c r="R8" s="89"/>
-      <c r="S8" s="90"/>
-      <c r="T8" s="91"/>
-      <c r="U8" s="37"/>
-      <c r="V8" s="89"/>
-      <c r="W8" s="90"/>
-      <c r="X8" s="91"/>
-      <c r="Y8" s="35"/>
-      <c r="Z8" s="89" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA8" s="90"/>
-      <c r="AB8" s="91"/>
+      <c r="AA8" s="77"/>
+      <c r="AB8" s="78"/>
       <c r="AC8" s="35"/>
-      <c r="AD8" s="89"/>
-      <c r="AE8" s="90"/>
-      <c r="AF8" s="91"/>
+      <c r="AD8" s="76"/>
+      <c r="AE8" s="77"/>
+      <c r="AF8" s="78"/>
       <c r="AG8" s="35"/>
-      <c r="AH8" s="103" t="s">
-        <v>112</v>
-      </c>
-      <c r="AI8" s="104"/>
-      <c r="AJ8" s="105"/>
+      <c r="AH8" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI8" s="77"/>
+      <c r="AJ8" s="78"/>
       <c r="AK8" s="37"/>
-      <c r="AL8" s="103" t="s">
-        <v>120</v>
-      </c>
-      <c r="AM8" s="104"/>
-      <c r="AN8" s="105"/>
+      <c r="AL8" s="76" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM8" s="77"/>
+      <c r="AN8" s="78"/>
       <c r="AP8" s="46" t="s">
         <v>16</v>
       </c>
       <c r="AQ8" s="25">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AR8" s="30"/>
     </row>
     <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="67"/>
-      <c r="C9" s="68"/>
-      <c r="D9" s="69"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="70"/>
       <c r="E9" s="43"/>
-      <c r="F9" s="137"/>
-      <c r="G9" s="138"/>
-      <c r="H9" s="139"/>
+      <c r="F9" s="121" t="s">
+        <v>88</v>
+      </c>
+      <c r="G9" s="122"/>
+      <c r="H9" s="123"/>
       <c r="I9" s="43"/>
-      <c r="J9" s="134" t="s">
-        <v>79</v>
-      </c>
-      <c r="K9" s="135"/>
-      <c r="L9" s="136"/>
+      <c r="J9" s="121" t="s">
+        <v>88</v>
+      </c>
+      <c r="K9" s="122"/>
+      <c r="L9" s="123"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="67"/>
-      <c r="O9" s="68"/>
-      <c r="P9" s="69"/>
+      <c r="N9" s="68"/>
+      <c r="O9" s="69"/>
+      <c r="P9" s="70"/>
       <c r="Q9" s="43"/>
-      <c r="R9" s="67"/>
-      <c r="S9" s="68"/>
-      <c r="T9" s="69"/>
+      <c r="R9" s="68"/>
+      <c r="S9" s="69"/>
+      <c r="T9" s="70"/>
       <c r="U9" s="44"/>
-      <c r="V9" s="67"/>
-      <c r="W9" s="68"/>
-      <c r="X9" s="69"/>
+      <c r="V9" s="68"/>
+      <c r="W9" s="69"/>
+      <c r="X9" s="70"/>
       <c r="Y9" s="43"/>
-      <c r="Z9" s="67"/>
-      <c r="AA9" s="68"/>
-      <c r="AB9" s="69"/>
+      <c r="Z9" s="68" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA9" s="69"/>
+      <c r="AB9" s="70"/>
       <c r="AC9" s="43"/>
-      <c r="AD9" s="67"/>
-      <c r="AE9" s="68"/>
-      <c r="AF9" s="69"/>
+      <c r="AD9" s="68"/>
+      <c r="AE9" s="69"/>
+      <c r="AF9" s="70"/>
       <c r="AG9" s="43"/>
-      <c r="AH9" s="134" t="s">
-        <v>79</v>
-      </c>
-      <c r="AI9" s="135"/>
-      <c r="AJ9" s="136"/>
+      <c r="AH9" s="68" t="s">
+        <v>12</v>
+      </c>
+      <c r="AI9" s="69"/>
+      <c r="AJ9" s="70"/>
       <c r="AK9" s="43"/>
-      <c r="AL9" s="134" t="s">
-        <v>79</v>
-      </c>
-      <c r="AM9" s="135"/>
-      <c r="AN9" s="136"/>
+      <c r="AL9" s="68" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM9" s="69"/>
+      <c r="AN9" s="70"/>
       <c r="AP9" s="46" t="s">
         <v>11</v>
       </c>
@@ -2880,55 +2759,57 @@
       <c r="AR9" s="30"/>
     </row>
     <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="106"/>
-      <c r="C10" s="107"/>
-      <c r="D10" s="108"/>
+      <c r="B10" s="89"/>
+      <c r="C10" s="90"/>
+      <c r="D10" s="91"/>
       <c r="E10" s="44"/>
-      <c r="F10" s="92"/>
-      <c r="G10" s="93"/>
-      <c r="H10" s="94"/>
+      <c r="F10" s="124"/>
+      <c r="G10" s="125"/>
+      <c r="H10" s="126"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="131" t="s">
-        <v>88</v>
-      </c>
-      <c r="K10" s="132"/>
-      <c r="L10" s="133"/>
+      <c r="J10" s="124"/>
+      <c r="K10" s="125"/>
+      <c r="L10" s="126"/>
       <c r="M10" s="5"/>
-      <c r="N10" s="106"/>
-      <c r="O10" s="107"/>
-      <c r="P10" s="108"/>
+      <c r="N10" s="89"/>
+      <c r="O10" s="90"/>
+      <c r="P10" s="91"/>
       <c r="Q10" s="44"/>
-      <c r="R10" s="106"/>
-      <c r="S10" s="107"/>
-      <c r="T10" s="108"/>
+      <c r="R10" s="89"/>
+      <c r="S10" s="90"/>
+      <c r="T10" s="91"/>
       <c r="U10" s="44"/>
-      <c r="V10" s="106"/>
-      <c r="W10" s="107"/>
-      <c r="X10" s="108"/>
+      <c r="V10" s="89"/>
+      <c r="W10" s="90"/>
+      <c r="X10" s="91"/>
       <c r="Y10" s="44"/>
-      <c r="Z10" s="106"/>
-      <c r="AA10" s="107"/>
-      <c r="AB10" s="108"/>
+      <c r="Z10" s="89" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA10" s="90"/>
+      <c r="AB10" s="91"/>
       <c r="AC10" s="44"/>
-      <c r="AD10" s="106"/>
-      <c r="AE10" s="107"/>
-      <c r="AF10" s="108"/>
+      <c r="AD10" s="89"/>
+      <c r="AE10" s="90"/>
+      <c r="AF10" s="91"/>
       <c r="AG10" s="44"/>
-      <c r="AH10" s="92"/>
-      <c r="AI10" s="93"/>
-      <c r="AJ10" s="94"/>
+      <c r="AH10" s="89"/>
+      <c r="AI10" s="90"/>
+      <c r="AJ10" s="91"/>
       <c r="AK10" s="44"/>
-      <c r="AL10" s="92"/>
-      <c r="AM10" s="93"/>
-      <c r="AN10" s="94"/>
-      <c r="AP10" s="46" t="s">
+      <c r="AL10" s="89"/>
+      <c r="AM10" s="90"/>
+      <c r="AN10" s="91"/>
+      <c r="AP10" s="56" t="s">
         <v>8</v>
       </c>
       <c r="AQ10" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AR10" s="30"/>
+        <v>1</v>
+      </c>
+      <c r="AR10" s="30" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="11" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="33"/>
@@ -2975,106 +2856,106 @@
       </c>
       <c r="AQ11" s="25">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AR11" s="30"/>
     </row>
     <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="81"/>
-      <c r="C12" s="82"/>
+      <c r="B12" s="79"/>
+      <c r="C12" s="80"/>
       <c r="D12" s="55"/>
       <c r="E12" s="39"/>
-      <c r="F12" s="81" t="s">
+      <c r="F12" s="79" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="82"/>
+      <c r="G12" s="80"/>
       <c r="H12" s="55" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I12" s="36"/>
-      <c r="J12" s="81"/>
-      <c r="K12" s="82"/>
+      <c r="J12" s="79"/>
+      <c r="K12" s="80"/>
       <c r="L12" s="55"/>
       <c r="M12" s="5"/>
-      <c r="N12" s="70"/>
-      <c r="O12" s="71"/>
+      <c r="N12" s="74"/>
+      <c r="O12" s="75"/>
       <c r="P12" s="34"/>
       <c r="Q12" s="23"/>
-      <c r="R12" s="70"/>
-      <c r="S12" s="71"/>
+      <c r="R12" s="74"/>
+      <c r="S12" s="75"/>
       <c r="T12" s="34"/>
       <c r="U12" s="36"/>
-      <c r="V12" s="70"/>
-      <c r="W12" s="71"/>
+      <c r="V12" s="74"/>
+      <c r="W12" s="75"/>
       <c r="X12" s="34"/>
       <c r="Y12" s="23"/>
-      <c r="Z12" s="70"/>
-      <c r="AA12" s="71"/>
+      <c r="Z12" s="74"/>
+      <c r="AA12" s="75"/>
       <c r="AB12" s="34"/>
       <c r="AC12" s="36"/>
-      <c r="AD12" s="70"/>
-      <c r="AE12" s="71"/>
+      <c r="AD12" s="74"/>
+      <c r="AE12" s="75"/>
       <c r="AF12" s="34"/>
       <c r="AG12" s="39"/>
-      <c r="AH12" s="70" t="s">
+      <c r="AH12" s="74" t="s">
         <v>41</v>
       </c>
-      <c r="AI12" s="71"/>
+      <c r="AI12" s="75"/>
       <c r="AJ12" s="34" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="AK12" s="36"/>
-      <c r="AL12" s="70"/>
-      <c r="AM12" s="71"/>
+      <c r="AL12" s="74"/>
+      <c r="AM12" s="75"/>
       <c r="AN12" s="34"/>
       <c r="AP12" s="46" t="s">
         <v>19</v>
       </c>
       <c r="AQ12" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR12" s="30"/>
     </row>
     <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="78"/>
-      <c r="C13" s="79"/>
+      <c r="B13" s="81"/>
+      <c r="C13" s="82"/>
       <c r="D13" s="61"/>
       <c r="E13" s="38"/>
-      <c r="F13" s="78"/>
-      <c r="G13" s="79"/>
+      <c r="F13" s="81"/>
+      <c r="G13" s="82"/>
       <c r="H13" s="61"/>
       <c r="I13" s="36"/>
-      <c r="J13" s="78"/>
-      <c r="K13" s="79"/>
+      <c r="J13" s="81"/>
+      <c r="K13" s="82"/>
       <c r="L13" s="61"/>
       <c r="M13" s="5"/>
-      <c r="N13" s="75"/>
-      <c r="O13" s="76"/>
+      <c r="N13" s="71"/>
+      <c r="O13" s="72"/>
       <c r="P13" s="18"/>
       <c r="Q13" s="36"/>
-      <c r="R13" s="75"/>
-      <c r="S13" s="76"/>
+      <c r="R13" s="71"/>
+      <c r="S13" s="72"/>
       <c r="T13" s="18"/>
       <c r="U13" s="36"/>
-      <c r="V13" s="75"/>
-      <c r="W13" s="76"/>
+      <c r="V13" s="71"/>
+      <c r="W13" s="72"/>
       <c r="X13" s="18"/>
       <c r="Y13" s="36"/>
-      <c r="Z13" s="75"/>
-      <c r="AA13" s="76"/>
+      <c r="Z13" s="71"/>
+      <c r="AA13" s="72"/>
       <c r="AB13" s="18"/>
       <c r="AC13" s="36"/>
-      <c r="AD13" s="75"/>
-      <c r="AE13" s="76"/>
+      <c r="AD13" s="71"/>
+      <c r="AE13" s="72"/>
       <c r="AF13" s="18"/>
       <c r="AG13" s="38"/>
-      <c r="AH13" s="75"/>
-      <c r="AI13" s="76"/>
+      <c r="AH13" s="71"/>
+      <c r="AI13" s="72"/>
       <c r="AJ13" s="18"/>
       <c r="AK13" s="36"/>
-      <c r="AL13" s="75"/>
-      <c r="AM13" s="76"/>
+      <c r="AL13" s="71"/>
+      <c r="AM13" s="72"/>
       <c r="AN13" s="18"/>
       <c r="AP13" s="46" t="s">
         <v>22</v>
@@ -3086,151 +2967,151 @@
       <c r="AR13" s="30"/>
     </row>
     <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="89"/>
-      <c r="C14" s="90"/>
-      <c r="D14" s="91"/>
+      <c r="B14" s="76"/>
+      <c r="C14" s="77"/>
+      <c r="D14" s="78"/>
       <c r="E14" s="37"/>
-      <c r="F14" s="89" t="s">
-        <v>37</v>
-      </c>
-      <c r="G14" s="90"/>
-      <c r="H14" s="91"/>
+      <c r="F14" s="76" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="77"/>
+      <c r="H14" s="78"/>
       <c r="I14" s="35"/>
-      <c r="J14" s="89"/>
-      <c r="K14" s="90"/>
-      <c r="L14" s="91"/>
+      <c r="J14" s="76"/>
+      <c r="K14" s="77"/>
+      <c r="L14" s="78"/>
       <c r="M14" s="3"/>
-      <c r="N14" s="89"/>
-      <c r="O14" s="90"/>
-      <c r="P14" s="91"/>
+      <c r="N14" s="76"/>
+      <c r="O14" s="77"/>
+      <c r="P14" s="78"/>
       <c r="Q14" s="35"/>
-      <c r="R14" s="89"/>
-      <c r="S14" s="90"/>
-      <c r="T14" s="91"/>
+      <c r="R14" s="76"/>
+      <c r="S14" s="77"/>
+      <c r="T14" s="78"/>
       <c r="U14" s="37"/>
-      <c r="V14" s="89"/>
-      <c r="W14" s="90"/>
-      <c r="X14" s="91"/>
+      <c r="V14" s="76"/>
+      <c r="W14" s="77"/>
+      <c r="X14" s="78"/>
       <c r="Y14" s="35"/>
-      <c r="Z14" s="89"/>
-      <c r="AA14" s="90"/>
-      <c r="AB14" s="91"/>
+      <c r="Z14" s="76"/>
+      <c r="AA14" s="77"/>
+      <c r="AB14" s="78"/>
       <c r="AC14" s="37"/>
-      <c r="AD14" s="89"/>
-      <c r="AE14" s="90"/>
-      <c r="AF14" s="91"/>
+      <c r="AD14" s="76"/>
+      <c r="AE14" s="77"/>
+      <c r="AF14" s="78"/>
       <c r="AG14" s="37"/>
-      <c r="AH14" s="89" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI14" s="90"/>
-      <c r="AJ14" s="91"/>
+      <c r="AH14" s="76" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI14" s="77"/>
+      <c r="AJ14" s="78"/>
       <c r="AK14" s="35"/>
-      <c r="AL14" s="89"/>
-      <c r="AM14" s="90"/>
-      <c r="AN14" s="91"/>
+      <c r="AL14" s="76"/>
+      <c r="AM14" s="77"/>
+      <c r="AN14" s="78"/>
       <c r="AP14" s="46" t="s">
         <v>23</v>
       </c>
       <c r="AQ14" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR14" s="30"/>
     </row>
     <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="67"/>
-      <c r="C15" s="68"/>
-      <c r="D15" s="69"/>
+      <c r="B15" s="68"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="70"/>
       <c r="E15" s="44"/>
-      <c r="F15" s="67" t="s">
-        <v>29</v>
-      </c>
-      <c r="G15" s="68"/>
-      <c r="H15" s="69"/>
+      <c r="F15" s="68" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="69"/>
+      <c r="H15" s="70"/>
       <c r="I15" s="43"/>
-      <c r="J15" s="67"/>
-      <c r="K15" s="68"/>
-      <c r="L15" s="69"/>
+      <c r="J15" s="68"/>
+      <c r="K15" s="69"/>
+      <c r="L15" s="70"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="67"/>
-      <c r="O15" s="68"/>
-      <c r="P15" s="69"/>
+      <c r="N15" s="68"/>
+      <c r="O15" s="69"/>
+      <c r="P15" s="70"/>
       <c r="Q15" s="43"/>
-      <c r="R15" s="67"/>
-      <c r="S15" s="68"/>
-      <c r="T15" s="69"/>
+      <c r="R15" s="68"/>
+      <c r="S15" s="69"/>
+      <c r="T15" s="70"/>
       <c r="U15" s="44"/>
-      <c r="V15" s="67"/>
-      <c r="W15" s="68"/>
-      <c r="X15" s="69"/>
+      <c r="V15" s="68"/>
+      <c r="W15" s="69"/>
+      <c r="X15" s="70"/>
       <c r="Y15" s="43"/>
-      <c r="Z15" s="67"/>
-      <c r="AA15" s="68"/>
-      <c r="AB15" s="69"/>
+      <c r="Z15" s="68"/>
+      <c r="AA15" s="69"/>
+      <c r="AB15" s="70"/>
       <c r="AC15" s="43"/>
-      <c r="AD15" s="67"/>
-      <c r="AE15" s="68"/>
-      <c r="AF15" s="69"/>
+      <c r="AD15" s="68"/>
+      <c r="AE15" s="69"/>
+      <c r="AF15" s="70"/>
       <c r="AG15" s="44"/>
-      <c r="AH15" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AI15" s="68"/>
-      <c r="AJ15" s="69"/>
+      <c r="AH15" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI15" s="69"/>
+      <c r="AJ15" s="70"/>
       <c r="AK15" s="43"/>
-      <c r="AL15" s="67"/>
-      <c r="AM15" s="68"/>
-      <c r="AN15" s="69"/>
+      <c r="AL15" s="68"/>
+      <c r="AM15" s="69"/>
+      <c r="AN15" s="70"/>
       <c r="AP15" s="46" t="s">
         <v>18</v>
       </c>
       <c r="AQ15" s="25">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AR15" s="30"/>
     </row>
     <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="106"/>
-      <c r="C16" s="107"/>
-      <c r="D16" s="108"/>
+      <c r="B16" s="89"/>
+      <c r="C16" s="90"/>
+      <c r="D16" s="91"/>
       <c r="E16" s="44"/>
-      <c r="F16" s="106"/>
-      <c r="G16" s="107"/>
-      <c r="H16" s="108"/>
+      <c r="F16" s="89"/>
+      <c r="G16" s="90"/>
+      <c r="H16" s="91"/>
       <c r="I16" s="44"/>
-      <c r="J16" s="106"/>
-      <c r="K16" s="107"/>
-      <c r="L16" s="108"/>
+      <c r="J16" s="89"/>
+      <c r="K16" s="90"/>
+      <c r="L16" s="91"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="106"/>
-      <c r="O16" s="107"/>
-      <c r="P16" s="108"/>
+      <c r="N16" s="89"/>
+      <c r="O16" s="90"/>
+      <c r="P16" s="91"/>
       <c r="Q16" s="44"/>
-      <c r="R16" s="106"/>
-      <c r="S16" s="107"/>
-      <c r="T16" s="108"/>
+      <c r="R16" s="89"/>
+      <c r="S16" s="90"/>
+      <c r="T16" s="91"/>
       <c r="U16" s="44"/>
-      <c r="V16" s="106"/>
-      <c r="W16" s="107"/>
-      <c r="X16" s="108"/>
+      <c r="V16" s="89"/>
+      <c r="W16" s="90"/>
+      <c r="X16" s="91"/>
       <c r="Y16" s="44"/>
-      <c r="Z16" s="106"/>
-      <c r="AA16" s="107"/>
-      <c r="AB16" s="108"/>
+      <c r="Z16" s="89"/>
+      <c r="AA16" s="90"/>
+      <c r="AB16" s="91"/>
       <c r="AC16" s="44"/>
-      <c r="AD16" s="106"/>
-      <c r="AE16" s="107"/>
-      <c r="AF16" s="108"/>
+      <c r="AD16" s="89"/>
+      <c r="AE16" s="90"/>
+      <c r="AF16" s="91"/>
       <c r="AG16" s="44"/>
-      <c r="AH16" s="106"/>
-      <c r="AI16" s="107"/>
-      <c r="AJ16" s="108"/>
+      <c r="AH16" s="89"/>
+      <c r="AI16" s="90"/>
+      <c r="AJ16" s="91"/>
       <c r="AK16" s="44"/>
-      <c r="AL16" s="106"/>
-      <c r="AM16" s="107"/>
-      <c r="AN16" s="108"/>
+      <c r="AL16" s="89"/>
+      <c r="AM16" s="90"/>
+      <c r="AN16" s="91"/>
       <c r="AP16" s="46" t="s">
         <v>24</v>
       </c>
@@ -3285,7 +3166,7 @@
       </c>
       <c r="AQ17" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AR17" s="30"/>
     </row>
@@ -3302,23 +3183,23 @@
       <c r="K18" s="33"/>
       <c r="L18" s="33"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="115" t="s">
-        <v>49</v>
-      </c>
-      <c r="O18" s="115"/>
-      <c r="P18" s="115"/>
-      <c r="Q18" s="115"/>
-      <c r="R18" s="115"/>
-      <c r="S18" s="115"/>
-      <c r="T18" s="115"/>
-      <c r="U18" s="115"/>
-      <c r="V18" s="115"/>
-      <c r="W18" s="115"/>
-      <c r="X18" s="115"/>
-      <c r="Y18" s="115"/>
-      <c r="Z18" s="115"/>
-      <c r="AA18" s="115"/>
-      <c r="AB18" s="115"/>
+      <c r="N18" s="102" t="s">
+        <v>48</v>
+      </c>
+      <c r="O18" s="102"/>
+      <c r="P18" s="102"/>
+      <c r="Q18" s="102"/>
+      <c r="R18" s="102"/>
+      <c r="S18" s="102"/>
+      <c r="T18" s="102"/>
+      <c r="U18" s="102"/>
+      <c r="V18" s="102"/>
+      <c r="W18" s="102"/>
+      <c r="X18" s="102"/>
+      <c r="Y18" s="102"/>
+      <c r="Z18" s="102"/>
+      <c r="AA18" s="102"/>
+      <c r="AB18" s="102"/>
       <c r="AC18" s="33"/>
       <c r="AD18" s="33"/>
       <c r="AE18" s="33"/>
@@ -3336,7 +3217,7 @@
       </c>
       <c r="AQ18" s="25">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR18" s="30"/>
     </row>
@@ -3353,21 +3234,21 @@
       <c r="K19" s="33"/>
       <c r="L19" s="33"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="115"/>
-      <c r="O19" s="115"/>
-      <c r="P19" s="115"/>
-      <c r="Q19" s="115"/>
-      <c r="R19" s="115"/>
-      <c r="S19" s="115"/>
-      <c r="T19" s="115"/>
-      <c r="U19" s="115"/>
-      <c r="V19" s="115"/>
-      <c r="W19" s="115"/>
-      <c r="X19" s="115"/>
-      <c r="Y19" s="115"/>
-      <c r="Z19" s="115"/>
-      <c r="AA19" s="115"/>
-      <c r="AB19" s="115"/>
+      <c r="N19" s="102"/>
+      <c r="O19" s="102"/>
+      <c r="P19" s="102"/>
+      <c r="Q19" s="102"/>
+      <c r="R19" s="102"/>
+      <c r="S19" s="102"/>
+      <c r="T19" s="102"/>
+      <c r="U19" s="102"/>
+      <c r="V19" s="102"/>
+      <c r="W19" s="102"/>
+      <c r="X19" s="102"/>
+      <c r="Y19" s="102"/>
+      <c r="Z19" s="102"/>
+      <c r="AA19" s="102"/>
+      <c r="AB19" s="102"/>
       <c r="AC19" s="33"/>
       <c r="AD19" s="33"/>
       <c r="AE19" s="33"/>
@@ -3390,222 +3271,216 @@
       <c r="AR19" s="30"/>
     </row>
     <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="81"/>
-      <c r="C20" s="82"/>
+      <c r="B20" s="79"/>
+      <c r="C20" s="80"/>
       <c r="D20" s="55"/>
       <c r="E20" s="39"/>
-      <c r="F20" s="81" t="s">
-        <v>47</v>
-      </c>
-      <c r="G20" s="82"/>
-      <c r="H20" s="57" t="s">
-        <v>89</v>
+      <c r="F20" s="79" t="s">
+        <v>46</v>
+      </c>
+      <c r="G20" s="80"/>
+      <c r="H20" s="55" t="s">
+        <v>58</v>
       </c>
       <c r="I20" s="36"/>
-      <c r="J20" s="81"/>
-      <c r="K20" s="82"/>
+      <c r="J20" s="79"/>
+      <c r="K20" s="80"/>
       <c r="L20" s="55"/>
       <c r="M20" s="4"/>
-      <c r="N20" s="70"/>
-      <c r="O20" s="71"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="75"/>
       <c r="P20" s="34"/>
       <c r="Q20" s="39"/>
-      <c r="R20" s="70"/>
-      <c r="S20" s="71"/>
+      <c r="R20" s="74"/>
+      <c r="S20" s="75"/>
       <c r="T20" s="34"/>
       <c r="U20" s="36"/>
-      <c r="V20" s="70" t="s">
-        <v>47</v>
-      </c>
-      <c r="W20" s="71"/>
+      <c r="V20" s="74" t="s">
+        <v>46</v>
+      </c>
+      <c r="W20" s="75"/>
       <c r="X20" s="34" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Y20" s="23"/>
-      <c r="Z20" s="70"/>
-      <c r="AA20" s="71"/>
+      <c r="Z20" s="74"/>
+      <c r="AA20" s="75"/>
       <c r="AB20" s="34"/>
       <c r="AC20" s="36"/>
-      <c r="AD20" s="70"/>
-      <c r="AE20" s="71"/>
+      <c r="AD20" s="74"/>
+      <c r="AE20" s="75"/>
       <c r="AF20" s="34"/>
       <c r="AG20" s="39"/>
-      <c r="AH20" s="70" t="s">
-        <v>47</v>
-      </c>
-      <c r="AI20" s="71"/>
-      <c r="AJ20" s="34" t="s">
-        <v>65</v>
-      </c>
+      <c r="AH20" s="74"/>
+      <c r="AI20" s="75"/>
+      <c r="AJ20" s="34"/>
       <c r="AK20" s="36"/>
-      <c r="AL20" s="70"/>
-      <c r="AM20" s="71"/>
+      <c r="AL20" s="74"/>
+      <c r="AM20" s="75"/>
       <c r="AN20" s="34"/>
       <c r="AP20" s="46" t="s">
         <v>26</v>
       </c>
       <c r="AQ20" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR20" s="30"/>
     </row>
     <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="78"/>
-      <c r="C21" s="79"/>
+      <c r="B21" s="81"/>
+      <c r="C21" s="82"/>
       <c r="D21" s="61"/>
       <c r="E21" s="38"/>
-      <c r="F21" s="78"/>
-      <c r="G21" s="79"/>
+      <c r="F21" s="81"/>
+      <c r="G21" s="82"/>
       <c r="H21" s="61"/>
       <c r="I21" s="36"/>
-      <c r="J21" s="78"/>
-      <c r="K21" s="79"/>
+      <c r="J21" s="81"/>
+      <c r="K21" s="82"/>
       <c r="L21" s="61"/>
       <c r="M21" s="15"/>
-      <c r="N21" s="75"/>
-      <c r="O21" s="76"/>
+      <c r="N21" s="71"/>
+      <c r="O21" s="72"/>
       <c r="P21" s="18"/>
       <c r="Q21" s="36"/>
-      <c r="R21" s="75"/>
-      <c r="S21" s="76"/>
+      <c r="R21" s="71"/>
+      <c r="S21" s="72"/>
       <c r="T21" s="18"/>
       <c r="U21" s="36"/>
-      <c r="V21" s="75" t="s">
-        <v>45</v>
-      </c>
-      <c r="W21" s="76"/>
+      <c r="V21" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="W21" s="72"/>
       <c r="X21" s="18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Y21" s="36"/>
-      <c r="Z21" s="75"/>
-      <c r="AA21" s="76"/>
+      <c r="Z21" s="71"/>
+      <c r="AA21" s="72"/>
       <c r="AB21" s="18"/>
       <c r="AC21" s="36"/>
-      <c r="AD21" s="75"/>
-      <c r="AE21" s="76"/>
+      <c r="AD21" s="71"/>
+      <c r="AE21" s="72"/>
       <c r="AF21" s="18"/>
       <c r="AG21" s="38"/>
-      <c r="AH21" s="75"/>
-      <c r="AI21" s="76"/>
+      <c r="AH21" s="71"/>
+      <c r="AI21" s="72"/>
       <c r="AJ21" s="18"/>
       <c r="AK21" s="36"/>
-      <c r="AL21" s="75"/>
-      <c r="AM21" s="76"/>
+      <c r="AL21" s="71"/>
+      <c r="AM21" s="72"/>
       <c r="AN21" s="18"/>
       <c r="AP21" s="46" t="s">
         <v>12</v>
       </c>
       <c r="AQ21" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR21" s="30"/>
     </row>
     <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="89"/>
-      <c r="C22" s="90"/>
-      <c r="D22" s="91"/>
+      <c r="B22" s="76"/>
+      <c r="C22" s="77"/>
+      <c r="D22" s="78"/>
       <c r="E22" s="35"/>
-      <c r="F22" s="140" t="s">
-        <v>9</v>
-      </c>
-      <c r="G22" s="141"/>
-      <c r="H22" s="142"/>
+      <c r="F22" s="76" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" s="77"/>
+      <c r="H22" s="78"/>
       <c r="I22" s="37"/>
-      <c r="J22" s="89"/>
-      <c r="K22" s="90"/>
-      <c r="L22" s="91"/>
+      <c r="J22" s="76"/>
+      <c r="K22" s="77"/>
+      <c r="L22" s="78"/>
       <c r="M22" s="4"/>
-      <c r="N22" s="89"/>
-      <c r="O22" s="90"/>
-      <c r="P22" s="91"/>
+      <c r="N22" s="76"/>
+      <c r="O22" s="77"/>
+      <c r="P22" s="78"/>
       <c r="Q22" s="35"/>
-      <c r="R22" s="89"/>
-      <c r="S22" s="90"/>
-      <c r="T22" s="91"/>
+      <c r="R22" s="76"/>
+      <c r="S22" s="77"/>
+      <c r="T22" s="78"/>
       <c r="U22" s="37"/>
-      <c r="V22" s="89" t="s">
-        <v>9</v>
-      </c>
-      <c r="W22" s="90"/>
-      <c r="X22" s="91"/>
+      <c r="V22" s="76" t="s">
+        <v>11</v>
+      </c>
+      <c r="W22" s="77"/>
+      <c r="X22" s="78"/>
       <c r="Y22" s="35"/>
-      <c r="Z22" s="89"/>
-      <c r="AA22" s="90"/>
-      <c r="AB22" s="91"/>
+      <c r="Z22" s="76"/>
+      <c r="AA22" s="77"/>
+      <c r="AB22" s="78"/>
       <c r="AC22" s="35"/>
-      <c r="AD22" s="89"/>
-      <c r="AE22" s="90"/>
-      <c r="AF22" s="91"/>
+      <c r="AD22" s="76"/>
+      <c r="AE22" s="77"/>
+      <c r="AF22" s="78"/>
       <c r="AG22" s="35"/>
-      <c r="AH22" s="89" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI22" s="90"/>
-      <c r="AJ22" s="91"/>
+      <c r="AH22" s="76"/>
+      <c r="AI22" s="77"/>
+      <c r="AJ22" s="78"/>
       <c r="AK22" s="37"/>
-      <c r="AL22" s="89"/>
-      <c r="AM22" s="90"/>
-      <c r="AN22" s="91"/>
+      <c r="AL22" s="76"/>
+      <c r="AM22" s="77"/>
+      <c r="AN22" s="78"/>
       <c r="AP22" s="46" t="s">
         <v>15</v>
       </c>
       <c r="AQ22" s="25">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR22" s="30"/>
     </row>
     <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="106"/>
-      <c r="C23" s="107"/>
-      <c r="D23" s="108"/>
+      <c r="B23" s="89"/>
+      <c r="C23" s="90"/>
+      <c r="D23" s="91"/>
       <c r="E23" s="44"/>
-      <c r="F23" s="106"/>
-      <c r="G23" s="107"/>
-      <c r="H23" s="108"/>
+      <c r="F23" s="89" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" s="90"/>
+      <c r="H23" s="91"/>
       <c r="I23" s="44"/>
-      <c r="J23" s="106"/>
-      <c r="K23" s="107"/>
-      <c r="L23" s="108"/>
+      <c r="J23" s="89"/>
+      <c r="K23" s="90"/>
+      <c r="L23" s="91"/>
       <c r="M23" s="4"/>
-      <c r="N23" s="106"/>
-      <c r="O23" s="107"/>
-      <c r="P23" s="108"/>
+      <c r="N23" s="89"/>
+      <c r="O23" s="90"/>
+      <c r="P23" s="91"/>
       <c r="Q23" s="44"/>
-      <c r="R23" s="106"/>
-      <c r="S23" s="107"/>
-      <c r="T23" s="108"/>
+      <c r="R23" s="89"/>
+      <c r="S23" s="90"/>
+      <c r="T23" s="91"/>
       <c r="U23" s="44"/>
-      <c r="V23" s="106"/>
-      <c r="W23" s="107"/>
-      <c r="X23" s="108"/>
+      <c r="V23" s="89"/>
+      <c r="W23" s="90"/>
+      <c r="X23" s="91"/>
       <c r="Y23" s="44"/>
-      <c r="Z23" s="106"/>
-      <c r="AA23" s="107"/>
-      <c r="AB23" s="108"/>
+      <c r="Z23" s="89"/>
+      <c r="AA23" s="90"/>
+      <c r="AB23" s="91"/>
       <c r="AC23" s="44"/>
-      <c r="AD23" s="106"/>
-      <c r="AE23" s="107"/>
-      <c r="AF23" s="108"/>
+      <c r="AD23" s="89"/>
+      <c r="AE23" s="90"/>
+      <c r="AF23" s="91"/>
       <c r="AG23" s="44"/>
-      <c r="AH23" s="106" t="s">
-        <v>15</v>
-      </c>
-      <c r="AI23" s="107"/>
-      <c r="AJ23" s="108"/>
+      <c r="AH23" s="89"/>
+      <c r="AI23" s="90"/>
+      <c r="AJ23" s="91"/>
       <c r="AK23" s="44"/>
-      <c r="AL23" s="106"/>
-      <c r="AM23" s="107"/>
-      <c r="AN23" s="108"/>
+      <c r="AL23" s="89"/>
+      <c r="AM23" s="90"/>
+      <c r="AN23" s="91"/>
       <c r="AP23" s="56" t="s">
         <v>20</v>
       </c>
       <c r="AQ23" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR23" s="30" t="s">
         <v>40</v>
@@ -3656,7 +3531,7 @@
       </c>
       <c r="AQ24" s="25">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AR24" s="30"/>
     </row>
@@ -3673,23 +3548,23 @@
       <c r="K25" s="33"/>
       <c r="L25" s="33"/>
       <c r="M25" s="4"/>
-      <c r="N25" s="115" t="s">
+      <c r="N25" s="102" t="s">
         <v>39</v>
       </c>
-      <c r="O25" s="115"/>
-      <c r="P25" s="115"/>
-      <c r="Q25" s="115"/>
-      <c r="R25" s="115"/>
-      <c r="S25" s="115"/>
-      <c r="T25" s="115"/>
-      <c r="U25" s="115"/>
-      <c r="V25" s="115"/>
-      <c r="W25" s="115"/>
-      <c r="X25" s="115"/>
-      <c r="Y25" s="115"/>
-      <c r="Z25" s="115"/>
-      <c r="AA25" s="115"/>
-      <c r="AB25" s="115"/>
+      <c r="O25" s="102"/>
+      <c r="P25" s="102"/>
+      <c r="Q25" s="102"/>
+      <c r="R25" s="102"/>
+      <c r="S25" s="102"/>
+      <c r="T25" s="102"/>
+      <c r="U25" s="102"/>
+      <c r="V25" s="102"/>
+      <c r="W25" s="102"/>
+      <c r="X25" s="102"/>
+      <c r="Y25" s="102"/>
+      <c r="Z25" s="102"/>
+      <c r="AA25" s="102"/>
+      <c r="AB25" s="102"/>
       <c r="AC25" s="33"/>
       <c r="AD25" s="33"/>
       <c r="AE25" s="33"/>
@@ -3702,12 +3577,12 @@
       <c r="AL25" s="33"/>
       <c r="AM25" s="33"/>
       <c r="AN25" s="33"/>
-      <c r="AP25" s="46" t="s">
+      <c r="AP25" s="56" t="s">
         <v>21</v>
       </c>
       <c r="AQ25" s="25">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AR25" s="30"/>
     </row>
@@ -3724,21 +3599,21 @@
       <c r="K26" s="33"/>
       <c r="L26" s="33"/>
       <c r="M26" s="4"/>
-      <c r="N26" s="115"/>
-      <c r="O26" s="115"/>
-      <c r="P26" s="115"/>
-      <c r="Q26" s="115"/>
-      <c r="R26" s="115"/>
-      <c r="S26" s="115"/>
-      <c r="T26" s="115"/>
-      <c r="U26" s="115"/>
-      <c r="V26" s="115"/>
-      <c r="W26" s="115"/>
-      <c r="X26" s="115"/>
-      <c r="Y26" s="115"/>
-      <c r="Z26" s="115"/>
-      <c r="AA26" s="115"/>
-      <c r="AB26" s="115"/>
+      <c r="N26" s="102"/>
+      <c r="O26" s="102"/>
+      <c r="P26" s="102"/>
+      <c r="Q26" s="102"/>
+      <c r="R26" s="102"/>
+      <c r="S26" s="102"/>
+      <c r="T26" s="102"/>
+      <c r="U26" s="102"/>
+      <c r="V26" s="102"/>
+      <c r="W26" s="102"/>
+      <c r="X26" s="102"/>
+      <c r="Y26" s="102"/>
+      <c r="Z26" s="102"/>
+      <c r="AA26" s="102"/>
+      <c r="AB26" s="102"/>
       <c r="AC26" s="33"/>
       <c r="AD26" s="33"/>
       <c r="AE26" s="33"/>
@@ -3756,132 +3631,112 @@
       </c>
       <c r="AQ26" s="25">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AR26" s="30"/>
+        <v>2</v>
+      </c>
+      <c r="AR26" s="30" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="81" t="s">
-        <v>64</v>
-      </c>
-      <c r="C27" s="82"/>
+      <c r="B27" s="79" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" s="80"/>
       <c r="D27" s="55" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E27" s="36"/>
-      <c r="F27" s="81" t="s">
-        <v>64</v>
-      </c>
-      <c r="G27" s="82"/>
-      <c r="H27" s="55" t="s">
-        <v>54</v>
-      </c>
+      <c r="F27" s="87" t="s">
+        <v>90</v>
+      </c>
+      <c r="G27" s="88"/>
+      <c r="H27" s="57"/>
       <c r="I27" s="36"/>
-      <c r="J27" s="81" t="s">
-        <v>64</v>
-      </c>
-      <c r="K27" s="82"/>
-      <c r="L27" s="55" t="s">
-        <v>54</v>
-      </c>
+      <c r="J27" s="79"/>
+      <c r="K27" s="80"/>
+      <c r="L27" s="55"/>
       <c r="M27" s="5"/>
-      <c r="N27" s="70" t="s">
-        <v>64</v>
-      </c>
-      <c r="O27" s="71"/>
-      <c r="P27" s="34" t="s">
-        <v>54</v>
-      </c>
+      <c r="N27" s="74"/>
+      <c r="O27" s="75"/>
+      <c r="P27" s="34"/>
       <c r="Q27" s="36"/>
-      <c r="R27" s="70" t="s">
-        <v>64</v>
-      </c>
-      <c r="S27" s="71"/>
-      <c r="T27" s="34" t="s">
-        <v>54</v>
-      </c>
+      <c r="R27" s="74" t="s">
+        <v>83</v>
+      </c>
+      <c r="S27" s="75"/>
+      <c r="T27" s="34"/>
       <c r="U27" s="36"/>
-      <c r="V27" s="70" t="s">
-        <v>64</v>
-      </c>
-      <c r="W27" s="71"/>
-      <c r="X27" s="34" t="s">
-        <v>54</v>
-      </c>
+      <c r="V27" s="74"/>
+      <c r="W27" s="75"/>
+      <c r="X27" s="34"/>
       <c r="Y27" s="36"/>
-      <c r="Z27" s="70" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA27" s="71"/>
-      <c r="AB27" s="34" t="s">
-        <v>54</v>
-      </c>
+      <c r="Z27" s="74"/>
+      <c r="AA27" s="75"/>
+      <c r="AB27" s="34"/>
       <c r="AC27" s="36"/>
-      <c r="AD27" s="70" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE27" s="71"/>
-      <c r="AF27" s="34" t="s">
-        <v>54</v>
-      </c>
+      <c r="AD27" s="74"/>
+      <c r="AE27" s="75"/>
+      <c r="AF27" s="34"/>
       <c r="AG27" s="36"/>
-      <c r="AH27" s="65" t="s">
-        <v>119</v>
-      </c>
-      <c r="AI27" s="66"/>
-      <c r="AJ27" s="57"/>
+      <c r="AH27" s="74"/>
+      <c r="AI27" s="75"/>
+      <c r="AJ27" s="34"/>
       <c r="AK27" s="36"/>
-      <c r="AL27" s="70"/>
-      <c r="AM27" s="71"/>
-      <c r="AN27" s="34"/>
+      <c r="AL27" s="74" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM27" s="75"/>
+      <c r="AN27" s="34" t="s">
+        <v>42</v>
+      </c>
       <c r="AP27" s="46" t="s">
         <v>13</v>
       </c>
       <c r="AQ27" s="25">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR27" s="30"/>
     </row>
     <row r="28" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="78"/>
-      <c r="C28" s="79"/>
+      <c r="B28" s="81"/>
+      <c r="C28" s="82"/>
       <c r="D28" s="61"/>
       <c r="E28" s="38"/>
-      <c r="F28" s="78"/>
-      <c r="G28" s="79"/>
+      <c r="F28" s="147"/>
+      <c r="G28" s="148"/>
       <c r="H28" s="61"/>
       <c r="I28" s="36"/>
-      <c r="J28" s="78"/>
-      <c r="K28" s="79"/>
+      <c r="J28" s="81"/>
+      <c r="K28" s="82"/>
       <c r="L28" s="61"/>
       <c r="M28" s="5"/>
-      <c r="N28" s="75"/>
-      <c r="O28" s="76"/>
+      <c r="N28" s="71"/>
+      <c r="O28" s="72"/>
       <c r="P28" s="18"/>
       <c r="Q28" s="38"/>
-      <c r="R28" s="75"/>
-      <c r="S28" s="76"/>
+      <c r="R28" s="71"/>
+      <c r="S28" s="72"/>
       <c r="T28" s="18"/>
       <c r="U28" s="38"/>
-      <c r="V28" s="75"/>
-      <c r="W28" s="76"/>
+      <c r="V28" s="71"/>
+      <c r="W28" s="72"/>
       <c r="X28" s="18"/>
       <c r="Y28" s="36"/>
-      <c r="Z28" s="75"/>
-      <c r="AA28" s="76"/>
+      <c r="Z28" s="71"/>
+      <c r="AA28" s="72"/>
       <c r="AB28" s="18"/>
       <c r="AC28" s="36"/>
-      <c r="AD28" s="75"/>
-      <c r="AE28" s="76"/>
+      <c r="AD28" s="71"/>
+      <c r="AE28" s="72"/>
       <c r="AF28" s="18"/>
       <c r="AG28" s="38"/>
-      <c r="AH28" s="146"/>
-      <c r="AI28" s="147"/>
+      <c r="AH28" s="127"/>
+      <c r="AI28" s="128"/>
       <c r="AJ28" s="18"/>
       <c r="AK28" s="36"/>
-      <c r="AL28" s="75"/>
-      <c r="AM28" s="76"/>
+      <c r="AL28" s="71"/>
+      <c r="AM28" s="72"/>
       <c r="AN28" s="18"/>
       <c r="AP28" s="46" t="s">
         <v>28</v>
@@ -3893,162 +3748,116 @@
       <c r="AR28" s="30"/>
     </row>
     <row r="29" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="111" t="s">
+      <c r="B29" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="C29" s="112"/>
+      <c r="C29" s="99"/>
       <c r="D29" s="41" t="s">
         <v>32</v>
       </c>
       <c r="E29" s="37"/>
-      <c r="F29" s="111" t="s">
-        <v>7</v>
-      </c>
-      <c r="G29" s="112"/>
-      <c r="H29" s="41" t="s">
-        <v>32</v>
-      </c>
+      <c r="F29" s="98" t="s">
+        <v>16</v>
+      </c>
+      <c r="G29" s="99"/>
+      <c r="H29" s="41"/>
       <c r="I29" s="35"/>
-      <c r="J29" s="111" t="s">
-        <v>7</v>
-      </c>
-      <c r="K29" s="112"/>
-      <c r="L29" s="41" t="s">
-        <v>32</v>
-      </c>
+      <c r="J29" s="98"/>
+      <c r="K29" s="99"/>
+      <c r="L29" s="41"/>
       <c r="M29" s="5"/>
-      <c r="N29" s="111" t="s">
-        <v>16</v>
-      </c>
-      <c r="O29" s="112"/>
-      <c r="P29" s="41" t="s">
-        <v>32</v>
-      </c>
+      <c r="N29" s="98"/>
+      <c r="O29" s="99"/>
+      <c r="P29" s="41"/>
       <c r="Q29" s="35"/>
-      <c r="R29" s="111" t="s">
-        <v>7</v>
-      </c>
-      <c r="S29" s="112"/>
-      <c r="T29" s="41" t="s">
-        <v>32</v>
-      </c>
+      <c r="R29" s="98" t="s">
+        <v>19</v>
+      </c>
+      <c r="S29" s="99"/>
+      <c r="T29" s="41"/>
       <c r="U29" s="37"/>
-      <c r="V29" s="111" t="s">
-        <v>16</v>
-      </c>
-      <c r="W29" s="112"/>
-      <c r="X29" s="41" t="s">
-        <v>32</v>
-      </c>
+      <c r="V29" s="98"/>
+      <c r="W29" s="99"/>
+      <c r="X29" s="41"/>
       <c r="Y29" s="35"/>
-      <c r="Z29" s="111" t="s">
-        <v>7</v>
-      </c>
-      <c r="AA29" s="112"/>
-      <c r="AB29" s="41" t="s">
-        <v>32</v>
-      </c>
+      <c r="Z29" s="98"/>
+      <c r="AA29" s="99"/>
+      <c r="AB29" s="41"/>
       <c r="AC29" s="35"/>
-      <c r="AD29" s="111" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE29" s="112"/>
-      <c r="AF29" s="41" t="s">
-        <v>32</v>
-      </c>
+      <c r="AD29" s="98"/>
+      <c r="AE29" s="99"/>
+      <c r="AF29" s="41"/>
       <c r="AG29" s="37"/>
-      <c r="AH29" s="111" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI29" s="112"/>
+      <c r="AH29" s="98"/>
+      <c r="AI29" s="99"/>
       <c r="AJ29" s="41"/>
       <c r="AK29" s="35"/>
-      <c r="AL29" s="111"/>
-      <c r="AM29" s="112"/>
-      <c r="AN29" s="41"/>
-      <c r="AP29" s="56" t="s">
+      <c r="AL29" s="98" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM29" s="99"/>
+      <c r="AN29" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP29" s="46" t="s">
         <v>29</v>
       </c>
       <c r="AQ29" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AR29" s="30" t="s">
-        <v>40</v>
-      </c>
+      <c r="AR29" s="30"/>
     </row>
     <row r="30" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="113" t="s">
-        <v>19</v>
-      </c>
-      <c r="C30" s="114"/>
+      <c r="B30" s="100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="101"/>
       <c r="D30" s="45" t="s">
         <v>33</v>
       </c>
       <c r="E30" s="43"/>
-      <c r="F30" s="113" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="114"/>
-      <c r="H30" s="45" t="s">
-        <v>33</v>
-      </c>
+      <c r="F30" s="131"/>
+      <c r="G30" s="132"/>
+      <c r="H30" s="45"/>
       <c r="I30" s="43"/>
-      <c r="J30" s="113" t="s">
-        <v>19</v>
-      </c>
-      <c r="K30" s="114"/>
-      <c r="L30" s="45" t="s">
-        <v>33</v>
-      </c>
+      <c r="J30" s="100"/>
+      <c r="K30" s="101"/>
+      <c r="L30" s="45"/>
       <c r="M30" s="5"/>
-      <c r="N30" s="113" t="s">
-        <v>19</v>
-      </c>
-      <c r="O30" s="114"/>
-      <c r="P30" s="45" t="s">
-        <v>33</v>
-      </c>
+      <c r="N30" s="100"/>
+      <c r="O30" s="101"/>
+      <c r="P30" s="45"/>
       <c r="Q30" s="43"/>
-      <c r="R30" s="113" t="s">
-        <v>16</v>
-      </c>
-      <c r="S30" s="114"/>
-      <c r="T30" s="45" t="s">
-        <v>33</v>
-      </c>
+      <c r="R30" s="100" t="s">
+        <v>12</v>
+      </c>
+      <c r="S30" s="101"/>
+      <c r="T30" s="45"/>
       <c r="U30" s="43"/>
-      <c r="V30" s="113" t="s">
-        <v>19</v>
-      </c>
-      <c r="W30" s="114"/>
-      <c r="X30" s="45" t="s">
-        <v>33</v>
-      </c>
+      <c r="V30" s="100"/>
+      <c r="W30" s="101"/>
+      <c r="X30" s="45"/>
       <c r="Y30" s="43"/>
-      <c r="Z30" s="113" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA30" s="114"/>
-      <c r="AB30" s="45" t="s">
-        <v>33</v>
-      </c>
+      <c r="Z30" s="100"/>
+      <c r="AA30" s="101"/>
+      <c r="AB30" s="45"/>
       <c r="AC30" s="43"/>
-      <c r="AD30" s="113" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE30" s="114"/>
-      <c r="AF30" s="45" t="s">
-        <v>33</v>
-      </c>
+      <c r="AD30" s="100"/>
+      <c r="AE30" s="101"/>
+      <c r="AF30" s="45"/>
       <c r="AG30" s="43"/>
-      <c r="AH30" s="157"/>
-      <c r="AI30" s="158"/>
+      <c r="AH30" s="131"/>
+      <c r="AI30" s="132"/>
       <c r="AJ30" s="45"/>
       <c r="AK30" s="43"/>
-      <c r="AL30" s="113"/>
-      <c r="AM30" s="114"/>
-      <c r="AN30" s="45"/>
+      <c r="AL30" s="100" t="s">
+        <v>29</v>
+      </c>
+      <c r="AM30" s="101"/>
+      <c r="AN30" s="45" t="s">
+        <v>33</v>
+      </c>
       <c r="AP30" s="46" t="s">
         <v>30</v>
       </c>
@@ -4059,247 +3868,199 @@
       <c r="AR30" s="30"/>
     </row>
     <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="109" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" s="110"/>
+      <c r="B31" s="96" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="97"/>
       <c r="D31" s="45" t="s">
         <v>34</v>
       </c>
       <c r="E31" s="43"/>
-      <c r="F31" s="109" t="s">
-        <v>8</v>
-      </c>
-      <c r="G31" s="110"/>
-      <c r="H31" s="45" t="s">
-        <v>34</v>
-      </c>
+      <c r="F31" s="96"/>
+      <c r="G31" s="97"/>
+      <c r="H31" s="45"/>
       <c r="I31" s="44"/>
-      <c r="J31" s="109" t="s">
-        <v>8</v>
-      </c>
-      <c r="K31" s="110"/>
-      <c r="L31" s="45" t="s">
-        <v>34</v>
-      </c>
+      <c r="J31" s="96"/>
+      <c r="K31" s="97"/>
+      <c r="L31" s="45"/>
       <c r="M31" s="6"/>
-      <c r="N31" s="109" t="s">
-        <v>9</v>
-      </c>
-      <c r="O31" s="110"/>
-      <c r="P31" s="45" t="s">
-        <v>34</v>
-      </c>
+      <c r="N31" s="96"/>
+      <c r="O31" s="97"/>
+      <c r="P31" s="45"/>
       <c r="Q31" s="43"/>
-      <c r="R31" s="109" t="s">
-        <v>8</v>
-      </c>
-      <c r="S31" s="110"/>
-      <c r="T31" s="45" t="s">
-        <v>34</v>
-      </c>
+      <c r="R31" s="96"/>
+      <c r="S31" s="97"/>
+      <c r="T31" s="45"/>
       <c r="U31" s="44"/>
-      <c r="V31" s="109" t="s">
-        <v>11</v>
-      </c>
-      <c r="W31" s="110"/>
-      <c r="X31" s="45" t="s">
-        <v>34</v>
-      </c>
+      <c r="V31" s="96"/>
+      <c r="W31" s="97"/>
+      <c r="X31" s="45"/>
       <c r="Y31" s="43"/>
-      <c r="Z31" s="109" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA31" s="110"/>
-      <c r="AB31" s="45" t="s">
-        <v>34</v>
-      </c>
+      <c r="Z31" s="96"/>
+      <c r="AA31" s="97"/>
+      <c r="AB31" s="45"/>
       <c r="AC31" s="43"/>
-      <c r="AD31" s="109" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE31" s="110"/>
-      <c r="AF31" s="45" t="s">
-        <v>34</v>
-      </c>
+      <c r="AD31" s="96"/>
+      <c r="AE31" s="97"/>
+      <c r="AF31" s="45"/>
       <c r="AG31" s="43"/>
-      <c r="AH31" s="109"/>
-      <c r="AI31" s="110"/>
+      <c r="AH31" s="96"/>
+      <c r="AI31" s="97"/>
       <c r="AJ31" s="45"/>
       <c r="AK31" s="44"/>
-      <c r="AL31" s="109"/>
-      <c r="AM31" s="110"/>
-      <c r="AN31" s="45"/>
+      <c r="AL31" s="96" t="s">
+        <v>11</v>
+      </c>
+      <c r="AM31" s="97"/>
+      <c r="AN31" s="45" t="s">
+        <v>34</v>
+      </c>
       <c r="AP31" s="48"/>
       <c r="AQ31" s="49"/>
       <c r="AR31" s="30"/>
     </row>
     <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="109" t="s">
-        <v>21</v>
-      </c>
-      <c r="C32" s="110"/>
+      <c r="B32" s="96" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="97"/>
       <c r="D32" s="45" t="s">
         <v>35</v>
       </c>
       <c r="E32" s="44"/>
-      <c r="F32" s="109" t="s">
-        <v>21</v>
-      </c>
-      <c r="G32" s="110"/>
-      <c r="H32" s="45" t="s">
-        <v>35</v>
-      </c>
+      <c r="F32" s="96"/>
+      <c r="G32" s="97"/>
+      <c r="H32" s="45"/>
       <c r="I32" s="44"/>
-      <c r="J32" s="109" t="s">
-        <v>21</v>
-      </c>
-      <c r="K32" s="110"/>
-      <c r="L32" s="45" t="s">
-        <v>35</v>
-      </c>
+      <c r="J32" s="96"/>
+      <c r="K32" s="97"/>
+      <c r="L32" s="45"/>
       <c r="M32" s="5"/>
-      <c r="N32" s="109" t="s">
-        <v>14</v>
-      </c>
-      <c r="O32" s="110"/>
-      <c r="P32" s="45" t="s">
-        <v>35</v>
-      </c>
+      <c r="N32" s="96"/>
+      <c r="O32" s="97"/>
+      <c r="P32" s="45"/>
       <c r="Q32" s="44"/>
-      <c r="R32" s="109" t="s">
-        <v>21</v>
-      </c>
-      <c r="S32" s="110"/>
-      <c r="T32" s="45" t="s">
-        <v>35</v>
-      </c>
+      <c r="R32" s="96"/>
+      <c r="S32" s="97"/>
+      <c r="T32" s="45"/>
       <c r="U32" s="44"/>
-      <c r="V32" s="109" t="s">
-        <v>21</v>
-      </c>
-      <c r="W32" s="110"/>
-      <c r="X32" s="45" t="s">
-        <v>35</v>
-      </c>
+      <c r="V32" s="96"/>
+      <c r="W32" s="97"/>
+      <c r="X32" s="45"/>
       <c r="Y32" s="44"/>
-      <c r="Z32" s="109" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA32" s="110"/>
-      <c r="AB32" s="45" t="s">
-        <v>35</v>
-      </c>
+      <c r="Z32" s="96"/>
+      <c r="AA32" s="97"/>
+      <c r="AB32" s="45"/>
       <c r="AC32" s="44"/>
-      <c r="AD32" s="109" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE32" s="110"/>
-      <c r="AF32" s="45" t="s">
-        <v>35</v>
-      </c>
+      <c r="AD32" s="96"/>
+      <c r="AE32" s="97"/>
+      <c r="AF32" s="45"/>
       <c r="AG32" s="44"/>
-      <c r="AH32" s="109"/>
-      <c r="AI32" s="110"/>
+      <c r="AH32" s="96"/>
+      <c r="AI32" s="97"/>
       <c r="AJ32" s="45"/>
       <c r="AK32" s="44"/>
-      <c r="AL32" s="109"/>
-      <c r="AM32" s="110"/>
-      <c r="AN32" s="45"/>
+      <c r="AL32" s="96" t="s">
+        <v>20</v>
+      </c>
+      <c r="AM32" s="97"/>
+      <c r="AN32" s="45" t="s">
+        <v>35</v>
+      </c>
       <c r="AP32" s="51"/>
       <c r="AQ32" s="52"/>
       <c r="AR32" s="30"/>
     </row>
     <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="109" t="s">
-        <v>14</v>
-      </c>
-      <c r="C33" s="110"/>
+      <c r="B33" s="96" t="s">
+        <v>21</v>
+      </c>
+      <c r="C33" s="97"/>
       <c r="D33" s="45" t="s">
         <v>35</v>
       </c>
       <c r="E33" s="44"/>
-      <c r="F33" s="109"/>
-      <c r="G33" s="110"/>
+      <c r="F33" s="96"/>
+      <c r="G33" s="97"/>
       <c r="H33" s="45"/>
       <c r="I33" s="44"/>
-      <c r="J33" s="109"/>
-      <c r="K33" s="110"/>
+      <c r="J33" s="96"/>
+      <c r="K33" s="97"/>
       <c r="L33" s="45"/>
       <c r="M33" s="5"/>
-      <c r="N33" s="109"/>
-      <c r="O33" s="110"/>
+      <c r="N33" s="96"/>
+      <c r="O33" s="97"/>
       <c r="P33" s="45"/>
       <c r="Q33" s="44"/>
-      <c r="R33" s="109"/>
-      <c r="S33" s="110"/>
+      <c r="R33" s="96"/>
+      <c r="S33" s="97"/>
       <c r="T33" s="45"/>
       <c r="U33" s="44"/>
-      <c r="V33" s="109"/>
-      <c r="W33" s="110"/>
+      <c r="V33" s="96"/>
+      <c r="W33" s="97"/>
       <c r="X33" s="45"/>
       <c r="Y33" s="44"/>
-      <c r="Z33" s="109"/>
-      <c r="AA33" s="110"/>
+      <c r="Z33" s="96"/>
+      <c r="AA33" s="97"/>
       <c r="AB33" s="45"/>
       <c r="AC33" s="44"/>
-      <c r="AD33" s="109" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE33" s="110"/>
-      <c r="AF33" s="45" t="s">
-        <v>35</v>
-      </c>
+      <c r="AD33" s="96"/>
+      <c r="AE33" s="97"/>
+      <c r="AF33" s="45"/>
       <c r="AG33" s="44"/>
-      <c r="AH33" s="109"/>
-      <c r="AI33" s="110"/>
+      <c r="AH33" s="96"/>
+      <c r="AI33" s="97"/>
       <c r="AJ33" s="45"/>
       <c r="AK33" s="44"/>
-      <c r="AL33" s="109"/>
-      <c r="AM33" s="110"/>
-      <c r="AN33" s="45"/>
+      <c r="AL33" s="96" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM33" s="97"/>
+      <c r="AN33" s="45" t="s">
+        <v>35</v>
+      </c>
       <c r="AR33" s="13"/>
     </row>
     <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="12"/>
-      <c r="B34" s="151"/>
-      <c r="C34" s="152"/>
+      <c r="B34" s="129"/>
+      <c r="C34" s="130"/>
       <c r="D34" s="42"/>
       <c r="E34" s="44"/>
-      <c r="F34" s="151"/>
-      <c r="G34" s="152"/>
+      <c r="F34" s="129"/>
+      <c r="G34" s="130"/>
       <c r="H34" s="42"/>
       <c r="I34" s="44"/>
-      <c r="J34" s="151"/>
-      <c r="K34" s="152"/>
+      <c r="J34" s="129"/>
+      <c r="K34" s="130"/>
       <c r="L34" s="42"/>
       <c r="M34" s="2"/>
-      <c r="N34" s="151"/>
-      <c r="O34" s="152"/>
+      <c r="N34" s="129"/>
+      <c r="O34" s="130"/>
       <c r="P34" s="42"/>
       <c r="Q34" s="44"/>
-      <c r="R34" s="151"/>
-      <c r="S34" s="152"/>
+      <c r="R34" s="129"/>
+      <c r="S34" s="130"/>
       <c r="T34" s="42"/>
       <c r="U34" s="44"/>
-      <c r="V34" s="151"/>
-      <c r="W34" s="152"/>
+      <c r="V34" s="129"/>
+      <c r="W34" s="130"/>
       <c r="X34" s="42"/>
       <c r="Y34" s="44"/>
-      <c r="Z34" s="151"/>
-      <c r="AA34" s="152"/>
+      <c r="Z34" s="129"/>
+      <c r="AA34" s="130"/>
       <c r="AB34" s="42"/>
       <c r="AC34" s="44"/>
-      <c r="AD34" s="151"/>
-      <c r="AE34" s="152"/>
+      <c r="AD34" s="129"/>
+      <c r="AE34" s="130"/>
       <c r="AF34" s="42"/>
       <c r="AG34" s="44"/>
-      <c r="AH34" s="151"/>
-      <c r="AI34" s="152"/>
+      <c r="AH34" s="129"/>
+      <c r="AI34" s="130"/>
       <c r="AJ34" s="42"/>
       <c r="AK34" s="44"/>
-      <c r="AL34" s="151"/>
-      <c r="AM34" s="152"/>
+      <c r="AL34" s="129"/>
+      <c r="AM34" s="130"/>
       <c r="AN34" s="42"/>
       <c r="AO34" s="12"/>
       <c r="AP34" s="12"/>
@@ -4365,23 +4126,23 @@
       <c r="K36" s="33"/>
       <c r="L36" s="33"/>
       <c r="M36" s="4"/>
-      <c r="N36" s="115" t="s">
+      <c r="N36" s="102" t="s">
         <v>36</v>
       </c>
-      <c r="O36" s="115"/>
-      <c r="P36" s="115"/>
-      <c r="Q36" s="115"/>
-      <c r="R36" s="115"/>
-      <c r="S36" s="115"/>
-      <c r="T36" s="115"/>
-      <c r="U36" s="115"/>
-      <c r="V36" s="115"/>
-      <c r="W36" s="115"/>
-      <c r="X36" s="115"/>
-      <c r="Y36" s="115"/>
-      <c r="Z36" s="115"/>
-      <c r="AA36" s="115"/>
-      <c r="AB36" s="115"/>
+      <c r="O36" s="102"/>
+      <c r="P36" s="102"/>
+      <c r="Q36" s="102"/>
+      <c r="R36" s="102"/>
+      <c r="S36" s="102"/>
+      <c r="T36" s="102"/>
+      <c r="U36" s="102"/>
+      <c r="V36" s="102"/>
+      <c r="W36" s="102"/>
+      <c r="X36" s="102"/>
+      <c r="Y36" s="102"/>
+      <c r="Z36" s="102"/>
+      <c r="AA36" s="102"/>
+      <c r="AB36" s="102"/>
       <c r="AC36" s="33"/>
       <c r="AD36" s="33"/>
       <c r="AE36" s="33"/>
@@ -4413,21 +4174,21 @@
       <c r="K37" s="33"/>
       <c r="L37" s="33"/>
       <c r="M37" s="5"/>
-      <c r="N37" s="115"/>
-      <c r="O37" s="115"/>
-      <c r="P37" s="115"/>
-      <c r="Q37" s="115"/>
-      <c r="R37" s="115"/>
-      <c r="S37" s="115"/>
-      <c r="T37" s="115"/>
-      <c r="U37" s="115"/>
-      <c r="V37" s="115"/>
-      <c r="W37" s="115"/>
-      <c r="X37" s="115"/>
-      <c r="Y37" s="115"/>
-      <c r="Z37" s="115"/>
-      <c r="AA37" s="115"/>
-      <c r="AB37" s="115"/>
+      <c r="N37" s="102"/>
+      <c r="O37" s="102"/>
+      <c r="P37" s="102"/>
+      <c r="Q37" s="102"/>
+      <c r="R37" s="102"/>
+      <c r="S37" s="102"/>
+      <c r="T37" s="102"/>
+      <c r="U37" s="102"/>
+      <c r="V37" s="102"/>
+      <c r="W37" s="102"/>
+      <c r="X37" s="102"/>
+      <c r="Y37" s="102"/>
+      <c r="Z37" s="102"/>
+      <c r="AA37" s="102"/>
+      <c r="AB37" s="102"/>
       <c r="AC37" s="33"/>
       <c r="AD37" s="33"/>
       <c r="AE37" s="33"/>
@@ -4447,76 +4208,74 @@
     </row>
     <row r="38" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="12"/>
-      <c r="B38" s="81" t="s">
-        <v>90</v>
-      </c>
-      <c r="C38" s="82"/>
-      <c r="D38" s="55" t="s">
-        <v>77</v>
-      </c>
+      <c r="B38" s="79" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" s="80"/>
+      <c r="D38" s="55"/>
       <c r="E38" s="36"/>
-      <c r="F38" s="81" t="s">
+      <c r="F38" s="79" t="s">
         <v>91</v>
       </c>
-      <c r="G38" s="82"/>
+      <c r="G38" s="80"/>
       <c r="H38" s="55" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I38" s="36"/>
-      <c r="J38" s="81" t="s">
-        <v>92</v>
-      </c>
-      <c r="K38" s="82"/>
-      <c r="L38" s="55" t="s">
-        <v>93</v>
+      <c r="J38" s="92" t="s">
+        <v>62</v>
+      </c>
+      <c r="K38" s="93"/>
+      <c r="L38" s="59" t="s">
+        <v>53</v>
       </c>
       <c r="M38" s="5"/>
-      <c r="N38" s="70" t="s">
-        <v>69</v>
-      </c>
-      <c r="O38" s="71"/>
-      <c r="P38" s="34"/>
+      <c r="N38" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="O38" s="75"/>
+      <c r="P38" s="34" t="s">
+        <v>52</v>
+      </c>
       <c r="Q38" s="36"/>
-      <c r="R38" s="70" t="s">
-        <v>69</v>
-      </c>
-      <c r="S38" s="71"/>
+      <c r="R38" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="S38" s="75"/>
       <c r="T38" s="34" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="U38" s="36"/>
-      <c r="V38" s="70" t="s">
-        <v>70</v>
-      </c>
-      <c r="W38" s="71"/>
+      <c r="V38" s="74" t="s">
+        <v>61</v>
+      </c>
+      <c r="W38" s="75"/>
       <c r="X38" s="34" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="Y38" s="36"/>
-      <c r="Z38" s="70"/>
-      <c r="AA38" s="71"/>
+      <c r="Z38" s="74"/>
+      <c r="AA38" s="75"/>
       <c r="AB38" s="34"/>
       <c r="AC38" s="36"/>
-      <c r="AD38" s="70" t="s">
-        <v>71</v>
-      </c>
-      <c r="AE38" s="71"/>
+      <c r="AD38" s="74"/>
+      <c r="AE38" s="75"/>
       <c r="AF38" s="34"/>
       <c r="AG38" s="36"/>
-      <c r="AH38" s="70" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI38" s="71"/>
+      <c r="AH38" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI38" s="75"/>
       <c r="AJ38" s="34" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="AK38" s="36"/>
-      <c r="AL38" s="98" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM38" s="99"/>
-      <c r="AN38" s="59" t="s">
-        <v>55</v>
+      <c r="AL38" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="AM38" s="75"/>
+      <c r="AN38" s="34" t="s">
+        <v>70</v>
       </c>
       <c r="AO38" s="31"/>
       <c r="AP38" s="31"/>
@@ -4525,63 +4284,61 @@
     </row>
     <row r="39" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="12"/>
-      <c r="B39" s="62" t="s">
-        <v>51</v>
-      </c>
-      <c r="C39" s="63"/>
-      <c r="D39" s="64"/>
+      <c r="B39" s="84" t="s">
+        <v>93</v>
+      </c>
+      <c r="C39" s="85"/>
+      <c r="D39" s="86"/>
       <c r="E39" s="36"/>
-      <c r="F39" s="62" t="s">
-        <v>94</v>
-      </c>
-      <c r="G39" s="63"/>
-      <c r="H39" s="64"/>
+      <c r="F39" s="84" t="s">
+        <v>93</v>
+      </c>
+      <c r="G39" s="85"/>
+      <c r="H39" s="86"/>
       <c r="I39" s="36"/>
-      <c r="J39" s="62" t="s">
-        <v>95</v>
-      </c>
-      <c r="K39" s="63"/>
-      <c r="L39" s="64"/>
+      <c r="J39" s="136" t="s">
+        <v>63</v>
+      </c>
+      <c r="K39" s="137"/>
+      <c r="L39" s="138"/>
       <c r="M39" s="5"/>
-      <c r="N39" s="72" t="s">
-        <v>68</v>
-      </c>
-      <c r="O39" s="73"/>
-      <c r="P39" s="74"/>
+      <c r="N39" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="O39" s="66"/>
+      <c r="P39" s="67"/>
       <c r="Q39" s="36"/>
-      <c r="R39" s="72" t="s">
-        <v>68</v>
-      </c>
-      <c r="S39" s="73"/>
-      <c r="T39" s="74"/>
+      <c r="R39" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="S39" s="66"/>
+      <c r="T39" s="67"/>
       <c r="U39" s="36"/>
-      <c r="V39" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="W39" s="73"/>
-      <c r="X39" s="74"/>
+      <c r="V39" s="65" t="s">
+        <v>60</v>
+      </c>
+      <c r="W39" s="66"/>
+      <c r="X39" s="67"/>
       <c r="Y39" s="37"/>
-      <c r="Z39" s="72"/>
-      <c r="AA39" s="73"/>
-      <c r="AB39" s="74"/>
+      <c r="Z39" s="65"/>
+      <c r="AA39" s="66"/>
+      <c r="AB39" s="67"/>
       <c r="AC39" s="36"/>
-      <c r="AD39" s="72" t="s">
-        <v>74</v>
-      </c>
-      <c r="AE39" s="73"/>
-      <c r="AF39" s="74"/>
+      <c r="AD39" s="65"/>
+      <c r="AE39" s="66"/>
+      <c r="AF39" s="67"/>
       <c r="AG39" s="36"/>
-      <c r="AH39" s="72" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI39" s="73"/>
-      <c r="AJ39" s="74"/>
+      <c r="AH39" s="65" t="s">
+        <v>71</v>
+      </c>
+      <c r="AI39" s="66"/>
+      <c r="AJ39" s="67"/>
       <c r="AK39" s="36"/>
-      <c r="AL39" s="100" t="s">
-        <v>75</v>
-      </c>
-      <c r="AM39" s="101"/>
-      <c r="AN39" s="102"/>
+      <c r="AL39" s="65" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM39" s="66"/>
+      <c r="AN39" s="67"/>
       <c r="AO39" s="31"/>
       <c r="AP39" s="31"/>
       <c r="AQ39" s="31"/>
@@ -4589,51 +4346,51 @@
     </row>
     <row r="40" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="12"/>
-      <c r="B40" s="78"/>
-      <c r="C40" s="79"/>
-      <c r="D40" s="80"/>
+      <c r="B40" s="81" t="s">
+        <v>94</v>
+      </c>
+      <c r="C40" s="82"/>
+      <c r="D40" s="83"/>
       <c r="E40" s="43"/>
-      <c r="F40" s="78"/>
-      <c r="G40" s="79"/>
-      <c r="H40" s="80"/>
+      <c r="F40" s="81"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="83"/>
       <c r="I40" s="43"/>
-      <c r="J40" s="78"/>
-      <c r="K40" s="79"/>
-      <c r="L40" s="80"/>
+      <c r="J40" s="114" t="s">
+        <v>85</v>
+      </c>
+      <c r="K40" s="115"/>
+      <c r="L40" s="140"/>
       <c r="M40" s="4"/>
-      <c r="N40" s="75" t="s">
-        <v>42</v>
-      </c>
-      <c r="O40" s="76"/>
-      <c r="P40" s="77"/>
+      <c r="N40" s="71"/>
+      <c r="O40" s="72"/>
+      <c r="P40" s="73"/>
       <c r="Q40" s="43"/>
-      <c r="R40" s="75"/>
-      <c r="S40" s="76"/>
-      <c r="T40" s="77"/>
+      <c r="R40" s="71"/>
+      <c r="S40" s="72"/>
+      <c r="T40" s="73"/>
       <c r="U40" s="35"/>
-      <c r="V40" s="75"/>
-      <c r="W40" s="76"/>
-      <c r="X40" s="77"/>
+      <c r="V40" s="71" t="s">
+        <v>74</v>
+      </c>
+      <c r="W40" s="72"/>
+      <c r="X40" s="73"/>
       <c r="Y40" s="36"/>
-      <c r="Z40" s="75"/>
-      <c r="AA40" s="76"/>
-      <c r="AB40" s="77"/>
+      <c r="Z40" s="71"/>
+      <c r="AA40" s="72"/>
+      <c r="AB40" s="73"/>
       <c r="AC40" s="36"/>
-      <c r="AD40" s="75" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE40" s="76"/>
-      <c r="AF40" s="77"/>
+      <c r="AD40" s="71"/>
+      <c r="AE40" s="72"/>
+      <c r="AF40" s="73"/>
       <c r="AG40" s="43"/>
-      <c r="AH40" s="75"/>
-      <c r="AI40" s="76"/>
-      <c r="AJ40" s="77"/>
+      <c r="AH40" s="71"/>
+      <c r="AI40" s="72"/>
+      <c r="AJ40" s="73"/>
       <c r="AK40" s="43"/>
-      <c r="AL40" s="127" t="s">
-        <v>86</v>
-      </c>
-      <c r="AM40" s="128"/>
-      <c r="AN40" s="153"/>
+      <c r="AL40" s="71"/>
+      <c r="AM40" s="72"/>
+      <c r="AN40" s="73"/>
       <c r="AO40" s="31"/>
       <c r="AP40" s="31"/>
       <c r="AQ40" s="31"/>
@@ -4641,63 +4398,61 @@
     </row>
     <row r="41" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12"/>
-      <c r="B41" s="67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" s="68"/>
-      <c r="D41" s="69"/>
+      <c r="B41" s="141" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="142"/>
+      <c r="D41" s="143"/>
       <c r="E41" s="37"/>
-      <c r="F41" s="159" t="s">
-        <v>96</v>
-      </c>
-      <c r="G41" s="160"/>
-      <c r="H41" s="161"/>
+      <c r="F41" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="G41" s="69"/>
+      <c r="H41" s="70"/>
       <c r="I41" s="31"/>
-      <c r="J41" s="67" t="s">
+      <c r="J41" s="121" t="s">
+        <v>95</v>
+      </c>
+      <c r="K41" s="122"/>
+      <c r="L41" s="123"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="O41" s="69"/>
+      <c r="P41" s="70"/>
+      <c r="Q41" s="32"/>
+      <c r="R41" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="S41" s="69"/>
+      <c r="T41" s="70"/>
+      <c r="U41" s="31"/>
+      <c r="V41" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="K41" s="68"/>
-      <c r="L41" s="69"/>
-      <c r="M41" s="5"/>
-      <c r="N41" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="O41" s="68"/>
-      <c r="P41" s="69"/>
-      <c r="Q41" s="32"/>
-      <c r="R41" s="67" t="s">
+      <c r="W41" s="69"/>
+      <c r="X41" s="70"/>
+      <c r="Y41" s="32"/>
+      <c r="Z41" s="68"/>
+      <c r="AA41" s="69"/>
+      <c r="AB41" s="70"/>
+      <c r="AC41" s="32"/>
+      <c r="AD41" s="68"/>
+      <c r="AE41" s="69"/>
+      <c r="AF41" s="70"/>
+      <c r="AG41" s="37"/>
+      <c r="AH41" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="S41" s="68"/>
-      <c r="T41" s="69"/>
-      <c r="U41" s="31"/>
-      <c r="V41" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="W41" s="68"/>
-      <c r="X41" s="69"/>
-      <c r="Y41" s="32"/>
-      <c r="Z41" s="67"/>
-      <c r="AA41" s="68"/>
-      <c r="AB41" s="69"/>
-      <c r="AC41" s="32"/>
-      <c r="AD41" s="148" t="s">
-        <v>24</v>
-      </c>
-      <c r="AE41" s="149"/>
-      <c r="AF41" s="150"/>
-      <c r="AG41" s="37"/>
-      <c r="AH41" s="67" t="s">
-        <v>24</v>
-      </c>
-      <c r="AI41" s="68"/>
-      <c r="AJ41" s="69"/>
+      <c r="AI41" s="69"/>
+      <c r="AJ41" s="70"/>
       <c r="AK41" s="31"/>
-      <c r="AL41" s="134" t="s">
-        <v>96</v>
-      </c>
-      <c r="AM41" s="135"/>
-      <c r="AN41" s="136"/>
+      <c r="AL41" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="AM41" s="69"/>
+      <c r="AN41" s="70"/>
       <c r="AO41" s="31"/>
       <c r="AP41" s="31"/>
       <c r="AQ41" s="31"/>
@@ -4705,63 +4460,61 @@
     </row>
     <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12"/>
-      <c r="B42" s="67" t="s">
-        <v>11</v>
-      </c>
-      <c r="C42" s="68"/>
-      <c r="D42" s="69"/>
+      <c r="B42" s="68" t="s">
+        <v>25</v>
+      </c>
+      <c r="C42" s="69"/>
+      <c r="D42" s="70"/>
       <c r="E42" s="44"/>
-      <c r="F42" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="G42" s="68"/>
-      <c r="H42" s="69"/>
+      <c r="F42" s="68" t="s">
+        <v>25</v>
+      </c>
+      <c r="G42" s="69"/>
+      <c r="H42" s="70"/>
       <c r="I42" s="31"/>
-      <c r="J42" s="67" t="s">
+      <c r="J42" s="121" t="s">
+        <v>96</v>
+      </c>
+      <c r="K42" s="122"/>
+      <c r="L42" s="123"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="O42" s="69"/>
+      <c r="P42" s="70"/>
+      <c r="Q42" s="31"/>
+      <c r="R42" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="S42" s="69"/>
+      <c r="T42" s="70"/>
+      <c r="U42" s="32"/>
+      <c r="V42" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="W42" s="69"/>
+      <c r="X42" s="70"/>
+      <c r="Y42" s="32"/>
+      <c r="Z42" s="68"/>
+      <c r="AA42" s="69"/>
+      <c r="AB42" s="70"/>
+      <c r="AC42" s="32"/>
+      <c r="AD42" s="68"/>
+      <c r="AE42" s="69"/>
+      <c r="AF42" s="70"/>
+      <c r="AG42" s="44"/>
+      <c r="AH42" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="K42" s="68"/>
-      <c r="L42" s="69"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="67" t="s">
-        <v>26</v>
-      </c>
-      <c r="O42" s="68"/>
-      <c r="P42" s="69"/>
-      <c r="Q42" s="31"/>
-      <c r="R42" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="S42" s="68"/>
-      <c r="T42" s="69"/>
-      <c r="U42" s="32"/>
-      <c r="V42" s="67" t="s">
-        <v>15</v>
-      </c>
-      <c r="W42" s="68"/>
-      <c r="X42" s="69"/>
-      <c r="Y42" s="32"/>
-      <c r="Z42" s="67"/>
-      <c r="AA42" s="68"/>
-      <c r="AB42" s="69"/>
-      <c r="AC42" s="32"/>
-      <c r="AD42" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE42" s="68"/>
-      <c r="AF42" s="69"/>
-      <c r="AG42" s="44"/>
-      <c r="AH42" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="AI42" s="68"/>
-      <c r="AJ42" s="69"/>
+      <c r="AI42" s="69"/>
+      <c r="AJ42" s="70"/>
       <c r="AK42" s="31"/>
-      <c r="AL42" s="134" t="s">
-        <v>88</v>
-      </c>
-      <c r="AM42" s="135"/>
-      <c r="AN42" s="136"/>
+      <c r="AL42" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM42" s="69"/>
+      <c r="AN42" s="70"/>
       <c r="AO42" s="31"/>
       <c r="AP42" s="31"/>
       <c r="AQ42" s="31"/>
@@ -4769,55 +4522,51 @@
     </row>
     <row r="43" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="12"/>
-      <c r="B43" s="83"/>
-      <c r="C43" s="84"/>
-      <c r="D43" s="85"/>
+      <c r="B43" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="69"/>
+      <c r="D43" s="70"/>
       <c r="E43" s="35"/>
-      <c r="F43" s="83" t="s">
-        <v>12</v>
-      </c>
-      <c r="G43" s="84"/>
-      <c r="H43" s="85"/>
+      <c r="F43" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" s="69"/>
+      <c r="H43" s="70"/>
       <c r="I43" s="40"/>
-      <c r="J43" s="83"/>
-      <c r="K43" s="84"/>
-      <c r="L43" s="85"/>
+      <c r="J43" s="124"/>
+      <c r="K43" s="125"/>
+      <c r="L43" s="126"/>
       <c r="M43" s="14"/>
-      <c r="N43" s="67" t="s">
-        <v>27</v>
-      </c>
-      <c r="O43" s="68"/>
-      <c r="P43" s="69"/>
+      <c r="N43" s="62"/>
+      <c r="O43" s="63"/>
+      <c r="P43" s="64"/>
       <c r="Q43" s="40"/>
-      <c r="R43" s="67" t="s">
-        <v>26</v>
-      </c>
-      <c r="S43" s="68"/>
-      <c r="T43" s="69"/>
+      <c r="R43" s="62"/>
+      <c r="S43" s="63"/>
+      <c r="T43" s="64"/>
       <c r="U43" s="40"/>
-      <c r="V43" s="83"/>
-      <c r="W43" s="84"/>
-      <c r="X43" s="85"/>
+      <c r="V43" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="W43" s="69"/>
+      <c r="X43" s="70"/>
       <c r="Y43" s="40"/>
-      <c r="Z43" s="83"/>
-      <c r="AA43" s="84"/>
-      <c r="AB43" s="85"/>
+      <c r="Z43" s="62"/>
+      <c r="AA43" s="63"/>
+      <c r="AB43" s="64"/>
       <c r="AC43" s="40"/>
-      <c r="AD43" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE43" s="68"/>
-      <c r="AF43" s="69"/>
+      <c r="AD43" s="62"/>
+      <c r="AE43" s="63"/>
+      <c r="AF43" s="64"/>
       <c r="AG43" s="35"/>
-      <c r="AH43" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI43" s="68"/>
-      <c r="AJ43" s="69"/>
+      <c r="AH43" s="62"/>
+      <c r="AI43" s="63"/>
+      <c r="AJ43" s="64"/>
       <c r="AK43" s="40"/>
-      <c r="AL43" s="92"/>
-      <c r="AM43" s="93"/>
-      <c r="AN43" s="94"/>
+      <c r="AL43" s="62"/>
+      <c r="AM43" s="63"/>
+      <c r="AN43" s="64"/>
       <c r="AO43" s="31"/>
       <c r="AP43" s="31"/>
       <c r="AQ43" s="31"/>
@@ -4825,47 +4574,47 @@
     </row>
     <row r="44" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="12"/>
-      <c r="B44" s="35"/>
-      <c r="C44" s="35"/>
-      <c r="D44" s="35"/>
+      <c r="B44" s="62" t="s">
+        <v>27</v>
+      </c>
+      <c r="C44" s="63"/>
+      <c r="D44" s="64"/>
       <c r="E44" s="50"/>
-      <c r="F44" s="35"/>
-      <c r="G44" s="35"/>
-      <c r="H44" s="35"/>
+      <c r="F44" s="62" t="s">
+        <v>27</v>
+      </c>
+      <c r="G44" s="63"/>
+      <c r="H44" s="64"/>
       <c r="I44" s="32"/>
       <c r="J44" s="35"/>
       <c r="K44" s="35"/>
       <c r="L44" s="35"/>
       <c r="M44" s="14"/>
-      <c r="N44" s="67"/>
-      <c r="O44" s="68"/>
-      <c r="P44" s="69"/>
+      <c r="N44" s="35"/>
+      <c r="O44" s="35"/>
+      <c r="P44" s="35"/>
       <c r="Q44" s="36"/>
-      <c r="R44" s="67" t="s">
-        <v>27</v>
-      </c>
-      <c r="S44" s="68"/>
-      <c r="T44" s="69"/>
+      <c r="R44" s="35"/>
+      <c r="S44" s="35"/>
+      <c r="T44" s="35"/>
       <c r="U44" s="50"/>
-      <c r="V44" s="35"/>
-      <c r="W44" s="35"/>
-      <c r="X44" s="35"/>
+      <c r="V44" s="62" t="s">
+        <v>13</v>
+      </c>
+      <c r="W44" s="63"/>
+      <c r="X44" s="64"/>
       <c r="Y44" s="32"/>
       <c r="Z44" s="35"/>
       <c r="AA44" s="35"/>
       <c r="AB44" s="35"/>
       <c r="AC44" s="36"/>
-      <c r="AD44" s="83" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE44" s="84"/>
-      <c r="AF44" s="85"/>
+      <c r="AD44" s="35"/>
+      <c r="AE44" s="35"/>
+      <c r="AF44" s="35"/>
       <c r="AG44" s="50"/>
-      <c r="AH44" s="83" t="s">
-        <v>27</v>
-      </c>
-      <c r="AI44" s="84"/>
-      <c r="AJ44" s="85"/>
+      <c r="AH44" s="35"/>
+      <c r="AI44" s="35"/>
+      <c r="AJ44" s="35"/>
       <c r="AK44" s="32"/>
       <c r="AL44" s="35"/>
       <c r="AM44" s="35"/>
@@ -4875,69 +4624,59 @@
       <c r="AQ44" s="31"/>
       <c r="AR44" s="13"/>
     </row>
-    <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="12"/>
-      <c r="B45" s="81" t="s">
-        <v>91</v>
-      </c>
-      <c r="C45" s="82"/>
-      <c r="D45" s="55" t="s">
-        <v>54</v>
-      </c>
+      <c r="B45" s="35"/>
+      <c r="C45" s="35"/>
+      <c r="D45" s="35"/>
       <c r="E45" s="36"/>
-      <c r="F45" s="81" t="s">
-        <v>91</v>
-      </c>
-      <c r="G45" s="82"/>
-      <c r="H45" s="55" t="s">
-        <v>43</v>
-      </c>
+      <c r="F45" s="35"/>
+      <c r="G45" s="35"/>
+      <c r="H45" s="35"/>
       <c r="I45" s="32"/>
-      <c r="J45" s="81" t="s">
-        <v>91</v>
-      </c>
-      <c r="K45" s="82"/>
+      <c r="J45" s="79" t="s">
+        <v>62</v>
+      </c>
+      <c r="K45" s="80"/>
       <c r="L45" s="55" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="M45" s="14"/>
-      <c r="N45" s="83"/>
-      <c r="O45" s="84"/>
-      <c r="P45" s="85"/>
+      <c r="N45" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="O45" s="75"/>
+      <c r="P45" s="34" t="s">
+        <v>70</v>
+      </c>
       <c r="Q45" s="36"/>
-      <c r="R45" s="83" t="s">
-        <v>14</v>
-      </c>
-      <c r="S45" s="84"/>
-      <c r="T45" s="85"/>
+      <c r="R45" s="74" t="s">
+        <v>68</v>
+      </c>
+      <c r="S45" s="75"/>
+      <c r="T45" s="34" t="s">
+        <v>42</v>
+      </c>
       <c r="U45" s="36"/>
-      <c r="V45" s="70" t="s">
-        <v>62</v>
-      </c>
-      <c r="W45" s="71"/>
-      <c r="X45" s="34" t="s">
-        <v>83</v>
-      </c>
+      <c r="V45" s="35"/>
+      <c r="W45" s="35"/>
+      <c r="X45" s="58"/>
       <c r="Y45" s="36"/>
-      <c r="Z45" s="70"/>
-      <c r="AA45" s="71"/>
+      <c r="Z45" s="74"/>
+      <c r="AA45" s="75"/>
       <c r="AB45" s="34"/>
       <c r="AC45" s="36"/>
-      <c r="AD45" s="35"/>
-      <c r="AE45" s="35"/>
-      <c r="AF45" s="35"/>
+      <c r="AD45" s="74"/>
+      <c r="AE45" s="75"/>
+      <c r="AF45" s="34"/>
       <c r="AG45" s="36"/>
-      <c r="AH45" s="35"/>
-      <c r="AI45" s="35"/>
-      <c r="AJ45" s="35"/>
+      <c r="AH45" s="74"/>
+      <c r="AI45" s="75"/>
+      <c r="AJ45" s="34"/>
       <c r="AK45" s="32"/>
-      <c r="AL45" s="70" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM45" s="71"/>
-      <c r="AN45" s="34" t="s">
-        <v>54</v>
-      </c>
+      <c r="AL45" s="74"/>
+      <c r="AM45" s="75"/>
+      <c r="AN45" s="34"/>
       <c r="AO45" s="31"/>
       <c r="AP45" s="31"/>
       <c r="AQ45" s="31"/>
@@ -4945,55 +4684,51 @@
     </row>
     <row r="46" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="12"/>
-      <c r="B46" s="62" t="s">
-        <v>97</v>
-      </c>
-      <c r="C46" s="63"/>
-      <c r="D46" s="64"/>
+      <c r="B46" s="79"/>
+      <c r="C46" s="80"/>
+      <c r="D46" s="55"/>
       <c r="E46" s="36"/>
-      <c r="F46" s="62" t="s">
-        <v>98</v>
-      </c>
-      <c r="G46" s="63"/>
-      <c r="H46" s="64"/>
+      <c r="F46" s="79"/>
+      <c r="G46" s="80"/>
+      <c r="H46" s="55"/>
       <c r="I46" s="54"/>
-      <c r="J46" s="62" t="s">
-        <v>99</v>
-      </c>
-      <c r="K46" s="63"/>
-      <c r="L46" s="64"/>
+      <c r="J46" s="84" t="s">
+        <v>50</v>
+      </c>
+      <c r="K46" s="85"/>
+      <c r="L46" s="86"/>
       <c r="M46" s="4"/>
-      <c r="N46" s="35"/>
-      <c r="O46" s="35"/>
-      <c r="P46" s="58"/>
+      <c r="N46" s="65" t="s">
+        <v>63</v>
+      </c>
+      <c r="O46" s="66"/>
+      <c r="P46" s="67"/>
       <c r="Q46" s="35"/>
-      <c r="R46" s="35"/>
-      <c r="S46" s="35"/>
-      <c r="T46" s="58"/>
+      <c r="R46" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="S46" s="66"/>
+      <c r="T46" s="67"/>
       <c r="U46" s="36"/>
-      <c r="V46" s="72" t="s">
-        <v>63</v>
-      </c>
-      <c r="W46" s="73"/>
-      <c r="X46" s="74"/>
+      <c r="V46" s="74"/>
+      <c r="W46" s="75"/>
+      <c r="X46" s="34"/>
       <c r="Y46" s="36"/>
-      <c r="Z46" s="72"/>
-      <c r="AA46" s="73"/>
-      <c r="AB46" s="74"/>
+      <c r="Z46" s="65"/>
+      <c r="AA46" s="66"/>
+      <c r="AB46" s="67"/>
       <c r="AC46" s="36"/>
-      <c r="AD46" s="70"/>
-      <c r="AE46" s="71"/>
-      <c r="AF46" s="34"/>
+      <c r="AD46" s="65"/>
+      <c r="AE46" s="66"/>
+      <c r="AF46" s="67"/>
       <c r="AG46" s="36"/>
-      <c r="AH46" s="70"/>
-      <c r="AI46" s="71"/>
-      <c r="AJ46" s="34"/>
+      <c r="AH46" s="65"/>
+      <c r="AI46" s="66"/>
+      <c r="AJ46" s="67"/>
       <c r="AK46" s="54"/>
-      <c r="AL46" s="72" t="s">
-        <v>51</v>
-      </c>
-      <c r="AM46" s="73"/>
-      <c r="AN46" s="74"/>
+      <c r="AL46" s="65"/>
+      <c r="AM46" s="66"/>
+      <c r="AN46" s="67"/>
       <c r="AO46" s="31"/>
       <c r="AP46" s="31"/>
       <c r="AQ46" s="31"/>
@@ -5001,49 +4736,47 @@
     </row>
     <row r="47" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="12"/>
-      <c r="B47" s="78"/>
-      <c r="C47" s="79"/>
-      <c r="D47" s="80"/>
+      <c r="B47" s="84"/>
+      <c r="C47" s="85"/>
+      <c r="D47" s="86"/>
       <c r="E47" s="43"/>
-      <c r="F47" s="78"/>
-      <c r="G47" s="79"/>
-      <c r="H47" s="80"/>
+      <c r="F47" s="84"/>
+      <c r="G47" s="85"/>
+      <c r="H47" s="86"/>
       <c r="I47" s="37"/>
-      <c r="J47" s="78"/>
-      <c r="K47" s="79"/>
-      <c r="L47" s="80"/>
+      <c r="J47" s="81"/>
+      <c r="K47" s="82"/>
+      <c r="L47" s="83"/>
       <c r="M47" s="4"/>
-      <c r="N47" s="70" t="s">
-        <v>62</v>
-      </c>
-      <c r="O47" s="71"/>
-      <c r="P47" s="34" t="s">
-        <v>83</v>
-      </c>
+      <c r="N47" s="71"/>
+      <c r="O47" s="72"/>
+      <c r="P47" s="73"/>
       <c r="Q47" s="37"/>
-      <c r="R47" s="70"/>
-      <c r="S47" s="71"/>
-      <c r="T47" s="34"/>
+      <c r="R47" s="71" t="s">
+        <v>73</v>
+      </c>
+      <c r="S47" s="72"/>
+      <c r="T47" s="73"/>
       <c r="U47" s="43"/>
-      <c r="V47" s="75"/>
-      <c r="W47" s="76"/>
-      <c r="X47" s="77"/>
+      <c r="V47" s="65"/>
+      <c r="W47" s="66"/>
+      <c r="X47" s="67"/>
       <c r="Y47" s="43"/>
-      <c r="Z47" s="75"/>
-      <c r="AA47" s="76"/>
-      <c r="AB47" s="77"/>
+      <c r="Z47" s="71"/>
+      <c r="AA47" s="72"/>
+      <c r="AB47" s="73"/>
       <c r="AC47" s="35"/>
-      <c r="AD47" s="72"/>
-      <c r="AE47" s="73"/>
-      <c r="AF47" s="74"/>
+      <c r="AD47" s="71"/>
+      <c r="AE47" s="72"/>
+      <c r="AF47" s="73"/>
       <c r="AG47" s="43"/>
-      <c r="AH47" s="72"/>
-      <c r="AI47" s="73"/>
-      <c r="AJ47" s="74"/>
+      <c r="AH47" s="71"/>
+      <c r="AI47" s="72"/>
+      <c r="AJ47" s="73"/>
       <c r="AK47" s="37"/>
-      <c r="AL47" s="75"/>
-      <c r="AM47" s="76"/>
-      <c r="AN47" s="77"/>
+      <c r="AL47" s="71"/>
+      <c r="AM47" s="72"/>
+      <c r="AN47" s="73"/>
       <c r="AO47" s="31"/>
       <c r="AP47" s="31"/>
       <c r="AQ47" s="31"/>
@@ -5051,165 +4784,149 @@
     </row>
     <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="12"/>
-      <c r="B48" s="67" t="s">
+      <c r="B48" s="81"/>
+      <c r="C48" s="82"/>
+      <c r="D48" s="83"/>
+      <c r="E48" s="37"/>
+      <c r="F48" s="81"/>
+      <c r="G48" s="82"/>
+      <c r="H48" s="83"/>
+      <c r="I48" s="44"/>
+      <c r="J48" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="K48" s="69"/>
+      <c r="L48" s="70"/>
+      <c r="M48" s="5"/>
+      <c r="N48" s="76" t="s">
+        <v>24</v>
+      </c>
+      <c r="O48" s="77"/>
+      <c r="P48" s="78"/>
+      <c r="Q48" s="44"/>
+      <c r="R48" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="C48" s="68"/>
-      <c r="D48" s="69"/>
-      <c r="E48" s="37"/>
-      <c r="F48" s="67" t="s">
-        <v>18</v>
-      </c>
-      <c r="G48" s="68"/>
-      <c r="H48" s="69"/>
-      <c r="I48" s="44"/>
-      <c r="J48" s="86" t="s">
-        <v>10</v>
-      </c>
-      <c r="K48" s="87"/>
-      <c r="L48" s="88"/>
-      <c r="M48" s="5"/>
-      <c r="N48" s="72" t="s">
-        <v>63</v>
-      </c>
-      <c r="O48" s="73"/>
-      <c r="P48" s="74"/>
-      <c r="Q48" s="44"/>
-      <c r="R48" s="72"/>
-      <c r="S48" s="73"/>
-      <c r="T48" s="74"/>
+      <c r="S48" s="69"/>
+      <c r="T48" s="70"/>
       <c r="U48" s="37"/>
-      <c r="V48" s="89" t="s">
-        <v>37</v>
-      </c>
-      <c r="W48" s="90"/>
-      <c r="X48" s="91"/>
+      <c r="V48" s="71"/>
+      <c r="W48" s="72"/>
+      <c r="X48" s="73"/>
       <c r="Y48" s="37"/>
-      <c r="Z48" s="67"/>
-      <c r="AA48" s="68"/>
-      <c r="AB48" s="69"/>
+      <c r="Z48" s="68"/>
+      <c r="AA48" s="69"/>
+      <c r="AB48" s="70"/>
       <c r="AC48" s="43"/>
-      <c r="AD48" s="75"/>
-      <c r="AE48" s="76"/>
-      <c r="AF48" s="77"/>
+      <c r="AD48" s="68"/>
+      <c r="AE48" s="69"/>
+      <c r="AF48" s="70"/>
       <c r="AG48" s="37"/>
-      <c r="AH48" s="75"/>
-      <c r="AI48" s="76"/>
-      <c r="AJ48" s="77"/>
+      <c r="AH48" s="68"/>
+      <c r="AI48" s="69"/>
+      <c r="AJ48" s="70"/>
       <c r="AK48" s="44"/>
-      <c r="AL48" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="AM48" s="68"/>
-      <c r="AN48" s="69"/>
+      <c r="AL48" s="68"/>
+      <c r="AM48" s="69"/>
+      <c r="AN48" s="70"/>
       <c r="AO48" s="31"/>
       <c r="AP48" s="31"/>
       <c r="AQ48" s="31"/>
       <c r="AR48" s="13"/>
     </row>
     <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="67" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="68"/>
-      <c r="D49" s="69"/>
+      <c r="B49" s="68"/>
+      <c r="C49" s="69"/>
+      <c r="D49" s="70"/>
       <c r="E49" s="35"/>
-      <c r="F49" s="67" t="s">
-        <v>15</v>
-      </c>
-      <c r="G49" s="68"/>
-      <c r="H49" s="69"/>
+      <c r="F49" s="68"/>
+      <c r="G49" s="69"/>
+      <c r="H49" s="70"/>
       <c r="I49" s="44"/>
-      <c r="J49" s="86" t="s">
-        <v>12</v>
-      </c>
-      <c r="K49" s="87"/>
-      <c r="L49" s="88"/>
+      <c r="J49" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="K49" s="69"/>
+      <c r="L49" s="70"/>
       <c r="M49" s="5"/>
-      <c r="N49" s="75"/>
-      <c r="O49" s="76"/>
-      <c r="P49" s="77"/>
+      <c r="N49" s="68" t="s">
+        <v>8</v>
+      </c>
+      <c r="O49" s="69"/>
+      <c r="P49" s="70"/>
       <c r="Q49" s="44"/>
-      <c r="R49" s="75"/>
-      <c r="S49" s="76"/>
-      <c r="T49" s="77"/>
+      <c r="R49" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="S49" s="69"/>
+      <c r="T49" s="70"/>
       <c r="U49" s="44"/>
-      <c r="V49" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="W49" s="68"/>
-      <c r="X49" s="69"/>
+      <c r="V49" s="68"/>
+      <c r="W49" s="69"/>
+      <c r="X49" s="70"/>
       <c r="Y49" s="35"/>
-      <c r="Z49" s="67"/>
-      <c r="AA49" s="68"/>
-      <c r="AB49" s="69"/>
+      <c r="Z49" s="68"/>
+      <c r="AA49" s="69"/>
+      <c r="AB49" s="70"/>
       <c r="AC49" s="35"/>
-      <c r="AD49" s="67"/>
-      <c r="AE49" s="68"/>
-      <c r="AF49" s="69"/>
+      <c r="AD49" s="68"/>
+      <c r="AE49" s="69"/>
+      <c r="AF49" s="70"/>
       <c r="AG49" s="35"/>
-      <c r="AH49" s="67"/>
-      <c r="AI49" s="68"/>
-      <c r="AJ49" s="69"/>
+      <c r="AH49" s="68"/>
+      <c r="AI49" s="69"/>
+      <c r="AJ49" s="70"/>
       <c r="AK49" s="44"/>
-      <c r="AL49" s="67" t="s">
-        <v>26</v>
-      </c>
-      <c r="AM49" s="68"/>
-      <c r="AN49" s="69"/>
+      <c r="AL49" s="68"/>
+      <c r="AM49" s="69"/>
+      <c r="AN49" s="70"/>
       <c r="AO49" s="31"/>
       <c r="AP49" s="31"/>
       <c r="AQ49" s="31"/>
       <c r="AR49" s="13"/>
     </row>
     <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="154" t="s">
-        <v>100</v>
-      </c>
-      <c r="C50" s="155"/>
-      <c r="D50" s="156"/>
+      <c r="B50" s="62"/>
+      <c r="C50" s="63"/>
+      <c r="D50" s="64"/>
       <c r="E50" s="50"/>
-      <c r="F50" s="83" t="s">
-        <v>14</v>
-      </c>
-      <c r="G50" s="84"/>
-      <c r="H50" s="85"/>
+      <c r="F50" s="62"/>
+      <c r="G50" s="63"/>
+      <c r="H50" s="64"/>
       <c r="I50" s="50"/>
-      <c r="J50" s="83" t="s">
-        <v>29</v>
-      </c>
-      <c r="K50" s="84"/>
-      <c r="L50" s="85"/>
+      <c r="J50" s="62"/>
+      <c r="K50" s="63"/>
+      <c r="L50" s="64"/>
       <c r="M50" s="5"/>
-      <c r="N50" s="89" t="s">
-        <v>37</v>
-      </c>
-      <c r="O50" s="90"/>
-      <c r="P50" s="91"/>
+      <c r="N50" s="62"/>
+      <c r="O50" s="63"/>
+      <c r="P50" s="64"/>
       <c r="Q50" s="50"/>
-      <c r="R50" s="67"/>
-      <c r="S50" s="68"/>
-      <c r="T50" s="69"/>
+      <c r="R50" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="S50" s="69"/>
+      <c r="T50" s="70"/>
       <c r="U50" s="50"/>
-      <c r="V50" s="83"/>
-      <c r="W50" s="84"/>
-      <c r="X50" s="85"/>
+      <c r="V50" s="62"/>
+      <c r="W50" s="63"/>
+      <c r="X50" s="64"/>
       <c r="Y50" s="50"/>
-      <c r="Z50" s="83"/>
-      <c r="AA50" s="84"/>
-      <c r="AB50" s="85"/>
+      <c r="Z50" s="62"/>
+      <c r="AA50" s="63"/>
+      <c r="AB50" s="64"/>
       <c r="AC50" s="50"/>
-      <c r="AD50" s="83"/>
-      <c r="AE50" s="84"/>
-      <c r="AF50" s="85"/>
+      <c r="AD50" s="62"/>
+      <c r="AE50" s="63"/>
+      <c r="AF50" s="64"/>
       <c r="AG50" s="50"/>
-      <c r="AH50" s="83"/>
-      <c r="AI50" s="84"/>
-      <c r="AJ50" s="85"/>
+      <c r="AH50" s="62"/>
+      <c r="AI50" s="63"/>
+      <c r="AJ50" s="64"/>
       <c r="AK50" s="50"/>
-      <c r="AL50" s="83"/>
-      <c r="AM50" s="84"/>
-      <c r="AN50" s="85"/>
+      <c r="AL50" s="62"/>
+      <c r="AM50" s="63"/>
+      <c r="AN50" s="64"/>
       <c r="AO50" s="31"/>
       <c r="AP50" s="31"/>
       <c r="AQ50" s="31"/>
@@ -5228,15 +4945,15 @@
       <c r="K51" s="35"/>
       <c r="L51" s="35"/>
       <c r="M51" s="14"/>
-      <c r="N51" s="83" t="s">
-        <v>12</v>
-      </c>
-      <c r="O51" s="84"/>
-      <c r="P51" s="85"/>
+      <c r="N51" s="35"/>
+      <c r="O51" s="35"/>
+      <c r="P51" s="35"/>
       <c r="Q51" s="35"/>
-      <c r="R51" s="83"/>
-      <c r="S51" s="84"/>
-      <c r="T51" s="85"/>
+      <c r="R51" s="62" t="s">
+        <v>14</v>
+      </c>
+      <c r="S51" s="63"/>
+      <c r="T51" s="64"/>
       <c r="U51" s="36"/>
       <c r="V51" s="35"/>
       <c r="W51" s="35"/>
@@ -5263,285 +4980,255 @@
       <c r="AR51" s="13"/>
     </row>
     <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="65" t="s">
-        <v>101</v>
-      </c>
-      <c r="C52" s="66"/>
-      <c r="D52" s="57" t="s">
-        <v>85</v>
-      </c>
+      <c r="B52" s="79"/>
+      <c r="C52" s="80"/>
+      <c r="D52" s="55"/>
       <c r="E52" s="36"/>
-      <c r="F52" s="65" t="s">
-        <v>101</v>
-      </c>
-      <c r="G52" s="66"/>
-      <c r="H52" s="57" t="s">
-        <v>102</v>
-      </c>
+      <c r="F52" s="79"/>
+      <c r="G52" s="80"/>
+      <c r="H52" s="55"/>
       <c r="I52" s="54"/>
-      <c r="J52" s="65" t="s">
-        <v>101</v>
-      </c>
-      <c r="K52" s="66"/>
-      <c r="L52" s="57" t="s">
-        <v>93</v>
-      </c>
+      <c r="J52" s="79"/>
+      <c r="K52" s="80"/>
+      <c r="L52" s="55"/>
       <c r="M52" s="14"/>
-      <c r="N52" s="35"/>
-      <c r="O52" s="35"/>
-      <c r="P52" s="35"/>
+      <c r="N52" s="74"/>
+      <c r="O52" s="75"/>
+      <c r="P52" s="34"/>
       <c r="Q52" s="31"/>
       <c r="R52" s="35"/>
       <c r="S52" s="35"/>
-      <c r="T52" s="35"/>
+      <c r="T52" s="58"/>
       <c r="U52" s="35"/>
-      <c r="V52" s="70"/>
-      <c r="W52" s="71"/>
+      <c r="V52" s="74"/>
+      <c r="W52" s="75"/>
       <c r="X52" s="34"/>
       <c r="Y52" s="36"/>
-      <c r="Z52" s="70"/>
-      <c r="AA52" s="71"/>
+      <c r="Z52" s="74"/>
+      <c r="AA52" s="75"/>
       <c r="AB52" s="34"/>
       <c r="AC52" s="36"/>
-      <c r="AD52" s="70"/>
-      <c r="AE52" s="71"/>
+      <c r="AD52" s="74"/>
+      <c r="AE52" s="75"/>
       <c r="AF52" s="34"/>
       <c r="AG52" s="36"/>
-      <c r="AH52" s="70"/>
-      <c r="AI52" s="71"/>
+      <c r="AH52" s="74"/>
+      <c r="AI52" s="75"/>
       <c r="AJ52" s="34"/>
       <c r="AK52" s="54"/>
-      <c r="AL52" s="70"/>
-      <c r="AM52" s="71"/>
+      <c r="AL52" s="74"/>
+      <c r="AM52" s="75"/>
       <c r="AN52" s="34"/>
       <c r="AR52" s="13"/>
     </row>
     <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="62" t="s">
-        <v>103</v>
-      </c>
-      <c r="C53" s="63"/>
-      <c r="D53" s="64"/>
+      <c r="B53" s="84"/>
+      <c r="C53" s="85"/>
+      <c r="D53" s="86"/>
       <c r="E53" s="36"/>
-      <c r="F53" s="62" t="s">
-        <v>104</v>
-      </c>
-      <c r="G53" s="63"/>
-      <c r="H53" s="64"/>
+      <c r="F53" s="84"/>
+      <c r="G53" s="85"/>
+      <c r="H53" s="86"/>
       <c r="I53" s="35"/>
-      <c r="J53" s="62" t="s">
-        <v>113</v>
-      </c>
-      <c r="K53" s="63"/>
-      <c r="L53" s="64"/>
+      <c r="J53" s="84"/>
+      <c r="K53" s="85"/>
+      <c r="L53" s="86"/>
       <c r="M53" s="4"/>
-      <c r="N53" s="70"/>
-      <c r="O53" s="71"/>
-      <c r="P53" s="34"/>
+      <c r="N53" s="65"/>
+      <c r="O53" s="66"/>
+      <c r="P53" s="67"/>
       <c r="Q53" s="32"/>
-      <c r="R53" s="70"/>
-      <c r="S53" s="71"/>
+      <c r="R53" s="74"/>
+      <c r="S53" s="75"/>
       <c r="T53" s="34"/>
       <c r="U53" s="43"/>
-      <c r="V53" s="72"/>
-      <c r="W53" s="73"/>
-      <c r="X53" s="74"/>
+      <c r="V53" s="65"/>
+      <c r="W53" s="66"/>
+      <c r="X53" s="67"/>
       <c r="Y53" s="36"/>
-      <c r="Z53" s="72"/>
-      <c r="AA53" s="73"/>
-      <c r="AB53" s="74"/>
+      <c r="Z53" s="65"/>
+      <c r="AA53" s="66"/>
+      <c r="AB53" s="67"/>
       <c r="AC53" s="35"/>
-      <c r="AD53" s="72"/>
-      <c r="AE53" s="73"/>
-      <c r="AF53" s="74"/>
+      <c r="AD53" s="65"/>
+      <c r="AE53" s="66"/>
+      <c r="AF53" s="67"/>
       <c r="AG53" s="36"/>
-      <c r="AH53" s="72"/>
-      <c r="AI53" s="73"/>
-      <c r="AJ53" s="74"/>
+      <c r="AH53" s="65"/>
+      <c r="AI53" s="66"/>
+      <c r="AJ53" s="67"/>
       <c r="AK53" s="35"/>
-      <c r="AL53" s="72"/>
-      <c r="AM53" s="73"/>
-      <c r="AN53" s="74"/>
+      <c r="AL53" s="65"/>
+      <c r="AM53" s="66"/>
+      <c r="AN53" s="67"/>
       <c r="AR53" s="13"/>
     </row>
     <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="78"/>
-      <c r="C54" s="79"/>
-      <c r="D54" s="80"/>
+      <c r="B54" s="81"/>
+      <c r="C54" s="82"/>
+      <c r="D54" s="83"/>
       <c r="E54" s="43"/>
-      <c r="F54" s="78"/>
-      <c r="G54" s="79"/>
-      <c r="H54" s="80"/>
+      <c r="F54" s="81"/>
+      <c r="G54" s="82"/>
+      <c r="H54" s="83"/>
       <c r="I54" s="35"/>
-      <c r="J54" s="78"/>
-      <c r="K54" s="79"/>
-      <c r="L54" s="80"/>
+      <c r="J54" s="81"/>
+      <c r="K54" s="82"/>
+      <c r="L54" s="83"/>
       <c r="M54" s="4"/>
-      <c r="N54" s="72"/>
-      <c r="O54" s="73"/>
-      <c r="P54" s="74"/>
+      <c r="N54" s="71"/>
+      <c r="O54" s="72"/>
+      <c r="P54" s="73"/>
       <c r="Q54" s="43"/>
-      <c r="R54" s="72"/>
-      <c r="S54" s="73"/>
-      <c r="T54" s="74"/>
+      <c r="R54" s="65"/>
+      <c r="S54" s="66"/>
+      <c r="T54" s="67"/>
       <c r="U54" s="37"/>
-      <c r="V54" s="75"/>
-      <c r="W54" s="76"/>
-      <c r="X54" s="77"/>
+      <c r="V54" s="71"/>
+      <c r="W54" s="72"/>
+      <c r="X54" s="73"/>
       <c r="Y54" s="43"/>
-      <c r="Z54" s="75"/>
-      <c r="AA54" s="76"/>
-      <c r="AB54" s="77"/>
+      <c r="Z54" s="71"/>
+      <c r="AA54" s="72"/>
+      <c r="AB54" s="73"/>
       <c r="AC54" s="31"/>
-      <c r="AD54" s="75"/>
-      <c r="AE54" s="76"/>
-      <c r="AF54" s="77"/>
+      <c r="AD54" s="71"/>
+      <c r="AE54" s="72"/>
+      <c r="AF54" s="73"/>
       <c r="AG54" s="43"/>
-      <c r="AH54" s="75"/>
-      <c r="AI54" s="76"/>
-      <c r="AJ54" s="77"/>
+      <c r="AH54" s="71"/>
+      <c r="AI54" s="72"/>
+      <c r="AJ54" s="73"/>
       <c r="AK54" s="35"/>
-      <c r="AL54" s="75"/>
-      <c r="AM54" s="76"/>
-      <c r="AN54" s="77"/>
+      <c r="AL54" s="71"/>
+      <c r="AM54" s="72"/>
+      <c r="AN54" s="73"/>
       <c r="AR54" s="13"/>
     </row>
     <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" s="68"/>
-      <c r="D55" s="69"/>
+      <c r="B55" s="76"/>
+      <c r="C55" s="77"/>
+      <c r="D55" s="78"/>
       <c r="E55" s="37"/>
-      <c r="F55" s="67" t="s">
-        <v>22</v>
-      </c>
-      <c r="G55" s="68"/>
-      <c r="H55" s="69"/>
+      <c r="F55" s="76"/>
+      <c r="G55" s="77"/>
+      <c r="H55" s="78"/>
       <c r="I55" s="40"/>
-      <c r="J55" s="67" t="s">
-        <v>26</v>
-      </c>
-      <c r="K55" s="68"/>
-      <c r="L55" s="69"/>
+      <c r="J55" s="76"/>
+      <c r="K55" s="77"/>
+      <c r="L55" s="78"/>
       <c r="M55" s="5"/>
-      <c r="N55" s="75"/>
-      <c r="O55" s="76"/>
-      <c r="P55" s="77"/>
+      <c r="N55" s="68"/>
+      <c r="O55" s="69"/>
+      <c r="P55" s="70"/>
       <c r="Q55" s="43"/>
-      <c r="R55" s="75"/>
-      <c r="S55" s="76"/>
-      <c r="T55" s="77"/>
+      <c r="R55" s="71"/>
+      <c r="S55" s="72"/>
+      <c r="T55" s="73"/>
       <c r="U55" s="44"/>
-      <c r="V55" s="67"/>
-      <c r="W55" s="68"/>
-      <c r="X55" s="69"/>
+      <c r="V55" s="68"/>
+      <c r="W55" s="69"/>
+      <c r="X55" s="70"/>
       <c r="Y55" s="37"/>
-      <c r="Z55" s="67"/>
-      <c r="AA55" s="68"/>
-      <c r="AB55" s="69"/>
+      <c r="Z55" s="68"/>
+      <c r="AA55" s="69"/>
+      <c r="AB55" s="70"/>
       <c r="AC55" s="35"/>
-      <c r="AD55" s="67"/>
-      <c r="AE55" s="68"/>
-      <c r="AF55" s="69"/>
+      <c r="AD55" s="68"/>
+      <c r="AE55" s="69"/>
+      <c r="AF55" s="70"/>
       <c r="AG55" s="37"/>
-      <c r="AH55" s="67"/>
-      <c r="AI55" s="68"/>
-      <c r="AJ55" s="69"/>
+      <c r="AH55" s="68"/>
+      <c r="AI55" s="69"/>
+      <c r="AJ55" s="70"/>
       <c r="AK55" s="40"/>
-      <c r="AL55" s="67"/>
-      <c r="AM55" s="68"/>
-      <c r="AN55" s="69"/>
+      <c r="AL55" s="68"/>
+      <c r="AM55" s="69"/>
+      <c r="AN55" s="70"/>
       <c r="AR55" s="13"/>
     </row>
     <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="C56" s="68"/>
-      <c r="D56" s="69"/>
+      <c r="B56" s="68"/>
+      <c r="C56" s="69"/>
+      <c r="D56" s="70"/>
       <c r="E56" s="44"/>
-      <c r="F56" s="67" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="68"/>
-      <c r="H56" s="69"/>
+      <c r="F56" s="68"/>
+      <c r="G56" s="69"/>
+      <c r="H56" s="70"/>
       <c r="I56" s="44"/>
-      <c r="J56" s="67" t="s">
-        <v>15</v>
-      </c>
-      <c r="K56" s="68"/>
-      <c r="L56" s="69"/>
+      <c r="J56" s="68"/>
+      <c r="K56" s="69"/>
+      <c r="L56" s="70"/>
       <c r="M56" s="5"/>
-      <c r="N56" s="67"/>
-      <c r="O56" s="68"/>
-      <c r="P56" s="69"/>
+      <c r="N56" s="68"/>
+      <c r="O56" s="69"/>
+      <c r="P56" s="70"/>
       <c r="Q56" s="43"/>
-      <c r="R56" s="67"/>
-      <c r="S56" s="68"/>
-      <c r="T56" s="69"/>
+      <c r="R56" s="68"/>
+      <c r="S56" s="69"/>
+      <c r="T56" s="70"/>
       <c r="U56" s="44"/>
-      <c r="V56" s="67"/>
-      <c r="W56" s="68"/>
-      <c r="X56" s="69"/>
+      <c r="V56" s="68"/>
+      <c r="W56" s="69"/>
+      <c r="X56" s="70"/>
       <c r="Y56" s="44"/>
-      <c r="Z56" s="67"/>
-      <c r="AA56" s="68"/>
-      <c r="AB56" s="69"/>
+      <c r="Z56" s="68"/>
+      <c r="AA56" s="69"/>
+      <c r="AB56" s="70"/>
       <c r="AC56" s="43"/>
-      <c r="AD56" s="67"/>
-      <c r="AE56" s="68"/>
-      <c r="AF56" s="69"/>
+      <c r="AD56" s="68"/>
+      <c r="AE56" s="69"/>
+      <c r="AF56" s="70"/>
       <c r="AG56" s="44"/>
-      <c r="AH56" s="67"/>
-      <c r="AI56" s="68"/>
-      <c r="AJ56" s="69"/>
+      <c r="AH56" s="68"/>
+      <c r="AI56" s="69"/>
+      <c r="AJ56" s="70"/>
       <c r="AK56" s="44"/>
-      <c r="AL56" s="67"/>
-      <c r="AM56" s="68"/>
-      <c r="AN56" s="69"/>
+      <c r="AL56" s="68"/>
+      <c r="AM56" s="69"/>
+      <c r="AN56" s="70"/>
       <c r="AR56" s="13"/>
     </row>
     <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="83"/>
-      <c r="C57" s="84"/>
-      <c r="D57" s="85"/>
+      <c r="B57" s="62"/>
+      <c r="C57" s="63"/>
+      <c r="D57" s="64"/>
       <c r="E57" s="35"/>
-      <c r="F57" s="83"/>
-      <c r="G57" s="84"/>
-      <c r="H57" s="85"/>
+      <c r="F57" s="62"/>
+      <c r="G57" s="63"/>
+      <c r="H57" s="64"/>
       <c r="I57" s="50"/>
-      <c r="J57" s="83"/>
-      <c r="K57" s="84"/>
-      <c r="L57" s="85"/>
+      <c r="J57" s="62"/>
+      <c r="K57" s="63"/>
+      <c r="L57" s="64"/>
       <c r="M57" s="5"/>
-      <c r="N57" s="83"/>
-      <c r="O57" s="84"/>
-      <c r="P57" s="85"/>
+      <c r="N57" s="62"/>
+      <c r="O57" s="63"/>
+      <c r="P57" s="64"/>
       <c r="Q57" s="31"/>
-      <c r="R57" s="83"/>
-      <c r="S57" s="84"/>
-      <c r="T57" s="85"/>
+      <c r="R57" s="62"/>
+      <c r="S57" s="63"/>
+      <c r="T57" s="64"/>
       <c r="U57" s="50"/>
-      <c r="V57" s="83"/>
-      <c r="W57" s="84"/>
-      <c r="X57" s="85"/>
+      <c r="V57" s="62"/>
+      <c r="W57" s="63"/>
+      <c r="X57" s="64"/>
       <c r="Y57" s="35"/>
-      <c r="Z57" s="83"/>
-      <c r="AA57" s="84"/>
-      <c r="AB57" s="85"/>
+      <c r="Z57" s="62"/>
+      <c r="AA57" s="63"/>
+      <c r="AB57" s="64"/>
       <c r="AC57" s="31"/>
-      <c r="AD57" s="83"/>
-      <c r="AE57" s="84"/>
-      <c r="AF57" s="85"/>
+      <c r="AD57" s="62"/>
+      <c r="AE57" s="63"/>
+      <c r="AF57" s="64"/>
       <c r="AG57" s="35"/>
-      <c r="AH57" s="83"/>
-      <c r="AI57" s="84"/>
-      <c r="AJ57" s="85"/>
+      <c r="AH57" s="62"/>
+      <c r="AI57" s="63"/>
+      <c r="AJ57" s="64"/>
       <c r="AK57" s="50"/>
-      <c r="AL57" s="83"/>
-      <c r="AM57" s="84"/>
-      <c r="AN57" s="85"/>
+      <c r="AL57" s="62"/>
+      <c r="AM57" s="63"/>
+      <c r="AN57" s="64"/>
       <c r="AR57" s="13"/>
     </row>
     <row r="58" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5587,265 +5274,255 @@
       <c r="AR58" s="13"/>
     </row>
     <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="65" t="s">
-        <v>101</v>
-      </c>
-      <c r="C59" s="66"/>
-      <c r="D59" s="57" t="s">
-        <v>102</v>
-      </c>
+      <c r="B59" s="79"/>
+      <c r="C59" s="80"/>
+      <c r="D59" s="55"/>
       <c r="E59" s="50"/>
-      <c r="F59" s="81"/>
-      <c r="G59" s="82"/>
+      <c r="F59" s="79"/>
+      <c r="G59" s="80"/>
       <c r="H59" s="55"/>
       <c r="I59" s="32"/>
-      <c r="J59" s="81"/>
-      <c r="K59" s="82"/>
+      <c r="J59" s="79"/>
+      <c r="K59" s="80"/>
       <c r="L59" s="55"/>
       <c r="M59" s="6"/>
-      <c r="N59" s="70"/>
-      <c r="O59" s="71"/>
+      <c r="N59" s="74"/>
+      <c r="O59" s="75"/>
       <c r="P59" s="34"/>
       <c r="Q59" s="36"/>
-      <c r="R59" s="70"/>
-      <c r="S59" s="71"/>
+      <c r="R59" s="74"/>
+      <c r="S59" s="75"/>
       <c r="T59" s="34"/>
       <c r="U59" s="50"/>
-      <c r="V59" s="70"/>
-      <c r="W59" s="71"/>
+      <c r="V59" s="74"/>
+      <c r="W59" s="75"/>
       <c r="X59" s="34"/>
       <c r="Y59" s="32"/>
-      <c r="Z59" s="70"/>
-      <c r="AA59" s="71"/>
+      <c r="Z59" s="74"/>
+      <c r="AA59" s="75"/>
       <c r="AB59" s="34"/>
       <c r="AC59" s="32"/>
-      <c r="AD59" s="70"/>
-      <c r="AE59" s="71"/>
+      <c r="AD59" s="74"/>
+      <c r="AE59" s="75"/>
       <c r="AF59" s="34"/>
       <c r="AG59" s="50"/>
-      <c r="AH59" s="70"/>
-      <c r="AI59" s="71"/>
+      <c r="AH59" s="74"/>
+      <c r="AI59" s="75"/>
       <c r="AJ59" s="34"/>
       <c r="AK59" s="32"/>
-      <c r="AL59" s="70"/>
-      <c r="AM59" s="71"/>
+      <c r="AL59" s="74"/>
+      <c r="AM59" s="75"/>
       <c r="AN59" s="34"/>
       <c r="AR59" s="13"/>
     </row>
     <row r="60" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="62" t="s">
-        <v>105</v>
-      </c>
-      <c r="C60" s="63"/>
-      <c r="D60" s="64"/>
+      <c r="B60" s="84"/>
+      <c r="C60" s="85"/>
+      <c r="D60" s="86"/>
       <c r="E60" s="32"/>
-      <c r="F60" s="62"/>
-      <c r="G60" s="63"/>
-      <c r="H60" s="64"/>
+      <c r="F60" s="84"/>
+      <c r="G60" s="85"/>
+      <c r="H60" s="86"/>
       <c r="I60" s="32"/>
-      <c r="J60" s="62"/>
-      <c r="K60" s="63"/>
-      <c r="L60" s="64"/>
+      <c r="J60" s="84"/>
+      <c r="K60" s="85"/>
+      <c r="L60" s="86"/>
       <c r="M60" s="4"/>
-      <c r="N60" s="72"/>
-      <c r="O60" s="73"/>
-      <c r="P60" s="74"/>
+      <c r="N60" s="65"/>
+      <c r="O60" s="66"/>
+      <c r="P60" s="67"/>
       <c r="Q60" s="43"/>
-      <c r="R60" s="72"/>
-      <c r="S60" s="73"/>
-      <c r="T60" s="74"/>
+      <c r="R60" s="65"/>
+      <c r="S60" s="66"/>
+      <c r="T60" s="67"/>
       <c r="U60" s="32"/>
-      <c r="V60" s="72"/>
-      <c r="W60" s="73"/>
-      <c r="X60" s="74"/>
+      <c r="V60" s="65"/>
+      <c r="W60" s="66"/>
+      <c r="X60" s="67"/>
       <c r="Y60" s="32"/>
-      <c r="Z60" s="72"/>
-      <c r="AA60" s="73"/>
-      <c r="AB60" s="74"/>
+      <c r="Z60" s="65"/>
+      <c r="AA60" s="66"/>
+      <c r="AB60" s="67"/>
       <c r="AC60" s="54"/>
-      <c r="AD60" s="72"/>
-      <c r="AE60" s="73"/>
-      <c r="AF60" s="74"/>
+      <c r="AD60" s="65"/>
+      <c r="AE60" s="66"/>
+      <c r="AF60" s="67"/>
       <c r="AG60" s="32"/>
-      <c r="AH60" s="72"/>
-      <c r="AI60" s="73"/>
-      <c r="AJ60" s="74"/>
+      <c r="AH60" s="65"/>
+      <c r="AI60" s="66"/>
+      <c r="AJ60" s="67"/>
       <c r="AK60" s="32"/>
-      <c r="AL60" s="72"/>
-      <c r="AM60" s="73"/>
-      <c r="AN60" s="74"/>
+      <c r="AL60" s="65"/>
+      <c r="AM60" s="66"/>
+      <c r="AN60" s="67"/>
       <c r="AR60" s="13"/>
     </row>
     <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="78"/>
-      <c r="C61" s="79"/>
-      <c r="D61" s="80"/>
+      <c r="B61" s="81"/>
+      <c r="C61" s="82"/>
+      <c r="D61" s="83"/>
       <c r="E61" s="32"/>
-      <c r="F61" s="78"/>
-      <c r="G61" s="79"/>
-      <c r="H61" s="80"/>
+      <c r="F61" s="81"/>
+      <c r="G61" s="82"/>
+      <c r="H61" s="83"/>
       <c r="I61" s="32"/>
-      <c r="J61" s="78"/>
-      <c r="K61" s="79"/>
-      <c r="L61" s="80"/>
+      <c r="J61" s="81"/>
+      <c r="K61" s="82"/>
+      <c r="L61" s="83"/>
       <c r="M61" s="4"/>
-      <c r="N61" s="75"/>
-      <c r="O61" s="76"/>
-      <c r="P61" s="77"/>
+      <c r="N61" s="71"/>
+      <c r="O61" s="72"/>
+      <c r="P61" s="73"/>
       <c r="Q61" s="37"/>
-      <c r="R61" s="75"/>
-      <c r="S61" s="76"/>
-      <c r="T61" s="77"/>
+      <c r="R61" s="71"/>
+      <c r="S61" s="72"/>
+      <c r="T61" s="73"/>
       <c r="U61" s="32"/>
-      <c r="V61" s="75"/>
-      <c r="W61" s="76"/>
-      <c r="X61" s="77"/>
+      <c r="V61" s="71"/>
+      <c r="W61" s="72"/>
+      <c r="X61" s="73"/>
       <c r="Y61" s="32"/>
-      <c r="Z61" s="75"/>
-      <c r="AA61" s="76"/>
-      <c r="AB61" s="77"/>
+      <c r="Z61" s="71"/>
+      <c r="AA61" s="72"/>
+      <c r="AB61" s="73"/>
       <c r="AC61" s="35"/>
-      <c r="AD61" s="75"/>
-      <c r="AE61" s="76"/>
-      <c r="AF61" s="77"/>
+      <c r="AD61" s="71"/>
+      <c r="AE61" s="72"/>
+      <c r="AF61" s="73"/>
       <c r="AG61" s="32"/>
-      <c r="AH61" s="75"/>
-      <c r="AI61" s="76"/>
-      <c r="AJ61" s="77"/>
+      <c r="AH61" s="71"/>
+      <c r="AI61" s="72"/>
+      <c r="AJ61" s="73"/>
       <c r="AK61" s="32"/>
-      <c r="AL61" s="75"/>
-      <c r="AM61" s="76"/>
-      <c r="AN61" s="77"/>
+      <c r="AL61" s="71"/>
+      <c r="AM61" s="72"/>
+      <c r="AN61" s="73"/>
       <c r="AR61" s="13"/>
     </row>
     <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="89" t="s">
-        <v>22</v>
-      </c>
-      <c r="C62" s="90"/>
-      <c r="D62" s="91"/>
+      <c r="B62" s="76"/>
+      <c r="C62" s="77"/>
+      <c r="D62" s="78"/>
       <c r="E62" s="37"/>
-      <c r="F62" s="67"/>
-      <c r="G62" s="68"/>
-      <c r="H62" s="69"/>
+      <c r="F62" s="68"/>
+      <c r="G62" s="69"/>
+      <c r="H62" s="70"/>
       <c r="I62" s="35"/>
-      <c r="J62" s="89"/>
-      <c r="K62" s="90"/>
-      <c r="L62" s="91"/>
+      <c r="J62" s="76"/>
+      <c r="K62" s="77"/>
+      <c r="L62" s="78"/>
       <c r="M62" s="4"/>
-      <c r="N62" s="67"/>
-      <c r="O62" s="68"/>
-      <c r="P62" s="69"/>
+      <c r="N62" s="68"/>
+      <c r="O62" s="69"/>
+      <c r="P62" s="70"/>
       <c r="Q62" s="44"/>
-      <c r="R62" s="89"/>
-      <c r="S62" s="90"/>
-      <c r="T62" s="91"/>
+      <c r="R62" s="76"/>
+      <c r="S62" s="77"/>
+      <c r="T62" s="78"/>
       <c r="U62" s="37"/>
-      <c r="V62" s="89"/>
-      <c r="W62" s="90"/>
-      <c r="X62" s="91"/>
+      <c r="V62" s="76"/>
+      <c r="W62" s="77"/>
+      <c r="X62" s="78"/>
       <c r="Y62" s="35"/>
-      <c r="Z62" s="67"/>
-      <c r="AA62" s="68"/>
-      <c r="AB62" s="69"/>
+      <c r="Z62" s="68"/>
+      <c r="AA62" s="69"/>
+      <c r="AB62" s="70"/>
       <c r="AC62" s="35"/>
-      <c r="AD62" s="89"/>
-      <c r="AE62" s="90"/>
-      <c r="AF62" s="91"/>
+      <c r="AD62" s="76"/>
+      <c r="AE62" s="77"/>
+      <c r="AF62" s="78"/>
       <c r="AG62" s="37"/>
-      <c r="AH62" s="67"/>
-      <c r="AI62" s="68"/>
-      <c r="AJ62" s="69"/>
+      <c r="AH62" s="68"/>
+      <c r="AI62" s="69"/>
+      <c r="AJ62" s="70"/>
       <c r="AK62" s="35"/>
-      <c r="AL62" s="89"/>
-      <c r="AM62" s="90"/>
-      <c r="AN62" s="91"/>
+      <c r="AL62" s="76"/>
+      <c r="AM62" s="77"/>
+      <c r="AN62" s="78"/>
       <c r="AR62" s="13"/>
     </row>
     <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="67" t="s">
-        <v>8</v>
-      </c>
-      <c r="C63" s="68"/>
-      <c r="D63" s="69"/>
+      <c r="B63" s="68"/>
+      <c r="C63" s="69"/>
+      <c r="D63" s="70"/>
       <c r="E63" s="44"/>
-      <c r="F63" s="67"/>
-      <c r="G63" s="68"/>
-      <c r="H63" s="69"/>
+      <c r="F63" s="68"/>
+      <c r="G63" s="69"/>
+      <c r="H63" s="70"/>
       <c r="I63" s="40"/>
-      <c r="J63" s="67"/>
-      <c r="K63" s="68"/>
-      <c r="L63" s="69"/>
+      <c r="J63" s="68"/>
+      <c r="K63" s="69"/>
+      <c r="L63" s="70"/>
       <c r="M63" s="5"/>
-      <c r="N63" s="67"/>
-      <c r="O63" s="68"/>
-      <c r="P63" s="69"/>
+      <c r="N63" s="68"/>
+      <c r="O63" s="69"/>
+      <c r="P63" s="70"/>
       <c r="Q63" s="44"/>
-      <c r="R63" s="67"/>
-      <c r="S63" s="68"/>
-      <c r="T63" s="69"/>
+      <c r="R63" s="68"/>
+      <c r="S63" s="69"/>
+      <c r="T63" s="70"/>
       <c r="U63" s="44"/>
-      <c r="V63" s="67"/>
-      <c r="W63" s="68"/>
-      <c r="X63" s="69"/>
+      <c r="V63" s="68"/>
+      <c r="W63" s="69"/>
+      <c r="X63" s="70"/>
       <c r="Y63" s="40"/>
-      <c r="Z63" s="67"/>
-      <c r="AA63" s="68"/>
-      <c r="AB63" s="69"/>
+      <c r="Z63" s="68"/>
+      <c r="AA63" s="69"/>
+      <c r="AB63" s="70"/>
       <c r="AC63" s="40"/>
-      <c r="AD63" s="67"/>
-      <c r="AE63" s="68"/>
-      <c r="AF63" s="69"/>
+      <c r="AD63" s="68"/>
+      <c r="AE63" s="69"/>
+      <c r="AF63" s="70"/>
       <c r="AG63" s="44"/>
-      <c r="AH63" s="67"/>
-      <c r="AI63" s="68"/>
-      <c r="AJ63" s="69"/>
+      <c r="AH63" s="68"/>
+      <c r="AI63" s="69"/>
+      <c r="AJ63" s="70"/>
       <c r="AK63" s="40"/>
-      <c r="AL63" s="67"/>
-      <c r="AM63" s="68"/>
-      <c r="AN63" s="69"/>
+      <c r="AL63" s="68"/>
+      <c r="AM63" s="69"/>
+      <c r="AN63" s="70"/>
       <c r="AR63" s="13"/>
     </row>
     <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="83"/>
-      <c r="C64" s="84"/>
-      <c r="D64" s="85"/>
+      <c r="B64" s="62"/>
+      <c r="C64" s="63"/>
+      <c r="D64" s="64"/>
       <c r="E64" s="35"/>
-      <c r="F64" s="83"/>
-      <c r="G64" s="84"/>
-      <c r="H64" s="85"/>
+      <c r="F64" s="62"/>
+      <c r="G64" s="63"/>
+      <c r="H64" s="64"/>
       <c r="I64" s="50"/>
-      <c r="J64" s="83"/>
-      <c r="K64" s="84"/>
-      <c r="L64" s="85"/>
+      <c r="J64" s="62"/>
+      <c r="K64" s="63"/>
+      <c r="L64" s="64"/>
       <c r="M64" s="5"/>
-      <c r="N64" s="83"/>
-      <c r="O64" s="84"/>
-      <c r="P64" s="85"/>
+      <c r="N64" s="62"/>
+      <c r="O64" s="63"/>
+      <c r="P64" s="64"/>
       <c r="Q64" s="50"/>
-      <c r="R64" s="83"/>
-      <c r="S64" s="84"/>
-      <c r="T64" s="85"/>
+      <c r="R64" s="62"/>
+      <c r="S64" s="63"/>
+      <c r="T64" s="64"/>
       <c r="U64" s="35"/>
-      <c r="V64" s="83"/>
-      <c r="W64" s="84"/>
-      <c r="X64" s="85"/>
+      <c r="V64" s="62"/>
+      <c r="W64" s="63"/>
+      <c r="X64" s="64"/>
       <c r="Y64" s="50"/>
-      <c r="Z64" s="83"/>
-      <c r="AA64" s="84"/>
-      <c r="AB64" s="85"/>
+      <c r="Z64" s="62"/>
+      <c r="AA64" s="63"/>
+      <c r="AB64" s="64"/>
       <c r="AC64" s="50"/>
-      <c r="AD64" s="83"/>
-      <c r="AE64" s="84"/>
-      <c r="AF64" s="85"/>
+      <c r="AD64" s="62"/>
+      <c r="AE64" s="63"/>
+      <c r="AF64" s="64"/>
       <c r="AG64" s="35"/>
-      <c r="AH64" s="83"/>
-      <c r="AI64" s="84"/>
-      <c r="AJ64" s="85"/>
+      <c r="AH64" s="62"/>
+      <c r="AI64" s="63"/>
+      <c r="AJ64" s="64"/>
       <c r="AK64" s="50"/>
-      <c r="AL64" s="83"/>
-      <c r="AM64" s="84"/>
-      <c r="AN64" s="85"/>
+      <c r="AL64" s="62"/>
+      <c r="AM64" s="63"/>
+      <c r="AN64" s="64"/>
       <c r="AR64" s="13"/>
     </row>
     <row r="65" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5896,52 +5573,46 @@
     </row>
     <row r="66" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="12"/>
-      <c r="B66" s="65" t="s">
-        <v>101</v>
-      </c>
-      <c r="C66" s="66"/>
-      <c r="D66" s="57" t="s">
-        <v>54</v>
-      </c>
+      <c r="B66" s="79"/>
+      <c r="C66" s="80"/>
+      <c r="D66" s="55"/>
       <c r="E66" s="36"/>
-      <c r="F66" s="81"/>
-      <c r="G66" s="82"/>
+      <c r="F66" s="79"/>
+      <c r="G66" s="80"/>
       <c r="H66" s="55"/>
       <c r="I66" s="32"/>
-      <c r="J66" s="81"/>
-      <c r="K66" s="82"/>
+      <c r="J66" s="79"/>
+      <c r="K66" s="80"/>
       <c r="L66" s="55"/>
       <c r="M66" s="6"/>
-      <c r="N66" s="70" t="s">
-        <v>107</v>
-      </c>
-      <c r="O66" s="71"/>
+      <c r="N66" s="74"/>
+      <c r="O66" s="75"/>
       <c r="P66" s="34"/>
       <c r="Q66" s="36"/>
-      <c r="R66" s="70"/>
-      <c r="S66" s="71"/>
+      <c r="R66" s="74"/>
+      <c r="S66" s="75"/>
       <c r="T66" s="34"/>
       <c r="U66" s="36"/>
-      <c r="V66" s="70"/>
-      <c r="W66" s="71"/>
+      <c r="V66" s="74"/>
+      <c r="W66" s="75"/>
       <c r="X66" s="34"/>
       <c r="Y66" s="36"/>
-      <c r="Z66" s="70"/>
-      <c r="AA66" s="71"/>
+      <c r="Z66" s="74"/>
+      <c r="AA66" s="75"/>
       <c r="AB66" s="34"/>
       <c r="AC66" s="36"/>
-      <c r="AD66" s="70"/>
-      <c r="AE66" s="71"/>
+      <c r="AD66" s="74"/>
+      <c r="AE66" s="75"/>
       <c r="AF66" s="34"/>
       <c r="AG66" s="36"/>
-      <c r="AH66" s="70"/>
-      <c r="AI66" s="71"/>
+      <c r="AH66" s="74"/>
+      <c r="AI66" s="75"/>
       <c r="AJ66" s="34"/>
       <c r="AK66" s="32"/>
-      <c r="AL66" s="98" t="s">
-        <v>114</v>
-      </c>
-      <c r="AM66" s="99"/>
+      <c r="AL66" s="92" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM66" s="93"/>
       <c r="AN66" s="59"/>
       <c r="AO66" s="17"/>
       <c r="AP66" s="12"/>
@@ -5950,51 +5621,47 @@
     </row>
     <row r="67" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="12"/>
-      <c r="B67" s="62" t="s">
-        <v>106</v>
-      </c>
-      <c r="C67" s="63"/>
-      <c r="D67" s="64"/>
+      <c r="B67" s="84"/>
+      <c r="C67" s="85"/>
+      <c r="D67" s="86"/>
       <c r="E67" s="36"/>
-      <c r="F67" s="62"/>
-      <c r="G67" s="63"/>
-      <c r="H67" s="64"/>
+      <c r="F67" s="84"/>
+      <c r="G67" s="85"/>
+      <c r="H67" s="86"/>
       <c r="I67" s="54"/>
-      <c r="J67" s="62"/>
-      <c r="K67" s="63"/>
-      <c r="L67" s="64"/>
+      <c r="J67" s="84"/>
+      <c r="K67" s="85"/>
+      <c r="L67" s="86"/>
       <c r="M67" s="4"/>
-      <c r="N67" s="72" t="s">
-        <v>108</v>
-      </c>
-      <c r="O67" s="73"/>
-      <c r="P67" s="74"/>
+      <c r="N67" s="65"/>
+      <c r="O67" s="66"/>
+      <c r="P67" s="67"/>
       <c r="Q67" s="37"/>
-      <c r="R67" s="72"/>
-      <c r="S67" s="73"/>
-      <c r="T67" s="74"/>
+      <c r="R67" s="65"/>
+      <c r="S67" s="66"/>
+      <c r="T67" s="67"/>
       <c r="U67" s="36"/>
-      <c r="V67" s="72"/>
-      <c r="W67" s="73"/>
-      <c r="X67" s="74"/>
+      <c r="V67" s="65"/>
+      <c r="W67" s="66"/>
+      <c r="X67" s="67"/>
       <c r="Y67" s="36"/>
-      <c r="Z67" s="72"/>
-      <c r="AA67" s="73"/>
-      <c r="AB67" s="74"/>
+      <c r="Z67" s="65"/>
+      <c r="AA67" s="66"/>
+      <c r="AB67" s="67"/>
       <c r="AC67" s="36"/>
-      <c r="AD67" s="72"/>
-      <c r="AE67" s="73"/>
-      <c r="AF67" s="74"/>
+      <c r="AD67" s="65"/>
+      <c r="AE67" s="66"/>
+      <c r="AF67" s="67"/>
       <c r="AG67" s="36"/>
-      <c r="AH67" s="72"/>
-      <c r="AI67" s="73"/>
-      <c r="AJ67" s="74"/>
+      <c r="AH67" s="65"/>
+      <c r="AI67" s="66"/>
+      <c r="AJ67" s="67"/>
       <c r="AK67" s="54"/>
-      <c r="AL67" s="100" t="s">
-        <v>51</v>
-      </c>
-      <c r="AM67" s="101"/>
-      <c r="AN67" s="102"/>
+      <c r="AL67" s="136" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM67" s="137"/>
+      <c r="AN67" s="138"/>
       <c r="AO67" s="17"/>
       <c r="AP67" s="12"/>
       <c r="AQ67" s="12"/>
@@ -6002,47 +5669,47 @@
     </row>
     <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="12"/>
-      <c r="B68" s="78"/>
-      <c r="C68" s="79"/>
-      <c r="D68" s="80"/>
+      <c r="B68" s="81"/>
+      <c r="C68" s="82"/>
+      <c r="D68" s="83"/>
       <c r="E68" s="43"/>
-      <c r="F68" s="78"/>
-      <c r="G68" s="79"/>
-      <c r="H68" s="80"/>
+      <c r="F68" s="81"/>
+      <c r="G68" s="82"/>
+      <c r="H68" s="83"/>
       <c r="I68" s="35"/>
-      <c r="J68" s="78"/>
-      <c r="K68" s="79"/>
-      <c r="L68" s="80"/>
+      <c r="J68" s="81"/>
+      <c r="K68" s="82"/>
+      <c r="L68" s="83"/>
       <c r="M68" s="4"/>
-      <c r="N68" s="75"/>
-      <c r="O68" s="76"/>
-      <c r="P68" s="77"/>
+      <c r="N68" s="71"/>
+      <c r="O68" s="72"/>
+      <c r="P68" s="73"/>
       <c r="Q68" s="36"/>
-      <c r="R68" s="75"/>
-      <c r="S68" s="76"/>
-      <c r="T68" s="77"/>
+      <c r="R68" s="71"/>
+      <c r="S68" s="72"/>
+      <c r="T68" s="73"/>
       <c r="U68" s="43"/>
-      <c r="V68" s="75"/>
-      <c r="W68" s="76"/>
-      <c r="X68" s="77"/>
+      <c r="V68" s="71"/>
+      <c r="W68" s="72"/>
+      <c r="X68" s="73"/>
       <c r="Y68" s="43"/>
-      <c r="Z68" s="75"/>
-      <c r="AA68" s="76"/>
-      <c r="AB68" s="77"/>
+      <c r="Z68" s="71"/>
+      <c r="AA68" s="72"/>
+      <c r="AB68" s="73"/>
       <c r="AC68" s="35"/>
-      <c r="AD68" s="75"/>
-      <c r="AE68" s="76"/>
-      <c r="AF68" s="77"/>
+      <c r="AD68" s="71"/>
+      <c r="AE68" s="72"/>
+      <c r="AF68" s="73"/>
       <c r="AG68" s="43"/>
-      <c r="AH68" s="75"/>
-      <c r="AI68" s="76"/>
-      <c r="AJ68" s="77"/>
+      <c r="AH68" s="71"/>
+      <c r="AI68" s="72"/>
+      <c r="AJ68" s="73"/>
       <c r="AK68" s="35"/>
-      <c r="AL68" s="127" t="s">
-        <v>78</v>
-      </c>
-      <c r="AM68" s="128"/>
-      <c r="AN68" s="153"/>
+      <c r="AL68" s="114" t="s">
+        <v>77</v>
+      </c>
+      <c r="AM68" s="115"/>
+      <c r="AN68" s="140"/>
       <c r="AO68" s="17"/>
       <c r="AP68" s="27" t="s">
         <v>32</v>
@@ -6052,51 +5719,47 @@
     </row>
     <row r="69" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="12"/>
-      <c r="B69" s="67" t="s">
-        <v>18</v>
-      </c>
-      <c r="C69" s="68"/>
-      <c r="D69" s="69"/>
+      <c r="B69" s="76"/>
+      <c r="C69" s="77"/>
+      <c r="D69" s="78"/>
       <c r="E69" s="37"/>
-      <c r="F69" s="89"/>
-      <c r="G69" s="90"/>
-      <c r="H69" s="91"/>
+      <c r="F69" s="76"/>
+      <c r="G69" s="77"/>
+      <c r="H69" s="78"/>
       <c r="I69" s="37"/>
-      <c r="J69" s="67"/>
-      <c r="K69" s="68"/>
-      <c r="L69" s="69"/>
+      <c r="J69" s="68"/>
+      <c r="K69" s="69"/>
+      <c r="L69" s="70"/>
       <c r="M69" s="4"/>
-      <c r="N69" s="67" t="s">
-        <v>22</v>
-      </c>
-      <c r="O69" s="68"/>
-      <c r="P69" s="69"/>
+      <c r="N69" s="68"/>
+      <c r="O69" s="69"/>
+      <c r="P69" s="70"/>
       <c r="Q69" s="43"/>
-      <c r="R69" s="67"/>
-      <c r="S69" s="68"/>
-      <c r="T69" s="69"/>
+      <c r="R69" s="68"/>
+      <c r="S69" s="69"/>
+      <c r="T69" s="70"/>
       <c r="U69" s="37"/>
-      <c r="V69" s="89"/>
-      <c r="W69" s="90"/>
-      <c r="X69" s="91"/>
+      <c r="V69" s="76"/>
+      <c r="W69" s="77"/>
+      <c r="X69" s="78"/>
       <c r="Y69" s="35"/>
-      <c r="Z69" s="89"/>
-      <c r="AA69" s="90"/>
-      <c r="AB69" s="91"/>
+      <c r="Z69" s="76"/>
+      <c r="AA69" s="77"/>
+      <c r="AB69" s="78"/>
       <c r="AC69" s="43"/>
-      <c r="AD69" s="67"/>
-      <c r="AE69" s="68"/>
-      <c r="AF69" s="69"/>
+      <c r="AD69" s="76"/>
+      <c r="AE69" s="77"/>
+      <c r="AF69" s="78"/>
       <c r="AG69" s="37"/>
-      <c r="AH69" s="89"/>
-      <c r="AI69" s="90"/>
-      <c r="AJ69" s="91"/>
+      <c r="AH69" s="76"/>
+      <c r="AI69" s="77"/>
+      <c r="AJ69" s="78"/>
       <c r="AK69" s="37"/>
-      <c r="AL69" s="67" t="s">
-        <v>80</v>
-      </c>
-      <c r="AM69" s="68"/>
-      <c r="AN69" s="69"/>
+      <c r="AL69" s="76" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM69" s="77"/>
+      <c r="AN69" s="78"/>
       <c r="AO69" s="12"/>
       <c r="AP69" s="27" t="s">
         <v>33</v>
@@ -6106,49 +5769,47 @@
     </row>
     <row r="70" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="12"/>
-      <c r="B70" s="67" t="s">
-        <v>26</v>
-      </c>
-      <c r="C70" s="68"/>
-      <c r="D70" s="69"/>
+      <c r="B70" s="68"/>
+      <c r="C70" s="69"/>
+      <c r="D70" s="70"/>
       <c r="E70" s="44"/>
-      <c r="F70" s="67"/>
-      <c r="G70" s="68"/>
-      <c r="H70" s="69"/>
+      <c r="F70" s="68"/>
+      <c r="G70" s="69"/>
+      <c r="H70" s="70"/>
       <c r="I70" s="44"/>
-      <c r="J70" s="67"/>
-      <c r="K70" s="68"/>
-      <c r="L70" s="69"/>
+      <c r="J70" s="68"/>
+      <c r="K70" s="69"/>
+      <c r="L70" s="70"/>
       <c r="M70" s="9"/>
-      <c r="N70" s="67"/>
-      <c r="O70" s="68"/>
-      <c r="P70" s="69"/>
+      <c r="N70" s="68"/>
+      <c r="O70" s="69"/>
+      <c r="P70" s="70"/>
       <c r="Q70" s="50"/>
-      <c r="R70" s="67"/>
-      <c r="S70" s="68"/>
-      <c r="T70" s="69"/>
+      <c r="R70" s="68"/>
+      <c r="S70" s="69"/>
+      <c r="T70" s="70"/>
       <c r="U70" s="44"/>
-      <c r="V70" s="67"/>
-      <c r="W70" s="68"/>
-      <c r="X70" s="69"/>
+      <c r="V70" s="68"/>
+      <c r="W70" s="69"/>
+      <c r="X70" s="70"/>
       <c r="Y70" s="40"/>
-      <c r="Z70" s="67"/>
-      <c r="AA70" s="68"/>
-      <c r="AB70" s="69"/>
+      <c r="Z70" s="68"/>
+      <c r="AA70" s="69"/>
+      <c r="AB70" s="70"/>
       <c r="AC70" s="44"/>
-      <c r="AD70" s="67"/>
-      <c r="AE70" s="68"/>
-      <c r="AF70" s="69"/>
+      <c r="AD70" s="68"/>
+      <c r="AE70" s="69"/>
+      <c r="AF70" s="70"/>
       <c r="AG70" s="44"/>
-      <c r="AH70" s="67"/>
-      <c r="AI70" s="68"/>
-      <c r="AJ70" s="69"/>
+      <c r="AH70" s="68"/>
+      <c r="AI70" s="69"/>
+      <c r="AJ70" s="70"/>
       <c r="AK70" s="44"/>
-      <c r="AL70" s="67" t="s">
-        <v>81</v>
-      </c>
-      <c r="AM70" s="68"/>
-      <c r="AN70" s="69"/>
+      <c r="AL70" s="68" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM70" s="69"/>
+      <c r="AN70" s="70"/>
       <c r="AO70" s="12"/>
       <c r="AP70" s="27" t="s">
         <v>34</v>
@@ -6158,47 +5819,45 @@
     </row>
     <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="12"/>
-      <c r="B71" s="83"/>
-      <c r="C71" s="84"/>
-      <c r="D71" s="85"/>
+      <c r="B71" s="62"/>
+      <c r="C71" s="63"/>
+      <c r="D71" s="64"/>
       <c r="E71" s="44"/>
-      <c r="F71" s="83"/>
-      <c r="G71" s="84"/>
-      <c r="H71" s="85"/>
+      <c r="F71" s="62"/>
+      <c r="G71" s="63"/>
+      <c r="H71" s="64"/>
       <c r="I71" s="44"/>
-      <c r="J71" s="83"/>
-      <c r="K71" s="84"/>
-      <c r="L71" s="85"/>
+      <c r="J71" s="62"/>
+      <c r="K71" s="63"/>
+      <c r="L71" s="64"/>
       <c r="M71" s="9"/>
-      <c r="N71" s="83"/>
-      <c r="O71" s="84"/>
-      <c r="P71" s="85"/>
+      <c r="N71" s="62"/>
+      <c r="O71" s="63"/>
+      <c r="P71" s="64"/>
       <c r="Q71" s="50"/>
-      <c r="R71" s="83"/>
-      <c r="S71" s="84"/>
-      <c r="T71" s="85"/>
+      <c r="R71" s="62"/>
+      <c r="S71" s="63"/>
+      <c r="T71" s="64"/>
       <c r="U71" s="44"/>
-      <c r="V71" s="83"/>
-      <c r="W71" s="84"/>
-      <c r="X71" s="85"/>
+      <c r="V71" s="62"/>
+      <c r="W71" s="63"/>
+      <c r="X71" s="64"/>
       <c r="Y71" s="44"/>
-      <c r="Z71" s="83"/>
-      <c r="AA71" s="84"/>
-      <c r="AB71" s="85"/>
+      <c r="Z71" s="62"/>
+      <c r="AA71" s="63"/>
+      <c r="AB71" s="64"/>
       <c r="AC71" s="50"/>
-      <c r="AD71" s="83"/>
-      <c r="AE71" s="84"/>
-      <c r="AF71" s="85"/>
+      <c r="AD71" s="62"/>
+      <c r="AE71" s="63"/>
+      <c r="AF71" s="64"/>
       <c r="AG71" s="44"/>
-      <c r="AH71" s="83"/>
-      <c r="AI71" s="84"/>
-      <c r="AJ71" s="85"/>
+      <c r="AH71" s="62"/>
+      <c r="AI71" s="63"/>
+      <c r="AJ71" s="64"/>
       <c r="AK71" s="44"/>
-      <c r="AL71" s="83" t="s">
-        <v>82</v>
-      </c>
-      <c r="AM71" s="84"/>
-      <c r="AN71" s="85"/>
+      <c r="AL71" s="62"/>
+      <c r="AM71" s="63"/>
+      <c r="AN71" s="64"/>
       <c r="AO71" s="12"/>
       <c r="AP71" s="27" t="s">
         <v>35</v>
@@ -6266,23 +5925,23 @@
       <c r="K73" s="33"/>
       <c r="L73" s="33"/>
       <c r="M73" s="14"/>
-      <c r="N73" s="115" t="s">
+      <c r="N73" s="102" t="s">
         <v>31</v>
       </c>
-      <c r="O73" s="115"/>
-      <c r="P73" s="115"/>
-      <c r="Q73" s="115"/>
-      <c r="R73" s="115"/>
-      <c r="S73" s="115"/>
-      <c r="T73" s="115"/>
-      <c r="U73" s="115"/>
-      <c r="V73" s="115"/>
-      <c r="W73" s="115"/>
-      <c r="X73" s="115"/>
-      <c r="Y73